--- a/dashboard/trading_system.xlsx
+++ b/dashboard/trading_system.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\husainnatha\tradingsystem\dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2ABC460-6772-40D7-B3D0-C640BA031C59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06458041-5BDE-4D4B-819F-94D1EEE7AD6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="3" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="INPUT_TRANSACTIONS" sheetId="1" r:id="rId1"/>
@@ -23,9 +23,6 @@
     <sheet name="metrics" sheetId="7" r:id="rId8"/>
     <sheet name="decision_engineering" sheetId="9" r:id="rId9"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId10"/>
-  </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -58,7 +55,7 @@
       </extLst>
     </bk>
   </futureMetadata>
-  <futureMetadata name="XLRICHVALUE" count="97">
+  <futureMetadata name="XLRICHVALUE" count="87">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -668,83 +665,13 @@
         </ext>
       </extLst>
     </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="262"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="264"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="266"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="268"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="270"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="272"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="274"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="276"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="278"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="280"/>
-        </ext>
-      </extLst>
-    </bk>
   </futureMetadata>
   <cellMetadata count="1">
     <bk>
       <rc t="1" v="0"/>
     </bk>
   </cellMetadata>
-  <valueMetadata count="97">
+  <valueMetadata count="87">
     <bk>
       <rc t="2" v="0"/>
     </bk>
@@ -1006,42 +933,12 @@
     <bk>
       <rc t="2" v="86"/>
     </bk>
-    <bk>
-      <rc t="2" v="87"/>
-    </bk>
-    <bk>
-      <rc t="2" v="88"/>
-    </bk>
-    <bk>
-      <rc t="2" v="89"/>
-    </bk>
-    <bk>
-      <rc t="2" v="90"/>
-    </bk>
-    <bk>
-      <rc t="2" v="91"/>
-    </bk>
-    <bk>
-      <rc t="2" v="92"/>
-    </bk>
-    <bk>
-      <rc t="2" v="93"/>
-    </bk>
-    <bk>
-      <rc t="2" v="94"/>
-    </bk>
-    <bk>
-      <rc t="2" v="95"/>
-    </bk>
-    <bk>
-      <rc t="2" v="96"/>
-    </bk>
   </valueMetadata>
 </metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1772" uniqueCount="447">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1764" uniqueCount="446">
   <si>
     <t>collected_timestamp</t>
   </si>
@@ -2269,9 +2166,6 @@
   </si>
   <si>
     <t>USD/GBP</t>
-  </si>
-  <si>
-    <t>SELL</t>
   </si>
   <si>
     <t>I think the BEST next step is:</t>
@@ -3122,60 +3016,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Trades"/>
-      <sheetName val="Watchlist"/>
-      <sheetName val="Variables"/>
-      <sheetName val="Run_Summary_v2"/>
-      <sheetName val="Tax_Lots"/>
-      <sheetName val="Tax_Lots_v2"/>
-      <sheetName val="Holdings"/>
-      <sheetName val="Sales"/>
-      <sheetName val="Tax_Lots_Validation_Report"/>
-      <sheetName val="Unmatched_Disposals"/>
-      <sheetName val="Market_Data_History"/>
-      <sheetName val="Config"/>
-      <sheetName val="ThirtyDay_Matches"/>
-      <sheetName val="SameDay_Matches"/>
-      <sheetName val="Section104_Pool"/>
-      <sheetName val="Tax_Dashboard"/>
-      <sheetName val="stock-trading-system_STAGE5_TAX"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2">
-        <row r="1">
-          <cell r="G1" t="e">
-            <v>#VALUE!</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-      <sheetData sheetId="7"/>
-      <sheetData sheetId="8"/>
-      <sheetData sheetId="9"/>
-      <sheetData sheetId="10"/>
-      <sheetData sheetId="11"/>
-      <sheetData sheetId="12"/>
-      <sheetData sheetId="13"/>
-      <sheetData sheetId="14"/>
-      <sheetData sheetId="15"/>
-      <sheetData sheetId="16" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
 <file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
 <rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
   <global>
@@ -3287,7 +3127,7 @@
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="281">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="261">
   <rv s="0">
     <v>https://www.bing.com/financeapi/forcetrigger?t=a1y4oc&amp;q=XNAS%3aMU&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
@@ -3304,11 +3144,11 @@
     <v>3</v>
     <v>Finance</v>
     <v>4</v>
-    <v>880.89</v>
+    <v>891.27</v>
     <v>92.22</v>
     <v>1.9930000000000001</v>
-    <v>128.83000000000001</v>
-    <v>0.17154499999999998</v>
+    <v>130.06</v>
+    <v>0.173182</v>
     <v>USD</v>
     <v>Micron Technology, Inc. provides memory and storage solutions. The Company delivers a portfolio of high-performance dynamic random-access memory (DRAM), NAND, and NOR memory and storage products through its Micron and Crucial brands. The Company's products enable advancing in artificial intelligence (AI) and compute-intensive applications. Its segments include Cloud Memory Business Unit (CMBU), Core Data Center Business Unit (CDBU), Mobile and Client Business Unit (MCBU) and Automotive and Embedded Business Unit (AEBU). CMBU is focused on memory solutions for large hyperscale cloud customers, and high bandwidth memory (HBM) for all data center customers. CDBU is focused on memory solutions for mid-tier cloud, enterprise, and OEM data center customers and storage solutions for all data center customers. MCBU is focused on memory and storage solutions for mobile and client segments. AEBU is focused on memory and storage solutions for the automotive, industrial, and consumer segments.</v>
     <v>53000</v>
@@ -3316,23 +3156,23 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>8000 S Federal Way, Po Box 6, BOISE, ID, 83716-9632 US</v>
-    <v>880.89</v>
+    <v>891.27</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46168.605484501561</v>
+    <v>46168.683481226566</v>
     <v>0</v>
     <v>820.29499999999996</v>
-    <v>992214205220</v>
+    <v>993601318039</v>
     <v>MICRON TECHNOLOGY, INC.</v>
     <v>MICRON TECHNOLOGY, INC.</v>
     <v>820.46</v>
-    <v>41.5381</v>
+    <v>41.5961</v>
     <v>751</v>
-    <v>879.83</v>
+    <v>881.06</v>
     <v>1127734000</v>
     <v>MU</v>
     <v>MICRON TECHNOLOGY, INC. (XNAS:MU)</v>
-    <v>25104573</v>
+    <v>41316331</v>
     <v>47860495</v>
     <v>1984</v>
   </rv>
@@ -3358,8 +3198,8 @@
     <v>16.489999999999998</v>
     <v>4.6150000000000002</v>
     <v>2.2159</v>
-    <v>0.82</v>
-    <v>0.12275399999999999</v>
+    <v>0.61109999999999998</v>
+    <v>9.1481999999999994E-2</v>
     <v>USD</v>
     <v>Enovix Corporation is a high-performance battery company. The Company is focused on designing, developing, manufacturing, and commercializing Lithium-ion, or Li-ion, batteries, including silicon-anode architectures, for smartphones, smart eyewear, defense, industrial and emerging edge artificial intelligence (AI) applications. Its silicon-anode battery architecture enables energy density and performance relative to conventional battery cells, particularly in space-constrained devices. It focuses on developing a battery architecture that allows the use of active silicon and no graphite in the battery's anode, which is the negative electrode that stores lithium ions when a battery is charged. Its AI-1 battery platform is architected as a unified silicon-anode platform designed to address the high-performance consumer electronics and defense applications. The AI-1 platform is designed to support AI-enabled smartphones and smart eyewear, as well as other edge-AI devices.</v>
     <v>664</v>
@@ -3370,20 +3210,20 @@
     <v>7.6349999999999998</v>
     <v>Machinery, Equipment &amp; Components</v>
     <v>Stock</v>
-    <v>46168.605474270313</v>
+    <v>46168.683445925781</v>
     <v>3</v>
     <v>6.81</v>
-    <v>1636150500</v>
+    <v>1590578254</v>
     <v>Enovix Corporation</v>
     <v>Enovix Corporation</v>
     <v>6.85</v>
     <v>0</v>
     <v>6.68</v>
-    <v>7.5</v>
+    <v>7.2911000000000001</v>
     <v>218153400</v>
     <v>ENVX</v>
     <v>Enovix Corporation (XNAS:ENVX)</v>
-    <v>3521047</v>
+    <v>5738079</v>
     <v>6968993</v>
     <v>2020</v>
   </rv>
@@ -3406,11 +3246,11 @@
     <v>3</v>
     <v>Finance</v>
     <v>4</v>
-    <v>108.751</v>
+    <v>109.93</v>
     <v>9.14</v>
     <v>3.2322000000000002</v>
-    <v>10.769</v>
-    <v>0.11333399999999999</v>
+    <v>14.44</v>
+    <v>0.15196799999999999</v>
     <v>USD</v>
     <v>Aehr Test Systems, Inc. offers test solutions for testing, burning-in, and stabilizing semiconductor devices in wafer level, singulated die, and package part form. The Company's products include the FOX-P family of test and burn-in systems and FOX WaferPak Aligner, FOX WaferPak Contactor, FOX DiePak Carrier and FOX DiePak Loader. The FOX-XP and FOX-NP systems are full wafer contact and singulated die/module test and burn-in systems that can test, burn-in and stabilize a range of devices such as silicon carbide-based and other power semiconductors, 2D and 3D sensors used in phones, tablets, and other computing devices, memory semiconductors, processors, microcontrollers, systems-on-a-chip, and photonics and integrated optical devices used in AI. FOX-CP system is a single-wafer compact test solution for logic, memory and photonic devices. FOX WaferPak Contactor contains a full wafer contactor capable of testing wafers up to 300 millimeters that enables integrated circuit manufacturers.</v>
     <v>136</v>
@@ -3418,23 +3258,23 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>400 Kato Ter, FREMONT, CA, 94539 US</v>
-    <v>106.53</v>
+    <v>109.93</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46168.605510392968</v>
+    <v>46168.683466596878</v>
     <v>6</v>
     <v>97.3</v>
-    <v>3327407864</v>
+    <v>3442872745</v>
     <v>AEHR TEST SYSTEMS</v>
     <v>AEHR TEST SYSTEMS</v>
     <v>99</v>
     <v>0</v>
     <v>95.02</v>
-    <v>105.789</v>
+    <v>109.46</v>
     <v>31453250</v>
     <v>AEHR</v>
     <v>AEHR TEST SYSTEMS (XNAS:AEHR)</v>
-    <v>848516</v>
+    <v>1548835</v>
     <v>2976553</v>
     <v>1977</v>
   </rv>
@@ -3457,11 +3297,11 @@
     <v>3</v>
     <v>Finance</v>
     <v>4</v>
-    <v>128.57990000000001</v>
+    <v>129.13</v>
     <v>41.49</v>
     <v>1.9541999999999999</v>
-    <v>11.57</v>
-    <v>9.9570000000000006E-2</v>
+    <v>10.08</v>
+    <v>8.6746999999999991E-2</v>
     <v>USD</v>
     <v>ON Semiconductor Corporation is engaged in providing intelligent power and intelligent sensing solutions. The Company’s intelligent power technologies enable the electrification of drivetrain in the automotive industry to allow for lighter and longer-range electric vehicles. Its segments include Power Solutions Group (PSG), the Analog and Mixed-Signal Group (AMG) and the Intelligent Sensing Group (ISG). PSG segment provides a portfolio of discrete, module, and integrated semiconductor devices designed to enable conversion across artificial intelligence (AI) data centers, energy infrastructure, automotive and industrial. AMG segment designs and develops a range of analog and mixed-signal solutions including power‑management, sensor‑interface, connectivity, and products that serve automotive, industrial automation, AI data center, computing, and mobile end markets.</v>
     <v>22600</v>
@@ -3469,23 +3309,23 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>5701 NORTH PIMA ROAD, SCOTTSDALE, AZ, 85250 US</v>
-    <v>128.57990000000001</v>
+    <v>129.13</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46168.60548443281</v>
+    <v>46168.683484212503</v>
     <v>9</v>
     <v>121.06</v>
-    <v>50073471864</v>
+    <v>49489536096</v>
     <v>ON SEMICONDUCTOR CORPORATION</v>
     <v>ON SEMICONDUCTOR CORPORATION</v>
     <v>122.8</v>
-    <v>91.238200000000006</v>
+    <v>90.174199999999999</v>
     <v>116.2</v>
-    <v>127.77</v>
+    <v>126.28</v>
     <v>391903200</v>
     <v>ON</v>
     <v>ON SEMICONDUCTOR CORPORATION (XNAS:ON)</v>
-    <v>4736584</v>
+    <v>7980312</v>
     <v>12940193</v>
     <v>2000</v>
   </rv>
@@ -3511,8 +3351,8 @@
     <v>745.61</v>
     <v>320</v>
     <v>2.3662999999999998</v>
-    <v>42.81</v>
-    <v>8.8876000000000011E-2</v>
+    <v>29.370100000000001</v>
+    <v>6.0974E-2</v>
     <v>USD</v>
     <v>AppLovin Corporation is a marketing platform. The Company provides end-to-end software and artificial intelligence (AI) solutions for businesses to reach, monetize and grow their global audiences. Its advertising solutions include a comprehensive suite of tools including AppDiscovery, MAX, Adjust, Wurl and Axon Ads Manager. AppDiscovery is powered by AXON, its AI-powered advertising engine, and matches advertiser demand with publisher supply through auctions at vast scale and at microsecond-level speeds. MAX is its monetization solution, utilizing an advanced in-app bidding technology that optimizes the value of a publisher’s advertising inventory by running a real-time competitive auction, driving more competition, and higher returns for publishers. Adjust is its measurement and analytics marketing platform which provides marketers with the visibility, insights, and data needed to scale their apps marketing and drive more informed results. Wurl is its connected TV (CTV) platform.</v>
     <v>898</v>
@@ -3520,23 +3360,23 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>1100 Page Mill Rd, PALO ALTO, CA, 94304-1047 US</v>
-    <v>535.35</v>
+    <v>538.81989999999996</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46168.605527025</v>
+    <v>46168.683447071096</v>
     <v>12</v>
-    <v>516.07000000000005</v>
-    <v>176197170600</v>
+    <v>510.34</v>
+    <v>171682170594</v>
     <v>APPLOVIN CORPORATION</v>
     <v>APPLOVIN CORPORATION</v>
     <v>518.20000000000005</v>
-    <v>45.578099999999999</v>
+    <v>44.410200000000003</v>
     <v>481.68</v>
-    <v>524.49</v>
+    <v>511.05009999999999</v>
     <v>335940000</v>
     <v>APP</v>
     <v>APPLOVIN CORPORATION (XNAS:APP)</v>
-    <v>1939411</v>
+    <v>3539656</v>
     <v>4466495</v>
     <v>2011</v>
   </rv>
@@ -3562,8 +3402,8 @@
     <v>57.42</v>
     <v>8.85</v>
     <v>2.2115</v>
-    <v>1.02</v>
-    <v>8.9473999999999998E-2</v>
+    <v>0.8952</v>
+    <v>7.8525999999999999E-2</v>
     <v>USD</v>
     <v>NuScale Power Corporation is a provider of proprietary advanced small modular reactor (SMR) nuclear technology. The NuScale Power Module, the Company's SMR technology, is a small pressurized water reactor that can generate approximately 77 megawatts of electricity (MWe) or 250 megawatts thermal (gross) and can be scaled to meet customer needs through an array of flexible configurations of up to 924 MWe (12 modules) of output. In addition to the sale of NPMs, it offers a diversified suite of services throughout the development and operating life of the power plant. The Company's suite of services is planned to include licensing support, testing, training, fuel supply services and program management, among others. It serves a range of customers consisting of domestic and international governments, utilities, state-owned enterprises and technology and industrial companies in need of carbon-free, reliable energy.</v>
     <v>428</v>
@@ -3574,20 +3414,20 @@
     <v>12.69</v>
     <v>Electrical Utilities &amp; IPPs</v>
     <v>Stock</v>
-    <v>46168.605513425784</v>
+    <v>46168.683461562498</v>
     <v>15</v>
     <v>11.99</v>
-    <v>4539276504</v>
+    <v>4493664450</v>
     <v>NUSCALE POWER CORPORATION</v>
     <v>NUSCALE POWER CORPORATION</v>
     <v>12.01</v>
     <v>0</v>
     <v>11.4</v>
-    <v>12.42</v>
+    <v>12.295199999999999</v>
     <v>365481200</v>
     <v>SMR</v>
     <v>NUSCALE POWER CORPORATION (XNYS:SMR)</v>
-    <v>22102257</v>
+    <v>30220468</v>
     <v>34084732</v>
     <v>2022</v>
   </rv>
@@ -3606,11 +3446,11 @@
     <v>3</v>
     <v>Finance</v>
     <v>4</v>
-    <v>1607.77</v>
+    <v>1632.9299000000001</v>
     <v>36.207000000000001</v>
     <v>2.734</v>
-    <v>127.675</v>
-    <v>8.6343000000000003E-2</v>
+    <v>115.2</v>
+    <v>7.7907000000000004E-2</v>
     <v>USD</v>
     <v>SanDisk Corporation is a developer, manufacturer and provider of data storage devices and solutions based on NAND flash technology and has consumer brands and franchises globally. The Company's solutions include a range of solid state drives (SSDs) embedded products, removable cards, universal serial bus (USB) drives, and wafers and components. Its broad portfolio of technology and products addresses multiple end markets of Datacenter, Edge and Consumer. Its Datacenter end market is composed primarily of products for public or private cloud environments and enterprise customers. The Company, through the Edge end market, provides original equipment manufacturer and channel customers a broad array of high-performance flash solutions across personal computer, mobile, gaming, automotive, virtual reality headsets, at-home entertainment, and industrial spaces. The Company serves the Consumer end market with a broad range of retail and other end-user products.</v>
     <v>11000</v>
@@ -3618,22 +3458,22 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>951 Sandisk Drive, MILPITAS, CA, 95035 US</v>
-    <v>1607.77</v>
+    <v>1632.9299000000001</v>
     <v>Computers, Phones &amp; Household Electronics</v>
     <v>Stock</v>
-    <v>46168.605518888282</v>
+    <v>46168.683472661716</v>
     <v>1520</v>
-    <v>237886271577</v>
+    <v>236038851322</v>
     <v>SANDISK CORPORATION</v>
     <v>SANDISK CORPORATION</v>
     <v>1535</v>
-    <v>56.790900000000001</v>
+    <v>56.349899999999998</v>
     <v>1478.69</v>
-    <v>1606.365</v>
+    <v>1593.89</v>
     <v>148089800</v>
     <v>SNDK</v>
     <v>SANDISK CORPORATION (XNAS:SNDK)</v>
-    <v>4360090</v>
+    <v>7287189</v>
     <v>14574189</v>
     <v>2024</v>
   </rv>
@@ -3659,8 +3499,8 @@
     <v>422.11</v>
     <v>77.02</v>
     <v>1.7878000000000001</v>
-    <v>28.992000000000001</v>
-    <v>8.0883999999999998E-2</v>
+    <v>24.565000000000001</v>
+    <v>6.8532999999999997E-2</v>
     <v>USD</v>
     <v>Teradyne, Inc. is a global supplier of automated test equipment and robotics solutions. It designs, develops, manufactures and sells automated test systems and robotics products. Its segment includes Semiconductor Test, Robotics, and Product Test. The Semiconductor Test segment includes operations related to the design, manufacturing and marketing of semiconductor test products and services, inclusive of storage and system level test products. The Robotics segment includes operations related to the design, manufacturing and marketing of collaborative robotic arms and autonomous mobile robots. The Product Test segment includes operations related to the design, manufacturing and marketing of products and services for defense/aerospace test, circuit-board test, wireless test systems, and silicon photonics testing. Its offerings also include defense/aerospace test instrumentation and systems, circuit-board test and inspection (production board test) systems, and wireless test systems.</v>
     <v>6600</v>
@@ -3668,23 +3508,23 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>600 Riverpark Dr, NORTH READING, MA, 01864-2634 US</v>
-    <v>388.22989999999999</v>
+    <v>389.54500000000002</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46168.605487950779</v>
+    <v>46168.683477673439</v>
     <v>20</v>
     <v>367.62</v>
-    <v>60649457630</v>
+    <v>59956445311</v>
     <v>TERADYNE, INC.</v>
     <v>TERADYNE, INC.</v>
     <v>373.44</v>
-    <v>71.705500000000001</v>
+    <v>70.886200000000002</v>
     <v>358.44</v>
-    <v>387.43200000000002</v>
+    <v>383.005</v>
     <v>156542200</v>
     <v>TER</v>
     <v>TERADYNE, INC. (XNAS:TER)</v>
-    <v>1113068</v>
+    <v>1736898</v>
     <v>4045460</v>
     <v>1960</v>
   </rv>
@@ -3710,8 +3550,8 @@
     <v>96.69</v>
     <v>48.3</v>
     <v>2.2088999999999999</v>
-    <v>6.81</v>
-    <v>7.7784000000000006E-2</v>
+    <v>6.73</v>
+    <v>7.6870000000000008E-2</v>
     <v>USD</v>
     <v>Ambarella, Inc. is a developer of low-power system-on-a-chip (SoC) semiconductors and software for edge artificial intelligence (AI) applications. The Company's technologies make electronic systems smarter, enabling them to become partially or fully autonomous with features, such as person detection, object classification, and analytics, in addition to performing complex data analysis in real time, delivering imagery, and preserving vital system resources, such as power and network bandwidth. It specializes in the development of deployable, scalable designs for intelligent electronic systems that utilize high-bandwidth sensors. Its products are used in a variety of human viewing, computer vision and edge AI applications, including a variety of automotive camera systems, video security cameras, mobile and fixed robots, industrial applications, and consumer devices, such as action, drone, and 360-degree cameras.</v>
     <v>959</v>
@@ -3719,23 +3559,23 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>3101 Jay Street, CA, 95054 US</v>
-    <v>94.65</v>
+    <v>96.358000000000004</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46168.605498714845</v>
+    <v>46168.683407325778</v>
     <v>23</v>
     <v>89.45</v>
-    <v>4138769252</v>
+    <v>4135260334</v>
     <v>AMBARELLA, INC.</v>
     <v>AMBARELLA, INC.</v>
     <v>92.04</v>
     <v>0</v>
     <v>87.55</v>
-    <v>94.36</v>
+    <v>94.28</v>
     <v>43861480</v>
     <v>AMBA</v>
     <v>AMBARELLA, INC. (XNAS:AMBA)</v>
-    <v>587859</v>
+    <v>1090120</v>
     <v>860616</v>
     <v>2004</v>
   </rv>
@@ -3761,8 +3601,8 @@
     <v>217.45</v>
     <v>58.61</v>
     <v>2.2723</v>
-    <v>11.68</v>
-    <v>5.9492000000000003E-2</v>
+    <v>8.1233000000000004</v>
+    <v>4.1375999999999996E-2</v>
     <v>USD</v>
     <v>Marvell Technology, Inc. together with its consolidated subsidiaries, is a supplier of data infrastructure semiconductor solutions, spanning the data center core to network edge. It is engaged in the design, development and sale of integrated circuits. Its product offerings include custom application-specific integrated circuits (ASICs), interconnects, ethernet solutions, fiber channel adapters, processors and storage controllers. In addition, it is also developing Ultra Accelerator LinkTM (UALinkTM) switches and ethernet for scale-up networking (ESUN) switches for the emerging scale-out artificial intelligence market. Its solutions integrate multiple analogs, mixed-signal and digital intellectual property components incorporating hardware, firmware and software technologies and its system knowledge to provide its customers with integrated solutions for their end products. It designs and manufactures photonic integrated circuits for ultra-high-bandwidth and low-power applications.</v>
     <v>7480</v>
@@ -3773,20 +3613,20 @@
     <v>217.45</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46168.605515751566</v>
+    <v>46168.683469803123</v>
     <v>26</v>
-    <v>206.9</v>
-    <v>182123821132</v>
+    <v>200.04</v>
+    <v>179009741065</v>
     <v>MARVELL TECHNOLOGY, INC.</v>
     <v>MARVELL TECHNOLOGY, INC.</v>
     <v>212.27</v>
-    <v>67.753500000000003</v>
+    <v>66.594999999999999</v>
     <v>196.33</v>
-    <v>208.01</v>
+    <v>204.45330000000001</v>
     <v>875553200</v>
     <v>MRVL</v>
     <v>MARVELL TECHNOLOGY, INC. (XNAS:MRVL)</v>
-    <v>14634162</v>
+    <v>24549917</v>
     <v>25867876</v>
     <v>2020</v>
   </rv>
@@ -3809,28 +3649,28 @@
     <v>9</v>
     <v>Finance</v>
     <v>10</v>
-    <v>568.85</v>
+    <v>571.41999999999996</v>
     <v>201.11500000000001</v>
     <v>1.6780999999999999</v>
-    <v>31.495000000000001</v>
-    <v>5.8613999999999999E-2</v>
+    <v>26.94</v>
+    <v>5.0137000000000001E-2</v>
     <v>USD</v>
     <v>Nasdaq Stock Market</v>
     <v>XNAS</v>
     <v>3.4000000000000002E-3</v>
-    <v>568.85</v>
+    <v>571.41999999999996</v>
     <v>ETF</v>
-    <v>46168.605504617968</v>
+    <v>46168.68349688594</v>
     <v>29</v>
     <v>555.41</v>
     <v>29566458901.66</v>
     <v>iShares:Semiconductor</v>
     <v>557.4</v>
     <v>537.33000000000004</v>
-    <v>568.82500000000005</v>
+    <v>564.27</v>
     <v>SOXX</v>
     <v>iShares:Semiconductor (XNAS:SOXX)</v>
-    <v>2572614</v>
+    <v>5124248</v>
     <v>7956742</v>
   </rv>
   <rv s="2">
@@ -3877,11 +3717,11 @@
     <v>3</v>
     <v>Finance</v>
     <v>4</v>
-    <v>495.41989999999998</v>
+    <v>496.88990000000001</v>
     <v>108.61539999999999</v>
     <v>2.4419</v>
-    <v>26.565000000000001</v>
-    <v>5.6821999999999998E-2</v>
+    <v>27.149899999999999</v>
+    <v>5.8073E-2</v>
     <v>USD</v>
     <v>Advanced Micro Devices, Inc. is a global semiconductor company. The Company is focused on high-performance computing and artificial intelligence (AI). Its segments include Data Center, Client and Gaming, and Embedded. Data Center segment includes AI accelerators, microprocessors (CPUs) for servers, graphics processing units (GPUs), accelerated processing units (APUs), data processing units (DPUs), Field Programmable Gate Arrays (FPGAs), and Adaptive system-on-Chip (SoC) products for data centers. Client and Gaming segment includes CPUs, APUs, chipsets for desktops and notebooks, discrete GPUs, and semi-custom SoC products and development services. Embedded segment includes embedded CPUs, APUs, FPGAs, system on modules (SOMs), and Adaptive SoC products. It markets and sells its products under the AMD trademark. Its products include AMD EPYC, AMD Ryzen, AMD Ryzen PRO, Virtex UltraScale+, among others.</v>
     <v>31000</v>
@@ -3889,23 +3729,23 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>2485 Augustine Drive, SANTA CLARA, CA, 95054 US</v>
-    <v>495.41989999999998</v>
+    <v>496.88990000000001</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46168.605546075778</v>
+    <v>46168.683499883591</v>
     <v>37</v>
     <v>480.23</v>
-    <v>805639189075</v>
+    <v>806592927599</v>
     <v>ADVANCED MICRO DEVICES, INC.</v>
     <v>ADVANCED MICRO DEVICES, INC.</v>
     <v>485</v>
-    <v>164.69720000000001</v>
+    <v>164.8921</v>
     <v>467.51</v>
-    <v>494.07499999999999</v>
+    <v>494.65989999999999</v>
     <v>1630601000</v>
     <v>AMD</v>
     <v>ADVANCED MICRO DEVICES, INC. (XNAS:AMD)</v>
-    <v>11444409</v>
+    <v>18569704</v>
     <v>43919238</v>
     <v>1969</v>
   </rv>
@@ -3931,8 +3771,8 @@
     <v>56</v>
     <v>16.59</v>
     <v>1.5019</v>
-    <v>2.92</v>
-    <v>5.6742999999999995E-2</v>
+    <v>2.87</v>
+    <v>5.5770999999999994E-2</v>
     <v>USD</v>
     <v>Photronics, Inc. is a manufacturer of photomasks, which are high-precision photographic quartz or glass plates containing microscopic images of electronic circuits. The Company manufactures photomasks, which are used as masters to transfer circuit patterns onto semiconductor wafers and FPD substrates. The photomasks the Company manufactures incorporate circuit designs provided on a confidential basis by its customers. The Company sells its photomasks to semiconductor designers and manufacturers, and manufacturers of FPDs. Photomask technology is also being applied to the fabrication of other higher-performance electronic products such as virtual reality/augmented reality advanced IC packages, photonics, micro-electronic mechanical systems, and certain nanotechnology applications. The Company operates approximately 11 manufacturing facilities, which are located in Taiwan, China, Korea, the United States, and Europe.</v>
     <v>1908</v>
@@ -3943,20 +3783,20 @@
     <v>54.76</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46168.605513263283</v>
+    <v>46168.683372777341</v>
     <v>40</v>
     <v>51.814999999999998</v>
-    <v>3206592288</v>
+    <v>3203643968</v>
     <v>PHOTRONICS, INC.</v>
     <v>PHOTRONICS, INC.</v>
     <v>53.67</v>
-    <v>23.231400000000001</v>
+    <v>23.21</v>
     <v>51.46</v>
-    <v>54.38</v>
+    <v>54.33</v>
     <v>58966390</v>
     <v>PLAB</v>
     <v>PHOTRONICS, INC. (XNAS:PLAB)</v>
-    <v>247938</v>
+    <v>461938</v>
     <v>796190</v>
     <v>1969</v>
   </rv>
@@ -3979,11 +3819,11 @@
     <v>3</v>
     <v>Finance</v>
     <v>4</v>
-    <v>1987.3</v>
+    <v>1998.32</v>
     <v>740.44</v>
     <v>1.5014000000000001</v>
-    <v>98.42</v>
-    <v>5.2118999999999999E-2</v>
+    <v>92.844999999999999</v>
+    <v>4.9166000000000001E-2</v>
     <v>USD</v>
     <v>KLA Corporation (KLA) develops industry equipment and services. The Company provides advanced process control and process-enabling solutions for manufacturing wafers and reticles, integrated circuits, packaging, and printed circuit boards. It operates through three segments, which include Semiconductor Process Control, Specialty Semiconductor Process, and PCB and Component Inspection. The Semiconductor Process Control segment offers a portfolio of inspection, metrology and data analytics products, and related services. The Specialty Semiconductor Process segment develops and sells advanced vacuum deposition and etching process tools. The PCB and Component Inspection segment enables electronic device manufacturers to inspect, test and measure PCBs, flat panel displays, and integrated circuits (ICs) to verify their quality, pattern the desired electronic circuitry on the relevant substrate and perform three-dimensional shaping of metalized circuits on multiple surfaces.</v>
     <v>15000</v>
@@ -3991,23 +3831,23 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>One Technology Drive, MILPITAS, CA, 95035 US</v>
-    <v>1987.3</v>
+    <v>1998.32</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46168.6054773375</v>
+    <v>46168.683473182813</v>
     <v>43</v>
     <v>1914.325</v>
-    <v>259530717000</v>
+    <v>258802468687</v>
     <v>KLA CORPORATION</v>
     <v>KLA CORPORATION</v>
     <v>1944.05</v>
-    <v>56.251100000000001</v>
+    <v>56.093299999999999</v>
     <v>1888.38</v>
-    <v>1986.8</v>
+    <v>1981.2249999999999</v>
     <v>130627500</v>
     <v>KLAC</v>
     <v>KLA CORPORATION (XNAS:KLAC)</v>
-    <v>182213</v>
+    <v>374029</v>
     <v>1025049</v>
     <v>1975</v>
   </rv>
@@ -4033,8 +3873,8 @@
     <v>412.7</v>
     <v>243.3</v>
     <v>1.1224000000000001</v>
-    <v>15.59</v>
-    <v>5.3015E-2</v>
+    <v>11.535</v>
+    <v>3.9224999999999996E-2</v>
     <v>USD</v>
     <v>Constellation Energy Corporation is a producer of emissions-free energy and an energy supplier to businesses, homes and public sector customers nationwide. The Company’s nuclear, hydro, wind, and solar generation facilities have the generating capacity to power the equivalent of 27 million homes, providing about 10% of the nation’s clean energy. Its segments include Mid-Atlantic, Midwest, New York, ERCOT, and Other Power Regions. Through its integrated business operations, it sells electricity, natural gas, and other energy-related products and sustainable solutions to various types of customers, including distribution utilities, municipalities, cooperatives, commercial, industrial, public sector, and residential customers in markets across multiple geographic regions. It operates approximately 55 gigawatts of capacity from nuclear, natural gas, geothermal, hydro, wind and solar facilities.</v>
     <v>15291</v>
@@ -4045,20 +3885,20 @@
     <v>310.45</v>
     <v>Electrical Utilities &amp; IPPs</v>
     <v>Stock</v>
-    <v>46168.60555663125</v>
+    <v>46168.683493425779</v>
     <v>46</v>
     <v>299.08010000000002</v>
-    <v>111846126366</v>
+    <v>110381500510</v>
     <v>CONSTELLATION ENERGY CORPORATION.</v>
     <v>CONSTELLATION ENERGY CORPORATION.</v>
     <v>299.99</v>
-    <v>26.902200000000001</v>
+    <v>26.549900000000001</v>
     <v>294.07</v>
-    <v>309.66000000000003</v>
+    <v>305.60500000000002</v>
     <v>361190100</v>
     <v>CEG</v>
     <v>CONSTELLATION ENERGY CORPORATION. (XNAS:CEG)</v>
-    <v>1020551</v>
+    <v>1851937</v>
     <v>3273799</v>
     <v>2021</v>
   </rv>
@@ -4084,8 +3924,8 @@
     <v>442.36</v>
     <v>231.13079999999999</v>
     <v>1.4200999999999999</v>
-    <v>20.190000000000001</v>
-    <v>4.8752000000000004E-2</v>
+    <v>8.06</v>
+    <v>1.9462E-2</v>
     <v>USD</v>
     <v>Broadcom Inc. is a global technology firm that designs, develops, and supplies a range of semiconductors, enterprise software and security solutions. The Company operates through two segments: semiconductor solutions and infrastructure software. Its semiconductor solutions segment includes all of its product lines and intellectual property (IP) licensing. It provides a variety of radio frequency semiconductor devices, wireless connectivity solutions, custom touch controllers, and inductive charging solutions for mobile applications. Its infrastructure software segment includes its private and hybrid cloud, application development and delivery, software-defined edge, application networking and security, mainframe, distributed and cybersecurity solutions, and its FC SAN business. It provides a portfolio of software solutions that enable customers to plan, develop, automate, manage and secure applications across mainframe, distributed, mobile and cloud platforms.</v>
     <v>33000</v>
@@ -4093,23 +3933,23 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>3421 Hillview Avenue, PALO ALTO, CA, 94304 US</v>
-    <v>434.87</v>
+    <v>435.31</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46168.60553048594</v>
+    <v>46168.683489767966</v>
     <v>49</v>
     <v>417</v>
-    <v>2056408352440</v>
+    <v>1998976829600</v>
     <v>BROADCOM INC.</v>
     <v>BROADCOM INC.</v>
     <v>418.69</v>
-    <v>84.7821</v>
+    <v>82.414299999999997</v>
     <v>414.14</v>
-    <v>434.33</v>
+    <v>422.2</v>
     <v>4734668000</v>
     <v>AVGO</v>
     <v>BROADCOM INC. (XNAS:AVGO)</v>
-    <v>5341488</v>
+    <v>8743289</v>
     <v>18847496</v>
     <v>2018</v>
   </rv>
@@ -4132,28 +3972,28 @@
     <v>9</v>
     <v>Finance</v>
     <v>10</v>
-    <v>601.90930000000003</v>
+    <v>603.73500000000001</v>
     <v>235.37</v>
     <v>1.5746</v>
-    <v>25.56</v>
-    <v>4.4349999999999994E-2</v>
+    <v>20.164999999999999</v>
+    <v>3.4988999999999999E-2</v>
     <v>USD</v>
     <v>Nasdaq Stock Market</v>
     <v>XNAS</v>
     <v>3.4999999999999996E-3</v>
-    <v>601.90930000000003</v>
+    <v>603.73500000000001</v>
     <v>ETF</v>
-    <v>46168.60555719844</v>
+    <v>46168.683522765627</v>
     <v>52</v>
     <v>589.1</v>
     <v>58790612118.779999</v>
     <v>VanEck:Semiconductor</v>
     <v>591.92999999999995</v>
     <v>576.32000000000005</v>
-    <v>601.88</v>
+    <v>596.48500000000001</v>
     <v>SMH</v>
     <v>VanEck:Semiconductor (XNAS:SMH)</v>
-    <v>2911624</v>
+    <v>6098128</v>
     <v>9705623</v>
   </rv>
   <rv s="2">
@@ -4178,8 +4018,8 @@
     <v>435.43</v>
     <v>311.89999999999998</v>
     <v>1.2076</v>
-    <v>16.389900000000001</v>
-    <v>4.1880000000000001E-2</v>
+    <v>16.5899</v>
+    <v>4.2390999999999998E-2</v>
     <v>USD</v>
     <v>Eaton Corporation plc is an intelligent power management company. Its Electrical Americas segment consists of electrical components, industrial components, power distribution and assemblies, residential products, circuit protection, utility power distribution, wiring devices and others. The Electrical Global segment consists of electrical components, industrial components, power distribution and assemblies, single phase and three phase power quality, and services. The Aerospace segment is a global supplier of aerospace fuel, hydraulics, and pneumatic systems for commercial and military use and filtration systems for industrial applications. The Vehicle segment designs, manufactures, markets, and supplies drivetrain, powertrain systems and critical components. The eMobility segment designs, manufactures, markets, and supplies mechanical, electrical, and electronic components and systems. The Company is also engaged in providing thermal monitoring for critical electrical equipment.</v>
     <v>97000</v>
@@ -4187,23 +4027,23 @@
     <v>XNYS</v>
     <v>XNYS</v>
     <v>EATON HOUSE 30 PEMBROKE ROAD DUBLIN 4, DUBLIN, D04 Y0C2 IE</v>
-    <v>408</v>
+    <v>409.65</v>
     <v>Machinery, Equipment &amp; Components</v>
     <v>Stock</v>
-    <v>46168.605529803128</v>
+    <v>46168.683453796097</v>
     <v>55</v>
     <v>398</v>
-    <v>158325403170</v>
+    <v>158403063170</v>
     <v>EATON CORPORATION PUBLIC LIMITED COMPANY</v>
     <v>EATON CORPORATION PUBLIC LIMITED COMPANY</v>
     <v>400.2</v>
-    <v>39.861899999999999</v>
+    <v>39.881500000000003</v>
     <v>391.35</v>
-    <v>407.73989999999998</v>
+    <v>407.93990000000002</v>
     <v>388300000</v>
     <v>ETN</v>
     <v>EATON CORPORATION PUBLIC LIMITED COMPANY (XNYS:ETN)</v>
-    <v>590607</v>
+    <v>1233419</v>
     <v>2864922</v>
     <v>2012</v>
   </rv>
@@ -4229,8 +4069,8 @@
     <v>379.935</v>
     <v>104.71</v>
     <v>2.0743999999999998</v>
-    <v>12.01</v>
-    <v>3.6676E-2</v>
+    <v>2.2549999999999999</v>
+    <v>6.8859999999999998E-3</v>
     <v>USD</v>
     <v>Vertiv Holdings Co. provides mission-critical digital infrastructure technologies and lifecycle services primarily for data centers, communication networks, and commercial and industrial environments. The Company operates in three business segments: the Americas; Asia Pacific, and Europe, Middle East &amp; Africa. The Company's offerings include alternate current (AC) and direct current (DC) power management, thermal management, low/medium voltage switchgear, busbar, air cooled and liquid cooled thermal management products, integrated modular solutions, racks, single phase UPS, rack power distribution, rack thermal systems, configurable integrated solutions, energy storage solutions, hardware, software for managing IT equipment, management systems for monitoring and controlling digital infrastructure, and services. It also provides preventative maintenance, acceptance testing, engineering and consulting, remote monitoring, training, spare parts, specialized fluid management, and others.</v>
     <v>34000</v>
@@ -4241,20 +4081,20 @@
     <v>343.31</v>
     <v>Machinery, Equipment &amp; Components</v>
     <v>Stock</v>
-    <v>46168.605528506247</v>
+    <v>46168.683516562502</v>
     <v>58</v>
-    <v>336</v>
-    <v>130393414336</v>
+    <v>328.58</v>
+    <v>126646432991</v>
     <v>VERTIV HOLDINGS CO</v>
     <v>VERTIV HOLDINGS CO</v>
     <v>341.06</v>
-    <v>85.229699999999994</v>
+    <v>82.780600000000007</v>
     <v>327.45999999999998</v>
-    <v>339.47</v>
+    <v>329.71499999999997</v>
     <v>384108800</v>
     <v>VRT</v>
     <v>VERTIV HOLDINGS CO (XNYS:VRT)</v>
-    <v>1720809</v>
+    <v>2966078</v>
     <v>5938554</v>
     <v>2016</v>
   </rv>
@@ -4276,8 +4116,8 @@
     <v>104.32</v>
     <v>41.73</v>
     <v>3.1070000000000002</v>
-    <v>1.355</v>
-    <v>2.9342E-2</v>
+    <v>1.54</v>
+    <v>3.3348000000000003E-2</v>
     <v>USD</v>
     <v>Tempus AI, Inc. is a technology company advancing precision medicine through the practical application of artificial intelligence in healthcare. It offers AI-enabled precision medicine solutions to physicians to deliver personalized patient care and, in parallel, facilitates discovery, development and delivery of optimal therapeutics. It provides three product lines: Genomics, Data and artificial intelligence applications (AI). The Genomics product line leverages its laboratories to provide next generation sequencing (NGS) diagnostics, polymerase chain reaction, profiling, molecular genotyping and other anatomic and molecular pathology testing. The data generated in its lab or ingested into its platform is structured and de-identified, prior to commercialization. Its AI Applications is focused on developing and providing diagnostics that are algorithmic in nature, implementing new software as a medical device, and building and deploying clinical decision support tools.</v>
     <v>3800</v>
@@ -4288,19 +4128,19 @@
     <v>48.21</v>
     <v>Biotechnology &amp; Medical Research</v>
     <v>Stock</v>
-    <v>46168.605554710157</v>
+    <v>46168.683502106251</v>
     <v>46.220100000000002</v>
-    <v>8535612767</v>
+    <v>8568832256</v>
     <v>TEMPUS AI, INC.</v>
     <v>TEMPUS AI, INC.</v>
     <v>47.07</v>
     <v>0</v>
     <v>46.18</v>
-    <v>47.534999999999997</v>
+    <v>47.72</v>
     <v>179564800</v>
     <v>TEM</v>
     <v>TEMPUS AI, INC. (XNAS:TEM)</v>
-    <v>1696565</v>
+    <v>2700326</v>
     <v>5813264</v>
     <v>2025</v>
   </rv>
@@ -4326,8 +4166,8 @@
     <v>308.64010000000002</v>
     <v>106.38</v>
     <v>1.0609999999999999</v>
-    <v>6.7999000000000001</v>
-    <v>2.3035999999999997E-2</v>
+    <v>8.3350000000000009</v>
+    <v>2.8235999999999997E-2</v>
     <v>USD</v>
     <v>Dell Technologies Inc. is engaged in designing, developing, manufacturing, marketing, selling, and supporting a wide range of comprehensive and integrated solutions, products, and services. The Company operates through two segments: Infrastructure Solutions Group (ISG) and Client Solutions Group (CSG). Its ISG segment enables the Company’s customer’s digital transformation with solutions that address artificial intelligence (AI), machine learning, data analytics, and multi cloud environments. Its comprehensive storage portfolio includes modern and traditional storage solutions, including all-flash arrays, scale-out file, object platforms, hyper-converged infrastructure, and software-defined storage. Its CSG segment offers branded personal computers (PCs) including notebooks, desktops, and workstations and branded peripherals that include displays, docking stations, keyboards, mice, and webcam and audio devices, as well as third-party software and peripherals.</v>
     <v>97000</v>
@@ -4338,20 +4178,20 @@
     <v>308.64010000000002</v>
     <v>Computers, Phones &amp; Household Electronics</v>
     <v>Stock</v>
-    <v>46168.605548251566</v>
+    <v>46168.683503796092</v>
     <v>63</v>
     <v>298.97000000000003</v>
-    <v>196163065960</v>
+    <v>197160218257</v>
     <v>DELL TECHNOLOGIES INC.</v>
     <v>DELL TECHNOLOGIES INC.</v>
     <v>300.26</v>
-    <v>34.606900000000003</v>
+    <v>34.782800000000002</v>
     <v>295.19</v>
-    <v>301.98989999999998</v>
+    <v>303.52499999999998</v>
     <v>649568300</v>
     <v>DELL</v>
     <v>DELL TECHNOLOGIES INC. (XNYS:DELL)</v>
-    <v>3893063</v>
+    <v>5839272</v>
     <v>6254903</v>
     <v>2013</v>
   </rv>
@@ -4377,8 +4217,8 @@
     <v>114.77</v>
     <v>34.2301</v>
     <v>2.64</v>
-    <v>2.7871999999999999</v>
-    <v>2.9190999999999998E-2</v>
+    <v>1.85</v>
+    <v>1.9376000000000001E-2</v>
     <v>USD</v>
     <v>Innodata Inc. is a global data engineering company. It provides a range of transferable solutions, platforms, and services for generative artificial intelligence (AI)/AI builders and adopters. Its Digital Data Solutions segment provides AI data preparation services, collecting or creating training data, annotating training data, and training AI algorithms for its customers, and AI model deployment and integration. It also provides a range of data engineering support services. Its Synodex segment provides an industry platform that transforms medical records into useable digital data organized in accordance with its proprietary data models or customer data models. Its Agility segment provides an industry platform that provides marketing communications and public relations professionals with the ability to target and distribute content to journalists and social media influencers worldwide and to monitor and analyze global news channels (print, Web, radio and TV) and social media channels.</v>
     <v>10020</v>
@@ -4389,20 +4229,20 @@
     <v>100.9</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46168.60548709453</v>
+    <v>46168.683489930467</v>
     <v>66</v>
     <v>94.4</v>
     <v>1490374656</v>
     <v>INNODATA INC.</v>
     <v>INNODATA INC.</v>
     <v>97.5</v>
-    <v>88.417500000000004</v>
+    <v>87.574200000000005</v>
     <v>95.48</v>
-    <v>98.267200000000003</v>
+    <v>97.33</v>
     <v>32655360</v>
     <v>INOD</v>
     <v>INNODATA INC. (XNAS:INOD)</v>
-    <v>588605</v>
+    <v>815062</v>
     <v>2667802</v>
     <v>1988</v>
   </rv>
@@ -4428,8 +4268,8 @@
     <v>280.67</v>
     <v>118.3</v>
     <v>1.1302000000000001</v>
-    <v>5</v>
-    <v>2.9035999999999999E-2</v>
+    <v>7.0149999999999997</v>
+    <v>4.0738000000000003E-2</v>
     <v>USD</v>
     <v>Snowflake Inc. is an artificial intelligence (AI) data cloud company. The Company provides a platform which powers the AI data cloud, enabling customers to consolidate data into a single source of truth to drive insights, apply AI to solve business problems, build data applications, and share data and data products. Its cloud-native architecture includes three independently scalable but logically integrated layers across storage, compute, and cloud services. The storage layer ingests massive amounts and varieties of structured, semi-structured, and unstructured data. The compute layer provides dedicated resources to enable users to simultaneously access common data sets for many use cases with minimal latency. The cloud services layer enables users to securely use AI within applications, tools, and processes. Its platform supports a wide range of product categories for customers’ business objectives, including analytics, data engineering, AI, applications and collaboration.</v>
     <v>9060</v>
@@ -4440,20 +4280,20 @@
     <v>181.27</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46168.605561990626</v>
+    <v>46168.68352896953</v>
     <v>69</v>
     <v>174.55009999999999</v>
-    <v>61418033879</v>
+    <v>62116438723</v>
     <v>SNOWFLAKE INC.</v>
     <v>SNOWFLAKE INC.</v>
     <v>177.19</v>
     <v>0</v>
     <v>172.2</v>
-    <v>177.2</v>
+    <v>179.215</v>
     <v>346602900</v>
     <v>SNOW</v>
     <v>SNOWFLAKE INC. (XNYS:SNOW)</v>
-    <v>3539960</v>
+    <v>6265669</v>
     <v>7091258</v>
     <v>2012</v>
   </rv>
@@ -4479,8 +4319,8 @@
     <v>19.84</v>
     <v>9.2002000000000006</v>
     <v>0.92749999999999999</v>
-    <v>0.245</v>
-    <v>2.2414999999999997E-2</v>
+    <v>0.41499999999999998</v>
+    <v>3.7969000000000003E-2</v>
     <v>USD</v>
     <v>UiPath, Inc. is focused on agentic automation and orchestration, empowering enterprises to harness the full potential of AI agents to autonomously execute and optimize complex business processes. It is focused on building and managing automations, starting with computer vision technology and user interface automation in its initial robotic process automation offering. Its AI-powered UiPath Platform offers a robust set of capabilities that allows its customers to discover opportunities for automation, automate using a digital workforce that seamlessly collaborates with humans, and operate a mission-critical automation program at scale. It enables employees to quickly build automations for both existing and new processes and to automate a range of actions including logging into applications, moving folders, filling in forms, reading emails and others. Its platform allows users to design and combine UI automations, API integrations and AI-based document understanding in a single workflow.</v>
     <v>3981</v>
@@ -4488,23 +4328,23 @@
     <v>XNYS</v>
     <v>XNYS</v>
     <v>One Vanderbilt Avenue, 60th Floor, NEW YORK, NY, 10017 US</v>
-    <v>11.29</v>
+    <v>11.38</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46168.605549582811</v>
+    <v>46168.683506330468</v>
     <v>72</v>
     <v>10.73</v>
-    <v>5815954995</v>
+    <v>5904430373</v>
     <v>UIPATH, INC.</v>
     <v>UIPATH, INC.</v>
     <v>10.91</v>
-    <v>21.490400000000001</v>
+    <v>21.817299999999999</v>
     <v>10.93</v>
-    <v>11.175000000000001</v>
+    <v>11.345000000000001</v>
     <v>520443400</v>
     <v>PATH</v>
     <v>UIPATH, INC. (XNYS:PATH)</v>
-    <v>9365216</v>
+    <v>20890381</v>
     <v>30135944</v>
     <v>2015</v>
   </rv>
@@ -4530,8 +4370,8 @@
     <v>30.38</v>
     <v>13.29</v>
     <v>1.3915999999999999</v>
-    <v>0.6</v>
-    <v>2.6362E-2</v>
+    <v>0.64</v>
+    <v>2.8119999999999999E-2</v>
     <v>USD</v>
     <v>Five9, Inc. helps organizations to create hyper-personalized artificial intelligence (AI)-driven customer experiences. The Company's Intelligent CX Platform, powered by its Five9 Genius AI suite, delivers a comprehensive suite of applications that enable customer service, sales, and marketing functions. It delivers a comprehensive, end-to-end cloud software solution for contact centers. Comprised of its Intelligent CX Platform and AI capabilities, including agentic AI agents, Agent Assist, Workflow Automation (WFA), AI Insights, AI Summaries, Workforce Engagement Management (WEM), and Revenue Execution, its solution allows simultaneous management and optimization of customer interactions across voice, chat, email, web, social media and mobile channels, either directly or through its application programming interfaces (APIs). The Company's agent interface is a browser-based design that provides visualization of customer profiles, context and cross-channel history.</v>
     <v>2910</v>
@@ -4539,23 +4379,23 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>3001 Bishop Drive, Suite 350, SAN RAMON, CA, 94583 US</v>
-    <v>23.5488</v>
+    <v>23.66</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46168.605510497655</v>
+    <v>46168.683415150001</v>
     <v>75</v>
     <v>22.06</v>
-    <v>1788534806</v>
+    <v>1791597366</v>
     <v>FIVE9, INC.</v>
     <v>FIVE9, INC.</v>
     <v>22.58</v>
-    <v>35.4208</v>
+    <v>35.481400000000001</v>
     <v>22.76</v>
-    <v>23.36</v>
+    <v>23.4</v>
     <v>76563990</v>
     <v>FIVN</v>
     <v>FIVE9, INC. (XNAS:FIVN)</v>
-    <v>740395</v>
+    <v>1229849</v>
     <v>4008334</v>
     <v>2001</v>
   </rv>
@@ -4581,8 +4421,8 @@
     <v>336.99</v>
     <v>114.625</v>
     <v>1.0414000000000001</v>
-    <v>4.1399999999999997</v>
-    <v>2.2700999999999999E-2</v>
+    <v>7.14</v>
+    <v>3.9150999999999998E-2</v>
     <v>USD</v>
     <v>Zscaler, Inc. is a cloud security company. The Company has developed a platform incorporating core security functionalities needed to enable fast and secure access to cloud resources based on identity, context and an organization's policies. Its Zscaler Zero Trust Exchange is a cloud-native platform that securely connects users, devices, applications and workloads, including artificial intelligence (AI) agents, without relying on hub-and-spoke network architecture and firewall-centric security. It delivers its solutions using a software-as-a-service (SaaS) business model and sells subscriptions to customers to access its cloud platform, together with related support services. Its services include Zscaler Internet Access (ZIA), Zscaler Private Access (ZPA), and Zscaler Digital Experience (ZDX). ZIA provides secure access to externally managed applications, including SaaS applications and internet destinations, regardless of device, location or network.</v>
     <v>7923</v>
@@ -4590,23 +4430,23 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>120 Holger Way, SAN JOSE, CA, 95134 US</v>
-    <v>188.25</v>
+    <v>189.64</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46168.605486053122</v>
+    <v>46168.683480161715</v>
     <v>78</v>
     <v>181.875</v>
-    <v>29989073457</v>
+    <v>30471445557</v>
     <v>ZSCALER, INC.</v>
     <v>ZSCALER, INC.</v>
     <v>183</v>
     <v>0</v>
     <v>182.37</v>
-    <v>186.51</v>
+    <v>189.51</v>
     <v>160790700</v>
     <v>ZS</v>
     <v>ZSCALER, INC. (XNAS:ZS)</v>
-    <v>1498213</v>
+    <v>2770092</v>
     <v>2977080</v>
     <v>2007</v>
   </rv>
@@ -4632,8 +4472,8 @@
     <v>651.73</v>
     <v>376.18</v>
     <v>1.2539</v>
-    <v>12.86</v>
-    <v>2.4506999999999998E-2</v>
+    <v>9.6150000000000002</v>
+    <v>1.8322999999999999E-2</v>
     <v>USD</v>
     <v>Synopsys, Inc. is engaged in providing engineering solutions from silicon to systems, enabling customers to innovate artificial intelligence (AI)-powered products. It delivers silicon design, intellectual property (IP), simulation and analysis solutions, and design services. It supplies mission-critical electronic design automation (EDA) software that engineers use to design and test integrated circuits (ICs). Its Design Automation segment includes its advanced silicon design, verification products and services, and Ansys products, and system integration products and services. This segment also includes digital, custom and field programmable gate array integrated circuit design software, verification software and hardware products, and manufacturing software products. Its Design IP segment includes its logic libraries, embedded memories, wired interface IP, memory interface IP, security IP, and embedded processors that serve companies in the semiconductor and electronics industries.</v>
     <v>28000</v>
@@ -4641,23 +4481,23 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>675 Almanor Ave, SUNNYVALE, CA, 94085 US</v>
-    <v>537.6</v>
+    <v>539.48</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46168.605569073436</v>
+    <v>46168.683479247658</v>
     <v>81</v>
     <v>524.17999999999995</v>
-    <v>102983731200</v>
+    <v>102362112510</v>
     <v>SYNOPSYS, INC.</v>
     <v>SYNOPSYS, INC.</v>
     <v>530</v>
-    <v>83.177300000000002</v>
+    <v>82.675299999999993</v>
     <v>524.74</v>
-    <v>537.6</v>
+    <v>534.35500000000002</v>
     <v>191562000</v>
     <v>SNPS</v>
     <v>SYNOPSYS, INC. (XNAS:SNPS)</v>
-    <v>328417</v>
+    <v>645475</v>
     <v>1650918</v>
     <v>1987</v>
   </rv>
@@ -4680,11 +4520,11 @@
     <v>3</v>
     <v>Finance</v>
     <v>4</v>
-    <v>382.32</v>
+    <v>383.24</v>
     <v>262.74900000000002</v>
     <v>1.1472</v>
-    <v>7.64</v>
-    <v>2.0449999999999999E-2</v>
+    <v>6.87</v>
+    <v>1.8388999999999999E-2</v>
     <v>USD</v>
     <v>Cadence Design Systems, Inc. is an electronic systems designing company. The Company applies its Intelligent System Design strategy to deliver software, hardware and intellectual property (IP) that turn design concepts into reality. Its product categories include Core Electronic Design Automation (EDA), Semiconductor IP, and System Design and Analysis (SD&amp;A). Core EDA includes software, hardware, and services used to design and verify a wide variety of semiconductors. The semiconductor IP portfolio includes silicon subsystems, software, and services that are used in semiconductor design. The SD&amp;A category provides solutions and services that enable the design and verification of complete electronic systems, from PCBs to complex system assemblies. Its semiconductors are used in various industries, including automotive, aerospace, biotech, hyperscale and cloud computing, data centers, telecommunications, medical technology, industrial Internet of things, and artificial intelligence (AI).</v>
     <v>13800</v>
@@ -4692,23 +4532,23 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>2655 Seely Avenue Bldg 5, SAN JOSE, CA, 95134 US</v>
-    <v>382.32</v>
+    <v>383.24</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46168.605529258595</v>
+    <v>46168.683495196092</v>
     <v>84</v>
     <v>369.96</v>
-    <v>105149333680</v>
+    <v>104936955360</v>
     <v>CADENCE DESIGN SYSTEMS, INC.</v>
     <v>CADENCE DESIGN SYSTEMS, INC.</v>
     <v>380</v>
-    <v>88.999600000000001</v>
+    <v>88.819900000000004</v>
     <v>373.59</v>
-    <v>381.23</v>
+    <v>380.46</v>
     <v>275816000</v>
     <v>CDNS</v>
     <v>CADENCE DESIGN SYSTEMS, INC. (XNAS:CDNS)</v>
-    <v>489738</v>
+    <v>790202</v>
     <v>2434453</v>
     <v>1987</v>
   </rv>
@@ -4734,8 +4574,8 @@
     <v>421.97</v>
     <v>190.56</v>
     <v>1.3918999999999999</v>
-    <v>10.17</v>
-    <v>2.5141E-2</v>
+    <v>6.7249999999999996</v>
+    <v>1.6625000000000001E-2</v>
     <v>USD</v>
     <v>Taiwan Semiconductor Manufacturing Co Ltd is a Taiwan-based integrated circuit foundry service provider. The Company is primarily engaged in integrated circuit manufacturing services. It offers advanced process technologies, specialised process solutions, advanced photomask and silicon stacking, and packaging-related technologies, while supporting a comprehensive design ecosystem. The Company's products serve diverse electronic sectors including artificial intelligence, high-performance computing, wired and wireless communications, automotive and industrial equipment, personal computing, information applications, consumer electronics, smart internet of things, and wearable devices.</v>
     <v>52045</v>
@@ -4746,20 +4586,20 @@
     <v>416.49</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46168.605561943747</v>
+    <v>46168.683527626563</v>
     <v>87</v>
-    <v>410.35</v>
-    <v>2150791758450</v>
+    <v>410.07010000000002</v>
+    <v>2132924248725</v>
     <v>Taiwan Semiconductor Manufacturing Company Limited</v>
     <v>Taiwan Semiconductor Manufacturing Company Limited</v>
     <v>413.12</v>
-    <v>35.086399999999998</v>
+    <v>34.795000000000002</v>
     <v>404.52</v>
-    <v>414.69</v>
+    <v>411.245</v>
     <v>5186505000</v>
     <v>TSM</v>
     <v>Taiwan Semiconductor Manufacturing Company Limited (XNYS:TSM)</v>
-    <v>2996422</v>
+    <v>4950921</v>
     <v>13560183</v>
     <v>1987</v>
   </rv>
@@ -4785,8 +4625,8 @@
     <v>179.8</v>
     <v>83.858000000000004</v>
     <v>1.6326000000000001</v>
-    <v>3.51</v>
-    <v>2.2787999999999999E-2</v>
+    <v>5.57</v>
+    <v>3.6162E-2</v>
     <v>USD</v>
     <v>Arista Networks, Inc. is a provider of data-driven, client-to-cloud networking for large artificial intelligence (AI), data center, campus and routing environments. Its platforms deliver availability, agility, automation, analytics, and security through an advanced network operating stack. Its platform is its Extensible Operating System (EOS), a modernized publish-subscribe state-sharing networking operating system. Its portfolio of products, services and technologies is grouped into various categories: Core (Data Center, Cloud and AI Networking), Cognitive Adjacencies (Campus and Routing), and Cognitive Network (Software and Services). It offers product portfolios of data-driven, high-speed, cloud and data center Ethernet switches. Its Cognitive Adjacencies include Cognitive Campus Switching, Cloud-Grade Routing and WAN Routing. Its software and services are based on subscription-based models and include various offerings: CloudVision, Arista A-Care Services, CloudEOS and others.</v>
     <v>5115</v>
@@ -4794,23 +4634,23 @@
     <v>XNYS</v>
     <v>XNYS</v>
     <v>5453 Great America Pkwy, SANTA CLARA, CA, 95054 US</v>
-    <v>157.74</v>
+    <v>159.68</v>
     <v>Communications &amp; Networking</v>
     <v>Stock</v>
-    <v>46168.605576851565</v>
+    <v>46168.683552464841</v>
     <v>90</v>
     <v>153.88999999999999</v>
-    <v>198374840620</v>
+    <v>200968798800</v>
     <v>ARISTA NETWORKS, INC.</v>
     <v>ARISTA NETWORKS, INC.</v>
     <v>157.13</v>
-    <v>53.959400000000002</v>
+    <v>54.664999999999999</v>
     <v>154.03</v>
-    <v>157.54</v>
+    <v>159.6</v>
     <v>1259203000</v>
     <v>ANET</v>
     <v>ARISTA NETWORKS, INC. (XNYS:ANET)</v>
-    <v>2993278</v>
+    <v>5652729</v>
     <v>11652560</v>
     <v>2011</v>
   </rv>
@@ -4836,8 +4676,8 @@
     <v>233.7</v>
     <v>59.21</v>
     <v>3.1960000000000002</v>
-    <v>2.4</v>
-    <v>1.0989000000000001E-2</v>
+    <v>-3.57</v>
+    <v>-1.6345000000000002E-2</v>
     <v>USD</v>
     <v>Credo Technology Group Holding Ltd is a Cayman Islands-based holding company. The Company delivers high-speed solutions to break bandwidth barriers on every wired connection in the data infrastructure market. It provides high-speed connectivity solutions that deliver improved power efficiency as data rates and corresponding bandwidth requirements increase exponentially throughout the data infrastructure market. Its connectivity solutions are optimized for optical and electrical Ethernet applications, including the emerging 100 gigabits per second (G), 200G, 400G, 800G and the emerging 1.6 terabits per second (T) port markets. Its products are based on its Serializer/Deserializer (SerDes) and Digital Signal Processor (DSP) technologies. Its product families include integrated circuits (ICs) for the optical and line card markets, active electrical cables (AECs) and SerDes Chiplets. The Company’s intellectual property (IP) solutions consist primarily of SerDes IP licensing.</v>
     <v>622</v>
@@ -4848,20 +4688,20 @@
     <v>233.7</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46168.605576157031</v>
+    <v>46168.683560925783</v>
     <v>93</v>
-    <v>220.76</v>
-    <v>40728382419</v>
+    <v>211.58</v>
+    <v>39627216516</v>
     <v>Credo Technology Group Holding Ltd</v>
     <v>Credo Technology Group Holding Ltd</v>
     <v>228.16</v>
-    <v>122.5361</v>
+    <v>119.2231</v>
     <v>218.41</v>
-    <v>220.81</v>
+    <v>214.84</v>
     <v>184449900</v>
     <v>CRDO</v>
     <v>Credo Technology Group Holding Ltd (XNAS:CRDO)</v>
-    <v>2748487</v>
+    <v>5644285</v>
     <v>6433756</v>
   </rv>
   <rv s="2">
@@ -4886,8 +4726,8 @@
     <v>22.17</v>
     <v>5.83</v>
     <v>2.7301000000000002</v>
-    <v>0.15</v>
-    <v>1.8360000000000001E-2</v>
+    <v>9.01E-2</v>
+    <v>1.1028E-2</v>
     <v>USD</v>
     <v>SoundHound AI, Inc. is engaged in conversational intelligence, offering voice and conversational artificial intelligence (AI) solutions that let businesses offer experiences to their customers. Through its proprietary technology, its voice AI delivers speed and accuracy in numerous languages to product creators and service providers across retail, financial services, healthcare, automotive, smart devices, and restaurants via AI-driven products, such as Smart Answering, Smart Ordering, Dynamic Drive Thru, and Amelia AI Agents. Along with SoundHound Chat AI, a voice assistant with integrated Generative AI, it powers various products and services, and processes billions of interactions each year for businesses. Its developer platform, Houndify, is an open-access platform that allows developers to leverage its Voice AI technology and a library of over 100 content domains, including commonly used domains for points of interest, weather, flight status, sports and more.</v>
     <v>954</v>
@@ -4898,20 +4738,20 @@
     <v>8.44</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46168.605507974222</v>
+    <v>46168.68348923594</v>
     <v>96</v>
     <v>8.1199999999999992</v>
-    <v>3600643072</v>
+    <v>3574720172</v>
     <v>SOUNDHOUND AI, INC.</v>
     <v>SOUNDHOUND AI, INC.</v>
     <v>8.1999999999999993</v>
     <v>0</v>
     <v>8.17</v>
-    <v>8.32</v>
+    <v>8.2600999999999996</v>
     <v>432769600</v>
     <v>SOUN</v>
     <v>SOUNDHOUND AI, INC. (XNAS:SOUN)</v>
-    <v>9489549</v>
+    <v>13729860</v>
     <v>31416425</v>
     <v>2020</v>
   </rv>
@@ -4937,8 +4777,8 @@
     <v>233.67</v>
     <v>15.06</v>
     <v>3.7349999999999999</v>
-    <v>3.86</v>
-    <v>2.1267999999999999E-2</v>
+    <v>0.06</v>
+    <v>3.3060000000000001E-4</v>
     <v>USD</v>
     <v>Applied Optoelectronics, Inc. is a developer and manufacturer of advanced optical and hybrid fiber coaxial (HFC) networking products that are the building blocks for artificial intelligence (AI) datacenters, Cable TV Broadband (CATV) and broadband fiber access networks around the world. The Company supplies this critical infrastructure to tier-one customers across cloud computing, CATV broadband, telecom, and fiber-to-the-home (FTTH) markets. It designs and manufactures a range of optical communications products at varying levels of integration, from components, subassemblies and modules to complete turn-key equipment. In the CATV market, it supplies a broad array of products, including lasers, transmitters and transceivers, and turn-key equipment. It supplies optical transceivers that plug into switches and servers within the data center and allow these network devices to send and receive data over fiber optic cables. In the telecom market, it supplies lasers and laser subassemblies.</v>
     <v>4691</v>
@@ -4949,20 +4789,20 @@
     <v>194.95</v>
     <v>Electronic Equipment &amp; Parts</v>
     <v>Stock</v>
-    <v>46168.605565832811</v>
+    <v>46168.683558553123</v>
     <v>99</v>
-    <v>180</v>
-    <v>14872997419</v>
+    <v>177.7801</v>
+    <v>14568074893</v>
     <v>APPLIED OPTOELECTRONICS, INC.</v>
     <v>APPLIED OPTOELECTRONICS, INC.</v>
     <v>186.61</v>
     <v>0</v>
     <v>181.49</v>
-    <v>185.35</v>
+    <v>181.55</v>
     <v>80242770</v>
     <v>AAOI</v>
     <v>APPLIED OPTOELECTRONICS, INC. (XNAS:AAOI)</v>
-    <v>4849309</v>
+    <v>6970130</v>
     <v>11357824</v>
     <v>2013</v>
   </rv>
@@ -4988,8 +4828,8 @@
     <v>90.9</v>
     <v>51.93</v>
     <v>1.5053000000000001</v>
-    <v>1.53</v>
-    <v>1.8725000000000002E-2</v>
+    <v>0.34499999999999997</v>
+    <v>4.2220000000000001E-3</v>
     <v>USD</v>
     <v>Skyworks Solutions, Inc. provides wireless networking services. The Company’s analog and mixed-signal semiconductors are connecting people, places, and things, spanning a number of new applications within the aerospace, automotive, broadband, cellular infrastructure, connected home, defense, entertainment and gaming, industrial, medical, smartphone, tablet, and wearable markets. It operates engineering, manufacturing, sales, and service facilities throughout Asia, Europe, and North America. The Company offers a range of products, such as Amplifiers, Attenuators, Diodes, Audio And Radio, Clocks And Timing, Front-End Modules, Isolation, Modems And DAAs, Optocouplers, Power Management, Power Over Ethernet, RF Passives, Television (TV) And Video, Switches, and Voice. Its engineering, marketing, operations, sales, and support facilities are located throughout Asia, Europe, and North America.</v>
     <v>10000</v>
@@ -4997,23 +4837,23 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>5260 California Avenue, IRVINE, CA, 92617 US</v>
-    <v>83.68</v>
+    <v>84.778999999999996</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46168.605591608597</v>
+    <v>46168.68354476797</v>
     <v>102</v>
     <v>80</v>
-    <v>12519787116</v>
+    <v>12341556124</v>
     <v>SKYWORKS SOLUTIONS, INC.</v>
     <v>SKYWORKS SOLUTIONS, INC.</v>
     <v>82.54</v>
-    <v>32.885599999999997</v>
+    <v>32.417400000000001</v>
     <v>81.709999999999994</v>
-    <v>83.24</v>
+    <v>82.055000000000007</v>
     <v>150405900</v>
     <v>SWKS</v>
     <v>SKYWORKS SOLUTIONS, INC. (XNAS:SWKS)</v>
-    <v>1011675</v>
+    <v>2232219</v>
     <v>4858739</v>
     <v>2002</v>
   </rv>
@@ -5036,28 +4876,28 @@
     <v>9</v>
     <v>Finance</v>
     <v>10</v>
-    <v>730.32</v>
+    <v>731.17</v>
     <v>511.93</v>
     <v>0.99850000000000005</v>
-    <v>12.58</v>
-    <v>1.7532000000000002E-2</v>
+    <v>9.8714999999999993</v>
+    <v>1.3756999999999998E-2</v>
     <v>USD</v>
     <v>Nasdaq Stock Market</v>
     <v>XNAS</v>
     <v>1.8E-3</v>
-    <v>730.32</v>
+    <v>731.17</v>
     <v>ETF</v>
-    <v>46168.60551018516</v>
+    <v>46168.683487823437</v>
     <v>105</v>
     <v>724.16</v>
     <v>440257379466.70001</v>
     <v>Invesco QQQ Trust 1</v>
     <v>726</v>
     <v>717.54</v>
-    <v>730.12</v>
+    <v>727.41150000000005</v>
     <v>QQQ</v>
     <v>Invesco QQQ Trust 1 (XNAS:QQQ)</v>
-    <v>10796831</v>
+    <v>19706470</v>
     <v>39466245</v>
   </rv>
   <rv s="2">
@@ -5082,8 +4922,8 @@
     <v>18.038</v>
     <v>2.2801999999999998</v>
     <v>1.3101</v>
-    <v>0.26500000000000001</v>
-    <v>1.5633999999999999E-2</v>
+    <v>-0.01</v>
+    <v>-5.8999999999999992E-4</v>
     <v>USD</v>
     <v>LightPath Technologies, Inc. is a global, vertically integrated provider of optics, photonics and infrared solutions for the industrial, commercial, defense, telecommunications, and medical industries. The Company designs and manufactures optical and infrared components including molded glass aspheric lenses and assemblies, custom molded glass freeform lenses, infrared lenses and thermal imaging assemblies, fused fiber collimators, and BlackDiamond (BD6) chalcogenide-based glass lenses. It also offers custom optical assemblies, including full engineering design support. Its business is organized into four product groups: infrared components, visible components, assemblies and modules, and engineering services. Its infrared product group comprises both molded and turned infrared lenses and assemblies using a variety of infrared glass materials. Its assemblies and modules product group is comprised of other value-added products, including both infrared and visible components.</v>
     <v>345</v>
@@ -5094,20 +4934,20 @@
     <v>18.038</v>
     <v>Computers, Phones &amp; Household Electronics</v>
     <v>Stock</v>
-    <v>46168.605553367968</v>
+    <v>46168.68351748828</v>
     <v>108</v>
-    <v>16.88</v>
-    <v>1080919693</v>
+    <v>16.75</v>
+    <v>1063652605</v>
     <v>LIGHTPATH TECHNOLOGIES, INC.</v>
     <v>LIGHTPATH TECHNOLOGIES, INC.</v>
     <v>17.96</v>
     <v>0</v>
     <v>16.95</v>
-    <v>17.215</v>
+    <v>16.940000000000001</v>
     <v>62789410</v>
     <v>LPTH</v>
     <v>LIGHTPATH TECHNOLOGIES, INC. (XNAS:LPTH)</v>
-    <v>2088124</v>
+    <v>3200746</v>
     <v>3805461</v>
     <v>1992</v>
   </rv>
@@ -5133,25 +4973,25 @@
     <v>290.51</v>
     <v>202.67</v>
     <v>0.99929999999999997</v>
-    <v>4.415</v>
-    <v>1.5485000000000001E-2</v>
+    <v>4.62</v>
+    <v>1.6204E-2</v>
     <v>USD</v>
     <v>NYSE Arca</v>
     <v>ARCX</v>
     <v>1.9E-3</v>
     <v>290.51</v>
     <v>ETF</v>
-    <v>46168.605543147656</v>
+    <v>46168.68352585625</v>
     <v>111</v>
     <v>287.74</v>
     <v>76877810344.919998</v>
     <v>iShares:Russ 2000 ETF</v>
     <v>288.55</v>
     <v>285.12</v>
-    <v>289.53500000000003</v>
+    <v>289.74</v>
     <v>IWM</v>
     <v>iShares:Russ 2000 ETF (ARCX:IWM)</v>
-    <v>6969903</v>
+    <v>12471961</v>
     <v>26339211</v>
   </rv>
   <rv s="2">
@@ -5176,8 +5016,8 @@
     <v>132.75</v>
     <v>18.965</v>
     <v>2.2282999999999999</v>
-    <v>2.7549999999999999</v>
-    <v>2.2989000000000002E-2</v>
+    <v>2.101</v>
+    <v>1.7532000000000002E-2</v>
     <v>USD</v>
     <v>Intel Corporation is a global designer and manufacturer of semiconductor products. The Company's segments include Intel Products, Intel Foundry, and All Other. Its Intel Products comprise Client Computing Group (CCG) and Data Center and AI (DCAI). CCG delivers platforms and processors that power PCs and edge devices, enabling enhanced performance, connectivity and user experience for consumer and commercial markets with capabilities that also support retail, industrial robotics and AI ecosystems at the edge. DCAI delivers workload-optimized solutions based upon its x86 architecture for data centers, including CPUs, AI accelerators, NICs, IPUs and custom ASICs, enabling performance and scalability for cloud, enterprise, telecommunication and HPC environments. The Intel Foundry segment comprises technology development, manufacturing and foundry services, developing new semiconductor process technologies and advanced packaging technologies. All Other segments include Mobileye and Other.</v>
     <v>83200</v>
@@ -5188,20 +5028,20 @@
     <v>125.62</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46168.605583541408</v>
+    <v>46168.683564640625</v>
     <v>114</v>
     <v>117.35</v>
-    <v>616162470000</v>
+    <v>612875466000</v>
     <v>INTEL CORPORATION</v>
     <v>INTEL CORPORATION</v>
     <v>122</v>
     <v>0</v>
     <v>119.84</v>
-    <v>122.595</v>
+    <v>121.941</v>
     <v>5026000000</v>
     <v>INTC</v>
     <v>INTEL CORPORATION (XNAS:INTC)</v>
-    <v>42953434</v>
+    <v>66152883</v>
     <v>151534568</v>
     <v>1989</v>
   </rv>
@@ -5220,11 +5060,11 @@
     <v>3</v>
     <v>Finance</v>
     <v>4</v>
-    <v>316.5</v>
+    <v>316.61</v>
     <v>84.78</v>
     <v>2.5950000000000002</v>
-    <v>2.2000000000000002</v>
-    <v>7.169E-3</v>
+    <v>8.9700000000000006</v>
+    <v>2.9229999999999999E-2</v>
     <v>USD</v>
     <v>Astera Labs, Inc. is a global semiconductor company. The Company provides semiconductor-based connectivity solutions for cloud and artificial intelligence (AI) infrastructure. It has developed and deployed its Intelligent Connectivity Platform built from the ground up for cloud and AI infrastructure. Its Intelligent Connectivity Platform provides its customers with the ability to deploy and operate high-performance cloud and AI infrastructure at scale, addressing an increasingly diverse set of requirements. It provides its connectivity products in various form factors, including Integrated Circuits (ICs), boards, and modules. Its PCIe, CXL and Ethernet semiconductor-based connectivity solutions are purpose-built to unleash the potential of accelerated computing at cloud-scale. The Company’s products include Aries products, which include its COSMOS software suite; Taurus products, which are hardware modules based on its Taurus ICs; Leo products; and Scorpio products.</v>
     <v>756</v>
@@ -5232,22 +5072,22 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>2345 North First Street, SAN JOSE, CA, 95131 US</v>
-    <v>316.5</v>
+    <v>316.61</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46168.605609235936</v>
+    <v>46168.683543078128</v>
     <v>290.5</v>
-    <v>52978753732</v>
+    <v>54139185215</v>
     <v>ASTERA LABS, INC.</v>
     <v>ASTERA LABS, INC.</v>
     <v>315</v>
-    <v>208.35919999999999</v>
+    <v>212.923</v>
     <v>306.88</v>
-    <v>309.08</v>
+    <v>315.85000000000002</v>
     <v>171407900</v>
     <v>ALAB</v>
     <v>ASTERA LABS, INC. (XNAS:ALAB)</v>
-    <v>3011391</v>
+    <v>4276218</v>
     <v>6287038</v>
     <v>2017</v>
   </rv>
@@ -5269,8 +5109,8 @@
     <v>187</v>
     <v>63.8</v>
     <v>2.4460000000000002</v>
-    <v>1.6</v>
-    <v>1.5167E-2</v>
+    <v>1.5</v>
+    <v>1.4218999999999999E-2</v>
     <v>USD</v>
     <v>CoreWeave, Inc. is a cloud infrastructure technology company. The Company offers the CoreWeave Cloud Platform, which consists of software and cloud services that deliver the automation and efficiency needed to manage complex artificial intelligence (AI) infrastructure. Its CoreWeave Cloud Platform is an integrated solution that is purpose-built for running AI workloads such as model training and inference. Its solutions include infrastructure services, managed software services, and application software services. Its Infrastructure Services provide its customers with access to advanced graphics processing unit (GPU) and central processing unit (CPU) compute, highly performant networking, and storage. Its Managed Software Services include CKS, a flexible virtual private cloud and a bare metal service that runs kubernetes directly on high-performance servers. Its Application Software Services build on top of its infrastructure and managed software services, integrating additional tools.</v>
     <v>2189</v>
@@ -5281,19 +5121,19 @@
     <v>109.2</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46168.605494721873</v>
+    <v>46168.683439814064</v>
     <v>106.02</v>
-    <v>58425134136</v>
+    <v>58370577096</v>
     <v>COREWEAVE, INC.</v>
     <v>COREWEAVE, INC.</v>
     <v>108.23</v>
     <v>0</v>
     <v>105.49</v>
-    <v>107.09</v>
+    <v>106.99</v>
     <v>545570400</v>
     <v>CRWV</v>
     <v>COREWEAVE, INC. (XNAS:CRWV)</v>
-    <v>7686109</v>
+    <v>12756802</v>
     <v>28779618</v>
     <v>2017</v>
   </rv>
@@ -5319,25 +5159,25 @@
     <v>92.65</v>
     <v>55.02</v>
     <v>2.0520999999999998</v>
-    <v>0.97</v>
-    <v>1.2696000000000001E-2</v>
+    <v>0.81499999999999995</v>
+    <v>1.0668E-2</v>
     <v>USD</v>
     <v>CBOE BZX Exchange</v>
     <v>BATS</v>
     <v>7.4999999999999997E-3</v>
     <v>77.790000000000006</v>
     <v>ETF</v>
-    <v>46168.605482777341</v>
+    <v>46168.683468286719</v>
     <v>121</v>
     <v>76.53</v>
     <v>6482466914.0900002</v>
     <v>ARK Innovation</v>
     <v>77.400000000000006</v>
     <v>76.400000000000006</v>
-    <v>77.37</v>
+    <v>77.215000000000003</v>
     <v>ARKK</v>
     <v>ARK Innovation (BATS:ARKK)</v>
-    <v>1211355</v>
+    <v>2446868</v>
     <v>7848548</v>
   </rv>
   <rv s="2">
@@ -5358,8 +5198,8 @@
     <v>324.99990000000003</v>
     <v>100.02</v>
     <v>1.151</v>
-    <v>7.37</v>
-    <v>2.4045E-2</v>
+    <v>14.6539</v>
+    <v>4.7808999999999997E-2</v>
     <v>USD</v>
     <v>Arm Holdings plc is a United Kingdom-based company. The Company is engaged in the design of central processing units (CPUs) and compute platforms for semiconductor chips. It develops and licenses CPU products and related technology. Its cloud and data center solutions include Arm AGI CPU and Arm Neoverse Compute Subsystems. The Arm Agentic Generalized Infrastructure (AGI) CPU is a production-ready system on a chip (SoC) for artificial intelligence (AI) data centers, delivering compute at scale. The Arm Neoverse Compute Subsystems (CSS) are pre-validated, performance-optimized compute platforms designed to accelerate infrastructure silicon development. The Company's primary markets include smartphone applications, processors and other chips used in mobile phones, consumer electronics, networking equipment, cloud and data center servers, automotive applications, Internet of Things (loT) and other embedded computing devices.</v>
     <v>9584</v>
@@ -5370,19 +5210,19 @@
     <v>324.99990000000003</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46168.60559679375</v>
+    <v>46168.683549825779</v>
     <v>300</v>
-    <v>333968320000</v>
+    <v>341718389600</v>
     <v>ARM HOLDINGS PLC</v>
     <v>ARM HOLDINGS PLC</v>
     <v>317.52</v>
-    <v>370.84120000000001</v>
+    <v>379.447</v>
     <v>306.51</v>
-    <v>313.88</v>
+    <v>321.16390000000001</v>
     <v>1064000000</v>
     <v>ARM</v>
     <v>ARM HOLDINGS PLC (XNAS:ARM)</v>
-    <v>4451259</v>
+    <v>6885427</v>
     <v>12284536</v>
     <v>2018</v>
   </rv>
@@ -5428,8 +5268,8 @@
     <v>345.72</v>
     <v>134.57</v>
     <v>1.5724</v>
-    <v>2.415</v>
-    <v>1.2573000000000001E-2</v>
+    <v>0.12</v>
+    <v>6.2469999999999995E-4</v>
     <v>USD</v>
     <v>Oracle Corporation offers integrated suites of applications plus secure, autonomous infrastructure in the Oracle Cloud. The Company operates through three businesses: cloud and license, hardware and service. Its cloud and license business is engaged in the sale, marketing and delivery of its enterprise applications and infrastructure technologies through cloud and on-premise deployment models including its cloud services and license support offerings, and its cloud license and on-premise license offerings. Its hardware business provides infrastructure technologies including Oracle Engineered Systems, servers, storage, industry-specific hardware, operating systems, virtualization, management and other hardware-related software to support diverse IT environments. Its services business provides services to customers and partners to help maximize the performance of their investments in Oracle applications and infrastructure technologies.</v>
     <v>162000</v>
@@ -5437,24 +5277,24 @@
     <v>XNYS</v>
     <v>XNYS</v>
     <v>2300 Oracle Way, AUSTIN, TX, 78741 US</v>
-    <v>195</v>
+    <v>195.196</v>
     <v>129</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46168.605518784374</v>
+    <v>46168.683472488279</v>
     <v>130</v>
     <v>190.61</v>
-    <v>559376566770</v>
+    <v>552776041200</v>
     <v>ORACLE CORPORATION</v>
     <v>ORACLE CORPORATION</v>
     <v>193.30500000000001</v>
-    <v>32.965800000000002</v>
+    <v>32.576799999999999</v>
     <v>192.08</v>
-    <v>194.495</v>
+    <v>192.2</v>
     <v>2876046000</v>
     <v>ORCL</v>
     <v>ORACLE CORPORATION (XNYS:ORCL)</v>
-    <v>3246479</v>
+    <v>5675675</v>
     <v>23762431</v>
     <v>2005</v>
   </rv>
@@ -5480,8 +5320,8 @@
     <v>62.357999999999997</v>
     <v>19.48</v>
     <v>1.7202</v>
-    <v>0.47</v>
-    <v>1.321E-2</v>
+    <v>1.1251</v>
+    <v>3.1621999999999997E-2</v>
     <v>USD</v>
     <v>Super Micro Computer, Inc. is an application-optimized Total IT solutions provider including server, artificial intelligence (AI) systems, storage, information of technology (IoT) devices, switches, software, and support services. Total IT Solutions include complete servers, storage systems, modular blade servers, workstations, full-rack scale solutions, networking devices, server sub-systems, server management and security software. Its products are designed and manufactured in-house (in the United States, Taiwan, and the Netherlands). Its portfolio of Server Building Block Solutions allows customers to optimize for their exact workload and application by selecting from a broad family of systems built from the Company’s flexible and reusable building blocks that support a comprehensive set of form factors, processors, memory, GPUs, storage, networking, power, and cooling solutions (air-conditioned, free air cooling or liquid cooling).</v>
     <v>6238</v>
@@ -5489,23 +5329,23 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>980 Rock Avenue, SAN JOSE, CA, 95131 US</v>
-    <v>36.36</v>
+    <v>36.799999999999997</v>
     <v>Computers, Phones &amp; Household Electronics</v>
     <v>Stock</v>
-    <v>46168.605610219529</v>
+    <v>46168.683562349215</v>
     <v>133</v>
     <v>35.434699999999999</v>
-    <v>21681136925</v>
+    <v>22075126184</v>
     <v>SUPER MICRO COMPUTER, INC.</v>
     <v>SUPER MICRO COMPUTER, INC.</v>
     <v>36</v>
-    <v>19.642600000000002</v>
+    <v>19.999500000000001</v>
     <v>35.58</v>
-    <v>36.049999999999997</v>
+    <v>36.705100000000002</v>
     <v>601418500</v>
     <v>SMCI</v>
     <v>SUPER MICRO COMPUTER, INC. (XNAS:SMCI)</v>
-    <v>10512235</v>
+    <v>20014116</v>
     <v>37059778</v>
     <v>2006</v>
   </rv>
@@ -5531,8 +5371,8 @@
     <v>153.85990000000001</v>
     <v>62.92</v>
     <v>2.2747999999999999</v>
-    <v>0.62990000000000002</v>
-    <v>8.5540000000000008E-3</v>
+    <v>0.63</v>
+    <v>8.5550000000000001E-3</v>
     <v>USD</v>
     <v>Robinhood Markets, Inc. is creating a financial services platform for everyone, regardless of their wealth, income, or background. It uses technology to provide access to the financial system. Its offerings include Brokerage, Robinhood Crypto, Custody, Robinhood Wallet, Robinhood Gold, and Robinhood Gold Card. Its Brokerage services include investing, options trading, fractional trading, recurring investment, access to investing on margin, fully paid securities lending, cash sweep, instant withdrawals, Robinhood retirement, 24-hour market, joint investing accounts, and event contracts. It also offers a variety of ways for its customers to grow their financial knowledge, including Robinhood Learn, In-App Education, Newsfeeds, Sherwood Snacks, and Crypto Learn and Earn. Its self-clearing system, order routing system, data platform, and other back-end infrastructure deliver the capabilities that allow its customers to focus on investing, saving and spending.</v>
     <v>2900</v>
@@ -5543,20 +5383,20 @@
     <v>76.025000000000006</v>
     <v>Financial Technology (Fintech) &amp; Infrastructure</v>
     <v>Stock</v>
-    <v>46168.605560878903</v>
+    <v>46168.683556955468</v>
     <v>136</v>
     <v>73.819999999999993</v>
-    <v>66880423726</v>
+    <v>66880513777</v>
     <v>ROBINHOOD MARKETS, INC.</v>
     <v>ROBINHOOD MARKETS, INC.</v>
     <v>74.42</v>
-    <v>41.316099999999999</v>
+    <v>41.316200000000002</v>
     <v>73.64</v>
-    <v>74.269900000000007</v>
+    <v>74.27</v>
     <v>900505100</v>
     <v>HOOD</v>
     <v>ROBINHOOD MARKETS, INC. (XNAS:HOOD)</v>
-    <v>6240183</v>
+    <v>10204070</v>
     <v>26479684</v>
     <v>2013</v>
   </rv>
@@ -5582,8 +5422,8 @@
     <v>404.47</v>
     <v>163.33000000000001</v>
     <v>1.2525999999999999</v>
-    <v>3.9701</v>
-    <v>1.0465E-2</v>
+    <v>2.94</v>
+    <v>7.7490000000000007E-3</v>
     <v>USD</v>
     <v>Alphabet Inc. is a holding company. The Company's segments include Google Services, Google Cloud, and Other Bets. The Google Services segment includes products and services such as ads, Android, Chrome, devices, Google Maps, Google Play, Search, and YouTube. The Google Cloud segment includes infrastructure and platform services, collaboration tools, and other services for enterprise customers. Its Other Bets segment is engaged in the sale of healthcare-related services and Internet services. Its Google Cloud provides enterprise-ready cloud services, including Google Cloud Platform and Google Workspace. Google Cloud Platform provides access to solutions such as artificial intelligence (AI) offerings, including its AI infrastructure, Vertex AI platform, and Gemini for Google Cloud; cybersecurity, and data and analytics. Google Workspace includes cloud-based communication and collaboration tools for enterprises, such as Calendar, Gmail, Docs, Drive, and Meet.</v>
     <v>194668</v>
@@ -5591,23 +5431,23 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>1600 Amphitheatre Parkway, MOUNTAIN VIEW, CA, 94043 US</v>
-    <v>384.41250000000002</v>
+    <v>385.39</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46168.605575624999</v>
+    <v>46168.683511990625</v>
     <v>139</v>
     <v>379.14</v>
-    <v>4644669811600</v>
+    <v>4632189120000</v>
     <v>ALPHABET INC.</v>
     <v>ALPHABET INC.</v>
     <v>380.63</v>
-    <v>29.277000000000001</v>
+    <v>29.1983</v>
     <v>379.38</v>
-    <v>383.3501</v>
+    <v>382.32</v>
     <v>12116000000</v>
     <v>GOOG</v>
     <v>ALPHABET INC. (XNAS:GOOG)</v>
-    <v>3957341</v>
+    <v>7555535</v>
     <v>18429688</v>
     <v>2015</v>
   </rv>
@@ -5633,8 +5473,8 @@
     <v>260</v>
     <v>158.83000000000001</v>
     <v>1.6654</v>
-    <v>2.37</v>
-    <v>1.0964E-2</v>
+    <v>3.89</v>
+    <v>1.7995000000000001E-2</v>
     <v>USD</v>
     <v>Cloudflare, Inc. is a connectivity cloud company. The Company delivers a range of services to businesses of all sizes and in all geographies, enhancing the performance of business-critical applications. Its full suite of products consists of application services that help deliver security, performance, and reliability for any organization's applications connected to the Internet, including Websites and application programming interfaces (APIs) and its secure access service edge (SASE) platform, which contains its suite of and workplace security services and network services solutions to help ensure traffic in and out of an organization’s network and devices is verified and authorized and data is protected and secured, as well as to securely connect data centers, cloud services, and branch offices to an organization with its connectivity cloud. The Company also offers developer-based solutions which build and deploys serverless and artificial intelligence applications.</v>
     <v>5483</v>
@@ -5642,22 +5482,22 @@
     <v>XNYS</v>
     <v>XNYS</v>
     <v>101 Townsend St, SAN FRANCISCO, CA, 94107-1934 US</v>
-    <v>219.06379999999999</v>
+    <v>220.59</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46168.60551517344</v>
+    <v>46168.683481099222</v>
     <v>142</v>
     <v>208.24</v>
-    <v>77246503348</v>
+    <v>77783771972</v>
     <v>CLOUDFLARE, INC.</v>
     <v>CLOUDFLARE, INC.</v>
     <v>216.96</v>
     <v>216.17</v>
-    <v>218.54</v>
+    <v>220.06</v>
     <v>353466200</v>
     <v>NET</v>
     <v>CLOUDFLARE, INC. (XNYS:NET)</v>
-    <v>941066</v>
+    <v>1578332</v>
     <v>4332008</v>
     <v>2009</v>
   </rv>
@@ -5683,8 +5523,8 @@
     <v>463.48500000000001</v>
     <v>305.44009999999997</v>
     <v>1.5677000000000001</v>
-    <v>3.165</v>
-    <v>6.9979999999999999E-3</v>
+    <v>2.29</v>
+    <v>5.0629999999999998E-3</v>
     <v>USD</v>
     <v>Rockwell Automation, Inc. is engaged in industrial automation and digital transformation. The Company operates in three segments: Intelligent Devices, Software &amp; Control, and Lifecycle Services. The Intelligent Devices segment portfolio includes power control, motion control, safety, sensing, and industrial components, and micro control and distributed input/output. The Software &amp; Control operating segment contains a comprehensive portfolio of production automation and production operations platforms, including hardware and software. This integrated portfolio is merging information technology (IT) and operational technology (OT), bringing the benefits of the Connected Enterprise to the production system. The Lifecycle Services segment includes consulting services, including cybersecurity and digital transformation strategy and design and professional services, including global automation and information program and project management and delivery capabilities, and connected services.</v>
     <v>26000</v>
@@ -5695,20 +5535,20 @@
     <v>458.53</v>
     <v>Machinery, Equipment &amp; Components</v>
     <v>Stock</v>
-    <v>46168.605602094533</v>
+    <v>46168.683437314059</v>
     <v>145</v>
     <v>452.28500000000003</v>
-    <v>50680254124</v>
+    <v>50582889462</v>
     <v>ROCKWELL AUTOMATION, INC.</v>
     <v>ROCKWELL AUTOMATION, INC.</v>
     <v>454.55</v>
-    <v>47.314100000000003</v>
+    <v>47.223199999999999</v>
     <v>452.29</v>
-    <v>455.45499999999998</v>
+    <v>454.58</v>
     <v>111273900</v>
     <v>ROK</v>
     <v>ROCKWELL AUTOMATION, INC. (XNYS:ROK)</v>
-    <v>126285</v>
+    <v>267037</v>
     <v>788597</v>
     <v>1996</v>
   </rv>
@@ -5734,8 +5574,8 @@
     <v>311.82</v>
     <v>195.07</v>
     <v>1.0824</v>
-    <v>2.68</v>
-    <v>8.6779999999999999E-3</v>
+    <v>1.22</v>
+    <v>3.9509999999999997E-3</v>
     <v>USD</v>
     <v>Apple Inc. designs, manufactures and markets smartphones, personal computers, tablets, wearables and accessories, and sells a variety of related services. Its product categories include iPhone, Mac, iPad, Wearables, Home and Accessories. Its services include advertising, AppleCare, cloud services, digital content, and payment services. The Company operates various platforms, including the App Store, that allow customers to discover and download applications and digital content, such as books, music, video, games and podcasts. It also offers digital content through subscription-based services, including Apple Arcade, Apple Fitness+, Apple Music, Apple News+, and Apple TV+. Its wearables include smartwatches, wireless headphones, and spatial computers. Its products include iPhone 16 Pro, iPhone 16, iPhone 15, iPhone 14, iPhone SE, MacBook Air, MacBook Pro, iMac, Mac mini, Mac Studio, Mac Pro, iPad Pro, iPad Air, AirPods, AirPods Pro, AirPods Max, Apple TV, Apple Vision Pro and others.</v>
     <v>166000</v>
@@ -5746,20 +5586,20 @@
     <v>311.82</v>
     <v>Computers, Phones &amp; Household Electronics</v>
     <v>Stock</v>
-    <v>46168.605603043747</v>
+    <v>46168.683556342185</v>
     <v>148</v>
     <v>309.35000000000002</v>
-    <v>4575112640000</v>
+    <v>4553669094400</v>
     <v>APPLE INC.</v>
     <v>APPLE INC.</v>
     <v>309.57</v>
-    <v>37.831899999999997</v>
+    <v>37.654499999999999</v>
     <v>308.82</v>
-    <v>311.5</v>
+    <v>310.04000000000002</v>
     <v>14687360000</v>
     <v>AAPL</v>
     <v>APPLE INC. (XNAS:AAPL)</v>
-    <v>9422483</v>
+    <v>16659446</v>
     <v>46783820</v>
     <v>1977</v>
   </rv>
@@ -5782,28 +5622,28 @@
     <v>9</v>
     <v>Finance</v>
     <v>10</v>
-    <v>751.8691</v>
+    <v>752.13</v>
     <v>578.42999999999995</v>
     <v>0.99870000000000003</v>
-    <v>5.9427000000000003</v>
-    <v>7.9699999999999997E-3</v>
+    <v>3.7050000000000001</v>
+    <v>4.9690000000000003E-3</v>
     <v>USD</v>
     <v>NYSE Arca</v>
     <v>ARCX</v>
     <v>9.4499999999999998E-4</v>
-    <v>751.8691</v>
+    <v>752.13</v>
     <v>ETF</v>
-    <v>46168.605606284378</v>
+    <v>46168.683550253903</v>
     <v>151</v>
-    <v>749.15</v>
+    <v>748.37</v>
     <v>735060829033.51001</v>
     <v>State Street SPDR S&amp;P500</v>
     <v>750.14</v>
     <v>745.64</v>
-    <v>751.58270000000005</v>
+    <v>749.34500000000003</v>
     <v>SPY</v>
     <v>State Street SPDR S&amp;P500 (ARCX:SPY)</v>
-    <v>7271177</v>
+    <v>16804518</v>
     <v>47879214</v>
   </rv>
   <rv s="2">
@@ -5828,8 +5668,8 @@
     <v>236.54</v>
     <v>132.91999999999999</v>
     <v>2.2374999999999998</v>
-    <v>2.7349999999999999</v>
-    <v>1.2701E-2</v>
+    <v>-2.78</v>
+    <v>-1.291E-2</v>
     <v>USD</v>
     <v>NVIDIA Corporation is an artificial intelligence (AI) infrastructure company. The Company is engaged in accelerated computing to help solve the challenging computational problems. Its segments include Compute &amp; Networking and Graphics. The Compute &amp; Networking segment includes its Data Center accelerated computing and networking platforms and AI solutions and software, and automotive platforms and autonomous and electric vehicle solutions, including software. The Graphics segment includes GeForce GPUs for gaming and personal computers (PCs), and Quadro/NVIDIA RTX GPUs for enterprise workstation graphics. Its technology stack includes the foundational NVIDIA CUDA development platform that runs on all NVIDIA GPUs, as well as hundreds of domain-specific software libraries, frameworks, algorithms, software development kits (SDKs), and application programming interfaces (APIs). Its platforms address four markets, which include Data Center, Gaming, Professional Visualization, and Automotive.</v>
     <v>42000</v>
@@ -5840,20 +5680,20 @@
     <v>218.18</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46168.605568043749</v>
+    <v>46168.683534270313</v>
     <v>154</v>
-    <v>214.28</v>
-    <v>5277173000000</v>
+    <v>212</v>
+    <v>5143710000000</v>
     <v>NVIDIA CORPORATION</v>
     <v>NVIDIA CORPORATION</v>
     <v>216.51</v>
-    <v>33.394300000000001</v>
+    <v>32.549799999999998</v>
     <v>215.33</v>
-    <v>218.065</v>
+    <v>212.55</v>
     <v>24200000000</v>
     <v>NVDA</v>
     <v>NVIDIA CORPORATION (XNAS:NVDA)</v>
-    <v>49996640</v>
+    <v>93010094</v>
     <v>156622118</v>
     <v>1998</v>
   </rv>
@@ -5879,8 +5719,8 @@
     <v>7.18</v>
     <v>2.77</v>
     <v>1.0073000000000001</v>
-    <v>3.5000000000000003E-2</v>
-    <v>1.1628000000000001E-2</v>
+    <v>-2.5000000000000001E-2</v>
+    <v>-8.3060000000000009E-3</v>
     <v>USD</v>
     <v>Recursion Pharmaceuticals, Inc. is a clinical-stage TechBio company decoding biology and chemistry to industrialize drug discovery. Its Recursion Operating System (OS), a platform built across diverse technologies, enables the Company to map and navigate trillions of biological and chemical relationships within the Recursion Data Universe. The Company integrates physical and digital components as iterative loops of atoms and bits, scaling wet lab biology and chemistry data organized into virtuous cycles with computational tools to rapidly translate silico hypotheses into validated insights and novel chemistry. Its clinical programs in oncology and rare diseases include REC-617, REC-1245, REC-3565 and REC-4539. Its REC-617 is an orally bioavailable, cyclin-dependent kinase 7 (CDK7) inhibitor for the treatment of advanced solid tumors. Its REV102 program targets ectonucleotide pyrophosphatase/phosphodiesterase 1 (ENPP1), an enzyme implicated in the pathogenesis of HPP.</v>
     <v>600</v>
@@ -5891,20 +5731,20 @@
     <v>3.14</v>
     <v>Biotechnology &amp; Medical Research</v>
     <v>Stock</v>
-    <v>46168.605593830471</v>
+    <v>46168.683581133591</v>
     <v>157</v>
-    <v>2.99</v>
-    <v>1613561334</v>
+    <v>2.98</v>
+    <v>1581767022</v>
     <v>RECURSION PHARMACEUTICALS, INC.</v>
     <v>RECURSION PHARMACEUTICALS, INC.</v>
     <v>3.03</v>
     <v>0</v>
     <v>3.01</v>
-    <v>3.0449999999999999</v>
+    <v>2.9849999999999999</v>
     <v>529905200</v>
     <v>RXRX</v>
     <v>RECURSION PHARMACEUTICALS, INC. (XNAS:RXRX)</v>
-    <v>9755377</v>
+    <v>15916324</v>
     <v>13106952</v>
     <v>2013</v>
   </rv>
@@ -5927,11 +5767,11 @@
     <v>3</v>
     <v>Finance</v>
     <v>4</v>
-    <v>674.84</v>
+    <v>677.49990000000003</v>
     <v>342.72</v>
     <v>1.1557999999999999</v>
-    <v>2.93</v>
-    <v>4.4159999999999998E-3</v>
+    <v>12.8</v>
+    <v>1.9293000000000001E-2</v>
     <v>USD</v>
     <v>CrowdStrike Holdings, Inc. is a global cybersecurity company that provides cloud-delivered protection of endpoints, cloud workloads, identity and data. Its Falcon platform is designed for cybersecurity consolidation, purpose-built to stop breaches. The platforms collect and integrate data from across the enterprise, including endpoints, cloud workloads, identities, and third-party sources. It offers 29 cloud modules on its Falcon platform via a software as a service (SaaS) subscription-based model that spans multiple large markets, including corporate endpoint and cloud workload security, managed security services, security and vulnerability management, information technology (IT) operations management, identity protection, next-generation security information and event management (SIEM) and log management, threat intelligence services, data protection, SaaS security posture management, automation and response (SOAR) and artificial intelligence powered workflow automation, and others.</v>
     <v>10698</v>
@@ -5939,23 +5779,23 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>206 E. 9TH STREET, SUITE 1400, AUSTIN, TX, 78701 US</v>
-    <v>669.69</v>
+    <v>677.49990000000003</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46168.60555172422</v>
+    <v>46168.683540728904</v>
     <v>160</v>
     <v>648</v>
-    <v>169620578235</v>
+    <v>172132853490</v>
     <v>CROWDSTRIKE HOLDINGS, INC.</v>
     <v>CROWDSTRIKE HOLDINGS, INC.</v>
     <v>664.38</v>
     <v>0</v>
     <v>663.46</v>
-    <v>666.39</v>
+    <v>676.26</v>
     <v>254536500</v>
     <v>CRWD</v>
     <v>CROWDSTRIKE HOLDINGS, INC. (XNAS:CRWD)</v>
-    <v>653576</v>
+    <v>1071573</v>
     <v>3021963</v>
     <v>2011</v>
   </rv>
@@ -5977,8 +5817,8 @@
     <v>12.24</v>
     <v>10.99</v>
     <v>0.84709999999999996</v>
-    <v>0.05</v>
-    <v>4.2339999999999999E-3</v>
+    <v>-0.06</v>
+    <v>-5.0590000000000001E-3</v>
     <v>CAD</v>
     <v>Atrium Mortgage Investment Corporation is a Canada-based company. The Company is a non-bank provider of residential and commercial mortgages that lends in urban centers in Canada. Its objectives are to provide its shareholders with dividends and preserve shareholders equity by lending within conservative risk parameters. Its investment strategy is to invest in commercial and residential mortgages from borrowers whose financing needs are not being met by the larger financial institutions. It finances various types of properties, which include residential houses, small multi-family residential properties comprising six units or fewer, residential apartment buildings, commercial and storefront retail properties, as well as residential and commercial land development sites. It also provides construction financing and short-term bridge loans to real estate developers. The Company is managed by Canadian Mortgage Capital Corporation (CMCC).</v>
     <v>0</v>
@@ -5986,22 +5826,22 @@
     <v>NEOE</v>
     <v>NEOE</v>
     <v>20 Adelaide Street East, Suite 900, TORONTO, ON, M5C 2T6 CA</v>
-    <v>11.94</v>
+    <v>11.84</v>
     <v>Banking Services</v>
     <v>Stock</v>
-    <v>46167.83323616875</v>
-    <v>11.86</v>
-    <v>570901736</v>
+    <v>46168.662617117967</v>
+    <v>11.8</v>
+    <v>568013532</v>
     <v>ATRIUM MORTGAGE INVESTMENT CORPORATION</v>
     <v>ATRIUM MORTGAGE INVESTMENT CORPORATION</v>
-    <v>11.94</v>
-    <v>11.2706</v>
     <v>11.81</v>
+    <v>11.2135</v>
     <v>11.86</v>
+    <v>11.8</v>
     <v>48136740</v>
     <v>AI</v>
     <v>ATRIUM MORTGAGE INVESTMENT CORPORATION (NEOE:AI)</v>
-    <v>6200</v>
+    <v>1500</v>
     <v>108590</v>
     <v>2001</v>
   </rv>
@@ -6027,8 +5867,8 @@
     <v>9.39</v>
     <v>3.01</v>
     <v>3.0284</v>
-    <v>0.01</v>
-    <v>2.392E-3</v>
+    <v>0.04</v>
+    <v>9.5689999999999994E-3</v>
     <v>USD</v>
     <v>BigBear.ai Holdings, Inc. operates as a specialized provider of artificial intelligence (AI) technology. The Company provides decision intelligence solutions for supply chains and logistics, enterprise operations, manned-unmanned teaming in autonomous systems, and cybersecurity. Its solutions include AI orchestration and sensor function, digital identity management, computer vision, cybersecurity, predictive intelligence, modeling &amp; simulation, enterprise automation and professional services. It offers Trueface, which performs one-to-many (1:N) facial matches with real-time photos, delivering identity verification. It also offers veriScan, which captures and transmits real-time photos into a biometric matching service supporting access control and biometric boarding/bag tags. The Company serves homeland &amp; border security, defense, intelligence, manufacturing &amp; suppy chain, travel and trade industries.</v>
     <v>579</v>
@@ -6039,20 +5879,20 @@
     <v>4.29</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46168.605603263284</v>
+    <v>46168.683550219532</v>
     <v>165</v>
     <v>4.1500000000000004</v>
-    <v>2006798405</v>
+    <v>2021166890</v>
     <v>BIGBEAR.AI HOLDINGS, INC.</v>
     <v>BIGBEAR.AI HOLDINGS, INC.</v>
     <v>4.25</v>
     <v>0</v>
     <v>4.18</v>
-    <v>4.1900000000000004</v>
+    <v>4.22</v>
     <v>478949500</v>
     <v>BBAI</v>
     <v>BIGBEAR.AI HOLDINGS, INC. (XNYS:BBAI)</v>
-    <v>13220114</v>
+    <v>24891393</v>
     <v>40816876</v>
     <v>2020</v>
   </rv>
@@ -6078,8 +5918,8 @@
     <v>211.47800000000001</v>
     <v>81.239999999999995</v>
     <v>0.84519999999999995</v>
-    <v>-1.01</v>
-    <v>-9.8890000000000002E-3</v>
+    <v>-0.31</v>
+    <v>-3.0349999999999999E-3</v>
     <v>USD</v>
     <v>ServiceNow, Inc. provides an artificial intelligence (AI) platform for business transformation. The Company’s AI platform connects people, processes, data, and devices to increase productivity and maximize business outcomes. Its intelligent platform, the Now Platform, is a cloud-based solution that helps enterprises and organizations across public and private sectors digitize workflows. The workflow applications built on the Now Platform are organized into four primary areas: Technology, CRM and Industry, Core Business and Creator. Its products include IT Service Management, IT Operations Management, HR Service Delivery, ServiceNow AI Agents, AI Experience, Build Agent, ServiceNow AI Control Tower, AI Agent Fabric, RaptorDB, Workflow Data Fabric, Workplace Service Delivery, ServiceNow Platform Encryption, Telecommunications Service Operations Management, and others. The Company also offers identity security, helping organizations secure access across the enterprise.</v>
     <v>29187</v>
@@ -6090,20 +5930,20 @@
     <v>102.54</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46168.605610532031</v>
+    <v>46168.683556921096</v>
     <v>168</v>
     <v>98.72</v>
-    <v>104285864960</v>
+    <v>105007780560</v>
     <v>SERVICENOW, INC.</v>
     <v>SERVICENOW, INC.</v>
     <v>100.6</v>
-    <v>60.1404</v>
+    <v>60.556699999999999</v>
     <v>102.13</v>
-    <v>101.12</v>
+    <v>101.82</v>
     <v>1031308000</v>
     <v>NOW</v>
     <v>SERVICENOW, INC. (XNYS:NOW)</v>
-    <v>8290675</v>
+    <v>12018396</v>
     <v>30167244</v>
     <v>2012</v>
   </rv>
@@ -6145,8 +5985,8 @@
     <v>555.45000000000005</v>
     <v>356.28</v>
     <v>1.0896999999999999</v>
-    <v>-0.62990000000000002</v>
-    <v>-1.505E-3</v>
+    <v>-2.81</v>
+    <v>-6.7130000000000002E-3</v>
     <v>USD</v>
     <v>Microsoft Corporation is a technology company. The Company develops and supports software, services, devices, and solutions. The Company’s segments include Productivity and Business Processes, Intelligent Cloud, and More Personal Computing. The Productivity and Business Processes segment consists of products and services in its portfolio of productivity, communication, and information services. This segment primarily comprises: Office Commercial, Office Consumer, LinkedIn, and Dynamics business solutions. The Intelligent Cloud segment consists of server products and cloud services, including Azure and other cloud services, SQL Server, Windows Server, Visual Studio, System Center, and related Client Access Licenses (CALs), and Nuance and GitHub; and Enterprise Services, including enterprise support services, industry solutions and Nuance professional services. The More Personal Computing segment primarily comprises Windows, Devices, Gaming, and search and news advertising.</v>
     <v>228000</v>
@@ -6158,20 +5998,20 @@
     <v>173</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46168.605549883592</v>
+    <v>46168.683520253908</v>
     <v>174</v>
     <v>413.17</v>
-    <v>3104640866743</v>
+    <v>3088446135600</v>
     <v>MICROSOFT CORPORATION</v>
     <v>MICROSOFT CORPORATION</v>
     <v>416.5</v>
-    <v>24.892800000000001</v>
+    <v>24.762899999999998</v>
     <v>418.57</v>
-    <v>417.94009999999997</v>
+    <v>415.76</v>
     <v>7428435000</v>
     <v>MSFT</v>
     <v>MICROSOFT CORPORATION (XNAS:MSFT)</v>
-    <v>9383019</v>
+    <v>14980013</v>
     <v>33521115</v>
     <v>1993</v>
   </rv>
@@ -6197,8 +6037,8 @@
     <v>498.83</v>
     <v>273.20999999999998</v>
     <v>1.7970999999999999</v>
-    <v>0.41</v>
-    <v>9.6240000000000008E-4</v>
+    <v>2.6673</v>
+    <v>6.2610000000000001E-3</v>
     <v>USD</v>
     <v>Tesla, Inc. designs, develops, manufactures, sells and leases high-performance fully electric vehicles and energy generation and storage systems, and offers services related to its products. Its segments include automotive, and energy generation and storage. The automotive segment includes the design, development, manufacturing, sales and leasing of high-performance fully electric vehicles, and sales of automotive regulatory credits. It also includes sales of used vehicles, non-warranty maintenance services and collisions, part sales, paid supercharging, insurance services revenue and retail merchandise sales. The energy generation and storage segment include the design, manufacture, installation, sales and leasing of solar energy generation and energy storage products and related services and sales of solar energy systems incentives. Its consumer vehicles include the Model 3, Y, S, X and Cybertruck. Its lithium-ion battery energy storage products include Powerwall and Megapack.</v>
     <v>134785</v>
@@ -6206,23 +6046,23 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>1 Tesla Road, AUSTIN, TX, 78725 US</v>
-    <v>433.67</v>
+    <v>434.56</v>
     <v>Automobiles &amp; Auto Parts</v>
     <v>Stock</v>
-    <v>46168.605548240623</v>
+    <v>46168.683502117972</v>
     <v>177</v>
     <v>426.12</v>
-    <v>1601515828080</v>
+    <v>1609993623865</v>
     <v>TESLA, INC.</v>
     <v>TESLA, INC.</v>
     <v>430</v>
-    <v>389.745</v>
+    <v>391.8082</v>
     <v>426.01</v>
-    <v>426.42</v>
+    <v>428.6773</v>
     <v>3755724000</v>
     <v>TSLA</v>
     <v>TESLA, INC. (XNAS:TSLA)</v>
-    <v>11914353</v>
+    <v>24725470</v>
     <v>57284541</v>
     <v>2024</v>
   </rv>
@@ -6248,8 +6088,8 @@
     <v>1335</v>
     <v>771.66</v>
     <v>0.35249999999999998</v>
-    <v>1.8</v>
-    <v>2.0479999999999999E-3</v>
+    <v>-2.8</v>
+    <v>-3.186E-3</v>
     <v>GBp</v>
     <v>The Sage Group plc is a United Kingdom-based company. It provides accounting, financial, human resources (HR) and payroll technology for small and mid-sized businesses. Its segments include North America, United Kingdom, Ireland, Africa and APAC (UKIA) and Europe. Its products include Sage Accounting, Payroll software, Sage Intacct, Sage X3, Sage HR, Sage People, Sage Earth, Sage Ai and Payments and Banking. Sage Accounting is designed to enable small businesses operating in any industry, and accountants and bookkeepers, to manage customer data, accounts, and people in a single solution. Sage Intacct helps growing mid-sized organizations thrive in with digital world with solutions across accounting, planning, and analytics. Sage People is an HR and people management solution for mid-sized businesses. Sage Payroll is an intuitive solution that helps small businesses to run their payroll reliably and flexibly. Sage People is an HR and people management solution for mid-sized businesses.</v>
     <v>11074</v>
@@ -6260,20 +6100,20 @@
     <v>884.6</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46168.59489649297</v>
+    <v>46168.655232291407</v>
     <v>180</v>
     <v>870.8</v>
     <v>10571700000</v>
     <v>THE SAGE GROUP PLC.</v>
     <v>THE SAGE GROUP PLC.</v>
     <v>880.8</v>
-    <v>25.2393</v>
+    <v>25.1248</v>
     <v>878.8</v>
-    <v>880.6</v>
+    <v>876</v>
     <v>909118800</v>
     <v>SGE</v>
     <v>THE SAGE GROUP PLC. (XLON:SGE)</v>
-    <v>1471744</v>
+    <v>5230317</v>
     <v>5328690</v>
     <v>1988</v>
   </rv>
@@ -6296,11 +6136,11 @@
     <v>3</v>
     <v>Finance</v>
     <v>4</v>
-    <v>224.76929999999999</v>
+    <v>225.9</v>
     <v>98.010099999999994</v>
     <v>1.4319999999999999</v>
-    <v>-1.3</v>
-    <v>-5.8469999999999998E-3</v>
+    <v>2.5750000000000002</v>
+    <v>1.1581999999999999E-2</v>
     <v>USD</v>
     <v>Datadog Inc provides an AI-powered observability and security platform for cloud applications. Its Software as a Service (SaaS) platform integrates and automates infrastructure monitoring, application performance monitoring, log management, user experience monitoring, cloud security and service management. Its proprietary platform combines the power of metrics, traces, logs, user sessions, security signals, and other data from a single agent and over 1,000 integrations to provide a unified view of infrastructure, application performance and real-time events impacting performance. Its solutions include built for dynamic cloud and hybrid infrastructures, simple but not simplistic, integrated data platform, built for collaboration, cloud-agnostic, ubiquitous, and integrates with its customers complex environments. Its platform is used by industries to enable digital transformation and cloud migration, and drive collaboration among development, operations, security and business teams.</v>
     <v>8100</v>
@@ -6308,23 +6148,23 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>620 8th Avenue, 45th Floor,, NEW YORK, NY, 10018 US</v>
-    <v>223.93</v>
+    <v>225.9</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46168.605621885938</v>
+    <v>46168.683501250001</v>
     <v>183</v>
     <v>218.33</v>
-    <v>78674323404</v>
+    <v>80053669179</v>
     <v>DATADOG, INC.</v>
     <v>DATADOG, INC.</v>
     <v>222.39</v>
-    <v>559.96960000000001</v>
+    <v>569.78719999999998</v>
     <v>222.32</v>
-    <v>221.02</v>
+    <v>224.89500000000001</v>
     <v>355960200</v>
     <v>DDOG</v>
     <v>DATADOG, INC. (XNAS:DDOG)</v>
-    <v>915483</v>
+    <v>1691623</v>
     <v>6380940</v>
     <v>2010</v>
   </rv>
@@ -6350,8 +6190,8 @@
     <v>796.25</v>
     <v>520.26</v>
     <v>1.2312000000000001</v>
-    <v>-2.1</v>
-    <v>-3.441E-3</v>
+    <v>-0.56000000000000005</v>
+    <v>-9.1759999999999997E-4</v>
     <v>USD</v>
     <v>Meta Platforms, Inc. is building human connections, powered by artificial intelligence and immersive technologies. The Company's products enable people to connect and share with friends and family through mobile devices, personal computers, virtual reality (VR) and mixed reality (MR) headsets, augmented reality (AR), and wearables. It also helps people discover and learn about what is going on in the world around them, enabling people to share their experiences, ideas, photos, videos, and other content with audiences ranging from their closest family members and friends to the public at large. The Company's segments include Family of Apps (FoA) and Reality Labs (RL). FoA segment includes Facebook, Instagram, Messenger, WhatsApp and Threads. RL segment includes its virtual, augmented, and mixed reality related consumer hardware, software and content. Its product offerings in VR include its Meta Quest devices, as well as software and content available through the Meta Horizon Store.</v>
     <v>77986</v>
@@ -6362,20 +6202,20 @@
     <v>614.47</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46168.60560993047</v>
+    <v>46168.683587036721</v>
     <v>186</v>
-    <v>605.58500000000004</v>
-    <v>1543767331680</v>
+    <v>605.30010000000004</v>
+    <v>1547676503100</v>
     <v>META PLATFORMS, INC.</v>
     <v>META PLATFORMS, INC.</v>
     <v>608.98</v>
-    <v>18.446400000000001</v>
+    <v>18.493099999999998</v>
     <v>610.26</v>
-    <v>608.16</v>
+    <v>609.70000000000005</v>
     <v>2538423000</v>
     <v>META</v>
     <v>META PLATFORMS, INC. (XNAS:META)</v>
-    <v>3551414</v>
+    <v>6078134</v>
     <v>15159019</v>
     <v>2004</v>
   </rv>
@@ -6401,8 +6241,8 @@
     <v>278.56</v>
     <v>196</v>
     <v>1.4549000000000001</v>
-    <v>-1.44</v>
-    <v>-5.4069999999999995E-3</v>
+    <v>-2.7</v>
+    <v>-1.0138000000000001E-2</v>
     <v>USD</v>
     <v>Amazon.com, Inc. provides a range of products and services to customers. The products offered through its stores include merchandise and content it has purchased for resale and products offered by third-party sellers. The Company’s segments include North America, International and Amazon Web Services (AWS). It serves consumers through its online and physical stores and focuses on selection, price, and convenience. Customers access its offerings through its websites, mobile apps, Alexa, devices, streaming, and physically visiting its stores. It also manufactures and sells electronic devices, including Kindle, Fire tablet, Fire TV, Echo, Ring, Blink, and eero, and develops and produces media content. It serves developers and enterprises of all sizes, including start-ups, government agencies, and academic institutions, through AWS, which offers a set of on-demand technology services, including compute, storage, database, analytics, and machine learning, and other services.</v>
     <v>1575000</v>
@@ -6413,20 +6253,20 @@
     <v>269.3</v>
     <v>Diversified Retail</v>
     <v>Stock</v>
-    <v>46168.605584270314</v>
+    <v>46168.68354563594</v>
     <v>189</v>
-    <v>264.68</v>
-    <v>2849343296800</v>
+    <v>263.22000000000003</v>
+    <v>2835789338200</v>
     <v>AMAZON.COM, INC.</v>
     <v>AMAZON.COM, INC.</v>
     <v>267.58999999999997</v>
-    <v>31.655100000000001</v>
+    <v>31.5045</v>
     <v>266.32</v>
-    <v>264.88</v>
+    <v>263.62</v>
     <v>10757110000</v>
     <v>AMZN</v>
     <v>AMAZON.COM, INC. (XNAS:AMZN)</v>
-    <v>8866444</v>
+    <v>16786193</v>
     <v>43543716</v>
     <v>1996</v>
   </rv>
@@ -6452,8 +6292,8 @@
     <v>1653.53</v>
     <v>683.48</v>
     <v>1.8283</v>
-    <v>4.17</v>
-    <v>2.5540000000000003E-3</v>
+    <v>-15.37</v>
+    <v>-9.4129999999999995E-3</v>
     <v>USD</v>
     <v>ASML Holding N.V. is a holding company based in the Netherlands. The Company operates through its subsidiaries in the Netherlands, the United States, Italy, France, Germany, the United Kingdom, Ireland, Belgium, South Korea, Taiwan, Singapore, China, Hong Kong, Japan, Malaysia and Israel. The Company operates through one business segment which is engage in development, production, marketing, sales, upgrading and servicing of advanced semiconductor equipment systems, consisting of lithography, metrology and inspection systems. The Company offers TWINSCAN systems, equipped with lithography system with a mercury lamp as light source (i-line), Krypton Fluoride (KrF) and Argon Fluoride (ArF) light sources for processing wafers for manufacturing environments for which imaging at a small resolution is required. TWINSCAN systems also include immersion lithography systems (TWINSCAN immersion systems).</v>
     <v>43882</v>
@@ -6464,20 +6304,20 @@
     <v>1648.01</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46168.605590647654</v>
+    <v>46168.683534270313</v>
     <v>192</v>
-    <v>1617.86</v>
-    <v>635424955239</v>
+    <v>1604.25</v>
+    <v>627840549181</v>
     <v>ASML Holding NV</v>
     <v>ASML Holding NV</v>
     <v>1642.92</v>
-    <v>56.282200000000003</v>
+    <v>55.610399999999998</v>
     <v>1632.9</v>
-    <v>1637.07</v>
+    <v>1617.53</v>
     <v>388147700</v>
     <v>ASML</v>
     <v>ASML Holding NV (XNAS:ASML)</v>
-    <v>536781</v>
+    <v>919958</v>
     <v>1666315</v>
     <v>1994</v>
   </rv>
@@ -6503,8 +6343,8 @@
     <v>107.5</v>
     <v>85.760099999999994</v>
     <v>0.78939999999999999</v>
-    <v>-0.36499999999999999</v>
-    <v>-4.0489999999999996E-3</v>
+    <v>0.03</v>
+    <v>3.3279999999999996E-4</v>
     <v>USD</v>
     <v>The Charles Schwab Corporation is a savings and loan holding company. The Company, through its subsidiaries, engages in wealth management, securities brokerage, banking, asset management, custody, and financial advisory services. The Company provides financial services to individuals and institutional clients through two segments: Investor Services, and Advisor Services. The Investor Services segment provides retail brokerage, investment advisory, and banking and trust services to individual investors, and retirement plan and business services, as well as other corporate brokerage services, to businesses and their employees. The Advisor Services segment provides custodial, trading, banking and trust, and support services to independent registered investment advisors (RIAs), independent retirement advisors, and recordkeepers. Its products and services include brokerage, mutual funds, exchange-traded funds (ETFs), managed investing solutions, alternative investments, banking, and trust.</v>
     <v>33500</v>
@@ -6515,20 +6355,20 @@
     <v>90.42</v>
     <v>Investment Banking &amp; Investment Services</v>
     <v>Stock</v>
-    <v>46168.605626457815</v>
+    <v>46168.683565497653</v>
     <v>195</v>
     <v>89.49</v>
-    <v>156148235975</v>
+    <v>156835194300</v>
     <v>THE CHARLES SCHWAB CORPORATION</v>
     <v>THE CHARLES SCHWAB CORPORATION</v>
     <v>89.75</v>
-    <v>17.804600000000001</v>
+    <v>17.882899999999999</v>
     <v>90.15</v>
-    <v>89.784999999999997</v>
+    <v>90.18</v>
     <v>1739135000</v>
     <v>SCHW</v>
     <v>THE CHARLES SCHWAB CORPORATION (XNYS:SCHW)</v>
-    <v>1041144</v>
+    <v>2260619</v>
     <v>10307089</v>
     <v>1986</v>
   </rv>
@@ -6554,8 +6394,8 @@
     <v>203.71</v>
     <v>91.84</v>
     <v>1.3674999999999999</v>
-    <v>-1.07</v>
-    <v>-5.6950000000000004E-3</v>
+    <v>0.50509999999999999</v>
+    <v>2.6879999999999999E-3</v>
     <v>USD</v>
     <v>Twilio Inc. provides a customer engagement platform to build direct, personalized relationships with their customers everywhere in the world. Its platform provides developers with tools to build, scale, and deploy real-time communications within software applications. Its segments include Twilio Communications (Communications) and Twilio Segment (Segment). The Communications segment consists of a variety of application programming interfaces (APIs) and software solutions to optimize communications between its customers and their end users. Its key offerings in its Communications segment include Messaging, Voice, Email (includes Marketing Campaigns), Flex and User Authentication and Identity. Its Twilio Flex is a digital engagement center for the entire customer journey. Twilio Segment is a customer data platform that provides businesses with the tools to harness the power of contextual data by unifying real-time information collected throughout each customer’s journey into a profile.</v>
     <v>5558</v>
@@ -6563,23 +6403,23 @@
     <v>XNYS</v>
     <v>XNYS</v>
     <v>101 Spear Street, Fifth Floor, SAN FRANCISCO, CA, 94105 US</v>
-    <v>188.34</v>
+    <v>188.86</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46168.605593356253</v>
+    <v>46168.68355403906</v>
     <v>198</v>
     <v>180.36</v>
-    <v>28352882259</v>
+    <v>28591941328</v>
     <v>TWILIO INC.</v>
     <v>TWILIO INC.</v>
     <v>188.34</v>
-    <v>290.39330000000001</v>
+    <v>292.84179999999998</v>
     <v>187.88</v>
-    <v>186.81</v>
+    <v>188.38509999999999</v>
     <v>151773900</v>
     <v>TWLO</v>
     <v>TWILIO INC. (XNYS:TWLO)</v>
-    <v>463657</v>
+    <v>661107</v>
     <v>2986723</v>
     <v>2008</v>
   </rv>
@@ -6605,8 +6445,8 @@
     <v>155.47</v>
     <v>74.510000000000005</v>
     <v>0.61119999999999997</v>
-    <v>-0.59</v>
-    <v>-5.7630000000000008E-3</v>
+    <v>0.36</v>
+    <v>3.5170000000000002E-3</v>
     <v>USD</v>
     <v>Qualys, Inc. is a provider of a cloud-based platform delivering information technology (IT), security and compliance solutions. The Company’s integrated suite of IT, security and compliance solutions delivered on Qualys' Enterprise TruRisk Platform enables its customers to identify and manage their IT and operational technology (OT) assets, collect, and analyze large amounts of IT security data, recommend, and implement remediation actions and verify the implementation of such actions. The Company provides its solutions through a software-as-a-service model, primarily with renewable annual subscriptions. Its cloud platform offers an integrated suite of solutions that automates the lifecycle of asset discovery and management, security and compliance assessments, and remediation for an organization’s IT infrastructure and assets, whether such infrastructure and assets reside inside the organization, on their network perimeter, on endpoints or in the cloud.</v>
     <v>2683</v>
@@ -6614,23 +6454,23 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>919 E. Hillsdale Blvd., FOSTER CITY, CA, 94404 US</v>
-    <v>102.5</v>
+    <v>102.82</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46168.605605937497</v>
+    <v>46168.683557013283</v>
     <v>201</v>
     <v>99.694999999999993</v>
-    <v>3584387277</v>
+    <v>3617843437</v>
     <v>QUALYS, INC.</v>
     <v>QUALYS, INC.</v>
     <v>101.4</v>
-    <v>18.276499999999999</v>
+    <v>18.447099999999999</v>
     <v>102.37</v>
-    <v>101.78</v>
+    <v>102.73</v>
     <v>35217010</v>
     <v>QLYS</v>
     <v>QUALYS, INC. (XNAS:QLYS)</v>
-    <v>41616</v>
+    <v>124725</v>
     <v>829984</v>
     <v>1999</v>
   </rv>
@@ -6672,8 +6512,8 @@
     <v>421.48</v>
     <v>224.13</v>
     <v>1.4095</v>
-    <v>-2.7749999999999999</v>
-    <v>-1.1337999999999999E-2</v>
+    <v>-2.15</v>
+    <v>-8.7840000000000001E-3</v>
     <v>USD</v>
     <v>Adobe Inc. is a global technology company. The Company's products, services and solutions are used around the world to imagine, create, manage, deliver, measure, optimize and engage with content across surfaces and fuel digital experiences. Its segments include Digital Media, Digital Experience, and Publishing and Advertising. The Digital Media segment is centered around Adobe Creative Cloud and Adobe Document Cloud, which include Adobe Express, Adobe Firefly, Photoshop and other products, offering a variety of tools for creative professionals, communicators and other consumers. The Digital Experience segment provides an integrated platform and set of products, services and solutions through Adobe Experience Cloud. The Publishing and Advertising segment contains legacy products and services. In addition, its Adobe GenStudio solution allows businesses to simplify their content supply chain process with generative artificial intelligence (AI) capabilities and intelligent automation.</v>
     <v>31360</v>
@@ -6685,20 +6525,20 @@
     <v>206</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46168.605597152346</v>
+    <v>46168.683560983591</v>
     <v>207</v>
     <v>238.57</v>
-    <v>97810337000</v>
+    <v>98062962000</v>
     <v>ADOBE INC.</v>
     <v>ADOBE INC.</v>
     <v>242</v>
-    <v>14.103899999999999</v>
+    <v>14.1403</v>
     <v>244.76</v>
-    <v>241.98500000000001</v>
+    <v>242.61</v>
     <v>404200000</v>
     <v>ADBE</v>
     <v>ADOBE INC. (XNAS:ADBE)</v>
-    <v>900682</v>
+    <v>1425821</v>
     <v>4992158</v>
     <v>1997</v>
   </rv>
@@ -6724,8 +6564,8 @@
     <v>57.55</v>
     <v>31.635000000000002</v>
     <v>0.72819999999999996</v>
-    <v>-0.51</v>
-    <v>-1.2376E-2</v>
+    <v>-0.15</v>
+    <v>-3.64E-3</v>
     <v>USD</v>
     <v>Dynatrace, Inc. is an artificial intelligence (AI)-powered observability platform. It is advancing observability for digital businesses and transforming the complexity of modern digital ecosystems into business assets. It enables organizations to analyze and automate. Its platform combines broad and deep observability, continuous runtime application security, and advanced AI to support information technology (IT) operations, development, security, and business teams, enabling organizations to optimize cloud and IT operations, accelerate secure software delivery, and improve digital performance. Its platform's solutions include infrastructure observability, application observability, AI observability, digital experience, business analytics, software delivery, threat observability, application security, and log management. Its application security detects, analyses, and remediates runtime application vulnerabilities and attacks in real time.</v>
     <v>5600</v>
@@ -6733,23 +6573,23 @@
     <v>XNYS</v>
     <v>XNYS</v>
     <v>280 CONGRESS STREET, 11TH FLOOR, BOSTON, MA, 02210 US</v>
-    <v>40.984999999999999</v>
+    <v>41.064999999999998</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46168.605605578123</v>
+    <v>46168.683546642969</v>
     <v>210</v>
     <v>39.984999999999999</v>
-    <v>11863060990</v>
+    <v>11967992242</v>
     <v>DYNATRACE, INC.</v>
     <v>DYNATRACE, INC.</v>
     <v>40.880000000000003</v>
-    <v>75.961200000000005</v>
+    <v>76.633099999999999</v>
     <v>41.21</v>
-    <v>40.700000000000003</v>
+    <v>41.06</v>
     <v>291475700</v>
     <v>DT</v>
     <v>DYNATRACE, INC. (XNYS:DT)</v>
-    <v>539643</v>
+    <v>1069700</v>
     <v>7111700</v>
     <v>2014</v>
   </rv>
@@ -6772,11 +6612,11 @@
     <v>3</v>
     <v>Finance</v>
     <v>4</v>
-    <v>134.19</v>
+    <v>134.80000000000001</v>
     <v>70.12</v>
     <v>1.038</v>
-    <v>-1.4300999999999999</v>
-    <v>-1.0678E-2</v>
+    <v>0.79</v>
+    <v>5.8989999999999997E-3</v>
     <v>USD</v>
     <v>Fortinet, Inc. is engaged in cybersecurity, driving the convergence of networking and security. The Company's integrated platform, Fortinet Security Fabric, spans secure networking, unified secure access service edge (SASE), and artificial intelligence (AI)-driven security operations (SecOps). Its products and services include FortiOS, FortiASIC, FortiCloud, FortiAI, FortiEndpoint, and OT Security. The FortiGuard Labs is a cybersecurity threat intelligence and research organization comprised of experienced threat hunters, researchers, analysts, engineers, and data scientists who develop and utilize machine learning and AI technologies. FortiGuard and Other Security Services is an AI-powered security that is integrated as part of the Fortinet Security Fabric to deliver detection and enforcement across the entire attack surface. FortiCare Technical Support Service is a technical support service which provides customers with access to operations and maintenance of Fortinet solutions.</v>
     <v>15311</v>
@@ -6784,23 +6624,23 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>909 Kifer Road, SUNNYVALE, CA, 94086 US</v>
-    <v>133.59020000000001</v>
+    <v>134.80000000000001</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46168.605609640625</v>
+    <v>46168.683558668752</v>
     <v>213</v>
     <v>130.6</v>
-    <v>97075839735</v>
+    <v>98702392448</v>
     <v>FORTINET, INC.</v>
     <v>FORTINET, INC.</v>
     <v>133.37</v>
-    <v>51.189900000000002</v>
+    <v>52.047600000000003</v>
     <v>133.93</v>
-    <v>132.4999</v>
+    <v>134.72</v>
     <v>732648400</v>
     <v>FTNT</v>
     <v>FORTINET, INC. (XNAS:FTNT)</v>
-    <v>807410</v>
+    <v>1465635</v>
     <v>5987731</v>
     <v>2000</v>
   </rv>
@@ -6826,8 +6666,8 @@
     <v>38.39</v>
     <v>8.18</v>
     <v>3.3182</v>
-    <v>-0.5</v>
-    <v>-1.3436999999999999E-2</v>
+    <v>-1.4999999999999999E-2</v>
+    <v>-4.0309999999999999E-4</v>
     <v>USD</v>
     <v>SkyWater Technology, Inc. is an independent, pure-play technology foundry that offers advanced semiconductor development and manufacturing services. The Company’s Technology-as-a-Service (TaaS) model leverages a foundation of proprietary technology, engineering know-how capabilities, and microelectronics manufacturing capacity to co-develop process technology intellectual property (IP) with its customers that enable disruptive concepts through its Advanced Technology Services (ATS) for diverse microelectronics (integrated circuits (ICs)) and related micro- and nanotechnology applications. In addition to differentiated technology development services, it supports customers with volume production of ICs for high-growth markets through its Wafer Services. Its Wafer Services include the manufacture of silicon-based analog and mixed-signal ICs for its end markets. Through its ATS model, it specializes in co-creating advanced solutions with its customers that directly serve its end markets.</v>
     <v>1551</v>
@@ -6838,20 +6678,20 @@
     <v>37.5</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46168.605593957815</v>
+    <v>46168.683401770315</v>
     <v>216</v>
     <v>36.450000000000003</v>
-    <v>1806300866</v>
+    <v>1830165097</v>
     <v>SKYWATER TECHNOLOGY, INC.</v>
     <v>SKYWATER TECHNOLOGY, INC.</v>
     <v>37.270000000000003</v>
-    <v>15.735799999999999</v>
+    <v>15.9437</v>
     <v>37.21</v>
-    <v>36.71</v>
+    <v>37.195</v>
     <v>49204600</v>
     <v>SKYT</v>
     <v>SKYWATER TECHNOLOGY, INC. (XNAS:SKYT)</v>
-    <v>194305</v>
+    <v>344785</v>
     <v>1272966</v>
     <v>2016</v>
   </rv>
@@ -6877,8 +6717,8 @@
     <v>82.663499999999999</v>
     <v>65.353800000000007</v>
     <v>0.36109999999999998</v>
-    <v>-0.98499999999999999</v>
-    <v>-1.2089000000000001E-2</v>
+    <v>-1.0101</v>
+    <v>-1.2397E-2</v>
     <v>USD</v>
     <v>The Coca-Cola Company is a beverage company. The Company's segments include Europe, Middle East and Africa (EMEA); Latin America; North America; Asia Pacific, and Bottling Investments. It sells multiple brands across several beverage categories worldwide. Its portfolio of sparkling soft drink brands includes Coca-Cola, Sprite and Fanta. Its water, sports, coffee and tea brands include Dasani, smartwater, vitaminwater, Topo Chico, BODYARMOR, Powerade, Costa, Georgia, Fuze Tea, Gold Peak and Ayataka. Its juice, value-added dairy and plant-based beverage brands include Minute Maid, Simply, innocent, Del Valle, fairlife and Santa Clara. It operates in two lines of business: concentrate operations and finished product operations. Its concentrate operations sell beverage concentrates, syrups, including fountain syrups, and certain finished beverages to authorized bottling operations. Its finished product operations sell sparkling soft drinks and a variety of other finished beverages.</v>
     <v>65900</v>
@@ -6889,20 +6729,20 @@
     <v>81.599999999999994</v>
     <v>Beverages</v>
     <v>Stock</v>
-    <v>46168.60563905078</v>
+    <v>46168.683601087498</v>
     <v>219</v>
-    <v>80.305000000000007</v>
-    <v>346328288590</v>
+    <v>80.265000000000001</v>
+    <v>346220296291</v>
     <v>THE COCA-COLA COMPANY</v>
     <v>THE COCA-COLA COMPANY</v>
     <v>80.97</v>
-    <v>25.340800000000002</v>
+    <v>25.332899999999999</v>
     <v>81.48</v>
-    <v>80.495000000000005</v>
+    <v>80.469899999999996</v>
     <v>4302482000</v>
     <v>KO</v>
     <v>THE COCA-COLA COMPANY (XNYS:KO)</v>
-    <v>2980022</v>
+    <v>5198183</v>
     <v>14263576</v>
     <v>1919</v>
   </rv>
@@ -6928,8 +6768,8 @@
     <v>87.88</v>
     <v>27.26</v>
     <v>1.9946999999999999</v>
-    <v>-0.69</v>
-    <v>-1.2770999999999999E-2</v>
+    <v>-0.22</v>
+    <v>-4.0720000000000001E-3</v>
     <v>USD</v>
     <v>Symbotic Inc. is an automation technology company, which focuses on reimagining the supply chain with its end-to-end, artificial intelligence-powered robotic and software platform. It is engaged in developing, commercializing, and deploying innovative and comprehensive technology solutions that improve supply chain operations. The Company automates the processing of pallets, cases and individual items in warehouses. Its systems enhance operations at the front end of the supply chain and therefore benefit all supply partners further down the chain, irrespective of fulfillment strategy. Its robotic-based automation systems, which include hardware and essential software, move, store and sort cases and reach in warehouses. Its systems are operational in a number of retailers, including Walmart, wholesale distributors, including C&amp;S Wholesale Grocers, and are being deployed in GreenBox Systems LLC, which is doing business as Exol (Exol), its warehouse-as-a-service joint venture.</v>
     <v>2000</v>
@@ -6940,20 +6780,20 @@
     <v>56.36</v>
     <v>Machinery, Equipment &amp; Components</v>
     <v>Stock</v>
-    <v>46168.605617164059</v>
+    <v>46168.68355366875</v>
     <v>222</v>
     <v>52.8</v>
-    <v>32148380712</v>
+    <v>32431652908</v>
     <v>SYMBOTIC INC.</v>
     <v>SYMBOTIC INC.</v>
     <v>55.52</v>
     <v>0</v>
     <v>54.03</v>
-    <v>53.34</v>
+    <v>53.81</v>
     <v>602706800</v>
     <v>SYM</v>
     <v>SYMBOTIC INC. (XNAS:SYM)</v>
-    <v>952793</v>
+    <v>1590479</v>
     <v>1811267</v>
     <v>2022</v>
   </rv>
@@ -6979,8 +6819,8 @@
     <v>257.08999999999997</v>
     <v>110.36</v>
     <v>1.0374000000000001</v>
-    <v>-2.94</v>
-    <v>-2.2943999999999999E-2</v>
+    <v>-2.88</v>
+    <v>-2.2475000000000002E-2</v>
     <v>USD</v>
     <v>Workday, Inc. is an enterprise artificial intelligence (AI) platform for managing people, money, and agents. The Company provides organizations with cloud solutions powered by artificial intelligence (AI) to solve business challenges, including supporting and empowering the workforce, managing finances and spending. It offers a suite of cloud-based enterprise solutions that address the needs of the C-suite on a platform designed to be open, extensible, and configurable, allowing integration with other applications and the ability for customers and partners to build custom applications. It offers Workday Build, which is an open developer platform that provides customers and partners with the ability to create and share AI-powered solutions. It serves financial services, government, healthcare, higher education, hospitality, manufacturing, professional and business services, retail, technology and media, and transportation.</v>
     <v>20834</v>
@@ -6991,20 +6831,20 @@
     <v>127.06</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46168.605627036719</v>
+    <v>46168.683576921096</v>
     <v>225</v>
     <v>122.18</v>
-    <v>30924400000</v>
+    <v>30939220000</v>
     <v>WORKDAY, INC.</v>
     <v>WORKDAY, INC.</v>
     <v>126.07</v>
-    <v>39.082299999999996</v>
+    <v>39.100999999999999</v>
     <v>128.13999999999999</v>
-    <v>125.2</v>
+    <v>125.26</v>
     <v>247000000</v>
     <v>WDAY</v>
     <v>WORKDAY, INC. (XNAS:WDAY)</v>
-    <v>1157261</v>
+    <v>1963570</v>
     <v>5179599</v>
     <v>2012</v>
   </rv>
@@ -7030,8 +6870,8 @@
     <v>21.4</v>
     <v>11.81</v>
     <v>0.85129999999999995</v>
-    <v>-0.34</v>
-    <v>-1.8172000000000001E-2</v>
+    <v>-0.1207</v>
+    <v>-6.4510000000000001E-3</v>
     <v>USD</v>
     <v>SentinelOne, Inc. is an artificial intelligence (AI)-powered cybersecurity provider. The Company’s Singularity Platform delivers AI-powered autonomous threat prevention, detection, response, and exposure management capabilities across an organization’s endpoints, cloud workloads, and identity credentials. The Company’s Singularity platform ingests, correlates, and queries petabytes of structured and unstructured data from a myriad of ever-expanding disparate external and internal sources in real time. Its distributed AI models run both locally on every endpoint and every cloud workload, as well as on its cloud platform. The Company through PingSafe Pte. Ltd. (PingSafe), which is a cloud native application protection platform (CNAPP) to bolster its cloud security product suite. By adding PingSafe’s CNAPP to its Cloud Workload Security (CWS), it provides enterprises with a comprehensive cloud security coverage that drives security, improved posture, and autonomous protection.</v>
     <v>2900</v>
@@ -7042,19 +6882,19 @@
     <v>18.669799999999999</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46168.605586226564</v>
+    <v>46168.683557453121</v>
     <v>228</v>
     <v>18.21</v>
-    <v>6273026177</v>
+    <v>6347913201</v>
     <v>SENTINELONE, INC.</v>
     <v>SENTINELONE, INC.</v>
     <v>18.649999999999999</v>
     <v>18.71</v>
-    <v>18.37</v>
+    <v>18.589300000000001</v>
     <v>341482100</v>
     <v>S</v>
     <v>SENTINELONE, INC. (XNYS:S)</v>
-    <v>2210641</v>
+    <v>4328478</v>
     <v>6933336</v>
     <v>2013</v>
   </rv>
@@ -7080,8 +6920,8 @@
     <v>120.79</v>
     <v>62.3</v>
     <v>0.97330000000000005</v>
-    <v>-2.73</v>
-    <v>-2.2673000000000002E-2</v>
+    <v>-2.57</v>
+    <v>-2.1343999999999998E-2</v>
     <v>USD</v>
     <v>Cisco Systems, Inc. designs and sells a range of technologies that power the Internet. The Company is integrating its product portfolios across networking, security, collaboration, applications and cloud. The Company's segments include the Americas; Europe, Middle East, and Africa (EMEA), and Asia Pacific, Japan, and China (APJC). Its Networking product category represents its core networking technologies of switching, routing, wireless, fifth generation (5G), silicon, optics solutions and compute products. Its Security product category consists of its cloud and application security, industrial security, network security, and user and device security offerings. Its Collaboration product category consists of its meetings, collaboration devices, calling, contact center and platform as a service (CPaaS) offering. Its Observability product category consists of its full stack observability offerings.</v>
     <v>86200</v>
@@ -7092,20 +6932,20 @@
     <v>120.77</v>
     <v>Communications &amp; Networking</v>
     <v>Stock</v>
-    <v>46168.60562790469</v>
+    <v>46168.683570578127</v>
     <v>231</v>
     <v>117.095</v>
-    <v>463828070800</v>
+    <v>464458700400</v>
     <v>CISCO SYSTEMS, INC.</v>
     <v>CISCO SYSTEMS, INC.</v>
     <v>120.48</v>
-    <v>39.2136</v>
+    <v>39.2669</v>
     <v>120.41</v>
-    <v>117.68</v>
+    <v>117.84</v>
     <v>3941435000</v>
     <v>CSCO</v>
     <v>CISCO SYSTEMS, INC. (XNAS:CSCO)</v>
-    <v>6543783</v>
+    <v>11350161</v>
     <v>24599703</v>
     <v>2021</v>
   </rv>
@@ -7131,8 +6971,8 @@
     <v>261.41199999999998</v>
     <v>139.57060000000001</v>
     <v>0.85740000000000005</v>
-    <v>-6.94</v>
-    <v>-2.6633E-2</v>
+    <v>-1.81</v>
+    <v>-6.9459999999999999E-3</v>
     <v>USD</v>
     <v>Palo Alto Networks, Inc. is a global artificial intelligence (AI) cybersecurity company, with a comprehensive portfolio of cybersecurity solutions and platforms across network, cloud, security operations, AI and Identity. Its network security platform includes Secure Access Service Edge (SASE), Next-Generation Firewalls, Cloud Delivered Security Services (CDSS), Prisma AIRS, and Strata Cloud Manager (SCM). It delivers security operations capabilities that unifies standalone Security Information and Event Management (SIEM) tools, endpoint security, security automation, cloud detection and response (CDR), as well as attack surface management (ASM) capabilities on its Cortex platform. It delivers comprehensive security across the cloud application development lifecycle through Cortex Cloud. Its Unit 42 brings together expertise across threat research, incident response, and security consulting to deliver intelligence-driven, response-ready outcomes that help customers reduce cyber risk.</v>
     <v>17027</v>
@@ -7143,20 +6983,20 @@
     <v>259.83999999999997</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46168.605639247653</v>
+    <v>46168.683593564063</v>
     <v>234</v>
     <v>250.77</v>
-    <v>205702040000</v>
+    <v>209862470000</v>
     <v>PALO ALTO NETWORKS, INC.</v>
     <v>PALO ALTO NETWORKS, INC.</v>
     <v>257.89999999999998</v>
-    <v>140.44300000000001</v>
+    <v>143.2835</v>
     <v>260.58</v>
-    <v>253.64</v>
+    <v>258.77</v>
     <v>811000000</v>
     <v>PANW</v>
     <v>PALO ALTO NETWORKS, INC. (XNAS:PANW)</v>
-    <v>1873687</v>
+    <v>3364248</v>
     <v>7476247</v>
     <v>2005</v>
   </rv>
@@ -7198,8 +7038,8 @@
     <v>324.89999999999998</v>
     <v>212.34</v>
     <v>0.58960000000000001</v>
-    <v>-7.3</v>
-    <v>-2.8757999999999999E-2</v>
+    <v>-3.0150000000000001</v>
+    <v>-1.1878E-2</v>
     <v>USD</v>
     <v>International Business Machines Corporation is a provider of global hybrid cloud and artificial intelligence (AI) and consulting expertise. The Company’s segments include Software, Consulting, Infrastructure and Financing. The Software segment includes hybrid cloud and AI platforms, which allow clients to realize their digital and AI transformations across the applications, data, and environments in which they operate. The Consulting segment focuses on integrating skills on strategy, experience, technology and operations by domain and industry. The Infrastructure segment is focused on the hybrid cloud infrastructure market, providing on-premises and cloud-based server and storage solutions. In addition, it offers a portfolio of life-cycle services for hybrid cloud infrastructure deployment. The Financing segment provides client and commercial financing, facilitating its clients’ acquisition of hardware, software and services. It helps clients in more than 175 countries.</v>
     <v>286800</v>
@@ -7211,20 +7051,20 @@
     <v>239</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46168.605640068752</v>
+    <v>46168.683590346875</v>
     <v>240</v>
     <v>245.45</v>
-    <v>231719321862</v>
+    <v>235746730372</v>
     <v>INTERNATIONAL BUSINESS MACHINES CORPORATION</v>
     <v>INTERNATIONAL BUSINESS MACHINES CORPORATION</v>
     <v>254.73</v>
-    <v>19.729500000000002</v>
+    <v>20.072399999999998</v>
     <v>253.84</v>
-    <v>246.54</v>
+    <v>250.82499999999999</v>
     <v>939885300</v>
     <v>IBM</v>
     <v>INTERNATIONAL BUSINESS MACHINES CORPORATION (XNYS:IBM)</v>
-    <v>3399060</v>
+    <v>4990868</v>
     <v>8239166</v>
     <v>1911</v>
   </rv>
@@ -7250,8 +7090,8 @@
     <v>84.64</v>
     <v>25.89</v>
     <v>3.1023000000000001</v>
-    <v>-2.11</v>
-    <v>-3.3155000000000004E-2</v>
+    <v>0.16</v>
+    <v>2.5140000000000002E-3</v>
     <v>USD</v>
     <v>IonQ, Inc. is engaged in the quantum computing and networking industry, delivering high-performance systems capable of solving complex commercial and research use cases. Its generation quantum computers, IonQ Forte and IonQ Forte Enterprise, are cutting-edge systems, boasting 36 algorithmic qubits. It sells specialized quantum computing and networking hardware together with related maintenance and support. It also sells access to several quantum computers of various qubit capacities and is in the process of researching and developing technologies for quantum computers with increasing computational capabilities. It makes access to its quantum computers available via three cloud platforms, Amazon Web Services' (AWS) Amazon Braket, Microsoft's Azure Quantum and Google's Cloud Marketplace, and also to select customers via its own cloud service. Its product portfolio also includes quantum key distribution (QKD) systems, quantum random number generators (QRNGs), and single-photon detectors.</v>
     <v>1132</v>
@@ -7262,20 +7102,20 @@
     <v>65</v>
     <v>Computers, Phones &amp; Household Electronics</v>
     <v>Stock</v>
-    <v>46168.605618344533</v>
+    <v>46168.683612071094</v>
     <v>243</v>
     <v>60.52</v>
-    <v>22967303100</v>
+    <v>23814626000</v>
     <v>IONQ, INC.</v>
     <v>IONQ, INC.</v>
     <v>64.28</v>
-    <v>1050</v>
+    <v>1088.7372</v>
     <v>63.64</v>
-    <v>61.53</v>
+    <v>63.8</v>
     <v>373270000</v>
     <v>IONQ</v>
     <v>IONQ, INC. (XNYS:IONQ)</v>
-    <v>12466432</v>
+    <v>19113186</v>
     <v>34430022</v>
     <v>2020</v>
   </rv>
@@ -7321,8 +7161,8 @@
     <v>444.72</v>
     <v>182.43</v>
     <v>1.5371999999999999</v>
-    <v>-16.63</v>
-    <v>-5.0991999999999996E-2</v>
+    <v>-17.649999999999999</v>
+    <v>-5.4120000000000001E-2</v>
     <v>USD</v>
     <v>MongoDB, Inc. is a developer data platform company. Its developer data platform is a globally distributed operational database integrated with a set of data services that allow development teams to address the growing variety of application requirements. Its customers can implement its developer data platform as a managed service offering, or they can choose a self-managed option. Its MongoDB Atlas is its managed multi-cloud database-as-a-service (DBaaS) offering that includes an integrated set of databases and related services. Atlas Vector Search allows the integration of an operational database and vector search in a unified, fully managed platform. MongoDB Enterprise Advanced is its proprietary self-managed commercial offering for enterprise customers that can run in the cloud, on-premises or in a hybrid environment. It also provides professional services for its customers.</v>
     <v>5636</v>
@@ -7334,20 +7174,20 @@
     <v>249</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46168.605586863283</v>
+    <v>46168.683578378907</v>
     <v>250</v>
-    <v>307.81</v>
-    <v>24914728335</v>
+    <v>306.50229999999999</v>
+    <v>24832618406</v>
     <v>MONGODB, INC.</v>
     <v>MONGODB, INC.</v>
     <v>313.04000000000002</v>
     <v>0</v>
     <v>326.13</v>
-    <v>309.5</v>
+    <v>308.48</v>
     <v>80499930</v>
     <v>MDB</v>
     <v>MONGODB, INC. (XNAS:MDB)</v>
-    <v>814118</v>
+    <v>1408140</v>
     <v>1596784</v>
     <v>2007</v>
   </rv>
@@ -7373,8 +7213,8 @@
     <v>18.709</v>
     <v>0.91510000000000002</v>
     <v>3.1711</v>
-    <v>-0.66910000000000003</v>
-    <v>-5.2069999999999998E-2</v>
+    <v>-0.90010000000000001</v>
+    <v>-7.0046999999999998E-2</v>
     <v>USD</v>
     <v>Lightwave Logic, Inc. is a technology platform company leveraging its proprietary engineered electro-optic (EO) polymers known as Perkinamine, to transmit data at higher speeds with less power in a small form factor. The Company’s organic polymers allow it to create next-generation photonic EO devices that convert data from electrical signals into light/optical signals for applications in telecommunications, and for data transmission potentially used to support generative Artificial Intelligence. It designs its own proprietary materials for electro-optical modulation devices. Electro-optical modulators convert data from electric signals into optical signals that can then be transmitted over high-speed fiber-optic cables. It is focused on testing and demonstrating the manufacturability and reliability of its devices. In polymer photonics, polymer devices such as modulators, waveguides, and multiplexers can be fabricated on to a silicon platform.</v>
     <v>34</v>
@@ -7385,20 +7225,20 @@
     <v>13.3</v>
     <v>Electronic Equipment &amp; Parts</v>
     <v>Stock</v>
-    <v>46168.60554841406</v>
+    <v>46168.683469039061</v>
     <v>253</v>
-    <v>11.81</v>
-    <v>1876828199</v>
+    <v>11.69</v>
+    <v>1841235812</v>
     <v>LIGHTWAVE LOGIC, INC.</v>
     <v>LIGHTWAVE LOGIC, INC.</v>
     <v>13.1</v>
     <v>0</v>
     <v>12.85</v>
-    <v>12.180899999999999</v>
+    <v>11.9499</v>
     <v>154079600</v>
     <v>LWLG</v>
     <v>LIGHTWAVE LOGIC, INC. (XNAS:LWLG)</v>
-    <v>2747657</v>
+    <v>4617481</v>
     <v>9859144</v>
     <v>1997</v>
   </rv>
@@ -7424,8 +7264,8 @@
     <v>20.81</v>
     <v>3.87</v>
     <v>0.75739999999999996</v>
-    <v>-1.085</v>
-    <v>-7.4366000000000002E-2</v>
+    <v>-1.38</v>
+    <v>-9.4585000000000002E-2</v>
     <v>USD</v>
     <v>POET Technologies Inc. is a design and development company. It offers high-speed optical engines, light source products and custom optical modules to the artificial intelligence (AI) systems market and to hyperscale data centers. Its photonic integration solutions are based on the POET Optical Interposer, a novel, patented platform that allows the integration of electronic and photonic devices into a single chip using wafer-level semiconductor manufacturing techniques. Its Optical Interposer-based products consume less power than comparable products, are smaller in size and are readily scalable to high production volumes. In addition, it has designed and produced novel light source products for chip-to-chip data communication within and between AI servers, the next frontier for solving bandwidth and latency problems in AI systems. Its Optical Interposer platform solves device integration challenges across a range of communication, computing and sensing applications.</v>
     <v>180</v>
@@ -7436,494 +7276,25 @@
     <v>15.074999999999999</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46168.605639710157</v>
+    <v>46168.683615948437</v>
     <v>256</v>
     <v>13.11</v>
-    <v>2330900877</v>
+    <v>2279985234</v>
     <v>POET Technologies Inc.</v>
     <v>POET Technologies Inc.</v>
     <v>15</v>
     <v>0</v>
     <v>14.59</v>
-    <v>13.505000000000001</v>
+    <v>13.21</v>
     <v>172595400</v>
     <v>POET</v>
     <v>POET Technologies Inc. (XNAS:POET)</v>
-    <v>21230342</v>
+    <v>30461204</v>
     <v>70503017</v>
     <v>2010</v>
   </rv>
   <rv s="2">
     <v>257</v>
-  </rv>
-  <rv s="1">
-    <v>en-GB</v>
-    <v>a1mou2</v>
-    <v>268435456</v>
-    <v>1</v>
-    <v>Powered by Refinitiv</v>
-    <v>0</v>
-    <v>APPLE INC. (XNAS:AAPL)</v>
-    <v>2</v>
-    <v>3</v>
-    <v>Finance</v>
-    <v>4</v>
-    <v>303.2</v>
-    <v>193.46</v>
-    <v>1.0683</v>
-    <v>2.2450000000000001</v>
-    <v>7.509E-3</v>
-    <v>USD</v>
-    <v>Apple Inc. designs, manufactures and markets smartphones, personal computers, tablets, wearables and accessories, and sells a variety of related services. Its product categories include iPhone, Mac, iPad, Wearables, Home and Accessories. Its services include advertising, AppleCare, cloud services, digital content, and payment services. The Company operates various platforms, including the App Store, that allow customers to discover and download applications and digital content, such as books, music, video, games and podcasts. It also offers digital content through subscription-based services, including Apple Arcade, Apple Fitness+, Apple Music, Apple News+, and Apple TV+. Its wearables include smartwatches, wireless headphones, and spatial computers. Its products include iPhone 16 Pro, iPhone 16, iPhone 15, iPhone 14, iPhone SE, MacBook Air, MacBook Pro, iMac, Mac mini, Mac Studio, Mac Pro, iPad Pro, iPad Air, AirPods, AirPods Pro, AirPods Max, Apple TV, Apple Vision Pro and others.</v>
-    <v>166000</v>
-    <v>Nasdaq Stock Market</v>
-    <v>XNAS</v>
-    <v>XNAS</v>
-    <v>One Apple Park Way, CUPERTINO, CA, 95014 US</v>
-    <v>302.37</v>
-    <v>Computers, Phones &amp; Household Electronics</v>
-    <v>Stock</v>
-    <v>46162.757255693752</v>
-    <v>148</v>
-    <v>298.08999999999997</v>
-    <v>4424053142400</v>
-    <v>APPLE INC.</v>
-    <v>APPLE INC.</v>
-    <v>298.38</v>
-    <v>36.582700000000003</v>
-    <v>298.97000000000003</v>
-    <v>301.21499999999997</v>
-    <v>14687360000</v>
-    <v>AAPL</v>
-    <v>APPLE INC. (XNAS:AAPL)</v>
-    <v>18926461</v>
-    <v>47976127</v>
-    <v>1977</v>
-  </rv>
-  <rv s="2">
-    <v>259</v>
-  </rv>
-  <rv s="1">
-    <v>en-GB</v>
-    <v>a1slm7</v>
-    <v>268435456</v>
-    <v>1</v>
-    <v>Powered by Refinitiv</v>
-    <v>0</v>
-    <v>META PLATFORMS, INC. (XNAS:META)</v>
-    <v>2</v>
-    <v>3</v>
-    <v>Finance</v>
-    <v>4</v>
-    <v>796.25</v>
-    <v>520.26</v>
-    <v>1.2390000000000001</v>
-    <v>2.0036999999999998</v>
-    <v>3.3250000000000003E-3</v>
-    <v>USD</v>
-    <v>Meta Platforms, Inc. is building human connections, powered by artificial intelligence and immersive technologies. The Company's products enable people to connect and share with friends and family through mobile devices, personal computers, virtual reality (VR) and mixed reality (MR) headsets, augmented reality (AR), and wearables. It also helps people discover and learn about what is going on in the world around them, enabling people to share their experiences, ideas, photos, videos, and other content with audiences ranging from their closest family members and friends to the public at large. The Company's segments include Family of Apps (FoA) and Reality Labs (RL). FoA segment includes Facebook, Instagram, Messenger, WhatsApp and Threads. RL segment includes its virtual, augmented, and mixed reality related consumer hardware, software and content. Its product offerings in VR include its Meta Quest devices, as well as software and content available through the Meta Horizon Store.</v>
-    <v>77986</v>
-    <v>Nasdaq Stock Market</v>
-    <v>XNAS</v>
-    <v>XNAS</v>
-    <v>1 Meta Way, MENLO PARK, CA, 94025 US</v>
-    <v>608</v>
-    <v>Software &amp; IT Services</v>
-    <v>Stock</v>
-    <v>46162.757256921097</v>
-    <v>186</v>
-    <v>597.80999999999995</v>
-    <v>1534765322195</v>
-    <v>META PLATFORMS, INC.</v>
-    <v>META PLATFORMS, INC.</v>
-    <v>600.28</v>
-    <v>18.338899999999999</v>
-    <v>602.61</v>
-    <v>604.61369999999999</v>
-    <v>2538423000</v>
-    <v>META</v>
-    <v>META PLATFORMS, INC. (XNAS:META)</v>
-    <v>6912875</v>
-    <v>15330478</v>
-    <v>2004</v>
-  </rv>
-  <rv s="2">
-    <v>261</v>
-  </rv>
-  <rv s="1">
-    <v>en-GB</v>
-    <v>c2mtww</v>
-    <v>268435456</v>
-    <v>1</v>
-    <v>Powered by Refinitiv</v>
-    <v>0</v>
-    <v>ROBINHOOD MARKETS, INC. (XNAS:HOOD)</v>
-    <v>2</v>
-    <v>3</v>
-    <v>Finance</v>
-    <v>4</v>
-    <v>153.85990000000001</v>
-    <v>62.631799999999998</v>
-    <v>2.29</v>
-    <v>2.0249999999999999</v>
-    <v>2.7306E-2</v>
-    <v>USD</v>
-    <v>Robinhood Markets, Inc. is creating a financial services platform for everyone, regardless of their wealth, income, or background. It uses technology to provide access to the financial system. Its offerings include Brokerage, Robinhood Crypto, Custody, Robinhood Wallet, Robinhood Gold, and Robinhood Gold Card. Its Brokerage services include investing, options trading, fractional trading, recurring investment, access to investing on margin, fully paid securities lending, cash sweep, instant withdrawals, Robinhood retirement, 24-hour market, joint investing accounts, and event contracts. It also offers a variety of ways for its customers to grow their financial knowledge, including Robinhood Learn, In-App Education, Newsfeeds, Sherwood Snacks, and Crypto Learn and Earn. Its self-clearing system, order routing system, data platform, and other back-end infrastructure deliver the capabilities that allow its customers to focus on investing, saving and spending.</v>
-    <v>2900</v>
-    <v>Nasdaq Stock Market</v>
-    <v>XNAS</v>
-    <v>XNAS</v>
-    <v>85 Willow Road, MENLO PARK, CA, 94025 US</v>
-    <v>76.349999999999994</v>
-    <v>Financial Technology (Fintech) &amp; Infrastructure</v>
-    <v>Stock</v>
-    <v>46162.757236967191</v>
-    <v>136</v>
-    <v>73.75</v>
-    <v>68604981043</v>
-    <v>ROBINHOOD MARKETS, INC.</v>
-    <v>ROBINHOOD MARKETS, INC.</v>
-    <v>74.75</v>
-    <v>42.381500000000003</v>
-    <v>74.16</v>
-    <v>76.185000000000002</v>
-    <v>900505100</v>
-    <v>HOOD</v>
-    <v>ROBINHOOD MARKETS, INC. (XNAS:HOOD)</v>
-    <v>11478018</v>
-    <v>31280816</v>
-    <v>2013</v>
-  </rv>
-  <rv s="2">
-    <v>263</v>
-  </rv>
-  <rv s="1">
-    <v>en-GB</v>
-    <v>a1yv52</v>
-    <v>268435456</v>
-    <v>1</v>
-    <v>Powered by Refinitiv</v>
-    <v>0</v>
-    <v>NVIDIA CORPORATION (XNAS:NVDA)</v>
-    <v>2</v>
-    <v>3</v>
-    <v>Finance</v>
-    <v>4</v>
-    <v>236.54</v>
-    <v>129.16</v>
-    <v>2.2471999999999999</v>
-    <v>4.05</v>
-    <v>1.8357999999999999E-2</v>
-    <v>USD</v>
-    <v>NVIDIA Corporation is an artificial intelligence (AI) infrastructure company. The Company is engaged in accelerated computing to help solve the challenging computational problems. Its segments include Compute &amp; Networking and Graphics. The Compute &amp; Networking segment includes its Data Center accelerated computing and networking platforms and AI solutions and software, and automotive platforms and autonomous and electric vehicle solutions, including software. The Graphics segment includes GeForce GPUs for gaming and personal computers (PCs), and Quadro/NVIDIA RTX GPUs for enterprise workstation graphics. Its technology stack includes the foundational NVIDIA CUDA development platform that runs on all NVIDIA GPUs, as well as hundreds of domain-specific software libraries, frameworks, algorithms, software development kits (SDKs), and application programming interfaces (APIs). Its platforms address four markets, which include Data Center, Gaming, Professional Visualization, and Automotive.</v>
-    <v>42000</v>
-    <v>Nasdaq Stock Market</v>
-    <v>XNAS</v>
-    <v>XNAS</v>
-    <v>2788 San Tomas Expressway, SANTA CLARA, CA, 95051 US</v>
-    <v>226.13</v>
-    <v>Semiconductors &amp; Semiconductor Equipment</v>
-    <v>Stock</v>
-    <v>46162.757250613278</v>
-    <v>154</v>
-    <v>220.495</v>
-    <v>5441384269800</v>
-    <v>NVIDIA CORPORATION</v>
-    <v>NVIDIA CORPORATION</v>
-    <v>223</v>
-    <v>45.832099999999997</v>
-    <v>220.61</v>
-    <v>224.66</v>
-    <v>24220530000</v>
-    <v>NVDA</v>
-    <v>NVIDIA CORPORATION (XNAS:NVDA)</v>
-    <v>91813288</v>
-    <v>153534782</v>
-    <v>1998</v>
-  </rv>
-  <rv s="2">
-    <v>265</v>
-  </rv>
-  <rv s="1">
-    <v>en-GB</v>
-    <v>a1ndww</v>
-    <v>268435456</v>
-    <v>1</v>
-    <v>Powered by Refinitiv</v>
-    <v>0</v>
-    <v>ADVANCED MICRO DEVICES, INC. (XNAS:AMD)</v>
-    <v>2</v>
-    <v>3</v>
-    <v>Finance</v>
-    <v>4</v>
-    <v>469.21499999999997</v>
-    <v>107.6671</v>
-    <v>2.4043999999999999</v>
-    <v>32.049999999999997</v>
-    <v>7.7406000000000003E-2</v>
-    <v>USD</v>
-    <v>Advanced Micro Devices, Inc. is a global semiconductor company. The Company is focused on high-performance computing and artificial intelligence (AI). Its segments include Data Center, Client and Gaming, and Embedded. Data Center segment includes AI accelerators, microprocessors (CPUs) for servers, graphics processing units (GPUs), accelerated processing units (APUs), data processing units (DPUs), Field Programmable Gate Arrays (FPGAs), and Adaptive system-on-Chip (SoC) products for data centers. Client and Gaming segment includes CPUs, APUs, chipsets for desktops and notebooks, discrete GPUs, and semi-custom SoC products and development services. Embedded segment includes embedded CPUs, APUs, FPGAs, system on modules (SOMs), and Adaptive SoC products. It markets and sells its products under the AMD trademark. Its products include AMD EPYC, AMD Ryzen, AMD Ryzen PRO, Virtex UltraScale+, among others.</v>
-    <v>31000</v>
-    <v>Nasdaq Stock Market</v>
-    <v>XNAS</v>
-    <v>XNAS</v>
-    <v>2485 Augustine Drive, SANTA CLARA, CA, 95054 US</v>
-    <v>448.75</v>
-    <v>Semiconductors &amp; Semiconductor Equipment</v>
-    <v>Stock</v>
-    <v>46162.757188923439</v>
-    <v>37</v>
-    <v>426.05</v>
-    <v>727411106100</v>
-    <v>ADVANCED MICRO DEVICES, INC.</v>
-    <v>ADVANCED MICRO DEVICES, INC.</v>
-    <v>429.23</v>
-    <v>148.70500000000001</v>
-    <v>414.05</v>
-    <v>446.1</v>
-    <v>1630601000</v>
-    <v>AMD</v>
-    <v>ADVANCED MICRO DEVICES, INC. (XNAS:AMD)</v>
-    <v>24025881</v>
-    <v>44995947</v>
-    <v>1969</v>
-  </rv>
-  <rv s="2">
-    <v>267</v>
-  </rv>
-  <rv s="3">
-    <v>en-GB</v>
-    <v>cgblqh</v>
-    <v>268435456</v>
-    <v>1</v>
-    <v>Powered by Refinitiv</v>
-    <v>5</v>
-    <v>COREWEAVE, INC. (XNAS:CRWV)</v>
-    <v>6</v>
-    <v>3</v>
-    <v>Finance</v>
-    <v>4</v>
-    <v>187</v>
-    <v>63.8</v>
-    <v>2.4279999999999999</v>
-    <v>2.3801000000000001</v>
-    <v>2.3845999999999999E-2</v>
-    <v>USD</v>
-    <v>CoreWeave, Inc. is a cloud infrastructure technology company. The Company offers the CoreWeave Cloud Platform, which consists of software and cloud services that deliver the automation and efficiency needed to manage complex artificial intelligence (AI) infrastructure. Its CoreWeave Cloud Platform is an integrated solution that is purpose-built for running AI workloads such as model training and inference. Its solutions include infrastructure services, managed software services, and application software services. Its Infrastructure Services provide its customers with access to advanced graphics processing unit (GPU) and central processing unit (CPU) compute, highly performant networking, and storage. Its Managed Software Services include CKS, a flexible virtual private cloud and a bare metal service that runs kubernetes directly on high-performance servers. Its Application Software Services build on top of its infrastructure and managed software services, integrating additional tools.</v>
-    <v>2189</v>
-    <v>Nasdaq Stock Market</v>
-    <v>XNAS</v>
-    <v>XNAS</v>
-    <v>290 W. Mt. Pleasant Avenue, Suite 4100, LIVINGSTON, NJ, 07039 US</v>
-    <v>102.74</v>
-    <v>Software &amp; IT Services</v>
-    <v>Stock</v>
-    <v>46162.757246828121</v>
-    <v>98.1</v>
-    <v>55751893733</v>
-    <v>COREWEAVE, INC.</v>
-    <v>COREWEAVE, INC.</v>
-    <v>101.35</v>
-    <v>0</v>
-    <v>99.81</v>
-    <v>102.1901</v>
-    <v>545570400</v>
-    <v>CRWV</v>
-    <v>COREWEAVE, INC. (XNAS:CRWV)</v>
-    <v>13757481</v>
-    <v>29714473</v>
-    <v>2017</v>
-  </rv>
-  <rv s="2">
-    <v>269</v>
-  </rv>
-  <rv s="1">
-    <v>en-GB</v>
-    <v>a24kar</v>
-    <v>268435456</v>
-    <v>1</v>
-    <v>Powered by Refinitiv</v>
-    <v>0</v>
-    <v>TESLA, INC. (XNAS:TSLA)</v>
-    <v>2</v>
-    <v>3</v>
-    <v>Finance</v>
-    <v>4</v>
-    <v>498.83</v>
-    <v>273.20999999999998</v>
-    <v>1.7888999999999999</v>
-    <v>8.4499999999999993</v>
-    <v>2.0910000000000002E-2</v>
-    <v>USD</v>
-    <v>Tesla, Inc. designs, develops, manufactures, sells and leases high-performance fully electric vehicles and energy generation and storage systems, and offers services related to its products. Its segments include automotive, and energy generation and storage. The automotive segment includes the design, development, manufacturing, sales and leasing of high-performance fully electric vehicles, and sales of automotive regulatory credits. It also includes sales of used vehicles, non-warranty maintenance services and collisions, part sales, paid supercharging, insurance services revenue and retail merchandise sales. The energy generation and storage segment include the design, manufacture, installation, sales and leasing of solar energy generation and energy storage products and related services and sales of solar energy systems incentives. Its consumer vehicles include the Model 3, Y, S, X and Cybertruck. Its lithium-ion battery energy storage products include Powerwall and Megapack.</v>
-    <v>134785</v>
-    <v>Nasdaq Stock Market</v>
-    <v>XNAS</v>
-    <v>XNAS</v>
-    <v>1 Tesla Road, AUSTIN, TX, 78725 US</v>
-    <v>415.15</v>
-    <v>Automobiles &amp; Auto Parts</v>
-    <v>Stock</v>
-    <v>46162.757200671091</v>
-    <v>177</v>
-    <v>406.39</v>
-    <v>1549461493440</v>
-    <v>TESLA, INC.</v>
-    <v>TESLA, INC.</v>
-    <v>407.69</v>
-    <v>377.077</v>
-    <v>404.11</v>
-    <v>412.56</v>
-    <v>3755724000</v>
-    <v>TSLA</v>
-    <v>TESLA, INC. (XNAS:TSLA)</v>
-    <v>29361376</v>
-    <v>62641710</v>
-    <v>2024</v>
-  </rv>
-  <rv s="2">
-    <v>271</v>
-  </rv>
-  <rv s="1">
-    <v>en-GB</v>
-    <v>a2nk77</v>
-    <v>268435456</v>
-    <v>1</v>
-    <v>Powered by Refinitiv</v>
-    <v>0</v>
-    <v>LIGHTWAVE LOGIC, INC. (XNAS:LWLG)</v>
-    <v>2</v>
-    <v>3</v>
-    <v>Finance</v>
-    <v>4</v>
-    <v>18.709</v>
-    <v>0.91510000000000002</v>
-    <v>3.2101000000000002</v>
-    <v>0.15</v>
-    <v>1.2942E-2</v>
-    <v>USD</v>
-    <v>Lightwave Logic, Inc. is a technology platform company leveraging its proprietary engineered electro-optic (EO) polymers known as Perkinamine, to transmit data at higher speeds with less power in a small form factor. The Company’s organic polymers allow it to create next-generation photonic EO devices that convert data from electrical signals into light/optical signals for applications in telecommunications, and for data transmission potentially used to support generative Artificial Intelligence. It designs its own proprietary materials for electro-optical modulation devices. Electro-optical modulators convert data from electric signals into optical signals that can then be transmitted over high-speed fiber-optic cables. It is focused on testing and demonstrating the manufacturability and reliability of its devices. In polymer photonics, polymer devices such as modulators, waveguides, and multiplexers can be fabricated on to a silicon platform.</v>
-    <v>34</v>
-    <v>Nasdaq Stock Market</v>
-    <v>XNAS</v>
-    <v>XNAS</v>
-    <v>369 Inverness Parkway, Suite 350, ENGLEWOOD, CO, 80112 US</v>
-    <v>12.15</v>
-    <v>Electronic Equipment &amp; Parts</v>
-    <v>Stock</v>
-    <v>46162.757242407031</v>
-    <v>253</v>
-    <v>11.01</v>
-    <v>1808894504</v>
-    <v>LIGHTWAVE LOGIC, INC.</v>
-    <v>LIGHTWAVE LOGIC, INC.</v>
-    <v>11.8</v>
-    <v>0</v>
-    <v>11.59</v>
-    <v>11.74</v>
-    <v>154079600</v>
-    <v>LWLG</v>
-    <v>LIGHTWAVE LOGIC, INC. (XNAS:LWLG)</v>
-    <v>3965799</v>
-    <v>10253177</v>
-    <v>1997</v>
-  </rv>
-  <rv s="2">
-    <v>273</v>
-  </rv>
-  <rv s="1">
-    <v>en-GB</v>
-    <v>a2si9c</v>
-    <v>268435456</v>
-    <v>1</v>
-    <v>Powered by Refinitiv</v>
-    <v>0</v>
-    <v>POET Technologies Inc. (XNAS:POET)</v>
-    <v>2</v>
-    <v>3</v>
-    <v>Finance</v>
-    <v>4</v>
-    <v>20.81</v>
-    <v>3.87</v>
-    <v>0.60660000000000003</v>
-    <v>0.99109999999999998</v>
-    <v>7.5830000000000009E-2</v>
-    <v>USD</v>
-    <v>POET Technologies Inc. is a design and development company. It offers high-speed optical engines, light source products and custom optical modules to the artificial intelligence (AI) systems market and to hyperscale data centers. Its photonic integration solutions are based on the POET Optical Interposer, a novel, patented platform that allows the integration of electronic and photonic devices into a single chip using wafer-level semiconductor manufacturing techniques. Its Optical Interposer-based products consume less power than comparable products, are smaller in size and are readily scalable to high production volumes. In addition, it has designed and produced novel light source products for chip-to-chip data communication within and between AI servers, the next frontier for solving bandwidth and latency problems in AI systems. Its Optical Interposer platform solves device integration challenges across a range of communication, computing and sensing applications.</v>
-    <v>180</v>
-    <v>Nasdaq Stock Market</v>
-    <v>XNAS</v>
-    <v>XNAS</v>
-    <v>120 Eglinton Avenue East, Suite 1107, TORONTO, ON, M4P 1E2 CA</v>
-    <v>14.88</v>
-    <v>Semiconductors &amp; Semiconductor Equipment</v>
-    <v>Stock</v>
-    <v>46162.757173946091</v>
-    <v>256</v>
-    <v>13.5801</v>
-    <v>2426881178</v>
-    <v>POET Technologies Inc.</v>
-    <v>POET Technologies Inc.</v>
-    <v>14.7</v>
-    <v>0</v>
-    <v>13.07</v>
-    <v>14.0611</v>
-    <v>172595400</v>
-    <v>POET</v>
-    <v>POET Technologies Inc. (XNAS:POET)</v>
-    <v>37876658</v>
-    <v>66226770</v>
-    <v>2010</v>
-  </rv>
-  <rv s="2">
-    <v>275</v>
-  </rv>
-  <rv s="1">
-    <v>en-GB</v>
-    <v>aodipr</v>
-    <v>268435456</v>
-    <v>1</v>
-    <v>Powered by Refinitiv</v>
-    <v>0</v>
-    <v>THE SAGE GROUP PLC. (XLON:SGE)</v>
-    <v>2</v>
-    <v>23</v>
-    <v>Finance</v>
-    <v>24</v>
-    <v>1335</v>
-    <v>771.66</v>
-    <v>0.3478</v>
-    <v>-11</v>
-    <v>-1.2115000000000001E-2</v>
-    <v>GBp</v>
-    <v>The Sage Group plc is a United Kingdom-based company. It provides accounting, financial, human resources (HR) and payroll technology for small and mid-sized businesses. Its segments include North America, United Kingdom, Ireland, Africa and APAC (UKIA) and Europe. Its products include Sage Accounting, Payroll software, Sage Intacct, Sage X3, Sage HR, Sage People, Sage Earth, Sage Ai and Payments and Banking. Sage Accounting is designed to enable small businesses operating in any industry, and accountants and bookkeepers, to manage customer data, accounts, and people in a single solution. Sage Intacct helps growing mid-sized organizations thrive in with digital world with solutions across accounting, planning, and analytics. Sage People is an HR and people management solution for mid-sized businesses. Sage Payroll is an intuitive solution that helps small businesses to run their payroll reliably and flexibly. Sage People is an HR and people management solution for mid-sized businesses.</v>
-    <v>11074</v>
-    <v>London Stock Exchange</v>
-    <v>XLON</v>
-    <v>XLON</v>
-    <v>C23-5 &amp; 6 Cobalt Park Way, Cobalt Park, NEWCASTLE UPON TYNE, NORTHUMBERLAND, NE28 9EJ GB</v>
-    <v>900</v>
-    <v>Software &amp; IT Services</v>
-    <v>Stock</v>
-    <v>46162.578735647658</v>
-    <v>180</v>
-    <v>871</v>
-    <v>10571700000</v>
-    <v>THE SAGE GROUP PLC.</v>
-    <v>THE SAGE GROUP PLC.</v>
-    <v>894.8</v>
-    <v>26.0246</v>
-    <v>908</v>
-    <v>897</v>
-    <v>910494500</v>
-    <v>SGE</v>
-    <v>THE SAGE GROUP PLC. (XLON:SGE)</v>
-    <v>4716965</v>
-    <v>5570840</v>
-    <v>1988</v>
-  </rv>
-  <rv s="2">
-    <v>277</v>
   </rv>
   <rv s="11">
     <v>en-GB</v>
@@ -7939,23 +7310,23 @@
     <v>28</v>
     <v>0.76859999999999995</v>
     <v>0.72099999999999997</v>
-    <v>2.3640000000000002E-3</v>
-    <v>3.1929999999999997E-3</v>
+    <v>3.1930000000000001E-3</v>
+    <v>4.3119999999999999E-3</v>
     <v>GBP</v>
     <v>USD</v>
-    <v>0.74309999999999998</v>
+    <v>0.74429999999999996</v>
     <v>Currency Pair</v>
-    <v>46168.605624999997</v>
+    <v>46168.683576388888</v>
     <v>0.74039999999999995</v>
     <v>US Dollar/UK Pound Sterling FX Cross Rate</v>
     <v>0.74050000000000005</v>
     <v>0.74039999999999995</v>
-    <v>0.74280000000000002</v>
+    <v>0.74360000000000004</v>
     <v>USDGBP</v>
     <v>USD/GBP</v>
   </rv>
   <rv s="2">
-    <v>279</v>
+    <v>259</v>
   </rv>
 </rvData>
 </file>
@@ -9238,9 +8609,7 @@
   <autoFilter ref="A1:M11" xr:uid="{D39CE96F-8D2C-4A60-A43A-B3602E27FDC2}"/>
   <tableColumns count="13">
     <tableColumn id="1" xr3:uid="{AE3CE10F-629F-414E-93DE-8949C4E58E7D}" name="Symbol" dataDxfId="30"/>
-    <tableColumn id="2" xr3:uid="{40700DF4-EB97-4DB9-BA32-772C3F8E34CC}" name="StockName" dataDxfId="29">
-      <calculatedColumnFormula>IFERROR(_xlfn.XLOOKUP(A2,[1]!tblWatchlist[Symbol],[1]!tblWatchlist[StockName]),"")</calculatedColumnFormula>
-    </tableColumn>
+    <tableColumn id="2" xr3:uid="{40700DF4-EB97-4DB9-BA32-772C3F8E34CC}" name="StockName" dataDxfId="29"/>
     <tableColumn id="3" xr3:uid="{BED1527E-0498-4FF1-8E69-ECDB2EB30C25}" name="TradeCurrency" dataDxfId="28">
       <calculatedColumnFormula>_FV(B2,"Currency")</calculatedColumnFormula>
     </tableColumn>
@@ -9588,12 +8957,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J12"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <dimension ref="A1:J10"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="10.4375" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.4375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.5625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.46484375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.46484375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.53125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
@@ -9863,64 +9232,6 @@
       </c>
       <c r="I10">
         <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10">
-      <c r="A11" s="1">
-        <v>45292</v>
-      </c>
-      <c r="B11" t="s">
-        <v>92</v>
-      </c>
-      <c r="C11" t="s">
-        <v>81</v>
-      </c>
-      <c r="D11" t="s">
-        <v>90</v>
-      </c>
-      <c r="E11">
-        <v>100</v>
-      </c>
-      <c r="F11" t="s">
-        <v>12</v>
-      </c>
-      <c r="G11">
-        <v>10</v>
-      </c>
-      <c r="H11">
-        <v>0.12</v>
-      </c>
-      <c r="I11">
-        <v>0.75</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10">
-      <c r="A12" s="1">
-        <v>45323</v>
-      </c>
-      <c r="B12" t="s">
-        <v>92</v>
-      </c>
-      <c r="C12" t="s">
-        <v>81</v>
-      </c>
-      <c r="D12" t="s">
-        <v>396</v>
-      </c>
-      <c r="E12">
-        <v>40</v>
-      </c>
-      <c r="F12" t="s">
-        <v>12</v>
-      </c>
-      <c r="G12">
-        <v>12</v>
-      </c>
-      <c r="H12">
-        <v>0.12</v>
-      </c>
-      <c r="I12">
-        <v>0.75</v>
       </c>
     </row>
   </sheetData>
@@ -9932,29 +9243,29 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:AE82"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="9.875" customWidth="1"/>
-    <col min="2" max="2" width="13.4375" customWidth="1"/>
-    <col min="3" max="3" width="16.3125" customWidth="1"/>
-    <col min="4" max="4" width="16.6875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.6875" customWidth="1"/>
+    <col min="1" max="1" width="9.86328125" customWidth="1"/>
+    <col min="2" max="2" width="13.46484375" customWidth="1"/>
+    <col min="3" max="3" width="16.33203125" customWidth="1"/>
+    <col min="4" max="4" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.6640625" customWidth="1"/>
     <col min="6" max="6" width="17" customWidth="1"/>
     <col min="7" max="7" width="10" customWidth="1"/>
-    <col min="10" max="10" width="12.125" customWidth="1"/>
-    <col min="11" max="11" width="11.5625" customWidth="1"/>
-    <col min="12" max="12" width="10.6875" customWidth="1"/>
-    <col min="13" max="13" width="10.125" customWidth="1"/>
-    <col min="15" max="15" width="16.3125" customWidth="1"/>
-    <col min="16" max="16" width="11.125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="17.125" customWidth="1"/>
-    <col min="18" max="18" width="17.6875" customWidth="1"/>
-    <col min="19" max="19" width="13.125" customWidth="1"/>
-    <col min="20" max="20" width="43.3125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="16.4375" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="20.3125" customWidth="1"/>
+    <col min="10" max="10" width="12.1328125" customWidth="1"/>
+    <col min="11" max="11" width="11.53125" customWidth="1"/>
+    <col min="12" max="12" width="10.6640625" customWidth="1"/>
+    <col min="13" max="13" width="10.1328125" customWidth="1"/>
+    <col min="15" max="15" width="16.33203125" customWidth="1"/>
+    <col min="16" max="16" width="11.1328125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="17.1328125" customWidth="1"/>
+    <col min="18" max="18" width="17.6640625" customWidth="1"/>
+    <col min="19" max="19" width="13.1328125" customWidth="1"/>
+    <col min="20" max="20" width="43.33203125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="16.46484375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="20.33203125" customWidth="1"/>
     <col min="24" max="26" width="10" customWidth="1"/>
-    <col min="30" max="31" width="10.875" customWidth="1"/>
+    <col min="30" max="31" width="10.86328125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:31">
@@ -10061,7 +9372,7 @@
       </c>
       <c r="C2" s="2">
         <f t="array" aca="1" ref="C2" ca="1">_FV(B2,"Last trade time",TRUE)</f>
-        <v>46168.605484501561</v>
+        <v>46168.683481226566</v>
       </c>
       <c r="D2" t="str">
         <f t="array" aca="1" ref="D2" ca="1">_FV(B2,"Currency")</f>
@@ -10069,19 +9380,19 @@
       </c>
       <c r="E2" s="3">
         <f t="array" aca="1" ref="E2" ca="1">_FV(B2,"Price")</f>
-        <v>879.83</v>
+        <v>881.06</v>
       </c>
       <c r="F2" s="4">
         <f t="array" aca="1" ref="F2" ca="1">_FV(B2,"Change (%)",TRUE)</f>
-        <v>0.17154499999999998</v>
+        <v>0.173182</v>
       </c>
       <c r="G2" s="5">
         <f t="array" aca="1" ref="G2" ca="1">_FV(B2,"Change")</f>
-        <v>128.83000000000001</v>
+        <v>130.06</v>
       </c>
       <c r="H2" s="6">
         <f t="array" aca="1" ref="H2" ca="1">_FV(B2,"P/E",TRUE)</f>
-        <v>41.5381</v>
+        <v>41.5961</v>
       </c>
       <c r="I2" s="6">
         <f t="array" aca="1" ref="I2" ca="1">_FV(B2,"Beta")</f>
@@ -10089,7 +9400,7 @@
       </c>
       <c r="J2" s="3">
         <f t="array" aca="1" ref="J2" ca="1">_FV(B2,"52 week high",TRUE)</f>
-        <v>880.89</v>
+        <v>891.27</v>
       </c>
       <c r="K2" s="3">
         <f t="array" aca="1" ref="K2" ca="1">_FV(B2,"52 week low",TRUE)</f>
@@ -10097,7 +9408,7 @@
       </c>
       <c r="L2" s="3">
         <f t="array" aca="1" ref="L2" ca="1">_FV(B2,"High")</f>
-        <v>880.89</v>
+        <v>891.27</v>
       </c>
       <c r="M2" s="3">
         <f t="array" aca="1" ref="M2" ca="1">_FV(B2,"Low")</f>
@@ -10113,7 +9424,7 @@
       </c>
       <c r="P2" s="7">
         <f t="array" aca="1" ref="P2" ca="1">_FV(B2,"Volume")</f>
-        <v>25104573</v>
+        <v>41316331</v>
       </c>
       <c r="Q2" s="7">
         <f t="array" aca="1" ref="Q2" ca="1">_FV(B2,"Volume average",TRUE)</f>
@@ -10133,7 +9444,7 @@
       </c>
       <c r="U2" s="7">
         <f t="array" aca="1" ref="U2" ca="1">_FV(B2,"Market cap",TRUE)</f>
-        <v>992214205220</v>
+        <v>993601318039</v>
       </c>
       <c r="V2" s="7">
         <f t="array" aca="1" ref="V2" ca="1">_FV(B2,"Shares outstanding",TRUE)</f>
@@ -10149,7 +9460,7 @@
       </c>
       <c r="C3" s="2">
         <f t="array" aca="1" ref="C3" ca="1">_FV(B3,"Last trade time",TRUE)</f>
-        <v>46168.605474270313</v>
+        <v>46168.683445925781</v>
       </c>
       <c r="D3" t="str">
         <f t="array" aca="1" ref="D3" ca="1">_FV(B3,"Currency")</f>
@@ -10157,15 +9468,15 @@
       </c>
       <c r="E3" s="3">
         <f t="array" aca="1" ref="E3" ca="1">_FV(B3,"Price")</f>
-        <v>7.5</v>
+        <v>7.2911000000000001</v>
       </c>
       <c r="F3" s="4">
         <f t="array" aca="1" ref="F3" ca="1">_FV(B3,"Change (%)",TRUE)</f>
-        <v>0.12275399999999999</v>
+        <v>9.1481999999999994E-2</v>
       </c>
       <c r="G3" s="5">
         <f t="array" aca="1" ref="G3" ca="1">_FV(B3,"Change")</f>
-        <v>0.82</v>
+        <v>0.61109999999999998</v>
       </c>
       <c r="H3" s="6">
         <f t="array" aca="1" ref="H3" ca="1">_FV(B3,"P/E",TRUE)</f>
@@ -10201,7 +9512,7 @@
       </c>
       <c r="P3" s="7">
         <f t="array" aca="1" ref="P3" ca="1">_FV(B3,"Volume")</f>
-        <v>3521047</v>
+        <v>5738079</v>
       </c>
       <c r="Q3" s="7">
         <f t="array" aca="1" ref="Q3" ca="1">_FV(B3,"Volume average",TRUE)</f>
@@ -10221,7 +9532,7 @@
       </c>
       <c r="U3" s="7">
         <f t="array" aca="1" ref="U3" ca="1">_FV(B3,"Market cap",TRUE)</f>
-        <v>1636150500</v>
+        <v>1590578254</v>
       </c>
       <c r="V3" s="7">
         <f t="array" aca="1" ref="V3" ca="1">_FV(B3,"Shares outstanding",TRUE)</f>
@@ -10237,7 +9548,7 @@
       </c>
       <c r="C4" s="2">
         <f t="array" aca="1" ref="C4" ca="1">_FV(B4,"Last trade time",TRUE)</f>
-        <v>46168.605510392968</v>
+        <v>46168.683466596878</v>
       </c>
       <c r="D4" t="str">
         <f t="array" aca="1" ref="D4" ca="1">_FV(B4,"Currency")</f>
@@ -10245,15 +9556,15 @@
       </c>
       <c r="E4" s="3">
         <f t="array" aca="1" ref="E4" ca="1">_FV(B4,"Price")</f>
-        <v>105.789</v>
+        <v>109.46</v>
       </c>
       <c r="F4" s="4">
         <f t="array" aca="1" ref="F4" ca="1">_FV(B4,"Change (%)",TRUE)</f>
-        <v>0.11333399999999999</v>
+        <v>0.15196799999999999</v>
       </c>
       <c r="G4" s="5">
         <f t="array" aca="1" ref="G4" ca="1">_FV(B4,"Change")</f>
-        <v>10.769</v>
+        <v>14.44</v>
       </c>
       <c r="H4" s="6">
         <f t="array" aca="1" ref="H4" ca="1">_FV(B4,"P/E",TRUE)</f>
@@ -10265,7 +9576,7 @@
       </c>
       <c r="J4" s="3">
         <f t="array" aca="1" ref="J4" ca="1">_FV(B4,"52 week high",TRUE)</f>
-        <v>108.751</v>
+        <v>109.93</v>
       </c>
       <c r="K4" s="3">
         <f t="array" aca="1" ref="K4" ca="1">_FV(B4,"52 week low",TRUE)</f>
@@ -10273,7 +9584,7 @@
       </c>
       <c r="L4" s="3">
         <f t="array" aca="1" ref="L4" ca="1">_FV(B4,"High")</f>
-        <v>106.53</v>
+        <v>109.93</v>
       </c>
       <c r="M4" s="3">
         <f t="array" aca="1" ref="M4" ca="1">_FV(B4,"Low")</f>
@@ -10289,7 +9600,7 @@
       </c>
       <c r="P4" s="7">
         <f t="array" aca="1" ref="P4" ca="1">_FV(B4,"Volume")</f>
-        <v>848516</v>
+        <v>1548835</v>
       </c>
       <c r="Q4" s="7">
         <f t="array" aca="1" ref="Q4" ca="1">_FV(B4,"Volume average",TRUE)</f>
@@ -10309,7 +9620,7 @@
       </c>
       <c r="U4" s="7">
         <f t="array" aca="1" ref="U4" ca="1">_FV(B4,"Market cap",TRUE)</f>
-        <v>3327407864</v>
+        <v>3442872745</v>
       </c>
       <c r="V4" s="7">
         <f t="array" aca="1" ref="V4" ca="1">_FV(B4,"Shares outstanding",TRUE)</f>
@@ -10325,7 +9636,7 @@
       </c>
       <c r="C5" s="2" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(B5,"Last trade time",TRUE)</f>
-        <v>46168.60548443281</v>
+        <v>46168.683484212503</v>
       </c>
       <c r="D5" t="str" cm="1">
         <f t="array" aca="1" ref="D5" ca="1">_FV(B5,"Currency")</f>
@@ -10333,19 +9644,19 @@
       </c>
       <c r="E5" s="3" cm="1">
         <f t="array" aca="1" ref="E5" ca="1">_FV(B5,"Price")</f>
-        <v>127.77</v>
+        <v>126.28</v>
       </c>
       <c r="F5" s="4" cm="1">
         <f t="array" aca="1" ref="F5" ca="1">_FV(B5,"Change (%)",TRUE)</f>
-        <v>9.9570000000000006E-2</v>
+        <v>8.6746999999999991E-2</v>
       </c>
       <c r="G5" s="5" cm="1">
         <f t="array" aca="1" ref="G5" ca="1">_FV(B5,"Change")</f>
-        <v>11.57</v>
+        <v>10.08</v>
       </c>
       <c r="H5" s="6" cm="1">
         <f t="array" aca="1" ref="H5" ca="1">_FV(B5,"P/E",TRUE)</f>
-        <v>91.238200000000006</v>
+        <v>90.174199999999999</v>
       </c>
       <c r="I5" s="6" cm="1">
         <f t="array" aca="1" ref="I5" ca="1">_FV(B5,"Beta")</f>
@@ -10353,7 +9664,7 @@
       </c>
       <c r="J5" s="3" cm="1">
         <f t="array" aca="1" ref="J5" ca="1">_FV(B5,"52 week high",TRUE)</f>
-        <v>128.57990000000001</v>
+        <v>129.13</v>
       </c>
       <c r="K5" s="3" cm="1">
         <f t="array" aca="1" ref="K5" ca="1">_FV(B5,"52 week low",TRUE)</f>
@@ -10361,7 +9672,7 @@
       </c>
       <c r="L5" s="3" cm="1">
         <f t="array" aca="1" ref="L5" ca="1">_FV(B5,"High")</f>
-        <v>128.57990000000001</v>
+        <v>129.13</v>
       </c>
       <c r="M5" s="3" cm="1">
         <f t="array" aca="1" ref="M5" ca="1">_FV(B5,"Low")</f>
@@ -10377,7 +9688,7 @@
       </c>
       <c r="P5" s="7" cm="1">
         <f t="array" aca="1" ref="P5" ca="1">_FV(B5,"Volume")</f>
-        <v>4736584</v>
+        <v>7980312</v>
       </c>
       <c r="Q5" s="7" cm="1">
         <f t="array" aca="1" ref="Q5" ca="1">_FV(B5,"Volume average",TRUE)</f>
@@ -10397,7 +9708,7 @@
       </c>
       <c r="U5" s="7" cm="1">
         <f t="array" aca="1" ref="U5" ca="1">_FV(B5,"Market cap",TRUE)</f>
-        <v>50073471864</v>
+        <v>49489536096</v>
       </c>
       <c r="V5" s="7" cm="1">
         <f t="array" aca="1" ref="V5" ca="1">_FV(B5,"Shares outstanding",TRUE)</f>
@@ -10413,7 +9724,7 @@
       </c>
       <c r="C6" s="2">
         <f t="array" aca="1" ref="C6" ca="1">_FV(B6,"Last trade time",TRUE)</f>
-        <v>46168.605527025</v>
+        <v>46168.683447071096</v>
       </c>
       <c r="D6" t="str">
         <f t="array" aca="1" ref="D6" ca="1">_FV(B6,"Currency")</f>
@@ -10421,19 +9732,19 @@
       </c>
       <c r="E6" s="3">
         <f t="array" aca="1" ref="E6" ca="1">_FV(B6,"Price")</f>
-        <v>524.49</v>
+        <v>511.05009999999999</v>
       </c>
       <c r="F6" s="4">
         <f t="array" aca="1" ref="F6" ca="1">_FV(B6,"Change (%)",TRUE)</f>
-        <v>8.8876000000000011E-2</v>
+        <v>6.0974E-2</v>
       </c>
       <c r="G6" s="5">
         <f t="array" aca="1" ref="G6" ca="1">_FV(B6,"Change")</f>
-        <v>42.81</v>
+        <v>29.370100000000001</v>
       </c>
       <c r="H6" s="6">
         <f t="array" aca="1" ref="H6" ca="1">_FV(B6,"P/E",TRUE)</f>
-        <v>45.578099999999999</v>
+        <v>44.410200000000003</v>
       </c>
       <c r="I6" s="6">
         <f t="array" aca="1" ref="I6" ca="1">_FV(B6,"Beta")</f>
@@ -10449,11 +9760,11 @@
       </c>
       <c r="L6" s="3">
         <f t="array" aca="1" ref="L6" ca="1">_FV(B6,"High")</f>
-        <v>535.35</v>
+        <v>538.81989999999996</v>
       </c>
       <c r="M6" s="3">
         <f t="array" aca="1" ref="M6" ca="1">_FV(B6,"Low")</f>
-        <v>516.07000000000005</v>
+        <v>510.34</v>
       </c>
       <c r="N6" s="3">
         <f t="array" aca="1" ref="N6" ca="1">_FV(B6,"Open")</f>
@@ -10465,7 +9776,7 @@
       </c>
       <c r="P6" s="7">
         <f t="array" aca="1" ref="P6" ca="1">_FV(B6,"Volume")</f>
-        <v>1939411</v>
+        <v>3539656</v>
       </c>
       <c r="Q6" s="7">
         <f t="array" aca="1" ref="Q6" ca="1">_FV(B6,"Volume average",TRUE)</f>
@@ -10485,7 +9796,7 @@
       </c>
       <c r="U6" s="7">
         <f t="array" aca="1" ref="U6" ca="1">_FV(B6,"Market cap",TRUE)</f>
-        <v>176197170600</v>
+        <v>171682170594</v>
       </c>
       <c r="V6" s="7">
         <f t="array" aca="1" ref="V6" ca="1">_FV(B6,"Shares outstanding",TRUE)</f>
@@ -10501,7 +9812,7 @@
       </c>
       <c r="C7" s="2" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(B7,"Last trade time",TRUE)</f>
-        <v>46168.605513425784</v>
+        <v>46168.683461562498</v>
       </c>
       <c r="D7" t="str" cm="1">
         <f t="array" aca="1" ref="D7" ca="1">_FV(B7,"Currency")</f>
@@ -10509,15 +9820,15 @@
       </c>
       <c r="E7" s="3" cm="1">
         <f t="array" aca="1" ref="E7" ca="1">_FV(B7,"Price")</f>
-        <v>12.42</v>
+        <v>12.295199999999999</v>
       </c>
       <c r="F7" s="4" cm="1">
         <f t="array" aca="1" ref="F7" ca="1">_FV(B7,"Change (%)",TRUE)</f>
-        <v>8.9473999999999998E-2</v>
+        <v>7.8525999999999999E-2</v>
       </c>
       <c r="G7" s="5" cm="1">
         <f t="array" aca="1" ref="G7" ca="1">_FV(B7,"Change")</f>
-        <v>1.02</v>
+        <v>0.8952</v>
       </c>
       <c r="H7" s="6" cm="1">
         <f t="array" aca="1" ref="H7" ca="1">_FV(B7,"P/E",TRUE)</f>
@@ -10553,7 +9864,7 @@
       </c>
       <c r="P7" s="7" cm="1">
         <f t="array" aca="1" ref="P7" ca="1">_FV(B7,"Volume")</f>
-        <v>22102257</v>
+        <v>30220468</v>
       </c>
       <c r="Q7" s="7" cm="1">
         <f t="array" aca="1" ref="Q7" ca="1">_FV(B7,"Volume average",TRUE)</f>
@@ -10573,7 +9884,7 @@
       </c>
       <c r="U7" s="7" cm="1">
         <f t="array" aca="1" ref="U7" ca="1">_FV(B7,"Market cap",TRUE)</f>
-        <v>4539276504</v>
+        <v>4493664450</v>
       </c>
       <c r="V7" s="7" cm="1">
         <f t="array" aca="1" ref="V7" ca="1">_FV(B7,"Shares outstanding",TRUE)</f>
@@ -10589,7 +9900,7 @@
       </c>
       <c r="C8" s="2">
         <f t="array" aca="1" ref="C8" ca="1">_FV(B8,"Last trade time",TRUE)</f>
-        <v>46168.605518888282</v>
+        <v>46168.683472661716</v>
       </c>
       <c r="D8" t="str">
         <f t="array" aca="1" ref="D8" ca="1">_FV(B8,"Currency")</f>
@@ -10597,19 +9908,19 @@
       </c>
       <c r="E8" s="3">
         <f t="array" aca="1" ref="E8" ca="1">_FV(B8,"Price")</f>
-        <v>1606.365</v>
+        <v>1593.89</v>
       </c>
       <c r="F8" s="4">
         <f t="array" aca="1" ref="F8" ca="1">_FV(B8,"Change (%)",TRUE)</f>
-        <v>8.6343000000000003E-2</v>
+        <v>7.7907000000000004E-2</v>
       </c>
       <c r="G8" s="5">
         <f t="array" aca="1" ref="G8" ca="1">_FV(B8,"Change")</f>
-        <v>127.675</v>
+        <v>115.2</v>
       </c>
       <c r="H8" s="6">
         <f t="array" aca="1" ref="H8" ca="1">_FV(B8,"P/E",TRUE)</f>
-        <v>56.790900000000001</v>
+        <v>56.349899999999998</v>
       </c>
       <c r="I8" s="6">
         <f t="array" aca="1" ref="I8" ca="1">_FV(B8,"Beta")</f>
@@ -10617,7 +9928,7 @@
       </c>
       <c r="J8" s="3">
         <f t="array" aca="1" ref="J8" ca="1">_FV(B8,"52 week high",TRUE)</f>
-        <v>1607.77</v>
+        <v>1632.9299000000001</v>
       </c>
       <c r="K8" s="3">
         <f t="array" aca="1" ref="K8" ca="1">_FV(B8,"52 week low",TRUE)</f>
@@ -10625,7 +9936,7 @@
       </c>
       <c r="L8" s="3">
         <f t="array" aca="1" ref="L8" ca="1">_FV(B8,"High")</f>
-        <v>1607.77</v>
+        <v>1632.9299000000001</v>
       </c>
       <c r="M8" s="3">
         <f t="array" aca="1" ref="M8" ca="1">_FV(B8,"Low")</f>
@@ -10641,7 +9952,7 @@
       </c>
       <c r="P8" s="7">
         <f t="array" aca="1" ref="P8" ca="1">_FV(B8,"Volume")</f>
-        <v>4360090</v>
+        <v>7287189</v>
       </c>
       <c r="Q8" s="7">
         <f t="array" aca="1" ref="Q8" ca="1">_FV(B8,"Volume average",TRUE)</f>
@@ -10661,7 +9972,7 @@
       </c>
       <c r="U8" s="7">
         <f t="array" aca="1" ref="U8" ca="1">_FV(B8,"Market cap",TRUE)</f>
-        <v>237886271577</v>
+        <v>236038851322</v>
       </c>
       <c r="V8" s="7">
         <f t="array" aca="1" ref="V8" ca="1">_FV(B8,"Shares outstanding",TRUE)</f>
@@ -10677,7 +9988,7 @@
       </c>
       <c r="C9" s="2" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(B9,"Last trade time",TRUE)</f>
-        <v>46168.605487950779</v>
+        <v>46168.683477673439</v>
       </c>
       <c r="D9" t="str" cm="1">
         <f t="array" aca="1" ref="D9" ca="1">_FV(B9,"Currency")</f>
@@ -10685,19 +9996,19 @@
       </c>
       <c r="E9" s="3" cm="1">
         <f t="array" aca="1" ref="E9" ca="1">_FV(B9,"Price")</f>
-        <v>387.43200000000002</v>
+        <v>383.005</v>
       </c>
       <c r="F9" s="4" cm="1">
         <f t="array" aca="1" ref="F9" ca="1">_FV(B9,"Change (%)",TRUE)</f>
-        <v>8.0883999999999998E-2</v>
+        <v>6.8532999999999997E-2</v>
       </c>
       <c r="G9" s="5" cm="1">
         <f t="array" aca="1" ref="G9" ca="1">_FV(B9,"Change")</f>
-        <v>28.992000000000001</v>
+        <v>24.565000000000001</v>
       </c>
       <c r="H9" s="6" cm="1">
         <f t="array" aca="1" ref="H9" ca="1">_FV(B9,"P/E",TRUE)</f>
-        <v>71.705500000000001</v>
+        <v>70.886200000000002</v>
       </c>
       <c r="I9" s="6" cm="1">
         <f t="array" aca="1" ref="I9" ca="1">_FV(B9,"Beta")</f>
@@ -10713,7 +10024,7 @@
       </c>
       <c r="L9" s="3" cm="1">
         <f t="array" aca="1" ref="L9" ca="1">_FV(B9,"High")</f>
-        <v>388.22989999999999</v>
+        <v>389.54500000000002</v>
       </c>
       <c r="M9" s="3" cm="1">
         <f t="array" aca="1" ref="M9" ca="1">_FV(B9,"Low")</f>
@@ -10729,7 +10040,7 @@
       </c>
       <c r="P9" s="7" cm="1">
         <f t="array" aca="1" ref="P9" ca="1">_FV(B9,"Volume")</f>
-        <v>1113068</v>
+        <v>1736898</v>
       </c>
       <c r="Q9" s="7" cm="1">
         <f t="array" aca="1" ref="Q9" ca="1">_FV(B9,"Volume average",TRUE)</f>
@@ -10749,7 +10060,7 @@
       </c>
       <c r="U9" s="7" cm="1">
         <f t="array" aca="1" ref="U9" ca="1">_FV(B9,"Market cap",TRUE)</f>
-        <v>60649457630</v>
+        <v>59956445311</v>
       </c>
       <c r="V9" s="7" cm="1">
         <f t="array" aca="1" ref="V9" ca="1">_FV(B9,"Shares outstanding",TRUE)</f>
@@ -10765,7 +10076,7 @@
       </c>
       <c r="C10" s="2">
         <f t="array" aca="1" ref="C10" ca="1">_FV(B10,"Last trade time",TRUE)</f>
-        <v>46168.605498714845</v>
+        <v>46168.683407325778</v>
       </c>
       <c r="D10" t="str">
         <f t="array" aca="1" ref="D10" ca="1">_FV(B10,"Currency")</f>
@@ -10773,15 +10084,15 @@
       </c>
       <c r="E10" s="3">
         <f t="array" aca="1" ref="E10" ca="1">_FV(B10,"Price")</f>
-        <v>94.36</v>
+        <v>94.28</v>
       </c>
       <c r="F10" s="4">
         <f t="array" aca="1" ref="F10" ca="1">_FV(B10,"Change (%)",TRUE)</f>
-        <v>7.7784000000000006E-2</v>
+        <v>7.6870000000000008E-2</v>
       </c>
       <c r="G10" s="5">
         <f t="array" aca="1" ref="G10" ca="1">_FV(B10,"Change")</f>
-        <v>6.81</v>
+        <v>6.73</v>
       </c>
       <c r="H10" s="6">
         <f t="array" aca="1" ref="H10" ca="1">_FV(B10,"P/E",TRUE)</f>
@@ -10801,7 +10112,7 @@
       </c>
       <c r="L10" s="3">
         <f t="array" aca="1" ref="L10" ca="1">_FV(B10,"High")</f>
-        <v>94.65</v>
+        <v>96.358000000000004</v>
       </c>
       <c r="M10" s="3">
         <f t="array" aca="1" ref="M10" ca="1">_FV(B10,"Low")</f>
@@ -10817,7 +10128,7 @@
       </c>
       <c r="P10" s="7">
         <f t="array" aca="1" ref="P10" ca="1">_FV(B10,"Volume")</f>
-        <v>587859</v>
+        <v>1090120</v>
       </c>
       <c r="Q10" s="7">
         <f t="array" aca="1" ref="Q10" ca="1">_FV(B10,"Volume average",TRUE)</f>
@@ -10837,7 +10148,7 @@
       </c>
       <c r="U10" s="7">
         <f t="array" aca="1" ref="U10" ca="1">_FV(B10,"Market cap",TRUE)</f>
-        <v>4138769252</v>
+        <v>4135260334</v>
       </c>
       <c r="V10" s="7">
         <f t="array" aca="1" ref="V10" ca="1">_FV(B10,"Shares outstanding",TRUE)</f>
@@ -10853,7 +10164,7 @@
       </c>
       <c r="C11" s="2">
         <f t="array" aca="1" ref="C11" ca="1">_FV(B11,"Last trade time",TRUE)</f>
-        <v>46168.605515751566</v>
+        <v>46168.683469803123</v>
       </c>
       <c r="D11" t="str">
         <f t="array" aca="1" ref="D11" ca="1">_FV(B11,"Currency")</f>
@@ -10861,19 +10172,19 @@
       </c>
       <c r="E11" s="3">
         <f t="array" aca="1" ref="E11" ca="1">_FV(B11,"Price")</f>
-        <v>208.01</v>
+        <v>204.45330000000001</v>
       </c>
       <c r="F11" s="4">
         <f t="array" aca="1" ref="F11" ca="1">_FV(B11,"Change (%)",TRUE)</f>
-        <v>5.9492000000000003E-2</v>
+        <v>4.1375999999999996E-2</v>
       </c>
       <c r="G11" s="5">
         <f t="array" aca="1" ref="G11" ca="1">_FV(B11,"Change")</f>
-        <v>11.68</v>
+        <v>8.1233000000000004</v>
       </c>
       <c r="H11" s="6">
         <f t="array" aca="1" ref="H11" ca="1">_FV(B11,"P/E",TRUE)</f>
-        <v>67.753500000000003</v>
+        <v>66.594999999999999</v>
       </c>
       <c r="I11" s="6">
         <f t="array" aca="1" ref="I11" ca="1">_FV(B11,"Beta")</f>
@@ -10893,7 +10204,7 @@
       </c>
       <c r="M11" s="3">
         <f t="array" aca="1" ref="M11" ca="1">_FV(B11,"Low")</f>
-        <v>206.9</v>
+        <v>200.04</v>
       </c>
       <c r="N11" s="3">
         <f t="array" aca="1" ref="N11" ca="1">_FV(B11,"Open")</f>
@@ -10905,7 +10216,7 @@
       </c>
       <c r="P11" s="7">
         <f t="array" aca="1" ref="P11" ca="1">_FV(B11,"Volume")</f>
-        <v>14634162</v>
+        <v>24549917</v>
       </c>
       <c r="Q11" s="7">
         <f t="array" aca="1" ref="Q11" ca="1">_FV(B11,"Volume average",TRUE)</f>
@@ -10925,7 +10236,7 @@
       </c>
       <c r="U11" s="7">
         <f t="array" aca="1" ref="U11" ca="1">_FV(B11,"Market cap",TRUE)</f>
-        <v>182123821132</v>
+        <v>179009741065</v>
       </c>
       <c r="V11" s="7">
         <f t="array" aca="1" ref="V11" ca="1">_FV(B11,"Shares outstanding",TRUE)</f>
@@ -10941,7 +10252,7 @@
       </c>
       <c r="C12" s="2" cm="1">
         <f t="array" aca="1" ref="C12" ca="1">_FV(B12,"Last trade time",TRUE)</f>
-        <v>46168.605504617968</v>
+        <v>46168.68349688594</v>
       </c>
       <c r="D12" t="str" cm="1">
         <f t="array" aca="1" ref="D12" ca="1">_FV(B12,"Currency")</f>
@@ -10949,15 +10260,15 @@
       </c>
       <c r="E12" s="3" cm="1">
         <f t="array" aca="1" ref="E12" ca="1">_FV(B12,"Price")</f>
-        <v>568.82500000000005</v>
+        <v>564.27</v>
       </c>
       <c r="F12" s="4" cm="1">
         <f t="array" aca="1" ref="F12" ca="1">_FV(B12,"Change (%)",TRUE)</f>
-        <v>5.8613999999999999E-2</v>
+        <v>5.0137000000000001E-2</v>
       </c>
       <c r="G12" s="5" cm="1">
         <f t="array" aca="1" ref="G12" ca="1">_FV(B12,"Change")</f>
-        <v>31.495000000000001</v>
+        <v>26.94</v>
       </c>
       <c r="H12" s="6" t="e" cm="1" vm="12">
         <f t="array" ref="H12">_FV(B12,"P/E",TRUE)</f>
@@ -10969,7 +10280,7 @@
       </c>
       <c r="J12" s="3" cm="1">
         <f t="array" aca="1" ref="J12" ca="1">_FV(B12,"52 week high",TRUE)</f>
-        <v>568.85</v>
+        <v>571.41999999999996</v>
       </c>
       <c r="K12" s="3" cm="1">
         <f t="array" aca="1" ref="K12" ca="1">_FV(B12,"52 week low",TRUE)</f>
@@ -10977,7 +10288,7 @@
       </c>
       <c r="L12" s="3" cm="1">
         <f t="array" aca="1" ref="L12" ca="1">_FV(B12,"High")</f>
-        <v>568.85</v>
+        <v>571.41999999999996</v>
       </c>
       <c r="M12" s="3" cm="1">
         <f t="array" aca="1" ref="M12" ca="1">_FV(B12,"Low")</f>
@@ -10993,7 +10304,7 @@
       </c>
       <c r="P12" s="7" cm="1">
         <f t="array" aca="1" ref="P12" ca="1">_FV(B12,"Volume")</f>
-        <v>2572614</v>
+        <v>5124248</v>
       </c>
       <c r="Q12" s="7" cm="1">
         <f t="array" aca="1" ref="Q12" ca="1">_FV(B12,"Volume average",TRUE)</f>
@@ -11029,7 +10340,7 @@
       </c>
       <c r="C13" s="2">
         <f t="array" aca="1" ref="C13" ca="1">_FV(B13,"Last trade time",TRUE)</f>
-        <v>46168.605546075778</v>
+        <v>46168.683499883591</v>
       </c>
       <c r="D13" t="str">
         <f t="array" aca="1" ref="D13" ca="1">_FV(B13,"Currency")</f>
@@ -11037,19 +10348,19 @@
       </c>
       <c r="E13" s="3">
         <f t="array" aca="1" ref="E13" ca="1">_FV(B13,"Price")</f>
-        <v>494.07499999999999</v>
+        <v>494.65989999999999</v>
       </c>
       <c r="F13" s="4">
         <f t="array" aca="1" ref="F13" ca="1">_FV(B13,"Change (%)",TRUE)</f>
-        <v>5.6821999999999998E-2</v>
+        <v>5.8073E-2</v>
       </c>
       <c r="G13" s="5">
         <f t="array" aca="1" ref="G13" ca="1">_FV(B13,"Change")</f>
-        <v>26.565000000000001</v>
+        <v>27.149899999999999</v>
       </c>
       <c r="H13" s="6">
         <f t="array" aca="1" ref="H13" ca="1">_FV(B13,"P/E",TRUE)</f>
-        <v>164.69720000000001</v>
+        <v>164.8921</v>
       </c>
       <c r="I13" s="6">
         <f t="array" aca="1" ref="I13" ca="1">_FV(B13,"Beta")</f>
@@ -11057,7 +10368,7 @@
       </c>
       <c r="J13" s="3">
         <f t="array" aca="1" ref="J13" ca="1">_FV(B13,"52 week high",TRUE)</f>
-        <v>495.41989999999998</v>
+        <v>496.88990000000001</v>
       </c>
       <c r="K13" s="3">
         <f t="array" aca="1" ref="K13" ca="1">_FV(B13,"52 week low",TRUE)</f>
@@ -11065,7 +10376,7 @@
       </c>
       <c r="L13" s="3">
         <f t="array" aca="1" ref="L13" ca="1">_FV(B13,"High")</f>
-        <v>495.41989999999998</v>
+        <v>496.88990000000001</v>
       </c>
       <c r="M13" s="3">
         <f t="array" aca="1" ref="M13" ca="1">_FV(B13,"Low")</f>
@@ -11081,7 +10392,7 @@
       </c>
       <c r="P13" s="7">
         <f t="array" aca="1" ref="P13" ca="1">_FV(B13,"Volume")</f>
-        <v>11444409</v>
+        <v>18569704</v>
       </c>
       <c r="Q13" s="7">
         <f t="array" aca="1" ref="Q13" ca="1">_FV(B13,"Volume average",TRUE)</f>
@@ -11101,7 +10412,7 @@
       </c>
       <c r="U13" s="7">
         <f t="array" aca="1" ref="U13" ca="1">_FV(B13,"Market cap",TRUE)</f>
-        <v>805639189075</v>
+        <v>806592927599</v>
       </c>
       <c r="V13" s="7">
         <f t="array" aca="1" ref="V13" ca="1">_FV(B13,"Shares outstanding",TRUE)</f>
@@ -11117,7 +10428,7 @@
       </c>
       <c r="C14" s="2">
         <f t="array" aca="1" ref="C14" ca="1">_FV(B14,"Last trade time",TRUE)</f>
-        <v>46168.605513263283</v>
+        <v>46168.683372777341</v>
       </c>
       <c r="D14" t="str">
         <f t="array" aca="1" ref="D14" ca="1">_FV(B14,"Currency")</f>
@@ -11125,19 +10436,19 @@
       </c>
       <c r="E14" s="3">
         <f t="array" aca="1" ref="E14" ca="1">_FV(B14,"Price")</f>
-        <v>54.38</v>
+        <v>54.33</v>
       </c>
       <c r="F14" s="4">
         <f t="array" aca="1" ref="F14" ca="1">_FV(B14,"Change (%)",TRUE)</f>
-        <v>5.6742999999999995E-2</v>
+        <v>5.5770999999999994E-2</v>
       </c>
       <c r="G14" s="5">
         <f t="array" aca="1" ref="G14" ca="1">_FV(B14,"Change")</f>
-        <v>2.92</v>
+        <v>2.87</v>
       </c>
       <c r="H14" s="6">
         <f t="array" aca="1" ref="H14" ca="1">_FV(B14,"P/E",TRUE)</f>
-        <v>23.231400000000001</v>
+        <v>23.21</v>
       </c>
       <c r="I14" s="6">
         <f t="array" aca="1" ref="I14" ca="1">_FV(B14,"Beta")</f>
@@ -11169,7 +10480,7 @@
       </c>
       <c r="P14" s="7">
         <f t="array" aca="1" ref="P14" ca="1">_FV(B14,"Volume")</f>
-        <v>247938</v>
+        <v>461938</v>
       </c>
       <c r="Q14" s="7">
         <f t="array" aca="1" ref="Q14" ca="1">_FV(B14,"Volume average",TRUE)</f>
@@ -11189,7 +10500,7 @@
       </c>
       <c r="U14" s="7">
         <f t="array" aca="1" ref="U14" ca="1">_FV(B14,"Market cap",TRUE)</f>
-        <v>3206592288</v>
+        <v>3203643968</v>
       </c>
       <c r="V14" s="7">
         <f t="array" aca="1" ref="V14" ca="1">_FV(B14,"Shares outstanding",TRUE)</f>
@@ -11205,7 +10516,7 @@
       </c>
       <c r="C15" s="2" cm="1">
         <f t="array" aca="1" ref="C15" ca="1">_FV(B15,"Last trade time",TRUE)</f>
-        <v>46168.6054773375</v>
+        <v>46168.683473182813</v>
       </c>
       <c r="D15" t="str" cm="1">
         <f t="array" aca="1" ref="D15" ca="1">_FV(B15,"Currency")</f>
@@ -11213,19 +10524,19 @@
       </c>
       <c r="E15" s="3" cm="1">
         <f t="array" aca="1" ref="E15" ca="1">_FV(B15,"Price")</f>
-        <v>1986.8</v>
+        <v>1981.2249999999999</v>
       </c>
       <c r="F15" s="4" cm="1">
         <f t="array" aca="1" ref="F15" ca="1">_FV(B15,"Change (%)",TRUE)</f>
-        <v>5.2118999999999999E-2</v>
+        <v>4.9166000000000001E-2</v>
       </c>
       <c r="G15" s="5" cm="1">
         <f t="array" aca="1" ref="G15" ca="1">_FV(B15,"Change")</f>
-        <v>98.42</v>
+        <v>92.844999999999999</v>
       </c>
       <c r="H15" s="6" cm="1">
         <f t="array" aca="1" ref="H15" ca="1">_FV(B15,"P/E",TRUE)</f>
-        <v>56.251100000000001</v>
+        <v>56.093299999999999</v>
       </c>
       <c r="I15" s="6" cm="1">
         <f t="array" aca="1" ref="I15" ca="1">_FV(B15,"Beta")</f>
@@ -11233,7 +10544,7 @@
       </c>
       <c r="J15" s="3" cm="1">
         <f t="array" aca="1" ref="J15" ca="1">_FV(B15,"52 week high",TRUE)</f>
-        <v>1987.3</v>
+        <v>1998.32</v>
       </c>
       <c r="K15" s="3" cm="1">
         <f t="array" aca="1" ref="K15" ca="1">_FV(B15,"52 week low",TRUE)</f>
@@ -11241,7 +10552,7 @@
       </c>
       <c r="L15" s="3" cm="1">
         <f t="array" aca="1" ref="L15" ca="1">_FV(B15,"High")</f>
-        <v>1987.3</v>
+        <v>1998.32</v>
       </c>
       <c r="M15" s="3" cm="1">
         <f t="array" aca="1" ref="M15" ca="1">_FV(B15,"Low")</f>
@@ -11257,7 +10568,7 @@
       </c>
       <c r="P15" s="7" cm="1">
         <f t="array" aca="1" ref="P15" ca="1">_FV(B15,"Volume")</f>
-        <v>182213</v>
+        <v>374029</v>
       </c>
       <c r="Q15" s="7" cm="1">
         <f t="array" aca="1" ref="Q15" ca="1">_FV(B15,"Volume average",TRUE)</f>
@@ -11277,7 +10588,7 @@
       </c>
       <c r="U15" s="7" cm="1">
         <f t="array" aca="1" ref="U15" ca="1">_FV(B15,"Market cap",TRUE)</f>
-        <v>259530717000</v>
+        <v>258802468687</v>
       </c>
       <c r="V15" s="7" cm="1">
         <f t="array" aca="1" ref="V15" ca="1">_FV(B15,"Shares outstanding",TRUE)</f>
@@ -11293,7 +10604,7 @@
       </c>
       <c r="C16" s="2" cm="1">
         <f t="array" aca="1" ref="C16" ca="1">_FV(B16,"Last trade time",TRUE)</f>
-        <v>46168.60555663125</v>
+        <v>46168.683493425779</v>
       </c>
       <c r="D16" t="str" cm="1">
         <f t="array" aca="1" ref="D16" ca="1">_FV(B16,"Currency")</f>
@@ -11301,19 +10612,19 @@
       </c>
       <c r="E16" s="3" cm="1">
         <f t="array" aca="1" ref="E16" ca="1">_FV(B16,"Price")</f>
-        <v>309.66000000000003</v>
+        <v>305.60500000000002</v>
       </c>
       <c r="F16" s="4" cm="1">
         <f t="array" aca="1" ref="F16" ca="1">_FV(B16,"Change (%)",TRUE)</f>
-        <v>5.3015E-2</v>
+        <v>3.9224999999999996E-2</v>
       </c>
       <c r="G16" s="5" cm="1">
         <f t="array" aca="1" ref="G16" ca="1">_FV(B16,"Change")</f>
-        <v>15.59</v>
+        <v>11.535</v>
       </c>
       <c r="H16" s="6" cm="1">
         <f t="array" aca="1" ref="H16" ca="1">_FV(B16,"P/E",TRUE)</f>
-        <v>26.902200000000001</v>
+        <v>26.549900000000001</v>
       </c>
       <c r="I16" s="6" cm="1">
         <f t="array" aca="1" ref="I16" ca="1">_FV(B16,"Beta")</f>
@@ -11345,7 +10656,7 @@
       </c>
       <c r="P16" s="7" cm="1">
         <f t="array" aca="1" ref="P16" ca="1">_FV(B16,"Volume")</f>
-        <v>1020551</v>
+        <v>1851937</v>
       </c>
       <c r="Q16" s="7" cm="1">
         <f t="array" aca="1" ref="Q16" ca="1">_FV(B16,"Volume average",TRUE)</f>
@@ -11365,7 +10676,7 @@
       </c>
       <c r="U16" s="7" cm="1">
         <f t="array" aca="1" ref="U16" ca="1">_FV(B16,"Market cap",TRUE)</f>
-        <v>111846126366</v>
+        <v>110381500510</v>
       </c>
       <c r="V16" s="7" cm="1">
         <f t="array" aca="1" ref="V16" ca="1">_FV(B16,"Shares outstanding",TRUE)</f>
@@ -11381,7 +10692,7 @@
       </c>
       <c r="C17" s="2">
         <f t="array" aca="1" ref="C17" ca="1">_FV(B17,"Last trade time",TRUE)</f>
-        <v>46168.60553048594</v>
+        <v>46168.683489767966</v>
       </c>
       <c r="D17" t="str">
         <f t="array" aca="1" ref="D17" ca="1">_FV(B17,"Currency")</f>
@@ -11389,19 +10700,19 @@
       </c>
       <c r="E17" s="3">
         <f t="array" aca="1" ref="E17" ca="1">_FV(B17,"Price")</f>
-        <v>434.33</v>
+        <v>422.2</v>
       </c>
       <c r="F17" s="4">
         <f t="array" aca="1" ref="F17" ca="1">_FV(B17,"Change (%)",TRUE)</f>
-        <v>4.8752000000000004E-2</v>
+        <v>1.9462E-2</v>
       </c>
       <c r="G17" s="5">
         <f t="array" aca="1" ref="G17" ca="1">_FV(B17,"Change")</f>
-        <v>20.190000000000001</v>
+        <v>8.06</v>
       </c>
       <c r="H17" s="6">
         <f t="array" aca="1" ref="H17" ca="1">_FV(B17,"P/E",TRUE)</f>
-        <v>84.7821</v>
+        <v>82.414299999999997</v>
       </c>
       <c r="I17" s="6">
         <f t="array" aca="1" ref="I17" ca="1">_FV(B17,"Beta")</f>
@@ -11417,7 +10728,7 @@
       </c>
       <c r="L17" s="3">
         <f t="array" aca="1" ref="L17" ca="1">_FV(B17,"High")</f>
-        <v>434.87</v>
+        <v>435.31</v>
       </c>
       <c r="M17" s="3">
         <f t="array" aca="1" ref="M17" ca="1">_FV(B17,"Low")</f>
@@ -11433,7 +10744,7 @@
       </c>
       <c r="P17" s="7">
         <f t="array" aca="1" ref="P17" ca="1">_FV(B17,"Volume")</f>
-        <v>5341488</v>
+        <v>8743289</v>
       </c>
       <c r="Q17" s="7">
         <f t="array" aca="1" ref="Q17" ca="1">_FV(B17,"Volume average",TRUE)</f>
@@ -11453,7 +10764,7 @@
       </c>
       <c r="U17" s="7">
         <f t="array" aca="1" ref="U17" ca="1">_FV(B17,"Market cap",TRUE)</f>
-        <v>2056408352440</v>
+        <v>1998976829600</v>
       </c>
       <c r="V17" s="7">
         <f t="array" aca="1" ref="V17" ca="1">_FV(B17,"Shares outstanding",TRUE)</f>
@@ -11469,7 +10780,7 @@
       </c>
       <c r="C18" s="2" cm="1">
         <f t="array" aca="1" ref="C18" ca="1">_FV(B18,"Last trade time",TRUE)</f>
-        <v>46168.60555719844</v>
+        <v>46168.683522765627</v>
       </c>
       <c r="D18" t="str" cm="1">
         <f t="array" aca="1" ref="D18" ca="1">_FV(B18,"Currency")</f>
@@ -11477,15 +10788,15 @@
       </c>
       <c r="E18" s="3" cm="1">
         <f t="array" aca="1" ref="E18" ca="1">_FV(B18,"Price")</f>
-        <v>601.88</v>
+        <v>596.48500000000001</v>
       </c>
       <c r="F18" s="4" cm="1">
         <f t="array" aca="1" ref="F18" ca="1">_FV(B18,"Change (%)",TRUE)</f>
-        <v>4.4349999999999994E-2</v>
+        <v>3.4988999999999999E-2</v>
       </c>
       <c r="G18" s="5" cm="1">
         <f t="array" aca="1" ref="G18" ca="1">_FV(B18,"Change")</f>
-        <v>25.56</v>
+        <v>20.164999999999999</v>
       </c>
       <c r="H18" s="6" t="e" cm="1" vm="12">
         <f t="array" ref="H18">_FV(B18,"P/E",TRUE)</f>
@@ -11497,7 +10808,7 @@
       </c>
       <c r="J18" s="3" cm="1">
         <f t="array" aca="1" ref="J18" ca="1">_FV(B18,"52 week high",TRUE)</f>
-        <v>601.90930000000003</v>
+        <v>603.73500000000001</v>
       </c>
       <c r="K18" s="3" cm="1">
         <f t="array" aca="1" ref="K18" ca="1">_FV(B18,"52 week low",TRUE)</f>
@@ -11505,7 +10816,7 @@
       </c>
       <c r="L18" s="3" cm="1">
         <f t="array" aca="1" ref="L18" ca="1">_FV(B18,"High")</f>
-        <v>601.90930000000003</v>
+        <v>603.73500000000001</v>
       </c>
       <c r="M18" s="3" cm="1">
         <f t="array" aca="1" ref="M18" ca="1">_FV(B18,"Low")</f>
@@ -11521,7 +10832,7 @@
       </c>
       <c r="P18" s="7" cm="1">
         <f t="array" aca="1" ref="P18" ca="1">_FV(B18,"Volume")</f>
-        <v>2911624</v>
+        <v>6098128</v>
       </c>
       <c r="Q18" s="7" cm="1">
         <f t="array" aca="1" ref="Q18" ca="1">_FV(B18,"Volume average",TRUE)</f>
@@ -11557,7 +10868,7 @@
       </c>
       <c r="C19" s="2" cm="1">
         <f t="array" aca="1" ref="C19" ca="1">_FV(B19,"Last trade time",TRUE)</f>
-        <v>46168.605529803128</v>
+        <v>46168.683453796097</v>
       </c>
       <c r="D19" t="str" cm="1">
         <f t="array" aca="1" ref="D19" ca="1">_FV(B19,"Currency")</f>
@@ -11565,19 +10876,19 @@
       </c>
       <c r="E19" s="3" cm="1">
         <f t="array" aca="1" ref="E19" ca="1">_FV(B19,"Price")</f>
-        <v>407.73989999999998</v>
+        <v>407.93990000000002</v>
       </c>
       <c r="F19" s="4" cm="1">
         <f t="array" aca="1" ref="F19" ca="1">_FV(B19,"Change (%)",TRUE)</f>
-        <v>4.1880000000000001E-2</v>
+        <v>4.2390999999999998E-2</v>
       </c>
       <c r="G19" s="5" cm="1">
         <f t="array" aca="1" ref="G19" ca="1">_FV(B19,"Change")</f>
-        <v>16.389900000000001</v>
+        <v>16.5899</v>
       </c>
       <c r="H19" s="6" cm="1">
         <f t="array" aca="1" ref="H19" ca="1">_FV(B19,"P/E",TRUE)</f>
-        <v>39.861899999999999</v>
+        <v>39.881500000000003</v>
       </c>
       <c r="I19" s="6" cm="1">
         <f t="array" aca="1" ref="I19" ca="1">_FV(B19,"Beta")</f>
@@ -11593,7 +10904,7 @@
       </c>
       <c r="L19" s="3" cm="1">
         <f t="array" aca="1" ref="L19" ca="1">_FV(B19,"High")</f>
-        <v>408</v>
+        <v>409.65</v>
       </c>
       <c r="M19" s="3" cm="1">
         <f t="array" aca="1" ref="M19" ca="1">_FV(B19,"Low")</f>
@@ -11609,7 +10920,7 @@
       </c>
       <c r="P19" s="7" cm="1">
         <f t="array" aca="1" ref="P19" ca="1">_FV(B19,"Volume")</f>
-        <v>590607</v>
+        <v>1233419</v>
       </c>
       <c r="Q19" s="7" cm="1">
         <f t="array" aca="1" ref="Q19" ca="1">_FV(B19,"Volume average",TRUE)</f>
@@ -11629,7 +10940,7 @@
       </c>
       <c r="U19" s="7" cm="1">
         <f t="array" aca="1" ref="U19" ca="1">_FV(B19,"Market cap",TRUE)</f>
-        <v>158325403170</v>
+        <v>158403063170</v>
       </c>
       <c r="V19" s="7" cm="1">
         <f t="array" aca="1" ref="V19" ca="1">_FV(B19,"Shares outstanding",TRUE)</f>
@@ -11645,7 +10956,7 @@
       </c>
       <c r="C20" s="2" cm="1">
         <f t="array" aca="1" ref="C20" ca="1">_FV(B20,"Last trade time",TRUE)</f>
-        <v>46168.605528506247</v>
+        <v>46168.683516562502</v>
       </c>
       <c r="D20" t="str" cm="1">
         <f t="array" aca="1" ref="D20" ca="1">_FV(B20,"Currency")</f>
@@ -11653,19 +10964,19 @@
       </c>
       <c r="E20" s="3" cm="1">
         <f t="array" aca="1" ref="E20" ca="1">_FV(B20,"Price")</f>
-        <v>339.47</v>
+        <v>329.71499999999997</v>
       </c>
       <c r="F20" s="4" cm="1">
         <f t="array" aca="1" ref="F20" ca="1">_FV(B20,"Change (%)",TRUE)</f>
-        <v>3.6676E-2</v>
+        <v>6.8859999999999998E-3</v>
       </c>
       <c r="G20" s="5" cm="1">
         <f t="array" aca="1" ref="G20" ca="1">_FV(B20,"Change")</f>
-        <v>12.01</v>
+        <v>2.2549999999999999</v>
       </c>
       <c r="H20" s="6" cm="1">
         <f t="array" aca="1" ref="H20" ca="1">_FV(B20,"P/E",TRUE)</f>
-        <v>85.229699999999994</v>
+        <v>82.780600000000007</v>
       </c>
       <c r="I20" s="6" cm="1">
         <f t="array" aca="1" ref="I20" ca="1">_FV(B20,"Beta")</f>
@@ -11685,7 +10996,7 @@
       </c>
       <c r="M20" s="3" cm="1">
         <f t="array" aca="1" ref="M20" ca="1">_FV(B20,"Low")</f>
-        <v>336</v>
+        <v>328.58</v>
       </c>
       <c r="N20" s="3" cm="1">
         <f t="array" aca="1" ref="N20" ca="1">_FV(B20,"Open")</f>
@@ -11697,7 +11008,7 @@
       </c>
       <c r="P20" s="7" cm="1">
         <f t="array" aca="1" ref="P20" ca="1">_FV(B20,"Volume")</f>
-        <v>1720809</v>
+        <v>2966078</v>
       </c>
       <c r="Q20" s="7" cm="1">
         <f t="array" aca="1" ref="Q20" ca="1">_FV(B20,"Volume average",TRUE)</f>
@@ -11717,7 +11028,7 @@
       </c>
       <c r="U20" s="7" cm="1">
         <f t="array" aca="1" ref="U20" ca="1">_FV(B20,"Market cap",TRUE)</f>
-        <v>130393414336</v>
+        <v>126646432991</v>
       </c>
       <c r="V20" s="7" cm="1">
         <f t="array" aca="1" ref="V20" ca="1">_FV(B20,"Shares outstanding",TRUE)</f>
@@ -11733,7 +11044,7 @@
       </c>
       <c r="C21" s="2">
         <f t="array" aca="1" ref="C21" ca="1">_FV(B21,"Last trade time",TRUE)</f>
-        <v>46168.605554710157</v>
+        <v>46168.683502106251</v>
       </c>
       <c r="D21" t="str">
         <f t="array" aca="1" ref="D21" ca="1">_FV(B21,"Currency")</f>
@@ -11741,15 +11052,15 @@
       </c>
       <c r="E21" s="3">
         <f t="array" aca="1" ref="E21" ca="1">_FV(B21,"Price")</f>
-        <v>47.534999999999997</v>
+        <v>47.72</v>
       </c>
       <c r="F21" s="4">
         <f t="array" aca="1" ref="F21" ca="1">_FV(B21,"Change (%)",TRUE)</f>
-        <v>2.9342E-2</v>
+        <v>3.3348000000000003E-2</v>
       </c>
       <c r="G21" s="5">
         <f t="array" aca="1" ref="G21" ca="1">_FV(B21,"Change")</f>
-        <v>1.355</v>
+        <v>1.54</v>
       </c>
       <c r="H21" s="6">
         <f t="array" aca="1" ref="H21" ca="1">_FV(B21,"P/E",TRUE)</f>
@@ -11785,7 +11096,7 @@
       </c>
       <c r="P21" s="7">
         <f t="array" aca="1" ref="P21" ca="1">_FV(B21,"Volume")</f>
-        <v>1696565</v>
+        <v>2700326</v>
       </c>
       <c r="Q21" s="7">
         <f t="array" aca="1" ref="Q21" ca="1">_FV(B21,"Volume average",TRUE)</f>
@@ -11805,7 +11116,7 @@
       </c>
       <c r="U21" s="7">
         <f t="array" aca="1" ref="U21" ca="1">_FV(B21,"Market cap",TRUE)</f>
-        <v>8535612767</v>
+        <v>8568832256</v>
       </c>
       <c r="V21" s="7">
         <f t="array" aca="1" ref="V21" ca="1">_FV(B21,"Shares outstanding",TRUE)</f>
@@ -11821,7 +11132,7 @@
       </c>
       <c r="C22" s="2" cm="1">
         <f t="array" aca="1" ref="C22" ca="1">_FV(B22,"Last trade time",TRUE)</f>
-        <v>46168.605548251566</v>
+        <v>46168.683503796092</v>
       </c>
       <c r="D22" t="str" cm="1">
         <f t="array" aca="1" ref="D22" ca="1">_FV(B22,"Currency")</f>
@@ -11829,19 +11140,19 @@
       </c>
       <c r="E22" s="3" cm="1">
         <f t="array" aca="1" ref="E22" ca="1">_FV(B22,"Price")</f>
-        <v>301.98989999999998</v>
+        <v>303.52499999999998</v>
       </c>
       <c r="F22" s="4" cm="1">
         <f t="array" aca="1" ref="F22" ca="1">_FV(B22,"Change (%)",TRUE)</f>
-        <v>2.3035999999999997E-2</v>
+        <v>2.8235999999999997E-2</v>
       </c>
       <c r="G22" s="5" cm="1">
         <f t="array" aca="1" ref="G22" ca="1">_FV(B22,"Change")</f>
-        <v>6.7999000000000001</v>
+        <v>8.3350000000000009</v>
       </c>
       <c r="H22" s="6" cm="1">
         <f t="array" aca="1" ref="H22" ca="1">_FV(B22,"P/E",TRUE)</f>
-        <v>34.606900000000003</v>
+        <v>34.782800000000002</v>
       </c>
       <c r="I22" s="6" cm="1">
         <f t="array" aca="1" ref="I22" ca="1">_FV(B22,"Beta")</f>
@@ -11873,7 +11184,7 @@
       </c>
       <c r="P22" s="7" cm="1">
         <f t="array" aca="1" ref="P22" ca="1">_FV(B22,"Volume")</f>
-        <v>3893063</v>
+        <v>5839272</v>
       </c>
       <c r="Q22" s="7" cm="1">
         <f t="array" aca="1" ref="Q22" ca="1">_FV(B22,"Volume average",TRUE)</f>
@@ -11893,7 +11204,7 @@
       </c>
       <c r="U22" s="7" cm="1">
         <f t="array" aca="1" ref="U22" ca="1">_FV(B22,"Market cap",TRUE)</f>
-        <v>196163065960</v>
+        <v>197160218257</v>
       </c>
       <c r="V22" s="7" cm="1">
         <f t="array" aca="1" ref="V22" ca="1">_FV(B22,"Shares outstanding",TRUE)</f>
@@ -11909,7 +11220,7 @@
       </c>
       <c r="C23" s="2">
         <f t="array" aca="1" ref="C23" ca="1">_FV(B23,"Last trade time",TRUE)</f>
-        <v>46168.60548709453</v>
+        <v>46168.683489930467</v>
       </c>
       <c r="D23" t="str">
         <f t="array" aca="1" ref="D23" ca="1">_FV(B23,"Currency")</f>
@@ -11917,19 +11228,19 @@
       </c>
       <c r="E23" s="3">
         <f t="array" aca="1" ref="E23" ca="1">_FV(B23,"Price")</f>
-        <v>98.267200000000003</v>
+        <v>97.33</v>
       </c>
       <c r="F23" s="4">
         <f t="array" aca="1" ref="F23" ca="1">_FV(B23,"Change (%)",TRUE)</f>
-        <v>2.9190999999999998E-2</v>
+        <v>1.9376000000000001E-2</v>
       </c>
       <c r="G23" s="5">
         <f t="array" aca="1" ref="G23" ca="1">_FV(B23,"Change")</f>
-        <v>2.7871999999999999</v>
+        <v>1.85</v>
       </c>
       <c r="H23" s="6">
         <f t="array" aca="1" ref="H23" ca="1">_FV(B23,"P/E",TRUE)</f>
-        <v>88.417500000000004</v>
+        <v>87.574200000000005</v>
       </c>
       <c r="I23" s="6">
         <f t="array" aca="1" ref="I23" ca="1">_FV(B23,"Beta")</f>
@@ -11961,7 +11272,7 @@
       </c>
       <c r="P23" s="7">
         <f t="array" aca="1" ref="P23" ca="1">_FV(B23,"Volume")</f>
-        <v>588605</v>
+        <v>815062</v>
       </c>
       <c r="Q23" s="7">
         <f t="array" aca="1" ref="Q23" ca="1">_FV(B23,"Volume average",TRUE)</f>
@@ -11997,7 +11308,7 @@
       </c>
       <c r="C24" s="2" cm="1">
         <f t="array" aca="1" ref="C24" ca="1">_FV(B24,"Last trade time",TRUE)</f>
-        <v>46168.605561990626</v>
+        <v>46168.68352896953</v>
       </c>
       <c r="D24" t="str" cm="1">
         <f t="array" aca="1" ref="D24" ca="1">_FV(B24,"Currency")</f>
@@ -12005,15 +11316,15 @@
       </c>
       <c r="E24" s="3" cm="1">
         <f t="array" aca="1" ref="E24" ca="1">_FV(B24,"Price")</f>
-        <v>177.2</v>
+        <v>179.215</v>
       </c>
       <c r="F24" s="4" cm="1">
         <f t="array" aca="1" ref="F24" ca="1">_FV(B24,"Change (%)",TRUE)</f>
-        <v>2.9035999999999999E-2</v>
+        <v>4.0738000000000003E-2</v>
       </c>
       <c r="G24" s="5" cm="1">
         <f t="array" aca="1" ref="G24" ca="1">_FV(B24,"Change")</f>
-        <v>5</v>
+        <v>7.0149999999999997</v>
       </c>
       <c r="H24" s="6" cm="1">
         <f t="array" aca="1" ref="H24" ca="1">_FV(B24,"P/E",TRUE)</f>
@@ -12049,7 +11360,7 @@
       </c>
       <c r="P24" s="7" cm="1">
         <f t="array" aca="1" ref="P24" ca="1">_FV(B24,"Volume")</f>
-        <v>3539960</v>
+        <v>6265669</v>
       </c>
       <c r="Q24" s="7" cm="1">
         <f t="array" aca="1" ref="Q24" ca="1">_FV(B24,"Volume average",TRUE)</f>
@@ -12069,7 +11380,7 @@
       </c>
       <c r="U24" s="7" cm="1">
         <f t="array" aca="1" ref="U24" ca="1">_FV(B24,"Market cap",TRUE)</f>
-        <v>61418033879</v>
+        <v>62116438723</v>
       </c>
       <c r="V24" s="7" cm="1">
         <f t="array" aca="1" ref="V24" ca="1">_FV(B24,"Shares outstanding",TRUE)</f>
@@ -12085,7 +11396,7 @@
       </c>
       <c r="C25" s="2">
         <f t="array" aca="1" ref="C25" ca="1">_FV(B25,"Last trade time",TRUE)</f>
-        <v>46168.605549582811</v>
+        <v>46168.683506330468</v>
       </c>
       <c r="D25" t="str">
         <f t="array" aca="1" ref="D25" ca="1">_FV(B25,"Currency")</f>
@@ -12093,19 +11404,19 @@
       </c>
       <c r="E25" s="3">
         <f t="array" aca="1" ref="E25" ca="1">_FV(B25,"Price")</f>
-        <v>11.175000000000001</v>
+        <v>11.345000000000001</v>
       </c>
       <c r="F25" s="4">
         <f t="array" aca="1" ref="F25" ca="1">_FV(B25,"Change (%)",TRUE)</f>
-        <v>2.2414999999999997E-2</v>
+        <v>3.7969000000000003E-2</v>
       </c>
       <c r="G25" s="5">
         <f t="array" aca="1" ref="G25" ca="1">_FV(B25,"Change")</f>
-        <v>0.245</v>
+        <v>0.41499999999999998</v>
       </c>
       <c r="H25" s="6">
         <f t="array" aca="1" ref="H25" ca="1">_FV(B25,"P/E",TRUE)</f>
-        <v>21.490400000000001</v>
+        <v>21.817299999999999</v>
       </c>
       <c r="I25" s="6">
         <f t="array" aca="1" ref="I25" ca="1">_FV(B25,"Beta")</f>
@@ -12121,7 +11432,7 @@
       </c>
       <c r="L25" s="3">
         <f t="array" aca="1" ref="L25" ca="1">_FV(B25,"High")</f>
-        <v>11.29</v>
+        <v>11.38</v>
       </c>
       <c r="M25" s="3">
         <f t="array" aca="1" ref="M25" ca="1">_FV(B25,"Low")</f>
@@ -12137,7 +11448,7 @@
       </c>
       <c r="P25" s="7">
         <f t="array" aca="1" ref="P25" ca="1">_FV(B25,"Volume")</f>
-        <v>9365216</v>
+        <v>20890381</v>
       </c>
       <c r="Q25" s="7">
         <f t="array" aca="1" ref="Q25" ca="1">_FV(B25,"Volume average",TRUE)</f>
@@ -12157,7 +11468,7 @@
       </c>
       <c r="U25" s="7">
         <f t="array" aca="1" ref="U25" ca="1">_FV(B25,"Market cap",TRUE)</f>
-        <v>5815954995</v>
+        <v>5904430373</v>
       </c>
       <c r="V25" s="7">
         <f t="array" aca="1" ref="V25" ca="1">_FV(B25,"Shares outstanding",TRUE)</f>
@@ -12173,7 +11484,7 @@
       </c>
       <c r="C26" s="2">
         <f t="array" aca="1" ref="C26" ca="1">_FV(B26,"Last trade time",TRUE)</f>
-        <v>46168.605510497655</v>
+        <v>46168.683415150001</v>
       </c>
       <c r="D26" t="str">
         <f t="array" aca="1" ref="D26" ca="1">_FV(B26,"Currency")</f>
@@ -12181,19 +11492,19 @@
       </c>
       <c r="E26" s="3">
         <f t="array" aca="1" ref="E26" ca="1">_FV(B26,"Price")</f>
-        <v>23.36</v>
+        <v>23.4</v>
       </c>
       <c r="F26" s="4">
         <f t="array" aca="1" ref="F26" ca="1">_FV(B26,"Change (%)",TRUE)</f>
-        <v>2.6362E-2</v>
+        <v>2.8119999999999999E-2</v>
       </c>
       <c r="G26" s="5">
         <f t="array" aca="1" ref="G26" ca="1">_FV(B26,"Change")</f>
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="H26" s="6">
         <f t="array" aca="1" ref="H26" ca="1">_FV(B26,"P/E",TRUE)</f>
-        <v>35.4208</v>
+        <v>35.481400000000001</v>
       </c>
       <c r="I26" s="6">
         <f t="array" aca="1" ref="I26" ca="1">_FV(B26,"Beta")</f>
@@ -12209,7 +11520,7 @@
       </c>
       <c r="L26" s="3">
         <f t="array" aca="1" ref="L26" ca="1">_FV(B26,"High")</f>
-        <v>23.5488</v>
+        <v>23.66</v>
       </c>
       <c r="M26" s="3">
         <f t="array" aca="1" ref="M26" ca="1">_FV(B26,"Low")</f>
@@ -12225,7 +11536,7 @@
       </c>
       <c r="P26" s="7">
         <f t="array" aca="1" ref="P26" ca="1">_FV(B26,"Volume")</f>
-        <v>740395</v>
+        <v>1229849</v>
       </c>
       <c r="Q26" s="7">
         <f t="array" aca="1" ref="Q26" ca="1">_FV(B26,"Volume average",TRUE)</f>
@@ -12245,7 +11556,7 @@
       </c>
       <c r="U26" s="7">
         <f t="array" aca="1" ref="U26" ca="1">_FV(B26,"Market cap",TRUE)</f>
-        <v>1788534806</v>
+        <v>1791597366</v>
       </c>
       <c r="V26" s="7">
         <f t="array" aca="1" ref="V26" ca="1">_FV(B26,"Shares outstanding",TRUE)</f>
@@ -12261,7 +11572,7 @@
       </c>
       <c r="C27" s="2" cm="1">
         <f t="array" aca="1" ref="C27" ca="1">_FV(B27,"Last trade time",TRUE)</f>
-        <v>46168.605486053122</v>
+        <v>46168.683480161715</v>
       </c>
       <c r="D27" t="str" cm="1">
         <f t="array" aca="1" ref="D27" ca="1">_FV(B27,"Currency")</f>
@@ -12269,15 +11580,15 @@
       </c>
       <c r="E27" s="3" cm="1">
         <f t="array" aca="1" ref="E27" ca="1">_FV(B27,"Price")</f>
-        <v>186.51</v>
+        <v>189.51</v>
       </c>
       <c r="F27" s="4" cm="1">
         <f t="array" aca="1" ref="F27" ca="1">_FV(B27,"Change (%)",TRUE)</f>
-        <v>2.2700999999999999E-2</v>
+        <v>3.9150999999999998E-2</v>
       </c>
       <c r="G27" s="5" cm="1">
         <f t="array" aca="1" ref="G27" ca="1">_FV(B27,"Change")</f>
-        <v>4.1399999999999997</v>
+        <v>7.14</v>
       </c>
       <c r="H27" s="6" cm="1">
         <f t="array" aca="1" ref="H27" ca="1">_FV(B27,"P/E",TRUE)</f>
@@ -12297,7 +11608,7 @@
       </c>
       <c r="L27" s="3" cm="1">
         <f t="array" aca="1" ref="L27" ca="1">_FV(B27,"High")</f>
-        <v>188.25</v>
+        <v>189.64</v>
       </c>
       <c r="M27" s="3" cm="1">
         <f t="array" aca="1" ref="M27" ca="1">_FV(B27,"Low")</f>
@@ -12313,7 +11624,7 @@
       </c>
       <c r="P27" s="7" cm="1">
         <f t="array" aca="1" ref="P27" ca="1">_FV(B27,"Volume")</f>
-        <v>1498213</v>
+        <v>2770092</v>
       </c>
       <c r="Q27" s="7" cm="1">
         <f t="array" aca="1" ref="Q27" ca="1">_FV(B27,"Volume average",TRUE)</f>
@@ -12333,7 +11644,7 @@
       </c>
       <c r="U27" s="7" cm="1">
         <f t="array" aca="1" ref="U27" ca="1">_FV(B27,"Market cap",TRUE)</f>
-        <v>29989073457</v>
+        <v>30471445557</v>
       </c>
       <c r="V27" s="7" cm="1">
         <f t="array" aca="1" ref="V27" ca="1">_FV(B27,"Shares outstanding",TRUE)</f>
@@ -12349,7 +11660,7 @@
       </c>
       <c r="C28" s="2" cm="1">
         <f t="array" aca="1" ref="C28" ca="1">_FV(B28,"Last trade time",TRUE)</f>
-        <v>46168.605569073436</v>
+        <v>46168.683479247658</v>
       </c>
       <c r="D28" t="str" cm="1">
         <f t="array" aca="1" ref="D28" ca="1">_FV(B28,"Currency")</f>
@@ -12357,19 +11668,19 @@
       </c>
       <c r="E28" s="3" cm="1">
         <f t="array" aca="1" ref="E28" ca="1">_FV(B28,"Price")</f>
-        <v>537.6</v>
+        <v>534.35500000000002</v>
       </c>
       <c r="F28" s="4" cm="1">
         <f t="array" aca="1" ref="F28" ca="1">_FV(B28,"Change (%)",TRUE)</f>
-        <v>2.4506999999999998E-2</v>
+        <v>1.8322999999999999E-2</v>
       </c>
       <c r="G28" s="5" cm="1">
         <f t="array" aca="1" ref="G28" ca="1">_FV(B28,"Change")</f>
-        <v>12.86</v>
+        <v>9.6150000000000002</v>
       </c>
       <c r="H28" s="6" cm="1">
         <f t="array" aca="1" ref="H28" ca="1">_FV(B28,"P/E",TRUE)</f>
-        <v>83.177300000000002</v>
+        <v>82.675299999999993</v>
       </c>
       <c r="I28" s="6" cm="1">
         <f t="array" aca="1" ref="I28" ca="1">_FV(B28,"Beta")</f>
@@ -12385,7 +11696,7 @@
       </c>
       <c r="L28" s="3" cm="1">
         <f t="array" aca="1" ref="L28" ca="1">_FV(B28,"High")</f>
-        <v>537.6</v>
+        <v>539.48</v>
       </c>
       <c r="M28" s="3" cm="1">
         <f t="array" aca="1" ref="M28" ca="1">_FV(B28,"Low")</f>
@@ -12401,7 +11712,7 @@
       </c>
       <c r="P28" s="7" cm="1">
         <f t="array" aca="1" ref="P28" ca="1">_FV(B28,"Volume")</f>
-        <v>328417</v>
+        <v>645475</v>
       </c>
       <c r="Q28" s="7" cm="1">
         <f t="array" aca="1" ref="Q28" ca="1">_FV(B28,"Volume average",TRUE)</f>
@@ -12421,7 +11732,7 @@
       </c>
       <c r="U28" s="7" cm="1">
         <f t="array" aca="1" ref="U28" ca="1">_FV(B28,"Market cap",TRUE)</f>
-        <v>102983731200</v>
+        <v>102362112510</v>
       </c>
       <c r="V28" s="7" cm="1">
         <f t="array" aca="1" ref="V28" ca="1">_FV(B28,"Shares outstanding",TRUE)</f>
@@ -12437,7 +11748,7 @@
       </c>
       <c r="C29" s="2" cm="1">
         <f t="array" aca="1" ref="C29" ca="1">_FV(B29,"Last trade time",TRUE)</f>
-        <v>46168.605529258595</v>
+        <v>46168.683495196092</v>
       </c>
       <c r="D29" t="str" cm="1">
         <f t="array" aca="1" ref="D29" ca="1">_FV(B29,"Currency")</f>
@@ -12445,19 +11756,19 @@
       </c>
       <c r="E29" s="3" cm="1">
         <f t="array" aca="1" ref="E29" ca="1">_FV(B29,"Price")</f>
-        <v>381.23</v>
+        <v>380.46</v>
       </c>
       <c r="F29" s="4" cm="1">
         <f t="array" aca="1" ref="F29" ca="1">_FV(B29,"Change (%)",TRUE)</f>
-        <v>2.0449999999999999E-2</v>
+        <v>1.8388999999999999E-2</v>
       </c>
       <c r="G29" s="5" cm="1">
         <f t="array" aca="1" ref="G29" ca="1">_FV(B29,"Change")</f>
-        <v>7.64</v>
+        <v>6.87</v>
       </c>
       <c r="H29" s="6" cm="1">
         <f t="array" aca="1" ref="H29" ca="1">_FV(B29,"P/E",TRUE)</f>
-        <v>88.999600000000001</v>
+        <v>88.819900000000004</v>
       </c>
       <c r="I29" s="6" cm="1">
         <f t="array" aca="1" ref="I29" ca="1">_FV(B29,"Beta")</f>
@@ -12465,7 +11776,7 @@
       </c>
       <c r="J29" s="3" cm="1">
         <f t="array" aca="1" ref="J29" ca="1">_FV(B29,"52 week high",TRUE)</f>
-        <v>382.32</v>
+        <v>383.24</v>
       </c>
       <c r="K29" s="3" cm="1">
         <f t="array" aca="1" ref="K29" ca="1">_FV(B29,"52 week low",TRUE)</f>
@@ -12473,7 +11784,7 @@
       </c>
       <c r="L29" s="3" cm="1">
         <f t="array" aca="1" ref="L29" ca="1">_FV(B29,"High")</f>
-        <v>382.32</v>
+        <v>383.24</v>
       </c>
       <c r="M29" s="3" cm="1">
         <f t="array" aca="1" ref="M29" ca="1">_FV(B29,"Low")</f>
@@ -12489,7 +11800,7 @@
       </c>
       <c r="P29" s="7" cm="1">
         <f t="array" aca="1" ref="P29" ca="1">_FV(B29,"Volume")</f>
-        <v>489738</v>
+        <v>790202</v>
       </c>
       <c r="Q29" s="7" cm="1">
         <f t="array" aca="1" ref="Q29" ca="1">_FV(B29,"Volume average",TRUE)</f>
@@ -12509,7 +11820,7 @@
       </c>
       <c r="U29" s="7" cm="1">
         <f t="array" aca="1" ref="U29" ca="1">_FV(B29,"Market cap",TRUE)</f>
-        <v>105149333680</v>
+        <v>104936955360</v>
       </c>
       <c r="V29" s="7" cm="1">
         <f t="array" aca="1" ref="V29" ca="1">_FV(B29,"Shares outstanding",TRUE)</f>
@@ -12525,7 +11836,7 @@
       </c>
       <c r="C30" s="2">
         <f t="array" aca="1" ref="C30" ca="1">_FV(B30,"Last trade time",TRUE)</f>
-        <v>46168.605561943747</v>
+        <v>46168.683527626563</v>
       </c>
       <c r="D30" t="str">
         <f t="array" aca="1" ref="D30" ca="1">_FV(B30,"Currency")</f>
@@ -12533,19 +11844,19 @@
       </c>
       <c r="E30" s="3">
         <f t="array" aca="1" ref="E30" ca="1">_FV(B30,"Price")</f>
-        <v>414.69</v>
+        <v>411.245</v>
       </c>
       <c r="F30" s="4">
         <f t="array" aca="1" ref="F30" ca="1">_FV(B30,"Change (%)",TRUE)</f>
-        <v>2.5141E-2</v>
+        <v>1.6625000000000001E-2</v>
       </c>
       <c r="G30" s="5">
         <f t="array" aca="1" ref="G30" ca="1">_FV(B30,"Change")</f>
-        <v>10.17</v>
+        <v>6.7249999999999996</v>
       </c>
       <c r="H30" s="6">
         <f t="array" aca="1" ref="H30" ca="1">_FV(B30,"P/E",TRUE)</f>
-        <v>35.086399999999998</v>
+        <v>34.795000000000002</v>
       </c>
       <c r="I30" s="6">
         <f t="array" aca="1" ref="I30" ca="1">_FV(B30,"Beta")</f>
@@ -12565,7 +11876,7 @@
       </c>
       <c r="M30" s="3">
         <f t="array" aca="1" ref="M30" ca="1">_FV(B30,"Low")</f>
-        <v>410.35</v>
+        <v>410.07010000000002</v>
       </c>
       <c r="N30" s="3">
         <f t="array" aca="1" ref="N30" ca="1">_FV(B30,"Open")</f>
@@ -12577,7 +11888,7 @@
       </c>
       <c r="P30" s="7">
         <f t="array" aca="1" ref="P30" ca="1">_FV(B30,"Volume")</f>
-        <v>2996422</v>
+        <v>4950921</v>
       </c>
       <c r="Q30" s="7">
         <f t="array" aca="1" ref="Q30" ca="1">_FV(B30,"Volume average",TRUE)</f>
@@ -12597,7 +11908,7 @@
       </c>
       <c r="U30" s="7">
         <f t="array" aca="1" ref="U30" ca="1">_FV(B30,"Market cap",TRUE)</f>
-        <v>2150791758450</v>
+        <v>2132924248725</v>
       </c>
       <c r="V30" s="7">
         <f t="array" aca="1" ref="V30" ca="1">_FV(B30,"Shares outstanding",TRUE)</f>
@@ -12613,7 +11924,7 @@
       </c>
       <c r="C31" s="2">
         <f t="array" aca="1" ref="C31" ca="1">_FV(B31,"Last trade time",TRUE)</f>
-        <v>46168.605576851565</v>
+        <v>46168.683552464841</v>
       </c>
       <c r="D31" t="str">
         <f t="array" aca="1" ref="D31" ca="1">_FV(B31,"Currency")</f>
@@ -12621,19 +11932,19 @@
       </c>
       <c r="E31" s="3">
         <f t="array" aca="1" ref="E31" ca="1">_FV(B31,"Price")</f>
-        <v>157.54</v>
+        <v>159.6</v>
       </c>
       <c r="F31" s="4">
         <f t="array" aca="1" ref="F31" ca="1">_FV(B31,"Change (%)",TRUE)</f>
-        <v>2.2787999999999999E-2</v>
+        <v>3.6162E-2</v>
       </c>
       <c r="G31" s="5">
         <f t="array" aca="1" ref="G31" ca="1">_FV(B31,"Change")</f>
-        <v>3.51</v>
+        <v>5.57</v>
       </c>
       <c r="H31" s="6">
         <f t="array" aca="1" ref="H31" ca="1">_FV(B31,"P/E",TRUE)</f>
-        <v>53.959400000000002</v>
+        <v>54.664999999999999</v>
       </c>
       <c r="I31" s="6">
         <f t="array" aca="1" ref="I31" ca="1">_FV(B31,"Beta")</f>
@@ -12649,7 +11960,7 @@
       </c>
       <c r="L31" s="3">
         <f t="array" aca="1" ref="L31" ca="1">_FV(B31,"High")</f>
-        <v>157.74</v>
+        <v>159.68</v>
       </c>
       <c r="M31" s="3">
         <f t="array" aca="1" ref="M31" ca="1">_FV(B31,"Low")</f>
@@ -12665,7 +11976,7 @@
       </c>
       <c r="P31" s="7">
         <f t="array" aca="1" ref="P31" ca="1">_FV(B31,"Volume")</f>
-        <v>2993278</v>
+        <v>5652729</v>
       </c>
       <c r="Q31" s="7">
         <f t="array" aca="1" ref="Q31" ca="1">_FV(B31,"Volume average",TRUE)</f>
@@ -12685,7 +11996,7 @@
       </c>
       <c r="U31" s="7">
         <f t="array" aca="1" ref="U31" ca="1">_FV(B31,"Market cap",TRUE)</f>
-        <v>198374840620</v>
+        <v>200968798800</v>
       </c>
       <c r="V31" s="7">
         <f t="array" aca="1" ref="V31" ca="1">_FV(B31,"Shares outstanding",TRUE)</f>
@@ -12701,7 +12012,7 @@
       </c>
       <c r="C32" s="2">
         <f t="array" aca="1" ref="C32" ca="1">_FV(B32,"Last trade time",TRUE)</f>
-        <v>46168.605576157031</v>
+        <v>46168.683560925783</v>
       </c>
       <c r="D32" t="str">
         <f t="array" aca="1" ref="D32" ca="1">_FV(B32,"Currency")</f>
@@ -12709,19 +12020,19 @@
       </c>
       <c r="E32" s="3">
         <f t="array" aca="1" ref="E32" ca="1">_FV(B32,"Price")</f>
-        <v>220.81</v>
+        <v>214.84</v>
       </c>
       <c r="F32" s="4">
         <f t="array" aca="1" ref="F32" ca="1">_FV(B32,"Change (%)",TRUE)</f>
-        <v>1.0989000000000001E-2</v>
+        <v>-1.6345000000000002E-2</v>
       </c>
       <c r="G32" s="5">
         <f t="array" aca="1" ref="G32" ca="1">_FV(B32,"Change")</f>
-        <v>2.4</v>
+        <v>-3.57</v>
       </c>
       <c r="H32" s="6">
         <f t="array" aca="1" ref="H32" ca="1">_FV(B32,"P/E",TRUE)</f>
-        <v>122.5361</v>
+        <v>119.2231</v>
       </c>
       <c r="I32" s="6">
         <f t="array" aca="1" ref="I32" ca="1">_FV(B32,"Beta")</f>
@@ -12741,7 +12052,7 @@
       </c>
       <c r="M32" s="3">
         <f t="array" aca="1" ref="M32" ca="1">_FV(B32,"Low")</f>
-        <v>220.76</v>
+        <v>211.58</v>
       </c>
       <c r="N32" s="3">
         <f t="array" aca="1" ref="N32" ca="1">_FV(B32,"Open")</f>
@@ -12753,7 +12064,7 @@
       </c>
       <c r="P32" s="7">
         <f t="array" aca="1" ref="P32" ca="1">_FV(B32,"Volume")</f>
-        <v>2748487</v>
+        <v>5644285</v>
       </c>
       <c r="Q32" s="7">
         <f t="array" aca="1" ref="Q32" ca="1">_FV(B32,"Volume average",TRUE)</f>
@@ -12773,7 +12084,7 @@
       </c>
       <c r="U32" s="7">
         <f t="array" aca="1" ref="U32" ca="1">_FV(B32,"Market cap",TRUE)</f>
-        <v>40728382419</v>
+        <v>39627216516</v>
       </c>
       <c r="V32" s="7">
         <f t="array" aca="1" ref="V32" ca="1">_FV(B32,"Shares outstanding",TRUE)</f>
@@ -12789,7 +12100,7 @@
       </c>
       <c r="C33" s="2">
         <f t="array" aca="1" ref="C33" ca="1">_FV(B33,"Last trade time",TRUE)</f>
-        <v>46168.605507974222</v>
+        <v>46168.68348923594</v>
       </c>
       <c r="D33" t="str">
         <f t="array" aca="1" ref="D33" ca="1">_FV(B33,"Currency")</f>
@@ -12797,15 +12108,15 @@
       </c>
       <c r="E33" s="3">
         <f t="array" aca="1" ref="E33" ca="1">_FV(B33,"Price")</f>
-        <v>8.32</v>
+        <v>8.2600999999999996</v>
       </c>
       <c r="F33" s="4">
         <f t="array" aca="1" ref="F33" ca="1">_FV(B33,"Change (%)",TRUE)</f>
-        <v>1.8360000000000001E-2</v>
+        <v>1.1028E-2</v>
       </c>
       <c r="G33" s="5">
         <f t="array" aca="1" ref="G33" ca="1">_FV(B33,"Change")</f>
-        <v>0.15</v>
+        <v>9.01E-2</v>
       </c>
       <c r="H33" s="6">
         <f t="array" aca="1" ref="H33" ca="1">_FV(B33,"P/E",TRUE)</f>
@@ -12841,7 +12152,7 @@
       </c>
       <c r="P33" s="7">
         <f t="array" aca="1" ref="P33" ca="1">_FV(B33,"Volume")</f>
-        <v>9489549</v>
+        <v>13729860</v>
       </c>
       <c r="Q33" s="7">
         <f t="array" aca="1" ref="Q33" ca="1">_FV(B33,"Volume average",TRUE)</f>
@@ -12861,7 +12172,7 @@
       </c>
       <c r="U33" s="7">
         <f t="array" aca="1" ref="U33" ca="1">_FV(B33,"Market cap",TRUE)</f>
-        <v>3600643072</v>
+        <v>3574720172</v>
       </c>
       <c r="V33" s="7">
         <f t="array" aca="1" ref="V33" ca="1">_FV(B33,"Shares outstanding",TRUE)</f>
@@ -12877,7 +12188,7 @@
       </c>
       <c r="C34" s="2">
         <f t="array" aca="1" ref="C34" ca="1">_FV(B34,"Last trade time",TRUE)</f>
-        <v>46168.605565832811</v>
+        <v>46168.683558553123</v>
       </c>
       <c r="D34" t="str">
         <f t="array" aca="1" ref="D34" ca="1">_FV(B34,"Currency")</f>
@@ -12885,15 +12196,15 @@
       </c>
       <c r="E34" s="3">
         <f t="array" aca="1" ref="E34" ca="1">_FV(B34,"Price")</f>
-        <v>185.35</v>
+        <v>181.55</v>
       </c>
       <c r="F34" s="4">
         <f t="array" aca="1" ref="F34" ca="1">_FV(B34,"Change (%)",TRUE)</f>
-        <v>2.1267999999999999E-2</v>
+        <v>3.3060000000000001E-4</v>
       </c>
       <c r="G34" s="5">
         <f t="array" aca="1" ref="G34" ca="1">_FV(B34,"Change")</f>
-        <v>3.86</v>
+        <v>0.06</v>
       </c>
       <c r="H34" s="6">
         <f t="array" aca="1" ref="H34" ca="1">_FV(B34,"P/E",TRUE)</f>
@@ -12917,7 +12228,7 @@
       </c>
       <c r="M34" s="3">
         <f t="array" aca="1" ref="M34" ca="1">_FV(B34,"Low")</f>
-        <v>180</v>
+        <v>177.7801</v>
       </c>
       <c r="N34" s="3">
         <f t="array" aca="1" ref="N34" ca="1">_FV(B34,"Open")</f>
@@ -12929,7 +12240,7 @@
       </c>
       <c r="P34" s="7">
         <f t="array" aca="1" ref="P34" ca="1">_FV(B34,"Volume")</f>
-        <v>4849309</v>
+        <v>6970130</v>
       </c>
       <c r="Q34" s="7">
         <f t="array" aca="1" ref="Q34" ca="1">_FV(B34,"Volume average",TRUE)</f>
@@ -12949,7 +12260,7 @@
       </c>
       <c r="U34" s="7">
         <f t="array" aca="1" ref="U34" ca="1">_FV(B34,"Market cap",TRUE)</f>
-        <v>14872997419</v>
+        <v>14568074893</v>
       </c>
       <c r="V34" s="7">
         <f t="array" aca="1" ref="V34" ca="1">_FV(B34,"Shares outstanding",TRUE)</f>
@@ -12965,7 +12276,7 @@
       </c>
       <c r="C35" s="2">
         <f t="array" aca="1" ref="C35" ca="1">_FV(B35,"Last trade time",TRUE)</f>
-        <v>46168.605591608597</v>
+        <v>46168.68354476797</v>
       </c>
       <c r="D35" t="str">
         <f t="array" aca="1" ref="D35" ca="1">_FV(B35,"Currency")</f>
@@ -12973,19 +12284,19 @@
       </c>
       <c r="E35" s="3">
         <f t="array" aca="1" ref="E35" ca="1">_FV(B35,"Price")</f>
-        <v>83.24</v>
+        <v>82.055000000000007</v>
       </c>
       <c r="F35" s="4">
         <f t="array" aca="1" ref="F35" ca="1">_FV(B35,"Change (%)",TRUE)</f>
-        <v>1.8725000000000002E-2</v>
+        <v>4.2220000000000001E-3</v>
       </c>
       <c r="G35" s="5">
         <f t="array" aca="1" ref="G35" ca="1">_FV(B35,"Change")</f>
-        <v>1.53</v>
+        <v>0.34499999999999997</v>
       </c>
       <c r="H35" s="6">
         <f t="array" aca="1" ref="H35" ca="1">_FV(B35,"P/E",TRUE)</f>
-        <v>32.885599999999997</v>
+        <v>32.417400000000001</v>
       </c>
       <c r="I35" s="6">
         <f t="array" aca="1" ref="I35" ca="1">_FV(B35,"Beta")</f>
@@ -13001,7 +12312,7 @@
       </c>
       <c r="L35" s="3">
         <f t="array" aca="1" ref="L35" ca="1">_FV(B35,"High")</f>
-        <v>83.68</v>
+        <v>84.778999999999996</v>
       </c>
       <c r="M35" s="3">
         <f t="array" aca="1" ref="M35" ca="1">_FV(B35,"Low")</f>
@@ -13017,7 +12328,7 @@
       </c>
       <c r="P35" s="7">
         <f t="array" aca="1" ref="P35" ca="1">_FV(B35,"Volume")</f>
-        <v>1011675</v>
+        <v>2232219</v>
       </c>
       <c r="Q35" s="7">
         <f t="array" aca="1" ref="Q35" ca="1">_FV(B35,"Volume average",TRUE)</f>
@@ -13037,7 +12348,7 @@
       </c>
       <c r="U35" s="7">
         <f t="array" aca="1" ref="U35" ca="1">_FV(B35,"Market cap",TRUE)</f>
-        <v>12519787116</v>
+        <v>12341556124</v>
       </c>
       <c r="V35" s="7">
         <f t="array" aca="1" ref="V35" ca="1">_FV(B35,"Shares outstanding",TRUE)</f>
@@ -13053,7 +12364,7 @@
       </c>
       <c r="C36" s="2" cm="1">
         <f t="array" aca="1" ref="C36" ca="1">_FV(B36,"Last trade time",TRUE)</f>
-        <v>46168.60551018516</v>
+        <v>46168.683487823437</v>
       </c>
       <c r="D36" t="str" cm="1">
         <f t="array" aca="1" ref="D36" ca="1">_FV(B36,"Currency")</f>
@@ -13061,15 +12372,15 @@
       </c>
       <c r="E36" s="3" cm="1">
         <f t="array" aca="1" ref="E36" ca="1">_FV(B36,"Price")</f>
-        <v>730.12</v>
+        <v>727.41150000000005</v>
       </c>
       <c r="F36" s="4" cm="1">
         <f t="array" aca="1" ref="F36" ca="1">_FV(B36,"Change (%)",TRUE)</f>
-        <v>1.7532000000000002E-2</v>
+        <v>1.3756999999999998E-2</v>
       </c>
       <c r="G36" s="5" cm="1">
         <f t="array" aca="1" ref="G36" ca="1">_FV(B36,"Change")</f>
-        <v>12.58</v>
+        <v>9.8714999999999993</v>
       </c>
       <c r="H36" s="6" t="e" cm="1" vm="12">
         <f t="array" ref="H36">_FV(B36,"P/E",TRUE)</f>
@@ -13081,7 +12392,7 @@
       </c>
       <c r="J36" s="3" cm="1">
         <f t="array" aca="1" ref="J36" ca="1">_FV(B36,"52 week high",TRUE)</f>
-        <v>730.32</v>
+        <v>731.17</v>
       </c>
       <c r="K36" s="3" cm="1">
         <f t="array" aca="1" ref="K36" ca="1">_FV(B36,"52 week low",TRUE)</f>
@@ -13089,7 +12400,7 @@
       </c>
       <c r="L36" s="3" cm="1">
         <f t="array" aca="1" ref="L36" ca="1">_FV(B36,"High")</f>
-        <v>730.32</v>
+        <v>731.17</v>
       </c>
       <c r="M36" s="3" cm="1">
         <f t="array" aca="1" ref="M36" ca="1">_FV(B36,"Low")</f>
@@ -13105,7 +12416,7 @@
       </c>
       <c r="P36" s="7" cm="1">
         <f t="array" aca="1" ref="P36" ca="1">_FV(B36,"Volume")</f>
-        <v>10796831</v>
+        <v>19706470</v>
       </c>
       <c r="Q36" s="7" cm="1">
         <f t="array" aca="1" ref="Q36" ca="1">_FV(B36,"Volume average",TRUE)</f>
@@ -13141,7 +12452,7 @@
       </c>
       <c r="C37" s="2">
         <f t="array" aca="1" ref="C37" ca="1">_FV(B37,"Last trade time",TRUE)</f>
-        <v>46168.605553367968</v>
+        <v>46168.68351748828</v>
       </c>
       <c r="D37" t="str">
         <f t="array" aca="1" ref="D37" ca="1">_FV(B37,"Currency")</f>
@@ -13149,15 +12460,15 @@
       </c>
       <c r="E37" s="3">
         <f t="array" aca="1" ref="E37" ca="1">_FV(B37,"Price")</f>
-        <v>17.215</v>
+        <v>16.940000000000001</v>
       </c>
       <c r="F37" s="4">
         <f t="array" aca="1" ref="F37" ca="1">_FV(B37,"Change (%)",TRUE)</f>
-        <v>1.5633999999999999E-2</v>
+        <v>-5.8999999999999992E-4</v>
       </c>
       <c r="G37" s="5">
         <f t="array" aca="1" ref="G37" ca="1">_FV(B37,"Change")</f>
-        <v>0.26500000000000001</v>
+        <v>-0.01</v>
       </c>
       <c r="H37" s="6">
         <f t="array" aca="1" ref="H37" ca="1">_FV(B37,"P/E",TRUE)</f>
@@ -13181,7 +12492,7 @@
       </c>
       <c r="M37" s="3">
         <f t="array" aca="1" ref="M37" ca="1">_FV(B37,"Low")</f>
-        <v>16.88</v>
+        <v>16.75</v>
       </c>
       <c r="N37" s="3">
         <f t="array" aca="1" ref="N37" ca="1">_FV(B37,"Open")</f>
@@ -13193,7 +12504,7 @@
       </c>
       <c r="P37" s="7">
         <f t="array" aca="1" ref="P37" ca="1">_FV(B37,"Volume")</f>
-        <v>2088124</v>
+        <v>3200746</v>
       </c>
       <c r="Q37" s="7">
         <f t="array" aca="1" ref="Q37" ca="1">_FV(B37,"Volume average",TRUE)</f>
@@ -13213,7 +12524,7 @@
       </c>
       <c r="U37" s="7">
         <f t="array" aca="1" ref="U37" ca="1">_FV(B37,"Market cap",TRUE)</f>
-        <v>1080919693</v>
+        <v>1063652605</v>
       </c>
       <c r="V37" s="7">
         <f t="array" aca="1" ref="V37" ca="1">_FV(B37,"Shares outstanding",TRUE)</f>
@@ -13229,7 +12540,7 @@
       </c>
       <c r="C38" s="2" cm="1">
         <f t="array" aca="1" ref="C38" ca="1">_FV(B38,"Last trade time",TRUE)</f>
-        <v>46168.605543147656</v>
+        <v>46168.68352585625</v>
       </c>
       <c r="D38" t="str" cm="1">
         <f t="array" aca="1" ref="D38" ca="1">_FV(B38,"Currency")</f>
@@ -13237,15 +12548,15 @@
       </c>
       <c r="E38" s="3" cm="1">
         <f t="array" aca="1" ref="E38" ca="1">_FV(B38,"Price")</f>
-        <v>289.53500000000003</v>
+        <v>289.74</v>
       </c>
       <c r="F38" s="4" cm="1">
         <f t="array" aca="1" ref="F38" ca="1">_FV(B38,"Change (%)",TRUE)</f>
-        <v>1.5485000000000001E-2</v>
+        <v>1.6204E-2</v>
       </c>
       <c r="G38" s="5" cm="1">
         <f t="array" aca="1" ref="G38" ca="1">_FV(B38,"Change")</f>
-        <v>4.415</v>
+        <v>4.62</v>
       </c>
       <c r="H38" s="6" t="e" cm="1" vm="12">
         <f t="array" ref="H38">_FV(B38,"P/E",TRUE)</f>
@@ -13281,7 +12592,7 @@
       </c>
       <c r="P38" s="7" cm="1">
         <f t="array" aca="1" ref="P38" ca="1">_FV(B38,"Volume")</f>
-        <v>6969903</v>
+        <v>12471961</v>
       </c>
       <c r="Q38" s="7" cm="1">
         <f t="array" aca="1" ref="Q38" ca="1">_FV(B38,"Volume average",TRUE)</f>
@@ -13317,7 +12628,7 @@
       </c>
       <c r="C39" s="2">
         <f t="array" aca="1" ref="C39" ca="1">_FV(B39,"Last trade time",TRUE)</f>
-        <v>46168.605583541408</v>
+        <v>46168.683564640625</v>
       </c>
       <c r="D39" t="str">
         <f t="array" aca="1" ref="D39" ca="1">_FV(B39,"Currency")</f>
@@ -13325,15 +12636,15 @@
       </c>
       <c r="E39" s="3">
         <f t="array" aca="1" ref="E39" ca="1">_FV(B39,"Price")</f>
-        <v>122.595</v>
+        <v>121.941</v>
       </c>
       <c r="F39" s="4">
         <f t="array" aca="1" ref="F39" ca="1">_FV(B39,"Change (%)",TRUE)</f>
-        <v>2.2989000000000002E-2</v>
+        <v>1.7532000000000002E-2</v>
       </c>
       <c r="G39" s="5">
         <f t="array" aca="1" ref="G39" ca="1">_FV(B39,"Change")</f>
-        <v>2.7549999999999999</v>
+        <v>2.101</v>
       </c>
       <c r="H39" s="6">
         <f t="array" aca="1" ref="H39" ca="1">_FV(B39,"P/E",TRUE)</f>
@@ -13369,7 +12680,7 @@
       </c>
       <c r="P39" s="7">
         <f t="array" aca="1" ref="P39" ca="1">_FV(B39,"Volume")</f>
-        <v>42953434</v>
+        <v>66152883</v>
       </c>
       <c r="Q39" s="7">
         <f t="array" aca="1" ref="Q39" ca="1">_FV(B39,"Volume average",TRUE)</f>
@@ -13389,7 +12700,7 @@
       </c>
       <c r="U39" s="7">
         <f t="array" aca="1" ref="U39" ca="1">_FV(B39,"Market cap",TRUE)</f>
-        <v>616162470000</v>
+        <v>612875466000</v>
       </c>
       <c r="V39" s="7">
         <f t="array" aca="1" ref="V39" ca="1">_FV(B39,"Shares outstanding",TRUE)</f>
@@ -13405,7 +12716,7 @@
       </c>
       <c r="C40" s="2">
         <f t="array" aca="1" ref="C40" ca="1">_FV(B40,"Last trade time",TRUE)</f>
-        <v>46168.605609235936</v>
+        <v>46168.683543078128</v>
       </c>
       <c r="D40" t="str">
         <f t="array" aca="1" ref="D40" ca="1">_FV(B40,"Currency")</f>
@@ -13413,19 +12724,19 @@
       </c>
       <c r="E40" s="3">
         <f t="array" aca="1" ref="E40" ca="1">_FV(B40,"Price")</f>
-        <v>309.08</v>
+        <v>315.85000000000002</v>
       </c>
       <c r="F40" s="4">
         <f t="array" aca="1" ref="F40" ca="1">_FV(B40,"Change (%)",TRUE)</f>
-        <v>7.169E-3</v>
+        <v>2.9229999999999999E-2</v>
       </c>
       <c r="G40" s="5">
         <f t="array" aca="1" ref="G40" ca="1">_FV(B40,"Change")</f>
-        <v>2.2000000000000002</v>
+        <v>8.9700000000000006</v>
       </c>
       <c r="H40" s="6">
         <f t="array" aca="1" ref="H40" ca="1">_FV(B40,"P/E",TRUE)</f>
-        <v>208.35919999999999</v>
+        <v>212.923</v>
       </c>
       <c r="I40" s="6">
         <f t="array" aca="1" ref="I40" ca="1">_FV(B40,"Beta")</f>
@@ -13433,7 +12744,7 @@
       </c>
       <c r="J40" s="3">
         <f t="array" aca="1" ref="J40" ca="1">_FV(B40,"52 week high",TRUE)</f>
-        <v>316.5</v>
+        <v>316.61</v>
       </c>
       <c r="K40" s="3">
         <f t="array" aca="1" ref="K40" ca="1">_FV(B40,"52 week low",TRUE)</f>
@@ -13441,7 +12752,7 @@
       </c>
       <c r="L40" s="3">
         <f t="array" aca="1" ref="L40" ca="1">_FV(B40,"High")</f>
-        <v>316.5</v>
+        <v>316.61</v>
       </c>
       <c r="M40" s="3">
         <f t="array" aca="1" ref="M40" ca="1">_FV(B40,"Low")</f>
@@ -13457,7 +12768,7 @@
       </c>
       <c r="P40" s="7">
         <f t="array" aca="1" ref="P40" ca="1">_FV(B40,"Volume")</f>
-        <v>3011391</v>
+        <v>4276218</v>
       </c>
       <c r="Q40" s="7">
         <f t="array" aca="1" ref="Q40" ca="1">_FV(B40,"Volume average",TRUE)</f>
@@ -13477,7 +12788,7 @@
       </c>
       <c r="U40" s="7">
         <f t="array" aca="1" ref="U40" ca="1">_FV(B40,"Market cap",TRUE)</f>
-        <v>52978753732</v>
+        <v>54139185215</v>
       </c>
       <c r="V40" s="7">
         <f t="array" aca="1" ref="V40" ca="1">_FV(B40,"Shares outstanding",TRUE)</f>
@@ -13493,7 +12804,7 @@
       </c>
       <c r="C41" s="2">
         <f t="array" aca="1" ref="C41" ca="1">_FV(B41,"Last trade time",TRUE)</f>
-        <v>46168.605494721873</v>
+        <v>46168.683439814064</v>
       </c>
       <c r="D41" t="str">
         <f t="array" aca="1" ref="D41" ca="1">_FV(B41,"Currency")</f>
@@ -13501,15 +12812,15 @@
       </c>
       <c r="E41" s="3">
         <f t="array" aca="1" ref="E41" ca="1">_FV(B41,"Price")</f>
-        <v>107.09</v>
+        <v>106.99</v>
       </c>
       <c r="F41" s="4">
         <f t="array" aca="1" ref="F41" ca="1">_FV(B41,"Change (%)",TRUE)</f>
-        <v>1.5167E-2</v>
+        <v>1.4218999999999999E-2</v>
       </c>
       <c r="G41" s="5">
         <f t="array" aca="1" ref="G41" ca="1">_FV(B41,"Change")</f>
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="H41" s="6">
         <f t="array" aca="1" ref="H41" ca="1">_FV(B41,"P/E",TRUE)</f>
@@ -13545,7 +12856,7 @@
       </c>
       <c r="P41" s="7">
         <f t="array" aca="1" ref="P41" ca="1">_FV(B41,"Volume")</f>
-        <v>7686109</v>
+        <v>12756802</v>
       </c>
       <c r="Q41" s="7">
         <f t="array" aca="1" ref="Q41" ca="1">_FV(B41,"Volume average",TRUE)</f>
@@ -13565,7 +12876,7 @@
       </c>
       <c r="U41" s="7">
         <f t="array" aca="1" ref="U41" ca="1">_FV(B41,"Market cap",TRUE)</f>
-        <v>58425134136</v>
+        <v>58370577096</v>
       </c>
       <c r="V41" s="7">
         <f t="array" aca="1" ref="V41" ca="1">_FV(B41,"Shares outstanding",TRUE)</f>
@@ -13581,7 +12892,7 @@
       </c>
       <c r="C42" s="2" cm="1">
         <f t="array" aca="1" ref="C42" ca="1">_FV(B42,"Last trade time",TRUE)</f>
-        <v>46168.605482777341</v>
+        <v>46168.683468286719</v>
       </c>
       <c r="D42" t="str" cm="1">
         <f t="array" aca="1" ref="D42" ca="1">_FV(B42,"Currency")</f>
@@ -13589,15 +12900,15 @@
       </c>
       <c r="E42" s="3" cm="1">
         <f t="array" aca="1" ref="E42" ca="1">_FV(B42,"Price")</f>
-        <v>77.37</v>
+        <v>77.215000000000003</v>
       </c>
       <c r="F42" s="4" cm="1">
         <f t="array" aca="1" ref="F42" ca="1">_FV(B42,"Change (%)",TRUE)</f>
-        <v>1.2696000000000001E-2</v>
+        <v>1.0668E-2</v>
       </c>
       <c r="G42" s="5" cm="1">
         <f t="array" aca="1" ref="G42" ca="1">_FV(B42,"Change")</f>
-        <v>0.97</v>
+        <v>0.81499999999999995</v>
       </c>
       <c r="H42" s="6" t="e" cm="1" vm="12">
         <f t="array" ref="H42">_FV(B42,"P/E",TRUE)</f>
@@ -13633,7 +12944,7 @@
       </c>
       <c r="P42" s="7" cm="1">
         <f t="array" aca="1" ref="P42" ca="1">_FV(B42,"Volume")</f>
-        <v>1211355</v>
+        <v>2446868</v>
       </c>
       <c r="Q42" s="7" cm="1">
         <f t="array" aca="1" ref="Q42" ca="1">_FV(B42,"Volume average",TRUE)</f>
@@ -13669,7 +12980,7 @@
       </c>
       <c r="C43" s="2">
         <f t="array" aca="1" ref="C43" ca="1">_FV(B43,"Last trade time",TRUE)</f>
-        <v>46168.60559679375</v>
+        <v>46168.683549825779</v>
       </c>
       <c r="D43" t="str">
         <f t="array" aca="1" ref="D43" ca="1">_FV(B43,"Currency")</f>
@@ -13677,19 +12988,19 @@
       </c>
       <c r="E43" s="3">
         <f t="array" aca="1" ref="E43" ca="1">_FV(B43,"Price")</f>
-        <v>313.88</v>
+        <v>321.16390000000001</v>
       </c>
       <c r="F43" s="4">
         <f t="array" aca="1" ref="F43" ca="1">_FV(B43,"Change (%)",TRUE)</f>
-        <v>2.4045E-2</v>
+        <v>4.7808999999999997E-2</v>
       </c>
       <c r="G43" s="5">
         <f t="array" aca="1" ref="G43" ca="1">_FV(B43,"Change")</f>
-        <v>7.37</v>
+        <v>14.6539</v>
       </c>
       <c r="H43" s="6">
         <f t="array" aca="1" ref="H43" ca="1">_FV(B43,"P/E",TRUE)</f>
-        <v>370.84120000000001</v>
+        <v>379.447</v>
       </c>
       <c r="I43" s="6">
         <f t="array" aca="1" ref="I43" ca="1">_FV(B43,"Beta")</f>
@@ -13721,7 +13032,7 @@
       </c>
       <c r="P43" s="7">
         <f t="array" aca="1" ref="P43" ca="1">_FV(B43,"Volume")</f>
-        <v>4451259</v>
+        <v>6885427</v>
       </c>
       <c r="Q43" s="7">
         <f t="array" aca="1" ref="Q43" ca="1">_FV(B43,"Volume average",TRUE)</f>
@@ -13741,7 +13052,7 @@
       </c>
       <c r="U43" s="7">
         <f t="array" aca="1" ref="U43" ca="1">_FV(B43,"Market cap",TRUE)</f>
-        <v>333968320000</v>
+        <v>341718389600</v>
       </c>
       <c r="V43" s="7">
         <f t="array" aca="1" ref="V43" ca="1">_FV(B43,"Shares outstanding",TRUE)</f>
@@ -13757,7 +13068,7 @@
       </c>
       <c r="C44" s="2">
         <f t="array" aca="1" ref="C44" ca="1">_FV(B44,"Last trade time",TRUE)</f>
-        <v>46168.605518784374</v>
+        <v>46168.683472488279</v>
       </c>
       <c r="D44" t="str">
         <f t="array" aca="1" ref="D44" ca="1">_FV(B44,"Currency")</f>
@@ -13765,19 +13076,19 @@
       </c>
       <c r="E44" s="3">
         <f t="array" aca="1" ref="E44" ca="1">_FV(B44,"Price")</f>
-        <v>194.495</v>
+        <v>192.2</v>
       </c>
       <c r="F44" s="4">
         <f t="array" aca="1" ref="F44" ca="1">_FV(B44,"Change (%)",TRUE)</f>
-        <v>1.2573000000000001E-2</v>
+        <v>6.2469999999999995E-4</v>
       </c>
       <c r="G44" s="5">
         <f t="array" aca="1" ref="G44" ca="1">_FV(B44,"Change")</f>
-        <v>2.415</v>
+        <v>0.12</v>
       </c>
       <c r="H44" s="6">
         <f t="array" aca="1" ref="H44" ca="1">_FV(B44,"P/E",TRUE)</f>
-        <v>32.965800000000002</v>
+        <v>32.576799999999999</v>
       </c>
       <c r="I44" s="6">
         <f t="array" aca="1" ref="I44" ca="1">_FV(B44,"Beta")</f>
@@ -13793,7 +13104,7 @@
       </c>
       <c r="L44" s="3">
         <f t="array" aca="1" ref="L44" ca="1">_FV(B44,"High")</f>
-        <v>195</v>
+        <v>195.196</v>
       </c>
       <c r="M44" s="3">
         <f t="array" aca="1" ref="M44" ca="1">_FV(B44,"Low")</f>
@@ -13809,7 +13120,7 @@
       </c>
       <c r="P44" s="7">
         <f t="array" aca="1" ref="P44" ca="1">_FV(B44,"Volume")</f>
-        <v>3246479</v>
+        <v>5675675</v>
       </c>
       <c r="Q44" s="7">
         <f t="array" aca="1" ref="Q44" ca="1">_FV(B44,"Volume average",TRUE)</f>
@@ -13829,7 +13140,7 @@
       </c>
       <c r="U44" s="7">
         <f t="array" aca="1" ref="U44" ca="1">_FV(B44,"Market cap",TRUE)</f>
-        <v>559376566770</v>
+        <v>552776041200</v>
       </c>
       <c r="V44" s="7">
         <f t="array" aca="1" ref="V44" ca="1">_FV(B44,"Shares outstanding",TRUE)</f>
@@ -13845,7 +13156,7 @@
       </c>
       <c r="C45" s="2">
         <f t="array" aca="1" ref="C45" ca="1">_FV(B45,"Last trade time",TRUE)</f>
-        <v>46168.605610219529</v>
+        <v>46168.683562349215</v>
       </c>
       <c r="D45" t="str">
         <f t="array" aca="1" ref="D45" ca="1">_FV(B45,"Currency")</f>
@@ -13853,19 +13164,19 @@
       </c>
       <c r="E45" s="3">
         <f t="array" aca="1" ref="E45" ca="1">_FV(B45,"Price")</f>
-        <v>36.049999999999997</v>
+        <v>36.705100000000002</v>
       </c>
       <c r="F45" s="4">
         <f t="array" aca="1" ref="F45" ca="1">_FV(B45,"Change (%)",TRUE)</f>
-        <v>1.321E-2</v>
+        <v>3.1621999999999997E-2</v>
       </c>
       <c r="G45" s="5">
         <f t="array" aca="1" ref="G45" ca="1">_FV(B45,"Change")</f>
-        <v>0.47</v>
+        <v>1.1251</v>
       </c>
       <c r="H45" s="6">
         <f t="array" aca="1" ref="H45" ca="1">_FV(B45,"P/E",TRUE)</f>
-        <v>19.642600000000002</v>
+        <v>19.999500000000001</v>
       </c>
       <c r="I45" s="6">
         <f t="array" aca="1" ref="I45" ca="1">_FV(B45,"Beta")</f>
@@ -13881,7 +13192,7 @@
       </c>
       <c r="L45" s="3">
         <f t="array" aca="1" ref="L45" ca="1">_FV(B45,"High")</f>
-        <v>36.36</v>
+        <v>36.799999999999997</v>
       </c>
       <c r="M45" s="3">
         <f t="array" aca="1" ref="M45" ca="1">_FV(B45,"Low")</f>
@@ -13897,7 +13208,7 @@
       </c>
       <c r="P45" s="7">
         <f t="array" aca="1" ref="P45" ca="1">_FV(B45,"Volume")</f>
-        <v>10512235</v>
+        <v>20014116</v>
       </c>
       <c r="Q45" s="7">
         <f t="array" aca="1" ref="Q45" ca="1">_FV(B45,"Volume average",TRUE)</f>
@@ -13917,7 +13228,7 @@
       </c>
       <c r="U45" s="7">
         <f t="array" aca="1" ref="U45" ca="1">_FV(B45,"Market cap",TRUE)</f>
-        <v>21681136925</v>
+        <v>22075126184</v>
       </c>
       <c r="V45" s="7">
         <f t="array" aca="1" ref="V45" ca="1">_FV(B45,"Shares outstanding",TRUE)</f>
@@ -13933,7 +13244,7 @@
       </c>
       <c r="C46" s="2">
         <f t="array" aca="1" ref="C46" ca="1">_FV(B46,"Last trade time",TRUE)</f>
-        <v>46168.605560878903</v>
+        <v>46168.683556955468</v>
       </c>
       <c r="D46" t="str">
         <f t="array" aca="1" ref="D46" ca="1">_FV(B46,"Currency")</f>
@@ -13941,19 +13252,19 @@
       </c>
       <c r="E46" s="3">
         <f t="array" aca="1" ref="E46" ca="1">_FV(B46,"Price")</f>
-        <v>74.269900000000007</v>
+        <v>74.27</v>
       </c>
       <c r="F46" s="4">
         <f t="array" aca="1" ref="F46" ca="1">_FV(B46,"Change (%)",TRUE)</f>
-        <v>8.5540000000000008E-3</v>
+        <v>8.5550000000000001E-3</v>
       </c>
       <c r="G46" s="5">
         <f t="array" aca="1" ref="G46" ca="1">_FV(B46,"Change")</f>
-        <v>0.62990000000000002</v>
+        <v>0.63</v>
       </c>
       <c r="H46" s="6">
         <f t="array" aca="1" ref="H46" ca="1">_FV(B46,"P/E",TRUE)</f>
-        <v>41.316099999999999</v>
+        <v>41.316200000000002</v>
       </c>
       <c r="I46" s="6">
         <f t="array" aca="1" ref="I46" ca="1">_FV(B46,"Beta")</f>
@@ -13985,7 +13296,7 @@
       </c>
       <c r="P46" s="7">
         <f t="array" aca="1" ref="P46" ca="1">_FV(B46,"Volume")</f>
-        <v>6240183</v>
+        <v>10204070</v>
       </c>
       <c r="Q46" s="7">
         <f t="array" aca="1" ref="Q46" ca="1">_FV(B46,"Volume average",TRUE)</f>
@@ -14005,7 +13316,7 @@
       </c>
       <c r="U46" s="7">
         <f t="array" aca="1" ref="U46" ca="1">_FV(B46,"Market cap",TRUE)</f>
-        <v>66880423726</v>
+        <v>66880513777</v>
       </c>
       <c r="V46" s="7">
         <f t="array" aca="1" ref="V46" ca="1">_FV(B46,"Shares outstanding",TRUE)</f>
@@ -14021,7 +13332,7 @@
       </c>
       <c r="C47" s="2">
         <f t="array" aca="1" ref="C47" ca="1">_FV(B47,"Last trade time",TRUE)</f>
-        <v>46168.605575624999</v>
+        <v>46168.683511990625</v>
       </c>
       <c r="D47" t="str">
         <f t="array" aca="1" ref="D47" ca="1">_FV(B47,"Currency")</f>
@@ -14029,19 +13340,19 @@
       </c>
       <c r="E47" s="3">
         <f t="array" aca="1" ref="E47" ca="1">_FV(B47,"Price")</f>
-        <v>383.3501</v>
+        <v>382.32</v>
       </c>
       <c r="F47" s="4">
         <f t="array" aca="1" ref="F47" ca="1">_FV(B47,"Change (%)",TRUE)</f>
-        <v>1.0465E-2</v>
+        <v>7.7490000000000007E-3</v>
       </c>
       <c r="G47" s="5">
         <f t="array" aca="1" ref="G47" ca="1">_FV(B47,"Change")</f>
-        <v>3.9701</v>
+        <v>2.94</v>
       </c>
       <c r="H47" s="6">
         <f t="array" aca="1" ref="H47" ca="1">_FV(B47,"P/E",TRUE)</f>
-        <v>29.277000000000001</v>
+        <v>29.1983</v>
       </c>
       <c r="I47" s="6">
         <f t="array" aca="1" ref="I47" ca="1">_FV(B47,"Beta")</f>
@@ -14057,7 +13368,7 @@
       </c>
       <c r="L47" s="3">
         <f t="array" aca="1" ref="L47" ca="1">_FV(B47,"High")</f>
-        <v>384.41250000000002</v>
+        <v>385.39</v>
       </c>
       <c r="M47" s="3">
         <f t="array" aca="1" ref="M47" ca="1">_FV(B47,"Low")</f>
@@ -14073,7 +13384,7 @@
       </c>
       <c r="P47" s="7">
         <f t="array" aca="1" ref="P47" ca="1">_FV(B47,"Volume")</f>
-        <v>3957341</v>
+        <v>7555535</v>
       </c>
       <c r="Q47" s="7">
         <f t="array" aca="1" ref="Q47" ca="1">_FV(B47,"Volume average",TRUE)</f>
@@ -14093,7 +13404,7 @@
       </c>
       <c r="U47" s="7">
         <f t="array" aca="1" ref="U47" ca="1">_FV(B47,"Market cap",TRUE)</f>
-        <v>4644669811600</v>
+        <v>4632189120000</v>
       </c>
       <c r="V47" s="7">
         <f t="array" aca="1" ref="V47" ca="1">_FV(B47,"Shares outstanding",TRUE)</f>
@@ -14109,7 +13420,7 @@
       </c>
       <c r="C48" s="2" cm="1">
         <f t="array" aca="1" ref="C48" ca="1">_FV(B48,"Last trade time",TRUE)</f>
-        <v>46168.60551517344</v>
+        <v>46168.683481099222</v>
       </c>
       <c r="D48" t="str" cm="1">
         <f t="array" aca="1" ref="D48" ca="1">_FV(B48,"Currency")</f>
@@ -14117,15 +13428,15 @@
       </c>
       <c r="E48" s="3" cm="1">
         <f t="array" aca="1" ref="E48" ca="1">_FV(B48,"Price")</f>
-        <v>218.54</v>
+        <v>220.06</v>
       </c>
       <c r="F48" s="4" cm="1">
         <f t="array" aca="1" ref="F48" ca="1">_FV(B48,"Change (%)",TRUE)</f>
-        <v>1.0964E-2</v>
+        <v>1.7995000000000001E-2</v>
       </c>
       <c r="G48" s="5" cm="1">
         <f t="array" aca="1" ref="G48" ca="1">_FV(B48,"Change")</f>
-        <v>2.37</v>
+        <v>3.89</v>
       </c>
       <c r="H48" s="6" t="e" cm="1" vm="12">
         <f t="array" ref="H48">_FV(B48,"P/E",TRUE)</f>
@@ -14145,7 +13456,7 @@
       </c>
       <c r="L48" s="3" cm="1">
         <f t="array" aca="1" ref="L48" ca="1">_FV(B48,"High")</f>
-        <v>219.06379999999999</v>
+        <v>220.59</v>
       </c>
       <c r="M48" s="3" cm="1">
         <f t="array" aca="1" ref="M48" ca="1">_FV(B48,"Low")</f>
@@ -14161,7 +13472,7 @@
       </c>
       <c r="P48" s="7" cm="1">
         <f t="array" aca="1" ref="P48" ca="1">_FV(B48,"Volume")</f>
-        <v>941066</v>
+        <v>1578332</v>
       </c>
       <c r="Q48" s="7" cm="1">
         <f t="array" aca="1" ref="Q48" ca="1">_FV(B48,"Volume average",TRUE)</f>
@@ -14181,7 +13492,7 @@
       </c>
       <c r="U48" s="7" cm="1">
         <f t="array" aca="1" ref="U48" ca="1">_FV(B48,"Market cap",TRUE)</f>
-        <v>77246503348</v>
+        <v>77783771972</v>
       </c>
       <c r="V48" s="7" cm="1">
         <f t="array" aca="1" ref="V48" ca="1">_FV(B48,"Shares outstanding",TRUE)</f>
@@ -14197,7 +13508,7 @@
       </c>
       <c r="C49" s="2" cm="1">
         <f t="array" aca="1" ref="C49" ca="1">_FV(B49,"Last trade time",TRUE)</f>
-        <v>46168.605602094533</v>
+        <v>46168.683437314059</v>
       </c>
       <c r="D49" t="str" cm="1">
         <f t="array" aca="1" ref="D49" ca="1">_FV(B49,"Currency")</f>
@@ -14205,19 +13516,19 @@
       </c>
       <c r="E49" s="3" cm="1">
         <f t="array" aca="1" ref="E49" ca="1">_FV(B49,"Price")</f>
-        <v>455.45499999999998</v>
+        <v>454.58</v>
       </c>
       <c r="F49" s="4" cm="1">
         <f t="array" aca="1" ref="F49" ca="1">_FV(B49,"Change (%)",TRUE)</f>
-        <v>6.9979999999999999E-3</v>
+        <v>5.0629999999999998E-3</v>
       </c>
       <c r="G49" s="5" cm="1">
         <f t="array" aca="1" ref="G49" ca="1">_FV(B49,"Change")</f>
-        <v>3.165</v>
+        <v>2.29</v>
       </c>
       <c r="H49" s="6" cm="1">
         <f t="array" aca="1" ref="H49" ca="1">_FV(B49,"P/E",TRUE)</f>
-        <v>47.314100000000003</v>
+        <v>47.223199999999999</v>
       </c>
       <c r="I49" s="6" cm="1">
         <f t="array" aca="1" ref="I49" ca="1">_FV(B49,"Beta")</f>
@@ -14249,7 +13560,7 @@
       </c>
       <c r="P49" s="7" cm="1">
         <f t="array" aca="1" ref="P49" ca="1">_FV(B49,"Volume")</f>
-        <v>126285</v>
+        <v>267037</v>
       </c>
       <c r="Q49" s="7" cm="1">
         <f t="array" aca="1" ref="Q49" ca="1">_FV(B49,"Volume average",TRUE)</f>
@@ -14269,7 +13580,7 @@
       </c>
       <c r="U49" s="7" cm="1">
         <f t="array" aca="1" ref="U49" ca="1">_FV(B49,"Market cap",TRUE)</f>
-        <v>50680254124</v>
+        <v>50582889462</v>
       </c>
       <c r="V49" s="7" cm="1">
         <f t="array" aca="1" ref="V49" ca="1">_FV(B49,"Shares outstanding",TRUE)</f>
@@ -14285,7 +13596,7 @@
       </c>
       <c r="C50" s="2">
         <f t="array" aca="1" ref="C50" ca="1">_FV(B50,"Last trade time",TRUE)</f>
-        <v>46168.605603043747</v>
+        <v>46168.683556342185</v>
       </c>
       <c r="D50" t="str">
         <f t="array" aca="1" ref="D50" ca="1">_FV(B50,"Currency")</f>
@@ -14293,19 +13604,19 @@
       </c>
       <c r="E50" s="3">
         <f t="array" aca="1" ref="E50" ca="1">_FV(B50,"Price")</f>
-        <v>311.5</v>
+        <v>310.04000000000002</v>
       </c>
       <c r="F50" s="4">
         <f t="array" aca="1" ref="F50" ca="1">_FV(B50,"Change (%)",TRUE)</f>
-        <v>8.6779999999999999E-3</v>
+        <v>3.9509999999999997E-3</v>
       </c>
       <c r="G50" s="5">
         <f t="array" aca="1" ref="G50" ca="1">_FV(B50,"Change")</f>
-        <v>2.68</v>
+        <v>1.22</v>
       </c>
       <c r="H50" s="6">
         <f t="array" aca="1" ref="H50" ca="1">_FV(B50,"P/E",TRUE)</f>
-        <v>37.831899999999997</v>
+        <v>37.654499999999999</v>
       </c>
       <c r="I50" s="6">
         <f t="array" aca="1" ref="I50" ca="1">_FV(B50,"Beta")</f>
@@ -14337,7 +13648,7 @@
       </c>
       <c r="P50" s="7">
         <f t="array" aca="1" ref="P50" ca="1">_FV(B50,"Volume")</f>
-        <v>9422483</v>
+        <v>16659446</v>
       </c>
       <c r="Q50" s="7">
         <f t="array" aca="1" ref="Q50" ca="1">_FV(B50,"Volume average",TRUE)</f>
@@ -14357,7 +13668,7 @@
       </c>
       <c r="U50" s="7">
         <f t="array" aca="1" ref="U50" ca="1">_FV(B50,"Market cap",TRUE)</f>
-        <v>4575112640000</v>
+        <v>4553669094400</v>
       </c>
       <c r="V50" s="7">
         <f t="array" aca="1" ref="V50" ca="1">_FV(B50,"Shares outstanding",TRUE)</f>
@@ -14373,7 +13684,7 @@
       </c>
       <c r="C51" s="2" cm="1">
         <f t="array" aca="1" ref="C51" ca="1">_FV(B51,"Last trade time",TRUE)</f>
-        <v>46168.605606284378</v>
+        <v>46168.683550253903</v>
       </c>
       <c r="D51" t="str" cm="1">
         <f t="array" aca="1" ref="D51" ca="1">_FV(B51,"Currency")</f>
@@ -14381,15 +13692,15 @@
       </c>
       <c r="E51" s="3" cm="1">
         <f t="array" aca="1" ref="E51" ca="1">_FV(B51,"Price")</f>
-        <v>751.58270000000005</v>
+        <v>749.34500000000003</v>
       </c>
       <c r="F51" s="4" cm="1">
         <f t="array" aca="1" ref="F51" ca="1">_FV(B51,"Change (%)",TRUE)</f>
-        <v>7.9699999999999997E-3</v>
+        <v>4.9690000000000003E-3</v>
       </c>
       <c r="G51" s="5" cm="1">
         <f t="array" aca="1" ref="G51" ca="1">_FV(B51,"Change")</f>
-        <v>5.9427000000000003</v>
+        <v>3.7050000000000001</v>
       </c>
       <c r="H51" s="6" t="e" cm="1" vm="12">
         <f t="array" ref="H51">_FV(B51,"P/E",TRUE)</f>
@@ -14401,7 +13712,7 @@
       </c>
       <c r="J51" s="3" cm="1">
         <f t="array" aca="1" ref="J51" ca="1">_FV(B51,"52 week high",TRUE)</f>
-        <v>751.8691</v>
+        <v>752.13</v>
       </c>
       <c r="K51" s="3" cm="1">
         <f t="array" aca="1" ref="K51" ca="1">_FV(B51,"52 week low",TRUE)</f>
@@ -14409,11 +13720,11 @@
       </c>
       <c r="L51" s="3" cm="1">
         <f t="array" aca="1" ref="L51" ca="1">_FV(B51,"High")</f>
-        <v>751.8691</v>
+        <v>752.13</v>
       </c>
       <c r="M51" s="3" cm="1">
         <f t="array" aca="1" ref="M51" ca="1">_FV(B51,"Low")</f>
-        <v>749.15</v>
+        <v>748.37</v>
       </c>
       <c r="N51" s="3" cm="1">
         <f t="array" aca="1" ref="N51" ca="1">_FV(B51,"Open")</f>
@@ -14425,7 +13736,7 @@
       </c>
       <c r="P51" s="7" cm="1">
         <f t="array" aca="1" ref="P51" ca="1">_FV(B51,"Volume")</f>
-        <v>7271177</v>
+        <v>16804518</v>
       </c>
       <c r="Q51" s="7" cm="1">
         <f t="array" aca="1" ref="Q51" ca="1">_FV(B51,"Volume average",TRUE)</f>
@@ -14461,7 +13772,7 @@
       </c>
       <c r="C52" s="2">
         <f t="array" aca="1" ref="C52" ca="1">_FV(B52,"Last trade time",TRUE)</f>
-        <v>46168.605568043749</v>
+        <v>46168.683534270313</v>
       </c>
       <c r="D52" t="str">
         <f t="array" aca="1" ref="D52" ca="1">_FV(B52,"Currency")</f>
@@ -14469,19 +13780,19 @@
       </c>
       <c r="E52" s="3">
         <f t="array" aca="1" ref="E52" ca="1">_FV(B52,"Price")</f>
-        <v>218.065</v>
+        <v>212.55</v>
       </c>
       <c r="F52" s="4">
         <f t="array" aca="1" ref="F52" ca="1">_FV(B52,"Change (%)",TRUE)</f>
-        <v>1.2701E-2</v>
+        <v>-1.291E-2</v>
       </c>
       <c r="G52" s="5">
         <f t="array" aca="1" ref="G52" ca="1">_FV(B52,"Change")</f>
-        <v>2.7349999999999999</v>
+        <v>-2.78</v>
       </c>
       <c r="H52" s="6">
         <f t="array" aca="1" ref="H52" ca="1">_FV(B52,"P/E",TRUE)</f>
-        <v>33.394300000000001</v>
+        <v>32.549799999999998</v>
       </c>
       <c r="I52" s="6">
         <f t="array" aca="1" ref="I52" ca="1">_FV(B52,"Beta")</f>
@@ -14501,7 +13812,7 @@
       </c>
       <c r="M52" s="3">
         <f t="array" aca="1" ref="M52" ca="1">_FV(B52,"Low")</f>
-        <v>214.28</v>
+        <v>212</v>
       </c>
       <c r="N52" s="3">
         <f t="array" aca="1" ref="N52" ca="1">_FV(B52,"Open")</f>
@@ -14513,7 +13824,7 @@
       </c>
       <c r="P52" s="7">
         <f t="array" aca="1" ref="P52" ca="1">_FV(B52,"Volume")</f>
-        <v>49996640</v>
+        <v>93010094</v>
       </c>
       <c r="Q52" s="7">
         <f t="array" aca="1" ref="Q52" ca="1">_FV(B52,"Volume average",TRUE)</f>
@@ -14533,7 +13844,7 @@
       </c>
       <c r="U52" s="7">
         <f t="array" aca="1" ref="U52" ca="1">_FV(B52,"Market cap",TRUE)</f>
-        <v>5277173000000</v>
+        <v>5143710000000</v>
       </c>
       <c r="V52" s="7">
         <f t="array" aca="1" ref="V52" ca="1">_FV(B52,"Shares outstanding",TRUE)</f>
@@ -14549,7 +13860,7 @@
       </c>
       <c r="C53" s="2" cm="1">
         <f t="array" aca="1" ref="C53" ca="1">_FV(B53,"Last trade time",TRUE)</f>
-        <v>46168.605593830471</v>
+        <v>46168.683581133591</v>
       </c>
       <c r="D53" t="str" cm="1">
         <f t="array" aca="1" ref="D53" ca="1">_FV(B53,"Currency")</f>
@@ -14557,15 +13868,15 @@
       </c>
       <c r="E53" s="3" cm="1">
         <f t="array" aca="1" ref="E53" ca="1">_FV(B53,"Price")</f>
-        <v>3.0449999999999999</v>
+        <v>2.9849999999999999</v>
       </c>
       <c r="F53" s="4" cm="1">
         <f t="array" aca="1" ref="F53" ca="1">_FV(B53,"Change (%)",TRUE)</f>
-        <v>1.1628000000000001E-2</v>
+        <v>-8.3060000000000009E-3</v>
       </c>
       <c r="G53" s="5" cm="1">
         <f t="array" aca="1" ref="G53" ca="1">_FV(B53,"Change")</f>
-        <v>3.5000000000000003E-2</v>
+        <v>-2.5000000000000001E-2</v>
       </c>
       <c r="H53" s="6" cm="1">
         <f t="array" aca="1" ref="H53" ca="1">_FV(B53,"P/E",TRUE)</f>
@@ -14589,7 +13900,7 @@
       </c>
       <c r="M53" s="3" cm="1">
         <f t="array" aca="1" ref="M53" ca="1">_FV(B53,"Low")</f>
-        <v>2.99</v>
+        <v>2.98</v>
       </c>
       <c r="N53" s="3" cm="1">
         <f t="array" aca="1" ref="N53" ca="1">_FV(B53,"Open")</f>
@@ -14601,7 +13912,7 @@
       </c>
       <c r="P53" s="7" cm="1">
         <f t="array" aca="1" ref="P53" ca="1">_FV(B53,"Volume")</f>
-        <v>9755377</v>
+        <v>15916324</v>
       </c>
       <c r="Q53" s="7" cm="1">
         <f t="array" aca="1" ref="Q53" ca="1">_FV(B53,"Volume average",TRUE)</f>
@@ -14621,7 +13932,7 @@
       </c>
       <c r="U53" s="7" cm="1">
         <f t="array" aca="1" ref="U53" ca="1">_FV(B53,"Market cap",TRUE)</f>
-        <v>1613561334</v>
+        <v>1581767022</v>
       </c>
       <c r="V53" s="7" cm="1">
         <f t="array" aca="1" ref="V53" ca="1">_FV(B53,"Shares outstanding",TRUE)</f>
@@ -14637,7 +13948,7 @@
       </c>
       <c r="C54" s="2" cm="1">
         <f t="array" aca="1" ref="C54" ca="1">_FV(B54,"Last trade time",TRUE)</f>
-        <v>46168.60555172422</v>
+        <v>46168.683540728904</v>
       </c>
       <c r="D54" t="str" cm="1">
         <f t="array" aca="1" ref="D54" ca="1">_FV(B54,"Currency")</f>
@@ -14645,15 +13956,15 @@
       </c>
       <c r="E54" s="3" cm="1">
         <f t="array" aca="1" ref="E54" ca="1">_FV(B54,"Price")</f>
-        <v>666.39</v>
+        <v>676.26</v>
       </c>
       <c r="F54" s="4" cm="1">
         <f t="array" aca="1" ref="F54" ca="1">_FV(B54,"Change (%)",TRUE)</f>
-        <v>4.4159999999999998E-3</v>
+        <v>1.9293000000000001E-2</v>
       </c>
       <c r="G54" s="5" cm="1">
         <f t="array" aca="1" ref="G54" ca="1">_FV(B54,"Change")</f>
-        <v>2.93</v>
+        <v>12.8</v>
       </c>
       <c r="H54" s="6" cm="1">
         <f t="array" aca="1" ref="H54" ca="1">_FV(B54,"P/E",TRUE)</f>
@@ -14665,7 +13976,7 @@
       </c>
       <c r="J54" s="3" cm="1">
         <f t="array" aca="1" ref="J54" ca="1">_FV(B54,"52 week high",TRUE)</f>
-        <v>674.84</v>
+        <v>677.49990000000003</v>
       </c>
       <c r="K54" s="3" cm="1">
         <f t="array" aca="1" ref="K54" ca="1">_FV(B54,"52 week low",TRUE)</f>
@@ -14673,7 +13984,7 @@
       </c>
       <c r="L54" s="3" cm="1">
         <f t="array" aca="1" ref="L54" ca="1">_FV(B54,"High")</f>
-        <v>669.69</v>
+        <v>677.49990000000003</v>
       </c>
       <c r="M54" s="3" cm="1">
         <f t="array" aca="1" ref="M54" ca="1">_FV(B54,"Low")</f>
@@ -14689,7 +14000,7 @@
       </c>
       <c r="P54" s="7" cm="1">
         <f t="array" aca="1" ref="P54" ca="1">_FV(B54,"Volume")</f>
-        <v>653576</v>
+        <v>1071573</v>
       </c>
       <c r="Q54" s="7" cm="1">
         <f t="array" aca="1" ref="Q54" ca="1">_FV(B54,"Volume average",TRUE)</f>
@@ -14709,7 +14020,7 @@
       </c>
       <c r="U54" s="7" cm="1">
         <f t="array" aca="1" ref="U54" ca="1">_FV(B54,"Market cap",TRUE)</f>
-        <v>169620578235</v>
+        <v>172132853490</v>
       </c>
       <c r="V54" s="7" cm="1">
         <f t="array" aca="1" ref="V54" ca="1">_FV(B54,"Shares outstanding",TRUE)</f>
@@ -14725,7 +14036,7 @@
       </c>
       <c r="C55" s="2">
         <f t="array" aca="1" ref="C55" ca="1">_FV(B55,"Last trade time",TRUE)</f>
-        <v>46167.83323616875</v>
+        <v>46168.662617117967</v>
       </c>
       <c r="D55" t="str">
         <f t="array" aca="1" ref="D55" ca="1">_FV(B55,"Currency")</f>
@@ -14733,19 +14044,19 @@
       </c>
       <c r="E55" s="3">
         <f t="array" aca="1" ref="E55" ca="1">_FV(B55,"Price")</f>
-        <v>11.86</v>
+        <v>11.8</v>
       </c>
       <c r="F55" s="4">
         <f t="array" aca="1" ref="F55" ca="1">_FV(B55,"Change (%)",TRUE)</f>
-        <v>4.2339999999999999E-3</v>
+        <v>-5.0590000000000001E-3</v>
       </c>
       <c r="G55" s="5">
         <f t="array" aca="1" ref="G55" ca="1">_FV(B55,"Change")</f>
-        <v>0.05</v>
+        <v>-0.06</v>
       </c>
       <c r="H55" s="6">
         <f t="array" aca="1" ref="H55" ca="1">_FV(B55,"P/E",TRUE)</f>
-        <v>11.2706</v>
+        <v>11.2135</v>
       </c>
       <c r="I55" s="6">
         <f t="array" aca="1" ref="I55" ca="1">_FV(B55,"Beta")</f>
@@ -14761,23 +14072,23 @@
       </c>
       <c r="L55" s="3">
         <f t="array" aca="1" ref="L55" ca="1">_FV(B55,"High")</f>
-        <v>11.94</v>
+        <v>11.84</v>
       </c>
       <c r="M55" s="3">
         <f t="array" aca="1" ref="M55" ca="1">_FV(B55,"Low")</f>
-        <v>11.86</v>
+        <v>11.8</v>
       </c>
       <c r="N55" s="3">
         <f t="array" aca="1" ref="N55" ca="1">_FV(B55,"Open")</f>
-        <v>11.94</v>
+        <v>11.81</v>
       </c>
       <c r="O55" s="3">
         <f t="array" aca="1" ref="O55" ca="1">_FV(B55,"Previous close",TRUE)</f>
-        <v>11.81</v>
+        <v>11.86</v>
       </c>
       <c r="P55" s="7">
         <f t="array" aca="1" ref="P55" ca="1">_FV(B55,"Volume")</f>
-        <v>6200</v>
+        <v>1500</v>
       </c>
       <c r="Q55" s="7">
         <f t="array" aca="1" ref="Q55" ca="1">_FV(B55,"Volume average",TRUE)</f>
@@ -14797,7 +14108,7 @@
       </c>
       <c r="U55" s="7">
         <f t="array" aca="1" ref="U55" ca="1">_FV(B55,"Market cap",TRUE)</f>
-        <v>570901736</v>
+        <v>568013532</v>
       </c>
       <c r="V55" s="7">
         <f t="array" aca="1" ref="V55" ca="1">_FV(B55,"Shares outstanding",TRUE)</f>
@@ -14813,7 +14124,7 @@
       </c>
       <c r="C56" s="2">
         <f t="array" aca="1" ref="C56" ca="1">_FV(B56,"Last trade time",TRUE)</f>
-        <v>46168.605603263284</v>
+        <v>46168.683550219532</v>
       </c>
       <c r="D56" t="str">
         <f t="array" aca="1" ref="D56" ca="1">_FV(B56,"Currency")</f>
@@ -14821,15 +14132,15 @@
       </c>
       <c r="E56" s="3">
         <f t="array" aca="1" ref="E56" ca="1">_FV(B56,"Price")</f>
-        <v>4.1900000000000004</v>
+        <v>4.22</v>
       </c>
       <c r="F56" s="4">
         <f t="array" aca="1" ref="F56" ca="1">_FV(B56,"Change (%)",TRUE)</f>
-        <v>2.392E-3</v>
+        <v>9.5689999999999994E-3</v>
       </c>
       <c r="G56" s="5">
         <f t="array" aca="1" ref="G56" ca="1">_FV(B56,"Change")</f>
-        <v>0.01</v>
+        <v>0.04</v>
       </c>
       <c r="H56" s="6">
         <f t="array" aca="1" ref="H56" ca="1">_FV(B56,"P/E",TRUE)</f>
@@ -14865,7 +14176,7 @@
       </c>
       <c r="P56" s="7">
         <f t="array" aca="1" ref="P56" ca="1">_FV(B56,"Volume")</f>
-        <v>13220114</v>
+        <v>24891393</v>
       </c>
       <c r="Q56" s="7">
         <f t="array" aca="1" ref="Q56" ca="1">_FV(B56,"Volume average",TRUE)</f>
@@ -14885,7 +14196,7 @@
       </c>
       <c r="U56" s="7">
         <f t="array" aca="1" ref="U56" ca="1">_FV(B56,"Market cap",TRUE)</f>
-        <v>2006798405</v>
+        <v>2021166890</v>
       </c>
       <c r="V56" s="7">
         <f t="array" aca="1" ref="V56" ca="1">_FV(B56,"Shares outstanding",TRUE)</f>
@@ -14901,7 +14212,7 @@
       </c>
       <c r="C57" s="2">
         <f t="array" aca="1" ref="C57" ca="1">_FV(B57,"Last trade time",TRUE)</f>
-        <v>46168.605610532031</v>
+        <v>46168.683556921096</v>
       </c>
       <c r="D57" t="str">
         <f t="array" aca="1" ref="D57" ca="1">_FV(B57,"Currency")</f>
@@ -14909,19 +14220,19 @@
       </c>
       <c r="E57" s="3">
         <f t="array" aca="1" ref="E57" ca="1">_FV(B57,"Price")</f>
-        <v>101.12</v>
+        <v>101.82</v>
       </c>
       <c r="F57" s="4">
         <f t="array" aca="1" ref="F57" ca="1">_FV(B57,"Change (%)",TRUE)</f>
-        <v>-9.8890000000000002E-3</v>
+        <v>-3.0349999999999999E-3</v>
       </c>
       <c r="G57" s="5">
         <f t="array" aca="1" ref="G57" ca="1">_FV(B57,"Change")</f>
-        <v>-1.01</v>
+        <v>-0.31</v>
       </c>
       <c r="H57" s="6">
         <f t="array" aca="1" ref="H57" ca="1">_FV(B57,"P/E",TRUE)</f>
-        <v>60.1404</v>
+        <v>60.556699999999999</v>
       </c>
       <c r="I57" s="6">
         <f t="array" aca="1" ref="I57" ca="1">_FV(B57,"Beta")</f>
@@ -14953,7 +14264,7 @@
       </c>
       <c r="P57" s="7">
         <f t="array" aca="1" ref="P57" ca="1">_FV(B57,"Volume")</f>
-        <v>8290675</v>
+        <v>12018396</v>
       </c>
       <c r="Q57" s="7">
         <f t="array" aca="1" ref="Q57" ca="1">_FV(B57,"Volume average",TRUE)</f>
@@ -14973,7 +14284,7 @@
       </c>
       <c r="U57" s="7">
         <f t="array" aca="1" ref="U57" ca="1">_FV(B57,"Market cap",TRUE)</f>
-        <v>104285864960</v>
+        <v>105007780560</v>
       </c>
       <c r="V57" s="7">
         <f t="array" aca="1" ref="V57" ca="1">_FV(B57,"Shares outstanding",TRUE)</f>
@@ -14989,7 +14300,7 @@
       </c>
       <c r="C58" s="2">
         <f t="array" aca="1" ref="C58" ca="1">_FV(B58,"Last trade time",TRUE)</f>
-        <v>46168.605549883592</v>
+        <v>46168.683520253908</v>
       </c>
       <c r="D58" t="str">
         <f t="array" aca="1" ref="D58" ca="1">_FV(B58,"Currency")</f>
@@ -14997,19 +14308,19 @@
       </c>
       <c r="E58" s="3">
         <f t="array" aca="1" ref="E58" ca="1">_FV(B58,"Price")</f>
-        <v>417.94009999999997</v>
+        <v>415.76</v>
       </c>
       <c r="F58" s="4">
         <f t="array" aca="1" ref="F58" ca="1">_FV(B58,"Change (%)",TRUE)</f>
-        <v>-1.505E-3</v>
+        <v>-6.7130000000000002E-3</v>
       </c>
       <c r="G58" s="5">
         <f t="array" aca="1" ref="G58" ca="1">_FV(B58,"Change")</f>
-        <v>-0.62990000000000002</v>
+        <v>-2.81</v>
       </c>
       <c r="H58" s="6">
         <f t="array" aca="1" ref="H58" ca="1">_FV(B58,"P/E",TRUE)</f>
-        <v>24.892800000000001</v>
+        <v>24.762899999999998</v>
       </c>
       <c r="I58" s="6">
         <f t="array" aca="1" ref="I58" ca="1">_FV(B58,"Beta")</f>
@@ -15041,7 +14352,7 @@
       </c>
       <c r="P58" s="7">
         <f t="array" aca="1" ref="P58" ca="1">_FV(B58,"Volume")</f>
-        <v>9383019</v>
+        <v>14980013</v>
       </c>
       <c r="Q58" s="7">
         <f t="array" aca="1" ref="Q58" ca="1">_FV(B58,"Volume average",TRUE)</f>
@@ -15061,7 +14372,7 @@
       </c>
       <c r="U58" s="7">
         <f t="array" aca="1" ref="U58" ca="1">_FV(B58,"Market cap",TRUE)</f>
-        <v>3104640866743</v>
+        <v>3088446135600</v>
       </c>
       <c r="V58" s="7">
         <f t="array" aca="1" ref="V58" ca="1">_FV(B58,"Shares outstanding",TRUE)</f>
@@ -15077,7 +14388,7 @@
       </c>
       <c r="C59" s="2">
         <f t="array" aca="1" ref="C59" ca="1">_FV(B59,"Last trade time",TRUE)</f>
-        <v>46168.605548240623</v>
+        <v>46168.683502117972</v>
       </c>
       <c r="D59" t="str">
         <f t="array" aca="1" ref="D59" ca="1">_FV(B59,"Currency")</f>
@@ -15085,19 +14396,19 @@
       </c>
       <c r="E59" s="3">
         <f t="array" aca="1" ref="E59" ca="1">_FV(B59,"Price")</f>
-        <v>426.42</v>
+        <v>428.6773</v>
       </c>
       <c r="F59" s="4">
         <f t="array" aca="1" ref="F59" ca="1">_FV(B59,"Change (%)",TRUE)</f>
-        <v>9.6240000000000008E-4</v>
+        <v>6.2610000000000001E-3</v>
       </c>
       <c r="G59" s="5">
         <f t="array" aca="1" ref="G59" ca="1">_FV(B59,"Change")</f>
-        <v>0.41</v>
+        <v>2.6673</v>
       </c>
       <c r="H59" s="6">
         <f t="array" aca="1" ref="H59" ca="1">_FV(B59,"P/E",TRUE)</f>
-        <v>389.745</v>
+        <v>391.8082</v>
       </c>
       <c r="I59" s="6">
         <f t="array" aca="1" ref="I59" ca="1">_FV(B59,"Beta")</f>
@@ -15113,7 +14424,7 @@
       </c>
       <c r="L59" s="3">
         <f t="array" aca="1" ref="L59" ca="1">_FV(B59,"High")</f>
-        <v>433.67</v>
+        <v>434.56</v>
       </c>
       <c r="M59" s="3">
         <f t="array" aca="1" ref="M59" ca="1">_FV(B59,"Low")</f>
@@ -15129,7 +14440,7 @@
       </c>
       <c r="P59" s="7">
         <f t="array" aca="1" ref="P59" ca="1">_FV(B59,"Volume")</f>
-        <v>11914353</v>
+        <v>24725470</v>
       </c>
       <c r="Q59" s="7">
         <f t="array" aca="1" ref="Q59" ca="1">_FV(B59,"Volume average",TRUE)</f>
@@ -15149,7 +14460,7 @@
       </c>
       <c r="U59" s="7">
         <f t="array" aca="1" ref="U59" ca="1">_FV(B59,"Market cap",TRUE)</f>
-        <v>1601515828080</v>
+        <v>1609993623865</v>
       </c>
       <c r="V59" s="7">
         <f t="array" aca="1" ref="V59" ca="1">_FV(B59,"Shares outstanding",TRUE)</f>
@@ -15165,7 +14476,7 @@
       </c>
       <c r="C60" s="2">
         <f t="array" aca="1" ref="C60" ca="1">_FV(B60,"Last trade time",TRUE)</f>
-        <v>46168.59489649297</v>
+        <v>46168.655232291407</v>
       </c>
       <c r="D60" t="str">
         <f t="array" aca="1" ref="D60" ca="1">_FV(B60,"Currency")</f>
@@ -15173,19 +14484,19 @@
       </c>
       <c r="E60" s="9">
         <f t="array" aca="1" ref="E60" ca="1">_FV(B60,"Price")</f>
-        <v>880.6</v>
+        <v>876</v>
       </c>
       <c r="F60" s="4">
         <f t="array" aca="1" ref="F60" ca="1">_FV(B60,"Change (%)",TRUE)</f>
-        <v>2.0479999999999999E-3</v>
+        <v>-3.186E-3</v>
       </c>
       <c r="G60" s="5">
         <f t="array" aca="1" ref="G60" ca="1">_FV(B60,"Change")</f>
-        <v>1.8</v>
+        <v>-2.8</v>
       </c>
       <c r="H60" s="6">
         <f t="array" aca="1" ref="H60" ca="1">_FV(B60,"P/E",TRUE)</f>
-        <v>25.2393</v>
+        <v>25.1248</v>
       </c>
       <c r="I60" s="6">
         <f t="array" aca="1" ref="I60" ca="1">_FV(B60,"Beta")</f>
@@ -15217,7 +14528,7 @@
       </c>
       <c r="P60" s="7">
         <f t="array" aca="1" ref="P60" ca="1">_FV(B60,"Volume")</f>
-        <v>1471744</v>
+        <v>5230317</v>
       </c>
       <c r="Q60" s="7">
         <f t="array" aca="1" ref="Q60" ca="1">_FV(B60,"Volume average",TRUE)</f>
@@ -15253,7 +14564,7 @@
       </c>
       <c r="C61" s="2">
         <f t="array" aca="1" ref="C61" ca="1">_FV(B61,"Last trade time",TRUE)</f>
-        <v>46168.605621885938</v>
+        <v>46168.683501250001</v>
       </c>
       <c r="D61" t="str">
         <f t="array" aca="1" ref="D61" ca="1">_FV(B61,"Currency")</f>
@@ -15261,19 +14572,19 @@
       </c>
       <c r="E61" s="3">
         <f t="array" aca="1" ref="E61" ca="1">_FV(B61,"Price")</f>
-        <v>221.02</v>
+        <v>224.89500000000001</v>
       </c>
       <c r="F61" s="4">
         <f t="array" aca="1" ref="F61" ca="1">_FV(B61,"Change (%)",TRUE)</f>
-        <v>-5.8469999999999998E-3</v>
+        <v>1.1581999999999999E-2</v>
       </c>
       <c r="G61" s="5">
         <f t="array" aca="1" ref="G61" ca="1">_FV(B61,"Change")</f>
-        <v>-1.3</v>
+        <v>2.5750000000000002</v>
       </c>
       <c r="H61" s="6">
         <f t="array" aca="1" ref="H61" ca="1">_FV(B61,"P/E",TRUE)</f>
-        <v>559.96960000000001</v>
+        <v>569.78719999999998</v>
       </c>
       <c r="I61" s="6">
         <f t="array" aca="1" ref="I61" ca="1">_FV(B61,"Beta")</f>
@@ -15281,7 +14592,7 @@
       </c>
       <c r="J61" s="3">
         <f t="array" aca="1" ref="J61" ca="1">_FV(B61,"52 week high",TRUE)</f>
-        <v>224.76929999999999</v>
+        <v>225.9</v>
       </c>
       <c r="K61" s="3">
         <f t="array" aca="1" ref="K61" ca="1">_FV(B61,"52 week low",TRUE)</f>
@@ -15289,7 +14600,7 @@
       </c>
       <c r="L61" s="3">
         <f t="array" aca="1" ref="L61" ca="1">_FV(B61,"High")</f>
-        <v>223.93</v>
+        <v>225.9</v>
       </c>
       <c r="M61" s="3">
         <f t="array" aca="1" ref="M61" ca="1">_FV(B61,"Low")</f>
@@ -15305,7 +14616,7 @@
       </c>
       <c r="P61" s="7">
         <f t="array" aca="1" ref="P61" ca="1">_FV(B61,"Volume")</f>
-        <v>915483</v>
+        <v>1691623</v>
       </c>
       <c r="Q61" s="7">
         <f t="array" aca="1" ref="Q61" ca="1">_FV(B61,"Volume average",TRUE)</f>
@@ -15325,7 +14636,7 @@
       </c>
       <c r="U61" s="7">
         <f t="array" aca="1" ref="U61" ca="1">_FV(B61,"Market cap",TRUE)</f>
-        <v>78674323404</v>
+        <v>80053669179</v>
       </c>
       <c r="V61" s="7">
         <f t="array" aca="1" ref="V61" ca="1">_FV(B61,"Shares outstanding",TRUE)</f>
@@ -15341,7 +14652,7 @@
       </c>
       <c r="C62" s="2">
         <f t="array" aca="1" ref="C62" ca="1">_FV(B62,"Last trade time",TRUE)</f>
-        <v>46168.60560993047</v>
+        <v>46168.683587036721</v>
       </c>
       <c r="D62" t="str">
         <f t="array" aca="1" ref="D62" ca="1">_FV(B62,"Currency")</f>
@@ -15349,19 +14660,19 @@
       </c>
       <c r="E62" s="3">
         <f t="array" aca="1" ref="E62" ca="1">_FV(B62,"Price")</f>
-        <v>608.16</v>
+        <v>609.70000000000005</v>
       </c>
       <c r="F62" s="4">
         <f t="array" aca="1" ref="F62" ca="1">_FV(B62,"Change (%)",TRUE)</f>
-        <v>-3.441E-3</v>
+        <v>-9.1759999999999997E-4</v>
       </c>
       <c r="G62" s="5">
         <f t="array" aca="1" ref="G62" ca="1">_FV(B62,"Change")</f>
-        <v>-2.1</v>
+        <v>-0.56000000000000005</v>
       </c>
       <c r="H62" s="6">
         <f t="array" aca="1" ref="H62" ca="1">_FV(B62,"P/E",TRUE)</f>
-        <v>18.446400000000001</v>
+        <v>18.493099999999998</v>
       </c>
       <c r="I62" s="6">
         <f t="array" aca="1" ref="I62" ca="1">_FV(B62,"Beta")</f>
@@ -15381,7 +14692,7 @@
       </c>
       <c r="M62" s="3">
         <f t="array" aca="1" ref="M62" ca="1">_FV(B62,"Low")</f>
-        <v>605.58500000000004</v>
+        <v>605.30010000000004</v>
       </c>
       <c r="N62" s="3">
         <f t="array" aca="1" ref="N62" ca="1">_FV(B62,"Open")</f>
@@ -15393,7 +14704,7 @@
       </c>
       <c r="P62" s="7">
         <f t="array" aca="1" ref="P62" ca="1">_FV(B62,"Volume")</f>
-        <v>3551414</v>
+        <v>6078134</v>
       </c>
       <c r="Q62" s="7">
         <f t="array" aca="1" ref="Q62" ca="1">_FV(B62,"Volume average",TRUE)</f>
@@ -15413,7 +14724,7 @@
       </c>
       <c r="U62" s="7">
         <f t="array" aca="1" ref="U62" ca="1">_FV(B62,"Market cap",TRUE)</f>
-        <v>1543767331680</v>
+        <v>1547676503100</v>
       </c>
       <c r="V62" s="7">
         <f t="array" aca="1" ref="V62" ca="1">_FV(B62,"Shares outstanding",TRUE)</f>
@@ -15429,7 +14740,7 @@
       </c>
       <c r="C63" s="2">
         <f t="array" aca="1" ref="C63" ca="1">_FV(B63,"Last trade time",TRUE)</f>
-        <v>46168.605584270314</v>
+        <v>46168.68354563594</v>
       </c>
       <c r="D63" t="str">
         <f t="array" aca="1" ref="D63" ca="1">_FV(B63,"Currency")</f>
@@ -15437,19 +14748,19 @@
       </c>
       <c r="E63" s="3">
         <f t="array" aca="1" ref="E63" ca="1">_FV(B63,"Price")</f>
-        <v>264.88</v>
+        <v>263.62</v>
       </c>
       <c r="F63" s="4">
         <f t="array" aca="1" ref="F63" ca="1">_FV(B63,"Change (%)",TRUE)</f>
-        <v>-5.4069999999999995E-3</v>
+        <v>-1.0138000000000001E-2</v>
       </c>
       <c r="G63" s="5">
         <f t="array" aca="1" ref="G63" ca="1">_FV(B63,"Change")</f>
-        <v>-1.44</v>
+        <v>-2.7</v>
       </c>
       <c r="H63" s="6">
         <f t="array" aca="1" ref="H63" ca="1">_FV(B63,"P/E",TRUE)</f>
-        <v>31.655100000000001</v>
+        <v>31.5045</v>
       </c>
       <c r="I63" s="6">
         <f t="array" aca="1" ref="I63" ca="1">_FV(B63,"Beta")</f>
@@ -15469,7 +14780,7 @@
       </c>
       <c r="M63" s="3">
         <f t="array" aca="1" ref="M63" ca="1">_FV(B63,"Low")</f>
-        <v>264.68</v>
+        <v>263.22000000000003</v>
       </c>
       <c r="N63" s="3">
         <f t="array" aca="1" ref="N63" ca="1">_FV(B63,"Open")</f>
@@ -15481,7 +14792,7 @@
       </c>
       <c r="P63" s="7">
         <f t="array" aca="1" ref="P63" ca="1">_FV(B63,"Volume")</f>
-        <v>8866444</v>
+        <v>16786193</v>
       </c>
       <c r="Q63" s="7">
         <f t="array" aca="1" ref="Q63" ca="1">_FV(B63,"Volume average",TRUE)</f>
@@ -15501,7 +14812,7 @@
       </c>
       <c r="U63" s="7">
         <f t="array" aca="1" ref="U63" ca="1">_FV(B63,"Market cap",TRUE)</f>
-        <v>2849343296800</v>
+        <v>2835789338200</v>
       </c>
       <c r="V63" s="7">
         <f t="array" aca="1" ref="V63" ca="1">_FV(B63,"Shares outstanding",TRUE)</f>
@@ -15517,7 +14828,7 @@
       </c>
       <c r="C64" s="2">
         <f t="array" aca="1" ref="C64" ca="1">_FV(B64,"Last trade time",TRUE)</f>
-        <v>46168.605590647654</v>
+        <v>46168.683534270313</v>
       </c>
       <c r="D64" t="str">
         <f t="array" aca="1" ref="D64" ca="1">_FV(B64,"Currency")</f>
@@ -15525,19 +14836,19 @@
       </c>
       <c r="E64" s="3">
         <f t="array" aca="1" ref="E64" ca="1">_FV(B64,"Price")</f>
-        <v>1637.07</v>
+        <v>1617.53</v>
       </c>
       <c r="F64" s="4">
         <f t="array" aca="1" ref="F64" ca="1">_FV(B64,"Change (%)",TRUE)</f>
-        <v>2.5540000000000003E-3</v>
+        <v>-9.4129999999999995E-3</v>
       </c>
       <c r="G64" s="5">
         <f t="array" aca="1" ref="G64" ca="1">_FV(B64,"Change")</f>
-        <v>4.17</v>
+        <v>-15.37</v>
       </c>
       <c r="H64" s="6">
         <f t="array" aca="1" ref="H64" ca="1">_FV(B64,"P/E",TRUE)</f>
-        <v>56.282200000000003</v>
+        <v>55.610399999999998</v>
       </c>
       <c r="I64" s="6">
         <f t="array" aca="1" ref="I64" ca="1">_FV(B64,"Beta")</f>
@@ -15557,7 +14868,7 @@
       </c>
       <c r="M64" s="3">
         <f t="array" aca="1" ref="M64" ca="1">_FV(B64,"Low")</f>
-        <v>1617.86</v>
+        <v>1604.25</v>
       </c>
       <c r="N64" s="3">
         <f t="array" aca="1" ref="N64" ca="1">_FV(B64,"Open")</f>
@@ -15569,7 +14880,7 @@
       </c>
       <c r="P64" s="7">
         <f t="array" aca="1" ref="P64" ca="1">_FV(B64,"Volume")</f>
-        <v>536781</v>
+        <v>919958</v>
       </c>
       <c r="Q64" s="7">
         <f t="array" aca="1" ref="Q64" ca="1">_FV(B64,"Volume average",TRUE)</f>
@@ -15589,7 +14900,7 @@
       </c>
       <c r="U64" s="7">
         <f t="array" aca="1" ref="U64" ca="1">_FV(B64,"Market cap",TRUE)</f>
-        <v>635424955239</v>
+        <v>627840549181</v>
       </c>
       <c r="V64" s="7">
         <f t="array" aca="1" ref="V64" ca="1">_FV(B64,"Shares outstanding",TRUE)</f>
@@ -15605,7 +14916,7 @@
       </c>
       <c r="C65" s="2">
         <f t="array" aca="1" ref="C65" ca="1">_FV(B65,"Last trade time",TRUE)</f>
-        <v>46168.605626457815</v>
+        <v>46168.683565497653</v>
       </c>
       <c r="D65" t="str">
         <f t="array" aca="1" ref="D65" ca="1">_FV(B65,"Currency")</f>
@@ -15613,19 +14924,19 @@
       </c>
       <c r="E65" s="3">
         <f t="array" aca="1" ref="E65" ca="1">_FV(B65,"Price")</f>
-        <v>89.784999999999997</v>
+        <v>90.18</v>
       </c>
       <c r="F65" s="4">
         <f t="array" aca="1" ref="F65" ca="1">_FV(B65,"Change (%)",TRUE)</f>
-        <v>-4.0489999999999996E-3</v>
+        <v>3.3279999999999996E-4</v>
       </c>
       <c r="G65" s="5">
         <f t="array" aca="1" ref="G65" ca="1">_FV(B65,"Change")</f>
-        <v>-0.36499999999999999</v>
+        <v>0.03</v>
       </c>
       <c r="H65" s="6">
         <f t="array" aca="1" ref="H65" ca="1">_FV(B65,"P/E",TRUE)</f>
-        <v>17.804600000000001</v>
+        <v>17.882899999999999</v>
       </c>
       <c r="I65" s="6">
         <f t="array" aca="1" ref="I65" ca="1">_FV(B65,"Beta")</f>
@@ -15657,7 +14968,7 @@
       </c>
       <c r="P65" s="7">
         <f t="array" aca="1" ref="P65" ca="1">_FV(B65,"Volume")</f>
-        <v>1041144</v>
+        <v>2260619</v>
       </c>
       <c r="Q65" s="7">
         <f t="array" aca="1" ref="Q65" ca="1">_FV(B65,"Volume average",TRUE)</f>
@@ -15677,7 +14988,7 @@
       </c>
       <c r="U65" s="7">
         <f t="array" aca="1" ref="U65" ca="1">_FV(B65,"Market cap",TRUE)</f>
-        <v>156148235975</v>
+        <v>156835194300</v>
       </c>
       <c r="V65" s="7">
         <f t="array" aca="1" ref="V65" ca="1">_FV(B65,"Shares outstanding",TRUE)</f>
@@ -15693,7 +15004,7 @@
       </c>
       <c r="C66" s="2" cm="1">
         <f t="array" aca="1" ref="C66" ca="1">_FV(B66,"Last trade time",TRUE)</f>
-        <v>46168.605593356253</v>
+        <v>46168.68355403906</v>
       </c>
       <c r="D66" t="str" cm="1">
         <f t="array" aca="1" ref="D66" ca="1">_FV(B66,"Currency")</f>
@@ -15701,19 +15012,19 @@
       </c>
       <c r="E66" s="3" cm="1">
         <f t="array" aca="1" ref="E66" ca="1">_FV(B66,"Price")</f>
-        <v>186.81</v>
+        <v>188.38509999999999</v>
       </c>
       <c r="F66" s="4" cm="1">
         <f t="array" aca="1" ref="F66" ca="1">_FV(B66,"Change (%)",TRUE)</f>
-        <v>-5.6950000000000004E-3</v>
+        <v>2.6879999999999999E-3</v>
       </c>
       <c r="G66" s="5" cm="1">
         <f t="array" aca="1" ref="G66" ca="1">_FV(B66,"Change")</f>
-        <v>-1.07</v>
+        <v>0.50509999999999999</v>
       </c>
       <c r="H66" s="6" cm="1">
         <f t="array" aca="1" ref="H66" ca="1">_FV(B66,"P/E",TRUE)</f>
-        <v>290.39330000000001</v>
+        <v>292.84179999999998</v>
       </c>
       <c r="I66" s="6" cm="1">
         <f t="array" aca="1" ref="I66" ca="1">_FV(B66,"Beta")</f>
@@ -15729,7 +15040,7 @@
       </c>
       <c r="L66" s="3" cm="1">
         <f t="array" aca="1" ref="L66" ca="1">_FV(B66,"High")</f>
-        <v>188.34</v>
+        <v>188.86</v>
       </c>
       <c r="M66" s="3" cm="1">
         <f t="array" aca="1" ref="M66" ca="1">_FV(B66,"Low")</f>
@@ -15745,7 +15056,7 @@
       </c>
       <c r="P66" s="7" cm="1">
         <f t="array" aca="1" ref="P66" ca="1">_FV(B66,"Volume")</f>
-        <v>463657</v>
+        <v>661107</v>
       </c>
       <c r="Q66" s="7" cm="1">
         <f t="array" aca="1" ref="Q66" ca="1">_FV(B66,"Volume average",TRUE)</f>
@@ -15765,7 +15076,7 @@
       </c>
       <c r="U66" s="7" cm="1">
         <f t="array" aca="1" ref="U66" ca="1">_FV(B66,"Market cap",TRUE)</f>
-        <v>28352882259</v>
+        <v>28591941328</v>
       </c>
       <c r="V66" s="7" cm="1">
         <f t="array" aca="1" ref="V66" ca="1">_FV(B66,"Shares outstanding",TRUE)</f>
@@ -15781,7 +15092,7 @@
       </c>
       <c r="C67" s="2">
         <f t="array" aca="1" ref="C67" ca="1">_FV(B67,"Last trade time",TRUE)</f>
-        <v>46168.605605937497</v>
+        <v>46168.683557013283</v>
       </c>
       <c r="D67" t="str">
         <f t="array" aca="1" ref="D67" ca="1">_FV(B67,"Currency")</f>
@@ -15789,19 +15100,19 @@
       </c>
       <c r="E67" s="3">
         <f t="array" aca="1" ref="E67" ca="1">_FV(B67,"Price")</f>
-        <v>101.78</v>
+        <v>102.73</v>
       </c>
       <c r="F67" s="4">
         <f t="array" aca="1" ref="F67" ca="1">_FV(B67,"Change (%)",TRUE)</f>
-        <v>-5.7630000000000008E-3</v>
+        <v>3.5170000000000002E-3</v>
       </c>
       <c r="G67" s="5">
         <f t="array" aca="1" ref="G67" ca="1">_FV(B67,"Change")</f>
-        <v>-0.59</v>
+        <v>0.36</v>
       </c>
       <c r="H67" s="6">
         <f t="array" aca="1" ref="H67" ca="1">_FV(B67,"P/E",TRUE)</f>
-        <v>18.276499999999999</v>
+        <v>18.447099999999999</v>
       </c>
       <c r="I67" s="6">
         <f t="array" aca="1" ref="I67" ca="1">_FV(B67,"Beta")</f>
@@ -15817,7 +15128,7 @@
       </c>
       <c r="L67" s="3">
         <f t="array" aca="1" ref="L67" ca="1">_FV(B67,"High")</f>
-        <v>102.5</v>
+        <v>102.82</v>
       </c>
       <c r="M67" s="3">
         <f t="array" aca="1" ref="M67" ca="1">_FV(B67,"Low")</f>
@@ -15833,7 +15144,7 @@
       </c>
       <c r="P67" s="7">
         <f t="array" aca="1" ref="P67" ca="1">_FV(B67,"Volume")</f>
-        <v>41616</v>
+        <v>124725</v>
       </c>
       <c r="Q67" s="7">
         <f t="array" aca="1" ref="Q67" ca="1">_FV(B67,"Volume average",TRUE)</f>
@@ -15853,7 +15164,7 @@
       </c>
       <c r="U67" s="7">
         <f t="array" aca="1" ref="U67" ca="1">_FV(B67,"Market cap",TRUE)</f>
-        <v>3584387277</v>
+        <v>3617843437</v>
       </c>
       <c r="V67" s="7">
         <f t="array" aca="1" ref="V67" ca="1">_FV(B67,"Shares outstanding",TRUE)</f>
@@ -15869,7 +15180,7 @@
       </c>
       <c r="C68" s="2">
         <f t="array" aca="1" ref="C68" ca="1">_FV(B68,"Last trade time",TRUE)</f>
-        <v>46168.605597152346</v>
+        <v>46168.683560983591</v>
       </c>
       <c r="D68" t="str">
         <f t="array" aca="1" ref="D68" ca="1">_FV(B68,"Currency")</f>
@@ -15877,19 +15188,19 @@
       </c>
       <c r="E68" s="3">
         <f t="array" aca="1" ref="E68" ca="1">_FV(B68,"Price")</f>
-        <v>241.98500000000001</v>
+        <v>242.61</v>
       </c>
       <c r="F68" s="4">
         <f t="array" aca="1" ref="F68" ca="1">_FV(B68,"Change (%)",TRUE)</f>
-        <v>-1.1337999999999999E-2</v>
+        <v>-8.7840000000000001E-3</v>
       </c>
       <c r="G68" s="5">
         <f t="array" aca="1" ref="G68" ca="1">_FV(B68,"Change")</f>
-        <v>-2.7749999999999999</v>
+        <v>-2.15</v>
       </c>
       <c r="H68" s="6">
         <f t="array" aca="1" ref="H68" ca="1">_FV(B68,"P/E",TRUE)</f>
-        <v>14.103899999999999</v>
+        <v>14.1403</v>
       </c>
       <c r="I68" s="6">
         <f t="array" aca="1" ref="I68" ca="1">_FV(B68,"Beta")</f>
@@ -15921,7 +15232,7 @@
       </c>
       <c r="P68" s="7">
         <f t="array" aca="1" ref="P68" ca="1">_FV(B68,"Volume")</f>
-        <v>900682</v>
+        <v>1425821</v>
       </c>
       <c r="Q68" s="7">
         <f t="array" aca="1" ref="Q68" ca="1">_FV(B68,"Volume average",TRUE)</f>
@@ -15941,7 +15252,7 @@
       </c>
       <c r="U68" s="7">
         <f t="array" aca="1" ref="U68" ca="1">_FV(B68,"Market cap",TRUE)</f>
-        <v>97810337000</v>
+        <v>98062962000</v>
       </c>
       <c r="V68" s="7">
         <f t="array" aca="1" ref="V68" ca="1">_FV(B68,"Shares outstanding",TRUE)</f>
@@ -15957,7 +15268,7 @@
       </c>
       <c r="C69" s="2" cm="1">
         <f t="array" aca="1" ref="C69" ca="1">_FV(B69,"Last trade time",TRUE)</f>
-        <v>46168.605605578123</v>
+        <v>46168.683546642969</v>
       </c>
       <c r="D69" t="str" cm="1">
         <f t="array" aca="1" ref="D69" ca="1">_FV(B69,"Currency")</f>
@@ -15965,19 +15276,19 @@
       </c>
       <c r="E69" s="3" cm="1">
         <f t="array" aca="1" ref="E69" ca="1">_FV(B69,"Price")</f>
-        <v>40.700000000000003</v>
+        <v>41.06</v>
       </c>
       <c r="F69" s="4" cm="1">
         <f t="array" aca="1" ref="F69" ca="1">_FV(B69,"Change (%)",TRUE)</f>
-        <v>-1.2376E-2</v>
+        <v>-3.64E-3</v>
       </c>
       <c r="G69" s="5" cm="1">
         <f t="array" aca="1" ref="G69" ca="1">_FV(B69,"Change")</f>
-        <v>-0.51</v>
+        <v>-0.15</v>
       </c>
       <c r="H69" s="6" cm="1">
         <f t="array" aca="1" ref="H69" ca="1">_FV(B69,"P/E",TRUE)</f>
-        <v>75.961200000000005</v>
+        <v>76.633099999999999</v>
       </c>
       <c r="I69" s="6" cm="1">
         <f t="array" aca="1" ref="I69" ca="1">_FV(B69,"Beta")</f>
@@ -15993,7 +15304,7 @@
       </c>
       <c r="L69" s="3" cm="1">
         <f t="array" aca="1" ref="L69" ca="1">_FV(B69,"High")</f>
-        <v>40.984999999999999</v>
+        <v>41.064999999999998</v>
       </c>
       <c r="M69" s="3" cm="1">
         <f t="array" aca="1" ref="M69" ca="1">_FV(B69,"Low")</f>
@@ -16009,7 +15320,7 @@
       </c>
       <c r="P69" s="7" cm="1">
         <f t="array" aca="1" ref="P69" ca="1">_FV(B69,"Volume")</f>
-        <v>539643</v>
+        <v>1069700</v>
       </c>
       <c r="Q69" s="7" cm="1">
         <f t="array" aca="1" ref="Q69" ca="1">_FV(B69,"Volume average",TRUE)</f>
@@ -16029,7 +15340,7 @@
       </c>
       <c r="U69" s="7" cm="1">
         <f t="array" aca="1" ref="U69" ca="1">_FV(B69,"Market cap",TRUE)</f>
-        <v>11863060990</v>
+        <v>11967992242</v>
       </c>
       <c r="V69" s="7" cm="1">
         <f t="array" aca="1" ref="V69" ca="1">_FV(B69,"Shares outstanding",TRUE)</f>
@@ -16045,7 +15356,7 @@
       </c>
       <c r="C70" s="2" cm="1">
         <f t="array" aca="1" ref="C70" ca="1">_FV(B70,"Last trade time",TRUE)</f>
-        <v>46168.605609640625</v>
+        <v>46168.683558668752</v>
       </c>
       <c r="D70" t="str" cm="1">
         <f t="array" aca="1" ref="D70" ca="1">_FV(B70,"Currency")</f>
@@ -16053,19 +15364,19 @@
       </c>
       <c r="E70" s="3" cm="1">
         <f t="array" aca="1" ref="E70" ca="1">_FV(B70,"Price")</f>
-        <v>132.4999</v>
+        <v>134.72</v>
       </c>
       <c r="F70" s="4" cm="1">
         <f t="array" aca="1" ref="F70" ca="1">_FV(B70,"Change (%)",TRUE)</f>
-        <v>-1.0678E-2</v>
+        <v>5.8989999999999997E-3</v>
       </c>
       <c r="G70" s="5" cm="1">
         <f t="array" aca="1" ref="G70" ca="1">_FV(B70,"Change")</f>
-        <v>-1.4300999999999999</v>
+        <v>0.79</v>
       </c>
       <c r="H70" s="6" cm="1">
         <f t="array" aca="1" ref="H70" ca="1">_FV(B70,"P/E",TRUE)</f>
-        <v>51.189900000000002</v>
+        <v>52.047600000000003</v>
       </c>
       <c r="I70" s="6" cm="1">
         <f t="array" aca="1" ref="I70" ca="1">_FV(B70,"Beta")</f>
@@ -16073,7 +15384,7 @@
       </c>
       <c r="J70" s="3" cm="1">
         <f t="array" aca="1" ref="J70" ca="1">_FV(B70,"52 week high",TRUE)</f>
-        <v>134.19</v>
+        <v>134.80000000000001</v>
       </c>
       <c r="K70" s="3" cm="1">
         <f t="array" aca="1" ref="K70" ca="1">_FV(B70,"52 week low",TRUE)</f>
@@ -16081,7 +15392,7 @@
       </c>
       <c r="L70" s="3" cm="1">
         <f t="array" aca="1" ref="L70" ca="1">_FV(B70,"High")</f>
-        <v>133.59020000000001</v>
+        <v>134.80000000000001</v>
       </c>
       <c r="M70" s="3" cm="1">
         <f t="array" aca="1" ref="M70" ca="1">_FV(B70,"Low")</f>
@@ -16097,7 +15408,7 @@
       </c>
       <c r="P70" s="7" cm="1">
         <f t="array" aca="1" ref="P70" ca="1">_FV(B70,"Volume")</f>
-        <v>807410</v>
+        <v>1465635</v>
       </c>
       <c r="Q70" s="7" cm="1">
         <f t="array" aca="1" ref="Q70" ca="1">_FV(B70,"Volume average",TRUE)</f>
@@ -16117,7 +15428,7 @@
       </c>
       <c r="U70" s="7" cm="1">
         <f t="array" aca="1" ref="U70" ca="1">_FV(B70,"Market cap",TRUE)</f>
-        <v>97075839735</v>
+        <v>98702392448</v>
       </c>
       <c r="V70" s="7" cm="1">
         <f t="array" aca="1" ref="V70" ca="1">_FV(B70,"Shares outstanding",TRUE)</f>
@@ -16133,7 +15444,7 @@
       </c>
       <c r="C71" s="2">
         <f t="array" aca="1" ref="C71" ca="1">_FV(B71,"Last trade time",TRUE)</f>
-        <v>46168.605593957815</v>
+        <v>46168.683401770315</v>
       </c>
       <c r="D71" t="str">
         <f t="array" aca="1" ref="D71" ca="1">_FV(B71,"Currency")</f>
@@ -16141,19 +15452,19 @@
       </c>
       <c r="E71" s="3">
         <f t="array" aca="1" ref="E71" ca="1">_FV(B71,"Price")</f>
-        <v>36.71</v>
+        <v>37.195</v>
       </c>
       <c r="F71" s="4">
         <f t="array" aca="1" ref="F71" ca="1">_FV(B71,"Change (%)",TRUE)</f>
-        <v>-1.3436999999999999E-2</v>
+        <v>-4.0309999999999999E-4</v>
       </c>
       <c r="G71" s="5">
         <f t="array" aca="1" ref="G71" ca="1">_FV(B71,"Change")</f>
-        <v>-0.5</v>
+        <v>-1.4999999999999999E-2</v>
       </c>
       <c r="H71" s="6">
         <f t="array" aca="1" ref="H71" ca="1">_FV(B71,"P/E",TRUE)</f>
-        <v>15.735799999999999</v>
+        <v>15.9437</v>
       </c>
       <c r="I71" s="6">
         <f t="array" aca="1" ref="I71" ca="1">_FV(B71,"Beta")</f>
@@ -16185,7 +15496,7 @@
       </c>
       <c r="P71" s="7">
         <f t="array" aca="1" ref="P71" ca="1">_FV(B71,"Volume")</f>
-        <v>194305</v>
+        <v>344785</v>
       </c>
       <c r="Q71" s="7">
         <f t="array" aca="1" ref="Q71" ca="1">_FV(B71,"Volume average",TRUE)</f>
@@ -16205,7 +15516,7 @@
       </c>
       <c r="U71" s="7">
         <f t="array" aca="1" ref="U71" ca="1">_FV(B71,"Market cap",TRUE)</f>
-        <v>1806300866</v>
+        <v>1830165097</v>
       </c>
       <c r="V71" s="7">
         <f t="array" aca="1" ref="V71" ca="1">_FV(B71,"Shares outstanding",TRUE)</f>
@@ -16221,7 +15532,7 @@
       </c>
       <c r="C72" s="2">
         <f t="array" aca="1" ref="C72" ca="1">_FV(B72,"Last trade time",TRUE)</f>
-        <v>46168.60563905078</v>
+        <v>46168.683601087498</v>
       </c>
       <c r="D72" t="str">
         <f t="array" aca="1" ref="D72" ca="1">_FV(B72,"Currency")</f>
@@ -16229,19 +15540,19 @@
       </c>
       <c r="E72" s="3">
         <f t="array" aca="1" ref="E72" ca="1">_FV(B72,"Price")</f>
-        <v>80.495000000000005</v>
+        <v>80.469899999999996</v>
       </c>
       <c r="F72" s="4">
         <f t="array" aca="1" ref="F72" ca="1">_FV(B72,"Change (%)",TRUE)</f>
-        <v>-1.2089000000000001E-2</v>
+        <v>-1.2397E-2</v>
       </c>
       <c r="G72" s="5">
         <f t="array" aca="1" ref="G72" ca="1">_FV(B72,"Change")</f>
-        <v>-0.98499999999999999</v>
+        <v>-1.0101</v>
       </c>
       <c r="H72" s="6">
         <f t="array" aca="1" ref="H72" ca="1">_FV(B72,"P/E",TRUE)</f>
-        <v>25.340800000000002</v>
+        <v>25.332899999999999</v>
       </c>
       <c r="I72" s="6">
         <f t="array" aca="1" ref="I72" ca="1">_FV(B72,"Beta")</f>
@@ -16261,7 +15572,7 @@
       </c>
       <c r="M72" s="3">
         <f t="array" aca="1" ref="M72" ca="1">_FV(B72,"Low")</f>
-        <v>80.305000000000007</v>
+        <v>80.265000000000001</v>
       </c>
       <c r="N72" s="3">
         <f t="array" aca="1" ref="N72" ca="1">_FV(B72,"Open")</f>
@@ -16273,7 +15584,7 @@
       </c>
       <c r="P72" s="7">
         <f t="array" aca="1" ref="P72" ca="1">_FV(B72,"Volume")</f>
-        <v>2980022</v>
+        <v>5198183</v>
       </c>
       <c r="Q72" s="7">
         <f t="array" aca="1" ref="Q72" ca="1">_FV(B72,"Volume average",TRUE)</f>
@@ -16293,7 +15604,7 @@
       </c>
       <c r="U72" s="7">
         <f t="array" aca="1" ref="U72" ca="1">_FV(B72,"Market cap",TRUE)</f>
-        <v>346328288590</v>
+        <v>346220296291</v>
       </c>
       <c r="V72" s="7">
         <f t="array" aca="1" ref="V72" ca="1">_FV(B72,"Shares outstanding",TRUE)</f>
@@ -16309,7 +15620,7 @@
       </c>
       <c r="C73" s="2" cm="1">
         <f t="array" aca="1" ref="C73" ca="1">_FV(B73,"Last trade time",TRUE)</f>
-        <v>46168.605617164059</v>
+        <v>46168.68355366875</v>
       </c>
       <c r="D73" t="str" cm="1">
         <f t="array" aca="1" ref="D73" ca="1">_FV(B73,"Currency")</f>
@@ -16317,15 +15628,15 @@
       </c>
       <c r="E73" s="3" cm="1">
         <f t="array" aca="1" ref="E73" ca="1">_FV(B73,"Price")</f>
-        <v>53.34</v>
+        <v>53.81</v>
       </c>
       <c r="F73" s="4" cm="1">
         <f t="array" aca="1" ref="F73" ca="1">_FV(B73,"Change (%)",TRUE)</f>
-        <v>-1.2770999999999999E-2</v>
+        <v>-4.0720000000000001E-3</v>
       </c>
       <c r="G73" s="5" cm="1">
         <f t="array" aca="1" ref="G73" ca="1">_FV(B73,"Change")</f>
-        <v>-0.69</v>
+        <v>-0.22</v>
       </c>
       <c r="H73" s="6" cm="1">
         <f t="array" aca="1" ref="H73" ca="1">_FV(B73,"P/E",TRUE)</f>
@@ -16361,7 +15672,7 @@
       </c>
       <c r="P73" s="7" cm="1">
         <f t="array" aca="1" ref="P73" ca="1">_FV(B73,"Volume")</f>
-        <v>952793</v>
+        <v>1590479</v>
       </c>
       <c r="Q73" s="7" cm="1">
         <f t="array" aca="1" ref="Q73" ca="1">_FV(B73,"Volume average",TRUE)</f>
@@ -16381,7 +15692,7 @@
       </c>
       <c r="U73" s="7" cm="1">
         <f t="array" aca="1" ref="U73" ca="1">_FV(B73,"Market cap",TRUE)</f>
-        <v>32148380712</v>
+        <v>32431652908</v>
       </c>
       <c r="V73" s="7" cm="1">
         <f t="array" aca="1" ref="V73" ca="1">_FV(B73,"Shares outstanding",TRUE)</f>
@@ -16397,7 +15708,7 @@
       </c>
       <c r="C74" s="2" cm="1">
         <f t="array" aca="1" ref="C74" ca="1">_FV(B74,"Last trade time",TRUE)</f>
-        <v>46168.605627036719</v>
+        <v>46168.683576921096</v>
       </c>
       <c r="D74" t="str" cm="1">
         <f t="array" aca="1" ref="D74" ca="1">_FV(B74,"Currency")</f>
@@ -16405,19 +15716,19 @@
       </c>
       <c r="E74" s="3" cm="1">
         <f t="array" aca="1" ref="E74" ca="1">_FV(B74,"Price")</f>
-        <v>125.2</v>
+        <v>125.26</v>
       </c>
       <c r="F74" s="4" cm="1">
         <f t="array" aca="1" ref="F74" ca="1">_FV(B74,"Change (%)",TRUE)</f>
-        <v>-2.2943999999999999E-2</v>
+        <v>-2.2475000000000002E-2</v>
       </c>
       <c r="G74" s="5" cm="1">
         <f t="array" aca="1" ref="G74" ca="1">_FV(B74,"Change")</f>
-        <v>-2.94</v>
+        <v>-2.88</v>
       </c>
       <c r="H74" s="6" cm="1">
         <f t="array" aca="1" ref="H74" ca="1">_FV(B74,"P/E",TRUE)</f>
-        <v>39.082299999999996</v>
+        <v>39.100999999999999</v>
       </c>
       <c r="I74" s="6" cm="1">
         <f t="array" aca="1" ref="I74" ca="1">_FV(B74,"Beta")</f>
@@ -16449,7 +15760,7 @@
       </c>
       <c r="P74" s="7" cm="1">
         <f t="array" aca="1" ref="P74" ca="1">_FV(B74,"Volume")</f>
-        <v>1157261</v>
+        <v>1963570</v>
       </c>
       <c r="Q74" s="7" cm="1">
         <f t="array" aca="1" ref="Q74" ca="1">_FV(B74,"Volume average",TRUE)</f>
@@ -16469,7 +15780,7 @@
       </c>
       <c r="U74" s="7" cm="1">
         <f t="array" aca="1" ref="U74" ca="1">_FV(B74,"Market cap",TRUE)</f>
-        <v>30924400000</v>
+        <v>30939220000</v>
       </c>
       <c r="V74" s="7" cm="1">
         <f t="array" aca="1" ref="V74" ca="1">_FV(B74,"Shares outstanding",TRUE)</f>
@@ -16485,7 +15796,7 @@
       </c>
       <c r="C75" s="2" cm="1">
         <f t="array" aca="1" ref="C75" ca="1">_FV(B75,"Last trade time",TRUE)</f>
-        <v>46168.605586226564</v>
+        <v>46168.683557453121</v>
       </c>
       <c r="D75" t="str" cm="1">
         <f t="array" aca="1" ref="D75" ca="1">_FV(B75,"Currency")</f>
@@ -16493,15 +15804,15 @@
       </c>
       <c r="E75" s="3" cm="1">
         <f t="array" aca="1" ref="E75" ca="1">_FV(B75,"Price")</f>
-        <v>18.37</v>
+        <v>18.589300000000001</v>
       </c>
       <c r="F75" s="4" cm="1">
         <f t="array" aca="1" ref="F75" ca="1">_FV(B75,"Change (%)",TRUE)</f>
-        <v>-1.8172000000000001E-2</v>
+        <v>-6.4510000000000001E-3</v>
       </c>
       <c r="G75" s="5" cm="1">
         <f t="array" aca="1" ref="G75" ca="1">_FV(B75,"Change")</f>
-        <v>-0.34</v>
+        <v>-0.1207</v>
       </c>
       <c r="H75" s="6" t="e" cm="1" vm="12">
         <f t="array" ref="H75">_FV(B75,"P/E",TRUE)</f>
@@ -16537,7 +15848,7 @@
       </c>
       <c r="P75" s="7" cm="1">
         <f t="array" aca="1" ref="P75" ca="1">_FV(B75,"Volume")</f>
-        <v>2210641</v>
+        <v>4328478</v>
       </c>
       <c r="Q75" s="7" cm="1">
         <f t="array" aca="1" ref="Q75" ca="1">_FV(B75,"Volume average",TRUE)</f>
@@ -16557,7 +15868,7 @@
       </c>
       <c r="U75" s="7" cm="1">
         <f t="array" aca="1" ref="U75" ca="1">_FV(B75,"Market cap",TRUE)</f>
-        <v>6273026177</v>
+        <v>6347913201</v>
       </c>
       <c r="V75" s="7" cm="1">
         <f t="array" aca="1" ref="V75" ca="1">_FV(B75,"Shares outstanding",TRUE)</f>
@@ -16573,7 +15884,7 @@
       </c>
       <c r="C76" s="2" cm="1">
         <f t="array" aca="1" ref="C76" ca="1">_FV(B76,"Last trade time",TRUE)</f>
-        <v>46168.60562790469</v>
+        <v>46168.683570578127</v>
       </c>
       <c r="D76" t="str" cm="1">
         <f t="array" aca="1" ref="D76" ca="1">_FV(B76,"Currency")</f>
@@ -16581,19 +15892,19 @@
       </c>
       <c r="E76" s="3" cm="1">
         <f t="array" aca="1" ref="E76" ca="1">_FV(B76,"Price")</f>
-        <v>117.68</v>
+        <v>117.84</v>
       </c>
       <c r="F76" s="4" cm="1">
         <f t="array" aca="1" ref="F76" ca="1">_FV(B76,"Change (%)",TRUE)</f>
-        <v>-2.2673000000000002E-2</v>
+        <v>-2.1343999999999998E-2</v>
       </c>
       <c r="G76" s="5" cm="1">
         <f t="array" aca="1" ref="G76" ca="1">_FV(B76,"Change")</f>
-        <v>-2.73</v>
+        <v>-2.57</v>
       </c>
       <c r="H76" s="6" cm="1">
         <f t="array" aca="1" ref="H76" ca="1">_FV(B76,"P/E",TRUE)</f>
-        <v>39.2136</v>
+        <v>39.2669</v>
       </c>
       <c r="I76" s="6" cm="1">
         <f t="array" aca="1" ref="I76" ca="1">_FV(B76,"Beta")</f>
@@ -16625,7 +15936,7 @@
       </c>
       <c r="P76" s="7" cm="1">
         <f t="array" aca="1" ref="P76" ca="1">_FV(B76,"Volume")</f>
-        <v>6543783</v>
+        <v>11350161</v>
       </c>
       <c r="Q76" s="7" cm="1">
         <f t="array" aca="1" ref="Q76" ca="1">_FV(B76,"Volume average",TRUE)</f>
@@ -16645,7 +15956,7 @@
       </c>
       <c r="U76" s="7" cm="1">
         <f t="array" aca="1" ref="U76" ca="1">_FV(B76,"Market cap",TRUE)</f>
-        <v>463828070800</v>
+        <v>464458700400</v>
       </c>
       <c r="V76" s="7" cm="1">
         <f t="array" aca="1" ref="V76" ca="1">_FV(B76,"Shares outstanding",TRUE)</f>
@@ -16661,7 +15972,7 @@
       </c>
       <c r="C77" s="2" cm="1">
         <f t="array" aca="1" ref="C77" ca="1">_FV(B77,"Last trade time",TRUE)</f>
-        <v>46168.605639247653</v>
+        <v>46168.683593564063</v>
       </c>
       <c r="D77" t="str" cm="1">
         <f t="array" aca="1" ref="D77" ca="1">_FV(B77,"Currency")</f>
@@ -16669,19 +15980,19 @@
       </c>
       <c r="E77" s="3" cm="1">
         <f t="array" aca="1" ref="E77" ca="1">_FV(B77,"Price")</f>
-        <v>253.64</v>
+        <v>258.77</v>
       </c>
       <c r="F77" s="4" cm="1">
         <f t="array" aca="1" ref="F77" ca="1">_FV(B77,"Change (%)",TRUE)</f>
-        <v>-2.6633E-2</v>
+        <v>-6.9459999999999999E-3</v>
       </c>
       <c r="G77" s="5" cm="1">
         <f t="array" aca="1" ref="G77" ca="1">_FV(B77,"Change")</f>
-        <v>-6.94</v>
+        <v>-1.81</v>
       </c>
       <c r="H77" s="6" cm="1">
         <f t="array" aca="1" ref="H77" ca="1">_FV(B77,"P/E",TRUE)</f>
-        <v>140.44300000000001</v>
+        <v>143.2835</v>
       </c>
       <c r="I77" s="6" cm="1">
         <f t="array" aca="1" ref="I77" ca="1">_FV(B77,"Beta")</f>
@@ -16713,7 +16024,7 @@
       </c>
       <c r="P77" s="7" cm="1">
         <f t="array" aca="1" ref="P77" ca="1">_FV(B77,"Volume")</f>
-        <v>1873687</v>
+        <v>3364248</v>
       </c>
       <c r="Q77" s="7" cm="1">
         <f t="array" aca="1" ref="Q77" ca="1">_FV(B77,"Volume average",TRUE)</f>
@@ -16733,7 +16044,7 @@
       </c>
       <c r="U77" s="7" cm="1">
         <f t="array" aca="1" ref="U77" ca="1">_FV(B77,"Market cap",TRUE)</f>
-        <v>205702040000</v>
+        <v>209862470000</v>
       </c>
       <c r="V77" s="7" cm="1">
         <f t="array" aca="1" ref="V77" ca="1">_FV(B77,"Shares outstanding",TRUE)</f>
@@ -16749,7 +16060,7 @@
       </c>
       <c r="C78" s="2">
         <f t="array" aca="1" ref="C78" ca="1">_FV(B78,"Last trade time",TRUE)</f>
-        <v>46168.605640068752</v>
+        <v>46168.683590346875</v>
       </c>
       <c r="D78" t="str">
         <f t="array" aca="1" ref="D78" ca="1">_FV(B78,"Currency")</f>
@@ -16757,19 +16068,19 @@
       </c>
       <c r="E78" s="3">
         <f t="array" aca="1" ref="E78" ca="1">_FV(B78,"Price")</f>
-        <v>246.54</v>
+        <v>250.82499999999999</v>
       </c>
       <c r="F78" s="4">
         <f t="array" aca="1" ref="F78" ca="1">_FV(B78,"Change (%)",TRUE)</f>
-        <v>-2.8757999999999999E-2</v>
+        <v>-1.1878E-2</v>
       </c>
       <c r="G78" s="5">
         <f t="array" aca="1" ref="G78" ca="1">_FV(B78,"Change")</f>
-        <v>-7.3</v>
+        <v>-3.0150000000000001</v>
       </c>
       <c r="H78" s="6">
         <f t="array" aca="1" ref="H78" ca="1">_FV(B78,"P/E",TRUE)</f>
-        <v>19.729500000000002</v>
+        <v>20.072399999999998</v>
       </c>
       <c r="I78" s="6">
         <f t="array" aca="1" ref="I78" ca="1">_FV(B78,"Beta")</f>
@@ -16801,7 +16112,7 @@
       </c>
       <c r="P78" s="7">
         <f t="array" aca="1" ref="P78" ca="1">_FV(B78,"Volume")</f>
-        <v>3399060</v>
+        <v>4990868</v>
       </c>
       <c r="Q78" s="7">
         <f t="array" aca="1" ref="Q78" ca="1">_FV(B78,"Volume average",TRUE)</f>
@@ -16821,7 +16132,7 @@
       </c>
       <c r="U78" s="7">
         <f t="array" aca="1" ref="U78" ca="1">_FV(B78,"Market cap",TRUE)</f>
-        <v>231719321862</v>
+        <v>235746730372</v>
       </c>
       <c r="V78" s="7">
         <f t="array" aca="1" ref="V78" ca="1">_FV(B78,"Shares outstanding",TRUE)</f>
@@ -16837,7 +16148,7 @@
       </c>
       <c r="C79" s="2">
         <f t="array" aca="1" ref="C79" ca="1">_FV(B79,"Last trade time",TRUE)</f>
-        <v>46168.605618344533</v>
+        <v>46168.683612071094</v>
       </c>
       <c r="D79" t="str">
         <f t="array" aca="1" ref="D79" ca="1">_FV(B79,"Currency")</f>
@@ -16845,19 +16156,19 @@
       </c>
       <c r="E79" s="3">
         <f t="array" aca="1" ref="E79" ca="1">_FV(B79,"Price")</f>
-        <v>61.53</v>
+        <v>63.8</v>
       </c>
       <c r="F79" s="4">
         <f t="array" aca="1" ref="F79" ca="1">_FV(B79,"Change (%)",TRUE)</f>
-        <v>-3.3155000000000004E-2</v>
+        <v>2.5140000000000002E-3</v>
       </c>
       <c r="G79" s="5">
         <f t="array" aca="1" ref="G79" ca="1">_FV(B79,"Change")</f>
-        <v>-2.11</v>
+        <v>0.16</v>
       </c>
       <c r="H79" s="6">
         <f t="array" aca="1" ref="H79" ca="1">_FV(B79,"P/E",TRUE)</f>
-        <v>1050</v>
+        <v>1088.7372</v>
       </c>
       <c r="I79" s="6">
         <f t="array" aca="1" ref="I79" ca="1">_FV(B79,"Beta")</f>
@@ -16889,7 +16200,7 @@
       </c>
       <c r="P79" s="7">
         <f t="array" aca="1" ref="P79" ca="1">_FV(B79,"Volume")</f>
-        <v>12466432</v>
+        <v>19113186</v>
       </c>
       <c r="Q79" s="7">
         <f t="array" aca="1" ref="Q79" ca="1">_FV(B79,"Volume average",TRUE)</f>
@@ -16909,7 +16220,7 @@
       </c>
       <c r="U79" s="7">
         <f t="array" aca="1" ref="U79" ca="1">_FV(B79,"Market cap",TRUE)</f>
-        <v>22967303100</v>
+        <v>23814626000</v>
       </c>
       <c r="V79" s="7">
         <f t="array" aca="1" ref="V79" ca="1">_FV(B79,"Shares outstanding",TRUE)</f>
@@ -16925,7 +16236,7 @@
       </c>
       <c r="C80" s="2" cm="1">
         <f t="array" aca="1" ref="C80" ca="1">_FV(B80,"Last trade time",TRUE)</f>
-        <v>46168.605586863283</v>
+        <v>46168.683578378907</v>
       </c>
       <c r="D80" t="str" cm="1">
         <f t="array" aca="1" ref="D80" ca="1">_FV(B80,"Currency")</f>
@@ -16933,15 +16244,15 @@
       </c>
       <c r="E80" s="3" cm="1">
         <f t="array" aca="1" ref="E80" ca="1">_FV(B80,"Price")</f>
-        <v>309.5</v>
+        <v>308.48</v>
       </c>
       <c r="F80" s="4" cm="1">
         <f t="array" aca="1" ref="F80" ca="1">_FV(B80,"Change (%)",TRUE)</f>
-        <v>-5.0991999999999996E-2</v>
+        <v>-5.4120000000000001E-2</v>
       </c>
       <c r="G80" s="5" cm="1">
         <f t="array" aca="1" ref="G80" ca="1">_FV(B80,"Change")</f>
-        <v>-16.63</v>
+        <v>-17.649999999999999</v>
       </c>
       <c r="H80" s="6" cm="1">
         <f t="array" aca="1" ref="H80" ca="1">_FV(B80,"P/E",TRUE)</f>
@@ -16965,7 +16276,7 @@
       </c>
       <c r="M80" s="3" cm="1">
         <f t="array" aca="1" ref="M80" ca="1">_FV(B80,"Low")</f>
-        <v>307.81</v>
+        <v>306.50229999999999</v>
       </c>
       <c r="N80" s="3" cm="1">
         <f t="array" aca="1" ref="N80" ca="1">_FV(B80,"Open")</f>
@@ -16977,7 +16288,7 @@
       </c>
       <c r="P80" s="7" cm="1">
         <f t="array" aca="1" ref="P80" ca="1">_FV(B80,"Volume")</f>
-        <v>814118</v>
+        <v>1408140</v>
       </c>
       <c r="Q80" s="7" cm="1">
         <f t="array" aca="1" ref="Q80" ca="1">_FV(B80,"Volume average",TRUE)</f>
@@ -16997,7 +16308,7 @@
       </c>
       <c r="U80" s="7" cm="1">
         <f t="array" aca="1" ref="U80" ca="1">_FV(B80,"Market cap",TRUE)</f>
-        <v>24914728335</v>
+        <v>24832618406</v>
       </c>
       <c r="V80" s="7" cm="1">
         <f t="array" aca="1" ref="V80" ca="1">_FV(B80,"Shares outstanding",TRUE)</f>
@@ -17013,7 +16324,7 @@
       </c>
       <c r="C81" s="2">
         <f t="array" aca="1" ref="C81" ca="1">_FV(B81,"Last trade time",TRUE)</f>
-        <v>46168.60554841406</v>
+        <v>46168.683469039061</v>
       </c>
       <c r="D81" t="str">
         <f t="array" aca="1" ref="D81" ca="1">_FV(B81,"Currency")</f>
@@ -17021,15 +16332,15 @@
       </c>
       <c r="E81" s="3">
         <f t="array" aca="1" ref="E81" ca="1">_FV(B81,"Price")</f>
-        <v>12.180899999999999</v>
+        <v>11.9499</v>
       </c>
       <c r="F81" s="4">
         <f t="array" aca="1" ref="F81" ca="1">_FV(B81,"Change (%)",TRUE)</f>
-        <v>-5.2069999999999998E-2</v>
+        <v>-7.0046999999999998E-2</v>
       </c>
       <c r="G81" s="5">
         <f t="array" aca="1" ref="G81" ca="1">_FV(B81,"Change")</f>
-        <v>-0.66910000000000003</v>
+        <v>-0.90010000000000001</v>
       </c>
       <c r="H81" s="6">
         <f t="array" aca="1" ref="H81" ca="1">_FV(B81,"P/E",TRUE)</f>
@@ -17053,7 +16364,7 @@
       </c>
       <c r="M81" s="3">
         <f t="array" aca="1" ref="M81" ca="1">_FV(B81,"Low")</f>
-        <v>11.81</v>
+        <v>11.69</v>
       </c>
       <c r="N81" s="3">
         <f t="array" aca="1" ref="N81" ca="1">_FV(B81,"Open")</f>
@@ -17065,7 +16376,7 @@
       </c>
       <c r="P81" s="7">
         <f t="array" aca="1" ref="P81" ca="1">_FV(B81,"Volume")</f>
-        <v>2747657</v>
+        <v>4617481</v>
       </c>
       <c r="Q81" s="7">
         <f t="array" aca="1" ref="Q81" ca="1">_FV(B81,"Volume average",TRUE)</f>
@@ -17085,7 +16396,7 @@
       </c>
       <c r="U81" s="7">
         <f t="array" aca="1" ref="U81" ca="1">_FV(B81,"Market cap",TRUE)</f>
-        <v>1876828199</v>
+        <v>1841235812</v>
       </c>
       <c r="V81" s="7">
         <f t="array" aca="1" ref="V81" ca="1">_FV(B81,"Shares outstanding",TRUE)</f>
@@ -17101,7 +16412,7 @@
       </c>
       <c r="C82" s="2">
         <f t="array" aca="1" ref="C82" ca="1">_FV(B82,"Last trade time",TRUE)</f>
-        <v>46168.605639710157</v>
+        <v>46168.683615948437</v>
       </c>
       <c r="D82" t="str">
         <f t="array" aca="1" ref="D82" ca="1">_FV(B82,"Currency")</f>
@@ -17109,15 +16420,15 @@
       </c>
       <c r="E82" s="3">
         <f t="array" aca="1" ref="E82" ca="1">_FV(B82,"Price")</f>
-        <v>13.505000000000001</v>
+        <v>13.21</v>
       </c>
       <c r="F82" s="4">
         <f t="array" aca="1" ref="F82" ca="1">_FV(B82,"Change (%)",TRUE)</f>
-        <v>-7.4366000000000002E-2</v>
+        <v>-9.4585000000000002E-2</v>
       </c>
       <c r="G82" s="5">
         <f t="array" aca="1" ref="G82" ca="1">_FV(B82,"Change")</f>
-        <v>-1.085</v>
+        <v>-1.38</v>
       </c>
       <c r="H82" s="6">
         <f t="array" aca="1" ref="H82" ca="1">_FV(B82,"P/E",TRUE)</f>
@@ -17153,7 +16464,7 @@
       </c>
       <c r="P82" s="7">
         <f t="array" aca="1" ref="P82" ca="1">_FV(B82,"Volume")</f>
-        <v>21230342</v>
+        <v>30461204</v>
       </c>
       <c r="Q82" s="7">
         <f t="array" aca="1" ref="Q82" ca="1">_FV(B82,"Volume average",TRUE)</f>
@@ -17173,7 +16484,7 @@
       </c>
       <c r="U82" s="7">
         <f t="array" aca="1" ref="U82" ca="1">_FV(B82,"Market cap",TRUE)</f>
-        <v>2330900877</v>
+        <v>2279985234</v>
       </c>
       <c r="V82" s="7">
         <f t="array" aca="1" ref="V82" ca="1">_FV(B82,"Shares outstanding",TRUE)</f>
@@ -17192,22 +16503,22 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{989027A5-E4FB-4AA7-BEAE-7B9653141BA1}">
   <dimension ref="A1:M11"/>
-  <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="15.4"/>
+  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="15.4"/>
   <cols>
-    <col min="1" max="1" width="9.875" style="16" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="45.875" style="16" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.4375" style="16" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.86328125" style="16" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="45.86328125" style="16" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.46484375" style="16" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12" style="16" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.4375" style="16" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.4375" style="16" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.3125" style="16" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.5625" style="16" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.46484375" style="16" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.46484375" style="16" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.33203125" style="16" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.53125" style="16" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="10" style="16" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.6875" style="16" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.125" style="16" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.125" style="16" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.3125" style="16" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.125" style="16"/>
+    <col min="10" max="10" width="7.6640625" style="16" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.1328125" style="16" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.1328125" style="16" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.33203125" style="16" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.1328125" style="16"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
@@ -17255,8 +16566,7 @@
       <c r="A2" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="B2" s="17" t="e" vm="87">
-        <f>IFERROR(_xlfn.XLOOKUP(A2,[1]!tblWatchlist[Symbol],[1]!tblWatchlist[StockName]),"")</f>
+      <c r="B2" s="17" t="e" vm="54">
         <v>#VALUE!</v>
       </c>
       <c r="C2" s="18" t="str">
@@ -17281,31 +16591,30 @@
       </c>
       <c r="I2" s="21">
         <f t="shared" ref="I2:I11" ca="1" si="2">_FV(B2,"Price")</f>
-        <v>301.21499999999997</v>
+        <v>310.04000000000002</v>
       </c>
       <c r="J2" s="22">
         <f ca="1">Config!$C$1</f>
-        <v>0.74280000000000002</v>
+        <v>0.74360000000000004</v>
       </c>
       <c r="K2" s="20">
         <f t="shared" ref="K2:K11" ca="1" si="3">F2*I2*J2</f>
-        <v>2013.6825180000001</v>
+        <v>2074.9116960000001</v>
       </c>
       <c r="L2" s="20">
         <f t="shared" ref="L2:L11" ca="1" si="4">K2-H2</f>
-        <v>1708.5262680000001</v>
+        <v>1769.7554460000001</v>
       </c>
       <c r="M2" s="23">
         <f t="shared" ref="M2:M11" ca="1" si="5">IF(H2=0,"",L2/H2)</f>
-        <v>5.5988572018433178</v>
+        <v>5.7995058138248856</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="B3" s="17" t="e" vm="88">
-        <f>IFERROR(_xlfn.XLOOKUP(A3,[1]!tblWatchlist[Symbol],[1]!tblWatchlist[StockName]),"")</f>
+      <c r="B3" s="17" t="e" vm="66">
         <v>#VALUE!</v>
       </c>
       <c r="C3" s="18" t="str">
@@ -17330,31 +16639,30 @@
       </c>
       <c r="I3" s="21">
         <f t="shared" ca="1" si="2"/>
-        <v>604.61369999999999</v>
+        <v>609.70000000000005</v>
       </c>
       <c r="J3" s="22">
         <f ca="1">Config!$C$1</f>
-        <v>0.74280000000000002</v>
+        <v>0.74360000000000004</v>
       </c>
       <c r="K3" s="20">
         <f t="shared" ca="1" si="3"/>
-        <v>2694.6423381600002</v>
+        <v>2720.2375200000001</v>
       </c>
       <c r="L3" s="20">
         <f t="shared" ca="1" si="4"/>
-        <v>-473.21766384000011</v>
+        <v>-447.62248200000022</v>
       </c>
       <c r="M3" s="23">
         <f t="shared" ca="1" si="5"/>
-        <v>-0.14938086390851815</v>
+        <v>-0.14130121966166362</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="B4" s="17" t="e" vm="89">
-        <f>IFERROR(_xlfn.XLOOKUP(A4,[1]!tblWatchlist[Symbol],[1]!tblWatchlist[StockName]),"")</f>
+      <c r="B4" s="17" t="e" vm="50">
         <v>#VALUE!</v>
       </c>
       <c r="C4" s="18" t="str">
@@ -17379,31 +16687,30 @@
       </c>
       <c r="I4" s="21">
         <f t="shared" ca="1" si="2"/>
-        <v>76.185000000000002</v>
+        <v>74.27</v>
       </c>
       <c r="J4" s="22">
         <f ca="1">Config!$C$1</f>
-        <v>0.74280000000000002</v>
+        <v>0.74360000000000004</v>
       </c>
       <c r="K4" s="20">
         <f t="shared" ca="1" si="3"/>
-        <v>4244.2663499999999</v>
+        <v>4142.0379000000003</v>
       </c>
       <c r="L4" s="20">
         <f t="shared" ca="1" si="4"/>
-        <v>596.46705000000065</v>
+        <v>494.23860000000104</v>
       </c>
       <c r="M4" s="23">
         <f t="shared" ca="1" si="5"/>
-        <v>0.16351421801084309</v>
+        <v>0.13548952652082616</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="17" t="s">
         <v>200</v>
       </c>
-      <c r="B5" s="17" t="e" vm="90">
-        <f>IFERROR(_xlfn.XLOOKUP(A5,[1]!tblWatchlist[Symbol],[1]!tblWatchlist[StockName]),"")</f>
+      <c r="B5" s="17" t="e" vm="56">
         <v>#VALUE!</v>
       </c>
       <c r="C5" s="18" t="str">
@@ -17428,31 +16735,30 @@
       </c>
       <c r="I5" s="21">
         <f t="shared" ca="1" si="2"/>
-        <v>224.66</v>
+        <v>212.55</v>
       </c>
       <c r="J5" s="22">
         <f ca="1">Config!$C$1</f>
-        <v>0.74280000000000002</v>
+        <v>0.74360000000000004</v>
       </c>
       <c r="K5" s="20">
         <f t="shared" ca="1" si="3"/>
-        <v>3003.7940640000002</v>
+        <v>2844.9392400000002</v>
       </c>
       <c r="L5" s="20">
         <f t="shared" ca="1" si="4"/>
-        <v>671.35406400000011</v>
+        <v>512.4992400000001</v>
       </c>
       <c r="M5" s="23">
         <f t="shared" ca="1" si="5"/>
-        <v>0.2878333693471215</v>
+        <v>0.21972665534804758</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="B6" s="17" t="e" vm="91">
-        <f>IFERROR(_xlfn.XLOOKUP(A6,[1]!tblWatchlist[Symbol],[1]!tblWatchlist[StockName]),"")</f>
+      <c r="B6" s="17" t="e" vm="17">
         <v>#VALUE!</v>
       </c>
       <c r="C6" s="18" t="str">
@@ -17477,31 +16783,30 @@
       </c>
       <c r="I6" s="21">
         <f t="shared" ca="1" si="2"/>
-        <v>446.1</v>
+        <v>494.65989999999999</v>
       </c>
       <c r="J6" s="22">
         <f ca="1">Config!$C$1</f>
-        <v>0.74280000000000002</v>
+        <v>0.74360000000000004</v>
       </c>
       <c r="K6" s="20">
         <f t="shared" ca="1" si="3"/>
-        <v>3976.3569600000005</v>
+        <v>4413.9492196800002</v>
       </c>
       <c r="L6" s="20">
         <f t="shared" ca="1" si="4"/>
-        <v>2116.8369600000005</v>
+        <v>2554.4292196800002</v>
       </c>
       <c r="M6" s="23">
         <f t="shared" ca="1" si="5"/>
-        <v>1.1383781621063502</v>
+        <v>1.373703546979866</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="B7" s="17" t="e" vm="92">
-        <f>IFERROR(_xlfn.XLOOKUP(A7,[1]!tblWatchlist[Symbol],[1]!tblWatchlist[StockName]),"")</f>
+      <c r="B7" s="17" t="e" vm="45">
         <v>#VALUE!</v>
       </c>
       <c r="C7" s="18" t="str">
@@ -17526,31 +16831,30 @@
       </c>
       <c r="I7" s="21">
         <f t="shared" ca="1" si="2"/>
-        <v>102.1901</v>
+        <v>106.99</v>
       </c>
       <c r="J7" s="22">
         <f ca="1">Config!$C$1</f>
-        <v>0.74280000000000002</v>
+        <v>0.74360000000000004</v>
       </c>
       <c r="K7" s="20">
         <f t="shared" ca="1" si="3"/>
-        <v>2353.1109946800002</v>
+        <v>2466.2906840000001</v>
       </c>
       <c r="L7" s="20">
         <f t="shared" ca="1" si="4"/>
-        <v>279.02099567999994</v>
+        <v>392.20068499999979</v>
       </c>
       <c r="M7" s="23">
         <f t="shared" ca="1" si="5"/>
-        <v>0.13452694715008839</v>
+        <v>0.18909530694863533</v>
       </c>
     </row>
     <row r="8" spans="1:13">
       <c r="A8" s="17" t="s">
         <v>64</v>
       </c>
-      <c r="B8" s="17" t="e" vm="93">
-        <f>IFERROR(_xlfn.XLOOKUP(A8,[1]!tblWatchlist[Symbol],[1]!tblWatchlist[StockName]),"")</f>
+      <c r="B8" s="17" t="e" vm="63">
         <v>#VALUE!</v>
       </c>
       <c r="C8" s="18" t="str">
@@ -17575,31 +16879,30 @@
       </c>
       <c r="I8" s="21">
         <f t="shared" ca="1" si="2"/>
-        <v>412.56</v>
+        <v>428.6773</v>
       </c>
       <c r="J8" s="22">
         <f ca="1">Config!$C$1</f>
-        <v>0.74280000000000002</v>
+        <v>0.74360000000000004</v>
       </c>
       <c r="K8" s="20">
         <f t="shared" ca="1" si="3"/>
-        <v>5516.092224</v>
+        <v>5737.7599250399999</v>
       </c>
       <c r="L8" s="20">
         <f t="shared" ca="1" si="4"/>
-        <v>661.82232400000066</v>
+        <v>883.49002504000055</v>
       </c>
       <c r="M8" s="23">
         <f t="shared" ca="1" si="5"/>
-        <v>0.1363381801246776</v>
+        <v>0.18200265812166741</v>
       </c>
     </row>
     <row r="9" spans="1:13">
       <c r="A9" s="17" t="s">
         <v>76</v>
       </c>
-      <c r="B9" s="17" t="e" vm="94">
-        <f>IFERROR(_xlfn.XLOOKUP(A9,[1]!tblWatchlist[Symbol],[1]!tblWatchlist[StockName]),"")</f>
+      <c r="B9" s="17" t="e" vm="85">
         <v>#VALUE!</v>
       </c>
       <c r="C9" s="18" t="str">
@@ -17624,31 +16927,30 @@
       </c>
       <c r="I9" s="21">
         <f t="shared" ca="1" si="2"/>
-        <v>11.74</v>
+        <v>11.9499</v>
       </c>
       <c r="J9" s="22">
         <f ca="1">Config!$C$1</f>
-        <v>0.74280000000000002</v>
+        <v>0.74360000000000004</v>
       </c>
       <c r="K9" s="20">
         <f t="shared" ca="1" si="3"/>
-        <v>1081.338528</v>
+        <v>1101.8572593599999</v>
       </c>
       <c r="L9" s="20">
         <f t="shared" ca="1" si="4"/>
-        <v>-11.891476000000011</v>
+        <v>8.6272553599999355</v>
       </c>
       <c r="M9" s="23">
         <f t="shared" ca="1" si="5"/>
-        <v>-1.0877378005077156E-2</v>
+        <v>7.8915281582410124E-3</v>
       </c>
     </row>
     <row r="10" spans="1:13">
       <c r="A10" s="17" t="s">
         <v>80</v>
       </c>
-      <c r="B10" s="17" t="e" vm="95">
-        <f>IFERROR(_xlfn.XLOOKUP(A10,[1]!tblWatchlist[Symbol],[1]!tblWatchlist[StockName]),"")</f>
+      <c r="B10" s="17" t="e" vm="86">
         <v>#VALUE!</v>
       </c>
       <c r="C10" s="18" t="str">
@@ -17673,31 +16975,30 @@
       </c>
       <c r="I10" s="21">
         <f t="shared" ca="1" si="2"/>
-        <v>14.0611</v>
+        <v>13.21</v>
       </c>
       <c r="J10" s="22">
         <f ca="1">Config!$C$1</f>
-        <v>0.74280000000000002</v>
+        <v>0.74360000000000004</v>
       </c>
       <c r="K10" s="20">
         <f t="shared" ca="1" si="3"/>
-        <v>4658.2849456800004</v>
+        <v>4381.0383760000004</v>
       </c>
       <c r="L10" s="20">
         <f t="shared" ca="1" si="4"/>
-        <v>2148.41480968</v>
+        <v>1871.16824</v>
       </c>
       <c r="M10" s="23">
         <f t="shared" ca="1" si="5"/>
-        <v>0.85598644283004433</v>
+        <v>0.74552392697978209</v>
       </c>
     </row>
     <row r="11" spans="1:13" hidden="1">
       <c r="A11" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="B11" s="17" t="e" vm="96">
-        <f>IFERROR(_xlfn.XLOOKUP(A11,[1]!tblWatchlist[Symbol],[1]!tblWatchlist[StockName]),"")</f>
+      <c r="B11" s="17" t="e" vm="64">
         <v>#VALUE!</v>
       </c>
       <c r="C11" s="18" t="str">
@@ -17722,23 +17023,23 @@
       </c>
       <c r="I11" s="21">
         <f t="shared" ca="1" si="2"/>
-        <v>897</v>
+        <v>876</v>
       </c>
       <c r="J11" s="22">
         <f ca="1">Config!$C$1</f>
-        <v>0.74280000000000002</v>
+        <v>0.74360000000000004</v>
       </c>
       <c r="K11" s="20">
         <f t="shared" ca="1" si="3"/>
-        <v>33314.58</v>
+        <v>32569.68</v>
       </c>
       <c r="L11" s="20">
         <f t="shared" ca="1" si="4"/>
-        <v>28314.58</v>
+        <v>27569.68</v>
       </c>
       <c r="M11" s="23">
         <f t="shared" ca="1" si="5"/>
-        <v>5.6629160000000001</v>
+        <v>5.5139360000000002</v>
       </c>
     </row>
   </sheetData>
@@ -17818,18 +17119,18 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02B94125-30C0-4E5C-96A7-41F5431259DA}">
   <dimension ref="A1:C1"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" t="s">
         <v>395</v>
       </c>
-      <c r="B1" t="e" vm="97">
+      <c r="B1" t="e" vm="87">
         <v>#VALUE!</v>
       </c>
       <c r="C1" s="3" cm="1">
         <f t="array" aca="1" ref="C1" ca="1">_FV(B1,"Price")</f>
-        <v>0.74280000000000002</v>
+        <v>0.74360000000000004</v>
       </c>
     </row>
   </sheetData>
@@ -17840,10 +17141,10 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:J402"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="19.5625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.4375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.53125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.46484375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
@@ -27567,11 +26868,11 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:C11"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="14.125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="34.125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.1328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="34.1328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.1328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -27703,12 +27004,12 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{44395F01-6AC6-4FB8-9BA9-DE7C42FEDA09}">
   <dimension ref="A1:B211"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="9.125" customWidth="1"/>
+    <col min="1" max="1" width="9.1328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="13.9">
+    <row r="1" spans="1:1">
       <c r="A1" s="12" t="s">
         <v>158</v>
       </c>
@@ -28565,14 +27866,14 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A54B789E-96C1-4A68-AB4A-B5AB39D199D7}">
   <dimension ref="A1:D199"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
-    <row r="1" spans="1:3" ht="30">
+    <row r="1" spans="1:3" ht="31.9">
       <c r="A1" s="25" t="s">
         <v>323</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="30">
+    <row r="5" spans="1:3" ht="31.9">
       <c r="A5" s="25" t="s">
         <v>324</v>
       </c>
@@ -28595,7 +27896,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="13.9">
+    <row r="13" spans="1:3">
       <c r="A13" s="27" t="s">
         <v>328</v>
       </c>
@@ -28622,7 +27923,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="13.9">
+    <row r="18" spans="1:3">
       <c r="A18" s="27" t="s">
         <v>331</v>
       </c>
@@ -28655,7 +27956,7 @@
         <v>5.31</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="22.5">
+    <row r="23" spans="1:3" ht="23.25">
       <c r="A23" s="30" t="s">
         <v>333</v>
       </c>
@@ -28683,7 +27984,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="33" spans="1:4" ht="30">
+    <row r="33" spans="1:4" ht="31.9">
       <c r="A33" s="25" t="s">
         <v>338</v>
       </c>
@@ -28693,7 +27994,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="37" spans="1:4" ht="27.75">
+    <row r="37" spans="1:4" ht="28.5">
       <c r="A37" s="27" t="s">
         <v>198</v>
       </c>
@@ -28725,7 +28026,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="46" spans="1:4" ht="30">
+    <row r="46" spans="1:4" ht="31.9">
       <c r="A46" s="25" t="s">
         <v>346</v>
       </c>
@@ -28755,7 +28056,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="60" spans="1:1" ht="22.5">
+    <row r="60" spans="1:1" ht="23.25">
       <c r="A60" s="30" t="s">
         <v>352</v>
       </c>
@@ -28787,7 +28088,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="72" spans="1:1" ht="22.5">
+    <row r="72" spans="1:1" ht="23.25">
       <c r="A72" s="30" t="s">
         <v>333</v>
       </c>
@@ -28820,7 +28121,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="84" spans="1:2" ht="30">
+    <row r="84" spans="1:2" ht="31.9">
       <c r="A84" s="25" t="s">
         <v>361</v>
       </c>
@@ -28840,12 +28141,12 @@
         <v>363</v>
       </c>
     </row>
-    <row r="94" spans="1:2" ht="22.5">
+    <row r="94" spans="1:2" ht="23.25">
       <c r="A94" s="30" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="96" spans="1:2" ht="13.9">
+    <row r="96" spans="1:2">
       <c r="A96" s="27" t="s">
         <v>364</v>
       </c>
@@ -28853,7 +28154,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="97" spans="1:2" ht="54">
+    <row r="97" spans="1:2" ht="57">
       <c r="A97" s="28" t="s">
         <v>365</v>
       </c>
@@ -28861,7 +28162,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="98" spans="1:2" ht="27">
+    <row r="98" spans="1:2" ht="28.5">
       <c r="A98" s="28" t="s">
         <v>367</v>
       </c>
@@ -28869,7 +28170,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="99" spans="1:2" ht="27">
+    <row r="99" spans="1:2" ht="28.5">
       <c r="A99" s="28" t="s">
         <v>369</v>
       </c>
@@ -28877,7 +28178,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="100" spans="1:2" ht="27">
+    <row r="100" spans="1:2" ht="28.5">
       <c r="A100" s="28" t="s">
         <v>371</v>
       </c>
@@ -28885,7 +28186,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="103" spans="1:2" ht="30">
+    <row r="103" spans="1:2" ht="31.9">
       <c r="A103" s="25" t="s">
         <v>373</v>
       </c>
@@ -28909,7 +28210,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="113" spans="1:1" ht="30">
+    <row r="113" spans="1:1" ht="31.9">
       <c r="A113" s="25" t="s">
         <v>375</v>
       </c>
@@ -28924,7 +28225,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="121" spans="1:1" ht="22.5">
+    <row r="121" spans="1:1" ht="23.25">
       <c r="A121" s="30" t="s">
         <v>98</v>
       </c>
@@ -28938,7 +28239,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:1" ht="22.5">
+    <row r="127" spans="1:1" ht="23.25">
       <c r="A127" s="30" t="s">
         <v>378</v>
       </c>
@@ -28952,7 +28253,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="133" spans="1:1" ht="22.5">
+    <row r="133" spans="1:1" ht="23.25">
       <c r="A133" s="30" t="s">
         <v>379</v>
       </c>
@@ -28966,7 +28267,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="139" spans="1:1" ht="30">
+    <row r="139" spans="1:1" ht="31.9">
       <c r="A139" s="25" t="s">
         <v>380</v>
       </c>
@@ -28981,12 +28282,12 @@
         <v>382</v>
       </c>
     </row>
-    <row r="147" spans="1:1" ht="22.5">
+    <row r="147" spans="1:1" ht="23.25">
       <c r="A147" s="30" t="s">
         <v>383</v>
       </c>
     </row>
-    <row r="149" spans="1:1" ht="17.25">
+    <row r="149" spans="1:1" ht="17.649999999999999">
       <c r="A149" s="32" t="s">
         <v>384</v>
       </c>
@@ -29000,7 +28301,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="153" spans="1:1" ht="17.25">
+    <row r="153" spans="1:1" ht="17.649999999999999">
       <c r="A153" s="32" t="s">
         <v>385</v>
       </c>
@@ -29014,7 +28315,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="157" spans="1:1" ht="17.25">
+    <row r="157" spans="1:1" ht="17.649999999999999">
       <c r="A157" s="32" t="s">
         <v>386</v>
       </c>
@@ -29028,7 +28329,7 @@
         <v>#NAME?</v>
       </c>
     </row>
-    <row r="161" spans="1:1" ht="17.25">
+    <row r="161" spans="1:1" ht="17.649999999999999">
       <c r="A161" s="32" t="s">
         <v>119</v>
       </c>
@@ -29042,7 +28343,7 @@
         <v>#NAME?</v>
       </c>
     </row>
-    <row r="167" spans="1:1" ht="30">
+    <row r="167" spans="1:1" ht="31.9">
       <c r="A167" s="25" t="s">
         <v>387</v>
       </c>
@@ -29056,7 +28357,7 @@
         <v>#NAME?</v>
       </c>
     </row>
-    <row r="173" spans="1:1" ht="30">
+    <row r="173" spans="1:1" ht="31.9">
       <c r="A173" s="25" t="s">
         <v>388</v>
       </c>
@@ -29076,12 +28377,12 @@
         <v>390</v>
       </c>
     </row>
-    <row r="183" spans="1:1" ht="22.5">
+    <row r="183" spans="1:1" ht="23.25">
       <c r="A183" s="30" t="s">
         <v>383</v>
       </c>
     </row>
-    <row r="185" spans="1:1" ht="17.25">
+    <row r="185" spans="1:1" ht="17.649999999999999">
       <c r="A185" s="32" t="s">
         <v>391</v>
       </c>
@@ -29095,7 +28396,7 @@
         <v>#NAME?</v>
       </c>
     </row>
-    <row r="189" spans="1:1" ht="17.25">
+    <row r="189" spans="1:1" ht="17.649999999999999">
       <c r="A189" s="32" t="s">
         <v>392</v>
       </c>
@@ -29109,7 +28410,7 @@
         <v>#NAME?</v>
       </c>
     </row>
-    <row r="193" spans="1:1" ht="17.25">
+    <row r="193" spans="1:1" ht="17.649999999999999">
       <c r="A193" s="32" t="s">
         <v>393</v>
       </c>
@@ -29123,7 +28424,7 @@
         <v>#NAME?</v>
       </c>
     </row>
-    <row r="197" spans="1:1" ht="17.25">
+    <row r="197" spans="1:1" ht="17.649999999999999">
       <c r="A197" s="32" t="s">
         <v>394</v>
       </c>
@@ -29145,31 +28446,31 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9DD66AE-11E1-41AC-875F-1DBE679B5DE3}">
   <dimension ref="A1:B46"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B11" t="s">
         <v>125</v>
@@ -29177,42 +28478,42 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
+        <v>401</v>
+      </c>
+      <c r="B12" t="s">
         <v>402</v>
-      </c>
-      <c r="B12" t="s">
-        <v>403</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
+        <v>403</v>
+      </c>
+      <c r="B13" t="s">
         <v>404</v>
-      </c>
-      <c r="B13" t="s">
-        <v>405</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
+        <v>405</v>
+      </c>
+      <c r="B14" t="s">
         <v>406</v>
-      </c>
-      <c r="B14" t="s">
-        <v>407</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
+        <v>407</v>
+      </c>
+      <c r="B15" t="s">
         <v>408</v>
-      </c>
-      <c r="B15" t="s">
-        <v>409</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
+        <v>409</v>
+      </c>
+      <c r="B16" t="s">
         <v>410</v>
-      </c>
-      <c r="B16" t="s">
-        <v>411</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -29222,134 +28523,134 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B22" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" t="s">
+        <v>413</v>
+      </c>
+      <c r="B23" t="s">
         <v>414</v>
-      </c>
-      <c r="B23" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
+        <v>415</v>
+      </c>
+      <c r="B24" t="s">
         <v>416</v>
-      </c>
-      <c r="B24" t="s">
-        <v>417</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" t="s">
+        <v>417</v>
+      </c>
+      <c r="B25" t="s">
         <v>418</v>
-      </c>
-      <c r="B25" t="s">
-        <v>419</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" t="s">
+        <v>419</v>
+      </c>
+      <c r="B26" t="s">
         <v>420</v>
-      </c>
-      <c r="B26" t="s">
-        <v>421</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
+        <v>422</v>
+      </c>
+      <c r="B31" t="s">
         <v>423</v>
-      </c>
-      <c r="B31" t="s">
-        <v>424</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
+        <v>424</v>
+      </c>
+      <c r="B32" t="s">
         <v>425</v>
-      </c>
-      <c r="B32" t="s">
-        <v>426</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
+        <v>426</v>
+      </c>
+      <c r="B33" t="s">
         <v>427</v>
-      </c>
-      <c r="B33" t="s">
-        <v>428</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B34" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
+        <v>429</v>
+      </c>
+      <c r="B35" t="s">
         <v>430</v>
-      </c>
-      <c r="B35" t="s">
-        <v>431</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B39" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" t="s">
+        <v>434</v>
+      </c>
+      <c r="B40" t="s">
         <v>435</v>
-      </c>
-      <c r="B40" t="s">
-        <v>436</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" t="s">
+        <v>436</v>
+      </c>
+      <c r="B41" t="s">
         <v>437</v>
-      </c>
-      <c r="B41" t="s">
-        <v>438</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" t="s">
+        <v>438</v>
+      </c>
+      <c r="B42" t="s">
         <v>439</v>
-      </c>
-      <c r="B42" t="s">
-        <v>440</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -29357,7 +28658,7 @@
         <v>152</v>
       </c>
       <c r="B43" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -29365,23 +28666,23 @@
         <v>153</v>
       </c>
       <c r="B44" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" t="s">
+        <v>442</v>
+      </c>
+      <c r="B45" t="s">
         <v>443</v>
-      </c>
-      <c r="B45" t="s">
-        <v>444</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" t="s">
+        <v>444</v>
+      </c>
+      <c r="B46" t="s">
         <v>445</v>
-      </c>
-      <c r="B46" t="s">
-        <v>446</v>
       </c>
     </row>
   </sheetData>

--- a/dashboard/trading_system.xlsx
+++ b/dashboard/trading_system.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\husainnatha\tradingsystem\dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78D2E7A7-97FD-4798-8462-C0C2C035B771}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2063A75-E978-4C9C-B807-BB0B021E352D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="353" yWindow="1343" windowWidth="16200" windowHeight="9307" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1000,7 +1000,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1944" uniqueCount="602">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1949" uniqueCount="607">
   <si>
     <t>collected_timestamp</t>
   </si>
@@ -2894,22 +2894,37 @@
     <t>seed</t>
   </si>
   <si>
-    <t>EmergencyReserve</t>
-  </si>
-  <si>
-    <t>TargetCashReserve</t>
-  </si>
-  <si>
-    <t>MaxDeploymentPercent</t>
-  </si>
-  <si>
-    <t>Contributions</t>
-  </si>
-  <si>
-    <t>CashReserve</t>
-  </si>
-  <si>
     <t>HOLDING</t>
+  </si>
+  <si>
+    <t>cash: 0</t>
+  </si>
+  <si>
+    <t>target_cash_reserve: 12000</t>
+  </si>
+  <si>
+    <t>emergency_reserve: 20000</t>
+  </si>
+  <si>
+    <t>cash_contributions: 33738.31</t>
+  </si>
+  <si>
+    <t>max_deployment_percent: 70</t>
+  </si>
+  <si>
+    <t>cash</t>
+  </si>
+  <si>
+    <t>target_cash_reserve</t>
+  </si>
+  <si>
+    <t>emergency_reserve</t>
+  </si>
+  <si>
+    <t>cash_contributions</t>
+  </si>
+  <si>
+    <t>max_deployment_percent</t>
   </si>
 </sst>
 </file>
@@ -3127,10 +3142,10 @@
     </xf>
     <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3589,9 +3604,6 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-    </dxf>
-    <dxf>
       <numFmt numFmtId="3" formatCode="#,##0"/>
     </dxf>
     <dxf>
@@ -3644,6 +3656,9 @@
     </dxf>
     <dxf>
       <numFmt numFmtId="27" formatCode="dd/mm/yyyy\ hh:mm"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -3788,11 +3803,9 @@
     <v>4</v>
     <v>233.67</v>
     <v>15.06</v>
-    <v>3.6577000000000002</v>
+    <v>3.6634000000000002</v>
     <v>27.26</v>
-    <v>-3.4739999999999997E-3</v>
     <v>0.17208500000000002</v>
-    <v>-0.64500000000000002</v>
     <v>USD</v>
     <v>Applied Optoelectronics, Inc. is a developer and manufacturer of advanced optical and hybrid fiber coaxial (HFC) networking products that are the building blocks for artificial intelligence (AI) datacenters, Cable TV Broadband (CATV) and broadband fiber access networks around the world. The Company supplies this critical infrastructure to tier-one customers across cloud computing, CATV broadband, telecom, and fiber-to-the-home (FTTH) markets. It designs and manufactures a range of optical communications products at varying levels of integration, from components, subassemblies and modules to complete turn-key equipment. In the CATV market, it supplies a broad array of products, including lasers, transmitters and transceivers, and turn-key equipment. It supplies optical transceivers that plug into switches and servers within the data center and allow these network devices to send and receive data over fiber optic cables. In the telecom market, it supplies lasers and laser subassemblies.</v>
     <v>4691</v>
@@ -3803,7 +3816,7 @@
     <v>191.98</v>
     <v>Electronic Equipment &amp; Parts</v>
     <v>Stock</v>
-    <v>46174.905480693749</v>
+    <v>46174.999913471875</v>
     <v>0</v>
     <v>149.05000000000001</v>
     <v>14898675105</v>
@@ -3813,11 +3826,10 @@
     <v>0</v>
     <v>158.41</v>
     <v>185.67</v>
-    <v>185.02500000000001</v>
     <v>80242770</v>
     <v>AAOI</v>
     <v>APPLIED OPTOELECTRONICS, INC. (XNAS:AAOI)</v>
-    <v>15976213</v>
+    <v>512706</v>
     <v>11698182</v>
     <v>2013</v>
   </rv>
@@ -3842,11 +3854,9 @@
     <v>4</v>
     <v>231.36</v>
     <v>91.84</v>
-    <v>1.3947000000000001</v>
-    <v>36.954999999999998</v>
-    <v>-3.3400000000000001E-3</v>
-    <v>0.19384699999999999</v>
-    <v>-0.76</v>
+    <v>1.367</v>
+    <v>36.9</v>
+    <v>0.19355899999999998</v>
     <v>USD</v>
     <v>Twilio Inc. provides a customer engagement platform to build direct, personalized relationships with their customers everywhere in the world. Its platform provides developers with tools to build, scale, and deploy real-time communications within software applications. Its segments include Twilio Communications (Communications) and Twilio Segment (Segment). The Communications segment consists of a variety of application programming interfaces (APIs) and software solutions to optimize communications between its customers and their end users. Its key offerings in its Communications segment include Messaging, Voice, Email (includes Marketing Campaigns), Flex and User Authentication and Identity. Its Twilio Flex is a digital engagement center for the entire customer journey. Twilio Segment is a customer data platform that provides businesses with the tools to harness the power of contextual data by unifying real-time information collected throughout each customer’s journey into a profile.</v>
     <v>5558</v>
@@ -3857,21 +3867,20 @@
     <v>231.36</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46174.905611087503</v>
+    <v>46174.999931666403</v>
     <v>3</v>
     <v>194.51249999999999</v>
-    <v>34542980770</v>
+    <v>34534633206</v>
     <v>TWILIO INC.</v>
     <v>TWILIO INC.</v>
     <v>195.36500000000001</v>
-    <v>353.79289999999997</v>
+    <v>353.70190000000002</v>
     <v>190.64</v>
-    <v>227.595</v>
-    <v>226.78</v>
+    <v>227.54</v>
     <v>151773900</v>
     <v>TWLO</v>
     <v>TWILIO INC. (XNYS:TWLO)</v>
-    <v>7279758</v>
+    <v>15989</v>
     <v>2987544</v>
     <v>2008</v>
   </rv>
@@ -3916,11 +3925,9 @@
     <v>4</v>
     <v>444.72</v>
     <v>183.64250000000001</v>
-    <v>1.5710999999999999</v>
+    <v>1.5391999999999999</v>
     <v>68.33</v>
-    <v>-4.1349999999999998E-3</v>
     <v>0.20363600000000001</v>
-    <v>-1.67</v>
     <v>USD</v>
     <v>MongoDB, Inc. is a developer data platform company. Its developer data platform is a globally distributed operational database integrated with a set of data services that allow development teams to address the growing variety of application requirements. Its customers can implement its developer data platform as a managed service offering, or they can choose a self-managed option. Its MongoDB Atlas is its managed multi-cloud database-as-a-service (DBaaS) offering that includes an integrated set of databases and related services. Atlas Vector Search allows the integration of an operational database and vector search in a unified, fully managed platform. MongoDB Enterprise Advanced is its proprietary self-managed commercial offering for enterprise customers that can run in the cloud, on-premises or in a hybrid environment. It also provides professional services for its customers.</v>
     <v>5636</v>
@@ -3932,21 +3939,20 @@
     <v>9</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46174.905448830468</v>
+    <v>46174.999311943749</v>
     <v>10</v>
     <v>345.5</v>
-    <v>32512311728</v>
+    <v>32484847888</v>
     <v>MONGODB, INC.</v>
     <v>MONGODB, INC.</v>
     <v>346</v>
     <v>0</v>
     <v>335.55</v>
     <v>403.88</v>
-    <v>402.21</v>
-    <v>80499930</v>
+    <v>80431930</v>
     <v>MDB</v>
     <v>MONGODB, INC. (XNAS:MDB)</v>
-    <v>6769673</v>
+    <v>26150</v>
     <v>2439978</v>
     <v>2007</v>
   </rv>
@@ -3969,9 +3975,7 @@
     <v>63.8</v>
     <v>2.4420000000000002</v>
     <v>15.29</v>
-    <v>2.2430000000000002E-3</v>
     <v>0.139596</v>
-    <v>0.28000000000000003</v>
     <v>USD</v>
     <v>CoreWeave, Inc. is a cloud infrastructure technology company. The Company offers the CoreWeave Cloud Platform, which consists of software and cloud services that deliver the automation and efficiency needed to manage complex artificial intelligence (AI) infrastructure. Its CoreWeave Cloud Platform is an integrated solution that is purpose-built for running AI workloads such as model training and inference. Its solutions include infrastructure services, managed software services, and application software services. Its Infrastructure Services provide its customers with access to advanced graphics processing unit (GPU) and central processing unit (CPU) compute, highly performant networking, and storage. Its Managed Software Services include CKS, a flexible virtual private cloud and a bare metal service that runs kubernetes directly on high-performance servers. Its Application Software Services build on top of its infrastructure and managed software services, integrating additional tools.</v>
     <v>2189</v>
@@ -3982,7 +3986,7 @@
     <v>127.8485</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46174.905605080472</v>
+    <v>46174.999966863281</v>
     <v>114.715</v>
     <v>68098097328</v>
     <v>COREWEAVE, INC.</v>
@@ -3991,11 +3995,10 @@
     <v>0</v>
     <v>109.53</v>
     <v>124.82</v>
-    <v>125.1</v>
     <v>545570400</v>
     <v>CRWV</v>
     <v>COREWEAVE, INC. (XNAS:CRWV)</v>
-    <v>58066760</v>
+    <v>1236784</v>
     <v>28595714</v>
     <v>2017</v>
   </rv>
@@ -4018,9 +4021,7 @@
     <v>100.02</v>
     <v>1.4450000000000001</v>
     <v>55.56</v>
-    <v>9.025E-3</v>
     <v>0.15726499999999999</v>
-    <v>3.69</v>
     <v>USD</v>
     <v>Arm Holdings plc is a United Kingdom-based company. The Company is engaged in the design of central processing units (CPUs) and compute platforms for semiconductor chips. It develops and licenses CPU products and related technology. Its cloud and data center solutions include Arm AGI CPU and Arm Neoverse Compute Subsystems. The Arm Agentic Generalized Infrastructure (AGI) CPU is a production-ready system on a chip (SoC) for artificial intelligence (AI) data centers, delivering compute at scale. The Arm Neoverse Compute Subsystems (CSS) are pre-validated, performance-optimized compute platforms designed to accelerate infrastructure silicon development. The Company's primary markets include smartphone applications, processors and other chips used in mobile phones, consumer electronics, networking equipment, cloud and data center servers, automotive applications, Internet of Things (loT) and other embedded computing devices.</v>
     <v>9584</v>
@@ -4031,20 +4032,19 @@
     <v>421.68990000000002</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46174.905622534374</v>
+    <v>46174.999942557813</v>
     <v>381.25</v>
     <v>436684099150</v>
     <v>ARM HOLDINGS PLC</v>
     <v>ARM HOLDINGS PLC</v>
     <v>389.95</v>
-    <v>417.40809999999999</v>
+    <v>483.05149999999998</v>
     <v>353.29</v>
     <v>408.85</v>
-    <v>412.54</v>
     <v>1068079000</v>
     <v>ARM</v>
     <v>ARM HOLDINGS PLC (XNAS:ARM)</v>
-    <v>20614850</v>
+    <v>452401</v>
     <v>12254946</v>
     <v>2018</v>
   </rv>
@@ -4069,11 +4069,9 @@
     <v>4</v>
     <v>20.81</v>
     <v>3.87</v>
-    <v>0.76549999999999996</v>
+    <v>0.72670000000000001</v>
     <v>1.6</v>
-    <v>0</v>
     <v>0.130187</v>
-    <v>0</v>
     <v>USD</v>
     <v>POET Technologies Inc. is a design and development company. It offers high-speed optical engines, light source products and custom optical modules to the artificial intelligence (AI) systems market and to hyperscale data centers. Its photonic integration solutions are based on the POET Optical Interposer, a novel, patented platform that allows the integration of electronic and photonic devices into a single chip using wafer-level semiconductor manufacturing techniques. Its Optical Interposer-based products consume less power than comparable products, are smaller in size and are readily scalable to high production volumes. In addition, it has designed and produced novel light source products for chip-to-chip data communication within and between AI servers, the next frontier for solving bandwidth and latency problems in AI systems. Its Optical Interposer platform solves device integration challenges across a range of communication, computing and sensing applications.</v>
     <v>180</v>
@@ -4084,7 +4082,7 @@
     <v>14.43</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46174.90552547422</v>
+    <v>46174.999884189063</v>
     <v>17</v>
     <v>11.62</v>
     <v>2397350106</v>
@@ -4094,11 +4092,10 @@
     <v>0</v>
     <v>12.29</v>
     <v>13.89</v>
-    <v>13.89</v>
     <v>172595400</v>
     <v>POET</v>
     <v>POET Technologies Inc. (XNAS:POET)</v>
-    <v>46362718</v>
+    <v>2967987</v>
     <v>66002318</v>
     <v>2010</v>
   </rv>
@@ -4123,11 +4120,9 @@
     <v>4</v>
     <v>278.70499999999998</v>
     <v>98.010099999999994</v>
-    <v>1.5619000000000001</v>
+    <v>1.5459000000000001</v>
     <v>30.14</v>
-    <v>-1.9819999999999998E-3</v>
     <v>0.121852</v>
-    <v>-0.55000000000000004</v>
     <v>USD</v>
     <v>Datadog Inc provides an AI-powered observability and security platform for cloud applications. Its Software as a Service (SaaS) platform integrates and automates infrastructure monitoring, application performance monitoring, log management, user experience monitoring, cloud security and service management. Its proprietary platform combines the power of metrics, traces, logs, user sessions, security signals, and other data from a single agent and over 1,000 integrations to provide a unified view of infrastructure, application performance and real-time events impacting performance. Its solutions include built for dynamic cloud and hybrid infrastructures, simple but not simplistic, integrated data platform, built for collaboration, cloud-agnostic, ubiquitous, and integrates with its customers complex environments. Its platform is used by industries to enable digital transformation and cloud migration, and drive collaboration among development, operations, security and business teams.</v>
     <v>8100</v>
@@ -4138,21 +4133,20 @@
     <v>278.70499999999998</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46174.905533969533</v>
+    <v>46174.999770450784</v>
     <v>20</v>
     <v>249.44</v>
     <v>98775395898</v>
     <v>DATADOG, INC.</v>
     <v>DATADOG, INC.</v>
     <v>251.77500000000001</v>
-    <v>703.0403</v>
+    <v>703.07590000000005</v>
     <v>247.35</v>
     <v>277.49</v>
-    <v>276.94</v>
     <v>355960200</v>
     <v>DDOG</v>
     <v>DATADOG, INC. (XNAS:DDOG)</v>
-    <v>11168410</v>
+    <v>47583</v>
     <v>6546440</v>
     <v>2026</v>
   </rv>
@@ -4177,11 +4171,9 @@
     <v>4</v>
     <v>16.625</v>
     <v>4</v>
-    <v>1.1495</v>
-    <v>1.4</v>
-    <v>1.4769000000000001E-2</v>
-    <v>9.4339999999999993E-2</v>
-    <v>0.24</v>
+    <v>1.1449</v>
+    <v>1.41</v>
+    <v>9.5013E-2</v>
     <v>USD</v>
     <v>Nokia Oyj is a Finland-based company engaged in the network and Internet protocol (IP) infrastructure, software, and related services market. The Company's businesses include Nokia Networks and Nokia Technologies. The Company's segments include Ultra Broadband Networks, IP Networks and Applications, and Nokia Technologies. The Ultra Broadband Networks segment comprises Mobile Networks and Fixed Networks operating segments. The IP Networks and Applications segment comprises IP/Optical Networks and Applications &amp; Analytics operating segments. The Applications &amp; Analytics operating segment offers software solutions spanning customer experience management, network operations and management, communications and collaboration, policy and charging, as well as Cloud, Internet of things (IoT), security, and analytics platforms that enable digital services providers and enterprises to accelerate and optimize their customer experience. The Company has Comptel Oyj among its subsidiaries.</v>
     <v>77586</v>
@@ -4192,21 +4184,20 @@
     <v>16.52</v>
     <v>Communications &amp; Networking</v>
     <v>Stock</v>
-    <v>46174.905569710158</v>
+    <v>46174.999974189064</v>
     <v>23</v>
     <v>14.93</v>
-    <v>93253977599</v>
+    <v>93311400000</v>
     <v>Nokia Oyj</v>
     <v>Nokia Oyj</v>
     <v>15.07</v>
-    <v>100.9323</v>
+    <v>101.01130000000001</v>
     <v>14.84</v>
-    <v>16.239999999999998</v>
-    <v>16.489999999999998</v>
+    <v>16.25</v>
     <v>5742240000</v>
     <v>NOK</v>
     <v>Nokia Oyj (XNYS:NOK)</v>
-    <v>171374832</v>
+    <v>11902305</v>
     <v>121991858</v>
     <v>1997</v>
   </rv>
@@ -4231,11 +4222,9 @@
     <v>4</v>
     <v>19.84</v>
     <v>9.2002000000000006</v>
-    <v>0.95540000000000003</v>
+    <v>0.95909999999999995</v>
     <v>1.38</v>
-    <v>-5.3439999999999998E-3</v>
     <v>0.11774699999999999</v>
-    <v>-7.0000000000000007E-2</v>
     <v>USD</v>
     <v>UiPath, Inc. is focused on agentic automation and orchestration, empowering enterprises to harness the full potential of AI agents to autonomously execute and optimize complex business processes. It is focused on building and managing automations, starting with computer vision technology and user interface automation in its initial robotic process automation offering. Its AI-powered UiPath Platform offers a robust set of capabilities that allows its customers to discover opportunities for automation, automate using a digital workforce that seamlessly collaborates with humans, and operate a mission-critical automation program at scale. It enables employees to quickly build automations for both existing and new processes and to automate a range of actions including logging into applications, moving folders, filling in forms, reading emails and others. Its platform allows users to design and combine UI automations, API integrations and AI-based document understanding in a single workflow.</v>
     <v>3981</v>
@@ -4246,21 +4235,20 @@
     <v>13.2</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46174.905613402341</v>
+    <v>46174.999883020311</v>
     <v>26</v>
     <v>11.9</v>
     <v>6817808540</v>
     <v>UIPATH, INC.</v>
     <v>UIPATH, INC.</v>
     <v>11.95</v>
-    <v>21.775300000000001</v>
+    <v>21.776399999999999</v>
     <v>11.72</v>
     <v>13.1</v>
-    <v>13.03</v>
     <v>520443400</v>
     <v>PATH</v>
     <v>UIPATH, INC. (XNYS:PATH)</v>
-    <v>67787642</v>
+    <v>341448</v>
     <v>36146448</v>
     <v>2015</v>
   </rv>
@@ -4285,11 +4273,9 @@
     <v>4</v>
     <v>276.8</v>
     <v>163.52000000000001</v>
-    <v>1.1524000000000001</v>
-    <v>18.43</v>
-    <v>-1.0019E-2</v>
-    <v>9.6442E-2</v>
-    <v>-2.1</v>
+    <v>1.1446000000000001</v>
+    <v>18.5</v>
+    <v>9.6807999999999991E-2</v>
     <v>USD</v>
     <v>Salesforce, Inc. is a customer relationship management (CRM) technology company. Its artificial intelligence (AI) powered Agentforce 360 Platform offers sales, service, marketing, commerce, collaboration, data management, integration, analytics, and information technology (IT) service solutions. It enables customers to build and deploy digital labor for employees and customers, leveraging autonomous AI agents across business functions. Its service offerings include Agentforce Sales, Agentforce Service, Agentforce 360 Platform, Slack and Others. The Agentforce Sales provides sales capabilities and tools built for organizations across prospecting, sales engagement, team collaboration, sales analytics and AI, sales programs, sales performance, partner management, and revenue and orders. The Agentforce Service provides field service solutions that enable companies to connect service agents, dispatchers and mobile employees through platform to schedule, dispatch and manage jobs.</v>
     <v>83334</v>
@@ -4300,21 +4286,20 @@
     <v>211.34</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46174.905654664064</v>
+    <v>46174.999968784374</v>
     <v>29</v>
     <v>198.21</v>
-    <v>171605070000</v>
+    <v>171662400000</v>
     <v>SALESFORCE, INC.</v>
     <v>SALESFORCE, INC.</v>
     <v>198.75</v>
-    <v>24.2422</v>
+    <v>24.2502</v>
     <v>191.1</v>
-    <v>209.53</v>
-    <v>207.5</v>
+    <v>209.6</v>
     <v>819000000</v>
     <v>CRM</v>
     <v>SALESFORCE, INC. (XNYS:CRM)</v>
-    <v>27523034</v>
+    <v>252830</v>
     <v>13384206</v>
     <v>1999</v>
   </rv>
@@ -4339,11 +4324,9 @@
     <v>4</v>
     <v>336.99</v>
     <v>114.625</v>
-    <v>0.9718</v>
+    <v>0.95489999999999997</v>
     <v>15.98</v>
-    <v>-3.8529999999999997E-3</v>
     <v>0.11436299999999999</v>
-    <v>-0.6</v>
     <v>USD</v>
     <v>Zscaler, Inc. is a cloud security company. The Company has developed a platform incorporating core security functionalities needed to enable fast and secure access to cloud resources based on identity, context and an organization's policies. Its Zscaler Zero Trust Exchange is a cloud-native platform that securely connects users, devices, applications and workloads, including artificial intelligence (AI) agents, without relying on hub-and-spoke network architecture and firewall-centric security. It delivers its solutions using a software-as-a-service (SaaS) business model and sells subscriptions to customers to access its cloud platform, together with related support services. Its services include Zscaler Internet Access (ZIA), Zscaler Private Access (ZPA), and Zscaler Digital Experience (ZDX). ZIA provides secure access to externally managed applications, including SaaS applications and internet destinations, regardless of device, location or network.</v>
     <v>7923</v>
@@ -4354,7 +4337,7 @@
     <v>157.69999999999999</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46174.90533741875</v>
+    <v>46174.999853587498</v>
     <v>32</v>
     <v>143.75</v>
     <v>25179786245</v>
@@ -4364,11 +4347,10 @@
     <v>0</v>
     <v>139.72999999999999</v>
     <v>155.71</v>
-    <v>155.11000000000001</v>
     <v>161709500</v>
     <v>ZS</v>
     <v>ZSCALER, INC. (XNAS:ZS)</v>
-    <v>10304127</v>
+    <v>149366</v>
     <v>5356823</v>
     <v>2007</v>
   </rv>
@@ -4393,11 +4375,9 @@
     <v>4</v>
     <v>284.99</v>
     <v>118.3</v>
-    <v>1.3536999999999999</v>
-    <v>24.45</v>
-    <v>-5.7110000000000006E-4</v>
-    <v>9.5676000000000011E-2</v>
-    <v>-0.16</v>
+    <v>1.3489</v>
+    <v>24.61</v>
+    <v>9.6301999999999999E-2</v>
     <v>USD</v>
     <v>Snowflake Inc. is an artificial intelligence (AI) data cloud company. The Company provides a platform which powers the AI data cloud, enabling customers to consolidate data into a single source of truth to drive insights, apply AI to solve business problems, build data applications, and share data and data products. Its cloud-native architecture includes three independently scalable but logically integrated layers across storage, compute, and cloud services. The storage layer ingests massive amounts and varieties of structured, semi-structured, and unstructured data. The compute layer provides dedicated resources to enable users to simultaneously access common data sets for many use cases with minimal latency. The cloud services layer enables users to securely use AI within applications, tools, and processes. Its platform supports a wide range of product categories for customers’ business objectives, including analytics, data engineering, AI, applications and collaboration.</v>
     <v>9060</v>
@@ -4408,7 +4388,7 @@
     <v>284.99</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46174.905452522653</v>
+    <v>46174.999906330471</v>
     <v>35</v>
     <v>258.31</v>
     <v>60745624254</v>
@@ -4417,12 +4397,11 @@
     <v>259.97000000000003</v>
     <v>0</v>
     <v>255.55</v>
-    <v>280</v>
-    <v>280</v>
-    <v>346602900</v>
+    <v>280.16000000000003</v>
+    <v>346600000</v>
     <v>SNOW</v>
     <v>SNOWFLAKE INC. (XNYS:SNOW)</v>
-    <v>20140059</v>
+    <v>121317</v>
     <v>9694888</v>
     <v>2012</v>
   </rv>
@@ -4447,11 +4426,9 @@
     <v>4</v>
     <v>211.47800000000001</v>
     <v>81.239999999999995</v>
-    <v>0.93969999999999998</v>
-    <v>11.52</v>
-    <v>-2.4658000000000003E-2</v>
-    <v>9.2627000000000001E-2</v>
-    <v>-3.35</v>
+    <v>0.92059999999999997</v>
+    <v>11.49</v>
+    <v>9.2385999999999996E-2</v>
     <v>USD</v>
     <v>ServiceNow, Inc. provides an artificial intelligence (AI) platform for business transformation. The Company’s AI platform connects people, processes, data, and devices to increase productivity and maximize business outcomes. Its intelligent platform, the Now Platform, is a cloud-based solution that helps enterprises and organizations across public and private sectors digitize workflows. The workflow applications built on the Now Platform are organized into four primary areas: Technology, CRM and Industry, Core Business and Creator. Its products include IT Service Management, IT Operations Management, HR Service Delivery, ServiceNow AI Agents, AI Experience, Build Agent, ServiceNow AI Control Tower, AI Agent Fabric, RaptorDB, Workflow Data Fabric, Workplace Service Delivery, ServiceNow Platform Encryption, Telecommunications Service Operations Management, and others. The Company also offers identity security, helping organizations secure access across the enterprise.</v>
     <v>29187</v>
@@ -4462,21 +4439,20 @@
     <v>139.19999999999999</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46174.905654513284</v>
+    <v>46174.999955022657</v>
     <v>38</v>
     <v>131.61000000000001</v>
-    <v>140144444120</v>
+    <v>140113504880</v>
     <v>SERVICENOW, INC.</v>
     <v>SERVICENOW, INC.</v>
     <v>135.77000000000001</v>
-    <v>80.819599999999994</v>
+    <v>80.802800000000005</v>
     <v>124.37</v>
-    <v>135.88999999999999</v>
-    <v>132.51</v>
+    <v>135.86000000000001</v>
     <v>1031308000</v>
     <v>NOW</v>
     <v>SERVICENOW, INC. (XNYS:NOW)</v>
-    <v>68288795</v>
+    <v>1098569</v>
     <v>29979723</v>
     <v>2012</v>
   </rv>
@@ -4501,11 +4477,9 @@
     <v>4</v>
     <v>469.47</v>
     <v>106.38</v>
-    <v>1.2961</v>
-    <v>45.2</v>
-    <v>4.3007999999999998E-2</v>
-    <v>0.107386</v>
-    <v>20.04</v>
+    <v>1.2963</v>
+    <v>45.05</v>
+    <v>0.10703</v>
     <v>USD</v>
     <v>Dell Technologies Inc. is engaged in designing, developing, manufacturing, marketing, selling, and supporting a wide range of comprehensive and integrated solutions, products, and services. The Company operates through two segments: Infrastructure Solutions Group (ISG) and Client Solutions Group (CSG). Its ISG segment enables the Company’s customer’s digital transformation with solutions that address artificial intelligence (AI), machine learning, data analytics, and multi cloud environments. Its comprehensive storage portfolio includes modern and traditional storage solutions, including all-flash arrays, scale-out file, object platforms, hyper-converged infrastructure, and software-defined storage. Its CSG segment offers branded personal computers (PCs) including notebooks, desktops, and workstations and branded peripherals that include displays, docking stations, keyboards, mice, and webcam and audio devices, as well as third-party software and peripherals.</v>
     <v>97000</v>
@@ -4516,21 +4490,20 @@
     <v>469.47</v>
     <v>Computers, Phones &amp; Household Electronics</v>
     <v>Stock</v>
-    <v>46174.905678668751</v>
+    <v>46174.999998321095</v>
     <v>41</v>
     <v>426.15</v>
-    <v>302770280313</v>
+    <v>302672845068</v>
     <v>DELL TECHNOLOGIES INC.</v>
     <v>DELL TECHNOLOGIES INC.</v>
     <v>426.15</v>
-    <v>37.014899999999997</v>
+    <v>37.003100000000003</v>
     <v>420.91</v>
-    <v>466.11</v>
-    <v>486</v>
+    <v>465.96</v>
     <v>649568300</v>
     <v>DELL</v>
     <v>DELL TECHNOLOGIES INC. (XNYS:DELL)</v>
-    <v>20465419</v>
+    <v>396044</v>
     <v>8689894</v>
     <v>2013</v>
   </rv>
@@ -4575,11 +4548,9 @@
     <v>4</v>
     <v>345.72</v>
     <v>134.57</v>
-    <v>1.649</v>
-    <v>22.29</v>
-    <v>-2.7200999999999999E-2</v>
-    <v>9.8724000000000006E-2</v>
-    <v>-6.75</v>
+    <v>1.6485000000000001</v>
+    <v>22.37</v>
+    <v>9.9079E-2</v>
     <v>USD</v>
     <v>Oracle Corporation offers integrated suites of applications plus secure, autonomous infrastructure in the Oracle Cloud. The Company operates through three businesses: cloud and license, hardware and service. Its cloud and license business is engaged in the sale, marketing and delivery of its enterprise applications and infrastructure technologies through cloud and on-premise deployment models including its cloud services and license support offerings, and its cloud license and on-premise license offerings. Its hardware business provides infrastructure technologies including Oracle Engineered Systems, servers, storage, industry-specific hardware, operating systems, virtualization, management and other hardware-related software to support diverse IT environments. Its services business provides services to customers and partners to help maximize the performance of their investments in Oracle applications and infrastructure technologies.</v>
     <v>162000</v>
@@ -4591,21 +4562,20 @@
     <v>47</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46174.905588935158</v>
+    <v>46174.999994120313</v>
     <v>48</v>
     <v>224.6</v>
-    <v>713460731220</v>
+    <v>713690814900</v>
     <v>ORACLE CORPORATION</v>
     <v>ORACLE CORPORATION</v>
     <v>230.5</v>
-    <v>42.046500000000002</v>
+    <v>42.060400000000001</v>
     <v>225.78</v>
-    <v>248.07</v>
-    <v>241.4</v>
+    <v>248.15</v>
     <v>2876046000</v>
     <v>ORCL</v>
     <v>ORACLE CORPORATION (XNYS:ORCL)</v>
-    <v>48000587</v>
+    <v>881574</v>
     <v>22158519</v>
     <v>2005</v>
   </rv>
@@ -4630,11 +4600,9 @@
     <v>4</v>
     <v>117.19</v>
     <v>34.2301</v>
-    <v>2.8334999999999999</v>
+    <v>2.8328000000000002</v>
     <v>10.34</v>
-    <v>-7.1109999999999993E-3</v>
     <v>9.8495000000000013E-2</v>
-    <v>-0.82</v>
     <v>USD</v>
     <v>Innodata Inc. is a global data engineering company. It provides a range of transferable solutions, platforms, and services for generative artificial intelligence (AI)/AI builders and adopters. Its Digital Data Solutions segment provides AI data preparation services, collecting or creating training data, annotating training data, and training AI algorithms for its customers, and AI model deployment and integration. It also provides a range of data engineering support services. Its Synodex segment provides an industry platform that transforms medical records into useable digital data organized in accordance with its proprietary data models or customer data models. Its Agility segment provides an industry platform that provides marketing communications and public relations professionals with the ability to target and distribute content to journalists and social media influencers worldwide and to monitor and analyze global news channels (print, Web, radio and TV) and social media channels.</v>
     <v>10020</v>
@@ -4645,21 +4613,20 @@
     <v>117.19</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46174.904556967187</v>
+    <v>46174.999599478906</v>
     <v>51</v>
     <v>100.26</v>
     <v>1490374656</v>
     <v>INNODATA INC.</v>
     <v>INNODATA INC.</v>
     <v>105.25</v>
-    <v>103.761</v>
+    <v>103.7582</v>
     <v>104.98</v>
     <v>115.32</v>
-    <v>114.5</v>
     <v>32655360</v>
     <v>INOD</v>
     <v>INNODATA INC. (XNAS:INOD)</v>
-    <v>2883385</v>
+    <v>23184</v>
     <v>2845833</v>
     <v>1988</v>
   </rv>
@@ -4684,11 +4651,9 @@
     <v>4</v>
     <v>271.2</v>
     <v>158.83000000000001</v>
-    <v>1.6959</v>
-    <v>28.97</v>
-    <v>-5.0360000000000005E-3</v>
-    <v>0.1198</v>
-    <v>-1.3638999999999999</v>
+    <v>1.6673</v>
+    <v>29</v>
+    <v>0.119924</v>
     <v>USD</v>
     <v>Cloudflare, Inc. is a connectivity cloud company. The Company delivers a range of services to businesses of all sizes and in all geographies, enhancing the performance of business-critical applications. Its full suite of products consists of application services that help deliver security, performance, and reliability for any organization's applications connected to the Internet, including Websites and application programming interfaces (APIs) and its secure access service edge (SASE) platform, which contains its suite of and workplace security services and network services solutions to help ensure traffic in and out of an organization’s network and devices is verified and authorized and data is protected and secured, as well as to securely connect data centers, cloud services, and branch offices to an organization with its connectivity cloud. The Company also offers developer-based solutions which build and deploys serverless and artificial intelligence applications.</v>
     <v>5483</v>
@@ -4699,20 +4664,19 @@
     <v>271.2</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46174.905250844531</v>
+    <v>46174.999460404688</v>
     <v>54</v>
     <v>242.37</v>
-    <v>95715112298</v>
+    <v>95725716284</v>
     <v>CLOUDFLARE, INC.</v>
     <v>CLOUDFLARE, INC.</v>
     <v>244</v>
     <v>241.82</v>
-    <v>270.79000000000002</v>
-    <v>269.45609999999999</v>
+    <v>270.82</v>
     <v>353466200</v>
     <v>NET</v>
     <v>CLOUDFLARE, INC. (XNYS:NET)</v>
-    <v>8448146</v>
+    <v>42019</v>
     <v>4616957</v>
     <v>2009</v>
   </rv>
@@ -4742,11 +4706,9 @@
     <v>4</v>
     <v>225.14</v>
     <v>59.53</v>
-    <v>2.2896999999999998</v>
+    <v>2.2728000000000002</v>
     <v>14.43</v>
-    <v>2.5979999999999996E-3</v>
     <v>7.0389999999999994E-2</v>
-    <v>0.56999999999999995</v>
     <v>USD</v>
     <v>Marvell Technology, Inc. together with its consolidated subsidiaries, is a supplier of data infrastructure semiconductor solutions, spanning the data center core to network edge. It is engaged in the design, development and sale of integrated circuits. Its product offerings include custom application-specific integrated circuits (ASICs), interconnects, ethernet solutions, fiber channel adapters, processors and storage controllers. In addition, it is also developing Ultra Accelerator LinkTM (UALinkTM) switches and ethernet for scale-up networking (ESUN) switches for the emerging scale-out artificial intelligence market. Its solutions integrate multiple analogs, mixed-signal and digital intellectual property components incorporating hardware, firmware and software technologies and its system knowledge to provide its customers with integrated solutions for their end products. It designs and manufactures photonic integrated circuits for ultra-high-bandwidth and low-power applications.</v>
     <v>7480</v>
@@ -4757,21 +4719,20 @@
     <v>225.14</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46174.905536758597</v>
+    <v>46174.999998645311</v>
     <v>58</v>
     <v>195.12</v>
     <v>191957364000</v>
     <v>MARVELL TECHNOLOGY, INC.</v>
     <v>MARVELL TECHNOLOGY, INC.</v>
     <v>198.91</v>
-    <v>75.1601</v>
+    <v>75.159400000000005</v>
     <v>205</v>
     <v>219.43</v>
-    <v>220</v>
     <v>874800000</v>
     <v>MRVL</v>
     <v>MARVELL TECHNOLOGY, INC. (XNAS:MRVL)</v>
-    <v>32782129</v>
+    <v>8766323</v>
     <v>27637961</v>
     <v>2020</v>
   </rv>
@@ -4796,11 +4757,9 @@
     <v>4</v>
     <v>414.92</v>
     <v>262.74900000000002</v>
-    <v>1.1528</v>
+    <v>1.1428</v>
     <v>39.229999999999997</v>
-    <v>-3.9839999999999997E-3</v>
     <v>0.104633</v>
-    <v>-1.65</v>
     <v>USD</v>
     <v>Cadence Design Systems, Inc. is an electronic systems designing company. The Company applies its Intelligent System Design strategy to deliver software, hardware and intellectual property (IP) that turn design concepts into reality. Its product categories include Core Electronic Design Automation (EDA), Semiconductor IP, and System Design and Analysis (SD&amp;A). Core EDA includes software, hardware, and services used to design and verify a wide variety of semiconductors. The semiconductor IP portfolio includes silicon subsystems, software, and services that are used in semiconductor design. The SD&amp;A category provides solutions and services that enable the design and verification of complete electronic systems, from PCBs to complex system assemblies. Its semiconductors are used in various industries, including automotive, aerospace, biotech, hyperscale and cloud computing, data centers, telecommunications, medical technology, industrial Internet of things, and artificial intelligence (AI).</v>
     <v>13800</v>
@@ -4811,21 +4770,20 @@
     <v>414.92</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46174.90548295078</v>
+    <v>46174.999646550779</v>
     <v>61</v>
     <v>383.935</v>
     <v>114231954560</v>
     <v>CADENCE DESIGN SYSTEMS, INC.</v>
     <v>CADENCE DESIGN SYSTEMS, INC.</v>
     <v>393</v>
-    <v>96.687299999999993</v>
+    <v>96.686599999999999</v>
     <v>374.93</v>
     <v>414.16</v>
-    <v>412.51</v>
     <v>275816000</v>
     <v>CDNS</v>
     <v>CADENCE DESIGN SYSTEMS, INC. (XNAS:CDNS)</v>
-    <v>4517987</v>
+    <v>14511</v>
     <v>2401130</v>
     <v>1987</v>
   </rv>
@@ -4850,11 +4808,9 @@
     <v>4</v>
     <v>21.4</v>
     <v>11.81</v>
-    <v>0.83279999999999998</v>
+    <v>0.82709999999999995</v>
     <v>1.24</v>
-    <v>-1.2313000000000001E-2</v>
     <v>7.4924000000000004E-2</v>
-    <v>-0.21929999999999999</v>
     <v>USD</v>
     <v>SentinelOne, Inc. is an artificial intelligence (AI)-powered cybersecurity provider. The Company’s Singularity Platform delivers AI-powered autonomous threat prevention, detection, response, and exposure management capabilities across an organization’s endpoints, cloud workloads, and identity credentials. The Company’s Singularity platform ingests, correlates, and queries petabytes of structured and unstructured data from a myriad of ever-expanding disparate external and internal sources in real time. Its distributed AI models run both locally on every endpoint and every cloud workload, as well as on its cloud platform. The Company through PingSafe Pte. Ltd. (PingSafe), which is a cloud native application protection platform (CNAPP) to bolster its cloud security product suite. By adding PingSafe’s CNAPP to its Cloud Workload Security (CWS), it provides enterprises with a comprehensive cloud security coverage that drives security, improved posture, and autonomous protection.</v>
     <v>2700</v>
@@ -4865,7 +4821,7 @@
     <v>18.2</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46174.905477245309</v>
+    <v>46174.999854513284</v>
     <v>64</v>
     <v>17.014399999999998</v>
     <v>6098477823</v>
@@ -4874,11 +4830,10 @@
     <v>17.05</v>
     <v>16.55</v>
     <v>17.79</v>
-    <v>17.590699999999998</v>
     <v>342803700</v>
     <v>S</v>
     <v>SENTINELONE, INC. (XNYS:S)</v>
-    <v>15645932</v>
+    <v>33463</v>
     <v>8901995</v>
     <v>2013</v>
   </rv>
@@ -4919,11 +4874,9 @@
     <v>4</v>
     <v>327.98</v>
     <v>212.34</v>
-    <v>0.65790000000000004</v>
-    <v>22.39</v>
-    <v>-1.9099999999999999E-2</v>
-    <v>7.5185000000000002E-2</v>
-    <v>-6.12</v>
+    <v>0.65410000000000001</v>
+    <v>22.62</v>
+    <v>7.5956999999999997E-2</v>
     <v>USD</v>
     <v>International Business Machines Corporation is a provider of global hybrid cloud and artificial intelligence (AI) and consulting expertise. The Company’s segments include Software, Consulting, Infrastructure and Financing. The Software segment includes hybrid cloud and AI platforms, which allow clients to realize their digital and AI transformations across the applications, data, and environments in which they operate. The Consulting segment focuses on integrating skills on strategy, experience, technology and operations by domain and industry. The Infrastructure segment is focused on the hybrid cloud infrastructure market, providing on-premises and cloud-based server and storage solutions. In addition, it offers a portfolio of life-cycle services for hybrid cloud infrastructure deployment. The Financing segment provides client and commercial financing, facilitating its clients’ acquisition of hardware, software and services. It helps clients in more than 175 countries.</v>
     <v>286800</v>
@@ -4935,21 +4888,20 @@
     <v>69</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46174.905581909377</v>
+    <v>46174.999994907033</v>
     <v>70</v>
     <v>308</v>
-    <v>300941874207</v>
+    <v>301158047826</v>
     <v>INTERNATIONAL BUSINESS MACHINES CORPORATION</v>
     <v>INTERNATIONAL BUSINESS MACHINES CORPORATION</v>
     <v>322.55</v>
-    <v>25.6234</v>
+    <v>25.6418</v>
     <v>297.8</v>
-    <v>320.19</v>
-    <v>314.3</v>
+    <v>320.42</v>
     <v>939885300</v>
     <v>IBM</v>
     <v>INTERNATIONAL BUSINESS MACHINES CORPORATION (XNYS:IBM)</v>
-    <v>32757881</v>
+    <v>388049</v>
     <v>8807761</v>
     <v>1911</v>
   </rv>
@@ -4971,14 +4923,12 @@
     <v>2</v>
     <v>3</v>
     <v>Finance</v>
-    <v>14</v>
+    <v>4</v>
     <v>30.38</v>
     <v>13.29</v>
-    <v>1.4527000000000001</v>
+    <v>1.4414</v>
     <v>1.91</v>
-    <v>7.6160000000000004E-3</v>
     <v>7.8438999999999995E-2</v>
-    <v>0.2</v>
     <v>USD</v>
     <v>Five9, Inc. helps organizations to create hyper-personalized artificial intelligence (AI)-driven customer experiences. The Company's Intelligent CX Platform, powered by its Five9 Genius AI suite, delivers a comprehensive suite of applications that enable customer service, sales, and marketing functions. It delivers a comprehensive, end-to-end cloud software solution for contact centers. Comprised of its Intelligent CX Platform and AI capabilities, including agentic AI agents, Agent Assist, Workflow Automation (WFA), AI Insights, AI Summaries, Workforce Engagement Management (WEM), and Revenue Execution, its solution allows simultaneous management and optimization of customer interactions across voice, chat, email, web, social media and mobile channels, either directly or through its application programming interfaces (APIs). The Company's agent interface is a browser-based design that provides visualization of customer profiles, context and cross-channel history.</v>
     <v>2910</v>
@@ -4989,21 +4939,20 @@
     <v>26.93</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46174.894934976561</v>
+    <v>46174.999963564063</v>
     <v>73</v>
     <v>24.05</v>
     <v>2010570377</v>
     <v>FIVE9, INC.</v>
     <v>FIVE9, INC.</v>
     <v>25.15</v>
-    <v>36.9236</v>
+    <v>39.819899999999997</v>
     <v>24.35</v>
     <v>26.26</v>
-    <v>26.46</v>
     <v>76563990</v>
     <v>FIVN</v>
     <v>FIVE9, INC. (XNAS:FIVN)</v>
-    <v>4843956</v>
+    <v>15937</v>
     <v>4177529</v>
     <v>2001</v>
   </rv>
@@ -5026,9 +4975,7 @@
     <v>41.73</v>
     <v>3.11</v>
     <v>2.33</v>
-    <v>-1.7050000000000001E-3</v>
     <v>4.6165999999999999E-2</v>
-    <v>-0.09</v>
     <v>USD</v>
     <v>Tempus AI, Inc. is a technology company advancing precision medicine through the practical application of artificial intelligence in healthcare. It offers AI-enabled precision medicine solutions to physicians to deliver personalized patient care and, in parallel, facilitates discovery, development and delivery of optimal therapeutics. It provides three product lines: Genomics, Data and artificial intelligence applications (AI). The Genomics product line leverages its laboratories to provide next generation sequencing (NGS) diagnostics, polymerase chain reaction, profiling, molecular genotyping and other anatomic and molecular pathology testing. The data generated in its lab or ingested into its platform is structured and de-identified, prior to commercialization. Its AI Applications is focused on developing and providing diagnostics that are algorithmic in nature, implementing new software as a medical device, and building and deploying clinical decision support tools.</v>
     <v>3800</v>
@@ -5039,7 +4986,7 @@
     <v>54.7485</v>
     <v>Biotechnology &amp; Medical Research</v>
     <v>Stock</v>
-    <v>46174.90537412031</v>
+    <v>46174.999492673436</v>
     <v>48.4</v>
     <v>9481021440</v>
     <v>TEMPUS AI, INC.</v>
@@ -5048,11 +4995,10 @@
     <v>0</v>
     <v>50.47</v>
     <v>52.8</v>
-    <v>52.71</v>
     <v>179564800</v>
     <v>TEM</v>
     <v>TEMPUS AI, INC. (XNAS:TEM)</v>
-    <v>9704993</v>
+    <v>95971</v>
     <v>6197369</v>
     <v>2025</v>
   </rv>
@@ -5077,11 +5023,9 @@
     <v>4</v>
     <v>257.08999999999997</v>
     <v>110.36</v>
-    <v>1.0840000000000001</v>
+    <v>1.0750999999999999</v>
     <v>11.04</v>
-    <v>-5.9150000000000001E-3</v>
     <v>7.5518000000000002E-2</v>
-    <v>-0.93</v>
     <v>USD</v>
     <v>Workday, Inc. is an enterprise artificial intelligence (AI) platform for managing people, money, and agents. The Company provides organizations with cloud solutions powered by artificial intelligence (AI) to solve business challenges, including supporting and empowering the workforce, managing finances and spending. It offers a suite of cloud-based enterprise solutions that address the needs of the C-suite on a platform designed to be open, extensible, and configurable, allowing integration with other applications and the ability for customers and partners to build custom applications. It offers Workday Build, which is an open developer platform that provides customers and partners with the ability to create and share AI-powered solutions. It serves financial services, government, healthcare, higher education, hospitality, manufacturing, professional and business services, retail, technology and media, and transportation.</v>
     <v>20834</v>
@@ -5092,7 +5036,7 @@
     <v>158.63999999999999</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46174.905370520311</v>
+    <v>46174.999899443748</v>
     <v>78</v>
     <v>149.06</v>
     <v>38835810000</v>
@@ -5102,11 +5046,10 @@
     <v>49.0807</v>
     <v>146.19</v>
     <v>157.22999999999999</v>
-    <v>156.30000000000001</v>
     <v>247000000</v>
     <v>WDAY</v>
     <v>WORKDAY, INC. (XNAS:WDAY)</v>
-    <v>9300933</v>
+    <v>40015</v>
     <v>5256251</v>
     <v>2012</v>
   </rv>
@@ -5117,23 +5060,23 @@
     <v>https://www.bing.com/financeapi/forcetrigger?t=aodipr&amp;q=XLON%3aSGE&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
   </rv>
-  <rv s="9">
+  <rv s="1">
     <v>en-GB</v>
     <v>aodipr</v>
     <v>268435456</v>
     <v>1</v>
     <v>Powered by Refinitiv</v>
-    <v>15</v>
+    <v>0</v>
     <v>THE SAGE GROUP PLC. (XLON:SGE)</v>
     <v>2</v>
-    <v>16</v>
+    <v>14</v>
     <v>Finance</v>
-    <v>17</v>
+    <v>15</v>
     <v>1335</v>
     <v>771.66</v>
-    <v>0.35199999999999998</v>
-    <v>65.2</v>
-    <v>7.7397999999999995E-2</v>
+    <v>0.33879999999999999</v>
+    <v>-13</v>
+    <v>-1.4322999999999999E-2</v>
     <v>GBp</v>
     <v>The Sage Group plc is a United Kingdom-based company. It provides accounting, financial, human resources (HR) and payroll technology for small and mid-sized businesses. Its segments include North America, United Kingdom, Ireland, Africa and APAC (UKIA) and Europe. Its products include Sage Accounting, Payroll software, Sage Intacct, Sage X3, Sage HR, Sage People, Sage Earth, Sage Ai and Payments and Banking. Sage Accounting is designed to enable small businesses operating in any industry, and accountants and bookkeepers, to manage customer data, accounts, and people in a single solution. Sage Intacct helps growing mid-sized organizations thrive in with digital world with solutions across accounting, planning, and analytics. Sage People is an HR and people management solution for mid-sized businesses. Sage Payroll is an intuitive solution that helps small businesses to run their payroll reliably and flexibly. Sage People is an HR and people management solution for mid-sized businesses.</v>
     <v>11074</v>
@@ -5141,23 +5084,23 @@
     <v>XLON</v>
     <v>XLON</v>
     <v>C23-5 &amp; 6 Cobalt Park Way, Cobalt Park, NEWCASTLE UPON TYNE, NORTHUMBERLAND, NE28 9EJ GB</v>
-    <v>907.6</v>
+    <v>918.6</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46174.556574154689</v>
+    <v>46175.476106539063</v>
     <v>81</v>
-    <v>846.6</v>
+    <v>893.2</v>
     <v>10571700000</v>
     <v>THE SAGE GROUP PLC.</v>
     <v>THE SAGE GROUP PLC.</v>
-    <v>846.6</v>
-    <v>24.144500000000001</v>
-    <v>842.4</v>
+    <v>916.8</v>
+    <v>0</v>
     <v>907.6</v>
-    <v>905653600</v>
+    <v>894.6</v>
+    <v>907731600</v>
     <v>SGE</v>
     <v>THE SAGE GROUP PLC. (XLON:SGE)</v>
-    <v>3968492</v>
+    <v>476451</v>
     <v>4875910</v>
     <v>1988</v>
   </rv>
@@ -5182,11 +5125,9 @@
     <v>4</v>
     <v>179.8</v>
     <v>85.58</v>
-    <v>1.6120000000000001</v>
-    <v>11.24</v>
-    <v>2.4610000000000001E-3</v>
-    <v>7.0483000000000004E-2</v>
-    <v>0.42</v>
+    <v>1.6085</v>
+    <v>11.21</v>
+    <v>7.0294999999999996E-2</v>
     <v>USD</v>
     <v>Arista Networks, Inc. is a provider of data-driven, client-to-cloud networking for large artificial intelligence (AI), data center, campus and routing environments. Its platforms deliver availability, agility, automation, analytics, and security through an advanced network operating stack. Its platform is its Extensible Operating System (EOS), a modernized publish-subscribe state-sharing networking operating system. Its portfolio of products, services and technologies is grouped into various categories: Core (Data Center, Cloud and AI Networking), Cognitive Adjacencies (Campus and Routing), and Cognitive Network (Software and Services). It offers product portfolios of data-driven, high-speed, cloud and data center Ethernet switches. Its Cognitive Adjacencies include Cognitive Campus Switching, Cloud-Grade Routing and WAN Routing. Its software and services are based on subscription-based models and include various offerings: CloudVision, Arista A-Care Services, CloudEOS and others.</v>
     <v>5115</v>
@@ -5197,21 +5138,20 @@
     <v>172.33</v>
     <v>Communications &amp; Networking</v>
     <v>Stock</v>
-    <v>46174.905671469533</v>
+    <v>46174.999933367966</v>
     <v>84</v>
     <v>161.28</v>
-    <v>214958544130</v>
+    <v>214920768040</v>
     <v>ARISTA NETWORKS, INC.</v>
     <v>ARISTA NETWORKS, INC.</v>
     <v>162.13999999999999</v>
-    <v>58.470300000000002</v>
+    <v>58.459499999999998</v>
     <v>159.47</v>
-    <v>170.71</v>
-    <v>171.1</v>
+    <v>170.68</v>
     <v>1259203000</v>
     <v>ANET</v>
     <v>ARISTA NETWORKS, INC. (XNYS:ANET)</v>
-    <v>9963116</v>
+    <v>65024</v>
     <v>12062738</v>
     <v>2011</v>
   </rv>
@@ -5236,11 +5176,9 @@
     <v>4</v>
     <v>1046.97</v>
     <v>94.4</v>
-    <v>2.1657999999999999</v>
-    <v>63.74</v>
-    <v>3.9589999999999998E-3</v>
-    <v>6.5643999999999994E-2</v>
-    <v>4.0999999999999996</v>
+    <v>2.1707000000000001</v>
+    <v>64.5</v>
+    <v>6.6425999999999999E-2</v>
     <v>USD</v>
     <v>Micron Technology, Inc. provides memory and storage solutions. The Company delivers a portfolio of high-performance dynamic random-access memory (DRAM), NAND, and NOR memory and storage products through its Micron and Crucial brands. The Company's products enable advancing in artificial intelligence (AI) and compute-intensive applications. Its segments include Cloud Memory Business Unit (CMBU), Core Data Center Business Unit (CDBU), Mobile and Client Business Unit (MCBU) and Automotive and Embedded Business Unit (AEBU). CMBU is focused on memory solutions for large hyperscale cloud customers, and high bandwidth memory (HBM) for all data center customers. CDBU is focused on memory solutions for mid-tier cloud, enterprise, and OEM data center customers and storage solutions for all data center customers. MCBU is focused on memory and storage solutions for mobile and client segments. AEBU is focused on memory and storage solutions for the automotive, industrial, and consumer segments.</v>
     <v>53000</v>
@@ -5251,21 +5189,20 @@
     <v>1046.97</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46174.905713008593</v>
+    <v>46174.999994027341</v>
     <v>87</v>
     <v>1009.5</v>
-    <v>1166911479160</v>
+    <v>1167768557000</v>
     <v>MICRON TECHNOLOGY, INC.</v>
     <v>MICRON TECHNOLOGY, INC.</v>
     <v>1009.72</v>
-    <v>48.851599999999998</v>
+    <v>48.887500000000003</v>
     <v>971</v>
-    <v>1034.74</v>
-    <v>1039.5999999999999</v>
+    <v>1035.5</v>
     <v>1127734000</v>
     <v>MU</v>
     <v>MICRON TECHNOLOGY, INC. (XNAS:MU)</v>
-    <v>46227755</v>
+    <v>1507152</v>
     <v>52465522</v>
     <v>1984</v>
   </rv>
@@ -5290,11 +5227,9 @@
     <v>4</v>
     <v>9.39</v>
     <v>3.01</v>
-    <v>3.0739999999999998</v>
-    <v>0.31</v>
-    <v>-1.8729999999999999E-3</v>
-    <v>6.1508E-2</v>
-    <v>-0.01</v>
+    <v>3.0806</v>
+    <v>0.3</v>
+    <v>5.9524000000000001E-2</v>
     <v>USD</v>
     <v>BigBear.ai Holdings, Inc. operates as a specialized provider of artificial intelligence (AI) technology. The Company provides decision intelligence solutions for supply chains and logistics, enterprise operations, manned-unmanned teaming in autonomous systems, and cybersecurity. Its solutions include AI orchestration and sensor function, digital identity management, computer vision, cybersecurity, predictive intelligence, modeling &amp; simulation, enterprise automation and professional services. It offers Trueface, which performs one-to-many (1:N) facial matches with real-time photos, delivering identity verification. It also offers veriScan, which captures and transmits real-time photos into a biometric matching service supporting access control and biometric boarding/bag tags. The Company serves homeland &amp; border security, defense, intelligence, manufacturing &amp; suppy chain, travel and trade industries.</v>
     <v>579</v>
@@ -5305,20 +5240,19 @@
     <v>5.46</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46174.905670010936</v>
+    <v>46174.999977707812</v>
     <v>90</v>
     <v>5.01</v>
-    <v>2562379825</v>
+    <v>2557590330</v>
     <v>BIGBEAR.AI HOLDINGS, INC.</v>
     <v>BIGBEAR.AI HOLDINGS, INC.</v>
     <v>5.17</v>
     <v>5.04</v>
-    <v>5.35</v>
-    <v>5.33</v>
+    <v>5.34</v>
     <v>478949500</v>
     <v>BBAI</v>
     <v>BIGBEAR.AI HOLDINGS, INC. (XNYS:BBAI)</v>
-    <v>83209853</v>
+    <v>831399</v>
     <v>46748790</v>
     <v>2020</v>
   </rv>
@@ -5343,11 +5277,9 @@
     <v>4</v>
     <v>96.69</v>
     <v>48.3</v>
-    <v>2.1486999999999998</v>
+    <v>2.1423000000000001</v>
     <v>3.49</v>
-    <v>3.9649999999999999E-4</v>
     <v>4.8350999999999998E-2</v>
-    <v>0.03</v>
     <v>USD</v>
     <v>Ambarella, Inc. is a developer of low-power system-on-a-chip (SoC) semiconductors and software for edge artificial intelligence (AI) applications. The Company's technologies make electronic systems smarter, enabling them to become partially or fully autonomous with features, such as person detection, object classification, and analytics, in addition to performing complex data analysis in real time, delivering imagery, and preserving vital system resources, such as power and network bandwidth. It specializes in the development of deployable, scalable designs for intelligent electronic systems that utilize high-bandwidth sensors. Its products are used in a variety of human viewing, computer vision and edge AI applications, including a variety of automotive camera systems, video security cameras, mobile and fixed robots, industrial applications, and consumer devices, such as action, drone, and 360-degree cameras.</v>
     <v>959</v>
@@ -5358,7 +5290,7 @@
     <v>77.989999999999995</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46174.905091955472</v>
+    <v>46174.999917765628</v>
     <v>93</v>
     <v>72.25</v>
     <v>3318998191</v>
@@ -5368,11 +5300,10 @@
     <v>0</v>
     <v>72.180000000000007</v>
     <v>75.67</v>
-    <v>75.7</v>
     <v>43861480</v>
     <v>AMBA</v>
     <v>AMBARELLA, INC. (XNAS:AMBA)</v>
-    <v>2889436</v>
+    <v>17577</v>
     <v>1300795</v>
     <v>2004</v>
   </rv>
@@ -5397,11 +5328,9 @@
     <v>4</v>
     <v>236.54</v>
     <v>135.4</v>
-    <v>2.2155999999999998</v>
+    <v>2.1993999999999998</v>
     <v>13.22</v>
-    <v>4.4569999999999999E-4</v>
     <v>6.2612000000000001E-2</v>
-    <v>0.1</v>
     <v>USD</v>
     <v>NVIDIA Corporation is an artificial intelligence (AI) infrastructure company. The Company is engaged in accelerated computing to help solve the challenging computational problems. Its segments include Compute &amp; Networking and Graphics. The Compute &amp; Networking segment includes its Data Center accelerated computing and networking platforms and AI solutions and software, and automotive platforms and autonomous and electric vehicle solutions, including software. The Graphics segment includes GeForce GPUs for gaming and personal computers (PCs), and Quadro/NVIDIA RTX GPUs for enterprise workstation graphics. Its technology stack includes the foundational NVIDIA CUDA development platform that runs on all NVIDIA GPUs, as well as hundreds of domain-specific software libraries, frameworks, algorithms, software development kits (SDKs), and application programming interfaces (APIs). Its platforms address four markets, which include Data Center, Gaming, Professional Visualization, and Automotive.</v>
     <v>42000</v>
@@ -5412,21 +5341,20 @@
     <v>224.87</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46174.905683853904</v>
+    <v>46174.999987071096</v>
     <v>96</v>
     <v>215.7</v>
     <v>5429512000000</v>
     <v>NVIDIA CORPORATION</v>
     <v>NVIDIA CORPORATION</v>
     <v>215.73</v>
-    <v>34.3583</v>
+    <v>34.358499999999999</v>
     <v>211.14</v>
     <v>224.36</v>
-    <v>224.46</v>
     <v>24200000000</v>
     <v>NVDA</v>
     <v>NVIDIA CORPORATION (XNAS:NVDA)</v>
-    <v>211381795</v>
+    <v>5918878</v>
     <v>170214952</v>
     <v>1998</v>
   </rv>
@@ -5451,11 +5379,9 @@
     <v>4</v>
     <v>18.709</v>
     <v>0.93010000000000004</v>
-    <v>3.0709</v>
+    <v>2.3961000000000001</v>
     <v>0.16</v>
-    <v>3.0672000000000001E-2</v>
     <v>1.4733000000000001E-2</v>
-    <v>0.33800000000000002</v>
     <v>USD</v>
     <v>Lightwave Logic, Inc. is a technology platform company leveraging its proprietary engineered electro-optic (EO) polymers known as Perkinamine, to transmit data at higher speeds with less power in a small form factor. The Company’s organic polymers allow it to create next-generation photonic EO devices that convert data from electrical signals into light/optical signals for applications in telecommunications, and for data transmission potentially used to support generative Artificial Intelligence. It designs its own proprietary materials for electro-optical modulation devices. Electro-optical modulators convert data from electric signals into optical signals that can then be transmitted over high-speed fiber-optic cables. It is focused on testing and demonstrating the manufacturability and reliability of its devices. In polymer photonics, polymer devices such as modulators, waveguides, and multiplexers can be fabricated on to a silicon platform.</v>
     <v>34</v>
@@ -5466,7 +5392,7 @@
     <v>11.78</v>
     <v>Electronic Equipment &amp; Parts</v>
     <v>Stock</v>
-    <v>46174.905646585154</v>
+    <v>46174.999897673435</v>
     <v>99</v>
     <v>10.220000000000001</v>
     <v>1697957192</v>
@@ -5476,11 +5402,10 @@
     <v>0</v>
     <v>10.86</v>
     <v>11.02</v>
-    <v>11.358000000000001</v>
     <v>154079600</v>
     <v>LWLG</v>
     <v>LIGHTWAVE LOGIC, INC. (XNAS:LWLG)</v>
-    <v>6329907</v>
+    <v>216199</v>
     <v>8992398</v>
     <v>1997</v>
   </rv>
@@ -5505,11 +5430,9 @@
     <v>4</v>
     <v>16.489999999999998</v>
     <v>4.6150000000000002</v>
-    <v>2.2595999999999998</v>
+    <v>2.2097000000000002</v>
     <v>0.6</v>
-    <v>6.5269999999999998E-4</v>
     <v>7.5187999999999991E-2</v>
-    <v>5.5999999999999999E-3</v>
     <v>USD</v>
     <v>Enovix Corporation is a high-performance battery company. The Company is focused on designing, developing, manufacturing, and commercializing Lithium-ion, or Li-ion, batteries, including silicon-anode architectures, for smartphones, smart eyewear, defense, industrial and emerging edge artificial intelligence (AI) applications. Its silicon-anode battery architecture enables energy density and performance relative to conventional battery cells, particularly in space-constrained devices. It focuses on developing a battery architecture that allows the use of active silicon and no graphite in the battery's anode, which is the negative electrode that stores lithium ions when a battery is charged. Its AI-1 battery platform is architected as a unified silicon-anode platform designed to address the high-performance consumer electronics and defense applications. The AI-1 platform is designed to support AI-enabled smartphones and smart eyewear, as well as other edge-AI devices.</v>
     <v>664</v>
@@ -5520,7 +5443,7 @@
     <v>8.6300000000000008</v>
     <v>Machinery, Equipment &amp; Components</v>
     <v>Stock</v>
-    <v>46174.905093657035</v>
+    <v>46174.999383402341</v>
     <v>102</v>
     <v>7.63</v>
     <v>1871756172</v>
@@ -5530,11 +5453,10 @@
     <v>0</v>
     <v>7.98</v>
     <v>8.58</v>
-    <v>8.5855999999999995</v>
     <v>218153400</v>
     <v>ENVX</v>
     <v>Enovix Corporation (XNAS:ENVX)</v>
-    <v>13239008</v>
+    <v>94455</v>
     <v>7439160</v>
     <v>2020</v>
   </rv>
@@ -5560,10 +5482,8 @@
     <v>449.39</v>
     <v>192.19499999999999</v>
     <v>1.3918999999999999</v>
-    <v>17.600000000000001</v>
-    <v>7.254E-3</v>
-    <v>4.2060000000000007E-2</v>
-    <v>3.16</v>
+    <v>17.18</v>
+    <v>4.1056000000000002E-2</v>
     <v>USD</v>
     <v>Taiwan Semiconductor Manufacturing Co Ltd is a Taiwan-based integrated circuit foundry service provider. The Company is primarily engaged in integrated circuit manufacturing services. It offers advanced process technologies, specialised process solutions, advanced photomask and silicon stacking, and packaging-related technologies, while supporting a comprehensive design ecosystem. The Company's products serve diverse electronic sectors including artificial intelligence, high-performance computing, wired and wireless communications, automotive and industrial equipment, personal computing, information applications, consumer electronics, smart internet of things, and wearable devices.</v>
     <v>52045</v>
@@ -5574,21 +5494,20 @@
     <v>449.39</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46174.905637753909</v>
+    <v>46174.999991492972</v>
     <v>105</v>
     <v>422.5</v>
-    <v>2261561987700</v>
+    <v>2259383668620</v>
     <v>Taiwan Semiconductor Manufacturing Company Limited</v>
     <v>Taiwan Semiconductor Manufacturing Company Limited</v>
     <v>424.88</v>
-    <v>36.893700000000003</v>
+    <v>36.8583</v>
     <v>418.45</v>
-    <v>436.05</v>
-    <v>438.79</v>
+    <v>435.63</v>
     <v>5186474000</v>
     <v>TSM</v>
     <v>Taiwan Semiconductor Manufacturing Company Limited (XNYS:TSM)</v>
-    <v>18002766</v>
+    <v>223095</v>
     <v>13359271</v>
     <v>1987</v>
   </rv>
@@ -5629,11 +5548,9 @@
     <v>4</v>
     <v>421.48</v>
     <v>224.13</v>
-    <v>1.4177999999999999</v>
+    <v>1.3987000000000001</v>
     <v>14.82</v>
-    <v>-1.7210000000000001E-3</v>
     <v>5.7173999999999996E-2</v>
-    <v>-0.47170000000000001</v>
     <v>USD</v>
     <v>Adobe Inc. is a global technology company. The Company's products, services and solutions are used around the world to imagine, create, manage, deliver, measure, optimize and engage with content across surfaces and fuel digital experiences. Its segments include Digital Media, Digital Experience, and Publishing and Advertising. The Digital Media segment is centered around Adobe Creative Cloud and Adobe Document Cloud, which include Adobe Express, Adobe Firefly, Photoshop and other products, offering a variety of tools for creative professionals, communicators and other consumers. The Digital Experience segment provides an integrated platform and set of products, services and solutions through Adobe Experience Cloud. The Publishing and Advertising segment contains legacy products and services. In addition, its Adobe GenStudio solution allows businesses to simplify their content supply chain process with generative artificial intelligence (AI) capabilities and intelligent automation.</v>
     <v>31360</v>
@@ -5645,21 +5562,20 @@
     <v>110</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46174.9055028125</v>
+    <v>46174.999709687501</v>
     <v>111</v>
     <v>262.3</v>
     <v>110762925999</v>
     <v>ADOBE INC.</v>
     <v>ADOBE INC.</v>
     <v>270</v>
-    <v>15.9716</v>
+    <v>15.9717</v>
     <v>259.20999999999998</v>
     <v>274.02999999999997</v>
-    <v>273.55829999999997</v>
     <v>404200000</v>
     <v>ADBE</v>
     <v>ADOBE INC. (XNAS:ADBE)</v>
-    <v>8507886</v>
+    <v>84049</v>
     <v>4715108</v>
     <v>1997</v>
   </rv>
@@ -5684,11 +5600,9 @@
     <v>4</v>
     <v>147.49</v>
     <v>70.12</v>
-    <v>1.1131</v>
+    <v>1.1052</v>
     <v>9.17</v>
-    <v>7.4759999999999996E-4</v>
     <v>6.6463999999999995E-2</v>
-    <v>0.11</v>
     <v>USD</v>
     <v>Fortinet, Inc. is engaged in cybersecurity, driving the convergence of networking and security. The Company's integrated platform, Fortinet Security Fabric, spans secure networking, unified secure access service edge (SASE), and artificial intelligence (AI)-driven security operations (SecOps). Its products and services include FortiOS, FortiASIC, FortiCloud, FortiAI, FortiEndpoint, and OT Security. The FortiGuard Labs is a cybersecurity threat intelligence and research organization comprised of experienced threat hunters, researchers, analysts, engineers, and data scientists who develop and utilize machine learning and AI technologies. FortiGuard and Other Security Services is an AI-powered security that is integrated as part of the Fortinet Security Fabric to deliver detection and enforcement across the entire attack surface. FortiCare Technical Support Service is a technical support service which provides customers with access to operations and maintenance of Fortinet solutions.</v>
     <v>15311</v>
@@ -5699,21 +5613,20 @@
     <v>147.49</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46174.905388367966</v>
+    <v>46174.998533633596</v>
     <v>114</v>
     <v>140.25</v>
     <v>107801885575</v>
     <v>FORTINET, INC.</v>
     <v>FORTINET, INC.</v>
     <v>141.16</v>
-    <v>56.8459</v>
+    <v>56.847000000000001</v>
     <v>137.97</v>
     <v>147.13999999999999</v>
-    <v>147.25</v>
     <v>732648400</v>
     <v>FTNT</v>
     <v>FORTINET, INC. (XNAS:FTNT)</v>
-    <v>7533997</v>
+    <v>11846</v>
     <v>6310039</v>
     <v>2000</v>
   </rv>
@@ -5738,11 +5651,9 @@
     <v>4</v>
     <v>302.95</v>
     <v>139.57060000000001</v>
-    <v>0.94020000000000004</v>
+    <v>0.9395</v>
     <v>18.79</v>
-    <v>8.9859999999999994E-4</v>
     <v>6.6705E-2</v>
-    <v>0.27</v>
     <v>USD</v>
     <v>Palo Alto Networks, Inc. is a global artificial intelligence (AI) cybersecurity company, with a comprehensive portfolio of cybersecurity solutions and platforms across network, cloud, security operations, AI and Identity. Its network security platform includes Secure Access Service Edge (SASE), Next-Generation Firewalls, Cloud Delivered Security Services (CDSS), Prisma AIRS, and Strata Cloud Manager (SCM). It delivers security operations capabilities that unifies standalone Security Information and Event Management (SIEM) tools, endpoint security, security automation, cloud detection and response (CDR), as well as attack surface management (ASM) capabilities on its Cortex platform. It delivers comprehensive security across the cloud application development lifecycle through Cortex Cloud. Its Unit 42 brings together expertise across threat research, incident response, and security consulting to deliver intelligence-driven, response-ready outcomes that help customers reduce cyber risk.</v>
     <v>17027</v>
@@ -5753,21 +5664,20 @@
     <v>302.95</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46174.905591585157</v>
+    <v>46174.999922962503</v>
     <v>117</v>
     <v>283.8</v>
     <v>243689280000</v>
     <v>PALO ALTO NETWORKS, INC.</v>
     <v>PALO ALTO NETWORKS, INC.</v>
     <v>285.42500000000001</v>
-    <v>155.97880000000001</v>
+    <v>166.38329999999999</v>
     <v>281.69</v>
     <v>300.48</v>
-    <v>300.75</v>
     <v>811000000</v>
     <v>PANW</v>
     <v>PALO ALTO NETWORKS, INC. (XNAS:PANW)</v>
-    <v>13666862</v>
+    <v>142043</v>
     <v>7979332</v>
     <v>2005</v>
   </rv>
@@ -5792,11 +5702,9 @@
     <v>4</v>
     <v>155.47</v>
     <v>74.510000000000005</v>
-    <v>0.6532</v>
+    <v>0.64800000000000002</v>
     <v>4.7300000000000004</v>
-    <v>8.5950000000000002E-3</v>
     <v>4.3278999999999998E-2</v>
-    <v>0.98</v>
     <v>USD</v>
     <v>Qualys, Inc. is a provider of a cloud-based platform delivering information technology (IT), security and compliance solutions. The Company’s integrated suite of IT, security and compliance solutions delivered on Qualys' Enterprise TruRisk Platform enables its customers to identify and manage their IT and operational technology (OT) assets, collect, and analyze large amounts of IT security data, recommend, and implement remediation actions and verify the implementation of such actions. The Company provides its solutions through a software-as-a-service model, primarily with renewable annual subscriptions. Its cloud platform offers an integrated suite of solutions that automates the lifecycle of asset discovery and management, security and compliance assessments, and remediation for an organization’s IT infrastructure and assets, whether such infrastructure and assets reside inside the organization, on their network perimeter, on endpoints or in the cloud.</v>
     <v>2683</v>
@@ -5807,7 +5715,7 @@
     <v>115.89</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46174.903102349221</v>
+    <v>46174.977704039062</v>
     <v>120</v>
     <v>110.9731</v>
     <v>4015443480</v>
@@ -5817,11 +5725,10 @@
     <v>20.474399999999999</v>
     <v>109.29</v>
     <v>114.02</v>
-    <v>115</v>
     <v>35217010</v>
     <v>QLYS</v>
     <v>QUALYS, INC. (XNAS:QLYS)</v>
-    <v>979300</v>
+    <v>654</v>
     <v>791597</v>
     <v>1999</v>
   </rv>
@@ -5846,11 +5753,9 @@
     <v>4</v>
     <v>785.66</v>
     <v>342.72</v>
-    <v>1.2517</v>
+    <v>1.2404999999999999</v>
     <v>51.17</v>
-    <v>-3.4139999999999999E-3</v>
     <v>7.0000000000000007E-2</v>
-    <v>-2.67</v>
     <v>USD</v>
     <v>CrowdStrike Holdings, Inc. is a global cybersecurity company that provides cloud-delivered protection of endpoints, cloud workloads, identity and data. Its Falcon platform is designed for cybersecurity consolidation, purpose-built to stop breaches. The platforms collect and integrate data from across the enterprise, including endpoints, cloud workloads, identities, and third-party sources. It offers 29 cloud modules on its Falcon platform via a software as a service (SaaS) subscription-based model that spans multiple large markets, including corporate endpoint and cloud workload security, managed security services, security and vulnerability management, information technology (IT) operations management, identity protection, next-generation security information and event management (SIEM) and log management, threat intelligence services, data protection, SaaS security posture management, automation and response (SOAR) and artificial intelligence powered workflow automation, and others.</v>
     <v>10698</v>
@@ -5861,7 +5766,7 @@
     <v>785.66</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46174.904037707813</v>
+    <v>46174.999823657032</v>
     <v>123</v>
     <v>734</v>
     <v>199090814205</v>
@@ -5871,11 +5776,10 @@
     <v>0</v>
     <v>731</v>
     <v>782.17</v>
-    <v>779.5</v>
     <v>254536500</v>
     <v>CRWD</v>
     <v>CROWDSTRIKE HOLDINGS, INC. (XNAS:CRWD)</v>
-    <v>4573482</v>
+    <v>42915</v>
     <v>3017412</v>
     <v>2011</v>
   </rv>
@@ -5900,11 +5804,9 @@
     <v>4</v>
     <v>22.17</v>
     <v>5.83</v>
-    <v>2.7349999999999999</v>
+    <v>2.7391999999999999</v>
     <v>0.25</v>
-    <v>2.0860000000000002E-3</v>
     <v>2.7778000000000001E-2</v>
-    <v>1.9300000000000001E-2</v>
     <v>USD</v>
     <v>SoundHound AI, Inc. is engaged in conversational intelligence, offering voice and conversational artificial intelligence (AI) solutions that let businesses offer experiences to their customers. Through its proprietary technology, its voice AI delivers speed and accuracy in numerous languages to product creators and service providers across retail, financial services, healthcare, automotive, smart devices, and restaurants via AI-driven products, such as Smart Answering, Smart Ordering, Dynamic Drive Thru, and Amelia AI Agents. Along with SoundHound Chat AI, a voice assistant with integrated Generative AI, it powers various products and services, and processes billions of interactions each year for businesses. Its developer platform, Houndify, is an open-access platform that allows developers to leverage its Voice AI technology and a library of over 100 content domains, including commonly used domains for points of interest, weather, flight status, sports and more.</v>
     <v>954</v>
@@ -5915,7 +5817,7 @@
     <v>9.52</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46174.905622164064</v>
+    <v>46174.999993772653</v>
     <v>126</v>
     <v>8.8149999999999995</v>
     <v>4003118800</v>
@@ -5925,11 +5827,10 @@
     <v>0</v>
     <v>9</v>
     <v>9.25</v>
-    <v>9.2692999999999994</v>
     <v>432769600</v>
     <v>SOUN</v>
     <v>SOUNDHOUND AI, INC. (XNAS:SOUN)</v>
-    <v>33877459</v>
+    <v>404432</v>
     <v>29985575</v>
     <v>2020</v>
   </rv>
@@ -5954,11 +5855,9 @@
     <v>4</v>
     <v>57.42</v>
     <v>8.85</v>
-    <v>2.2128999999999999</v>
+    <v>2.2183000000000002</v>
     <v>0.22</v>
-    <v>-7.7579999999999999E-4</v>
     <v>1.7364000000000001E-2</v>
-    <v>-0.01</v>
     <v>USD</v>
     <v>NuScale Power Corporation is a provider of proprietary advanced small modular reactor (SMR) nuclear technology. The NuScale Power Module, the Company's SMR technology, is a small pressurized water reactor that can generate approximately 77 megawatts of electricity (MWe) or 250 megawatts thermal (gross) and can be scaled to meet customer needs through an array of flexible configurations of up to 924 MWe (12 modules) of output. In addition to the sale of NPMs, it offers a diversified suite of services throughout the development and operating life of the power plant. The Company's suite of services is planned to include licensing support, testing, training, fuel supply services and program management, among others. It serves a range of customers consisting of domestic and international governments, utilities, state-owned enterprises and technology and industrial companies in need of carbon-free, reliable energy.</v>
     <v>428</v>
@@ -5969,7 +5868,7 @@
     <v>13.4</v>
     <v>Electrical Utilities &amp; IPPs</v>
     <v>Stock</v>
-    <v>46174.905608310153</v>
+    <v>46174.999944745316</v>
     <v>129</v>
     <v>11.98</v>
     <v>4711052668</v>
@@ -5979,11 +5878,10 @@
     <v>0</v>
     <v>12.67</v>
     <v>12.89</v>
-    <v>12.88</v>
     <v>365481200</v>
     <v>SMR</v>
     <v>NUSCALE POWER CORPORATION (XNYS:SMR)</v>
-    <v>41351160</v>
+    <v>990612</v>
     <v>31458700</v>
     <v>2022</v>
   </rv>
@@ -6006,9 +5904,7 @@
     <v>36.207000000000001</v>
     <v>2.73</v>
     <v>66.45</v>
-    <v>2.2599999999999999E-3</v>
     <v>3.9203999999999996E-2</v>
-    <v>3.98</v>
     <v>USD</v>
     <v>SanDisk Corporation is a developer, manufacturer and provider of data storage devices and solutions based on NAND flash technology and has consumer brands and franchises globally. The Company's solutions include a range of solid state drives (SSDs) embedded products, removable cards, universal serial bus (USB) drives, and wafers and components. Its broad portfolio of technology and products addresses multiple end markets of Datacenter, Edge and Consumer. Its Datacenter end market is composed primarily of products for public or private cloud environments and enterprise customers. The Company, through the Edge end market, provides original equipment manufacturer and channel customers a broad array of high-performance flash solutions across personal computer, mobile, gaming, automotive, virtual reality headsets, at-home entertainment, and industrial spaces. The Company serves the Consumer end market with a broad range of retail and other end-user products.</v>
     <v>11000</v>
@@ -6019,20 +5915,19 @@
     <v>1804</v>
     <v>Computers, Phones &amp; Household Electronics</v>
     <v>Stock</v>
-    <v>46174.905683390622</v>
+    <v>46174.999994803125</v>
     <v>1686.16</v>
     <v>260849816414</v>
     <v>SANDISK CORPORATION</v>
     <v>SANDISK CORPORATION</v>
     <v>1731.15</v>
-    <v>59.9238</v>
+    <v>62.273099999999999</v>
     <v>1694.98</v>
     <v>1761.43</v>
-    <v>1765.41</v>
     <v>148089800</v>
     <v>SNDK</v>
     <v>SANDISK CORPORATION (XNAS:SNDK)</v>
-    <v>9637122</v>
+    <v>273723</v>
     <v>14284176</v>
     <v>2024</v>
   </rv>
@@ -6057,11 +5952,9 @@
     <v>4</v>
     <v>7.18</v>
     <v>2.77</v>
-    <v>1.04</v>
+    <v>0.99950000000000006</v>
     <v>0.2</v>
-    <v>-5.2769999999999996E-3</v>
     <v>5.5709999999999996E-2</v>
-    <v>-0.02</v>
     <v>USD</v>
     <v>Recursion Pharmaceuticals, Inc. is a clinical-stage TechBio company decoding biology and chemistry to industrialize drug discovery. Its Recursion Operating System (OS), a platform built across diverse technologies, enables the Company to map and navigate trillions of biological and chemical relationships within the Recursion Data Universe. The Company integrates physical and digital components as iterative loops of atoms and bits, scaling wet lab biology and chemistry data organized into virtuous cycles with computational tools to rapidly translate silico hypotheses into validated insights and novel chemistry. Its clinical programs in oncology and rare diseases include REC-617, REC-1245, REC-3565 and REC-4539. Its REC-617 is an orally bioavailable, cyclin-dependent kinase 7 (CDK7) inhibitor for the treatment of advanced solid tumors. Its REV102 program targets ectonucleotide pyrophosphatase/phosphodiesterase 1 (ENPP1), an enzyme implicated in the pathogenesis of HPP.</v>
     <v>600</v>
@@ -6072,7 +5965,7 @@
     <v>3.85</v>
     <v>Biotechnology &amp; Medical Research</v>
     <v>Stock</v>
-    <v>46174.90564188594</v>
+    <v>46174.999510902344</v>
     <v>134</v>
     <v>3.45</v>
     <v>2008340708</v>
@@ -6082,11 +5975,10 @@
     <v>0</v>
     <v>3.59</v>
     <v>3.79</v>
-    <v>3.77</v>
     <v>529905200</v>
     <v>RXRX</v>
     <v>RECURSION PHARMACEUTICALS, INC. (XNAS:RXRX)</v>
-    <v>30784543</v>
+    <v>314465</v>
     <v>15807701</v>
     <v>2013</v>
   </rv>
@@ -6108,14 +6000,12 @@
     <v>2</v>
     <v>3</v>
     <v>Finance</v>
-    <v>14</v>
+    <v>16</v>
     <v>57.55</v>
     <v>31.635000000000002</v>
-    <v>0.75149999999999995</v>
+    <v>0.73699999999999999</v>
     <v>1.88</v>
-    <v>1.124E-3</v>
     <v>4.4142000000000001E-2</v>
-    <v>0.05</v>
     <v>USD</v>
     <v>Dynatrace, Inc. is an artificial intelligence (AI)-powered observability platform. It is advancing observability for digital businesses and transforming the complexity of modern digital ecosystems into business assets. It enables organizations to analyze and automate. Its platform combines broad and deep observability, continuous runtime application security, and advanced AI to support information technology (IT) operations, development, security, and business teams, enabling organizations to optimize cloud and IT operations, accelerate secure software delivery, and improve digital performance. Its platform's solutions include infrastructure observability, application observability, AI observability, digital experience, business analytics, software delivery, threat observability, application security, and log management. Its application security detects, analyses, and remediates runtime application vulnerabilities and attacks in real time.</v>
     <v>5600</v>
@@ -6126,21 +6016,20 @@
     <v>44.84</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46174.890703553123</v>
+    <v>46174.999616041408</v>
     <v>137</v>
     <v>42.54</v>
     <v>12961924379</v>
     <v>DYNATRACE, INC.</v>
     <v>DYNATRACE, INC.</v>
     <v>43.53</v>
-    <v>82.997399999999999</v>
+    <v>82.998900000000006</v>
     <v>42.59</v>
     <v>44.47</v>
-    <v>44.52</v>
     <v>291475700</v>
     <v>DT</v>
     <v>DYNATRACE, INC. (XNYS:DT)</v>
-    <v>6620980</v>
+    <v>5042</v>
     <v>6464198</v>
     <v>2014</v>
   </rv>
@@ -6165,36 +6054,33 @@
     <v>4</v>
     <v>62.357999999999997</v>
     <v>19.48</v>
-    <v>1.8606</v>
+    <v>1.8712</v>
     <v>0.79</v>
-    <v>5.6741E-2</v>
     <v>1.7139999999999999E-2</v>
-    <v>2.66</v>
     <v>USD</v>
-    <v>Super Micro Computer, Inc. is an application-optimized Total IT solutions provider including server, artificial intelligence (AI) systems, storage, information of technology (IoT) devices, switches, software, and support services. Total IT Solutions include complete servers, storage systems, modular blade servers, workstations, full-rack scale solutions, networking devices, server sub-systems, server management and security software. Its products are designed and manufactured in-house (in the United States, Taiwan, and the Netherlands). Its portfolio of Server Building Block Solutions allows customers to optimize for their exact workload and application by selecting from a broad family of systems built from the Company’s flexible and reusable building blocks that support a comprehensive set of form factors, processors, memory, GPUs, storage, networking, power, and cooling solutions (air-conditioned, free air cooling or liquid cooling).</v>
+    <v>Super Micro Computer, Inc. is an application-optimized Total IT solutions provider including server, artificial intelligence (AI) systems, storage, Internet of Things (IoT) devices, switches, software, and support services. Total IT Solutions include complete servers, storage systems, modular blade servers, workstations, full-rack scale solutions, networking devices, server sub-systems, and server management. Its products are designed and manufactured in-house (in the United States, Taiwan, and the Netherlands). The Company's portfolio of Server Building Block Solutions allows customers to optimize for their exact workload and application by selecting from a broad family of systems built from the Company's flexible and reusable building blocks that support a comprehensive set of form factors, processors, memory, GPUs, storage, networking, power, and cooling solutions (air-conditioned, free air cooling or liquid cooling).</v>
     <v>6238</v>
     <v>Nasdaq Stock Market</v>
     <v>XNAS</v>
     <v>XNAS</v>
-    <v>980 Rock Avenue, SAN JOSE, CA, 95131 US</v>
+    <v>980 Rock Avenue, CA, 95131 US</v>
     <v>48.08</v>
     <v>Computers, Phones &amp; Household Electronics</v>
     <v>Stock</v>
-    <v>46174.905663217185</v>
+    <v>46174.999978089843</v>
     <v>140</v>
     <v>45.655000000000001</v>
     <v>28194499280</v>
     <v>SUPER MICRO COMPUTER, INC.</v>
     <v>SUPER MICRO COMPUTER, INC.</v>
     <v>45.8</v>
-    <v>25.543500000000002</v>
+    <v>25.5442</v>
     <v>46.09</v>
     <v>46.88</v>
-    <v>49.54</v>
     <v>601418500</v>
     <v>SMCI</v>
     <v>SUPER MICRO COMPUTER, INC. (XNAS:SMCI)</v>
-    <v>49571477</v>
+    <v>1047681</v>
     <v>41965821</v>
     <v>2006</v>
   </rv>
@@ -6219,11 +6105,9 @@
     <v>4</v>
     <v>466.05</v>
     <v>241.11</v>
-    <v>1.4283999999999999</v>
+    <v>1.4334</v>
     <v>13.2</v>
-    <v>3.2233999999999999E-2</v>
     <v>2.9544999999999998E-2</v>
-    <v>14.8269</v>
     <v>USD</v>
     <v>Broadcom Inc. is a global technology firm that designs, develops, and supplies a range of semiconductors, enterprise software and security solutions. The Company operates through two segments: semiconductor solutions and infrastructure software. Its semiconductor solutions segment includes all of its product lines and intellectual property (IP) licensing. It provides a variety of radio frequency semiconductor devices, wireless connectivity solutions, custom touch controllers, and inductive charging solutions for mobile applications. Its infrastructure software segment includes its private and hybrid cloud, application development and delivery, software-defined edge, application networking and security, mainframe, distributed and cybersecurity solutions, and its FC SAN business. It provides a portfolio of software solutions that enable customers to plan, develop, automate, manage and secure applications across mainframe, distributed, mobile and cloud platforms.</v>
     <v>33000</v>
@@ -6234,21 +6118,20 @@
     <v>466.05</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46174.90570631875</v>
+    <v>46174.999984108596</v>
     <v>143</v>
     <v>442.22</v>
     <v>2177805239960</v>
     <v>BROADCOM INC.</v>
     <v>BROADCOM INC.</v>
     <v>450.09</v>
-    <v>89.787000000000006</v>
+    <v>89.786500000000004</v>
     <v>446.77</v>
     <v>459.97</v>
-    <v>474.79689999999999</v>
     <v>4734668000</v>
     <v>AVGO</v>
     <v>BROADCOM INC. (XNAS:AVGO)</v>
-    <v>30345239</v>
+    <v>872832</v>
     <v>19784145</v>
     <v>2018</v>
   </rv>
@@ -6273,11 +6156,9 @@
     <v>4</v>
     <v>651.73</v>
     <v>376.18</v>
-    <v>1.2188000000000001</v>
+    <v>1.2116</v>
     <v>16.670000000000002</v>
-    <v>4.2659999999999996E-4</v>
     <v>3.5049000000000004E-2</v>
-    <v>0.21</v>
     <v>USD</v>
     <v>Synopsys, Inc. is engaged in providing engineering solutions from silicon to systems, enabling customers to innovate artificial intelligence (AI)-powered products. It delivers silicon design, intellectual property (IP), simulation and analysis solutions, and design services. It supplies mission-critical electronic design automation (EDA) software that engineers use to design and test integrated circuits (ICs). Its Design Automation segment includes its advanced silicon design, verification products and services, and Ansys products, and system integration products and services. This segment also includes digital, custom and field programmable gate array integrated circuit design software, verification software and hardware products, and manufacturing software products. Its Design IP segment includes its logic libraries, embedded memories, wired interface IP, memory interface IP, security IP, and embedded processors that serve companies in the semiconductor and electronics industries.</v>
     <v>28000</v>
@@ -6288,21 +6169,20 @@
     <v>494.25009999999997</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46174.905540705469</v>
+    <v>46174.999967210155</v>
     <v>146</v>
     <v>470.74</v>
     <v>94263344597</v>
     <v>SYNOPSYS, INC.</v>
     <v>SYNOPSYS, INC.</v>
     <v>484.07</v>
-    <v>110.22709999999999</v>
+    <v>114.0904</v>
     <v>475.62</v>
     <v>492.29</v>
-    <v>492.5</v>
     <v>191479300</v>
     <v>SNPS</v>
     <v>SYNOPSYS, INC. (XNAS:SNPS)</v>
-    <v>2581417</v>
+    <v>8398</v>
     <v>1853514</v>
     <v>1987</v>
   </rv>
@@ -6327,11 +6207,9 @@
     <v>4</v>
     <v>87.88</v>
     <v>27.26</v>
-    <v>1.92</v>
+    <v>1.9258999999999999</v>
     <v>1.9750000000000001</v>
-    <v>4.1320000000000003E-3</v>
     <v>4.2541999999999996E-2</v>
-    <v>0.2</v>
     <v>USD</v>
     <v>Symbotic Inc. is an automation technology company, which focuses on reimagining the supply chain with its end-to-end, artificial intelligence-powered robotic and software platform. It is engaged in developing, commercializing, and deploying innovative and comprehensive technology solutions that improve supply chain operations. The Company automates the processing of pallets, cases and individual items in warehouses. Its systems enhance operations at the front end of the supply chain and therefore benefit all supply partners further down the chain, irrespective of fulfillment strategy. Its robotic-based automation systems, which include hardware and essential software, move, store and sort cases and reach in warehouses. Its systems are operational in a number of retailers, including Walmart, wholesale distributors, including C&amp;S Wholesale Grocers, and are being deployed in GreenBox Systems LLC, which is doing business as Exol (Exol), its warehouse-as-a-service joint venture.</v>
     <v>2000</v>
@@ -6342,7 +6220,7 @@
     <v>48.59</v>
     <v>Machinery, Equipment &amp; Components</v>
     <v>Stock</v>
-    <v>46174.905060428122</v>
+    <v>46174.999932649996</v>
     <v>149</v>
     <v>45.35</v>
     <v>29171009120</v>
@@ -6352,11 +6230,10 @@
     <v>0</v>
     <v>46.424999999999997</v>
     <v>48.4</v>
-    <v>48.6</v>
     <v>602706800</v>
     <v>SYM</v>
     <v>SYMBOTIC INC. (XNAS:SYM)</v>
-    <v>3686848</v>
+    <v>13956</v>
     <v>2373031</v>
     <v>2022</v>
   </rv>
@@ -6381,11 +6258,9 @@
     <v>4</v>
     <v>76.87</v>
     <v>8.3149999999999995</v>
-    <v>4.2304000000000004</v>
+    <v>4.2316000000000003</v>
     <v>1.79</v>
-    <v>-5.3569999999999998E-3</v>
     <v>2.8170999999999998E-2</v>
-    <v>-0.35</v>
     <v>USD</v>
     <v>IREN Limited is an Australia-based company, which owns and operates data centers powered by 100% renewable energy. Its facilities are optimized for Bitcoin mining, artificial intelligence (AI) cloud services, and other power-dense compute. Its data center mining facilities are in Canal Flats, Mackenzie, Prince George and Childress. Bitcoin Mining provides security to the Bitcoin network. Al Cloud Services provides cloud compute to Al customers, approximately 1,896 NVIDIA H100 and H200 GPUs. Its Canal Flats facility is in the Canadian Rockies, 100 kilometers (km) from Cranbrook regional airport and 500km east of Vancouver. Its facility is in Prince George, the city in northern British Columbia, located 500 km north of Vancouver. Its facility is located in Childress County, Texas, over 250 miles northwest of Dallas and in close proximity to multiple wind and solar generating facilities in the region. Its Childress operations comprise 200 Mega Watt of operating data centers.</v>
     <v>257</v>
@@ -6396,21 +6271,20 @@
     <v>66.5</v>
     <v>Financial Technology (Fintech) &amp; Infrastructure</v>
     <v>Stock</v>
-    <v>46174.905730462502</v>
+    <v>46174.999978228909</v>
     <v>152</v>
     <v>60.26</v>
     <v>23347550471</v>
     <v>IREN LIMITED</v>
     <v>IREN LIMITED</v>
     <v>62.2</v>
-    <v>142.42420000000001</v>
+    <v>142.41489999999999</v>
     <v>63.54</v>
     <v>65.33</v>
-    <v>64.98</v>
     <v>357378700</v>
     <v>IREN</v>
     <v>IREN LIMITED (XNAS:IREN)</v>
-    <v>56204598</v>
+    <v>1001447</v>
     <v>52913649</v>
     <v>2018</v>
   </rv>
@@ -6435,11 +6309,9 @@
     <v>4</v>
     <v>15.28</v>
     <v>1.26</v>
-    <v>2.6013000000000002</v>
+    <v>2.6246</v>
     <v>0.24</v>
-    <v>-7.428999999999999E-4</v>
     <v>1.8154E-2</v>
-    <v>-0.01</v>
     <v>USD</v>
     <v>Ondas Inc. is a provider of autonomous systems, robotics, and mission-critical connectivity solutions for defense, security, and industrial markets. Through its business units, Ondas Autonomous Systems (OAS), Ondas Capital and Ondas Networks, it develops and deploys integrated technologies that deliver advanced sensing, mobility, and communications capabilities. OAS delivers a portfolio of artificial-intelligence (AI)-powered defense and security platforms to protect sensitive sites, populations, and critical infrastructure. OAS also provides an integrated suite of autonomous aerial, ground, and counter-UAS solutions through its operating companies. It also provides Airborne Missile Protection Systems (AMPS) and airborne intelligence, surveillance and reconnaissance (ISR) solutions for the military, government and others. It also specializes in the procurement, integration, and lifecycle support of heavy engineering equipment for military and national infrastructure programs.</v>
     <v>459</v>
@@ -6450,21 +6322,20 @@
     <v>13.91</v>
     <v>Communications &amp; Networking</v>
     <v>Stock</v>
-    <v>46174.905744560157</v>
+    <v>46174.999945068746</v>
     <v>155</v>
     <v>12.8</v>
-    <v>6795827476</v>
+    <v>6832361954</v>
     <v>ONDAS INC.</v>
     <v>ONDAS INC.</v>
     <v>13.244999999999999</v>
-    <v>33.337499999999999</v>
+    <v>33.942799999999998</v>
     <v>13.22</v>
     <v>13.46</v>
-    <v>13.45</v>
-    <v>504890600</v>
+    <v>507604900</v>
     <v>ONDS</v>
     <v>ONDAS INC. (XNAS:ONDS)</v>
-    <v>86728015</v>
+    <v>780004</v>
     <v>76019422</v>
     <v>2014</v>
   </rv>
@@ -6489,11 +6360,9 @@
     <v>4</v>
     <v>379.935</v>
     <v>105.68</v>
-    <v>2.0386000000000002</v>
-    <v>7.71</v>
-    <v>7.3899999999999999E-3</v>
-    <v>2.4420999999999998E-2</v>
-    <v>2.39</v>
+    <v>2.0379</v>
+    <v>7.68</v>
+    <v>2.4326E-2</v>
     <v>USD</v>
     <v>Vertiv Holdings Co. provides mission-critical digital infrastructure technologies and lifecycle services primarily for data centers, communication networks, and commercial and industrial environments. The Company operates in three business segments: the Americas; Asia Pacific, and Europe, Middle East &amp; Africa. The Company's offerings include alternate current (AC) and direct current (DC) power management, thermal management, low/medium voltage switchgear, busbar, air cooled and liquid cooled thermal management products, integrated modular solutions, racks, single phase UPS, rack power distribution, rack thermal systems, configurable integrated solutions, energy storage solutions, hardware, software for managing IT equipment, management systems for monitoring and controlling digital infrastructure, and services. It also provides preventative maintenance, acceptance testing, engineering and consulting, remote monitoring, training, spare parts, specialized fluid management, and others.</v>
     <v>34000</v>
@@ -6504,21 +6373,20 @@
     <v>328.58</v>
     <v>Machinery, Equipment &amp; Components</v>
     <v>Stock</v>
-    <v>46174.905310890623</v>
+    <v>46174.999683703129</v>
     <v>158</v>
     <v>313.13010000000003</v>
-    <v>124228468096</v>
+    <v>124216944832</v>
     <v>VERTIV HOLDINGS CO</v>
     <v>VERTIV HOLDINGS CO</v>
     <v>317.99</v>
-    <v>81.200100000000006</v>
+    <v>81.1922</v>
     <v>315.70999999999998</v>
-    <v>323.42</v>
-    <v>325.77999999999997</v>
+    <v>323.39</v>
     <v>384108800</v>
     <v>VRT</v>
     <v>VERTIV HOLDINGS CO (XNYS:VRT)</v>
-    <v>6140574</v>
+    <v>121313</v>
     <v>5761262</v>
     <v>2016</v>
   </rv>
@@ -6559,11 +6427,9 @@
     <v>4</v>
     <v>555.45000000000005</v>
     <v>356.28</v>
-    <v>1.1085</v>
+    <v>1.1014999999999999</v>
     <v>10.28</v>
-    <v>-1.5656E-2</v>
     <v>2.2831999999999998E-2</v>
-    <v>-7.21</v>
     <v>USD</v>
     <v>Microsoft Corporation is a technology company. The Company develops and supports software, services, devices, and solutions. The Company’s segments include Productivity and Business Processes, Intelligent Cloud, and More Personal Computing. The Productivity and Business Processes segment consists of products and services in its portfolio of productivity, communication, and information services. This segment primarily comprises: Office Commercial, Office Consumer, LinkedIn, and Dynamics business solutions. The Intelligent Cloud segment consists of server products and cloud services, including Azure and other cloud services, SQL Server, Windows Server, Visual Studio, System Center, and related Client Access Licenses (CALs), and Nuance and GitHub; and Enterprise Services, including enterprise support services, industry solutions and Nuance professional services. The More Personal Computing segment primarily comprises Windows, Devices, Gaming, and search and news advertising.</v>
     <v>228000</v>
@@ -6575,7 +6441,7 @@
     <v>163</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46174.90572489531</v>
+    <v>46174.999959849221</v>
     <v>164</v>
     <v>458.27</v>
     <v>3420942886200</v>
@@ -6585,11 +6451,10 @@
     <v>27.428899999999999</v>
     <v>450.24</v>
     <v>460.52</v>
-    <v>453.31</v>
     <v>7428435000</v>
     <v>MSFT</v>
     <v>MICROSOFT CORPORATION (XNAS:MSFT)</v>
-    <v>53242355</v>
+    <v>745173</v>
     <v>35876618</v>
     <v>1993</v>
   </rv>
@@ -6600,32 +6465,30 @@
     <v>https://www.bing.com/financeapi/forcetrigger?t=a235f2&amp;q=XNAS%3aSMH&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
   </rv>
-  <rv s="10">
+  <rv s="9">
     <v>en-GB</v>
     <v>a235f2</v>
     <v>268435456</v>
     <v>1</v>
     <v>Powered by Refinitiv</v>
+    <v>17</v>
+    <v>VanEck:Semiconductor (XNAS:SMH)</v>
     <v>18</v>
-    <v>VanEck:Semiconductor (XNAS:SMH)</v>
     <v>19</v>
+    <v>Finance</v>
     <v>20</v>
-    <v>Finance</v>
-    <v>21</v>
     <v>613.42989999999998</v>
     <v>238.96</v>
-    <v>1.5746</v>
+    <v>1.5567</v>
     <v>8.8800000000000008</v>
-    <v>5.1990000000000005E-3</v>
     <v>1.4825999999999999E-2</v>
-    <v>3.16</v>
     <v>USD</v>
     <v>Nasdaq Stock Market</v>
     <v>XNAS</v>
     <v>3.4999999999999996E-3</v>
     <v>613.42989999999998</v>
     <v>ETF</v>
-    <v>46174.905592603907</v>
+    <v>46174.99998989531</v>
     <v>167</v>
     <v>593.09</v>
     <v>67822489502.050003</v>
@@ -6633,10 +6496,9 @@
     <v>596.09500000000003</v>
     <v>598.92999999999995</v>
     <v>607.80999999999995</v>
-    <v>610.97</v>
     <v>SMH</v>
     <v>VanEck:Semiconductor (XNAS:SMH)</v>
-    <v>8600167</v>
+    <v>130195</v>
     <v>10043907</v>
   </rv>
   <rv s="2">
@@ -6680,11 +6542,9 @@
     <v>4</v>
     <v>1654.2</v>
     <v>683.48</v>
-    <v>1.8226</v>
+    <v>1.8242</v>
     <v>15.81</v>
-    <v>2.6400000000000002E-4</v>
     <v>9.8029999999999992E-3</v>
-    <v>0.43</v>
     <v>USD</v>
     <v>ASML Holding N.V. is a holding company based in the Netherlands. The Company operates through its subsidiaries in the Netherlands, the United States, Italy, France, Germany, the United Kingdom, Ireland, Belgium, South Korea, Taiwan, Singapore, China, Hong Kong, Japan, Malaysia and Israel. The Company operates through one business segment which is engage in development, production, marketing, sales, upgrading and servicing of advanced semiconductor equipment systems, consisting of lithography, metrology and inspection systems. The Company offers TWINSCAN systems, equipped with lithography system with a mercury lamp as light source (i-line), Krypton Fluoride (KrF) and Argon Fluoride (ArF) light sources for processing wafers for manufacturing environments for which imaging at a small resolution is required. TWINSCAN systems also include immersion lithography systems (TWINSCAN immersion systems).</v>
     <v>43882</v>
@@ -6695,7 +6555,7 @@
     <v>1646.53</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46174.905073610935</v>
+    <v>46174.997350786718</v>
     <v>174</v>
     <v>1585.61</v>
     <v>632125699789</v>
@@ -6705,11 +6565,10 @@
     <v>55.99</v>
     <v>1612.76</v>
     <v>1628.57</v>
-    <v>1629</v>
     <v>388147700</v>
     <v>ASML</v>
     <v>ASML Holding NV (XNAS:ASML)</v>
-    <v>1057960</v>
+    <v>36938</v>
     <v>1597155</v>
     <v>1994</v>
   </rv>
@@ -6734,11 +6593,9 @@
     <v>4</v>
     <v>107.5</v>
     <v>83.96</v>
-    <v>0.7702</v>
+    <v>0.77200000000000002</v>
     <v>1.39</v>
-    <v>-8.3389999999999992E-3</v>
     <v>1.5913E-2</v>
-    <v>-0.74</v>
     <v>USD</v>
     <v>The Charles Schwab Corporation is a savings and loan holding company. The Company, through its subsidiaries, engages in wealth management, securities brokerage, banking, asset management, custody, and financial advisory services. The Company provides financial services to individuals and institutional clients through two segments: Investor Services, and Advisor Services. The Investor Services segment provides retail brokerage, investment advisory, and banking and trust services to individual investors, and retirement plan and business services, as well as other corporate brokerage services, to businesses and their employees. The Advisor Services segment provides custodial, trading, banking and trust, and support services to independent registered investment advisors (RIAs), independent retirement advisors, and recordkeepers. Its products and services include brokerage, mutual funds, exchange-traded funds (ETFs), managed investing solutions, alternative investments, banking, and trust.</v>
     <v>33500</v>
@@ -6749,21 +6606,20 @@
     <v>89.194999999999993</v>
     <v>Investment Banking &amp; Investment Services</v>
     <v>Stock</v>
-    <v>46174.904217314062</v>
+    <v>46174.999527325781</v>
     <v>177</v>
     <v>86.017399999999995</v>
     <v>154330839900</v>
     <v>THE CHARLES SCHWAB CORPORATION</v>
     <v>THE CHARLES SCHWAB CORPORATION</v>
     <v>86.81</v>
-    <v>17.5974</v>
+    <v>17.5975</v>
     <v>87.35</v>
     <v>88.74</v>
-    <v>88</v>
     <v>1739135000</v>
     <v>SCHW</v>
     <v>THE CHARLES SCHWAB CORPORATION (XNYS:SCHW)</v>
-    <v>13960790</v>
+    <v>3593</v>
     <v>10892440</v>
     <v>1986</v>
   </rv>
@@ -6774,32 +6630,30 @@
     <v>https://www.bing.com/financeapi/forcetrigger?t=a23bxm&amp;q=XNAS%3aSOXX&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
   </rv>
-  <rv s="10">
+  <rv s="9">
     <v>en-GB</v>
     <v>a23bxm</v>
     <v>268435456</v>
     <v>1</v>
     <v>Powered by Refinitiv</v>
+    <v>17</v>
+    <v>iShares:Semiconductor (XNAS:SOXX)</v>
     <v>18</v>
-    <v>iShares:Semiconductor (XNAS:SOXX)</v>
     <v>19</v>
+    <v>Finance</v>
     <v>20</v>
-    <v>Finance</v>
-    <v>21</v>
     <v>584.5</v>
     <v>204.29</v>
-    <v>1.6780999999999999</v>
+    <v>1.7036</v>
     <v>2.85</v>
-    <v>3.4269999999999999E-3</v>
     <v>5.0080000000000003E-3</v>
-    <v>1.96</v>
     <v>USD</v>
     <v>Nasdaq Stock Market</v>
     <v>XNAS</v>
     <v>3.4000000000000002E-3</v>
     <v>577.99</v>
     <v>ETF</v>
-    <v>46174.905516805469</v>
+    <v>46174.999908946091</v>
     <v>180</v>
     <v>557.38</v>
     <v>38373488686.160004</v>
@@ -6807,10 +6661,9 @@
     <v>563.66999999999996</v>
     <v>569.08000000000004</v>
     <v>571.92999999999995</v>
-    <v>573.89</v>
     <v>SOXX</v>
     <v>iShares:Semiconductor (XNAS:SOXX)</v>
-    <v>6971620</v>
+    <v>197256</v>
     <v>8352182</v>
   </rv>
   <rv s="2">
@@ -6834,11 +6687,9 @@
     <v>4</v>
     <v>463.48500000000001</v>
     <v>305.44009999999997</v>
-    <v>1.5652999999999999</v>
-    <v>5.68</v>
-    <v>-1.5329999999999999E-4</v>
-    <v>1.2593E-2</v>
-    <v>-7.0000000000000007E-2</v>
+    <v>1.5595000000000001</v>
+    <v>5.65</v>
+    <v>1.2525999999999999E-2</v>
     <v>USD</v>
     <v>Rockwell Automation, Inc. is engaged in industrial automation and digital transformation. The Company operates in three segments: Intelligent Devices, Software &amp; Control, and Lifecycle Services. The Intelligent Devices segment portfolio includes power control, motion control, safety, sensing, and industrial components, and micro control and distributed input/output. The Software &amp; Control operating segment contains a comprehensive portfolio of production automation and production operations platforms, including hardware and software. This integrated portfolio is merging information technology (IT) and operational technology (OT), bringing the benefits of the Connected Enterprise to the production system. The Lifecycle Services segment includes consulting services, including cybersecurity and digital transformation strategy and design and professional services, including global automation and information program and project management and delivery capabilities, and connected services.</v>
     <v>26000</v>
@@ -6849,21 +6700,20 @@
     <v>457.41</v>
     <v>Machinery, Equipment &amp; Components</v>
     <v>Stock</v>
-    <v>46174.902086770315</v>
+    <v>46174.994004791406</v>
     <v>183</v>
     <v>446</v>
-    <v>50823241086</v>
+    <v>50819902869</v>
     <v>ROCKWELL AUTOMATION, INC.</v>
     <v>ROCKWELL AUTOMATION, INC.</v>
     <v>452.15</v>
-    <v>47.447600000000001</v>
+    <v>47.444699999999997</v>
     <v>451.06</v>
-    <v>456.74</v>
-    <v>456.64</v>
+    <v>456.71</v>
     <v>111273900</v>
     <v>ROK</v>
     <v>ROCKWELL AUTOMATION, INC. (XNYS:ROK)</v>
-    <v>815931</v>
+    <v>227</v>
     <v>815468</v>
     <v>1996</v>
   </rv>
@@ -6888,11 +6738,9 @@
     <v>4</v>
     <v>2060.08</v>
     <v>751.96</v>
-    <v>1.5009999999999999</v>
+    <v>1.5045999999999999</v>
     <v>18.329999999999998</v>
-    <v>-1.134E-3</v>
     <v>9.5379999999999996E-3</v>
-    <v>-2.2000000000000002</v>
     <v>USD</v>
     <v>KLA Corporation (KLA) develops industry equipment and services. The Company provides advanced process control and process-enabling solutions for manufacturing wafers and reticles, integrated circuits, packaging, and printed circuit boards. It operates through three segments, which include Semiconductor Process Control, Specialty Semiconductor Process, and PCB and Component Inspection. The Semiconductor Process Control segment offers a portfolio of inspection, metrology and data analytics products, and related services. The Specialty Semiconductor Process segment develops and sells advanced vacuum deposition and etching process tools. The PCB and Component Inspection segment enables electronic device manufacturers to inspect, test and measure PCBs, flat panel displays, and integrated circuits (ICs) to verify their quality, pattern the desired electronic circuitry on the relevant substrate and perform three-dimensional shaping of metalized circuits on multiple surfaces.</v>
     <v>15000</v>
@@ -6903,7 +6751,7 @@
     <v>1948.05</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46174.905482858594</v>
+    <v>46174.999302256248</v>
     <v>186</v>
     <v>1886</v>
     <v>253422575100</v>
@@ -6913,11 +6761,10 @@
     <v>54.927199999999999</v>
     <v>1921.71</v>
     <v>1940.04</v>
-    <v>1937.84</v>
     <v>130627500</v>
     <v>KLAC</v>
     <v>KLA CORPORATION (XNAS:KLAC)</v>
-    <v>735788</v>
+    <v>10152</v>
     <v>1073929</v>
     <v>1975</v>
   </rv>
@@ -6928,43 +6775,40 @@
     <v>https://www.bing.com/financeapi/forcetrigger?t=a21mim&amp;q=XNAS%3aQQQ&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
   </rv>
-  <rv s="10">
+  <rv s="9">
     <v>en-GB</v>
     <v>a21mim</v>
     <v>268435456</v>
     <v>1</v>
     <v>Powered by Refinitiv</v>
+    <v>17</v>
+    <v>Invesco QQQ Trust 1 (XNAS:QQQ)</v>
     <v>18</v>
-    <v>Invesco QQQ Trust 1 (XNAS:QQQ)</v>
     <v>19</v>
+    <v>Finance</v>
     <v>20</v>
-    <v>Finance</v>
-    <v>21</v>
     <v>745.65</v>
     <v>515.97</v>
-    <v>0.99850000000000005</v>
+    <v>1.0089999999999999</v>
     <v>4.43</v>
-    <v>-1.1849999999999999E-3</v>
     <v>6.0000000000000001E-3</v>
-    <v>-0.88</v>
     <v>USD</v>
     <v>Nasdaq Stock Market</v>
     <v>XNAS</v>
     <v>1.8E-3</v>
     <v>745.65</v>
     <v>ETF</v>
-    <v>46174.90555854141</v>
+    <v>46174.999994918748</v>
     <v>189</v>
     <v>735.99</v>
-    <v>440257379466.70001</v>
+    <v>493987523137.08002</v>
     <v>Invesco QQQ Trust 1</v>
     <v>737.04</v>
     <v>738.31</v>
     <v>742.74</v>
-    <v>741.86</v>
     <v>QQQ</v>
     <v>Invesco QQQ Trust 1 (XNAS:QQQ)</v>
-    <v>33646470</v>
+    <v>673215</v>
     <v>38890154</v>
   </rv>
   <rv s="2">
@@ -6988,11 +6832,9 @@
     <v>4</v>
     <v>435.43</v>
     <v>311.89999999999998</v>
-    <v>1.1911</v>
+    <v>1.1931</v>
     <v>-0.52</v>
-    <v>-8.4979999999999995E-4</v>
     <v>-1.2979999999999999E-3</v>
-    <v>-0.34</v>
     <v>USD</v>
     <v>Eaton Corporation plc is an intelligent power management company. Its Electrical Americas segment consists of electrical components, industrial components, power distribution and assemblies, residential products, circuit protection, utility power distribution, wiring devices and others. The Electrical Global segment consists of electrical components, industrial components, power distribution and assemblies, single phase and three phase power quality, and services. The Aerospace segment is a global supplier of aerospace fuel, hydraulics, and pneumatic systems for commercial and military use and filtration systems for industrial applications. The Vehicle segment designs, manufactures, markets, and supplies drivetrain, powertrain systems and critical components. The eMobility segment designs, manufactures, markets, and supplies mechanical, electrical, and electronic components and systems. The Company is also engaged in providing thermal monitoring for critical electrical equipment.</v>
     <v>97000</v>
@@ -7003,21 +6845,20 @@
     <v>404.23</v>
     <v>Machinery, Equipment &amp; Components</v>
     <v>Stock</v>
-    <v>46174.902648124997</v>
+    <v>46174.99811246484</v>
     <v>192</v>
     <v>393.59500000000003</v>
     <v>155351064000</v>
     <v>EATON CORPORATION PUBLIC LIMITED COMPANY</v>
     <v>EATON CORPORATION PUBLIC LIMITED COMPANY</v>
     <v>396.08</v>
-    <v>39.113100000000003</v>
+    <v>39.113</v>
     <v>400.6</v>
     <v>400.08</v>
-    <v>399.74</v>
     <v>388300000</v>
     <v>ETN</v>
     <v>EATON CORPORATION PUBLIC LIMITED COMPANY (XNYS:ETN)</v>
-    <v>2338084</v>
+    <v>4695</v>
     <v>2917408</v>
     <v>2012</v>
   </rv>
@@ -7042,11 +6883,9 @@
     <v>4</v>
     <v>121.95</v>
     <v>62.71</v>
-    <v>1.0015000000000001</v>
+    <v>1.004</v>
     <v>0.91</v>
-    <v>6.2639999999999996E-3</v>
     <v>7.5570000000000003E-3</v>
-    <v>0.76</v>
     <v>USD</v>
     <v>Cisco Systems, Inc. designs and sells a range of technologies that power the Internet. The Company is integrating its product portfolios across networking, security, collaboration, applications and cloud. The Company's segments include the Americas; Europe, Middle East, and Africa (EMEA), and Asia Pacific, Japan, and China (APJC). Its Networking product category represents its core networking technologies of switching, routing, wireless, fifth generation (5G), silicon, optics solutions and compute products. Its Security product category consists of its cloud and application security, industrial security, network security, and user and device security offerings. Its Collaboration product category consists of its meetings, collaboration devices, calling, contact center and platform as a service (CPaaS) offering. Its Observability product category consists of its full stack observability offerings.</v>
     <v>86200</v>
@@ -7057,21 +6896,20 @@
     <v>121.95</v>
     <v>Communications &amp; Networking</v>
     <v>Stock</v>
-    <v>46174.905058738281</v>
+    <v>46174.999851365625</v>
     <v>195</v>
     <v>118.3</v>
     <v>478214308550</v>
     <v>CISCO SYSTEMS, INC.</v>
     <v>CISCO SYSTEMS, INC.</v>
     <v>119.8</v>
-    <v>40.127299999999998</v>
+    <v>40.430500000000002</v>
     <v>120.42</v>
     <v>121.33</v>
-    <v>122.09</v>
     <v>3941435000</v>
     <v>CSCO</v>
     <v>CISCO SYSTEMS, INC. (XNAS:CSCO)</v>
-    <v>23937354</v>
+    <v>53645</v>
     <v>26105243</v>
     <v>2021</v>
   </rv>
@@ -7096,11 +6934,9 @@
     <v>4</v>
     <v>745.61</v>
     <v>320</v>
-    <v>2.4472999999999998</v>
+    <v>2.4569999999999999</v>
     <v>0.61</v>
-    <v>2.9329999999999998E-3</v>
     <v>9.9500000000000001E-4</v>
-    <v>1.8</v>
     <v>USD</v>
     <v>AppLovin Corporation is a marketing platform. The Company provides end-to-end software and artificial intelligence (AI) solutions for businesses to reach, monetize and grow their global audiences. Its advertising solutions include a comprehensive suite of tools including AppDiscovery, MAX, Adjust, Wurl and Axon Ads Manager. AppDiscovery is powered by AXON, its AI-powered advertising engine, and matches advertiser demand with publisher supply through auctions at vast scale and at microsecond-level speeds. MAX is its monetization solution, utilizing an advanced in-app bidding technology that optimizes the value of a publisher’s advertising inventory by running a real-time competitive auction, driving more competition, and higher returns for publishers. Adjust is its measurement and analytics marketing platform which provides marketers with the visibility, insights, and data needed to scale their apps marketing and drive more informed results. Wurl is its connected TV (CTV) platform.</v>
     <v>898</v>
@@ -7111,21 +6947,20 @@
     <v>622</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46174.904568135935</v>
+    <v>46174.999862673438</v>
     <v>198</v>
     <v>584.86</v>
     <v>206166378000</v>
     <v>APPLOVIN CORPORATION</v>
     <v>APPLOVIN CORPORATION</v>
     <v>615.20000000000005</v>
-    <v>53.330399999999997</v>
+    <v>53.330300000000001</v>
     <v>613.09</v>
     <v>613.70000000000005</v>
-    <v>615.5</v>
     <v>335940000</v>
     <v>APP</v>
     <v>APPLOVIN CORPORATION (XNAS:APP)</v>
-    <v>4296795</v>
+    <v>22807</v>
     <v>4967141</v>
     <v>2011</v>
   </rv>
@@ -7136,43 +6971,40 @@
     <v>https://www.bing.com/financeapi/forcetrigger?t=a23hqh&amp;q=ARCX%3aSPY&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
   </rv>
-  <rv s="10">
+  <rv s="9">
     <v>en-GB</v>
     <v>a23hqh</v>
     <v>268435456</v>
     <v>1</v>
     <v>Powered by Refinitiv</v>
+    <v>17</v>
+    <v>State Street SPDR S&amp;P500 (ARCX:SPY)</v>
     <v>18</v>
-    <v>State Street SPDR S&amp;P500 (ARCX:SPY)</v>
     <v>19</v>
+    <v>Finance</v>
     <v>20</v>
-    <v>Finance</v>
-    <v>21</v>
     <v>760.28</v>
     <v>585.05999999999995</v>
     <v>0.99709999999999999</v>
-    <v>1.99</v>
-    <v>-9.9529999999999996E-4</v>
-    <v>2.6310000000000001E-3</v>
-    <v>-0.755</v>
+    <v>2.06</v>
+    <v>2.7229999999999997E-3</v>
     <v>USD</v>
     <v>NYSE Arca</v>
     <v>ARCX</v>
     <v>9.4499999999999998E-4</v>
     <v>760.28</v>
     <v>ETF</v>
-    <v>46174.90571398125</v>
+    <v>46175.000000010936</v>
     <v>201</v>
     <v>754.69</v>
     <v>783796407176.76001</v>
     <v>State Street SPDR S&amp;P500</v>
     <v>755.36</v>
     <v>756.48</v>
-    <v>758.47</v>
-    <v>757.78499999999997</v>
+    <v>758.54</v>
     <v>SPY</v>
     <v>State Street SPDR S&amp;P500 (ARCX:SPY)</v>
-    <v>43471924</v>
+    <v>234355</v>
     <v>45219436</v>
   </rv>
   <rv s="2">
@@ -7182,32 +7014,30 @@
     <v>https://www.bing.com/financeapi/forcetrigger?t=a1nq6h&amp;q=ARCX%3aARKK&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
   </rv>
-  <rv s="10">
+  <rv s="9">
     <v>en-GB</v>
     <v>a1nq6h</v>
     <v>268435456</v>
     <v>1</v>
     <v>Powered by Refinitiv</v>
+    <v>17</v>
+    <v>ARK Innovation (BATS:ARKK)</v>
     <v>18</v>
-    <v>ARK Innovation (BATS:ARKK)</v>
     <v>19</v>
+    <v>Finance</v>
     <v>20</v>
-    <v>Finance</v>
-    <v>21</v>
     <v>92.65</v>
     <v>55.22</v>
-    <v>2.0520999999999998</v>
+    <v>2.0400999999999998</v>
     <v>-0.63</v>
-    <v>-1.2310000000000002E-6</v>
     <v>-7.6880000000000004E-3</v>
-    <v>-1E-4</v>
     <v>USD</v>
     <v>CBOE BZX Exchange</v>
     <v>BATS</v>
     <v>7.4999999999999997E-3</v>
     <v>82.144999999999996</v>
     <v>ETF</v>
-    <v>46174.905266481248</v>
+    <v>46174.994492013284</v>
     <v>204</v>
     <v>79.92</v>
     <v>7266077935.0299997</v>
@@ -7215,10 +7045,9 @@
     <v>80.765000000000001</v>
     <v>81.95</v>
     <v>81.319999999999993</v>
-    <v>81.259900000000002</v>
     <v>ARKK</v>
     <v>ARK Innovation (BATS:ARKK)</v>
-    <v>6989695</v>
+    <v>12261</v>
     <v>7520632</v>
   </rv>
   <rv s="2">
@@ -7228,43 +7057,40 @@
     <v>https://www.bing.com/financeapi/forcetrigger?t=a1vxfr&amp;q=ARCX%3aIWM&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
   </rv>
-  <rv s="10">
+  <rv s="9">
     <v>en-GB</v>
     <v>a1vxfr</v>
     <v>268435456</v>
     <v>1</v>
     <v>Powered by Refinitiv</v>
+    <v>17</v>
+    <v>iShares:Russ 2000 ETF (ARCX:IWM)</v>
     <v>18</v>
-    <v>iShares:Russ 2000 ETF (ARCX:IWM)</v>
     <v>19</v>
+    <v>Finance</v>
     <v>20</v>
-    <v>Finance</v>
-    <v>21</v>
     <v>292.74</v>
     <v>202.67</v>
     <v>0.99929999999999997</v>
-    <v>-1.48</v>
-    <v>-8.9969999999999991E-4</v>
-    <v>-5.0960000000000007E-3</v>
-    <v>-0.26</v>
+    <v>-1.45</v>
+    <v>-4.993E-3</v>
     <v>USD</v>
     <v>NYSE Arca</v>
     <v>ARCX</v>
     <v>1.9E-3</v>
     <v>290.61</v>
     <v>ETF</v>
-    <v>46174.904567418751</v>
+    <v>46175.000001897657</v>
     <v>207</v>
     <v>286.27</v>
-    <v>76877810344.919998</v>
+    <v>80933362748.720001</v>
     <v>iShares:Russ 2000 ETF</v>
     <v>288.37</v>
     <v>290.43</v>
-    <v>288.95</v>
-    <v>288.72000000000003</v>
+    <v>288.98</v>
     <v>IWM</v>
     <v>iShares:Russ 2000 ETF (ARCX:IWM)</v>
-    <v>23764702</v>
+    <v>176165</v>
     <v>25991529</v>
   </rv>
   <rv s="2">
@@ -7288,11 +7114,9 @@
     <v>4</v>
     <v>129.13</v>
     <v>41.49</v>
-    <v>1.968</v>
+    <v>1.9777</v>
     <v>0.3</v>
-    <v>-3.3079999999999996E-4</v>
     <v>2.4870000000000001E-3</v>
-    <v>-0.04</v>
     <v>USD</v>
     <v>ON Semiconductor Corporation is engaged in providing intelligent power and intelligent sensing solutions. The Company’s intelligent power technologies enable the electrification of drivetrain in the automotive industry to allow for lighter and longer-range electric vehicles. Its segments include Power Solutions Group (PSG), the Analog and Mixed-Signal Group (AMG) and the Intelligent Sensing Group (ISG). PSG segment provides a portfolio of discrete, module, and integrated semiconductor devices designed to enable conversion across artificial intelligence (AI) data centers, energy infrastructure, automotive and industrial. AMG segment designs and develops a range of analog and mixed-signal solutions including power‑management, sensor‑interface, connectivity, and products that serve automotive, industrial automation, AI data center, computing, and mobile end markets.</v>
     <v>22600</v>
@@ -7303,21 +7127,20 @@
     <v>121.05</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46174.905740601564</v>
+    <v>46174.999666967189</v>
     <v>210</v>
     <v>115.81</v>
     <v>47388934944</v>
     <v>ON SEMICONDUCTOR CORPORATION</v>
     <v>ON SEMICONDUCTOR CORPORATION</v>
     <v>119.38500000000001</v>
-    <v>86.346800000000002</v>
+    <v>86.347999999999999</v>
     <v>120.62</v>
     <v>120.92</v>
-    <v>120.88</v>
     <v>391903200</v>
     <v>ON</v>
     <v>ON SEMICONDUCTOR CORPORATION (XNAS:ON)</v>
-    <v>9122072</v>
+    <v>104376</v>
     <v>12974330</v>
     <v>2000</v>
   </rv>
@@ -7342,11 +7165,9 @@
     <v>4</v>
     <v>39.284999999999997</v>
     <v>8.18</v>
-    <v>3.3237999999999999</v>
+    <v>3.3254000000000001</v>
     <v>-0.57999999999999996</v>
-    <v>-5.5469999999999998E-4</v>
     <v>-1.4879E-2</v>
-    <v>-2.1299999999999999E-2</v>
     <v>USD</v>
     <v>SkyWater Technology, Inc. is an independent, pure-play technology foundry that offers advanced semiconductor development and manufacturing services. The Company’s Technology-as-a-Service (TaaS) model leverages a foundation of proprietary technology, engineering know-how capabilities, and microelectronics manufacturing capacity to co-develop process technology intellectual property (IP) with its customers that enable disruptive concepts through its Advanced Technology Services (ATS) for diverse microelectronics (integrated circuits (ICs)) and related micro- and nanotechnology applications. In addition to differentiated technology development services, it supports customers with volume production of ICs for high-growth markets through its Wafer Services. Its Wafer Services include the manufacture of silicon-based analog and mixed-signal ICs for its end markets. Through its ATS model, it specializes in co-creating advanced solutions with its customers that directly serve its end markets.</v>
     <v>1551</v>
@@ -7357,21 +7178,20 @@
     <v>39.099899999999998</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46174.905136770314</v>
+    <v>46174.992959814066</v>
     <v>213</v>
     <v>37.869999999999997</v>
     <v>1889456640</v>
     <v>SKYWATER TECHNOLOGY, INC.</v>
     <v>SKYWATER TECHNOLOGY, INC.</v>
     <v>38.76</v>
-    <v>16.4602</v>
+    <v>16.460100000000001</v>
     <v>38.979999999999997</v>
     <v>38.4</v>
-    <v>38.378700000000002</v>
     <v>49204600</v>
     <v>SKYT</v>
     <v>SKYWATER TECHNOLOGY, INC. (XNAS:SKYT)</v>
-    <v>748851</v>
+    <v>5275</v>
     <v>1246138</v>
     <v>2016</v>
   </rv>
@@ -7396,11 +7216,9 @@
     <v>4</v>
     <v>18.940000000000001</v>
     <v>2.75</v>
-    <v>1.3325</v>
+    <v>1.3373999999999999</v>
     <v>-0.42499999999999999</v>
-    <v>-1.9027000000000002E-2</v>
     <v>-2.5028999999999999E-2</v>
-    <v>-0.315</v>
     <v>USD</v>
     <v>LightPath Technologies, Inc. is a global, vertically integrated provider of optics, photonics and infrared solutions for the industrial, commercial, defense, telecommunications, and medical industries. The Company designs and manufactures optical and infrared components including molded glass aspheric lenses and assemblies, custom molded glass freeform lenses, infrared lenses and thermal imaging assemblies, fused fiber collimators, and BlackDiamond (BD6) chalcogenide-based glass lenses. It also offers custom optical assemblies, including full engineering design support. Its business is organized into four product groups: infrared components, visible components, assemblies and modules, and engineering services. Its infrared product group comprises both molded and turned infrared lenses and assemblies using a variety of infrared glass materials. Its assemblies and modules product group is comprised of other value-added products, including both infrared and visible components.</v>
     <v>345</v>
@@ -7411,7 +7229,7 @@
     <v>17.139900000000001</v>
     <v>Computers, Phones &amp; Household Electronics</v>
     <v>Stock</v>
-    <v>46174.904755890624</v>
+    <v>46174.999420508597</v>
     <v>216</v>
     <v>15.48</v>
     <v>1039478682</v>
@@ -7421,11 +7239,10 @@
     <v>0</v>
     <v>16.98</v>
     <v>16.555</v>
-    <v>16.239999999999998</v>
     <v>62789410</v>
     <v>LPTH</v>
     <v>LIGHTPATH TECHNOLOGIES, INC. (XNAS:LPTH)</v>
-    <v>3211412</v>
+    <v>63519</v>
     <v>4309853</v>
     <v>1992</v>
   </rv>
@@ -7450,11 +7267,9 @@
     <v>4</v>
     <v>82.663499999999999</v>
     <v>65.353800000000007</v>
-    <v>0.35110000000000002</v>
-    <v>-0.4</v>
-    <v>3.8150000000000006E-4</v>
-    <v>-5.0629999999999998E-3</v>
-    <v>0.03</v>
+    <v>0.3548</v>
+    <v>-0.37</v>
+    <v>-4.6829999999999997E-3</v>
     <v>USD</v>
     <v>The Coca-Cola Company is a beverage company. The Company's segments include Europe, Middle East and Africa (EMEA); Latin America; North America; Asia Pacific, and Bottling Investments. It sells multiple brands across several beverage categories worldwide. Its portfolio of sparkling soft drink brands includes Coca-Cola, Sprite and Fanta. Its water, sports, coffee and tea brands include Dasani, smartwater, vitaminwater, Topo Chico, BODYARMOR, Powerade, Costa, Georgia, Fuze Tea, Gold Peak and Ayataka. Its juice, value-added dairy and plant-based beverage brands include Minute Maid, Simply, innocent, Del Valle, fairlife and Santa Clara. It operates in two lines of business: concentrate operations and finished product operations. Its concentrate operations sell beverage concentrates, syrups, including fountain syrups, and certain finished beverages to authorized bottling operations. Its finished product operations sell sparkling soft drinks and a variety of other finished beverages.</v>
     <v>65900</v>
@@ -7465,21 +7280,20 @@
     <v>79.2</v>
     <v>Beverages</v>
     <v>Stock</v>
-    <v>46174.905241492968</v>
+    <v>46174.99991173594</v>
     <v>219</v>
     <v>78.430000000000007</v>
-    <v>338218110020</v>
+    <v>338347184480</v>
     <v>THE COCA-COLA COMPANY</v>
     <v>THE COCA-COLA COMPANY</v>
     <v>78.575000000000003</v>
-    <v>24.747399999999999</v>
+    <v>24.757000000000001</v>
     <v>79.010000000000005</v>
-    <v>78.61</v>
-    <v>78.67</v>
+    <v>78.64</v>
     <v>4302482000</v>
     <v>KO</v>
     <v>THE COCA-COLA COMPANY (XNYS:KO)</v>
-    <v>12767660</v>
+    <v>25888</v>
     <v>15464867</v>
     <v>1919</v>
   </rv>
@@ -7504,11 +7318,9 @@
     <v>4</v>
     <v>527.19989999999996</v>
     <v>111.01</v>
-    <v>2.5004</v>
+    <v>2.4937</v>
     <v>-5.97</v>
-    <v>7.2530000000000001E-4</v>
     <v>-1.1568E-2</v>
-    <v>0.37</v>
     <v>USD</v>
     <v>Advanced Micro Devices, Inc. is a global semiconductor company. The Company is focused on high-performance computing and artificial intelligence (AI). Its segments include Data Center, Client and Gaming, and Embedded. Data Center segment includes AI accelerators, microprocessors (CPUs) for servers, graphics processing units (GPUs), accelerated processing units (APUs), data processing units (DPUs), Field Programmable Gate Arrays (FPGAs), and Adaptive system-on-Chip (SoC) products for data centers. Client and Gaming segment includes CPUs, APUs, chipsets for desktops and notebooks, discrete GPUs, and semi-custom SoC products and development services. Embedded segment includes embedded CPUs, APUs, FPGAs, system on modules (SOMs), and Adaptive SoC products. It markets and sells its products under the AMD trademark. Its products include AMD EPYC, AMD Ryzen, AMD Ryzen PRO, Virtex UltraScale+, among others.</v>
     <v>31000</v>
@@ -7519,7 +7331,7 @@
     <v>517.5</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46174.905693911722</v>
+    <v>46174.999937106251</v>
     <v>222</v>
     <v>486.8</v>
     <v>831818488130</v>
@@ -7529,11 +7341,10 @@
     <v>170.04900000000001</v>
     <v>516.1</v>
     <v>510.13</v>
-    <v>510.5</v>
     <v>1630601000</v>
     <v>AMD</v>
     <v>ADVANCED MICRO DEVICES, INC. (XNAS:AMD)</v>
-    <v>33195941</v>
+    <v>300001</v>
     <v>42313085</v>
     <v>1969</v>
   </rv>
@@ -7558,11 +7369,9 @@
     <v>4</v>
     <v>112</v>
     <v>9.3800000000000008</v>
-    <v>3.1882000000000001</v>
+    <v>3.1863999999999999</v>
     <v>1.29</v>
-    <v>-1.282E-4</v>
     <v>1.3972E-2</v>
-    <v>-1.2E-2</v>
     <v>USD</v>
     <v>Aehr Test Systems, Inc. offers test solutions for testing, burning-in, and stabilizing semiconductor devices in wafer level, singulated die, and package part form. The Company's products include the FOX-P family of test and burn-in systems and FOX WaferPak Aligner, FOX WaferPak Contactor, FOX DiePak Carrier and FOX DiePak Loader. The FOX-XP and FOX-NP systems are full wafer contact and singulated die/module test and burn-in systems that can test, burn-in and stabilize a range of devices such as silicon carbide-based and other power semiconductors, 2D and 3D sensors used in phones, tablets, and other computing devices, memory semiconductors, processors, microcontrollers, systems-on-a-chip, and photonics and integrated optical devices used in AI. FOX-CP system is a single-wafer compact test solution for logic, memory and photonic devices. FOX WaferPak Contactor contains a full wafer contactor capable of testing wafers up to 300 millimeters that enables integrated circuit manufacturers.</v>
     <v>136</v>
@@ -7573,7 +7382,7 @@
     <v>93.74</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46174.904788853906</v>
+    <v>46174.999708228905</v>
     <v>225</v>
     <v>86.577100000000002</v>
     <v>2944653265</v>
@@ -7583,11 +7392,10 @@
     <v>0</v>
     <v>92.33</v>
     <v>93.62</v>
-    <v>93.608000000000004</v>
     <v>31453250</v>
     <v>AEHR</v>
     <v>AEHR TEST SYSTEMS (XNAS:AEHR)</v>
-    <v>1524668</v>
+    <v>57560</v>
     <v>2736355</v>
     <v>1977</v>
   </rv>
@@ -7612,11 +7420,9 @@
     <v>4</v>
     <v>422.11</v>
     <v>77.78</v>
-    <v>1.7908999999999999</v>
+    <v>1.7958000000000001</v>
     <v>-4.84</v>
-    <v>-5.4939999999999998E-3</v>
     <v>-1.2929999999999999E-2</v>
-    <v>-2.0299999999999998</v>
     <v>USD</v>
     <v>Teradyne, Inc. is a global supplier of automated test equipment and robotics solutions. It designs, develops, manufactures and sells automated test systems and robotics products. Its segment includes Semiconductor Test, Robotics, and Product Test. The Semiconductor Test segment includes operations related to the design, manufacturing and marketing of semiconductor test products and services, inclusive of storage and system level test products. The Robotics segment includes operations related to the design, manufacturing and marketing of collaborative robotic arms and autonomous mobile robots. The Product Test segment includes operations related to the design, manufacturing and marketing of products and services for defense/aerospace test, circuit-board test, wireless test systems, and silicon photonics testing. Its offerings also include defense/aerospace test instrumentation and systems, circuit-board test and inspection (production board test) systems, and wireless test systems.</v>
     <v>6600</v>
@@ -7627,21 +7433,20 @@
     <v>376.7</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46174.905606620312</v>
+    <v>46174.999666967189</v>
     <v>228</v>
     <v>360.14</v>
     <v>57837646634</v>
     <v>TERADYNE, INC.</v>
     <v>TERADYNE, INC.</v>
     <v>366.51</v>
-    <v>68.381100000000004</v>
+    <v>68.381699999999995</v>
     <v>374.31</v>
     <v>369.47</v>
-    <v>367.44</v>
     <v>156542200</v>
     <v>TER</v>
     <v>TERADYNE, INC. (XNAS:TER)</v>
-    <v>2520772</v>
+    <v>28788</v>
     <v>4278758</v>
     <v>1960</v>
   </rv>
@@ -7652,25 +7457,23 @@
     <v>https://www.bing.com/financeapi/forcetrigger?t=c4s6z2&amp;q=XNAS%3aCRDO&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
   </rv>
-  <rv s="11">
+  <rv s="10">
     <v>en-GB</v>
     <v>c4s6z2</v>
     <v>268435456</v>
     <v>1</v>
     <v>Powered by Refinitiv</v>
-    <v>22</v>
+    <v>21</v>
     <v>Credo Technology Group Holding Ltd (XNAS:CRDO)</v>
     <v>2</v>
-    <v>23</v>
+    <v>22</v>
     <v>Finance</v>
     <v>4</v>
     <v>243.21</v>
     <v>59.88</v>
-    <v>3.2275</v>
+    <v>3.2351999999999999</v>
     <v>-9.93</v>
-    <v>-0.10216699999999999</v>
     <v>-4.2070999999999997E-2</v>
-    <v>-23.1</v>
     <v>USD</v>
     <v>Credo Technology Group Holding Ltd is a Cayman Islands-based holding company. The Company delivers high-speed solutions to break bandwidth barriers on every wired connection in the data infrastructure market. It provides high-speed connectivity solutions that deliver improved power efficiency as data rates and corresponding bandwidth requirements increase exponentially throughout the data infrastructure market. Its connectivity solutions are optimized for optical and electrical Ethernet applications, including the emerging 100 gigabits per second (G), 200G, 400G, 800G and the emerging 1.6 terabits per second (T) port markets. Its products are based on its Serializer/Deserializer (SerDes) and Digital Signal Processor (DSP) technologies. Its product families include integrated circuits (ICs) for the optical and line card markets, active electrical cables (AECs) and SerDes Chiplets. The Company’s intellectual property (IP) solutions consist primarily of SerDes IP licensing.</v>
     <v>622</v>
@@ -7681,21 +7484,20 @@
     <v>243.21</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46174.905720196097</v>
+    <v>46174.999991191406</v>
     <v>231</v>
     <v>223.54</v>
     <v>41704122390</v>
     <v>Credo Technology Group Holding Ltd</v>
     <v>Credo Technology Group Holding Ltd</v>
     <v>240.02</v>
-    <v>130.98589999999999</v>
+    <v>125.4752</v>
     <v>236.03</v>
     <v>226.1</v>
-    <v>203</v>
     <v>184449900</v>
     <v>CRDO</v>
     <v>Credo Technology Group Holding Ltd (XNAS:CRDO)</v>
-    <v>12646832</v>
+    <v>738221</v>
     <v>6281895</v>
   </rv>
   <rv s="2">
@@ -7719,11 +7521,9 @@
     <v>4</v>
     <v>404.47</v>
     <v>163.33000000000001</v>
-    <v>1.2369000000000001</v>
+    <v>1.2385999999999999</v>
     <v>-3.85</v>
-    <v>-1.9404999999999999E-2</v>
     <v>-1.0227999999999999E-2</v>
-    <v>-7.23</v>
     <v>USD</v>
     <v>Alphabet Inc. is a holding company. The Company's segments include Google Services, Google Cloud, and Other Bets. The Google Services segment includes products and services such as ads, Android, Chrome, devices, Google Maps, Google Play, Search, and YouTube. The Google Cloud segment includes infrastructure and platform services, collaboration tools, and other services for enterprise customers. Its Other Bets segment is engaged in the sale of healthcare-related services and Internet services. Its Google Cloud provides enterprise-ready cloud services, including Google Cloud Platform and Google Workspace. Google Cloud Platform provides access to solutions such as artificial intelligence (AI) offerings, including its AI infrastructure, Vertex AI platform, and Gemini for Google Cloud; cybersecurity, and data and analytics. Google Workspace includes cloud-based communication and collaboration tools for enterprises, such as Calendar, Gmail, Docs, Drive, and Meet.</v>
     <v>194668</v>
@@ -7734,21 +7534,20 @@
     <v>374.6</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46174.905754640626</v>
+    <v>46174.999999941407</v>
     <v>234</v>
     <v>369.71</v>
     <v>4514179280000</v>
     <v>ALPHABET INC.</v>
     <v>ALPHABET INC.</v>
     <v>372.57499999999999</v>
-    <v>28.454499999999999</v>
+    <v>28.4544</v>
     <v>376.43</v>
     <v>372.58</v>
-    <v>365.35</v>
     <v>12116000000</v>
     <v>GOOG</v>
     <v>ALPHABET INC. (XNAS:GOOG)</v>
-    <v>18729341</v>
+    <v>638897</v>
     <v>20347311</v>
     <v>2015</v>
   </rv>
@@ -7773,11 +7572,9 @@
     <v>4</v>
     <v>56</v>
     <v>16.61</v>
-    <v>1.3632</v>
+    <v>1.3715999999999999</v>
     <v>-0.48</v>
-    <v>9.4130000000000006E-4</v>
     <v>-1.4838E-2</v>
-    <v>0.03</v>
     <v>USD</v>
     <v>Photronics, Inc. is a manufacturer of photomasks, which are high-precision photographic quartz or glass plates containing microscopic images of electronic circuits. The Company manufactures photomasks, which are used as masters to transfer circuit patterns onto semiconductor wafers and FPD substrates. The photomasks the Company manufactures incorporate circuit designs provided on a confidential basis by its customers. The Company sells its photomasks to semiconductor designers and manufacturers, and manufacturers of FPDs. Photomask technology is also being applied to the fabrication of other higher-performance electronic products such as virtual reality/augmented reality advanced IC packages, photonics, micro-electronic mechanical systems, and certain nanotechnology applications. The Company operates approximately 11 manufacturing facilities, which are located in Taiwan, China, Korea, the United States, and Europe.</v>
     <v>1908</v>
@@ -7788,42 +7585,41 @@
     <v>33.575000000000003</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46174.904835335154</v>
+    <v>46174.999644767966</v>
     <v>237</v>
     <v>31.46</v>
     <v>1879258849</v>
     <v>PHOTRONICS, INC.</v>
     <v>PHOTRONICS, INC.</v>
     <v>32.375</v>
-    <v>11.8476</v>
+    <v>11.671799999999999</v>
     <v>32.35</v>
     <v>31.87</v>
-    <v>31.9</v>
     <v>58966390</v>
     <v>PLAB</v>
     <v>PHOTRONICS, INC. (XNAS:PLAB)</v>
-    <v>3648078</v>
+    <v>30760</v>
     <v>1415399</v>
     <v>1969</v>
   </rv>
   <rv s="2">
     <v>238</v>
   </rv>
-  <rv s="12">
+  <rv s="6">
     <v>en-GB</v>
     <v>cdocfr</v>
     <v>268435456</v>
     <v>1</v>
     <v>Powered by Refinitiv</v>
-    <v>24</v>
+    <v>23</v>
     <v>ATRIUM MORTGAGE INVESTMENT CORPORATION (NEOE:AI)</v>
     <v>11</v>
+    <v>24</v>
+    <v>Finance</v>
     <v>25</v>
-    <v>Finance</v>
-    <v>26</v>
     <v>12.24</v>
     <v>10.99</v>
-    <v>0.84619999999999995</v>
+    <v>0.83940000000000003</v>
     <v>-0.13</v>
     <v>-1.098E-2</v>
     <v>CAD</v>
@@ -7873,11 +7669,9 @@
     <v>4</v>
     <v>315</v>
     <v>195.07</v>
-    <v>1.0921000000000001</v>
+    <v>1.0873999999999999</v>
     <v>-5.75</v>
-    <v>3.2650000000000001E-5</v>
     <v>-1.8426000000000001E-2</v>
-    <v>0.01</v>
     <v>USD</v>
     <v>Apple Inc. designs, manufactures and markets smartphones, personal computers, tablets, wearables and accessories, and sells a variety of related services. Its product categories include iPhone, Mac, iPad, Wearables, Home and Accessories. Its services include advertising, AppleCare, cloud services, digital content, and payment services. The Company operates various platforms, including the App Store, that allow customers to discover and download applications and digital content, such as books, music, video, games and podcasts. It also offers digital content through subscription-based services, including Apple Arcade, Apple Fitness+, Apple Music, Apple News+, and Apple TV+. Its wearables include smartwatches, wireless headphones, and spatial computers. Its products include iPhone 16 Pro, iPhone 16, iPhone 15, iPhone 14, iPhone SE, MacBook Air, MacBook Pro, iMac, Mac mini, Mac Studio, Mac Pro, iPad Pro, iPad Air, AirPods, AirPods Pro, AirPods Max, Apple TV, Apple Vision Pro and others.</v>
     <v>166000</v>
@@ -7888,21 +7682,20 @@
     <v>310.94</v>
     <v>Computers, Phones &amp; Household Electronics</v>
     <v>Stock</v>
-    <v>46174.905331064059</v>
+    <v>46174.999923171097</v>
     <v>242</v>
     <v>305.02</v>
     <v>4498885241600</v>
     <v>APPLE INC.</v>
     <v>APPLE INC.</v>
     <v>309.625</v>
-    <v>37.201500000000003</v>
+    <v>37.2014</v>
     <v>312.06</v>
     <v>306.31</v>
-    <v>306.32</v>
     <v>14687360000</v>
     <v>AAPL</v>
     <v>APPLE INC. (XNAS:AAPL)</v>
-    <v>48773256</v>
+    <v>245050</v>
     <v>48913012</v>
     <v>1977</v>
   </rv>
@@ -7927,11 +7720,9 @@
     <v>4</v>
     <v>153.85990000000001</v>
     <v>63.515000000000001</v>
-    <v>2.3483000000000001</v>
+    <v>2.3519000000000001</v>
     <v>-3.57</v>
-    <v>-7.2740000000000001E-3</v>
     <v>-3.7858000000000003E-2</v>
-    <v>-0.66</v>
     <v>USD</v>
     <v>Robinhood Markets, Inc. is creating a financial services platform for everyone, regardless of their wealth, income, or background. It uses technology to provide access to the financial system. Its offerings include Brokerage, Robinhood Crypto, Custody, Robinhood Wallet, Robinhood Gold, and Robinhood Gold Card. Its Brokerage services include investing, options trading, fractional trading, recurring investment, access to investing on margin, fully paid securities lending, cash sweep, instant withdrawals, Robinhood retirement, 24-hour market, joint investing accounts, and event contracts. It also offers a variety of ways for its customers to grow their financial knowledge, including Robinhood Learn, In-App Education, Newsfeeds, Sherwood Snacks, and Crypto Learn and Earn. Its self-clearing system, order routing system, data platform, and other back-end infrastructure deliver the capabilities that allow its customers to focus on investing, saving and spending.</v>
     <v>2900</v>
@@ -7942,7 +7733,7 @@
     <v>92.4</v>
     <v>Financial Technology (Fintech) &amp; Infrastructure</v>
     <v>Stock</v>
-    <v>46174.905757245309</v>
+    <v>46174.999978425782</v>
     <v>245</v>
     <v>85.559899999999999</v>
     <v>81702827723</v>
@@ -7952,11 +7743,10 @@
     <v>50.472900000000003</v>
     <v>94.3</v>
     <v>90.73</v>
-    <v>90.07</v>
     <v>900505100</v>
     <v>HOOD</v>
     <v>ROBINHOOD MARKETS, INC. (XNAS:HOOD)</v>
-    <v>42426915</v>
+    <v>403352</v>
     <v>27288691</v>
     <v>2013</v>
   </rv>
@@ -7981,11 +7771,9 @@
     <v>4</v>
     <v>84.64</v>
     <v>25.89</v>
-    <v>3.1793999999999998</v>
-    <v>-2.84</v>
-    <v>-9.2379999999999997E-3</v>
-    <v>-3.9405999999999997E-2</v>
-    <v>-0.64</v>
+    <v>3.1894</v>
+    <v>-2.79</v>
+    <v>-3.8711999999999996E-2</v>
     <v>USD</v>
     <v>IonQ, Inc. is engaged in the quantum computing and networking industry, delivering high-performance systems capable of solving complex commercial and research use cases. Its generation quantum computers, IonQ Forte and IonQ Forte Enterprise, are cutting-edge systems, boasting 36 algorithmic qubits. It sells specialized quantum computing and networking hardware together with related maintenance and support. It also sells access to several quantum computers of various qubit capacities and is in the process of researching and developing technologies for quantum computers with increasing computational capabilities. It makes access to its quantum computers available via three cloud platforms, Amazon Web Services' (AWS) Amazon Braket, Microsoft's Azure Quantum and Google's Cloud Marketplace, and also to select customers via its own cloud service. Its product portfolio also includes quantum key distribution (QKD) systems, quantum random number generators (QRNGs), and single-photon detectors.</v>
     <v>1132</v>
@@ -7996,21 +7784,20 @@
     <v>72.42</v>
     <v>Computers, Phones &amp; Household Electronics</v>
     <v>Stock</v>
-    <v>46174.905742488278</v>
+    <v>46174.999785728905</v>
     <v>248</v>
     <v>66.97</v>
-    <v>25841482100</v>
+    <v>25860145600</v>
     <v>IONQ, INC.</v>
     <v>IONQ, INC.</v>
     <v>69.644999999999996</v>
-    <v>1181.3993</v>
+    <v>1182.05</v>
     <v>72.069999999999993</v>
-    <v>69.23</v>
-    <v>68.64</v>
+    <v>69.28</v>
     <v>373270000</v>
     <v>IONQ</v>
     <v>IONQ, INC. (XNYS:IONQ)</v>
-    <v>28162128</v>
+    <v>475649</v>
     <v>32956907</v>
     <v>2020</v>
   </rv>
@@ -8035,11 +7822,9 @@
     <v>4</v>
     <v>278.56</v>
     <v>196</v>
-    <v>1.4477</v>
+    <v>1.4463999999999999</v>
     <v>-9.3800000000000008</v>
-    <v>-6.1609999999999998E-3</v>
     <v>-3.4659000000000002E-2</v>
-    <v>-1.6095999999999999</v>
     <v>USD</v>
     <v>Amazon.com, Inc. provides a range of products and services to customers. The products offered through its stores include merchandise and content it has purchased for resale and products offered by third-party sellers. The Company’s segments include North America, International and Amazon Web Services (AWS). It serves consumers through its online and physical stores and focuses on selection, price, and convenience. Customers access its offerings through its websites, mobile apps, Alexa, devices, streaming, and physically visiting its stores. It also manufactures and sells electronic devices, including Kindle, Fire tablet, Fire TV, Echo, Ring, Blink, and eero, and develops and produces media content. It serves developers and enterprises of all sizes, including start-ups, government agencies, and academic institutions, through AWS, which offers a set of on-demand technology services, including compute, storage, database, analytics, and machine learning, and other services.</v>
     <v>1575000</v>
@@ -8050,7 +7835,7 @@
     <v>266.63</v>
     <v>Diversified Retail</v>
     <v>Stock</v>
-    <v>46174.90574208281</v>
+    <v>46174.999957221873</v>
     <v>251</v>
     <v>260.7</v>
     <v>2810402558600</v>
@@ -8060,11 +7845,10 @@
     <v>31.2224</v>
     <v>270.64</v>
     <v>261.26</v>
-    <v>259.65039999999999</v>
     <v>10757110000</v>
     <v>AMZN</v>
     <v>AMAZON.COM, INC. (XNAS:AMZN)</v>
-    <v>53312057</v>
+    <v>484589</v>
     <v>44180835</v>
     <v>1996</v>
   </rv>
@@ -8089,11 +7873,9 @@
     <v>4</v>
     <v>498.83</v>
     <v>273.20999999999998</v>
-    <v>1.802</v>
+    <v>1.8019000000000001</v>
     <v>-19.91</v>
-    <v>-1.157E-3</v>
     <v>-4.5686999999999998E-2</v>
-    <v>-0.48120000000000002</v>
     <v>USD</v>
     <v>Tesla, Inc. designs, develops, manufactures, sells and leases high-performance fully electric vehicles and energy generation and storage systems, and offers services related to its products. Its segments include automotive, and energy generation and storage. The automotive segment includes the design, development, manufacturing, sales and leasing of high-performance fully electric vehicles, and sales of automotive regulatory credits. It also includes sales of used vehicles, non-warranty maintenance services and collisions, part sales, paid supercharging, insurance services revenue and retail merchandise sales. The energy generation and storage segment include the design, manufacture, installation, sales and leasing of solar energy generation and energy storage products and related services and sales of solar energy systems incentives. Its consumer vehicles include the Model 3, Y, S, X and Cybertruck. Its lithium-ion battery energy storage products include Powerwall and Megapack.</v>
     <v>134785</v>
@@ -8104,21 +7886,20 @@
     <v>429.6</v>
     <v>Automobiles &amp; Auto Parts</v>
     <v>Stock</v>
-    <v>46174.905778286717</v>
+    <v>46174.999990115626</v>
     <v>254</v>
     <v>415.43</v>
     <v>1561930497120</v>
     <v>TESLA, INC.</v>
     <v>TESLA, INC.</v>
     <v>427.49</v>
-    <v>380.11149999999998</v>
+    <v>380.12540000000001</v>
     <v>435.79</v>
     <v>415.88</v>
-    <v>415.39879999999999</v>
     <v>3755724000</v>
     <v>TSLA</v>
     <v>TESLA, INC. (XNAS:TSLA)</v>
-    <v>44497485</v>
+    <v>768704</v>
     <v>53142959</v>
     <v>2024</v>
   </rv>
@@ -8143,11 +7924,9 @@
     <v>4</v>
     <v>796.25</v>
     <v>520.26</v>
-    <v>1.2309000000000001</v>
+    <v>1.2323</v>
     <v>-32.04</v>
-    <v>-1.998E-4</v>
     <v>-5.0654999999999999E-2</v>
-    <v>-0.12</v>
     <v>USD</v>
     <v>Meta Platforms, Inc. is building human connections, powered by artificial intelligence and immersive technologies. The Company's products enable people to connect and share with friends and family through mobile devices, personal computers, virtual reality (VR) and mixed reality (MR) headsets, augmented reality (AR), and wearables. It also helps people discover and learn about what is going on in the world around them, enabling people to share their experiences, ideas, photos, videos, and other content with audiences ranging from their closest family members and friends to the public at large. The Company's segments include Family of Apps (FoA) and Reality Labs (RL). FoA segment includes Facebook, Instagram, Messenger, WhatsApp and Threads. RL segment includes its virtual, augmented, and mixed reality related consumer hardware, software and content. Its product offerings in VR include its Meta Quest devices, as well as software and content available through the Meta Horizon Store.</v>
     <v>77986</v>
@@ -8158,7 +7937,7 @@
     <v>635.74990000000003</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46174.905725103905</v>
+    <v>46174.999996666404</v>
     <v>257</v>
     <v>599.53</v>
     <v>1524246858810</v>
@@ -8168,11 +7947,10 @@
     <v>18.213200000000001</v>
     <v>632.51</v>
     <v>600.47</v>
-    <v>600.35</v>
     <v>2538423000</v>
     <v>META</v>
     <v>META PLATFORMS, INC. (XNAS:META)</v>
-    <v>28917906</v>
+    <v>334131</v>
     <v>16354221</v>
     <v>2004</v>
   </rv>
@@ -8197,11 +7975,9 @@
     <v>4</v>
     <v>457.22</v>
     <v>104.16500000000001</v>
-    <v>3.4996</v>
+    <v>3.4756</v>
     <v>-9.31</v>
-    <v>-4.8070000000000005E-3</v>
     <v>-5.8520000000000003E-2</v>
-    <v>-0.72</v>
     <v>USD</v>
     <v>Strategy Inc. is a bitcoin treasury and business intelligence company. The Company provides cloud-native, artificial intelligence (AI)-powered enterprise analytics software to thousands of global customers. Its Software Business segment is engaged in the design, development, marketing, and sales of enterprise analytics software platform through cloud subscriptions and licensing arrangements and related services. Its Strategy ONE platform provides access to AI-powered workflows, unlimited data sources, cloud-native technologies, and performance to speed up time from data to action. Strategy One delivers visualization, reporting, and embedded analytics capabilities across retail, banking, technology, manufacturing, insurance, consulting, healthcare, public sector, and others. Its Strategy Mosaic is a universal intelligence layer that provides enterprises with consistent definitions and governance across data sources, regardless of where that data resides or which tools access it.</v>
     <v>1511</v>
@@ -8212,7 +7988,7 @@
     <v>153.87</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46174.905610010937</v>
+    <v>46174.99999954844</v>
     <v>260</v>
     <v>144.29</v>
     <v>53650881462</v>
@@ -8222,11 +7998,10 @@
     <v>0</v>
     <v>159.09</v>
     <v>149.78</v>
-    <v>149.06</v>
     <v>358197900</v>
     <v>MSTR</v>
     <v>STRATEGY INC (XNAS:MSTR)</v>
-    <v>17679798</v>
+    <v>509324</v>
     <v>14837018</v>
     <v>1989</v>
   </rv>
@@ -8251,11 +8026,9 @@
     <v>4</v>
     <v>132.75</v>
     <v>18.965</v>
-    <v>2.2214999999999998</v>
+    <v>2.2315</v>
     <v>-5.35</v>
-    <v>2.1949999999999999E-3</v>
     <v>-4.6651999999999999E-2</v>
-    <v>0.24</v>
     <v>USD</v>
     <v>Intel Corporation is a global designer and manufacturer of semiconductor products. The Company's segments include Intel Products, Intel Foundry, and All Other. Its Intel Products comprise Client Computing Group (CCG) and Data Center and AI (DCAI). CCG delivers platforms and processors that power PCs and edge devices, enabling enhanced performance, connectivity and user experience for consumer and commercial markets with capabilities that also support retail, industrial robotics and AI ecosystems at the edge. DCAI delivers workload-optimized solutions based upon its x86 architecture for data centers, including CPUs, AI accelerators, NICs, IPUs and custom ASICs, enabling performance and scalability for cloud, enterprise, telecommunication and HPC environments. The Intel Foundry segment comprises technology development, manufacturing and foundry services, developing new semiconductor process technologies and advanced packaging technologies. All Other segments include Mobileye and Other.</v>
     <v>83200</v>
@@ -8266,7 +8039,7 @@
     <v>113.3</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46174.905762303126</v>
+    <v>46174.999999964843</v>
     <v>263</v>
     <v>106.33</v>
     <v>549492580000</v>
@@ -8276,11 +8049,10 @@
     <v>0</v>
     <v>114.68</v>
     <v>109.33</v>
-    <v>109.57</v>
     <v>5026000000</v>
     <v>INTC</v>
     <v>INTEL CORPORATION (XNAS:INTC)</v>
-    <v>134424917</v>
+    <v>4578516</v>
     <v>153807580</v>
     <v>1989</v>
   </rv>
@@ -8305,11 +8077,9 @@
     <v>4</v>
     <v>90.9</v>
     <v>51.93</v>
-    <v>1.4936</v>
+    <v>1.4829000000000001</v>
     <v>-2.36</v>
-    <v>-2.5169999999999997E-3</v>
     <v>-3.0314999999999998E-2</v>
-    <v>-0.19</v>
     <v>USD</v>
     <v>Skyworks Solutions, Inc. provides wireless networking services. The Company’s analog and mixed-signal semiconductors are connecting people, places, and things, spanning a number of new applications within the aerospace, automotive, broadband, cellular infrastructure, connected home, defense, entertainment and gaming, industrial, medical, smartphone, tablet, and wearable markets. It operates engineering, manufacturing, sales, and service facilities throughout Asia, Europe, and North America. The Company offers a range of products, such as Amplifiers, Attenuators, Diodes, Audio And Radio, Clocks And Timing, Front-End Modules, Isolation, Modems And DAAs, Optocouplers, Power Management, Power Over Ethernet, RF Passives, Television (TV) And Video, Switches, and Voice. Its engineering, marketing, operations, sales, and support facilities are located throughout Asia, Europe, and North America.</v>
     <v>10000</v>
@@ -8320,21 +8090,20 @@
     <v>77.81</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46174.902074779689</v>
+    <v>46174.999487765628</v>
     <v>266</v>
     <v>74.16</v>
     <v>11354141391</v>
     <v>SKYWORKS SOLUTIONS, INC.</v>
     <v>SKYWORKS SOLUTIONS, INC.</v>
     <v>77.8</v>
-    <v>29.823799999999999</v>
+    <v>29.8233</v>
     <v>77.849999999999994</v>
     <v>75.489999999999995</v>
-    <v>75.3</v>
     <v>150405900</v>
     <v>SWKS</v>
     <v>SKYWORKS SOLUTIONS, INC. (XNAS:SWKS)</v>
-    <v>4866425</v>
+    <v>12439</v>
     <v>5285933</v>
     <v>2002</v>
   </rv>
@@ -8357,9 +8126,7 @@
     <v>84.78</v>
     <v>2.625</v>
     <v>-22.76</v>
-    <v>-1.9557000000000001E-2</v>
     <v>-6.6385E-2</v>
-    <v>-6.26</v>
     <v>USD</v>
     <v>Astera Labs, Inc. is a global semiconductor company. The Company provides semiconductor-based connectivity solutions for cloud and artificial intelligence (AI) infrastructure. It has developed and deployed its Intelligent Connectivity Platform built from the ground up for cloud and AI infrastructure. Its Intelligent Connectivity Platform provides its customers with the ability to deploy and operate high-performance cloud and AI infrastructure at scale, addressing an increasingly diverse set of requirements. It provides its connectivity products in various form factors, including Integrated Circuits (ICs), boards, and modules. Its PCIe, CXL and Ethernet semiconductor-based connectivity solutions are purpose-built to unleash the potential of accelerated computing at cloud-scale. The Company’s products include Aries products, which include its COSMOS software suite; Taurus products, which are hardware modules based on its Taurus ICs; Leo products; and Scorpio products.</v>
     <v>756</v>
@@ -8370,20 +8137,19 @@
     <v>333.42989999999998</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46174.905565231253</v>
+    <v>46174.999917719528</v>
     <v>316.00009999999997</v>
     <v>54865954710</v>
     <v>ASTERA LABS, INC.</v>
     <v>ASTERA LABS, INC.</v>
     <v>328.12</v>
-    <v>215.78129999999999</v>
+    <v>215.7799</v>
     <v>342.85</v>
     <v>320.08999999999997</v>
-    <v>313.83</v>
     <v>171407900</v>
     <v>ALAB</v>
     <v>ASTERA LABS, INC. (XNAS:ALAB)</v>
-    <v>5536599</v>
+    <v>81620</v>
     <v>6216413</v>
     <v>2017</v>
   </rv>
@@ -8408,11 +8174,9 @@
     <v>4</v>
     <v>412.7</v>
     <v>243.3</v>
-    <v>1.091</v>
+    <v>1.0992999999999999</v>
     <v>-22.05</v>
-    <v>2.6350000000000002E-3</v>
     <v>-7.6629000000000003E-2</v>
-    <v>0.7</v>
     <v>USD</v>
     <v>Constellation Energy Corporation is a producer of emissions-free energy and an energy supplier to businesses, homes and public sector customers nationwide. The Company’s nuclear, hydro, wind, and solar generation facilities have the generating capacity to power the equivalent of 27 million homes, providing about 10% of the nation’s clean energy. Its segments include Mid-Atlantic, Midwest, New York, ERCOT, and Other Power Regions. Through its integrated business operations, it sells electricity, natural gas, and other energy-related products and sustainable solutions to various types of customers, including distribution utilities, municipalities, cooperatives, commercial, industrial, public sector, and residential customers in markets across multiple geographic regions. It operates approximately 55 gigawatts of capacity from nuclear, natural gas, geothermal, hydro, wind and solar facilities.</v>
     <v>15291</v>
@@ -8423,21 +8187,20 @@
     <v>278.61</v>
     <v>Electrical Utilities &amp; IPPs</v>
     <v>Stock</v>
-    <v>46174.905717696092</v>
+    <v>46174.999793796094</v>
     <v>271</v>
     <v>264.20999999999998</v>
     <v>95968209570</v>
     <v>CONSTELLATION ENERGY CORPORATION.</v>
     <v>CONSTELLATION ENERGY CORPORATION.</v>
     <v>275</v>
-    <v>23.083100000000002</v>
+    <v>23.083200000000001</v>
     <v>287.75</v>
     <v>265.7</v>
-    <v>266.39999999999998</v>
     <v>361190100</v>
     <v>CEG</v>
     <v>CONSTELLATION ENERGY CORPORATION. (XNAS:CEG)</v>
-    <v>11448720</v>
+    <v>41216</v>
     <v>3298261</v>
     <v>2021</v>
   </rv>
@@ -8478,11 +8241,9 @@
     <v>4</v>
     <v>259.92</v>
     <v>121.99</v>
-    <v>1.5985</v>
+    <v>1.6017999999999999</v>
     <v>-22.03</v>
-    <v>4.411E-3</v>
     <v>-8.7761999999999993E-2</v>
-    <v>1.01</v>
     <v>USD</v>
     <v>Qualcomm Incorporated is engaged in the development and commercialization of foundational technologies for the wireless industry, including third generation (3G), fourth generation (4G) and fifth generation (5G) wireless connectivity, and high-performance and low-power computing, including on-device artificial intelligence. Its segments include Qualcomm CDMA Technologies (QCT), Qualcomm Technology Licensing (QTL) and Qualcomm Strategic Initiatives. QCT develops and supplies integrated circuits and system software based on 3G/4G/5G and other technologies, including radio frequency front-end, digital cockpit and advanced driver assistance and automated driving, Internet of things including consumer electronic devices, industrial devices and edge networking products. QTL grants licenses or otherwise provides rights to use portions of its intellectual property portfolio that includes certain patent rights essential to and/or useful in the manufacture and sale of certain wireless products.</v>
     <v>52000</v>
@@ -8494,53 +8255,52 @@
     <v>276</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46174.905740682814</v>
+    <v>46174.999967696094</v>
     <v>277</v>
     <v>226.81180000000001</v>
     <v>241355460000</v>
     <v>QUALCOMM INCORPORATED</v>
     <v>QUALCOMM INCORPORATED</v>
     <v>233.33</v>
-    <v>24.908100000000001</v>
+    <v>24.908000000000001</v>
     <v>251.02</v>
     <v>228.99</v>
-    <v>230</v>
     <v>1054000000</v>
     <v>QCOM</v>
     <v>QUALCOMM INCORPORATED (XNAS:QCOM)</v>
-    <v>21105476</v>
+    <v>403719</v>
     <v>31038670</v>
     <v>1991</v>
   </rv>
   <rv s="2">
     <v>278</v>
   </rv>
-  <rv s="13">
+  <rv s="11">
     <v>en-GB</v>
     <v>avyu4c</v>
     <v>268435456</v>
     <v>1</v>
     <v>Powered by Refinitiv</v>
+    <v>26</v>
+    <v>USD/GBP</v>
     <v>27</v>
-    <v>USD/GBP</v>
     <v>28</v>
+    <v>Finance</v>
     <v>29</v>
-    <v>Finance</v>
-    <v>30</v>
     <v>0.76859999999999995</v>
     <v>0.72099999999999997</v>
-    <v>-3.8699999999999997E-4</v>
-    <v>-5.2070000000000003E-4</v>
+    <v>-8.2799999999999996E-4</v>
+    <v>-1.114E-3</v>
     <v>GBP</v>
     <v>USD</v>
-    <v>0.74319999999999997</v>
+    <v>0.74360000000000004</v>
     <v>Currency Pair</v>
-    <v>46174.905810185184</v>
-    <v>0.74280000000000002</v>
+    <v>46175.487256944441</v>
+    <v>0.74180000000000001</v>
     <v>US Dollar/UK Pound Sterling FX Cross Rate</v>
     <v>0.74319999999999997</v>
     <v>0.74319999999999997</v>
-    <v>0.74280000000000002</v>
+    <v>0.74229999999999996</v>
     <v>USDGBP</v>
     <v>USD/GBP</v>
   </rv>
@@ -8551,217 +8311,10 @@
 </file>
 
 <file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="14">
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="12">
   <s t="_hyperlink">
     <k n="Address" t="s"/>
     <k n="Text" t="s"/>
-  </s>
-  <s t="_linkedentitycore">
-    <k n="%EntityCulture" t="s"/>
-    <k n="%EntityId" t="s"/>
-    <k n="%EntityServiceId"/>
-    <k n="%IsRefreshable" t="b"/>
-    <k n="%ProviderInfo" t="s"/>
-    <k n="_Display" t="spb"/>
-    <k n="_DisplayString" t="s"/>
-    <k n="_Flags" t="spb"/>
-    <k n="_Format" t="spb"/>
-    <k n="_Icon" t="s"/>
-    <k n="_SubLabel" t="spb"/>
-    <k n="52 week high"/>
-    <k n="52 week low"/>
-    <k n="Beta"/>
-    <k n="Change"/>
-    <k n="Change % (Extended hours)"/>
-    <k n="Change (%)"/>
-    <k n="Change (Extended hours)"/>
-    <k n="Currency" t="s"/>
-    <k n="Description" t="s"/>
-    <k n="Employees"/>
-    <k n="Exchange" t="s"/>
-    <k n="Exchange abbreviation" t="s"/>
-    <k n="ExchangeID" t="s"/>
-    <k n="Headquarters" t="s"/>
-    <k n="High"/>
-    <k n="Industry" t="s"/>
-    <k n="Instrument type" t="s"/>
-    <k n="Last trade time"/>
-    <k n="LearnMoreOnLink" t="r"/>
-    <k n="Low"/>
-    <k n="Market cap"/>
-    <k n="Name" t="s"/>
-    <k n="Official name" t="s"/>
-    <k n="Open"/>
-    <k n="P/E"/>
-    <k n="Previous close"/>
-    <k n="Price"/>
-    <k n="Price (Extended hours)"/>
-    <k n="Shares outstanding"/>
-    <k n="Ticker symbol" t="s"/>
-    <k n="UniqueName" t="s"/>
-    <k n="Volume"/>
-    <k n="Volume average"/>
-    <k n="Year incorporated"/>
-  </s>
-  <s t="_linkedentity">
-    <k n="%cvi" t="r"/>
-  </s>
-  <s t="_sourceattribution">
-    <k n="License" t="r"/>
-    <k n="Source" t="r"/>
-  </s>
-  <s t="_imageurl">
-    <k n="_Provider" t="spb"/>
-    <k n="Address" t="s"/>
-    <k n="Attribution" t="r"/>
-    <k n="ComputedImage" t="b"/>
-    <k n="More Images Address" t="s"/>
-    <k n="Text" t="s"/>
-  </s>
-  <s t="_linkedentitycore">
-    <k n="%EntityCulture" t="s"/>
-    <k n="%EntityId" t="s"/>
-    <k n="%EntityServiceId"/>
-    <k n="%IsRefreshable" t="b"/>
-    <k n="%ProviderInfo" t="s"/>
-    <k n="_Display" t="spb"/>
-    <k n="_DisplayString" t="s"/>
-    <k n="_Flags" t="spb"/>
-    <k n="_Format" t="spb"/>
-    <k n="_Icon" t="s"/>
-    <k n="_SubLabel" t="spb"/>
-    <k n="52 week high"/>
-    <k n="52 week low"/>
-    <k n="Beta"/>
-    <k n="Change"/>
-    <k n="Change % (Extended hours)"/>
-    <k n="Change (%)"/>
-    <k n="Change (Extended hours)"/>
-    <k n="Currency" t="s"/>
-    <k n="Description" t="s"/>
-    <k n="Employees"/>
-    <k n="Exchange" t="s"/>
-    <k n="Exchange abbreviation" t="s"/>
-    <k n="ExchangeID" t="s"/>
-    <k n="Headquarters" t="s"/>
-    <k n="High"/>
-    <k n="Image" t="r"/>
-    <k n="Industry" t="s"/>
-    <k n="Instrument type" t="s"/>
-    <k n="Last trade time"/>
-    <k n="LearnMoreOnLink" t="r"/>
-    <k n="Low"/>
-    <k n="Market cap"/>
-    <k n="Name" t="s"/>
-    <k n="Official name" t="s"/>
-    <k n="Open"/>
-    <k n="P/E"/>
-    <k n="Previous close"/>
-    <k n="Price"/>
-    <k n="Price (Extended hours)"/>
-    <k n="Shares outstanding"/>
-    <k n="Ticker symbol" t="s"/>
-    <k n="UniqueName" t="s"/>
-    <k n="Volume"/>
-    <k n="Volume average"/>
-    <k n="Year incorporated"/>
-  </s>
-  <s t="_linkedentitycore">
-    <k n="%EntityCulture" t="s"/>
-    <k n="%EntityId" t="s"/>
-    <k n="%EntityServiceId"/>
-    <k n="%IsRefreshable" t="b"/>
-    <k n="%ProviderInfo" t="s"/>
-    <k n="_Display" t="spb"/>
-    <k n="_DisplayString" t="s"/>
-    <k n="_Flags" t="spb"/>
-    <k n="_Format" t="spb"/>
-    <k n="_Icon" t="s"/>
-    <k n="_SubLabel" t="spb"/>
-    <k n="52 week high"/>
-    <k n="52 week low"/>
-    <k n="Beta"/>
-    <k n="Change"/>
-    <k n="Change % (Extended hours)"/>
-    <k n="Change (%)"/>
-    <k n="Change (Extended hours)"/>
-    <k n="Currency" t="s"/>
-    <k n="Description" t="s"/>
-    <k n="Employees"/>
-    <k n="Exchange" t="s"/>
-    <k n="Exchange abbreviation" t="s"/>
-    <k n="ExchangeID" t="s"/>
-    <k n="Headquarters" t="s"/>
-    <k n="High"/>
-    <k n="Industry" t="s"/>
-    <k n="Instrument type" t="s"/>
-    <k n="Last trade time"/>
-    <k n="Low"/>
-    <k n="Market cap"/>
-    <k n="Name" t="s"/>
-    <k n="Official name" t="s"/>
-    <k n="Open"/>
-    <k n="P/E"/>
-    <k n="Previous close"/>
-    <k n="Price"/>
-    <k n="Price (Extended hours)"/>
-    <k n="Shares outstanding"/>
-    <k n="Ticker symbol" t="s"/>
-    <k n="UniqueName" t="s"/>
-    <k n="Volume"/>
-    <k n="Volume average"/>
-    <k n="Year incorporated"/>
-  </s>
-  <s t="_linkedentitycore">
-    <k n="%EntityCulture" t="s"/>
-    <k n="%EntityId" t="s"/>
-    <k n="%EntityServiceId"/>
-    <k n="%IsRefreshable" t="b"/>
-    <k n="%ProviderInfo" t="s"/>
-    <k n="_Display" t="spb"/>
-    <k n="_DisplayString" t="s"/>
-    <k n="_Flags" t="spb"/>
-    <k n="_Format" t="spb"/>
-    <k n="_Icon" t="s"/>
-    <k n="_SubLabel" t="spb"/>
-    <k n="52 week high"/>
-    <k n="52 week low"/>
-    <k n="Beta"/>
-    <k n="Change"/>
-    <k n="Change % (Extended hours)"/>
-    <k n="Change (%)"/>
-    <k n="Change (Extended hours)"/>
-    <k n="Currency" t="s"/>
-    <k n="Description" t="s"/>
-    <k n="Employees"/>
-    <k n="Exchange" t="s"/>
-    <k n="Exchange abbreviation" t="s"/>
-    <k n="ExchangeID" t="s"/>
-    <k n="Headquarters" t="s"/>
-    <k n="High"/>
-    <k n="Industry" t="s"/>
-    <k n="Instrument type" t="s"/>
-    <k n="Last trade time"/>
-    <k n="LearnMoreOnLink" t="r"/>
-    <k n="Low"/>
-    <k n="Market cap"/>
-    <k n="Name" t="s"/>
-    <k n="Official name" t="s"/>
-    <k n="Open"/>
-    <k n="Previous close"/>
-    <k n="Price"/>
-    <k n="Price (Extended hours)"/>
-    <k n="Shares outstanding"/>
-    <k n="Ticker symbol" t="s"/>
-    <k n="UniqueName" t="s"/>
-    <k n="Volume"/>
-    <k n="Volume average"/>
-    <k n="Year incorporated"/>
-  </s>
-  <s t="_error">
-    <k n="errorType" t="i"/>
-    <k n="field" t="s"/>
-    <k n="subType" t="i"/>
   </s>
   <s t="_linkedentitycore">
     <k n="%EntityCulture" t="s"/>
@@ -8807,44 +8360,20 @@
     <k n="Volume average"/>
     <k n="Year incorporated"/>
   </s>
-  <s t="_linkedentitycore">
-    <k n="%EntityCulture" t="s"/>
-    <k n="%EntityId" t="s"/>
-    <k n="%EntityServiceId"/>
-    <k n="%IsRefreshable" t="b"/>
-    <k n="%ProviderInfo" t="s"/>
-    <k n="_Display" t="spb"/>
-    <k n="_DisplayString" t="s"/>
-    <k n="_Flags" t="spb"/>
-    <k n="_Format" t="spb"/>
-    <k n="_Icon" t="s"/>
-    <k n="_SubLabel" t="spb"/>
-    <k n="52 week high"/>
-    <k n="52 week low"/>
-    <k n="Beta"/>
-    <k n="Change"/>
-    <k n="Change % (Extended hours)"/>
-    <k n="Change (%)"/>
-    <k n="Change (Extended hours)"/>
-    <k n="Currency" t="s"/>
-    <k n="Exchange" t="s"/>
-    <k n="Exchange abbreviation" t="s"/>
-    <k n="Expense ratio"/>
-    <k n="High"/>
-    <k n="Instrument type" t="s"/>
-    <k n="Last trade time"/>
-    <k n="LearnMoreOnLink" t="r"/>
-    <k n="Low"/>
-    <k n="Market cap"/>
-    <k n="Name" t="s"/>
-    <k n="Open"/>
-    <k n="Previous close"/>
-    <k n="Price"/>
-    <k n="Price (Extended hours)"/>
-    <k n="Ticker symbol" t="s"/>
-    <k n="UniqueName" t="s"/>
-    <k n="Volume"/>
-    <k n="Volume average"/>
+  <s t="_linkedentity">
+    <k n="%cvi" t="r"/>
+  </s>
+  <s t="_sourceattribution">
+    <k n="License" t="r"/>
+    <k n="Source" t="r"/>
+  </s>
+  <s t="_imageurl">
+    <k n="_Provider" t="spb"/>
+    <k n="Address" t="s"/>
+    <k n="Attribution" t="r"/>
+    <k n="ComputedImage" t="b"/>
+    <k n="More Images Address" t="s"/>
+    <k n="Text" t="s"/>
   </s>
   <s t="_linkedentitycore">
     <k n="%EntityCulture" t="s"/>
@@ -8862,9 +8391,7 @@
     <k n="52 week low"/>
     <k n="Beta"/>
     <k n="Change"/>
-    <k n="Change % (Extended hours)"/>
     <k n="Change (%)"/>
-    <k n="Change (Extended hours)"/>
     <k n="Currency" t="s"/>
     <k n="Description" t="s"/>
     <k n="Employees"/>
@@ -8873,6 +8400,7 @@
     <k n="ExchangeID" t="s"/>
     <k n="Headquarters" t="s"/>
     <k n="High"/>
+    <k n="Image" t="r"/>
     <k n="Industry" t="s"/>
     <k n="Instrument type" t="s"/>
     <k n="Last trade time"/>
@@ -8885,12 +8413,12 @@
     <k n="P/E"/>
     <k n="Previous close"/>
     <k n="Price"/>
-    <k n="Price (Extended hours)"/>
     <k n="Shares outstanding"/>
     <k n="Ticker symbol" t="s"/>
     <k n="UniqueName" t="s"/>
     <k n="Volume"/>
     <k n="Volume average"/>
+    <k n="Year incorporated"/>
   </s>
   <s t="_linkedentitycore">
     <k n="%EntityCulture" t="s"/>
@@ -8949,6 +8477,133 @@
     <k n="_SubLabel" t="spb"/>
     <k n="52 week high"/>
     <k n="52 week low"/>
+    <k n="Beta"/>
+    <k n="Change"/>
+    <k n="Change (%)"/>
+    <k n="Currency" t="s"/>
+    <k n="Description" t="s"/>
+    <k n="Employees"/>
+    <k n="Exchange" t="s"/>
+    <k n="Exchange abbreviation" t="s"/>
+    <k n="ExchangeID" t="s"/>
+    <k n="Headquarters" t="s"/>
+    <k n="High"/>
+    <k n="Industry" t="s"/>
+    <k n="Instrument type" t="s"/>
+    <k n="Last trade time"/>
+    <k n="LearnMoreOnLink" t="r"/>
+    <k n="Low"/>
+    <k n="Market cap"/>
+    <k n="Name" t="s"/>
+    <k n="Official name" t="s"/>
+    <k n="Open"/>
+    <k n="Previous close"/>
+    <k n="Price"/>
+    <k n="Shares outstanding"/>
+    <k n="Ticker symbol" t="s"/>
+    <k n="UniqueName" t="s"/>
+    <k n="Volume"/>
+    <k n="Volume average"/>
+    <k n="Year incorporated"/>
+  </s>
+  <s t="_error">
+    <k n="errorType" t="i"/>
+    <k n="field" t="s"/>
+    <k n="subType" t="i"/>
+  </s>
+  <s t="_linkedentitycore">
+    <k n="%EntityCulture" t="s"/>
+    <k n="%EntityId" t="s"/>
+    <k n="%EntityServiceId"/>
+    <k n="%IsRefreshable" t="b"/>
+    <k n="%ProviderInfo" t="s"/>
+    <k n="_Display" t="spb"/>
+    <k n="_DisplayString" t="s"/>
+    <k n="_Flags" t="spb"/>
+    <k n="_Format" t="spb"/>
+    <k n="_Icon" t="s"/>
+    <k n="_SubLabel" t="spb"/>
+    <k n="52 week high"/>
+    <k n="52 week low"/>
+    <k n="Beta"/>
+    <k n="Change"/>
+    <k n="Change (%)"/>
+    <k n="Currency" t="s"/>
+    <k n="Exchange" t="s"/>
+    <k n="Exchange abbreviation" t="s"/>
+    <k n="Expense ratio"/>
+    <k n="High"/>
+    <k n="Instrument type" t="s"/>
+    <k n="Last trade time"/>
+    <k n="LearnMoreOnLink" t="r"/>
+    <k n="Low"/>
+    <k n="Market cap"/>
+    <k n="Name" t="s"/>
+    <k n="Open"/>
+    <k n="Previous close"/>
+    <k n="Price"/>
+    <k n="Ticker symbol" t="s"/>
+    <k n="UniqueName" t="s"/>
+    <k n="Volume"/>
+    <k n="Volume average"/>
+  </s>
+  <s t="_linkedentitycore">
+    <k n="%EntityCulture" t="s"/>
+    <k n="%EntityId" t="s"/>
+    <k n="%EntityServiceId"/>
+    <k n="%IsRefreshable" t="b"/>
+    <k n="%ProviderInfo" t="s"/>
+    <k n="_Display" t="spb"/>
+    <k n="_DisplayString" t="s"/>
+    <k n="_Flags" t="spb"/>
+    <k n="_Format" t="spb"/>
+    <k n="_Icon" t="s"/>
+    <k n="_SubLabel" t="spb"/>
+    <k n="52 week high"/>
+    <k n="52 week low"/>
+    <k n="Beta"/>
+    <k n="Change"/>
+    <k n="Change (%)"/>
+    <k n="Currency" t="s"/>
+    <k n="Description" t="s"/>
+    <k n="Employees"/>
+    <k n="Exchange" t="s"/>
+    <k n="Exchange abbreviation" t="s"/>
+    <k n="ExchangeID" t="s"/>
+    <k n="Headquarters" t="s"/>
+    <k n="High"/>
+    <k n="Industry" t="s"/>
+    <k n="Instrument type" t="s"/>
+    <k n="Last trade time"/>
+    <k n="LearnMoreOnLink" t="r"/>
+    <k n="Low"/>
+    <k n="Market cap"/>
+    <k n="Name" t="s"/>
+    <k n="Official name" t="s"/>
+    <k n="Open"/>
+    <k n="P/E"/>
+    <k n="Previous close"/>
+    <k n="Price"/>
+    <k n="Shares outstanding"/>
+    <k n="Ticker symbol" t="s"/>
+    <k n="UniqueName" t="s"/>
+    <k n="Volume"/>
+    <k n="Volume average"/>
+  </s>
+  <s t="_linkedentitycore">
+    <k n="%EntityCulture" t="s"/>
+    <k n="%EntityId" t="s"/>
+    <k n="%EntityServiceId"/>
+    <k n="%IsRefreshable" t="b"/>
+    <k n="%ProviderInfo" t="s"/>
+    <k n="_Display" t="spb"/>
+    <k n="_DisplayString" t="s"/>
+    <k n="_Flags" t="spb"/>
+    <k n="_Format" t="spb"/>
+    <k n="_Icon" t="s"/>
+    <k n="_SubLabel" t="spb"/>
+    <k n="52 week high"/>
+    <k n="52 week low"/>
     <k n="Change"/>
     <k n="Change (%)"/>
     <k n="Currency" t="s"/>
@@ -8969,194 +8624,7 @@
 
 <file path=xl/richData/rdsupportingpropertybag.xml><?xml version="1.0" encoding="utf-8"?>
 <supportingPropertyBags xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2">
-  <spbArrays count="9">
-    <a count="45">
-      <v t="s">%EntityServiceId</v>
-      <v t="s">_Format</v>
-      <v t="s">%IsRefreshable</v>
-      <v t="s">%EntityCulture</v>
-      <v t="s">%EntityId</v>
-      <v t="s">_Icon</v>
-      <v t="s">_Display</v>
-      <v t="s">Name</v>
-      <v t="s">_SubLabel</v>
-      <v t="s">Price</v>
-      <v t="s">Price (Extended hours)</v>
-      <v t="s">Exchange</v>
-      <v t="s">Official name</v>
-      <v t="s">Last trade time</v>
-      <v t="s">Ticker symbol</v>
-      <v t="s">Exchange abbreviation</v>
-      <v t="s">Change</v>
-      <v t="s">Change (Extended hours)</v>
-      <v t="s">Change (%)</v>
-      <v t="s">Change % (Extended hours)</v>
-      <v t="s">Currency</v>
-      <v t="s">Previous close</v>
-      <v t="s">Open</v>
-      <v t="s">High</v>
-      <v t="s">Low</v>
-      <v t="s">52 week high</v>
-      <v t="s">52 week low</v>
-      <v t="s">Volume</v>
-      <v t="s">Volume average</v>
-      <v t="s">Market cap</v>
-      <v t="s">Beta</v>
-      <v t="s">P/E</v>
-      <v t="s">Shares outstanding</v>
-      <v t="s">Description</v>
-      <v t="s">Employees</v>
-      <v t="s">Headquarters</v>
-      <v t="s">Industry</v>
-      <v t="s">Instrument type</v>
-      <v t="s">Year incorporated</v>
-      <v t="s">_Flags</v>
-      <v t="s">UniqueName</v>
-      <v t="s">_DisplayString</v>
-      <v t="s">LearnMoreOnLink</v>
-      <v t="s">ExchangeID</v>
-      <v t="s">%ProviderInfo</v>
-    </a>
-    <a count="46">
-      <v t="s">%EntityServiceId</v>
-      <v t="s">_Format</v>
-      <v t="s">%IsRefreshable</v>
-      <v t="s">%EntityCulture</v>
-      <v t="s">%EntityId</v>
-      <v t="s">_Icon</v>
-      <v t="s">_Display</v>
-      <v t="s">Name</v>
-      <v t="s">_SubLabel</v>
-      <v t="s">Price</v>
-      <v t="s">Price (Extended hours)</v>
-      <v t="s">Exchange</v>
-      <v t="s">Official name</v>
-      <v t="s">Last trade time</v>
-      <v t="s">Ticker symbol</v>
-      <v t="s">Exchange abbreviation</v>
-      <v t="s">Change</v>
-      <v t="s">Change (Extended hours)</v>
-      <v t="s">Change (%)</v>
-      <v t="s">Change % (Extended hours)</v>
-      <v t="s">Currency</v>
-      <v t="s">Previous close</v>
-      <v t="s">Open</v>
-      <v t="s">High</v>
-      <v t="s">Low</v>
-      <v t="s">52 week high</v>
-      <v t="s">52 week low</v>
-      <v t="s">Volume</v>
-      <v t="s">Volume average</v>
-      <v t="s">Market cap</v>
-      <v t="s">Beta</v>
-      <v t="s">P/E</v>
-      <v t="s">Shares outstanding</v>
-      <v t="s">Description</v>
-      <v t="s">Employees</v>
-      <v t="s">Headquarters</v>
-      <v t="s">Industry</v>
-      <v t="s">Instrument type</v>
-      <v t="s">Year incorporated</v>
-      <v t="s">_Flags</v>
-      <v t="s">UniqueName</v>
-      <v t="s">_DisplayString</v>
-      <v t="s">LearnMoreOnLink</v>
-      <v t="s">Image</v>
-      <v t="s">ExchangeID</v>
-      <v t="s">%ProviderInfo</v>
-    </a>
-    <a count="44">
-      <v t="s">%EntityServiceId</v>
-      <v t="s">_Format</v>
-      <v t="s">%IsRefreshable</v>
-      <v t="s">%EntityCulture</v>
-      <v t="s">%EntityId</v>
-      <v t="s">_Icon</v>
-      <v t="s">_Display</v>
-      <v t="s">Name</v>
-      <v t="s">_SubLabel</v>
-      <v t="s">Price</v>
-      <v t="s">Price (Extended hours)</v>
-      <v t="s">Exchange</v>
-      <v t="s">Official name</v>
-      <v t="s">Last trade time</v>
-      <v t="s">Ticker symbol</v>
-      <v t="s">Exchange abbreviation</v>
-      <v t="s">Change</v>
-      <v t="s">Change (Extended hours)</v>
-      <v t="s">Change (%)</v>
-      <v t="s">Change % (Extended hours)</v>
-      <v t="s">Currency</v>
-      <v t="s">Previous close</v>
-      <v t="s">Open</v>
-      <v t="s">High</v>
-      <v t="s">Low</v>
-      <v t="s">52 week high</v>
-      <v t="s">52 week low</v>
-      <v t="s">Volume</v>
-      <v t="s">Volume average</v>
-      <v t="s">Market cap</v>
-      <v t="s">Beta</v>
-      <v t="s">P/E</v>
-      <v t="s">Shares outstanding</v>
-      <v t="s">Description</v>
-      <v t="s">Employees</v>
-      <v t="s">Headquarters</v>
-      <v t="s">Industry</v>
-      <v t="s">Instrument type</v>
-      <v t="s">Year incorporated</v>
-      <v t="s">_Flags</v>
-      <v t="s">UniqueName</v>
-      <v t="s">_DisplayString</v>
-      <v t="s">ExchangeID</v>
-      <v t="s">%ProviderInfo</v>
-    </a>
-    <a count="44">
-      <v t="s">%EntityServiceId</v>
-      <v t="s">_Format</v>
-      <v t="s">%IsRefreshable</v>
-      <v t="s">%EntityCulture</v>
-      <v t="s">%EntityId</v>
-      <v t="s">_Icon</v>
-      <v t="s">_Display</v>
-      <v t="s">Name</v>
-      <v t="s">_SubLabel</v>
-      <v t="s">Price</v>
-      <v t="s">Price (Extended hours)</v>
-      <v t="s">Exchange</v>
-      <v t="s">Official name</v>
-      <v t="s">Last trade time</v>
-      <v t="s">Ticker symbol</v>
-      <v t="s">Exchange abbreviation</v>
-      <v t="s">Change</v>
-      <v t="s">Change (Extended hours)</v>
-      <v t="s">Change (%)</v>
-      <v t="s">Change % (Extended hours)</v>
-      <v t="s">Currency</v>
-      <v t="s">Previous close</v>
-      <v t="s">Open</v>
-      <v t="s">High</v>
-      <v t="s">Low</v>
-      <v t="s">52 week high</v>
-      <v t="s">52 week low</v>
-      <v t="s">Volume</v>
-      <v t="s">Volume average</v>
-      <v t="s">Market cap</v>
-      <v t="s">Beta</v>
-      <v t="s">Shares outstanding</v>
-      <v t="s">Description</v>
-      <v t="s">Employees</v>
-      <v t="s">Headquarters</v>
-      <v t="s">Industry</v>
-      <v t="s">Instrument type</v>
-      <v t="s">Year incorporated</v>
-      <v t="s">_Flags</v>
-      <v t="s">UniqueName</v>
-      <v t="s">_DisplayString</v>
-      <v t="s">LearnMoreOnLink</v>
-      <v t="s">ExchangeID</v>
-      <v t="s">%ProviderInfo</v>
-    </a>
+  <spbArrays count="8">
     <a count="42">
       <v t="s">%EntityServiceId</v>
       <v t="s">_Format</v>
@@ -9201,7 +8669,7 @@
       <v t="s">ExchangeID</v>
       <v t="s">%ProviderInfo</v>
     </a>
-    <a count="37">
+    <a count="43">
       <v t="s">%EntityServiceId</v>
       <v t="s">_Format</v>
       <v t="s">%IsRefreshable</v>
@@ -9212,16 +8680,144 @@
       <v t="s">Name</v>
       <v t="s">_SubLabel</v>
       <v t="s">Price</v>
-      <v t="s">Price (Extended hours)</v>
+      <v t="s">Exchange</v>
+      <v t="s">Official name</v>
+      <v t="s">Last trade time</v>
+      <v t="s">Ticker symbol</v>
+      <v t="s">Exchange abbreviation</v>
+      <v t="s">Change</v>
+      <v t="s">Change (%)</v>
+      <v t="s">Currency</v>
+      <v t="s">Previous close</v>
+      <v t="s">Open</v>
+      <v t="s">High</v>
+      <v t="s">Low</v>
+      <v t="s">52 week high</v>
+      <v t="s">52 week low</v>
+      <v t="s">Volume</v>
+      <v t="s">Volume average</v>
+      <v t="s">Market cap</v>
+      <v t="s">Beta</v>
+      <v t="s">P/E</v>
+      <v t="s">Shares outstanding</v>
+      <v t="s">Description</v>
+      <v t="s">Employees</v>
+      <v t="s">Headquarters</v>
+      <v t="s">Industry</v>
+      <v t="s">Instrument type</v>
+      <v t="s">Year incorporated</v>
+      <v t="s">_Flags</v>
+      <v t="s">UniqueName</v>
+      <v t="s">_DisplayString</v>
+      <v t="s">LearnMoreOnLink</v>
+      <v t="s">Image</v>
+      <v t="s">ExchangeID</v>
+      <v t="s">%ProviderInfo</v>
+    </a>
+    <a count="41">
+      <v t="s">%EntityServiceId</v>
+      <v t="s">_Format</v>
+      <v t="s">%IsRefreshable</v>
+      <v t="s">%EntityCulture</v>
+      <v t="s">%EntityId</v>
+      <v t="s">_Icon</v>
+      <v t="s">_Display</v>
+      <v t="s">Name</v>
+      <v t="s">_SubLabel</v>
+      <v t="s">Price</v>
+      <v t="s">Exchange</v>
+      <v t="s">Official name</v>
+      <v t="s">Last trade time</v>
+      <v t="s">Ticker symbol</v>
+      <v t="s">Exchange abbreviation</v>
+      <v t="s">Change</v>
+      <v t="s">Change (%)</v>
+      <v t="s">Currency</v>
+      <v t="s">Previous close</v>
+      <v t="s">Open</v>
+      <v t="s">High</v>
+      <v t="s">Low</v>
+      <v t="s">52 week high</v>
+      <v t="s">52 week low</v>
+      <v t="s">Volume</v>
+      <v t="s">Volume average</v>
+      <v t="s">Market cap</v>
+      <v t="s">Beta</v>
+      <v t="s">P/E</v>
+      <v t="s">Shares outstanding</v>
+      <v t="s">Description</v>
+      <v t="s">Employees</v>
+      <v t="s">Headquarters</v>
+      <v t="s">Industry</v>
+      <v t="s">Instrument type</v>
+      <v t="s">Year incorporated</v>
+      <v t="s">_Flags</v>
+      <v t="s">UniqueName</v>
+      <v t="s">_DisplayString</v>
+      <v t="s">ExchangeID</v>
+      <v t="s">%ProviderInfo</v>
+    </a>
+    <a count="41">
+      <v t="s">%EntityServiceId</v>
+      <v t="s">_Format</v>
+      <v t="s">%IsRefreshable</v>
+      <v t="s">%EntityCulture</v>
+      <v t="s">%EntityId</v>
+      <v t="s">_Icon</v>
+      <v t="s">_Display</v>
+      <v t="s">Name</v>
+      <v t="s">_SubLabel</v>
+      <v t="s">Price</v>
+      <v t="s">Exchange</v>
+      <v t="s">Official name</v>
+      <v t="s">Last trade time</v>
+      <v t="s">Ticker symbol</v>
+      <v t="s">Exchange abbreviation</v>
+      <v t="s">Change</v>
+      <v t="s">Change (%)</v>
+      <v t="s">Currency</v>
+      <v t="s">Previous close</v>
+      <v t="s">Open</v>
+      <v t="s">High</v>
+      <v t="s">Low</v>
+      <v t="s">52 week high</v>
+      <v t="s">52 week low</v>
+      <v t="s">Volume</v>
+      <v t="s">Volume average</v>
+      <v t="s">Market cap</v>
+      <v t="s">Beta</v>
+      <v t="s">Shares outstanding</v>
+      <v t="s">Description</v>
+      <v t="s">Employees</v>
+      <v t="s">Headquarters</v>
+      <v t="s">Industry</v>
+      <v t="s">Instrument type</v>
+      <v t="s">Year incorporated</v>
+      <v t="s">_Flags</v>
+      <v t="s">UniqueName</v>
+      <v t="s">_DisplayString</v>
+      <v t="s">LearnMoreOnLink</v>
+      <v t="s">ExchangeID</v>
+      <v t="s">%ProviderInfo</v>
+    </a>
+    <a count="34">
+      <v t="s">%EntityServiceId</v>
+      <v t="s">_Format</v>
+      <v t="s">%IsRefreshable</v>
+      <v t="s">%EntityCulture</v>
+      <v t="s">%EntityId</v>
+      <v t="s">_Icon</v>
+      <v t="s">_Display</v>
+      <v t="s">Name</v>
+      <v t="s">_SubLabel</v>
+      <v t="s">Price</v>
       <v t="s">Exchange</v>
       <v t="s">Last trade time</v>
       <v t="s">Ticker symbol</v>
       <v t="s">Exchange abbreviation</v>
       <v t="s">Change</v>
-      <v t="s">Change (Extended hours)</v>
       <v t="s">Expense ratio</v>
       <v t="s">Change (%)</v>
-      <v t="s">Change % (Extended hours)</v>
       <v t="s">Currency</v>
       <v t="s">Previous close</v>
       <v t="s">Open</v>
@@ -9240,7 +8836,7 @@
       <v t="s">LearnMoreOnLink</v>
       <v t="s">%ProviderInfo</v>
     </a>
-    <a count="44">
+    <a count="41">
       <v t="s">%EntityServiceId</v>
       <v t="s">_Format</v>
       <v t="s">%IsRefreshable</v>
@@ -9251,16 +8847,13 @@
       <v t="s">Name</v>
       <v t="s">_SubLabel</v>
       <v t="s">Price</v>
-      <v t="s">Price (Extended hours)</v>
       <v t="s">Exchange</v>
       <v t="s">Official name</v>
       <v t="s">Last trade time</v>
       <v t="s">Ticker symbol</v>
       <v t="s">Exchange abbreviation</v>
       <v t="s">Change</v>
-      <v t="s">Change (Extended hours)</v>
       <v t="s">Change (%)</v>
-      <v t="s">Change % (Extended hours)</v>
       <v t="s">Currency</v>
       <v t="s">Previous close</v>
       <v t="s">Open</v>
@@ -9359,7 +8952,7 @@
       <v t="s">%ProviderInfo</v>
     </a>
   </spbArrays>
-  <spbData count="31">
+  <spbData count="30">
     <spb s="0">
       <v>0</v>
       <v>Name</v>
@@ -9397,19 +8990,13 @@
       <v>8</v>
       <v>9</v>
       <v>4</v>
-      <v>1</v>
-      <v>1</v>
-      <v>5</v>
     </spb>
     <spb s="4">
-      <v>at close</v>
+      <v>Real-Time Nasdaq Last Sale</v>
       <v>from previous close</v>
       <v>from previous close</v>
       <v>Source: Nasdaq Last Sale</v>
       <v>GMT</v>
-      <v>Real-Time Nasdaq Last Sale</v>
-      <v>from close</v>
-      <v>from close</v>
     </spb>
     <spb s="0">
       <v>1</v>
@@ -9449,9 +9036,6 @@
       <v>8</v>
       <v>9</v>
       <v>4</v>
-      <v>1</v>
-      <v>1</v>
-      <v>5</v>
     </spb>
     <spb s="8">
       <v>Powered by Refinitiv</v>
@@ -9490,26 +9074,8 @@
       <v>8</v>
       <v>9</v>
       <v>4</v>
-      <v>1</v>
-      <v>1</v>
-      <v>5</v>
     </spb>
-    <spb s="4">
-      <v>at close</v>
-      <v>from previous close</v>
-      <v>from previous close</v>
-      <v>Source: Nasdaq</v>
-      <v>GMT</v>
-      <v>Delayed 15 minutes</v>
-      <v>from close</v>
-      <v>from close</v>
-    </spb>
-    <spb s="0">
-      <v>4</v>
-      <v>Name</v>
-      <v>LearnMoreOnLink</v>
-    </spb>
-    <spb s="12">
+    <spb s="3">
       <v>11</v>
       <v>2</v>
       <v>2</v>
@@ -9531,24 +9097,31 @@
       <v>9</v>
       <v>4</v>
     </spb>
-    <spb s="13">
+    <spb s="4">
       <v>Delayed 15 minutes</v>
       <v>from previous close</v>
       <v>from previous close</v>
       <v>LSE</v>
       <v>GMT</v>
     </spb>
+    <spb s="4">
+      <v>Delayed 15 minutes</v>
+      <v>from previous close</v>
+      <v>from previous close</v>
+      <v>Source: Nasdaq</v>
+      <v>GMT</v>
+    </spb>
     <spb s="0">
-      <v>5</v>
+      <v>4</v>
       <v>Name</v>
       <v>LearnMoreOnLink</v>
     </spb>
-    <spb s="14">
+    <spb s="12">
       <v>1</v>
       <v>1</v>
       <v>1</v>
     </spb>
-    <spb s="15">
+    <spb s="13">
       <v>1</v>
       <v>2</v>
       <v>1</v>
@@ -9566,26 +9139,20 @@
       <v>4</v>
       <v>7</v>
       <v>9</v>
-      <v>1</v>
-      <v>1</v>
-      <v>5</v>
     </spb>
-    <spb s="16">
-      <v>at close</v>
+    <spb s="14">
+      <v>Real-Time Nasdaq Last Sale</v>
       <v>from previous close</v>
       <v>Source: Nasdaq Last Sale</v>
       <v>from previous close</v>
       <v>GMT</v>
-      <v>Real-Time Nasdaq Last Sale</v>
-      <v>from close</v>
-      <v>from close</v>
     </spb>
     <spb s="0">
-      <v>6</v>
+      <v>5</v>
       <v>Name</v>
       <v>LearnMoreOnLink</v>
     </spb>
-    <spb s="17">
+    <spb s="15">
       <v>1</v>
       <v>2</v>
       <v>2</v>
@@ -9605,15 +9172,12 @@
       <v>7</v>
       <v>9</v>
       <v>4</v>
-      <v>1</v>
-      <v>1</v>
-      <v>5</v>
     </spb>
     <spb s="9">
-      <v>7</v>
+      <v>6</v>
       <v>Name</v>
     </spb>
-    <spb s="12">
+    <spb s="3">
       <v>13</v>
       <v>2</v>
       <v>2</v>
@@ -9635,20 +9199,20 @@
       <v>9</v>
       <v>4</v>
     </spb>
-    <spb s="18">
+    <spb s="16">
       <v>from previous close</v>
       <v>from previous close</v>
       <v>GMT</v>
     </spb>
     <spb s="9">
-      <v>8</v>
+      <v>7</v>
       <v>Name</v>
     </spb>
-    <spb s="19">
+    <spb s="17">
       <v>1</v>
       <v>1</v>
     </spb>
-    <spb s="20">
+    <spb s="18">
       <v>15</v>
       <v>15</v>
       <v>3</v>
@@ -9662,7 +9226,7 @@
       <v>7</v>
       <v>9</v>
     </spb>
-    <spb s="21">
+    <spb s="19">
       <v>GMT</v>
     </spb>
   </spbData>
@@ -9670,7 +9234,7 @@
 </file>
 
 <file path=xl/richData/rdsupportingpropertybagstructure.xml><?xml version="1.0" encoding="utf-8"?>
-<spbStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" count="22">
+<spbStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" count="20">
   <s>
     <k n="^Order" t="spba"/>
     <k n="TitleProperty" t="s"/>
@@ -9708,9 +9272,6 @@
     <k n="Year incorporated" t="i"/>
     <k n="`%EntityServiceId" t="i"/>
     <k n="Shares outstanding" t="i"/>
-    <k n="Price (Extended hours)" t="i"/>
-    <k n="Change (Extended hours)" t="i"/>
-    <k n="Change % (Extended hours)" t="i"/>
   </s>
   <s>
     <k n="Price" t="s"/>
@@ -9718,9 +9279,6 @@
     <k n="Change (%)" t="s"/>
     <k n="ExchangeID" t="s"/>
     <k n="Last trade time" t="s"/>
-    <k n="Price (Extended hours)" t="s"/>
-    <k n="Change (Extended hours)" t="s"/>
-    <k n="Change % (Extended hours)" t="s"/>
   </s>
   <s>
     <k n="ShowInDotNotation" t="b"/>
@@ -9755,9 +9313,6 @@
     <k n="Year incorporated" t="i"/>
     <k n="`%EntityServiceId" t="i"/>
     <k n="Shares outstanding" t="i"/>
-    <k n="Price (Extended hours)" t="i"/>
-    <k n="Change (Extended hours)" t="i"/>
-    <k n="Change % (Extended hours)" t="i"/>
   </s>
   <s>
     <k n="name" t="s"/>
@@ -9791,38 +9346,6 @@
     <k n="Year incorporated" t="i"/>
     <k n="`%EntityServiceId" t="i"/>
     <k n="Shares outstanding" t="i"/>
-    <k n="Price (Extended hours)" t="i"/>
-    <k n="Change (Extended hours)" t="i"/>
-    <k n="Change % (Extended hours)" t="i"/>
-  </s>
-  <s>
-    <k n="Low" t="i"/>
-    <k n="P/E" t="i"/>
-    <k n="Beta" t="i"/>
-    <k n="High" t="i"/>
-    <k n="Name" t="i"/>
-    <k n="Open" t="i"/>
-    <k n="Price" t="i"/>
-    <k n="Change" t="i"/>
-    <k n="Volume" t="i"/>
-    <k n="Employees" t="i"/>
-    <k n="Change (%)" t="i"/>
-    <k n="Market cap" t="i"/>
-    <k n="52 week low" t="i"/>
-    <k n="52 week high" t="i"/>
-    <k n="Previous close" t="i"/>
-    <k n="Volume average" t="i"/>
-    <k n="Last trade time" t="i"/>
-    <k n="Year incorporated" t="i"/>
-    <k n="`%EntityServiceId" t="i"/>
-    <k n="Shares outstanding" t="i"/>
-  </s>
-  <s>
-    <k n="Price" t="s"/>
-    <k n="Change" t="s"/>
-    <k n="Change (%)" t="s"/>
-    <k n="ExchangeID" t="s"/>
-    <k n="Last trade time" t="s"/>
   </s>
   <s>
     <k n="UniqueName" t="spb"/>
@@ -9847,9 +9370,6 @@
     <k n="Volume average" t="i"/>
     <k n="Last trade time" t="i"/>
     <k n="`%EntityServiceId" t="i"/>
-    <k n="Price (Extended hours)" t="i"/>
-    <k n="Change (Extended hours)" t="i"/>
-    <k n="Change % (Extended hours)" t="i"/>
   </s>
   <s>
     <k n="Price" t="s"/>
@@ -9857,9 +9377,6 @@
     <k n="Exchange" t="s"/>
     <k n="Change (%)" t="s"/>
     <k n="Last trade time" t="s"/>
-    <k n="Price (Extended hours)" t="s"/>
-    <k n="Change (Extended hours)" t="s"/>
-    <k n="Change % (Extended hours)" t="s"/>
   </s>
   <s>
     <k n="Low" t="i"/>
@@ -9881,9 +9398,6 @@
     <k n="Last trade time" t="i"/>
     <k n="`%EntityServiceId" t="i"/>
     <k n="Shares outstanding" t="i"/>
-    <k n="Price (Extended hours)" t="i"/>
-    <k n="Change (Extended hours)" t="i"/>
-    <k n="Change % (Extended hours)" t="i"/>
   </s>
   <s>
     <k n="Change" t="s"/>
@@ -9997,7 +9511,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{F82495E7-9F34-4C1F-83EC-FA45D59FA2BD}" name="tblContributions" displayName="tblContributions" ref="A1:C2" totalsRowShown="0">
   <autoFilter ref="A1:C2" xr:uid="{F82495E7-9F34-4C1F-83EC-FA45D59FA2BD}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{EAE9033F-E950-4D8F-AC60-78CCDA7A0C9E}" name="DATE" dataDxfId="34"/>
+    <tableColumn id="1" xr3:uid="{EAE9033F-E950-4D8F-AC60-78CCDA7A0C9E}" name="DATE" dataDxfId="52"/>
     <tableColumn id="2" xr3:uid="{1D40F1FF-D66C-4703-9DEC-93C768793D8F}" name="AMMOUNT"/>
     <tableColumn id="3" xr3:uid="{49855D82-DE07-4257-837D-DD0BE41E988B}" name="Notes"/>
   </tableColumns>
@@ -10006,7 +9520,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{0F5D2F70-2765-43A5-94CB-6AA0CBF0815D}" name="tblCash" displayName="tblCash" ref="A1:B6" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{0F5D2F70-2765-43A5-94CB-6AA0CBF0815D}" name="tblCashReserve" displayName="tblCashReserve" ref="A1:B6" totalsRowShown="0">
   <autoFilter ref="A1:B6" xr:uid="{0F5D2F70-2765-43A5-94CB-6AA0CBF0815D}"/>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{A6D3B042-E459-4CE1-A73F-81F35D8391E9}" name="ACCOUNT"/>
@@ -10025,64 +9539,64 @@
   <tableColumns count="31">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="symbol"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="StockName"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="LastTradeTime" dataDxfId="52">
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="LastTradeTime" dataDxfId="51">
       <calculatedColumnFormula array="1">_FV(B2,"Last trade time",TRUE)</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="TradeCurrency">
       <calculatedColumnFormula array="1">_FV(B2,"Currency")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="StockPrice" dataDxfId="51">
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="StockPrice" dataDxfId="50">
       <calculatedColumnFormula array="1">_FV(B2,"Price")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="ChangePercent" dataDxfId="50">
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="ChangePercent" dataDxfId="49">
       <calculatedColumnFormula array="1">_FV(B2,"Change (%)",TRUE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Change" dataDxfId="49">
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Change" dataDxfId="48">
       <calculatedColumnFormula array="1">_FV(B2,"Change")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="P/E" dataDxfId="48">
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="P/E" dataDxfId="47">
       <calculatedColumnFormula array="1">_FV(B2,"P/E",TRUE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Beta" dataDxfId="47">
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Beta" dataDxfId="46">
       <calculatedColumnFormula array="1">_FV(B2,"Beta")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="52WkHigh" dataDxfId="46">
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="52WkHigh" dataDxfId="45">
       <calculatedColumnFormula array="1">_FV(B2,"52 week high",TRUE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="52WkLow" dataDxfId="45">
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="52WkLow" dataDxfId="44">
       <calculatedColumnFormula array="1">_FV(B2,"52 week low",TRUE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="DayHigh" dataDxfId="44">
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="DayHigh" dataDxfId="43">
       <calculatedColumnFormula array="1">_FV(B2,"High")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="DayLow" dataDxfId="43">
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="DayLow" dataDxfId="42">
       <calculatedColumnFormula array="1">_FV(B2,"Low")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="Open" dataDxfId="42">
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="Open" dataDxfId="41">
       <calculatedColumnFormula array="1">_FV(B2,"Open")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="PreviousClose" dataDxfId="41">
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="PreviousClose" dataDxfId="40">
       <calculatedColumnFormula array="1">_FV(B2,"Previous close",TRUE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Volume" dataDxfId="40">
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Volume" dataDxfId="39">
       <calculatedColumnFormula array="1">_FV(B2,"Volume")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="AverageVolume" dataDxfId="39">
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="AverageVolume" dataDxfId="38">
       <calculatedColumnFormula array="1">_FV(B2,"Volume average",TRUE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="YearIncorported" dataDxfId="38">
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="YearIncorported" dataDxfId="37">
       <calculatedColumnFormula array="1">_FV(B2,"Year incorporated",TRUE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="Employees" dataDxfId="37">
+    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="Employees" dataDxfId="36">
       <calculatedColumnFormula array="1">_FV(B2,"Employees")</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="Industry">
       <calculatedColumnFormula array="1">_FV(B2,"Industry")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0000-000015000000}" name="MarketCap" dataDxfId="36">
+    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0000-000015000000}" name="MarketCap" dataDxfId="35">
       <calculatedColumnFormula array="1">_FV(B2,"Market cap",TRUE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0000-000016000000}" name="SharesOutstanding" dataDxfId="35">
+    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0000-000016000000}" name="SharesOutstanding" dataDxfId="34">
       <calculatedColumnFormula array="1">_FV(B2,"Shares outstanding",TRUE)</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="23" xr3:uid="{00000000-0010-0000-0000-000017000000}" name="50SMA"/>
@@ -11319,10 +10833,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{454C0B5F-D414-47E1-932F-9CDB777530FB}">
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="19.46484375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="24.19921875" customWidth="1"/>
     <col min="2" max="2" width="14.46484375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="14.9296875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="15.73046875" bestFit="1" customWidth="1"/>
@@ -11349,11 +10863,10 @@
     </row>
     <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="B2">
-        <f>+B12</f>
-        <v>10199.26</v>
+        <v>0</v>
       </c>
       <c r="C2">
         <v>11.84</v>
@@ -11376,7 +10889,7 @@
     </row>
     <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>596</v>
+        <v>603</v>
       </c>
       <c r="B3">
         <v>12000</v>
@@ -11399,10 +10912,10 @@
     </row>
     <row r="4" spans="1:9">
       <c r="A4" t="s">
-        <v>597</v>
+        <v>604</v>
       </c>
       <c r="B4">
-        <v>12000</v>
+        <v>20000</v>
       </c>
       <c r="G4" t="s">
         <v>457</v>
@@ -11414,7 +10927,7 @@
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>599</v>
+        <v>605</v>
       </c>
       <c r="B5">
         <f>SUM(CONTRIBUTIONS!B2:B1048576)</f>
@@ -11441,7 +10954,7 @@
     </row>
     <row r="6" spans="1:9">
       <c r="A6" t="s">
-        <v>598</v>
+        <v>606</v>
       </c>
       <c r="B6">
         <v>70</v>
@@ -11450,7 +10963,7 @@
     <row r="7" spans="1:9">
       <c r="D7">
         <f>+C5/D9</f>
-        <v>0.47091923597526886</v>
+        <v>0.40081368394354044</v>
       </c>
       <c r="G7" t="s">
         <v>461</v>
@@ -11473,7 +10986,7 @@
       </c>
       <c r="D9">
         <f>+B5+B4</f>
-        <v>45738.31</v>
+        <v>53738.31</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -11486,10 +10999,13 @@
     </row>
     <row r="11" spans="1:9">
       <c r="A11" t="s">
-        <v>601</v>
+        <v>596</v>
       </c>
       <c r="B11">
         <v>10000</v>
+      </c>
+      <c r="F11" t="s">
+        <v>597</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -11501,6 +11017,9 @@
         <f>SUM(C2:C3)</f>
         <v>21539.05</v>
       </c>
+      <c r="F12" t="s">
+        <v>598</v>
+      </c>
     </row>
     <row r="13" spans="1:9">
       <c r="C13">
@@ -11514,6 +11033,19 @@
       <c r="E13">
         <f>+C5/D13</f>
         <v>1</v>
+      </c>
+      <c r="F13" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="F14" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="F15" t="s">
+        <v>601</v>
       </c>
     </row>
   </sheetData>
@@ -11942,7 +11474,7 @@
       </c>
       <c r="C2" s="2">
         <f t="array" aca="1" ref="C2" ca="1">_FV(B2,"Last trade time",TRUE)</f>
-        <v>46174.905480693749</v>
+        <v>46174.999913471875</v>
       </c>
       <c r="D2" t="str">
         <f t="array" aca="1" ref="D2" ca="1">_FV(B2,"Currency")</f>
@@ -11966,7 +11498,7 @@
       </c>
       <c r="I2" s="6">
         <f t="array" aca="1" ref="I2" ca="1">_FV(B2,"Beta")</f>
-        <v>3.6577000000000002</v>
+        <v>3.6634000000000002</v>
       </c>
       <c r="J2" s="3">
         <f t="array" aca="1" ref="J2" ca="1">_FV(B2,"52 week high",TRUE)</f>
@@ -11994,7 +11526,7 @@
       </c>
       <c r="P2" s="7">
         <f t="array" aca="1" ref="P2" ca="1">_FV(B2,"Volume")</f>
-        <v>15976213</v>
+        <v>512706</v>
       </c>
       <c r="Q2" s="7">
         <f t="array" aca="1" ref="Q2" ca="1">_FV(B2,"Volume average",TRUE)</f>
@@ -12030,7 +11562,7 @@
       </c>
       <c r="C3" s="2" cm="1">
         <f t="array" aca="1" ref="C3" ca="1">_FV(B3,"Last trade time",TRUE)</f>
-        <v>46174.905611087503</v>
+        <v>46174.999931666403</v>
       </c>
       <c r="D3" t="str" cm="1">
         <f t="array" aca="1" ref="D3" ca="1">_FV(B3,"Currency")</f>
@@ -12038,23 +11570,23 @@
       </c>
       <c r="E3" s="3" cm="1">
         <f t="array" aca="1" ref="E3" ca="1">_FV(B3,"Price")</f>
-        <v>227.595</v>
+        <v>227.54</v>
       </c>
       <c r="F3" s="4" cm="1">
         <f t="array" aca="1" ref="F3" ca="1">_FV(B3,"Change (%)",TRUE)</f>
-        <v>0.19384699999999999</v>
+        <v>0.19355899999999998</v>
       </c>
       <c r="G3" s="5" cm="1">
         <f t="array" aca="1" ref="G3" ca="1">_FV(B3,"Change")</f>
-        <v>36.954999999999998</v>
+        <v>36.9</v>
       </c>
       <c r="H3" s="6" cm="1">
         <f t="array" aca="1" ref="H3" ca="1">_FV(B3,"P/E",TRUE)</f>
-        <v>353.79289999999997</v>
+        <v>353.70190000000002</v>
       </c>
       <c r="I3" s="6" cm="1">
         <f t="array" aca="1" ref="I3" ca="1">_FV(B3,"Beta")</f>
-        <v>1.3947000000000001</v>
+        <v>1.367</v>
       </c>
       <c r="J3" s="3" cm="1">
         <f t="array" aca="1" ref="J3" ca="1">_FV(B3,"52 week high",TRUE)</f>
@@ -12082,7 +11614,7 @@
       </c>
       <c r="P3" s="7" cm="1">
         <f t="array" aca="1" ref="P3" ca="1">_FV(B3,"Volume")</f>
-        <v>7279758</v>
+        <v>15989</v>
       </c>
       <c r="Q3" s="7" cm="1">
         <f t="array" aca="1" ref="Q3" ca="1">_FV(B3,"Volume average",TRUE)</f>
@@ -12102,7 +11634,7 @@
       </c>
       <c r="U3" s="7" cm="1">
         <f t="array" aca="1" ref="U3" ca="1">_FV(B3,"Market cap",TRUE)</f>
-        <v>34542980770</v>
+        <v>34534633206</v>
       </c>
       <c r="V3" s="7" cm="1">
         <f t="array" aca="1" ref="V3" ca="1">_FV(B3,"Shares outstanding",TRUE)</f>
@@ -12118,7 +11650,7 @@
       </c>
       <c r="C4" s="2" cm="1">
         <f t="array" aca="1" ref="C4" ca="1">_FV(B4,"Last trade time",TRUE)</f>
-        <v>46174.905448830468</v>
+        <v>46174.999311943749</v>
       </c>
       <c r="D4" t="str" cm="1">
         <f t="array" aca="1" ref="D4" ca="1">_FV(B4,"Currency")</f>
@@ -12142,7 +11674,7 @@
       </c>
       <c r="I4" s="6" cm="1">
         <f t="array" aca="1" ref="I4" ca="1">_FV(B4,"Beta")</f>
-        <v>1.5710999999999999</v>
+        <v>1.5391999999999999</v>
       </c>
       <c r="J4" s="3" cm="1">
         <f t="array" aca="1" ref="J4" ca="1">_FV(B4,"52 week high",TRUE)</f>
@@ -12170,7 +11702,7 @@
       </c>
       <c r="P4" s="7" cm="1">
         <f t="array" aca="1" ref="P4" ca="1">_FV(B4,"Volume")</f>
-        <v>6769673</v>
+        <v>26150</v>
       </c>
       <c r="Q4" s="7" cm="1">
         <f t="array" aca="1" ref="Q4" ca="1">_FV(B4,"Volume average",TRUE)</f>
@@ -12190,11 +11722,11 @@
       </c>
       <c r="U4" s="7" cm="1">
         <f t="array" aca="1" ref="U4" ca="1">_FV(B4,"Market cap",TRUE)</f>
-        <v>32512311728</v>
+        <v>32484847888</v>
       </c>
       <c r="V4" s="7" cm="1">
         <f t="array" aca="1" ref="V4" ca="1">_FV(B4,"Shares outstanding",TRUE)</f>
-        <v>80499930</v>
+        <v>80431930</v>
       </c>
     </row>
     <row r="5" spans="1:31">
@@ -12206,7 +11738,7 @@
       </c>
       <c r="C5" s="2">
         <f t="array" aca="1" ref="C5" ca="1">_FV(B5,"Last trade time",TRUE)</f>
-        <v>46174.905605080472</v>
+        <v>46174.999966863281</v>
       </c>
       <c r="D5" t="str">
         <f t="array" aca="1" ref="D5" ca="1">_FV(B5,"Currency")</f>
@@ -12258,7 +11790,7 @@
       </c>
       <c r="P5" s="7">
         <f t="array" aca="1" ref="P5" ca="1">_FV(B5,"Volume")</f>
-        <v>58066760</v>
+        <v>1236784</v>
       </c>
       <c r="Q5" s="7">
         <f t="array" aca="1" ref="Q5" ca="1">_FV(B5,"Volume average",TRUE)</f>
@@ -12294,7 +11826,7 @@
       </c>
       <c r="C6" s="2">
         <f t="array" aca="1" ref="C6" ca="1">_FV(B6,"Last trade time",TRUE)</f>
-        <v>46174.905622534374</v>
+        <v>46174.999942557813</v>
       </c>
       <c r="D6" t="str">
         <f t="array" aca="1" ref="D6" ca="1">_FV(B6,"Currency")</f>
@@ -12314,7 +11846,7 @@
       </c>
       <c r="H6" s="6">
         <f t="array" aca="1" ref="H6" ca="1">_FV(B6,"P/E",TRUE)</f>
-        <v>417.40809999999999</v>
+        <v>483.05149999999998</v>
       </c>
       <c r="I6" s="6">
         <f t="array" aca="1" ref="I6" ca="1">_FV(B6,"Beta")</f>
@@ -12346,7 +11878,7 @@
       </c>
       <c r="P6" s="7">
         <f t="array" aca="1" ref="P6" ca="1">_FV(B6,"Volume")</f>
-        <v>20614850</v>
+        <v>452401</v>
       </c>
       <c r="Q6" s="7">
         <f t="array" aca="1" ref="Q6" ca="1">_FV(B6,"Volume average",TRUE)</f>
@@ -12382,7 +11914,7 @@
       </c>
       <c r="C7" s="2">
         <f t="array" aca="1" ref="C7" ca="1">_FV(B7,"Last trade time",TRUE)</f>
-        <v>46174.90552547422</v>
+        <v>46174.999884189063</v>
       </c>
       <c r="D7" t="str">
         <f t="array" aca="1" ref="D7" ca="1">_FV(B7,"Currency")</f>
@@ -12406,7 +11938,7 @@
       </c>
       <c r="I7" s="6">
         <f t="array" aca="1" ref="I7" ca="1">_FV(B7,"Beta")</f>
-        <v>0.76549999999999996</v>
+        <v>0.72670000000000001</v>
       </c>
       <c r="J7" s="3">
         <f t="array" aca="1" ref="J7" ca="1">_FV(B7,"52 week high",TRUE)</f>
@@ -12434,7 +11966,7 @@
       </c>
       <c r="P7" s="7">
         <f t="array" aca="1" ref="P7" ca="1">_FV(B7,"Volume")</f>
-        <v>46362718</v>
+        <v>2967987</v>
       </c>
       <c r="Q7" s="7">
         <f t="array" aca="1" ref="Q7" ca="1">_FV(B7,"Volume average",TRUE)</f>
@@ -12470,7 +12002,7 @@
       </c>
       <c r="C8" s="2">
         <f t="array" aca="1" ref="C8" ca="1">_FV(B8,"Last trade time",TRUE)</f>
-        <v>46174.905533969533</v>
+        <v>46174.999770450784</v>
       </c>
       <c r="D8" t="str">
         <f t="array" aca="1" ref="D8" ca="1">_FV(B8,"Currency")</f>
@@ -12490,11 +12022,11 @@
       </c>
       <c r="H8" s="6">
         <f t="array" aca="1" ref="H8" ca="1">_FV(B8,"P/E",TRUE)</f>
-        <v>703.0403</v>
+        <v>703.07590000000005</v>
       </c>
       <c r="I8" s="6">
         <f t="array" aca="1" ref="I8" ca="1">_FV(B8,"Beta")</f>
-        <v>1.5619000000000001</v>
+        <v>1.5459000000000001</v>
       </c>
       <c r="J8" s="3">
         <f t="array" aca="1" ref="J8" ca="1">_FV(B8,"52 week high",TRUE)</f>
@@ -12522,7 +12054,7 @@
       </c>
       <c r="P8" s="7">
         <f t="array" aca="1" ref="P8" ca="1">_FV(B8,"Volume")</f>
-        <v>11168410</v>
+        <v>47583</v>
       </c>
       <c r="Q8" s="7">
         <f t="array" aca="1" ref="Q8" ca="1">_FV(B8,"Volume average",TRUE)</f>
@@ -12558,7 +12090,7 @@
       </c>
       <c r="C9" s="2">
         <f t="array" aca="1" ref="C9" ca="1">_FV(B9,"Last trade time",TRUE)</f>
-        <v>46174.905569710158</v>
+        <v>46174.999974189064</v>
       </c>
       <c r="D9" t="str">
         <f t="array" aca="1" ref="D9" ca="1">_FV(B9,"Currency")</f>
@@ -12566,23 +12098,23 @@
       </c>
       <c r="E9" s="3">
         <f t="array" aca="1" ref="E9" ca="1">_FV(B9,"Price")</f>
-        <v>16.239999999999998</v>
+        <v>16.25</v>
       </c>
       <c r="F9" s="4">
         <f t="array" aca="1" ref="F9" ca="1">_FV(B9,"Change (%)",TRUE)</f>
-        <v>9.4339999999999993E-2</v>
+        <v>9.5013E-2</v>
       </c>
       <c r="G9" s="5">
         <f t="array" aca="1" ref="G9" ca="1">_FV(B9,"Change")</f>
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="H9" s="6">
         <f t="array" aca="1" ref="H9" ca="1">_FV(B9,"P/E",TRUE)</f>
-        <v>100.9323</v>
+        <v>101.01130000000001</v>
       </c>
       <c r="I9" s="6">
         <f t="array" aca="1" ref="I9" ca="1">_FV(B9,"Beta")</f>
-        <v>1.1495</v>
+        <v>1.1449</v>
       </c>
       <c r="J9" s="3">
         <f t="array" aca="1" ref="J9" ca="1">_FV(B9,"52 week high",TRUE)</f>
@@ -12610,7 +12142,7 @@
       </c>
       <c r="P9" s="7">
         <f t="array" aca="1" ref="P9" ca="1">_FV(B9,"Volume")</f>
-        <v>171374832</v>
+        <v>11902305</v>
       </c>
       <c r="Q9" s="7">
         <f t="array" aca="1" ref="Q9" ca="1">_FV(B9,"Volume average",TRUE)</f>
@@ -12630,7 +12162,7 @@
       </c>
       <c r="U9" s="7">
         <f t="array" aca="1" ref="U9" ca="1">_FV(B9,"Market cap",TRUE)</f>
-        <v>93253977599</v>
+        <v>93311400000</v>
       </c>
       <c r="V9" s="7">
         <f t="array" aca="1" ref="V9" ca="1">_FV(B9,"Shares outstanding",TRUE)</f>
@@ -12646,7 +12178,7 @@
       </c>
       <c r="C10" s="2">
         <f t="array" aca="1" ref="C10" ca="1">_FV(B10,"Last trade time",TRUE)</f>
-        <v>46174.905613402341</v>
+        <v>46174.999883020311</v>
       </c>
       <c r="D10" t="str">
         <f t="array" aca="1" ref="D10" ca="1">_FV(B10,"Currency")</f>
@@ -12666,11 +12198,11 @@
       </c>
       <c r="H10" s="6">
         <f t="array" aca="1" ref="H10" ca="1">_FV(B10,"P/E",TRUE)</f>
-        <v>21.775300000000001</v>
+        <v>21.776399999999999</v>
       </c>
       <c r="I10" s="6">
         <f t="array" aca="1" ref="I10" ca="1">_FV(B10,"Beta")</f>
-        <v>0.95540000000000003</v>
+        <v>0.95909999999999995</v>
       </c>
       <c r="J10" s="3">
         <f t="array" aca="1" ref="J10" ca="1">_FV(B10,"52 week high",TRUE)</f>
@@ -12698,7 +12230,7 @@
       </c>
       <c r="P10" s="7">
         <f t="array" aca="1" ref="P10" ca="1">_FV(B10,"Volume")</f>
-        <v>67787642</v>
+        <v>341448</v>
       </c>
       <c r="Q10" s="7">
         <f t="array" aca="1" ref="Q10" ca="1">_FV(B10,"Volume average",TRUE)</f>
@@ -12734,7 +12266,7 @@
       </c>
       <c r="C11" s="2">
         <f t="array" aca="1" ref="C11" ca="1">_FV(B11,"Last trade time",TRUE)</f>
-        <v>46174.905654664064</v>
+        <v>46174.999968784374</v>
       </c>
       <c r="D11" t="str">
         <f t="array" aca="1" ref="D11" ca="1">_FV(B11,"Currency")</f>
@@ -12742,23 +12274,23 @@
       </c>
       <c r="E11" s="3">
         <f t="array" aca="1" ref="E11" ca="1">_FV(B11,"Price")</f>
-        <v>209.53</v>
+        <v>209.6</v>
       </c>
       <c r="F11" s="4">
         <f t="array" aca="1" ref="F11" ca="1">_FV(B11,"Change (%)",TRUE)</f>
-        <v>9.6442E-2</v>
+        <v>9.6807999999999991E-2</v>
       </c>
       <c r="G11" s="5">
         <f t="array" aca="1" ref="G11" ca="1">_FV(B11,"Change")</f>
-        <v>18.43</v>
+        <v>18.5</v>
       </c>
       <c r="H11" s="6">
         <f t="array" aca="1" ref="H11" ca="1">_FV(B11,"P/E",TRUE)</f>
-        <v>24.2422</v>
+        <v>24.2502</v>
       </c>
       <c r="I11" s="6">
         <f t="array" aca="1" ref="I11" ca="1">_FV(B11,"Beta")</f>
-        <v>1.1524000000000001</v>
+        <v>1.1446000000000001</v>
       </c>
       <c r="J11" s="3">
         <f t="array" aca="1" ref="J11" ca="1">_FV(B11,"52 week high",TRUE)</f>
@@ -12786,7 +12318,7 @@
       </c>
       <c r="P11" s="7">
         <f t="array" aca="1" ref="P11" ca="1">_FV(B11,"Volume")</f>
-        <v>27523034</v>
+        <v>252830</v>
       </c>
       <c r="Q11" s="7">
         <f t="array" aca="1" ref="Q11" ca="1">_FV(B11,"Volume average",TRUE)</f>
@@ -12806,7 +12338,7 @@
       </c>
       <c r="U11" s="7">
         <f t="array" aca="1" ref="U11" ca="1">_FV(B11,"Market cap",TRUE)</f>
-        <v>171605070000</v>
+        <v>171662400000</v>
       </c>
       <c r="V11" s="7">
         <f t="array" aca="1" ref="V11" ca="1">_FV(B11,"Shares outstanding",TRUE)</f>
@@ -12822,7 +12354,7 @@
       </c>
       <c r="C12" s="2" cm="1">
         <f t="array" aca="1" ref="C12" ca="1">_FV(B12,"Last trade time",TRUE)</f>
-        <v>46174.90533741875</v>
+        <v>46174.999853587498</v>
       </c>
       <c r="D12" t="str" cm="1">
         <f t="array" aca="1" ref="D12" ca="1">_FV(B12,"Currency")</f>
@@ -12846,7 +12378,7 @@
       </c>
       <c r="I12" s="6" cm="1">
         <f t="array" aca="1" ref="I12" ca="1">_FV(B12,"Beta")</f>
-        <v>0.9718</v>
+        <v>0.95489999999999997</v>
       </c>
       <c r="J12" s="3" cm="1">
         <f t="array" aca="1" ref="J12" ca="1">_FV(B12,"52 week high",TRUE)</f>
@@ -12874,7 +12406,7 @@
       </c>
       <c r="P12" s="7" cm="1">
         <f t="array" aca="1" ref="P12" ca="1">_FV(B12,"Volume")</f>
-        <v>10304127</v>
+        <v>149366</v>
       </c>
       <c r="Q12" s="7" cm="1">
         <f t="array" aca="1" ref="Q12" ca="1">_FV(B12,"Volume average",TRUE)</f>
@@ -12910,7 +12442,7 @@
       </c>
       <c r="C13" s="2" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(B13,"Last trade time",TRUE)</f>
-        <v>46174.905452522653</v>
+        <v>46174.999906330471</v>
       </c>
       <c r="D13" t="str" cm="1">
         <f t="array" aca="1" ref="D13" ca="1">_FV(B13,"Currency")</f>
@@ -12918,15 +12450,15 @@
       </c>
       <c r="E13" s="3" cm="1">
         <f t="array" aca="1" ref="E13" ca="1">_FV(B13,"Price")</f>
-        <v>280</v>
+        <v>280.16000000000003</v>
       </c>
       <c r="F13" s="4" cm="1">
         <f t="array" aca="1" ref="F13" ca="1">_FV(B13,"Change (%)",TRUE)</f>
-        <v>9.5676000000000011E-2</v>
+        <v>9.6301999999999999E-2</v>
       </c>
       <c r="G13" s="5" cm="1">
         <f t="array" aca="1" ref="G13" ca="1">_FV(B13,"Change")</f>
-        <v>24.45</v>
+        <v>24.61</v>
       </c>
       <c r="H13" s="6" cm="1">
         <f t="array" aca="1" ref="H13" ca="1">_FV(B13,"P/E",TRUE)</f>
@@ -12934,7 +12466,7 @@
       </c>
       <c r="I13" s="6" cm="1">
         <f t="array" aca="1" ref="I13" ca="1">_FV(B13,"Beta")</f>
-        <v>1.3536999999999999</v>
+        <v>1.3489</v>
       </c>
       <c r="J13" s="3" cm="1">
         <f t="array" aca="1" ref="J13" ca="1">_FV(B13,"52 week high",TRUE)</f>
@@ -12962,7 +12494,7 @@
       </c>
       <c r="P13" s="7" cm="1">
         <f t="array" aca="1" ref="P13" ca="1">_FV(B13,"Volume")</f>
-        <v>20140059</v>
+        <v>121317</v>
       </c>
       <c r="Q13" s="7" cm="1">
         <f t="array" aca="1" ref="Q13" ca="1">_FV(B13,"Volume average",TRUE)</f>
@@ -12986,7 +12518,7 @@
       </c>
       <c r="V13" s="7" cm="1">
         <f t="array" aca="1" ref="V13" ca="1">_FV(B13,"Shares outstanding",TRUE)</f>
-        <v>346602900</v>
+        <v>346600000</v>
       </c>
     </row>
     <row r="14" spans="1:31">
@@ -12998,7 +12530,7 @@
       </c>
       <c r="C14" s="2">
         <f t="array" aca="1" ref="C14" ca="1">_FV(B14,"Last trade time",TRUE)</f>
-        <v>46174.905654513284</v>
+        <v>46174.999955022657</v>
       </c>
       <c r="D14" t="str">
         <f t="array" aca="1" ref="D14" ca="1">_FV(B14,"Currency")</f>
@@ -13006,23 +12538,23 @@
       </c>
       <c r="E14" s="3">
         <f t="array" aca="1" ref="E14" ca="1">_FV(B14,"Price")</f>
-        <v>135.88999999999999</v>
+        <v>135.86000000000001</v>
       </c>
       <c r="F14" s="4">
         <f t="array" aca="1" ref="F14" ca="1">_FV(B14,"Change (%)",TRUE)</f>
-        <v>9.2627000000000001E-2</v>
+        <v>9.2385999999999996E-2</v>
       </c>
       <c r="G14" s="5">
         <f t="array" aca="1" ref="G14" ca="1">_FV(B14,"Change")</f>
-        <v>11.52</v>
+        <v>11.49</v>
       </c>
       <c r="H14" s="6">
         <f t="array" aca="1" ref="H14" ca="1">_FV(B14,"P/E",TRUE)</f>
-        <v>80.819599999999994</v>
+        <v>80.802800000000005</v>
       </c>
       <c r="I14" s="6">
         <f t="array" aca="1" ref="I14" ca="1">_FV(B14,"Beta")</f>
-        <v>0.93969999999999998</v>
+        <v>0.92059999999999997</v>
       </c>
       <c r="J14" s="3">
         <f t="array" aca="1" ref="J14" ca="1">_FV(B14,"52 week high",TRUE)</f>
@@ -13050,7 +12582,7 @@
       </c>
       <c r="P14" s="7">
         <f t="array" aca="1" ref="P14" ca="1">_FV(B14,"Volume")</f>
-        <v>68288795</v>
+        <v>1098569</v>
       </c>
       <c r="Q14" s="7">
         <f t="array" aca="1" ref="Q14" ca="1">_FV(B14,"Volume average",TRUE)</f>
@@ -13070,7 +12602,7 @@
       </c>
       <c r="U14" s="7">
         <f t="array" aca="1" ref="U14" ca="1">_FV(B14,"Market cap",TRUE)</f>
-        <v>140144444120</v>
+        <v>140113504880</v>
       </c>
       <c r="V14" s="7">
         <f t="array" aca="1" ref="V14" ca="1">_FV(B14,"Shares outstanding",TRUE)</f>
@@ -13086,7 +12618,7 @@
       </c>
       <c r="C15" s="2" cm="1">
         <f t="array" aca="1" ref="C15" ca="1">_FV(B15,"Last trade time",TRUE)</f>
-        <v>46174.905678668751</v>
+        <v>46174.999998321095</v>
       </c>
       <c r="D15" t="str" cm="1">
         <f t="array" aca="1" ref="D15" ca="1">_FV(B15,"Currency")</f>
@@ -13094,23 +12626,23 @@
       </c>
       <c r="E15" s="3" cm="1">
         <f t="array" aca="1" ref="E15" ca="1">_FV(B15,"Price")</f>
-        <v>466.11</v>
+        <v>465.96</v>
       </c>
       <c r="F15" s="4" cm="1">
         <f t="array" aca="1" ref="F15" ca="1">_FV(B15,"Change (%)",TRUE)</f>
-        <v>0.107386</v>
+        <v>0.10703</v>
       </c>
       <c r="G15" s="5" cm="1">
         <f t="array" aca="1" ref="G15" ca="1">_FV(B15,"Change")</f>
-        <v>45.2</v>
+        <v>45.05</v>
       </c>
       <c r="H15" s="6" cm="1">
         <f t="array" aca="1" ref="H15" ca="1">_FV(B15,"P/E",TRUE)</f>
-        <v>37.014899999999997</v>
+        <v>37.003100000000003</v>
       </c>
       <c r="I15" s="6" cm="1">
         <f t="array" aca="1" ref="I15" ca="1">_FV(B15,"Beta")</f>
-        <v>1.2961</v>
+        <v>1.2963</v>
       </c>
       <c r="J15" s="3" cm="1">
         <f t="array" aca="1" ref="J15" ca="1">_FV(B15,"52 week high",TRUE)</f>
@@ -13138,7 +12670,7 @@
       </c>
       <c r="P15" s="7" cm="1">
         <f t="array" aca="1" ref="P15" ca="1">_FV(B15,"Volume")</f>
-        <v>20465419</v>
+        <v>396044</v>
       </c>
       <c r="Q15" s="7" cm="1">
         <f t="array" aca="1" ref="Q15" ca="1">_FV(B15,"Volume average",TRUE)</f>
@@ -13158,7 +12690,7 @@
       </c>
       <c r="U15" s="7" cm="1">
         <f t="array" aca="1" ref="U15" ca="1">_FV(B15,"Market cap",TRUE)</f>
-        <v>302770280313</v>
+        <v>302672845068</v>
       </c>
       <c r="V15" s="7" cm="1">
         <f t="array" aca="1" ref="V15" ca="1">_FV(B15,"Shares outstanding",TRUE)</f>
@@ -13174,7 +12706,7 @@
       </c>
       <c r="C16" s="2">
         <f t="array" aca="1" ref="C16" ca="1">_FV(B16,"Last trade time",TRUE)</f>
-        <v>46174.905588935158</v>
+        <v>46174.999994120313</v>
       </c>
       <c r="D16" t="str">
         <f t="array" aca="1" ref="D16" ca="1">_FV(B16,"Currency")</f>
@@ -13182,23 +12714,23 @@
       </c>
       <c r="E16" s="3">
         <f t="array" aca="1" ref="E16" ca="1">_FV(B16,"Price")</f>
-        <v>248.07</v>
+        <v>248.15</v>
       </c>
       <c r="F16" s="4">
         <f t="array" aca="1" ref="F16" ca="1">_FV(B16,"Change (%)",TRUE)</f>
-        <v>9.8724000000000006E-2</v>
+        <v>9.9079E-2</v>
       </c>
       <c r="G16" s="5">
         <f t="array" aca="1" ref="G16" ca="1">_FV(B16,"Change")</f>
-        <v>22.29</v>
+        <v>22.37</v>
       </c>
       <c r="H16" s="6">
         <f t="array" aca="1" ref="H16" ca="1">_FV(B16,"P/E",TRUE)</f>
-        <v>42.046500000000002</v>
+        <v>42.060400000000001</v>
       </c>
       <c r="I16" s="6">
         <f t="array" aca="1" ref="I16" ca="1">_FV(B16,"Beta")</f>
-        <v>1.649</v>
+        <v>1.6485000000000001</v>
       </c>
       <c r="J16" s="3">
         <f t="array" aca="1" ref="J16" ca="1">_FV(B16,"52 week high",TRUE)</f>
@@ -13226,7 +12758,7 @@
       </c>
       <c r="P16" s="7">
         <f t="array" aca="1" ref="P16" ca="1">_FV(B16,"Volume")</f>
-        <v>48000587</v>
+        <v>881574</v>
       </c>
       <c r="Q16" s="7">
         <f t="array" aca="1" ref="Q16" ca="1">_FV(B16,"Volume average",TRUE)</f>
@@ -13246,7 +12778,7 @@
       </c>
       <c r="U16" s="7">
         <f t="array" aca="1" ref="U16" ca="1">_FV(B16,"Market cap",TRUE)</f>
-        <v>713460731220</v>
+        <v>713690814900</v>
       </c>
       <c r="V16" s="7">
         <f t="array" aca="1" ref="V16" ca="1">_FV(B16,"Shares outstanding",TRUE)</f>
@@ -13262,7 +12794,7 @@
       </c>
       <c r="C17" s="2">
         <f t="array" aca="1" ref="C17" ca="1">_FV(B17,"Last trade time",TRUE)</f>
-        <v>46174.904556967187</v>
+        <v>46174.999599478906</v>
       </c>
       <c r="D17" t="str">
         <f t="array" aca="1" ref="D17" ca="1">_FV(B17,"Currency")</f>
@@ -13282,11 +12814,11 @@
       </c>
       <c r="H17" s="6">
         <f t="array" aca="1" ref="H17" ca="1">_FV(B17,"P/E",TRUE)</f>
-        <v>103.761</v>
+        <v>103.7582</v>
       </c>
       <c r="I17" s="6">
         <f t="array" aca="1" ref="I17" ca="1">_FV(B17,"Beta")</f>
-        <v>2.8334999999999999</v>
+        <v>2.8328000000000002</v>
       </c>
       <c r="J17" s="3">
         <f t="array" aca="1" ref="J17" ca="1">_FV(B17,"52 week high",TRUE)</f>
@@ -13314,7 +12846,7 @@
       </c>
       <c r="P17" s="7">
         <f t="array" aca="1" ref="P17" ca="1">_FV(B17,"Volume")</f>
-        <v>2883385</v>
+        <v>23184</v>
       </c>
       <c r="Q17" s="7">
         <f t="array" aca="1" ref="Q17" ca="1">_FV(B17,"Volume average",TRUE)</f>
@@ -13350,7 +12882,7 @@
       </c>
       <c r="C18" s="2" cm="1">
         <f t="array" aca="1" ref="C18" ca="1">_FV(B18,"Last trade time",TRUE)</f>
-        <v>46174.905250844531</v>
+        <v>46174.999460404688</v>
       </c>
       <c r="D18" t="str" cm="1">
         <f t="array" aca="1" ref="D18" ca="1">_FV(B18,"Currency")</f>
@@ -13358,15 +12890,15 @@
       </c>
       <c r="E18" s="3" cm="1">
         <f t="array" aca="1" ref="E18" ca="1">_FV(B18,"Price")</f>
-        <v>270.79000000000002</v>
+        <v>270.82</v>
       </c>
       <c r="F18" s="4" cm="1">
         <f t="array" aca="1" ref="F18" ca="1">_FV(B18,"Change (%)",TRUE)</f>
-        <v>0.1198</v>
+        <v>0.119924</v>
       </c>
       <c r="G18" s="5" cm="1">
         <f t="array" aca="1" ref="G18" ca="1">_FV(B18,"Change")</f>
-        <v>28.97</v>
+        <v>29</v>
       </c>
       <c r="H18" s="6" t="e" cm="1" vm="18">
         <f t="array" ref="H18">_FV(B18,"P/E",TRUE)</f>
@@ -13374,7 +12906,7 @@
       </c>
       <c r="I18" s="6" cm="1">
         <f t="array" aca="1" ref="I18" ca="1">_FV(B18,"Beta")</f>
-        <v>1.6959</v>
+        <v>1.6673</v>
       </c>
       <c r="J18" s="3" cm="1">
         <f t="array" aca="1" ref="J18" ca="1">_FV(B18,"52 week high",TRUE)</f>
@@ -13402,7 +12934,7 @@
       </c>
       <c r="P18" s="7" cm="1">
         <f t="array" aca="1" ref="P18" ca="1">_FV(B18,"Volume")</f>
-        <v>8448146</v>
+        <v>42019</v>
       </c>
       <c r="Q18" s="7" cm="1">
         <f t="array" aca="1" ref="Q18" ca="1">_FV(B18,"Volume average",TRUE)</f>
@@ -13422,7 +12954,7 @@
       </c>
       <c r="U18" s="7" cm="1">
         <f t="array" aca="1" ref="U18" ca="1">_FV(B18,"Market cap",TRUE)</f>
-        <v>95715112298</v>
+        <v>95725716284</v>
       </c>
       <c r="V18" s="7" cm="1">
         <f t="array" aca="1" ref="V18" ca="1">_FV(B18,"Shares outstanding",TRUE)</f>
@@ -13438,7 +12970,7 @@
       </c>
       <c r="C19" s="2">
         <f t="array" aca="1" ref="C19" ca="1">_FV(B19,"Last trade time",TRUE)</f>
-        <v>46174.905536758597</v>
+        <v>46174.999998645311</v>
       </c>
       <c r="D19" t="str">
         <f t="array" aca="1" ref="D19" ca="1">_FV(B19,"Currency")</f>
@@ -13458,11 +12990,11 @@
       </c>
       <c r="H19" s="6">
         <f t="array" aca="1" ref="H19" ca="1">_FV(B19,"P/E",TRUE)</f>
-        <v>75.1601</v>
+        <v>75.159400000000005</v>
       </c>
       <c r="I19" s="6">
         <f t="array" aca="1" ref="I19" ca="1">_FV(B19,"Beta")</f>
-        <v>2.2896999999999998</v>
+        <v>2.2728000000000002</v>
       </c>
       <c r="J19" s="3">
         <f t="array" aca="1" ref="J19" ca="1">_FV(B19,"52 week high",TRUE)</f>
@@ -13490,7 +13022,7 @@
       </c>
       <c r="P19" s="7">
         <f t="array" aca="1" ref="P19" ca="1">_FV(B19,"Volume")</f>
-        <v>32782129</v>
+        <v>8766323</v>
       </c>
       <c r="Q19" s="7">
         <f t="array" aca="1" ref="Q19" ca="1">_FV(B19,"Volume average",TRUE)</f>
@@ -13526,7 +13058,7 @@
       </c>
       <c r="C20" s="2" cm="1">
         <f t="array" aca="1" ref="C20" ca="1">_FV(B20,"Last trade time",TRUE)</f>
-        <v>46174.90548295078</v>
+        <v>46174.999646550779</v>
       </c>
       <c r="D20" t="str" cm="1">
         <f t="array" aca="1" ref="D20" ca="1">_FV(B20,"Currency")</f>
@@ -13546,11 +13078,11 @@
       </c>
       <c r="H20" s="6" cm="1">
         <f t="array" aca="1" ref="H20" ca="1">_FV(B20,"P/E",TRUE)</f>
-        <v>96.687299999999993</v>
+        <v>96.686599999999999</v>
       </c>
       <c r="I20" s="6" cm="1">
         <f t="array" aca="1" ref="I20" ca="1">_FV(B20,"Beta")</f>
-        <v>1.1528</v>
+        <v>1.1428</v>
       </c>
       <c r="J20" s="3" cm="1">
         <f t="array" aca="1" ref="J20" ca="1">_FV(B20,"52 week high",TRUE)</f>
@@ -13578,7 +13110,7 @@
       </c>
       <c r="P20" s="7" cm="1">
         <f t="array" aca="1" ref="P20" ca="1">_FV(B20,"Volume")</f>
-        <v>4517987</v>
+        <v>14511</v>
       </c>
       <c r="Q20" s="7" cm="1">
         <f t="array" aca="1" ref="Q20" ca="1">_FV(B20,"Volume average",TRUE)</f>
@@ -13614,7 +13146,7 @@
       </c>
       <c r="C21" s="2" cm="1">
         <f t="array" aca="1" ref="C21" ca="1">_FV(B21,"Last trade time",TRUE)</f>
-        <v>46174.905477245309</v>
+        <v>46174.999854513284</v>
       </c>
       <c r="D21" t="str" cm="1">
         <f t="array" aca="1" ref="D21" ca="1">_FV(B21,"Currency")</f>
@@ -13638,7 +13170,7 @@
       </c>
       <c r="I21" s="6" cm="1">
         <f t="array" aca="1" ref="I21" ca="1">_FV(B21,"Beta")</f>
-        <v>0.83279999999999998</v>
+        <v>0.82709999999999995</v>
       </c>
       <c r="J21" s="3" cm="1">
         <f t="array" aca="1" ref="J21" ca="1">_FV(B21,"52 week high",TRUE)</f>
@@ -13666,7 +13198,7 @@
       </c>
       <c r="P21" s="7" cm="1">
         <f t="array" aca="1" ref="P21" ca="1">_FV(B21,"Volume")</f>
-        <v>15645932</v>
+        <v>33463</v>
       </c>
       <c r="Q21" s="7" cm="1">
         <f t="array" aca="1" ref="Q21" ca="1">_FV(B21,"Volume average",TRUE)</f>
@@ -13702,7 +13234,7 @@
       </c>
       <c r="C22" s="2">
         <f t="array" aca="1" ref="C22" ca="1">_FV(B22,"Last trade time",TRUE)</f>
-        <v>46174.905581909377</v>
+        <v>46174.999994907033</v>
       </c>
       <c r="D22" t="str">
         <f t="array" aca="1" ref="D22" ca="1">_FV(B22,"Currency")</f>
@@ -13710,23 +13242,23 @@
       </c>
       <c r="E22" s="3">
         <f t="array" aca="1" ref="E22" ca="1">_FV(B22,"Price")</f>
-        <v>320.19</v>
+        <v>320.42</v>
       </c>
       <c r="F22" s="4">
         <f t="array" aca="1" ref="F22" ca="1">_FV(B22,"Change (%)",TRUE)</f>
-        <v>7.5185000000000002E-2</v>
+        <v>7.5956999999999997E-2</v>
       </c>
       <c r="G22" s="5">
         <f t="array" aca="1" ref="G22" ca="1">_FV(B22,"Change")</f>
-        <v>22.39</v>
+        <v>22.62</v>
       </c>
       <c r="H22" s="6">
         <f t="array" aca="1" ref="H22" ca="1">_FV(B22,"P/E",TRUE)</f>
-        <v>25.6234</v>
+        <v>25.6418</v>
       </c>
       <c r="I22" s="6">
         <f t="array" aca="1" ref="I22" ca="1">_FV(B22,"Beta")</f>
-        <v>0.65790000000000004</v>
+        <v>0.65410000000000001</v>
       </c>
       <c r="J22" s="3">
         <f t="array" aca="1" ref="J22" ca="1">_FV(B22,"52 week high",TRUE)</f>
@@ -13754,7 +13286,7 @@
       </c>
       <c r="P22" s="7">
         <f t="array" aca="1" ref="P22" ca="1">_FV(B22,"Volume")</f>
-        <v>32757881</v>
+        <v>388049</v>
       </c>
       <c r="Q22" s="7">
         <f t="array" aca="1" ref="Q22" ca="1">_FV(B22,"Volume average",TRUE)</f>
@@ -13774,7 +13306,7 @@
       </c>
       <c r="U22" s="7">
         <f t="array" aca="1" ref="U22" ca="1">_FV(B22,"Market cap",TRUE)</f>
-        <v>300941874207</v>
+        <v>301158047826</v>
       </c>
       <c r="V22" s="7">
         <f t="array" aca="1" ref="V22" ca="1">_FV(B22,"Shares outstanding",TRUE)</f>
@@ -13790,7 +13322,7 @@
       </c>
       <c r="C23" s="2">
         <f t="array" aca="1" ref="C23" ca="1">_FV(B23,"Last trade time",TRUE)</f>
-        <v>46174.894934976561</v>
+        <v>46174.999963564063</v>
       </c>
       <c r="D23" t="str">
         <f t="array" aca="1" ref="D23" ca="1">_FV(B23,"Currency")</f>
@@ -13810,11 +13342,11 @@
       </c>
       <c r="H23" s="6">
         <f t="array" aca="1" ref="H23" ca="1">_FV(B23,"P/E",TRUE)</f>
-        <v>36.9236</v>
+        <v>39.819899999999997</v>
       </c>
       <c r="I23" s="6">
         <f t="array" aca="1" ref="I23" ca="1">_FV(B23,"Beta")</f>
-        <v>1.4527000000000001</v>
+        <v>1.4414</v>
       </c>
       <c r="J23" s="3">
         <f t="array" aca="1" ref="J23" ca="1">_FV(B23,"52 week high",TRUE)</f>
@@ -13842,7 +13374,7 @@
       </c>
       <c r="P23" s="7">
         <f t="array" aca="1" ref="P23" ca="1">_FV(B23,"Volume")</f>
-        <v>4843956</v>
+        <v>15937</v>
       </c>
       <c r="Q23" s="7">
         <f t="array" aca="1" ref="Q23" ca="1">_FV(B23,"Volume average",TRUE)</f>
@@ -13878,7 +13410,7 @@
       </c>
       <c r="C24" s="2">
         <f t="array" aca="1" ref="C24" ca="1">_FV(B24,"Last trade time",TRUE)</f>
-        <v>46174.90537412031</v>
+        <v>46174.999492673436</v>
       </c>
       <c r="D24" t="str">
         <f t="array" aca="1" ref="D24" ca="1">_FV(B24,"Currency")</f>
@@ -13930,7 +13462,7 @@
       </c>
       <c r="P24" s="7">
         <f t="array" aca="1" ref="P24" ca="1">_FV(B24,"Volume")</f>
-        <v>9704993</v>
+        <v>95971</v>
       </c>
       <c r="Q24" s="7">
         <f t="array" aca="1" ref="Q24" ca="1">_FV(B24,"Volume average",TRUE)</f>
@@ -13966,7 +13498,7 @@
       </c>
       <c r="C25" s="2" cm="1">
         <f t="array" aca="1" ref="C25" ca="1">_FV(B25,"Last trade time",TRUE)</f>
-        <v>46174.905370520311</v>
+        <v>46174.999899443748</v>
       </c>
       <c r="D25" t="str" cm="1">
         <f t="array" aca="1" ref="D25" ca="1">_FV(B25,"Currency")</f>
@@ -13990,7 +13522,7 @@
       </c>
       <c r="I25" s="6" cm="1">
         <f t="array" aca="1" ref="I25" ca="1">_FV(B25,"Beta")</f>
-        <v>1.0840000000000001</v>
+        <v>1.0750999999999999</v>
       </c>
       <c r="J25" s="3" cm="1">
         <f t="array" aca="1" ref="J25" ca="1">_FV(B25,"52 week high",TRUE)</f>
@@ -14018,7 +13550,7 @@
       </c>
       <c r="P25" s="7" cm="1">
         <f t="array" aca="1" ref="P25" ca="1">_FV(B25,"Volume")</f>
-        <v>9300933</v>
+        <v>40015</v>
       </c>
       <c r="Q25" s="7" cm="1">
         <f t="array" aca="1" ref="Q25" ca="1">_FV(B25,"Volume average",TRUE)</f>
@@ -14054,7 +13586,7 @@
       </c>
       <c r="C26" s="2">
         <f t="array" aca="1" ref="C26" ca="1">_FV(B26,"Last trade time",TRUE)</f>
-        <v>46174.556574154689</v>
+        <v>46175.476106539063</v>
       </c>
       <c r="D26" t="str">
         <f t="array" aca="1" ref="D26" ca="1">_FV(B26,"Currency")</f>
@@ -14062,23 +13594,23 @@
       </c>
       <c r="E26" s="9">
         <f t="array" aca="1" ref="E26" ca="1">_FV(B26,"Price")</f>
-        <v>907.6</v>
+        <v>894.6</v>
       </c>
       <c r="F26" s="4">
         <f t="array" aca="1" ref="F26" ca="1">_FV(B26,"Change (%)",TRUE)</f>
-        <v>7.7397999999999995E-2</v>
+        <v>-1.4322999999999999E-2</v>
       </c>
       <c r="G26" s="5">
         <f t="array" aca="1" ref="G26" ca="1">_FV(B26,"Change")</f>
-        <v>65.2</v>
+        <v>-13</v>
       </c>
       <c r="H26" s="6">
         <f t="array" aca="1" ref="H26" ca="1">_FV(B26,"P/E",TRUE)</f>
-        <v>24.144500000000001</v>
+        <v>0</v>
       </c>
       <c r="I26" s="6">
         <f t="array" aca="1" ref="I26" ca="1">_FV(B26,"Beta")</f>
-        <v>0.35199999999999998</v>
+        <v>0.33879999999999999</v>
       </c>
       <c r="J26" s="9">
         <f t="array" aca="1" ref="J26" ca="1">_FV(B26,"52 week high",TRUE)</f>
@@ -14090,23 +13622,23 @@
       </c>
       <c r="L26" s="9">
         <f t="array" aca="1" ref="L26" ca="1">_FV(B26,"High")</f>
-        <v>907.6</v>
+        <v>918.6</v>
       </c>
       <c r="M26" s="9">
         <f t="array" aca="1" ref="M26" ca="1">_FV(B26,"Low")</f>
-        <v>846.6</v>
+        <v>893.2</v>
       </c>
       <c r="N26" s="9">
         <f t="array" aca="1" ref="N26" ca="1">_FV(B26,"Open")</f>
-        <v>846.6</v>
+        <v>916.8</v>
       </c>
       <c r="O26" s="9">
         <f t="array" aca="1" ref="O26" ca="1">_FV(B26,"Previous close",TRUE)</f>
-        <v>842.4</v>
+        <v>907.6</v>
       </c>
       <c r="P26" s="7">
         <f t="array" aca="1" ref="P26" ca="1">_FV(B26,"Volume")</f>
-        <v>3968492</v>
+        <v>476451</v>
       </c>
       <c r="Q26" s="7">
         <f t="array" aca="1" ref="Q26" ca="1">_FV(B26,"Volume average",TRUE)</f>
@@ -14130,7 +13662,7 @@
       </c>
       <c r="V26" s="7">
         <f t="array" aca="1" ref="V26" ca="1">_FV(B26,"Shares outstanding",TRUE)</f>
-        <v>905653600</v>
+        <v>907731600</v>
       </c>
     </row>
     <row r="27" spans="1:22">
@@ -14142,7 +13674,7 @@
       </c>
       <c r="C27" s="2">
         <f t="array" aca="1" ref="C27" ca="1">_FV(B27,"Last trade time",TRUE)</f>
-        <v>46174.905671469533</v>
+        <v>46174.999933367966</v>
       </c>
       <c r="D27" t="str">
         <f t="array" aca="1" ref="D27" ca="1">_FV(B27,"Currency")</f>
@@ -14150,23 +13682,23 @@
       </c>
       <c r="E27" s="3">
         <f t="array" aca="1" ref="E27" ca="1">_FV(B27,"Price")</f>
-        <v>170.71</v>
+        <v>170.68</v>
       </c>
       <c r="F27" s="4">
         <f t="array" aca="1" ref="F27" ca="1">_FV(B27,"Change (%)",TRUE)</f>
-        <v>7.0483000000000004E-2</v>
+        <v>7.0294999999999996E-2</v>
       </c>
       <c r="G27" s="5">
         <f t="array" aca="1" ref="G27" ca="1">_FV(B27,"Change")</f>
-        <v>11.24</v>
+        <v>11.21</v>
       </c>
       <c r="H27" s="6">
         <f t="array" aca="1" ref="H27" ca="1">_FV(B27,"P/E",TRUE)</f>
-        <v>58.470300000000002</v>
+        <v>58.459499999999998</v>
       </c>
       <c r="I27" s="6">
         <f t="array" aca="1" ref="I27" ca="1">_FV(B27,"Beta")</f>
-        <v>1.6120000000000001</v>
+        <v>1.6085</v>
       </c>
       <c r="J27" s="3">
         <f t="array" aca="1" ref="J27" ca="1">_FV(B27,"52 week high",TRUE)</f>
@@ -14194,7 +13726,7 @@
       </c>
       <c r="P27" s="7">
         <f t="array" aca="1" ref="P27" ca="1">_FV(B27,"Volume")</f>
-        <v>9963116</v>
+        <v>65024</v>
       </c>
       <c r="Q27" s="7">
         <f t="array" aca="1" ref="Q27" ca="1">_FV(B27,"Volume average",TRUE)</f>
@@ -14214,7 +13746,7 @@
       </c>
       <c r="U27" s="7">
         <f t="array" aca="1" ref="U27" ca="1">_FV(B27,"Market cap",TRUE)</f>
-        <v>214958544130</v>
+        <v>214920768040</v>
       </c>
       <c r="V27" s="7">
         <f t="array" aca="1" ref="V27" ca="1">_FV(B27,"Shares outstanding",TRUE)</f>
@@ -14230,7 +13762,7 @@
       </c>
       <c r="C28" s="2">
         <f t="array" aca="1" ref="C28" ca="1">_FV(B28,"Last trade time",TRUE)</f>
-        <v>46174.905713008593</v>
+        <v>46174.999994027341</v>
       </c>
       <c r="D28" t="str">
         <f t="array" aca="1" ref="D28" ca="1">_FV(B28,"Currency")</f>
@@ -14238,23 +13770,23 @@
       </c>
       <c r="E28" s="3">
         <f t="array" aca="1" ref="E28" ca="1">_FV(B28,"Price")</f>
-        <v>1034.74</v>
+        <v>1035.5</v>
       </c>
       <c r="F28" s="4">
         <f t="array" aca="1" ref="F28" ca="1">_FV(B28,"Change (%)",TRUE)</f>
-        <v>6.5643999999999994E-2</v>
+        <v>6.6425999999999999E-2</v>
       </c>
       <c r="G28" s="5">
         <f t="array" aca="1" ref="G28" ca="1">_FV(B28,"Change")</f>
-        <v>63.74</v>
+        <v>64.5</v>
       </c>
       <c r="H28" s="6">
         <f t="array" aca="1" ref="H28" ca="1">_FV(B28,"P/E",TRUE)</f>
-        <v>48.851599999999998</v>
+        <v>48.887500000000003</v>
       </c>
       <c r="I28" s="6">
         <f t="array" aca="1" ref="I28" ca="1">_FV(B28,"Beta")</f>
-        <v>2.1657999999999999</v>
+        <v>2.1707000000000001</v>
       </c>
       <c r="J28" s="3">
         <f t="array" aca="1" ref="J28" ca="1">_FV(B28,"52 week high",TRUE)</f>
@@ -14282,7 +13814,7 @@
       </c>
       <c r="P28" s="7">
         <f t="array" aca="1" ref="P28" ca="1">_FV(B28,"Volume")</f>
-        <v>46227755</v>
+        <v>1507152</v>
       </c>
       <c r="Q28" s="7">
         <f t="array" aca="1" ref="Q28" ca="1">_FV(B28,"Volume average",TRUE)</f>
@@ -14302,7 +13834,7 @@
       </c>
       <c r="U28" s="7">
         <f t="array" aca="1" ref="U28" ca="1">_FV(B28,"Market cap",TRUE)</f>
-        <v>1166911479160</v>
+        <v>1167768557000</v>
       </c>
       <c r="V28" s="7">
         <f t="array" aca="1" ref="V28" ca="1">_FV(B28,"Shares outstanding",TRUE)</f>
@@ -14318,7 +13850,7 @@
       </c>
       <c r="C29" s="2">
         <f t="array" aca="1" ref="C29" ca="1">_FV(B29,"Last trade time",TRUE)</f>
-        <v>46174.905670010936</v>
+        <v>46174.999977707812</v>
       </c>
       <c r="D29" t="str">
         <f t="array" aca="1" ref="D29" ca="1">_FV(B29,"Currency")</f>
@@ -14326,15 +13858,15 @@
       </c>
       <c r="E29" s="3">
         <f t="array" aca="1" ref="E29" ca="1">_FV(B29,"Price")</f>
-        <v>5.35</v>
+        <v>5.34</v>
       </c>
       <c r="F29" s="4">
         <f t="array" aca="1" ref="F29" ca="1">_FV(B29,"Change (%)",TRUE)</f>
-        <v>6.1508E-2</v>
+        <v>5.9524000000000001E-2</v>
       </c>
       <c r="G29" s="5">
         <f t="array" aca="1" ref="G29" ca="1">_FV(B29,"Change")</f>
-        <v>0.31</v>
+        <v>0.3</v>
       </c>
       <c r="H29" s="6" t="e" vm="18">
         <f t="array" ref="H29">_FV(B29,"P/E",TRUE)</f>
@@ -14342,7 +13874,7 @@
       </c>
       <c r="I29" s="6">
         <f t="array" aca="1" ref="I29" ca="1">_FV(B29,"Beta")</f>
-        <v>3.0739999999999998</v>
+        <v>3.0806</v>
       </c>
       <c r="J29" s="3">
         <f t="array" aca="1" ref="J29" ca="1">_FV(B29,"52 week high",TRUE)</f>
@@ -14370,7 +13902,7 @@
       </c>
       <c r="P29" s="7">
         <f t="array" aca="1" ref="P29" ca="1">_FV(B29,"Volume")</f>
-        <v>83209853</v>
+        <v>831399</v>
       </c>
       <c r="Q29" s="7">
         <f t="array" aca="1" ref="Q29" ca="1">_FV(B29,"Volume average",TRUE)</f>
@@ -14390,7 +13922,7 @@
       </c>
       <c r="U29" s="7">
         <f t="array" aca="1" ref="U29" ca="1">_FV(B29,"Market cap",TRUE)</f>
-        <v>2562379825</v>
+        <v>2557590330</v>
       </c>
       <c r="V29" s="7">
         <f t="array" aca="1" ref="V29" ca="1">_FV(B29,"Shares outstanding",TRUE)</f>
@@ -14406,7 +13938,7 @@
       </c>
       <c r="C30" s="2">
         <f t="array" aca="1" ref="C30" ca="1">_FV(B30,"Last trade time",TRUE)</f>
-        <v>46174.905091955472</v>
+        <v>46174.999917765628</v>
       </c>
       <c r="D30" t="str">
         <f t="array" aca="1" ref="D30" ca="1">_FV(B30,"Currency")</f>
@@ -14430,7 +13962,7 @@
       </c>
       <c r="I30" s="6">
         <f t="array" aca="1" ref="I30" ca="1">_FV(B30,"Beta")</f>
-        <v>2.1486999999999998</v>
+        <v>2.1423000000000001</v>
       </c>
       <c r="J30" s="3">
         <f t="array" aca="1" ref="J30" ca="1">_FV(B30,"52 week high",TRUE)</f>
@@ -14458,7 +13990,7 @@
       </c>
       <c r="P30" s="7">
         <f t="array" aca="1" ref="P30" ca="1">_FV(B30,"Volume")</f>
-        <v>2889436</v>
+        <v>17577</v>
       </c>
       <c r="Q30" s="7">
         <f t="array" aca="1" ref="Q30" ca="1">_FV(B30,"Volume average",TRUE)</f>
@@ -14494,7 +14026,7 @@
       </c>
       <c r="C31" s="2">
         <f t="array" aca="1" ref="C31" ca="1">_FV(B31,"Last trade time",TRUE)</f>
-        <v>46174.905683853904</v>
+        <v>46174.999987071096</v>
       </c>
       <c r="D31" t="str">
         <f t="array" aca="1" ref="D31" ca="1">_FV(B31,"Currency")</f>
@@ -14514,11 +14046,11 @@
       </c>
       <c r="H31" s="6">
         <f t="array" aca="1" ref="H31" ca="1">_FV(B31,"P/E",TRUE)</f>
-        <v>34.3583</v>
+        <v>34.358499999999999</v>
       </c>
       <c r="I31" s="6">
         <f t="array" aca="1" ref="I31" ca="1">_FV(B31,"Beta")</f>
-        <v>2.2155999999999998</v>
+        <v>2.1993999999999998</v>
       </c>
       <c r="J31" s="3">
         <f t="array" aca="1" ref="J31" ca="1">_FV(B31,"52 week high",TRUE)</f>
@@ -14546,7 +14078,7 @@
       </c>
       <c r="P31" s="7">
         <f t="array" aca="1" ref="P31" ca="1">_FV(B31,"Volume")</f>
-        <v>211381795</v>
+        <v>5918878</v>
       </c>
       <c r="Q31" s="7">
         <f t="array" aca="1" ref="Q31" ca="1">_FV(B31,"Volume average",TRUE)</f>
@@ -14582,7 +14114,7 @@
       </c>
       <c r="C32" s="2">
         <f t="array" aca="1" ref="C32" ca="1">_FV(B32,"Last trade time",TRUE)</f>
-        <v>46174.905646585154</v>
+        <v>46174.999897673435</v>
       </c>
       <c r="D32" t="str">
         <f t="array" aca="1" ref="D32" ca="1">_FV(B32,"Currency")</f>
@@ -14606,7 +14138,7 @@
       </c>
       <c r="I32" s="6">
         <f t="array" aca="1" ref="I32" ca="1">_FV(B32,"Beta")</f>
-        <v>3.0709</v>
+        <v>2.3961000000000001</v>
       </c>
       <c r="J32" s="3">
         <f t="array" aca="1" ref="J32" ca="1">_FV(B32,"52 week high",TRUE)</f>
@@ -14634,7 +14166,7 @@
       </c>
       <c r="P32" s="7">
         <f t="array" aca="1" ref="P32" ca="1">_FV(B32,"Volume")</f>
-        <v>6329907</v>
+        <v>216199</v>
       </c>
       <c r="Q32" s="7">
         <f t="array" aca="1" ref="Q32" ca="1">_FV(B32,"Volume average",TRUE)</f>
@@ -14670,7 +14202,7 @@
       </c>
       <c r="C33" s="2">
         <f t="array" aca="1" ref="C33" ca="1">_FV(B33,"Last trade time",TRUE)</f>
-        <v>46174.905093657035</v>
+        <v>46174.999383402341</v>
       </c>
       <c r="D33" t="str">
         <f t="array" aca="1" ref="D33" ca="1">_FV(B33,"Currency")</f>
@@ -14694,7 +14226,7 @@
       </c>
       <c r="I33" s="6">
         <f t="array" aca="1" ref="I33" ca="1">_FV(B33,"Beta")</f>
-        <v>2.2595999999999998</v>
+        <v>2.2097000000000002</v>
       </c>
       <c r="J33" s="3">
         <f t="array" aca="1" ref="J33" ca="1">_FV(B33,"52 week high",TRUE)</f>
@@ -14722,7 +14254,7 @@
       </c>
       <c r="P33" s="7">
         <f t="array" aca="1" ref="P33" ca="1">_FV(B33,"Volume")</f>
-        <v>13239008</v>
+        <v>94455</v>
       </c>
       <c r="Q33" s="7">
         <f t="array" aca="1" ref="Q33" ca="1">_FV(B33,"Volume average",TRUE)</f>
@@ -14758,7 +14290,7 @@
       </c>
       <c r="C34" s="2">
         <f t="array" aca="1" ref="C34" ca="1">_FV(B34,"Last trade time",TRUE)</f>
-        <v>46174.905637753909</v>
+        <v>46174.999991492972</v>
       </c>
       <c r="D34" t="str">
         <f t="array" aca="1" ref="D34" ca="1">_FV(B34,"Currency")</f>
@@ -14766,19 +14298,19 @@
       </c>
       <c r="E34" s="3">
         <f t="array" aca="1" ref="E34" ca="1">_FV(B34,"Price")</f>
-        <v>436.05</v>
+        <v>435.63</v>
       </c>
       <c r="F34" s="4">
         <f t="array" aca="1" ref="F34" ca="1">_FV(B34,"Change (%)",TRUE)</f>
-        <v>4.2060000000000007E-2</v>
+        <v>4.1056000000000002E-2</v>
       </c>
       <c r="G34" s="5">
         <f t="array" aca="1" ref="G34" ca="1">_FV(B34,"Change")</f>
-        <v>17.600000000000001</v>
+        <v>17.18</v>
       </c>
       <c r="H34" s="6">
         <f t="array" aca="1" ref="H34" ca="1">_FV(B34,"P/E",TRUE)</f>
-        <v>36.893700000000003</v>
+        <v>36.8583</v>
       </c>
       <c r="I34" s="6">
         <f t="array" aca="1" ref="I34" ca="1">_FV(B34,"Beta")</f>
@@ -14810,7 +14342,7 @@
       </c>
       <c r="P34" s="7">
         <f t="array" aca="1" ref="P34" ca="1">_FV(B34,"Volume")</f>
-        <v>18002766</v>
+        <v>223095</v>
       </c>
       <c r="Q34" s="7">
         <f t="array" aca="1" ref="Q34" ca="1">_FV(B34,"Volume average",TRUE)</f>
@@ -14830,7 +14362,7 @@
       </c>
       <c r="U34" s="7">
         <f t="array" aca="1" ref="U34" ca="1">_FV(B34,"Market cap",TRUE)</f>
-        <v>2261561987700</v>
+        <v>2259383668620</v>
       </c>
       <c r="V34" s="7">
         <f t="array" aca="1" ref="V34" ca="1">_FV(B34,"Shares outstanding",TRUE)</f>
@@ -14846,7 +14378,7 @@
       </c>
       <c r="C35" s="2">
         <f t="array" aca="1" ref="C35" ca="1">_FV(B35,"Last trade time",TRUE)</f>
-        <v>46174.9055028125</v>
+        <v>46174.999709687501</v>
       </c>
       <c r="D35" t="str">
         <f t="array" aca="1" ref="D35" ca="1">_FV(B35,"Currency")</f>
@@ -14866,11 +14398,11 @@
       </c>
       <c r="H35" s="6">
         <f t="array" aca="1" ref="H35" ca="1">_FV(B35,"P/E",TRUE)</f>
-        <v>15.9716</v>
+        <v>15.9717</v>
       </c>
       <c r="I35" s="6">
         <f t="array" aca="1" ref="I35" ca="1">_FV(B35,"Beta")</f>
-        <v>1.4177999999999999</v>
+        <v>1.3987000000000001</v>
       </c>
       <c r="J35" s="3">
         <f t="array" aca="1" ref="J35" ca="1">_FV(B35,"52 week high",TRUE)</f>
@@ -14898,7 +14430,7 @@
       </c>
       <c r="P35" s="7">
         <f t="array" aca="1" ref="P35" ca="1">_FV(B35,"Volume")</f>
-        <v>8507886</v>
+        <v>84049</v>
       </c>
       <c r="Q35" s="7">
         <f t="array" aca="1" ref="Q35" ca="1">_FV(B35,"Volume average",TRUE)</f>
@@ -14934,7 +14466,7 @@
       </c>
       <c r="C36" s="2" cm="1">
         <f t="array" aca="1" ref="C36" ca="1">_FV(B36,"Last trade time",TRUE)</f>
-        <v>46174.905388367966</v>
+        <v>46174.998533633596</v>
       </c>
       <c r="D36" t="str" cm="1">
         <f t="array" aca="1" ref="D36" ca="1">_FV(B36,"Currency")</f>
@@ -14954,11 +14486,11 @@
       </c>
       <c r="H36" s="6" cm="1">
         <f t="array" aca="1" ref="H36" ca="1">_FV(B36,"P/E",TRUE)</f>
-        <v>56.8459</v>
+        <v>56.847000000000001</v>
       </c>
       <c r="I36" s="6" cm="1">
         <f t="array" aca="1" ref="I36" ca="1">_FV(B36,"Beta")</f>
-        <v>1.1131</v>
+        <v>1.1052</v>
       </c>
       <c r="J36" s="3" cm="1">
         <f t="array" aca="1" ref="J36" ca="1">_FV(B36,"52 week high",TRUE)</f>
@@ -14986,7 +14518,7 @@
       </c>
       <c r="P36" s="7" cm="1">
         <f t="array" aca="1" ref="P36" ca="1">_FV(B36,"Volume")</f>
-        <v>7533997</v>
+        <v>11846</v>
       </c>
       <c r="Q36" s="7" cm="1">
         <f t="array" aca="1" ref="Q36" ca="1">_FV(B36,"Volume average",TRUE)</f>
@@ -15022,7 +14554,7 @@
       </c>
       <c r="C37" s="2" cm="1">
         <f t="array" aca="1" ref="C37" ca="1">_FV(B37,"Last trade time",TRUE)</f>
-        <v>46174.905591585157</v>
+        <v>46174.999922962503</v>
       </c>
       <c r="D37" t="str" cm="1">
         <f t="array" aca="1" ref="D37" ca="1">_FV(B37,"Currency")</f>
@@ -15042,11 +14574,11 @@
       </c>
       <c r="H37" s="6" cm="1">
         <f t="array" aca="1" ref="H37" ca="1">_FV(B37,"P/E",TRUE)</f>
-        <v>155.97880000000001</v>
+        <v>166.38329999999999</v>
       </c>
       <c r="I37" s="6" cm="1">
         <f t="array" aca="1" ref="I37" ca="1">_FV(B37,"Beta")</f>
-        <v>0.94020000000000004</v>
+        <v>0.9395</v>
       </c>
       <c r="J37" s="3" cm="1">
         <f t="array" aca="1" ref="J37" ca="1">_FV(B37,"52 week high",TRUE)</f>
@@ -15074,7 +14606,7 @@
       </c>
       <c r="P37" s="7" cm="1">
         <f t="array" aca="1" ref="P37" ca="1">_FV(B37,"Volume")</f>
-        <v>13666862</v>
+        <v>142043</v>
       </c>
       <c r="Q37" s="7" cm="1">
         <f t="array" aca="1" ref="Q37" ca="1">_FV(B37,"Volume average",TRUE)</f>
@@ -15110,7 +14642,7 @@
       </c>
       <c r="C38" s="2">
         <f t="array" aca="1" ref="C38" ca="1">_FV(B38,"Last trade time",TRUE)</f>
-        <v>46174.903102349221</v>
+        <v>46174.977704039062</v>
       </c>
       <c r="D38" t="str">
         <f t="array" aca="1" ref="D38" ca="1">_FV(B38,"Currency")</f>
@@ -15134,7 +14666,7 @@
       </c>
       <c r="I38" s="6">
         <f t="array" aca="1" ref="I38" ca="1">_FV(B38,"Beta")</f>
-        <v>0.6532</v>
+        <v>0.64800000000000002</v>
       </c>
       <c r="J38" s="3">
         <f t="array" aca="1" ref="J38" ca="1">_FV(B38,"52 week high",TRUE)</f>
@@ -15162,7 +14694,7 @@
       </c>
       <c r="P38" s="7">
         <f t="array" aca="1" ref="P38" ca="1">_FV(B38,"Volume")</f>
-        <v>979300</v>
+        <v>654</v>
       </c>
       <c r="Q38" s="7">
         <f t="array" aca="1" ref="Q38" ca="1">_FV(B38,"Volume average",TRUE)</f>
@@ -15198,7 +14730,7 @@
       </c>
       <c r="C39" s="2" cm="1">
         <f t="array" aca="1" ref="C39" ca="1">_FV(B39,"Last trade time",TRUE)</f>
-        <v>46174.904037707813</v>
+        <v>46174.999823657032</v>
       </c>
       <c r="D39" t="str" cm="1">
         <f t="array" aca="1" ref="D39" ca="1">_FV(B39,"Currency")</f>
@@ -15222,7 +14754,7 @@
       </c>
       <c r="I39" s="6" cm="1">
         <f t="array" aca="1" ref="I39" ca="1">_FV(B39,"Beta")</f>
-        <v>1.2517</v>
+        <v>1.2404999999999999</v>
       </c>
       <c r="J39" s="3" cm="1">
         <f t="array" aca="1" ref="J39" ca="1">_FV(B39,"52 week high",TRUE)</f>
@@ -15250,7 +14782,7 @@
       </c>
       <c r="P39" s="7" cm="1">
         <f t="array" aca="1" ref="P39" ca="1">_FV(B39,"Volume")</f>
-        <v>4573482</v>
+        <v>42915</v>
       </c>
       <c r="Q39" s="7" cm="1">
         <f t="array" aca="1" ref="Q39" ca="1">_FV(B39,"Volume average",TRUE)</f>
@@ -15286,7 +14818,7 @@
       </c>
       <c r="C40" s="2">
         <f t="array" aca="1" ref="C40" ca="1">_FV(B40,"Last trade time",TRUE)</f>
-        <v>46174.905622164064</v>
+        <v>46174.999993772653</v>
       </c>
       <c r="D40" t="str">
         <f t="array" aca="1" ref="D40" ca="1">_FV(B40,"Currency")</f>
@@ -15310,7 +14842,7 @@
       </c>
       <c r="I40" s="6">
         <f t="array" aca="1" ref="I40" ca="1">_FV(B40,"Beta")</f>
-        <v>2.7349999999999999</v>
+        <v>2.7391999999999999</v>
       </c>
       <c r="J40" s="3">
         <f t="array" aca="1" ref="J40" ca="1">_FV(B40,"52 week high",TRUE)</f>
@@ -15338,7 +14870,7 @@
       </c>
       <c r="P40" s="7">
         <f t="array" aca="1" ref="P40" ca="1">_FV(B40,"Volume")</f>
-        <v>33877459</v>
+        <v>404432</v>
       </c>
       <c r="Q40" s="7">
         <f t="array" aca="1" ref="Q40" ca="1">_FV(B40,"Volume average",TRUE)</f>
@@ -15374,7 +14906,7 @@
       </c>
       <c r="C41" s="2" cm="1">
         <f t="array" aca="1" ref="C41" ca="1">_FV(B41,"Last trade time",TRUE)</f>
-        <v>46174.905608310153</v>
+        <v>46174.999944745316</v>
       </c>
       <c r="D41" t="str" cm="1">
         <f t="array" aca="1" ref="D41" ca="1">_FV(B41,"Currency")</f>
@@ -15398,7 +14930,7 @@
       </c>
       <c r="I41" s="6" cm="1">
         <f t="array" aca="1" ref="I41" ca="1">_FV(B41,"Beta")</f>
-        <v>2.2128999999999999</v>
+        <v>2.2183000000000002</v>
       </c>
       <c r="J41" s="3" cm="1">
         <f t="array" aca="1" ref="J41" ca="1">_FV(B41,"52 week high",TRUE)</f>
@@ -15426,7 +14958,7 @@
       </c>
       <c r="P41" s="7" cm="1">
         <f t="array" aca="1" ref="P41" ca="1">_FV(B41,"Volume")</f>
-        <v>41351160</v>
+        <v>990612</v>
       </c>
       <c r="Q41" s="7" cm="1">
         <f t="array" aca="1" ref="Q41" ca="1">_FV(B41,"Volume average",TRUE)</f>
@@ -15462,7 +14994,7 @@
       </c>
       <c r="C42" s="2">
         <f t="array" aca="1" ref="C42" ca="1">_FV(B42,"Last trade time",TRUE)</f>
-        <v>46174.905683390622</v>
+        <v>46174.999994803125</v>
       </c>
       <c r="D42" t="str">
         <f t="array" aca="1" ref="D42" ca="1">_FV(B42,"Currency")</f>
@@ -15482,7 +15014,7 @@
       </c>
       <c r="H42" s="6">
         <f t="array" aca="1" ref="H42" ca="1">_FV(B42,"P/E",TRUE)</f>
-        <v>59.9238</v>
+        <v>62.273099999999999</v>
       </c>
       <c r="I42" s="6">
         <f t="array" aca="1" ref="I42" ca="1">_FV(B42,"Beta")</f>
@@ -15514,7 +15046,7 @@
       </c>
       <c r="P42" s="7">
         <f t="array" aca="1" ref="P42" ca="1">_FV(B42,"Volume")</f>
-        <v>9637122</v>
+        <v>273723</v>
       </c>
       <c r="Q42" s="7">
         <f t="array" aca="1" ref="Q42" ca="1">_FV(B42,"Volume average",TRUE)</f>
@@ -15550,7 +15082,7 @@
       </c>
       <c r="C43" s="2" cm="1">
         <f t="array" aca="1" ref="C43" ca="1">_FV(B43,"Last trade time",TRUE)</f>
-        <v>46174.90564188594</v>
+        <v>46174.999510902344</v>
       </c>
       <c r="D43" t="str" cm="1">
         <f t="array" aca="1" ref="D43" ca="1">_FV(B43,"Currency")</f>
@@ -15574,7 +15106,7 @@
       </c>
       <c r="I43" s="6" cm="1">
         <f t="array" aca="1" ref="I43" ca="1">_FV(B43,"Beta")</f>
-        <v>1.04</v>
+        <v>0.99950000000000006</v>
       </c>
       <c r="J43" s="3" cm="1">
         <f t="array" aca="1" ref="J43" ca="1">_FV(B43,"52 week high",TRUE)</f>
@@ -15602,7 +15134,7 @@
       </c>
       <c r="P43" s="7" cm="1">
         <f t="array" aca="1" ref="P43" ca="1">_FV(B43,"Volume")</f>
-        <v>30784543</v>
+        <v>314465</v>
       </c>
       <c r="Q43" s="7" cm="1">
         <f t="array" aca="1" ref="Q43" ca="1">_FV(B43,"Volume average",TRUE)</f>
@@ -15638,7 +15170,7 @@
       </c>
       <c r="C44" s="2" cm="1">
         <f t="array" aca="1" ref="C44" ca="1">_FV(B44,"Last trade time",TRUE)</f>
-        <v>46174.890703553123</v>
+        <v>46174.999616041408</v>
       </c>
       <c r="D44" t="str" cm="1">
         <f t="array" aca="1" ref="D44" ca="1">_FV(B44,"Currency")</f>
@@ -15658,11 +15190,11 @@
       </c>
       <c r="H44" s="6" cm="1">
         <f t="array" aca="1" ref="H44" ca="1">_FV(B44,"P/E",TRUE)</f>
-        <v>82.997399999999999</v>
+        <v>82.998900000000006</v>
       </c>
       <c r="I44" s="6" cm="1">
         <f t="array" aca="1" ref="I44" ca="1">_FV(B44,"Beta")</f>
-        <v>0.75149999999999995</v>
+        <v>0.73699999999999999</v>
       </c>
       <c r="J44" s="3" cm="1">
         <f t="array" aca="1" ref="J44" ca="1">_FV(B44,"52 week high",TRUE)</f>
@@ -15690,7 +15222,7 @@
       </c>
       <c r="P44" s="7" cm="1">
         <f t="array" aca="1" ref="P44" ca="1">_FV(B44,"Volume")</f>
-        <v>6620980</v>
+        <v>5042</v>
       </c>
       <c r="Q44" s="7" cm="1">
         <f t="array" aca="1" ref="Q44" ca="1">_FV(B44,"Volume average",TRUE)</f>
@@ -15726,7 +15258,7 @@
       </c>
       <c r="C45" s="2">
         <f t="array" aca="1" ref="C45" ca="1">_FV(B45,"Last trade time",TRUE)</f>
-        <v>46174.905663217185</v>
+        <v>46174.999978089843</v>
       </c>
       <c r="D45" t="str">
         <f t="array" aca="1" ref="D45" ca="1">_FV(B45,"Currency")</f>
@@ -15746,11 +15278,11 @@
       </c>
       <c r="H45" s="6">
         <f t="array" aca="1" ref="H45" ca="1">_FV(B45,"P/E",TRUE)</f>
-        <v>25.543500000000002</v>
+        <v>25.5442</v>
       </c>
       <c r="I45" s="6">
         <f t="array" aca="1" ref="I45" ca="1">_FV(B45,"Beta")</f>
-        <v>1.8606</v>
+        <v>1.8712</v>
       </c>
       <c r="J45" s="3">
         <f t="array" aca="1" ref="J45" ca="1">_FV(B45,"52 week high",TRUE)</f>
@@ -15778,7 +15310,7 @@
       </c>
       <c r="P45" s="7">
         <f t="array" aca="1" ref="P45" ca="1">_FV(B45,"Volume")</f>
-        <v>49571477</v>
+        <v>1047681</v>
       </c>
       <c r="Q45" s="7">
         <f t="array" aca="1" ref="Q45" ca="1">_FV(B45,"Volume average",TRUE)</f>
@@ -15814,7 +15346,7 @@
       </c>
       <c r="C46" s="2">
         <f t="array" aca="1" ref="C46" ca="1">_FV(B46,"Last trade time",TRUE)</f>
-        <v>46174.90570631875</v>
+        <v>46174.999984108596</v>
       </c>
       <c r="D46" t="str">
         <f t="array" aca="1" ref="D46" ca="1">_FV(B46,"Currency")</f>
@@ -15834,11 +15366,11 @@
       </c>
       <c r="H46" s="6">
         <f t="array" aca="1" ref="H46" ca="1">_FV(B46,"P/E",TRUE)</f>
-        <v>89.787000000000006</v>
+        <v>89.786500000000004</v>
       </c>
       <c r="I46" s="6">
         <f t="array" aca="1" ref="I46" ca="1">_FV(B46,"Beta")</f>
-        <v>1.4283999999999999</v>
+        <v>1.4334</v>
       </c>
       <c r="J46" s="3">
         <f t="array" aca="1" ref="J46" ca="1">_FV(B46,"52 week high",TRUE)</f>
@@ -15866,7 +15398,7 @@
       </c>
       <c r="P46" s="7">
         <f t="array" aca="1" ref="P46" ca="1">_FV(B46,"Volume")</f>
-        <v>30345239</v>
+        <v>872832</v>
       </c>
       <c r="Q46" s="7">
         <f t="array" aca="1" ref="Q46" ca="1">_FV(B46,"Volume average",TRUE)</f>
@@ -15902,7 +15434,7 @@
       </c>
       <c r="C47" s="2" cm="1">
         <f t="array" aca="1" ref="C47" ca="1">_FV(B47,"Last trade time",TRUE)</f>
-        <v>46174.905540705469</v>
+        <v>46174.999967210155</v>
       </c>
       <c r="D47" t="str" cm="1">
         <f t="array" aca="1" ref="D47" ca="1">_FV(B47,"Currency")</f>
@@ -15922,11 +15454,11 @@
       </c>
       <c r="H47" s="6" cm="1">
         <f t="array" aca="1" ref="H47" ca="1">_FV(B47,"P/E",TRUE)</f>
-        <v>110.22709999999999</v>
+        <v>114.0904</v>
       </c>
       <c r="I47" s="6" cm="1">
         <f t="array" aca="1" ref="I47" ca="1">_FV(B47,"Beta")</f>
-        <v>1.2188000000000001</v>
+        <v>1.2116</v>
       </c>
       <c r="J47" s="3" cm="1">
         <f t="array" aca="1" ref="J47" ca="1">_FV(B47,"52 week high",TRUE)</f>
@@ -15954,7 +15486,7 @@
       </c>
       <c r="P47" s="7" cm="1">
         <f t="array" aca="1" ref="P47" ca="1">_FV(B47,"Volume")</f>
-        <v>2581417</v>
+        <v>8398</v>
       </c>
       <c r="Q47" s="7" cm="1">
         <f t="array" aca="1" ref="Q47" ca="1">_FV(B47,"Volume average",TRUE)</f>
@@ -15990,7 +15522,7 @@
       </c>
       <c r="C48" s="2" cm="1">
         <f t="array" aca="1" ref="C48" ca="1">_FV(B48,"Last trade time",TRUE)</f>
-        <v>46174.905060428122</v>
+        <v>46174.999932649996</v>
       </c>
       <c r="D48" t="str" cm="1">
         <f t="array" aca="1" ref="D48" ca="1">_FV(B48,"Currency")</f>
@@ -16014,7 +15546,7 @@
       </c>
       <c r="I48" s="6" cm="1">
         <f t="array" aca="1" ref="I48" ca="1">_FV(B48,"Beta")</f>
-        <v>1.92</v>
+        <v>1.9258999999999999</v>
       </c>
       <c r="J48" s="3" cm="1">
         <f t="array" aca="1" ref="J48" ca="1">_FV(B48,"52 week high",TRUE)</f>
@@ -16042,7 +15574,7 @@
       </c>
       <c r="P48" s="7" cm="1">
         <f t="array" aca="1" ref="P48" ca="1">_FV(B48,"Volume")</f>
-        <v>3686848</v>
+        <v>13956</v>
       </c>
       <c r="Q48" s="7" cm="1">
         <f t="array" aca="1" ref="Q48" ca="1">_FV(B48,"Volume average",TRUE)</f>
@@ -16078,7 +15610,7 @@
       </c>
       <c r="C49" s="2">
         <f t="array" aca="1" ref="C49" ca="1">_FV(B49,"Last trade time",TRUE)</f>
-        <v>46174.905730462502</v>
+        <v>46174.999978228909</v>
       </c>
       <c r="D49" t="str">
         <f t="array" aca="1" ref="D49" ca="1">_FV(B49,"Currency")</f>
@@ -16098,11 +15630,11 @@
       </c>
       <c r="H49" s="6">
         <f t="array" aca="1" ref="H49" ca="1">_FV(B49,"P/E",TRUE)</f>
-        <v>142.42420000000001</v>
+        <v>142.41489999999999</v>
       </c>
       <c r="I49" s="6">
         <f t="array" aca="1" ref="I49" ca="1">_FV(B49,"Beta")</f>
-        <v>4.2304000000000004</v>
+        <v>4.2316000000000003</v>
       </c>
       <c r="J49" s="3">
         <f t="array" aca="1" ref="J49" ca="1">_FV(B49,"52 week high",TRUE)</f>
@@ -16130,7 +15662,7 @@
       </c>
       <c r="P49" s="7">
         <f t="array" aca="1" ref="P49" ca="1">_FV(B49,"Volume")</f>
-        <v>56204598</v>
+        <v>1001447</v>
       </c>
       <c r="Q49" s="7">
         <f t="array" aca="1" ref="Q49" ca="1">_FV(B49,"Volume average",TRUE)</f>
@@ -16166,7 +15698,7 @@
       </c>
       <c r="C50" s="2">
         <f t="array" aca="1" ref="C50" ca="1">_FV(B50,"Last trade time",TRUE)</f>
-        <v>46174.905744560157</v>
+        <v>46174.999945068746</v>
       </c>
       <c r="D50" t="str">
         <f t="array" aca="1" ref="D50" ca="1">_FV(B50,"Currency")</f>
@@ -16186,11 +15718,11 @@
       </c>
       <c r="H50" s="6">
         <f t="array" aca="1" ref="H50" ca="1">_FV(B50,"P/E",TRUE)</f>
-        <v>33.337499999999999</v>
+        <v>33.942799999999998</v>
       </c>
       <c r="I50" s="6">
         <f t="array" aca="1" ref="I50" ca="1">_FV(B50,"Beta")</f>
-        <v>2.6013000000000002</v>
+        <v>2.6246</v>
       </c>
       <c r="J50" s="3">
         <f t="array" aca="1" ref="J50" ca="1">_FV(B50,"52 week high",TRUE)</f>
@@ -16218,7 +15750,7 @@
       </c>
       <c r="P50" s="7">
         <f t="array" aca="1" ref="P50" ca="1">_FV(B50,"Volume")</f>
-        <v>86728015</v>
+        <v>780004</v>
       </c>
       <c r="Q50" s="7">
         <f t="array" aca="1" ref="Q50" ca="1">_FV(B50,"Volume average",TRUE)</f>
@@ -16238,11 +15770,11 @@
       </c>
       <c r="U50" s="7">
         <f t="array" aca="1" ref="U50" ca="1">_FV(B50,"Market cap",TRUE)</f>
-        <v>6795827476</v>
+        <v>6832361954</v>
       </c>
       <c r="V50" s="7">
         <f t="array" aca="1" ref="V50" ca="1">_FV(B50,"Shares outstanding",TRUE)</f>
-        <v>504890600</v>
+        <v>507604900</v>
       </c>
     </row>
     <row r="51" spans="1:22">
@@ -16254,7 +15786,7 @@
       </c>
       <c r="C51" s="2" cm="1">
         <f t="array" aca="1" ref="C51" ca="1">_FV(B51,"Last trade time",TRUE)</f>
-        <v>46174.905310890623</v>
+        <v>46174.999683703129</v>
       </c>
       <c r="D51" t="str" cm="1">
         <f t="array" aca="1" ref="D51" ca="1">_FV(B51,"Currency")</f>
@@ -16262,23 +15794,23 @@
       </c>
       <c r="E51" s="3" cm="1">
         <f t="array" aca="1" ref="E51" ca="1">_FV(B51,"Price")</f>
-        <v>323.42</v>
+        <v>323.39</v>
       </c>
       <c r="F51" s="4" cm="1">
         <f t="array" aca="1" ref="F51" ca="1">_FV(B51,"Change (%)",TRUE)</f>
-        <v>2.4420999999999998E-2</v>
+        <v>2.4326E-2</v>
       </c>
       <c r="G51" s="5" cm="1">
         <f t="array" aca="1" ref="G51" ca="1">_FV(B51,"Change")</f>
-        <v>7.71</v>
+        <v>7.68</v>
       </c>
       <c r="H51" s="6" cm="1">
         <f t="array" aca="1" ref="H51" ca="1">_FV(B51,"P/E",TRUE)</f>
-        <v>81.200100000000006</v>
+        <v>81.1922</v>
       </c>
       <c r="I51" s="6" cm="1">
         <f t="array" aca="1" ref="I51" ca="1">_FV(B51,"Beta")</f>
-        <v>2.0386000000000002</v>
+        <v>2.0379</v>
       </c>
       <c r="J51" s="3" cm="1">
         <f t="array" aca="1" ref="J51" ca="1">_FV(B51,"52 week high",TRUE)</f>
@@ -16306,7 +15838,7 @@
       </c>
       <c r="P51" s="7" cm="1">
         <f t="array" aca="1" ref="P51" ca="1">_FV(B51,"Volume")</f>
-        <v>6140574</v>
+        <v>121313</v>
       </c>
       <c r="Q51" s="7" cm="1">
         <f t="array" aca="1" ref="Q51" ca="1">_FV(B51,"Volume average",TRUE)</f>
@@ -16326,7 +15858,7 @@
       </c>
       <c r="U51" s="7" cm="1">
         <f t="array" aca="1" ref="U51" ca="1">_FV(B51,"Market cap",TRUE)</f>
-        <v>124228468096</v>
+        <v>124216944832</v>
       </c>
       <c r="V51" s="7" cm="1">
         <f t="array" aca="1" ref="V51" ca="1">_FV(B51,"Shares outstanding",TRUE)</f>
@@ -16342,7 +15874,7 @@
       </c>
       <c r="C52" s="2">
         <f t="array" aca="1" ref="C52" ca="1">_FV(B52,"Last trade time",TRUE)</f>
-        <v>46174.90572489531</v>
+        <v>46174.999959849221</v>
       </c>
       <c r="D52" t="str">
         <f t="array" aca="1" ref="D52" ca="1">_FV(B52,"Currency")</f>
@@ -16366,7 +15898,7 @@
       </c>
       <c r="I52" s="6">
         <f t="array" aca="1" ref="I52" ca="1">_FV(B52,"Beta")</f>
-        <v>1.1085</v>
+        <v>1.1014999999999999</v>
       </c>
       <c r="J52" s="3">
         <f t="array" aca="1" ref="J52" ca="1">_FV(B52,"52 week high",TRUE)</f>
@@ -16394,7 +15926,7 @@
       </c>
       <c r="P52" s="7">
         <f t="array" aca="1" ref="P52" ca="1">_FV(B52,"Volume")</f>
-        <v>53242355</v>
+        <v>745173</v>
       </c>
       <c r="Q52" s="7">
         <f t="array" aca="1" ref="Q52" ca="1">_FV(B52,"Volume average",TRUE)</f>
@@ -16430,7 +15962,7 @@
       </c>
       <c r="C53" s="2" cm="1">
         <f t="array" aca="1" ref="C53" ca="1">_FV(B53,"Last trade time",TRUE)</f>
-        <v>46174.905592603907</v>
+        <v>46174.99998989531</v>
       </c>
       <c r="D53" t="str" cm="1">
         <f t="array" aca="1" ref="D53" ca="1">_FV(B53,"Currency")</f>
@@ -16454,7 +15986,7 @@
       </c>
       <c r="I53" s="6" cm="1">
         <f t="array" aca="1" ref="I53" ca="1">_FV(B53,"Beta")</f>
-        <v>1.5746</v>
+        <v>1.5567</v>
       </c>
       <c r="J53" s="3" cm="1">
         <f t="array" aca="1" ref="J53" ca="1">_FV(B53,"52 week high",TRUE)</f>
@@ -16482,7 +16014,7 @@
       </c>
       <c r="P53" s="7" cm="1">
         <f t="array" aca="1" ref="P53" ca="1">_FV(B53,"Volume")</f>
-        <v>8600167</v>
+        <v>130195</v>
       </c>
       <c r="Q53" s="7" cm="1">
         <f t="array" aca="1" ref="Q53" ca="1">_FV(B53,"Volume average",TRUE)</f>
@@ -16518,7 +16050,7 @@
       </c>
       <c r="C54" s="2">
         <f t="array" aca="1" ref="C54" ca="1">_FV(B54,"Last trade time",TRUE)</f>
-        <v>46174.905073610935</v>
+        <v>46174.997350786718</v>
       </c>
       <c r="D54" t="str">
         <f t="array" aca="1" ref="D54" ca="1">_FV(B54,"Currency")</f>
@@ -16542,7 +16074,7 @@
       </c>
       <c r="I54" s="6">
         <f t="array" aca="1" ref="I54" ca="1">_FV(B54,"Beta")</f>
-        <v>1.8226</v>
+        <v>1.8242</v>
       </c>
       <c r="J54" s="3">
         <f t="array" aca="1" ref="J54" ca="1">_FV(B54,"52 week high",TRUE)</f>
@@ -16570,7 +16102,7 @@
       </c>
       <c r="P54" s="7">
         <f t="array" aca="1" ref="P54" ca="1">_FV(B54,"Volume")</f>
-        <v>1057960</v>
+        <v>36938</v>
       </c>
       <c r="Q54" s="7">
         <f t="array" aca="1" ref="Q54" ca="1">_FV(B54,"Volume average",TRUE)</f>
@@ -16606,7 +16138,7 @@
       </c>
       <c r="C55" s="2">
         <f t="array" aca="1" ref="C55" ca="1">_FV(B55,"Last trade time",TRUE)</f>
-        <v>46174.904217314062</v>
+        <v>46174.999527325781</v>
       </c>
       <c r="D55" t="str">
         <f t="array" aca="1" ref="D55" ca="1">_FV(B55,"Currency")</f>
@@ -16626,11 +16158,11 @@
       </c>
       <c r="H55" s="6">
         <f t="array" aca="1" ref="H55" ca="1">_FV(B55,"P/E",TRUE)</f>
-        <v>17.5974</v>
+        <v>17.5975</v>
       </c>
       <c r="I55" s="6">
         <f t="array" aca="1" ref="I55" ca="1">_FV(B55,"Beta")</f>
-        <v>0.7702</v>
+        <v>0.77200000000000002</v>
       </c>
       <c r="J55" s="3">
         <f t="array" aca="1" ref="J55" ca="1">_FV(B55,"52 week high",TRUE)</f>
@@ -16658,7 +16190,7 @@
       </c>
       <c r="P55" s="7">
         <f t="array" aca="1" ref="P55" ca="1">_FV(B55,"Volume")</f>
-        <v>13960790</v>
+        <v>3593</v>
       </c>
       <c r="Q55" s="7">
         <f t="array" aca="1" ref="Q55" ca="1">_FV(B55,"Volume average",TRUE)</f>
@@ -16694,7 +16226,7 @@
       </c>
       <c r="C56" s="2" cm="1">
         <f t="array" aca="1" ref="C56" ca="1">_FV(B56,"Last trade time",TRUE)</f>
-        <v>46174.905516805469</v>
+        <v>46174.999908946091</v>
       </c>
       <c r="D56" t="str" cm="1">
         <f t="array" aca="1" ref="D56" ca="1">_FV(B56,"Currency")</f>
@@ -16718,7 +16250,7 @@
       </c>
       <c r="I56" s="6" cm="1">
         <f t="array" aca="1" ref="I56" ca="1">_FV(B56,"Beta")</f>
-        <v>1.6780999999999999</v>
+        <v>1.7036</v>
       </c>
       <c r="J56" s="3" cm="1">
         <f t="array" aca="1" ref="J56" ca="1">_FV(B56,"52 week high",TRUE)</f>
@@ -16746,7 +16278,7 @@
       </c>
       <c r="P56" s="7" cm="1">
         <f t="array" aca="1" ref="P56" ca="1">_FV(B56,"Volume")</f>
-        <v>6971620</v>
+        <v>197256</v>
       </c>
       <c r="Q56" s="7" cm="1">
         <f t="array" aca="1" ref="Q56" ca="1">_FV(B56,"Volume average",TRUE)</f>
@@ -16782,7 +16314,7 @@
       </c>
       <c r="C57" s="2" cm="1">
         <f t="array" aca="1" ref="C57" ca="1">_FV(B57,"Last trade time",TRUE)</f>
-        <v>46174.902086770315</v>
+        <v>46174.994004791406</v>
       </c>
       <c r="D57" t="str" cm="1">
         <f t="array" aca="1" ref="D57" ca="1">_FV(B57,"Currency")</f>
@@ -16790,23 +16322,23 @@
       </c>
       <c r="E57" s="3" cm="1">
         <f t="array" aca="1" ref="E57" ca="1">_FV(B57,"Price")</f>
-        <v>456.74</v>
+        <v>456.71</v>
       </c>
       <c r="F57" s="4" cm="1">
         <f t="array" aca="1" ref="F57" ca="1">_FV(B57,"Change (%)",TRUE)</f>
-        <v>1.2593E-2</v>
+        <v>1.2525999999999999E-2</v>
       </c>
       <c r="G57" s="5" cm="1">
         <f t="array" aca="1" ref="G57" ca="1">_FV(B57,"Change")</f>
-        <v>5.68</v>
+        <v>5.65</v>
       </c>
       <c r="H57" s="6" cm="1">
         <f t="array" aca="1" ref="H57" ca="1">_FV(B57,"P/E",TRUE)</f>
-        <v>47.447600000000001</v>
+        <v>47.444699999999997</v>
       </c>
       <c r="I57" s="6" cm="1">
         <f t="array" aca="1" ref="I57" ca="1">_FV(B57,"Beta")</f>
-        <v>1.5652999999999999</v>
+        <v>1.5595000000000001</v>
       </c>
       <c r="J57" s="3" cm="1">
         <f t="array" aca="1" ref="J57" ca="1">_FV(B57,"52 week high",TRUE)</f>
@@ -16834,7 +16366,7 @@
       </c>
       <c r="P57" s="7" cm="1">
         <f t="array" aca="1" ref="P57" ca="1">_FV(B57,"Volume")</f>
-        <v>815931</v>
+        <v>227</v>
       </c>
       <c r="Q57" s="7" cm="1">
         <f t="array" aca="1" ref="Q57" ca="1">_FV(B57,"Volume average",TRUE)</f>
@@ -16854,7 +16386,7 @@
       </c>
       <c r="U57" s="7" cm="1">
         <f t="array" aca="1" ref="U57" ca="1">_FV(B57,"Market cap",TRUE)</f>
-        <v>50823241086</v>
+        <v>50819902869</v>
       </c>
       <c r="V57" s="7" cm="1">
         <f t="array" aca="1" ref="V57" ca="1">_FV(B57,"Shares outstanding",TRUE)</f>
@@ -16870,7 +16402,7 @@
       </c>
       <c r="C58" s="2" cm="1">
         <f t="array" aca="1" ref="C58" ca="1">_FV(B58,"Last trade time",TRUE)</f>
-        <v>46174.905482858594</v>
+        <v>46174.999302256248</v>
       </c>
       <c r="D58" t="str" cm="1">
         <f t="array" aca="1" ref="D58" ca="1">_FV(B58,"Currency")</f>
@@ -16894,7 +16426,7 @@
       </c>
       <c r="I58" s="6" cm="1">
         <f t="array" aca="1" ref="I58" ca="1">_FV(B58,"Beta")</f>
-        <v>1.5009999999999999</v>
+        <v>1.5045999999999999</v>
       </c>
       <c r="J58" s="3" cm="1">
         <f t="array" aca="1" ref="J58" ca="1">_FV(B58,"52 week high",TRUE)</f>
@@ -16922,7 +16454,7 @@
       </c>
       <c r="P58" s="7" cm="1">
         <f t="array" aca="1" ref="P58" ca="1">_FV(B58,"Volume")</f>
-        <v>735788</v>
+        <v>10152</v>
       </c>
       <c r="Q58" s="7" cm="1">
         <f t="array" aca="1" ref="Q58" ca="1">_FV(B58,"Volume average",TRUE)</f>
@@ -16958,7 +16490,7 @@
       </c>
       <c r="C59" s="2" cm="1">
         <f t="array" aca="1" ref="C59" ca="1">_FV(B59,"Last trade time",TRUE)</f>
-        <v>46174.90555854141</v>
+        <v>46174.999994918748</v>
       </c>
       <c r="D59" t="str" cm="1">
         <f t="array" aca="1" ref="D59" ca="1">_FV(B59,"Currency")</f>
@@ -16982,7 +16514,7 @@
       </c>
       <c r="I59" s="6" cm="1">
         <f t="array" aca="1" ref="I59" ca="1">_FV(B59,"Beta")</f>
-        <v>0.99850000000000005</v>
+        <v>1.0089999999999999</v>
       </c>
       <c r="J59" s="3" cm="1">
         <f t="array" aca="1" ref="J59" ca="1">_FV(B59,"52 week high",TRUE)</f>
@@ -17010,7 +16542,7 @@
       </c>
       <c r="P59" s="7" cm="1">
         <f t="array" aca="1" ref="P59" ca="1">_FV(B59,"Volume")</f>
-        <v>33646470</v>
+        <v>673215</v>
       </c>
       <c r="Q59" s="7" cm="1">
         <f t="array" aca="1" ref="Q59" ca="1">_FV(B59,"Volume average",TRUE)</f>
@@ -17030,7 +16562,7 @@
       </c>
       <c r="U59" s="7" cm="1">
         <f t="array" aca="1" ref="U59" ca="1">_FV(B59,"Market cap",TRUE)</f>
-        <v>440257379466.70001</v>
+        <v>493987523137.08002</v>
       </c>
       <c r="V59" s="7" t="e" cm="1" vm="57">
         <f t="array" ref="V59">_FV(B59,"Shares outstanding",TRUE)</f>
@@ -17046,7 +16578,7 @@
       </c>
       <c r="C60" s="2" cm="1">
         <f t="array" aca="1" ref="C60" ca="1">_FV(B60,"Last trade time",TRUE)</f>
-        <v>46174.902648124997</v>
+        <v>46174.99811246484</v>
       </c>
       <c r="D60" t="str" cm="1">
         <f t="array" aca="1" ref="D60" ca="1">_FV(B60,"Currency")</f>
@@ -17066,11 +16598,11 @@
       </c>
       <c r="H60" s="6" cm="1">
         <f t="array" aca="1" ref="H60" ca="1">_FV(B60,"P/E",TRUE)</f>
-        <v>39.113100000000003</v>
+        <v>39.113</v>
       </c>
       <c r="I60" s="6" cm="1">
         <f t="array" aca="1" ref="I60" ca="1">_FV(B60,"Beta")</f>
-        <v>1.1911</v>
+        <v>1.1931</v>
       </c>
       <c r="J60" s="3" cm="1">
         <f t="array" aca="1" ref="J60" ca="1">_FV(B60,"52 week high",TRUE)</f>
@@ -17098,7 +16630,7 @@
       </c>
       <c r="P60" s="7" cm="1">
         <f t="array" aca="1" ref="P60" ca="1">_FV(B60,"Volume")</f>
-        <v>2338084</v>
+        <v>4695</v>
       </c>
       <c r="Q60" s="7" cm="1">
         <f t="array" aca="1" ref="Q60" ca="1">_FV(B60,"Volume average",TRUE)</f>
@@ -17134,7 +16666,7 @@
       </c>
       <c r="C61" s="2" cm="1">
         <f t="array" aca="1" ref="C61" ca="1">_FV(B61,"Last trade time",TRUE)</f>
-        <v>46174.905058738281</v>
+        <v>46174.999851365625</v>
       </c>
       <c r="D61" t="str" cm="1">
         <f t="array" aca="1" ref="D61" ca="1">_FV(B61,"Currency")</f>
@@ -17154,11 +16686,11 @@
       </c>
       <c r="H61" s="6" cm="1">
         <f t="array" aca="1" ref="H61" ca="1">_FV(B61,"P/E",TRUE)</f>
-        <v>40.127299999999998</v>
+        <v>40.430500000000002</v>
       </c>
       <c r="I61" s="6" cm="1">
         <f t="array" aca="1" ref="I61" ca="1">_FV(B61,"Beta")</f>
-        <v>1.0015000000000001</v>
+        <v>1.004</v>
       </c>
       <c r="J61" s="3" cm="1">
         <f t="array" aca="1" ref="J61" ca="1">_FV(B61,"52 week high",TRUE)</f>
@@ -17186,7 +16718,7 @@
       </c>
       <c r="P61" s="7" cm="1">
         <f t="array" aca="1" ref="P61" ca="1">_FV(B61,"Volume")</f>
-        <v>23937354</v>
+        <v>53645</v>
       </c>
       <c r="Q61" s="7" cm="1">
         <f t="array" aca="1" ref="Q61" ca="1">_FV(B61,"Volume average",TRUE)</f>
@@ -17222,7 +16754,7 @@
       </c>
       <c r="C62" s="2">
         <f t="array" aca="1" ref="C62" ca="1">_FV(B62,"Last trade time",TRUE)</f>
-        <v>46174.904568135935</v>
+        <v>46174.999862673438</v>
       </c>
       <c r="D62" t="str">
         <f t="array" aca="1" ref="D62" ca="1">_FV(B62,"Currency")</f>
@@ -17242,11 +16774,11 @@
       </c>
       <c r="H62" s="6">
         <f t="array" aca="1" ref="H62" ca="1">_FV(B62,"P/E",TRUE)</f>
-        <v>53.330399999999997</v>
+        <v>53.330300000000001</v>
       </c>
       <c r="I62" s="6">
         <f t="array" aca="1" ref="I62" ca="1">_FV(B62,"Beta")</f>
-        <v>2.4472999999999998</v>
+        <v>2.4569999999999999</v>
       </c>
       <c r="J62" s="3">
         <f t="array" aca="1" ref="J62" ca="1">_FV(B62,"52 week high",TRUE)</f>
@@ -17274,7 +16806,7 @@
       </c>
       <c r="P62" s="7">
         <f t="array" aca="1" ref="P62" ca="1">_FV(B62,"Volume")</f>
-        <v>4296795</v>
+        <v>22807</v>
       </c>
       <c r="Q62" s="7">
         <f t="array" aca="1" ref="Q62" ca="1">_FV(B62,"Volume average",TRUE)</f>
@@ -17310,7 +16842,7 @@
       </c>
       <c r="C63" s="2" cm="1">
         <f t="array" aca="1" ref="C63" ca="1">_FV(B63,"Last trade time",TRUE)</f>
-        <v>46174.90571398125</v>
+        <v>46175.000000010936</v>
       </c>
       <c r="D63" t="str" cm="1">
         <f t="array" aca="1" ref="D63" ca="1">_FV(B63,"Currency")</f>
@@ -17318,15 +16850,15 @@
       </c>
       <c r="E63" s="3" cm="1">
         <f t="array" aca="1" ref="E63" ca="1">_FV(B63,"Price")</f>
-        <v>758.47</v>
+        <v>758.54</v>
       </c>
       <c r="F63" s="4" cm="1">
         <f t="array" aca="1" ref="F63" ca="1">_FV(B63,"Change (%)",TRUE)</f>
-        <v>2.6310000000000001E-3</v>
+        <v>2.7229999999999997E-3</v>
       </c>
       <c r="G63" s="5" cm="1">
         <f t="array" aca="1" ref="G63" ca="1">_FV(B63,"Change")</f>
-        <v>1.99</v>
+        <v>2.06</v>
       </c>
       <c r="H63" s="6" t="e" vm="18">
         <f t="array" ref="H63">_FV(B63,"P/E",TRUE)</f>
@@ -17362,7 +16894,7 @@
       </c>
       <c r="P63" s="7" cm="1">
         <f t="array" aca="1" ref="P63" ca="1">_FV(B63,"Volume")</f>
-        <v>43471924</v>
+        <v>234355</v>
       </c>
       <c r="Q63" s="7" cm="1">
         <f t="array" aca="1" ref="Q63" ca="1">_FV(B63,"Volume average",TRUE)</f>
@@ -17398,7 +16930,7 @@
       </c>
       <c r="C64" s="2" cm="1">
         <f t="array" aca="1" ref="C64" ca="1">_FV(B64,"Last trade time",TRUE)</f>
-        <v>46174.905266481248</v>
+        <v>46174.994492013284</v>
       </c>
       <c r="D64" t="str" cm="1">
         <f t="array" aca="1" ref="D64" ca="1">_FV(B64,"Currency")</f>
@@ -17422,7 +16954,7 @@
       </c>
       <c r="I64" s="6" cm="1">
         <f t="array" aca="1" ref="I64" ca="1">_FV(B64,"Beta")</f>
-        <v>2.0520999999999998</v>
+        <v>2.0400999999999998</v>
       </c>
       <c r="J64" s="3" cm="1">
         <f t="array" aca="1" ref="J64" ca="1">_FV(B64,"52 week high",TRUE)</f>
@@ -17450,7 +16982,7 @@
       </c>
       <c r="P64" s="7" cm="1">
         <f t="array" aca="1" ref="P64" ca="1">_FV(B64,"Volume")</f>
-        <v>6989695</v>
+        <v>12261</v>
       </c>
       <c r="Q64" s="7" cm="1">
         <f t="array" aca="1" ref="Q64" ca="1">_FV(B64,"Volume average",TRUE)</f>
@@ -17486,7 +17018,7 @@
       </c>
       <c r="C65" s="2" cm="1">
         <f t="array" aca="1" ref="C65" ca="1">_FV(B65,"Last trade time",TRUE)</f>
-        <v>46174.904567418751</v>
+        <v>46175.000001897657</v>
       </c>
       <c r="D65" t="str" cm="1">
         <f t="array" aca="1" ref="D65" ca="1">_FV(B65,"Currency")</f>
@@ -17494,15 +17026,15 @@
       </c>
       <c r="E65" s="3" cm="1">
         <f t="array" aca="1" ref="E65" ca="1">_FV(B65,"Price")</f>
-        <v>288.95</v>
+        <v>288.98</v>
       </c>
       <c r="F65" s="4" cm="1">
         <f t="array" aca="1" ref="F65" ca="1">_FV(B65,"Change (%)",TRUE)</f>
-        <v>-5.0960000000000007E-3</v>
+        <v>-4.993E-3</v>
       </c>
       <c r="G65" s="5" cm="1">
         <f t="array" aca="1" ref="G65" ca="1">_FV(B65,"Change")</f>
-        <v>-1.48</v>
+        <v>-1.45</v>
       </c>
       <c r="H65" s="6" t="e" vm="18">
         <f t="array" ref="H65">_FV(B65,"P/E",TRUE)</f>
@@ -17538,7 +17070,7 @@
       </c>
       <c r="P65" s="7" cm="1">
         <f t="array" aca="1" ref="P65" ca="1">_FV(B65,"Volume")</f>
-        <v>23764702</v>
+        <v>176165</v>
       </c>
       <c r="Q65" s="7" cm="1">
         <f t="array" aca="1" ref="Q65" ca="1">_FV(B65,"Volume average",TRUE)</f>
@@ -17558,7 +17090,7 @@
       </c>
       <c r="U65" s="7" cm="1">
         <f t="array" aca="1" ref="U65" ca="1">_FV(B65,"Market cap",TRUE)</f>
-        <v>76877810344.919998</v>
+        <v>80933362748.720001</v>
       </c>
       <c r="V65" s="7" t="e" cm="1" vm="57">
         <f t="array" ref="V65">_FV(B65,"Shares outstanding",TRUE)</f>
@@ -17574,7 +17106,7 @@
       </c>
       <c r="C66" s="2" cm="1">
         <f t="array" aca="1" ref="C66" ca="1">_FV(B66,"Last trade time",TRUE)</f>
-        <v>46174.905740601564</v>
+        <v>46174.999666967189</v>
       </c>
       <c r="D66" t="str" cm="1">
         <f t="array" aca="1" ref="D66" ca="1">_FV(B66,"Currency")</f>
@@ -17594,11 +17126,11 @@
       </c>
       <c r="H66" s="6" cm="1">
         <f t="array" aca="1" ref="H66" ca="1">_FV(B66,"P/E",TRUE)</f>
-        <v>86.346800000000002</v>
+        <v>86.347999999999999</v>
       </c>
       <c r="I66" s="6" cm="1">
         <f t="array" aca="1" ref="I66" ca="1">_FV(B66,"Beta")</f>
-        <v>1.968</v>
+        <v>1.9777</v>
       </c>
       <c r="J66" s="3" cm="1">
         <f t="array" aca="1" ref="J66" ca="1">_FV(B66,"52 week high",TRUE)</f>
@@ -17626,7 +17158,7 @@
       </c>
       <c r="P66" s="7" cm="1">
         <f t="array" aca="1" ref="P66" ca="1">_FV(B66,"Volume")</f>
-        <v>9122072</v>
+        <v>104376</v>
       </c>
       <c r="Q66" s="7" cm="1">
         <f t="array" aca="1" ref="Q66" ca="1">_FV(B66,"Volume average",TRUE)</f>
@@ -17662,7 +17194,7 @@
       </c>
       <c r="C67" s="2">
         <f t="array" aca="1" ref="C67" ca="1">_FV(B67,"Last trade time",TRUE)</f>
-        <v>46174.905136770314</v>
+        <v>46174.992959814066</v>
       </c>
       <c r="D67" t="str">
         <f t="array" aca="1" ref="D67" ca="1">_FV(B67,"Currency")</f>
@@ -17682,11 +17214,11 @@
       </c>
       <c r="H67" s="6">
         <f t="array" aca="1" ref="H67" ca="1">_FV(B67,"P/E",TRUE)</f>
-        <v>16.4602</v>
+        <v>16.460100000000001</v>
       </c>
       <c r="I67" s="6">
         <f t="array" aca="1" ref="I67" ca="1">_FV(B67,"Beta")</f>
-        <v>3.3237999999999999</v>
+        <v>3.3254000000000001</v>
       </c>
       <c r="J67" s="3">
         <f t="array" aca="1" ref="J67" ca="1">_FV(B67,"52 week high",TRUE)</f>
@@ -17714,7 +17246,7 @@
       </c>
       <c r="P67" s="7">
         <f t="array" aca="1" ref="P67" ca="1">_FV(B67,"Volume")</f>
-        <v>748851</v>
+        <v>5275</v>
       </c>
       <c r="Q67" s="7">
         <f t="array" aca="1" ref="Q67" ca="1">_FV(B67,"Volume average",TRUE)</f>
@@ -17750,7 +17282,7 @@
       </c>
       <c r="C68" s="2">
         <f t="array" aca="1" ref="C68" ca="1">_FV(B68,"Last trade time",TRUE)</f>
-        <v>46174.904755890624</v>
+        <v>46174.999420508597</v>
       </c>
       <c r="D68" t="str">
         <f t="array" aca="1" ref="D68" ca="1">_FV(B68,"Currency")</f>
@@ -17774,7 +17306,7 @@
       </c>
       <c r="I68" s="6">
         <f t="array" aca="1" ref="I68" ca="1">_FV(B68,"Beta")</f>
-        <v>1.3325</v>
+        <v>1.3373999999999999</v>
       </c>
       <c r="J68" s="3">
         <f t="array" aca="1" ref="J68" ca="1">_FV(B68,"52 week high",TRUE)</f>
@@ -17802,7 +17334,7 @@
       </c>
       <c r="P68" s="7">
         <f t="array" aca="1" ref="P68" ca="1">_FV(B68,"Volume")</f>
-        <v>3211412</v>
+        <v>63519</v>
       </c>
       <c r="Q68" s="7">
         <f t="array" aca="1" ref="Q68" ca="1">_FV(B68,"Volume average",TRUE)</f>
@@ -17838,7 +17370,7 @@
       </c>
       <c r="C69" s="2">
         <f t="array" aca="1" ref="C69" ca="1">_FV(B69,"Last trade time",TRUE)</f>
-        <v>46174.905241492968</v>
+        <v>46174.99991173594</v>
       </c>
       <c r="D69" t="str">
         <f t="array" aca="1" ref="D69" ca="1">_FV(B69,"Currency")</f>
@@ -17846,23 +17378,23 @@
       </c>
       <c r="E69" s="3">
         <f t="array" aca="1" ref="E69" ca="1">_FV(B69,"Price")</f>
-        <v>78.61</v>
+        <v>78.64</v>
       </c>
       <c r="F69" s="4">
         <f t="array" aca="1" ref="F69" ca="1">_FV(B69,"Change (%)",TRUE)</f>
-        <v>-5.0629999999999998E-3</v>
+        <v>-4.6829999999999997E-3</v>
       </c>
       <c r="G69" s="5">
         <f t="array" aca="1" ref="G69" ca="1">_FV(B69,"Change")</f>
-        <v>-0.4</v>
+        <v>-0.37</v>
       </c>
       <c r="H69" s="6">
         <f t="array" aca="1" ref="H69" ca="1">_FV(B69,"P/E",TRUE)</f>
-        <v>24.747399999999999</v>
+        <v>24.757000000000001</v>
       </c>
       <c r="I69" s="6">
         <f t="array" aca="1" ref="I69" ca="1">_FV(B69,"Beta")</f>
-        <v>0.35110000000000002</v>
+        <v>0.3548</v>
       </c>
       <c r="J69" s="3">
         <f t="array" aca="1" ref="J69" ca="1">_FV(B69,"52 week high",TRUE)</f>
@@ -17890,7 +17422,7 @@
       </c>
       <c r="P69" s="7">
         <f t="array" aca="1" ref="P69" ca="1">_FV(B69,"Volume")</f>
-        <v>12767660</v>
+        <v>25888</v>
       </c>
       <c r="Q69" s="7">
         <f t="array" aca="1" ref="Q69" ca="1">_FV(B69,"Volume average",TRUE)</f>
@@ -17910,7 +17442,7 @@
       </c>
       <c r="U69" s="7">
         <f t="array" aca="1" ref="U69" ca="1">_FV(B69,"Market cap",TRUE)</f>
-        <v>338218110020</v>
+        <v>338347184480</v>
       </c>
       <c r="V69" s="7">
         <f t="array" aca="1" ref="V69" ca="1">_FV(B69,"Shares outstanding",TRUE)</f>
@@ -17926,7 +17458,7 @@
       </c>
       <c r="C70" s="2">
         <f t="array" aca="1" ref="C70" ca="1">_FV(B70,"Last trade time",TRUE)</f>
-        <v>46174.905693911722</v>
+        <v>46174.999937106251</v>
       </c>
       <c r="D70" t="str">
         <f t="array" aca="1" ref="D70" ca="1">_FV(B70,"Currency")</f>
@@ -17950,7 +17482,7 @@
       </c>
       <c r="I70" s="6">
         <f t="array" aca="1" ref="I70" ca="1">_FV(B70,"Beta")</f>
-        <v>2.5004</v>
+        <v>2.4937</v>
       </c>
       <c r="J70" s="3">
         <f t="array" aca="1" ref="J70" ca="1">_FV(B70,"52 week high",TRUE)</f>
@@ -17978,7 +17510,7 @@
       </c>
       <c r="P70" s="7">
         <f t="array" aca="1" ref="P70" ca="1">_FV(B70,"Volume")</f>
-        <v>33195941</v>
+        <v>300001</v>
       </c>
       <c r="Q70" s="7">
         <f t="array" aca="1" ref="Q70" ca="1">_FV(B70,"Volume average",TRUE)</f>
@@ -18014,7 +17546,7 @@
       </c>
       <c r="C71" s="2">
         <f t="array" aca="1" ref="C71" ca="1">_FV(B71,"Last trade time",TRUE)</f>
-        <v>46174.904788853906</v>
+        <v>46174.999708228905</v>
       </c>
       <c r="D71" t="str">
         <f t="array" aca="1" ref="D71" ca="1">_FV(B71,"Currency")</f>
@@ -18038,7 +17570,7 @@
       </c>
       <c r="I71" s="6">
         <f t="array" aca="1" ref="I71" ca="1">_FV(B71,"Beta")</f>
-        <v>3.1882000000000001</v>
+        <v>3.1863999999999999</v>
       </c>
       <c r="J71" s="3">
         <f t="array" aca="1" ref="J71" ca="1">_FV(B71,"52 week high",TRUE)</f>
@@ -18066,7 +17598,7 @@
       </c>
       <c r="P71" s="7">
         <f t="array" aca="1" ref="P71" ca="1">_FV(B71,"Volume")</f>
-        <v>1524668</v>
+        <v>57560</v>
       </c>
       <c r="Q71" s="7">
         <f t="array" aca="1" ref="Q71" ca="1">_FV(B71,"Volume average",TRUE)</f>
@@ -18102,7 +17634,7 @@
       </c>
       <c r="C72" s="2" cm="1">
         <f t="array" aca="1" ref="C72" ca="1">_FV(B72,"Last trade time",TRUE)</f>
-        <v>46174.905606620312</v>
+        <v>46174.999666967189</v>
       </c>
       <c r="D72" t="str" cm="1">
         <f t="array" aca="1" ref="D72" ca="1">_FV(B72,"Currency")</f>
@@ -18122,11 +17654,11 @@
       </c>
       <c r="H72" s="6" cm="1">
         <f t="array" aca="1" ref="H72" ca="1">_FV(B72,"P/E",TRUE)</f>
-        <v>68.381100000000004</v>
+        <v>68.381699999999995</v>
       </c>
       <c r="I72" s="6" cm="1">
         <f t="array" aca="1" ref="I72" ca="1">_FV(B72,"Beta")</f>
-        <v>1.7908999999999999</v>
+        <v>1.7958000000000001</v>
       </c>
       <c r="J72" s="3" cm="1">
         <f t="array" aca="1" ref="J72" ca="1">_FV(B72,"52 week high",TRUE)</f>
@@ -18154,7 +17686,7 @@
       </c>
       <c r="P72" s="7" cm="1">
         <f t="array" aca="1" ref="P72" ca="1">_FV(B72,"Volume")</f>
-        <v>2520772</v>
+        <v>28788</v>
       </c>
       <c r="Q72" s="7" cm="1">
         <f t="array" aca="1" ref="Q72" ca="1">_FV(B72,"Volume average",TRUE)</f>
@@ -18190,7 +17722,7 @@
       </c>
       <c r="C73" s="2">
         <f t="array" aca="1" ref="C73" ca="1">_FV(B73,"Last trade time",TRUE)</f>
-        <v>46174.905720196097</v>
+        <v>46174.999991191406</v>
       </c>
       <c r="D73" t="str">
         <f t="array" aca="1" ref="D73" ca="1">_FV(B73,"Currency")</f>
@@ -18210,11 +17742,11 @@
       </c>
       <c r="H73" s="6">
         <f t="array" aca="1" ref="H73" ca="1">_FV(B73,"P/E",TRUE)</f>
-        <v>130.98589999999999</v>
+        <v>125.4752</v>
       </c>
       <c r="I73" s="6">
         <f t="array" aca="1" ref="I73" ca="1">_FV(B73,"Beta")</f>
-        <v>3.2275</v>
+        <v>3.2351999999999999</v>
       </c>
       <c r="J73" s="3">
         <f t="array" aca="1" ref="J73" ca="1">_FV(B73,"52 week high",TRUE)</f>
@@ -18242,7 +17774,7 @@
       </c>
       <c r="P73" s="7">
         <f t="array" aca="1" ref="P73" ca="1">_FV(B73,"Volume")</f>
-        <v>12646832</v>
+        <v>738221</v>
       </c>
       <c r="Q73" s="7">
         <f t="array" aca="1" ref="Q73" ca="1">_FV(B73,"Volume average",TRUE)</f>
@@ -18278,7 +17810,7 @@
       </c>
       <c r="C74" s="2">
         <f t="array" aca="1" ref="C74" ca="1">_FV(B74,"Last trade time",TRUE)</f>
-        <v>46174.905754640626</v>
+        <v>46174.999999941407</v>
       </c>
       <c r="D74" t="str">
         <f t="array" aca="1" ref="D74" ca="1">_FV(B74,"Currency")</f>
@@ -18298,11 +17830,11 @@
       </c>
       <c r="H74" s="6">
         <f t="array" aca="1" ref="H74" ca="1">_FV(B74,"P/E",TRUE)</f>
-        <v>28.454499999999999</v>
+        <v>28.4544</v>
       </c>
       <c r="I74" s="6">
         <f t="array" aca="1" ref="I74" ca="1">_FV(B74,"Beta")</f>
-        <v>1.2369000000000001</v>
+        <v>1.2385999999999999</v>
       </c>
       <c r="J74" s="3">
         <f t="array" aca="1" ref="J74" ca="1">_FV(B74,"52 week high",TRUE)</f>
@@ -18330,7 +17862,7 @@
       </c>
       <c r="P74" s="7">
         <f t="array" aca="1" ref="P74" ca="1">_FV(B74,"Volume")</f>
-        <v>18729341</v>
+        <v>638897</v>
       </c>
       <c r="Q74" s="7">
         <f t="array" aca="1" ref="Q74" ca="1">_FV(B74,"Volume average",TRUE)</f>
@@ -18366,7 +17898,7 @@
       </c>
       <c r="C75" s="2">
         <f t="array" aca="1" ref="C75" ca="1">_FV(B75,"Last trade time",TRUE)</f>
-        <v>46174.904835335154</v>
+        <v>46174.999644767966</v>
       </c>
       <c r="D75" t="str">
         <f t="array" aca="1" ref="D75" ca="1">_FV(B75,"Currency")</f>
@@ -18386,11 +17918,11 @@
       </c>
       <c r="H75" s="6">
         <f t="array" aca="1" ref="H75" ca="1">_FV(B75,"P/E",TRUE)</f>
-        <v>11.8476</v>
+        <v>11.671799999999999</v>
       </c>
       <c r="I75" s="6">
         <f t="array" aca="1" ref="I75" ca="1">_FV(B75,"Beta")</f>
-        <v>1.3632</v>
+        <v>1.3715999999999999</v>
       </c>
       <c r="J75" s="3">
         <f t="array" aca="1" ref="J75" ca="1">_FV(B75,"52 week high",TRUE)</f>
@@ -18418,7 +17950,7 @@
       </c>
       <c r="P75" s="7">
         <f t="array" aca="1" ref="P75" ca="1">_FV(B75,"Volume")</f>
-        <v>3648078</v>
+        <v>30760</v>
       </c>
       <c r="Q75" s="7">
         <f t="array" aca="1" ref="Q75" ca="1">_FV(B75,"Volume average",TRUE)</f>
@@ -18478,7 +18010,7 @@
       </c>
       <c r="I76" s="6">
         <f t="array" aca="1" ref="I76" ca="1">_FV(B76,"Beta")</f>
-        <v>0.84619999999999995</v>
+        <v>0.83940000000000003</v>
       </c>
       <c r="J76" s="3">
         <f t="array" aca="1" ref="J76" ca="1">_FV(B76,"52 week high",TRUE)</f>
@@ -18542,7 +18074,7 @@
       </c>
       <c r="C77" s="2">
         <f t="array" aca="1" ref="C77" ca="1">_FV(B77,"Last trade time",TRUE)</f>
-        <v>46174.905331064059</v>
+        <v>46174.999923171097</v>
       </c>
       <c r="D77" t="str">
         <f t="array" aca="1" ref="D77" ca="1">_FV(B77,"Currency")</f>
@@ -18562,11 +18094,11 @@
       </c>
       <c r="H77" s="6">
         <f t="array" aca="1" ref="H77" ca="1">_FV(B77,"P/E",TRUE)</f>
-        <v>37.201500000000003</v>
+        <v>37.2014</v>
       </c>
       <c r="I77" s="6">
         <f t="array" aca="1" ref="I77" ca="1">_FV(B77,"Beta")</f>
-        <v>1.0921000000000001</v>
+        <v>1.0873999999999999</v>
       </c>
       <c r="J77" s="3">
         <f t="array" aca="1" ref="J77" ca="1">_FV(B77,"52 week high",TRUE)</f>
@@ -18594,7 +18126,7 @@
       </c>
       <c r="P77" s="7">
         <f t="array" aca="1" ref="P77" ca="1">_FV(B77,"Volume")</f>
-        <v>48773256</v>
+        <v>245050</v>
       </c>
       <c r="Q77" s="7">
         <f t="array" aca="1" ref="Q77" ca="1">_FV(B77,"Volume average",TRUE)</f>
@@ -18630,7 +18162,7 @@
       </c>
       <c r="C78" s="2">
         <f t="array" aca="1" ref="C78" ca="1">_FV(B78,"Last trade time",TRUE)</f>
-        <v>46174.905757245309</v>
+        <v>46174.999978425782</v>
       </c>
       <c r="D78" t="str">
         <f t="array" aca="1" ref="D78" ca="1">_FV(B78,"Currency")</f>
@@ -18654,7 +18186,7 @@
       </c>
       <c r="I78" s="6">
         <f t="array" aca="1" ref="I78" ca="1">_FV(B78,"Beta")</f>
-        <v>2.3483000000000001</v>
+        <v>2.3519000000000001</v>
       </c>
       <c r="J78" s="3">
         <f t="array" aca="1" ref="J78" ca="1">_FV(B78,"52 week high",TRUE)</f>
@@ -18682,7 +18214,7 @@
       </c>
       <c r="P78" s="7">
         <f t="array" aca="1" ref="P78" ca="1">_FV(B78,"Volume")</f>
-        <v>42426915</v>
+        <v>403352</v>
       </c>
       <c r="Q78" s="7">
         <f t="array" aca="1" ref="Q78" ca="1">_FV(B78,"Volume average",TRUE)</f>
@@ -18718,7 +18250,7 @@
       </c>
       <c r="C79" s="2">
         <f t="array" aca="1" ref="C79" ca="1">_FV(B79,"Last trade time",TRUE)</f>
-        <v>46174.905742488278</v>
+        <v>46174.999785728905</v>
       </c>
       <c r="D79" t="str">
         <f t="array" aca="1" ref="D79" ca="1">_FV(B79,"Currency")</f>
@@ -18726,23 +18258,23 @@
       </c>
       <c r="E79" s="3">
         <f t="array" aca="1" ref="E79" ca="1">_FV(B79,"Price")</f>
-        <v>69.23</v>
+        <v>69.28</v>
       </c>
       <c r="F79" s="4">
         <f t="array" aca="1" ref="F79" ca="1">_FV(B79,"Change (%)",TRUE)</f>
-        <v>-3.9405999999999997E-2</v>
+        <v>-3.8711999999999996E-2</v>
       </c>
       <c r="G79" s="5">
         <f t="array" aca="1" ref="G79" ca="1">_FV(B79,"Change")</f>
-        <v>-2.84</v>
+        <v>-2.79</v>
       </c>
       <c r="H79" s="6">
         <f t="array" aca="1" ref="H79" ca="1">_FV(B79,"P/E",TRUE)</f>
-        <v>1181.3993</v>
+        <v>1182.05</v>
       </c>
       <c r="I79" s="6">
         <f t="array" aca="1" ref="I79" ca="1">_FV(B79,"Beta")</f>
-        <v>3.1793999999999998</v>
+        <v>3.1894</v>
       </c>
       <c r="J79" s="3">
         <f t="array" aca="1" ref="J79" ca="1">_FV(B79,"52 week high",TRUE)</f>
@@ -18770,7 +18302,7 @@
       </c>
       <c r="P79" s="7">
         <f t="array" aca="1" ref="P79" ca="1">_FV(B79,"Volume")</f>
-        <v>28162128</v>
+        <v>475649</v>
       </c>
       <c r="Q79" s="7">
         <f t="array" aca="1" ref="Q79" ca="1">_FV(B79,"Volume average",TRUE)</f>
@@ -18790,7 +18322,7 @@
       </c>
       <c r="U79" s="7">
         <f t="array" aca="1" ref="U79" ca="1">_FV(B79,"Market cap",TRUE)</f>
-        <v>25841482100</v>
+        <v>25860145600</v>
       </c>
       <c r="V79" s="7">
         <f t="array" aca="1" ref="V79" ca="1">_FV(B79,"Shares outstanding",TRUE)</f>
@@ -18806,7 +18338,7 @@
       </c>
       <c r="C80" s="2">
         <f t="array" aca="1" ref="C80" ca="1">_FV(B80,"Last trade time",TRUE)</f>
-        <v>46174.90574208281</v>
+        <v>46174.999957221873</v>
       </c>
       <c r="D80" t="str">
         <f t="array" aca="1" ref="D80" ca="1">_FV(B80,"Currency")</f>
@@ -18830,7 +18362,7 @@
       </c>
       <c r="I80" s="6">
         <f t="array" aca="1" ref="I80" ca="1">_FV(B80,"Beta")</f>
-        <v>1.4477</v>
+        <v>1.4463999999999999</v>
       </c>
       <c r="J80" s="3">
         <f t="array" aca="1" ref="J80" ca="1">_FV(B80,"52 week high",TRUE)</f>
@@ -18858,7 +18390,7 @@
       </c>
       <c r="P80" s="7">
         <f t="array" aca="1" ref="P80" ca="1">_FV(B80,"Volume")</f>
-        <v>53312057</v>
+        <v>484589</v>
       </c>
       <c r="Q80" s="7">
         <f t="array" aca="1" ref="Q80" ca="1">_FV(B80,"Volume average",TRUE)</f>
@@ -18894,7 +18426,7 @@
       </c>
       <c r="C81" s="2">
         <f t="array" aca="1" ref="C81" ca="1">_FV(B81,"Last trade time",TRUE)</f>
-        <v>46174.905778286717</v>
+        <v>46174.999990115626</v>
       </c>
       <c r="D81" t="str">
         <f t="array" aca="1" ref="D81" ca="1">_FV(B81,"Currency")</f>
@@ -18914,11 +18446,11 @@
       </c>
       <c r="H81" s="6">
         <f t="array" aca="1" ref="H81" ca="1">_FV(B81,"P/E",TRUE)</f>
-        <v>380.11149999999998</v>
+        <v>380.12540000000001</v>
       </c>
       <c r="I81" s="6">
         <f t="array" aca="1" ref="I81" ca="1">_FV(B81,"Beta")</f>
-        <v>1.802</v>
+        <v>1.8019000000000001</v>
       </c>
       <c r="J81" s="3">
         <f t="array" aca="1" ref="J81" ca="1">_FV(B81,"52 week high",TRUE)</f>
@@ -18946,7 +18478,7 @@
       </c>
       <c r="P81" s="7">
         <f t="array" aca="1" ref="P81" ca="1">_FV(B81,"Volume")</f>
-        <v>44497485</v>
+        <v>768704</v>
       </c>
       <c r="Q81" s="7">
         <f t="array" aca="1" ref="Q81" ca="1">_FV(B81,"Volume average",TRUE)</f>
@@ -18982,7 +18514,7 @@
       </c>
       <c r="C82" s="2">
         <f t="array" aca="1" ref="C82" ca="1">_FV(B82,"Last trade time",TRUE)</f>
-        <v>46174.905725103905</v>
+        <v>46174.999996666404</v>
       </c>
       <c r="D82" t="str">
         <f t="array" aca="1" ref="D82" ca="1">_FV(B82,"Currency")</f>
@@ -19006,7 +18538,7 @@
       </c>
       <c r="I82" s="6">
         <f t="array" aca="1" ref="I82" ca="1">_FV(B82,"Beta")</f>
-        <v>1.2309000000000001</v>
+        <v>1.2323</v>
       </c>
       <c r="J82" s="3">
         <f t="array" aca="1" ref="J82" ca="1">_FV(B82,"52 week high",TRUE)</f>
@@ -19034,7 +18566,7 @@
       </c>
       <c r="P82" s="7">
         <f t="array" aca="1" ref="P82" ca="1">_FV(B82,"Volume")</f>
-        <v>28917906</v>
+        <v>334131</v>
       </c>
       <c r="Q82" s="7">
         <f t="array" aca="1" ref="Q82" ca="1">_FV(B82,"Volume average",TRUE)</f>
@@ -19070,7 +18602,7 @@
       </c>
       <c r="C83" s="2">
         <f t="array" aca="1" ref="C83" ca="1">_FV(B83,"Last trade time",TRUE)</f>
-        <v>46174.905610010937</v>
+        <v>46174.99999954844</v>
       </c>
       <c r="D83" t="str">
         <f t="array" aca="1" ref="D83" ca="1">_FV(B83,"Currency")</f>
@@ -19094,7 +18626,7 @@
       </c>
       <c r="I83" s="6">
         <f t="array" aca="1" ref="I83" ca="1">_FV(B83,"Beta")</f>
-        <v>3.4996</v>
+        <v>3.4756</v>
       </c>
       <c r="J83" s="3">
         <f t="array" aca="1" ref="J83" ca="1">_FV(B83,"52 week high",TRUE)</f>
@@ -19122,7 +18654,7 @@
       </c>
       <c r="P83" s="7">
         <f t="array" aca="1" ref="P83" ca="1">_FV(B83,"Volume")</f>
-        <v>17679798</v>
+        <v>509324</v>
       </c>
       <c r="Q83" s="7">
         <f t="array" aca="1" ref="Q83" ca="1">_FV(B83,"Volume average",TRUE)</f>
@@ -19158,7 +18690,7 @@
       </c>
       <c r="C84" s="2">
         <f t="array" aca="1" ref="C84" ca="1">_FV(B84,"Last trade time",TRUE)</f>
-        <v>46174.905762303126</v>
+        <v>46174.999999964843</v>
       </c>
       <c r="D84" t="str">
         <f t="array" aca="1" ref="D84" ca="1">_FV(B84,"Currency")</f>
@@ -19182,7 +18714,7 @@
       </c>
       <c r="I84" s="6">
         <f t="array" aca="1" ref="I84" ca="1">_FV(B84,"Beta")</f>
-        <v>2.2214999999999998</v>
+        <v>2.2315</v>
       </c>
       <c r="J84" s="3">
         <f t="array" aca="1" ref="J84" ca="1">_FV(B84,"52 week high",TRUE)</f>
@@ -19210,7 +18742,7 @@
       </c>
       <c r="P84" s="7">
         <f t="array" aca="1" ref="P84" ca="1">_FV(B84,"Volume")</f>
-        <v>134424917</v>
+        <v>4578516</v>
       </c>
       <c r="Q84" s="7">
         <f t="array" aca="1" ref="Q84" ca="1">_FV(B84,"Volume average",TRUE)</f>
@@ -19246,7 +18778,7 @@
       </c>
       <c r="C85" s="2">
         <f t="array" aca="1" ref="C85" ca="1">_FV(B85,"Last trade time",TRUE)</f>
-        <v>46174.902074779689</v>
+        <v>46174.999487765628</v>
       </c>
       <c r="D85" t="str">
         <f t="array" aca="1" ref="D85" ca="1">_FV(B85,"Currency")</f>
@@ -19266,11 +18798,11 @@
       </c>
       <c r="H85" s="6">
         <f t="array" aca="1" ref="H85" ca="1">_FV(B85,"P/E",TRUE)</f>
-        <v>29.823799999999999</v>
+        <v>29.8233</v>
       </c>
       <c r="I85" s="6">
         <f t="array" aca="1" ref="I85" ca="1">_FV(B85,"Beta")</f>
-        <v>1.4936</v>
+        <v>1.4829000000000001</v>
       </c>
       <c r="J85" s="3">
         <f t="array" aca="1" ref="J85" ca="1">_FV(B85,"52 week high",TRUE)</f>
@@ -19298,7 +18830,7 @@
       </c>
       <c r="P85" s="7">
         <f t="array" aca="1" ref="P85" ca="1">_FV(B85,"Volume")</f>
-        <v>4866425</v>
+        <v>12439</v>
       </c>
       <c r="Q85" s="7">
         <f t="array" aca="1" ref="Q85" ca="1">_FV(B85,"Volume average",TRUE)</f>
@@ -19334,7 +18866,7 @@
       </c>
       <c r="C86" s="2">
         <f t="array" aca="1" ref="C86" ca="1">_FV(B86,"Last trade time",TRUE)</f>
-        <v>46174.905565231253</v>
+        <v>46174.999917719528</v>
       </c>
       <c r="D86" t="str">
         <f t="array" aca="1" ref="D86" ca="1">_FV(B86,"Currency")</f>
@@ -19354,7 +18886,7 @@
       </c>
       <c r="H86" s="6">
         <f t="array" aca="1" ref="H86" ca="1">_FV(B86,"P/E",TRUE)</f>
-        <v>215.78129999999999</v>
+        <v>215.7799</v>
       </c>
       <c r="I86" s="6">
         <f t="array" aca="1" ref="I86" ca="1">_FV(B86,"Beta")</f>
@@ -19386,7 +18918,7 @@
       </c>
       <c r="P86" s="7">
         <f t="array" aca="1" ref="P86" ca="1">_FV(B86,"Volume")</f>
-        <v>5536599</v>
+        <v>81620</v>
       </c>
       <c r="Q86" s="7">
         <f t="array" aca="1" ref="Q86" ca="1">_FV(B86,"Volume average",TRUE)</f>
@@ -19422,7 +18954,7 @@
       </c>
       <c r="C87" s="2" cm="1">
         <f t="array" aca="1" ref="C87" ca="1">_FV(B87,"Last trade time",TRUE)</f>
-        <v>46174.905717696092</v>
+        <v>46174.999793796094</v>
       </c>
       <c r="D87" t="str" cm="1">
         <f t="array" aca="1" ref="D87" ca="1">_FV(B87,"Currency")</f>
@@ -19442,11 +18974,11 @@
       </c>
       <c r="H87" s="6" cm="1">
         <f t="array" aca="1" ref="H87" ca="1">_FV(B87,"P/E",TRUE)</f>
-        <v>23.083100000000002</v>
+        <v>23.083200000000001</v>
       </c>
       <c r="I87" s="6" cm="1">
         <f t="array" aca="1" ref="I87" ca="1">_FV(B87,"Beta")</f>
-        <v>1.091</v>
+        <v>1.0992999999999999</v>
       </c>
       <c r="J87" s="3" cm="1">
         <f t="array" aca="1" ref="J87" ca="1">_FV(B87,"52 week high",TRUE)</f>
@@ -19474,7 +19006,7 @@
       </c>
       <c r="P87" s="7" cm="1">
         <f t="array" aca="1" ref="P87" ca="1">_FV(B87,"Volume")</f>
-        <v>11448720</v>
+        <v>41216</v>
       </c>
       <c r="Q87" s="7" cm="1">
         <f t="array" aca="1" ref="Q87" ca="1">_FV(B87,"Volume average",TRUE)</f>
@@ -19510,7 +19042,7 @@
       </c>
       <c r="C88" s="2" cm="1">
         <f t="array" aca="1" ref="C88" ca="1">_FV(B88,"Last trade time",TRUE)</f>
-        <v>46174.905740682814</v>
+        <v>46174.999967696094</v>
       </c>
       <c r="D88" t="str" cm="1">
         <f t="array" aca="1" ref="D88" ca="1">_FV(B88,"Currency")</f>
@@ -19530,11 +19062,11 @@
       </c>
       <c r="H88" s="6" cm="1">
         <f t="array" aca="1" ref="H88" ca="1">_FV(B88,"P/E",TRUE)</f>
-        <v>24.908100000000001</v>
+        <v>24.908000000000001</v>
       </c>
       <c r="I88" s="6" cm="1">
         <f t="array" aca="1" ref="I88" ca="1">_FV(B88,"Beta")</f>
-        <v>1.5985</v>
+        <v>1.6017999999999999</v>
       </c>
       <c r="J88" s="3" cm="1">
         <f t="array" aca="1" ref="J88" ca="1">_FV(B88,"52 week high",TRUE)</f>
@@ -19562,7 +19094,7 @@
       </c>
       <c r="P88" s="7" cm="1">
         <f t="array" aca="1" ref="P88" ca="1">_FV(B88,"Volume")</f>
-        <v>21105476</v>
+        <v>403719</v>
       </c>
       <c r="Q88" s="7" cm="1">
         <f t="array" aca="1" ref="Q88" ca="1">_FV(B88,"Volume average",TRUE)</f>
@@ -19813,19 +19345,19 @@
       </c>
       <c r="J2" s="22">
         <f ca="1">Config!$C$1</f>
-        <v>0.74280000000000002</v>
+        <v>0.74229999999999996</v>
       </c>
       <c r="K2" s="20">
         <f t="shared" ref="K2:K11" ca="1" si="3">F2*I2*J2</f>
-        <v>2047.743612</v>
+        <v>2046.3652169999998</v>
       </c>
       <c r="L2" s="20">
         <f t="shared" ref="L2:L11" ca="1" si="4">K2-H2</f>
-        <v>1742.587362</v>
+        <v>1741.2089669999998</v>
       </c>
       <c r="M2" s="23">
         <f t="shared" ref="M2:M11" ca="1" si="5">IF(H2=0,"",L2/H2)</f>
-        <v>5.7104757382488476</v>
+        <v>5.7059587244239625</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -19861,19 +19393,19 @@
       </c>
       <c r="J3" s="22">
         <f ca="1">Config!$C$1</f>
-        <v>0.74280000000000002</v>
+        <v>0.74229999999999996</v>
       </c>
       <c r="K3" s="20">
         <f t="shared" ca="1" si="3"/>
-        <v>2676.174696</v>
+        <v>2674.373286</v>
       </c>
       <c r="L3" s="20">
         <f t="shared" ca="1" si="4"/>
-        <v>-491.68530600000031</v>
+        <v>-493.48671600000034</v>
       </c>
       <c r="M3" s="23">
         <f t="shared" ca="1" si="5"/>
-        <v>-0.15521055403003262</v>
+        <v>-0.15577920605343729</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -19909,19 +19441,19 @@
       </c>
       <c r="J4" s="22">
         <f ca="1">Config!$C$1</f>
-        <v>0.74280000000000002</v>
+        <v>0.74229999999999996</v>
       </c>
       <c r="K4" s="20">
         <f t="shared" ca="1" si="3"/>
-        <v>5054.5682999999999</v>
+        <v>5051.1659249999993</v>
       </c>
       <c r="L4" s="20">
         <f t="shared" ca="1" si="4"/>
-        <v>1406.7690000000007</v>
+        <v>1403.3666250000001</v>
       </c>
       <c r="M4" s="23">
         <f t="shared" ca="1" si="5"/>
-        <v>0.38564868412579634</v>
+        <v>0.38471596422533455</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -19957,19 +19489,19 @@
       </c>
       <c r="J5" s="22">
         <f ca="1">Config!$C$1</f>
-        <v>0.74280000000000002</v>
+        <v>0.74229999999999996</v>
       </c>
       <c r="K5" s="20">
         <f t="shared" ca="1" si="3"/>
-        <v>2999.7829440000005</v>
+        <v>2997.763704</v>
       </c>
       <c r="L5" s="20">
         <f t="shared" ca="1" si="4"/>
-        <v>667.34294400000044</v>
+        <v>665.32370399999991</v>
       </c>
       <c r="M5" s="23">
         <f t="shared" ca="1" si="5"/>
-        <v>0.2861136595153575</v>
+        <v>0.28524793949683591</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -20005,19 +19537,19 @@
       </c>
       <c r="J6" s="22">
         <f ca="1">Config!$C$1</f>
-        <v>0.74280000000000002</v>
+        <v>0.74229999999999996</v>
       </c>
       <c r="K6" s="20">
         <f t="shared" ca="1" si="3"/>
-        <v>4547.0947679999999</v>
+        <v>4544.0339879999992</v>
       </c>
       <c r="L6" s="20">
         <f t="shared" ca="1" si="4"/>
-        <v>2687.5747679999999</v>
+        <v>2684.5139879999992</v>
       </c>
       <c r="M6" s="23">
         <f t="shared" ca="1" si="5"/>
-        <v>1.4453056530717605</v>
+        <v>1.4436596476510064</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -20053,19 +19585,19 @@
       </c>
       <c r="J7" s="22">
         <f ca="1">Config!$C$1</f>
-        <v>0.74280000000000002</v>
+        <v>0.74229999999999996</v>
       </c>
       <c r="K7" s="20">
         <f t="shared" ca="1" si="3"/>
-        <v>2874.2051759999999</v>
+        <v>2872.2704659999995</v>
       </c>
       <c r="L7" s="20">
         <f t="shared" ca="1" si="4"/>
-        <v>800.11517699999968</v>
+        <v>798.18046699999923</v>
       </c>
       <c r="M7" s="23">
         <f t="shared" ca="1" si="5"/>
-        <v>0.3857668555297824</v>
+        <v>0.38483405608475679</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -20101,19 +19633,19 @@
       </c>
       <c r="J8" s="22">
         <f ca="1">Config!$C$1</f>
-        <v>0.74280000000000002</v>
+        <v>0.74229999999999996</v>
       </c>
       <c r="K8" s="20">
         <f t="shared" ca="1" si="3"/>
-        <v>5560.4819520000001</v>
+        <v>5556.7390319999995</v>
       </c>
       <c r="L8" s="20">
         <f t="shared" ca="1" si="4"/>
-        <v>706.21205200000077</v>
+        <v>702.46913200000017</v>
       </c>
       <c r="M8" s="23">
         <f t="shared" ca="1" si="5"/>
-        <v>0.14548265064536292</v>
+        <v>0.14471159339533227</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -20149,19 +19681,19 @@
       </c>
       <c r="J9" s="22">
         <f ca="1">Config!$C$1</f>
-        <v>0.74280000000000002</v>
+        <v>0.74229999999999996</v>
       </c>
       <c r="K9" s="20">
         <f t="shared" ca="1" si="3"/>
-        <v>1015.021344</v>
+        <v>1014.3381039999999</v>
       </c>
       <c r="L9" s="20">
         <f t="shared" ca="1" si="4"/>
-        <v>-78.208660000000009</v>
+        <v>-78.891900000000078</v>
       </c>
       <c r="M9" s="23">
         <f t="shared" ca="1" si="5"/>
-        <v>-7.1539072028615869E-2</v>
+        <v>-7.2164045728112011E-2</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -20197,19 +19729,19 @@
       </c>
       <c r="J10" s="22">
         <f ca="1">Config!$C$1</f>
-        <v>0.74280000000000002</v>
+        <v>0.74229999999999996</v>
       </c>
       <c r="K10" s="20">
         <f t="shared" ca="1" si="3"/>
-        <v>4601.6014320000004</v>
+        <v>4598.5039619999998</v>
       </c>
       <c r="L10" s="20">
         <f t="shared" ca="1" si="4"/>
-        <v>2091.7312959999999</v>
+        <v>2088.6338259999993</v>
       </c>
       <c r="M10" s="23">
         <f t="shared" ca="1" si="5"/>
-        <v>0.83340220117269026</v>
+        <v>0.83216808552838961</v>
       </c>
     </row>
     <row r="11" spans="1:13" hidden="1">
@@ -20241,23 +19773,23 @@
       </c>
       <c r="I11" s="21">
         <f t="shared" ca="1" si="2"/>
-        <v>907.6</v>
+        <v>894.6</v>
       </c>
       <c r="J11" s="22">
         <f ca="1">Config!$C$1</f>
-        <v>0.74280000000000002</v>
+        <v>0.74229999999999996</v>
       </c>
       <c r="K11" s="20">
         <f t="shared" ca="1" si="3"/>
-        <v>33708.264000000003</v>
+        <v>33203.078999999998</v>
       </c>
       <c r="L11" s="20">
         <f t="shared" ca="1" si="4"/>
-        <v>28708.264000000003</v>
+        <v>28203.078999999998</v>
       </c>
       <c r="M11" s="23">
         <f t="shared" ca="1" si="5"/>
-        <v>5.7416528000000007</v>
+        <v>5.6406158</v>
       </c>
     </row>
   </sheetData>
@@ -20348,7 +19880,7 @@
       </c>
       <c r="C1" s="3" cm="1">
         <f t="array" aca="1" ref="C1" ca="1">_FV(B1,"Price")</f>
-        <v>0.74280000000000002</v>
+        <v>0.74229999999999996</v>
       </c>
     </row>
   </sheetData>

--- a/dashboard/trading_system.xlsx
+++ b/dashboard/trading_system.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\husainnatha\tradingsystem\dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2063A75-E978-4C9C-B807-BB0B021E352D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB4DE365-0BBE-4192-B497-17133FA8C8BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="353" yWindow="1343" windowWidth="16200" windowHeight="9307" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CONTRIBUTIONS" sheetId="11" r:id="rId1"/>
@@ -1000,7 +1000,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1949" uniqueCount="607">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1950" uniqueCount="608">
   <si>
     <t>collected_timestamp</t>
   </si>
@@ -2925,6 +2925,9 @@
   </si>
   <si>
     <t>max_deployment_percent</t>
+  </si>
+  <si>
+    <t>Column1</t>
   </si>
 </sst>
 </file>
@@ -3068,7 +3071,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -3146,11 +3149,44 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="9" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="53">
+  <dxfs count="54">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FFF0F0F0"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="13" formatCode="0%"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF0C0E12"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FFA0A0A0"/>
@@ -9511,7 +9547,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{F82495E7-9F34-4C1F-83EC-FA45D59FA2BD}" name="tblContributions" displayName="tblContributions" ref="A1:C2" totalsRowShown="0">
   <autoFilter ref="A1:C2" xr:uid="{F82495E7-9F34-4C1F-83EC-FA45D59FA2BD}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{EAE9033F-E950-4D8F-AC60-78CCDA7A0C9E}" name="DATE" dataDxfId="52"/>
+    <tableColumn id="1" xr3:uid="{EAE9033F-E950-4D8F-AC60-78CCDA7A0C9E}" name="DATE" dataDxfId="53"/>
     <tableColumn id="2" xr3:uid="{1D40F1FF-D66C-4703-9DEC-93C768793D8F}" name="AMMOUNT"/>
     <tableColumn id="3" xr3:uid="{49855D82-DE07-4257-837D-DD0BE41E988B}" name="Notes"/>
   </tableColumns>
@@ -9539,64 +9575,64 @@
   <tableColumns count="31">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="symbol"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="StockName"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="LastTradeTime" dataDxfId="51">
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="LastTradeTime" dataDxfId="52">
       <calculatedColumnFormula array="1">_FV(B2,"Last trade time",TRUE)</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="TradeCurrency">
       <calculatedColumnFormula array="1">_FV(B2,"Currency")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="StockPrice" dataDxfId="50">
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="StockPrice" dataDxfId="51">
       <calculatedColumnFormula array="1">_FV(B2,"Price")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="ChangePercent" dataDxfId="49">
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="ChangePercent" dataDxfId="50">
       <calculatedColumnFormula array="1">_FV(B2,"Change (%)",TRUE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Change" dataDxfId="48">
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Change" dataDxfId="49">
       <calculatedColumnFormula array="1">_FV(B2,"Change")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="P/E" dataDxfId="47">
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="P/E" dataDxfId="48">
       <calculatedColumnFormula array="1">_FV(B2,"P/E",TRUE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Beta" dataDxfId="46">
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Beta" dataDxfId="47">
       <calculatedColumnFormula array="1">_FV(B2,"Beta")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="52WkHigh" dataDxfId="45">
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="52WkHigh" dataDxfId="46">
       <calculatedColumnFormula array="1">_FV(B2,"52 week high",TRUE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="52WkLow" dataDxfId="44">
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="52WkLow" dataDxfId="45">
       <calculatedColumnFormula array="1">_FV(B2,"52 week low",TRUE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="DayHigh" dataDxfId="43">
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="DayHigh" dataDxfId="44">
       <calculatedColumnFormula array="1">_FV(B2,"High")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="DayLow" dataDxfId="42">
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="DayLow" dataDxfId="43">
       <calculatedColumnFormula array="1">_FV(B2,"Low")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="Open" dataDxfId="41">
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="Open" dataDxfId="42">
       <calculatedColumnFormula array="1">_FV(B2,"Open")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="PreviousClose" dataDxfId="40">
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="PreviousClose" dataDxfId="41">
       <calculatedColumnFormula array="1">_FV(B2,"Previous close",TRUE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Volume" dataDxfId="39">
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Volume" dataDxfId="40">
       <calculatedColumnFormula array="1">_FV(B2,"Volume")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="AverageVolume" dataDxfId="38">
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="AverageVolume" dataDxfId="39">
       <calculatedColumnFormula array="1">_FV(B2,"Volume average",TRUE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="YearIncorported" dataDxfId="37">
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="YearIncorported" dataDxfId="38">
       <calculatedColumnFormula array="1">_FV(B2,"Year incorporated",TRUE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="Employees" dataDxfId="36">
+    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="Employees" dataDxfId="37">
       <calculatedColumnFormula array="1">_FV(B2,"Employees")</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="Industry">
       <calculatedColumnFormula array="1">_FV(B2,"Industry")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0000-000015000000}" name="MarketCap" dataDxfId="35">
+    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0000-000015000000}" name="MarketCap" dataDxfId="36">
       <calculatedColumnFormula array="1">_FV(B2,"Market cap",TRUE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0000-000016000000}" name="SharesOutstanding" dataDxfId="34">
+    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0000-000016000000}" name="SharesOutstanding" dataDxfId="35">
       <calculatedColumnFormula array="1">_FV(B2,"Shares outstanding",TRUE)</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="23" xr3:uid="{00000000-0010-0000-0000-000017000000}" name="50SMA"/>
@@ -9614,35 +9650,38 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{D39CE96F-8D2C-4A60-A43A-B3602E27FDC2}" name="tblHoldings" displayName="tblHoldings" ref="A1:M11" totalsRowShown="0" headerRowDxfId="33" dataDxfId="32" tableBorderDxfId="31">
-  <autoFilter ref="A1:M11" xr:uid="{D39CE96F-8D2C-4A60-A43A-B3602E27FDC2}"/>
-  <tableColumns count="13">
-    <tableColumn id="1" xr3:uid="{AE3CE10F-629F-414E-93DE-8949C4E58E7D}" name="Symbol" dataDxfId="30"/>
-    <tableColumn id="2" xr3:uid="{40700DF4-EB97-4DB9-BA32-772C3F8E34CC}" name="StockName" dataDxfId="29"/>
-    <tableColumn id="3" xr3:uid="{BED1527E-0498-4FF1-8E69-ECDB2EB30C25}" name="TradeCurrency" dataDxfId="28">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{D39CE96F-8D2C-4A60-A43A-B3602E27FDC2}" name="tblHoldings" displayName="tblHoldings" ref="A1:N11" totalsRowShown="0" headerRowDxfId="34" dataDxfId="33" tableBorderDxfId="32">
+  <autoFilter ref="A1:N11" xr:uid="{D39CE96F-8D2C-4A60-A43A-B3602E27FDC2}"/>
+  <tableColumns count="14">
+    <tableColumn id="1" xr3:uid="{AE3CE10F-629F-414E-93DE-8949C4E58E7D}" name="Symbol" dataDxfId="31"/>
+    <tableColumn id="2" xr3:uid="{40700DF4-EB97-4DB9-BA32-772C3F8E34CC}" name="StockName" dataDxfId="30"/>
+    <tableColumn id="3" xr3:uid="{BED1527E-0498-4FF1-8E69-ECDB2EB30C25}" name="TradeCurrency" dataDxfId="29">
       <calculatedColumnFormula>_FV(B2,"Currency")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{2218CAC2-8A57-48EA-B1D3-CD7E0BA08ECA}" name="TotalBought" dataDxfId="27"/>
-    <tableColumn id="5" xr3:uid="{77160EAF-769F-4559-B5AE-C08A0AC76566}" name="TotalSold" dataDxfId="26"/>
-    <tableColumn id="6" xr3:uid="{324BA50C-3A95-4946-A384-C4EF731BD7F3}" name="NetPosition" dataDxfId="25"/>
-    <tableColumn id="7" xr3:uid="{24A211AE-9FE1-4D72-98D4-96F240F7DCFD}" name="AvgCost" dataDxfId="24"/>
-    <tableColumn id="8" xr3:uid="{E1C8BF44-8957-447E-B3C1-A76A00A619B8}" name="AvgBuyCost" dataDxfId="23">
+    <tableColumn id="4" xr3:uid="{2218CAC2-8A57-48EA-B1D3-CD7E0BA08ECA}" name="TotalBought" dataDxfId="28"/>
+    <tableColumn id="5" xr3:uid="{77160EAF-769F-4559-B5AE-C08A0AC76566}" name="TotalSold" dataDxfId="27"/>
+    <tableColumn id="6" xr3:uid="{324BA50C-3A95-4946-A384-C4EF731BD7F3}" name="NetPosition" dataDxfId="26"/>
+    <tableColumn id="7" xr3:uid="{24A211AE-9FE1-4D72-98D4-96F240F7DCFD}" name="AvgCost" dataDxfId="25"/>
+    <tableColumn id="8" xr3:uid="{E1C8BF44-8957-447E-B3C1-A76A00A619B8}" name="AvgBuyCost" dataDxfId="24">
       <calculatedColumnFormula>F2*G2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{73ED87C5-FB66-49D5-B1EF-4BE32DC6D51F}" name="StockPrice" dataDxfId="22">
+    <tableColumn id="9" xr3:uid="{73ED87C5-FB66-49D5-B1EF-4BE32DC6D51F}" name="StockPrice" dataDxfId="23">
       <calculatedColumnFormula>_FV(B2,"Price")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{1E08B942-A194-43F5-A7DB-404EC54A5C02}" name="FXRate" dataDxfId="21">
+    <tableColumn id="10" xr3:uid="{1E08B942-A194-43F5-A7DB-404EC54A5C02}" name="FXRate" dataDxfId="22">
       <calculatedColumnFormula>Config!$C$1</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{96D6E4C8-F5BD-4A3E-88A2-BF403C882136}" name="MarketValue" dataDxfId="20">
+    <tableColumn id="14" xr3:uid="{42171935-FB72-4173-A1EB-132DDE8201DD}" name="Column1" dataDxfId="0">
+      <calculatedColumnFormula array="1">_FV(B2,"Change (%)",TRUE)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="11" xr3:uid="{96D6E4C8-F5BD-4A3E-88A2-BF403C882136}" name="MarketValue" dataDxfId="21">
       <calculatedColumnFormula>F2*I2*J2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{E928C781-D2C4-42A1-A053-38B541581BCB}" name="P&amp;L" dataDxfId="19">
-      <calculatedColumnFormula>K2-H2</calculatedColumnFormula>
+    <tableColumn id="12" xr3:uid="{E928C781-D2C4-42A1-A053-38B541581BCB}" name="P&amp;L" dataDxfId="20">
+      <calculatedColumnFormula>L2-H2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{53BE744D-B35A-4E6B-8EA9-E422203F974E}" name="P&amp;LPercent" dataDxfId="18">
-      <calculatedColumnFormula>IF(H2=0,"",L2/H2)</calculatedColumnFormula>
+    <tableColumn id="13" xr3:uid="{53BE744D-B35A-4E6B-8EA9-E422203F974E}" name="P&amp;LPercent" dataDxfId="19">
+      <calculatedColumnFormula>IF(H2=0,"",M2/H2)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
@@ -19252,7 +19291,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{989027A5-E4FB-4AA7-BEAE-7B9653141BA1}">
-  <dimension ref="A1:M11"/>
+  <dimension ref="A1:N11"/>
   <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="15.4"/>
   <cols>
     <col min="1" max="1" width="9.86328125" style="16" bestFit="1" customWidth="1"/>
@@ -19265,13 +19304,14 @@
     <col min="8" max="8" width="11.53125" style="16" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="10" style="16" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="7.6640625" style="16" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.1328125" style="16" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.1328125" style="16" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.33203125" style="16" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.1328125" style="16"/>
+    <col min="11" max="11" width="7.6640625" style="41" customWidth="1"/>
+    <col min="12" max="12" width="12.1328125" style="16" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.1328125" style="16" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.33203125" style="16" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="9.1328125" style="16"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:14">
       <c r="A1" s="13" t="s">
         <v>312</v>
       </c>
@@ -19302,17 +19342,20 @@
       <c r="J1" s="15" t="s">
         <v>318</v>
       </c>
-      <c r="K1" s="15" t="s">
+      <c r="K1" s="39" t="s">
+        <v>607</v>
+      </c>
+      <c r="L1" s="15" t="s">
         <v>319</v>
       </c>
-      <c r="L1" s="15" t="s">
+      <c r="M1" s="15" t="s">
         <v>320</v>
       </c>
-      <c r="M1" s="15" t="s">
+      <c r="N1" s="15" t="s">
         <v>321</v>
       </c>
     </row>
-    <row r="2" spans="1:13" hidden="1">
+    <row r="2" spans="1:14" hidden="1">
       <c r="A2" s="17" t="s">
         <v>35</v>
       </c>
@@ -19347,20 +19390,24 @@
         <f ca="1">Config!$C$1</f>
         <v>0.74229999999999996</v>
       </c>
-      <c r="K2" s="20">
-        <f t="shared" ref="K2:K11" ca="1" si="3">F2*I2*J2</f>
+      <c r="K2" s="40" cm="1">
+        <f t="array" aca="1" ref="K2" ca="1">_FV(B2,"Change (%)",TRUE)</f>
+        <v>-1.8426000000000001E-2</v>
+      </c>
+      <c r="L2" s="20">
+        <f t="shared" ref="L2:L11" ca="1" si="3">F2*I2*J2</f>
         <v>2046.3652169999998</v>
       </c>
-      <c r="L2" s="20">
-        <f t="shared" ref="L2:L11" ca="1" si="4">K2-H2</f>
+      <c r="M2" s="20">
+        <f t="shared" ref="M2:M11" ca="1" si="4">L2-H2</f>
         <v>1741.2089669999998</v>
       </c>
-      <c r="M2" s="23">
-        <f t="shared" ref="M2:M11" ca="1" si="5">IF(H2=0,"",L2/H2)</f>
+      <c r="N2" s="23">
+        <f t="shared" ref="N2:N11" ca="1" si="5">IF(H2=0,"",M2/H2)</f>
         <v>5.7059587244239625</v>
       </c>
     </row>
-    <row r="3" spans="1:13">
+    <row r="3" spans="1:14">
       <c r="A3" s="17" t="s">
         <v>41</v>
       </c>
@@ -19395,20 +19442,24 @@
         <f ca="1">Config!$C$1</f>
         <v>0.74229999999999996</v>
       </c>
-      <c r="K3" s="20">
+      <c r="K3" s="40" cm="1">
+        <f t="array" aca="1" ref="K3" ca="1">_FV(B3,"Change (%)",TRUE)</f>
+        <v>-5.0654999999999999E-2</v>
+      </c>
+      <c r="L3" s="20">
         <f t="shared" ca="1" si="3"/>
         <v>2674.373286</v>
       </c>
-      <c r="L3" s="20">
+      <c r="M3" s="20">
         <f t="shared" ca="1" si="4"/>
         <v>-493.48671600000034</v>
       </c>
-      <c r="M3" s="23">
+      <c r="N3" s="23">
         <f t="shared" ca="1" si="5"/>
         <v>-0.15577920605343729</v>
       </c>
     </row>
-    <row r="4" spans="1:13">
+    <row r="4" spans="1:14">
       <c r="A4" s="17" t="s">
         <v>60</v>
       </c>
@@ -19443,20 +19494,24 @@
         <f ca="1">Config!$C$1</f>
         <v>0.74229999999999996</v>
       </c>
-      <c r="K4" s="20">
+      <c r="K4" s="40" cm="1">
+        <f t="array" aca="1" ref="K4" ca="1">_FV(B4,"Change (%)",TRUE)</f>
+        <v>-3.7858000000000003E-2</v>
+      </c>
+      <c r="L4" s="20">
         <f t="shared" ca="1" si="3"/>
         <v>5051.1659249999993</v>
       </c>
-      <c r="L4" s="20">
+      <c r="M4" s="20">
         <f t="shared" ca="1" si="4"/>
         <v>1403.3666250000001</v>
       </c>
-      <c r="M4" s="23">
+      <c r="N4" s="23">
         <f t="shared" ca="1" si="5"/>
         <v>0.38471596422533455</v>
       </c>
     </row>
-    <row r="5" spans="1:13">
+    <row r="5" spans="1:14">
       <c r="A5" s="17" t="s">
         <v>200</v>
       </c>
@@ -19491,20 +19546,24 @@
         <f ca="1">Config!$C$1</f>
         <v>0.74229999999999996</v>
       </c>
-      <c r="K5" s="20">
+      <c r="K5" s="40" cm="1">
+        <f t="array" aca="1" ref="K5" ca="1">_FV(B5,"Change (%)",TRUE)</f>
+        <v>6.2612000000000001E-2</v>
+      </c>
+      <c r="L5" s="20">
         <f t="shared" ca="1" si="3"/>
         <v>2997.763704</v>
       </c>
-      <c r="L5" s="20">
+      <c r="M5" s="20">
         <f t="shared" ca="1" si="4"/>
         <v>665.32370399999991</v>
       </c>
-      <c r="M5" s="23">
+      <c r="N5" s="23">
         <f t="shared" ca="1" si="5"/>
         <v>0.28524793949683591</v>
       </c>
     </row>
-    <row r="6" spans="1:13">
+    <row r="6" spans="1:14">
       <c r="A6" s="17" t="s">
         <v>63</v>
       </c>
@@ -19539,20 +19598,24 @@
         <f ca="1">Config!$C$1</f>
         <v>0.74229999999999996</v>
       </c>
-      <c r="K6" s="20">
+      <c r="K6" s="40" cm="1">
+        <f t="array" aca="1" ref="K6" ca="1">_FV(B6,"Change (%)",TRUE)</f>
+        <v>-1.1568E-2</v>
+      </c>
+      <c r="L6" s="20">
         <f t="shared" ca="1" si="3"/>
         <v>4544.0339879999992</v>
       </c>
-      <c r="L6" s="20">
+      <c r="M6" s="20">
         <f t="shared" ca="1" si="4"/>
         <v>2684.5139879999992</v>
       </c>
-      <c r="M6" s="23">
+      <c r="N6" s="23">
         <f t="shared" ca="1" si="5"/>
         <v>1.4436596476510064</v>
       </c>
     </row>
-    <row r="7" spans="1:13">
+    <row r="7" spans="1:14">
       <c r="A7" s="17" t="s">
         <v>70</v>
       </c>
@@ -19587,20 +19650,24 @@
         <f ca="1">Config!$C$1</f>
         <v>0.74229999999999996</v>
       </c>
-      <c r="K7" s="20">
+      <c r="K7" s="40" cm="1">
+        <f t="array" aca="1" ref="K7" ca="1">_FV(B7,"Change (%)",TRUE)</f>
+        <v>0.139596</v>
+      </c>
+      <c r="L7" s="20">
         <f t="shared" ca="1" si="3"/>
         <v>2872.2704659999995</v>
       </c>
-      <c r="L7" s="20">
+      <c r="M7" s="20">
         <f t="shared" ca="1" si="4"/>
         <v>798.18046699999923</v>
       </c>
-      <c r="M7" s="23">
+      <c r="N7" s="23">
         <f t="shared" ca="1" si="5"/>
         <v>0.38483405608475679</v>
       </c>
     </row>
-    <row r="8" spans="1:13">
+    <row r="8" spans="1:14">
       <c r="A8" s="17" t="s">
         <v>64</v>
       </c>
@@ -19635,20 +19702,24 @@
         <f ca="1">Config!$C$1</f>
         <v>0.74229999999999996</v>
       </c>
-      <c r="K8" s="20">
+      <c r="K8" s="40" cm="1">
+        <f t="array" aca="1" ref="K8" ca="1">_FV(B8,"Change (%)",TRUE)</f>
+        <v>-4.5686999999999998E-2</v>
+      </c>
+      <c r="L8" s="20">
         <f t="shared" ca="1" si="3"/>
         <v>5556.7390319999995</v>
       </c>
-      <c r="L8" s="20">
+      <c r="M8" s="20">
         <f t="shared" ca="1" si="4"/>
         <v>702.46913200000017</v>
       </c>
-      <c r="M8" s="23">
+      <c r="N8" s="23">
         <f t="shared" ca="1" si="5"/>
         <v>0.14471159339533227</v>
       </c>
     </row>
-    <row r="9" spans="1:13">
+    <row r="9" spans="1:14">
       <c r="A9" s="17" t="s">
         <v>76</v>
       </c>
@@ -19683,20 +19754,24 @@
         <f ca="1">Config!$C$1</f>
         <v>0.74229999999999996</v>
       </c>
-      <c r="K9" s="20">
+      <c r="K9" s="40" cm="1">
+        <f t="array" aca="1" ref="K9" ca="1">_FV(B9,"Change (%)",TRUE)</f>
+        <v>1.4733000000000001E-2</v>
+      </c>
+      <c r="L9" s="20">
         <f t="shared" ca="1" si="3"/>
         <v>1014.3381039999999</v>
       </c>
-      <c r="L9" s="20">
+      <c r="M9" s="20">
         <f t="shared" ca="1" si="4"/>
         <v>-78.891900000000078</v>
       </c>
-      <c r="M9" s="23">
+      <c r="N9" s="23">
         <f t="shared" ca="1" si="5"/>
         <v>-7.2164045728112011E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:13">
+    <row r="10" spans="1:14">
       <c r="A10" s="17" t="s">
         <v>80</v>
       </c>
@@ -19731,20 +19806,24 @@
         <f ca="1">Config!$C$1</f>
         <v>0.74229999999999996</v>
       </c>
-      <c r="K10" s="20">
+      <c r="K10" s="40" cm="1">
+        <f t="array" aca="1" ref="K10" ca="1">_FV(B10,"Change (%)",TRUE)</f>
+        <v>0.130187</v>
+      </c>
+      <c r="L10" s="20">
         <f t="shared" ca="1" si="3"/>
         <v>4598.5039619999998</v>
       </c>
-      <c r="L10" s="20">
+      <c r="M10" s="20">
         <f t="shared" ca="1" si="4"/>
         <v>2088.6338259999993</v>
       </c>
-      <c r="M10" s="23">
+      <c r="N10" s="23">
         <f t="shared" ca="1" si="5"/>
         <v>0.83216808552838961</v>
       </c>
     </row>
-    <row r="11" spans="1:13" hidden="1">
+    <row r="11" spans="1:14" hidden="1">
       <c r="A11" s="17" t="s">
         <v>32</v>
       </c>
@@ -19779,83 +19858,87 @@
         <f ca="1">Config!$C$1</f>
         <v>0.74229999999999996</v>
       </c>
-      <c r="K11" s="20">
+      <c r="K11" s="40" cm="1">
+        <f t="array" aca="1" ref="K11" ca="1">_FV(B11,"Change (%)",TRUE)</f>
+        <v>-1.4322999999999999E-2</v>
+      </c>
+      <c r="L11" s="20">
         <f t="shared" ca="1" si="3"/>
         <v>33203.078999999998</v>
       </c>
-      <c r="L11" s="20">
+      <c r="M11" s="20">
         <f t="shared" ca="1" si="4"/>
         <v>28203.078999999998</v>
       </c>
-      <c r="M11" s="23">
+      <c r="N11" s="23">
         <f t="shared" ca="1" si="5"/>
         <v>5.6406158</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A2:A11">
-    <cfRule type="expression" dxfId="17" priority="16" stopIfTrue="1">
-      <formula>L2&gt;0</formula>
+    <cfRule type="expression" dxfId="18" priority="16" stopIfTrue="1">
+      <formula>M2&gt;0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="16" priority="17" stopIfTrue="1">
-      <formula>L2&lt;0</formula>
+    <cfRule type="expression" dxfId="17" priority="17" stopIfTrue="1">
+      <formula>M2&lt;0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="15" priority="18" stopIfTrue="1">
-      <formula>L2=0</formula>
+    <cfRule type="expression" dxfId="16" priority="18" stopIfTrue="1">
+      <formula>M2=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G2:G11">
-    <cfRule type="cellIs" dxfId="14" priority="1" stopIfTrue="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="15" priority="1" stopIfTrue="1" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="13" priority="2" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="14" priority="2" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="12" priority="3" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="3" stopIfTrue="1" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H2:H11">
-    <cfRule type="cellIs" dxfId="11" priority="4" stopIfTrue="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="12" priority="4" stopIfTrue="1" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="10" priority="5" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="11" priority="5" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="9" priority="6" stopIfTrue="1" operator="equal">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K11">
-    <cfRule type="cellIs" dxfId="8" priority="7" stopIfTrue="1" operator="greaterThan">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="7" priority="8" stopIfTrue="1" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="9" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="6" stopIfTrue="1" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:L11">
-    <cfRule type="cellIs" dxfId="5" priority="10" stopIfTrue="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="9" priority="7" stopIfTrue="1" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="11" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="8" priority="8" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="12" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="9" stopIfTrue="1" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M2:M11">
-    <cfRule type="cellIs" dxfId="2" priority="13" stopIfTrue="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="6" priority="10" stopIfTrue="1" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="14" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="5" priority="11" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="15" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="12" stopIfTrue="1" operator="equal">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N2:N11">
+    <cfRule type="cellIs" dxfId="3" priority="13" stopIfTrue="1" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="14" stopIfTrue="1" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="15" stopIfTrue="1" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>

--- a/dashboard/trading_system.xlsx
+++ b/dashboard/trading_system.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\husainnatha\tradingsystem\dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB655EB0-977F-4A2B-8587-2544B1B380F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{383D8EAD-BE5F-4AFF-88BC-C171070C06DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CONTRIBUTIONS" sheetId="11" r:id="rId1"/>
@@ -1081,7 +1081,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1963" uniqueCount="618">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1975" uniqueCount="618">
   <si>
     <t>collected_timestamp</t>
   </si>
@@ -3943,11 +3943,11 @@
     <v>4</v>
     <v>233.67</v>
     <v>15.29</v>
-    <v>3.6524999999999999</v>
+    <v>3.6288</v>
     <v>-25.89</v>
-    <v>-1.7006E-2</v>
+    <v>-1.8952E-2</v>
     <v>-0.127606</v>
-    <v>-3.01</v>
+    <v>-3.3544999999999998</v>
     <v>USD</v>
     <v>Applied Optoelectronics, Inc. is a developer and manufacturer of advanced optical and hybrid fiber coaxial (HFC) networking products that are the building blocks for artificial intelligence (AI) datacenters, Cable TV Broadband (CATV) and broadband fiber access networks around the world. The Company supplies this critical infrastructure to tier-one customers across cloud computing, CATV broadband, telecom, and fiber-to-the-home (FTTH) markets. It designs and manufactures a range of optical communications products at varying levels of integration, from components, subassemblies and modules to complete turn-key equipment. In the CATV market, it supplies a broad array of products, including lasers, transmitters and transceivers, and turn-key equipment. It supplies optical transceivers that plug into switches and servers within the data center and allow these network devices to send and receive data over fiber optic cables. In the telecom market, it supplies lasers and laser subassemblies.</v>
     <v>4691</v>
@@ -3958,7 +3958,7 @@
     <v>208.5</v>
     <v>Electronic Equipment &amp; Parts</v>
     <v>Stock</v>
-    <v>46178.903395763278</v>
+    <v>46178.999954316409</v>
     <v>0</v>
     <v>174.23</v>
     <v>14202970290</v>
@@ -3968,11 +3968,11 @@
     <v>0</v>
     <v>202.89</v>
     <v>177</v>
-    <v>173.99</v>
+    <v>173.6455</v>
     <v>80242770</v>
     <v>AAOI</v>
     <v>APPLIED OPTOELECTRONICS, INC. (XNAS:AAOI)</v>
-    <v>19683738</v>
+    <v>19828156</v>
     <v>12222923</v>
     <v>2013</v>
   </rv>
@@ -3997,11 +3997,11 @@
     <v>4</v>
     <v>316.94</v>
     <v>195.07</v>
-    <v>1.0863</v>
+    <v>1.0832999999999999</v>
     <v>-3.89</v>
-    <v>1.9850000000000002E-3</v>
+    <v>1.4289999999999999E-3</v>
     <v>-1.2499E-2</v>
-    <v>0.61</v>
+    <v>0.43919999999999998</v>
     <v>USD</v>
     <v>Apple Inc. designs, manufactures and markets smartphones, personal computers, tablets, wearables and accessories, and sells a variety of related services. Its product categories include iPhone, Mac, iPad, Wearables, Home and Accessories. Its services include advertising, AppleCare, cloud services, digital content, and payment services. The Company operates various platforms, including the App Store, that allow customers to discover and download applications and digital content, such as books, music, video, games and podcasts. It also offers digital content through subscription-based services, including Apple Arcade, Apple Fitness+, Apple Music, Apple News+, and Apple TV+. Its wearables include smartwatches, wireless headphones, and spatial computers. Its products include iPhone 16 Pro, iPhone 16, iPhone 15, iPhone 14, iPhone SE, MacBook Air, MacBook Pro, iMac, Mac mini, Mac Studio, Mac Pro, iPad Pro, iPad Air, AirPods, AirPods Pro, AirPods Max, Apple TV, Apple Vision Pro and others.</v>
     <v>166000</v>
@@ -4012,21 +4012,21 @@
     <v>315.17</v>
     <v>Computers, Phones &amp; Household Electronics</v>
     <v>Stock</v>
-    <v>46178.903317210155</v>
+    <v>46178.999989015625</v>
     <v>3</v>
     <v>307.14999999999998</v>
     <v>4514013222400</v>
     <v>APPLE INC.</v>
     <v>APPLE INC.</v>
     <v>312.86</v>
-    <v>37.326599999999999</v>
+    <v>37.798999999999999</v>
     <v>311.23</v>
     <v>307.33999999999997</v>
-    <v>307.95</v>
+    <v>307.7792</v>
     <v>14687360000</v>
     <v>AAPL</v>
     <v>APPLE INC. (XNAS:AAPL)</v>
-    <v>65217745</v>
+    <v>65310502</v>
     <v>50489004</v>
     <v>1977</v>
   </rv>
@@ -4071,11 +4071,11 @@
     <v>4</v>
     <v>421.48</v>
     <v>224.13</v>
-    <v>1.4020999999999999</v>
+    <v>1.395</v>
     <v>-6.98</v>
-    <v>-1.7899999999999999E-3</v>
+    <v>-7.3460000000000001E-3</v>
     <v>-2.7009999999999999E-2</v>
-    <v>-0.45</v>
+    <v>-1.8471</v>
     <v>USD</v>
     <v>Adobe Inc. is a global technology company. The Company's products, services and solutions are used around the world to imagine, create, manage, deliver, measure, optimize and engage with content across surfaces and fuel digital experiences. Its segments include Digital Media, Digital Experience, and Publishing and Advertising. The Digital Media segment is centered around Adobe Creative Cloud and Adobe Document Cloud, which include Adobe Express, Adobe Firefly, Photoshop and other products, offering a variety of tools for creative professionals, communicators and other consumers. The Digital Experience segment provides an integrated platform and set of products, services and solutions through Adobe Experience Cloud. The Publishing and Advertising segment contains legacy products and services. In addition, its Adobe GenStudio solution allows businesses to simplify their content supply chain process with generative artificial intelligence (AI) capabilities and intelligent automation.</v>
     <v>31360</v>
@@ -4087,7 +4087,7 @@
     <v>9</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46178.903395647656</v>
+    <v>46178.999899421091</v>
     <v>10</v>
     <v>249.05</v>
     <v>101632048000</v>
@@ -4097,11 +4097,11 @@
     <v>15.0618</v>
     <v>258.42</v>
     <v>251.44</v>
-    <v>250.99</v>
+    <v>249.59289999999999</v>
     <v>404200000</v>
     <v>ADBE</v>
     <v>ADOBE INC. (XNAS:ADBE)</v>
-    <v>4900885</v>
+    <v>4909175</v>
     <v>4936048</v>
     <v>1997</v>
   </rv>
@@ -4126,11 +4126,11 @@
     <v>4</v>
     <v>121.8</v>
     <v>10.887499999999999</v>
-    <v>3.1669</v>
+    <v>3.1621999999999999</v>
     <v>-18.13</v>
-    <v>-4.5710000000000004E-3</v>
+    <v>-1.9806999999999998E-2</v>
     <v>-0.15551600000000002</v>
-    <v>-0.45</v>
+    <v>-1.95</v>
     <v>USD</v>
     <v>Aehr Test Systems, Inc. offers test solutions for testing, burning-in, and stabilizing semiconductor devices in wafer level, singulated die, and package part form. The Company's products include the FOX-P family of test and burn-in systems and FOX WaferPak Aligner, FOX WaferPak Contactor, FOX DiePak Carrier and FOX DiePak Loader. The FOX-XP and FOX-NP systems are full wafer contact and singulated die/module test and burn-in systems that can test, burn-in and stabilize a range of devices such as silicon carbide-based and other power semiconductors, 2D and 3D sensors used in phones, tablets, and other computing devices, memory semiconductors, processors, microcontrollers, systems-on-a-chip, and photonics and integrated optical devices used in AI. FOX-CP system is a single-wafer compact test solution for logic, memory and photonic devices. FOX WaferPak Contactor contains a full wafer contactor capable of testing wafers up to 300 millimeters that enables integrated circuit manufacturers.</v>
     <v>136</v>
@@ -4141,7 +4141,7 @@
     <v>111.7855</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46178.903194525003</v>
+    <v>46178.999445092188</v>
     <v>13</v>
     <v>96.9</v>
     <v>3096572462</v>
@@ -4151,11 +4151,11 @@
     <v>0</v>
     <v>116.58</v>
     <v>98.45</v>
-    <v>98</v>
+    <v>96.5</v>
     <v>31453250</v>
     <v>AEHR</v>
     <v>AEHR TEST SYSTEMS (XNAS:AEHR)</v>
-    <v>2338404</v>
+    <v>2352316</v>
     <v>2549949</v>
     <v>1977</v>
   </rv>
@@ -4176,7 +4176,7 @@
     <v>13</v>
     <v>12.24</v>
     <v>10.99</v>
-    <v>0.83899999999999997</v>
+    <v>0.83889999999999998</v>
     <v>-0.02</v>
     <v>-1.701E-3</v>
     <v>CAD</v>
@@ -4195,7 +4195,7 @@
     <v>ATRIUM MORTGAGE INVESTMENT CORPORATION</v>
     <v>ATRIUM MORTGAGE INVESTMENT CORPORATION</v>
     <v>11.76</v>
-    <v>11.156499999999999</v>
+    <v>10.3893</v>
     <v>11.76</v>
     <v>11.74</v>
     <v>48239690</v>
@@ -4224,9 +4224,9 @@
     <v>84.78</v>
     <v>2.64</v>
     <v>-40.99</v>
-    <v>-1.9113000000000002E-2</v>
+    <v>-2.7029999999999998E-2</v>
     <v>-0.114481</v>
-    <v>-6.0598999999999998</v>
+    <v>-8.57</v>
     <v>USD</v>
     <v>Astera Labs, Inc. is a global semiconductor company. The Company provides semiconductor-based connectivity solutions for cloud and artificial intelligence (AI) infrastructure. It has developed and deployed its Intelligent Connectivity Platform built from the ground up for cloud and AI infrastructure. Its Intelligent Connectivity Platform provides its customers with the ability to deploy and operate high-performance cloud and AI infrastructure at scale, addressing an increasingly diverse set of requirements. It provides its connectivity products in various form factors, including Integrated Circuits (ICs), boards, and modules. Its PCIe, CXL and Ethernet semiconductor-based connectivity solutions are purpose-built to unleash the potential of accelerated computing at cloud-scale. The Company’s products include Aries products, which include its COSMOS software suite; Taurus products, which are hardware modules based on its Taurus ICs; Leo products; and Scorpio products.</v>
     <v>756</v>
@@ -4237,20 +4237,20 @@
     <v>349</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46178.903431978906</v>
+    <v>46178.999956735941</v>
     <v>314.83999999999997</v>
     <v>54346588774</v>
     <v>ASTERA LABS, INC.</v>
     <v>ASTERA LABS, INC.</v>
     <v>342.75</v>
-    <v>241.36949999999999</v>
+    <v>213.73869999999999</v>
     <v>358.05</v>
     <v>317.06</v>
-    <v>311.00009999999997</v>
+    <v>308.49</v>
     <v>171407900</v>
     <v>ALAB</v>
     <v>ASTERA LABS, INC. (XNAS:ALAB)</v>
-    <v>7300236</v>
+    <v>7315038</v>
     <v>6145101</v>
     <v>2017</v>
   </rv>
@@ -4275,11 +4275,11 @@
     <v>4</v>
     <v>96.69</v>
     <v>48.3</v>
-    <v>2.145</v>
+    <v>2.1604000000000001</v>
     <v>-8.5299999999999994</v>
-    <v>-2.8339999999999997E-3</v>
+    <v>-4.2509999999999996E-3</v>
     <v>-0.11839000000000001</v>
-    <v>-0.18</v>
+    <v>-0.27</v>
     <v>USD</v>
     <v>Ambarella, Inc. is a developer of low-power system-on-a-chip (SoC) semiconductors and software for edge artificial intelligence (AI) applications. The Company's technologies make electronic systems smarter, enabling them to become partially or fully autonomous with features, such as person detection, object classification, and analytics, in addition to performing complex data analysis in real time, delivering imagery, and preserving vital system resources, such as power and network bandwidth. It specializes in the development of deployable, scalable designs for intelligent electronic systems that utilize high-bandwidth sensors. Its products are used in a variety of human viewing, computer vision and edge AI applications, including a variety of automotive camera systems, video security cameras, mobile and fixed robots, industrial applications, and consumer devices, such as action, drone, and 360-degree cameras.</v>
     <v>959</v>
@@ -4290,7 +4290,7 @@
     <v>70.260000000000005</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46178.902898587497</v>
+    <v>46178.999421805471</v>
     <v>20</v>
     <v>63.253500000000003</v>
     <v>2786506793</v>
@@ -4300,11 +4300,11 @@
     <v>0</v>
     <v>72.05</v>
     <v>63.52</v>
-    <v>63.34</v>
+    <v>63.25</v>
     <v>43868180</v>
     <v>AMBA</v>
     <v>AMBARELLA, INC. (XNAS:AMBA)</v>
-    <v>2111285</v>
+    <v>2124450</v>
     <v>1545901</v>
     <v>2004</v>
   </rv>
@@ -4329,11 +4329,11 @@
     <v>4</v>
     <v>546.44000000000005</v>
     <v>114.71</v>
-    <v>2.4918999999999998</v>
+    <v>2.5061</v>
     <v>-56.82</v>
-    <v>1.3289999999999999E-3</v>
+    <v>-1.6544E-2</v>
     <v>-0.10860099999999999</v>
-    <v>0.62</v>
+    <v>-7.7160000000000002</v>
     <v>USD</v>
     <v>Advanced Micro Devices, Inc. is a global semiconductor company. The Company is focused on high-performance computing and artificial intelligence (AI). Its segments include Data Center, Client and Gaming, and Embedded. Data Center segment includes AI accelerators, microprocessors (CPUs) for servers, graphics processing units (GPUs), accelerated processing units (APUs), data processing units (DPUs), Field Programmable Gate Arrays (FPGAs), and Adaptive system-on-Chip (SoC) products for data centers. Client and Gaming segment includes CPUs, APUs, chipsets for desktops and notebooks, discrete GPUs, and semi-custom SoC products and development services. Embedded segment includes embedded CPUs, APUs, FPGAs, system on modules (SOMs), and Adaptive SoC products. It markets and sells its products under the AMD trademark. Its products include AMD EPYC, AMD Ryzen, AMD Ryzen PRO, Virtex UltraScale+, among others.</v>
     <v>31000</v>
@@ -4344,7 +4344,7 @@
     <v>505.62</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46178.903431481252</v>
+    <v>46178.999982383597</v>
     <v>23</v>
     <v>463.95</v>
     <v>760479694380</v>
@@ -4354,11 +4354,11 @@
     <v>174.4058</v>
     <v>523.20000000000005</v>
     <v>466.38</v>
-    <v>467</v>
+    <v>458.66399999999999</v>
     <v>1630601000</v>
     <v>AMD</v>
     <v>ADVANCED MICRO DEVICES, INC. (XNAS:AMD)</v>
-    <v>46690771</v>
+    <v>46900606</v>
     <v>38161677</v>
     <v>1969</v>
   </rv>
@@ -4383,11 +4383,11 @@
     <v>4</v>
     <v>278.56</v>
     <v>196</v>
-    <v>1.4490000000000001</v>
+    <v>1.4587000000000001</v>
     <v>-7.76</v>
-    <v>2.627E-3</v>
+    <v>-9.3479999999999995E-4</v>
     <v>-3.0575999999999999E-2</v>
-    <v>0.64629999999999999</v>
+    <v>-0.23</v>
     <v>USD</v>
     <v>Amazon.com, Inc. provides a range of products and services to customers. The products offered through its stores include merchandise and content it has purchased for resale and products offered by third-party sellers. The Company’s segments include North America, International and Amazon Web Services (AWS). It serves consumers through its online and physical stores and focuses on selection, price, and convenience. Customers access its offerings through its websites, mobile apps, Alexa, devices, streaming, and physically visiting its stores. It also manufactures and sells electronic devices, including Kindle, Fire tablet, Fire TV, Echo, Ring, Blink, and eero, and develops and produces media content. It serves developers and enterprises of all sizes, including start-ups, government agencies, and academic institutions, through AWS, which offers a set of on-demand technology services, including compute, storage, database, analytics, and machine learning, and other services.</v>
     <v>1575000</v>
@@ -4398,7 +4398,7 @@
     <v>256.38</v>
     <v>Diversified Retail</v>
     <v>Stock</v>
-    <v>46178.903375948437</v>
+    <v>46178.999997349216</v>
     <v>26</v>
     <v>245.78</v>
     <v>2646571773300</v>
@@ -4408,11 +4408,11 @@
     <v>30.329699999999999</v>
     <v>253.79</v>
     <v>246.03</v>
-    <v>246.6763</v>
+    <v>245.8</v>
     <v>10757110000</v>
     <v>AMZN</v>
     <v>AMAZON.COM, INC. (XNAS:AMZN)</v>
-    <v>55469366</v>
+    <v>55607844</v>
     <v>42947346</v>
     <v>1996</v>
   </rv>
@@ -4437,13 +4437,13 @@
     <v>4</v>
     <v>179.8</v>
     <v>85.58</v>
-    <v>1.6099000000000001</v>
-    <v>-11.805</v>
-    <v>-8.2319999999999997E-3</v>
-    <v>-7.1109999999999993E-2</v>
-    <v>-1.27</v>
+    <v>1.6153999999999999</v>
+    <v>-11.74</v>
+    <v>-1.1894999999999999E-2</v>
+    <v>-7.0719000000000004E-2</v>
+    <v>-1.835</v>
     <v>USD</v>
-    <v>Arista Networks, Inc. is a provider of data-driven, client-to-cloud networking for large artificial intelligence (AI), data center, campus and routing environments. Its platforms deliver availability, agility, automation, analytics, and security through an advanced network operating stack. Its platform is its Extensible Operating System (EOS), a modernized publish-subscribe state-sharing networking operating system. Its portfolio of products, services and technologies is grouped into various categories: Core (Data Center, Cloud and AI Networking), Cognitive Adjacencies (Campus and Routing), and Cognitive Network (Software and Services). It offers product portfolios of data-driven, high-speed, cloud and data center Ethernet switches. Its Cognitive Adjacencies include Cognitive Campus Switching, Cloud-Grade Routing and WAN Routing. Its software and services are based on subscription-based models and include various offerings: CloudVision, Arista A-Care Services, CloudEOS and others.</v>
+    <v>Arista Networks, Inc. is a provider of data-driven, client-to-cloud networking for large artificial intelligence (AI), data center, campus and routing environments. The Company's cloud networking solutions consist of its Extensible Operating System (EOS), a set of network applications and its Ethernet switching and routing platforms. Its platforms deliver availability, agility, automation, analytics, and security through an advanced network operating stack. It offers a robust set of solutions, ranging from modular and fixed-form-factor campus spine switches to Power-over-Ethernet (PoE) leaf switches and Wi-Fi access points, all managed through CloudVision. The Company's network-as-a-service approach empowers customers of all sizes to leverage their data through offerings spanning three categories: Core (AI, Cloud, and Data Center Networking), Cognitive Adjacencies (Campus and Routing), and Cognitive Networks (Software and Services).</v>
     <v>5115</v>
     <v>New York Stock Exchange</v>
     <v>XNYS</v>
@@ -4452,21 +4452,21 @@
     <v>161.19319999999999</v>
     <v>Communications &amp; Networking</v>
     <v>Stock</v>
-    <v>46178.903462823437</v>
+    <v>46178.999909189064</v>
     <v>29</v>
     <v>152.19</v>
-    <v>194175398615</v>
+    <v>194257246810</v>
     <v>ARISTA NETWORKS, INC.</v>
     <v>ARISTA NETWORKS, INC.</v>
     <v>159.46</v>
-    <v>56.859900000000003</v>
+    <v>52.839399999999998</v>
     <v>166.01</v>
-    <v>154.20500000000001</v>
-    <v>153</v>
+    <v>154.27000000000001</v>
+    <v>152.435</v>
     <v>1259203000</v>
     <v>ANET</v>
     <v>ARISTA NETWORKS, INC. (XNYS:ANET)</v>
-    <v>9075002</v>
+    <v>9094700</v>
     <v>12440510</v>
     <v>2011</v>
   </rv>
@@ -4491,11 +4491,11 @@
     <v>4</v>
     <v>745.61</v>
     <v>320</v>
-    <v>2.4645999999999999</v>
+    <v>2.4725000000000001</v>
     <v>-1.67</v>
-    <v>-9.332E-3</v>
+    <v>-1.2270000000000001E-2</v>
     <v>-2.9880000000000002E-3</v>
-    <v>-5.2</v>
+    <v>-6.8365999999999998</v>
     <v>USD</v>
     <v>AppLovin Corporation is a marketing platform. The Company provides end-to-end software and artificial intelligence (AI) solutions for businesses to reach, monetize and grow their global audiences. Its advertising solutions include a comprehensive suite of tools including AppDiscovery, MAX, Adjust, Wurl and Axon Ads Manager. AppDiscovery is powered by AXON, its AI-powered advertising engine, and matches advertiser demand with publisher supply through auctions at vast scale and at microsecond-level speeds. MAX is its monetization solution, utilizing an advanced in-app bidding technology that optimizes the value of a publisher’s advertising inventory by running a real-time competitive auction, driving more competition, and higher returns for publishers. Adjust is its measurement and analytics marketing platform which provides marketers with the visibility, insights, and data needed to scale their apps marketing and drive more informed results. Wurl is its connected TV (CTV) platform.</v>
     <v>898</v>
@@ -4506,21 +4506,21 @@
     <v>595</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46178.90282993047</v>
+    <v>46178.999783228908</v>
     <v>32</v>
     <v>548.78</v>
     <v>187185768000</v>
     <v>APPLOVIN CORPORATION</v>
     <v>APPLOVIN CORPORATION</v>
     <v>577.91499999999996</v>
-    <v>48.565600000000003</v>
+    <v>48.4206</v>
     <v>558.87</v>
     <v>557.20000000000005</v>
-    <v>552</v>
+    <v>550.36339999999996</v>
     <v>335940000</v>
     <v>APP</v>
     <v>APPLOVIN CORPORATION (XNAS:APP)</v>
-    <v>5542167</v>
+    <v>5547042</v>
     <v>5064206</v>
     <v>2011</v>
   </rv>
@@ -4546,28 +4546,28 @@
     <v>92.65</v>
     <v>55.64</v>
     <v>2.0400999999999998</v>
-    <v>-5.52</v>
-    <v>-6.5780000000000005E-3</v>
-    <v>-6.8940000000000001E-2</v>
-    <v>-0.49</v>
+    <v>-5.58</v>
+    <v>-6.7119999999999994E-4</v>
+    <v>-6.9689000000000001E-2</v>
+    <v>-0.05</v>
     <v>USD</v>
     <v>CBOE BZX Exchange</v>
     <v>BATS</v>
     <v>7.4999999999999997E-3</v>
     <v>78.75</v>
     <v>ETF</v>
-    <v>46178.902926515628</v>
+    <v>46178.999827649997</v>
     <v>35</v>
     <v>73.61</v>
     <v>7262198811.6000004</v>
     <v>ARK Innovation</v>
     <v>78.59</v>
     <v>80.069999999999993</v>
-    <v>74.55</v>
-    <v>74</v>
+    <v>74.489999999999995</v>
+    <v>74.44</v>
     <v>ARKK</v>
     <v>ARK Innovation (BATS:ARKK)</v>
-    <v>13976817</v>
+    <v>13983063</v>
     <v>7182449</v>
   </rv>
   <rv s="2">
@@ -4614,9 +4614,9 @@
     <v>100.02</v>
     <v>1.421</v>
     <v>-50.51</v>
-    <v>-1.3413999999999999E-2</v>
+    <v>-2.3212E-2</v>
     <v>-0.12837999999999999</v>
-    <v>-4.5999999999999996</v>
+    <v>-7.96</v>
     <v>USD</v>
     <v>Arm Holdings plc is a United Kingdom-based company. The Company is engaged in the design of central processing units (CPUs) and compute platforms for semiconductor chips. It develops and licenses CPU products and related technology. Its cloud and data center solutions include Arm AGI CPU and Arm Neoverse Compute Subsystems. The Arm Agentic Generalized Infrastructure (AGI) CPU is a production-ready system on a chip (SoC) for artificial intelligence (AI) data centers, delivering compute at scale. The Arm Neoverse Compute Subsystems (CSS) are pre-validated, performance-optimized compute platforms designed to accelerate infrastructure silicon development. The Company's primary markets include smartphone applications, processors and other chips used in mobile phones, consumer electronics, networking equipment, cloud and data center servers, automotive applications, Internet of Things (loT) and other embedded computing devices.</v>
     <v>9584</v>
@@ -4627,7 +4627,7 @@
     <v>373.74</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46178.903495253908</v>
+    <v>46178.999999305466</v>
     <v>337.55130000000003</v>
     <v>366276331470</v>
     <v>ARM HOLDINGS PLC</v>
@@ -4636,11 +4636,11 @@
     <v>405.16300000000001</v>
     <v>393.44</v>
     <v>342.93</v>
-    <v>338.33</v>
+    <v>334.97</v>
     <v>1068079000</v>
     <v>ARM</v>
     <v>ARM HOLDINGS PLC (XNAS:ARM)</v>
-    <v>14787010</v>
+    <v>14885094</v>
     <v>12457415</v>
     <v>2018</v>
   </rv>
@@ -4665,11 +4665,11 @@
     <v>4</v>
     <v>1779.2850000000001</v>
     <v>683.48</v>
-    <v>1.8173999999999999</v>
+    <v>1.806</v>
     <v>-115.73</v>
-    <v>1.078E-3</v>
+    <v>-5.4819999999999999E-4</v>
     <v>-6.5850000000000006E-2</v>
-    <v>1.77</v>
+    <v>-0.9</v>
     <v>USD</v>
     <v>ASML Holding N.V. is a holding company based in the Netherlands. The Company operates through its subsidiaries in the Netherlands, the United States, Italy, France, Germany, the United Kingdom, Ireland, Belgium, South Korea, Taiwan, Singapore, China, Hong Kong, Japan, Malaysia and Israel. The Company operates through one business segment which is engage in development, production, marketing, sales, upgrading and servicing of advanced semiconductor equipment systems, consisting of lithography, metrology and inspection systems. The Company offers TWINSCAN systems, equipped with lithography system with a mercury lamp as light source (i-line), Krypton Fluoride (KrF) and Argon Fluoride (ArF) light sources for processing wafers for manufacturing environments for which imaging at a small resolution is required. TWINSCAN systems also include immersion lithography systems (TWINSCAN immersion systems).</v>
     <v>43882</v>
@@ -4680,21 +4680,21 @@
     <v>1705.4791</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46178.903399675779</v>
+    <v>46178.999889490624</v>
     <v>45</v>
     <v>1638.38</v>
     <v>637237604998</v>
     <v>ASML Holding NV</v>
     <v>ASML Holding NV</v>
     <v>1685.36</v>
-    <v>60.421500000000002</v>
+    <v>56.442799999999998</v>
     <v>1757.47</v>
     <v>1641.74</v>
-    <v>1643.51</v>
+    <v>1640.84</v>
     <v>388147700</v>
     <v>ASML</v>
     <v>ASML Holding NV (XNAS:ASML)</v>
-    <v>2730988</v>
+    <v>2744563</v>
     <v>1611416</v>
     <v>1994</v>
   </rv>
@@ -4719,11 +4719,11 @@
     <v>4</v>
     <v>495</v>
     <v>241.11</v>
-    <v>1.4407000000000001</v>
+    <v>1.4705999999999999</v>
     <v>-33.18</v>
-    <v>1.6850000000000001E-3</v>
+    <v>-1.8410000000000002E-3</v>
     <v>-7.9205999999999999E-2</v>
-    <v>0.65</v>
+    <v>-0.71</v>
     <v>USD</v>
     <v>Broadcom Inc. is a global technology firm that designs, develops, and supplies a range of semiconductors, enterprise software and security solutions. The Company operates through two segments: semiconductor solutions and infrastructure software. Its semiconductor solutions segment includes all of its product lines and intellectual property (IP) licensing. It provides a variety of radio frequency semiconductor devices, wireless connectivity solutions, custom touch controllers, and inductive charging solutions for mobile applications. Its infrastructure software segment includes its private and hybrid cloud, application development and delivery, software-defined edge, application networking and security, mainframe, distributed and cybersecurity solutions, and its FC SAN business. It provides a portfolio of software solutions that enable customers to plan, develop, automate, manage and secure applications across mainframe, distributed, mobile and cloud platforms.</v>
     <v>33000</v>
@@ -4734,7 +4734,7 @@
     <v>410.5</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46178.90349016172</v>
+    <v>46178.999999513282</v>
     <v>48</v>
     <v>385.59</v>
     <v>1826303487640</v>
@@ -4744,11 +4744,11 @@
     <v>69.777900000000002</v>
     <v>418.91</v>
     <v>385.73</v>
-    <v>386.38</v>
+    <v>385.02</v>
     <v>4734668000</v>
     <v>AVGO</v>
     <v>BROADCOM INC. (XNAS:AVGO)</v>
-    <v>50908163</v>
+    <v>51146089</v>
     <v>24527113</v>
     <v>2018</v>
   </rv>
@@ -4759,25 +4759,25 @@
     <v>https://www.bing.com/financeapi/forcetrigger?t=c4efww&amp;q=XNYS%3aBBAI&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
   </rv>
-  <rv s="1">
+  <rv s="10">
     <v>en-GB</v>
     <v>c4efww</v>
     <v>268435456</v>
     <v>1</v>
     <v>Powered by Refinitiv</v>
-    <v>0</v>
+    <v>19</v>
     <v>BIGBEAR.AI HOLDINGS, INC. (XNYS:BBAI)</v>
     <v>2</v>
-    <v>3</v>
+    <v>20</v>
     <v>Finance</v>
     <v>4</v>
     <v>9.39</v>
     <v>3.01</v>
-    <v>3.089</v>
+    <v>3.1166</v>
     <v>-0.56999999999999995</v>
-    <v>7.0950000000000006E-3</v>
+    <v>-7.0709999999999992E-3</v>
     <v>-0.11949700000000001</v>
-    <v>2.98E-2</v>
+    <v>-2.9700000000000001E-2</v>
     <v>USD</v>
     <v>BigBear.ai Holdings, Inc. operates as a specialized provider of artificial intelligence (AI) technology. The Company provides decision intelligence solutions for supply chains and logistics, enterprise operations, manned-unmanned teaming in autonomous systems, and cybersecurity. Its solutions include AI orchestration and sensor function, digital identity management, computer vision, cybersecurity, predictive intelligence, modeling &amp; simulation, enterprise automation and professional services. It offers Trueface, which performs one-to-many (1:N) facial matches with real-time photos, delivering identity verification. It also offers veriScan, which captures and transmits real-time photos into a biometric matching service supporting access control and biometric boarding/bag tags. The Company serves homeland &amp; border security, defense, intelligence, manufacturing &amp; suppy chain, travel and trade industries.</v>
     <v>579</v>
@@ -4788,21 +4788,20 @@
     <v>4.67</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46178.903381064061</v>
+    <v>46178.999910971877</v>
     <v>51</v>
     <v>4.1100000000000003</v>
     <v>2011587900</v>
     <v>BIGBEAR.AI HOLDINGS, INC.</v>
     <v>BIGBEAR.AI HOLDINGS, INC.</v>
     <v>4.62</v>
-    <v>0</v>
     <v>4.7699999999999996</v>
     <v>4.2</v>
-    <v>4.2298</v>
+    <v>4.1703000000000001</v>
     <v>478949500</v>
     <v>BBAI</v>
     <v>BIGBEAR.AI HOLDINGS, INC. (XNYS:BBAI)</v>
-    <v>37855966</v>
+    <v>38122015</v>
     <v>49035400</v>
     <v>2020</v>
   </rv>
@@ -4813,21 +4812,21 @@
     <v>https://www.bing.com/financeapi/forcetrigger?t=af5lim&amp;q=XFRA%3aBMW&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
   </rv>
-  <rv s="10">
+  <rv s="11">
     <v>en-GB</v>
     <v>af5lim</v>
     <v>268435456</v>
     <v>1</v>
     <v>Powered by Refinitiv</v>
-    <v>19</v>
+    <v>21</v>
     <v>Bayerische Motoren Werke AG (XFRA:BMW)</v>
     <v>2</v>
-    <v>20</v>
+    <v>22</v>
     <v>Finance</v>
-    <v>21</v>
+    <v>23</v>
     <v>115.25</v>
     <v>36.884999999999998</v>
-    <v>0.96250000000000002</v>
+    <v>0.96240000000000003</v>
     <v>-0.08</v>
     <v>-1.1329999999999999E-3</v>
     <v>EUR</v>
@@ -4878,11 +4877,11 @@
     <v>4</v>
     <v>416.69</v>
     <v>262.74900000000002</v>
-    <v>1.1415999999999999</v>
+    <v>1.1416999999999999</v>
     <v>-35.49</v>
-    <v>-7.1370000000000001E-3</v>
+    <v>-5.8220000000000008E-3</v>
     <v>-8.6207999999999993E-2</v>
-    <v>-2.6848999999999998</v>
+    <v>-2.19</v>
     <v>USD</v>
     <v>Cadence Design Systems, Inc. is an electronic systems designing company. The Company applies its Intelligent System Design strategy to deliver software, hardware and intellectual property (IP) that turn design concepts into reality. Its product categories include Core Electronic Design Automation (EDA), Semiconductor IP, and System Design and Analysis (SD&amp;A). Core EDA includes software, hardware, and services used to design and verify a wide variety of semiconductors. The semiconductor IP portfolio includes silicon subsystems, software, and services that are used in semiconductor design. The SD&amp;A category provides solutions and services that enable the design and verification of complete electronic systems, from PCBs to complex system assemblies. Its semiconductors are used in various industries, including automotive, aerospace, biotech, hyperscale and cloud computing, data centers, telecommunications, medical technology, industrial Internet of things, and artificial intelligence (AI).</v>
     <v>13800</v>
@@ -4893,7 +4892,7 @@
     <v>407</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46178.90310594844</v>
+    <v>46178.99911732578</v>
     <v>57</v>
     <v>373.54</v>
     <v>103759221040</v>
@@ -4903,11 +4902,11 @@
     <v>96.107600000000005</v>
     <v>411.68</v>
     <v>376.19</v>
-    <v>373.50510000000003</v>
+    <v>374</v>
     <v>275816000</v>
     <v>CDNS</v>
     <v>CADENCE DESIGN SYSTEMS, INC. (XNAS:CDNS)</v>
-    <v>3518659</v>
+    <v>3520057</v>
     <v>2336395</v>
     <v>1987</v>
   </rv>
@@ -4932,11 +4931,11 @@
     <v>4</v>
     <v>412.7</v>
     <v>243.3</v>
-    <v>1.1014999999999999</v>
+    <v>1.1292</v>
     <v>-9.76</v>
-    <v>-1.2950000000000001E-3</v>
+    <v>-2.4720000000000002E-3</v>
     <v>-3.6886999999999996E-2</v>
-    <v>-0.33</v>
+    <v>-0.63</v>
     <v>USD</v>
     <v>Constellation Energy Corporation is a producer of emissions-free energy and an energy supplier to businesses, homes and public sector customers nationwide. The Company’s nuclear, hydro, wind, and solar generation facilities have the generating capacity to power the equivalent of 27 million homes, providing about 10% of the nation’s clean energy. Its segments include Mid-Atlantic, Midwest, New York, ERCOT, and Other Power Regions. Through its integrated business operations, it sells electricity, natural gas, and other energy-related products and sustainable solutions to various types of customers, including distribution utilities, municipalities, cooperatives, commercial, industrial, public sector, and residential customers in markets across multiple geographic regions. It operates approximately 55 gigawatts of capacity from nuclear, natural gas, geothermal, hydro, wind and solar facilities.</v>
     <v>15291</v>
@@ -4947,7 +4946,7 @@
     <v>261.86500000000001</v>
     <v>Electrical Utilities &amp; IPPs</v>
     <v>Stock</v>
-    <v>46178.90344726797</v>
+    <v>46178.999882233591</v>
     <v>60</v>
     <v>253.68</v>
     <v>91509962660</v>
@@ -4957,11 +4956,11 @@
     <v>22.986699999999999</v>
     <v>264.58999999999997</v>
     <v>254.83</v>
-    <v>254.5</v>
+    <v>254.2</v>
     <v>359102000</v>
     <v>CEG</v>
     <v>CONSTELLATION ENERGY CORPORATION. (XNAS:CEG)</v>
-    <v>4118632</v>
+    <v>4130674</v>
     <v>3928221</v>
     <v>2021</v>
   </rv>
@@ -4972,25 +4971,25 @@
     <v>https://www.bing.com/financeapi/forcetrigger?t=c4s6z2&amp;q=XNAS%3aCRDO&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
   </rv>
-  <rv s="11">
+  <rv s="12">
     <v>en-GB</v>
     <v>c4s6z2</v>
     <v>268435456</v>
     <v>1</v>
     <v>Powered by Refinitiv</v>
-    <v>22</v>
+    <v>24</v>
     <v>Credo Technology Group Holding Ltd (XNAS:CRDO)</v>
     <v>2</v>
-    <v>23</v>
+    <v>25</v>
     <v>Finance</v>
     <v>4</v>
     <v>245.94990000000001</v>
     <v>66.75</v>
-    <v>3.2399</v>
+    <v>3.2572999999999999</v>
     <v>-10.61</v>
-    <v>-4.2529999999999998E-3</v>
+    <v>-1.6869000000000002E-2</v>
     <v>-4.8781999999999999E-2</v>
-    <v>-0.88</v>
+    <v>-3.49</v>
     <v>USD</v>
     <v>Credo Technology Group Holding Ltd is a Cayman Islands-based holding company. The Company delivers high-speed solutions to break bandwidth barriers on every wired connection in the data infrastructure market. It provides high-speed connectivity solutions that deliver improved power efficiency as data rates and corresponding bandwidth requirements increase exponentially throughout the data infrastructure market. Its connectivity solutions are optimized for optical and electrical Ethernet applications, including the emerging 100 gigabits per second (G), 200G, 400G, 800G and the emerging 1.6 terabits per second (T) port markets. Its products are based on its Serializer/Deserializer (SerDes) and Digital Signal Processor (DSP) technologies. Its product families include integrated circuits (ICs) for the optical and line card markets, active electrical cables (AECs) and SerDes Chiplets. The Company’s intellectual property (IP) solutions consist primarily of SerDes IP licensing.</v>
     <v>622</v>
@@ -5001,21 +5000,21 @@
     <v>234.22</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46178.90315803203</v>
+    <v>46178.999983356247</v>
     <v>63</v>
     <v>202.68</v>
     <v>38160839811</v>
     <v>Credo Technology Group Holding Ltd</v>
     <v>Credo Technology Group Holding Ltd</v>
     <v>208.12</v>
-    <v>87.708299999999994</v>
+    <v>83.430099999999996</v>
     <v>217.5</v>
     <v>206.89</v>
-    <v>206.01</v>
+    <v>203.4</v>
     <v>184449900</v>
     <v>CRDO</v>
     <v>Credo Technology Group Holding Ltd (XNAS:CRDO)</v>
-    <v>15599147</v>
+    <v>15917879</v>
     <v>7171883</v>
   </rv>
   <rv s="2">
@@ -5039,11 +5038,11 @@
     <v>4</v>
     <v>276.8</v>
     <v>163.52000000000001</v>
-    <v>1.1515</v>
-    <v>-3.07</v>
-    <v>-2.532E-3</v>
-    <v>-1.6265000000000002E-2</v>
-    <v>-0.47</v>
+    <v>1.1476999999999999</v>
+    <v>-3.09</v>
+    <v>-8.6719999999999992E-3</v>
+    <v>-1.6371E-2</v>
+    <v>-1.61</v>
     <v>USD</v>
     <v>Salesforce, Inc. is a customer relationship management (CRM) technology company. Its artificial intelligence (AI) powered Agentforce 360 Platform offers sales, service, marketing, commerce, collaboration, data management, integration, analytics, and information technology (IT) service solutions. It enables customers to build and deploy digital labor for employees and customers, leveraging autonomous AI agents across business functions. Its service offerings include Agentforce Sales, Agentforce Service, Agentforce 360 Platform, Slack and Others. The Agentforce Sales provides sales capabilities and tools built for organizations across prospecting, sales engagement, team collaboration, sales analytics and AI, sales programs, sales performance, partner management, and revenue and orders. The Agentforce Service provides field service solutions that enable companies to connect service agents, dispatchers and mobile employees through platform to schedule, dispatch and manage jobs.</v>
     <v>83334</v>
@@ -5054,21 +5053,21 @@
     <v>192.51</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46178.903353471876</v>
+    <v>46178.999831515626</v>
     <v>66</v>
     <v>184.83</v>
-    <v>152071920000</v>
+    <v>152055540000</v>
     <v>SALESFORCE, INC.</v>
     <v>SALESFORCE, INC.</v>
     <v>189.8</v>
     <v>21.838000000000001</v>
     <v>188.75</v>
-    <v>185.68</v>
-    <v>185.19</v>
+    <v>185.66</v>
+    <v>184.05</v>
     <v>819000000</v>
     <v>CRM</v>
     <v>SALESFORCE, INC. (XNYS:CRM)</v>
-    <v>13158104</v>
+    <v>13183928</v>
     <v>14868214</v>
     <v>1999</v>
   </rv>
@@ -5093,14 +5092,14 @@
     <v>4</v>
     <v>785.66</v>
     <v>342.72</v>
-    <v>1.2464999999999999</v>
+    <v>1.2632000000000001</v>
     <v>-48.07</v>
-    <v>-4.6129999999999999E-3</v>
+    <v>-8.9899999999999997E-3</v>
     <v>-6.6848000000000005E-2</v>
-    <v>-3.0952000000000002</v>
+    <v>-6.0327999999999999</v>
     <v>USD</v>
-    <v>CrowdStrike Holdings, Inc. is a global cybersecurity company that provides cloud-delivered protection of endpoints, cloud workloads, identity and data. Its Falcon platform is designed for cybersecurity consolidation, purpose-built to stop breaches. The platforms collect and integrate data from across the enterprise, including endpoints, cloud workloads, identities, and third-party sources. It offers 29 cloud modules on its Falcon platform via a software as a service (SaaS) subscription-based model that spans multiple large markets, including corporate endpoint and cloud workload security, managed security services, security and vulnerability management, information technology (IT) operations management, identity protection, next-generation security information and event management (SIEM) and log management, threat intelligence services, data protection, SaaS security posture management, automation and response (SOAR) and artificial intelligence powered workflow automation, and others.</v>
-    <v>10698</v>
+    <v>CrowdStrike Holdings, Inc. is a global cybersecurity company. The Company provides a cloud-native platform for protecting critical areas of enterprise risk - endpoints and cloud workloads, identity, and data. The Company's artificial intelligence (AI)-native CrowdStrike Falcon platform is a cloud-native unified platform built with AI at the core, capable of harnessing security and enterprise data to deliver highly modular solutions through a single lightweight sensor. Using cloud-scale AI, its Security Cloud enriches and correlates cybersecurity events with indicators of attack, threat intelligence, and enterprise data (including data from across endpoints, workloads, identities, DevOps, IT assets, and configurations) to create actionable data, identify shifts in adversary tactics, and automatically prevent threats in real-time across its customer base. It sells its Falcon platform via a partner-first subscription model to organizations of all sizes across multiple industries globally.</v>
+    <v>11157</v>
     <v>Nasdaq Stock Market</v>
     <v>XNAS</v>
     <v>XNAS</v>
@@ -5108,21 +5107,21 @@
     <v>706.22</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46178.903419467184</v>
+    <v>46178.999852626563</v>
     <v>69</v>
     <v>670.1</v>
-    <v>170799082230</v>
+    <v>170818072096</v>
     <v>CROWDSTRIKE HOLDINGS, INC.</v>
     <v>CROWDSTRIKE HOLDINGS, INC.</v>
     <v>696.74</v>
     <v>0</v>
     <v>719.09</v>
     <v>671.02</v>
-    <v>667.9248</v>
-    <v>254536500</v>
+    <v>664.98720000000003</v>
+    <v>254564800</v>
     <v>CRWD</v>
     <v>CROWDSTRIKE HOLDINGS, INC. (XNAS:CRWD)</v>
-    <v>5228185</v>
+    <v>5238819</v>
     <v>3542032</v>
     <v>2011</v>
   </rv>
@@ -5145,9 +5144,9 @@
     <v>63.8</v>
     <v>2.4409999999999998</v>
     <v>-7.64</v>
-    <v>-9.3629999999999998E-3</v>
+    <v>-2.3210999999999999E-2</v>
     <v>-7.0720999999999992E-2</v>
-    <v>-0.94</v>
+    <v>-2.3302</v>
     <v>USD</v>
     <v>CoreWeave, Inc. is a cloud infrastructure technology company. The Company offers the CoreWeave Cloud Platform, which consists of software and cloud services that deliver the automation and efficiency needed to manage complex artificial intelligence (AI) infrastructure. Its CoreWeave Cloud Platform is an integrated solution that is purpose-built for running AI workloads such as model training and inference. Its solutions include infrastructure services, managed software services, and application software services. Its Infrastructure Services provide its customers with access to advanced graphics processing unit (GPU) and central processing unit (CPU) compute, highly performant networking, and storage. Its Managed Software Services include CKS, a flexible virtual private cloud and a bare metal service that runs kubernetes directly on high-performance servers. Its Application Software Services build on top of its infrastructure and managed software services, integrating additional tools.</v>
     <v>2189</v>
@@ -5158,7 +5157,7 @@
     <v>104.8</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46178.903467430471</v>
+    <v>46178.999998159372</v>
     <v>95.540099999999995</v>
     <v>54769812456</v>
     <v>COREWEAVE, INC.</v>
@@ -5167,11 +5166,11 @@
     <v>0</v>
     <v>108.03</v>
     <v>100.39</v>
-    <v>99.45</v>
+    <v>98.059799999999996</v>
     <v>545570400</v>
     <v>CRWV</v>
     <v>COREWEAVE, INC. (XNAS:CRWV)</v>
-    <v>32311434</v>
+    <v>32460769</v>
     <v>29874791</v>
     <v>2017</v>
   </rv>
@@ -5196,11 +5195,11 @@
     <v>4</v>
     <v>130.3656</v>
     <v>63.865000000000002</v>
-    <v>0.998</v>
+    <v>0.99519999999999997</v>
     <v>-8.36</v>
-    <v>-2.4660000000000003E-3</v>
+    <v>-5.0149999999999995E-3</v>
     <v>-6.430799999999999E-2</v>
-    <v>-0.3</v>
+    <v>-0.61</v>
     <v>USD</v>
     <v>Cisco Systems, Inc. designs and sells a range of technologies that power the Internet. The Company is integrating its product portfolios across networking, security, collaboration, applications and cloud. The Company's segments include the Americas; Europe, Middle East, and Africa (EMEA), and Asia Pacific, Japan, and China (APJC). Its Networking product category represents its core networking technologies of switching, routing, wireless, fifth generation (5G), silicon, optics solutions and compute products. Its Security product category consists of its cloud and application security, industrial security, network security, and user and device security offerings. Its Collaboration product category consists of its meetings, collaboration devices, calling, contact center and platform as a service (CPaaS) offering. Its Observability product category consists of its full stack observability offerings.</v>
     <v>86200</v>
@@ -5211,21 +5210,21 @@
     <v>128.84</v>
     <v>Communications &amp; Networking</v>
     <v>Stock</v>
-    <v>46178.903468298435</v>
+    <v>46178.999662777343</v>
     <v>74</v>
     <v>121.55</v>
     <v>479436153400</v>
     <v>CISCO SYSTEMS, INC.</v>
     <v>CISCO SYSTEMS, INC.</v>
     <v>128.66</v>
-    <v>43.319600000000001</v>
+    <v>40.533200000000001</v>
     <v>130</v>
     <v>121.64</v>
-    <v>121.34</v>
+    <v>121.03</v>
     <v>3941435000</v>
     <v>CSCO</v>
     <v>CISCO SYSTEMS, INC. (XNAS:CSCO)</v>
-    <v>33139415</v>
+    <v>33169341</v>
     <v>27650547</v>
     <v>2021</v>
   </rv>
@@ -5250,11 +5249,11 @@
     <v>4</v>
     <v>278.70499999999998</v>
     <v>98.010099999999994</v>
-    <v>1.5549999999999999</v>
+    <v>1.5597000000000001</v>
     <v>-9.49</v>
-    <v>-1.3284000000000001E-2</v>
+    <v>-1.149E-2</v>
     <v>-3.8956999999999999E-2</v>
-    <v>-3.1099000000000001</v>
+    <v>-2.69</v>
     <v>USD</v>
     <v>Datadog Inc provides an AI-powered observability and security platform for cloud applications. Its Software as a Service (SaaS) platform integrates and automates infrastructure monitoring, application performance monitoring, log management, user experience monitoring, cloud security and service management. Its proprietary platform combines the power of metrics, traces, logs, user sessions, security signals, and other data from a single agent and over 1,000 integrations to provide a unified view of infrastructure, application performance and real-time events impacting performance. Its solutions include built for dynamic cloud and hybrid infrastructures, simple but not simplistic, integrated data platform, built for collaboration, cloud-agnostic, ubiquitous, and integrates with its customers complex environments. Its platform is used by industries to enable digital transformation and cloud migration, and drive collaboration among development, operations, security and business teams.</v>
     <v>8100</v>
@@ -5265,23 +5264,23 @@
     <v>241.61</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46178.902660046093</v>
+    <v>46178.99972727969</v>
     <v>77</v>
     <v>230.57</v>
     <v>83333842422</v>
     <v>DATADOG, INC.</v>
     <v>DATADOG, INC.</v>
     <v>237.4</v>
-    <v>617.20889999999997</v>
+    <v>593.13400000000001</v>
     <v>243.6</v>
     <v>234.11</v>
-    <v>231.0001</v>
+    <v>231.42</v>
     <v>355960200</v>
     <v>DDOG</v>
     <v>DATADOG, INC. (XNAS:DDOG)</v>
-    <v>6787014</v>
+    <v>6792767</v>
     <v>7441402</v>
-    <v>2026</v>
+    <v>2010</v>
   </rv>
   <rv s="2">
     <v>78</v>
@@ -5304,11 +5303,11 @@
     <v>4</v>
     <v>469.47</v>
     <v>109.17</v>
-    <v>1.3033999999999999</v>
-    <v>-27.41</v>
-    <v>-7.0740000000000004E-3</v>
-    <v>-6.4945000000000003E-2</v>
-    <v>-2.79</v>
+    <v>1.319</v>
+    <v>-27.66</v>
+    <v>-1.5507E-2</v>
+    <v>-6.5536999999999998E-2</v>
+    <v>-6.1157000000000004</v>
     <v>USD</v>
     <v>Dell Technologies Inc. is engaged in designing, developing, manufacturing, marketing, selling, and supporting a wide range of comprehensive and integrated solutions, products, and services. The Company operates through two segments: Infrastructure Solutions Group (ISG) and Client Solutions Group (CSG). Its ISG segment enables the Company’s customer’s digital transformation with solutions that address artificial intelligence (AI), machine learning, data analytics, and multi cloud environments. Its comprehensive storage portfolio includes modern and traditional storage solutions, including all-flash arrays, scale-out file, object platforms, hyper-converged infrastructure, and software-defined storage. Its CSG segment offers branded personal computers (PCs) including notebooks, desktops, and workstations and branded peripherals that include displays, docking stations, keyboards, mice, and webcam and audio devices, as well as third-party software and peripherals.</v>
     <v>97000</v>
@@ -5319,21 +5318,21 @@
     <v>412.9</v>
     <v>Computers, Phones &amp; Household Electronics</v>
     <v>Stock</v>
-    <v>46178.903500323438</v>
+    <v>46178.999995555467</v>
     <v>80</v>
     <v>386.27499999999998</v>
-    <v>256345633912</v>
+    <v>256183241837</v>
     <v>DELL TECHNOLOGIES INC.</v>
     <v>DELL TECHNOLOGIES INC.</v>
     <v>405.77</v>
-    <v>33.516100000000002</v>
+    <v>31.319400000000002</v>
     <v>422.05</v>
-    <v>394.64</v>
-    <v>391.6</v>
+    <v>394.39</v>
+    <v>388.27429999999998</v>
     <v>649568300</v>
     <v>DELL</v>
     <v>DELL TECHNOLOGIES INC. (XNYS:DELL)</v>
-    <v>10946010</v>
+    <v>10990345</v>
     <v>10485112</v>
     <v>2013</v>
   </rv>
@@ -5374,11 +5373,11 @@
     <v>4</v>
     <v>124.69</v>
     <v>92.185000000000002</v>
-    <v>1.3942000000000001</v>
-    <v>0.4</v>
-    <v>-1.0030000000000001E-4</v>
-    <v>4.0270000000000002E-3</v>
-    <v>-0.01</v>
+    <v>1.3836999999999999</v>
+    <v>0.37</v>
+    <v>-9.0160000000000001E-4</v>
+    <v>3.725E-3</v>
+    <v>-8.9899999999999994E-2</v>
     <v>USD</v>
     <v>The Walt Disney Company is a diversified worldwide entertainment company. The Company's segments include Entertainment, Sports and Experiences. The Entertainment segment generally encompasses its non-sports focused global film and episodic content production and distribution activities. The lines of business within the Entertainment segment along with their business activities include Linear Networks, Direct-to-Consumer, and Content Sales/Licensing. The Sports segment encompasses its sports-focused global television and direct-to-consumer (DTC) video streaming content production and distribution activities. The lines of business within the Sports segment include ESPN and Star. The Experiences segment includes Parks and Experiences and Consumer Products. Parks and Experiences consists of Walt Disney World Resort in Florida, Disneyland Resort in California, Disney Cruise Line, and others. Consumer Products includes licensing of its trade names, characters, visual, literary and other IP.</v>
     <v>231000</v>
@@ -5390,21 +5389,21 @@
     <v>85</v>
     <v>Media &amp; Publishing</v>
     <v>Stock</v>
-    <v>46178.903126249999</v>
+    <v>46178.999763101565</v>
     <v>86</v>
     <v>99.088999999999999</v>
-    <v>173199607140</v>
+    <v>173147511810</v>
     <v>THE WALT DISNEY COMPANY</v>
     <v>THE WALT DISNEY COMPANY</v>
     <v>99.68</v>
     <v>15.8965</v>
     <v>99.34</v>
-    <v>99.74</v>
-    <v>99.7</v>
+    <v>99.71</v>
+    <v>99.620099999999994</v>
     <v>1736511000</v>
     <v>DIS</v>
     <v>THE WALT DISNEY COMPANY (XNYS:DIS)</v>
-    <v>9495916</v>
+    <v>9501571</v>
     <v>9257497</v>
     <v>2018</v>
   </rv>
@@ -5429,10 +5428,10 @@
     <v>4</v>
     <v>57.55</v>
     <v>31.635000000000002</v>
-    <v>0.73829999999999996</v>
-    <v>-1.05</v>
+    <v>0.73470000000000002</v>
+    <v>-1.06</v>
     <v>-9.7179999999999992E-3</v>
-    <v>-2.4277000000000003E-2</v>
+    <v>-2.4509E-2</v>
     <v>-0.41</v>
     <v>USD</v>
     <v>Dynatrace, Inc. is an artificial intelligence (AI)-powered observability platform. It is advancing observability for digital businesses and transforming the complexity of modern digital ecosystems into business assets. It enables organizations to analyze and automate. Its platform combines broad and deep observability, continuous runtime application security, and advanced AI to support information technology (IT) operations, development, security, and business teams, enabling organizations to optimize cloud and IT operations, accelerate secure software delivery, and improve digital performance. Its platform's solutions include infrastructure observability, application observability, AI observability, digital experience, business analytics, software delivery, threat observability, application security, and log management. Its application security detects, analyses, and remediates runtime application vulnerabilities and attacks in real time.</v>
@@ -5444,21 +5443,21 @@
     <v>43.77</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46178.899437337503</v>
+    <v>46178.987539606249</v>
     <v>89</v>
     <v>41.91</v>
-    <v>12300274540</v>
+    <v>12297359783</v>
     <v>DYNATRACE, INC.</v>
     <v>DYNATRACE, INC.</v>
     <v>43.3</v>
-    <v>80.721900000000005</v>
+    <v>78.742099999999994</v>
     <v>43.25</v>
-    <v>42.2</v>
+    <v>42.19</v>
     <v>41.78</v>
     <v>291475700</v>
     <v>DT</v>
     <v>DYNATRACE, INC. (XNYS:DT)</v>
-    <v>4740219</v>
+    <v>4743799</v>
     <v>6445716</v>
     <v>2014</v>
   </rv>
@@ -5483,11 +5482,11 @@
     <v>4</v>
     <v>16.489999999999998</v>
     <v>4.6150000000000002</v>
-    <v>2.2103999999999999</v>
+    <v>2.2221000000000002</v>
     <v>-1.08</v>
-    <v>1.374E-3</v>
+    <v>1.5109999999999998E-2</v>
     <v>-0.129187</v>
-    <v>0.01</v>
+    <v>0.11</v>
     <v>USD</v>
     <v>Enovix Corporation is a high-performance battery company. The Company is focused on designing, developing, manufacturing, and commercializing Lithium-ion, or Li-ion, batteries, including silicon-anode architectures, for smartphones, smart eyewear, defense, industrial and emerging edge artificial intelligence (AI) applications. Its silicon-anode battery architecture enables energy density and performance relative to conventional battery cells, particularly in space-constrained devices. It focuses on developing a battery architecture that allows the use of active silicon and no graphite in the battery's anode, which is the negative electrode that stores lithium ions when a battery is charged. Its AI-1 battery platform is architected as a unified silicon-anode platform designed to address the high-performance consumer electronics and defense applications. The AI-1 platform is designed to support AI-enabled smartphones and smart eyewear, as well as other edge-AI devices.</v>
     <v>664</v>
@@ -5498,7 +5497,7 @@
     <v>8.23</v>
     <v>Machinery, Equipment &amp; Components</v>
     <v>Stock</v>
-    <v>46178.90348910859</v>
+    <v>46178.998154142966</v>
     <v>92</v>
     <v>7.1</v>
     <v>1588156752</v>
@@ -5508,11 +5507,11 @@
     <v>0</v>
     <v>8.36</v>
     <v>7.28</v>
-    <v>7.29</v>
+    <v>7.39</v>
     <v>218153400</v>
     <v>ENVX</v>
     <v>Enovix Corporation (XNAS:ENVX)</v>
-    <v>8497863</v>
+    <v>8551995</v>
     <v>8283580</v>
     <v>2020</v>
   </rv>
@@ -5537,11 +5536,11 @@
     <v>4</v>
     <v>435.43</v>
     <v>311.91500000000002</v>
-    <v>1.1893</v>
-    <v>-22.61</v>
-    <v>-5.6879999999999995E-3</v>
-    <v>-5.4012000000000004E-2</v>
-    <v>-2.2521</v>
+    <v>1.1889000000000001</v>
+    <v>-22.67</v>
+    <v>-5.1520000000000003E-3</v>
+    <v>-5.4154999999999995E-2</v>
+    <v>-2.04</v>
     <v>USD</v>
     <v>Eaton Corporation plc is an intelligent power management company. Its Electrical Americas segment consists of electrical components, industrial components, power distribution and assemblies, residential products, circuit protection, utility power distribution, wiring devices and others. The Electrical Global segment consists of electrical components, industrial components, power distribution and assemblies, single phase and three phase power quality, and services. The Aerospace segment is a global supplier of aerospace fuel, hydraulics, and pneumatic systems for commercial and military use and filtration systems for industrial applications. The Vehicle segment designs, manufactures, markets, and supplies drivetrain, powertrain systems and critical components. The eMobility segment designs, manufactures, markets, and supplies mechanical, electrical, and electronic components and systems. The Company is also engaged in providing thermal monitoring for critical electrical equipment.</v>
     <v>97000</v>
@@ -5552,21 +5551,21 @@
     <v>410.61</v>
     <v>Machinery, Equipment &amp; Components</v>
     <v>Stock</v>
-    <v>46178.900008078126</v>
+    <v>46178.999700774999</v>
     <v>95</v>
     <v>393.17</v>
-    <v>153766800000</v>
+    <v>153743502000</v>
     <v>EATON CORPORATION PUBLIC LIMITED COMPANY</v>
     <v>EATON CORPORATION PUBLIC LIMITED COMPANY</v>
     <v>408.55</v>
-    <v>40.924599999999998</v>
+    <v>38.708399999999997</v>
     <v>418.61</v>
-    <v>396</v>
-    <v>393.68790000000001</v>
+    <v>395.94</v>
+    <v>393.9</v>
     <v>388300000</v>
     <v>ETN</v>
     <v>EATON CORPORATION PUBLIC LIMITED COMPANY (XNYS:ETN)</v>
-    <v>2535660</v>
+    <v>2538045</v>
     <v>2880792</v>
     <v>2012</v>
   </rv>
@@ -5591,11 +5590,11 @@
     <v>4</v>
     <v>30.38</v>
     <v>13.29</v>
-    <v>1.4453</v>
+    <v>1.4363999999999999</v>
     <v>-0.94</v>
-    <v>-1.0204E-2</v>
+    <v>0</v>
     <v>-3.8429999999999999E-2</v>
-    <v>-0.24</v>
+    <v>0</v>
     <v>USD</v>
     <v>Five9, Inc. helps organizations to create hyper-personalized artificial intelligence (AI)-driven customer experiences. The Company's Intelligent CX Platform, powered by its Five9 Genius AI suite, delivers a comprehensive suite of applications that enable customer service, sales, and marketing functions. It delivers a comprehensive, end-to-end cloud software solution for contact centers. Comprised of its Intelligent CX Platform and AI capabilities, including agentic AI agents, Agent Assist, Workflow Automation (WFA), AI Insights, AI Summaries, Workforce Engagement Management (WEM), and Revenue Execution, its solution allows simultaneous management and optimization of customer interactions across voice, chat, email, web, social media and mobile channels, either directly or through its application programming interfaces (APIs). The Company's agent interface is a browser-based design that provides visualization of customer profiles, context and cross-channel history.</v>
     <v>2910</v>
@@ -5606,7 +5605,7 @@
     <v>24.94</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46178.893552719528</v>
+    <v>46178.992053853908</v>
     <v>98</v>
     <v>22.600100000000001</v>
     <v>1800785044</v>
@@ -5616,11 +5615,11 @@
     <v>37.090400000000002</v>
     <v>24.46</v>
     <v>23.52</v>
-    <v>23.28</v>
+    <v>23.52</v>
     <v>76563990</v>
     <v>FIVN</v>
     <v>FIVE9, INC. (XNAS:FIVN)</v>
-    <v>3371039</v>
+    <v>3372747</v>
     <v>4442698</v>
     <v>2001</v>
   </rv>
@@ -5645,11 +5644,11 @@
     <v>4</v>
     <v>150.07</v>
     <v>70.12</v>
-    <v>1.1027</v>
+    <v>1.0900000000000001</v>
     <v>-4.99</v>
-    <v>-1.073E-2</v>
+    <v>-6.0819999999999997E-3</v>
     <v>-3.3340000000000002E-2</v>
-    <v>-1.5524</v>
+    <v>-0.88</v>
     <v>USD</v>
     <v>Fortinet, Inc. is engaged in cybersecurity, driving the convergence of networking and security. The Company's integrated platform, Fortinet Security Fabric, spans secure networking, unified secure access service edge (SASE), and artificial intelligence (AI)-driven security operations (SecOps). Its products and services include FortiOS, FortiASIC, FortiCloud, FortiAI, FortiEndpoint, and OT Security. The FortiGuard Labs is a cybersecurity threat intelligence and research organization comprised of experienced threat hunters, researchers, analysts, engineers, and data scientists who develop and utilize machine learning and AI technologies. FortiGuard and Other Security Services is an AI-powered security that is integrated as part of the Fortinet Security Fabric to deliver detection and enforcement across the entire attack surface. FortiCare Technical Support Service is a technical support service which provides customers with access to operations and maintenance of Fortinet solutions.</v>
     <v>15311</v>
@@ -5660,7 +5659,7 @@
     <v>149.05000000000001</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46178.903107765625</v>
+    <v>46178.999772974217</v>
     <v>101</v>
     <v>143.45500000000001</v>
     <v>105999570512</v>
@@ -5670,11 +5669,11 @@
     <v>57.8245</v>
     <v>149.66999999999999</v>
     <v>144.68</v>
-    <v>143.1276</v>
+    <v>143.80000000000001</v>
     <v>732648400</v>
     <v>FTNT</v>
     <v>FORTINET, INC. (XNAS:FTNT)</v>
-    <v>7119075</v>
+    <v>7122674</v>
     <v>6701223</v>
     <v>2000</v>
   </rv>
@@ -5701,9 +5700,9 @@
     <v>163.33000000000001</v>
     <v>1.2397</v>
     <v>-3.51</v>
-    <v>-4.8120000000000003E-3</v>
+    <v>-1.1346E-2</v>
     <v>-9.5049999999999996E-3</v>
-    <v>-1.76</v>
+    <v>-4.1500000000000004</v>
     <v>USD</v>
     <v>Alphabet Inc. is a holding company. The Company's segments include Google Services, Google Cloud, and Other Bets. The Google Services segment includes products and services such as ads, Android, Chrome, devices, Google Maps, Google Play, Search, and YouTube. The Google Cloud segment includes infrastructure and platform services, collaboration tools, and other services for enterprise customers. Its Other Bets segment is engaged in the sale of healthcare-related services and Internet services. Its Google Cloud provides enterprise-ready cloud services, including Google Cloud Platform and Google Workspace. Google Cloud Platform provides access to solutions such as artificial intelligence (AI) offerings, including its AI infrastructure, Vertex AI platform, and Gemini for Google Cloud; cybersecurity, and data and analytics. Google Workspace includes cloud-based communication and collaboration tools for enterprises, such as Calendar, Gmail, Docs, Drive, and Meet.</v>
     <v>194668</v>
@@ -5714,21 +5713,21 @@
     <v>369.2</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46178.903474316408</v>
+    <v>46178.999992812503</v>
     <v>104</v>
     <v>361.63</v>
-    <v>4431548160000</v>
+    <v>4452967065600</v>
     <v>ALPHABET INC.</v>
     <v>ALPHABET INC.</v>
     <v>363.38</v>
     <v>28.201599999999999</v>
     <v>369.27</v>
     <v>365.76</v>
-    <v>364</v>
-    <v>12116000000</v>
+    <v>361.61</v>
+    <v>12174560000</v>
     <v>GOOG</v>
     <v>ALPHABET INC. (XNAS:GOOG)</v>
-    <v>23299314</v>
+    <v>23411519</v>
     <v>22670483</v>
     <v>2015</v>
   </rv>
@@ -5753,11 +5752,11 @@
     <v>4</v>
     <v>153.85990000000001</v>
     <v>63.515000000000001</v>
-    <v>2.3544999999999998</v>
+    <v>2.3706999999999998</v>
     <v>-5.86</v>
-    <v>-2.6679999999999998E-3</v>
+    <v>-1.3217000000000001E-2</v>
     <v>-6.6341999999999998E-2</v>
-    <v>-0.22</v>
+    <v>-1.0900000000000001</v>
     <v>USD</v>
     <v>Robinhood Markets, Inc. is focused on providing financial services offering retail brokerage, crypto, advisory, digital banking services, and private markets access to investors. Its offerings include Brokerage, Robinhood Crypto, Custody, Robinhood Wallet, Robinhood Gold, and Robinhood Gold Card. Brokerage services include investing, options trading, fractional trading, recurring investment, access to investing on margin, fully paid securities lending, cash sweep, instant withdrawals, Robinhood retirement, 24-hour market, joint investing accounts, and event contracts. It also offers a variety of ways for its customers to grow their financial knowledge, including Robinhood Learn, In-App Education, Newsfeeds, Sherwood Snacks, and Crypto Learn and Earn. It also operates regulated crypto platforms including Bitbuy and Coinsquare. Its self-clearing system, order routing system, data platform, and other back-end infrastructure allow its customers to focus on investing, saving and spending.</v>
     <v>2900</v>
@@ -5768,7 +5767,7 @@
     <v>87.329899999999995</v>
     <v>Financial Technology (Fintech) &amp; Infrastructure</v>
     <v>Stock</v>
-    <v>46178.903469803125</v>
+    <v>46178.999968020311</v>
     <v>107</v>
     <v>79.489999999999995</v>
     <v>74264655597</v>
@@ -5778,11 +5777,11 @@
     <v>49.137700000000002</v>
     <v>88.33</v>
     <v>82.47</v>
-    <v>82.25</v>
+    <v>81.38</v>
     <v>900505100</v>
     <v>HOOD</v>
     <v>ROBINHOOD MARKETS, INC. (XNAS:HOOD)</v>
-    <v>35758006</v>
+    <v>35905094</v>
     <v>26208893</v>
     <v>2013</v>
   </rv>
@@ -5823,11 +5822,11 @@
     <v>4</v>
     <v>332.46</v>
     <v>212.34</v>
-    <v>0.65800000000000003</v>
-    <v>-16.9191</v>
-    <v>-9.9710000000000007E-3</v>
-    <v>-5.6066000000000005E-2</v>
-    <v>-2.84</v>
+    <v>0.66869999999999996</v>
+    <v>-16.93</v>
+    <v>-1.4359E-2</v>
+    <v>-5.6101999999999999E-2</v>
+    <v>-4.09</v>
     <v>USD</v>
     <v>International Business Machines Corporation is a provider of global hybrid cloud and artificial intelligence (AI) and consulting expertise. The Company’s segments include Software, Consulting, Infrastructure and Financing. The Software segment includes hybrid cloud and AI platforms, which allow clients to realize their digital and AI transformations across the applications, data, and environments in which they operate. The Consulting segment focuses on integrating skills on strategy, experience, technology and operations by domain and industry. The Infrastructure segment is focused on the hybrid cloud infrastructure market, providing on-premises and cloud-based server and storage solutions. In addition, it offers a portfolio of life-cycle services for hybrid cloud infrastructure deployment. The Financing segment provides client and commercial financing, facilitating its clients’ acquisition of hardware, software and services. It helps clients in more than 175 countries.</v>
     <v>286800</v>
@@ -5839,21 +5838,21 @@
     <v>112</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46178.903447187498</v>
+    <v>46178.999949687503</v>
     <v>113</v>
     <v>281.07010000000002</v>
-    <v>267727173601</v>
+    <v>267716928851</v>
     <v>INTERNATIONAL BUSINESS MACHINES CORPORATION</v>
     <v>INTERNATIONAL BUSINESS MACHINES CORPORATION</v>
     <v>300</v>
     <v>24.1493</v>
     <v>301.77</v>
-    <v>284.85090000000002</v>
-    <v>282</v>
+    <v>284.83999999999997</v>
+    <v>280.75</v>
     <v>939885300</v>
     <v>IBM</v>
     <v>INTERNATIONAL BUSINESS MACHINES CORPORATION (XNYS:IBM)</v>
-    <v>12469379</v>
+    <v>12509480</v>
     <v>10573417</v>
     <v>1911</v>
   </rv>
@@ -5878,11 +5877,11 @@
     <v>4</v>
     <v>125.14</v>
     <v>34.2301</v>
-    <v>2.8271999999999999</v>
+    <v>2.8405999999999998</v>
     <v>-19.53</v>
-    <v>-9.5130000000000006E-3</v>
+    <v>-1.4416E-2</v>
     <v>-0.16074100000000002</v>
-    <v>-0.97</v>
+    <v>-1.47</v>
     <v>USD</v>
     <v>Innodata Inc. is a global data engineering company. It provides a range of transferable solutions, platforms, and services for generative artificial intelligence (AI)/AI builders and adopters. Its Digital Data Solutions segment provides AI data preparation services, collecting or creating training data, annotating training data, and training AI algorithms for its customers, and AI model deployment and integration. It also provides a range of data engineering support services. Its Synodex segment provides an industry platform that transforms medical records into useable digital data organized in accordance with its proprietary data models or customer data models. Its Agility segment provides an industry platform that provides marketing communications and public relations professionals with the ability to target and distribute content to journalists and social media influencers worldwide and to monitor and analyze global news channels (print, Web, radio and TV) and social media channels.</v>
     <v>10020</v>
@@ -5893,7 +5892,7 @@
     <v>119.2</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46178.902878483597</v>
+    <v>46178.99981981406</v>
     <v>116</v>
     <v>100.19</v>
     <v>1490374656</v>
@@ -5903,11 +5902,11 @@
     <v>109.3186</v>
     <v>121.5</v>
     <v>101.97</v>
-    <v>101</v>
+    <v>100.5</v>
     <v>32655360</v>
     <v>INOD</v>
     <v>INNODATA INC. (XNAS:INOD)</v>
-    <v>2115570</v>
+    <v>2127529</v>
     <v>3083448</v>
     <v>1988</v>
   </rv>
@@ -5932,11 +5931,11 @@
     <v>4</v>
     <v>132.75</v>
     <v>18.965</v>
-    <v>2.2303000000000002</v>
+    <v>2.2513000000000001</v>
     <v>-12.61</v>
-    <v>-1.2806E-2</v>
+    <v>-2.2638999999999999E-2</v>
     <v>-0.11281100000000001</v>
-    <v>-1.27</v>
+    <v>-2.2450999999999999</v>
     <v>USD</v>
     <v>Intel Corporation is a global designer and manufacturer of semiconductor products. The Company's segments include Intel Products, Intel Foundry, and All Other. Its Intel Products comprise Client Computing Group (CCG) and Data Center and AI (DCAI). CCG delivers platforms and processors that power PCs and edge devices, enabling enhanced performance, connectivity and user experience for consumer and commercial markets with capabilities that also support retail, industrial robotics and AI ecosystems at the edge. DCAI delivers workload-optimized solutions based upon its x86 architecture for data centers, including CPUs, AI accelerators, NICs, IPUs and custom ASICs, enabling performance and scalability for cloud, enterprise, telecommunication and HPC environments. The Intel Foundry segment comprises technology development, manufacturing and foundry services, developing new semiconductor process technologies and advanced packaging technologies. All Other segments include Mobileye and Other.</v>
     <v>83200</v>
@@ -5947,7 +5946,7 @@
     <v>106.48</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46178.903523587498</v>
+    <v>46178.999997430466</v>
     <v>119</v>
     <v>98.33</v>
     <v>498428420000</v>
@@ -5957,11 +5956,11 @@
     <v>0</v>
     <v>111.78</v>
     <v>99.17</v>
-    <v>97.9</v>
+    <v>96.924899999999994</v>
     <v>5026000000</v>
     <v>INTC</v>
     <v>INTEL CORPORATION (XNAS:INTC)</v>
-    <v>144184718</v>
+    <v>145209405</v>
     <v>137584440</v>
     <v>1989</v>
   </rv>
@@ -5986,11 +5985,11 @@
     <v>4</v>
     <v>84.64</v>
     <v>25.89</v>
-    <v>3.1943999999999999</v>
+    <v>3.2339000000000002</v>
     <v>-8.8800000000000008</v>
-    <v>-1.9560000000000001E-2</v>
+    <v>-2.6945999999999998E-2</v>
     <v>-0.135242</v>
-    <v>-1.1106</v>
+    <v>-1.53</v>
     <v>USD</v>
     <v>IonQ, Inc. is engaged in the quantum computing and networking industry, delivering high-performance systems capable of solving complex commercial and research use cases. Its generation quantum computers, IonQ Forte and IonQ Forte Enterprise, are cutting-edge systems, boasting 36 algorithmic qubits. It sells specialized quantum computing and networking hardware together with related maintenance and support. It also sells access to several quantum computers of various qubit capacities and is in the process of researching and developing technologies for quantum computers with increasing computational capabilities. It makes access to its quantum computers available via three cloud platforms, Amazon Web Services' (AWS) Amazon Braket, Microsoft's Azure Quantum and Google's Cloud Marketplace, and also to select customers via its own cloud service. Its product portfolio also includes quantum key distribution (QKD) systems, quantum random number generators (QRNGs), and single-photon detectors.</v>
     <v>1132</v>
@@ -6001,21 +6000,21 @@
     <v>63.79</v>
     <v>Computers, Phones &amp; Household Electronics</v>
     <v>Stock</v>
-    <v>46178.903377546092</v>
+    <v>46178.999946029689</v>
     <v>122</v>
     <v>55.84</v>
     <v>21194270600</v>
     <v>IONQ, INC.</v>
     <v>IONQ, INC.</v>
     <v>63.51</v>
-    <v>1120.2860000000001</v>
+    <v>968.94200000000001</v>
     <v>65.66</v>
     <v>56.78</v>
-    <v>55.669400000000003</v>
+    <v>55.25</v>
     <v>373270000</v>
     <v>IONQ</v>
     <v>IONQ, INC. (XNYS:IONQ)</v>
-    <v>31840107</v>
+    <v>32124857</v>
     <v>34451097</v>
     <v>2020</v>
   </rv>
@@ -6040,11 +6039,11 @@
     <v>4</v>
     <v>76.87</v>
     <v>8.82</v>
-    <v>4.2358000000000002</v>
+    <v>4.2521000000000004</v>
     <v>-7.51</v>
-    <v>-2.7600000000000003E-3</v>
+    <v>-2.0423E-2</v>
     <v>-0.121403</v>
-    <v>-0.15</v>
+    <v>-1.1100000000000001</v>
     <v>USD</v>
     <v>IREN Limited is an Australia-based company, which owns and operates data centers powered by 100% renewable energy. Its facilities are optimized for Bitcoin mining, artificial intelligence (AI) cloud services, and other power-dense compute. Its data center mining facilities are in Canal Flats, Mackenzie, Prince George and Childress. Bitcoin Mining provides security to the Bitcoin network. Al Cloud Services provides cloud compute to Al customers, approximately 1,896 NVIDIA H100 and H200 GPUs. Its Canal Flats facility is in the Canadian Rockies, 100 kilometers (km) from Cranbrook regional airport and 500km east of Vancouver. Its facility is in Prince George, the city in northern British Columbia, located 500 km north of Vancouver. Its facility is located in Childress County, Texas, over 250 miles northwest of Dallas and in close proximity to multiple wind and solar generating facilities in the region. Its Childress operations comprise 200 Mega Watt of operating data centers.</v>
     <v>257</v>
@@ -6055,7 +6054,7 @@
     <v>59.31</v>
     <v>Financial Technology (Fintech) &amp; Infrastructure</v>
     <v>Stock</v>
-    <v>46178.903505508591</v>
+    <v>46178.999985601564</v>
     <v>125</v>
     <v>51.04</v>
     <v>19423532345</v>
@@ -6065,11 +6064,11 @@
     <v>134.85059999999999</v>
     <v>61.86</v>
     <v>54.35</v>
-    <v>54.2</v>
+    <v>53.24</v>
     <v>357378700</v>
     <v>IREN</v>
     <v>IREN LIMITED (XNAS:IREN)</v>
-    <v>63853899</v>
+    <v>64148748</v>
     <v>55882084</v>
     <v>2018</v>
   </rv>
@@ -6091,32 +6090,32 @@
     <v>16</v>
     <v>17</v>
     <v>Finance</v>
-    <v>18</v>
+    <v>26</v>
     <v>292.875</v>
     <v>206.81</v>
     <v>0.99929999999999997</v>
-    <v>-10.43</v>
-    <v>-3.8800000000000002E-3</v>
-    <v>-3.5718E-2</v>
-    <v>-1.0928</v>
+    <v>-10.36</v>
+    <v>-7.3499999999999998E-3</v>
+    <v>-3.5478000000000003E-2</v>
+    <v>-2.0699999999999998</v>
     <v>USD</v>
     <v>NYSE Arca</v>
     <v>ARCX</v>
     <v>1.9E-3</v>
     <v>289.39499999999998</v>
     <v>ETF</v>
-    <v>46178.90330844844</v>
+    <v>46178.999925196091</v>
     <v>128</v>
     <v>280.14999999999998</v>
     <v>80933362748.720001</v>
     <v>iShares:Russ 2000 ETF</v>
     <v>289.10000000000002</v>
     <v>292.01</v>
-    <v>281.58</v>
-    <v>280.55720000000002</v>
+    <v>281.64999999999998</v>
+    <v>279.58</v>
     <v>IWM</v>
     <v>iShares:Russ 2000 ETF (ARCX:IWM)</v>
-    <v>35684498</v>
+    <v>35812835</v>
     <v>25877273</v>
   </rv>
   <rv s="2">
@@ -6140,11 +6139,11 @@
     <v>4</v>
     <v>2156.69</v>
     <v>777.42</v>
-    <v>1.4964999999999999</v>
+    <v>1.4967999999999999</v>
     <v>-201.9</v>
-    <v>-1.089E-4</v>
+    <v>-7.3609999999999995E-3</v>
     <v>-9.4740000000000005E-2</v>
-    <v>-0.21</v>
+    <v>-14.2</v>
     <v>USD</v>
     <v>KLA Corporation (KLA) develops industry equipment and services. The Company provides advanced process control and process-enabling solutions for manufacturing wafers and reticles, integrated circuits, packaging, and printed circuit boards. It operates through three segments, which include Semiconductor Process Control, Specialty Semiconductor Process, and PCB and Component Inspection. The Semiconductor Process Control segment offers a portfolio of inspection, metrology and data analytics products, and related services. The Specialty Semiconductor Process segment develops and sells advanced vacuum deposition and etching process tools. The PCB and Component Inspection segment enables electronic device manufacturers to inspect, test and measure PCBs, flat panel displays, and integrated circuits (ICs) to verify their quality, pattern the desired electronic circuitry on the relevant substrate and perform three-dimensional shaping of metalized circuits on multiple surfaces.</v>
     <v>15000</v>
@@ -6155,7 +6154,7 @@
     <v>2054.96</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46178.903519305466</v>
+    <v>46178.999734050783</v>
     <v>131</v>
     <v>1927.73</v>
     <v>252006573000</v>
@@ -6165,11 +6164,11 @@
     <v>603.36530000000005</v>
     <v>2131.1</v>
     <v>1929.2</v>
-    <v>1928.99</v>
+    <v>1915</v>
     <v>130627500</v>
     <v>KLAC</v>
     <v>KLA CORPORATION (XNAS:KLAC)</v>
-    <v>1857490</v>
+    <v>1858629</v>
     <v>1031830</v>
     <v>1975</v>
   </rv>
@@ -6194,11 +6193,11 @@
     <v>4</v>
     <v>82.663499999999999</v>
     <v>65.353800000000007</v>
-    <v>0.35670000000000002</v>
-    <v>2.68</v>
-    <v>-2.3909999999999999E-3</v>
-    <v>3.4887000000000001E-2</v>
-    <v>-0.19</v>
+    <v>0.35089999999999999</v>
+    <v>2.66</v>
+    <v>-1.0070000000000001E-3</v>
+    <v>3.4626000000000004E-2</v>
+    <v>-0.08</v>
     <v>USD</v>
     <v>The Coca-Cola Company is a beverage company. The Company's segments include Europe, Middle East and Africa (EMEA); Latin America; North America; Asia Pacific, and Bottling Investments. It sells multiple brands across several beverage categories worldwide. Its portfolio of sparkling soft drink brands includes Coca-Cola, Sprite and Fanta. Its water, sports, coffee and tea brands include Dasani, smartwater, vitaminwater, Topo Chico, BODYARMOR, Powerade, Costa, Georgia, Fuze Tea, Gold Peak and Ayataka. Its juice, value-added dairy and plant-based beverage brands include Minute Maid, Simply, innocent, Del Valle, fairlife and Santa Clara. It operates in two lines of business: concentrate operations and finished product operations. Its concentrate operations sell beverage concentrates, syrups, including fountain syrups, and certain finished beverages to authorized bottling operations. Its finished product operations sell sparkling soft drinks and a variety of other finished beverages.</v>
     <v>65900</v>
@@ -6209,21 +6208,21 @@
     <v>80.7393</v>
     <v>Beverages</v>
     <v>Stock</v>
-    <v>46178.903096562499</v>
+    <v>46178.99997203672</v>
     <v>134</v>
     <v>77.48</v>
-    <v>342047319000</v>
+    <v>341961269360</v>
     <v>THE COCA-COLA COMPANY</v>
     <v>THE COCA-COLA COMPANY</v>
     <v>77.510000000000005</v>
-    <v>24.184100000000001</v>
+    <v>25.0212</v>
     <v>76.819999999999993</v>
-    <v>79.5</v>
-    <v>79.290000000000006</v>
+    <v>79.48</v>
+    <v>79.400000000000006</v>
     <v>4302482000</v>
     <v>KO</v>
     <v>THE COCA-COLA COMPANY (XNYS:KO)</v>
-    <v>25696678</v>
+    <v>25708070</v>
     <v>14777230</v>
     <v>1919</v>
   </rv>
@@ -6248,11 +6247,11 @@
     <v>4</v>
     <v>18.940000000000001</v>
     <v>2.75</v>
-    <v>1.3332999999999999</v>
+    <v>1.37</v>
     <v>-2.69</v>
-    <v>9.5509999999999987E-3</v>
+    <v>-2.0089999999999999E-3</v>
     <v>-0.152667</v>
-    <v>0.1426</v>
+    <v>-0.03</v>
     <v>USD</v>
     <v>LightPath Technologies, Inc. is a global, vertically integrated provider of optics, photonics and infrared solutions for the industrial, commercial, defense, telecommunications, and medical industries. The Company designs and manufactures optical and infrared components including molded glass aspheric lenses and assemblies, custom molded glass freeform lenses, infrared lenses and thermal imaging assemblies, fused fiber collimators, and BlackDiamond (BD6) chalcogenide-based glass lenses. It also offers custom optical assemblies, including full engineering design support. Its business is organized into four product groups: infrared components, visible components, assemblies and modules, and engineering services. Its infrared product group comprises both molded and turned infrared lenses and assemblies using a variety of infrared glass materials. Its assemblies and modules product group is comprised of other value-added products, including both infrared and visible components.</v>
     <v>345</v>
@@ -6261,9 +6260,9 @@
     <v>XNAS</v>
     <v>2603 CHALLENGER TECH CT, STE 100, ORLANDO, FL, 32826-2716 US</v>
     <v>16.91</v>
-    <v>Computers, Phones &amp; Household Electronics</v>
+    <v>Office Equipment</v>
     <v>Stock</v>
-    <v>46178.902286168748</v>
+    <v>46178.999348020312</v>
     <v>137</v>
     <v>14.79</v>
     <v>990766893</v>
@@ -6273,11 +6272,11 @@
     <v>0</v>
     <v>17.62</v>
     <v>14.93</v>
-    <v>15.0726</v>
+    <v>14.9</v>
     <v>66360810</v>
     <v>LPTH</v>
     <v>LIGHTPATH TECHNOLOGIES, INC. (XNAS:LPTH)</v>
-    <v>4709234</v>
+    <v>4736560</v>
     <v>4157456</v>
     <v>1992</v>
   </rv>
@@ -6302,11 +6301,11 @@
     <v>4</v>
     <v>18.709</v>
     <v>1.04</v>
-    <v>2.3871000000000002</v>
+    <v>2.4003000000000001</v>
     <v>-2.04</v>
-    <v>-1.3787000000000001E-2</v>
+    <v>-1.4793000000000001E-2</v>
     <v>-0.167488</v>
-    <v>-0.13980000000000001</v>
+    <v>-0.15</v>
     <v>USD</v>
     <v>Lightwave Logic, Inc. is a technology platform company leveraging its proprietary engineered electro-optic (EO) polymers known as Perkinamine, to transmit data at higher speeds with less power in a small form factor. The Company’s organic polymers allow it to create next-generation photonic EO devices that convert data from electrical signals into light/optical signals for applications in telecommunications, and for data transmission potentially used to support generative Artificial Intelligence. It designs its own proprietary materials for electro-optical modulation devices. Electro-optical modulators convert data from electric signals into optical signals that can then be transmitted over high-speed fiber-optic cables. It is focused on testing and demonstrating the manufacturability and reliability of its devices. In polymer photonics, polymer devices such as modulators, waveguides, and multiplexers can be fabricated on to a silicon platform.</v>
     <v>34</v>
@@ -6317,7 +6316,7 @@
     <v>11.75</v>
     <v>Electronic Equipment &amp; Parts</v>
     <v>Stock</v>
-    <v>46178.903039825782</v>
+    <v>46178.99998152734</v>
     <v>140</v>
     <v>10.119999999999999</v>
     <v>1562367144</v>
@@ -6327,11 +6326,11 @@
     <v>0</v>
     <v>12.18</v>
     <v>10.14</v>
-    <v>10.0002</v>
+    <v>9.99</v>
     <v>154079600</v>
     <v>LWLG</v>
     <v>LIGHTWAVE LOGIC, INC. (XNAS:LWLG)</v>
-    <v>5458829</v>
+    <v>5509318</v>
     <v>9037233</v>
     <v>1997</v>
   </rv>
@@ -6372,11 +6371,11 @@
     <v>4</v>
     <v>341.75</v>
     <v>271.85000000000002</v>
-    <v>0.41560000000000002</v>
-    <v>7.0549999999999997</v>
-    <v>-1.2149999999999999E-3</v>
-    <v>2.5869E-2</v>
-    <v>-0.34</v>
+    <v>0.40989999999999999</v>
+    <v>7.12</v>
+    <v>-5.3600000000000002E-4</v>
+    <v>2.6107000000000002E-2</v>
+    <v>-0.15</v>
     <v>USD</v>
     <v>McDonald's Corporation is a global foodservice retailer. Its segment includes U.S., International Operated Markets, and International Developmental Licensed Markets &amp; Corporate. The U.S. segment is its largest market and is 95% franchised. The International Operated Markets segment comprises markets or countries in which it operates and franchises restaurants, including Australia, Canada, France, Germany, Italy, Poland, Spain, and the United Kingdom. This segment is 89% franchised. The International Developmental Licensed Markets &amp; Corporate segment comprises development licensee and affiliate markets, including equity method investments in China and Japan. This segment is 99% franchised. Its menu features hamburgers and cheeseburgers, the Big Mac, the Quarter Pounder with Cheese, the Filet-O-Fish, and several chicken sandwiches, such as the McChicken and McCrispy as well as Chicken McNuggets, Fries, shakes, sundaes, cookies, soft drinks, coffee, and other beverages.</v>
     <v>150000</v>
@@ -6388,21 +6387,21 @@
     <v>145</v>
     <v>Hotels &amp; Entertainment Services</v>
     <v>Stock</v>
-    <v>46178.903093923436</v>
+    <v>46178.999868414059</v>
     <v>146</v>
     <v>274.39999999999998</v>
-    <v>198781788172</v>
+    <v>198827971055</v>
     <v>MCDONALD'S CORPORATION</v>
     <v>MCDONALD'S CORPORATION</v>
     <v>274.39999999999998</v>
     <v>22.479900000000001</v>
     <v>272.72000000000003</v>
-    <v>279.77499999999998</v>
-    <v>279.5</v>
+    <v>279.83999999999997</v>
+    <v>279.69</v>
     <v>710505900</v>
     <v>MCD</v>
     <v>MCDONALD'S CORPORATION (XNYS:MCD)</v>
-    <v>5416099</v>
+    <v>5428103</v>
     <v>4352026</v>
     <v>1964</v>
   </rv>
@@ -6447,11 +6446,11 @@
     <v>4</v>
     <v>444.72</v>
     <v>196</v>
-    <v>1.5414000000000001</v>
+    <v>1.5269999999999999</v>
     <v>-29.44</v>
-    <v>-9.6940000000000004E-4</v>
+    <v>-4.9610000000000001E-3</v>
     <v>-7.7436999999999992E-2</v>
-    <v>-0.34</v>
+    <v>-1.74</v>
     <v>USD</v>
     <v>MongoDB, Inc. is a developer data platform company. Its developer data platform is a globally distributed operational database integrated with a set of data services that allow development teams to address the growing variety of application requirements. Its customers can implement its developer data platform as a managed service offering, or they can choose a self-managed option. Its MongoDB Atlas is its managed multi-cloud database-as-a-service (DBaaS) offering that includes an integrated set of databases and related services. Atlas Vector Search allows the integration of an operational database and vector search in a unified, fully managed platform. MongoDB Enterprise Advanced is its proprietary self-managed commercial offering for enterprise customers that can run in the cloud, on-premises or in a hybrid environment. It also provides professional services for its customers.</v>
     <v>5636</v>
@@ -6463,7 +6462,7 @@
     <v>152</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46178.895453796096</v>
+    <v>46178.999710474222</v>
     <v>153</v>
     <v>350.11</v>
     <v>28210695128</v>
@@ -6473,11 +6472,11 @@
     <v>0</v>
     <v>380.18</v>
     <v>350.74</v>
-    <v>350.4</v>
+    <v>349</v>
     <v>80431930</v>
     <v>MDB</v>
     <v>MONGODB, INC. (XNAS:MDB)</v>
-    <v>1780269</v>
+    <v>1786156</v>
     <v>2746215</v>
     <v>2007</v>
   </rv>
@@ -6502,11 +6501,11 @@
     <v>4</v>
     <v>796.25</v>
     <v>520.26</v>
-    <v>1.2296</v>
+    <v>1.2386999999999999</v>
     <v>-34.57</v>
-    <v>-3.2040000000000003E-3</v>
+    <v>-5.3629999999999997E-3</v>
     <v>-5.5084999999999995E-2</v>
-    <v>-1.9</v>
+    <v>-3.18</v>
     <v>USD</v>
     <v>Meta Platforms, Inc. is building human connections, powered by artificial intelligence and immersive technologies. The Company's products enable people to connect and share with friends and family through mobile devices, personal computers, virtual reality (VR) and mixed reality (MR) headsets, augmented reality (AR), and wearables. It also helps people discover and learn about what is going on in the world around them, enabling people to share their experiences, ideas, photos, videos, and other content with audiences ranging from their closest family members and friends to the public at large. The Company's segments include Family of Apps (FoA) and Reality Labs (RL). FoA segment includes Facebook, Instagram, Messenger, WhatsApp and Threads. RL segment includes its virtual, augmented, and mixed reality related consumer hardware, software and content. Its product offerings in VR include its Meta Quest devices, as well as software and content available through the Meta Horizon Store.</v>
     <v>77986</v>
@@ -6517,7 +6516,7 @@
     <v>629.14499999999998</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46178.903478969529</v>
+    <v>46178.999988992968</v>
     <v>156</v>
     <v>582.91</v>
     <v>1505284839000</v>
@@ -6527,11 +6526,11 @@
     <v>19.0352</v>
     <v>627.57000000000005</v>
     <v>593</v>
-    <v>591.1</v>
+    <v>589.82000000000005</v>
     <v>2538423000</v>
     <v>META</v>
     <v>META PLATFORMS, INC. (XNAS:META)</v>
-    <v>29619204</v>
+    <v>30091610</v>
     <v>17801115</v>
     <v>2004</v>
   </rv>
@@ -6556,11 +6555,11 @@
     <v>4</v>
     <v>324.2</v>
     <v>61.44</v>
-    <v>2.2330999999999999</v>
+    <v>2.1796000000000002</v>
     <v>-52.96</v>
-    <v>6.0837000000000002E-2</v>
+    <v>3.5715999999999998E-2</v>
     <v>-0.16736699999999999</v>
-    <v>16.0288</v>
+    <v>9.41</v>
     <v>USD</v>
     <v>Marvell Technology, Inc. together with its consolidated subsidiaries, is a supplier of data infrastructure semiconductor solutions, spanning the data center core to network edge. It is engaged in the design, development and sale of integrated circuits. Its product offerings include custom application-specific integrated circuits (ASICs), interconnects, ethernet solutions, fiber channel adapters, processors and storage controllers. In addition, it is also developing Ultra Accelerator LinkTM (UALinkTM) switches and ethernet for scale-up networking (ESUN) switches for the emerging scale-out artificial intelligence market. Its solutions integrate multiple analogs, mixed-signal and digital intellectual property components incorporating hardware, firmware and software technologies and its system knowledge to provide its customers with integrated solutions for their end products. It designs and manufactures photonic integrated circuits for ultra-high-bandwidth and low-power applications.</v>
     <v>7480</v>
@@ -6571,7 +6570,7 @@
     <v>300.72430000000003</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46178.903561006249</v>
+    <v>46178.999995358594</v>
     <v>159</v>
     <v>261.39</v>
     <v>230483556000</v>
@@ -6581,11 +6580,11 @@
     <v>108.3839</v>
     <v>316.43</v>
     <v>263.47000000000003</v>
-    <v>279.49880000000002</v>
+    <v>272.88</v>
     <v>874800000</v>
     <v>MRVL</v>
     <v>MARVELL TECHNOLOGY, INC. (XNAS:MRVL)</v>
-    <v>91834421</v>
+    <v>93976392</v>
     <v>36932388</v>
     <v>2020</v>
   </rv>
@@ -6626,11 +6625,11 @@
     <v>4</v>
     <v>555.45000000000005</v>
     <v>356.28</v>
-    <v>1.1068</v>
+    <v>1.1158999999999999</v>
     <v>-11.38</v>
-    <v>-3.1680000000000002E-3</v>
+    <v>-1.0248E-2</v>
     <v>-2.6585999999999999E-2</v>
-    <v>-1.32</v>
+    <v>-4.2699999999999996</v>
     <v>USD</v>
     <v>Microsoft Corporation is a technology company. The Company develops and supports software, services, devices, and solutions. The Company’s segments include Productivity and Business Processes, Intelligent Cloud, and More Personal Computing. The Productivity and Business Processes segment consists of products and services in its portfolio of productivity, communication, and information services. This segment primarily comprises: Office Commercial, Office Consumer, LinkedIn, and Dynamics business solutions. The Intelligent Cloud segment consists of server products and cloud services, including Azure and other cloud services, SQL Server, Windows Server, Visual Studio, System Center, and related Client Access Licenses (CALs), and Nuance and GitHub; and Enterprise Services, including enterprise support services, industry solutions and Nuance professional services. The More Personal Computing segment primarily comprises Windows, Devices, Gaming, and search and news advertising.</v>
     <v>228000</v>
@@ -6642,7 +6641,7 @@
     <v>164</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46178.90349166641</v>
+    <v>46178.99999871484</v>
     <v>165</v>
     <v>414.4</v>
     <v>3095206011450</v>
@@ -6652,11 +6651,11 @@
     <v>25.494900000000001</v>
     <v>428.05</v>
     <v>416.67</v>
-    <v>415.35</v>
+    <v>412.4</v>
     <v>7428435000</v>
     <v>MSFT</v>
     <v>MICROSOFT CORPORATION (XNAS:MSFT)</v>
-    <v>34602619</v>
+    <v>34782164</v>
     <v>37058663</v>
     <v>1993</v>
   </rv>
@@ -6681,11 +6680,11 @@
     <v>4</v>
     <v>457.22</v>
     <v>104.16500000000001</v>
-    <v>3.4868000000000001</v>
+    <v>3.5194000000000001</v>
     <v>-8.93</v>
-    <v>8.8009999999999998E-3</v>
+    <v>-4.0679999999999996E-3</v>
     <v>-6.9027000000000005E-2</v>
-    <v>1.06</v>
+    <v>-0.49</v>
     <v>USD</v>
     <v>Strategy Inc. is a bitcoin treasury and business intelligence company. The Company provides cloud-native, artificial intelligence (AI)-powered enterprise analytics software to thousands of global customers. Its Software Business segment is engaged in the design, development, marketing, and sales of enterprise analytics software platform through cloud subscriptions and licensing arrangements and related services. Its Strategy ONE platform provides access to AI-powered workflows, unlimited data sources, cloud-native technologies, and performance to speed up time from data to action. Strategy One delivers visualization, reporting, and embedded analytics capabilities across retail, banking, technology, manufacturing, insurance, consulting, healthcare, public sector, and others. Its Strategy Mosaic is a universal intelligence layer that provides enterprises with consistent definitions and governance across data sources, regardless of where that data resides or which tools access it.</v>
     <v>1511</v>
@@ -6696,7 +6695,7 @@
     <v>125.2953</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46178.903323182814</v>
+    <v>46178.999999524996</v>
     <v>168</v>
     <v>114.31</v>
     <v>43141355076</v>
@@ -6706,11 +6705,11 @@
     <v>0</v>
     <v>129.37</v>
     <v>120.44</v>
-    <v>121.5</v>
+    <v>119.95</v>
     <v>358197900</v>
     <v>MSTR</v>
     <v>STRATEGY INC (XNAS:MSTR)</v>
-    <v>41714099</v>
+    <v>41943521</v>
     <v>16365965</v>
     <v>1989</v>
   </rv>
@@ -6735,11 +6734,11 @@
     <v>4</v>
     <v>1089.29</v>
     <v>103.38</v>
-    <v>2.1732</v>
+    <v>2.1979000000000002</v>
     <v>-131.99</v>
-    <v>6.5380000000000004E-3</v>
+    <v>-7.8820000000000001E-3</v>
     <v>-0.13252</v>
-    <v>5.6489000000000003</v>
+    <v>-6.81</v>
     <v>USD</v>
     <v>Micron Technology, Inc. provides memory and storage solutions. The Company delivers a portfolio of high-performance dynamic random-access memory (DRAM), NAND, and NOR memory and storage products through its Micron and Crucial brands. The Company's products enable advancing in artificial intelligence (AI) and compute-intensive applications. Its segments include Cloud Memory Business Unit (CMBU), Core Data Center Business Unit (CDBU), Mobile and Client Business Unit (MCBU) and Automotive and Embedded Business Unit (AEBU). CMBU is focused on memory solutions for large hyperscale cloud customers, and high bandwidth memory (HBM) for all data center customers. CDBU is focused on memory solutions for mid-tier cloud, enterprise, and OEM data center customers and storage solutions for all data center customers. MCBU is focused on memory and storage solutions for mobile and client segments. AEBU is focused on memory and storage solutions for the automotive, industrial, and consumer segments.</v>
     <v>53000</v>
@@ -6750,21 +6749,21 @@
     <v>961.89</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46178.90346648125</v>
+    <v>46178.999999339845</v>
     <v>171</v>
     <v>864.01</v>
     <v>974373453340</v>
     <v>MICRON TECHNOLOGY, INC.</v>
     <v>MICRON TECHNOLOGY, INC.</v>
     <v>944.4</v>
-    <v>40.791200000000003</v>
+    <v>47.022599999999997</v>
     <v>996</v>
     <v>864.01</v>
-    <v>869.65890000000002</v>
+    <v>857.2</v>
     <v>1127734000</v>
     <v>MU</v>
     <v>MICRON TECHNOLOGY, INC. (XNAS:MU)</v>
-    <v>76156083</v>
+    <v>77250536</v>
     <v>53729736</v>
     <v>1984</v>
   </rv>
@@ -6775,25 +6774,25 @@
     <v>https://www.bing.com/financeapi/forcetrigger?t=brh6oc&amp;q=XNYS%3aNET&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
   </rv>
-  <rv s="1">
+  <rv s="10">
     <v>en-GB</v>
     <v>brh6oc</v>
     <v>268435456</v>
     <v>1</v>
     <v>Powered by Refinitiv</v>
-    <v>0</v>
+    <v>19</v>
     <v>CLOUDFLARE, INC. (XNYS:NET)</v>
     <v>2</v>
-    <v>3</v>
+    <v>20</v>
     <v>Finance</v>
     <v>4</v>
     <v>276.815</v>
     <v>158.83000000000001</v>
-    <v>1.6660999999999999</v>
-    <v>-18.36</v>
-    <v>-8.3359999999999997E-3</v>
-    <v>-6.8344000000000002E-2</v>
-    <v>-2.085</v>
+    <v>1.6554</v>
+    <v>-18.53</v>
+    <v>-1.6433E-2</v>
+    <v>-6.8977000000000011E-2</v>
+    <v>-4.1100000000000003</v>
     <v>USD</v>
     <v>Cloudflare, Inc. is a connectivity cloud company. The Company delivers a range of services to businesses of all sizes and in all geographies, enhancing the performance of business-critical applications. Its full suite of products consists of application services that help deliver security, performance, and reliability for any organization's applications connected to the Internet, including Websites and application programming interfaces (APIs) and its secure access service edge (SASE) platform, which contains its suite of and workplace security services and network services solutions to help ensure traffic in and out of an organization’s network and devices is verified and authorized and data is protected and secured, as well as to securely connect data centers, cloud services, and branch offices to an organization with its connectivity cloud. The Company also offers developer-based solutions which build and deploys serverless and artificial intelligence applications.</v>
     <v>5483</v>
@@ -6804,21 +6803,20 @@
     <v>268.82</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46178.903350092187</v>
+    <v>46178.999969756253</v>
     <v>174</v>
     <v>246.94</v>
-    <v>88465520536</v>
+    <v>88405431282</v>
     <v>CLOUDFLARE, INC.</v>
     <v>CLOUDFLARE, INC.</v>
     <v>267.87</v>
-    <v>0</v>
     <v>268.64</v>
-    <v>250.28</v>
-    <v>248.02500000000001</v>
+    <v>250.11</v>
+    <v>246</v>
     <v>353466200</v>
     <v>NET</v>
     <v>CLOUDFLARE, INC. (XNYS:NET)</v>
-    <v>4732524</v>
+    <v>4735502</v>
     <v>5034853</v>
     <v>2009</v>
   </rv>
@@ -6829,19 +6827,19 @@
     <v>https://www.bing.com/financeapi/forcetrigger?t=afgp6h&amp;q=XFRA%3aNKE&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
   </rv>
-  <rv s="12">
+  <rv s="13">
     <v>en-GB</v>
     <v>afgp6h</v>
     <v>268435456</v>
     <v>1</v>
     <v>Powered by Refinitiv</v>
-    <v>24</v>
+    <v>27</v>
     <v>NIKE, INC. (XFRA:NKE)</v>
     <v>2</v>
-    <v>25</v>
+    <v>28</v>
     <v>Finance</v>
-    <v>21</v>
-    <v>1.1182000000000001</v>
+    <v>23</v>
+    <v>1.1197999999999999</v>
     <v>9.5000000000000001E-2</v>
     <v>2.5430000000000001E-3</v>
     <v>EUR</v>
@@ -6902,11 +6900,11 @@
     <v>4</v>
     <v>17.45</v>
     <v>4</v>
-    <v>1.1414</v>
-    <v>-2.27</v>
-    <v>-7.0169999999999998E-3</v>
-    <v>-0.13658200000000001</v>
-    <v>-0.1009</v>
+    <v>1.1538999999999999</v>
+    <v>-2.2400000000000002</v>
+    <v>-2.0861999999999999E-2</v>
+    <v>-0.13477700000000001</v>
+    <v>-0.3</v>
     <v>USD</v>
     <v>Nokia Oyj is a Finland-based company engaged in the network and Internet protocol (IP) infrastructure, software, and related services market. The Company's businesses include Nokia Networks and Nokia Technologies. The Company's segments include Ultra Broadband Networks, IP Networks and Applications, and Nokia Technologies. The Ultra Broadband Networks segment comprises Mobile Networks and Fixed Networks operating segments. The IP Networks and Applications segment comprises IP/Optical Networks and Applications &amp; Analytics operating segments. The Applications &amp; Analytics operating segment offers software solutions spanning customer experience management, network operations and management, communications and collaboration, policy and charging, as well as Cloud, Internet of things (IoT), security, and analytics platforms that enable digital services providers and enterprises to accelerate and optimize their customer experience. The Company has Comptel Oyj among its subsidiaries.</v>
     <v>77586</v>
@@ -6917,21 +6915,21 @@
     <v>15.67</v>
     <v>Communications &amp; Networking</v>
     <v>Stock</v>
-    <v>46178.903528946095</v>
+    <v>46178.999996816405</v>
     <v>182</v>
     <v>14</v>
-    <v>82401144000</v>
+    <v>82573411200</v>
     <v>Nokia Oyj</v>
     <v>Nokia Oyj</v>
     <v>15.66</v>
-    <v>103.3112</v>
+    <v>89.372299999999996</v>
     <v>16.62</v>
-    <v>14.35</v>
-    <v>14.2791</v>
+    <v>14.38</v>
+    <v>14.08</v>
     <v>5742240000</v>
     <v>NOK</v>
     <v>Nokia Oyj (XNYS:NOK)</v>
-    <v>182912447</v>
+    <v>185183792</v>
     <v>122942145</v>
     <v>1997</v>
   </rv>
@@ -6956,11 +6954,11 @@
     <v>4</v>
     <v>211.47800000000001</v>
     <v>81.239999999999995</v>
-    <v>0.92969999999999997</v>
-    <v>-6.89</v>
-    <v>-3.1119999999999997E-3</v>
-    <v>-5.7724999999999999E-2</v>
-    <v>-0.35</v>
+    <v>0.94669999999999999</v>
+    <v>-6.91</v>
+    <v>-1.3774E-2</v>
+    <v>-5.7891999999999999E-2</v>
+    <v>-1.5488999999999999</v>
     <v>USD</v>
     <v>ServiceNow, Inc. provides an artificial intelligence (AI) platform for business transformation. The Company’s AI platform connects people, processes, data, and devices to increase productivity and maximize business outcomes. Its intelligent platform, the Now Platform, is a cloud-based solution that helps enterprises and organizations across public and private sectors digitize workflows. The workflow applications built on the Now Platform are organized into four primary areas: Technology, CRM and Industry, Core Business and Creator. Its products include IT Service Management, IT Operations Management, HR Service Delivery, ServiceNow AI Agents, AI Experience, Build Agent, ServiceNow AI Control Tower, AI Agent Fabric, RaptorDB, Workflow Data Fabric, Workplace Service Delivery, ServiceNow Platform Encryption, Telecommunications Service Operations Management, and others. The Company also offers identity security, helping organizations secure access across the enterprise.</v>
     <v>29187</v>
@@ -6971,21 +6969,21 @@
     <v>121.2</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46178.903395219531</v>
+    <v>46178.999993587502</v>
     <v>185</v>
     <v>111.562</v>
-    <v>115991210760</v>
+    <v>115970584600</v>
     <v>SERVICENOW, INC.</v>
     <v>SERVICENOW, INC.</v>
     <v>119.19</v>
     <v>70.989400000000003</v>
     <v>119.36</v>
-    <v>112.47</v>
-    <v>112.1</v>
+    <v>112.45</v>
+    <v>110.9011</v>
     <v>1031308000</v>
     <v>NOW</v>
     <v>SERVICENOW, INC. (XNYS:NOW)</v>
-    <v>31277351</v>
+    <v>31452022</v>
     <v>32427047</v>
     <v>2012</v>
   </rv>
@@ -7010,11 +7008,11 @@
     <v>4</v>
     <v>236.54</v>
     <v>138.83000000000001</v>
-    <v>2.2008000000000001</v>
+    <v>2.2010999999999998</v>
     <v>-13.56</v>
-    <v>9.6539999999999994E-5</v>
+    <v>-5.071E-3</v>
     <v>-6.2013999999999993E-2</v>
-    <v>1.9800000000000002E-2</v>
+    <v>-1.04</v>
     <v>USD</v>
     <v>NVIDIA Corporation is an artificial intelligence (AI) infrastructure company. The Company is engaged in accelerated computing to help solve the challenging computational problems. Its segments include Compute &amp; Networking and Graphics. The Compute &amp; Networking segment includes its Data Center accelerated computing and networking platforms and AI solutions and software, and automotive platforms and autonomous and electric vehicle solutions, including software. The Graphics segment includes GeForce GPUs for gaming and personal computers (PCs), and Quadro/NVIDIA RTX GPUs for enterprise workstation graphics. Its technology stack includes the foundational NVIDIA CUDA development platform that runs on all NVIDIA GPUs, as well as hundreds of domain-specific software libraries, frameworks, algorithms, software development kits (SDKs), and application programming interfaces (APIs). Its platforms address four markets, which include Data Center, Gaming, Professional Visualization, and Automotive.</v>
     <v>42000</v>
@@ -7025,7 +7023,7 @@
     <v>214.87</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46178.903472603903</v>
+    <v>46178.99999732578</v>
     <v>188</v>
     <v>204.33</v>
     <v>4963420000000</v>
@@ -7035,11 +7033,11 @@
     <v>33.485599999999998</v>
     <v>218.66</v>
     <v>205.1</v>
-    <v>205.1198</v>
+    <v>204.06</v>
     <v>24200000000</v>
     <v>NVDA</v>
     <v>NVIDIA CORPORATION (XNAS:NVDA)</v>
-    <v>218200155</v>
+    <v>219655531</v>
     <v>171448900</v>
     <v>1998</v>
   </rv>
@@ -7064,11 +7062,11 @@
     <v>4</v>
     <v>134.91999999999999</v>
     <v>44.56</v>
-    <v>1.9702</v>
+    <v>1.9728000000000001</v>
     <v>-14.56</v>
-    <v>-6.4809999999999998E-3</v>
+    <v>-1.6715000000000001E-2</v>
     <v>-0.11045400000000001</v>
-    <v>-0.76</v>
+    <v>-1.96</v>
     <v>USD</v>
     <v>ON Semiconductor Corporation is engaged in providing intelligent power and intelligent sensing solutions. The Company’s intelligent power technologies enable the electrification of drivetrain in the automotive industry to allow for lighter and longer-range electric vehicles. Its segments include Power Solutions Group (PSG), the Analog and Mixed-Signal Group (AMG) and the Intelligent Sensing Group (ISG). PSG segment provides a portfolio of discrete, module, and integrated semiconductor devices designed to enable conversion across artificial intelligence (AI) data centers, energy infrastructure, automotive and industrial. AMG segment designs and develops a range of analog and mixed-signal solutions including power‑management, sensor‑interface, connectivity, and products that serve automotive, industrial automation, AI data center, computing, and mobile end markets.</v>
     <v>22600</v>
@@ -7079,7 +7077,7 @@
     <v>126.31</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46178.901148390622</v>
+    <v>46178.999814721872</v>
     <v>191</v>
     <v>116.72</v>
     <v>45954569232</v>
@@ -7089,11 +7087,11 @@
     <v>94.131600000000006</v>
     <v>131.82</v>
     <v>117.26</v>
-    <v>116.5</v>
+    <v>115.3</v>
     <v>391903200</v>
     <v>ON</v>
     <v>ON SEMICONDUCTOR CORPORATION (XNAS:ON)</v>
-    <v>19047617</v>
+    <v>19056593</v>
     <v>12667476</v>
     <v>2000</v>
   </rv>
@@ -7118,11 +7116,11 @@
     <v>4</v>
     <v>15.28</v>
     <v>1.36</v>
-    <v>2.6339999999999999</v>
+    <v>2.6793</v>
     <v>-1.54</v>
-    <v>-4.7939999999999997E-3</v>
+    <v>-1.7373E-2</v>
     <v>-0.12865500000000002</v>
-    <v>-0.05</v>
+    <v>-0.1812</v>
     <v>USD</v>
     <v>Ondas Inc. is a provider of autonomous systems, robotics, and mission-critical connectivity solutions for defense, security, and industrial markets. Through its business units, Ondas Autonomous Systems (OAS), Ondas Capital and Ondas Networks, it develops and deploys integrated technologies that deliver advanced sensing, mobility, and communications capabilities. OAS delivers a portfolio of artificial-intelligence (AI)-powered defense and security platforms to protect sensitive sites, populations, and critical infrastructure. OAS also provides an integrated suite of autonomous aerial, ground, and counter-UAS solutions through its operating companies. It also provides Airborne Missile Protection Systems (AMPS) and airborne intelligence, surveillance and reconnaissance (ISR) solutions for the military, government and others. It also specializes in the procurement, integration, and lifecycle support of heavy engineering equipment for military and national infrastructure programs.</v>
     <v>459</v>
@@ -7133,7 +7131,7 @@
     <v>11.659599999999999</v>
     <v>Communications &amp; Networking</v>
     <v>Stock</v>
-    <v>46178.903343032034</v>
+    <v>46178.999996851562</v>
     <v>194</v>
     <v>10.33</v>
     <v>5294319107</v>
@@ -7143,11 +7141,11 @@
     <v>30.185300000000002</v>
     <v>11.97</v>
     <v>10.43</v>
-    <v>10.38</v>
+    <v>10.248799999999999</v>
     <v>507604900</v>
     <v>ONDS</v>
     <v>ONDAS INC. (XNAS:ONDS)</v>
-    <v>63470473</v>
+    <v>63881353</v>
     <v>81454467</v>
     <v>2014</v>
   </rv>
@@ -7188,11 +7186,11 @@
     <v>4</v>
     <v>345.72</v>
     <v>134.57</v>
-    <v>1.651</v>
-    <v>-22.93</v>
-    <v>-5.522E-3</v>
-    <v>-9.7020999999999996E-2</v>
-    <v>-1.18</v>
+    <v>1.6594</v>
+    <v>-22.66</v>
+    <v>-1.6286000000000002E-2</v>
+    <v>-9.5878999999999992E-2</v>
+    <v>-3.48</v>
     <v>USD</v>
     <v>Oracle Corporation offers integrated suites of applications plus secure, autonomous infrastructure in the Oracle Cloud. The Company operates through three businesses: cloud and license, hardware and service. Its cloud and license business is engaged in the sale, marketing and delivery of its enterprise applications and infrastructure technologies through cloud and on-premise deployment models including its cloud services and license support offerings, and its cloud license and on-premise license offerings. Its hardware business provides infrastructure technologies including Oracle Engineered Systems, servers, storage, industry-specific hardware, operating systems, virtualization, management and other hardware-related software to support diverse IT environments. Its services business provides services to customers and partners to help maximize the performance of their investments in Oracle applications and infrastructure technologies.</v>
     <v>162000</v>
@@ -7204,21 +7202,21 @@
     <v>199</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46178.90353287031</v>
+    <v>46178.999998680469</v>
     <v>200</v>
-    <v>209.45</v>
-    <v>613776976860</v>
+    <v>209.45009999999999</v>
+    <v>614553509280</v>
     <v>ORACLE CORPORATION</v>
     <v>ORACLE CORPORATION</v>
     <v>229.49</v>
     <v>40.058599999999998</v>
     <v>236.34</v>
-    <v>213.41</v>
-    <v>212.5</v>
+    <v>213.68</v>
+    <v>210.2</v>
     <v>2876046000</v>
     <v>ORCL</v>
     <v>ORACLE CORPORATION (XNYS:ORCL)</v>
-    <v>28858851</v>
+    <v>29019876</v>
     <v>22686026</v>
     <v>2005</v>
   </rv>
@@ -7243,11 +7241,11 @@
     <v>4</v>
     <v>302.95</v>
     <v>139.57060000000001</v>
-    <v>0.94479999999999997</v>
+    <v>0.95150000000000001</v>
     <v>-7.2</v>
-    <v>-7.5349999999999992E-3</v>
+    <v>-1.2645E-2</v>
     <v>-2.5783E-2</v>
-    <v>-2.0499999999999998</v>
+    <v>-3.44</v>
     <v>USD</v>
     <v>Palo Alto Networks, Inc. is a global artificial intelligence (AI) cybersecurity company, with a comprehensive portfolio of cybersecurity solutions and platforms across network, cloud, security operations, AI and Identity. Its network security platform includes Secure Access Service Edge (SASE), Next-Generation Firewalls, Cloud Delivered Security Services (CDSS), Prisma AIRS, and Strata Cloud Manager (SCM). It delivers security operations capabilities that unifies standalone Security Information and Event Management (SIEM) tools, endpoint security, security automation, cloud detection and response (CDR), as well as attack surface management (ASM) capabilities on its Cortex platform. It delivers comprehensive security across the cloud application development lifecycle through Cortex Cloud. Its Unit 42 brings together expertise across threat research, incident response, and security consulting to deliver intelligence-driven, response-ready outcomes that help customers reduce cyber risk.</v>
     <v>21491</v>
@@ -7258,21 +7256,21 @@
     <v>280.64</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46178.90344487266</v>
+    <v>46178.999910335158</v>
     <v>203</v>
     <v>269.39999999999998</v>
     <v>221720750000</v>
     <v>PALO ALTO NETWORKS, INC.</v>
     <v>PALO ALTO NETWORKS, INC.</v>
     <v>278.99</v>
-    <v>229.9357</v>
+    <v>224.0016</v>
     <v>279.25</v>
     <v>272.05</v>
-    <v>270</v>
+    <v>268.61</v>
     <v>815000000</v>
     <v>PANW</v>
     <v>PALO ALTO NETWORKS, INC. (XNAS:PANW)</v>
-    <v>7777903</v>
+    <v>7795476</v>
     <v>9365602</v>
     <v>2005</v>
   </rv>
@@ -7297,11 +7295,11 @@
     <v>4</v>
     <v>19.84</v>
     <v>9.2002000000000006</v>
-    <v>0.96640000000000004</v>
+    <v>0.96460000000000001</v>
     <v>-0.43</v>
-    <v>-8.0070000000000002E-3</v>
+    <v>-9.7859999999999996E-3</v>
     <v>-3.6846999999999998E-2</v>
-    <v>-0.09</v>
+    <v>-0.11</v>
     <v>USD</v>
     <v>UiPath, Inc. is focused on agentic automation and orchestration, empowering enterprises to harness the full potential of AI agents to autonomously execute and optimize complex business processes. It is focused on building and managing automations, starting with computer vision technology and user interface automation in its initial robotic process automation offering. Its AI-powered UiPath Platform offers a robust set of capabilities that allows its customers to discover opportunities for automation, automate using a digital workforce that seamlessly collaborates with humans, and operate a mission-critical automation program at scale. It enables employees to quickly build automations for both existing and new processes and to automate a range of actions including logging into applications, moving folders, filling in forms, reading emails and others. Its platform allows users to design and combine UI automations, API integrations and AI-based document understanding in a single workflow.</v>
     <v>3981</v>
@@ -7312,21 +7310,21 @@
     <v>11.94</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46178.903380253905</v>
+    <v>46178.999919571092</v>
     <v>206</v>
     <v>11.045</v>
-    <v>5849783816</v>
+    <v>5823672172</v>
     <v>UIPATH, INC.</v>
     <v>UIPATH, INC.</v>
     <v>11.64</v>
     <v>19.3992</v>
     <v>11.67</v>
     <v>11.24</v>
-    <v>11.15</v>
-    <v>520443400</v>
+    <v>11.13</v>
+    <v>518120300</v>
     <v>PATH</v>
     <v>UIPATH, INC. (XNYS:PATH)</v>
-    <v>35487140</v>
+    <v>35568433</v>
     <v>40933553</v>
     <v>2015</v>
   </rv>
@@ -7351,11 +7349,11 @@
     <v>4</v>
     <v>167.25</v>
     <v>137.62</v>
-    <v>0.3861</v>
+    <v>0.37519999999999998</v>
     <v>5.76</v>
-    <v>-2.32E-3</v>
+    <v>4.0939999999999998E-4</v>
     <v>4.0915E-2</v>
-    <v>-0.34</v>
+    <v>0.06</v>
     <v>USD</v>
     <v>The Procter &amp; Gamble Company is focused on providing branded consumer packaged goods to consumers across the world. The Company’s segments include Beauty, Grooming, Health Care, Fabric &amp; Home Care and Baby, Feminine &amp; Family Care. The Company’s products are sold in approximately 180 countries and territories primarily through mass merchandisers, e-commerce, including social commerce channels, grocery stores, membership club stores, drug stores, department stores, distributors, wholesalers, specialty beauty stores, including airport duty-free stores), high-frequency stores, pharmacies, electronics stores and professional channels. It also sells direct to individual consumers. It has operations in approximately 70 countries. It offers products under brands, such as Head &amp; Shoulders, Herbal Essences, Pantene, Rejoice, Olay, Old Spice, Safeguard, Secret, SK-II, Braun, Gillette, Venus, Crest, Oral-B, Ariel, Downy, Gain, Tide, Always, Always Discreet, Tampax, Bounty and others.</v>
     <v>109000</v>
@@ -7366,21 +7364,21 @@
     <v>148.22999999999999</v>
     <v>Personal &amp; Household Products &amp; Services</v>
     <v>Stock</v>
-    <v>46178.902205948434</v>
+    <v>46178.999661064059</v>
     <v>209</v>
     <v>141.80000000000001</v>
     <v>341232897460</v>
     <v>THE PROCTER &amp; GAMBLE COMPANY</v>
     <v>THE PROCTER &amp; GAMBLE COMPANY</v>
     <v>142.22</v>
-    <v>20.589200000000002</v>
+    <v>21.4315</v>
     <v>140.78</v>
     <v>146.54</v>
-    <v>146.19999999999999</v>
+    <v>146.6</v>
     <v>2328599000</v>
     <v>PG</v>
     <v>THE PROCTER &amp; GAMBLE COMPANY (XNYS:PG)</v>
-    <v>10956862</v>
+    <v>10963204</v>
     <v>8501627</v>
     <v>1905</v>
   </rv>
@@ -7405,11 +7403,11 @@
     <v>4</v>
     <v>56</v>
     <v>17.57</v>
-    <v>1.3727</v>
+    <v>1.3917999999999999</v>
     <v>-2.37</v>
-    <v>-2.4009999999999999E-3</v>
+    <v>-1.0634999999999999E-2</v>
     <v>-7.5190000000000007E-2</v>
-    <v>-7.0000000000000007E-2</v>
+    <v>-0.31</v>
     <v>USD</v>
     <v>Photronics, Inc. is a manufacturer of photomasks, which are high-precision photographic quartz or glass plates containing microscopic images of electronic circuits. The Company manufactures photomasks, which are used as masters to transfer circuit patterns onto semiconductor wafers and FPD substrates. The photomasks the Company manufactures incorporate circuit designs provided on a confidential basis by its customers. The Company sells its photomasks to semiconductor designers and manufacturers, and manufacturers of FPDs. Photomask technology is also being applied to the fabrication of other higher-performance electronic products such as virtual reality/augmented reality advanced IC packages, photonics, micro-electronic mechanical systems, and certain nanotechnology applications. The Company operates approximately 11 manufacturing facilities, which are located in Taiwan, China, Korea, the United States, and Europe.</v>
     <v>1908</v>
@@ -7420,7 +7418,7 @@
     <v>31.035</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46178.903352522655</v>
+    <v>46178.997146411719</v>
     <v>212</v>
     <v>28.87</v>
     <v>1718870268</v>
@@ -7430,11 +7428,11 @@
     <v>11.5436</v>
     <v>31.52</v>
     <v>29.15</v>
-    <v>29.08</v>
+    <v>28.84</v>
     <v>58966390</v>
     <v>PLAB</v>
     <v>PHOTRONICS, INC. (XNAS:PLAB)</v>
-    <v>2404767</v>
+    <v>2418177</v>
     <v>1730338</v>
     <v>1969</v>
   </rv>
@@ -7459,11 +7457,11 @@
     <v>4</v>
     <v>20.81</v>
     <v>3.87</v>
-    <v>0.71440000000000003</v>
+    <v>0.74539999999999995</v>
     <v>-3.6150000000000002</v>
-    <v>1.0959999999999999E-4</v>
+    <v>-1.7663999999999999E-2</v>
     <v>-0.23360299999999998</v>
-    <v>1.2999999999999999E-3</v>
+    <v>-0.20949999999999999</v>
     <v>USD</v>
     <v>POET Technologies Inc. is a design and development company. It offers high-speed optical engines, light source products and custom optical modules to the artificial intelligence (AI) systems market and to hyperscale data centers. Its photonic integration solutions are based on the POET Optical Interposer, a novel, patented platform that allows the integration of electronic and photonic devices into a single chip using wafer-level semiconductor manufacturing techniques. Its Optical Interposer-based products consume less power than comparable products, are smaller in size and are readily scalable to high production volumes. In addition, it has designed and produced novel light source products for chip-to-chip data communication within and between AI servers, the next frontier for solving bandwidth and latency problems in AI systems. Its Optical Interposer platform solves device integration challenges across a range of communication, computing and sensing applications.</v>
     <v>180</v>
@@ -7474,7 +7472,7 @@
     <v>14.79</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46178.903495728904</v>
+    <v>46178.99990655078</v>
     <v>215</v>
     <v>11.8</v>
     <v>2046981444</v>
@@ -7484,11 +7482,11 @@
     <v>0</v>
     <v>15.475</v>
     <v>11.86</v>
-    <v>11.8613</v>
+    <v>11.650499999999999</v>
     <v>172595400</v>
     <v>POET</v>
     <v>POET Technologies Inc. (XNAS:POET)</v>
-    <v>56920442</v>
+    <v>57201960</v>
     <v>55707356</v>
     <v>2010</v>
   </rv>
@@ -7529,11 +7527,11 @@
     <v>4</v>
     <v>259.92</v>
     <v>121.99</v>
-    <v>1.5986</v>
+    <v>1.6242000000000001</v>
     <v>-26.63</v>
-    <v>-7.1319999999999995E-3</v>
+    <v>-1.9356999999999999E-2</v>
     <v>-0.10978300000000001</v>
-    <v>-1.54</v>
+    <v>-4.18</v>
     <v>USD</v>
     <v>Qualcomm Incorporated is engaged in the development and commercialization of foundational technologies for the wireless industry, including third generation (3G), fourth generation (4G) and fifth generation (5G) wireless connectivity, and high-performance and low-power computing, including on-device artificial intelligence. Its segments include Qualcomm CDMA Technologies (QCT), Qualcomm Technology Licensing (QTL) and Qualcomm Strategic Initiatives. QCT develops and supplies integrated circuits and system software based on 3G/4G/5G and other technologies, including radio frequency front-end, digital cockpit and advanced driver assistance and automated driving, Internet of things including consumer electronic devices, industrial devices and edge networking products. QTL grants licenses or otherwise provides rights to use portions of its intellectual property portfolio that includes certain patent rights essential to and/or useful in the manufacture and sale of certain wireless products.</v>
     <v>52000</v>
@@ -7545,7 +7543,7 @@
     <v>220</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46178.903501770314</v>
+    <v>46178.999979687498</v>
     <v>221</v>
     <v>215</v>
     <v>227600760000</v>
@@ -7555,11 +7553,11 @@
     <v>26.385100000000001</v>
     <v>242.57</v>
     <v>215.94</v>
-    <v>214.4</v>
+    <v>211.76</v>
     <v>1054000000</v>
     <v>QCOM</v>
     <v>QUALCOMM INCORPORATED (XNAS:QCOM)</v>
-    <v>24134590</v>
+    <v>24189155</v>
     <v>28705078</v>
     <v>1991</v>
   </rv>
@@ -7581,14 +7579,14 @@
     <v>2</v>
     <v>3</v>
     <v>Finance</v>
-    <v>26</v>
+    <v>4</v>
     <v>155.47</v>
     <v>74.510000000000005</v>
-    <v>0.64910000000000001</v>
+    <v>0.64410000000000001</v>
     <v>-1.625</v>
-    <v>0</v>
+    <v>-1.0919000000000002E-2</v>
     <v>-1.4571000000000001E-2</v>
-    <v>0</v>
+    <v>-1.2</v>
     <v>USD</v>
     <v>Qualys, Inc. is a provider of a cloud-based platform delivering information technology (IT), security and compliance solutions. The Company’s integrated suite of IT, security and compliance solutions delivered on Qualys' Enterprise TruRisk Platform enables its customers to identify and manage their IT and operational technology (OT) assets, collect, and analyze large amounts of IT security data, recommend, and implement remediation actions and verify the implementation of such actions. The Company provides its solutions through a software-as-a-service model, primarily with renewable annual subscriptions. Its cloud platform offers an integrated suite of solutions that automates the lifecycle of asset discovery and management, security and compliance assessments, and remediation for an organization’s IT infrastructure and assets, whether such infrastructure and assets reside inside the organization, on their network perimeter, on endpoints or in the cloud.</v>
     <v>2683</v>
@@ -7599,21 +7597,21 @@
     <v>113.1</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46178.843999258592</v>
+    <v>46178.916445555471</v>
     <v>224</v>
     <v>107.09910000000001</v>
     <v>3870349399</v>
     <v>QUALYS, INC.</v>
     <v>QUALYS, INC.</v>
     <v>112.02</v>
-    <v>19.7346</v>
+    <v>20.026399999999999</v>
     <v>111.52500000000001</v>
     <v>109.9</v>
-    <v>109.9</v>
+    <v>108.7</v>
     <v>35217010</v>
     <v>QLYS</v>
     <v>QUALYS, INC. (XNAS:QLYS)</v>
-    <v>589306</v>
+    <v>589331</v>
     <v>809737</v>
     <v>1999</v>
   </rv>
@@ -7635,21 +7633,21 @@
     <v>16</v>
     <v>17</v>
     <v>Finance</v>
-    <v>18</v>
+    <v>26</v>
     <v>748.65</v>
     <v>522.66</v>
     <v>1.0089999999999999</v>
     <v>-35.549999999999997</v>
-    <v>-2.5719999999999996E-3</v>
+    <v>-6.7510000000000001E-3</v>
     <v>-4.8000999999999995E-2</v>
-    <v>-1.8134999999999999</v>
+    <v>-4.76</v>
     <v>USD</v>
     <v>Nasdaq Stock Market</v>
     <v>XNAS</v>
     <v>1.8E-3</v>
     <v>731.69</v>
     <v>ETF</v>
-    <v>46178.903533599216</v>
+    <v>46178.999995671096</v>
     <v>227</v>
     <v>704.32</v>
     <v>493987523137.08002</v>
@@ -7657,10 +7655,10 @@
     <v>730.06</v>
     <v>740.61</v>
     <v>705.06</v>
-    <v>703.24649999999997</v>
+    <v>700.3</v>
     <v>QQQ</v>
     <v>Invesco QQQ Trust 1 (XNAS:QQQ)</v>
-    <v>98922418</v>
+    <v>99606571</v>
     <v>38925183</v>
   </rv>
   <rv s="2">
@@ -7684,11 +7682,11 @@
     <v>4</v>
     <v>468.11</v>
     <v>305.44009999999997</v>
-    <v>1.5580000000000001</v>
-    <v>-15.56</v>
-    <v>-6.0670000000000003E-3</v>
-    <v>-3.3661999999999997E-2</v>
-    <v>-2.71</v>
+    <v>1.5501</v>
+    <v>-15.53</v>
+    <v>-4.3200000000000001E-3</v>
+    <v>-3.3597000000000002E-2</v>
+    <v>-1.93</v>
     <v>USD</v>
     <v>Rockwell Automation, Inc. is engaged in industrial automation and digital transformation. The Company operates in three segments: Intelligent Devices, Software &amp; Control, and Lifecycle Services. The Intelligent Devices segment portfolio includes power control, motion control, safety, sensing, and industrial components, and micro control and distributed input/output. The Software &amp; Control operating segment contains a comprehensive portfolio of production automation and production operations platforms, including hardware and software. This integrated portfolio is merging information technology (IT) and operational technology (OT), bringing the benefits of the Connected Enterprise to the production system. The Lifecycle Services segment includes consulting services, including cybersecurity and digital transformation strategy and design and professional services, including global automation and information program and project management and delivery capabilities, and connected services.</v>
     <v>26000</v>
@@ -7699,21 +7697,21 @@
     <v>456.11500000000001</v>
     <v>Machinery, Equipment &amp; Components</v>
     <v>Stock</v>
-    <v>46178.899622407029</v>
+    <v>46178.997122060158</v>
     <v>230</v>
     <v>441.2</v>
-    <v>49703825652</v>
+    <v>49707163869</v>
     <v>ROCKWELL AUTOMATION, INC.</v>
     <v>ROCKWELL AUTOMATION, INC.</v>
     <v>456.1</v>
     <v>48.019100000000002</v>
     <v>462.24</v>
-    <v>446.68</v>
-    <v>444</v>
+    <v>446.71</v>
+    <v>444.78</v>
     <v>111273900</v>
     <v>ROK</v>
     <v>ROCKWELL AUTOMATION, INC. (XNYS:ROK)</v>
-    <v>843971</v>
+    <v>844023</v>
     <v>807415</v>
     <v>1996</v>
   </rv>
@@ -7738,11 +7736,11 @@
     <v>4</v>
     <v>7.18</v>
     <v>2.77</v>
-    <v>0.99790000000000001</v>
+    <v>1.0123</v>
     <v>-0.48499999999999999</v>
-    <v>-1.5079999999999998E-3</v>
+    <v>-1.0558000000000001E-2</v>
     <v>-0.127632</v>
-    <v>-5.0000000000000001E-3</v>
+    <v>-3.5000000000000003E-2</v>
     <v>USD</v>
     <v>Recursion Pharmaceuticals, Inc. is a clinical-stage TechBio company decoding biology and chemistry to industrialize drug discovery. Its Recursion Operating System (OS), a platform built across diverse technologies, enables the Company to map and navigate trillions of biological and chemical relationships within the Recursion Data Universe. The Company integrates physical and digital components as iterative loops of atoms and bits, scaling wet lab biology and chemistry data organized into virtuous cycles with computational tools to rapidly translate silico hypotheses into validated insights and novel chemistry. Its clinical programs in oncology and rare diseases include REC-617, REC-1245, REC-3565 and REC-4539. Its REC-617 is an orally bioavailable, cyclin-dependent kinase 7 (CDK7) inhibitor for the treatment of advanced solid tumors. Its REV102 program targets ectonucleotide pyrophosphatase/phosphodiesterase 1 (ENPP1), an enzyme implicated in the pathogenesis of HPP.</v>
     <v>600</v>
@@ -7753,7 +7751,7 @@
     <v>3.7</v>
     <v>Biotechnology &amp; Medical Research</v>
     <v>Stock</v>
-    <v>46178.902245450779</v>
+    <v>46178.999583865625</v>
     <v>233</v>
     <v>3.2050000000000001</v>
     <v>1756635738</v>
@@ -7763,11 +7761,11 @@
     <v>0</v>
     <v>3.8</v>
     <v>3.3149999999999999</v>
-    <v>3.31</v>
+    <v>3.28</v>
     <v>529905200</v>
     <v>RXRX</v>
     <v>RECURSION PHARMACEUTICALS, INC. (XNAS:RXRX)</v>
-    <v>26796035</v>
+    <v>26943925</v>
     <v>18521126</v>
     <v>2013</v>
   </rv>
@@ -7778,25 +7776,25 @@
     <v>https://www.bing.com/financeapi/forcetrigger?t=c2kadm&amp;q=XNYS%3aS&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
   </rv>
-  <rv s="1">
+  <rv s="10">
     <v>en-GB</v>
     <v>c2kadm</v>
     <v>268435456</v>
     <v>1</v>
     <v>Powered by Refinitiv</v>
-    <v>0</v>
+    <v>19</v>
     <v>SENTINELONE, INC. (XNYS:S)</v>
     <v>2</v>
-    <v>3</v>
+    <v>20</v>
     <v>Finance</v>
     <v>4</v>
     <v>21.4</v>
     <v>11.81</v>
-    <v>0.83179999999999998</v>
-    <v>-0.56999999999999995</v>
-    <v>-1.0031000000000002E-2</v>
-    <v>-3.4483E-2</v>
-    <v>-0.16</v>
+    <v>0.83299999999999996</v>
+    <v>-0.57999999999999996</v>
+    <v>-3.1350000000000002E-3</v>
+    <v>-3.5088000000000001E-2</v>
+    <v>-0.05</v>
     <v>USD</v>
     <v>SentinelOne, Inc. is an artificial intelligence (AI)-powered cybersecurity provider. The Company’s Singularity Platform delivers AI-powered autonomous threat prevention, detection, response, and exposure management capabilities across an organization’s endpoints, cloud workloads, and identity credentials. The Company’s Singularity platform ingests, correlates, and queries petabytes of structured and unstructured data from a myriad of ever-expanding disparate external and internal sources in real time. Its distributed AI models run both locally on every endpoint and every cloud workload, as well as on its cloud platform. The Company through PingSafe Pte. Ltd. (PingSafe), which is a cloud native application protection platform (CNAPP) to bolster its cloud security product suite. By adding PingSafe’s CNAPP to its Cloud Workload Security (CWS), it provides enterprises with a comprehensive cloud security coverage that drives security, improved posture, and autonomous protection.</v>
     <v>2700</v>
@@ -7807,21 +7805,20 @@
     <v>16.61</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46178.900013390623</v>
+    <v>46178.999621689065</v>
     <v>236</v>
     <v>15.640700000000001</v>
-    <v>5471147052</v>
+    <v>5467719015</v>
     <v>SENTINELONE, INC.</v>
     <v>SENTINELONE, INC.</v>
     <v>16.5</v>
-    <v>0</v>
     <v>16.53</v>
-    <v>15.96</v>
-    <v>15.79</v>
+    <v>15.95</v>
+    <v>15.9</v>
     <v>342803700</v>
     <v>S</v>
     <v>SENTINELONE, INC. (XNYS:S)</v>
-    <v>7571048</v>
+    <v>7589492</v>
     <v>9826033</v>
     <v>2013</v>
   </rv>
@@ -7832,21 +7829,21 @@
     <v>https://www.bing.com/financeapi/forcetrigger?t=aftlr7&amp;q=XETR%3aSAP&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
   </rv>
-  <rv s="10">
+  <rv s="11">
     <v>en-GB</v>
     <v>aftlr7</v>
     <v>268435456</v>
     <v>1</v>
     <v>Powered by Refinitiv</v>
-    <v>19</v>
+    <v>21</v>
     <v>SAP SE (XETR:SAP)</v>
     <v>2</v>
-    <v>20</v>
+    <v>22</v>
     <v>Finance</v>
-    <v>21</v>
+    <v>23</v>
     <v>273.55</v>
     <v>135.44</v>
-    <v>1.0986</v>
+    <v>1.1012</v>
     <v>-3.02</v>
     <v>-1.8359E-2</v>
     <v>EUR</v>
@@ -7897,11 +7894,11 @@
     <v>4</v>
     <v>107.5</v>
     <v>83.96</v>
-    <v>0.77229999999999999</v>
-    <v>0.81</v>
-    <v>-3.9283999999999999E-2</v>
-    <v>9.2049999999999996E-3</v>
-    <v>-3.49</v>
+    <v>0.76190000000000002</v>
+    <v>0.84</v>
+    <v>-8.3299999999999989E-3</v>
+    <v>9.5449999999999997E-3</v>
+    <v>-0.74</v>
     <v>USD</v>
     <v>The Charles Schwab Corporation is a savings and loan holding company. The Company, through its subsidiaries, engages in wealth management, securities brokerage, banking, asset management, custody, and financial advisory services. The Company provides financial services to individuals and institutional clients through two segments: Investor Services, and Advisor Services. The Investor Services segment provides retail brokerage, investment advisory, and banking and trust services to individual investors, and retirement plan and business services, as well as other corporate brokerage services, to businesses and their employees. The Advisor Services segment provides custodial, trading, banking and trust, and support services to independent registered investment advisors (RIAs), independent retirement advisors, and recordkeepers. Its products and services include brokerage, mutual funds, exchange-traded funds (ETFs), managed investing solutions, alternative investments, banking, and trust.</v>
     <v>33500</v>
@@ -7912,21 +7909,21 @@
     <v>88.94</v>
     <v>Investment Banking &amp; Investment Services</v>
     <v>Stock</v>
-    <v>46178.899415474218</v>
+    <v>46178.997039478905</v>
     <v>242</v>
     <v>87.674999999999997</v>
-    <v>154452579350</v>
+    <v>154504753400</v>
     <v>THE CHARLES SCHWAB CORPORATION</v>
     <v>THE CHARLES SCHWAB CORPORATION</v>
     <v>88.46</v>
-    <v>17.450700000000001</v>
+    <v>17.6172</v>
     <v>88</v>
-    <v>88.81</v>
-    <v>85.35</v>
+    <v>88.84</v>
+    <v>88.1</v>
     <v>1739135000</v>
     <v>SCHW</v>
     <v>THE CHARLES SCHWAB CORPORATION (XNYS:SCHW)</v>
-    <v>9211116</v>
+    <v>9213892</v>
     <v>11334281</v>
     <v>1986</v>
   </rv>
@@ -7946,12 +7943,12 @@
     <v>0</v>
     <v>THE SAGE GROUP PLC. (XLON:SGE)</v>
     <v>2</v>
-    <v>27</v>
+    <v>29</v>
     <v>Finance</v>
-    <v>28</v>
+    <v>30</v>
     <v>1335</v>
     <v>771.66</v>
-    <v>0.3473</v>
+    <v>0.35010000000000002</v>
     <v>-13.2</v>
     <v>1.8391000000000001E-2</v>
     <v>-1.4945999999999999E-2</v>
@@ -8005,11 +8002,11 @@
     <v>4</v>
     <v>39.93</v>
     <v>8.18</v>
-    <v>3.3264</v>
+    <v>3.3321999999999998</v>
     <v>-2.98</v>
-    <v>1.4299999999999998E-3</v>
+    <v>-7.4350000000000006E-3</v>
     <v>-7.8523999999999997E-2</v>
-    <v>0.05</v>
+    <v>-0.26</v>
     <v>USD</v>
     <v>SkyWater Technology, Inc. is an independent, pure-play technology foundry that offers advanced semiconductor development and manufacturing services. The Company’s Technology-as-a-Service (TaaS) model leverages a foundation of proprietary technology, engineering know-how capabilities, and microelectronics manufacturing capacity to co-develop process technology intellectual property (IP) with its customers that enable disruptive concepts through its Advanced Technology Services (ATS) for diverse microelectronics (integrated circuits (ICs)) and related micro- and nanotechnology applications. In addition to differentiated technology development services, it supports customers with volume production of ICs for high-growth markets through its Wafer Services. Its Wafer Services include the manufacture of silicon-based analog and mixed-signal ICs for its end markets. Through its ATS model, it specializes in co-creating advanced solutions with its customers that directly serve its end markets.</v>
     <v>1551</v>
@@ -8020,7 +8017,7 @@
     <v>36.770000000000003</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46178.895729560158</v>
+    <v>46178.994646573439</v>
     <v>248</v>
     <v>34.81</v>
     <v>1720684862</v>
@@ -8030,11 +8027,11 @@
     <v>16.267199999999999</v>
     <v>37.950000000000003</v>
     <v>34.97</v>
-    <v>35.020000000000003</v>
+    <v>34.71</v>
     <v>49204600</v>
     <v>SKYT</v>
     <v>SKYWATER TECHNOLOGY, INC. (XNAS:SKYT)</v>
-    <v>1097087</v>
+    <v>1097538</v>
     <v>1173283</v>
     <v>2016</v>
   </rv>
@@ -8059,11 +8056,11 @@
     <v>4</v>
     <v>62.357999999999997</v>
     <v>19.48</v>
-    <v>1.8715999999999999</v>
+    <v>1.8985000000000001</v>
     <v>-5.26</v>
-    <v>-6.2439999999999996E-3</v>
+    <v>-2.2393999999999997E-2</v>
     <v>-0.112154</v>
-    <v>-0.26</v>
+    <v>-0.9325</v>
     <v>USD</v>
     <v>Super Micro Computer, Inc. is an application-optimized Total IT solutions provider including server, artificial intelligence (AI) systems, storage, Internet of Things (IoT) devices, switches, software, and support services. Total IT Solutions include complete servers, storage systems, modular blade servers, workstations, full-rack scale solutions, networking devices, server sub-systems, and server management. Its products are designed and manufactured in-house (in the United States, Taiwan, and the Netherlands). The Company's portfolio of Server Building Block Solutions allows customers to optimize for their exact workload and application by selecting from a broad family of systems built from the Company's flexible and reusable building blocks that support a comprehensive set of form factors, processors, memory, GPUs, storage, networking, power, and cooling solutions (air-conditioned, free air cooling or liquid cooling).</v>
     <v>6238</v>
@@ -8074,7 +8071,7 @@
     <v>45.259900000000002</v>
     <v>Computers, Phones &amp; Household Electronics</v>
     <v>Stock</v>
-    <v>46178.90346310156</v>
+    <v>46178.999962187503</v>
     <v>251</v>
     <v>41.040100000000002</v>
     <v>25043066340</v>
@@ -8084,11 +8081,11 @@
     <v>25.555099999999999</v>
     <v>46.9</v>
     <v>41.64</v>
-    <v>41.38</v>
+    <v>40.707500000000003</v>
     <v>601418500</v>
     <v>SMCI</v>
     <v>SUPER MICRO COMPUTER, INC. (XNAS:SMCI)</v>
-    <v>48999521</v>
+    <v>49259573</v>
     <v>44861883</v>
     <v>2006</v>
   </rv>
@@ -8110,21 +8107,21 @@
     <v>16</v>
     <v>17</v>
     <v>Finance</v>
-    <v>18</v>
+    <v>26</v>
     <v>642.77</v>
     <v>249.76</v>
     <v>1.5567</v>
     <v>-57.84</v>
-    <v>-2.8679999999999999E-3</v>
+    <v>-5.8279999999999998E-3</v>
     <v>-9.2171000000000003E-2</v>
-    <v>-1.6339999999999999</v>
+    <v>-3.32</v>
     <v>USD</v>
     <v>Nasdaq Stock Market</v>
     <v>XNAS</v>
     <v>3.4999999999999996E-3</v>
     <v>607</v>
     <v>ETF</v>
-    <v>46178.903555450779</v>
+    <v>46178.999983529684</v>
     <v>254</v>
     <v>569.69000000000005</v>
     <v>67822489502.050003</v>
@@ -8132,10 +8129,10 @@
     <v>605.09</v>
     <v>627.53</v>
     <v>569.69000000000005</v>
-    <v>568.05600000000004</v>
+    <v>566.37</v>
     <v>SMH</v>
     <v>VanEck:Semiconductor (XNAS:SMH)</v>
-    <v>21985741</v>
+    <v>22038001</v>
     <v>9925831</v>
   </rv>
   <rv s="2">
@@ -8145,25 +8142,25 @@
     <v>https://www.bing.com/financeapi/forcetrigger?t=bx1rdm&amp;q=XNYS%3aSMR&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
   </rv>
-  <rv s="1">
+  <rv s="10">
     <v>en-GB</v>
     <v>bx1rdm</v>
     <v>268435456</v>
     <v>1</v>
     <v>Powered by Refinitiv</v>
-    <v>0</v>
+    <v>19</v>
     <v>NUSCALE POWER CORPORATION (XNYS:SMR)</v>
     <v>2</v>
-    <v>3</v>
+    <v>20</v>
     <v>Finance</v>
     <v>4</v>
     <v>57.42</v>
     <v>8.85</v>
-    <v>2.2237</v>
-    <v>-1.5049999999999999</v>
-    <v>3.81E-3</v>
-    <v>-0.125417</v>
-    <v>0.04</v>
+    <v>2.2553000000000001</v>
+    <v>-1.5</v>
+    <v>-1.2418999999999999E-2</v>
+    <v>-0.125</v>
+    <v>-0.13039999999999999</v>
     <v>USD</v>
     <v>NuScale Power Corporation is a provider of proprietary advanced small modular reactor (SMR) nuclear technology. The NuScale Power Module, the Company's SMR technology, is a small pressurized water reactor that can generate approximately 77 megawatts of electricity (MWe) or 250 megawatts thermal (gross) and can be scaled to meet customer needs through an array of flexible configurations of up to 924 MWe (12 modules) of output. In addition to the sale of NPMs, it offers a diversified suite of services throughout the development and operating life of the power plant. The Company's suite of services is planned to include licensing support, testing, training, fuel supply services and program management, among others. It serves a range of customers consisting of domestic and international governments, utilities, state-owned enterprises and technology and industrial companies in need of carbon-free, reliable energy.</v>
     <v>428</v>
@@ -8174,21 +8171,20 @@
     <v>12.24</v>
     <v>Electrical Utilities &amp; IPPs</v>
     <v>Stock</v>
-    <v>46178.903532291406</v>
+    <v>46178.999920265625</v>
     <v>257</v>
     <v>10.15</v>
-    <v>3835725193</v>
+    <v>3837552600</v>
     <v>NUSCALE POWER CORPORATION</v>
     <v>NUSCALE POWER CORPORATION</v>
     <v>12.2</v>
-    <v>0</v>
     <v>12</v>
-    <v>10.494999999999999</v>
-    <v>10.54</v>
+    <v>10.5</v>
+    <v>10.3696</v>
     <v>365481200</v>
     <v>SMR</v>
     <v>NUSCALE POWER CORPORATION (XNYS:SMR)</v>
-    <v>49643477</v>
+    <v>50039710</v>
     <v>34103479</v>
     <v>2022</v>
   </rv>
@@ -8211,9 +8207,9 @@
     <v>37.33</v>
     <v>2.746</v>
     <v>-200.36</v>
-    <v>-4.0530000000000002E-3</v>
+    <v>-1.9124000000000002E-2</v>
     <v>-0.113862</v>
-    <v>-6.32</v>
+    <v>-29.82</v>
     <v>USD</v>
     <v>SanDisk Corporation is a developer, manufacturer and provider of data storage devices and solutions based on NAND flash technology and has consumer brands and franchises globally. The Company's solutions include a range of solid state drives (SSDs) embedded products, removable cards, universal serial bus (USB) drives, and wafers and components. Its broad portfolio of technology and products addresses multiple end markets of Datacenter, Edge and Consumer. Its Datacenter end market is composed primarily of products for public or private cloud environments and enterprise customers. The Company, through the Edge end market, provides original equipment manufacturer and channel customers a broad array of high-performance flash solutions across personal computer, mobile, gaming, automotive, virtual reality headsets, at-home entertainment, and industrial spaces. The Company serves the Consumer end market with a broad range of retail and other end-user products.</v>
     <v>11000</v>
@@ -8224,7 +8220,7 @@
     <v>1681.9999</v>
     <v>Computers, Phones &amp; Household Electronics</v>
     <v>Stock</v>
-    <v>46178.903556631252</v>
+    <v>46178.999999015628</v>
     <v>1514.36</v>
     <v>230919386936</v>
     <v>SANDISK CORPORATION</v>
@@ -8233,11 +8229,11 @@
     <v>62.211199999999998</v>
     <v>1759.68</v>
     <v>1559.32</v>
-    <v>1553</v>
+    <v>1529.5</v>
     <v>148089800</v>
     <v>SNDK</v>
     <v>SANDISK CORPORATION (XNAS:SNDK)</v>
-    <v>13139609</v>
+    <v>13288987</v>
     <v>13846622</v>
     <v>2024</v>
   </rv>
@@ -8248,25 +8244,25 @@
     <v>https://www.bing.com/financeapi/forcetrigger?t=bvlqa2&amp;q=XNYS%3aSNOW&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
   </rv>
-  <rv s="1">
+  <rv s="10">
     <v>en-GB</v>
     <v>bvlqa2</v>
     <v>268435456</v>
     <v>1</v>
     <v>Powered by Refinitiv</v>
-    <v>0</v>
+    <v>19</v>
     <v>SNOWFLAKE INC. (XNYS:SNOW)</v>
     <v>2</v>
-    <v>3</v>
+    <v>20</v>
     <v>Finance</v>
     <v>4</v>
     <v>284.99</v>
     <v>118.3</v>
-    <v>1.3585</v>
-    <v>-5.95</v>
-    <v>-7.6429999999999996E-3</v>
-    <v>-2.4367E-2</v>
-    <v>-1.821</v>
+    <v>1.3641000000000001</v>
+    <v>-5.92</v>
+    <v>-1.3431E-2</v>
+    <v>-2.4243999999999998E-2</v>
+    <v>-3.2</v>
     <v>USD</v>
     <v>Snowflake Inc. is an artificial intelligence (AI) data cloud company. The Company provides a platform which powers the AI data cloud, enabling customers to consolidate data into a single source of truth to drive insights, apply AI to solve business problems, build data applications, and share data and data products. Its cloud-native architecture includes three independently scalable but logically integrated layers across storage, compute, and cloud services. The storage layer ingests massive amounts and varieties of structured, semi-structured, and unstructured data. The compute layer provides dedicated resources to enable users to simultaneously access common data sets for many use cases with minimal latency. The cloud services layer enables users to securely use AI within applications, tools, and processes. Its platform supports a wide range of product categories for customers’ business objectives, including analytics, data engineering, AI, applications and collaboration.</v>
     <v>9060</v>
@@ -8277,21 +8273,20 @@
     <v>247.55</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46178.903320763282</v>
+    <v>46178.999972001562</v>
     <v>262</v>
     <v>235</v>
     <v>60745624254</v>
     <v>SNOWFLAKE INC.</v>
     <v>SNOWFLAKE INC.</v>
     <v>242.2</v>
-    <v>0</v>
     <v>244.18</v>
-    <v>238.23</v>
-    <v>236.43899999999999</v>
+    <v>238.26</v>
+    <v>235.06</v>
     <v>346600000</v>
     <v>SNOW</v>
     <v>SNOWFLAKE INC. (XNYS:SNOW)</v>
-    <v>7148731</v>
+    <v>7162806</v>
     <v>10883534</v>
     <v>2012</v>
   </rv>
@@ -8316,11 +8311,11 @@
     <v>4</v>
     <v>651.73</v>
     <v>376.18</v>
-    <v>1.2104999999999999</v>
+    <v>1.2114</v>
     <v>-29.63</v>
-    <v>-4.6470000000000001E-3</v>
+    <v>-3.4420000000000002E-4</v>
     <v>-5.9922000000000003E-2</v>
-    <v>-2.16</v>
+    <v>-0.16</v>
     <v>USD</v>
     <v>Synopsys, Inc. is engaged in providing engineering solutions from silicon to systems, enabling customers to innovate artificial intelligence (AI)-powered products. It delivers silicon design, intellectual property (IP), simulation and analysis solutions, and design services. It supplies mission-critical electronic design automation (EDA) software that engineers use to design and test integrated circuits (ICs). Its Design Automation segment includes its silicon design, verification products and services, Ansys products, system integration products and services, digital, custom and field programmable gate array integrated circuit design software, verification software and hardware products, manufacturing software products and others. Its Design IP segment's portfolio includes logic libraries, embedded memories, interface IP, security IP, and subsystems that serve companies in the semiconductor and electronics industries.</v>
     <v>28000</v>
@@ -8331,21 +8326,21 @@
     <v>488.952</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46178.902526296093</v>
+    <v>46178.999514108596</v>
     <v>265</v>
     <v>458.53</v>
     <v>89009152605</v>
     <v>SYNOPSYS, INC.</v>
     <v>SYNOPSYS, INC.</v>
     <v>487.98</v>
-    <v>114.598</v>
+    <v>107.7313</v>
     <v>494.48</v>
     <v>464.85</v>
-    <v>462.69</v>
+    <v>464.69</v>
     <v>191479300</v>
     <v>SNPS</v>
     <v>SYNOPSYS, INC. (XNAS:SNPS)</v>
-    <v>1837962</v>
+    <v>1839401</v>
     <v>1884765</v>
     <v>1987</v>
   </rv>
@@ -8370,11 +8365,11 @@
     <v>4</v>
     <v>22.17</v>
     <v>5.83</v>
-    <v>2.7570999999999999</v>
+    <v>2.8</v>
     <v>-0.62</v>
-    <v>1.34E-3</v>
+    <v>-2.7060000000000001E-3</v>
     <v>-7.7403E-2</v>
-    <v>9.9000000000000008E-3</v>
+    <v>-0.02</v>
     <v>USD</v>
     <v>SoundHound AI, Inc. is engaged in conversational intelligence, offering voice and conversational artificial intelligence (AI) solutions that let businesses offer experiences to their customers. Through its proprietary technology, its voice AI delivers speed and accuracy in numerous languages to product creators and service providers across retail, financial services, healthcare, automotive, smart devices, and restaurants via AI-driven products, such as Smart Answering, Smart Ordering, Dynamic Drive Thru, and Amelia AI Agents. Along with SoundHound Chat AI, a voice assistant with integrated Generative AI, it powers various products and services, and processes billions of interactions each year for businesses. Its developer platform, Houndify, is an open-access platform that allows developers to leverage its Voice AI technology and a library of over 100 content domains, including commonly used domains for points of interest, weather, flight status, sports and more.</v>
     <v>954</v>
@@ -8385,7 +8380,7 @@
     <v>7.94</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46178.903227464842</v>
+    <v>46178.999919166403</v>
     <v>268</v>
     <v>7.21</v>
     <v>3198167344</v>
@@ -8395,11 +8390,11 @@
     <v>0</v>
     <v>8.01</v>
     <v>7.39</v>
-    <v>7.3998999999999997</v>
+    <v>7.37</v>
     <v>432769600</v>
     <v>SOUN</v>
     <v>SOUNDHOUND AI, INC. (XNAS:SOUN)</v>
-    <v>31706696</v>
+    <v>31875812</v>
     <v>30633277</v>
     <v>2020</v>
   </rv>
@@ -8421,21 +8416,21 @@
     <v>16</v>
     <v>17</v>
     <v>Finance</v>
-    <v>18</v>
+    <v>26</v>
     <v>618.84</v>
     <v>214.41</v>
     <v>1.7036</v>
     <v>-62.95</v>
-    <v>7.2249999999999994E-4</v>
+    <v>-7.744E-3</v>
     <v>-0.10444300000000001</v>
-    <v>0.39</v>
+    <v>-4.18</v>
     <v>USD</v>
     <v>Nasdaq Stock Market</v>
     <v>XNAS</v>
     <v>3.4000000000000002E-3</v>
     <v>580.5</v>
     <v>ETF</v>
-    <v>46178.903428171092</v>
+    <v>46178.999932997656</v>
     <v>271</v>
     <v>539.57000000000005</v>
     <v>38373488686.160004</v>
@@ -8443,10 +8438,10 @@
     <v>577.86</v>
     <v>602.72</v>
     <v>539.77</v>
-    <v>540.16</v>
+    <v>535.59</v>
     <v>SOXX</v>
     <v>iShares:Semiconductor (XNAS:SOXX)</v>
-    <v>22286805</v>
+    <v>22377273</v>
     <v>8332202</v>
   </rv>
   <rv s="2">
@@ -8467,32 +8462,32 @@
     <v>16</v>
     <v>17</v>
     <v>Finance</v>
-    <v>18</v>
+    <v>26</v>
     <v>760.4</v>
     <v>591.04999999999995</v>
     <v>0.99709999999999999</v>
-    <v>-19.68</v>
-    <v>-2.908E-3</v>
-    <v>-2.5994000000000003E-2</v>
-    <v>-2.145</v>
+    <v>-19.54</v>
+    <v>-3.444E-3</v>
+    <v>-2.5809000000000002E-2</v>
+    <v>-2.5402999999999998</v>
     <v>USD</v>
     <v>NYSE Arca</v>
     <v>ARCX</v>
     <v>9.4499999999999998E-4</v>
     <v>752.82</v>
     <v>ETF</v>
-    <v>46178.903564582812</v>
+    <v>46178.999997407031</v>
     <v>274</v>
     <v>735.52499999999998</v>
     <v>783796407176.76001</v>
     <v>State Street SPDR S&amp;P500</v>
     <v>752.31</v>
     <v>757.09</v>
-    <v>737.41</v>
-    <v>735.40499999999997</v>
+    <v>737.55</v>
+    <v>735.00969999999995</v>
     <v>SPY</v>
     <v>State Street SPDR S&amp;P500 (ARCX:SPY)</v>
-    <v>92040132</v>
+    <v>93989416</v>
     <v>44866988</v>
   </rv>
   <rv s="2">
@@ -8516,11 +8511,11 @@
     <v>4</v>
     <v>90.9</v>
     <v>51.93</v>
-    <v>1.4782</v>
+    <v>1.4797</v>
     <v>-6.36</v>
-    <v>-1.8894000000000001E-2</v>
+    <v>-1.1960999999999999E-2</v>
     <v>-7.9570000000000002E-2</v>
-    <v>-1.39</v>
+    <v>-0.88</v>
     <v>USD</v>
     <v>Skyworks Solutions, Inc. provides wireless networking services. The Company’s analog and mixed-signal semiconductors are connecting people, places, and things, spanning a number of new applications within the aerospace, automotive, broadband, cellular infrastructure, connected home, defense, entertainment and gaming, industrial, medical, smartphone, tablet, and wearable markets. It operates engineering, manufacturing, sales, and service facilities throughout Asia, Europe, and North America. The Company offers a range of products, such as Amplifiers, Attenuators, Diodes, Audio And Radio, Clocks And Timing, Front-End Modules, Isolation, Modems And DAAs, Optocouplers, Power Management, Power Over Ethernet, RF Passives, Television (TV) And Video, Switches, and Voice. Its engineering, marketing, operations, sales, and support facilities are located throughout Asia, Europe, and North America.</v>
     <v>10000</v>
@@ -8531,7 +8526,7 @@
     <v>78.37</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46178.900726203123</v>
+    <v>46178.999581770309</v>
     <v>277</v>
     <v>72.8</v>
     <v>11065362062</v>
@@ -8541,11 +8536,11 @@
     <v>31.577400000000001</v>
     <v>79.930000000000007</v>
     <v>73.569999999999993</v>
-    <v>72.180000000000007</v>
+    <v>72.69</v>
     <v>150405900</v>
     <v>SWKS</v>
     <v>SKYWORKS SOLUTIONS, INC. (XNAS:SWKS)</v>
-    <v>7168503</v>
+    <v>7170155</v>
     <v>5532867</v>
     <v>2002</v>
   </rv>
@@ -8570,11 +8565,11 @@
     <v>4</v>
     <v>87.88</v>
     <v>27.26</v>
-    <v>1.9272</v>
+    <v>1.9351</v>
     <v>-3.39</v>
-    <v>4.0889999999999998E-3</v>
+    <v>5.2249999999999996E-3</v>
     <v>-7.1503999999999998E-2</v>
-    <v>0.18</v>
+    <v>0.23</v>
     <v>USD</v>
     <v>Symbotic Inc. is an automation technology company, which focuses on reimagining the supply chain with its end-to-end, artificial intelligence-powered robotic and software platform. It is engaged in developing, commercializing, and deploying innovative and comprehensive technology solutions that improve supply chain operations. The Company automates the processing of pallets, cases and individual items in warehouses. Its systems enhance operations at the front end of the supply chain and therefore benefit all supply partners further down the chain, irrespective of fulfillment strategy. Its robotic-based automation systems, which include hardware and essential software, move, store and sort cases and reach in warehouses. Its systems are operational in a number of retailers, including Walmart, wholesale distributors, including C&amp;S Wholesale Grocers, and are being deployed in GreenBox Systems LLC, which is doing business as Exol (Exol), its warehouse-as-a-service joint venture.</v>
     <v>2000</v>
@@ -8585,7 +8580,7 @@
     <v>46.75</v>
     <v>Machinery, Equipment &amp; Components</v>
     <v>Stock</v>
-    <v>46178.903448541409</v>
+    <v>46178.999755971876</v>
     <v>280</v>
     <v>43.29</v>
     <v>26531153336</v>
@@ -8595,11 +8590,11 @@
     <v>0</v>
     <v>47.41</v>
     <v>44.02</v>
-    <v>44.2</v>
+    <v>44.25</v>
     <v>602706800</v>
     <v>SYM</v>
     <v>SYMBOTIC INC. (XNAS:SYM)</v>
-    <v>2842944</v>
+    <v>2850144</v>
     <v>2544090</v>
     <v>2022</v>
   </rv>
@@ -8622,9 +8617,9 @@
     <v>41.73</v>
     <v>3.121</v>
     <v>-5.83</v>
-    <v>-3.4069999999999999E-3</v>
+    <v>-1.0123E-2</v>
     <v>-0.11155799999999999</v>
-    <v>-0.15820000000000001</v>
+    <v>-0.47</v>
     <v>USD</v>
     <v>Tempus AI, Inc. is a technology company advancing precision medicine through the practical application of artificial intelligence in healthcare. It offers AI-enabled precision medicine solutions to physicians to deliver personalized patient care and, in parallel, facilitates discovery, development and delivery of optimal therapeutics. It provides three product lines: Genomics, Data and artificial intelligence applications (AI). The Genomics product line leverages its laboratories to provide next generation sequencing (NGS) diagnostics, polymerase chain reaction, profiling, molecular genotyping and other anatomic and molecular pathology testing. The data generated in its lab or ingested into its platform is structured and de-identified, prior to commercialization. Its AI Applications is focused on developing and providing diagnostics that are algorithmic in nature, implementing new software as a medical device, and building and deploying clinical decision support tools.</v>
     <v>3800</v>
@@ -8635,7 +8630,7 @@
     <v>52.23</v>
     <v>Biotechnology &amp; Medical Research</v>
     <v>Stock</v>
-    <v>46178.903331365625</v>
+    <v>46178.999955810155</v>
     <v>45.84</v>
     <v>8337193664</v>
     <v>TEMPUS AI, INC.</v>
@@ -8644,11 +8639,11 @@
     <v>0</v>
     <v>52.26</v>
     <v>46.43</v>
-    <v>46.271799999999999</v>
+    <v>45.96</v>
     <v>179564800</v>
     <v>TEM</v>
     <v>TEMPUS AI, INC. (XNAS:TEM)</v>
-    <v>8819522</v>
+    <v>8873465</v>
     <v>7115978</v>
     <v>2025</v>
   </rv>
@@ -8673,11 +8668,11 @@
     <v>4</v>
     <v>422.11</v>
     <v>81.069999999999993</v>
-    <v>1.7878000000000001</v>
+    <v>1.7955000000000001</v>
     <v>-48.93</v>
-    <v>-1.3969999999999998E-3</v>
+    <v>-1.7964000000000001E-2</v>
     <v>-0.12026199999999999</v>
-    <v>-0.5</v>
+    <v>-6.43</v>
     <v>USD</v>
     <v>Teradyne, Inc. is a global supplier of automated test equipment and robotics solutions. It designs, develops, manufactures and sells automated test systems and robotics products. Its segment includes Semiconductor Test, Robotics, and Product Test. The Semiconductor Test segment includes operations related to the design, manufacturing and marketing of semiconductor test products and services, inclusive of storage and system level test products. The Robotics segment includes operations related to the design, manufacturing and marketing of collaborative robotic arms and autonomous mobile robots. The Product Test segment includes operations related to the design, manufacturing and marketing of products and services for defense/aerospace test, circuit-board test, wireless test systems, and silicon photonics testing. Its offerings also include defense/aerospace test instrumentation and systems, circuit-board test and inspection (production board test) systems, and wireless test systems.</v>
     <v>6600</v>
@@ -8688,7 +8683,7 @@
     <v>392.92</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46178.90289351852</v>
+    <v>46178.999655485939</v>
     <v>285</v>
     <v>354.13</v>
     <v>56031149646</v>
@@ -8698,11 +8693,11 @@
     <v>75.301900000000003</v>
     <v>406.86</v>
     <v>357.93</v>
-    <v>357.43</v>
+    <v>351.5</v>
     <v>156542200</v>
     <v>TER</v>
     <v>TERADYNE, INC. (XNAS:TER)</v>
-    <v>5466474</v>
+    <v>5471125</v>
     <v>3817823</v>
     <v>1960</v>
   </rv>
@@ -8727,11 +8722,11 @@
     <v>4</v>
     <v>498.83</v>
     <v>273.20999999999998</v>
-    <v>1.802</v>
+    <v>1.8163</v>
     <v>-27.45</v>
-    <v>1.611E-3</v>
+    <v>8.2479999999999999E-4</v>
     <v>-6.5599000000000005E-2</v>
-    <v>0.63</v>
+    <v>0.32250000000000001</v>
     <v>USD</v>
     <v>Tesla, Inc. designs, develops, manufactures, sells and leases high-performance fully electric vehicles and energy generation and storage systems, and offers services related to its products. Its segments include automotive, and energy generation and storage. The automotive segment includes the design, development, manufacturing, sales and leasing of high-performance fully electric vehicles, and sales of automotive regulatory credits. It also includes sales of used vehicles, non-warranty maintenance services and collisions, part sales, paid supercharging, insurance services revenue and retail merchandise sales. The energy generation and storage segment include the design, manufacture, installation, sales and leasing of solar energy generation and energy storage products and related services and sales of solar energy systems incentives. Its consumer vehicles include the Model 3, Y, S, X and Cybertruck. Its lithium-ion battery energy storage products include Powerwall and Megapack.</v>
     <v>134785</v>
@@ -8742,21 +8737,21 @@
     <v>424.67989999999998</v>
     <v>Automobiles &amp; Auto Parts</v>
     <v>Stock</v>
-    <v>46178.90356746484</v>
+    <v>46178.999997360937</v>
     <v>288</v>
     <v>388.59</v>
     <v>1468488084000</v>
     <v>TESLA, INC.</v>
     <v>TESLA, INC.</v>
     <v>420.5</v>
-    <v>382.47449999999998</v>
+    <v>357.37139999999999</v>
     <v>418.45</v>
     <v>391</v>
-    <v>391.63</v>
+    <v>391.32249999999999</v>
     <v>3755724000</v>
     <v>TSLA</v>
     <v>TESLA, INC. (XNAS:TSLA)</v>
-    <v>63032456</v>
+    <v>63420177</v>
     <v>50602142</v>
     <v>2024</v>
   </rv>
@@ -8776,16 +8771,16 @@
     <v>0</v>
     <v>Taiwan Semiconductor Manufacturing Company Limited (XNYS:TSM)</v>
     <v>2</v>
-    <v>29</v>
+    <v>31</v>
     <v>Finance</v>
     <v>4</v>
     <v>450.16359999999997</v>
     <v>202.28</v>
-    <v>1.2762</v>
-    <v>-29.72</v>
-    <v>-9.5620000000000011E-3</v>
-    <v>-6.6798999999999997E-2</v>
-    <v>-3.97</v>
+    <v>1.2768999999999999</v>
+    <v>-29.75</v>
+    <v>-8.7670000000000005E-3</v>
+    <v>-6.6866000000000009E-2</v>
+    <v>-3.64</v>
     <v>USD</v>
     <v>Taiwan Semiconductor Manufacturing Co Ltd is a Taiwan-based integrated circuit foundry service provider. The Company is primarily engaged in integrated circuit manufacturing services. It offers advanced process technologies, specialised process solutions, advanced photomask and silicon stacking, and packaging-related technologies, while supporting a comprehensive design ecosystem. The Company's products serve diverse electronic sectors including artificial intelligence, high-performance computing, wired and wireless communications, automotive and industrial equipment, personal computing, information applications, consumer electronics, smart internet of things, and wearable devices.</v>
     <v>52045</v>
@@ -8796,21 +8791,21 @@
     <v>433.9</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46178.90356491875</v>
+    <v>46178.999977060157</v>
     <v>291</v>
     <v>412.79</v>
     <v>2264881331060</v>
     <v>Taiwan Semiconductor Manufacturing Company Limited</v>
     <v>Taiwan Semiconductor Manufacturing Company Limited</v>
     <v>429.77</v>
-    <v>37.644300000000001</v>
+    <v>35.127000000000002</v>
     <v>444.92</v>
-    <v>415.2</v>
-    <v>411.2</v>
+    <v>415.17</v>
+    <v>411.53</v>
     <v>25932370000</v>
     <v>TSM</v>
     <v>Taiwan Semiconductor Manufacturing Company Limited (XNYS:TSM)</v>
-    <v>19467361</v>
+    <v>19644166</v>
     <v>12807836</v>
     <v>1987</v>
   </rv>
@@ -8835,11 +8830,11 @@
     <v>4</v>
     <v>238.47989999999999</v>
     <v>91.84</v>
-    <v>1.3594999999999999</v>
-    <v>-10.52</v>
-    <v>-6.6820000000000004E-3</v>
-    <v>-4.4455999999999996E-2</v>
-    <v>-1.51</v>
+    <v>1.3119000000000001</v>
+    <v>-10.65</v>
+    <v>-1.7257000000000002E-2</v>
+    <v>-4.5004999999999996E-2</v>
+    <v>-3.9</v>
     <v>USD</v>
     <v>Twilio Inc. provides a customer engagement platform to build direct, personalized relationships with their customers everywhere in the world. Its platform provides developers with tools to build, scale, and deploy real-time communications within software applications. Its segments include Twilio Communications (Communications) and Twilio Segment (Segment). The Communications segment consists of a variety of application programming interfaces (APIs) and software solutions to optimize communications between its customers and their end users. Its key offerings in its Communications segment include Messaging, Voice, Email (includes Marketing Campaigns), Flex and User Authentication and Identity. Its Twilio Flex is a digital engagement center for the entire customer journey. Twilio Segment is a customer data platform that provides businesses with the tools to harness the power of contextual data by unifying real-time information collected throughout each customer’s journey into a profile.</v>
     <v>5558</v>
@@ -8850,21 +8845,21 @@
     <v>237.3</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46178.898249791404</v>
+    <v>46178.99986462891</v>
     <v>294</v>
     <v>224.23</v>
-    <v>34319114268</v>
+    <v>34299383661</v>
     <v>TWILIO INC.</v>
     <v>TWILIO INC.</v>
     <v>233.79499999999999</v>
-    <v>367.84750000000003</v>
+    <v>351.298</v>
     <v>236.64</v>
-    <v>226.12</v>
-    <v>224.48</v>
+    <v>225.99</v>
+    <v>222.09</v>
     <v>151773900</v>
     <v>TWLO</v>
     <v>TWILIO INC. (XNYS:TWLO)</v>
-    <v>3384902</v>
+    <v>3389142</v>
     <v>3392471</v>
     <v>2008</v>
   </rv>
@@ -8889,11 +8884,11 @@
     <v>4</v>
     <v>379.935</v>
     <v>107.38</v>
-    <v>2.0377000000000001</v>
-    <v>-23.48</v>
-    <v>-3.96E-3</v>
-    <v>-7.248700000000001E-2</v>
-    <v>-1.19</v>
+    <v>2.0459000000000001</v>
+    <v>-23.41</v>
+    <v>-1.0813999999999999E-2</v>
+    <v>-7.2271000000000002E-2</v>
+    <v>-3.2498</v>
     <v>USD</v>
     <v>Vertiv Holdings Co. provides mission-critical digital infrastructure technologies and lifecycle services primarily for data centers, communication networks, and commercial and industrial environments. The Company operates in three business segments: the Americas; Asia Pacific, and Europe, Middle East &amp; Africa. The Company's offerings include alternate current (AC) and direct current (DC) power management, thermal management, low/medium voltage switchgear, busbar, air cooled and liquid cooled thermal management products, integrated modular solutions, racks, single phase UPS, rack power distribution, rack thermal systems, configurable integrated solutions, energy storage solutions, hardware, software for managing IT equipment, management systems for monitoring and controlling digital infrastructure, and services. It also provides preventative maintenance, acceptance testing, engineering and consulting, remote monitoring, training, spare parts, specialized fluid management, and others.</v>
     <v>34000</v>
@@ -8904,21 +8899,21 @@
     <v>315</v>
     <v>Machinery, Equipment &amp; Components</v>
     <v>Stock</v>
-    <v>46178.903557638281</v>
+    <v>46178.999989050782</v>
     <v>297</v>
     <v>294.39499999999998</v>
-    <v>115401647872</v>
+    <v>115428535488</v>
     <v>VERTIV HOLDINGS CO</v>
     <v>VERTIV HOLDINGS CO</v>
     <v>313.755</v>
     <v>81.325199999999995</v>
     <v>323.92</v>
-    <v>300.44</v>
-    <v>299.32</v>
+    <v>300.51</v>
+    <v>297.2602</v>
     <v>384108800</v>
     <v>VRT</v>
     <v>VERTIV HOLDINGS CO (XNYS:VRT)</v>
-    <v>7295984</v>
+    <v>7330005</v>
     <v>5671869</v>
     <v>2016</v>
   </rv>
@@ -8943,11 +8938,11 @@
     <v>4</v>
     <v>257.08999999999997</v>
     <v>110.36</v>
-    <v>1.0787</v>
+    <v>1.0722</v>
     <v>-3.63</v>
-    <v>-4.4390000000000002E-3</v>
+    <v>-6.0990000000000003E-3</v>
     <v>-2.4542000000000001E-2</v>
-    <v>-0.64039999999999997</v>
+    <v>-0.88</v>
     <v>USD</v>
     <v>Workday, Inc. is an enterprise artificial intelligence (AI) platform for managing people, money, and agents. The Company provides organizations with cloud solutions powered by artificial intelligence (AI) to solve business challenges, including supporting and empowering the workforce, managing finances and spending. It offers a suite of cloud-based enterprise solutions that address the needs of the C-suite on a platform designed to be open, extensible, and configurable, allowing integration with other applications and the ability for customers and partners to build custom applications. It offers Workday Build, which is an open developer platform that provides customers and partners with the ability to create and share AI-powered solutions. It serves financial services, government, healthcare, higher education, hospitality, manufacturing, professional and business services, retail, technology and media, and transportation.</v>
     <v>20834</v>
@@ -8958,7 +8953,7 @@
     <v>151.5</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46178.902455821095</v>
+    <v>46178.999292812499</v>
     <v>300</v>
     <v>143.53</v>
     <v>35637160000</v>
@@ -8968,11 +8963,11 @@
     <v>46.171399999999998</v>
     <v>147.91</v>
     <v>144.28</v>
-    <v>143.6396</v>
+    <v>143.4</v>
     <v>247000000</v>
     <v>WDAY</v>
     <v>WORKDAY, INC. (XNAS:WDAY)</v>
-    <v>4594660</v>
+    <v>4596224</v>
     <v>5505662</v>
     <v>2012</v>
   </rv>
@@ -8997,11 +8992,11 @@
     <v>4</v>
     <v>336.99</v>
     <v>114.625</v>
-    <v>0.9647</v>
+    <v>0.97170000000000001</v>
     <v>-4.4800000000000004</v>
-    <v>-3.9760000000000004E-3</v>
+    <v>-9.2040000000000004E-3</v>
     <v>-3.3120999999999998E-2</v>
-    <v>-0.52</v>
+    <v>-1.2037</v>
     <v>USD</v>
     <v>Zscaler, Inc. is a cloud security company. The Company has developed a platform incorporating core security functionalities needed to enable fast and secure access to cloud resources based on identity, context and an organization's policies. Its Zscaler Zero Trust Exchange is a cloud-native platform that securely connects users, devices, applications and workloads, including artificial intelligence (AI) agents, without relying on hub-and-spoke network architecture and firewall-centric security. It delivers its solutions using a software-as-a-service (SaaS) business model and sells subscriptions to customers to access its cloud platform, together with related support services. Its services include Zscaler Internet Access (ZIA), Zscaler Private Access (ZPA), and Zscaler Digital Experience (ZDX). ZIA provides secure access to externally managed applications, including SaaS applications and internet destinations, regardless of device, location or network.</v>
     <v>7923</v>
@@ -9012,7 +9007,7 @@
     <v>137.2099</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46178.903391226566</v>
+    <v>46178.999975450781</v>
     <v>303</v>
     <v>128.97999999999999</v>
     <v>21148368410</v>
@@ -9022,29 +9017,29 @@
     <v>0</v>
     <v>135.26</v>
     <v>130.78</v>
-    <v>130.26</v>
+    <v>129.5763</v>
     <v>161709500</v>
     <v>ZS</v>
     <v>ZSCALER, INC. (XNAS:ZS)</v>
-    <v>4598738</v>
+    <v>4617922</v>
     <v>6283847</v>
     <v>2007</v>
   </rv>
   <rv s="2">
     <v>304</v>
   </rv>
-  <rv s="13">
+  <rv s="14">
     <v>en-GB</v>
     <v>avyu4c</v>
     <v>268435456</v>
     <v>1</v>
     <v>Powered by Refinitiv</v>
-    <v>30</v>
+    <v>32</v>
     <v>USD/GBP</v>
-    <v>31</v>
-    <v>32</v>
+    <v>33</v>
+    <v>34</v>
     <v>Finance</v>
-    <v>33</v>
+    <v>35</v>
     <v>0.76859999999999995</v>
     <v>0.72099999999999997</v>
     <v>4.7569999999999999E-3</v>
@@ -9066,7 +9061,7 @@
 </file>
 
 <file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="14">
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="15">
   <s t="_hyperlink">
     <k n="Address" t="s"/>
     <k n="Text" t="s"/>
@@ -9330,6 +9325,52 @@
     <k n="52 week low"/>
     <k n="Beta"/>
     <k n="Change"/>
+    <k n="Change % (Extended hours)"/>
+    <k n="Change (%)"/>
+    <k n="Change (Extended hours)"/>
+    <k n="Currency" t="s"/>
+    <k n="Description" t="s"/>
+    <k n="Employees"/>
+    <k n="Exchange" t="s"/>
+    <k n="Exchange abbreviation" t="s"/>
+    <k n="ExchangeID" t="s"/>
+    <k n="Headquarters" t="s"/>
+    <k n="High"/>
+    <k n="Industry" t="s"/>
+    <k n="Instrument type" t="s"/>
+    <k n="Last trade time"/>
+    <k n="LearnMoreOnLink" t="r"/>
+    <k n="Low"/>
+    <k n="Market cap"/>
+    <k n="Name" t="s"/>
+    <k n="Official name" t="s"/>
+    <k n="Open"/>
+    <k n="Previous close"/>
+    <k n="Price"/>
+    <k n="Price (Extended hours)"/>
+    <k n="Shares outstanding"/>
+    <k n="Ticker symbol" t="s"/>
+    <k n="UniqueName" t="s"/>
+    <k n="Volume"/>
+    <k n="Volume average"/>
+    <k n="Year incorporated"/>
+  </s>
+  <s t="_linkedentitycore">
+    <k n="%EntityCulture" t="s"/>
+    <k n="%EntityId" t="s"/>
+    <k n="%EntityServiceId"/>
+    <k n="%IsRefreshable" t="b"/>
+    <k n="%ProviderInfo" t="s"/>
+    <k n="_Display" t="spb"/>
+    <k n="_DisplayString" t="s"/>
+    <k n="_Flags" t="spb"/>
+    <k n="_Format" t="spb"/>
+    <k n="_Icon" t="s"/>
+    <k n="_SubLabel" t="spb"/>
+    <k n="52 week high"/>
+    <k n="52 week low"/>
+    <k n="Beta"/>
+    <k n="Change"/>
     <k n="Change (%)"/>
     <k n="Currency" t="s"/>
     <k n="Description" t="s"/>
@@ -9477,7 +9518,7 @@
 
 <file path=xl/richData/rdsupportingpropertybag.xml><?xml version="1.0" encoding="utf-8"?>
 <supportingPropertyBags xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2">
-  <spbArrays count="9">
+  <spbArrays count="10">
     <a count="45">
       <v t="s">%EntityServiceId</v>
       <v t="s">_Format</v>
@@ -9701,6 +9742,52 @@
       <v t="s">LearnMoreOnLink</v>
       <v t="s">%ProviderInfo</v>
     </a>
+    <a count="44">
+      <v t="s">%EntityServiceId</v>
+      <v t="s">_Format</v>
+      <v t="s">%IsRefreshable</v>
+      <v t="s">%EntityCulture</v>
+      <v t="s">%EntityId</v>
+      <v t="s">_Icon</v>
+      <v t="s">_Display</v>
+      <v t="s">Name</v>
+      <v t="s">_SubLabel</v>
+      <v t="s">Price</v>
+      <v t="s">Price (Extended hours)</v>
+      <v t="s">Exchange</v>
+      <v t="s">Official name</v>
+      <v t="s">Last trade time</v>
+      <v t="s">Ticker symbol</v>
+      <v t="s">Exchange abbreviation</v>
+      <v t="s">Change</v>
+      <v t="s">Change (Extended hours)</v>
+      <v t="s">Change (%)</v>
+      <v t="s">Change % (Extended hours)</v>
+      <v t="s">Currency</v>
+      <v t="s">Previous close</v>
+      <v t="s">Open</v>
+      <v t="s">High</v>
+      <v t="s">Low</v>
+      <v t="s">52 week high</v>
+      <v t="s">52 week low</v>
+      <v t="s">Volume</v>
+      <v t="s">Volume average</v>
+      <v t="s">Market cap</v>
+      <v t="s">Beta</v>
+      <v t="s">Shares outstanding</v>
+      <v t="s">Description</v>
+      <v t="s">Employees</v>
+      <v t="s">Headquarters</v>
+      <v t="s">Industry</v>
+      <v t="s">Instrument type</v>
+      <v t="s">Year incorporated</v>
+      <v t="s">_Flags</v>
+      <v t="s">UniqueName</v>
+      <v t="s">_DisplayString</v>
+      <v t="s">LearnMoreOnLink</v>
+      <v t="s">ExchangeID</v>
+      <v t="s">%ProviderInfo</v>
+    </a>
     <a count="42">
       <v t="s">%EntityServiceId</v>
       <v t="s">_Format</v>
@@ -9860,7 +9947,7 @@
       <v t="s">%ProviderInfo</v>
     </a>
   </spbArrays>
-  <spbData count="34">
+  <spbData count="36">
     <spb s="0">
       <v>0</v>
       <v>Name</v>
@@ -9906,9 +9993,9 @@
       <v>at close</v>
       <v>from previous close</v>
       <v>from previous close</v>
-      <v>Source: Nasdaq Last Sale</v>
+      <v>Source: Nasdaq</v>
       <v>GMT</v>
-      <v>Real-Time Nasdaq Last Sale</v>
+      <v>Delayed 15 minutes</v>
       <v>from close</v>
       <v>from close</v>
     </spb>
@@ -10032,15 +10119,43 @@
     <spb s="15">
       <v>at close</v>
       <v>from previous close</v>
-      <v>Source: Nasdaq Last Sale</v>
       <v>from previous close</v>
       <v>GMT</v>
-      <v>Real-Time Nasdaq Last Sale</v>
+      <v>BATS BZX Real-Time Last Price</v>
       <v>from close</v>
       <v>from close</v>
     </spb>
     <spb s="0">
       <v>5</v>
+      <v>Name</v>
+      <v>LearnMoreOnLink</v>
+    </spb>
+    <spb s="16">
+      <v>1</v>
+      <v>2</v>
+      <v>1</v>
+      <v>3</v>
+      <v>1</v>
+      <v>1</v>
+      <v>1</v>
+      <v>4</v>
+      <v>4</v>
+      <v>5</v>
+      <v>6</v>
+      <v>1</v>
+      <v>1</v>
+      <v>1</v>
+      <v>4</v>
+      <v>7</v>
+      <v>8</v>
+      <v>9</v>
+      <v>4</v>
+      <v>1</v>
+      <v>1</v>
+      <v>5</v>
+    </spb>
+    <spb s="0">
+      <v>6</v>
       <v>Name</v>
       <v>LearnMoreOnLink</v>
     </spb>
@@ -10066,18 +10181,18 @@
       <v>9</v>
       <v>4</v>
     </spb>
-    <spb s="16">
+    <spb s="17">
       <v>Delayed 15 minutes</v>
       <v>from previous close</v>
       <v>from previous close</v>
       <v>GMT</v>
     </spb>
     <spb s="0">
-      <v>6</v>
+      <v>7</v>
       <v>Name</v>
       <v>LearnMoreOnLink</v>
     </spb>
-    <spb s="17">
+    <spb s="18">
       <v>1</v>
       <v>2</v>
       <v>2</v>
@@ -10101,12 +10216,22 @@
       <v>1</v>
       <v>5</v>
     </spb>
+    <spb s="19">
+      <v>at close</v>
+      <v>from previous close</v>
+      <v>Source: Nasdaq</v>
+      <v>from previous close</v>
+      <v>GMT</v>
+      <v>Delayed 15 minutes</v>
+      <v>from close</v>
+      <v>from close</v>
+    </spb>
     <spb s="0">
-      <v>7</v>
+      <v>8</v>
       <v>Name</v>
       <v>LearnMoreOnLink</v>
     </spb>
-    <spb s="18">
+    <spb s="20">
       <v>13</v>
       <v>2</v>
       <v>2</v>
@@ -10125,16 +10250,6 @@
       <v>8</v>
       <v>9</v>
       <v>4</v>
-    </spb>
-    <spb s="4">
-      <v>at close</v>
-      <v>from previous close</v>
-      <v>from previous close</v>
-      <v>Source: Nasdaq</v>
-      <v>GMT</v>
-      <v>Delayed 15 minutes</v>
-      <v>from close</v>
-      <v>from close</v>
     </spb>
     <spb s="3">
       <v>15</v>
@@ -10197,14 +10312,14 @@
       <v>5</v>
     </spb>
     <spb s="9">
-      <v>8</v>
+      <v>9</v>
       <v>Name</v>
     </spb>
-    <spb s="19">
+    <spb s="21">
       <v>1</v>
       <v>1</v>
     </spb>
-    <spb s="20">
+    <spb s="22">
       <v>3</v>
       <v>18</v>
       <v>18</v>
@@ -10215,7 +10330,7 @@
       <v>7</v>
       <v>9</v>
     </spb>
-    <spb s="21">
+    <spb s="23">
       <v>GMT</v>
     </spb>
   </spbData>
@@ -10223,7 +10338,7 @@
 </file>
 
 <file path=xl/richData/rdsupportingpropertybagstructure.xml><?xml version="1.0" encoding="utf-8"?>
-<spbStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" count="22">
+<spbStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" count="24">
   <s>
     <k n="^Order" t="spba"/>
     <k n="TitleProperty" t="s"/>
@@ -10381,12 +10496,35 @@
   <s>
     <k n="Price" t="s"/>
     <k n="Change" t="s"/>
-    <k n="Exchange" t="s"/>
     <k n="Change (%)" t="s"/>
     <k n="Last trade time" t="s"/>
     <k n="Price (Extended hours)" t="s"/>
     <k n="Change (Extended hours)" t="s"/>
     <k n="Change % (Extended hours)" t="s"/>
+  </s>
+  <s>
+    <k n="Low" t="i"/>
+    <k n="Beta" t="i"/>
+    <k n="High" t="i"/>
+    <k n="Name" t="i"/>
+    <k n="Open" t="i"/>
+    <k n="Price" t="i"/>
+    <k n="Change" t="i"/>
+    <k n="Volume" t="i"/>
+    <k n="Employees" t="i"/>
+    <k n="Change (%)" t="i"/>
+    <k n="Market cap" t="i"/>
+    <k n="52 week low" t="i"/>
+    <k n="52 week high" t="i"/>
+    <k n="Previous close" t="i"/>
+    <k n="Volume average" t="i"/>
+    <k n="Last trade time" t="i"/>
+    <k n="Year incorporated" t="i"/>
+    <k n="`%EntityServiceId" t="i"/>
+    <k n="Shares outstanding" t="i"/>
+    <k n="Price (Extended hours)" t="i"/>
+    <k n="Change (Extended hours)" t="i"/>
+    <k n="Change % (Extended hours)" t="i"/>
   </s>
   <s>
     <k n="Price" t="s"/>
@@ -10417,6 +10555,16 @@
     <k n="Price (Extended hours)" t="i"/>
     <k n="Change (Extended hours)" t="i"/>
     <k n="Change % (Extended hours)" t="i"/>
+  </s>
+  <s>
+    <k n="Price" t="s"/>
+    <k n="Change" t="s"/>
+    <k n="Exchange" t="s"/>
+    <k n="Change (%)" t="s"/>
+    <k n="Last trade time" t="s"/>
+    <k n="Price (Extended hours)" t="s"/>
+    <k n="Change (Extended hours)" t="s"/>
+    <k n="Change % (Extended hours)" t="s"/>
   </s>
   <s>
     <k n="Low" t="i"/>
@@ -13837,7 +13985,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="10.46484375" style="1" bestFit="1" customWidth="1"/>
@@ -13931,25 +14079,25 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="1">
-        <v>46059</v>
+        <v>45859</v>
       </c>
       <c r="B4" t="s">
         <v>322</v>
       </c>
       <c r="C4" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="D4" t="s">
         <v>90</v>
       </c>
       <c r="E4">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F4" t="s">
         <v>91</v>
       </c>
       <c r="G4">
-        <v>154.96</v>
+        <v>129.58000000000001</v>
       </c>
       <c r="I4">
         <v>1</v>
@@ -13963,19 +14111,19 @@
         <v>322</v>
       </c>
       <c r="C5" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D5" t="s">
         <v>90</v>
       </c>
       <c r="E5">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="F5" t="s">
         <v>91</v>
       </c>
       <c r="G5">
-        <v>66.906129000000007</v>
+        <v>154.96</v>
       </c>
       <c r="I5">
         <v>1</v>
@@ -13989,7 +14137,7 @@
         <v>322</v>
       </c>
       <c r="C6" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="D6" t="s">
         <v>90</v>
@@ -14001,7 +14149,7 @@
         <v>91</v>
       </c>
       <c r="G6">
-        <v>62.462299999999999</v>
+        <v>66.906129000000007</v>
       </c>
       <c r="I6">
         <v>1</v>
@@ -14009,25 +14157,25 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="1">
-        <v>46125</v>
+        <v>46059</v>
       </c>
       <c r="B7" t="s">
         <v>322</v>
       </c>
       <c r="C7" t="s">
-        <v>76</v>
+        <v>60</v>
       </c>
       <c r="D7" t="s">
         <v>90</v>
       </c>
       <c r="E7">
-        <v>80</v>
+        <v>31</v>
       </c>
       <c r="F7" t="s">
         <v>91</v>
       </c>
       <c r="G7">
-        <v>8.8163710000000002</v>
+        <v>62.462299999999999</v>
       </c>
       <c r="I7">
         <v>1</v>
@@ -14035,25 +14183,25 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="1">
-        <v>46125</v>
+        <v>46108</v>
       </c>
       <c r="B8" t="s">
         <v>322</v>
       </c>
       <c r="C8" t="s">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="D8" t="s">
         <v>90</v>
       </c>
       <c r="E8">
-        <v>44</v>
+        <v>11</v>
       </c>
       <c r="F8" t="s">
         <v>91</v>
       </c>
       <c r="G8">
-        <v>8.8163710000000002</v>
+        <v>275.78359999999998</v>
       </c>
       <c r="I8">
         <v>1</v>
@@ -14061,25 +14209,25 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="1">
-        <v>46125</v>
+        <v>46119</v>
       </c>
       <c r="B9" t="s">
         <v>322</v>
       </c>
       <c r="C9" t="s">
-        <v>80</v>
+        <v>64</v>
       </c>
       <c r="D9" t="s">
         <v>90</v>
       </c>
       <c r="E9">
-        <v>444</v>
+        <v>7</v>
       </c>
       <c r="F9" t="s">
         <v>91</v>
       </c>
       <c r="G9">
-        <v>5.6261940000000008</v>
+        <v>260.09289999999999</v>
       </c>
       <c r="I9">
         <v>1</v>
@@ -14087,30 +14235,108 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="1">
-        <v>46139</v>
+        <v>46125</v>
       </c>
       <c r="B10" t="s">
-        <v>92</v>
+        <v>322</v>
       </c>
       <c r="C10" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="D10" t="s">
         <v>90</v>
       </c>
       <c r="E10">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="F10" t="s">
         <v>91</v>
       </c>
       <c r="G10">
+        <v>8.8163710000000002</v>
+      </c>
+      <c r="I10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="A11" s="1">
+        <v>46125</v>
+      </c>
+      <c r="B11" t="s">
+        <v>322</v>
+      </c>
+      <c r="C11" t="s">
+        <v>76</v>
+      </c>
+      <c r="D11" t="s">
+        <v>90</v>
+      </c>
+      <c r="E11">
+        <v>44</v>
+      </c>
+      <c r="F11" t="s">
+        <v>91</v>
+      </c>
+      <c r="G11">
+        <v>8.8163710000000002</v>
+      </c>
+      <c r="I11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="A12" s="1">
+        <v>46125</v>
+      </c>
+      <c r="B12" t="s">
+        <v>322</v>
+      </c>
+      <c r="C12" t="s">
+        <v>80</v>
+      </c>
+      <c r="D12" t="s">
+        <v>90</v>
+      </c>
+      <c r="E12">
+        <v>444</v>
+      </c>
+      <c r="F12" t="s">
+        <v>91</v>
+      </c>
+      <c r="G12">
+        <v>5.6261940000000008</v>
+      </c>
+      <c r="I12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="A13" s="1">
+        <v>46139</v>
+      </c>
+      <c r="B13" t="s">
+        <v>92</v>
+      </c>
+      <c r="C13" t="s">
+        <v>80</v>
+      </c>
+      <c r="D13" t="s">
+        <v>90</v>
+      </c>
+      <c r="E13">
+        <v>2</v>
+      </c>
+      <c r="F13" t="s">
+        <v>91</v>
+      </c>
+      <c r="G13">
         <v>5.92</v>
       </c>
-      <c r="H10">
+      <c r="H13">
         <v>0.12</v>
       </c>
-      <c r="I10">
+      <c r="I13">
         <v>1</v>
       </c>
     </row>
@@ -14298,7 +14524,7 @@
       </c>
       <c r="C2" s="2">
         <f t="array" aca="1" ref="C2" ca="1">_FV(B2,"Last trade time",TRUE)</f>
-        <v>46178.903395763278</v>
+        <v>46178.999954316409</v>
       </c>
       <c r="D2" t="str">
         <f t="array" aca="1" ref="D2" ca="1">_FV(B2,"Currency")</f>
@@ -14322,7 +14548,7 @@
       </c>
       <c r="I2" s="6">
         <f t="array" aca="1" ref="I2" ca="1">_FV(B2,"Beta")</f>
-        <v>3.6524999999999999</v>
+        <v>3.6288</v>
       </c>
       <c r="J2" s="3">
         <f t="array" aca="1" ref="J2" ca="1">_FV(B2,"52 week high",TRUE)</f>
@@ -14350,7 +14576,7 @@
       </c>
       <c r="P2" s="7">
         <f t="array" aca="1" ref="P2" ca="1">_FV(B2,"Volume")</f>
-        <v>19683738</v>
+        <v>19828156</v>
       </c>
       <c r="Q2" s="7">
         <f t="array" aca="1" ref="Q2" ca="1">_FV(B2,"Volume average",TRUE)</f>
@@ -14386,7 +14612,7 @@
       </c>
       <c r="C3" s="2">
         <f t="array" aca="1" ref="C3" ca="1">_FV(B3,"Last trade time",TRUE)</f>
-        <v>46178.903317210155</v>
+        <v>46178.999989015625</v>
       </c>
       <c r="D3" t="str">
         <f t="array" aca="1" ref="D3" ca="1">_FV(B3,"Currency")</f>
@@ -14406,11 +14632,11 @@
       </c>
       <c r="H3" s="6">
         <f t="array" aca="1" ref="H3" ca="1">_FV(B3,"P/E",TRUE)</f>
-        <v>37.326599999999999</v>
+        <v>37.798999999999999</v>
       </c>
       <c r="I3" s="6">
         <f t="array" aca="1" ref="I3" ca="1">_FV(B3,"Beta")</f>
-        <v>1.0863</v>
+        <v>1.0832999999999999</v>
       </c>
       <c r="J3" s="3">
         <f t="array" aca="1" ref="J3" ca="1">_FV(B3,"52 week high",TRUE)</f>
@@ -14438,7 +14664,7 @@
       </c>
       <c r="P3" s="7">
         <f t="array" aca="1" ref="P3" ca="1">_FV(B3,"Volume")</f>
-        <v>65217745</v>
+        <v>65310502</v>
       </c>
       <c r="Q3" s="7">
         <f t="array" aca="1" ref="Q3" ca="1">_FV(B3,"Volume average",TRUE)</f>
@@ -14474,7 +14700,7 @@
       </c>
       <c r="C4" s="2">
         <f t="array" aca="1" ref="C4" ca="1">_FV(B4,"Last trade time",TRUE)</f>
-        <v>46178.903395647656</v>
+        <v>46178.999899421091</v>
       </c>
       <c r="D4" t="str">
         <f t="array" aca="1" ref="D4" ca="1">_FV(B4,"Currency")</f>
@@ -14498,7 +14724,7 @@
       </c>
       <c r="I4" s="6">
         <f t="array" aca="1" ref="I4" ca="1">_FV(B4,"Beta")</f>
-        <v>1.4020999999999999</v>
+        <v>1.395</v>
       </c>
       <c r="J4" s="3">
         <f t="array" aca="1" ref="J4" ca="1">_FV(B4,"52 week high",TRUE)</f>
@@ -14526,7 +14752,7 @@
       </c>
       <c r="P4" s="7">
         <f t="array" aca="1" ref="P4" ca="1">_FV(B4,"Volume")</f>
-        <v>4900885</v>
+        <v>4909175</v>
       </c>
       <c r="Q4" s="7">
         <f t="array" aca="1" ref="Q4" ca="1">_FV(B4,"Volume average",TRUE)</f>
@@ -14562,7 +14788,7 @@
       </c>
       <c r="C5" s="2">
         <f t="array" aca="1" ref="C5" ca="1">_FV(B5,"Last trade time",TRUE)</f>
-        <v>46178.903194525003</v>
+        <v>46178.999445092188</v>
       </c>
       <c r="D5" t="str">
         <f t="array" aca="1" ref="D5" ca="1">_FV(B5,"Currency")</f>
@@ -14586,7 +14812,7 @@
       </c>
       <c r="I5" s="6">
         <f t="array" aca="1" ref="I5" ca="1">_FV(B5,"Beta")</f>
-        <v>3.1669</v>
+        <v>3.1621999999999999</v>
       </c>
       <c r="J5" s="3">
         <f t="array" aca="1" ref="J5" ca="1">_FV(B5,"52 week high",TRUE)</f>
@@ -14614,7 +14840,7 @@
       </c>
       <c r="P5" s="7">
         <f t="array" aca="1" ref="P5" ca="1">_FV(B5,"Volume")</f>
-        <v>2338404</v>
+        <v>2352316</v>
       </c>
       <c r="Q5" s="7">
         <f t="array" aca="1" ref="Q5" ca="1">_FV(B5,"Volume average",TRUE)</f>
@@ -14670,11 +14896,11 @@
       </c>
       <c r="H6" s="6">
         <f t="array" aca="1" ref="H6" ca="1">_FV(B6,"P/E",TRUE)</f>
-        <v>11.156499999999999</v>
+        <v>10.3893</v>
       </c>
       <c r="I6" s="6">
         <f t="array" aca="1" ref="I6" ca="1">_FV(B6,"Beta")</f>
-        <v>0.83899999999999997</v>
+        <v>0.83889999999999998</v>
       </c>
       <c r="J6" s="3">
         <f t="array" aca="1" ref="J6" ca="1">_FV(B6,"52 week high",TRUE)</f>
@@ -14738,7 +14964,7 @@
       </c>
       <c r="C7" s="2">
         <f t="array" aca="1" ref="C7" ca="1">_FV(B7,"Last trade time",TRUE)</f>
-        <v>46178.903431978906</v>
+        <v>46178.999956735941</v>
       </c>
       <c r="D7" t="str">
         <f t="array" aca="1" ref="D7" ca="1">_FV(B7,"Currency")</f>
@@ -14758,7 +14984,7 @@
       </c>
       <c r="H7" s="6">
         <f t="array" aca="1" ref="H7" ca="1">_FV(B7,"P/E",TRUE)</f>
-        <v>241.36949999999999</v>
+        <v>213.73869999999999</v>
       </c>
       <c r="I7" s="6">
         <f t="array" aca="1" ref="I7" ca="1">_FV(B7,"Beta")</f>
@@ -14790,7 +15016,7 @@
       </c>
       <c r="P7" s="7">
         <f t="array" aca="1" ref="P7" ca="1">_FV(B7,"Volume")</f>
-        <v>7300236</v>
+        <v>7315038</v>
       </c>
       <c r="Q7" s="7">
         <f t="array" aca="1" ref="Q7" ca="1">_FV(B7,"Volume average",TRUE)</f>
@@ -14826,7 +15052,7 @@
       </c>
       <c r="C8" s="2">
         <f t="array" aca="1" ref="C8" ca="1">_FV(B8,"Last trade time",TRUE)</f>
-        <v>46178.902898587497</v>
+        <v>46178.999421805471</v>
       </c>
       <c r="D8" t="str">
         <f t="array" aca="1" ref="D8" ca="1">_FV(B8,"Currency")</f>
@@ -14850,7 +15076,7 @@
       </c>
       <c r="I8" s="6">
         <f t="array" aca="1" ref="I8" ca="1">_FV(B8,"Beta")</f>
-        <v>2.145</v>
+        <v>2.1604000000000001</v>
       </c>
       <c r="J8" s="3">
         <f t="array" aca="1" ref="J8" ca="1">_FV(B8,"52 week high",TRUE)</f>
@@ -14878,7 +15104,7 @@
       </c>
       <c r="P8" s="7">
         <f t="array" aca="1" ref="P8" ca="1">_FV(B8,"Volume")</f>
-        <v>2111285</v>
+        <v>2124450</v>
       </c>
       <c r="Q8" s="7">
         <f t="array" aca="1" ref="Q8" ca="1">_FV(B8,"Volume average",TRUE)</f>
@@ -14914,7 +15140,7 @@
       </c>
       <c r="C9" s="2">
         <f t="array" aca="1" ref="C9" ca="1">_FV(B9,"Last trade time",TRUE)</f>
-        <v>46178.903431481252</v>
+        <v>46178.999982383597</v>
       </c>
       <c r="D9" t="str">
         <f t="array" aca="1" ref="D9" ca="1">_FV(B9,"Currency")</f>
@@ -14938,7 +15164,7 @@
       </c>
       <c r="I9" s="6">
         <f t="array" aca="1" ref="I9" ca="1">_FV(B9,"Beta")</f>
-        <v>2.4918999999999998</v>
+        <v>2.5061</v>
       </c>
       <c r="J9" s="3">
         <f t="array" aca="1" ref="J9" ca="1">_FV(B9,"52 week high",TRUE)</f>
@@ -14966,7 +15192,7 @@
       </c>
       <c r="P9" s="7">
         <f t="array" aca="1" ref="P9" ca="1">_FV(B9,"Volume")</f>
-        <v>46690771</v>
+        <v>46900606</v>
       </c>
       <c r="Q9" s="7">
         <f t="array" aca="1" ref="Q9" ca="1">_FV(B9,"Volume average",TRUE)</f>
@@ -15002,7 +15228,7 @@
       </c>
       <c r="C10" s="2">
         <f t="array" aca="1" ref="C10" ca="1">_FV(B10,"Last trade time",TRUE)</f>
-        <v>46178.903375948437</v>
+        <v>46178.999997349216</v>
       </c>
       <c r="D10" t="str">
         <f t="array" aca="1" ref="D10" ca="1">_FV(B10,"Currency")</f>
@@ -15026,7 +15252,7 @@
       </c>
       <c r="I10" s="6">
         <f t="array" aca="1" ref="I10" ca="1">_FV(B10,"Beta")</f>
-        <v>1.4490000000000001</v>
+        <v>1.4587000000000001</v>
       </c>
       <c r="J10" s="3">
         <f t="array" aca="1" ref="J10" ca="1">_FV(B10,"52 week high",TRUE)</f>
@@ -15054,7 +15280,7 @@
       </c>
       <c r="P10" s="7">
         <f t="array" aca="1" ref="P10" ca="1">_FV(B10,"Volume")</f>
-        <v>55469366</v>
+        <v>55607844</v>
       </c>
       <c r="Q10" s="7">
         <f t="array" aca="1" ref="Q10" ca="1">_FV(B10,"Volume average",TRUE)</f>
@@ -15090,7 +15316,7 @@
       </c>
       <c r="C11" s="2">
         <f t="array" aca="1" ref="C11" ca="1">_FV(B11,"Last trade time",TRUE)</f>
-        <v>46178.903462823437</v>
+        <v>46178.999909189064</v>
       </c>
       <c r="D11" t="str">
         <f t="array" aca="1" ref="D11" ca="1">_FV(B11,"Currency")</f>
@@ -15098,23 +15324,23 @@
       </c>
       <c r="E11" s="3">
         <f t="array" aca="1" ref="E11" ca="1">_FV(B11,"Price")</f>
-        <v>154.20500000000001</v>
+        <v>154.27000000000001</v>
       </c>
       <c r="F11" s="4">
         <f t="array" aca="1" ref="F11" ca="1">_FV(B11,"Change (%)",TRUE)</f>
-        <v>-7.1109999999999993E-2</v>
+        <v>-7.0719000000000004E-2</v>
       </c>
       <c r="G11" s="5">
         <f t="array" aca="1" ref="G11" ca="1">_FV(B11,"Change")</f>
-        <v>-11.805</v>
+        <v>-11.74</v>
       </c>
       <c r="H11" s="6">
         <f t="array" aca="1" ref="H11" ca="1">_FV(B11,"P/E",TRUE)</f>
-        <v>56.859900000000003</v>
+        <v>52.839399999999998</v>
       </c>
       <c r="I11" s="6">
         <f t="array" aca="1" ref="I11" ca="1">_FV(B11,"Beta")</f>
-        <v>1.6099000000000001</v>
+        <v>1.6153999999999999</v>
       </c>
       <c r="J11" s="3">
         <f t="array" aca="1" ref="J11" ca="1">_FV(B11,"52 week high",TRUE)</f>
@@ -15142,7 +15368,7 @@
       </c>
       <c r="P11" s="7">
         <f t="array" aca="1" ref="P11" ca="1">_FV(B11,"Volume")</f>
-        <v>9075002</v>
+        <v>9094700</v>
       </c>
       <c r="Q11" s="7">
         <f t="array" aca="1" ref="Q11" ca="1">_FV(B11,"Volume average",TRUE)</f>
@@ -15162,7 +15388,7 @@
       </c>
       <c r="U11" s="7">
         <f t="array" aca="1" ref="U11" ca="1">_FV(B11,"Market cap",TRUE)</f>
-        <v>194175398615</v>
+        <v>194257246810</v>
       </c>
       <c r="V11" s="7">
         <f t="array" aca="1" ref="V11" ca="1">_FV(B11,"Shares outstanding",TRUE)</f>
@@ -15178,7 +15404,7 @@
       </c>
       <c r="C12" s="2">
         <f t="array" aca="1" ref="C12" ca="1">_FV(B12,"Last trade time",TRUE)</f>
-        <v>46178.90282993047</v>
+        <v>46178.999783228908</v>
       </c>
       <c r="D12" t="str">
         <f t="array" aca="1" ref="D12" ca="1">_FV(B12,"Currency")</f>
@@ -15198,11 +15424,11 @@
       </c>
       <c r="H12" s="6">
         <f t="array" aca="1" ref="H12" ca="1">_FV(B12,"P/E",TRUE)</f>
-        <v>48.565600000000003</v>
+        <v>48.4206</v>
       </c>
       <c r="I12" s="6">
         <f t="array" aca="1" ref="I12" ca="1">_FV(B12,"Beta")</f>
-        <v>2.4645999999999999</v>
+        <v>2.4725000000000001</v>
       </c>
       <c r="J12" s="3">
         <f t="array" aca="1" ref="J12" ca="1">_FV(B12,"52 week high",TRUE)</f>
@@ -15230,7 +15456,7 @@
       </c>
       <c r="P12" s="7">
         <f t="array" aca="1" ref="P12" ca="1">_FV(B12,"Volume")</f>
-        <v>5542167</v>
+        <v>5547042</v>
       </c>
       <c r="Q12" s="7">
         <f t="array" aca="1" ref="Q12" ca="1">_FV(B12,"Volume average",TRUE)</f>
@@ -15266,7 +15492,7 @@
       </c>
       <c r="C13" s="2" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(B13,"Last trade time",TRUE)</f>
-        <v>46178.902926515628</v>
+        <v>46178.999827649997</v>
       </c>
       <c r="D13" t="str" cm="1">
         <f t="array" aca="1" ref="D13" ca="1">_FV(B13,"Currency")</f>
@@ -15274,15 +15500,15 @@
       </c>
       <c r="E13" s="3" cm="1">
         <f t="array" aca="1" ref="E13" ca="1">_FV(B13,"Price")</f>
-        <v>74.55</v>
+        <v>74.489999999999995</v>
       </c>
       <c r="F13" s="4" cm="1">
         <f t="array" aca="1" ref="F13" ca="1">_FV(B13,"Change (%)",TRUE)</f>
-        <v>-6.8940000000000001E-2</v>
+        <v>-6.9689000000000001E-2</v>
       </c>
       <c r="G13" s="5" cm="1">
         <f t="array" aca="1" ref="G13" ca="1">_FV(B13,"Change")</f>
-        <v>-5.52</v>
+        <v>-5.58</v>
       </c>
       <c r="H13" s="6" t="e" vm="13">
         <f t="array" ref="H13">_FV(B13,"P/E",TRUE)</f>
@@ -15318,7 +15544,7 @@
       </c>
       <c r="P13" s="7" cm="1">
         <f t="array" aca="1" ref="P13" ca="1">_FV(B13,"Volume")</f>
-        <v>13976817</v>
+        <v>13983063</v>
       </c>
       <c r="Q13" s="7" cm="1">
         <f t="array" aca="1" ref="Q13" ca="1">_FV(B13,"Volume average",TRUE)</f>
@@ -15354,7 +15580,7 @@
       </c>
       <c r="C14" s="2">
         <f t="array" aca="1" ref="C14" ca="1">_FV(B14,"Last trade time",TRUE)</f>
-        <v>46178.903495253908</v>
+        <v>46178.999999305466</v>
       </c>
       <c r="D14" t="str">
         <f t="array" aca="1" ref="D14" ca="1">_FV(B14,"Currency")</f>
@@ -15406,7 +15632,7 @@
       </c>
       <c r="P14" s="7">
         <f t="array" aca="1" ref="P14" ca="1">_FV(B14,"Volume")</f>
-        <v>14787010</v>
+        <v>14885094</v>
       </c>
       <c r="Q14" s="7">
         <f t="array" aca="1" ref="Q14" ca="1">_FV(B14,"Volume average",TRUE)</f>
@@ -15442,7 +15668,7 @@
       </c>
       <c r="C15" s="2">
         <f t="array" aca="1" ref="C15" ca="1">_FV(B15,"Last trade time",TRUE)</f>
-        <v>46178.903399675779</v>
+        <v>46178.999889490624</v>
       </c>
       <c r="D15" t="str">
         <f t="array" aca="1" ref="D15" ca="1">_FV(B15,"Currency")</f>
@@ -15462,11 +15688,11 @@
       </c>
       <c r="H15" s="6">
         <f t="array" aca="1" ref="H15" ca="1">_FV(B15,"P/E",TRUE)</f>
-        <v>60.421500000000002</v>
+        <v>56.442799999999998</v>
       </c>
       <c r="I15" s="6">
         <f t="array" aca="1" ref="I15" ca="1">_FV(B15,"Beta")</f>
-        <v>1.8173999999999999</v>
+        <v>1.806</v>
       </c>
       <c r="J15" s="3">
         <f t="array" aca="1" ref="J15" ca="1">_FV(B15,"52 week high",TRUE)</f>
@@ -15494,7 +15720,7 @@
       </c>
       <c r="P15" s="7">
         <f t="array" aca="1" ref="P15" ca="1">_FV(B15,"Volume")</f>
-        <v>2730988</v>
+        <v>2744563</v>
       </c>
       <c r="Q15" s="7">
         <f t="array" aca="1" ref="Q15" ca="1">_FV(B15,"Volume average",TRUE)</f>
@@ -15530,7 +15756,7 @@
       </c>
       <c r="C16" s="2">
         <f t="array" aca="1" ref="C16" ca="1">_FV(B16,"Last trade time",TRUE)</f>
-        <v>46178.90349016172</v>
+        <v>46178.999999513282</v>
       </c>
       <c r="D16" t="str">
         <f t="array" aca="1" ref="D16" ca="1">_FV(B16,"Currency")</f>
@@ -15554,7 +15780,7 @@
       </c>
       <c r="I16" s="6">
         <f t="array" aca="1" ref="I16" ca="1">_FV(B16,"Beta")</f>
-        <v>1.4407000000000001</v>
+        <v>1.4705999999999999</v>
       </c>
       <c r="J16" s="3">
         <f t="array" aca="1" ref="J16" ca="1">_FV(B16,"52 week high",TRUE)</f>
@@ -15582,7 +15808,7 @@
       </c>
       <c r="P16" s="7">
         <f t="array" aca="1" ref="P16" ca="1">_FV(B16,"Volume")</f>
-        <v>50908163</v>
+        <v>51146089</v>
       </c>
       <c r="Q16" s="7">
         <f t="array" aca="1" ref="Q16" ca="1">_FV(B16,"Volume average",TRUE)</f>
@@ -15618,7 +15844,7 @@
       </c>
       <c r="C17" s="2">
         <f t="array" aca="1" ref="C17" ca="1">_FV(B17,"Last trade time",TRUE)</f>
-        <v>46178.903381064061</v>
+        <v>46178.999910971877</v>
       </c>
       <c r="D17" t="str">
         <f t="array" aca="1" ref="D17" ca="1">_FV(B17,"Currency")</f>
@@ -15636,13 +15862,13 @@
         <f t="array" aca="1" ref="G17" ca="1">_FV(B17,"Change")</f>
         <v>-0.56999999999999995</v>
       </c>
-      <c r="H17" s="6">
-        <f t="array" aca="1" ref="H17" ca="1">_FV(B17,"P/E",TRUE)</f>
-        <v>0</v>
+      <c r="H17" s="6" t="e" vm="13">
+        <f t="array" ref="H17">_FV(B17,"P/E",TRUE)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="I17" s="6">
         <f t="array" aca="1" ref="I17" ca="1">_FV(B17,"Beta")</f>
-        <v>3.089</v>
+        <v>3.1166</v>
       </c>
       <c r="J17" s="3">
         <f t="array" aca="1" ref="J17" ca="1">_FV(B17,"52 week high",TRUE)</f>
@@ -15670,7 +15896,7 @@
       </c>
       <c r="P17" s="7">
         <f t="array" aca="1" ref="P17" ca="1">_FV(B17,"Volume")</f>
-        <v>37855966</v>
+        <v>38122015</v>
       </c>
       <c r="Q17" s="7">
         <f t="array" aca="1" ref="Q17" ca="1">_FV(B17,"Volume average",TRUE)</f>
@@ -15730,7 +15956,7 @@
       </c>
       <c r="I18" s="6" cm="1">
         <f t="array" aca="1" ref="I18" ca="1">_FV(B18,"Beta")</f>
-        <v>0.96250000000000002</v>
+        <v>0.96240000000000003</v>
       </c>
       <c r="J18" s="3" cm="1">
         <f t="array" aca="1" ref="J18" ca="1">_FV(B18,"52 week high",TRUE)</f>
@@ -15794,7 +16020,7 @@
       </c>
       <c r="C19" s="2" cm="1">
         <f t="array" aca="1" ref="C19" ca="1">_FV(B19,"Last trade time",TRUE)</f>
-        <v>46178.90310594844</v>
+        <v>46178.99911732578</v>
       </c>
       <c r="D19" t="str" cm="1">
         <f t="array" aca="1" ref="D19" ca="1">_FV(B19,"Currency")</f>
@@ -15818,7 +16044,7 @@
       </c>
       <c r="I19" s="6" cm="1">
         <f t="array" aca="1" ref="I19" ca="1">_FV(B19,"Beta")</f>
-        <v>1.1415999999999999</v>
+        <v>1.1416999999999999</v>
       </c>
       <c r="J19" s="3" cm="1">
         <f t="array" aca="1" ref="J19" ca="1">_FV(B19,"52 week high",TRUE)</f>
@@ -15846,7 +16072,7 @@
       </c>
       <c r="P19" s="7" cm="1">
         <f t="array" aca="1" ref="P19" ca="1">_FV(B19,"Volume")</f>
-        <v>3518659</v>
+        <v>3520057</v>
       </c>
       <c r="Q19" s="7" cm="1">
         <f t="array" aca="1" ref="Q19" ca="1">_FV(B19,"Volume average",TRUE)</f>
@@ -15882,7 +16108,7 @@
       </c>
       <c r="C20" s="2" cm="1">
         <f t="array" aca="1" ref="C20" ca="1">_FV(B20,"Last trade time",TRUE)</f>
-        <v>46178.90344726797</v>
+        <v>46178.999882233591</v>
       </c>
       <c r="D20" t="str" cm="1">
         <f t="array" aca="1" ref="D20" ca="1">_FV(B20,"Currency")</f>
@@ -15906,7 +16132,7 @@
       </c>
       <c r="I20" s="6" cm="1">
         <f t="array" aca="1" ref="I20" ca="1">_FV(B20,"Beta")</f>
-        <v>1.1014999999999999</v>
+        <v>1.1292</v>
       </c>
       <c r="J20" s="3" cm="1">
         <f t="array" aca="1" ref="J20" ca="1">_FV(B20,"52 week high",TRUE)</f>
@@ -15934,7 +16160,7 @@
       </c>
       <c r="P20" s="7" cm="1">
         <f t="array" aca="1" ref="P20" ca="1">_FV(B20,"Volume")</f>
-        <v>4118632</v>
+        <v>4130674</v>
       </c>
       <c r="Q20" s="7" cm="1">
         <f t="array" aca="1" ref="Q20" ca="1">_FV(B20,"Volume average",TRUE)</f>
@@ -15970,7 +16196,7 @@
       </c>
       <c r="C21" s="2">
         <f t="array" aca="1" ref="C21" ca="1">_FV(B21,"Last trade time",TRUE)</f>
-        <v>46178.90315803203</v>
+        <v>46178.999983356247</v>
       </c>
       <c r="D21" t="str">
         <f t="array" aca="1" ref="D21" ca="1">_FV(B21,"Currency")</f>
@@ -15990,11 +16216,11 @@
       </c>
       <c r="H21" s="6">
         <f t="array" aca="1" ref="H21" ca="1">_FV(B21,"P/E",TRUE)</f>
-        <v>87.708299999999994</v>
+        <v>83.430099999999996</v>
       </c>
       <c r="I21" s="6">
         <f t="array" aca="1" ref="I21" ca="1">_FV(B21,"Beta")</f>
-        <v>3.2399</v>
+        <v>3.2572999999999999</v>
       </c>
       <c r="J21" s="3">
         <f t="array" aca="1" ref="J21" ca="1">_FV(B21,"52 week high",TRUE)</f>
@@ -16022,7 +16248,7 @@
       </c>
       <c r="P21" s="7">
         <f t="array" aca="1" ref="P21" ca="1">_FV(B21,"Volume")</f>
-        <v>15599147</v>
+        <v>15917879</v>
       </c>
       <c r="Q21" s="7">
         <f t="array" aca="1" ref="Q21" ca="1">_FV(B21,"Volume average",TRUE)</f>
@@ -16058,7 +16284,7 @@
       </c>
       <c r="C22" s="2">
         <f t="array" aca="1" ref="C22" ca="1">_FV(B22,"Last trade time",TRUE)</f>
-        <v>46178.903353471876</v>
+        <v>46178.999831515626</v>
       </c>
       <c r="D22" t="str">
         <f t="array" aca="1" ref="D22" ca="1">_FV(B22,"Currency")</f>
@@ -16066,15 +16292,15 @@
       </c>
       <c r="E22" s="3">
         <f t="array" aca="1" ref="E22" ca="1">_FV(B22,"Price")</f>
-        <v>185.68</v>
+        <v>185.66</v>
       </c>
       <c r="F22" s="4">
         <f t="array" aca="1" ref="F22" ca="1">_FV(B22,"Change (%)",TRUE)</f>
-        <v>-1.6265000000000002E-2</v>
+        <v>-1.6371E-2</v>
       </c>
       <c r="G22" s="5">
         <f t="array" aca="1" ref="G22" ca="1">_FV(B22,"Change")</f>
-        <v>-3.07</v>
+        <v>-3.09</v>
       </c>
       <c r="H22" s="6">
         <f t="array" aca="1" ref="H22" ca="1">_FV(B22,"P/E",TRUE)</f>
@@ -16082,7 +16308,7 @@
       </c>
       <c r="I22" s="6">
         <f t="array" aca="1" ref="I22" ca="1">_FV(B22,"Beta")</f>
-        <v>1.1515</v>
+        <v>1.1476999999999999</v>
       </c>
       <c r="J22" s="3">
         <f t="array" aca="1" ref="J22" ca="1">_FV(B22,"52 week high",TRUE)</f>
@@ -16110,7 +16336,7 @@
       </c>
       <c r="P22" s="7">
         <f t="array" aca="1" ref="P22" ca="1">_FV(B22,"Volume")</f>
-        <v>13158104</v>
+        <v>13183928</v>
       </c>
       <c r="Q22" s="7">
         <f t="array" aca="1" ref="Q22" ca="1">_FV(B22,"Volume average",TRUE)</f>
@@ -16130,7 +16356,7 @@
       </c>
       <c r="U22" s="7">
         <f t="array" aca="1" ref="U22" ca="1">_FV(B22,"Market cap",TRUE)</f>
-        <v>152071920000</v>
+        <v>152055540000</v>
       </c>
       <c r="V22" s="7">
         <f t="array" aca="1" ref="V22" ca="1">_FV(B22,"Shares outstanding",TRUE)</f>
@@ -16146,7 +16372,7 @@
       </c>
       <c r="C23" s="2" cm="1">
         <f t="array" aca="1" ref="C23" ca="1">_FV(B23,"Last trade time",TRUE)</f>
-        <v>46178.903419467184</v>
+        <v>46178.999852626563</v>
       </c>
       <c r="D23" t="str" cm="1">
         <f t="array" aca="1" ref="D23" ca="1">_FV(B23,"Currency")</f>
@@ -16170,7 +16396,7 @@
       </c>
       <c r="I23" s="6" cm="1">
         <f t="array" aca="1" ref="I23" ca="1">_FV(B23,"Beta")</f>
-        <v>1.2464999999999999</v>
+        <v>1.2632000000000001</v>
       </c>
       <c r="J23" s="3" cm="1">
         <f t="array" aca="1" ref="J23" ca="1">_FV(B23,"52 week high",TRUE)</f>
@@ -16198,7 +16424,7 @@
       </c>
       <c r="P23" s="7" cm="1">
         <f t="array" aca="1" ref="P23" ca="1">_FV(B23,"Volume")</f>
-        <v>5228185</v>
+        <v>5238819</v>
       </c>
       <c r="Q23" s="7" cm="1">
         <f t="array" aca="1" ref="Q23" ca="1">_FV(B23,"Volume average",TRUE)</f>
@@ -16210,7 +16436,7 @@
       </c>
       <c r="S23" s="7" cm="1">
         <f t="array" aca="1" ref="S23" ca="1">_FV(B23,"Employees")</f>
-        <v>10698</v>
+        <v>11157</v>
       </c>
       <c r="T23" t="str" cm="1">
         <f t="array" aca="1" ref="T23" ca="1">_FV(B23,"Industry")</f>
@@ -16218,11 +16444,11 @@
       </c>
       <c r="U23" s="7" cm="1">
         <f t="array" aca="1" ref="U23" ca="1">_FV(B23,"Market cap",TRUE)</f>
-        <v>170799082230</v>
+        <v>170818072096</v>
       </c>
       <c r="V23" s="7" cm="1">
         <f t="array" aca="1" ref="V23" ca="1">_FV(B23,"Shares outstanding",TRUE)</f>
-        <v>254536500</v>
+        <v>254564800</v>
       </c>
     </row>
     <row r="24" spans="1:22">
@@ -16234,7 +16460,7 @@
       </c>
       <c r="C24" s="2">
         <f t="array" aca="1" ref="C24" ca="1">_FV(B24,"Last trade time",TRUE)</f>
-        <v>46178.903467430471</v>
+        <v>46178.999998159372</v>
       </c>
       <c r="D24" t="str">
         <f t="array" aca="1" ref="D24" ca="1">_FV(B24,"Currency")</f>
@@ -16286,7 +16512,7 @@
       </c>
       <c r="P24" s="7">
         <f t="array" aca="1" ref="P24" ca="1">_FV(B24,"Volume")</f>
-        <v>32311434</v>
+        <v>32460769</v>
       </c>
       <c r="Q24" s="7">
         <f t="array" aca="1" ref="Q24" ca="1">_FV(B24,"Volume average",TRUE)</f>
@@ -16322,7 +16548,7 @@
       </c>
       <c r="C25" s="2" cm="1">
         <f t="array" aca="1" ref="C25" ca="1">_FV(B25,"Last trade time",TRUE)</f>
-        <v>46178.903468298435</v>
+        <v>46178.999662777343</v>
       </c>
       <c r="D25" t="str" cm="1">
         <f t="array" aca="1" ref="D25" ca="1">_FV(B25,"Currency")</f>
@@ -16342,11 +16568,11 @@
       </c>
       <c r="H25" s="6" cm="1">
         <f t="array" aca="1" ref="H25" ca="1">_FV(B25,"P/E",TRUE)</f>
-        <v>43.319600000000001</v>
+        <v>40.533200000000001</v>
       </c>
       <c r="I25" s="6" cm="1">
         <f t="array" aca="1" ref="I25" ca="1">_FV(B25,"Beta")</f>
-        <v>0.998</v>
+        <v>0.99519999999999997</v>
       </c>
       <c r="J25" s="3" cm="1">
         <f t="array" aca="1" ref="J25" ca="1">_FV(B25,"52 week high",TRUE)</f>
@@ -16374,7 +16600,7 @@
       </c>
       <c r="P25" s="7" cm="1">
         <f t="array" aca="1" ref="P25" ca="1">_FV(B25,"Volume")</f>
-        <v>33139415</v>
+        <v>33169341</v>
       </c>
       <c r="Q25" s="7" cm="1">
         <f t="array" aca="1" ref="Q25" ca="1">_FV(B25,"Volume average",TRUE)</f>
@@ -16410,7 +16636,7 @@
       </c>
       <c r="C26" s="2">
         <f t="array" aca="1" ref="C26" ca="1">_FV(B26,"Last trade time",TRUE)</f>
-        <v>46178.903468298435</v>
+        <v>46178.999662777343</v>
       </c>
       <c r="D26" t="str">
         <f t="array" aca="1" ref="D26" ca="1">_FV(B26,"Currency")</f>
@@ -16430,11 +16656,11 @@
       </c>
       <c r="H26" s="6">
         <f t="array" aca="1" ref="H26" ca="1">_FV(B26,"P/E",TRUE)</f>
-        <v>43.319600000000001</v>
+        <v>40.533200000000001</v>
       </c>
       <c r="I26" s="6">
         <f t="array" aca="1" ref="I26" ca="1">_FV(B26,"Beta")</f>
-        <v>0.998</v>
+        <v>0.99519999999999997</v>
       </c>
       <c r="J26" s="3">
         <f t="array" aca="1" ref="J26" ca="1">_FV(B26,"52 week high",TRUE)</f>
@@ -16462,7 +16688,7 @@
       </c>
       <c r="P26" s="7">
         <f t="array" aca="1" ref="P26" ca="1">_FV(B26,"Volume")</f>
-        <v>33139415</v>
+        <v>33169341</v>
       </c>
       <c r="Q26" s="7">
         <f t="array" aca="1" ref="Q26" ca="1">_FV(B26,"Volume average",TRUE)</f>
@@ -16498,7 +16724,7 @@
       </c>
       <c r="C27" s="2">
         <f t="array" aca="1" ref="C27" ca="1">_FV(B27,"Last trade time",TRUE)</f>
-        <v>46178.902660046093</v>
+        <v>46178.99972727969</v>
       </c>
       <c r="D27" t="str">
         <f t="array" aca="1" ref="D27" ca="1">_FV(B27,"Currency")</f>
@@ -16518,11 +16744,11 @@
       </c>
       <c r="H27" s="6">
         <f t="array" aca="1" ref="H27" ca="1">_FV(B27,"P/E",TRUE)</f>
-        <v>617.20889999999997</v>
+        <v>593.13400000000001</v>
       </c>
       <c r="I27" s="6">
         <f t="array" aca="1" ref="I27" ca="1">_FV(B27,"Beta")</f>
-        <v>1.5549999999999999</v>
+        <v>1.5597000000000001</v>
       </c>
       <c r="J27" s="3">
         <f t="array" aca="1" ref="J27" ca="1">_FV(B27,"52 week high",TRUE)</f>
@@ -16550,7 +16776,7 @@
       </c>
       <c r="P27" s="7">
         <f t="array" aca="1" ref="P27" ca="1">_FV(B27,"Volume")</f>
-        <v>6787014</v>
+        <v>6792767</v>
       </c>
       <c r="Q27" s="7">
         <f t="array" aca="1" ref="Q27" ca="1">_FV(B27,"Volume average",TRUE)</f>
@@ -16558,7 +16784,7 @@
       </c>
       <c r="R27" s="8">
         <f t="array" aca="1" ref="R27" ca="1">_FV(B27,"Year incorporated",TRUE)</f>
-        <v>2026</v>
+        <v>2010</v>
       </c>
       <c r="S27" s="7">
         <f t="array" aca="1" ref="S27" ca="1">_FV(B27,"Employees")</f>
@@ -16586,7 +16812,7 @@
       </c>
       <c r="C28" s="2" cm="1">
         <f t="array" aca="1" ref="C28" ca="1">_FV(B28,"Last trade time",TRUE)</f>
-        <v>46178.903500323438</v>
+        <v>46178.999995555467</v>
       </c>
       <c r="D28" t="str" cm="1">
         <f t="array" aca="1" ref="D28" ca="1">_FV(B28,"Currency")</f>
@@ -16594,23 +16820,23 @@
       </c>
       <c r="E28" s="3" cm="1">
         <f t="array" aca="1" ref="E28" ca="1">_FV(B28,"Price")</f>
-        <v>394.64</v>
+        <v>394.39</v>
       </c>
       <c r="F28" s="4" cm="1">
         <f t="array" aca="1" ref="F28" ca="1">_FV(B28,"Change (%)",TRUE)</f>
-        <v>-6.4945000000000003E-2</v>
+        <v>-6.5536999999999998E-2</v>
       </c>
       <c r="G28" s="5" cm="1">
         <f t="array" aca="1" ref="G28" ca="1">_FV(B28,"Change")</f>
-        <v>-27.41</v>
+        <v>-27.66</v>
       </c>
       <c r="H28" s="6" cm="1">
         <f t="array" aca="1" ref="H28" ca="1">_FV(B28,"P/E",TRUE)</f>
-        <v>33.516100000000002</v>
+        <v>31.319400000000002</v>
       </c>
       <c r="I28" s="6" cm="1">
         <f t="array" aca="1" ref="I28" ca="1">_FV(B28,"Beta")</f>
-        <v>1.3033999999999999</v>
+        <v>1.319</v>
       </c>
       <c r="J28" s="3" cm="1">
         <f t="array" aca="1" ref="J28" ca="1">_FV(B28,"52 week high",TRUE)</f>
@@ -16638,7 +16864,7 @@
       </c>
       <c r="P28" s="7" cm="1">
         <f t="array" aca="1" ref="P28" ca="1">_FV(B28,"Volume")</f>
-        <v>10946010</v>
+        <v>10990345</v>
       </c>
       <c r="Q28" s="7" cm="1">
         <f t="array" aca="1" ref="Q28" ca="1">_FV(B28,"Volume average",TRUE)</f>
@@ -16658,7 +16884,7 @@
       </c>
       <c r="U28" s="7" cm="1">
         <f t="array" aca="1" ref="U28" ca="1">_FV(B28,"Market cap",TRUE)</f>
-        <v>256345633912</v>
+        <v>256183241837</v>
       </c>
       <c r="V28" s="7" cm="1">
         <f t="array" aca="1" ref="V28" ca="1">_FV(B28,"Shares outstanding",TRUE)</f>
@@ -16674,7 +16900,7 @@
       </c>
       <c r="C29" s="2" cm="1">
         <f t="array" aca="1" ref="C29" ca="1">_FV(B29,"Last trade time",TRUE)</f>
-        <v>46178.903126249999</v>
+        <v>46178.999763101565</v>
       </c>
       <c r="D29" t="str" cm="1">
         <f t="array" aca="1" ref="D29" ca="1">_FV(B29,"Currency")</f>
@@ -16682,15 +16908,15 @@
       </c>
       <c r="E29" s="3" cm="1">
         <f t="array" aca="1" ref="E29" ca="1">_FV(B29,"Price")</f>
-        <v>99.74</v>
+        <v>99.71</v>
       </c>
       <c r="F29" s="4" cm="1">
         <f t="array" aca="1" ref="F29" ca="1">_FV(B29,"Change (%)",TRUE)</f>
-        <v>4.0270000000000002E-3</v>
+        <v>3.725E-3</v>
       </c>
       <c r="G29" s="5" cm="1">
         <f t="array" aca="1" ref="G29" ca="1">_FV(B29,"Change")</f>
-        <v>0.4</v>
+        <v>0.37</v>
       </c>
       <c r="H29" s="6" cm="1">
         <f t="array" aca="1" ref="H29" ca="1">_FV(B29,"P/E",TRUE)</f>
@@ -16698,7 +16924,7 @@
       </c>
       <c r="I29" s="6" cm="1">
         <f t="array" aca="1" ref="I29" ca="1">_FV(B29,"Beta")</f>
-        <v>1.3942000000000001</v>
+        <v>1.3836999999999999</v>
       </c>
       <c r="J29" s="3" cm="1">
         <f t="array" aca="1" ref="J29" ca="1">_FV(B29,"52 week high",TRUE)</f>
@@ -16726,7 +16952,7 @@
       </c>
       <c r="P29" s="7" cm="1">
         <f t="array" aca="1" ref="P29" ca="1">_FV(B29,"Volume")</f>
-        <v>9495916</v>
+        <v>9501571</v>
       </c>
       <c r="Q29" s="7" cm="1">
         <f t="array" aca="1" ref="Q29" ca="1">_FV(B29,"Volume average",TRUE)</f>
@@ -16746,7 +16972,7 @@
       </c>
       <c r="U29" s="7" cm="1">
         <f t="array" aca="1" ref="U29" ca="1">_FV(B29,"Market cap",TRUE)</f>
-        <v>173199607140</v>
+        <v>173147511810</v>
       </c>
       <c r="V29" s="7" cm="1">
         <f t="array" aca="1" ref="V29" ca="1">_FV(B29,"Shares outstanding",TRUE)</f>
@@ -16762,7 +16988,7 @@
       </c>
       <c r="C30" s="2" cm="1">
         <f t="array" aca="1" ref="C30" ca="1">_FV(B30,"Last trade time",TRUE)</f>
-        <v>46178.899437337503</v>
+        <v>46178.987539606249</v>
       </c>
       <c r="D30" t="str" cm="1">
         <f t="array" aca="1" ref="D30" ca="1">_FV(B30,"Currency")</f>
@@ -16770,23 +16996,23 @@
       </c>
       <c r="E30" s="3" cm="1">
         <f t="array" aca="1" ref="E30" ca="1">_FV(B30,"Price")</f>
-        <v>42.2</v>
+        <v>42.19</v>
       </c>
       <c r="F30" s="4" cm="1">
         <f t="array" aca="1" ref="F30" ca="1">_FV(B30,"Change (%)",TRUE)</f>
-        <v>-2.4277000000000003E-2</v>
+        <v>-2.4509E-2</v>
       </c>
       <c r="G30" s="5" cm="1">
         <f t="array" aca="1" ref="G30" ca="1">_FV(B30,"Change")</f>
-        <v>-1.05</v>
+        <v>-1.06</v>
       </c>
       <c r="H30" s="6" cm="1">
         <f t="array" aca="1" ref="H30" ca="1">_FV(B30,"P/E",TRUE)</f>
-        <v>80.721900000000005</v>
+        <v>78.742099999999994</v>
       </c>
       <c r="I30" s="6" cm="1">
         <f t="array" aca="1" ref="I30" ca="1">_FV(B30,"Beta")</f>
-        <v>0.73829999999999996</v>
+        <v>0.73470000000000002</v>
       </c>
       <c r="J30" s="3" cm="1">
         <f t="array" aca="1" ref="J30" ca="1">_FV(B30,"52 week high",TRUE)</f>
@@ -16814,7 +17040,7 @@
       </c>
       <c r="P30" s="7" cm="1">
         <f t="array" aca="1" ref="P30" ca="1">_FV(B30,"Volume")</f>
-        <v>4740219</v>
+        <v>4743799</v>
       </c>
       <c r="Q30" s="7" cm="1">
         <f t="array" aca="1" ref="Q30" ca="1">_FV(B30,"Volume average",TRUE)</f>
@@ -16834,7 +17060,7 @@
       </c>
       <c r="U30" s="7" cm="1">
         <f t="array" aca="1" ref="U30" ca="1">_FV(B30,"Market cap",TRUE)</f>
-        <v>12300274540</v>
+        <v>12297359783</v>
       </c>
       <c r="V30" s="7" cm="1">
         <f t="array" aca="1" ref="V30" ca="1">_FV(B30,"Shares outstanding",TRUE)</f>
@@ -16850,7 +17076,7 @@
       </c>
       <c r="C31" s="2">
         <f t="array" aca="1" ref="C31" ca="1">_FV(B31,"Last trade time",TRUE)</f>
-        <v>46178.90348910859</v>
+        <v>46178.998154142966</v>
       </c>
       <c r="D31" t="str">
         <f t="array" aca="1" ref="D31" ca="1">_FV(B31,"Currency")</f>
@@ -16874,7 +17100,7 @@
       </c>
       <c r="I31" s="6">
         <f t="array" aca="1" ref="I31" ca="1">_FV(B31,"Beta")</f>
-        <v>2.2103999999999999</v>
+        <v>2.2221000000000002</v>
       </c>
       <c r="J31" s="3">
         <f t="array" aca="1" ref="J31" ca="1">_FV(B31,"52 week high",TRUE)</f>
@@ -16902,7 +17128,7 @@
       </c>
       <c r="P31" s="7">
         <f t="array" aca="1" ref="P31" ca="1">_FV(B31,"Volume")</f>
-        <v>8497863</v>
+        <v>8551995</v>
       </c>
       <c r="Q31" s="7">
         <f t="array" aca="1" ref="Q31" ca="1">_FV(B31,"Volume average",TRUE)</f>
@@ -16938,7 +17164,7 @@
       </c>
       <c r="C32" s="2" cm="1">
         <f t="array" aca="1" ref="C32" ca="1">_FV(B32,"Last trade time",TRUE)</f>
-        <v>46178.900008078126</v>
+        <v>46178.999700774999</v>
       </c>
       <c r="D32" t="str" cm="1">
         <f t="array" aca="1" ref="D32" ca="1">_FV(B32,"Currency")</f>
@@ -16946,23 +17172,23 @@
       </c>
       <c r="E32" s="3" cm="1">
         <f t="array" aca="1" ref="E32" ca="1">_FV(B32,"Price")</f>
-        <v>396</v>
+        <v>395.94</v>
       </c>
       <c r="F32" s="4" cm="1">
         <f t="array" aca="1" ref="F32" ca="1">_FV(B32,"Change (%)",TRUE)</f>
-        <v>-5.4012000000000004E-2</v>
+        <v>-5.4154999999999995E-2</v>
       </c>
       <c r="G32" s="5" cm="1">
         <f t="array" aca="1" ref="G32" ca="1">_FV(B32,"Change")</f>
-        <v>-22.61</v>
+        <v>-22.67</v>
       </c>
       <c r="H32" s="6" cm="1">
         <f t="array" aca="1" ref="H32" ca="1">_FV(B32,"P/E",TRUE)</f>
-        <v>40.924599999999998</v>
+        <v>38.708399999999997</v>
       </c>
       <c r="I32" s="6" cm="1">
         <f t="array" aca="1" ref="I32" ca="1">_FV(B32,"Beta")</f>
-        <v>1.1893</v>
+        <v>1.1889000000000001</v>
       </c>
       <c r="J32" s="3" cm="1">
         <f t="array" aca="1" ref="J32" ca="1">_FV(B32,"52 week high",TRUE)</f>
@@ -16990,7 +17216,7 @@
       </c>
       <c r="P32" s="7" cm="1">
         <f t="array" aca="1" ref="P32" ca="1">_FV(B32,"Volume")</f>
-        <v>2535660</v>
+        <v>2538045</v>
       </c>
       <c r="Q32" s="7" cm="1">
         <f t="array" aca="1" ref="Q32" ca="1">_FV(B32,"Volume average",TRUE)</f>
@@ -17010,7 +17236,7 @@
       </c>
       <c r="U32" s="7" cm="1">
         <f t="array" aca="1" ref="U32" ca="1">_FV(B32,"Market cap",TRUE)</f>
-        <v>153766800000</v>
+        <v>153743502000</v>
       </c>
       <c r="V32" s="7" cm="1">
         <f t="array" aca="1" ref="V32" ca="1">_FV(B32,"Shares outstanding",TRUE)</f>
@@ -17026,7 +17252,7 @@
       </c>
       <c r="C33" s="2">
         <f t="array" aca="1" ref="C33" ca="1">_FV(B33,"Last trade time",TRUE)</f>
-        <v>46178.893552719528</v>
+        <v>46178.992053853908</v>
       </c>
       <c r="D33" t="str">
         <f t="array" aca="1" ref="D33" ca="1">_FV(B33,"Currency")</f>
@@ -17050,7 +17276,7 @@
       </c>
       <c r="I33" s="6">
         <f t="array" aca="1" ref="I33" ca="1">_FV(B33,"Beta")</f>
-        <v>1.4453</v>
+        <v>1.4363999999999999</v>
       </c>
       <c r="J33" s="3">
         <f t="array" aca="1" ref="J33" ca="1">_FV(B33,"52 week high",TRUE)</f>
@@ -17078,7 +17304,7 @@
       </c>
       <c r="P33" s="7">
         <f t="array" aca="1" ref="P33" ca="1">_FV(B33,"Volume")</f>
-        <v>3371039</v>
+        <v>3372747</v>
       </c>
       <c r="Q33" s="7">
         <f t="array" aca="1" ref="Q33" ca="1">_FV(B33,"Volume average",TRUE)</f>
@@ -17114,7 +17340,7 @@
       </c>
       <c r="C34" s="2" cm="1">
         <f t="array" aca="1" ref="C34" ca="1">_FV(B34,"Last trade time",TRUE)</f>
-        <v>46178.903107765625</v>
+        <v>46178.999772974217</v>
       </c>
       <c r="D34" t="str" cm="1">
         <f t="array" aca="1" ref="D34" ca="1">_FV(B34,"Currency")</f>
@@ -17138,7 +17364,7 @@
       </c>
       <c r="I34" s="6" cm="1">
         <f t="array" aca="1" ref="I34" ca="1">_FV(B34,"Beta")</f>
-        <v>1.1027</v>
+        <v>1.0900000000000001</v>
       </c>
       <c r="J34" s="3" cm="1">
         <f t="array" aca="1" ref="J34" ca="1">_FV(B34,"52 week high",TRUE)</f>
@@ -17166,7 +17392,7 @@
       </c>
       <c r="P34" s="7" cm="1">
         <f t="array" aca="1" ref="P34" ca="1">_FV(B34,"Volume")</f>
-        <v>7119075</v>
+        <v>7122674</v>
       </c>
       <c r="Q34" s="7" cm="1">
         <f t="array" aca="1" ref="Q34" ca="1">_FV(B34,"Volume average",TRUE)</f>
@@ -17202,7 +17428,7 @@
       </c>
       <c r="C35" s="2">
         <f t="array" aca="1" ref="C35" ca="1">_FV(B35,"Last trade time",TRUE)</f>
-        <v>46178.903474316408</v>
+        <v>46178.999992812503</v>
       </c>
       <c r="D35" t="str">
         <f t="array" aca="1" ref="D35" ca="1">_FV(B35,"Currency")</f>
@@ -17254,7 +17480,7 @@
       </c>
       <c r="P35" s="7">
         <f t="array" aca="1" ref="P35" ca="1">_FV(B35,"Volume")</f>
-        <v>23299314</v>
+        <v>23411519</v>
       </c>
       <c r="Q35" s="7">
         <f t="array" aca="1" ref="Q35" ca="1">_FV(B35,"Volume average",TRUE)</f>
@@ -17274,11 +17500,11 @@
       </c>
       <c r="U35" s="7">
         <f t="array" aca="1" ref="U35" ca="1">_FV(B35,"Market cap",TRUE)</f>
-        <v>4431548160000</v>
+        <v>4452967065600</v>
       </c>
       <c r="V35" s="7">
         <f t="array" aca="1" ref="V35" ca="1">_FV(B35,"Shares outstanding",TRUE)</f>
-        <v>12116000000</v>
+        <v>12174560000</v>
       </c>
     </row>
     <row r="36" spans="1:22">
@@ -17290,7 +17516,7 @@
       </c>
       <c r="C36" s="2">
         <f t="array" aca="1" ref="C36" ca="1">_FV(B36,"Last trade time",TRUE)</f>
-        <v>46178.903469803125</v>
+        <v>46178.999968020311</v>
       </c>
       <c r="D36" t="str">
         <f t="array" aca="1" ref="D36" ca="1">_FV(B36,"Currency")</f>
@@ -17314,7 +17540,7 @@
       </c>
       <c r="I36" s="6">
         <f t="array" aca="1" ref="I36" ca="1">_FV(B36,"Beta")</f>
-        <v>2.3544999999999998</v>
+        <v>2.3706999999999998</v>
       </c>
       <c r="J36" s="3">
         <f t="array" aca="1" ref="J36" ca="1">_FV(B36,"52 week high",TRUE)</f>
@@ -17342,7 +17568,7 @@
       </c>
       <c r="P36" s="7">
         <f t="array" aca="1" ref="P36" ca="1">_FV(B36,"Volume")</f>
-        <v>35758006</v>
+        <v>35905094</v>
       </c>
       <c r="Q36" s="7">
         <f t="array" aca="1" ref="Q36" ca="1">_FV(B36,"Volume average",TRUE)</f>
@@ -17378,7 +17604,7 @@
       </c>
       <c r="C37" s="2">
         <f t="array" aca="1" ref="C37" ca="1">_FV(B37,"Last trade time",TRUE)</f>
-        <v>46178.903447187498</v>
+        <v>46178.999949687503</v>
       </c>
       <c r="D37" t="str">
         <f t="array" aca="1" ref="D37" ca="1">_FV(B37,"Currency")</f>
@@ -17386,15 +17612,15 @@
       </c>
       <c r="E37" s="3">
         <f t="array" aca="1" ref="E37" ca="1">_FV(B37,"Price")</f>
-        <v>284.85090000000002</v>
+        <v>284.83999999999997</v>
       </c>
       <c r="F37" s="4">
         <f t="array" aca="1" ref="F37" ca="1">_FV(B37,"Change (%)",TRUE)</f>
-        <v>-5.6066000000000005E-2</v>
+        <v>-5.6101999999999999E-2</v>
       </c>
       <c r="G37" s="5">
         <f t="array" aca="1" ref="G37" ca="1">_FV(B37,"Change")</f>
-        <v>-16.9191</v>
+        <v>-16.93</v>
       </c>
       <c r="H37" s="6">
         <f t="array" aca="1" ref="H37" ca="1">_FV(B37,"P/E",TRUE)</f>
@@ -17402,7 +17628,7 @@
       </c>
       <c r="I37" s="6">
         <f t="array" aca="1" ref="I37" ca="1">_FV(B37,"Beta")</f>
-        <v>0.65800000000000003</v>
+        <v>0.66869999999999996</v>
       </c>
       <c r="J37" s="3">
         <f t="array" aca="1" ref="J37" ca="1">_FV(B37,"52 week high",TRUE)</f>
@@ -17430,7 +17656,7 @@
       </c>
       <c r="P37" s="7">
         <f t="array" aca="1" ref="P37" ca="1">_FV(B37,"Volume")</f>
-        <v>12469379</v>
+        <v>12509480</v>
       </c>
       <c r="Q37" s="7">
         <f t="array" aca="1" ref="Q37" ca="1">_FV(B37,"Volume average",TRUE)</f>
@@ -17450,7 +17676,7 @@
       </c>
       <c r="U37" s="7">
         <f t="array" aca="1" ref="U37" ca="1">_FV(B37,"Market cap",TRUE)</f>
-        <v>267727173601</v>
+        <v>267716928851</v>
       </c>
       <c r="V37" s="7">
         <f t="array" aca="1" ref="V37" ca="1">_FV(B37,"Shares outstanding",TRUE)</f>
@@ -17466,7 +17692,7 @@
       </c>
       <c r="C38" s="2">
         <f t="array" aca="1" ref="C38" ca="1">_FV(B38,"Last trade time",TRUE)</f>
-        <v>46178.902878483597</v>
+        <v>46178.99981981406</v>
       </c>
       <c r="D38" t="str">
         <f t="array" aca="1" ref="D38" ca="1">_FV(B38,"Currency")</f>
@@ -17490,7 +17716,7 @@
       </c>
       <c r="I38" s="6">
         <f t="array" aca="1" ref="I38" ca="1">_FV(B38,"Beta")</f>
-        <v>2.8271999999999999</v>
+        <v>2.8405999999999998</v>
       </c>
       <c r="J38" s="3">
         <f t="array" aca="1" ref="J38" ca="1">_FV(B38,"52 week high",TRUE)</f>
@@ -17518,7 +17744,7 @@
       </c>
       <c r="P38" s="7">
         <f t="array" aca="1" ref="P38" ca="1">_FV(B38,"Volume")</f>
-        <v>2115570</v>
+        <v>2127529</v>
       </c>
       <c r="Q38" s="7">
         <f t="array" aca="1" ref="Q38" ca="1">_FV(B38,"Volume average",TRUE)</f>
@@ -17554,7 +17780,7 @@
       </c>
       <c r="C39" s="2">
         <f t="array" aca="1" ref="C39" ca="1">_FV(B39,"Last trade time",TRUE)</f>
-        <v>46178.903523587498</v>
+        <v>46178.999997430466</v>
       </c>
       <c r="D39" t="str">
         <f t="array" aca="1" ref="D39" ca="1">_FV(B39,"Currency")</f>
@@ -17578,7 +17804,7 @@
       </c>
       <c r="I39" s="6">
         <f t="array" aca="1" ref="I39" ca="1">_FV(B39,"Beta")</f>
-        <v>2.2303000000000002</v>
+        <v>2.2513000000000001</v>
       </c>
       <c r="J39" s="3">
         <f t="array" aca="1" ref="J39" ca="1">_FV(B39,"52 week high",TRUE)</f>
@@ -17606,7 +17832,7 @@
       </c>
       <c r="P39" s="7">
         <f t="array" aca="1" ref="P39" ca="1">_FV(B39,"Volume")</f>
-        <v>144184718</v>
+        <v>145209405</v>
       </c>
       <c r="Q39" s="7">
         <f t="array" aca="1" ref="Q39" ca="1">_FV(B39,"Volume average",TRUE)</f>
@@ -17642,7 +17868,7 @@
       </c>
       <c r="C40" s="2">
         <f t="array" aca="1" ref="C40" ca="1">_FV(B40,"Last trade time",TRUE)</f>
-        <v>46178.903377546092</v>
+        <v>46178.999946029689</v>
       </c>
       <c r="D40" t="str">
         <f t="array" aca="1" ref="D40" ca="1">_FV(B40,"Currency")</f>
@@ -17662,11 +17888,11 @@
       </c>
       <c r="H40" s="6">
         <f t="array" aca="1" ref="H40" ca="1">_FV(B40,"P/E",TRUE)</f>
-        <v>1120.2860000000001</v>
+        <v>968.94200000000001</v>
       </c>
       <c r="I40" s="6">
         <f t="array" aca="1" ref="I40" ca="1">_FV(B40,"Beta")</f>
-        <v>3.1943999999999999</v>
+        <v>3.2339000000000002</v>
       </c>
       <c r="J40" s="3">
         <f t="array" aca="1" ref="J40" ca="1">_FV(B40,"52 week high",TRUE)</f>
@@ -17694,7 +17920,7 @@
       </c>
       <c r="P40" s="7">
         <f t="array" aca="1" ref="P40" ca="1">_FV(B40,"Volume")</f>
-        <v>31840107</v>
+        <v>32124857</v>
       </c>
       <c r="Q40" s="7">
         <f t="array" aca="1" ref="Q40" ca="1">_FV(B40,"Volume average",TRUE)</f>
@@ -17730,7 +17956,7 @@
       </c>
       <c r="C41" s="2">
         <f t="array" aca="1" ref="C41" ca="1">_FV(B41,"Last trade time",TRUE)</f>
-        <v>46178.903505508591</v>
+        <v>46178.999985601564</v>
       </c>
       <c r="D41" t="str">
         <f t="array" aca="1" ref="D41" ca="1">_FV(B41,"Currency")</f>
@@ -17754,7 +17980,7 @@
       </c>
       <c r="I41" s="6">
         <f t="array" aca="1" ref="I41" ca="1">_FV(B41,"Beta")</f>
-        <v>4.2358000000000002</v>
+        <v>4.2521000000000004</v>
       </c>
       <c r="J41" s="3">
         <f t="array" aca="1" ref="J41" ca="1">_FV(B41,"52 week high",TRUE)</f>
@@ -17782,7 +18008,7 @@
       </c>
       <c r="P41" s="7">
         <f t="array" aca="1" ref="P41" ca="1">_FV(B41,"Volume")</f>
-        <v>63853899</v>
+        <v>64148748</v>
       </c>
       <c r="Q41" s="7">
         <f t="array" aca="1" ref="Q41" ca="1">_FV(B41,"Volume average",TRUE)</f>
@@ -17818,7 +18044,7 @@
       </c>
       <c r="C42" s="2" cm="1">
         <f t="array" aca="1" ref="C42" ca="1">_FV(B42,"Last trade time",TRUE)</f>
-        <v>46178.90330844844</v>
+        <v>46178.999925196091</v>
       </c>
       <c r="D42" t="str" cm="1">
         <f t="array" aca="1" ref="D42" ca="1">_FV(B42,"Currency")</f>
@@ -17826,15 +18052,15 @@
       </c>
       <c r="E42" s="3" cm="1">
         <f t="array" aca="1" ref="E42" ca="1">_FV(B42,"Price")</f>
-        <v>281.58</v>
+        <v>281.64999999999998</v>
       </c>
       <c r="F42" s="4" cm="1">
         <f t="array" aca="1" ref="F42" ca="1">_FV(B42,"Change (%)",TRUE)</f>
-        <v>-3.5718E-2</v>
+        <v>-3.5478000000000003E-2</v>
       </c>
       <c r="G42" s="5" cm="1">
         <f t="array" aca="1" ref="G42" ca="1">_FV(B42,"Change")</f>
-        <v>-10.43</v>
+        <v>-10.36</v>
       </c>
       <c r="H42" s="6" t="e" vm="13">
         <f t="array" ref="H42">_FV(B42,"P/E",TRUE)</f>
@@ -17870,7 +18096,7 @@
       </c>
       <c r="P42" s="7" cm="1">
         <f t="array" aca="1" ref="P42" ca="1">_FV(B42,"Volume")</f>
-        <v>35684498</v>
+        <v>35812835</v>
       </c>
       <c r="Q42" s="7" cm="1">
         <f t="array" aca="1" ref="Q42" ca="1">_FV(B42,"Volume average",TRUE)</f>
@@ -17906,7 +18132,7 @@
       </c>
       <c r="C43" s="2" cm="1">
         <f t="array" aca="1" ref="C43" ca="1">_FV(B43,"Last trade time",TRUE)</f>
-        <v>46178.903519305466</v>
+        <v>46178.999734050783</v>
       </c>
       <c r="D43" t="str" cm="1">
         <f t="array" aca="1" ref="D43" ca="1">_FV(B43,"Currency")</f>
@@ -17930,7 +18156,7 @@
       </c>
       <c r="I43" s="6" cm="1">
         <f t="array" aca="1" ref="I43" ca="1">_FV(B43,"Beta")</f>
-        <v>1.4964999999999999</v>
+        <v>1.4967999999999999</v>
       </c>
       <c r="J43" s="3" cm="1">
         <f t="array" aca="1" ref="J43" ca="1">_FV(B43,"52 week high",TRUE)</f>
@@ -17958,7 +18184,7 @@
       </c>
       <c r="P43" s="7" cm="1">
         <f t="array" aca="1" ref="P43" ca="1">_FV(B43,"Volume")</f>
-        <v>1857490</v>
+        <v>1858629</v>
       </c>
       <c r="Q43" s="7" cm="1">
         <f t="array" aca="1" ref="Q43" ca="1">_FV(B43,"Volume average",TRUE)</f>
@@ -17994,7 +18220,7 @@
       </c>
       <c r="C44" s="2">
         <f t="array" aca="1" ref="C44" ca="1">_FV(B44,"Last trade time",TRUE)</f>
-        <v>46178.903096562499</v>
+        <v>46178.99997203672</v>
       </c>
       <c r="D44" t="str">
         <f t="array" aca="1" ref="D44" ca="1">_FV(B44,"Currency")</f>
@@ -18002,23 +18228,23 @@
       </c>
       <c r="E44" s="3">
         <f t="array" aca="1" ref="E44" ca="1">_FV(B44,"Price")</f>
-        <v>79.5</v>
+        <v>79.48</v>
       </c>
       <c r="F44" s="4">
         <f t="array" aca="1" ref="F44" ca="1">_FV(B44,"Change (%)",TRUE)</f>
-        <v>3.4887000000000001E-2</v>
+        <v>3.4626000000000004E-2</v>
       </c>
       <c r="G44" s="5">
         <f t="array" aca="1" ref="G44" ca="1">_FV(B44,"Change")</f>
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="H44" s="6">
         <f t="array" aca="1" ref="H44" ca="1">_FV(B44,"P/E",TRUE)</f>
-        <v>24.184100000000001</v>
+        <v>25.0212</v>
       </c>
       <c r="I44" s="6">
         <f t="array" aca="1" ref="I44" ca="1">_FV(B44,"Beta")</f>
-        <v>0.35670000000000002</v>
+        <v>0.35089999999999999</v>
       </c>
       <c r="J44" s="3">
         <f t="array" aca="1" ref="J44" ca="1">_FV(B44,"52 week high",TRUE)</f>
@@ -18046,7 +18272,7 @@
       </c>
       <c r="P44" s="7">
         <f t="array" aca="1" ref="P44" ca="1">_FV(B44,"Volume")</f>
-        <v>25696678</v>
+        <v>25708070</v>
       </c>
       <c r="Q44" s="7">
         <f t="array" aca="1" ref="Q44" ca="1">_FV(B44,"Volume average",TRUE)</f>
@@ -18066,7 +18292,7 @@
       </c>
       <c r="U44" s="7">
         <f t="array" aca="1" ref="U44" ca="1">_FV(B44,"Market cap",TRUE)</f>
-        <v>342047319000</v>
+        <v>341961269360</v>
       </c>
       <c r="V44" s="7">
         <f t="array" aca="1" ref="V44" ca="1">_FV(B44,"Shares outstanding",TRUE)</f>
@@ -18082,7 +18308,7 @@
       </c>
       <c r="C45" s="2">
         <f t="array" aca="1" ref="C45" ca="1">_FV(B45,"Last trade time",TRUE)</f>
-        <v>46178.902286168748</v>
+        <v>46178.999348020312</v>
       </c>
       <c r="D45" t="str">
         <f t="array" aca="1" ref="D45" ca="1">_FV(B45,"Currency")</f>
@@ -18106,7 +18332,7 @@
       </c>
       <c r="I45" s="6">
         <f t="array" aca="1" ref="I45" ca="1">_FV(B45,"Beta")</f>
-        <v>1.3332999999999999</v>
+        <v>1.37</v>
       </c>
       <c r="J45" s="3">
         <f t="array" aca="1" ref="J45" ca="1">_FV(B45,"52 week high",TRUE)</f>
@@ -18134,7 +18360,7 @@
       </c>
       <c r="P45" s="7">
         <f t="array" aca="1" ref="P45" ca="1">_FV(B45,"Volume")</f>
-        <v>4709234</v>
+        <v>4736560</v>
       </c>
       <c r="Q45" s="7">
         <f t="array" aca="1" ref="Q45" ca="1">_FV(B45,"Volume average",TRUE)</f>
@@ -18150,7 +18376,7 @@
       </c>
       <c r="T45" t="str">
         <f t="array" aca="1" ref="T45" ca="1">_FV(B45,"Industry")</f>
-        <v>Computers, Phones &amp; Household Electronics</v>
+        <v>Office Equipment</v>
       </c>
       <c r="U45" s="7">
         <f t="array" aca="1" ref="U45" ca="1">_FV(B45,"Market cap",TRUE)</f>
@@ -18170,7 +18396,7 @@
       </c>
       <c r="C46" s="2">
         <f t="array" aca="1" ref="C46" ca="1">_FV(B46,"Last trade time",TRUE)</f>
-        <v>46178.903039825782</v>
+        <v>46178.99998152734</v>
       </c>
       <c r="D46" t="str">
         <f t="array" aca="1" ref="D46" ca="1">_FV(B46,"Currency")</f>
@@ -18194,7 +18420,7 @@
       </c>
       <c r="I46" s="6">
         <f t="array" aca="1" ref="I46" ca="1">_FV(B46,"Beta")</f>
-        <v>2.3871000000000002</v>
+        <v>2.4003000000000001</v>
       </c>
       <c r="J46" s="3">
         <f t="array" aca="1" ref="J46" ca="1">_FV(B46,"52 week high",TRUE)</f>
@@ -18222,7 +18448,7 @@
       </c>
       <c r="P46" s="7">
         <f t="array" aca="1" ref="P46" ca="1">_FV(B46,"Volume")</f>
-        <v>5458829</v>
+        <v>5509318</v>
       </c>
       <c r="Q46" s="7">
         <f t="array" aca="1" ref="Q46" ca="1">_FV(B46,"Volume average",TRUE)</f>
@@ -18258,7 +18484,7 @@
       </c>
       <c r="C47" s="2" cm="1">
         <f t="array" aca="1" ref="C47" ca="1">_FV(B47,"Last trade time",TRUE)</f>
-        <v>46178.903093923436</v>
+        <v>46178.999868414059</v>
       </c>
       <c r="D47" t="str" cm="1">
         <f t="array" aca="1" ref="D47" ca="1">_FV(B47,"Currency")</f>
@@ -18266,15 +18492,15 @@
       </c>
       <c r="E47" s="3" cm="1">
         <f t="array" aca="1" ref="E47" ca="1">_FV(B47,"Price")</f>
-        <v>279.77499999999998</v>
+        <v>279.83999999999997</v>
       </c>
       <c r="F47" s="4" cm="1">
         <f t="array" aca="1" ref="F47" ca="1">_FV(B47,"Change (%)",TRUE)</f>
-        <v>2.5869E-2</v>
+        <v>2.6107000000000002E-2</v>
       </c>
       <c r="G47" s="5" cm="1">
         <f t="array" aca="1" ref="G47" ca="1">_FV(B47,"Change")</f>
-        <v>7.0549999999999997</v>
+        <v>7.12</v>
       </c>
       <c r="H47" s="6" cm="1">
         <f t="array" aca="1" ref="H47" ca="1">_FV(B47,"P/E",TRUE)</f>
@@ -18282,7 +18508,7 @@
       </c>
       <c r="I47" s="6" cm="1">
         <f t="array" aca="1" ref="I47" ca="1">_FV(B47,"Beta")</f>
-        <v>0.41560000000000002</v>
+        <v>0.40989999999999999</v>
       </c>
       <c r="J47" s="3" cm="1">
         <f t="array" aca="1" ref="J47" ca="1">_FV(B47,"52 week high",TRUE)</f>
@@ -18310,7 +18536,7 @@
       </c>
       <c r="P47" s="7" cm="1">
         <f t="array" aca="1" ref="P47" ca="1">_FV(B47,"Volume")</f>
-        <v>5416099</v>
+        <v>5428103</v>
       </c>
       <c r="Q47" s="7" cm="1">
         <f t="array" aca="1" ref="Q47" ca="1">_FV(B47,"Volume average",TRUE)</f>
@@ -18330,7 +18556,7 @@
       </c>
       <c r="U47" s="7" cm="1">
         <f t="array" aca="1" ref="U47" ca="1">_FV(B47,"Market cap",TRUE)</f>
-        <v>198781788172</v>
+        <v>198827971055</v>
       </c>
       <c r="V47" s="7" cm="1">
         <f t="array" aca="1" ref="V47" ca="1">_FV(B47,"Shares outstanding",TRUE)</f>
@@ -18346,7 +18572,7 @@
       </c>
       <c r="C48" s="2" cm="1">
         <f t="array" aca="1" ref="C48" ca="1">_FV(B48,"Last trade time",TRUE)</f>
-        <v>46178.895453796096</v>
+        <v>46178.999710474222</v>
       </c>
       <c r="D48" t="str" cm="1">
         <f t="array" aca="1" ref="D48" ca="1">_FV(B48,"Currency")</f>
@@ -18370,7 +18596,7 @@
       </c>
       <c r="I48" s="6" cm="1">
         <f t="array" aca="1" ref="I48" ca="1">_FV(B48,"Beta")</f>
-        <v>1.5414000000000001</v>
+        <v>1.5269999999999999</v>
       </c>
       <c r="J48" s="3" cm="1">
         <f t="array" aca="1" ref="J48" ca="1">_FV(B48,"52 week high",TRUE)</f>
@@ -18398,7 +18624,7 @@
       </c>
       <c r="P48" s="7" cm="1">
         <f t="array" aca="1" ref="P48" ca="1">_FV(B48,"Volume")</f>
-        <v>1780269</v>
+        <v>1786156</v>
       </c>
       <c r="Q48" s="7" cm="1">
         <f t="array" aca="1" ref="Q48" ca="1">_FV(B48,"Volume average",TRUE)</f>
@@ -18434,7 +18660,7 @@
       </c>
       <c r="C49" s="2">
         <f t="array" aca="1" ref="C49" ca="1">_FV(B49,"Last trade time",TRUE)</f>
-        <v>46178.903478969529</v>
+        <v>46178.999988992968</v>
       </c>
       <c r="D49" t="str">
         <f t="array" aca="1" ref="D49" ca="1">_FV(B49,"Currency")</f>
@@ -18458,7 +18684,7 @@
       </c>
       <c r="I49" s="6">
         <f t="array" aca="1" ref="I49" ca="1">_FV(B49,"Beta")</f>
-        <v>1.2296</v>
+        <v>1.2386999999999999</v>
       </c>
       <c r="J49" s="3">
         <f t="array" aca="1" ref="J49" ca="1">_FV(B49,"52 week high",TRUE)</f>
@@ -18486,7 +18712,7 @@
       </c>
       <c r="P49" s="7">
         <f t="array" aca="1" ref="P49" ca="1">_FV(B49,"Volume")</f>
-        <v>29619204</v>
+        <v>30091610</v>
       </c>
       <c r="Q49" s="7">
         <f t="array" aca="1" ref="Q49" ca="1">_FV(B49,"Volume average",TRUE)</f>
@@ -18522,7 +18748,7 @@
       </c>
       <c r="C50" s="2">
         <f t="array" aca="1" ref="C50" ca="1">_FV(B50,"Last trade time",TRUE)</f>
-        <v>46178.903561006249</v>
+        <v>46178.999995358594</v>
       </c>
       <c r="D50" t="str">
         <f t="array" aca="1" ref="D50" ca="1">_FV(B50,"Currency")</f>
@@ -18546,7 +18772,7 @@
       </c>
       <c r="I50" s="6">
         <f t="array" aca="1" ref="I50" ca="1">_FV(B50,"Beta")</f>
-        <v>2.2330999999999999</v>
+        <v>2.1796000000000002</v>
       </c>
       <c r="J50" s="3">
         <f t="array" aca="1" ref="J50" ca="1">_FV(B50,"52 week high",TRUE)</f>
@@ -18574,7 +18800,7 @@
       </c>
       <c r="P50" s="7">
         <f t="array" aca="1" ref="P50" ca="1">_FV(B50,"Volume")</f>
-        <v>91834421</v>
+        <v>93976392</v>
       </c>
       <c r="Q50" s="7">
         <f t="array" aca="1" ref="Q50" ca="1">_FV(B50,"Volume average",TRUE)</f>
@@ -18610,7 +18836,7 @@
       </c>
       <c r="C51" s="2">
         <f t="array" aca="1" ref="C51" ca="1">_FV(B51,"Last trade time",TRUE)</f>
-        <v>46178.90349166641</v>
+        <v>46178.99999871484</v>
       </c>
       <c r="D51" t="str">
         <f t="array" aca="1" ref="D51" ca="1">_FV(B51,"Currency")</f>
@@ -18634,7 +18860,7 @@
       </c>
       <c r="I51" s="6">
         <f t="array" aca="1" ref="I51" ca="1">_FV(B51,"Beta")</f>
-        <v>1.1068</v>
+        <v>1.1158999999999999</v>
       </c>
       <c r="J51" s="3">
         <f t="array" aca="1" ref="J51" ca="1">_FV(B51,"52 week high",TRUE)</f>
@@ -18662,7 +18888,7 @@
       </c>
       <c r="P51" s="7">
         <f t="array" aca="1" ref="P51" ca="1">_FV(B51,"Volume")</f>
-        <v>34602619</v>
+        <v>34782164</v>
       </c>
       <c r="Q51" s="7">
         <f t="array" aca="1" ref="Q51" ca="1">_FV(B51,"Volume average",TRUE)</f>
@@ -18698,7 +18924,7 @@
       </c>
       <c r="C52" s="2">
         <f t="array" aca="1" ref="C52" ca="1">_FV(B52,"Last trade time",TRUE)</f>
-        <v>46178.903323182814</v>
+        <v>46178.999999524996</v>
       </c>
       <c r="D52" t="str">
         <f t="array" aca="1" ref="D52" ca="1">_FV(B52,"Currency")</f>
@@ -18722,7 +18948,7 @@
       </c>
       <c r="I52" s="6">
         <f t="array" aca="1" ref="I52" ca="1">_FV(B52,"Beta")</f>
-        <v>3.4868000000000001</v>
+        <v>3.5194000000000001</v>
       </c>
       <c r="J52" s="3">
         <f t="array" aca="1" ref="J52" ca="1">_FV(B52,"52 week high",TRUE)</f>
@@ -18750,7 +18976,7 @@
       </c>
       <c r="P52" s="7">
         <f t="array" aca="1" ref="P52" ca="1">_FV(B52,"Volume")</f>
-        <v>41714099</v>
+        <v>41943521</v>
       </c>
       <c r="Q52" s="7">
         <f t="array" aca="1" ref="Q52" ca="1">_FV(B52,"Volume average",TRUE)</f>
@@ -18786,7 +19012,7 @@
       </c>
       <c r="C53" s="2">
         <f t="array" aca="1" ref="C53" ca="1">_FV(B53,"Last trade time",TRUE)</f>
-        <v>46178.90346648125</v>
+        <v>46178.999999339845</v>
       </c>
       <c r="D53" t="str">
         <f t="array" aca="1" ref="D53" ca="1">_FV(B53,"Currency")</f>
@@ -18806,11 +19032,11 @@
       </c>
       <c r="H53" s="6">
         <f t="array" aca="1" ref="H53" ca="1">_FV(B53,"P/E",TRUE)</f>
-        <v>40.791200000000003</v>
+        <v>47.022599999999997</v>
       </c>
       <c r="I53" s="6">
         <f t="array" aca="1" ref="I53" ca="1">_FV(B53,"Beta")</f>
-        <v>2.1732</v>
+        <v>2.1979000000000002</v>
       </c>
       <c r="J53" s="3">
         <f t="array" aca="1" ref="J53" ca="1">_FV(B53,"52 week high",TRUE)</f>
@@ -18838,7 +19064,7 @@
       </c>
       <c r="P53" s="7">
         <f t="array" aca="1" ref="P53" ca="1">_FV(B53,"Volume")</f>
-        <v>76156083</v>
+        <v>77250536</v>
       </c>
       <c r="Q53" s="7">
         <f t="array" aca="1" ref="Q53" ca="1">_FV(B53,"Volume average",TRUE)</f>
@@ -18874,7 +19100,7 @@
       </c>
       <c r="C54" s="2" cm="1">
         <f t="array" aca="1" ref="C54" ca="1">_FV(B54,"Last trade time",TRUE)</f>
-        <v>46178.903350092187</v>
+        <v>46178.999969756253</v>
       </c>
       <c r="D54" t="str" cm="1">
         <f t="array" aca="1" ref="D54" ca="1">_FV(B54,"Currency")</f>
@@ -18882,23 +19108,23 @@
       </c>
       <c r="E54" s="3" cm="1">
         <f t="array" aca="1" ref="E54" ca="1">_FV(B54,"Price")</f>
-        <v>250.28</v>
+        <v>250.11</v>
       </c>
       <c r="F54" s="4" cm="1">
         <f t="array" aca="1" ref="F54" ca="1">_FV(B54,"Change (%)",TRUE)</f>
-        <v>-6.8344000000000002E-2</v>
+        <v>-6.8977000000000011E-2</v>
       </c>
       <c r="G54" s="5" cm="1">
         <f t="array" aca="1" ref="G54" ca="1">_FV(B54,"Change")</f>
-        <v>-18.36</v>
-      </c>
-      <c r="H54" s="6" cm="1">
-        <f t="array" aca="1" ref="H54" ca="1">_FV(B54,"P/E",TRUE)</f>
-        <v>0</v>
+        <v>-18.53</v>
+      </c>
+      <c r="H54" s="6" t="e" cm="1" vm="13">
+        <f t="array" ref="H54">_FV(B54,"P/E",TRUE)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="I54" s="6" cm="1">
         <f t="array" aca="1" ref="I54" ca="1">_FV(B54,"Beta")</f>
-        <v>1.6660999999999999</v>
+        <v>1.6554</v>
       </c>
       <c r="J54" s="3" cm="1">
         <f t="array" aca="1" ref="J54" ca="1">_FV(B54,"52 week high",TRUE)</f>
@@ -18926,7 +19152,7 @@
       </c>
       <c r="P54" s="7" cm="1">
         <f t="array" aca="1" ref="P54" ca="1">_FV(B54,"Volume")</f>
-        <v>4732524</v>
+        <v>4735502</v>
       </c>
       <c r="Q54" s="7" cm="1">
         <f t="array" aca="1" ref="Q54" ca="1">_FV(B54,"Volume average",TRUE)</f>
@@ -18946,7 +19172,7 @@
       </c>
       <c r="U54" s="7" cm="1">
         <f t="array" aca="1" ref="U54" ca="1">_FV(B54,"Market cap",TRUE)</f>
-        <v>88465520536</v>
+        <v>88405431282</v>
       </c>
       <c r="V54" s="7" cm="1">
         <f t="array" aca="1" ref="V54" ca="1">_FV(B54,"Shares outstanding",TRUE)</f>
@@ -18986,7 +19212,7 @@
       </c>
       <c r="I55" s="6" cm="1">
         <f t="array" aca="1" ref="I55" ca="1">_FV(B55,"Beta")</f>
-        <v>1.1182000000000001</v>
+        <v>1.1197999999999999</v>
       </c>
       <c r="J55" s="3" t="e" cm="1" vm="59">
         <f t="array" ref="J55">_FV(B55,"52 week high",TRUE)</f>
@@ -19050,7 +19276,7 @@
       </c>
       <c r="C56" s="2">
         <f t="array" aca="1" ref="C56" ca="1">_FV(B56,"Last trade time",TRUE)</f>
-        <v>46178.903528946095</v>
+        <v>46178.999996816405</v>
       </c>
       <c r="D56" t="str">
         <f t="array" aca="1" ref="D56" ca="1">_FV(B56,"Currency")</f>
@@ -19058,23 +19284,23 @@
       </c>
       <c r="E56" s="3">
         <f t="array" aca="1" ref="E56" ca="1">_FV(B56,"Price")</f>
-        <v>14.35</v>
+        <v>14.38</v>
       </c>
       <c r="F56" s="4">
         <f t="array" aca="1" ref="F56" ca="1">_FV(B56,"Change (%)",TRUE)</f>
-        <v>-0.13658200000000001</v>
+        <v>-0.13477700000000001</v>
       </c>
       <c r="G56" s="5">
         <f t="array" aca="1" ref="G56" ca="1">_FV(B56,"Change")</f>
-        <v>-2.27</v>
+        <v>-2.2400000000000002</v>
       </c>
       <c r="H56" s="6">
         <f t="array" aca="1" ref="H56" ca="1">_FV(B56,"P/E",TRUE)</f>
-        <v>103.3112</v>
+        <v>89.372299999999996</v>
       </c>
       <c r="I56" s="6">
         <f t="array" aca="1" ref="I56" ca="1">_FV(B56,"Beta")</f>
-        <v>1.1414</v>
+        <v>1.1538999999999999</v>
       </c>
       <c r="J56" s="3">
         <f t="array" aca="1" ref="J56" ca="1">_FV(B56,"52 week high",TRUE)</f>
@@ -19102,7 +19328,7 @@
       </c>
       <c r="P56" s="7">
         <f t="array" aca="1" ref="P56" ca="1">_FV(B56,"Volume")</f>
-        <v>182912447</v>
+        <v>185183792</v>
       </c>
       <c r="Q56" s="7">
         <f t="array" aca="1" ref="Q56" ca="1">_FV(B56,"Volume average",TRUE)</f>
@@ -19122,7 +19348,7 @@
       </c>
       <c r="U56" s="7">
         <f t="array" aca="1" ref="U56" ca="1">_FV(B56,"Market cap",TRUE)</f>
-        <v>82401144000</v>
+        <v>82573411200</v>
       </c>
       <c r="V56" s="7">
         <f t="array" aca="1" ref="V56" ca="1">_FV(B56,"Shares outstanding",TRUE)</f>
@@ -19138,7 +19364,7 @@
       </c>
       <c r="C57" s="2">
         <f t="array" aca="1" ref="C57" ca="1">_FV(B57,"Last trade time",TRUE)</f>
-        <v>46178.903395219531</v>
+        <v>46178.999993587502</v>
       </c>
       <c r="D57" t="str">
         <f t="array" aca="1" ref="D57" ca="1">_FV(B57,"Currency")</f>
@@ -19146,15 +19372,15 @@
       </c>
       <c r="E57" s="3">
         <f t="array" aca="1" ref="E57" ca="1">_FV(B57,"Price")</f>
-        <v>112.47</v>
+        <v>112.45</v>
       </c>
       <c r="F57" s="4">
         <f t="array" aca="1" ref="F57" ca="1">_FV(B57,"Change (%)",TRUE)</f>
-        <v>-5.7724999999999999E-2</v>
+        <v>-5.7891999999999999E-2</v>
       </c>
       <c r="G57" s="5">
         <f t="array" aca="1" ref="G57" ca="1">_FV(B57,"Change")</f>
-        <v>-6.89</v>
+        <v>-6.91</v>
       </c>
       <c r="H57" s="6">
         <f t="array" aca="1" ref="H57" ca="1">_FV(B57,"P/E",TRUE)</f>
@@ -19162,7 +19388,7 @@
       </c>
       <c r="I57" s="6">
         <f t="array" aca="1" ref="I57" ca="1">_FV(B57,"Beta")</f>
-        <v>0.92969999999999997</v>
+        <v>0.94669999999999999</v>
       </c>
       <c r="J57" s="3">
         <f t="array" aca="1" ref="J57" ca="1">_FV(B57,"52 week high",TRUE)</f>
@@ -19190,7 +19416,7 @@
       </c>
       <c r="P57" s="7">
         <f t="array" aca="1" ref="P57" ca="1">_FV(B57,"Volume")</f>
-        <v>31277351</v>
+        <v>31452022</v>
       </c>
       <c r="Q57" s="7">
         <f t="array" aca="1" ref="Q57" ca="1">_FV(B57,"Volume average",TRUE)</f>
@@ -19210,7 +19436,7 @@
       </c>
       <c r="U57" s="7">
         <f t="array" aca="1" ref="U57" ca="1">_FV(B57,"Market cap",TRUE)</f>
-        <v>115991210760</v>
+        <v>115970584600</v>
       </c>
       <c r="V57" s="7">
         <f t="array" aca="1" ref="V57" ca="1">_FV(B57,"Shares outstanding",TRUE)</f>
@@ -19226,7 +19452,7 @@
       </c>
       <c r="C58" s="2">
         <f t="array" aca="1" ref="C58" ca="1">_FV(B58,"Last trade time",TRUE)</f>
-        <v>46178.903472603903</v>
+        <v>46178.99999732578</v>
       </c>
       <c r="D58" t="str">
         <f t="array" aca="1" ref="D58" ca="1">_FV(B58,"Currency")</f>
@@ -19250,7 +19476,7 @@
       </c>
       <c r="I58" s="6">
         <f t="array" aca="1" ref="I58" ca="1">_FV(B58,"Beta")</f>
-        <v>2.2008000000000001</v>
+        <v>2.2010999999999998</v>
       </c>
       <c r="J58" s="3">
         <f t="array" aca="1" ref="J58" ca="1">_FV(B58,"52 week high",TRUE)</f>
@@ -19278,7 +19504,7 @@
       </c>
       <c r="P58" s="7">
         <f t="array" aca="1" ref="P58" ca="1">_FV(B58,"Volume")</f>
-        <v>218200155</v>
+        <v>219655531</v>
       </c>
       <c r="Q58" s="7">
         <f t="array" aca="1" ref="Q58" ca="1">_FV(B58,"Volume average",TRUE)</f>
@@ -19314,7 +19540,7 @@
       </c>
       <c r="C59" s="2" cm="1">
         <f t="array" aca="1" ref="C59" ca="1">_FV(B59,"Last trade time",TRUE)</f>
-        <v>46178.901148390622</v>
+        <v>46178.999814721872</v>
       </c>
       <c r="D59" t="str" cm="1">
         <f t="array" aca="1" ref="D59" ca="1">_FV(B59,"Currency")</f>
@@ -19338,7 +19564,7 @@
       </c>
       <c r="I59" s="6" cm="1">
         <f t="array" aca="1" ref="I59" ca="1">_FV(B59,"Beta")</f>
-        <v>1.9702</v>
+        <v>1.9728000000000001</v>
       </c>
       <c r="J59" s="3" cm="1">
         <f t="array" aca="1" ref="J59" ca="1">_FV(B59,"52 week high",TRUE)</f>
@@ -19366,7 +19592,7 @@
       </c>
       <c r="P59" s="7" cm="1">
         <f t="array" aca="1" ref="P59" ca="1">_FV(B59,"Volume")</f>
-        <v>19047617</v>
+        <v>19056593</v>
       </c>
       <c r="Q59" s="7" cm="1">
         <f t="array" aca="1" ref="Q59" ca="1">_FV(B59,"Volume average",TRUE)</f>
@@ -19402,7 +19628,7 @@
       </c>
       <c r="C60" s="2">
         <f t="array" aca="1" ref="C60" ca="1">_FV(B60,"Last trade time",TRUE)</f>
-        <v>46178.903343032034</v>
+        <v>46178.999996851562</v>
       </c>
       <c r="D60" t="str">
         <f t="array" aca="1" ref="D60" ca="1">_FV(B60,"Currency")</f>
@@ -19426,7 +19652,7 @@
       </c>
       <c r="I60" s="6">
         <f t="array" aca="1" ref="I60" ca="1">_FV(B60,"Beta")</f>
-        <v>2.6339999999999999</v>
+        <v>2.6793</v>
       </c>
       <c r="J60" s="3">
         <f t="array" aca="1" ref="J60" ca="1">_FV(B60,"52 week high",TRUE)</f>
@@ -19454,7 +19680,7 @@
       </c>
       <c r="P60" s="7">
         <f t="array" aca="1" ref="P60" ca="1">_FV(B60,"Volume")</f>
-        <v>63470473</v>
+        <v>63881353</v>
       </c>
       <c r="Q60" s="7">
         <f t="array" aca="1" ref="Q60" ca="1">_FV(B60,"Volume average",TRUE)</f>
@@ -19490,7 +19716,7 @@
       </c>
       <c r="C61" s="2">
         <f t="array" aca="1" ref="C61" ca="1">_FV(B61,"Last trade time",TRUE)</f>
-        <v>46178.90353287031</v>
+        <v>46178.999998680469</v>
       </c>
       <c r="D61" t="str">
         <f t="array" aca="1" ref="D61" ca="1">_FV(B61,"Currency")</f>
@@ -19498,15 +19724,15 @@
       </c>
       <c r="E61" s="3">
         <f t="array" aca="1" ref="E61" ca="1">_FV(B61,"Price")</f>
-        <v>213.41</v>
+        <v>213.68</v>
       </c>
       <c r="F61" s="4">
         <f t="array" aca="1" ref="F61" ca="1">_FV(B61,"Change (%)",TRUE)</f>
-        <v>-9.7020999999999996E-2</v>
+        <v>-9.5878999999999992E-2</v>
       </c>
       <c r="G61" s="5">
         <f t="array" aca="1" ref="G61" ca="1">_FV(B61,"Change")</f>
-        <v>-22.93</v>
+        <v>-22.66</v>
       </c>
       <c r="H61" s="6">
         <f t="array" aca="1" ref="H61" ca="1">_FV(B61,"P/E",TRUE)</f>
@@ -19514,7 +19740,7 @@
       </c>
       <c r="I61" s="6">
         <f t="array" aca="1" ref="I61" ca="1">_FV(B61,"Beta")</f>
-        <v>1.651</v>
+        <v>1.6594</v>
       </c>
       <c r="J61" s="3">
         <f t="array" aca="1" ref="J61" ca="1">_FV(B61,"52 week high",TRUE)</f>
@@ -19530,7 +19756,7 @@
       </c>
       <c r="M61" s="3">
         <f t="array" aca="1" ref="M61" ca="1">_FV(B61,"Low")</f>
-        <v>209.45</v>
+        <v>209.45009999999999</v>
       </c>
       <c r="N61" s="3">
         <f t="array" aca="1" ref="N61" ca="1">_FV(B61,"Open")</f>
@@ -19542,7 +19768,7 @@
       </c>
       <c r="P61" s="7">
         <f t="array" aca="1" ref="P61" ca="1">_FV(B61,"Volume")</f>
-        <v>28858851</v>
+        <v>29019876</v>
       </c>
       <c r="Q61" s="7">
         <f t="array" aca="1" ref="Q61" ca="1">_FV(B61,"Volume average",TRUE)</f>
@@ -19562,7 +19788,7 @@
       </c>
       <c r="U61" s="7">
         <f t="array" aca="1" ref="U61" ca="1">_FV(B61,"Market cap",TRUE)</f>
-        <v>613776976860</v>
+        <v>614553509280</v>
       </c>
       <c r="V61" s="7">
         <f t="array" aca="1" ref="V61" ca="1">_FV(B61,"Shares outstanding",TRUE)</f>
@@ -19578,7 +19804,7 @@
       </c>
       <c r="C62" s="2" cm="1">
         <f t="array" aca="1" ref="C62" ca="1">_FV(B62,"Last trade time",TRUE)</f>
-        <v>46178.90344487266</v>
+        <v>46178.999910335158</v>
       </c>
       <c r="D62" t="str" cm="1">
         <f t="array" aca="1" ref="D62" ca="1">_FV(B62,"Currency")</f>
@@ -19598,11 +19824,11 @@
       </c>
       <c r="H62" s="6" cm="1">
         <f t="array" aca="1" ref="H62" ca="1">_FV(B62,"P/E",TRUE)</f>
-        <v>229.9357</v>
+        <v>224.0016</v>
       </c>
       <c r="I62" s="6" cm="1">
         <f t="array" aca="1" ref="I62" ca="1">_FV(B62,"Beta")</f>
-        <v>0.94479999999999997</v>
+        <v>0.95150000000000001</v>
       </c>
       <c r="J62" s="3" cm="1">
         <f t="array" aca="1" ref="J62" ca="1">_FV(B62,"52 week high",TRUE)</f>
@@ -19630,7 +19856,7 @@
       </c>
       <c r="P62" s="7" cm="1">
         <f t="array" aca="1" ref="P62" ca="1">_FV(B62,"Volume")</f>
-        <v>7777903</v>
+        <v>7795476</v>
       </c>
       <c r="Q62" s="7" cm="1">
         <f t="array" aca="1" ref="Q62" ca="1">_FV(B62,"Volume average",TRUE)</f>
@@ -19666,7 +19892,7 @@
       </c>
       <c r="C63" s="2">
         <f t="array" aca="1" ref="C63" ca="1">_FV(B63,"Last trade time",TRUE)</f>
-        <v>46178.903380253905</v>
+        <v>46178.999919571092</v>
       </c>
       <c r="D63" t="str">
         <f t="array" aca="1" ref="D63" ca="1">_FV(B63,"Currency")</f>
@@ -19690,7 +19916,7 @@
       </c>
       <c r="I63" s="6">
         <f t="array" aca="1" ref="I63" ca="1">_FV(B63,"Beta")</f>
-        <v>0.96640000000000004</v>
+        <v>0.96460000000000001</v>
       </c>
       <c r="J63" s="3">
         <f t="array" aca="1" ref="J63" ca="1">_FV(B63,"52 week high",TRUE)</f>
@@ -19718,7 +19944,7 @@
       </c>
       <c r="P63" s="7">
         <f t="array" aca="1" ref="P63" ca="1">_FV(B63,"Volume")</f>
-        <v>35487140</v>
+        <v>35568433</v>
       </c>
       <c r="Q63" s="7">
         <f t="array" aca="1" ref="Q63" ca="1">_FV(B63,"Volume average",TRUE)</f>
@@ -19738,11 +19964,11 @@
       </c>
       <c r="U63" s="7">
         <f t="array" aca="1" ref="U63" ca="1">_FV(B63,"Market cap",TRUE)</f>
-        <v>5849783816</v>
+        <v>5823672172</v>
       </c>
       <c r="V63" s="7">
         <f t="array" aca="1" ref="V63" ca="1">_FV(B63,"Shares outstanding",TRUE)</f>
-        <v>520443400</v>
+        <v>518120300</v>
       </c>
     </row>
     <row r="64" spans="1:22">
@@ -19754,7 +19980,7 @@
       </c>
       <c r="C64" s="2" cm="1">
         <f t="array" aca="1" ref="C64" ca="1">_FV(B64,"Last trade time",TRUE)</f>
-        <v>46178.902205948434</v>
+        <v>46178.999661064059</v>
       </c>
       <c r="D64" t="str" cm="1">
         <f t="array" aca="1" ref="D64" ca="1">_FV(B64,"Currency")</f>
@@ -19774,11 +20000,11 @@
       </c>
       <c r="H64" s="6" cm="1">
         <f t="array" aca="1" ref="H64" ca="1">_FV(B64,"P/E",TRUE)</f>
-        <v>20.589200000000002</v>
+        <v>21.4315</v>
       </c>
       <c r="I64" s="6" cm="1">
         <f t="array" aca="1" ref="I64" ca="1">_FV(B64,"Beta")</f>
-        <v>0.3861</v>
+        <v>0.37519999999999998</v>
       </c>
       <c r="J64" s="3" cm="1">
         <f t="array" aca="1" ref="J64" ca="1">_FV(B64,"52 week high",TRUE)</f>
@@ -19806,7 +20032,7 @@
       </c>
       <c r="P64" s="7" cm="1">
         <f t="array" aca="1" ref="P64" ca="1">_FV(B64,"Volume")</f>
-        <v>10956862</v>
+        <v>10963204</v>
       </c>
       <c r="Q64" s="7" cm="1">
         <f t="array" aca="1" ref="Q64" ca="1">_FV(B64,"Volume average",TRUE)</f>
@@ -19842,7 +20068,7 @@
       </c>
       <c r="C65" s="2">
         <f t="array" aca="1" ref="C65" ca="1">_FV(B65,"Last trade time",TRUE)</f>
-        <v>46178.903352522655</v>
+        <v>46178.997146411719</v>
       </c>
       <c r="D65" t="str">
         <f t="array" aca="1" ref="D65" ca="1">_FV(B65,"Currency")</f>
@@ -19866,7 +20092,7 @@
       </c>
       <c r="I65" s="6">
         <f t="array" aca="1" ref="I65" ca="1">_FV(B65,"Beta")</f>
-        <v>1.3727</v>
+        <v>1.3917999999999999</v>
       </c>
       <c r="J65" s="3">
         <f t="array" aca="1" ref="J65" ca="1">_FV(B65,"52 week high",TRUE)</f>
@@ -19894,7 +20120,7 @@
       </c>
       <c r="P65" s="7">
         <f t="array" aca="1" ref="P65" ca="1">_FV(B65,"Volume")</f>
-        <v>2404767</v>
+        <v>2418177</v>
       </c>
       <c r="Q65" s="7">
         <f t="array" aca="1" ref="Q65" ca="1">_FV(B65,"Volume average",TRUE)</f>
@@ -19930,7 +20156,7 @@
       </c>
       <c r="C66" s="2">
         <f t="array" aca="1" ref="C66" ca="1">_FV(B66,"Last trade time",TRUE)</f>
-        <v>46178.903495728904</v>
+        <v>46178.99990655078</v>
       </c>
       <c r="D66" t="str">
         <f t="array" aca="1" ref="D66" ca="1">_FV(B66,"Currency")</f>
@@ -19954,7 +20180,7 @@
       </c>
       <c r="I66" s="6">
         <f t="array" aca="1" ref="I66" ca="1">_FV(B66,"Beta")</f>
-        <v>0.71440000000000003</v>
+        <v>0.74539999999999995</v>
       </c>
       <c r="J66" s="3">
         <f t="array" aca="1" ref="J66" ca="1">_FV(B66,"52 week high",TRUE)</f>
@@ -19982,7 +20208,7 @@
       </c>
       <c r="P66" s="7">
         <f t="array" aca="1" ref="P66" ca="1">_FV(B66,"Volume")</f>
-        <v>56920442</v>
+        <v>57201960</v>
       </c>
       <c r="Q66" s="7">
         <f t="array" aca="1" ref="Q66" ca="1">_FV(B66,"Volume average",TRUE)</f>
@@ -20018,7 +20244,7 @@
       </c>
       <c r="C67" s="2" cm="1">
         <f t="array" aca="1" ref="C67" ca="1">_FV(B67,"Last trade time",TRUE)</f>
-        <v>46178.903501770314</v>
+        <v>46178.999979687498</v>
       </c>
       <c r="D67" t="str" cm="1">
         <f t="array" aca="1" ref="D67" ca="1">_FV(B67,"Currency")</f>
@@ -20042,7 +20268,7 @@
       </c>
       <c r="I67" s="6" cm="1">
         <f t="array" aca="1" ref="I67" ca="1">_FV(B67,"Beta")</f>
-        <v>1.5986</v>
+        <v>1.6242000000000001</v>
       </c>
       <c r="J67" s="3" cm="1">
         <f t="array" aca="1" ref="J67" ca="1">_FV(B67,"52 week high",TRUE)</f>
@@ -20070,7 +20296,7 @@
       </c>
       <c r="P67" s="7" cm="1">
         <f t="array" aca="1" ref="P67" ca="1">_FV(B67,"Volume")</f>
-        <v>24134590</v>
+        <v>24189155</v>
       </c>
       <c r="Q67" s="7" cm="1">
         <f t="array" aca="1" ref="Q67" ca="1">_FV(B67,"Volume average",TRUE)</f>
@@ -20106,7 +20332,7 @@
       </c>
       <c r="C68" s="2">
         <f t="array" aca="1" ref="C68" ca="1">_FV(B68,"Last trade time",TRUE)</f>
-        <v>46178.843999258592</v>
+        <v>46178.916445555471</v>
       </c>
       <c r="D68" t="str">
         <f t="array" aca="1" ref="D68" ca="1">_FV(B68,"Currency")</f>
@@ -20126,11 +20352,11 @@
       </c>
       <c r="H68" s="6">
         <f t="array" aca="1" ref="H68" ca="1">_FV(B68,"P/E",TRUE)</f>
-        <v>19.7346</v>
+        <v>20.026399999999999</v>
       </c>
       <c r="I68" s="6">
         <f t="array" aca="1" ref="I68" ca="1">_FV(B68,"Beta")</f>
-        <v>0.64910000000000001</v>
+        <v>0.64410000000000001</v>
       </c>
       <c r="J68" s="3">
         <f t="array" aca="1" ref="J68" ca="1">_FV(B68,"52 week high",TRUE)</f>
@@ -20158,7 +20384,7 @@
       </c>
       <c r="P68" s="7">
         <f t="array" aca="1" ref="P68" ca="1">_FV(B68,"Volume")</f>
-        <v>589306</v>
+        <v>589331</v>
       </c>
       <c r="Q68" s="7">
         <f t="array" aca="1" ref="Q68" ca="1">_FV(B68,"Volume average",TRUE)</f>
@@ -20194,7 +20420,7 @@
       </c>
       <c r="C69" s="2" cm="1">
         <f t="array" aca="1" ref="C69" ca="1">_FV(B69,"Last trade time",TRUE)</f>
-        <v>46178.903533599216</v>
+        <v>46178.999995671096</v>
       </c>
       <c r="D69" t="str" cm="1">
         <f t="array" aca="1" ref="D69" ca="1">_FV(B69,"Currency")</f>
@@ -20246,7 +20472,7 @@
       </c>
       <c r="P69" s="7" cm="1">
         <f t="array" aca="1" ref="P69" ca="1">_FV(B69,"Volume")</f>
-        <v>98922418</v>
+        <v>99606571</v>
       </c>
       <c r="Q69" s="7" cm="1">
         <f t="array" aca="1" ref="Q69" ca="1">_FV(B69,"Volume average",TRUE)</f>
@@ -20282,7 +20508,7 @@
       </c>
       <c r="C70" s="2" cm="1">
         <f t="array" aca="1" ref="C70" ca="1">_FV(B70,"Last trade time",TRUE)</f>
-        <v>46178.899622407029</v>
+        <v>46178.997122060158</v>
       </c>
       <c r="D70" t="str" cm="1">
         <f t="array" aca="1" ref="D70" ca="1">_FV(B70,"Currency")</f>
@@ -20290,15 +20516,15 @@
       </c>
       <c r="E70" s="3" cm="1">
         <f t="array" aca="1" ref="E70" ca="1">_FV(B70,"Price")</f>
-        <v>446.68</v>
+        <v>446.71</v>
       </c>
       <c r="F70" s="4" cm="1">
         <f t="array" aca="1" ref="F70" ca="1">_FV(B70,"Change (%)",TRUE)</f>
-        <v>-3.3661999999999997E-2</v>
+        <v>-3.3597000000000002E-2</v>
       </c>
       <c r="G70" s="5" cm="1">
         <f t="array" aca="1" ref="G70" ca="1">_FV(B70,"Change")</f>
-        <v>-15.56</v>
+        <v>-15.53</v>
       </c>
       <c r="H70" s="6" cm="1">
         <f t="array" aca="1" ref="H70" ca="1">_FV(B70,"P/E",TRUE)</f>
@@ -20306,7 +20532,7 @@
       </c>
       <c r="I70" s="6" cm="1">
         <f t="array" aca="1" ref="I70" ca="1">_FV(B70,"Beta")</f>
-        <v>1.5580000000000001</v>
+        <v>1.5501</v>
       </c>
       <c r="J70" s="3" cm="1">
         <f t="array" aca="1" ref="J70" ca="1">_FV(B70,"52 week high",TRUE)</f>
@@ -20334,7 +20560,7 @@
       </c>
       <c r="P70" s="7" cm="1">
         <f t="array" aca="1" ref="P70" ca="1">_FV(B70,"Volume")</f>
-        <v>843971</v>
+        <v>844023</v>
       </c>
       <c r="Q70" s="7" cm="1">
         <f t="array" aca="1" ref="Q70" ca="1">_FV(B70,"Volume average",TRUE)</f>
@@ -20354,7 +20580,7 @@
       </c>
       <c r="U70" s="7" cm="1">
         <f t="array" aca="1" ref="U70" ca="1">_FV(B70,"Market cap",TRUE)</f>
-        <v>49703825652</v>
+        <v>49707163869</v>
       </c>
       <c r="V70" s="7" cm="1">
         <f t="array" aca="1" ref="V70" ca="1">_FV(B70,"Shares outstanding",TRUE)</f>
@@ -20370,7 +20596,7 @@
       </c>
       <c r="C71" s="2" cm="1">
         <f t="array" aca="1" ref="C71" ca="1">_FV(B71,"Last trade time",TRUE)</f>
-        <v>46178.902245450779</v>
+        <v>46178.999583865625</v>
       </c>
       <c r="D71" t="str" cm="1">
         <f t="array" aca="1" ref="D71" ca="1">_FV(B71,"Currency")</f>
@@ -20394,7 +20620,7 @@
       </c>
       <c r="I71" s="6" cm="1">
         <f t="array" aca="1" ref="I71" ca="1">_FV(B71,"Beta")</f>
-        <v>0.99790000000000001</v>
+        <v>1.0123</v>
       </c>
       <c r="J71" s="3" cm="1">
         <f t="array" aca="1" ref="J71" ca="1">_FV(B71,"52 week high",TRUE)</f>
@@ -20422,7 +20648,7 @@
       </c>
       <c r="P71" s="7" cm="1">
         <f t="array" aca="1" ref="P71" ca="1">_FV(B71,"Volume")</f>
-        <v>26796035</v>
+        <v>26943925</v>
       </c>
       <c r="Q71" s="7" cm="1">
         <f t="array" aca="1" ref="Q71" ca="1">_FV(B71,"Volume average",TRUE)</f>
@@ -20458,7 +20684,7 @@
       </c>
       <c r="C72" s="2" cm="1">
         <f t="array" aca="1" ref="C72" ca="1">_FV(B72,"Last trade time",TRUE)</f>
-        <v>46178.900013390623</v>
+        <v>46178.999621689065</v>
       </c>
       <c r="D72" t="str" cm="1">
         <f t="array" aca="1" ref="D72" ca="1">_FV(B72,"Currency")</f>
@@ -20466,23 +20692,23 @@
       </c>
       <c r="E72" s="3" cm="1">
         <f t="array" aca="1" ref="E72" ca="1">_FV(B72,"Price")</f>
-        <v>15.96</v>
+        <v>15.95</v>
       </c>
       <c r="F72" s="4" cm="1">
         <f t="array" aca="1" ref="F72" ca="1">_FV(B72,"Change (%)",TRUE)</f>
-        <v>-3.4483E-2</v>
+        <v>-3.5088000000000001E-2</v>
       </c>
       <c r="G72" s="5" cm="1">
         <f t="array" aca="1" ref="G72" ca="1">_FV(B72,"Change")</f>
-        <v>-0.56999999999999995</v>
-      </c>
-      <c r="H72" s="6" cm="1">
-        <f t="array" aca="1" ref="H72" ca="1">_FV(B72,"P/E",TRUE)</f>
-        <v>0</v>
+        <v>-0.57999999999999996</v>
+      </c>
+      <c r="H72" s="6" t="e" cm="1" vm="13">
+        <f t="array" ref="H72">_FV(B72,"P/E",TRUE)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="I72" s="6" cm="1">
         <f t="array" aca="1" ref="I72" ca="1">_FV(B72,"Beta")</f>
-        <v>0.83179999999999998</v>
+        <v>0.83299999999999996</v>
       </c>
       <c r="J72" s="3" cm="1">
         <f t="array" aca="1" ref="J72" ca="1">_FV(B72,"52 week high",TRUE)</f>
@@ -20510,7 +20736,7 @@
       </c>
       <c r="P72" s="7" cm="1">
         <f t="array" aca="1" ref="P72" ca="1">_FV(B72,"Volume")</f>
-        <v>7571048</v>
+        <v>7589492</v>
       </c>
       <c r="Q72" s="7" cm="1">
         <f t="array" aca="1" ref="Q72" ca="1">_FV(B72,"Volume average",TRUE)</f>
@@ -20530,7 +20756,7 @@
       </c>
       <c r="U72" s="7" cm="1">
         <f t="array" aca="1" ref="U72" ca="1">_FV(B72,"Market cap",TRUE)</f>
-        <v>5471147052</v>
+        <v>5467719015</v>
       </c>
       <c r="V72" s="7" cm="1">
         <f t="array" aca="1" ref="V72" ca="1">_FV(B72,"Shares outstanding",TRUE)</f>
@@ -20570,7 +20796,7 @@
       </c>
       <c r="I73" s="6" cm="1">
         <f t="array" aca="1" ref="I73" ca="1">_FV(B73,"Beta")</f>
-        <v>1.0986</v>
+        <v>1.1012</v>
       </c>
       <c r="J73" s="3" cm="1">
         <f t="array" aca="1" ref="J73" ca="1">_FV(B73,"52 week high",TRUE)</f>
@@ -20634,7 +20860,7 @@
       </c>
       <c r="C74" s="2">
         <f t="array" aca="1" ref="C74" ca="1">_FV(B74,"Last trade time",TRUE)</f>
-        <v>46178.899415474218</v>
+        <v>46178.997039478905</v>
       </c>
       <c r="D74" t="str">
         <f t="array" aca="1" ref="D74" ca="1">_FV(B74,"Currency")</f>
@@ -20642,23 +20868,23 @@
       </c>
       <c r="E74" s="3">
         <f t="array" aca="1" ref="E74" ca="1">_FV(B74,"Price")</f>
-        <v>88.81</v>
+        <v>88.84</v>
       </c>
       <c r="F74" s="4">
         <f t="array" aca="1" ref="F74" ca="1">_FV(B74,"Change (%)",TRUE)</f>
-        <v>9.2049999999999996E-3</v>
+        <v>9.5449999999999997E-3</v>
       </c>
       <c r="G74" s="5">
         <f t="array" aca="1" ref="G74" ca="1">_FV(B74,"Change")</f>
-        <v>0.81</v>
+        <v>0.84</v>
       </c>
       <c r="H74" s="6">
         <f t="array" aca="1" ref="H74" ca="1">_FV(B74,"P/E",TRUE)</f>
-        <v>17.450700000000001</v>
+        <v>17.6172</v>
       </c>
       <c r="I74" s="6">
         <f t="array" aca="1" ref="I74" ca="1">_FV(B74,"Beta")</f>
-        <v>0.77229999999999999</v>
+        <v>0.76190000000000002</v>
       </c>
       <c r="J74" s="3">
         <f t="array" aca="1" ref="J74" ca="1">_FV(B74,"52 week high",TRUE)</f>
@@ -20686,7 +20912,7 @@
       </c>
       <c r="P74" s="7">
         <f t="array" aca="1" ref="P74" ca="1">_FV(B74,"Volume")</f>
-        <v>9211116</v>
+        <v>9213892</v>
       </c>
       <c r="Q74" s="7">
         <f t="array" aca="1" ref="Q74" ca="1">_FV(B74,"Volume average",TRUE)</f>
@@ -20706,7 +20932,7 @@
       </c>
       <c r="U74" s="7">
         <f t="array" aca="1" ref="U74" ca="1">_FV(B74,"Market cap",TRUE)</f>
-        <v>154452579350</v>
+        <v>154504753400</v>
       </c>
       <c r="V74" s="7">
         <f t="array" aca="1" ref="V74" ca="1">_FV(B74,"Shares outstanding",TRUE)</f>
@@ -20746,7 +20972,7 @@
       </c>
       <c r="I75" s="6">
         <f t="array" aca="1" ref="I75" ca="1">_FV(B75,"Beta")</f>
-        <v>0.3473</v>
+        <v>0.35010000000000002</v>
       </c>
       <c r="J75" s="9">
         <f t="array" aca="1" ref="J75" ca="1">_FV(B75,"52 week high",TRUE)</f>
@@ -20810,7 +21036,7 @@
       </c>
       <c r="C76" s="2">
         <f t="array" aca="1" ref="C76" ca="1">_FV(B76,"Last trade time",TRUE)</f>
-        <v>46178.895729560158</v>
+        <v>46178.994646573439</v>
       </c>
       <c r="D76" t="str">
         <f t="array" aca="1" ref="D76" ca="1">_FV(B76,"Currency")</f>
@@ -20834,7 +21060,7 @@
       </c>
       <c r="I76" s="6">
         <f t="array" aca="1" ref="I76" ca="1">_FV(B76,"Beta")</f>
-        <v>3.3264</v>
+        <v>3.3321999999999998</v>
       </c>
       <c r="J76" s="3">
         <f t="array" aca="1" ref="J76" ca="1">_FV(B76,"52 week high",TRUE)</f>
@@ -20862,7 +21088,7 @@
       </c>
       <c r="P76" s="7">
         <f t="array" aca="1" ref="P76" ca="1">_FV(B76,"Volume")</f>
-        <v>1097087</v>
+        <v>1097538</v>
       </c>
       <c r="Q76" s="7">
         <f t="array" aca="1" ref="Q76" ca="1">_FV(B76,"Volume average",TRUE)</f>
@@ -20898,7 +21124,7 @@
       </c>
       <c r="C77" s="2">
         <f t="array" aca="1" ref="C77" ca="1">_FV(B77,"Last trade time",TRUE)</f>
-        <v>46178.90346310156</v>
+        <v>46178.999962187503</v>
       </c>
       <c r="D77" t="str">
         <f t="array" aca="1" ref="D77" ca="1">_FV(B77,"Currency")</f>
@@ -20922,7 +21148,7 @@
       </c>
       <c r="I77" s="6">
         <f t="array" aca="1" ref="I77" ca="1">_FV(B77,"Beta")</f>
-        <v>1.8715999999999999</v>
+        <v>1.8985000000000001</v>
       </c>
       <c r="J77" s="3">
         <f t="array" aca="1" ref="J77" ca="1">_FV(B77,"52 week high",TRUE)</f>
@@ -20950,7 +21176,7 @@
       </c>
       <c r="P77" s="7">
         <f t="array" aca="1" ref="P77" ca="1">_FV(B77,"Volume")</f>
-        <v>48999521</v>
+        <v>49259573</v>
       </c>
       <c r="Q77" s="7">
         <f t="array" aca="1" ref="Q77" ca="1">_FV(B77,"Volume average",TRUE)</f>
@@ -20986,7 +21212,7 @@
       </c>
       <c r="C78" s="2" cm="1">
         <f t="array" aca="1" ref="C78" ca="1">_FV(B78,"Last trade time",TRUE)</f>
-        <v>46178.903555450779</v>
+        <v>46178.999983529684</v>
       </c>
       <c r="D78" t="str" cm="1">
         <f t="array" aca="1" ref="D78" ca="1">_FV(B78,"Currency")</f>
@@ -21038,7 +21264,7 @@
       </c>
       <c r="P78" s="7" cm="1">
         <f t="array" aca="1" ref="P78" ca="1">_FV(B78,"Volume")</f>
-        <v>21985741</v>
+        <v>22038001</v>
       </c>
       <c r="Q78" s="7" cm="1">
         <f t="array" aca="1" ref="Q78" ca="1">_FV(B78,"Volume average",TRUE)</f>
@@ -21074,7 +21300,7 @@
       </c>
       <c r="C79" s="2" cm="1">
         <f t="array" aca="1" ref="C79" ca="1">_FV(B79,"Last trade time",TRUE)</f>
-        <v>46178.903532291406</v>
+        <v>46178.999920265625</v>
       </c>
       <c r="D79" t="str" cm="1">
         <f t="array" aca="1" ref="D79" ca="1">_FV(B79,"Currency")</f>
@@ -21082,23 +21308,23 @@
       </c>
       <c r="E79" s="3" cm="1">
         <f t="array" aca="1" ref="E79" ca="1">_FV(B79,"Price")</f>
-        <v>10.494999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="F79" s="4" cm="1">
         <f t="array" aca="1" ref="F79" ca="1">_FV(B79,"Change (%)",TRUE)</f>
-        <v>-0.125417</v>
+        <v>-0.125</v>
       </c>
       <c r="G79" s="5" cm="1">
         <f t="array" aca="1" ref="G79" ca="1">_FV(B79,"Change")</f>
-        <v>-1.5049999999999999</v>
-      </c>
-      <c r="H79" s="6" cm="1">
-        <f t="array" aca="1" ref="H79" ca="1">_FV(B79,"P/E",TRUE)</f>
-        <v>0</v>
+        <v>-1.5</v>
+      </c>
+      <c r="H79" s="6" t="e" cm="1" vm="13">
+        <f t="array" ref="H79">_FV(B79,"P/E",TRUE)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="I79" s="6" cm="1">
         <f t="array" aca="1" ref="I79" ca="1">_FV(B79,"Beta")</f>
-        <v>2.2237</v>
+        <v>2.2553000000000001</v>
       </c>
       <c r="J79" s="3" cm="1">
         <f t="array" aca="1" ref="J79" ca="1">_FV(B79,"52 week high",TRUE)</f>
@@ -21126,7 +21352,7 @@
       </c>
       <c r="P79" s="7" cm="1">
         <f t="array" aca="1" ref="P79" ca="1">_FV(B79,"Volume")</f>
-        <v>49643477</v>
+        <v>50039710</v>
       </c>
       <c r="Q79" s="7" cm="1">
         <f t="array" aca="1" ref="Q79" ca="1">_FV(B79,"Volume average",TRUE)</f>
@@ -21146,7 +21372,7 @@
       </c>
       <c r="U79" s="7" cm="1">
         <f t="array" aca="1" ref="U79" ca="1">_FV(B79,"Market cap",TRUE)</f>
-        <v>3835725193</v>
+        <v>3837552600</v>
       </c>
       <c r="V79" s="7" cm="1">
         <f t="array" aca="1" ref="V79" ca="1">_FV(B79,"Shares outstanding",TRUE)</f>
@@ -21162,7 +21388,7 @@
       </c>
       <c r="C80" s="2">
         <f t="array" aca="1" ref="C80" ca="1">_FV(B80,"Last trade time",TRUE)</f>
-        <v>46178.903556631252</v>
+        <v>46178.999999015628</v>
       </c>
       <c r="D80" t="str">
         <f t="array" aca="1" ref="D80" ca="1">_FV(B80,"Currency")</f>
@@ -21214,7 +21440,7 @@
       </c>
       <c r="P80" s="7">
         <f t="array" aca="1" ref="P80" ca="1">_FV(B80,"Volume")</f>
-        <v>13139609</v>
+        <v>13288987</v>
       </c>
       <c r="Q80" s="7">
         <f t="array" aca="1" ref="Q80" ca="1">_FV(B80,"Volume average",TRUE)</f>
@@ -21250,7 +21476,7 @@
       </c>
       <c r="C81" s="2" cm="1">
         <f t="array" aca="1" ref="C81" ca="1">_FV(B81,"Last trade time",TRUE)</f>
-        <v>46178.903320763282</v>
+        <v>46178.999972001562</v>
       </c>
       <c r="D81" t="str" cm="1">
         <f t="array" aca="1" ref="D81" ca="1">_FV(B81,"Currency")</f>
@@ -21258,23 +21484,23 @@
       </c>
       <c r="E81" s="3" cm="1">
         <f t="array" aca="1" ref="E81" ca="1">_FV(B81,"Price")</f>
-        <v>238.23</v>
+        <v>238.26</v>
       </c>
       <c r="F81" s="4" cm="1">
         <f t="array" aca="1" ref="F81" ca="1">_FV(B81,"Change (%)",TRUE)</f>
-        <v>-2.4367E-2</v>
+        <v>-2.4243999999999998E-2</v>
       </c>
       <c r="G81" s="5" cm="1">
         <f t="array" aca="1" ref="G81" ca="1">_FV(B81,"Change")</f>
-        <v>-5.95</v>
-      </c>
-      <c r="H81" s="6" cm="1">
-        <f t="array" aca="1" ref="H81" ca="1">_FV(B81,"P/E",TRUE)</f>
-        <v>0</v>
+        <v>-5.92</v>
+      </c>
+      <c r="H81" s="6" t="e" cm="1" vm="13">
+        <f t="array" ref="H81">_FV(B81,"P/E",TRUE)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="I81" s="6" cm="1">
         <f t="array" aca="1" ref="I81" ca="1">_FV(B81,"Beta")</f>
-        <v>1.3585</v>
+        <v>1.3641000000000001</v>
       </c>
       <c r="J81" s="3" cm="1">
         <f t="array" aca="1" ref="J81" ca="1">_FV(B81,"52 week high",TRUE)</f>
@@ -21302,7 +21528,7 @@
       </c>
       <c r="P81" s="7" cm="1">
         <f t="array" aca="1" ref="P81" ca="1">_FV(B81,"Volume")</f>
-        <v>7148731</v>
+        <v>7162806</v>
       </c>
       <c r="Q81" s="7" cm="1">
         <f t="array" aca="1" ref="Q81" ca="1">_FV(B81,"Volume average",TRUE)</f>
@@ -21338,7 +21564,7 @@
       </c>
       <c r="C82" s="2" cm="1">
         <f t="array" aca="1" ref="C82" ca="1">_FV(B82,"Last trade time",TRUE)</f>
-        <v>46178.902526296093</v>
+        <v>46178.999514108596</v>
       </c>
       <c r="D82" t="str" cm="1">
         <f t="array" aca="1" ref="D82" ca="1">_FV(B82,"Currency")</f>
@@ -21358,11 +21584,11 @@
       </c>
       <c r="H82" s="6" cm="1">
         <f t="array" aca="1" ref="H82" ca="1">_FV(B82,"P/E",TRUE)</f>
-        <v>114.598</v>
+        <v>107.7313</v>
       </c>
       <c r="I82" s="6" cm="1">
         <f t="array" aca="1" ref="I82" ca="1">_FV(B82,"Beta")</f>
-        <v>1.2104999999999999</v>
+        <v>1.2114</v>
       </c>
       <c r="J82" s="3" cm="1">
         <f t="array" aca="1" ref="J82" ca="1">_FV(B82,"52 week high",TRUE)</f>
@@ -21390,7 +21616,7 @@
       </c>
       <c r="P82" s="7" cm="1">
         <f t="array" aca="1" ref="P82" ca="1">_FV(B82,"Volume")</f>
-        <v>1837962</v>
+        <v>1839401</v>
       </c>
       <c r="Q82" s="7" cm="1">
         <f t="array" aca="1" ref="Q82" ca="1">_FV(B82,"Volume average",TRUE)</f>
@@ -21426,7 +21652,7 @@
       </c>
       <c r="C83" s="2">
         <f t="array" aca="1" ref="C83" ca="1">_FV(B83,"Last trade time",TRUE)</f>
-        <v>46178.903227464842</v>
+        <v>46178.999919166403</v>
       </c>
       <c r="D83" t="str">
         <f t="array" aca="1" ref="D83" ca="1">_FV(B83,"Currency")</f>
@@ -21450,7 +21676,7 @@
       </c>
       <c r="I83" s="6">
         <f t="array" aca="1" ref="I83" ca="1">_FV(B83,"Beta")</f>
-        <v>2.7570999999999999</v>
+        <v>2.8</v>
       </c>
       <c r="J83" s="3">
         <f t="array" aca="1" ref="J83" ca="1">_FV(B83,"52 week high",TRUE)</f>
@@ -21478,7 +21704,7 @@
       </c>
       <c r="P83" s="7">
         <f t="array" aca="1" ref="P83" ca="1">_FV(B83,"Volume")</f>
-        <v>31706696</v>
+        <v>31875812</v>
       </c>
       <c r="Q83" s="7">
         <f t="array" aca="1" ref="Q83" ca="1">_FV(B83,"Volume average",TRUE)</f>
@@ -21514,7 +21740,7 @@
       </c>
       <c r="C84" s="2" cm="1">
         <f t="array" aca="1" ref="C84" ca="1">_FV(B84,"Last trade time",TRUE)</f>
-        <v>46178.903428171092</v>
+        <v>46178.999932997656</v>
       </c>
       <c r="D84" t="str" cm="1">
         <f t="array" aca="1" ref="D84" ca="1">_FV(B84,"Currency")</f>
@@ -21566,7 +21792,7 @@
       </c>
       <c r="P84" s="7" cm="1">
         <f t="array" aca="1" ref="P84" ca="1">_FV(B84,"Volume")</f>
-        <v>22286805</v>
+        <v>22377273</v>
       </c>
       <c r="Q84" s="7" cm="1">
         <f t="array" aca="1" ref="Q84" ca="1">_FV(B84,"Volume average",TRUE)</f>
@@ -21602,7 +21828,7 @@
       </c>
       <c r="C85" s="2" cm="1">
         <f t="array" aca="1" ref="C85" ca="1">_FV(B85,"Last trade time",TRUE)</f>
-        <v>46178.903564582812</v>
+        <v>46178.999997407031</v>
       </c>
       <c r="D85" t="str" cm="1">
         <f t="array" aca="1" ref="D85" ca="1">_FV(B85,"Currency")</f>
@@ -21610,15 +21836,15 @@
       </c>
       <c r="E85" s="3" cm="1">
         <f t="array" aca="1" ref="E85" ca="1">_FV(B85,"Price")</f>
-        <v>737.41</v>
+        <v>737.55</v>
       </c>
       <c r="F85" s="4" cm="1">
         <f t="array" aca="1" ref="F85" ca="1">_FV(B85,"Change (%)",TRUE)</f>
-        <v>-2.5994000000000003E-2</v>
+        <v>-2.5809000000000002E-2</v>
       </c>
       <c r="G85" s="5" cm="1">
         <f t="array" aca="1" ref="G85" ca="1">_FV(B85,"Change")</f>
-        <v>-19.68</v>
+        <v>-19.54</v>
       </c>
       <c r="H85" s="6" t="e" vm="13">
         <f t="array" ref="H85">_FV(B85,"P/E",TRUE)</f>
@@ -21654,7 +21880,7 @@
       </c>
       <c r="P85" s="7" cm="1">
         <f t="array" aca="1" ref="P85" ca="1">_FV(B85,"Volume")</f>
-        <v>92040132</v>
+        <v>93989416</v>
       </c>
       <c r="Q85" s="7" cm="1">
         <f t="array" aca="1" ref="Q85" ca="1">_FV(B85,"Volume average",TRUE)</f>
@@ -21690,7 +21916,7 @@
       </c>
       <c r="C86" s="2">
         <f t="array" aca="1" ref="C86" ca="1">_FV(B86,"Last trade time",TRUE)</f>
-        <v>46178.900726203123</v>
+        <v>46178.999581770309</v>
       </c>
       <c r="D86" t="str">
         <f t="array" aca="1" ref="D86" ca="1">_FV(B86,"Currency")</f>
@@ -21714,7 +21940,7 @@
       </c>
       <c r="I86" s="6">
         <f t="array" aca="1" ref="I86" ca="1">_FV(B86,"Beta")</f>
-        <v>1.4782</v>
+        <v>1.4797</v>
       </c>
       <c r="J86" s="3">
         <f t="array" aca="1" ref="J86" ca="1">_FV(B86,"52 week high",TRUE)</f>
@@ -21742,7 +21968,7 @@
       </c>
       <c r="P86" s="7">
         <f t="array" aca="1" ref="P86" ca="1">_FV(B86,"Volume")</f>
-        <v>7168503</v>
+        <v>7170155</v>
       </c>
       <c r="Q86" s="7">
         <f t="array" aca="1" ref="Q86" ca="1">_FV(B86,"Volume average",TRUE)</f>
@@ -21778,7 +22004,7 @@
       </c>
       <c r="C87" s="2" cm="1">
         <f t="array" aca="1" ref="C87" ca="1">_FV(B87,"Last trade time",TRUE)</f>
-        <v>46178.903448541409</v>
+        <v>46178.999755971876</v>
       </c>
       <c r="D87" t="str" cm="1">
         <f t="array" aca="1" ref="D87" ca="1">_FV(B87,"Currency")</f>
@@ -21802,7 +22028,7 @@
       </c>
       <c r="I87" s="6" cm="1">
         <f t="array" aca="1" ref="I87" ca="1">_FV(B87,"Beta")</f>
-        <v>1.9272</v>
+        <v>1.9351</v>
       </c>
       <c r="J87" s="3" cm="1">
         <f t="array" aca="1" ref="J87" ca="1">_FV(B87,"52 week high",TRUE)</f>
@@ -21830,7 +22056,7 @@
       </c>
       <c r="P87" s="7" cm="1">
         <f t="array" aca="1" ref="P87" ca="1">_FV(B87,"Volume")</f>
-        <v>2842944</v>
+        <v>2850144</v>
       </c>
       <c r="Q87" s="7" cm="1">
         <f t="array" aca="1" ref="Q87" ca="1">_FV(B87,"Volume average",TRUE)</f>
@@ -21866,7 +22092,7 @@
       </c>
       <c r="C88" s="2">
         <f t="array" aca="1" ref="C88" ca="1">_FV(B88,"Last trade time",TRUE)</f>
-        <v>46178.903331365625</v>
+        <v>46178.999955810155</v>
       </c>
       <c r="D88" t="str">
         <f t="array" aca="1" ref="D88" ca="1">_FV(B88,"Currency")</f>
@@ -21918,7 +22144,7 @@
       </c>
       <c r="P88" s="7">
         <f t="array" aca="1" ref="P88" ca="1">_FV(B88,"Volume")</f>
-        <v>8819522</v>
+        <v>8873465</v>
       </c>
       <c r="Q88" s="7">
         <f t="array" aca="1" ref="Q88" ca="1">_FV(B88,"Volume average",TRUE)</f>
@@ -21954,7 +22180,7 @@
       </c>
       <c r="C89" s="2" cm="1">
         <f t="array" aca="1" ref="C89" ca="1">_FV(B89,"Last trade time",TRUE)</f>
-        <v>46178.90289351852</v>
+        <v>46178.999655485939</v>
       </c>
       <c r="D89" t="str" cm="1">
         <f t="array" aca="1" ref="D89" ca="1">_FV(B89,"Currency")</f>
@@ -21978,7 +22204,7 @@
       </c>
       <c r="I89" s="6" cm="1">
         <f t="array" aca="1" ref="I89" ca="1">_FV(B89,"Beta")</f>
-        <v>1.7878000000000001</v>
+        <v>1.7955000000000001</v>
       </c>
       <c r="J89" s="3" cm="1">
         <f t="array" aca="1" ref="J89" ca="1">_FV(B89,"52 week high",TRUE)</f>
@@ -22006,7 +22232,7 @@
       </c>
       <c r="P89" s="7" cm="1">
         <f t="array" aca="1" ref="P89" ca="1">_FV(B89,"Volume")</f>
-        <v>5466474</v>
+        <v>5471125</v>
       </c>
       <c r="Q89" s="7" cm="1">
         <f t="array" aca="1" ref="Q89" ca="1">_FV(B89,"Volume average",TRUE)</f>
@@ -22042,7 +22268,7 @@
       </c>
       <c r="C90" s="2">
         <f t="array" aca="1" ref="C90" ca="1">_FV(B90,"Last trade time",TRUE)</f>
-        <v>46178.90356746484</v>
+        <v>46178.999997360937</v>
       </c>
       <c r="D90" t="str">
         <f t="array" aca="1" ref="D90" ca="1">_FV(B90,"Currency")</f>
@@ -22062,11 +22288,11 @@
       </c>
       <c r="H90" s="6">
         <f t="array" aca="1" ref="H90" ca="1">_FV(B90,"P/E",TRUE)</f>
-        <v>382.47449999999998</v>
+        <v>357.37139999999999</v>
       </c>
       <c r="I90" s="6">
         <f t="array" aca="1" ref="I90" ca="1">_FV(B90,"Beta")</f>
-        <v>1.802</v>
+        <v>1.8163</v>
       </c>
       <c r="J90" s="3">
         <f t="array" aca="1" ref="J90" ca="1">_FV(B90,"52 week high",TRUE)</f>
@@ -22094,7 +22320,7 @@
       </c>
       <c r="P90" s="7">
         <f t="array" aca="1" ref="P90" ca="1">_FV(B90,"Volume")</f>
-        <v>63032456</v>
+        <v>63420177</v>
       </c>
       <c r="Q90" s="7">
         <f t="array" aca="1" ref="Q90" ca="1">_FV(B90,"Volume average",TRUE)</f>
@@ -22130,7 +22356,7 @@
       </c>
       <c r="C91" s="2">
         <f t="array" aca="1" ref="C91" ca="1">_FV(B91,"Last trade time",TRUE)</f>
-        <v>46178.90356491875</v>
+        <v>46178.999977060157</v>
       </c>
       <c r="D91" t="str">
         <f t="array" aca="1" ref="D91" ca="1">_FV(B91,"Currency")</f>
@@ -22138,23 +22364,23 @@
       </c>
       <c r="E91" s="3">
         <f t="array" aca="1" ref="E91" ca="1">_FV(B91,"Price")</f>
-        <v>415.2</v>
+        <v>415.17</v>
       </c>
       <c r="F91" s="4">
         <f t="array" aca="1" ref="F91" ca="1">_FV(B91,"Change (%)",TRUE)</f>
-        <v>-6.6798999999999997E-2</v>
+        <v>-6.6866000000000009E-2</v>
       </c>
       <c r="G91" s="5">
         <f t="array" aca="1" ref="G91" ca="1">_FV(B91,"Change")</f>
-        <v>-29.72</v>
+        <v>-29.75</v>
       </c>
       <c r="H91" s="6">
         <f t="array" aca="1" ref="H91" ca="1">_FV(B91,"P/E",TRUE)</f>
-        <v>37.644300000000001</v>
+        <v>35.127000000000002</v>
       </c>
       <c r="I91" s="6">
         <f t="array" aca="1" ref="I91" ca="1">_FV(B91,"Beta")</f>
-        <v>1.2762</v>
+        <v>1.2768999999999999</v>
       </c>
       <c r="J91" s="3">
         <f t="array" aca="1" ref="J91" ca="1">_FV(B91,"52 week high",TRUE)</f>
@@ -22182,7 +22408,7 @@
       </c>
       <c r="P91" s="7">
         <f t="array" aca="1" ref="P91" ca="1">_FV(B91,"Volume")</f>
-        <v>19467361</v>
+        <v>19644166</v>
       </c>
       <c r="Q91" s="7">
         <f t="array" aca="1" ref="Q91" ca="1">_FV(B91,"Volume average",TRUE)</f>
@@ -22218,7 +22444,7 @@
       </c>
       <c r="C92" s="2" cm="1">
         <f t="array" aca="1" ref="C92" ca="1">_FV(B92,"Last trade time",TRUE)</f>
-        <v>46178.898249791404</v>
+        <v>46178.99986462891</v>
       </c>
       <c r="D92" t="str" cm="1">
         <f t="array" aca="1" ref="D92" ca="1">_FV(B92,"Currency")</f>
@@ -22226,23 +22452,23 @@
       </c>
       <c r="E92" s="3" cm="1">
         <f t="array" aca="1" ref="E92" ca="1">_FV(B92,"Price")</f>
-        <v>226.12</v>
+        <v>225.99</v>
       </c>
       <c r="F92" s="4" cm="1">
         <f t="array" aca="1" ref="F92" ca="1">_FV(B92,"Change (%)",TRUE)</f>
-        <v>-4.4455999999999996E-2</v>
+        <v>-4.5004999999999996E-2</v>
       </c>
       <c r="G92" s="5" cm="1">
         <f t="array" aca="1" ref="G92" ca="1">_FV(B92,"Change")</f>
-        <v>-10.52</v>
+        <v>-10.65</v>
       </c>
       <c r="H92" s="6" cm="1">
         <f t="array" aca="1" ref="H92" ca="1">_FV(B92,"P/E",TRUE)</f>
-        <v>367.84750000000003</v>
+        <v>351.298</v>
       </c>
       <c r="I92" s="6" cm="1">
         <f t="array" aca="1" ref="I92" ca="1">_FV(B92,"Beta")</f>
-        <v>1.3594999999999999</v>
+        <v>1.3119000000000001</v>
       </c>
       <c r="J92" s="3" cm="1">
         <f t="array" aca="1" ref="J92" ca="1">_FV(B92,"52 week high",TRUE)</f>
@@ -22270,7 +22496,7 @@
       </c>
       <c r="P92" s="7" cm="1">
         <f t="array" aca="1" ref="P92" ca="1">_FV(B92,"Volume")</f>
-        <v>3384902</v>
+        <v>3389142</v>
       </c>
       <c r="Q92" s="7" cm="1">
         <f t="array" aca="1" ref="Q92" ca="1">_FV(B92,"Volume average",TRUE)</f>
@@ -22290,7 +22516,7 @@
       </c>
       <c r="U92" s="7" cm="1">
         <f t="array" aca="1" ref="U92" ca="1">_FV(B92,"Market cap",TRUE)</f>
-        <v>34319114268</v>
+        <v>34299383661</v>
       </c>
       <c r="V92" s="7" cm="1">
         <f t="array" aca="1" ref="V92" ca="1">_FV(B92,"Shares outstanding",TRUE)</f>
@@ -22306,7 +22532,7 @@
       </c>
       <c r="C93" s="2" cm="1">
         <f t="array" aca="1" ref="C93" ca="1">_FV(B93,"Last trade time",TRUE)</f>
-        <v>46178.903557638281</v>
+        <v>46178.999989050782</v>
       </c>
       <c r="D93" t="str" cm="1">
         <f t="array" aca="1" ref="D93" ca="1">_FV(B93,"Currency")</f>
@@ -22314,15 +22540,15 @@
       </c>
       <c r="E93" s="3" cm="1">
         <f t="array" aca="1" ref="E93" ca="1">_FV(B93,"Price")</f>
-        <v>300.44</v>
+        <v>300.51</v>
       </c>
       <c r="F93" s="4" cm="1">
         <f t="array" aca="1" ref="F93" ca="1">_FV(B93,"Change (%)",TRUE)</f>
-        <v>-7.248700000000001E-2</v>
+        <v>-7.2271000000000002E-2</v>
       </c>
       <c r="G93" s="5" cm="1">
         <f t="array" aca="1" ref="G93" ca="1">_FV(B93,"Change")</f>
-        <v>-23.48</v>
+        <v>-23.41</v>
       </c>
       <c r="H93" s="6" cm="1">
         <f t="array" aca="1" ref="H93" ca="1">_FV(B93,"P/E",TRUE)</f>
@@ -22330,7 +22556,7 @@
       </c>
       <c r="I93" s="6" cm="1">
         <f t="array" aca="1" ref="I93" ca="1">_FV(B93,"Beta")</f>
-        <v>2.0377000000000001</v>
+        <v>2.0459000000000001</v>
       </c>
       <c r="J93" s="3" cm="1">
         <f t="array" aca="1" ref="J93" ca="1">_FV(B93,"52 week high",TRUE)</f>
@@ -22358,7 +22584,7 @@
       </c>
       <c r="P93" s="7" cm="1">
         <f t="array" aca="1" ref="P93" ca="1">_FV(B93,"Volume")</f>
-        <v>7295984</v>
+        <v>7330005</v>
       </c>
       <c r="Q93" s="7" cm="1">
         <f t="array" aca="1" ref="Q93" ca="1">_FV(B93,"Volume average",TRUE)</f>
@@ -22378,7 +22604,7 @@
       </c>
       <c r="U93" s="7" cm="1">
         <f t="array" aca="1" ref="U93" ca="1">_FV(B93,"Market cap",TRUE)</f>
-        <v>115401647872</v>
+        <v>115428535488</v>
       </c>
       <c r="V93" s="7" cm="1">
         <f t="array" aca="1" ref="V93" ca="1">_FV(B93,"Shares outstanding",TRUE)</f>
@@ -22394,7 +22620,7 @@
       </c>
       <c r="C94" s="2" cm="1">
         <f t="array" aca="1" ref="C94" ca="1">_FV(B94,"Last trade time",TRUE)</f>
-        <v>46178.902455821095</v>
+        <v>46178.999292812499</v>
       </c>
       <c r="D94" t="str" cm="1">
         <f t="array" aca="1" ref="D94" ca="1">_FV(B94,"Currency")</f>
@@ -22418,7 +22644,7 @@
       </c>
       <c r="I94" s="6" cm="1">
         <f t="array" aca="1" ref="I94" ca="1">_FV(B94,"Beta")</f>
-        <v>1.0787</v>
+        <v>1.0722</v>
       </c>
       <c r="J94" s="3" cm="1">
         <f t="array" aca="1" ref="J94" ca="1">_FV(B94,"52 week high",TRUE)</f>
@@ -22446,7 +22672,7 @@
       </c>
       <c r="P94" s="7" cm="1">
         <f t="array" aca="1" ref="P94" ca="1">_FV(B94,"Volume")</f>
-        <v>4594660</v>
+        <v>4596224</v>
       </c>
       <c r="Q94" s="7" cm="1">
         <f t="array" aca="1" ref="Q94" ca="1">_FV(B94,"Volume average",TRUE)</f>
@@ -22482,7 +22708,7 @@
       </c>
       <c r="C95" s="2" cm="1">
         <f t="array" aca="1" ref="C95" ca="1">_FV(B95,"Last trade time",TRUE)</f>
-        <v>46178.903391226566</v>
+        <v>46178.999975450781</v>
       </c>
       <c r="D95" t="str" cm="1">
         <f t="array" aca="1" ref="D95" ca="1">_FV(B95,"Currency")</f>
@@ -22506,7 +22732,7 @@
       </c>
       <c r="I95" s="6" cm="1">
         <f t="array" aca="1" ref="I95" ca="1">_FV(B95,"Beta")</f>
-        <v>0.9647</v>
+        <v>0.97170000000000001</v>
       </c>
       <c r="J95" s="3" cm="1">
         <f t="array" aca="1" ref="J95" ca="1">_FV(B95,"52 week high",TRUE)</f>
@@ -22534,7 +22760,7 @@
       </c>
       <c r="P95" s="7" cm="1">
         <f t="array" aca="1" ref="P95" ca="1">_FV(B95,"Volume")</f>
-        <v>4598738</v>
+        <v>4617922</v>
       </c>
       <c r="Q95" s="7" cm="1">
         <f t="array" aca="1" ref="Q95" ca="1">_FV(B95,"Volume average",TRUE)</f>

--- a/dashboard/trading_system.xlsx
+++ b/dashboard/trading_system.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\husainnatha\tradingsystem\dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B7FFDED-677F-4CCC-84DE-E0AD7134E252}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98DECB54-7CA7-4FA0-B92D-0A5A579548F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3943,8 +3943,8 @@
     <v>233.67</v>
     <v>15.29</v>
     <v>3.6288</v>
-    <v>23.9</v>
-    <v>0.13502800000000001</v>
+    <v>19.350000000000001</v>
+    <v>0.109322</v>
     <v>USD</v>
     <v>Applied Optoelectronics, Inc. is a developer and manufacturer of advanced optical and hybrid fiber coaxial (HFC) networking products that are the building blocks for artificial intelligence (AI) datacenters, Cable TV Broadband (CATV) and broadband fiber access networks around the world. The Company supplies this critical infrastructure to tier-one customers across cloud computing, CATV broadband, telecom, and fiber-to-the-home (FTTH) markets. It designs and manufactures a range of optical communications products at varying levels of integration, from components, subassemblies and modules to complete turn-key equipment. In the CATV market, it supplies a broad array of products, including lasers, transmitters and transceivers, and turn-key equipment. It supplies optical transceivers that plug into switches and servers within the data center and allow these network devices to send and receive data over fiber optic cables. In the telecom market, it supplies lasers and laser subassemblies.</v>
     <v>4691</v>
@@ -3952,23 +3952,23 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>13139 Jess Pirtle Blvd, SUGAR LAND, TX, 77478 US</v>
-    <v>203</v>
+    <v>203.19990000000001</v>
     <v>Electronic Equipment &amp; Parts</v>
     <v>Stock</v>
-    <v>46181.758863853909</v>
+    <v>46181.825966017968</v>
     <v>0</v>
     <v>177.05</v>
-    <v>16120772493</v>
+    <v>15755667889</v>
     <v>APPLIED OPTOELECTRONICS, INC.</v>
     <v>APPLIED OPTOELECTRONICS, INC.</v>
     <v>183.57</v>
     <v>0</v>
     <v>177</v>
-    <v>200.9</v>
+    <v>196.35</v>
     <v>80242770</v>
     <v>AAOI</v>
     <v>APPLIED OPTOELECTRONICS, INC. (XNAS:AAOI)</v>
-    <v>11147888</v>
+    <v>13347907</v>
     <v>12662531</v>
     <v>2013</v>
   </rv>
@@ -3994,8 +3994,8 @@
     <v>317.39999999999998</v>
     <v>195.07</v>
     <v>1.0832999999999999</v>
-    <v>-2.3149999999999999</v>
-    <v>-7.5319999999999996E-3</v>
+    <v>-5.44</v>
+    <v>-1.77E-2</v>
     <v>USD</v>
     <v>Apple Inc. designs, manufactures and markets smartphones, personal computers, tablets, wearables and accessories, and sells a variety of related services. Its product categories include iPhone, Mac, iPad, Wearables, Home and Accessories. Its services include advertising, AppleCare, cloud services, digital content, and payment services. The Company operates various platforms, including the App Store, that allow customers to discover and download applications and digital content, such as books, music, video, games and podcasts. It also offers digital content through subscription-based services, including Apple Arcade, Apple Fitness+, Apple Music, Apple News+, and Apple TV+. Its wearables include smartwatches, wireless headphones, and spatial computers. Its products include iPhone 16 Pro, iPhone 16, iPhone 15, iPhone 14, iPhone SE, MacBook Air, MacBook Pro, iMac, Mac mini, Mac Studio, Mac Pro, iPad Pro, iPad Air, AirPods, AirPods Pro, AirPods Max, Apple TV, Apple Vision Pro and others.</v>
     <v>166000</v>
@@ -4006,20 +4006,20 @@
     <v>317.39999999999998</v>
     <v>Computers, Phones &amp; Household Electronics</v>
     <v>Stock</v>
-    <v>46181.758899710156</v>
+    <v>46181.825948032034</v>
     <v>3</v>
-    <v>303.70999999999998</v>
-    <v>4480011984000</v>
+    <v>301.74</v>
+    <v>4434113984000</v>
     <v>APPLE INC.</v>
     <v>APPLE INC.</v>
     <v>308.88</v>
-    <v>37.045499999999997</v>
+    <v>36.665900000000001</v>
     <v>307.33999999999997</v>
-    <v>305.02499999999998</v>
+    <v>301.89999999999998</v>
     <v>14687360000</v>
     <v>AAPL</v>
     <v>APPLE INC. (XNAS:AAPL)</v>
-    <v>43021555</v>
+    <v>60015935</v>
     <v>49427495</v>
     <v>1977</v>
   </rv>
@@ -4065,8 +4065,8 @@
     <v>419.82</v>
     <v>224.13</v>
     <v>1.395</v>
-    <v>-4.83</v>
-    <v>-1.9209E-2</v>
+    <v>-4.9800000000000004</v>
+    <v>-1.9806000000000001E-2</v>
     <v>USD</v>
     <v>Adobe Inc. is a global technology company. The Company's products, services and solutions are used around the world to imagine, create, manage, deliver, measure, optimize and engage with content across surfaces and fuel digital experiences. Its segments include Digital Media, Digital Experience, and Publishing and Advertising. The Digital Media segment is centered around Adobe Creative Cloud and Adobe Document Cloud, which include Adobe Express, Adobe Firefly, Photoshop and other products, offering a variety of tools for creative professionals, communicators and other consumers. The Digital Experience segment provides an integrated platform and set of products, services and solutions through Adobe Experience Cloud. The Publishing and Advertising segment contains legacy products and services. In addition, its Adobe GenStudio solution allows businesses to simplify their content supply chain process with generative artificial intelligence (AI) capabilities and intelligent automation.</v>
     <v>31360</v>
@@ -4078,20 +4078,20 @@
     <v>9</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46181.758875821091</v>
+    <v>46181.825974166408</v>
     <v>10</v>
     <v>244.25</v>
-    <v>99679762000</v>
+    <v>99619132000</v>
     <v>ADOBE INC.</v>
     <v>ADOBE INC.</v>
     <v>249.06</v>
-    <v>14.3735</v>
+    <v>14.364699999999999</v>
     <v>251.44</v>
-    <v>246.61</v>
+    <v>246.46</v>
     <v>404200000</v>
     <v>ADBE</v>
     <v>ADOBE INC. (XNAS:ADBE)</v>
-    <v>2572980</v>
+    <v>3258285</v>
     <v>4927250</v>
     <v>1997</v>
   </rv>
@@ -4117,8 +4117,8 @@
     <v>121.8</v>
     <v>10.887499999999999</v>
     <v>3.1621999999999999</v>
-    <v>-1.24</v>
-    <v>-1.2595E-2</v>
+    <v>-2.93</v>
+    <v>-2.9761000000000003E-2</v>
     <v>USD</v>
     <v>Aehr Test Systems, Inc. offers test solutions for testing, burning-in, and stabilizing semiconductor devices in wafer level, singulated die, and package part form. The Company's products include the FOX-P family of test and burn-in systems and FOX WaferPak Aligner, FOX WaferPak Contactor, FOX DiePak Carrier and FOX DiePak Loader. The FOX-XP and FOX-NP systems are full wafer contact and singulated die/module test and burn-in systems that can test, burn-in and stabilize a range of devices such as silicon carbide-based and other power semiconductors, 2D and 3D sensors used in phones, tablets, and other computing devices, memory semiconductors, processors, microcontrollers, systems-on-a-chip, and photonics and integrated optical devices used in AI. FOX-CP system is a single-wafer compact test solution for logic, memory and photonic devices. FOX WaferPak Contactor contains a full wafer contactor capable of testing wafers up to 300 millimeters that enables integrated circuit manufacturers.</v>
     <v>136</v>
@@ -4129,20 +4129,20 @@
     <v>105</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46181.758891863283</v>
+    <v>46181.825937303125</v>
     <v>13</v>
-    <v>94.868300000000005</v>
-    <v>3057570432</v>
+    <v>93.65</v>
+    <v>3004414440</v>
     <v>AEHR TEST SYSTEMS</v>
     <v>AEHR TEST SYSTEMS</v>
     <v>105</v>
     <v>0</v>
     <v>98.45</v>
-    <v>97.21</v>
+    <v>95.52</v>
     <v>31453250</v>
     <v>AEHR</v>
     <v>AEHR TEST SYSTEMS (XNAS:AEHR)</v>
-    <v>1262529</v>
+    <v>1520191</v>
     <v>2521127</v>
     <v>1977</v>
   </rv>
@@ -4176,7 +4176,7 @@
     <v>11.74</v>
     <v>Banking Services</v>
     <v>Stock</v>
-    <v>46181.750029096875</v>
+    <v>46181.815370207813</v>
     <v>11.67</v>
     <v>563439579</v>
     <v>ATRIUM MORTGAGE INVESTMENT CORPORATION</v>
@@ -4188,7 +4188,7 @@
     <v>48239690</v>
     <v>AI</v>
     <v>ATRIUM MORTGAGE INVESTMENT CORPORATION (NEOE:AI)</v>
-    <v>3500</v>
+    <v>9800</v>
     <v>124400</v>
     <v>2001</v>
   </rv>
@@ -4210,8 +4210,8 @@
     <v>372.37</v>
     <v>84.78</v>
     <v>2.64</v>
-    <v>33.835000000000001</v>
-    <v>0.106715</v>
+    <v>28.2775</v>
+    <v>8.9186999999999989E-2</v>
     <v>USD</v>
     <v>Astera Labs, Inc. is a global semiconductor company. The Company provides semiconductor-based connectivity solutions for cloud and artificial intelligence (AI) infrastructure. It has developed and deployed its Intelligent Connectivity Platform built from the ground up for cloud and AI infrastructure. Its Intelligent Connectivity Platform provides its customers with the ability to deploy and operate high-performance cloud and AI infrastructure at scale, addressing an increasingly diverse set of requirements. It provides its connectivity products in various form factors, including Integrated Circuits (ICs), boards, and modules. Its PCIe, CXL and Ethernet semiconductor-based connectivity solutions are purpose-built to unleash the potential of accelerated computing at cloud-scale. The Company’s products include Aries products, which include its COSMOS software suite; Taurus products, which are hardware modules based on its Taurus ICs; Leo products; and Scorpio products.</v>
     <v>756</v>
@@ -4222,19 +4222,19 @@
     <v>353.78980000000001</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46181.758867128905</v>
+    <v>46181.825956712499</v>
     <v>328.01</v>
-    <v>60146175070</v>
+    <v>59193575666</v>
     <v>ASTERA LABS, INC.</v>
     <v>ASTERA LABS, INC.</v>
     <v>330.5</v>
-    <v>236.5478</v>
+    <v>232.8013</v>
     <v>317.06</v>
-    <v>350.89499999999998</v>
+    <v>345.33749999999998</v>
     <v>171407900</v>
     <v>ALAB</v>
     <v>ASTERA LABS, INC. (XNAS:ALAB)</v>
-    <v>3064381</v>
+    <v>3681695</v>
     <v>6231624</v>
     <v>2017</v>
   </rv>
@@ -4260,8 +4260,8 @@
     <v>96.69</v>
     <v>48.3</v>
     <v>2.1604000000000001</v>
-    <v>5.2798999999999996</v>
-    <v>8.3122000000000001E-2</v>
+    <v>5.4260000000000002</v>
+    <v>8.5421999999999998E-2</v>
     <v>USD</v>
     <v>Ambarella, Inc. is a developer of low-power system-on-a-chip (SoC) semiconductors and software for edge artificial intelligence (AI) applications. The Company's technologies make electronic systems smarter, enabling them to become partially or fully autonomous with features, such as person detection, object classification, and analytics, in addition to performing complex data analysis in real time, delivering imagery, and preserving vital system resources, such as power and network bandwidth. It specializes in the development of deployable, scalable designs for intelligent electronic systems that utilize high-bandwidth sensors. Its products are used in a variety of human viewing, computer vision and edge AI applications, including a variety of automotive camera systems, video security cameras, mobile and fixed robots, industrial applications, and consumer devices, such as action, drone, and 360-degree cameras.</v>
     <v>959</v>
@@ -4269,23 +4269,23 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>3101 Jay Street, CA, 95054 US</v>
-    <v>68.927199999999999</v>
+    <v>69.5</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46181.758867916404</v>
+    <v>46181.825866967185</v>
     <v>20</v>
     <v>64.67</v>
-    <v>3018126397</v>
+    <v>3024535538</v>
     <v>AMBARELLA, INC.</v>
     <v>AMBARELLA, INC.</v>
     <v>66.010000000000005</v>
     <v>0</v>
     <v>63.52</v>
-    <v>68.799899999999994</v>
+    <v>68.945999999999998</v>
     <v>43868180</v>
     <v>AMBA</v>
     <v>AMBARELLA, INC. (XNAS:AMBA)</v>
-    <v>1060162</v>
+    <v>1477734</v>
     <v>1601017</v>
     <v>2004</v>
   </rv>
@@ -4311,8 +4311,8 @@
     <v>546.44000000000005</v>
     <v>115.06</v>
     <v>2.5061</v>
-    <v>25.007000000000001</v>
-    <v>5.3619E-2</v>
+    <v>21.59</v>
+    <v>4.6293000000000001E-2</v>
     <v>USD</v>
     <v>Advanced Micro Devices, Inc. is a global semiconductor company. The Company is focused on high-performance computing and artificial intelligence (AI). Its segments include Data Center, Client and Gaming, and Embedded. Data Center segment includes AI accelerators, microprocessors (CPUs) for servers, graphics processing units (GPUs), accelerated processing units (APUs), data processing units (DPUs), Field Programmable Gate Arrays (FPGAs), and Adaptive system-on-Chip (SoC) products for data centers. Client and Gaming segment includes CPUs, APUs, chipsets for desktops and notebooks, discrete GPUs, and semi-custom SoC products and development services. Embedded segment includes embedded CPUs, APUs, FPGAs, system on modules (SOMs), and Adaptive SoC products. It markets and sells its products under the AMD trademark. Its products include AMD EPYC, AMD Ryzen, AMD Ryzen PRO, Virtex UltraScale+, among others.</v>
     <v>31000</v>
@@ -4320,23 +4320,23 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>2485 Augustine Drive, SANTA CLARA, CA, 95054 US</v>
-    <v>494.3</v>
+    <v>494.97</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46181.758904421091</v>
+    <v>46181.825970185157</v>
     <v>23</v>
     <v>477.71</v>
-    <v>801256133587</v>
+    <v>795684369970</v>
     <v>ADVANCED MICRO DEVICES, INC.</v>
     <v>ADVANCED MICRO DEVICES, INC.</v>
     <v>485</v>
-    <v>163.80109999999999</v>
+    <v>162.66210000000001</v>
     <v>466.38</v>
-    <v>491.387</v>
+    <v>487.97</v>
     <v>1630601000</v>
     <v>AMD</v>
     <v>ADVANCED MICRO DEVICES, INC. (XNAS:AMD)</v>
-    <v>16964275</v>
+    <v>19825701</v>
     <v>38353088</v>
     <v>1969</v>
   </rv>
@@ -4362,8 +4362,8 @@
     <v>278.56</v>
     <v>196</v>
     <v>1.4587000000000001</v>
-    <v>-1.9550000000000001</v>
-    <v>-7.9459999999999999E-3</v>
+    <v>-0.76500000000000001</v>
+    <v>-3.1090000000000002E-3</v>
     <v>USD</v>
     <v>Amazon.com, Inc. provides a range of products and services to customers. The products offered through its stores include merchandise and content it has purchased for resale and products offered by third-party sellers. The Company’s segments include North America, International and Amazon Web Services (AWS). It serves consumers through its online and physical stores and focuses on selection, price, and convenience. Customers access its offerings through its websites, mobile apps, Alexa, devices, streaming, and physically visiting its stores. It also manufactures and sells electronic devices, including Kindle, Fire tablet, Fire TV, Echo, Ring, Blink, and eero, and develops and produces media content. It serves developers and enterprises of all sizes, including start-ups, government agencies, and academic institutions, through AWS, which offers a set of on-demand technology services, including compute, storage, database, analytics, and machine learning, and other services.</v>
     <v>1575000</v>
@@ -4374,20 +4374,20 @@
     <v>249.42</v>
     <v>Diversified Retail</v>
     <v>Stock</v>
-    <v>46181.758903923437</v>
+    <v>46181.825973946092</v>
     <v>26</v>
-    <v>244.05</v>
-    <v>2625541623250</v>
+    <v>243.39500000000001</v>
+    <v>2638342584150</v>
     <v>AMAZON.COM, INC.</v>
     <v>AMAZON.COM, INC.</v>
     <v>246.55</v>
-    <v>29.168700000000001</v>
+    <v>29.3109</v>
     <v>246.03</v>
-    <v>244.07499999999999</v>
+    <v>245.26499999999999</v>
     <v>10757110000</v>
     <v>AMZN</v>
     <v>AMAZON.COM, INC. (XNAS:AMZN)</v>
-    <v>19573650</v>
+    <v>25089297</v>
     <v>41132665</v>
     <v>1996</v>
   </rv>
@@ -4413,8 +4413,8 @@
     <v>179.8</v>
     <v>85.58</v>
     <v>1.6153999999999999</v>
-    <v>2.8650000000000002</v>
-    <v>1.8571000000000001E-2</v>
+    <v>1.7350000000000001</v>
+    <v>1.1247E-2</v>
     <v>USD</v>
     <v>Arista Networks, Inc. is a provider of data-driven, client-to-cloud networking for large artificial intelligence (AI), data center, campus and routing environments. The Company's cloud networking solutions consist of its Extensible Operating System (EOS), a set of network applications and its Ethernet switching and routing platforms. Its platforms deliver availability, agility, automation, analytics, and security through an advanced network operating stack. It offers a robust set of solutions, ranging from modular and fixed-form-factor campus spine switches to Power-over-Ethernet (PoE) leaf switches and Wi-Fi access points, all managed through CloudVision. The Company's network-as-a-service approach empowers customers of all sizes to leverage their data through offerings spanning three categories: Core (AI, Cloud, and Data Center Networking), Cognitive Adjacencies (Campus and Routing), and Cognitive Networks (Software and Services).</v>
     <v>5115</v>
@@ -4425,20 +4425,20 @@
     <v>159.22999999999999</v>
     <v>Communications &amp; Networking</v>
     <v>Stock</v>
-    <v>46181.75886929375</v>
+    <v>46181.825975</v>
     <v>29</v>
     <v>153.2525</v>
-    <v>197864863405</v>
+    <v>196441964015</v>
     <v>ARISTA NETWORKS, INC.</v>
     <v>ARISTA NETWORKS, INC.</v>
     <v>156.30000000000001</v>
-    <v>53.820700000000002</v>
+    <v>53.433700000000002</v>
     <v>154.27000000000001</v>
-    <v>157.13499999999999</v>
+    <v>156.005</v>
     <v>1259203000</v>
     <v>ANET</v>
     <v>ARISTA NETWORKS, INC. (XNYS:ANET)</v>
-    <v>3559049</v>
+    <v>4305599</v>
     <v>12558631</v>
     <v>2011</v>
   </rv>
@@ -4464,8 +4464,8 @@
     <v>745.61</v>
     <v>320</v>
     <v>2.4725000000000001</v>
-    <v>10.8</v>
-    <v>1.9382999999999997E-2</v>
+    <v>9.5998999999999999</v>
+    <v>1.7229000000000001E-2</v>
     <v>USD</v>
     <v>AppLovin Corporation is a marketing platform. The Company provides end-to-end software and artificial intelligence (AI) solutions for businesses to reach, monetize and grow their global audiences. Its advertising solutions include a comprehensive suite of tools including AppDiscovery, MAX, Adjust, Wurl and Axon Ads Manager. AppDiscovery is powered by AXON, its AI-powered advertising engine, and matches advertiser demand with publisher supply through auctions at vast scale and at microsecond-level speeds. MAX is its monetization solution, utilizing an advanced in-app bidding technology that optimizes the value of a publisher’s advertising inventory by running a real-time competitive auction, driving more competition, and higher returns for publishers. Adjust is its measurement and analytics marketing platform which provides marketers with the visibility, insights, and data needed to scale their apps marketing and drive more informed results. Wurl is its connected TV (CTV) platform.</v>
     <v>898</v>
@@ -4476,20 +4476,20 @@
     <v>573.70000000000005</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46181.758901133595</v>
+    <v>46181.825963159376</v>
     <v>32</v>
     <v>557.41999999999996</v>
-    <v>190813920000</v>
+    <v>190410758406</v>
     <v>APPLOVIN CORPORATION</v>
     <v>APPLOVIN CORPORATION</v>
     <v>558.03</v>
-    <v>49.359099999999998</v>
+    <v>49.254800000000003</v>
     <v>557.20000000000005</v>
-    <v>568</v>
+    <v>566.79989999999998</v>
     <v>335940000</v>
     <v>APP</v>
     <v>APPLOVIN CORPORATION (XNAS:APP)</v>
-    <v>2365034</v>
+    <v>3406341</v>
     <v>5196178</v>
     <v>2011</v>
   </rv>
@@ -4515,25 +4515,25 @@
     <v>92.65</v>
     <v>48.53</v>
     <v>2.0400999999999998</v>
-    <v>1.53</v>
-    <v>2.0539999999999999E-2</v>
+    <v>1.2549999999999999</v>
+    <v>1.6848000000000002E-2</v>
     <v>USD</v>
     <v>CBOE BZX Exchange</v>
     <v>BATS</v>
     <v>7.4999999999999997E-3</v>
     <v>76.37</v>
     <v>ETF</v>
-    <v>46181.758902800779</v>
+    <v>46181.825989606252</v>
     <v>35</v>
     <v>75.040000000000006</v>
     <v>7262198811.6000004</v>
     <v>ARK Innovation</v>
     <v>75.959999999999994</v>
     <v>74.489999999999995</v>
-    <v>76.02</v>
+    <v>75.745000000000005</v>
     <v>ARKK</v>
     <v>ARK Innovation (BATS:ARKK)</v>
-    <v>3731911</v>
+    <v>4797308</v>
     <v>10004016</v>
   </rv>
   <rv s="2">
@@ -4579,8 +4579,8 @@
     <v>427.99</v>
     <v>100.02</v>
     <v>1.421</v>
-    <v>7.665</v>
-    <v>2.2351999999999997E-2</v>
+    <v>3.46</v>
+    <v>1.0089999999999998E-2</v>
     <v>USD</v>
     <v>Arm Holdings plc is a United Kingdom-based company. The Company is engaged in the design of central processing units (CPUs) and compute platforms for semiconductor chips. It develops and licenses CPU products and related technology. Its cloud and data center solutions include Arm AGI CPU and Arm Neoverse Compute Subsystems. The Arm Agentic Generalized Infrastructure (AGI) CPU is a production-ready system on a chip (SoC) for artificial intelligence (AI) data centers, delivering compute at scale. The Arm Neoverse Compute Subsystems (CSS) are pre-validated, performance-optimized compute platforms designed to accelerate infrastructure silicon development. The Company's primary markets include smartphone applications, processors and other chips used in mobile phones, consumer electronics, networking equipment, cloud and data center servers, automotive applications, Internet of Things (loT) and other embedded computing devices.</v>
     <v>9584</v>
@@ -4591,19 +4591,19 @@
     <v>364.35</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46181.758895543753</v>
+    <v>46181.825989606252</v>
     <v>339.00599999999997</v>
-    <v>374463157005</v>
+    <v>369971884810</v>
     <v>ARM HOLDINGS PLC</v>
     <v>ARM HOLDINGS PLC</v>
     <v>354</v>
-    <v>414.21899999999999</v>
+    <v>409.2509</v>
     <v>342.93</v>
-    <v>350.59500000000003</v>
+    <v>346.39</v>
     <v>1068079000</v>
     <v>ARM</v>
     <v>ARM HOLDINGS PLC (XNAS:ARM)</v>
-    <v>6540411</v>
+    <v>7555717</v>
     <v>12743586</v>
     <v>2018</v>
   </rv>
@@ -4629,8 +4629,8 @@
     <v>1779.2850000000001</v>
     <v>683.48</v>
     <v>1.806</v>
-    <v>113.02</v>
-    <v>6.8842E-2</v>
+    <v>100.42</v>
+    <v>6.1166999999999999E-2</v>
     <v>USD</v>
     <v>ASML Holding N.V. is a holding company based in the Netherlands. The Company operates through its subsidiaries in the Netherlands, the United States, Italy, France, Germany, the United Kingdom, Ireland, Belgium, South Korea, Taiwan, Singapore, China, Hong Kong, Japan, Malaysia and Israel. The Company operates through one business segment which is engage in development, production, marketing, sales, upgrading and servicing of advanced semiconductor equipment systems, consisting of lithography, metrology and inspection systems. The Company offers TWINSCAN systems, equipped with lithography system with a mercury lamp as light source (i-line), Krypton Fluoride (KrF) and Argon Fluoride (ArF) light sources for processing wafers for manufacturing environments for which imaging at a small resolution is required. TWINSCAN systems also include immersion lithography systems (TWINSCAN immersion systems).</v>
     <v>43882</v>
@@ -4641,20 +4641,20 @@
     <v>1769.4</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46181.758839108596</v>
+    <v>46181.825922685159</v>
     <v>45</v>
     <v>1719.67</v>
-    <v>681106058052</v>
+    <v>676215397032</v>
     <v>ASML Holding NV</v>
     <v>ASML Holding NV</v>
     <v>1730.16</v>
-    <v>60.328400000000002</v>
+    <v>59.895200000000003</v>
     <v>1641.74</v>
-    <v>1754.76</v>
+    <v>1742.16</v>
     <v>388147700</v>
     <v>ASML</v>
     <v>ASML Holding NV (XNAS:ASML)</v>
-    <v>1450679</v>
+    <v>1662882</v>
     <v>1664620</v>
     <v>1994</v>
   </rv>
@@ -4680,8 +4680,8 @@
     <v>495</v>
     <v>241.11</v>
     <v>1.4705999999999999</v>
-    <v>8.8049999999999997</v>
-    <v>2.2827E-2</v>
+    <v>11.015000000000001</v>
+    <v>2.8555999999999998E-2</v>
     <v>USD</v>
     <v>Broadcom Inc. is a global technology firm that designs, develops, and supplies a range of semiconductors, enterprise software and security solutions. The Company operates through two segments: semiconductor solutions and infrastructure software. Its semiconductor solutions segment includes all of its product lines and intellectual property (IP) licensing. It provides a variety of radio frequency semiconductor devices, wireless connectivity solutions, custom touch controllers, and inductive charging solutions for mobile applications. Its infrastructure software segment includes its private and hybrid cloud, application development and delivery, software-defined edge, application networking and security, mainframe, distributed and cybersecurity solutions, and its FC SAN business. It provides a portfolio of software solutions that enable customers to plan, develop, automate, manage and secure applications across mainframe, distributed, mobile and cloud platforms.</v>
     <v>33000</v>
@@ -4692,20 +4692,20 @@
     <v>402.83800000000002</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46181.758919883592</v>
+    <v>46181.825985474221</v>
     <v>48</v>
     <v>391.35</v>
-    <v>1867992239380</v>
+    <v>1878455855660</v>
     <v>BROADCOM INC.</v>
     <v>BROADCOM INC.</v>
     <v>402.54</v>
-    <v>65.717500000000001</v>
+    <v>66.085599999999999</v>
     <v>385.73</v>
-    <v>394.53500000000003</v>
+    <v>396.745</v>
     <v>4734668000</v>
     <v>AVGO</v>
     <v>BROADCOM INC. (XNAS:AVGO)</v>
-    <v>19143209</v>
+    <v>23865805</v>
     <v>25700093</v>
     <v>2018</v>
   </rv>
@@ -4731,8 +4731,8 @@
     <v>9.39</v>
     <v>3.01</v>
     <v>3.1166</v>
-    <v>0.17499999999999999</v>
-    <v>4.1666999999999996E-2</v>
+    <v>9.01E-2</v>
+    <v>2.1451999999999999E-2</v>
     <v>USD</v>
     <v>BigBear.ai Holdings, Inc. operates as a specialized provider of artificial intelligence (AI) technology. The Company provides decision intelligence solutions for supply chains and logistics, enterprise operations, manned-unmanned teaming in autonomous systems, and cybersecurity. Its solutions include AI orchestration and sensor function, digital identity management, computer vision, cybersecurity, predictive intelligence, modeling &amp; simulation, enterprise automation and professional services. It offers Trueface, which performs one-to-many (1:N) facial matches with real-time photos, delivering identity verification. It also offers veriScan, which captures and transmits real-time photos into a biometric matching service supporting access control and biometric boarding/bag tags. The Company serves homeland &amp; border security, defense, intelligence, manufacturing &amp; suppy chain, travel and trade industries.</v>
     <v>579</v>
@@ -4743,20 +4743,20 @@
     <v>4.49</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46181.758934895312</v>
+    <v>46181.825999189059</v>
     <v>51</v>
     <v>4.2</v>
-    <v>2095404062</v>
+    <v>2054741249</v>
     <v>BIGBEAR.AI HOLDINGS, INC.</v>
     <v>BIGBEAR.AI HOLDINGS, INC.</v>
     <v>4.3099999999999996</v>
     <v>0</v>
     <v>4.2</v>
-    <v>4.375</v>
+    <v>4.2900999999999998</v>
     <v>478949500</v>
     <v>BBAI</v>
     <v>BIGBEAR.AI HOLDINGS, INC. (XNYS:BBAI)</v>
-    <v>26688996</v>
+    <v>31405814</v>
     <v>49028546</v>
     <v>2020</v>
   </rv>
@@ -4782,8 +4782,8 @@
     <v>115.25</v>
     <v>36.884999999999998</v>
     <v>0.96240000000000003</v>
-    <v>-0.94</v>
-    <v>-1.3332999999999999E-2</v>
+    <v>-0.57999999999999996</v>
+    <v>-8.2269999999999999E-3</v>
     <v>EUR</v>
     <v>Bayerische Motoren Werke AG (BMW) is a Germany-based company. The Company is engaged in the development and manufacturing of automobiles and motorcycles. Its business is divided into three segments: Automotive segment, Motorcycles segment, and Financial Services segment. The Automotive segment has three brands BMW, MINI and Rolls-Royce. The product range includes automobiles ranging from the compact class to the luxury class. The Motorcycles segment develops manufactures and sells motorcycles and scooters in the Sport, Tour, Roadster, Heritage, Adventure and Urban Mobility categories, as well as motorcycles for private use and special-purpose vehicles for operational use. The Financial Services segment offers credit financing and the leasing of BMW Group brand automobiles and motorcycles to retail customers. It also handles financing for dealerships and customer deposits.</v>
     <v>154540</v>
@@ -4794,20 +4794,20 @@
     <v>70.12</v>
     <v>Automobiles &amp; Auto Parts</v>
     <v>Stock</v>
-    <v>46181.73541666667</v>
+    <v>46181.755555555559</v>
     <v>54</v>
     <v>69</v>
     <v>54471310000</v>
     <v>Bayerische Motoren Werke AG</v>
     <v>Bayerische Motoren Werke AG</v>
     <v>69.680000000000007</v>
-    <v>6.2667000000000002</v>
+    <v>6.2991000000000001</v>
     <v>70.5</v>
-    <v>69.56</v>
+    <v>69.92</v>
     <v>615810400</v>
     <v>BMW</v>
     <v>Bayerische Motoren Werke AG (XFRA:BMW)</v>
-    <v>2973</v>
+    <v>2975</v>
     <v>1234460</v>
     <v>1995</v>
   </rv>
@@ -4833,8 +4833,8 @@
     <v>416.69</v>
     <v>262.74900000000002</v>
     <v>1.1416999999999999</v>
-    <v>19.664999999999999</v>
-    <v>5.2274000000000001E-2</v>
+    <v>17.79</v>
+    <v>4.7289999999999999E-2</v>
     <v>USD</v>
     <v>Cadence Design Systems, Inc. is an electronic systems designing company. The Company applies its Intelligent System Design strategy to deliver software, hardware and intellectual property (IP) that turn design concepts into reality. Its product categories include Core Electronic Design Automation (EDA), Semiconductor IP, and System Design and Analysis (SD&amp;A). Core EDA includes software, hardware, and services used to design and verify a wide variety of semiconductors. The semiconductor IP portfolio includes silicon subsystems, software, and services that are used in semiconductor design. The SD&amp;A category provides solutions and services that enable the design and verification of complete electronic systems, from PCBs to complex system assemblies. Its semiconductors are used in various industries, including automotive, aerospace, biotech, hyperscale and cloud computing, data centers, telecommunications, medical technology, industrial Internet of things, and artificial intelligence (AI).</v>
     <v>13800</v>
@@ -4842,23 +4842,23 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>2655 Seely Avenue Bldg 5, SAN JOSE, CA, 95134 US</v>
-    <v>396.6653</v>
+    <v>396.71</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46181.758938147657</v>
+    <v>46181.825981978909</v>
     <v>57</v>
     <v>381.84500000000003</v>
-    <v>109183142680</v>
+    <v>108665987680</v>
     <v>CADENCE DESIGN SYSTEMS, INC.</v>
     <v>CADENCE DESIGN SYSTEMS, INC.</v>
     <v>383</v>
-    <v>92.413899999999998</v>
+    <v>91.976200000000006</v>
     <v>376.19</v>
-    <v>395.85500000000002</v>
+    <v>393.98</v>
     <v>275816000</v>
     <v>CDNS</v>
     <v>CADENCE DESIGN SYSTEMS, INC. (XNAS:CDNS)</v>
-    <v>1226075</v>
+    <v>1616594</v>
     <v>2394087</v>
     <v>1987</v>
   </rv>
@@ -4884,8 +4884,8 @@
     <v>412.7</v>
     <v>243.3</v>
     <v>1.1292</v>
-    <v>-2.3199999999999998</v>
-    <v>-9.1039999999999992E-3</v>
+    <v>-3.17</v>
+    <v>-1.244E-2</v>
     <v>USD</v>
     <v>Constellation Energy Corporation is a producer of emissions-free energy and an energy supplier to businesses, homes and public sector customers nationwide. The Company’s nuclear, hydro, wind, and solar generation facilities have the generating capacity to power the equivalent of 27 million homes, providing about 10% of the nation’s clean energy. Its segments include Mid-Atlantic, Midwest, New York, ERCOT, and Other Power Regions. Through its integrated business operations, it sells electricity, natural gas, and other energy-related products and sustainable solutions to various types of customers, including distribution utilities, municipalities, cooperatives, commercial, industrial, public sector, and residential customers in markets across multiple geographic regions. It operates approximately 55 gigawatts of capacity from nuclear, natural gas, geothermal, hydro, wind and solar facilities.</v>
     <v>15291</v>
@@ -4896,20 +4896,20 @@
     <v>256.06</v>
     <v>Electrical Utilities &amp; IPPs</v>
     <v>Stock</v>
-    <v>46181.758894039063</v>
+    <v>46181.82599376094</v>
     <v>60</v>
     <v>250.14</v>
-    <v>90676846020</v>
+    <v>90371609320</v>
     <v>CONSTELLATION ENERGY CORPORATION.</v>
     <v>CONSTELLATION ENERGY CORPORATION.</v>
     <v>255.74</v>
-    <v>21.937200000000001</v>
+    <v>21.863299999999999</v>
     <v>254.83</v>
-    <v>252.51</v>
+    <v>251.66</v>
     <v>359102000</v>
     <v>CEG</v>
     <v>CONSTELLATION ENERGY CORPORATION. (XNAS:CEG)</v>
-    <v>2116877</v>
+    <v>2710695</v>
     <v>3977191</v>
     <v>2021</v>
   </rv>
@@ -4935,8 +4935,8 @@
     <v>245.94990000000001</v>
     <v>66.75</v>
     <v>3.2572999999999999</v>
-    <v>19.75</v>
-    <v>9.546099999999999E-2</v>
+    <v>14.64</v>
+    <v>7.0762000000000005E-2</v>
     <v>USD</v>
     <v>Credo Technology Group Holding Ltd is a Cayman Islands-based holding company. The Company delivers high-speed solutions to break bandwidth barriers on every wired connection in the data infrastructure market. It provides high-speed connectivity solutions that deliver improved power efficiency as data rates and corresponding bandwidth requirements increase exponentially throughout the data infrastructure market. Its connectivity solutions are optimized for optical and electrical Ethernet applications, including the emerging 100 gigabits per second (G), 200G, 400G, 800G and the emerging 1.6 terabits per second (T) port markets. Its products are based on its Serializer/Deserializer (SerDes) and Digital Signal Processor (DSP) technologies. Its product families include integrated circuits (ICs) for the optical and line card markets, active electrical cables (AECs) and SerDes Chiplets. The Company’s intellectual property (IP) solutions consist primarily of SerDes IP licensing.</v>
     <v>622</v>
@@ -4947,20 +4947,20 @@
     <v>227.511</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46181.758886122654</v>
+    <v>46181.82596602969</v>
     <v>63</v>
     <v>211.5</v>
-    <v>41803725336</v>
+    <v>40861186347</v>
     <v>Credo Technology Group Holding Ltd</v>
     <v>Credo Technology Group Holding Ltd</v>
     <v>218.05</v>
-    <v>91.394499999999994</v>
+    <v>89.333799999999997</v>
     <v>206.89</v>
-    <v>226.64</v>
+    <v>221.53</v>
     <v>184449900</v>
     <v>CRDO</v>
     <v>Credo Technology Group Holding Ltd (XNAS:CRDO)</v>
-    <v>5994597</v>
+    <v>7066931</v>
     <v>7631043</v>
   </rv>
   <rv s="2">
@@ -4985,8 +4985,8 @@
     <v>276.8</v>
     <v>163.52000000000001</v>
     <v>1.1476999999999999</v>
-    <v>-2.5350000000000001</v>
-    <v>-1.3653999999999999E-2</v>
+    <v>-2.5379999999999998</v>
+    <v>-1.367E-2</v>
     <v>USD</v>
     <v>Salesforce, Inc. is a customer relationship management (CRM) technology company. Its artificial intelligence (AI) powered Agentforce 360 Platform offers sales, service, marketing, commerce, collaboration, data management, integration, analytics, and information technology (IT) service solutions. It enables customers to build and deploy digital labor for employees and customers, leveraging autonomous AI agents across business functions. Its service offerings include Agentforce Sales, Agentforce Service, Agentforce 360 Platform, Slack and Others. The Agentforce Sales provides sales capabilities and tools built for organizations across prospecting, sales engagement, team collaboration, sales analytics and AI, sales programs, sales performance, partner management, and revenue and orders. The Agentforce Service provides field service solutions that enable companies to connect service agents, dispatchers and mobile employees through platform to schedule, dispatch and manage jobs.</v>
     <v>83334</v>
@@ -4997,20 +4997,20 @@
     <v>185</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46181.758869617966</v>
+    <v>46181.825937626563</v>
     <v>66</v>
     <v>181.71</v>
-    <v>149979375000</v>
+    <v>149976918000</v>
     <v>SALESFORCE, INC.</v>
     <v>SALESFORCE, INC.</v>
     <v>183.75</v>
-    <v>21.187200000000001</v>
+    <v>21.186800000000002</v>
     <v>185.66</v>
-    <v>183.125</v>
+    <v>183.12200000000001</v>
     <v>819000000</v>
     <v>CRM</v>
     <v>SALESFORCE, INC. (XNYS:CRM)</v>
-    <v>6659826</v>
+    <v>8822584</v>
     <v>14819240</v>
     <v>1999</v>
   </rv>
@@ -5036,8 +5036,8 @@
     <v>785.66</v>
     <v>342.72</v>
     <v>1.2632000000000001</v>
-    <v>-12.1</v>
-    <v>-1.8031999999999999E-2</v>
+    <v>-16.13</v>
+    <v>-2.4038E-2</v>
     <v>USD</v>
     <v>CrowdStrike Holdings, Inc. is a global cybersecurity company. The Company provides a cloud-native platform for protecting critical areas of enterprise risk - endpoints and cloud workloads, identity, and data. The Company's artificial intelligence (AI)-native CrowdStrike Falcon platform is a cloud-native unified platform built with AI at the core, capable of harnessing security and enterprise data to deliver highly modular solutions through a single lightweight sensor. Using cloud-scale AI, its Security Cloud enriches and correlates cybersecurity events with indicators of attack, threat intelligence, and enterprise data (including data from across endpoints, workloads, identities, DevOps, IT assets, and configurations) to create actionable data, identify shifts in adversary tactics, and automatically prevent threats in real-time across its customer base. It sells its Falcon platform via a partner-first subscription model to organizations of all sizes across multiple industries globally.</v>
     <v>11157</v>
@@ -5048,20 +5048,20 @@
     <v>684</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46181.758942985936</v>
+    <v>46181.826024351562</v>
     <v>69</v>
-    <v>653.5104</v>
-    <v>167737838016</v>
+    <v>652.01</v>
+    <v>166711941872</v>
     <v>CROWDSTRIKE HOLDINGS, INC.</v>
     <v>CROWDSTRIKE HOLDINGS, INC.</v>
     <v>675</v>
     <v>0</v>
     <v>671.02</v>
-    <v>658.92</v>
+    <v>654.89</v>
     <v>254564800</v>
     <v>CRWD</v>
     <v>CROWDSTRIKE HOLDINGS, INC. (XNAS:CRWD)</v>
-    <v>2127180</v>
+    <v>2628913</v>
     <v>3653876</v>
     <v>2011</v>
   </rv>
@@ -5083,8 +5083,8 @@
     <v>187</v>
     <v>63.8</v>
     <v>2.4409999999999998</v>
-    <v>2.71</v>
-    <v>2.6995000000000002E-2</v>
+    <v>1.74</v>
+    <v>1.7332E-2</v>
     <v>USD</v>
     <v>CoreWeave, Inc. is a cloud infrastructure technology company. The Company offers the CoreWeave Cloud Platform, which consists of software and cloud services that deliver the automation and efficiency needed to manage complex artificial intelligence (AI) infrastructure. Its CoreWeave Cloud Platform is an integrated solution that is purpose-built for running AI workloads such as model training and inference. Its solutions include infrastructure services, managed software services, and application software services. Its Infrastructure Services provide its customers with access to advanced graphics processing unit (GPU) and central processing unit (CPU) compute, highly performant networking, and storage. Its Managed Software Services include CKS, a flexible virtual private cloud and a bare metal service that runs kubernetes directly on high-performance servers. Its Application Software Services build on top of its infrastructure and managed software services, integrating additional tools.</v>
     <v>2189</v>
@@ -5095,19 +5095,19 @@
     <v>104.3</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46181.75893204844</v>
+    <v>46181.825990428122</v>
     <v>98.4</v>
-    <v>56248308240</v>
+    <v>55719104952</v>
     <v>COREWEAVE, INC.</v>
     <v>COREWEAVE, INC.</v>
     <v>101.58</v>
     <v>0</v>
     <v>100.39</v>
-    <v>103.1</v>
+    <v>102.13</v>
     <v>545570400</v>
     <v>CRWV</v>
     <v>COREWEAVE, INC. (XNAS:CRWV)</v>
-    <v>16824429</v>
+    <v>20039820</v>
     <v>30162031</v>
     <v>2017</v>
   </rv>
@@ -5133,8 +5133,8 @@
     <v>130.3656</v>
     <v>63.865000000000002</v>
     <v>0.99519999999999997</v>
-    <v>3.58</v>
-    <v>2.9430999999999999E-2</v>
+    <v>3.09</v>
+    <v>2.5402999999999998E-2</v>
     <v>USD</v>
     <v>Cisco Systems, Inc. designs and sells a range of technologies that power the Internet. The Company is integrating its product portfolios across networking, security, collaboration, applications and cloud. The Company's segments include the Americas; Europe, Middle East, and Africa (EMEA), and Asia Pacific, Japan, and China (APJC). Its Networking product category represents its core networking technologies of switching, routing, wireless, fifth generation (5G), silicon, optics solutions and compute products. Its Security product category consists of its cloud and application security, industrial security, network security, and user and device security offerings. Its Collaboration product category consists of its meetings, collaboration devices, calling, contact center and platform as a service (CPaaS) offering. Its Observability product category consists of its full stack observability offerings.</v>
     <v>86200</v>
@@ -5145,20 +5145,20 @@
     <v>126.435</v>
     <v>Communications &amp; Networking</v>
     <v>Stock</v>
-    <v>46181.758947789065</v>
+    <v>46181.826010289064</v>
     <v>74</v>
     <v>122</v>
-    <v>493546490700</v>
+    <v>491615187550</v>
     <v>CISCO SYSTEMS, INC.</v>
     <v>CISCO SYSTEMS, INC.</v>
     <v>123.51</v>
-    <v>41.726100000000002</v>
+    <v>41.562800000000003</v>
     <v>121.64</v>
-    <v>125.22</v>
+    <v>124.73</v>
     <v>3941435000</v>
     <v>CSCO</v>
     <v>CISCO SYSTEMS, INC. (XNAS:CSCO)</v>
-    <v>12785093</v>
+    <v>16775930</v>
     <v>28109851</v>
     <v>2021</v>
   </rv>
@@ -5184,8 +5184,8 @@
     <v>278.70499999999998</v>
     <v>98.010099999999994</v>
     <v>1.5597000000000001</v>
-    <v>-3.9</v>
-    <v>-1.6659E-2</v>
+    <v>-2.6875</v>
+    <v>-1.1479999999999999E-2</v>
     <v>USD</v>
     <v>Datadog Inc provides an AI-powered observability and security platform for cloud applications. Its Software as a Service (SaaS) platform integrates and automates infrastructure monitoring, application performance monitoring, log management, user experience monitoring, cloud security and service management. Its proprietary platform combines the power of metrics, traces, logs, user sessions, security signals, and other data from a single agent and over 1,000 integrations to provide a unified view of infrastructure, application performance and real-time events impacting performance. Its solutions include built for dynamic cloud and hybrid infrastructures, simple but not simplistic, integrated data platform, built for collaboration, cloud-agnostic, ubiquitous, and integrates with its customers complex environments. Its platform is used by industries to enable digital transformation and cloud migration, and drive collaboration among development, operations, security and business teams.</v>
     <v>8100</v>
@@ -5196,20 +5196,20 @@
     <v>240.79</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46181.758938414059</v>
+    <v>46181.825991735939</v>
     <v>77</v>
     <v>228.74</v>
-    <v>81945597642</v>
+    <v>82377199384</v>
     <v>DATADOG, INC.</v>
     <v>DATADOG, INC.</v>
     <v>237.81</v>
-    <v>583.25310000000002</v>
+    <v>586.32510000000002</v>
     <v>234.11</v>
-    <v>230.21</v>
+    <v>231.42250000000001</v>
     <v>355960200</v>
     <v>DDOG</v>
     <v>DATADOG, INC. (XNAS:DDOG)</v>
-    <v>3172274</v>
+    <v>4089468</v>
     <v>7426693</v>
     <v>2010</v>
   </rv>
@@ -5235,8 +5235,8 @@
     <v>469.47</v>
     <v>109.17</v>
     <v>1.319</v>
-    <v>5.0650000000000004</v>
-    <v>1.2843E-2</v>
+    <v>3.8050000000000002</v>
+    <v>9.6480000000000003E-3</v>
     <v>USD</v>
     <v>Dell Technologies Inc. is engaged in designing, developing, manufacturing, marketing, selling, and supporting a wide range of comprehensive and integrated solutions, products, and services. The Company operates through two segments: Infrastructure Solutions Group (ISG) and Client Solutions Group (CSG). Its ISG segment enables the Company’s customer’s digital transformation with solutions that address artificial intelligence (AI), machine learning, data analytics, and multi cloud environments. Its comprehensive storage portfolio includes modern and traditional storage solutions, including all-flash arrays, scale-out file, object platforms, hyper-converged infrastructure, and software-defined storage. Its CSG segment offers branded personal computers (PCs) including notebooks, desktops, and workstations and branded peripherals that include displays, docking stations, keyboards, mice, and webcam and audio devices, as well as third-party software and peripherals.</v>
     <v>97000</v>
@@ -5247,20 +5247,20 @@
     <v>406.49990000000003</v>
     <v>Computers, Phones &amp; Household Electronics</v>
     <v>Stock</v>
-    <v>46181.758905751565</v>
+    <v>46181.826010253906</v>
     <v>80</v>
     <v>385.61</v>
-    <v>259473305276</v>
+    <v>258654849218</v>
     <v>DELL TECHNOLOGIES INC.</v>
     <v>DELL TECHNOLOGIES INC.</v>
     <v>398.57</v>
-    <v>31.721699999999998</v>
+    <v>31.621600000000001</v>
     <v>394.39</v>
-    <v>399.45499999999998</v>
+    <v>398.19499999999999</v>
     <v>649568300</v>
     <v>DELL</v>
     <v>DELL TECHNOLOGIES INC. (XNYS:DELL)</v>
-    <v>5911913</v>
+    <v>6861807</v>
     <v>10699293</v>
     <v>2013</v>
   </rv>
@@ -5302,8 +5302,8 @@
     <v>124.69</v>
     <v>92.185000000000002</v>
     <v>1.3836999999999999</v>
-    <v>-0.53</v>
-    <v>-5.3149999999999994E-3</v>
+    <v>-0.47499999999999998</v>
+    <v>-4.764E-3</v>
     <v>USD</v>
     <v>The Walt Disney Company is a diversified worldwide entertainment company. The Company's segments include Entertainment, Sports and Experiences. The Entertainment segment generally encompasses its non-sports focused global film and episodic content production and distribution activities. The lines of business within the Entertainment segment along with their business activities include Linear Networks, Direct-to-Consumer, and Content Sales/Licensing. The Sports segment encompasses its sports-focused global television and direct-to-consumer (DTC) video streaming content production and distribution activities. The lines of business within the Sports segment include ESPN and Star. The Experiences segment includes Parks and Experiences and Consumer Products. Parks and Experiences consists of Walt Disney World Resort in Florida, Disneyland Resort in California, Disney Cruise Line, and others. Consumer Products includes licensing of its trade names, characters, visual, literary and other IP.</v>
     <v>231000</v>
@@ -5315,20 +5315,20 @@
     <v>85</v>
     <v>Media &amp; Publishing</v>
     <v>Stock</v>
-    <v>46181.758964142966</v>
+    <v>46181.825999513283</v>
     <v>86</v>
     <v>98.4101</v>
-    <v>172227160980</v>
+    <v>172322669085</v>
     <v>THE WALT DISNEY COMPANY</v>
     <v>THE WALT DISNEY COMPANY</v>
     <v>99.24</v>
-    <v>15.870799999999999</v>
+    <v>15.8796</v>
     <v>99.71</v>
-    <v>99.18</v>
+    <v>99.234999999999999</v>
     <v>1736511000</v>
     <v>DIS</v>
     <v>THE WALT DISNEY COMPANY (XNYS:DIS)</v>
-    <v>4286092</v>
+    <v>5558613</v>
     <v>9269420</v>
     <v>2018</v>
   </rv>
@@ -5354,8 +5354,8 @@
     <v>57.55</v>
     <v>31.635000000000002</v>
     <v>0.73470000000000002</v>
-    <v>-0.62</v>
-    <v>-1.4695E-2</v>
+    <v>-0.27</v>
+    <v>-6.4000000000000003E-3</v>
     <v>USD</v>
     <v>Dynatrace, Inc. is an artificial intelligence (AI)-powered observability platform. It is advancing observability for digital businesses and transforming the complexity of modern digital ecosystems into business assets. It enables organizations to analyze and automate. Its platform combines broad and deep observability, continuous runtime application security, and advanced AI to support information technology (IT) operations, development, security, and business teams, enabling organizations to optimize cloud and IT operations, accelerate secure software delivery, and improve digital performance. Its platform's solutions include infrastructure observability, application observability, AI observability, digital experience, business analytics, software delivery, threat observability, application security, and log management. Its application security detects, analyses, and remediates runtime application vulnerabilities and attacks in real time.</v>
     <v>5600</v>
@@ -5366,20 +5366,20 @@
     <v>42.47</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46181.758930404685</v>
+    <v>46181.826015138278</v>
     <v>89</v>
     <v>41.43</v>
-    <v>12116644849</v>
+    <v>12218661344</v>
     <v>DYNATRACE, INC.</v>
     <v>DYNATRACE, INC.</v>
     <v>42.14</v>
-    <v>77.584900000000005</v>
+    <v>78.238100000000003</v>
     <v>42.19</v>
-    <v>41.57</v>
+    <v>41.92</v>
     <v>291475700</v>
     <v>DT</v>
     <v>DYNATRACE, INC. (XNYS:DT)</v>
-    <v>2956675</v>
+    <v>3742724</v>
     <v>6380004</v>
     <v>2014</v>
   </rv>
@@ -5405,8 +5405,8 @@
     <v>16.489999999999998</v>
     <v>4.6150000000000002</v>
     <v>2.2221000000000002</v>
-    <v>6.5000000000000002E-2</v>
-    <v>8.9289999999999994E-3</v>
+    <v>-5.0000000000000001E-3</v>
+    <v>-6.868E-4</v>
     <v>USD</v>
     <v>Enovix Corporation is a high-performance battery company. The Company is focused on designing, developing, manufacturing, and commercializing Lithium-ion, or Li-ion, batteries, including silicon-anode architectures, for smartphones, smart eyewear, defense, industrial and emerging edge artificial intelligence (AI) applications. Its silicon-anode battery architecture enables energy density and performance relative to conventional battery cells, particularly in space-constrained devices. It focuses on developing a battery architecture that allows the use of active silicon and no graphite in the battery's anode, which is the negative electrode that stores lithium ions when a battery is charged. Its AI-1 battery platform is architected as a unified silicon-anode platform designed to address the high-performance consumer electronics and defense applications. The AI-1 platform is designed to support AI-enabled smartphones and smart eyewear, as well as other edge-AI devices.</v>
     <v>664</v>
@@ -5417,20 +5417,20 @@
     <v>7.68</v>
     <v>Machinery, Equipment &amp; Components</v>
     <v>Stock</v>
-    <v>46181.758947106253</v>
+    <v>46181.825978807814</v>
     <v>92</v>
-    <v>7.2801</v>
-    <v>1602336723</v>
+    <v>7.2549999999999999</v>
+    <v>1587065985</v>
     <v>Enovix Corporation</v>
     <v>Enovix Corporation</v>
     <v>7.68</v>
     <v>0</v>
     <v>7.28</v>
-    <v>7.3449999999999998</v>
+    <v>7.2750000000000004</v>
     <v>218153400</v>
     <v>ENVX</v>
     <v>Enovix Corporation (XNAS:ENVX)</v>
-    <v>2341776</v>
+    <v>2901221</v>
     <v>8453190</v>
     <v>2020</v>
   </rv>
@@ -5456,8 +5456,8 @@
     <v>435.43</v>
     <v>311.91500000000002</v>
     <v>1.1889000000000001</v>
-    <v>7.89</v>
-    <v>1.9927E-2</v>
+    <v>8.9</v>
+    <v>2.2477999999999998E-2</v>
     <v>USD</v>
     <v>Eaton Corporation plc is an intelligent power management company. Its Electrical Americas segment consists of electrical components, industrial components, power distribution and assemblies, residential products, circuit protection, utility power distribution, wiring devices and others. The Electrical Global segment consists of electrical components, industrial components, power distribution and assemblies, single phase and three phase power quality, and services. The Aerospace segment is a global supplier of aerospace fuel, hydraulics, and pneumatic systems for commercial and military use and filtration systems for industrial applications. The Vehicle segment designs, manufactures, markets, and supplies drivetrain, powertrain systems and critical components. The eMobility segment designs, manufactures, markets, and supplies mechanical, electrical, and electronic components and systems. The Company is also engaged in providing thermal monitoring for critical electrical equipment.</v>
     <v>97000</v>
@@ -5465,23 +5465,23 @@
     <v>XNYS</v>
     <v>XNYS</v>
     <v>EATON HOUSE 30 PEMBROKE ROAD DUBLIN 4, DUBLIN, D04 Y0C2 IE</v>
-    <v>406.04</v>
+    <v>406.5</v>
     <v>Machinery, Equipment &amp; Components</v>
     <v>Stock</v>
-    <v>46181.758920624998</v>
+    <v>46181.826001585156</v>
     <v>95</v>
     <v>398.1</v>
-    <v>156807189000</v>
+    <v>157199372000</v>
     <v>EATON CORPORATION PUBLIC LIMITED COMPANY</v>
     <v>EATON CORPORATION PUBLIC LIMITED COMPANY</v>
     <v>401.92</v>
-    <v>39.479700000000001</v>
+    <v>39.578400000000002</v>
     <v>395.94</v>
-    <v>403.83</v>
+    <v>404.84</v>
     <v>388300000</v>
     <v>ETN</v>
     <v>EATON CORPORATION PUBLIC LIMITED COMPANY (XNYS:ETN)</v>
-    <v>938536</v>
+    <v>1372109</v>
     <v>2852274</v>
     <v>2012</v>
   </rv>
@@ -5507,8 +5507,8 @@
     <v>30.38</v>
     <v>13.29</v>
     <v>1.4363999999999999</v>
-    <v>-0.24</v>
-    <v>-1.0204E-2</v>
+    <v>-0.51500000000000001</v>
+    <v>-2.1895999999999999E-2</v>
     <v>USD</v>
     <v>Five9, Inc. helps organizations to create hyper-personalized artificial intelligence (AI)-driven customer experiences. The Company's Intelligent CX Platform, powered by its Five9 Genius AI suite, delivers a comprehensive suite of applications that enable customer service, sales, and marketing functions. It delivers a comprehensive, end-to-end cloud software solution for contact centers. Comprised of its Intelligent CX Platform and AI capabilities, including agentic AI agents, Agent Assist, Workflow Automation (WFA), AI Insights, AI Summaries, Workforce Engagement Management (WEM), and Revenue Execution, its solution allows simultaneous management and optimization of customer interactions across voice, chat, email, web, social media and mobile channels, either directly or through its application programming interfaces (APIs). The Company's agent interface is a browser-based design that provides visualization of customer profiles, context and cross-channel history.</v>
     <v>2910</v>
@@ -5519,20 +5519,20 @@
     <v>23.6128</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46181.758822812502</v>
+    <v>46181.825951805469</v>
     <v>98</v>
     <v>22.83</v>
-    <v>1782409687</v>
+    <v>1761354589</v>
     <v>FIVE9, INC.</v>
     <v>FIVE9, INC.</v>
     <v>23.13</v>
-    <v>35.299500000000002</v>
+    <v>34.8825</v>
     <v>23.52</v>
-    <v>23.28</v>
+    <v>23.004999999999999</v>
     <v>76563990</v>
     <v>FIVN</v>
     <v>FIVE9, INC. (XNAS:FIVN)</v>
-    <v>1092189</v>
+    <v>1491276</v>
     <v>4384778</v>
     <v>2001</v>
   </rv>
@@ -5558,8 +5558,8 @@
     <v>150.07</v>
     <v>70.12</v>
     <v>1.0900000000000001</v>
-    <v>-1.37</v>
-    <v>-9.469E-3</v>
+    <v>-1.7649999999999999</v>
+    <v>-1.2199E-2</v>
     <v>USD</v>
     <v>Fortinet, Inc. is engaged in cybersecurity, driving the convergence of networking and security. The Company's integrated platform, Fortinet Security Fabric, spans secure networking, unified secure access service edge (SASE), and artificial intelligence (AI)-driven security operations (SecOps). Its products and services include FortiOS, FortiASIC, FortiCloud, FortiAI, FortiEndpoint, and OT Security. The FortiGuard Labs is a cybersecurity threat intelligence and research organization comprised of experienced threat hunters, researchers, analysts, engineers, and data scientists who develop and utilize machine learning and AI technologies. FortiGuard and Other Security Services is an AI-powered security that is integrated as part of the Fortinet Security Fabric to deliver detection and enforcement across the entire attack surface. FortiCare Technical Support Service is a technical support service which provides customers with access to operations and maintenance of Fortinet solutions.</v>
     <v>15311</v>
@@ -5570,20 +5570,20 @@
     <v>147</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46181.758943957815</v>
+    <v>46181.826022314061</v>
     <v>101</v>
-    <v>142.84</v>
-    <v>104995842204</v>
+    <v>142.505</v>
+    <v>104706446086</v>
     <v>FORTINET, INC.</v>
     <v>FORTINET, INC.</v>
     <v>145.78</v>
-    <v>55.366199999999999</v>
+    <v>55.2136</v>
     <v>144.68</v>
-    <v>143.31</v>
+    <v>142.91499999999999</v>
     <v>732648400</v>
     <v>FTNT</v>
     <v>FORTINET, INC. (XNAS:FTNT)</v>
-    <v>2687980</v>
+    <v>3551295</v>
     <v>6753709</v>
     <v>2000</v>
   </rv>
@@ -5609,8 +5609,8 @@
     <v>404.47</v>
     <v>163.33000000000001</v>
     <v>1.2397</v>
-    <v>-4.7</v>
-    <v>-1.2858000000000001E-2</v>
+    <v>-4.8099999999999996</v>
+    <v>-1.3159000000000001E-2</v>
     <v>USD</v>
     <v>Alphabet Inc. is a holding company. The Company's segments include Google Services, Google Cloud, and Other Bets. The Google Services segment includes products and services such as ads, Android, Chrome, devices, Google Maps, Google Play, Search, and YouTube. The Google Cloud segment includes infrastructure and platform services, collaboration tools, and other services for enterprise customers. Its Other Bets segment is engaged in the sale of healthcare-related services and Internet services. Its Google Cloud provides enterprise-ready cloud services, including Google Cloud Platform and Google Workspace. Google Cloud Platform provides access to solutions such as artificial intelligence (AI) offerings, including its AI infrastructure, Vertex AI platform, and Gemini for Google Cloud; cybersecurity, and data and analytics. Google Workspace includes cloud-based communication and collaboration tools for enterprises, such as Calendar, Gmail, Docs, Drive, and Meet.</v>
     <v>194668</v>
@@ -5621,20 +5621,20 @@
     <v>363.38</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46181.758937360937</v>
+    <v>46181.826011620309</v>
     <v>104</v>
     <v>357.89</v>
-    <v>4393068230399</v>
+    <v>4391729028800</v>
     <v>ALPHABET INC.</v>
     <v>ALPHABET INC.</v>
     <v>362.44</v>
-    <v>27.5579</v>
+    <v>27.549499999999998</v>
     <v>365.54</v>
-    <v>360.84</v>
+    <v>360.73</v>
     <v>12174560000</v>
     <v>GOOG</v>
     <v>ALPHABET INC. (XNAS:GOOG)</v>
-    <v>12148052</v>
+    <v>14088604</v>
     <v>21824123</v>
     <v>2015</v>
   </rv>
@@ -5660,8 +5660,8 @@
     <v>153.85990000000001</v>
     <v>63.515000000000001</v>
     <v>2.3706999999999998</v>
-    <v>2.5299999999999998</v>
-    <v>3.0678E-2</v>
+    <v>2.5049999999999999</v>
+    <v>3.0374999999999999E-2</v>
     <v>USD</v>
     <v>Robinhood Markets, Inc. is focused on providing financial services offering retail brokerage, crypto, advisory, digital banking services, and private markets access to investors. Its offerings include Brokerage, Robinhood Crypto, Custody, Robinhood Wallet, Robinhood Gold, and Robinhood Gold Card. Brokerage services include investing, options trading, fractional trading, recurring investment, access to investing on margin, fully paid securities lending, cash sweep, instant withdrawals, Robinhood retirement, 24-hour market, joint investing accounts, and event contracts. It also offers a variety of ways for its customers to grow their financial knowledge, including Robinhood Learn, In-App Education, Newsfeeds, Sherwood Snacks, and Crypto Learn and Earn. It also operates regulated crypto platforms including Bitbuy and Coinsquare. Its self-clearing system, order routing system, data platform, and other back-end infrastructure allow its customers to focus on investing, saving and spending.</v>
     <v>2900</v>
@@ -5672,20 +5672,20 @@
     <v>85.63</v>
     <v>Financial Technology (Fintech) &amp; Infrastructure</v>
     <v>Stock</v>
-    <v>46181.758916863284</v>
+    <v>46181.825964710159</v>
     <v>107</v>
     <v>82.813999999999993</v>
-    <v>76542933500</v>
+    <v>76520420872</v>
     <v>ROBINHOOD MARKETS, INC.</v>
     <v>ROBINHOOD MARKETS, INC.</v>
     <v>84.63</v>
-    <v>47.285299999999999</v>
+    <v>47.2714</v>
     <v>82.47</v>
-    <v>85</v>
+    <v>84.974999999999994</v>
     <v>900505100</v>
     <v>HOOD</v>
     <v>ROBINHOOD MARKETS, INC. (XNAS:HOOD)</v>
-    <v>14061290</v>
+    <v>17027385</v>
     <v>26397606</v>
     <v>2013</v>
   </rv>
@@ -5727,8 +5727,8 @@
     <v>332.46</v>
     <v>212.34</v>
     <v>0.66869999999999996</v>
-    <v>-3.53</v>
-    <v>-1.2393000000000001E-2</v>
+    <v>-4.24</v>
+    <v>-1.4886E-2</v>
     <v>USD</v>
     <v>International Business Machines Corporation is a provider of global hybrid cloud and artificial intelligence (AI) and consulting expertise. The Company’s segments include Software, Consulting, Infrastructure and Financing. The Software segment includes hybrid cloud and AI platforms, which allow clients to realize their digital and AI transformations across the applications, data, and environments in which they operate. The Consulting segment focuses on integrating skills on strategy, experience, technology and operations by domain and industry. The Infrastructure segment is focused on the hybrid cloud infrastructure market, providing on-premises and cloud-based server and storage solutions. In addition, it offers a portfolio of life-cycle services for hybrid cloud infrastructure deployment. The Financing segment provides client and commercial financing, facilitating its clients’ acquisition of hardware, software and services. It helps clients in more than 175 countries.</v>
     <v>286800</v>
@@ -5740,20 +5740,20 @@
     <v>112</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46181.758948344534</v>
+    <v>46181.826026435156</v>
     <v>113</v>
     <v>279.8</v>
-    <v>264399133743</v>
+    <v>263731815180</v>
     <v>INTERNATIONAL BUSINESS MACHINES CORPORATION</v>
     <v>INTERNATIONAL BUSINESS MACHINES CORPORATION</v>
     <v>286.43</v>
-    <v>22.512</v>
+    <v>22.455200000000001</v>
     <v>284.83999999999997</v>
-    <v>281.31</v>
+    <v>280.60000000000002</v>
     <v>939885300</v>
     <v>IBM</v>
     <v>INTERNATIONAL BUSINESS MACHINES CORPORATION (XNYS:IBM)</v>
-    <v>4004148</v>
+    <v>4939164</v>
     <v>10822463</v>
     <v>1911</v>
   </rv>
@@ -5779,8 +5779,8 @@
     <v>125.14</v>
     <v>34.2301</v>
     <v>2.8405999999999998</v>
-    <v>0.03</v>
-    <v>2.942E-4</v>
+    <v>0.25</v>
+    <v>2.4520000000000002E-3</v>
     <v>USD</v>
     <v>Innodata Inc. is a global data engineering company. It provides a range of transferable solutions, platforms, and services for generative artificial intelligence (AI)/AI builders and adopters. Its Digital Data Solutions segment provides AI data preparation services, collecting or creating training data, annotating training data, and training AI algorithms for its customers, and AI model deployment and integration. It also provides a range of data engineering support services. Its Synodex segment provides an industry platform that transforms medical records into useable digital data organized in accordance with its proprietary data models or customer data models. Its Agility segment provides an industry platform that provides marketing communications and public relations professionals with the ability to target and distribute content to journalists and social media influencers worldwide and to monitor and analyze global news channels (print, Web, radio and TV) and social media channels.</v>
     <v>10020</v>
@@ -5791,20 +5791,20 @@
     <v>107</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46181.758876596876</v>
+    <v>46181.825943645315</v>
     <v>116</v>
     <v>99.36</v>
     <v>1490374656</v>
     <v>INNODATA INC.</v>
     <v>INNODATA INC.</v>
     <v>106.49</v>
-    <v>91.7761</v>
+    <v>91.974100000000007</v>
     <v>101.97</v>
-    <v>102</v>
+    <v>102.22</v>
     <v>32655360</v>
     <v>INOD</v>
     <v>INNODATA INC. (XNAS:INOD)</v>
-    <v>649431</v>
+    <v>829012</v>
     <v>3123807</v>
     <v>1988</v>
   </rv>
@@ -5830,8 +5830,8 @@
     <v>132.75</v>
     <v>18.965</v>
     <v>2.2513000000000001</v>
-    <v>12.83</v>
-    <v>0.12937399999999999</v>
+    <v>10.1899</v>
+    <v>0.102752</v>
     <v>USD</v>
     <v>Intel Corporation is a global designer and manufacturer of semiconductor products. The Company's segments include Intel Products, Intel Foundry, and All Other. Its Intel Products comprise Client Computing Group (CCG) and Data Center and AI (DCAI). CCG delivers platforms and processors that power PCs and edge devices, enabling enhanced performance, connectivity and user experience for consumer and commercial markets with capabilities that also support retail, industrial robotics and AI ecosystems at the edge. DCAI delivers workload-optimized solutions based upon its x86 architecture for data centers, including CPUs, AI accelerators, NICs, IPUs and custom ASICs, enabling performance and scalability for cloud, enterprise, telecommunication and HPC environments. The Intel Foundry segment comprises technology development, manufacturing and foundry services, developing new semiconductor process technologies and advanced packaging technologies. All Other segments include Mobileye and Other.</v>
     <v>83200</v>
@@ -5839,23 +5839,23 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>2200 Mission College Blvd, Rnb-4-151, SANTA CLARA, CA, 95054 US</v>
-    <v>112.5</v>
+    <v>112.54</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46181.758973830467</v>
+    <v>46181.826046122653</v>
     <v>119</v>
     <v>106.66</v>
-    <v>562912000000</v>
+    <v>549642857400</v>
     <v>INTEL CORPORATION</v>
     <v>INTEL CORPORATION</v>
     <v>111</v>
     <v>0</v>
     <v>99.17</v>
-    <v>112</v>
+    <v>109.3599</v>
     <v>5026000000</v>
     <v>INTC</v>
     <v>INTEL CORPORATION (XNAS:INTC)</v>
-    <v>101417633</v>
+    <v>118480614</v>
     <v>136968924</v>
     <v>1989</v>
   </rv>
@@ -5881,8 +5881,8 @@
     <v>84.64</v>
     <v>25.89</v>
     <v>3.2339000000000002</v>
-    <v>7.72</v>
-    <v>0.135963</v>
+    <v>6.0549999999999997</v>
+    <v>0.10664</v>
     <v>USD</v>
     <v>IonQ, Inc. is engaged in the quantum computing and networking industry, delivering high-performance systems capable of solving complex commercial and research use cases. Its generation quantum computers, IonQ Forte and IonQ Forte Enterprise, are cutting-edge systems, boasting 36 algorithmic qubits. It sells specialized quantum computing and networking hardware together with related maintenance and support. It also sells access to several quantum computers of various qubit capacities and is in the process of researching and developing technologies for quantum computers with increasing computational capabilities. It makes access to its quantum computers available via three cloud platforms, Amazon Web Services' (AWS) Amazon Braket, Microsoft's Azure Quantum and Google's Cloud Marketplace, and also to select customers via its own cloud service. Its product portfolio also includes quantum key distribution (QKD) systems, quantum random number generators (QRNGs), and single-photon detectors.</v>
     <v>1132</v>
@@ -5890,23 +5890,23 @@
     <v>XNYS</v>
     <v>XNYS</v>
     <v>4505 Campus Drive, Suite 100, COLLEGE PARK, MD, 20740 US</v>
-    <v>64.680000000000007</v>
+    <v>64.900000000000006</v>
     <v>Computers, Phones &amp; Household Electronics</v>
     <v>Stock</v>
-    <v>46181.758906921095</v>
+    <v>46181.825954375003</v>
     <v>122</v>
     <v>57.97</v>
-    <v>24075915000</v>
+    <v>23454420450</v>
     <v>IONQ, INC.</v>
     <v>IONQ, INC.</v>
     <v>59.6</v>
-    <v>1100.6826000000001</v>
+    <v>1072.2696000000001</v>
     <v>56.78</v>
-    <v>64.5</v>
+    <v>62.835000000000001</v>
     <v>373270000</v>
     <v>IONQ</v>
     <v>IONQ, INC. (XNYS:IONQ)</v>
-    <v>20856303</v>
+    <v>24745918</v>
     <v>34805739</v>
     <v>2020</v>
   </rv>
@@ -5932,8 +5932,8 @@
     <v>76.87</v>
     <v>9.52</v>
     <v>4.2521000000000004</v>
-    <v>5.18</v>
-    <v>9.530799999999999E-2</v>
+    <v>4.835</v>
+    <v>8.8960000000000011E-2</v>
     <v>USD</v>
     <v>IREN Limited is an Australia-based company, which owns and operates data centers powered by 100% renewable energy. Its facilities are optimized for Bitcoin mining, artificial intelligence (AI) cloud services, and other power-dense compute. Its data center mining facilities are in Canal Flats, Mackenzie, Prince George and Childress. Bitcoin Mining provides security to the Bitcoin network. Al Cloud Services provides cloud compute to Al customers, approximately 1,896 NVIDIA H100 and H200 GPUs. Its Canal Flats facility is in the Canadian Rockies, 100 kilometers (km) from Cranbrook regional airport and 500km east of Vancouver. Its facility is in Prince George, the city in northern British Columbia, located 500 km north of Vancouver. Its facility is located in Childress County, Texas, over 250 miles northwest of Dallas and in close proximity to multiple wind and solar generating facilities in the region. Its Childress operations comprise 200 Mega Watt of operating data centers.</v>
     <v>257</v>
@@ -5944,20 +5944,20 @@
     <v>59.67</v>
     <v>Financial Technology (Fintech) &amp; Infrastructure</v>
     <v>Stock</v>
-    <v>46181.758986353903</v>
+    <v>46181.82602209453</v>
     <v>125</v>
     <v>55.14</v>
-    <v>21274754011</v>
+    <v>21151458359</v>
     <v>IREN LIMITED</v>
     <v>IREN LIMITED</v>
     <v>56.21</v>
-    <v>129.77979999999999</v>
+    <v>129.02770000000001</v>
     <v>54.35</v>
-    <v>59.53</v>
+    <v>59.185000000000002</v>
     <v>357378700</v>
     <v>IREN</v>
     <v>IREN LIMITED (XNAS:IREN)</v>
-    <v>26151104</v>
+    <v>31627223</v>
     <v>57276849</v>
     <v>2018</v>
   </rv>
@@ -5983,25 +5983,25 @@
     <v>292.875</v>
     <v>206.81</v>
     <v>0.99929999999999997</v>
-    <v>3.02</v>
-    <v>1.0723E-2</v>
+    <v>2.64</v>
+    <v>9.3729999999999994E-3</v>
     <v>USD</v>
     <v>NYSE Arca</v>
     <v>ARCX</v>
     <v>1.9E-3</v>
     <v>286.83999999999997</v>
     <v>ETF</v>
-    <v>46181.758987603906</v>
+    <v>46181.82605148125</v>
     <v>128</v>
     <v>283.57499999999999</v>
     <v>80933362748.720001</v>
     <v>iShares:Russ 2000 ETF</v>
     <v>285.45999999999998</v>
     <v>281.64999999999998</v>
-    <v>284.67</v>
+    <v>284.29000000000002</v>
     <v>IWM</v>
     <v>iShares:Russ 2000 ETF (ARCX:IWM)</v>
-    <v>19561406</v>
+    <v>23721756</v>
     <v>26140958</v>
   </rv>
   <rv s="2">
@@ -6026,8 +6026,8 @@
     <v>2156.69</v>
     <v>811</v>
     <v>1.4967999999999999</v>
-    <v>198</v>
-    <v>0.10263299999999999</v>
+    <v>174.78</v>
+    <v>9.0596999999999997E-2</v>
     <v>USD</v>
     <v>KLA Corporation (KLA) develops industry equipment and services. The Company provides advanced process control and process-enabling solutions for manufacturing wafers and reticles, integrated circuits, packaging, and printed circuit boards. It operates through three segments, which include Semiconductor Process Control, Specialty Semiconductor Process, and PCB and Component Inspection. The Semiconductor Process Control segment offers a portfolio of inspection, metrology and data analytics products, and related services. The Specialty Semiconductor Process segment develops and sells advanced vacuum deposition and etching process tools. The PCB and Component Inspection segment enables electronic device manufacturers to inspect, test and measure PCBs, flat panel displays, and integrated circuits (ICs) to verify their quality, pattern the desired electronic circuitry on the relevant substrate and perform three-dimensional shaping of metalized circuits on multiple surfaces.</v>
     <v>15000</v>
@@ -6038,20 +6038,20 @@
     <v>2135.21</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46181.758929409378</v>
+    <v>46181.826017117972</v>
     <v>131</v>
     <v>2003.56</v>
-    <v>277870818000</v>
+    <v>274837647450</v>
     <v>KLA CORPORATION</v>
     <v>KLA CORPORATION</v>
     <v>2029.99</v>
-    <v>602.26499999999999</v>
+    <v>595.69079999999997</v>
     <v>1929.2</v>
-    <v>2127.1999999999998</v>
+    <v>2103.98</v>
     <v>130627500</v>
     <v>KLAC</v>
     <v>KLA CORPORATION (XNAS:KLAC)</v>
-    <v>648848</v>
+    <v>814506</v>
     <v>1030535</v>
     <v>1975</v>
   </rv>
@@ -6077,8 +6077,8 @@
     <v>82.663499999999999</v>
     <v>65.353800000000007</v>
     <v>0.35089999999999999</v>
-    <v>-0.01</v>
-    <v>-1.2579999999999999E-4</v>
+    <v>1.4999999999999999E-2</v>
+    <v>1.8870000000000001E-4</v>
     <v>USD</v>
     <v>The Coca-Cola Company is a beverage company. The Company's segments include Europe, Middle East and Africa (EMEA); Latin America; North America; Asia Pacific, and Bottling Investments. It sells multiple brands across several beverage categories worldwide. Its portfolio of sparkling soft drink brands includes Coca-Cola, Sprite and Fanta. Its water, sports, coffee and tea brands include Dasani, smartwater, vitaminwater, Topo Chico, BODYARMOR, Powerade, Costa, Georgia, Fuze Tea, Gold Peak and Ayataka. Its juice, value-added dairy and plant-based beverage brands include Minute Maid, Simply, innocent, Del Valle, fairlife and Santa Clara. It operates in two lines of business: concentrate operations and finished product operations. Its concentrate operations sell beverage concentrates, syrups, including fountain syrups, and certain finished beverages to authorized bottling operations. Its finished product operations sell sparkling soft drinks and a variety of other finished beverages.</v>
     <v>65900</v>
@@ -6089,20 +6089,20 @@
     <v>79.930000000000007</v>
     <v>Beverages</v>
     <v>Stock</v>
-    <v>46181.758965370311</v>
+    <v>46181.826043089844</v>
     <v>134</v>
     <v>79.099999999999994</v>
-    <v>341918244540</v>
+    <v>342025806590</v>
     <v>THE COCA-COLA COMPANY</v>
     <v>THE COCA-COLA COMPANY</v>
     <v>79.31</v>
-    <v>25.0181</v>
+    <v>25.026</v>
     <v>79.48</v>
-    <v>79.47</v>
+    <v>79.495000000000005</v>
     <v>4302482000</v>
     <v>KO</v>
     <v>THE COCA-COLA COMPANY (XNYS:KO)</v>
-    <v>5724137</v>
+    <v>7092673</v>
     <v>15199866</v>
     <v>1919</v>
   </rv>
@@ -6128,8 +6128,8 @@
     <v>18.940000000000001</v>
     <v>2.75</v>
     <v>1.37</v>
-    <v>0.11990000000000001</v>
-    <v>8.0309999999999999E-3</v>
+    <v>-0.09</v>
+    <v>-6.0280000000000004E-3</v>
     <v>USD</v>
     <v>LightPath Technologies, Inc. is a global, vertically integrated provider of optics, photonics and infrared solutions for the industrial, commercial, defense, telecommunications, and medical industries. The Company designs and manufactures optical and infrared components including molded glass aspheric lenses and assemblies, custom molded glass freeform lenses, infrared lenses and thermal imaging assemblies, fused fiber collimators, and BlackDiamond (BD6) chalcogenide-based glass lenses. It also offers custom optical assemblies, including full engineering design support. Its business is organized into four product groups: infrared components, visible components, assemblies and modules, and engineering services. Its infrared product group comprises both molded and turned infrared lenses and assemblies using a variety of infrared glass materials. Its assemblies and modules product group is comprised of other value-added products, including both infrared and visible components.</v>
     <v>345</v>
@@ -6140,20 +6140,20 @@
     <v>15.645</v>
     <v>Office Equipment</v>
     <v>Stock</v>
-    <v>46181.758853356252</v>
+    <v>46181.82598611094</v>
     <v>137</v>
-    <v>14.7</v>
-    <v>998723554</v>
+    <v>14.56</v>
+    <v>984794420</v>
     <v>LIGHTPATH TECHNOLOGIES, INC.</v>
     <v>LIGHTPATH TECHNOLOGIES, INC.</v>
     <v>15.56</v>
     <v>0</v>
     <v>14.93</v>
-    <v>15.049899999999999</v>
+    <v>14.84</v>
     <v>66360810</v>
     <v>LPTH</v>
     <v>LIGHTPATH TECHNOLOGIES, INC. (XNAS:LPTH)</v>
-    <v>1765365</v>
+    <v>2529351</v>
     <v>4270950</v>
     <v>1992</v>
   </rv>
@@ -6179,8 +6179,8 @@
     <v>18.709</v>
     <v>1.0900000000000001</v>
     <v>2.4003000000000001</v>
-    <v>2.5000000000000001E-2</v>
-    <v>2.4650000000000002E-3</v>
+    <v>-0.11990000000000001</v>
+    <v>-1.1823999999999999E-2</v>
     <v>USD</v>
     <v>Lightwave Logic, Inc. is a technology platform company leveraging its proprietary engineered electro-optic (EO) polymers known as Perkinamine, to transmit data at higher speeds with less power in a small form factor. The Company’s organic polymers allow it to create next-generation photonic EO devices that convert data from electrical signals into light/optical signals for applications in telecommunications, and for data transmission potentially used to support generative Artificial Intelligence. It designs its own proprietary materials for electro-optical modulation devices. Electro-optical modulators convert data from electric signals into optical signals that can then be transmitted over high-speed fiber-optic cables. It is focused on testing and demonstrating the manufacturability and reliability of its devices. In polymer photonics, polymer devices such as modulators, waveguides, and multiplexers can be fabricated on to a silicon platform.</v>
     <v>34</v>
@@ -6191,20 +6191,20 @@
     <v>10.87</v>
     <v>Electronic Equipment &amp; Parts</v>
     <v>Stock</v>
-    <v>46181.75886872656</v>
+    <v>46181.82605111094</v>
     <v>140</v>
-    <v>9.92</v>
-    <v>1566219133</v>
+    <v>9.8901000000000003</v>
+    <v>1543892999</v>
     <v>LIGHTWAVE LOGIC, INC.</v>
     <v>LIGHTWAVE LOGIC, INC.</v>
     <v>10.87</v>
     <v>0</v>
     <v>10.14</v>
-    <v>10.164999999999999</v>
+    <v>10.020099999999999</v>
     <v>154079600</v>
     <v>LWLG</v>
     <v>LIGHTWAVE LOGIC, INC. (XNAS:LWLG)</v>
-    <v>3259873</v>
+    <v>4365654</v>
     <v>8923133</v>
     <v>1997</v>
   </rv>
@@ -6246,8 +6246,8 @@
     <v>341.75</v>
     <v>271.85000000000002</v>
     <v>0.40989999999999999</v>
-    <v>-1.82</v>
-    <v>-6.5039999999999994E-3</v>
+    <v>-1.66</v>
+    <v>-5.9319999999999998E-3</v>
     <v>USD</v>
     <v>McDonald's Corporation is a global foodservice retailer. Its segment includes U.S., International Operated Markets, and International Developmental Licensed Markets &amp; Corporate. The U.S. segment is its largest market and is 95% franchised. The International Operated Markets segment comprises markets or countries in which it operates and franchises restaurants, including Australia, Canada, France, Germany, Italy, Poland, Spain, and the United Kingdom. This segment is 89% franchised. The International Developmental Licensed Markets &amp; Corporate segment comprises development licensee and affiliate markets, including equity method investments in China and Japan. This segment is 99% franchised. Its menu features hamburgers and cheeseburgers, the Big Mac, the Quarter Pounder with Cheese, the Filet-O-Fish, and several chicken sandwiches, such as the McChicken and McCrispy as well as Chicken McNuggets, Fries, shakes, sundaes, cookies, soft drinks, coffee, and other beverages.</v>
     <v>150000</v>
@@ -6259,20 +6259,20 @@
     <v>145</v>
     <v>Hotels &amp; Entertainment Services</v>
     <v>Stock</v>
-    <v>46181.758988171096</v>
+    <v>46181.82603943281</v>
     <v>146</v>
     <v>277.35000000000002</v>
-    <v>197534850318</v>
+    <v>197648531262</v>
     <v>MCDONALD'S CORPORATION</v>
     <v>MCDONALD'S CORPORATION</v>
     <v>278.01</v>
-    <v>22.916799999999999</v>
+    <v>22.93</v>
     <v>279.83999999999997</v>
-    <v>278.02</v>
+    <v>278.18</v>
     <v>710505900</v>
     <v>MCD</v>
     <v>MCDONALD'S CORPORATION (XNYS:MCD)</v>
-    <v>1763031</v>
+    <v>2386957</v>
     <v>4403643</v>
     <v>1964</v>
   </rv>
@@ -6318,8 +6318,8 @@
     <v>444.72</v>
     <v>196</v>
     <v>1.5269999999999999</v>
-    <v>2.7</v>
-    <v>7.698E-3</v>
+    <v>1.7749999999999999</v>
+    <v>5.0609999999999995E-3</v>
     <v>USD</v>
     <v>MongoDB, Inc. is a developer data platform company. Its developer data platform is a globally distributed operational database integrated with a set of data services that allow development teams to address the growing variety of application requirements. Its customers can implement its developer data platform as a managed service offering, or they can choose a self-managed option. Its MongoDB Atlas is its managed multi-cloud database-as-a-service (DBaaS) offering that includes an integrated set of databases and related services. Atlas Vector Search allows the integration of an operational database and vector search in a unified, fully managed platform. MongoDB Enterprise Advanced is its proprietary self-managed commercial offering for enterprise customers that can run in the cloud, on-premises or in a hybrid environment. It also provides professional services for its customers.</v>
     <v>5636</v>
@@ -6331,20 +6331,20 @@
     <v>152</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46181.75896818281</v>
+    <v>46181.825996539061</v>
     <v>153</v>
     <v>344.14010000000002</v>
-    <v>28427861339</v>
+    <v>28353461803</v>
     <v>MONGODB, INC.</v>
     <v>MONGODB, INC.</v>
     <v>348.74</v>
     <v>0</v>
     <v>350.74</v>
-    <v>353.44</v>
+    <v>352.51499999999999</v>
     <v>80431930</v>
     <v>MDB</v>
     <v>MONGODB, INC. (XNAS:MDB)</v>
-    <v>1184915</v>
+    <v>1361915</v>
     <v>2743891</v>
     <v>2007</v>
   </rv>
@@ -6370,8 +6370,8 @@
     <v>796.25</v>
     <v>520.26</v>
     <v>1.2386999999999999</v>
-    <v>-5.57</v>
-    <v>-9.3930000000000003E-3</v>
+    <v>-3.43</v>
+    <v>-5.7840000000000001E-3</v>
     <v>USD</v>
     <v>Meta Platforms, Inc. is building human connections, powered by artificial intelligence and immersive technologies. The Company's products enable people to connect and share with friends and family through mobile devices, personal computers, virtual reality (VR) and mixed reality (MR) headsets, augmented reality (AR), and wearables. It also helps people discover and learn about what is going on in the world around them, enabling people to share their experiences, ideas, photos, videos, and other content with audiences ranging from their closest family members and friends to the public at large. The Company's segments include Family of Apps (FoA) and Reality Labs (RL). FoA segment includes Facebook, Instagram, Messenger, WhatsApp and Threads. RL segment includes its virtual, augmented, and mixed reality related consumer hardware, software and content. Its product offerings in VR include its Meta Quest devices, as well as software and content available through the Meta Horizon Store.</v>
     <v>77986</v>
@@ -6382,20 +6382,20 @@
     <v>592</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46181.758963703127</v>
+    <v>46181.826033089841</v>
     <v>156</v>
     <v>579.22</v>
-    <v>1491145822889</v>
+    <v>1496578048110</v>
     <v>META PLATFORMS, INC.</v>
     <v>META PLATFORMS, INC.</v>
     <v>590.64</v>
-    <v>17.817599999999999</v>
+    <v>17.8826</v>
     <v>593</v>
-    <v>587.42999999999995</v>
+    <v>589.57000000000005</v>
     <v>2538423000</v>
     <v>META</v>
     <v>META PLATFORMS, INC. (XNAS:META)</v>
-    <v>8993627</v>
+    <v>10708591</v>
     <v>16894180</v>
     <v>2004</v>
   </rv>
@@ -6421,8 +6421,8 @@
     <v>324.2</v>
     <v>61.44</v>
     <v>2.1796000000000002</v>
-    <v>37.11</v>
-    <v>0.140851</v>
+    <v>27.89</v>
+    <v>0.10585599999999999</v>
     <v>USD</v>
     <v>Marvell Technology, Inc. together with its consolidated subsidiaries, is a supplier of data infrastructure semiconductor solutions, spanning the data center core to network edge. It is engaged in the design, development and sale of integrated circuits. Its product offerings include custom application-specific integrated circuits (ASICs), interconnects, ethernet solutions, fiber channel adapters, processors and storage controllers. In addition, it is also developing Ultra Accelerator LinkTM (UALinkTM) switches and ethernet for scale-up networking (ESUN) switches for the emerging scale-out artificial intelligence market. Its solutions integrate multiple analogs, mixed-signal and digital intellectual property components incorporating hardware, firmware and software technologies and its system knowledge to provide its customers with integrated solutions for their end products. It designs and manufactures photonic integrated circuits for ultra-high-bandwidth and low-power applications.</v>
     <v>7480</v>
@@ -6433,20 +6433,20 @@
     <v>304.95999999999998</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46181.75899583281</v>
+    <v>46181.826047303126</v>
     <v>159</v>
     <v>281.36</v>
-    <v>262947384000</v>
+    <v>254881728000</v>
     <v>MARVELL TECHNOLOGY, INC.</v>
     <v>MARVELL TECHNOLOGY, INC.</v>
     <v>288.66000000000003</v>
-    <v>102.956</v>
+    <v>99.797899999999998</v>
     <v>263.47000000000003</v>
-    <v>300.58</v>
+    <v>291.36</v>
     <v>874800000</v>
     <v>MRVL</v>
     <v>MARVELL TECHNOLOGY, INC. (XNAS:MRVL)</v>
-    <v>61583056</v>
+    <v>73446248</v>
     <v>39878362</v>
     <v>2020</v>
   </rv>
@@ -6488,8 +6488,8 @@
     <v>555.45000000000005</v>
     <v>356.28</v>
     <v>1.1158999999999999</v>
-    <v>-4.3499999999999996</v>
-    <v>-1.044E-2</v>
+    <v>-3.83</v>
+    <v>-9.1920000000000005E-3</v>
     <v>USD</v>
     <v>Microsoft Corporation is a technology company. The Company develops and supports software, services, devices, and solutions. The Company’s segments include Productivity and Business Processes, Intelligent Cloud, and More Personal Computing. The Productivity and Business Processes segment consists of products and services in its portfolio of productivity, communication, and information services. This segment primarily comprises: Office Commercial, Office Consumer, LinkedIn, and Dynamics business solutions. The Intelligent Cloud segment consists of server products and cloud services, including Azure and other cloud services, SQL Server, Windows Server, Visual Studio, System Center, and related Client Access Licenses (CALs), and Nuance and GitHub; and Enterprise Services, including enterprise support services, industry solutions and Nuance professional services. The More Personal Computing segment primarily comprises Windows, Devices, Gaming, and search and news advertising.</v>
     <v>228000</v>
@@ -6501,20 +6501,20 @@
     <v>164</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46181.758975080469</v>
+    <v>46181.826041828128</v>
     <v>165</v>
     <v>408.56</v>
-    <v>3062892319200</v>
+    <v>3066755105400</v>
     <v>MICROSOFT CORPORATION</v>
     <v>MICROSOFT CORPORATION</v>
     <v>414.1</v>
-    <v>24.5581</v>
+    <v>24.588999999999999</v>
     <v>416.67</v>
-    <v>412.32</v>
+    <v>412.84</v>
     <v>7428435000</v>
     <v>MSFT</v>
     <v>MICROSOFT CORPORATION (XNAS:MSFT)</v>
-    <v>17476438</v>
+    <v>21060799</v>
     <v>35613573</v>
     <v>1993</v>
   </rv>
@@ -6540,8 +6540,8 @@
     <v>457.22</v>
     <v>104.16500000000001</v>
     <v>3.5194000000000001</v>
-    <v>7.48</v>
-    <v>6.2106000000000001E-2</v>
+    <v>6.9249999999999998</v>
+    <v>5.7497999999999994E-2</v>
     <v>USD</v>
     <v>Strategy Inc. is a bitcoin treasury and business intelligence company. The Company provides cloud-native, artificial intelligence (AI)-powered enterprise analytics software to thousands of global customers. Its Software Business segment is engaged in the design, development, marketing, and sales of enterprise analytics software platform through cloud subscriptions and licensing arrangements and related services. Its Strategy ONE platform provides access to AI-powered workflows, unlimited data sources, cloud-native technologies, and performance to speed up time from data to action. Strategy One delivers visualization, reporting, and embedded analytics capabilities across retail, banking, technology, manufacturing, insurance, consulting, healthcare, public sector, and others. Its Strategy Mosaic is a universal intelligence layer that provides enterprises with consistent definitions and governance across data sources, regardless of where that data resides or which tools access it.</v>
     <v>1511</v>
@@ -6552,20 +6552,20 @@
     <v>129</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46181.758922522655</v>
+    <v>46181.825977128909</v>
     <v>168</v>
     <v>123.145</v>
-    <v>45820675368</v>
+    <v>45621875533</v>
     <v>STRATEGY INC</v>
     <v>STRATEGY INC</v>
     <v>126.02</v>
     <v>0</v>
     <v>120.44</v>
-    <v>127.92</v>
+    <v>127.36499999999999</v>
     <v>358197900</v>
     <v>MSTR</v>
     <v>STRATEGY INC (XNAS:MSTR)</v>
-    <v>13978206</v>
+    <v>16458677</v>
     <v>17546194</v>
     <v>1989</v>
   </rv>
@@ -6591,8 +6591,8 @@
     <v>1089.29</v>
     <v>103.38</v>
     <v>2.1979000000000002</v>
-    <v>89.44</v>
-    <v>0.103517</v>
+    <v>72.8</v>
+    <v>8.4258E-2</v>
     <v>USD</v>
     <v>Micron Technology, Inc. provides memory and storage solutions. The Company delivers a portfolio of high-performance dynamic random-access memory (DRAM), NAND, and NOR memory and storage products through its Micron and Crucial brands. The Company's products enable advancing in artificial intelligence (AI) and compute-intensive applications. Its segments include Cloud Memory Business Unit (CMBU), Core Data Center Business Unit (CDBU), Mobile and Client Business Unit (MCBU) and Automotive and Embedded Business Unit (AEBU). CMBU is focused on memory solutions for large hyperscale cloud customers, and high bandwidth memory (HBM) for all data center customers. CDBU is focused on memory solutions for mid-tier cloud, enterprise, and OEM data center customers and storage solutions for all data center customers. MCBU is focused on memory and storage solutions for mobile and client segments. AEBU is focused on memory and storage solutions for the automotive, industrial, and consumer segments.</v>
     <v>53000</v>
@@ -6603,20 +6603,20 @@
     <v>962.95</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46181.758937175779</v>
+    <v>46181.825993876562</v>
     <v>171</v>
     <v>916.5</v>
-    <v>1075237982300</v>
+    <v>1056472488539</v>
     <v>MICRON TECHNOLOGY, INC.</v>
     <v>MICRON TECHNOLOGY, INC.</v>
     <v>941.92</v>
-    <v>45.013800000000003</v>
+    <v>44.228200000000001</v>
     <v>864.01</v>
-    <v>953.45</v>
+    <v>936.81</v>
     <v>1127734000</v>
     <v>MU</v>
     <v>MICRON TECHNOLOGY, INC. (XNAS:MU)</v>
-    <v>39949230</v>
+    <v>47167463</v>
     <v>55357582</v>
     <v>1984</v>
   </rv>
@@ -6642,8 +6642,8 @@
     <v>276.815</v>
     <v>158.83000000000001</v>
     <v>1.6554</v>
-    <v>-1.97</v>
-    <v>-7.8770000000000003E-3</v>
+    <v>-2.5295999999999998</v>
+    <v>-1.0114000000000001E-2</v>
     <v>USD</v>
     <v>Cloudflare, Inc. is a connectivity cloud company. The Company delivers a range of services to businesses of all sizes and in all geographies, enhancing the performance of business-critical applications. Its full suite of products consists of application services that help deliver security, performance, and reliability for any organization's applications connected to the Internet, including Websites and application programming interfaces (APIs) and its secure access service edge (SASE) platform, which contains its suite of and workplace security services and network services solutions to help ensure traffic in and out of an organization’s network and devices is verified and authorized and data is protected and secured, as well as to securely connect data centers, cloud services, and branch offices to an organization with its connectivity cloud. The Company also offers developer-based solutions which build and deploys serverless and artificial intelligence applications.</v>
     <v>5483</v>
@@ -6654,19 +6654,19 @@
     <v>254.62799999999999</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46181.758879108595</v>
+    <v>46181.825942742966</v>
     <v>174</v>
     <v>246.01</v>
-    <v>87709102868</v>
+    <v>87511303182</v>
     <v>CLOUDFLARE, INC.</v>
     <v>CLOUDFLARE, INC.</v>
     <v>253.16</v>
     <v>250.11</v>
-    <v>248.14</v>
+    <v>247.5804</v>
     <v>353466200</v>
     <v>NET</v>
     <v>CLOUDFLARE, INC. (XNYS:NET)</v>
-    <v>1692810</v>
+    <v>2501060</v>
     <v>5102124</v>
     <v>2009</v>
   </rv>
@@ -6702,7 +6702,7 @@
     <v>37.945</v>
     <v>Textiles &amp; Apparel</v>
     <v>Stock</v>
-    <v>46181.747916666667</v>
+    <v>46181.81527777778</v>
     <v>177</v>
     <v>36.979999999999997</v>
     <v>98149420000</v>
@@ -6751,8 +6751,8 @@
     <v>17.45</v>
     <v>4</v>
     <v>1.1538999999999999</v>
-    <v>0.27500000000000002</v>
-    <v>1.9124000000000002E-2</v>
+    <v>0.155</v>
+    <v>1.0779E-2</v>
     <v>USD</v>
     <v>Nokia Oyj is a Finland-based company engaged in the network and Internet protocol (IP) infrastructure, software, and related services market. The Company's businesses include Nokia Networks and Nokia Technologies. The Company's segments include Ultra Broadband Networks, IP Networks and Applications, and Nokia Technologies. The Ultra Broadband Networks segment comprises Mobile Networks and Fixed Networks operating segments. The IP Networks and Applications segment comprises IP/Optical Networks and Applications &amp; Analytics operating segments. The Applications &amp; Analytics operating segment offers software solutions spanning customer experience management, network operations and management, communications and collaboration, policy and charging, as well as Cloud, Internet of things (IoT), security, and analytics platforms that enable digital services providers and enterprises to accelerate and optimize their customer experience. The Company has Comptel Oyj among its subsidiaries.</v>
     <v>77586</v>
@@ -6763,20 +6763,20 @@
     <v>15.06</v>
     <v>Communications &amp; Networking</v>
     <v>Stock</v>
-    <v>46181.758973483593</v>
+    <v>46181.826048171097</v>
     <v>182</v>
     <v>14.445</v>
-    <v>84152527200</v>
+    <v>83463458400</v>
     <v>Nokia Oyj</v>
     <v>Nokia Oyj</v>
     <v>14.86</v>
-    <v>91.081400000000002</v>
+    <v>90.335599999999999</v>
     <v>14.38</v>
-    <v>14.654999999999999</v>
+    <v>14.535</v>
     <v>5742240000</v>
     <v>NOK</v>
     <v>Nokia Oyj (XNYS:NOK)</v>
-    <v>84324029</v>
+    <v>97159904</v>
     <v>124889753</v>
     <v>1997</v>
   </rv>
@@ -6802,8 +6802,8 @@
     <v>211.47800000000001</v>
     <v>81.239999999999995</v>
     <v>0.94669999999999999</v>
-    <v>2.37</v>
-    <v>2.1076000000000001E-2</v>
+    <v>2.4998999999999998</v>
+    <v>2.2231000000000001E-2</v>
     <v>USD</v>
     <v>ServiceNow, Inc. provides an artificial intelligence (AI) platform for business transformation. The Company’s AI platform connects people, processes, data, and devices to increase productivity and maximize business outcomes. Its intelligent platform, the Now Platform, is a cloud-based solution that helps enterprises and organizations across public and private sectors digitize workflows. The workflow applications built on the Now Platform are organized into four primary areas: Technology, CRM and Industry, Core Business and Creator. Its products include IT Service Management, IT Operations Management, HR Service Delivery, ServiceNow AI Agents, AI Experience, Build Agent, ServiceNow AI Control Tower, AI Agent Fabric, RaptorDB, Workflow Data Fabric, Workplace Service Delivery, ServiceNow Platform Encryption, Telecommunications Service Operations Management, and others. The Company also offers identity security, helping organizations secure access across the enterprise.</v>
     <v>29187</v>
@@ -6814,20 +6814,20 @@
     <v>115.36</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46181.758879594534</v>
+    <v>46181.825956562498</v>
     <v>185</v>
     <v>111.2</v>
-    <v>118414784560</v>
+    <v>118548751469</v>
     <v>SERVICENOW, INC.</v>
     <v>SERVICENOW, INC.</v>
     <v>111.37</v>
-    <v>68.288300000000007</v>
+    <v>68.365600000000001</v>
     <v>112.45</v>
-    <v>114.82</v>
+    <v>114.9499</v>
     <v>1031308000</v>
     <v>NOW</v>
     <v>SERVICENOW, INC. (XNYS:NOW)</v>
-    <v>13131042</v>
+    <v>15931641</v>
     <v>32799040</v>
     <v>2012</v>
   </rv>
@@ -6853,8 +6853,8 @@
     <v>236.54</v>
     <v>140.85499999999999</v>
     <v>2.2010999999999998</v>
-    <v>3.87</v>
-    <v>1.8869E-2</v>
+    <v>2.7349999999999999</v>
+    <v>1.3335E-2</v>
     <v>USD</v>
     <v>NVIDIA Corporation is an artificial intelligence (AI) infrastructure company. The Company is engaged in accelerated computing to help solve the challenging computational problems. Its segments include Compute &amp; Networking and Graphics. The Compute &amp; Networking segment includes its Data Center accelerated computing and networking platforms and AI solutions and software, and automotive platforms and autonomous and electric vehicle solutions, including software. The Graphics segment includes GeForce GPUs for gaming and personal computers (PCs), and Quadro/NVIDIA RTX GPUs for enterprise workstation graphics. Its technology stack includes the foundational NVIDIA CUDA development platform that runs on all NVIDIA GPUs, as well as hundreds of domain-specific software libraries, frameworks, algorithms, software development kits (SDKs), and application programming interfaces (APIs). Its platforms address four markets, which include Data Center, Gaming, Professional Visualization, and Automotive.</v>
     <v>42000</v>
@@ -6865,20 +6865,20 @@
     <v>210.46</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46181.758916353909</v>
+    <v>46181.825983159375</v>
     <v>188</v>
     <v>206</v>
-    <v>5057074000000</v>
+    <v>5029607000000</v>
     <v>NVIDIA CORPORATION</v>
     <v>NVIDIA CORPORATION</v>
     <v>210</v>
-    <v>32.0015</v>
+    <v>31.8277</v>
     <v>205.1</v>
-    <v>208.97</v>
+    <v>207.83500000000001</v>
     <v>24200000000</v>
     <v>NVDA</v>
     <v>NVIDIA CORPORATION (XNAS:NVDA)</v>
-    <v>92076976</v>
+    <v>107341423</v>
     <v>171225555</v>
     <v>1998</v>
   </rv>
@@ -6904,8 +6904,8 @@
     <v>134.91999999999999</v>
     <v>44.56</v>
     <v>1.9728000000000001</v>
-    <v>5.22</v>
-    <v>4.4516E-2</v>
+    <v>4.09</v>
+    <v>3.4880000000000001E-2</v>
     <v>USD</v>
     <v>ON Semiconductor Corporation is engaged in providing intelligent power and intelligent sensing solutions. The Company’s intelligent power technologies enable the electrification of drivetrain in the automotive industry to allow for lighter and longer-range electric vehicles. Its segments include Power Solutions Group (PSG), the Analog and Mixed-Signal Group (AMG) and the Intelligent Sensing Group (ISG). PSG segment provides a portfolio of discrete, module, and integrated semiconductor devices designed to enable conversion across artificial intelligence (AI) data centers, energy infrastructure, automotive and industrial. AMG segment designs and develops a range of analog and mixed-signal solutions including power‑management, sensor‑interface, connectivity, and products that serve automotive, industrial automation, AI data center, computing, and mobile end markets.</v>
     <v>22600</v>
@@ -6916,20 +6916,20 @@
     <v>124.53</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46181.758901503905</v>
+    <v>46181.82596407344</v>
     <v>191</v>
     <v>119.84</v>
-    <v>48000303936</v>
+    <v>47557453320</v>
     <v>ON SEMICONDUCTOR CORPORATION</v>
     <v>ON SEMICONDUCTOR CORPORATION</v>
     <v>122.57</v>
-    <v>87.460700000000003</v>
+    <v>86.653800000000004</v>
     <v>117.26</v>
-    <v>122.48</v>
+    <v>121.35</v>
     <v>391903200</v>
     <v>ON</v>
     <v>ON SEMICONDUCTOR CORPORATION (XNAS:ON)</v>
-    <v>5973169</v>
+    <v>8388512</v>
     <v>13048433</v>
     <v>2000</v>
   </rv>
@@ -6955,8 +6955,8 @@
     <v>15.28</v>
     <v>1.36</v>
     <v>2.6793</v>
-    <v>7.0000000000000007E-2</v>
-    <v>6.711E-3</v>
+    <v>-0.125</v>
+    <v>-1.1984999999999999E-2</v>
     <v>USD</v>
     <v>Ondas Inc. is a provider of autonomous systems, robotics, and mission-critical connectivity solutions for defense, security, and industrial markets. Through its business units, Ondas Autonomous Systems (OAS), Ondas Capital and Ondas Networks, it develops and deploys integrated technologies that deliver advanced sensing, mobility, and communications capabilities. OAS delivers a portfolio of artificial-intelligence (AI)-powered defense and security platforms to protect sensitive sites, populations, and critical infrastructure. OAS also provides an integrated suite of autonomous aerial, ground, and counter-UAS solutions through its operating companies. It also provides Airborne Missile Protection Systems (AMPS) and airborne intelligence, surveillance and reconnaissance (ISR) solutions for the military, government and others. It also specializes in the procurement, integration, and lifecycle support of heavy engineering equipment for military and national infrastructure programs.</v>
     <v>459</v>
@@ -6967,20 +6967,20 @@
     <v>10.84</v>
     <v>Communications &amp; Networking</v>
     <v>Stock</v>
-    <v>46181.758914628903</v>
+    <v>46181.825999756249</v>
     <v>194</v>
-    <v>10.365</v>
-    <v>5329851450</v>
+    <v>10.25</v>
+    <v>5230868494</v>
     <v>ONDAS INC.</v>
     <v>ONDAS INC.</v>
     <v>10.84</v>
-    <v>26.475000000000001</v>
+    <v>25.9834</v>
     <v>10.43</v>
-    <v>10.5</v>
+    <v>10.305</v>
     <v>507604900</v>
     <v>ONDS</v>
     <v>ONDAS INC. (XNAS:ONDS)</v>
-    <v>28451220</v>
+    <v>35683679</v>
     <v>82580678</v>
     <v>2014</v>
   </rv>
@@ -7022,8 +7022,8 @@
     <v>345.72</v>
     <v>134.57</v>
     <v>1.6594</v>
-    <v>-0.6</v>
-    <v>-2.8079999999999997E-3</v>
+    <v>-1.41</v>
+    <v>-6.5990000000000007E-3</v>
     <v>USD</v>
     <v>Oracle Corporation offers integrated suites of applications plus secure, autonomous infrastructure in the Oracle Cloud. The Company operates through three businesses: cloud and license, hardware and service. Its cloud and license business is engaged in the sale, marketing and delivery of its enterprise applications and infrastructure technologies through cloud and on-premise deployment models including its cloud services and license support offerings, and its cloud license and on-premise license offerings. Its hardware business provides infrastructure technologies including Oracle Engineered Systems, servers, storage, industry-specific hardware, operating systems, virtualization, management and other hardware-related software to support diverse IT environments. Its services business provides services to customers and partners to help maximize the performance of their investments in Oracle applications and infrastructure technologies.</v>
     <v>162000</v>
@@ -7035,20 +7035,20 @@
     <v>199</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46181.75898615703</v>
+    <v>46181.826033448437</v>
     <v>200</v>
     <v>209.33099999999999</v>
-    <v>612827881680</v>
+    <v>610498284420</v>
     <v>ORACLE CORPORATION</v>
     <v>ORACLE CORPORATION</v>
     <v>217.72</v>
-    <v>36.115900000000003</v>
+    <v>35.9786</v>
     <v>213.68</v>
-    <v>213.08</v>
+    <v>212.27</v>
     <v>2876046000</v>
     <v>ORCL</v>
     <v>ORACLE CORPORATION (XNYS:ORCL)</v>
-    <v>12506811</v>
+    <v>14747163</v>
     <v>23006166</v>
     <v>2005</v>
   </rv>
@@ -7074,8 +7074,8 @@
     <v>302.95</v>
     <v>139.57060000000001</v>
     <v>0.95150000000000001</v>
-    <v>-4.6399999999999997</v>
-    <v>-1.7056000000000002E-2</v>
+    <v>-5.83</v>
+    <v>-2.1429999999999998E-2</v>
     <v>USD</v>
     <v>Palo Alto Networks, Inc. is a global artificial intelligence (AI) cybersecurity company, with a comprehensive portfolio of cybersecurity solutions and platforms across network, cloud, security operations, AI and Identity. Its network security platform includes Secure Access Service Edge (SASE), Next-Generation Firewalls, Cloud Delivered Security Services (CDSS), Prisma AIRS, and Strata Cloud Manager (SCM). It delivers security operations capabilities that unifies standalone Security Information and Event Management (SIEM) tools, endpoint security, security automation, cloud detection and response (CDR), as well as attack surface management (ASM) capabilities on its Cortex platform. It delivers comprehensive security across the cloud application development lifecycle through Cortex Cloud. Its Unit 42 brings together expertise across threat research, incident response, and security consulting to deliver intelligence-driven, response-ready outcomes that help customers reduce cyber risk.</v>
     <v>21491</v>
@@ -7086,20 +7086,20 @@
     <v>273.05</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46181.758976620309</v>
+    <v>46181.826059964842</v>
     <v>203</v>
     <v>264.42</v>
-    <v>217939150000</v>
+    <v>216969300000</v>
     <v>PALO ALTO NETWORKS, INC.</v>
     <v>PALO ALTO NETWORKS, INC.</v>
     <v>269.76</v>
-    <v>220.18109999999999</v>
+    <v>219.2013</v>
     <v>272.05</v>
-    <v>267.41000000000003</v>
+    <v>266.22000000000003</v>
     <v>815000000</v>
     <v>PANW</v>
     <v>PALO ALTO NETWORKS, INC. (XNAS:PANW)</v>
-    <v>3770185</v>
+    <v>4709365</v>
     <v>9446561</v>
     <v>2005</v>
   </rv>
@@ -7137,7 +7137,7 @@
     <v>11.24</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46181.758948448434</v>
+    <v>46181.826027892967</v>
     <v>206</v>
     <v>10.9</v>
     <v>5805537961</v>
@@ -7150,7 +7150,7 @@
     <v>518120300</v>
     <v>PATH</v>
     <v>UIPATH, INC. (XNYS:PATH)</v>
-    <v>21825731</v>
+    <v>34354214</v>
     <v>41596067</v>
     <v>2015</v>
   </rv>
@@ -7176,8 +7176,8 @@
     <v>167.25</v>
     <v>137.62</v>
     <v>0.37519999999999998</v>
-    <v>-1.0999000000000001</v>
-    <v>-7.5060000000000005E-3</v>
+    <v>-1.3</v>
+    <v>-8.8710000000000004E-3</v>
     <v>USD</v>
     <v>The Procter &amp; Gamble Company is focused on providing branded consumer packaged goods to consumers across the world. The Company’s segments include Beauty, Grooming, Health Care, Fabric &amp; Home Care and Baby, Feminine &amp; Family Care. The Company’s products are sold in approximately 180 countries and territories primarily through mass merchandisers, e-commerce, including social commerce channels, grocery stores, membership club stores, drug stores, department stores, distributors, wholesalers, specialty beauty stores, including airport duty-free stores), high-frequency stores, pharmacies, electronics stores and professional channels. It also sells direct to individual consumers. It has operations in approximately 70 countries. It offers products under brands, such as Head &amp; Shoulders, Herbal Essences, Pantene, Rejoice, Olay, Old Spice, Safeguard, Secret, SK-II, Braun, Gillette, Venus, Crest, Oral-B, Ariel, Downy, Gain, Tide, Always, Always Discreet, Tampax, Bounty and others.</v>
     <v>109000</v>
@@ -7188,20 +7188,20 @@
     <v>146.55000000000001</v>
     <v>Personal &amp; Household Products &amp; Services</v>
     <v>Stock</v>
-    <v>46181.758914964841</v>
+    <v>46181.825993749997</v>
     <v>209</v>
     <v>145.05000000000001</v>
-    <v>338671671419</v>
+    <v>338205718760</v>
     <v>THE PROCTER &amp; GAMBLE COMPANY</v>
     <v>THE PROCTER &amp; GAMBLE COMPANY</v>
     <v>145.53</v>
-    <v>21.270600000000002</v>
+    <v>21.241399999999999</v>
     <v>146.54</v>
-    <v>145.4401</v>
+    <v>145.24</v>
     <v>2328599000</v>
     <v>PG</v>
     <v>THE PROCTER &amp; GAMBLE COMPANY (XNYS:PG)</v>
-    <v>2976290</v>
+    <v>3914585</v>
     <v>8560487</v>
     <v>1905</v>
   </rv>
@@ -7227,8 +7227,8 @@
     <v>56</v>
     <v>18</v>
     <v>1.3917999999999999</v>
-    <v>1.2050000000000001</v>
-    <v>4.1338E-2</v>
+    <v>0.69</v>
+    <v>2.3671000000000001E-2</v>
     <v>USD</v>
     <v>Photronics, Inc. is a manufacturer of photomasks, which are high-precision photographic quartz or glass plates containing microscopic images of electronic circuits. The Company manufactures photomasks, which are used as masters to transfer circuit patterns onto semiconductor wafers and FPD substrates. The photomasks the Company manufactures incorporate circuit designs provided on a confidential basis by its customers. The Company sells its photomasks to semiconductor designers and manufacturers, and manufacturers of FPDs. Photomask technology is also being applied to the fabrication of other higher-performance electronic products such as virtual reality/augmented reality advanced IC packages, photonics, micro-electronic mechanical systems, and certain nanotechnology applications. The Company operates approximately 11 manufacturing facilities, which are located in Taiwan, China, Korea, the United States, and Europe.</v>
     <v>1908</v>
@@ -7239,20 +7239,20 @@
     <v>30.96</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46181.758994930467</v>
+    <v>46181.826017800784</v>
     <v>212</v>
     <v>29.31</v>
-    <v>1789924768</v>
+    <v>1759557077</v>
     <v>PHOTRONICS, INC.</v>
     <v>PHOTRONICS, INC.</v>
     <v>30.57</v>
-    <v>11.117000000000001</v>
+    <v>10.9284</v>
     <v>29.15</v>
-    <v>30.355</v>
+    <v>29.84</v>
     <v>58966390</v>
     <v>PLAB</v>
     <v>PHOTRONICS, INC. (XNAS:PLAB)</v>
-    <v>1206206</v>
+    <v>1548575</v>
     <v>1801489</v>
     <v>1969</v>
   </rv>
@@ -7278,8 +7278,8 @@
     <v>20.81</v>
     <v>3.87</v>
     <v>0.74539999999999995</v>
-    <v>0.63500000000000001</v>
-    <v>5.3540999999999998E-2</v>
+    <v>0.32500000000000001</v>
+    <v>2.7403E-2</v>
     <v>USD</v>
     <v>POET Technologies Inc. is a design and development company. It offers high-speed optical engines, light source products and custom optical modules to the artificial intelligence (AI) systems market and to hyperscale data centers. Its photonic integration solutions are based on the POET Optical Interposer, a novel, patented platform that allows the integration of electronic and photonic devices into a single chip using wafer-level semiconductor manufacturing techniques. Its Optical Interposer-based products consume less power than comparable products, are smaller in size and are readily scalable to high production volumes. In addition, it has designed and produced novel light source products for chip-to-chip data communication within and between AI servers, the next frontier for solving bandwidth and latency problems in AI systems. Its Optical Interposer platform solves device integration challenges across a range of communication, computing and sensing applications.</v>
     <v>180</v>
@@ -7290,20 +7290,20 @@
     <v>13.07</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46181.758940798434</v>
+    <v>46181.825984397656</v>
     <v>215</v>
     <v>11.77</v>
-    <v>2156579523</v>
+    <v>2103074949</v>
     <v>POET Technologies Inc.</v>
     <v>POET Technologies Inc.</v>
     <v>12.26</v>
     <v>0</v>
     <v>11.86</v>
-    <v>12.494999999999999</v>
+    <v>12.185</v>
     <v>172595400</v>
     <v>POET</v>
     <v>POET Technologies Inc. (XNAS:POET)</v>
-    <v>21413310</v>
+    <v>24883865</v>
     <v>56812072</v>
     <v>2010</v>
   </rv>
@@ -7345,8 +7345,8 @@
     <v>259.92</v>
     <v>121.99</v>
     <v>1.6242000000000001</v>
-    <v>4.2343999999999999</v>
-    <v>1.9609000000000001E-2</v>
+    <v>0.62</v>
+    <v>2.8710000000000003E-3</v>
     <v>USD</v>
     <v>Qualcomm Incorporated is engaged in the development and commercialization of foundational technologies for the wireless industry, including third generation (3G), fourth generation (4G) and fifth generation (5G) wireless connectivity, and high-performance and low-power computing, including on-device artificial intelligence. Its segments include Qualcomm CDMA Technologies (QCT), Qualcomm Technology Licensing (QTL) and Qualcomm Strategic Initiatives. QCT develops and supplies integrated circuits and system software based on 3G/4G/5G and other technologies, including radio frequency front-end, digital cockpit and advanced driver assistance and automated driving, Internet of things including consumer electronic devices, industrial devices and edge networking products. QTL grants licenses or otherwise provides rights to use portions of its intellectual property portfolio that includes certain patent rights essential to and/or useful in the manufacture and sale of certain wireless products.</v>
     <v>52000</v>
@@ -7358,20 +7358,20 @@
     <v>220</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46181.758989918751</v>
+    <v>46181.826027858595</v>
     <v>221</v>
     <v>214.63</v>
-    <v>232063817600</v>
+    <v>228254240000</v>
     <v>QUALCOMM INCORPORATED</v>
     <v>QUALCOMM INCORPORATED</v>
     <v>220.86</v>
-    <v>23.949200000000001</v>
+    <v>23.556000000000001</v>
     <v>215.94</v>
-    <v>220.17439999999999</v>
+    <v>216.56</v>
     <v>1054000000</v>
     <v>QCOM</v>
     <v>QUALCOMM INCORPORATED (XNAS:QCOM)</v>
-    <v>9964355</v>
+    <v>11641443</v>
     <v>27227337</v>
     <v>1991</v>
   </rv>
@@ -7397,8 +7397,8 @@
     <v>155.47</v>
     <v>74.510000000000005</v>
     <v>0.64410000000000001</v>
-    <v>-0.23</v>
-    <v>-2.0930000000000002E-3</v>
+    <v>-0.13500000000000001</v>
+    <v>-1.2280000000000001E-3</v>
     <v>USD</v>
     <v>Qualys, Inc. is a provider of a cloud-based platform delivering information technology (IT), security and compliance solutions. The Company’s integrated suite of IT, security and compliance solutions delivered on Qualys' Enterprise TruRisk Platform enables its customers to identify and manage their IT and operational technology (OT) assets, collect, and analyze large amounts of IT security data, recommend, and implement remediation actions and verify the implementation of such actions. The Company provides its solutions through a software-as-a-service model, primarily with renewable annual subscriptions. Its cloud platform offers an integrated suite of solutions that automates the lifecycle of asset discovery and management, security and compliance assessments, and remediation for an organization’s IT infrastructure and assets, whether such infrastructure and assets reside inside the organization, on their network perimeter, on endpoints or in the cloud.</v>
     <v>2683</v>
@@ -7409,20 +7409,20 @@
     <v>110.2</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46181.758913657031</v>
+    <v>46181.825977673434</v>
     <v>224</v>
     <v>106.75</v>
-    <v>3862249486</v>
+    <v>3865595102</v>
     <v>QUALYS, INC.</v>
     <v>QUALYS, INC.</v>
     <v>108.96</v>
-    <v>19.693300000000001</v>
+    <v>19.7104</v>
     <v>109.9</v>
-    <v>109.67</v>
+    <v>109.765</v>
     <v>35217010</v>
     <v>QLYS</v>
     <v>QUALYS, INC. (XNAS:QLYS)</v>
-    <v>218782</v>
+    <v>315101</v>
     <v>791613</v>
     <v>1999</v>
   </rv>
@@ -7448,25 +7448,25 @@
     <v>748.65</v>
     <v>523.65</v>
     <v>1.0089999999999999</v>
-    <v>13.505000000000001</v>
-    <v>1.9154000000000001E-2</v>
+    <v>10.51</v>
+    <v>1.4906999999999998E-2</v>
     <v>USD</v>
     <v>Nasdaq Stock Market</v>
     <v>XNAS</v>
     <v>1.8E-3</v>
     <v>723.02760000000001</v>
     <v>ETF</v>
-    <v>46181.758978657032</v>
+    <v>46181.826052950782</v>
     <v>227</v>
     <v>713.1</v>
     <v>493987523137.08002</v>
     <v>Invesco QQQ Trust 1</v>
     <v>717.92</v>
     <v>705.06</v>
-    <v>718.56500000000005</v>
+    <v>715.57</v>
     <v>QQQ</v>
     <v>Invesco QQQ Trust 1 (XNAS:QQQ)</v>
-    <v>32577622</v>
+    <v>41500485</v>
     <v>41284556</v>
   </rv>
   <rv s="2">
@@ -7491,8 +7491,8 @@
     <v>468.11</v>
     <v>305.44009999999997</v>
     <v>1.5501</v>
-    <v>3.73</v>
-    <v>8.3499999999999998E-3</v>
+    <v>5.0761000000000003</v>
+    <v>1.1363000000000002E-2</v>
     <v>USD</v>
     <v>Rockwell Automation, Inc. is engaged in industrial automation and digital transformation. The Company operates in three segments: Intelligent Devices, Software &amp; Control, and Lifecycle Services. The Intelligent Devices segment portfolio includes power control, motion control, safety, sensing, and industrial components, and micro control and distributed input/output. The Software &amp; Control operating segment contains a comprehensive portfolio of production automation and production operations platforms, including hardware and software. This integrated portfolio is merging information technology (IT) and operational technology (OT), bringing the benefits of the Connected Enterprise to the production system. The Lifecycle Services segment includes consulting services, including cybersecurity and digital transformation strategy and design and professional services, including global automation and information program and project management and delivery capabilities, and connected services.</v>
     <v>26000</v>
@@ -7503,20 +7503,20 @@
     <v>453.36</v>
     <v>Machinery, Equipment &amp; Components</v>
     <v>Stock</v>
-    <v>46181.758874779691</v>
+    <v>46181.825838193748</v>
     <v>230</v>
     <v>447.44</v>
-    <v>50122215516</v>
+    <v>50272001312</v>
     <v>ROCKWELL AUTOMATION, INC.</v>
     <v>ROCKWELL AUTOMATION, INC.</v>
     <v>448.22</v>
-    <v>46.793100000000003</v>
+    <v>46.933</v>
     <v>446.71</v>
-    <v>450.44</v>
+    <v>451.78609999999998</v>
     <v>111273900</v>
     <v>ROK</v>
     <v>ROCKWELL AUTOMATION, INC. (XNYS:ROK)</v>
-    <v>334996</v>
+    <v>504313</v>
     <v>814730</v>
     <v>1996</v>
   </rv>
@@ -7542,8 +7542,8 @@
     <v>7.18</v>
     <v>2.77</v>
     <v>1.0123</v>
-    <v>0</v>
-    <v>0</v>
+    <v>-2.5000000000000001E-3</v>
+    <v>-7.5410000000000006E-4</v>
     <v>USD</v>
     <v>Recursion Pharmaceuticals, Inc. is a clinical-stage TechBio company decoding biology and chemistry to industrialize drug discovery. Its Recursion Operating System (OS), a platform built across diverse technologies, enables the Company to map and navigate trillions of biological and chemical relationships within the Recursion Data Universe. The Company integrates physical and digital components as iterative loops of atoms and bits, scaling wet lab biology and chemistry data organized into virtuous cycles with computational tools to rapidly translate silico hypotheses into validated insights and novel chemistry. Its clinical programs in oncology and rare diseases include REC-617, REC-1245, REC-3565 and REC-4539. Its REC-617 is an orally bioavailable, cyclin-dependent kinase 7 (CDK7) inhibitor for the treatment of advanced solid tumors. Its REV102 program targets ectonucleotide pyrophosphatase/phosphodiesterase 1 (ENPP1), an enzyme implicated in the pathogenesis of HPP.</v>
     <v>600</v>
@@ -7554,20 +7554,20 @@
     <v>3.41</v>
     <v>Biotechnology &amp; Medical Research</v>
     <v>Stock</v>
-    <v>46181.758983321095</v>
+    <v>46181.826022106252</v>
     <v>233</v>
     <v>3.28</v>
-    <v>1756635738</v>
+    <v>1755310975</v>
     <v>RECURSION PHARMACEUTICALS, INC.</v>
     <v>RECURSION PHARMACEUTICALS, INC.</v>
     <v>3.41</v>
     <v>0</v>
     <v>3.3149999999999999</v>
-    <v>3.3149999999999999</v>
+    <v>3.3125</v>
     <v>529905200</v>
     <v>RXRX</v>
     <v>RECURSION PHARMACEUTICALS, INC. (XNAS:RXRX)</v>
-    <v>10546617</v>
+    <v>14070341</v>
     <v>19070875</v>
     <v>2013</v>
   </rv>
@@ -7593,8 +7593,8 @@
     <v>21.4</v>
     <v>11.81</v>
     <v>0.83299999999999996</v>
-    <v>-0.255</v>
-    <v>-1.5987000000000001E-2</v>
+    <v>-0.20499999999999999</v>
+    <v>-1.2853000000000002E-2</v>
     <v>USD</v>
     <v>SentinelOne, Inc. is an artificial intelligence (AI)-powered cybersecurity provider. The Company’s Singularity Platform delivers AI-powered autonomous threat prevention, detection, response, and exposure management capabilities across an organization’s endpoints, cloud workloads, and identity credentials. The Company’s Singularity platform ingests, correlates, and queries petabytes of structured and unstructured data from a myriad of ever-expanding disparate external and internal sources in real time. Its distributed AI models run both locally on every endpoint and every cloud workload, as well as on its cloud platform. The Company through PingSafe Pte. Ltd. (PingSafe), which is a cloud native application protection platform (CNAPP) to bolster its cloud security product suite. By adding PingSafe’s CNAPP to its Cloud Workload Security (CWS), it provides enterprises with a comprehensive cloud security coverage that drives security, improved posture, and autonomous protection.</v>
     <v>2700</v>
@@ -7605,19 +7605,19 @@
     <v>15.984999999999999</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46181.758981885934</v>
+    <v>46181.826070740623</v>
     <v>236</v>
     <v>15.54</v>
-    <v>5380304071</v>
+    <v>5397444256</v>
     <v>SENTINELONE, INC.</v>
     <v>SENTINELONE, INC.</v>
     <v>15.87</v>
     <v>15.95</v>
-    <v>15.695</v>
+    <v>15.744999999999999</v>
     <v>342803700</v>
     <v>S</v>
     <v>SENTINELONE, INC. (XNYS:S)</v>
-    <v>3556133</v>
+    <v>4558351</v>
     <v>9857531</v>
     <v>2013</v>
   </rv>
@@ -7655,7 +7655,7 @@
     <v>161.08000000000001</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46181.746990740743</v>
+    <v>46181.815532407411</v>
     <v>239</v>
     <v>157.32</v>
     <v>262224200000</v>
@@ -7668,7 +7668,7 @@
     <v>1228504000</v>
     <v>SAP</v>
     <v>SAP SE (XETR:SAP)</v>
-    <v>2043878</v>
+    <v>2043989</v>
     <v>3211530</v>
     <v>2014</v>
   </rv>
@@ -7694,8 +7694,8 @@
     <v>107.5</v>
     <v>83.96</v>
     <v>0.76190000000000002</v>
-    <v>-0.12</v>
-    <v>-1.351E-3</v>
+    <v>-0.48</v>
+    <v>-5.4029999999999998E-3</v>
     <v>USD</v>
     <v>The Charles Schwab Corporation is a savings and loan holding company. The Company, through its subsidiaries, engages in wealth management, securities brokerage, banking, asset management, custody, and financial advisory services. The Company provides financial services to individuals and institutional clients through two segments: Investor Services, and Advisor Services. The Investor Services segment provides retail brokerage, investment advisory, and banking and trust services to individual investors, and retirement plan and business services, as well as other corporate brokerage services, to businesses and their employees. The Advisor Services segment provides custodial, trading, banking and trust, and support services to independent registered investment advisors (RIAs), independent retirement advisors, and recordkeepers. Its products and services include brokerage, mutual funds, exchange-traded funds (ETFs), managed investing solutions, alternative investments, banking, and trust.</v>
     <v>33500</v>
@@ -7706,20 +7706,20 @@
     <v>88.92</v>
     <v>Investment Banking &amp; Investment Services</v>
     <v>Stock</v>
-    <v>46181.758986700785</v>
+    <v>46181.826051515622</v>
     <v>242</v>
     <v>87.77</v>
-    <v>154296057200</v>
+    <v>153669968600</v>
     <v>THE CHARLES SCHWAB CORPORATION</v>
     <v>THE CHARLES SCHWAB CORPORATION</v>
     <v>88.28</v>
-    <v>17.593399999999999</v>
+    <v>17.521999999999998</v>
     <v>88.84</v>
-    <v>88.72</v>
+    <v>88.36</v>
     <v>1739135000</v>
     <v>SCHW</v>
     <v>THE CHARLES SCHWAB CORPORATION (XNYS:SCHW)</v>
-    <v>3699177</v>
+    <v>5358193</v>
     <v>11200426</v>
     <v>1986</v>
   </rv>
@@ -7799,8 +7799,8 @@
     <v>39.93</v>
     <v>8.18</v>
     <v>3.3321999999999998</v>
-    <v>1.9</v>
-    <v>5.4332000000000005E-2</v>
+    <v>1.62</v>
+    <v>4.6325000000000005E-2</v>
     <v>USD</v>
     <v>SkyWater Technology, Inc. is an independent, pure-play technology foundry that offers advanced semiconductor development and manufacturing services. The Company’s Technology-as-a-Service (TaaS) model leverages a foundation of proprietary technology, engineering know-how capabilities, and microelectronics manufacturing capacity to co-develop process technology intellectual property (IP) with its customers that enable disruptive concepts through its Advanced Technology Services (ATS) for diverse microelectronics (integrated circuits (ICs)) and related micro- and nanotechnology applications. In addition to differentiated technology development services, it supports customers with volume production of ICs for high-growth markets through its Wafer Services. Its Wafer Services include the manufacture of silicon-based analog and mixed-signal ICs for its end markets. Through its ATS model, it specializes in co-creating advanced solutions with its customers that directly serve its end markets.</v>
     <v>1551</v>
@@ -7811,20 +7811,20 @@
     <v>37.020000000000003</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46181.758976296092</v>
+    <v>46181.825991238278</v>
     <v>248</v>
     <v>35.549999999999997</v>
-    <v>1814173601</v>
+    <v>1800396314</v>
     <v>SKYWATER TECHNOLOGY, INC.</v>
     <v>SKYWATER TECHNOLOGY, INC.</v>
     <v>36.06</v>
-    <v>15.804399999999999</v>
+    <v>15.6843</v>
     <v>34.97</v>
-    <v>36.869999999999997</v>
+    <v>36.590000000000003</v>
     <v>49204600</v>
     <v>SKYT</v>
     <v>SKYWATER TECHNOLOGY, INC. (XNAS:SKYT)</v>
-    <v>392180</v>
+    <v>509281</v>
     <v>1186807</v>
     <v>2016</v>
   </rv>
@@ -7850,8 +7850,8 @@
     <v>62.357999999999997</v>
     <v>19.48</v>
     <v>1.8985000000000001</v>
-    <v>2.89</v>
-    <v>6.9404000000000007E-2</v>
+    <v>2.0950000000000002</v>
+    <v>5.0312000000000003E-2</v>
     <v>USD</v>
     <v>Super Micro Computer, Inc. is an application-optimized Total IT solutions provider including server, artificial intelligence (AI) systems, storage, Internet of Things (IoT) devices, switches, software, and support services. Total IT Solutions include complete servers, storage systems, modular blade servers, workstations, full-rack scale solutions, networking devices, server sub-systems, and server management. Its products are designed and manufactured in-house (in the United States, Taiwan, and the Netherlands). The Company's portfolio of Server Building Block Solutions allows customers to optimize for their exact workload and application by selecting from a broad family of systems built from the Company's flexible and reusable building blocks that support a comprehensive set of form factors, processors, memory, GPUs, storage, networking, power, and cooling solutions (air-conditioned, free air cooling or liquid cooling).</v>
     <v>6238</v>
@@ -7862,20 +7862,20 @@
     <v>44.73</v>
     <v>Computers, Phones &amp; Household Electronics</v>
     <v>Stock</v>
-    <v>46181.758996457815</v>
+    <v>46181.826085578126</v>
     <v>251</v>
     <v>42.19</v>
-    <v>26781165805</v>
+    <v>26303038097</v>
     <v>SUPER MICRO COMPUTER, INC.</v>
     <v>SUPER MICRO COMPUTER, INC.</v>
     <v>43.75</v>
-    <v>24.263100000000001</v>
+    <v>23.829899999999999</v>
     <v>41.64</v>
-    <v>44.53</v>
+    <v>43.734999999999999</v>
     <v>601418500</v>
     <v>SMCI</v>
     <v>SUPER MICRO COMPUTER, INC. (XNAS:SMCI)</v>
-    <v>21802515</v>
+    <v>26927326</v>
     <v>45991141</v>
     <v>2006</v>
   </rv>
@@ -7901,25 +7901,25 @@
     <v>642.77</v>
     <v>255</v>
     <v>1.5567</v>
-    <v>32.520000000000003</v>
-    <v>5.7084000000000003E-2</v>
+    <v>26.31</v>
+    <v>4.6182999999999995E-2</v>
     <v>USD</v>
     <v>Nasdaq Stock Market</v>
     <v>XNAS</v>
     <v>3.4999999999999996E-3</v>
     <v>606.20000000000005</v>
     <v>ETF</v>
-    <v>46181.759005983593</v>
+    <v>46181.826084120315</v>
     <v>254</v>
     <v>588.54</v>
     <v>67822489502.050003</v>
     <v>VanEck:Semiconductor</v>
     <v>597.30999999999995</v>
     <v>569.69000000000005</v>
-    <v>602.21</v>
+    <v>596</v>
     <v>SMH</v>
     <v>VanEck:Semiconductor (XNAS:SMH)</v>
-    <v>10543031</v>
+    <v>12377521</v>
     <v>10471285</v>
   </rv>
   <rv s="2">
@@ -7944,8 +7944,8 @@
     <v>57.42</v>
     <v>8.85</v>
     <v>2.2553000000000001</v>
-    <v>0.28499999999999998</v>
-    <v>2.7143E-2</v>
+    <v>0.16500000000000001</v>
+    <v>1.5713999999999999E-2</v>
     <v>USD</v>
     <v>NuScale Power Corporation is a provider of proprietary advanced small modular reactor (SMR) nuclear technology. The NuScale Power Module, the Company's SMR technology, is a small pressurized water reactor that can generate approximately 77 megawatts of electricity (MWe) or 250 megawatts thermal (gross) and can be scaled to meet customer needs through an array of flexible configurations of up to 924 MWe (12 modules) of output. In addition to the sale of NPMs, it offers a diversified suite of services throughout the development and operating life of the power plant. The Company's suite of services is planned to include licensing support, testing, training, fuel supply services and program management, among others. It serves a range of customers consisting of domestic and international governments, utilities, state-owned enterprises and technology and industrial companies in need of carbon-free, reliable energy.</v>
     <v>428</v>
@@ -7956,20 +7956,20 @@
     <v>10.98</v>
     <v>Electrical Utilities &amp; IPPs</v>
     <v>Stock</v>
-    <v>46181.759013171097</v>
+    <v>46181.826056874997</v>
     <v>257</v>
     <v>10.565</v>
-    <v>3941714742</v>
+    <v>3897856997</v>
     <v>NUSCALE POWER CORPORATION</v>
     <v>NUSCALE POWER CORPORATION</v>
     <v>10.89</v>
     <v>0</v>
     <v>10.5</v>
-    <v>10.785</v>
+    <v>10.664999999999999</v>
     <v>365481200</v>
     <v>SMR</v>
     <v>NUSCALE POWER CORPORATION (XNYS:SMR)</v>
-    <v>17149803</v>
+    <v>19821544</v>
     <v>34994181</v>
     <v>2022</v>
   </rv>
@@ -7991,8 +7991,8 @@
     <v>1861</v>
     <v>39.44</v>
     <v>2.746</v>
-    <v>73.099999999999994</v>
-    <v>4.6878999999999997E-2</v>
+    <v>68.069900000000004</v>
+    <v>4.3653999999999998E-2</v>
     <v>USD</v>
     <v>SanDisk Corporation is a developer, manufacturer and provider of data storage devices and solutions based on NAND flash technology and has consumer brands and franchises globally. The Company's solutions include a range of solid state drives (SSDs) embedded products, removable cards, universal serial bus (USB) drives, and wafers and components. Its broad portfolio of technology and products addresses multiple end markets of Datacenter, Edge and Consumer. Its Datacenter end market is composed primarily of products for public or private cloud environments and enterprise customers. The Company, through the Edge end market, provides original equipment manufacturer and channel customers a broad array of high-performance flash solutions across personal computer, mobile, gaming, automotive, virtual reality headsets, at-home entertainment, and industrial spaces. The Company serves the Consumer end market with a broad range of retail and other end-user products.</v>
     <v>11000</v>
@@ -8003,19 +8003,19 @@
     <v>1694.9875</v>
     <v>Computers, Phones &amp; Household Electronics</v>
     <v>Stock</v>
-    <v>46181.759005844535</v>
+    <v>46181.826078448437</v>
     <v>1602</v>
-    <v>241744751316</v>
+    <v>240999844813</v>
     <v>SANDISK CORPORATION</v>
     <v>SANDISK CORPORATION</v>
     <v>1633.01</v>
-    <v>57.7121</v>
+    <v>57.534199999999998</v>
     <v>1559.32</v>
-    <v>1632.42</v>
+    <v>1627.3898999999999</v>
     <v>148089800</v>
     <v>SNDK</v>
     <v>SANDISK CORPORATION (XNAS:SNDK)</v>
-    <v>6258773</v>
+    <v>7219610</v>
     <v>13774651</v>
     <v>2024</v>
   </rv>
@@ -8041,8 +8041,8 @@
     <v>284.99</v>
     <v>118.3</v>
     <v>1.3641000000000001</v>
-    <v>3.7149999999999999</v>
-    <v>1.5592E-2</v>
+    <v>1.9350000000000001</v>
+    <v>8.1209999999999997E-3</v>
     <v>USD</v>
     <v>Snowflake Inc. is an artificial intelligence (AI) data cloud company. The Company provides a platform which powers the AI data cloud, enabling customers to consolidate data into a single source of truth to drive insights, apply AI to solve business problems, build data applications, and share data and data products. Its cloud-native architecture includes three independently scalable but logically integrated layers across storage, compute, and cloud services. The storage layer ingests massive amounts and varieties of structured, semi-structured, and unstructured data. The compute layer provides dedicated resources to enable users to simultaneously access common data sets for many use cases with minimal latency. The cloud services layer enables users to securely use AI within applications, tools, and processes. Its platform supports a wide range of product categories for customers’ business objectives, including analytics, data engineering, AI, applications and collaboration.</v>
     <v>9060</v>
@@ -8053,7 +8053,7 @@
     <v>247.18989999999999</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46181.759018378907</v>
+    <v>46181.826090253904</v>
     <v>262</v>
     <v>238.02</v>
     <v>60745624254</v>
@@ -8062,11 +8062,11 @@
     <v>239.92</v>
     <v>0</v>
     <v>238.26</v>
-    <v>241.97499999999999</v>
+    <v>240.19499999999999</v>
     <v>346600000</v>
     <v>SNOW</v>
     <v>SNOWFLAKE INC. (XNYS:SNOW)</v>
-    <v>3298589</v>
+    <v>3965337</v>
     <v>10840381</v>
     <v>2012</v>
   </rv>
@@ -8092,8 +8092,8 @@
     <v>651.73</v>
     <v>376.18</v>
     <v>1.2114</v>
-    <v>8.51</v>
-    <v>1.8307E-2</v>
+    <v>7.27</v>
+    <v>1.5639E-2</v>
     <v>USD</v>
     <v>Synopsys, Inc. is engaged in providing engineering solutions from silicon to systems, enabling customers to innovate artificial intelligence (AI)-powered products. It delivers silicon design, intellectual property (IP), simulation and analysis solutions, and design services. It supplies mission-critical electronic design automation (EDA) software that engineers use to design and test integrated circuits (ICs). Its Design Automation segment includes its silicon design, verification products and services, Ansys products, system integration products and services, digital, custom and field programmable gate array integrated circuit design software, verification software and hardware products, manufacturing software products and others. Its Design IP segment's portfolio includes logic libraries, embedded memories, interface IP, security IP, and subsystems that serve companies in the semiconductor and electronics industries.</v>
     <v>28000</v>
@@ -8104,20 +8104,20 @@
     <v>478.51</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46181.758963888278</v>
+    <v>46181.82608239531</v>
     <v>265</v>
     <v>463.38</v>
-    <v>90638641448</v>
+    <v>90401207116</v>
     <v>SYNOPSYS, INC.</v>
     <v>SYNOPSYS, INC.</v>
     <v>467.28</v>
-    <v>109.70359999999999</v>
+    <v>109.4162</v>
     <v>464.85</v>
-    <v>473.36</v>
+    <v>472.12</v>
     <v>191479300</v>
     <v>SNPS</v>
     <v>SYNOPSYS, INC. (XNAS:SNPS)</v>
-    <v>633893</v>
+    <v>837948</v>
     <v>1904672</v>
     <v>1987</v>
   </rv>
@@ -8143,8 +8143,8 @@
     <v>22.17</v>
     <v>5.83</v>
     <v>2.8</v>
-    <v>0.19989999999999999</v>
-    <v>2.7050000000000001E-2</v>
+    <v>0.125</v>
+    <v>1.6914999999999999E-2</v>
     <v>USD</v>
     <v>SoundHound AI, Inc. is engaged in conversational intelligence, offering voice and conversational artificial intelligence (AI) solutions that let businesses offer experiences to their customers. Through its proprietary technology, its voice AI delivers speed and accuracy in numerous languages to product creators and service providers across retail, financial services, healthcare, automotive, smart devices, and restaurants via AI-driven products, such as Smart Answering, Smart Ordering, Dynamic Drive Thru, and Amelia AI Agents. Along with SoundHound Chat AI, a voice assistant with integrated Generative AI, it powers various products and services, and processes billions of interactions each year for businesses. Its developer platform, Houndify, is an open-access platform that allows developers to leverage its Voice AI technology and a library of over 100 content domains, including commonly used domains for points of interest, weather, flight status, sports and more.</v>
     <v>954</v>
@@ -8152,23 +8152,23 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>5400 Betsy Ross Drive, SANTA CLARA, CA, 95054 US</v>
-    <v>7.6</v>
+    <v>7.6459999999999999</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46181.759004640626</v>
+    <v>46181.826075103905</v>
     <v>268</v>
     <v>7.3150000000000004</v>
-    <v>3284677987</v>
+    <v>3252263544</v>
     <v>SOUNDHOUND AI, INC.</v>
     <v>SOUNDHOUND AI, INC.</v>
     <v>7.47</v>
     <v>0</v>
     <v>7.39</v>
-    <v>7.5899000000000001</v>
+    <v>7.5149999999999997</v>
     <v>432769600</v>
     <v>SOUN</v>
     <v>SOUNDHOUND AI, INC. (XNAS:SOUN)</v>
-    <v>16074578</v>
+    <v>19247625</v>
     <v>31097964</v>
     <v>2020</v>
   </rv>
@@ -8194,25 +8194,25 @@
     <v>618.84</v>
     <v>219.13</v>
     <v>1.7036</v>
-    <v>37.164999999999999</v>
-    <v>6.8852999999999998E-2</v>
+    <v>29.47</v>
+    <v>5.4597E-2</v>
     <v>USD</v>
     <v>Nasdaq Stock Market</v>
     <v>XNAS</v>
     <v>3.4000000000000002E-3</v>
     <v>581.37990000000002</v>
     <v>ETF</v>
-    <v>46181.75902225625</v>
+    <v>46181.826077835154</v>
     <v>271</v>
     <v>560.79</v>
     <v>38373488686.160004</v>
     <v>iShares:Semiconductor</v>
     <v>570.20000000000005</v>
     <v>539.77</v>
-    <v>576.93499999999995</v>
+    <v>569.24</v>
     <v>SOXX</v>
     <v>iShares:Semiconductor (XNAS:SOXX)</v>
-    <v>8126630</v>
+    <v>10994344</v>
     <v>9020483</v>
   </rv>
   <rv s="2">
@@ -8237,25 +8237,25 @@
     <v>760.4</v>
     <v>591.89</v>
     <v>0.99870000000000003</v>
-    <v>3.58</v>
-    <v>4.8539999999999998E-3</v>
+    <v>1.66</v>
+    <v>2.251E-3</v>
     <v>USD</v>
     <v>NYSE Arca</v>
     <v>ARCX</v>
     <v>9.4499999999999998E-4</v>
     <v>745.34</v>
     <v>ETF</v>
-    <v>46181.759019883597</v>
+    <v>46181.826099964841</v>
     <v>274</v>
-    <v>740.08</v>
+    <v>738.19</v>
     <v>783796407176.76001</v>
     <v>State Street SPDR S&amp;P500</v>
     <v>743.27</v>
     <v>737.55</v>
-    <v>741.13</v>
+    <v>739.21</v>
     <v>SPY</v>
     <v>State Street SPDR S&amp;P500 (ARCX:SPY)</v>
-    <v>29181595</v>
+    <v>38023073</v>
     <v>46904570</v>
   </rv>
   <rv s="2">
@@ -8280,8 +8280,8 @@
     <v>90.9</v>
     <v>51.93</v>
     <v>1.4797</v>
-    <v>3.39</v>
-    <v>4.6079000000000002E-2</v>
+    <v>2.08</v>
+    <v>2.8271999999999999E-2</v>
     <v>USD</v>
     <v>Skyworks Solutions, Inc. provides wireless networking services. The Company’s analog and mixed-signal semiconductors are connecting people, places, and things, spanning a number of new applications within the aerospace, automotive, broadband, cellular infrastructure, connected home, defense, entertainment and gaming, industrial, medical, smartphone, tablet, and wearable markets. It operates engineering, manufacturing, sales, and service facilities throughout Asia, Europe, and North America. The Company offers a range of products, such as Amplifiers, Attenuators, Diodes, Audio And Radio, Clocks And Timing, Front-End Modules, Isolation, Modems And DAAs, Optocouplers, Power Management, Power Over Ethernet, RF Passives, Television (TV) And Video, Switches, and Voice. Its engineering, marketing, operations, sales, and support facilities are located throughout Asia, Europe, and North America.</v>
     <v>10000</v>
@@ -8292,20 +8292,20 @@
     <v>78.89</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46181.758993796095</v>
+    <v>46181.826069721872</v>
     <v>277</v>
     <v>74.239999999999995</v>
-    <v>11575238064</v>
+    <v>11378206335</v>
     <v>SKYWORKS SOLUTIONS, INC.</v>
     <v>SKYWORKS SOLUTIONS, INC.</v>
     <v>75.34</v>
-    <v>30.404599999999999</v>
+    <v>29.887</v>
     <v>73.569999999999993</v>
-    <v>76.959999999999994</v>
+    <v>75.650000000000006</v>
     <v>150405900</v>
     <v>SWKS</v>
     <v>SKYWORKS SOLUTIONS, INC. (XNAS:SWKS)</v>
-    <v>2629542</v>
+    <v>3795020</v>
     <v>5492773</v>
     <v>2002</v>
   </rv>
@@ -8331,8 +8331,8 @@
     <v>87.88</v>
     <v>27.26</v>
     <v>1.9351</v>
-    <v>0.73</v>
-    <v>1.6583000000000001E-2</v>
+    <v>0.65</v>
+    <v>1.4766E-2</v>
     <v>USD</v>
     <v>Symbotic Inc. is an automation technology company, which focuses on reimagining the supply chain with its end-to-end, artificial intelligence-powered robotic and software platform. It is engaged in developing, commercializing, and deploying innovative and comprehensive technology solutions that improve supply chain operations. The Company automates the processing of pallets, cases and individual items in warehouses. Its systems enhance operations at the front end of the supply chain and therefore benefit all supply partners further down the chain, irrespective of fulfillment strategy. Its robotic-based automation systems, which include hardware and essential software, move, store and sort cases and reach in warehouses. Its systems are operational in a number of retailers, including Walmart, wholesale distributors, including C&amp;S Wholesale Grocers, and are being deployed in GreenBox Systems LLC, which is doing business as Exol (Exol), its warehouse-as-a-service joint venture.</v>
     <v>2000</v>
@@ -8343,20 +8343,20 @@
     <v>45.18</v>
     <v>Machinery, Equipment &amp; Components</v>
     <v>Stock</v>
-    <v>46181.758995253906</v>
+    <v>46181.826050659372</v>
     <v>280</v>
     <v>44.01</v>
-    <v>26971129300</v>
+    <v>26922912756</v>
     <v>SYMBOTIC INC.</v>
     <v>SYMBOTIC INC.</v>
     <v>44.76</v>
     <v>0</v>
     <v>44.02</v>
-    <v>44.75</v>
+    <v>44.67</v>
     <v>602706800</v>
     <v>SYM</v>
     <v>SYMBOTIC INC. (XNAS:SYM)</v>
-    <v>702676</v>
+    <v>983168</v>
     <v>2616913</v>
     <v>2022</v>
   </rv>
@@ -8378,8 +8378,8 @@
     <v>104.32</v>
     <v>41.73</v>
     <v>3.121</v>
-    <v>1.6</v>
-    <v>3.4460000000000005E-2</v>
+    <v>1.95</v>
+    <v>4.1999000000000002E-2</v>
     <v>USD</v>
     <v>Tempus AI, Inc. is a technology company advancing precision medicine through the practical application of artificial intelligence in healthcare. It offers AI-enabled precision medicine solutions to physicians to deliver personalized patient care and, in parallel, facilitates discovery, development and delivery of optimal therapeutics. It provides three product lines: Genomics, Data and artificial intelligence applications (AI). The Genomics product line leverages its laboratories to provide next generation sequencing (NGS) diagnostics, polymerase chain reaction, profiling, molecular genotyping and other anatomic and molecular pathology testing. The data generated in its lab or ingested into its platform is structured and de-identified, prior to commercialization. Its AI Applications is focused on developing and providing diagnostics that are algorithmic in nature, implementing new software as a medical device, and building and deploying clinical decision support tools.</v>
     <v>3800</v>
@@ -8387,22 +8387,22 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>600 West Chicago Avenue, Suite 510, CHICAGO, IL, 60654 US</v>
-    <v>48.4221</v>
+    <v>48.44</v>
     <v>Biotechnology &amp; Medical Research</v>
     <v>Stock</v>
-    <v>46181.758948645314</v>
+    <v>46181.826012279686</v>
     <v>46.18</v>
-    <v>8624497344</v>
+    <v>8687345024</v>
     <v>TEMPUS AI, INC.</v>
     <v>TEMPUS AI, INC.</v>
     <v>47.36</v>
     <v>0</v>
     <v>46.43</v>
-    <v>48.03</v>
+    <v>48.38</v>
     <v>179564800</v>
     <v>TEM</v>
     <v>TEMPUS AI, INC. (XNAS:TEM)</v>
-    <v>3094866</v>
+    <v>3854567</v>
     <v>7222696</v>
     <v>2025</v>
   </rv>
@@ -8428,8 +8428,8 @@
     <v>422.11</v>
     <v>83</v>
     <v>1.7955000000000001</v>
-    <v>19.18</v>
-    <v>5.3586000000000002E-2</v>
+    <v>13.355</v>
+    <v>3.7311999999999998E-2</v>
     <v>USD</v>
     <v>Teradyne, Inc. is a global supplier of automated test equipment and robotics solutions. It designs, develops, manufactures and sells automated test systems and robotics products. Its segment includes Semiconductor Test, Robotics, and Product Test. The Semiconductor Test segment includes operations related to the design, manufacturing and marketing of semiconductor test products and services, inclusive of storage and system level test products. The Robotics segment includes operations related to the design, manufacturing and marketing of collaborative robotic arms and autonomous mobile robots. The Product Test segment includes operations related to the design, manufacturing and marketing of products and services for defense/aerospace test, circuit-board test, wireless test systems, and silicon photonics testing. Its offerings also include defense/aerospace test instrumentation and systems, circuit-board test and inspection (production board test) systems, and wireless test systems.</v>
     <v>6600</v>
@@ -8440,20 +8440,20 @@
     <v>380.16500000000002</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46181.758974988283</v>
+    <v>46181.826097661717</v>
     <v>285</v>
     <v>368.41</v>
-    <v>59033629042</v>
+    <v>58121770727</v>
     <v>TERADYNE, INC.</v>
     <v>TERADYNE, INC.</v>
     <v>375.36</v>
-    <v>69.795100000000005</v>
+    <v>68.716999999999999</v>
     <v>357.93</v>
-    <v>377.11</v>
+    <v>371.28500000000003</v>
     <v>156542200</v>
     <v>TER</v>
     <v>TERADYNE, INC. (XNAS:TER)</v>
-    <v>1344398</v>
+    <v>1768341</v>
     <v>3723215</v>
     <v>1960</v>
   </rv>
@@ -8479,8 +8479,8 @@
     <v>498.83</v>
     <v>281.85000000000002</v>
     <v>1.8163</v>
-    <v>19.7</v>
-    <v>5.0384000000000005E-2</v>
+    <v>17.885000000000002</v>
+    <v>4.5742000000000005E-2</v>
     <v>USD</v>
     <v>Tesla, Inc. designs, develops, manufactures, sells and leases high-performance fully electric vehicles and energy generation and storage systems, and offers services related to its products. Its segments include automotive, and energy generation and storage. The automotive segment includes the design, development, manufacturing, sales and leasing of high-performance fully electric vehicles, and sales of automotive regulatory credits. It also includes sales of used vehicles, non-warranty maintenance services and collisions, part sales, paid supercharging, insurance services revenue and retail merchandise sales. The energy generation and storage segment include the design, manufacture, installation, sales and leasing of solar energy generation and energy storage products and related services and sales of solar energy systems incentives. Its consumer vehicles include the Model 3, Y, S, X and Cybertruck. Its lithium-ion battery energy storage products include Powerwall and Megapack.</v>
     <v>134785</v>
@@ -8488,23 +8488,23 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>1 Tesla Road, AUSTIN, TX, 78725 US</v>
-    <v>411.83</v>
+    <v>412.94</v>
     <v>Automobiles &amp; Auto Parts</v>
     <v>Stock</v>
-    <v>46181.759033738279</v>
+    <v>46181.826093726566</v>
     <v>288</v>
     <v>394.72</v>
-    <v>1542475846800</v>
+    <v>1535659207740</v>
     <v>TESLA, INC.</v>
     <v>TESLA, INC.</v>
     <v>396</v>
-    <v>375.37700000000001</v>
+    <v>373.71809999999999</v>
     <v>391</v>
-    <v>410.7</v>
+    <v>408.88499999999999</v>
     <v>3755724000</v>
     <v>TSLA</v>
     <v>TESLA, INC. (XNAS:TSLA)</v>
-    <v>33961318</v>
+    <v>42341061</v>
     <v>51095907</v>
     <v>2024</v>
   </rv>
@@ -8530,8 +8530,8 @@
     <v>450.16359999999997</v>
     <v>205.87</v>
     <v>1.3887</v>
-    <v>13.6</v>
-    <v>3.2757999999999995E-2</v>
+    <v>11.195</v>
+    <v>2.6964999999999999E-2</v>
     <v>USD</v>
     <v>Taiwan Semiconductor Manufacturing Co Ltd is a Taiwan-based integrated circuit foundry service provider. The Company is primarily engaged in integrated circuit manufacturing services. It offers advanced process technologies, specialised process solutions, advanced photomask and silicon stacking, and packaging-related technologies, while supporting a comprehensive design ecosystem. The Company's products serve diverse electronic sectors including artificial intelligence, high-performance computing, wired and wireless communications, automotive and industrial equipment, personal computing, information applications, consumer electronics, smart internet of things, and wearable devices.</v>
     <v>52045</v>
@@ -8542,20 +8542,20 @@
     <v>433.81</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46181.759024513281</v>
+    <v>46181.826098750003</v>
     <v>291</v>
     <v>422.54</v>
-    <v>2223804456980</v>
+    <v>2211330987010</v>
     <v>Taiwan Semiconductor Manufacturing Company Limited</v>
     <v>Taiwan Semiconductor Manufacturing Company Limited</v>
     <v>424.4</v>
-    <v>36.277700000000003</v>
+    <v>36.074199999999998</v>
     <v>415.17</v>
-    <v>428.77</v>
+    <v>426.36500000000001</v>
     <v>5186474000</v>
     <v>TSM</v>
     <v>Taiwan Semiconductor Manufacturing Company Limited (XNYS:TSM)</v>
-    <v>8269153</v>
+    <v>9466198</v>
     <v>13082077</v>
     <v>1987</v>
   </rv>
@@ -8581,8 +8581,8 @@
     <v>238.47989999999999</v>
     <v>91.84</v>
     <v>1.3119000000000001</v>
-    <v>-12.36</v>
-    <v>-5.4692999999999999E-2</v>
+    <v>-12.43</v>
+    <v>-5.5002000000000002E-2</v>
     <v>USD</v>
     <v>Twilio Inc. provides a customer engagement platform to build direct, personalized relationships with their customers everywhere in the world. Its platform provides developers with tools to build, scale, and deploy real-time communications within software applications. Its segments include Twilio Communications (Communications) and Twilio Segment (Segment). The Communications segment consists of a variety of application programming interfaces (APIs) and software solutions to optimize communications between its customers and their end users. Its key offerings in its Communications segment include Messaging, Voice, Email (includes Marketing Campaigns), Flex and User Authentication and Identity. Its Twilio Flex is a digital engagement center for the entire customer journey. Twilio Segment is a customer data platform that provides businesses with the tools to harness the power of contextual data by unifying real-time information collected throughout each customer’s journey into a profile.</v>
     <v>5558</v>
@@ -8593,20 +8593,20 @@
     <v>227.4</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46181.759025844534</v>
+    <v>46181.826084883593</v>
     <v>294</v>
-    <v>212.53</v>
-    <v>32423458257</v>
+    <v>212.01009999999999</v>
+    <v>32412834084</v>
     <v>TWILIO INC.</v>
     <v>TWILIO INC.</v>
     <v>227.4</v>
-    <v>332.08460000000002</v>
+    <v>331.97579999999999</v>
     <v>225.99</v>
-    <v>213.63</v>
+    <v>213.56</v>
     <v>151773900</v>
     <v>TWLO</v>
     <v>TWILIO INC. (XNYS:TWLO)</v>
-    <v>1671334</v>
+    <v>2155716</v>
     <v>3299011</v>
     <v>2008</v>
   </rv>
@@ -8632,8 +8632,8 @@
     <v>379.935</v>
     <v>107.38</v>
     <v>2.0459000000000001</v>
-    <v>1.49</v>
-    <v>4.9580000000000006E-3</v>
+    <v>0.94</v>
+    <v>3.1280000000000001E-3</v>
     <v>USD</v>
     <v>Vertiv Holdings Co. provides mission-critical digital infrastructure technologies and lifecycle services primarily for data centers, communication networks, and commercial and industrial environments. The Company operates in three business segments: the Americas; Asia Pacific, and Europe, Middle East &amp; Africa. The Company's offerings include alternate current (AC) and direct current (DC) power management, thermal management, low/medium voltage switchgear, busbar, air cooled and liquid cooled thermal management products, integrated modular solutions, racks, single phase UPS, rack power distribution, rack thermal systems, configurable integrated solutions, energy storage solutions, hardware, software for managing IT equipment, management systems for monitoring and controlling digital infrastructure, and services. It also provides preventative maintenance, acceptance testing, engineering and consulting, remote monitoring, training, spare parts, specialized fluid management, and others.</v>
     <v>34000</v>
@@ -8644,20 +8644,20 @@
     <v>310.60660000000001</v>
     <v>Machinery, Equipment &amp; Components</v>
     <v>Stock</v>
-    <v>46181.759030196095</v>
+    <v>46181.826102488281</v>
     <v>297</v>
     <v>300.22000000000003</v>
-    <v>116000857600</v>
+    <v>115789597760</v>
     <v>VERTIV HOLDINGS CO</v>
     <v>VERTIV HOLDINGS CO</v>
     <v>309.82</v>
-    <v>75.822199999999995</v>
+    <v>75.684200000000004</v>
     <v>300.51</v>
-    <v>302</v>
+    <v>301.45</v>
     <v>384108800</v>
     <v>VRT</v>
     <v>VERTIV HOLDINGS CO (XNYS:VRT)</v>
-    <v>3093135</v>
+    <v>3936692</v>
     <v>5714322</v>
     <v>2016</v>
   </rv>
@@ -8683,8 +8683,8 @@
     <v>257.08999999999997</v>
     <v>110.36</v>
     <v>1.0722</v>
-    <v>-0.65500000000000003</v>
-    <v>-4.5399999999999998E-3</v>
+    <v>-0.33</v>
+    <v>-2.287E-3</v>
     <v>USD</v>
     <v>Workday, Inc. is an enterprise artificial intelligence (AI) platform for managing people, money, and agents. The Company provides organizations with cloud solutions powered by artificial intelligence (AI) to solve business challenges, including supporting and empowering the workforce, managing finances and spending. It offers a suite of cloud-based enterprise solutions that address the needs of the C-suite on a platform designed to be open, extensible, and configurable, allowing integration with other applications and the ability for customers and partners to build custom applications. It offers Workday Build, which is an open developer platform that provides customers and partners with the ability to create and share AI-powered solutions. It serves financial services, government, healthcare, higher education, hospitality, manufacturing, professional and business services, retail, technology and media, and transportation.</v>
     <v>20834</v>
@@ -8695,20 +8695,20 @@
     <v>145.47999999999999</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46181.759015601565</v>
+    <v>46181.826111620314</v>
     <v>300</v>
     <v>141.155</v>
-    <v>35475375000</v>
+    <v>35555650000</v>
     <v>WORKDAY, INC.</v>
     <v>WORKDAY, INC.</v>
     <v>142.5</v>
-    <v>44.833799999999997</v>
+    <v>44.935200000000002</v>
     <v>144.28</v>
-    <v>143.625</v>
+    <v>143.94999999999999</v>
     <v>247000000</v>
     <v>WDAY</v>
     <v>WORKDAY, INC. (XNAS:WDAY)</v>
-    <v>1615228</v>
+    <v>2200528</v>
     <v>5465337</v>
     <v>2012</v>
   </rv>
@@ -8734,8 +8734,8 @@
     <v>336.99</v>
     <v>114.625</v>
     <v>0.97170000000000001</v>
-    <v>-0.79</v>
-    <v>-6.0409999999999995E-3</v>
+    <v>-1.4750000000000001</v>
+    <v>-1.1278E-2</v>
     <v>USD</v>
     <v>Zscaler, Inc. is a cloud security company. The Company has developed a platform incorporating core security functionalities needed to enable fast and secure access to cloud resources based on identity, context and an organization's policies. Its Zscaler Zero Trust Exchange is a cloud-native platform that securely connects users, devices, applications and workloads, including artificial intelligence (AI) agents, without relying on hub-and-spoke network architecture and firewall-centric security. It delivers its solutions using a software-as-a-service (SaaS) business model and sells subscriptions to customers to access its cloud platform, together with related support services. Its services include Zscaler Internet Access (ZIA), Zscaler Private Access (ZPA), and Zscaler Digital Experience (ZDX). ZIA provides secure access to externally managed applications, including SaaS applications and internet destinations, regardless of device, location or network.</v>
     <v>7923</v>
@@ -8746,20 +8746,20 @@
     <v>132.07</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46181.759036978903</v>
+    <v>46181.826076943747</v>
     <v>303</v>
     <v>127.73650000000001</v>
-    <v>21020617905</v>
+    <v>20909846897</v>
     <v>ZSCALER, INC.</v>
     <v>ZSCALER, INC.</v>
     <v>130.80000000000001</v>
     <v>0</v>
     <v>130.78</v>
-    <v>129.99</v>
+    <v>129.30500000000001</v>
     <v>161709500</v>
     <v>ZS</v>
     <v>ZSCALER, INC. (XNAS:ZS)</v>
-    <v>2039066</v>
+    <v>2590553</v>
     <v>6373489</v>
     <v>2007</v>
   </rv>
@@ -8780,18 +8780,18 @@
     <v>33</v>
     <v>0.76859999999999995</v>
     <v>0.72099999999999997</v>
-    <v>-2.81E-4</v>
-    <v>-3.7490000000000001E-4</v>
+    <v>-4.3000000000000002E-5</v>
+    <v>-5.7370000000000001E-5</v>
     <v>GBP</v>
     <v>USD</v>
     <v>0.75149999999999995</v>
     <v>Currency Pair</v>
-    <v>46181.758958333332</v>
+    <v>46181.82608796296</v>
     <v>0.748</v>
     <v>US Dollar/UK Pound Sterling FX Cross Rate</v>
     <v>0.749</v>
     <v>0.74950000000000006</v>
-    <v>0.74919999999999998</v>
+    <v>0.74950000000000006</v>
     <v>USDGBP</v>
     <v>USD/GBP</v>
   </rv>
@@ -13751,6 +13751,10 @@
         <f>1/1.3403</f>
         <v>0.74610161904051331</v>
       </c>
+      <c r="J5">
+        <f>+G5*E5*I5+H5</f>
+        <v>1887.3677169588898</v>
+      </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="11">
@@ -14182,7 +14186,7 @@
       </c>
       <c r="C2" s="2">
         <f t="array" aca="1" ref="C2" ca="1">_FV(B2,"Last trade time",TRUE)</f>
-        <v>46181.758863853909</v>
+        <v>46181.825966017968</v>
       </c>
       <c r="D2" t="str">
         <f t="array" aca="1" ref="D2" ca="1">_FV(B2,"Currency")</f>
@@ -14190,15 +14194,15 @@
       </c>
       <c r="E2" s="3">
         <f t="array" aca="1" ref="E2" ca="1">_FV(B2,"Price")</f>
-        <v>200.9</v>
+        <v>196.35</v>
       </c>
       <c r="F2" s="4">
         <f t="array" aca="1" ref="F2" ca="1">_FV(B2,"Change (%)",TRUE)</f>
-        <v>0.13502800000000001</v>
+        <v>0.109322</v>
       </c>
       <c r="G2" s="5">
         <f t="array" aca="1" ref="G2" ca="1">_FV(B2,"Change")</f>
-        <v>23.9</v>
+        <v>19.350000000000001</v>
       </c>
       <c r="H2" s="6">
         <f t="array" aca="1" ref="H2" ca="1">_FV(B2,"P/E",TRUE)</f>
@@ -14218,7 +14222,7 @@
       </c>
       <c r="L2" s="3">
         <f t="array" aca="1" ref="L2" ca="1">_FV(B2,"High")</f>
-        <v>203</v>
+        <v>203.19990000000001</v>
       </c>
       <c r="M2" s="3">
         <f t="array" aca="1" ref="M2" ca="1">_FV(B2,"Low")</f>
@@ -14234,7 +14238,7 @@
       </c>
       <c r="P2" s="7">
         <f t="array" aca="1" ref="P2" ca="1">_FV(B2,"Volume")</f>
-        <v>11147888</v>
+        <v>13347907</v>
       </c>
       <c r="Q2" s="7">
         <f t="array" aca="1" ref="Q2" ca="1">_FV(B2,"Volume average",TRUE)</f>
@@ -14254,7 +14258,7 @@
       </c>
       <c r="U2" s="7">
         <f t="array" aca="1" ref="U2" ca="1">_FV(B2,"Market cap",TRUE)</f>
-        <v>16120772493</v>
+        <v>15755667889</v>
       </c>
       <c r="V2" s="7">
         <f t="array" aca="1" ref="V2" ca="1">_FV(B2,"Shares outstanding",TRUE)</f>
@@ -14270,7 +14274,7 @@
       </c>
       <c r="C3" s="2">
         <f t="array" aca="1" ref="C3" ca="1">_FV(B3,"Last trade time",TRUE)</f>
-        <v>46181.758899710156</v>
+        <v>46181.825948032034</v>
       </c>
       <c r="D3" t="str">
         <f t="array" aca="1" ref="D3" ca="1">_FV(B3,"Currency")</f>
@@ -14278,19 +14282,19 @@
       </c>
       <c r="E3" s="3">
         <f t="array" aca="1" ref="E3" ca="1">_FV(B3,"Price")</f>
-        <v>305.02499999999998</v>
+        <v>301.89999999999998</v>
       </c>
       <c r="F3" s="4">
         <f t="array" aca="1" ref="F3" ca="1">_FV(B3,"Change (%)",TRUE)</f>
-        <v>-7.5319999999999996E-3</v>
+        <v>-1.77E-2</v>
       </c>
       <c r="G3" s="5">
         <f t="array" aca="1" ref="G3" ca="1">_FV(B3,"Change")</f>
-        <v>-2.3149999999999999</v>
+        <v>-5.44</v>
       </c>
       <c r="H3" s="6">
         <f t="array" aca="1" ref="H3" ca="1">_FV(B3,"P/E",TRUE)</f>
-        <v>37.045499999999997</v>
+        <v>36.665900000000001</v>
       </c>
       <c r="I3" s="6">
         <f t="array" aca="1" ref="I3" ca="1">_FV(B3,"Beta")</f>
@@ -14310,7 +14314,7 @@
       </c>
       <c r="M3" s="3">
         <f t="array" aca="1" ref="M3" ca="1">_FV(B3,"Low")</f>
-        <v>303.70999999999998</v>
+        <v>301.74</v>
       </c>
       <c r="N3" s="3">
         <f t="array" aca="1" ref="N3" ca="1">_FV(B3,"Open")</f>
@@ -14322,7 +14326,7 @@
       </c>
       <c r="P3" s="7">
         <f t="array" aca="1" ref="P3" ca="1">_FV(B3,"Volume")</f>
-        <v>43021555</v>
+        <v>60015935</v>
       </c>
       <c r="Q3" s="7">
         <f t="array" aca="1" ref="Q3" ca="1">_FV(B3,"Volume average",TRUE)</f>
@@ -14342,7 +14346,7 @@
       </c>
       <c r="U3" s="7">
         <f t="array" aca="1" ref="U3" ca="1">_FV(B3,"Market cap",TRUE)</f>
-        <v>4480011984000</v>
+        <v>4434113984000</v>
       </c>
       <c r="V3" s="7">
         <f t="array" aca="1" ref="V3" ca="1">_FV(B3,"Shares outstanding",TRUE)</f>
@@ -14358,7 +14362,7 @@
       </c>
       <c r="C4" s="2">
         <f t="array" aca="1" ref="C4" ca="1">_FV(B4,"Last trade time",TRUE)</f>
-        <v>46181.758875821091</v>
+        <v>46181.825974166408</v>
       </c>
       <c r="D4" t="str">
         <f t="array" aca="1" ref="D4" ca="1">_FV(B4,"Currency")</f>
@@ -14366,19 +14370,19 @@
       </c>
       <c r="E4" s="3">
         <f t="array" aca="1" ref="E4" ca="1">_FV(B4,"Price")</f>
-        <v>246.61</v>
+        <v>246.46</v>
       </c>
       <c r="F4" s="4">
         <f t="array" aca="1" ref="F4" ca="1">_FV(B4,"Change (%)",TRUE)</f>
-        <v>-1.9209E-2</v>
+        <v>-1.9806000000000001E-2</v>
       </c>
       <c r="G4" s="5">
         <f t="array" aca="1" ref="G4" ca="1">_FV(B4,"Change")</f>
-        <v>-4.83</v>
+        <v>-4.9800000000000004</v>
       </c>
       <c r="H4" s="6">
         <f t="array" aca="1" ref="H4" ca="1">_FV(B4,"P/E",TRUE)</f>
-        <v>14.3735</v>
+        <v>14.364699999999999</v>
       </c>
       <c r="I4" s="6">
         <f t="array" aca="1" ref="I4" ca="1">_FV(B4,"Beta")</f>
@@ -14410,7 +14414,7 @@
       </c>
       <c r="P4" s="7">
         <f t="array" aca="1" ref="P4" ca="1">_FV(B4,"Volume")</f>
-        <v>2572980</v>
+        <v>3258285</v>
       </c>
       <c r="Q4" s="7">
         <f t="array" aca="1" ref="Q4" ca="1">_FV(B4,"Volume average",TRUE)</f>
@@ -14430,7 +14434,7 @@
       </c>
       <c r="U4" s="7">
         <f t="array" aca="1" ref="U4" ca="1">_FV(B4,"Market cap",TRUE)</f>
-        <v>99679762000</v>
+        <v>99619132000</v>
       </c>
       <c r="V4" s="7">
         <f t="array" aca="1" ref="V4" ca="1">_FV(B4,"Shares outstanding",TRUE)</f>
@@ -14446,7 +14450,7 @@
       </c>
       <c r="C5" s="2">
         <f t="array" aca="1" ref="C5" ca="1">_FV(B5,"Last trade time",TRUE)</f>
-        <v>46181.758891863283</v>
+        <v>46181.825937303125</v>
       </c>
       <c r="D5" t="str">
         <f t="array" aca="1" ref="D5" ca="1">_FV(B5,"Currency")</f>
@@ -14454,15 +14458,15 @@
       </c>
       <c r="E5" s="3">
         <f t="array" aca="1" ref="E5" ca="1">_FV(B5,"Price")</f>
-        <v>97.21</v>
+        <v>95.52</v>
       </c>
       <c r="F5" s="4">
         <f t="array" aca="1" ref="F5" ca="1">_FV(B5,"Change (%)",TRUE)</f>
-        <v>-1.2595E-2</v>
+        <v>-2.9761000000000003E-2</v>
       </c>
       <c r="G5" s="5">
         <f t="array" aca="1" ref="G5" ca="1">_FV(B5,"Change")</f>
-        <v>-1.24</v>
+        <v>-2.93</v>
       </c>
       <c r="H5" s="6">
         <f t="array" aca="1" ref="H5" ca="1">_FV(B5,"P/E",TRUE)</f>
@@ -14486,7 +14490,7 @@
       </c>
       <c r="M5" s="3">
         <f t="array" aca="1" ref="M5" ca="1">_FV(B5,"Low")</f>
-        <v>94.868300000000005</v>
+        <v>93.65</v>
       </c>
       <c r="N5" s="3">
         <f t="array" aca="1" ref="N5" ca="1">_FV(B5,"Open")</f>
@@ -14498,7 +14502,7 @@
       </c>
       <c r="P5" s="7">
         <f t="array" aca="1" ref="P5" ca="1">_FV(B5,"Volume")</f>
-        <v>1262529</v>
+        <v>1520191</v>
       </c>
       <c r="Q5" s="7">
         <f t="array" aca="1" ref="Q5" ca="1">_FV(B5,"Volume average",TRUE)</f>
@@ -14518,7 +14522,7 @@
       </c>
       <c r="U5" s="7">
         <f t="array" aca="1" ref="U5" ca="1">_FV(B5,"Market cap",TRUE)</f>
-        <v>3057570432</v>
+        <v>3004414440</v>
       </c>
       <c r="V5" s="7">
         <f t="array" aca="1" ref="V5" ca="1">_FV(B5,"Shares outstanding",TRUE)</f>
@@ -14534,7 +14538,7 @@
       </c>
       <c r="C6" s="2">
         <f t="array" aca="1" ref="C6" ca="1">_FV(B6,"Last trade time",TRUE)</f>
-        <v>46181.750029096875</v>
+        <v>46181.815370207813</v>
       </c>
       <c r="D6" t="str">
         <f t="array" aca="1" ref="D6" ca="1">_FV(B6,"Currency")</f>
@@ -14586,7 +14590,7 @@
       </c>
       <c r="P6" s="7">
         <f t="array" aca="1" ref="P6" ca="1">_FV(B6,"Volume")</f>
-        <v>3500</v>
+        <v>9800</v>
       </c>
       <c r="Q6" s="7">
         <f t="array" aca="1" ref="Q6" ca="1">_FV(B6,"Volume average",TRUE)</f>
@@ -14622,7 +14626,7 @@
       </c>
       <c r="C7" s="2">
         <f t="array" aca="1" ref="C7" ca="1">_FV(B7,"Last trade time",TRUE)</f>
-        <v>46181.758867128905</v>
+        <v>46181.825956712499</v>
       </c>
       <c r="D7" t="str">
         <f t="array" aca="1" ref="D7" ca="1">_FV(B7,"Currency")</f>
@@ -14630,19 +14634,19 @@
       </c>
       <c r="E7" s="3">
         <f t="array" aca="1" ref="E7" ca="1">_FV(B7,"Price")</f>
-        <v>350.89499999999998</v>
+        <v>345.33749999999998</v>
       </c>
       <c r="F7" s="4">
         <f t="array" aca="1" ref="F7" ca="1">_FV(B7,"Change (%)",TRUE)</f>
-        <v>0.106715</v>
+        <v>8.9186999999999989E-2</v>
       </c>
       <c r="G7" s="5">
         <f t="array" aca="1" ref="G7" ca="1">_FV(B7,"Change")</f>
-        <v>33.835000000000001</v>
+        <v>28.2775</v>
       </c>
       <c r="H7" s="6">
         <f t="array" aca="1" ref="H7" ca="1">_FV(B7,"P/E",TRUE)</f>
-        <v>236.5478</v>
+        <v>232.8013</v>
       </c>
       <c r="I7" s="6">
         <f t="array" aca="1" ref="I7" ca="1">_FV(B7,"Beta")</f>
@@ -14674,7 +14678,7 @@
       </c>
       <c r="P7" s="7">
         <f t="array" aca="1" ref="P7" ca="1">_FV(B7,"Volume")</f>
-        <v>3064381</v>
+        <v>3681695</v>
       </c>
       <c r="Q7" s="7">
         <f t="array" aca="1" ref="Q7" ca="1">_FV(B7,"Volume average",TRUE)</f>
@@ -14694,7 +14698,7 @@
       </c>
       <c r="U7" s="7">
         <f t="array" aca="1" ref="U7" ca="1">_FV(B7,"Market cap",TRUE)</f>
-        <v>60146175070</v>
+        <v>59193575666</v>
       </c>
       <c r="V7" s="7">
         <f t="array" aca="1" ref="V7" ca="1">_FV(B7,"Shares outstanding",TRUE)</f>
@@ -14710,7 +14714,7 @@
       </c>
       <c r="C8" s="2">
         <f t="array" aca="1" ref="C8" ca="1">_FV(B8,"Last trade time",TRUE)</f>
-        <v>46181.758867916404</v>
+        <v>46181.825866967185</v>
       </c>
       <c r="D8" t="str">
         <f t="array" aca="1" ref="D8" ca="1">_FV(B8,"Currency")</f>
@@ -14718,15 +14722,15 @@
       </c>
       <c r="E8" s="3">
         <f t="array" aca="1" ref="E8" ca="1">_FV(B8,"Price")</f>
-        <v>68.799899999999994</v>
+        <v>68.945999999999998</v>
       </c>
       <c r="F8" s="4">
         <f t="array" aca="1" ref="F8" ca="1">_FV(B8,"Change (%)",TRUE)</f>
-        <v>8.3122000000000001E-2</v>
+        <v>8.5421999999999998E-2</v>
       </c>
       <c r="G8" s="5">
         <f t="array" aca="1" ref="G8" ca="1">_FV(B8,"Change")</f>
-        <v>5.2798999999999996</v>
+        <v>5.4260000000000002</v>
       </c>
       <c r="H8" s="6">
         <f t="array" aca="1" ref="H8" ca="1">_FV(B8,"P/E",TRUE)</f>
@@ -14746,7 +14750,7 @@
       </c>
       <c r="L8" s="3">
         <f t="array" aca="1" ref="L8" ca="1">_FV(B8,"High")</f>
-        <v>68.927199999999999</v>
+        <v>69.5</v>
       </c>
       <c r="M8" s="3">
         <f t="array" aca="1" ref="M8" ca="1">_FV(B8,"Low")</f>
@@ -14762,7 +14766,7 @@
       </c>
       <c r="P8" s="7">
         <f t="array" aca="1" ref="P8" ca="1">_FV(B8,"Volume")</f>
-        <v>1060162</v>
+        <v>1477734</v>
       </c>
       <c r="Q8" s="7">
         <f t="array" aca="1" ref="Q8" ca="1">_FV(B8,"Volume average",TRUE)</f>
@@ -14782,7 +14786,7 @@
       </c>
       <c r="U8" s="7">
         <f t="array" aca="1" ref="U8" ca="1">_FV(B8,"Market cap",TRUE)</f>
-        <v>3018126397</v>
+        <v>3024535538</v>
       </c>
       <c r="V8" s="7">
         <f t="array" aca="1" ref="V8" ca="1">_FV(B8,"Shares outstanding",TRUE)</f>
@@ -14798,7 +14802,7 @@
       </c>
       <c r="C9" s="2">
         <f t="array" aca="1" ref="C9" ca="1">_FV(B9,"Last trade time",TRUE)</f>
-        <v>46181.758904421091</v>
+        <v>46181.825970185157</v>
       </c>
       <c r="D9" t="str">
         <f t="array" aca="1" ref="D9" ca="1">_FV(B9,"Currency")</f>
@@ -14806,19 +14810,19 @@
       </c>
       <c r="E9" s="3">
         <f t="array" aca="1" ref="E9" ca="1">_FV(B9,"Price")</f>
-        <v>491.387</v>
+        <v>487.97</v>
       </c>
       <c r="F9" s="4">
         <f t="array" aca="1" ref="F9" ca="1">_FV(B9,"Change (%)",TRUE)</f>
-        <v>5.3619E-2</v>
+        <v>4.6293000000000001E-2</v>
       </c>
       <c r="G9" s="5">
         <f t="array" aca="1" ref="G9" ca="1">_FV(B9,"Change")</f>
-        <v>25.007000000000001</v>
+        <v>21.59</v>
       </c>
       <c r="H9" s="6">
         <f t="array" aca="1" ref="H9" ca="1">_FV(B9,"P/E",TRUE)</f>
-        <v>163.80109999999999</v>
+        <v>162.66210000000001</v>
       </c>
       <c r="I9" s="6">
         <f t="array" aca="1" ref="I9" ca="1">_FV(B9,"Beta")</f>
@@ -14834,7 +14838,7 @@
       </c>
       <c r="L9" s="3">
         <f t="array" aca="1" ref="L9" ca="1">_FV(B9,"High")</f>
-        <v>494.3</v>
+        <v>494.97</v>
       </c>
       <c r="M9" s="3">
         <f t="array" aca="1" ref="M9" ca="1">_FV(B9,"Low")</f>
@@ -14850,7 +14854,7 @@
       </c>
       <c r="P9" s="7">
         <f t="array" aca="1" ref="P9" ca="1">_FV(B9,"Volume")</f>
-        <v>16964275</v>
+        <v>19825701</v>
       </c>
       <c r="Q9" s="7">
         <f t="array" aca="1" ref="Q9" ca="1">_FV(B9,"Volume average",TRUE)</f>
@@ -14870,7 +14874,7 @@
       </c>
       <c r="U9" s="7">
         <f t="array" aca="1" ref="U9" ca="1">_FV(B9,"Market cap",TRUE)</f>
-        <v>801256133587</v>
+        <v>795684369970</v>
       </c>
       <c r="V9" s="7">
         <f t="array" aca="1" ref="V9" ca="1">_FV(B9,"Shares outstanding",TRUE)</f>
@@ -14886,7 +14890,7 @@
       </c>
       <c r="C10" s="2">
         <f t="array" aca="1" ref="C10" ca="1">_FV(B10,"Last trade time",TRUE)</f>
-        <v>46181.758903923437</v>
+        <v>46181.825973946092</v>
       </c>
       <c r="D10" t="str">
         <f t="array" aca="1" ref="D10" ca="1">_FV(B10,"Currency")</f>
@@ -14894,19 +14898,19 @@
       </c>
       <c r="E10" s="3">
         <f t="array" aca="1" ref="E10" ca="1">_FV(B10,"Price")</f>
-        <v>244.07499999999999</v>
+        <v>245.26499999999999</v>
       </c>
       <c r="F10" s="4">
         <f t="array" aca="1" ref="F10" ca="1">_FV(B10,"Change (%)",TRUE)</f>
-        <v>-7.9459999999999999E-3</v>
+        <v>-3.1090000000000002E-3</v>
       </c>
       <c r="G10" s="5">
         <f t="array" aca="1" ref="G10" ca="1">_FV(B10,"Change")</f>
-        <v>-1.9550000000000001</v>
+        <v>-0.76500000000000001</v>
       </c>
       <c r="H10" s="6">
         <f t="array" aca="1" ref="H10" ca="1">_FV(B10,"P/E",TRUE)</f>
-        <v>29.168700000000001</v>
+        <v>29.3109</v>
       </c>
       <c r="I10" s="6">
         <f t="array" aca="1" ref="I10" ca="1">_FV(B10,"Beta")</f>
@@ -14926,7 +14930,7 @@
       </c>
       <c r="M10" s="3">
         <f t="array" aca="1" ref="M10" ca="1">_FV(B10,"Low")</f>
-        <v>244.05</v>
+        <v>243.39500000000001</v>
       </c>
       <c r="N10" s="3">
         <f t="array" aca="1" ref="N10" ca="1">_FV(B10,"Open")</f>
@@ -14938,7 +14942,7 @@
       </c>
       <c r="P10" s="7">
         <f t="array" aca="1" ref="P10" ca="1">_FV(B10,"Volume")</f>
-        <v>19573650</v>
+        <v>25089297</v>
       </c>
       <c r="Q10" s="7">
         <f t="array" aca="1" ref="Q10" ca="1">_FV(B10,"Volume average",TRUE)</f>
@@ -14958,7 +14962,7 @@
       </c>
       <c r="U10" s="7">
         <f t="array" aca="1" ref="U10" ca="1">_FV(B10,"Market cap",TRUE)</f>
-        <v>2625541623250</v>
+        <v>2638342584150</v>
       </c>
       <c r="V10" s="7">
         <f t="array" aca="1" ref="V10" ca="1">_FV(B10,"Shares outstanding",TRUE)</f>
@@ -14974,7 +14978,7 @@
       </c>
       <c r="C11" s="2">
         <f t="array" aca="1" ref="C11" ca="1">_FV(B11,"Last trade time",TRUE)</f>
-        <v>46181.75886929375</v>
+        <v>46181.825975</v>
       </c>
       <c r="D11" t="str">
         <f t="array" aca="1" ref="D11" ca="1">_FV(B11,"Currency")</f>
@@ -14982,19 +14986,19 @@
       </c>
       <c r="E11" s="3">
         <f t="array" aca="1" ref="E11" ca="1">_FV(B11,"Price")</f>
-        <v>157.13499999999999</v>
+        <v>156.005</v>
       </c>
       <c r="F11" s="4">
         <f t="array" aca="1" ref="F11" ca="1">_FV(B11,"Change (%)",TRUE)</f>
-        <v>1.8571000000000001E-2</v>
+        <v>1.1247E-2</v>
       </c>
       <c r="G11" s="5">
         <f t="array" aca="1" ref="G11" ca="1">_FV(B11,"Change")</f>
-        <v>2.8650000000000002</v>
+        <v>1.7350000000000001</v>
       </c>
       <c r="H11" s="6">
         <f t="array" aca="1" ref="H11" ca="1">_FV(B11,"P/E",TRUE)</f>
-        <v>53.820700000000002</v>
+        <v>53.433700000000002</v>
       </c>
       <c r="I11" s="6">
         <f t="array" aca="1" ref="I11" ca="1">_FV(B11,"Beta")</f>
@@ -15026,7 +15030,7 @@
       </c>
       <c r="P11" s="7">
         <f t="array" aca="1" ref="P11" ca="1">_FV(B11,"Volume")</f>
-        <v>3559049</v>
+        <v>4305599</v>
       </c>
       <c r="Q11" s="7">
         <f t="array" aca="1" ref="Q11" ca="1">_FV(B11,"Volume average",TRUE)</f>
@@ -15046,7 +15050,7 @@
       </c>
       <c r="U11" s="7">
         <f t="array" aca="1" ref="U11" ca="1">_FV(B11,"Market cap",TRUE)</f>
-        <v>197864863405</v>
+        <v>196441964015</v>
       </c>
       <c r="V11" s="7">
         <f t="array" aca="1" ref="V11" ca="1">_FV(B11,"Shares outstanding",TRUE)</f>
@@ -15062,7 +15066,7 @@
       </c>
       <c r="C12" s="2">
         <f t="array" aca="1" ref="C12" ca="1">_FV(B12,"Last trade time",TRUE)</f>
-        <v>46181.758901133595</v>
+        <v>46181.825963159376</v>
       </c>
       <c r="D12" t="str">
         <f t="array" aca="1" ref="D12" ca="1">_FV(B12,"Currency")</f>
@@ -15070,19 +15074,19 @@
       </c>
       <c r="E12" s="3">
         <f t="array" aca="1" ref="E12" ca="1">_FV(B12,"Price")</f>
-        <v>568</v>
+        <v>566.79989999999998</v>
       </c>
       <c r="F12" s="4">
         <f t="array" aca="1" ref="F12" ca="1">_FV(B12,"Change (%)",TRUE)</f>
-        <v>1.9382999999999997E-2</v>
+        <v>1.7229000000000001E-2</v>
       </c>
       <c r="G12" s="5">
         <f t="array" aca="1" ref="G12" ca="1">_FV(B12,"Change")</f>
-        <v>10.8</v>
+        <v>9.5998999999999999</v>
       </c>
       <c r="H12" s="6">
         <f t="array" aca="1" ref="H12" ca="1">_FV(B12,"P/E",TRUE)</f>
-        <v>49.359099999999998</v>
+        <v>49.254800000000003</v>
       </c>
       <c r="I12" s="6">
         <f t="array" aca="1" ref="I12" ca="1">_FV(B12,"Beta")</f>
@@ -15114,7 +15118,7 @@
       </c>
       <c r="P12" s="7">
         <f t="array" aca="1" ref="P12" ca="1">_FV(B12,"Volume")</f>
-        <v>2365034</v>
+        <v>3406341</v>
       </c>
       <c r="Q12" s="7">
         <f t="array" aca="1" ref="Q12" ca="1">_FV(B12,"Volume average",TRUE)</f>
@@ -15134,7 +15138,7 @@
       </c>
       <c r="U12" s="7">
         <f t="array" aca="1" ref="U12" ca="1">_FV(B12,"Market cap",TRUE)</f>
-        <v>190813920000</v>
+        <v>190410758406</v>
       </c>
       <c r="V12" s="7">
         <f t="array" aca="1" ref="V12" ca="1">_FV(B12,"Shares outstanding",TRUE)</f>
@@ -15150,7 +15154,7 @@
       </c>
       <c r="C13" s="2" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(B13,"Last trade time",TRUE)</f>
-        <v>46181.758902800779</v>
+        <v>46181.825989606252</v>
       </c>
       <c r="D13" t="str" cm="1">
         <f t="array" aca="1" ref="D13" ca="1">_FV(B13,"Currency")</f>
@@ -15158,15 +15162,15 @@
       </c>
       <c r="E13" s="3" cm="1">
         <f t="array" aca="1" ref="E13" ca="1">_FV(B13,"Price")</f>
-        <v>76.02</v>
+        <v>75.745000000000005</v>
       </c>
       <c r="F13" s="4" cm="1">
         <f t="array" aca="1" ref="F13" ca="1">_FV(B13,"Change (%)",TRUE)</f>
-        <v>2.0539999999999999E-2</v>
+        <v>1.6848000000000002E-2</v>
       </c>
       <c r="G13" s="5" cm="1">
         <f t="array" aca="1" ref="G13" ca="1">_FV(B13,"Change")</f>
-        <v>1.53</v>
+        <v>1.2549999999999999</v>
       </c>
       <c r="H13" s="6" t="e" vm="13">
         <f t="array" ref="H13">_FV(B13,"P/E",TRUE)</f>
@@ -15202,7 +15206,7 @@
       </c>
       <c r="P13" s="7" cm="1">
         <f t="array" aca="1" ref="P13" ca="1">_FV(B13,"Volume")</f>
-        <v>3731911</v>
+        <v>4797308</v>
       </c>
       <c r="Q13" s="7" cm="1">
         <f t="array" aca="1" ref="Q13" ca="1">_FV(B13,"Volume average",TRUE)</f>
@@ -15238,7 +15242,7 @@
       </c>
       <c r="C14" s="2">
         <f t="array" aca="1" ref="C14" ca="1">_FV(B14,"Last trade time",TRUE)</f>
-        <v>46181.758895543753</v>
+        <v>46181.825989606252</v>
       </c>
       <c r="D14" t="str">
         <f t="array" aca="1" ref="D14" ca="1">_FV(B14,"Currency")</f>
@@ -15246,19 +15250,19 @@
       </c>
       <c r="E14" s="3">
         <f t="array" aca="1" ref="E14" ca="1">_FV(B14,"Price")</f>
-        <v>350.59500000000003</v>
+        <v>346.39</v>
       </c>
       <c r="F14" s="4">
         <f t="array" aca="1" ref="F14" ca="1">_FV(B14,"Change (%)",TRUE)</f>
-        <v>2.2351999999999997E-2</v>
+        <v>1.0089999999999998E-2</v>
       </c>
       <c r="G14" s="5">
         <f t="array" aca="1" ref="G14" ca="1">_FV(B14,"Change")</f>
-        <v>7.665</v>
+        <v>3.46</v>
       </c>
       <c r="H14" s="6">
         <f t="array" aca="1" ref="H14" ca="1">_FV(B14,"P/E",TRUE)</f>
-        <v>414.21899999999999</v>
+        <v>409.2509</v>
       </c>
       <c r="I14" s="6">
         <f t="array" aca="1" ref="I14" ca="1">_FV(B14,"Beta")</f>
@@ -15290,7 +15294,7 @@
       </c>
       <c r="P14" s="7">
         <f t="array" aca="1" ref="P14" ca="1">_FV(B14,"Volume")</f>
-        <v>6540411</v>
+        <v>7555717</v>
       </c>
       <c r="Q14" s="7">
         <f t="array" aca="1" ref="Q14" ca="1">_FV(B14,"Volume average",TRUE)</f>
@@ -15310,7 +15314,7 @@
       </c>
       <c r="U14" s="7">
         <f t="array" aca="1" ref="U14" ca="1">_FV(B14,"Market cap",TRUE)</f>
-        <v>374463157005</v>
+        <v>369971884810</v>
       </c>
       <c r="V14" s="7">
         <f t="array" aca="1" ref="V14" ca="1">_FV(B14,"Shares outstanding",TRUE)</f>
@@ -15326,7 +15330,7 @@
       </c>
       <c r="C15" s="2">
         <f t="array" aca="1" ref="C15" ca="1">_FV(B15,"Last trade time",TRUE)</f>
-        <v>46181.758839108596</v>
+        <v>46181.825922685159</v>
       </c>
       <c r="D15" t="str">
         <f t="array" aca="1" ref="D15" ca="1">_FV(B15,"Currency")</f>
@@ -15334,19 +15338,19 @@
       </c>
       <c r="E15" s="3">
         <f t="array" aca="1" ref="E15" ca="1">_FV(B15,"Price")</f>
-        <v>1754.76</v>
+        <v>1742.16</v>
       </c>
       <c r="F15" s="4">
         <f t="array" aca="1" ref="F15" ca="1">_FV(B15,"Change (%)",TRUE)</f>
-        <v>6.8842E-2</v>
+        <v>6.1166999999999999E-2</v>
       </c>
       <c r="G15" s="5">
         <f t="array" aca="1" ref="G15" ca="1">_FV(B15,"Change")</f>
-        <v>113.02</v>
+        <v>100.42</v>
       </c>
       <c r="H15" s="6">
         <f t="array" aca="1" ref="H15" ca="1">_FV(B15,"P/E",TRUE)</f>
-        <v>60.328400000000002</v>
+        <v>59.895200000000003</v>
       </c>
       <c r="I15" s="6">
         <f t="array" aca="1" ref="I15" ca="1">_FV(B15,"Beta")</f>
@@ -15378,7 +15382,7 @@
       </c>
       <c r="P15" s="7">
         <f t="array" aca="1" ref="P15" ca="1">_FV(B15,"Volume")</f>
-        <v>1450679</v>
+        <v>1662882</v>
       </c>
       <c r="Q15" s="7">
         <f t="array" aca="1" ref="Q15" ca="1">_FV(B15,"Volume average",TRUE)</f>
@@ -15398,7 +15402,7 @@
       </c>
       <c r="U15" s="7">
         <f t="array" aca="1" ref="U15" ca="1">_FV(B15,"Market cap",TRUE)</f>
-        <v>681106058052</v>
+        <v>676215397032</v>
       </c>
       <c r="V15" s="7">
         <f t="array" aca="1" ref="V15" ca="1">_FV(B15,"Shares outstanding",TRUE)</f>
@@ -15414,7 +15418,7 @@
       </c>
       <c r="C16" s="2">
         <f t="array" aca="1" ref="C16" ca="1">_FV(B16,"Last trade time",TRUE)</f>
-        <v>46181.758919883592</v>
+        <v>46181.825985474221</v>
       </c>
       <c r="D16" t="str">
         <f t="array" aca="1" ref="D16" ca="1">_FV(B16,"Currency")</f>
@@ -15422,19 +15426,19 @@
       </c>
       <c r="E16" s="3">
         <f t="array" aca="1" ref="E16" ca="1">_FV(B16,"Price")</f>
-        <v>394.53500000000003</v>
+        <v>396.745</v>
       </c>
       <c r="F16" s="4">
         <f t="array" aca="1" ref="F16" ca="1">_FV(B16,"Change (%)",TRUE)</f>
-        <v>2.2827E-2</v>
+        <v>2.8555999999999998E-2</v>
       </c>
       <c r="G16" s="5">
         <f t="array" aca="1" ref="G16" ca="1">_FV(B16,"Change")</f>
-        <v>8.8049999999999997</v>
+        <v>11.015000000000001</v>
       </c>
       <c r="H16" s="6">
         <f t="array" aca="1" ref="H16" ca="1">_FV(B16,"P/E",TRUE)</f>
-        <v>65.717500000000001</v>
+        <v>66.085599999999999</v>
       </c>
       <c r="I16" s="6">
         <f t="array" aca="1" ref="I16" ca="1">_FV(B16,"Beta")</f>
@@ -15466,7 +15470,7 @@
       </c>
       <c r="P16" s="7">
         <f t="array" aca="1" ref="P16" ca="1">_FV(B16,"Volume")</f>
-        <v>19143209</v>
+        <v>23865805</v>
       </c>
       <c r="Q16" s="7">
         <f t="array" aca="1" ref="Q16" ca="1">_FV(B16,"Volume average",TRUE)</f>
@@ -15486,7 +15490,7 @@
       </c>
       <c r="U16" s="7">
         <f t="array" aca="1" ref="U16" ca="1">_FV(B16,"Market cap",TRUE)</f>
-        <v>1867992239380</v>
+        <v>1878455855660</v>
       </c>
       <c r="V16" s="7">
         <f t="array" aca="1" ref="V16" ca="1">_FV(B16,"Shares outstanding",TRUE)</f>
@@ -15502,7 +15506,7 @@
       </c>
       <c r="C17" s="2">
         <f t="array" aca="1" ref="C17" ca="1">_FV(B17,"Last trade time",TRUE)</f>
-        <v>46181.758934895312</v>
+        <v>46181.825999189059</v>
       </c>
       <c r="D17" t="str">
         <f t="array" aca="1" ref="D17" ca="1">_FV(B17,"Currency")</f>
@@ -15510,15 +15514,15 @@
       </c>
       <c r="E17" s="3">
         <f t="array" aca="1" ref="E17" ca="1">_FV(B17,"Price")</f>
-        <v>4.375</v>
+        <v>4.2900999999999998</v>
       </c>
       <c r="F17" s="4">
         <f t="array" aca="1" ref="F17" ca="1">_FV(B17,"Change (%)",TRUE)</f>
-        <v>4.1666999999999996E-2</v>
+        <v>2.1451999999999999E-2</v>
       </c>
       <c r="G17" s="5">
         <f t="array" aca="1" ref="G17" ca="1">_FV(B17,"Change")</f>
-        <v>0.17499999999999999</v>
+        <v>9.01E-2</v>
       </c>
       <c r="H17" s="6">
         <f t="array" aca="1" ref="H17" ca="1">_FV(B17,"P/E",TRUE)</f>
@@ -15554,7 +15558,7 @@
       </c>
       <c r="P17" s="7">
         <f t="array" aca="1" ref="P17" ca="1">_FV(B17,"Volume")</f>
-        <v>26688996</v>
+        <v>31405814</v>
       </c>
       <c r="Q17" s="7">
         <f t="array" aca="1" ref="Q17" ca="1">_FV(B17,"Volume average",TRUE)</f>
@@ -15574,7 +15578,7 @@
       </c>
       <c r="U17" s="7">
         <f t="array" aca="1" ref="U17" ca="1">_FV(B17,"Market cap",TRUE)</f>
-        <v>2095404062</v>
+        <v>2054741249</v>
       </c>
       <c r="V17" s="7">
         <f t="array" aca="1" ref="V17" ca="1">_FV(B17,"Shares outstanding",TRUE)</f>
@@ -15590,7 +15594,7 @@
       </c>
       <c r="C18" s="2" cm="1">
         <f t="array" aca="1" ref="C18" ca="1">_FV(B18,"Last trade time",TRUE)</f>
-        <v>46181.73541666667</v>
+        <v>46181.755555555559</v>
       </c>
       <c r="D18" t="str" cm="1">
         <f t="array" aca="1" ref="D18" ca="1">_FV(B18,"Currency")</f>
@@ -15598,19 +15602,19 @@
       </c>
       <c r="E18" s="3" cm="1">
         <f t="array" aca="1" ref="E18" ca="1">_FV(B18,"Price")</f>
-        <v>69.56</v>
+        <v>69.92</v>
       </c>
       <c r="F18" s="4" cm="1">
         <f t="array" aca="1" ref="F18" ca="1">_FV(B18,"Change (%)",TRUE)</f>
-        <v>-1.3332999999999999E-2</v>
+        <v>-8.2269999999999999E-3</v>
       </c>
       <c r="G18" s="5" cm="1">
         <f t="array" aca="1" ref="G18" ca="1">_FV(B18,"Change")</f>
-        <v>-0.94</v>
+        <v>-0.57999999999999996</v>
       </c>
       <c r="H18" s="6" cm="1">
         <f t="array" aca="1" ref="H18" ca="1">_FV(B18,"P/E",TRUE)</f>
-        <v>6.2667000000000002</v>
+        <v>6.2991000000000001</v>
       </c>
       <c r="I18" s="6" cm="1">
         <f t="array" aca="1" ref="I18" ca="1">_FV(B18,"Beta")</f>
@@ -15642,7 +15646,7 @@
       </c>
       <c r="P18" s="7" cm="1">
         <f t="array" aca="1" ref="P18" ca="1">_FV(B18,"Volume")</f>
-        <v>2973</v>
+        <v>2975</v>
       </c>
       <c r="Q18" s="7" cm="1">
         <f t="array" aca="1" ref="Q18" ca="1">_FV(B18,"Volume average",TRUE)</f>
@@ -15678,7 +15682,7 @@
       </c>
       <c r="C19" s="2" cm="1">
         <f t="array" aca="1" ref="C19" ca="1">_FV(B19,"Last trade time",TRUE)</f>
-        <v>46181.758938147657</v>
+        <v>46181.825981978909</v>
       </c>
       <c r="D19" t="str" cm="1">
         <f t="array" aca="1" ref="D19" ca="1">_FV(B19,"Currency")</f>
@@ -15686,19 +15690,19 @@
       </c>
       <c r="E19" s="3" cm="1">
         <f t="array" aca="1" ref="E19" ca="1">_FV(B19,"Price")</f>
-        <v>395.85500000000002</v>
+        <v>393.98</v>
       </c>
       <c r="F19" s="4" cm="1">
         <f t="array" aca="1" ref="F19" ca="1">_FV(B19,"Change (%)",TRUE)</f>
-        <v>5.2274000000000001E-2</v>
+        <v>4.7289999999999999E-2</v>
       </c>
       <c r="G19" s="5" cm="1">
         <f t="array" aca="1" ref="G19" ca="1">_FV(B19,"Change")</f>
-        <v>19.664999999999999</v>
+        <v>17.79</v>
       </c>
       <c r="H19" s="6" cm="1">
         <f t="array" aca="1" ref="H19" ca="1">_FV(B19,"P/E",TRUE)</f>
-        <v>92.413899999999998</v>
+        <v>91.976200000000006</v>
       </c>
       <c r="I19" s="6" cm="1">
         <f t="array" aca="1" ref="I19" ca="1">_FV(B19,"Beta")</f>
@@ -15714,7 +15718,7 @@
       </c>
       <c r="L19" s="3" cm="1">
         <f t="array" aca="1" ref="L19" ca="1">_FV(B19,"High")</f>
-        <v>396.6653</v>
+        <v>396.71</v>
       </c>
       <c r="M19" s="3" cm="1">
         <f t="array" aca="1" ref="M19" ca="1">_FV(B19,"Low")</f>
@@ -15730,7 +15734,7 @@
       </c>
       <c r="P19" s="7" cm="1">
         <f t="array" aca="1" ref="P19" ca="1">_FV(B19,"Volume")</f>
-        <v>1226075</v>
+        <v>1616594</v>
       </c>
       <c r="Q19" s="7" cm="1">
         <f t="array" aca="1" ref="Q19" ca="1">_FV(B19,"Volume average",TRUE)</f>
@@ -15750,7 +15754,7 @@
       </c>
       <c r="U19" s="7" cm="1">
         <f t="array" aca="1" ref="U19" ca="1">_FV(B19,"Market cap",TRUE)</f>
-        <v>109183142680</v>
+        <v>108665987680</v>
       </c>
       <c r="V19" s="7" cm="1">
         <f t="array" aca="1" ref="V19" ca="1">_FV(B19,"Shares outstanding",TRUE)</f>
@@ -15766,7 +15770,7 @@
       </c>
       <c r="C20" s="2" cm="1">
         <f t="array" aca="1" ref="C20" ca="1">_FV(B20,"Last trade time",TRUE)</f>
-        <v>46181.758894039063</v>
+        <v>46181.82599376094</v>
       </c>
       <c r="D20" t="str" cm="1">
         <f t="array" aca="1" ref="D20" ca="1">_FV(B20,"Currency")</f>
@@ -15774,19 +15778,19 @@
       </c>
       <c r="E20" s="3" cm="1">
         <f t="array" aca="1" ref="E20" ca="1">_FV(B20,"Price")</f>
-        <v>252.51</v>
+        <v>251.66</v>
       </c>
       <c r="F20" s="4" cm="1">
         <f t="array" aca="1" ref="F20" ca="1">_FV(B20,"Change (%)",TRUE)</f>
-        <v>-9.1039999999999992E-3</v>
+        <v>-1.244E-2</v>
       </c>
       <c r="G20" s="5" cm="1">
         <f t="array" aca="1" ref="G20" ca="1">_FV(B20,"Change")</f>
-        <v>-2.3199999999999998</v>
+        <v>-3.17</v>
       </c>
       <c r="H20" s="6" cm="1">
         <f t="array" aca="1" ref="H20" ca="1">_FV(B20,"P/E",TRUE)</f>
-        <v>21.937200000000001</v>
+        <v>21.863299999999999</v>
       </c>
       <c r="I20" s="6" cm="1">
         <f t="array" aca="1" ref="I20" ca="1">_FV(B20,"Beta")</f>
@@ -15818,7 +15822,7 @@
       </c>
       <c r="P20" s="7" cm="1">
         <f t="array" aca="1" ref="P20" ca="1">_FV(B20,"Volume")</f>
-        <v>2116877</v>
+        <v>2710695</v>
       </c>
       <c r="Q20" s="7" cm="1">
         <f t="array" aca="1" ref="Q20" ca="1">_FV(B20,"Volume average",TRUE)</f>
@@ -15838,7 +15842,7 @@
       </c>
       <c r="U20" s="7" cm="1">
         <f t="array" aca="1" ref="U20" ca="1">_FV(B20,"Market cap",TRUE)</f>
-        <v>90676846020</v>
+        <v>90371609320</v>
       </c>
       <c r="V20" s="7" cm="1">
         <f t="array" aca="1" ref="V20" ca="1">_FV(B20,"Shares outstanding",TRUE)</f>
@@ -15854,7 +15858,7 @@
       </c>
       <c r="C21" s="2">
         <f t="array" aca="1" ref="C21" ca="1">_FV(B21,"Last trade time",TRUE)</f>
-        <v>46181.758886122654</v>
+        <v>46181.82596602969</v>
       </c>
       <c r="D21" t="str">
         <f t="array" aca="1" ref="D21" ca="1">_FV(B21,"Currency")</f>
@@ -15862,19 +15866,19 @@
       </c>
       <c r="E21" s="3">
         <f t="array" aca="1" ref="E21" ca="1">_FV(B21,"Price")</f>
-        <v>226.64</v>
+        <v>221.53</v>
       </c>
       <c r="F21" s="4">
         <f t="array" aca="1" ref="F21" ca="1">_FV(B21,"Change (%)",TRUE)</f>
-        <v>9.546099999999999E-2</v>
+        <v>7.0762000000000005E-2</v>
       </c>
       <c r="G21" s="5">
         <f t="array" aca="1" ref="G21" ca="1">_FV(B21,"Change")</f>
-        <v>19.75</v>
+        <v>14.64</v>
       </c>
       <c r="H21" s="6">
         <f t="array" aca="1" ref="H21" ca="1">_FV(B21,"P/E",TRUE)</f>
-        <v>91.394499999999994</v>
+        <v>89.333799999999997</v>
       </c>
       <c r="I21" s="6">
         <f t="array" aca="1" ref="I21" ca="1">_FV(B21,"Beta")</f>
@@ -15906,7 +15910,7 @@
       </c>
       <c r="P21" s="7">
         <f t="array" aca="1" ref="P21" ca="1">_FV(B21,"Volume")</f>
-        <v>5994597</v>
+        <v>7066931</v>
       </c>
       <c r="Q21" s="7">
         <f t="array" aca="1" ref="Q21" ca="1">_FV(B21,"Volume average",TRUE)</f>
@@ -15926,7 +15930,7 @@
       </c>
       <c r="U21" s="7">
         <f t="array" aca="1" ref="U21" ca="1">_FV(B21,"Market cap",TRUE)</f>
-        <v>41803725336</v>
+        <v>40861186347</v>
       </c>
       <c r="V21" s="7">
         <f t="array" aca="1" ref="V21" ca="1">_FV(B21,"Shares outstanding",TRUE)</f>
@@ -15942,7 +15946,7 @@
       </c>
       <c r="C22" s="2">
         <f t="array" aca="1" ref="C22" ca="1">_FV(B22,"Last trade time",TRUE)</f>
-        <v>46181.758869617966</v>
+        <v>46181.825937626563</v>
       </c>
       <c r="D22" t="str">
         <f t="array" aca="1" ref="D22" ca="1">_FV(B22,"Currency")</f>
@@ -15950,19 +15954,19 @@
       </c>
       <c r="E22" s="3">
         <f t="array" aca="1" ref="E22" ca="1">_FV(B22,"Price")</f>
-        <v>183.125</v>
+        <v>183.12200000000001</v>
       </c>
       <c r="F22" s="4">
         <f t="array" aca="1" ref="F22" ca="1">_FV(B22,"Change (%)",TRUE)</f>
-        <v>-1.3653999999999999E-2</v>
+        <v>-1.367E-2</v>
       </c>
       <c r="G22" s="5">
         <f t="array" aca="1" ref="G22" ca="1">_FV(B22,"Change")</f>
-        <v>-2.5350000000000001</v>
+        <v>-2.5379999999999998</v>
       </c>
       <c r="H22" s="6">
         <f t="array" aca="1" ref="H22" ca="1">_FV(B22,"P/E",TRUE)</f>
-        <v>21.187200000000001</v>
+        <v>21.186800000000002</v>
       </c>
       <c r="I22" s="6">
         <f t="array" aca="1" ref="I22" ca="1">_FV(B22,"Beta")</f>
@@ -15994,7 +15998,7 @@
       </c>
       <c r="P22" s="7">
         <f t="array" aca="1" ref="P22" ca="1">_FV(B22,"Volume")</f>
-        <v>6659826</v>
+        <v>8822584</v>
       </c>
       <c r="Q22" s="7">
         <f t="array" aca="1" ref="Q22" ca="1">_FV(B22,"Volume average",TRUE)</f>
@@ -16014,7 +16018,7 @@
       </c>
       <c r="U22" s="7">
         <f t="array" aca="1" ref="U22" ca="1">_FV(B22,"Market cap",TRUE)</f>
-        <v>149979375000</v>
+        <v>149976918000</v>
       </c>
       <c r="V22" s="7">
         <f t="array" aca="1" ref="V22" ca="1">_FV(B22,"Shares outstanding",TRUE)</f>
@@ -16030,7 +16034,7 @@
       </c>
       <c r="C23" s="2" cm="1">
         <f t="array" aca="1" ref="C23" ca="1">_FV(B23,"Last trade time",TRUE)</f>
-        <v>46181.758942985936</v>
+        <v>46181.826024351562</v>
       </c>
       <c r="D23" t="str" cm="1">
         <f t="array" aca="1" ref="D23" ca="1">_FV(B23,"Currency")</f>
@@ -16038,15 +16042,15 @@
       </c>
       <c r="E23" s="3" cm="1">
         <f t="array" aca="1" ref="E23" ca="1">_FV(B23,"Price")</f>
-        <v>658.92</v>
+        <v>654.89</v>
       </c>
       <c r="F23" s="4" cm="1">
         <f t="array" aca="1" ref="F23" ca="1">_FV(B23,"Change (%)",TRUE)</f>
-        <v>-1.8031999999999999E-2</v>
+        <v>-2.4038E-2</v>
       </c>
       <c r="G23" s="5" cm="1">
         <f t="array" aca="1" ref="G23" ca="1">_FV(B23,"Change")</f>
-        <v>-12.1</v>
+        <v>-16.13</v>
       </c>
       <c r="H23" s="6" cm="1">
         <f t="array" aca="1" ref="H23" ca="1">_FV(B23,"P/E",TRUE)</f>
@@ -16070,7 +16074,7 @@
       </c>
       <c r="M23" s="3" cm="1">
         <f t="array" aca="1" ref="M23" ca="1">_FV(B23,"Low")</f>
-        <v>653.5104</v>
+        <v>652.01</v>
       </c>
       <c r="N23" s="3" cm="1">
         <f t="array" aca="1" ref="N23" ca="1">_FV(B23,"Open")</f>
@@ -16082,7 +16086,7 @@
       </c>
       <c r="P23" s="7" cm="1">
         <f t="array" aca="1" ref="P23" ca="1">_FV(B23,"Volume")</f>
-        <v>2127180</v>
+        <v>2628913</v>
       </c>
       <c r="Q23" s="7" cm="1">
         <f t="array" aca="1" ref="Q23" ca="1">_FV(B23,"Volume average",TRUE)</f>
@@ -16102,7 +16106,7 @@
       </c>
       <c r="U23" s="7" cm="1">
         <f t="array" aca="1" ref="U23" ca="1">_FV(B23,"Market cap",TRUE)</f>
-        <v>167737838016</v>
+        <v>166711941872</v>
       </c>
       <c r="V23" s="7" cm="1">
         <f t="array" aca="1" ref="V23" ca="1">_FV(B23,"Shares outstanding",TRUE)</f>
@@ -16118,7 +16122,7 @@
       </c>
       <c r="C24" s="2">
         <f t="array" aca="1" ref="C24" ca="1">_FV(B24,"Last trade time",TRUE)</f>
-        <v>46181.75893204844</v>
+        <v>46181.825990428122</v>
       </c>
       <c r="D24" t="str">
         <f t="array" aca="1" ref="D24" ca="1">_FV(B24,"Currency")</f>
@@ -16126,15 +16130,15 @@
       </c>
       <c r="E24" s="3">
         <f t="array" aca="1" ref="E24" ca="1">_FV(B24,"Price")</f>
-        <v>103.1</v>
+        <v>102.13</v>
       </c>
       <c r="F24" s="4">
         <f t="array" aca="1" ref="F24" ca="1">_FV(B24,"Change (%)",TRUE)</f>
-        <v>2.6995000000000002E-2</v>
+        <v>1.7332E-2</v>
       </c>
       <c r="G24" s="5">
         <f t="array" aca="1" ref="G24" ca="1">_FV(B24,"Change")</f>
-        <v>2.71</v>
+        <v>1.74</v>
       </c>
       <c r="H24" s="6">
         <f t="array" aca="1" ref="H24" ca="1">_FV(B24,"P/E",TRUE)</f>
@@ -16170,7 +16174,7 @@
       </c>
       <c r="P24" s="7">
         <f t="array" aca="1" ref="P24" ca="1">_FV(B24,"Volume")</f>
-        <v>16824429</v>
+        <v>20039820</v>
       </c>
       <c r="Q24" s="7">
         <f t="array" aca="1" ref="Q24" ca="1">_FV(B24,"Volume average",TRUE)</f>
@@ -16190,7 +16194,7 @@
       </c>
       <c r="U24" s="7">
         <f t="array" aca="1" ref="U24" ca="1">_FV(B24,"Market cap",TRUE)</f>
-        <v>56248308240</v>
+        <v>55719104952</v>
       </c>
       <c r="V24" s="7">
         <f t="array" aca="1" ref="V24" ca="1">_FV(B24,"Shares outstanding",TRUE)</f>
@@ -16206,7 +16210,7 @@
       </c>
       <c r="C25" s="2" cm="1">
         <f t="array" aca="1" ref="C25" ca="1">_FV(B25,"Last trade time",TRUE)</f>
-        <v>46181.758947789065</v>
+        <v>46181.826010289064</v>
       </c>
       <c r="D25" t="str" cm="1">
         <f t="array" aca="1" ref="D25" ca="1">_FV(B25,"Currency")</f>
@@ -16214,19 +16218,19 @@
       </c>
       <c r="E25" s="3" cm="1">
         <f t="array" aca="1" ref="E25" ca="1">_FV(B25,"Price")</f>
-        <v>125.22</v>
+        <v>124.73</v>
       </c>
       <c r="F25" s="4" cm="1">
         <f t="array" aca="1" ref="F25" ca="1">_FV(B25,"Change (%)",TRUE)</f>
-        <v>2.9430999999999999E-2</v>
+        <v>2.5402999999999998E-2</v>
       </c>
       <c r="G25" s="5" cm="1">
         <f t="array" aca="1" ref="G25" ca="1">_FV(B25,"Change")</f>
-        <v>3.58</v>
+        <v>3.09</v>
       </c>
       <c r="H25" s="6" cm="1">
         <f t="array" aca="1" ref="H25" ca="1">_FV(B25,"P/E",TRUE)</f>
-        <v>41.726100000000002</v>
+        <v>41.562800000000003</v>
       </c>
       <c r="I25" s="6" cm="1">
         <f t="array" aca="1" ref="I25" ca="1">_FV(B25,"Beta")</f>
@@ -16258,7 +16262,7 @@
       </c>
       <c r="P25" s="7" cm="1">
         <f t="array" aca="1" ref="P25" ca="1">_FV(B25,"Volume")</f>
-        <v>12785093</v>
+        <v>16775930</v>
       </c>
       <c r="Q25" s="7" cm="1">
         <f t="array" aca="1" ref="Q25" ca="1">_FV(B25,"Volume average",TRUE)</f>
@@ -16278,7 +16282,7 @@
       </c>
       <c r="U25" s="7" cm="1">
         <f t="array" aca="1" ref="U25" ca="1">_FV(B25,"Market cap",TRUE)</f>
-        <v>493546490700</v>
+        <v>491615187550</v>
       </c>
       <c r="V25" s="7" cm="1">
         <f t="array" aca="1" ref="V25" ca="1">_FV(B25,"Shares outstanding",TRUE)</f>
@@ -16294,7 +16298,7 @@
       </c>
       <c r="C26" s="2">
         <f t="array" aca="1" ref="C26" ca="1">_FV(B26,"Last trade time",TRUE)</f>
-        <v>46181.758947789065</v>
+        <v>46181.826010289064</v>
       </c>
       <c r="D26" t="str">
         <f t="array" aca="1" ref="D26" ca="1">_FV(B26,"Currency")</f>
@@ -16302,19 +16306,19 @@
       </c>
       <c r="E26" s="3">
         <f t="array" aca="1" ref="E26" ca="1">_FV(B26,"Price")</f>
-        <v>125.22</v>
+        <v>124.73</v>
       </c>
       <c r="F26" s="4">
         <f t="array" aca="1" ref="F26" ca="1">_FV(B26,"Change (%)",TRUE)</f>
-        <v>2.9430999999999999E-2</v>
+        <v>2.5402999999999998E-2</v>
       </c>
       <c r="G26" s="5">
         <f t="array" aca="1" ref="G26" ca="1">_FV(B26,"Change")</f>
-        <v>3.58</v>
+        <v>3.09</v>
       </c>
       <c r="H26" s="6">
         <f t="array" aca="1" ref="H26" ca="1">_FV(B26,"P/E",TRUE)</f>
-        <v>41.726100000000002</v>
+        <v>41.562800000000003</v>
       </c>
       <c r="I26" s="6">
         <f t="array" aca="1" ref="I26" ca="1">_FV(B26,"Beta")</f>
@@ -16346,7 +16350,7 @@
       </c>
       <c r="P26" s="7">
         <f t="array" aca="1" ref="P26" ca="1">_FV(B26,"Volume")</f>
-        <v>12785093</v>
+        <v>16775930</v>
       </c>
       <c r="Q26" s="7">
         <f t="array" aca="1" ref="Q26" ca="1">_FV(B26,"Volume average",TRUE)</f>
@@ -16366,7 +16370,7 @@
       </c>
       <c r="U26" s="7">
         <f t="array" aca="1" ref="U26" ca="1">_FV(B26,"Market cap",TRUE)</f>
-        <v>493546490700</v>
+        <v>491615187550</v>
       </c>
       <c r="V26" s="7">
         <f t="array" aca="1" ref="V26" ca="1">_FV(B26,"Shares outstanding",TRUE)</f>
@@ -16382,7 +16386,7 @@
       </c>
       <c r="C27" s="2">
         <f t="array" aca="1" ref="C27" ca="1">_FV(B27,"Last trade time",TRUE)</f>
-        <v>46181.758938414059</v>
+        <v>46181.825991735939</v>
       </c>
       <c r="D27" t="str">
         <f t="array" aca="1" ref="D27" ca="1">_FV(B27,"Currency")</f>
@@ -16390,19 +16394,19 @@
       </c>
       <c r="E27" s="3">
         <f t="array" aca="1" ref="E27" ca="1">_FV(B27,"Price")</f>
-        <v>230.21</v>
+        <v>231.42250000000001</v>
       </c>
       <c r="F27" s="4">
         <f t="array" aca="1" ref="F27" ca="1">_FV(B27,"Change (%)",TRUE)</f>
-        <v>-1.6659E-2</v>
+        <v>-1.1479999999999999E-2</v>
       </c>
       <c r="G27" s="5">
         <f t="array" aca="1" ref="G27" ca="1">_FV(B27,"Change")</f>
-        <v>-3.9</v>
+        <v>-2.6875</v>
       </c>
       <c r="H27" s="6">
         <f t="array" aca="1" ref="H27" ca="1">_FV(B27,"P/E",TRUE)</f>
-        <v>583.25310000000002</v>
+        <v>586.32510000000002</v>
       </c>
       <c r="I27" s="6">
         <f t="array" aca="1" ref="I27" ca="1">_FV(B27,"Beta")</f>
@@ -16434,7 +16438,7 @@
       </c>
       <c r="P27" s="7">
         <f t="array" aca="1" ref="P27" ca="1">_FV(B27,"Volume")</f>
-        <v>3172274</v>
+        <v>4089468</v>
       </c>
       <c r="Q27" s="7">
         <f t="array" aca="1" ref="Q27" ca="1">_FV(B27,"Volume average",TRUE)</f>
@@ -16454,7 +16458,7 @@
       </c>
       <c r="U27" s="7">
         <f t="array" aca="1" ref="U27" ca="1">_FV(B27,"Market cap",TRUE)</f>
-        <v>81945597642</v>
+        <v>82377199384</v>
       </c>
       <c r="V27" s="7">
         <f t="array" aca="1" ref="V27" ca="1">_FV(B27,"Shares outstanding",TRUE)</f>
@@ -16470,7 +16474,7 @@
       </c>
       <c r="C28" s="2" cm="1">
         <f t="array" aca="1" ref="C28" ca="1">_FV(B28,"Last trade time",TRUE)</f>
-        <v>46181.758905751565</v>
+        <v>46181.826010253906</v>
       </c>
       <c r="D28" t="str" cm="1">
         <f t="array" aca="1" ref="D28" ca="1">_FV(B28,"Currency")</f>
@@ -16478,19 +16482,19 @@
       </c>
       <c r="E28" s="3" cm="1">
         <f t="array" aca="1" ref="E28" ca="1">_FV(B28,"Price")</f>
-        <v>399.45499999999998</v>
+        <v>398.19499999999999</v>
       </c>
       <c r="F28" s="4" cm="1">
         <f t="array" aca="1" ref="F28" ca="1">_FV(B28,"Change (%)",TRUE)</f>
-        <v>1.2843E-2</v>
+        <v>9.6480000000000003E-3</v>
       </c>
       <c r="G28" s="5" cm="1">
         <f t="array" aca="1" ref="G28" ca="1">_FV(B28,"Change")</f>
-        <v>5.0650000000000004</v>
+        <v>3.8050000000000002</v>
       </c>
       <c r="H28" s="6" cm="1">
         <f t="array" aca="1" ref="H28" ca="1">_FV(B28,"P/E",TRUE)</f>
-        <v>31.721699999999998</v>
+        <v>31.621600000000001</v>
       </c>
       <c r="I28" s="6" cm="1">
         <f t="array" aca="1" ref="I28" ca="1">_FV(B28,"Beta")</f>
@@ -16522,7 +16526,7 @@
       </c>
       <c r="P28" s="7" cm="1">
         <f t="array" aca="1" ref="P28" ca="1">_FV(B28,"Volume")</f>
-        <v>5911913</v>
+        <v>6861807</v>
       </c>
       <c r="Q28" s="7" cm="1">
         <f t="array" aca="1" ref="Q28" ca="1">_FV(B28,"Volume average",TRUE)</f>
@@ -16542,7 +16546,7 @@
       </c>
       <c r="U28" s="7" cm="1">
         <f t="array" aca="1" ref="U28" ca="1">_FV(B28,"Market cap",TRUE)</f>
-        <v>259473305276</v>
+        <v>258654849218</v>
       </c>
       <c r="V28" s="7" cm="1">
         <f t="array" aca="1" ref="V28" ca="1">_FV(B28,"Shares outstanding",TRUE)</f>
@@ -16558,7 +16562,7 @@
       </c>
       <c r="C29" s="2" cm="1">
         <f t="array" aca="1" ref="C29" ca="1">_FV(B29,"Last trade time",TRUE)</f>
-        <v>46181.758964142966</v>
+        <v>46181.825999513283</v>
       </c>
       <c r="D29" t="str" cm="1">
         <f t="array" aca="1" ref="D29" ca="1">_FV(B29,"Currency")</f>
@@ -16566,19 +16570,19 @@
       </c>
       <c r="E29" s="3" cm="1">
         <f t="array" aca="1" ref="E29" ca="1">_FV(B29,"Price")</f>
-        <v>99.18</v>
+        <v>99.234999999999999</v>
       </c>
       <c r="F29" s="4" cm="1">
         <f t="array" aca="1" ref="F29" ca="1">_FV(B29,"Change (%)",TRUE)</f>
-        <v>-5.3149999999999994E-3</v>
+        <v>-4.764E-3</v>
       </c>
       <c r="G29" s="5" cm="1">
         <f t="array" aca="1" ref="G29" ca="1">_FV(B29,"Change")</f>
-        <v>-0.53</v>
+        <v>-0.47499999999999998</v>
       </c>
       <c r="H29" s="6" cm="1">
         <f t="array" aca="1" ref="H29" ca="1">_FV(B29,"P/E",TRUE)</f>
-        <v>15.870799999999999</v>
+        <v>15.8796</v>
       </c>
       <c r="I29" s="6" cm="1">
         <f t="array" aca="1" ref="I29" ca="1">_FV(B29,"Beta")</f>
@@ -16610,7 +16614,7 @@
       </c>
       <c r="P29" s="7" cm="1">
         <f t="array" aca="1" ref="P29" ca="1">_FV(B29,"Volume")</f>
-        <v>4286092</v>
+        <v>5558613</v>
       </c>
       <c r="Q29" s="7" cm="1">
         <f t="array" aca="1" ref="Q29" ca="1">_FV(B29,"Volume average",TRUE)</f>
@@ -16630,7 +16634,7 @@
       </c>
       <c r="U29" s="7" cm="1">
         <f t="array" aca="1" ref="U29" ca="1">_FV(B29,"Market cap",TRUE)</f>
-        <v>172227160980</v>
+        <v>172322669085</v>
       </c>
       <c r="V29" s="7" cm="1">
         <f t="array" aca="1" ref="V29" ca="1">_FV(B29,"Shares outstanding",TRUE)</f>
@@ -16646,7 +16650,7 @@
       </c>
       <c r="C30" s="2" cm="1">
         <f t="array" aca="1" ref="C30" ca="1">_FV(B30,"Last trade time",TRUE)</f>
-        <v>46181.758930404685</v>
+        <v>46181.826015138278</v>
       </c>
       <c r="D30" t="str" cm="1">
         <f t="array" aca="1" ref="D30" ca="1">_FV(B30,"Currency")</f>
@@ -16654,19 +16658,19 @@
       </c>
       <c r="E30" s="3" cm="1">
         <f t="array" aca="1" ref="E30" ca="1">_FV(B30,"Price")</f>
-        <v>41.57</v>
+        <v>41.92</v>
       </c>
       <c r="F30" s="4" cm="1">
         <f t="array" aca="1" ref="F30" ca="1">_FV(B30,"Change (%)",TRUE)</f>
-        <v>-1.4695E-2</v>
+        <v>-6.4000000000000003E-3</v>
       </c>
       <c r="G30" s="5" cm="1">
         <f t="array" aca="1" ref="G30" ca="1">_FV(B30,"Change")</f>
-        <v>-0.62</v>
+        <v>-0.27</v>
       </c>
       <c r="H30" s="6" cm="1">
         <f t="array" aca="1" ref="H30" ca="1">_FV(B30,"P/E",TRUE)</f>
-        <v>77.584900000000005</v>
+        <v>78.238100000000003</v>
       </c>
       <c r="I30" s="6" cm="1">
         <f t="array" aca="1" ref="I30" ca="1">_FV(B30,"Beta")</f>
@@ -16698,7 +16702,7 @@
       </c>
       <c r="P30" s="7" cm="1">
         <f t="array" aca="1" ref="P30" ca="1">_FV(B30,"Volume")</f>
-        <v>2956675</v>
+        <v>3742724</v>
       </c>
       <c r="Q30" s="7" cm="1">
         <f t="array" aca="1" ref="Q30" ca="1">_FV(B30,"Volume average",TRUE)</f>
@@ -16718,7 +16722,7 @@
       </c>
       <c r="U30" s="7" cm="1">
         <f t="array" aca="1" ref="U30" ca="1">_FV(B30,"Market cap",TRUE)</f>
-        <v>12116644849</v>
+        <v>12218661344</v>
       </c>
       <c r="V30" s="7" cm="1">
         <f t="array" aca="1" ref="V30" ca="1">_FV(B30,"Shares outstanding",TRUE)</f>
@@ -16734,7 +16738,7 @@
       </c>
       <c r="C31" s="2">
         <f t="array" aca="1" ref="C31" ca="1">_FV(B31,"Last trade time",TRUE)</f>
-        <v>46181.758947106253</v>
+        <v>46181.825978807814</v>
       </c>
       <c r="D31" t="str">
         <f t="array" aca="1" ref="D31" ca="1">_FV(B31,"Currency")</f>
@@ -16742,15 +16746,15 @@
       </c>
       <c r="E31" s="3">
         <f t="array" aca="1" ref="E31" ca="1">_FV(B31,"Price")</f>
-        <v>7.3449999999999998</v>
+        <v>7.2750000000000004</v>
       </c>
       <c r="F31" s="4">
         <f t="array" aca="1" ref="F31" ca="1">_FV(B31,"Change (%)",TRUE)</f>
-        <v>8.9289999999999994E-3</v>
+        <v>-6.868E-4</v>
       </c>
       <c r="G31" s="5">
         <f t="array" aca="1" ref="G31" ca="1">_FV(B31,"Change")</f>
-        <v>6.5000000000000002E-2</v>
+        <v>-5.0000000000000001E-3</v>
       </c>
       <c r="H31" s="6">
         <f t="array" aca="1" ref="H31" ca="1">_FV(B31,"P/E",TRUE)</f>
@@ -16774,7 +16778,7 @@
       </c>
       <c r="M31" s="3">
         <f t="array" aca="1" ref="M31" ca="1">_FV(B31,"Low")</f>
-        <v>7.2801</v>
+        <v>7.2549999999999999</v>
       </c>
       <c r="N31" s="3">
         <f t="array" aca="1" ref="N31" ca="1">_FV(B31,"Open")</f>
@@ -16786,7 +16790,7 @@
       </c>
       <c r="P31" s="7">
         <f t="array" aca="1" ref="P31" ca="1">_FV(B31,"Volume")</f>
-        <v>2341776</v>
+        <v>2901221</v>
       </c>
       <c r="Q31" s="7">
         <f t="array" aca="1" ref="Q31" ca="1">_FV(B31,"Volume average",TRUE)</f>
@@ -16806,7 +16810,7 @@
       </c>
       <c r="U31" s="7">
         <f t="array" aca="1" ref="U31" ca="1">_FV(B31,"Market cap",TRUE)</f>
-        <v>1602336723</v>
+        <v>1587065985</v>
       </c>
       <c r="V31" s="7">
         <f t="array" aca="1" ref="V31" ca="1">_FV(B31,"Shares outstanding",TRUE)</f>
@@ -16822,7 +16826,7 @@
       </c>
       <c r="C32" s="2" cm="1">
         <f t="array" aca="1" ref="C32" ca="1">_FV(B32,"Last trade time",TRUE)</f>
-        <v>46181.758920624998</v>
+        <v>46181.826001585156</v>
       </c>
       <c r="D32" t="str" cm="1">
         <f t="array" aca="1" ref="D32" ca="1">_FV(B32,"Currency")</f>
@@ -16830,19 +16834,19 @@
       </c>
       <c r="E32" s="3" cm="1">
         <f t="array" aca="1" ref="E32" ca="1">_FV(B32,"Price")</f>
-        <v>403.83</v>
+        <v>404.84</v>
       </c>
       <c r="F32" s="4" cm="1">
         <f t="array" aca="1" ref="F32" ca="1">_FV(B32,"Change (%)",TRUE)</f>
-        <v>1.9927E-2</v>
+        <v>2.2477999999999998E-2</v>
       </c>
       <c r="G32" s="5" cm="1">
         <f t="array" aca="1" ref="G32" ca="1">_FV(B32,"Change")</f>
-        <v>7.89</v>
+        <v>8.9</v>
       </c>
       <c r="H32" s="6" cm="1">
         <f t="array" aca="1" ref="H32" ca="1">_FV(B32,"P/E",TRUE)</f>
-        <v>39.479700000000001</v>
+        <v>39.578400000000002</v>
       </c>
       <c r="I32" s="6" cm="1">
         <f t="array" aca="1" ref="I32" ca="1">_FV(B32,"Beta")</f>
@@ -16858,7 +16862,7 @@
       </c>
       <c r="L32" s="3" cm="1">
         <f t="array" aca="1" ref="L32" ca="1">_FV(B32,"High")</f>
-        <v>406.04</v>
+        <v>406.5</v>
       </c>
       <c r="M32" s="3" cm="1">
         <f t="array" aca="1" ref="M32" ca="1">_FV(B32,"Low")</f>
@@ -16874,7 +16878,7 @@
       </c>
       <c r="P32" s="7" cm="1">
         <f t="array" aca="1" ref="P32" ca="1">_FV(B32,"Volume")</f>
-        <v>938536</v>
+        <v>1372109</v>
       </c>
       <c r="Q32" s="7" cm="1">
         <f t="array" aca="1" ref="Q32" ca="1">_FV(B32,"Volume average",TRUE)</f>
@@ -16894,7 +16898,7 @@
       </c>
       <c r="U32" s="7" cm="1">
         <f t="array" aca="1" ref="U32" ca="1">_FV(B32,"Market cap",TRUE)</f>
-        <v>156807189000</v>
+        <v>157199372000</v>
       </c>
       <c r="V32" s="7" cm="1">
         <f t="array" aca="1" ref="V32" ca="1">_FV(B32,"Shares outstanding",TRUE)</f>
@@ -16910,7 +16914,7 @@
       </c>
       <c r="C33" s="2">
         <f t="array" aca="1" ref="C33" ca="1">_FV(B33,"Last trade time",TRUE)</f>
-        <v>46181.758822812502</v>
+        <v>46181.825951805469</v>
       </c>
       <c r="D33" t="str">
         <f t="array" aca="1" ref="D33" ca="1">_FV(B33,"Currency")</f>
@@ -16918,19 +16922,19 @@
       </c>
       <c r="E33" s="3">
         <f t="array" aca="1" ref="E33" ca="1">_FV(B33,"Price")</f>
-        <v>23.28</v>
+        <v>23.004999999999999</v>
       </c>
       <c r="F33" s="4">
         <f t="array" aca="1" ref="F33" ca="1">_FV(B33,"Change (%)",TRUE)</f>
-        <v>-1.0204E-2</v>
+        <v>-2.1895999999999999E-2</v>
       </c>
       <c r="G33" s="5">
         <f t="array" aca="1" ref="G33" ca="1">_FV(B33,"Change")</f>
-        <v>-0.24</v>
+        <v>-0.51500000000000001</v>
       </c>
       <c r="H33" s="6">
         <f t="array" aca="1" ref="H33" ca="1">_FV(B33,"P/E",TRUE)</f>
-        <v>35.299500000000002</v>
+        <v>34.8825</v>
       </c>
       <c r="I33" s="6">
         <f t="array" aca="1" ref="I33" ca="1">_FV(B33,"Beta")</f>
@@ -16962,7 +16966,7 @@
       </c>
       <c r="P33" s="7">
         <f t="array" aca="1" ref="P33" ca="1">_FV(B33,"Volume")</f>
-        <v>1092189</v>
+        <v>1491276</v>
       </c>
       <c r="Q33" s="7">
         <f t="array" aca="1" ref="Q33" ca="1">_FV(B33,"Volume average",TRUE)</f>
@@ -16982,7 +16986,7 @@
       </c>
       <c r="U33" s="7">
         <f t="array" aca="1" ref="U33" ca="1">_FV(B33,"Market cap",TRUE)</f>
-        <v>1782409687</v>
+        <v>1761354589</v>
       </c>
       <c r="V33" s="7">
         <f t="array" aca="1" ref="V33" ca="1">_FV(B33,"Shares outstanding",TRUE)</f>
@@ -16998,7 +17002,7 @@
       </c>
       <c r="C34" s="2" cm="1">
         <f t="array" aca="1" ref="C34" ca="1">_FV(B34,"Last trade time",TRUE)</f>
-        <v>46181.758943957815</v>
+        <v>46181.826022314061</v>
       </c>
       <c r="D34" t="str" cm="1">
         <f t="array" aca="1" ref="D34" ca="1">_FV(B34,"Currency")</f>
@@ -17006,19 +17010,19 @@
       </c>
       <c r="E34" s="3" cm="1">
         <f t="array" aca="1" ref="E34" ca="1">_FV(B34,"Price")</f>
-        <v>143.31</v>
+        <v>142.91499999999999</v>
       </c>
       <c r="F34" s="4" cm="1">
         <f t="array" aca="1" ref="F34" ca="1">_FV(B34,"Change (%)",TRUE)</f>
-        <v>-9.469E-3</v>
+        <v>-1.2199E-2</v>
       </c>
       <c r="G34" s="5" cm="1">
         <f t="array" aca="1" ref="G34" ca="1">_FV(B34,"Change")</f>
-        <v>-1.37</v>
+        <v>-1.7649999999999999</v>
       </c>
       <c r="H34" s="6" cm="1">
         <f t="array" aca="1" ref="H34" ca="1">_FV(B34,"P/E",TRUE)</f>
-        <v>55.366199999999999</v>
+        <v>55.2136</v>
       </c>
       <c r="I34" s="6" cm="1">
         <f t="array" aca="1" ref="I34" ca="1">_FV(B34,"Beta")</f>
@@ -17038,7 +17042,7 @@
       </c>
       <c r="M34" s="3" cm="1">
         <f t="array" aca="1" ref="M34" ca="1">_FV(B34,"Low")</f>
-        <v>142.84</v>
+        <v>142.505</v>
       </c>
       <c r="N34" s="3" cm="1">
         <f t="array" aca="1" ref="N34" ca="1">_FV(B34,"Open")</f>
@@ -17050,7 +17054,7 @@
       </c>
       <c r="P34" s="7" cm="1">
         <f t="array" aca="1" ref="P34" ca="1">_FV(B34,"Volume")</f>
-        <v>2687980</v>
+        <v>3551295</v>
       </c>
       <c r="Q34" s="7" cm="1">
         <f t="array" aca="1" ref="Q34" ca="1">_FV(B34,"Volume average",TRUE)</f>
@@ -17070,7 +17074,7 @@
       </c>
       <c r="U34" s="7" cm="1">
         <f t="array" aca="1" ref="U34" ca="1">_FV(B34,"Market cap",TRUE)</f>
-        <v>104995842204</v>
+        <v>104706446086</v>
       </c>
       <c r="V34" s="7" cm="1">
         <f t="array" aca="1" ref="V34" ca="1">_FV(B34,"Shares outstanding",TRUE)</f>
@@ -17086,7 +17090,7 @@
       </c>
       <c r="C35" s="2">
         <f t="array" aca="1" ref="C35" ca="1">_FV(B35,"Last trade time",TRUE)</f>
-        <v>46181.758937360937</v>
+        <v>46181.826011620309</v>
       </c>
       <c r="D35" t="str">
         <f t="array" aca="1" ref="D35" ca="1">_FV(B35,"Currency")</f>
@@ -17094,19 +17098,19 @@
       </c>
       <c r="E35" s="3">
         <f t="array" aca="1" ref="E35" ca="1">_FV(B35,"Price")</f>
-        <v>360.84</v>
+        <v>360.73</v>
       </c>
       <c r="F35" s="4">
         <f t="array" aca="1" ref="F35" ca="1">_FV(B35,"Change (%)",TRUE)</f>
-        <v>-1.2858000000000001E-2</v>
+        <v>-1.3159000000000001E-2</v>
       </c>
       <c r="G35" s="5">
         <f t="array" aca="1" ref="G35" ca="1">_FV(B35,"Change")</f>
-        <v>-4.7</v>
+        <v>-4.8099999999999996</v>
       </c>
       <c r="H35" s="6">
         <f t="array" aca="1" ref="H35" ca="1">_FV(B35,"P/E",TRUE)</f>
-        <v>27.5579</v>
+        <v>27.549499999999998</v>
       </c>
       <c r="I35" s="6">
         <f t="array" aca="1" ref="I35" ca="1">_FV(B35,"Beta")</f>
@@ -17138,7 +17142,7 @@
       </c>
       <c r="P35" s="7">
         <f t="array" aca="1" ref="P35" ca="1">_FV(B35,"Volume")</f>
-        <v>12148052</v>
+        <v>14088604</v>
       </c>
       <c r="Q35" s="7">
         <f t="array" aca="1" ref="Q35" ca="1">_FV(B35,"Volume average",TRUE)</f>
@@ -17158,7 +17162,7 @@
       </c>
       <c r="U35" s="7">
         <f t="array" aca="1" ref="U35" ca="1">_FV(B35,"Market cap",TRUE)</f>
-        <v>4393068230399</v>
+        <v>4391729028800</v>
       </c>
       <c r="V35" s="7">
         <f t="array" aca="1" ref="V35" ca="1">_FV(B35,"Shares outstanding",TRUE)</f>
@@ -17174,7 +17178,7 @@
       </c>
       <c r="C36" s="2">
         <f t="array" aca="1" ref="C36" ca="1">_FV(B36,"Last trade time",TRUE)</f>
-        <v>46181.758916863284</v>
+        <v>46181.825964710159</v>
       </c>
       <c r="D36" t="str">
         <f t="array" aca="1" ref="D36" ca="1">_FV(B36,"Currency")</f>
@@ -17182,19 +17186,19 @@
       </c>
       <c r="E36" s="3">
         <f t="array" aca="1" ref="E36" ca="1">_FV(B36,"Price")</f>
-        <v>85</v>
+        <v>84.974999999999994</v>
       </c>
       <c r="F36" s="4">
         <f t="array" aca="1" ref="F36" ca="1">_FV(B36,"Change (%)",TRUE)</f>
-        <v>3.0678E-2</v>
+        <v>3.0374999999999999E-2</v>
       </c>
       <c r="G36" s="5">
         <f t="array" aca="1" ref="G36" ca="1">_FV(B36,"Change")</f>
-        <v>2.5299999999999998</v>
+        <v>2.5049999999999999</v>
       </c>
       <c r="H36" s="6">
         <f t="array" aca="1" ref="H36" ca="1">_FV(B36,"P/E",TRUE)</f>
-        <v>47.285299999999999</v>
+        <v>47.2714</v>
       </c>
       <c r="I36" s="6">
         <f t="array" aca="1" ref="I36" ca="1">_FV(B36,"Beta")</f>
@@ -17226,7 +17230,7 @@
       </c>
       <c r="P36" s="7">
         <f t="array" aca="1" ref="P36" ca="1">_FV(B36,"Volume")</f>
-        <v>14061290</v>
+        <v>17027385</v>
       </c>
       <c r="Q36" s="7">
         <f t="array" aca="1" ref="Q36" ca="1">_FV(B36,"Volume average",TRUE)</f>
@@ -17246,7 +17250,7 @@
       </c>
       <c r="U36" s="7">
         <f t="array" aca="1" ref="U36" ca="1">_FV(B36,"Market cap",TRUE)</f>
-        <v>76542933500</v>
+        <v>76520420872</v>
       </c>
       <c r="V36" s="7">
         <f t="array" aca="1" ref="V36" ca="1">_FV(B36,"Shares outstanding",TRUE)</f>
@@ -17262,7 +17266,7 @@
       </c>
       <c r="C37" s="2">
         <f t="array" aca="1" ref="C37" ca="1">_FV(B37,"Last trade time",TRUE)</f>
-        <v>46181.758948344534</v>
+        <v>46181.826026435156</v>
       </c>
       <c r="D37" t="str">
         <f t="array" aca="1" ref="D37" ca="1">_FV(B37,"Currency")</f>
@@ -17270,19 +17274,19 @@
       </c>
       <c r="E37" s="3">
         <f t="array" aca="1" ref="E37" ca="1">_FV(B37,"Price")</f>
-        <v>281.31</v>
+        <v>280.60000000000002</v>
       </c>
       <c r="F37" s="4">
         <f t="array" aca="1" ref="F37" ca="1">_FV(B37,"Change (%)",TRUE)</f>
-        <v>-1.2393000000000001E-2</v>
+        <v>-1.4886E-2</v>
       </c>
       <c r="G37" s="5">
         <f t="array" aca="1" ref="G37" ca="1">_FV(B37,"Change")</f>
-        <v>-3.53</v>
+        <v>-4.24</v>
       </c>
       <c r="H37" s="6">
         <f t="array" aca="1" ref="H37" ca="1">_FV(B37,"P/E",TRUE)</f>
-        <v>22.512</v>
+        <v>22.455200000000001</v>
       </c>
       <c r="I37" s="6">
         <f t="array" aca="1" ref="I37" ca="1">_FV(B37,"Beta")</f>
@@ -17314,7 +17318,7 @@
       </c>
       <c r="P37" s="7">
         <f t="array" aca="1" ref="P37" ca="1">_FV(B37,"Volume")</f>
-        <v>4004148</v>
+        <v>4939164</v>
       </c>
       <c r="Q37" s="7">
         <f t="array" aca="1" ref="Q37" ca="1">_FV(B37,"Volume average",TRUE)</f>
@@ -17334,7 +17338,7 @@
       </c>
       <c r="U37" s="7">
         <f t="array" aca="1" ref="U37" ca="1">_FV(B37,"Market cap",TRUE)</f>
-        <v>264399133743</v>
+        <v>263731815180</v>
       </c>
       <c r="V37" s="7">
         <f t="array" aca="1" ref="V37" ca="1">_FV(B37,"Shares outstanding",TRUE)</f>
@@ -17350,7 +17354,7 @@
       </c>
       <c r="C38" s="2">
         <f t="array" aca="1" ref="C38" ca="1">_FV(B38,"Last trade time",TRUE)</f>
-        <v>46181.758876596876</v>
+        <v>46181.825943645315</v>
       </c>
       <c r="D38" t="str">
         <f t="array" aca="1" ref="D38" ca="1">_FV(B38,"Currency")</f>
@@ -17358,19 +17362,19 @@
       </c>
       <c r="E38" s="3">
         <f t="array" aca="1" ref="E38" ca="1">_FV(B38,"Price")</f>
-        <v>102</v>
+        <v>102.22</v>
       </c>
       <c r="F38" s="4">
         <f t="array" aca="1" ref="F38" ca="1">_FV(B38,"Change (%)",TRUE)</f>
-        <v>2.942E-4</v>
+        <v>2.4520000000000002E-3</v>
       </c>
       <c r="G38" s="5">
         <f t="array" aca="1" ref="G38" ca="1">_FV(B38,"Change")</f>
-        <v>0.03</v>
+        <v>0.25</v>
       </c>
       <c r="H38" s="6">
         <f t="array" aca="1" ref="H38" ca="1">_FV(B38,"P/E",TRUE)</f>
-        <v>91.7761</v>
+        <v>91.974100000000007</v>
       </c>
       <c r="I38" s="6">
         <f t="array" aca="1" ref="I38" ca="1">_FV(B38,"Beta")</f>
@@ -17402,7 +17406,7 @@
       </c>
       <c r="P38" s="7">
         <f t="array" aca="1" ref="P38" ca="1">_FV(B38,"Volume")</f>
-        <v>649431</v>
+        <v>829012</v>
       </c>
       <c r="Q38" s="7">
         <f t="array" aca="1" ref="Q38" ca="1">_FV(B38,"Volume average",TRUE)</f>
@@ -17438,7 +17442,7 @@
       </c>
       <c r="C39" s="2">
         <f t="array" aca="1" ref="C39" ca="1">_FV(B39,"Last trade time",TRUE)</f>
-        <v>46181.758973830467</v>
+        <v>46181.826046122653</v>
       </c>
       <c r="D39" t="str">
         <f t="array" aca="1" ref="D39" ca="1">_FV(B39,"Currency")</f>
@@ -17446,15 +17450,15 @@
       </c>
       <c r="E39" s="3">
         <f t="array" aca="1" ref="E39" ca="1">_FV(B39,"Price")</f>
-        <v>112</v>
+        <v>109.3599</v>
       </c>
       <c r="F39" s="4">
         <f t="array" aca="1" ref="F39" ca="1">_FV(B39,"Change (%)",TRUE)</f>
-        <v>0.12937399999999999</v>
+        <v>0.102752</v>
       </c>
       <c r="G39" s="5">
         <f t="array" aca="1" ref="G39" ca="1">_FV(B39,"Change")</f>
-        <v>12.83</v>
+        <v>10.1899</v>
       </c>
       <c r="H39" s="6">
         <f t="array" aca="1" ref="H39" ca="1">_FV(B39,"P/E",TRUE)</f>
@@ -17474,7 +17478,7 @@
       </c>
       <c r="L39" s="3">
         <f t="array" aca="1" ref="L39" ca="1">_FV(B39,"High")</f>
-        <v>112.5</v>
+        <v>112.54</v>
       </c>
       <c r="M39" s="3">
         <f t="array" aca="1" ref="M39" ca="1">_FV(B39,"Low")</f>
@@ -17490,7 +17494,7 @@
       </c>
       <c r="P39" s="7">
         <f t="array" aca="1" ref="P39" ca="1">_FV(B39,"Volume")</f>
-        <v>101417633</v>
+        <v>118480614</v>
       </c>
       <c r="Q39" s="7">
         <f t="array" aca="1" ref="Q39" ca="1">_FV(B39,"Volume average",TRUE)</f>
@@ -17510,7 +17514,7 @@
       </c>
       <c r="U39" s="7">
         <f t="array" aca="1" ref="U39" ca="1">_FV(B39,"Market cap",TRUE)</f>
-        <v>562912000000</v>
+        <v>549642857400</v>
       </c>
       <c r="V39" s="7">
         <f t="array" aca="1" ref="V39" ca="1">_FV(B39,"Shares outstanding",TRUE)</f>
@@ -17526,7 +17530,7 @@
       </c>
       <c r="C40" s="2">
         <f t="array" aca="1" ref="C40" ca="1">_FV(B40,"Last trade time",TRUE)</f>
-        <v>46181.758906921095</v>
+        <v>46181.825954375003</v>
       </c>
       <c r="D40" t="str">
         <f t="array" aca="1" ref="D40" ca="1">_FV(B40,"Currency")</f>
@@ -17534,19 +17538,19 @@
       </c>
       <c r="E40" s="3">
         <f t="array" aca="1" ref="E40" ca="1">_FV(B40,"Price")</f>
-        <v>64.5</v>
+        <v>62.835000000000001</v>
       </c>
       <c r="F40" s="4">
         <f t="array" aca="1" ref="F40" ca="1">_FV(B40,"Change (%)",TRUE)</f>
-        <v>0.135963</v>
+        <v>0.10664</v>
       </c>
       <c r="G40" s="5">
         <f t="array" aca="1" ref="G40" ca="1">_FV(B40,"Change")</f>
-        <v>7.72</v>
+        <v>6.0549999999999997</v>
       </c>
       <c r="H40" s="6">
         <f t="array" aca="1" ref="H40" ca="1">_FV(B40,"P/E",TRUE)</f>
-        <v>1100.6826000000001</v>
+        <v>1072.2696000000001</v>
       </c>
       <c r="I40" s="6">
         <f t="array" aca="1" ref="I40" ca="1">_FV(B40,"Beta")</f>
@@ -17562,7 +17566,7 @@
       </c>
       <c r="L40" s="3">
         <f t="array" aca="1" ref="L40" ca="1">_FV(B40,"High")</f>
-        <v>64.680000000000007</v>
+        <v>64.900000000000006</v>
       </c>
       <c r="M40" s="3">
         <f t="array" aca="1" ref="M40" ca="1">_FV(B40,"Low")</f>
@@ -17578,7 +17582,7 @@
       </c>
       <c r="P40" s="7">
         <f t="array" aca="1" ref="P40" ca="1">_FV(B40,"Volume")</f>
-        <v>20856303</v>
+        <v>24745918</v>
       </c>
       <c r="Q40" s="7">
         <f t="array" aca="1" ref="Q40" ca="1">_FV(B40,"Volume average",TRUE)</f>
@@ -17598,7 +17602,7 @@
       </c>
       <c r="U40" s="7">
         <f t="array" aca="1" ref="U40" ca="1">_FV(B40,"Market cap",TRUE)</f>
-        <v>24075915000</v>
+        <v>23454420450</v>
       </c>
       <c r="V40" s="7">
         <f t="array" aca="1" ref="V40" ca="1">_FV(B40,"Shares outstanding",TRUE)</f>
@@ -17614,7 +17618,7 @@
       </c>
       <c r="C41" s="2">
         <f t="array" aca="1" ref="C41" ca="1">_FV(B41,"Last trade time",TRUE)</f>
-        <v>46181.758986353903</v>
+        <v>46181.82602209453</v>
       </c>
       <c r="D41" t="str">
         <f t="array" aca="1" ref="D41" ca="1">_FV(B41,"Currency")</f>
@@ -17622,19 +17626,19 @@
       </c>
       <c r="E41" s="3">
         <f t="array" aca="1" ref="E41" ca="1">_FV(B41,"Price")</f>
-        <v>59.53</v>
+        <v>59.185000000000002</v>
       </c>
       <c r="F41" s="4">
         <f t="array" aca="1" ref="F41" ca="1">_FV(B41,"Change (%)",TRUE)</f>
-        <v>9.530799999999999E-2</v>
+        <v>8.8960000000000011E-2</v>
       </c>
       <c r="G41" s="5">
         <f t="array" aca="1" ref="G41" ca="1">_FV(B41,"Change")</f>
-        <v>5.18</v>
+        <v>4.835</v>
       </c>
       <c r="H41" s="6">
         <f t="array" aca="1" ref="H41" ca="1">_FV(B41,"P/E",TRUE)</f>
-        <v>129.77979999999999</v>
+        <v>129.02770000000001</v>
       </c>
       <c r="I41" s="6">
         <f t="array" aca="1" ref="I41" ca="1">_FV(B41,"Beta")</f>
@@ -17666,7 +17670,7 @@
       </c>
       <c r="P41" s="7">
         <f t="array" aca="1" ref="P41" ca="1">_FV(B41,"Volume")</f>
-        <v>26151104</v>
+        <v>31627223</v>
       </c>
       <c r="Q41" s="7">
         <f t="array" aca="1" ref="Q41" ca="1">_FV(B41,"Volume average",TRUE)</f>
@@ -17686,7 +17690,7 @@
       </c>
       <c r="U41" s="7">
         <f t="array" aca="1" ref="U41" ca="1">_FV(B41,"Market cap",TRUE)</f>
-        <v>21274754011</v>
+        <v>21151458359</v>
       </c>
       <c r="V41" s="7">
         <f t="array" aca="1" ref="V41" ca="1">_FV(B41,"Shares outstanding",TRUE)</f>
@@ -17702,7 +17706,7 @@
       </c>
       <c r="C42" s="2" cm="1">
         <f t="array" aca="1" ref="C42" ca="1">_FV(B42,"Last trade time",TRUE)</f>
-        <v>46181.758987603906</v>
+        <v>46181.82605148125</v>
       </c>
       <c r="D42" t="str" cm="1">
         <f t="array" aca="1" ref="D42" ca="1">_FV(B42,"Currency")</f>
@@ -17710,15 +17714,15 @@
       </c>
       <c r="E42" s="3" cm="1">
         <f t="array" aca="1" ref="E42" ca="1">_FV(B42,"Price")</f>
-        <v>284.67</v>
+        <v>284.29000000000002</v>
       </c>
       <c r="F42" s="4" cm="1">
         <f t="array" aca="1" ref="F42" ca="1">_FV(B42,"Change (%)",TRUE)</f>
-        <v>1.0723E-2</v>
+        <v>9.3729999999999994E-3</v>
       </c>
       <c r="G42" s="5" cm="1">
         <f t="array" aca="1" ref="G42" ca="1">_FV(B42,"Change")</f>
-        <v>3.02</v>
+        <v>2.64</v>
       </c>
       <c r="H42" s="6" t="e" vm="13">
         <f t="array" ref="H42">_FV(B42,"P/E",TRUE)</f>
@@ -17754,7 +17758,7 @@
       </c>
       <c r="P42" s="7" cm="1">
         <f t="array" aca="1" ref="P42" ca="1">_FV(B42,"Volume")</f>
-        <v>19561406</v>
+        <v>23721756</v>
       </c>
       <c r="Q42" s="7" cm="1">
         <f t="array" aca="1" ref="Q42" ca="1">_FV(B42,"Volume average",TRUE)</f>
@@ -17790,7 +17794,7 @@
       </c>
       <c r="C43" s="2" cm="1">
         <f t="array" aca="1" ref="C43" ca="1">_FV(B43,"Last trade time",TRUE)</f>
-        <v>46181.758929409378</v>
+        <v>46181.826017117972</v>
       </c>
       <c r="D43" t="str" cm="1">
         <f t="array" aca="1" ref="D43" ca="1">_FV(B43,"Currency")</f>
@@ -17798,19 +17802,19 @@
       </c>
       <c r="E43" s="3" cm="1">
         <f t="array" aca="1" ref="E43" ca="1">_FV(B43,"Price")</f>
-        <v>2127.1999999999998</v>
+        <v>2103.98</v>
       </c>
       <c r="F43" s="4" cm="1">
         <f t="array" aca="1" ref="F43" ca="1">_FV(B43,"Change (%)",TRUE)</f>
-        <v>0.10263299999999999</v>
+        <v>9.0596999999999997E-2</v>
       </c>
       <c r="G43" s="5" cm="1">
         <f t="array" aca="1" ref="G43" ca="1">_FV(B43,"Change")</f>
-        <v>198</v>
+        <v>174.78</v>
       </c>
       <c r="H43" s="6" cm="1">
         <f t="array" aca="1" ref="H43" ca="1">_FV(B43,"P/E",TRUE)</f>
-        <v>602.26499999999999</v>
+        <v>595.69079999999997</v>
       </c>
       <c r="I43" s="6" cm="1">
         <f t="array" aca="1" ref="I43" ca="1">_FV(B43,"Beta")</f>
@@ -17842,7 +17846,7 @@
       </c>
       <c r="P43" s="7" cm="1">
         <f t="array" aca="1" ref="P43" ca="1">_FV(B43,"Volume")</f>
-        <v>648848</v>
+        <v>814506</v>
       </c>
       <c r="Q43" s="7" cm="1">
         <f t="array" aca="1" ref="Q43" ca="1">_FV(B43,"Volume average",TRUE)</f>
@@ -17862,7 +17866,7 @@
       </c>
       <c r="U43" s="7" cm="1">
         <f t="array" aca="1" ref="U43" ca="1">_FV(B43,"Market cap",TRUE)</f>
-        <v>277870818000</v>
+        <v>274837647450</v>
       </c>
       <c r="V43" s="7" cm="1">
         <f t="array" aca="1" ref="V43" ca="1">_FV(B43,"Shares outstanding",TRUE)</f>
@@ -17878,7 +17882,7 @@
       </c>
       <c r="C44" s="2">
         <f t="array" aca="1" ref="C44" ca="1">_FV(B44,"Last trade time",TRUE)</f>
-        <v>46181.758965370311</v>
+        <v>46181.826043089844</v>
       </c>
       <c r="D44" t="str">
         <f t="array" aca="1" ref="D44" ca="1">_FV(B44,"Currency")</f>
@@ -17886,19 +17890,19 @@
       </c>
       <c r="E44" s="3">
         <f t="array" aca="1" ref="E44" ca="1">_FV(B44,"Price")</f>
-        <v>79.47</v>
+        <v>79.495000000000005</v>
       </c>
       <c r="F44" s="4">
         <f t="array" aca="1" ref="F44" ca="1">_FV(B44,"Change (%)",TRUE)</f>
-        <v>-1.2579999999999999E-4</v>
+        <v>1.8870000000000001E-4</v>
       </c>
       <c r="G44" s="5">
         <f t="array" aca="1" ref="G44" ca="1">_FV(B44,"Change")</f>
-        <v>-0.01</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="H44" s="6">
         <f t="array" aca="1" ref="H44" ca="1">_FV(B44,"P/E",TRUE)</f>
-        <v>25.0181</v>
+        <v>25.026</v>
       </c>
       <c r="I44" s="6">
         <f t="array" aca="1" ref="I44" ca="1">_FV(B44,"Beta")</f>
@@ -17930,7 +17934,7 @@
       </c>
       <c r="P44" s="7">
         <f t="array" aca="1" ref="P44" ca="1">_FV(B44,"Volume")</f>
-        <v>5724137</v>
+        <v>7092673</v>
       </c>
       <c r="Q44" s="7">
         <f t="array" aca="1" ref="Q44" ca="1">_FV(B44,"Volume average",TRUE)</f>
@@ -17950,7 +17954,7 @@
       </c>
       <c r="U44" s="7">
         <f t="array" aca="1" ref="U44" ca="1">_FV(B44,"Market cap",TRUE)</f>
-        <v>341918244540</v>
+        <v>342025806590</v>
       </c>
       <c r="V44" s="7">
         <f t="array" aca="1" ref="V44" ca="1">_FV(B44,"Shares outstanding",TRUE)</f>
@@ -17966,7 +17970,7 @@
       </c>
       <c r="C45" s="2">
         <f t="array" aca="1" ref="C45" ca="1">_FV(B45,"Last trade time",TRUE)</f>
-        <v>46181.758853356252</v>
+        <v>46181.82598611094</v>
       </c>
       <c r="D45" t="str">
         <f t="array" aca="1" ref="D45" ca="1">_FV(B45,"Currency")</f>
@@ -17974,15 +17978,15 @@
       </c>
       <c r="E45" s="3">
         <f t="array" aca="1" ref="E45" ca="1">_FV(B45,"Price")</f>
-        <v>15.049899999999999</v>
+        <v>14.84</v>
       </c>
       <c r="F45" s="4">
         <f t="array" aca="1" ref="F45" ca="1">_FV(B45,"Change (%)",TRUE)</f>
-        <v>8.0309999999999999E-3</v>
+        <v>-6.0280000000000004E-3</v>
       </c>
       <c r="G45" s="5">
         <f t="array" aca="1" ref="G45" ca="1">_FV(B45,"Change")</f>
-        <v>0.11990000000000001</v>
+        <v>-0.09</v>
       </c>
       <c r="H45" s="6">
         <f t="array" aca="1" ref="H45" ca="1">_FV(B45,"P/E",TRUE)</f>
@@ -18006,7 +18010,7 @@
       </c>
       <c r="M45" s="3">
         <f t="array" aca="1" ref="M45" ca="1">_FV(B45,"Low")</f>
-        <v>14.7</v>
+        <v>14.56</v>
       </c>
       <c r="N45" s="3">
         <f t="array" aca="1" ref="N45" ca="1">_FV(B45,"Open")</f>
@@ -18018,7 +18022,7 @@
       </c>
       <c r="P45" s="7">
         <f t="array" aca="1" ref="P45" ca="1">_FV(B45,"Volume")</f>
-        <v>1765365</v>
+        <v>2529351</v>
       </c>
       <c r="Q45" s="7">
         <f t="array" aca="1" ref="Q45" ca="1">_FV(B45,"Volume average",TRUE)</f>
@@ -18038,7 +18042,7 @@
       </c>
       <c r="U45" s="7">
         <f t="array" aca="1" ref="U45" ca="1">_FV(B45,"Market cap",TRUE)</f>
-        <v>998723554</v>
+        <v>984794420</v>
       </c>
       <c r="V45" s="7">
         <f t="array" aca="1" ref="V45" ca="1">_FV(B45,"Shares outstanding",TRUE)</f>
@@ -18054,7 +18058,7 @@
       </c>
       <c r="C46" s="2">
         <f t="array" aca="1" ref="C46" ca="1">_FV(B46,"Last trade time",TRUE)</f>
-        <v>46181.75886872656</v>
+        <v>46181.82605111094</v>
       </c>
       <c r="D46" t="str">
         <f t="array" aca="1" ref="D46" ca="1">_FV(B46,"Currency")</f>
@@ -18062,15 +18066,15 @@
       </c>
       <c r="E46" s="3">
         <f t="array" aca="1" ref="E46" ca="1">_FV(B46,"Price")</f>
-        <v>10.164999999999999</v>
+        <v>10.020099999999999</v>
       </c>
       <c r="F46" s="4">
         <f t="array" aca="1" ref="F46" ca="1">_FV(B46,"Change (%)",TRUE)</f>
-        <v>2.4650000000000002E-3</v>
+        <v>-1.1823999999999999E-2</v>
       </c>
       <c r="G46" s="5">
         <f t="array" aca="1" ref="G46" ca="1">_FV(B46,"Change")</f>
-        <v>2.5000000000000001E-2</v>
+        <v>-0.11990000000000001</v>
       </c>
       <c r="H46" s="6">
         <f t="array" aca="1" ref="H46" ca="1">_FV(B46,"P/E",TRUE)</f>
@@ -18094,7 +18098,7 @@
       </c>
       <c r="M46" s="3">
         <f t="array" aca="1" ref="M46" ca="1">_FV(B46,"Low")</f>
-        <v>9.92</v>
+        <v>9.8901000000000003</v>
       </c>
       <c r="N46" s="3">
         <f t="array" aca="1" ref="N46" ca="1">_FV(B46,"Open")</f>
@@ -18106,7 +18110,7 @@
       </c>
       <c r="P46" s="7">
         <f t="array" aca="1" ref="P46" ca="1">_FV(B46,"Volume")</f>
-        <v>3259873</v>
+        <v>4365654</v>
       </c>
       <c r="Q46" s="7">
         <f t="array" aca="1" ref="Q46" ca="1">_FV(B46,"Volume average",TRUE)</f>
@@ -18126,7 +18130,7 @@
       </c>
       <c r="U46" s="7">
         <f t="array" aca="1" ref="U46" ca="1">_FV(B46,"Market cap",TRUE)</f>
-        <v>1566219133</v>
+        <v>1543892999</v>
       </c>
       <c r="V46" s="7">
         <f t="array" aca="1" ref="V46" ca="1">_FV(B46,"Shares outstanding",TRUE)</f>
@@ -18142,7 +18146,7 @@
       </c>
       <c r="C47" s="2" cm="1">
         <f t="array" aca="1" ref="C47" ca="1">_FV(B47,"Last trade time",TRUE)</f>
-        <v>46181.758988171096</v>
+        <v>46181.82603943281</v>
       </c>
       <c r="D47" t="str" cm="1">
         <f t="array" aca="1" ref="D47" ca="1">_FV(B47,"Currency")</f>
@@ -18150,19 +18154,19 @@
       </c>
       <c r="E47" s="3" cm="1">
         <f t="array" aca="1" ref="E47" ca="1">_FV(B47,"Price")</f>
-        <v>278.02</v>
+        <v>278.18</v>
       </c>
       <c r="F47" s="4" cm="1">
         <f t="array" aca="1" ref="F47" ca="1">_FV(B47,"Change (%)",TRUE)</f>
-        <v>-6.5039999999999994E-3</v>
+        <v>-5.9319999999999998E-3</v>
       </c>
       <c r="G47" s="5" cm="1">
         <f t="array" aca="1" ref="G47" ca="1">_FV(B47,"Change")</f>
-        <v>-1.82</v>
+        <v>-1.66</v>
       </c>
       <c r="H47" s="6" cm="1">
         <f t="array" aca="1" ref="H47" ca="1">_FV(B47,"P/E",TRUE)</f>
-        <v>22.916799999999999</v>
+        <v>22.93</v>
       </c>
       <c r="I47" s="6" cm="1">
         <f t="array" aca="1" ref="I47" ca="1">_FV(B47,"Beta")</f>
@@ -18194,7 +18198,7 @@
       </c>
       <c r="P47" s="7" cm="1">
         <f t="array" aca="1" ref="P47" ca="1">_FV(B47,"Volume")</f>
-        <v>1763031</v>
+        <v>2386957</v>
       </c>
       <c r="Q47" s="7" cm="1">
         <f t="array" aca="1" ref="Q47" ca="1">_FV(B47,"Volume average",TRUE)</f>
@@ -18214,7 +18218,7 @@
       </c>
       <c r="U47" s="7" cm="1">
         <f t="array" aca="1" ref="U47" ca="1">_FV(B47,"Market cap",TRUE)</f>
-        <v>197534850318</v>
+        <v>197648531262</v>
       </c>
       <c r="V47" s="7" cm="1">
         <f t="array" aca="1" ref="V47" ca="1">_FV(B47,"Shares outstanding",TRUE)</f>
@@ -18230,7 +18234,7 @@
       </c>
       <c r="C48" s="2" cm="1">
         <f t="array" aca="1" ref="C48" ca="1">_FV(B48,"Last trade time",TRUE)</f>
-        <v>46181.75896818281</v>
+        <v>46181.825996539061</v>
       </c>
       <c r="D48" t="str" cm="1">
         <f t="array" aca="1" ref="D48" ca="1">_FV(B48,"Currency")</f>
@@ -18238,15 +18242,15 @@
       </c>
       <c r="E48" s="3" cm="1">
         <f t="array" aca="1" ref="E48" ca="1">_FV(B48,"Price")</f>
-        <v>353.44</v>
+        <v>352.51499999999999</v>
       </c>
       <c r="F48" s="4" cm="1">
         <f t="array" aca="1" ref="F48" ca="1">_FV(B48,"Change (%)",TRUE)</f>
-        <v>7.698E-3</v>
+        <v>5.0609999999999995E-3</v>
       </c>
       <c r="G48" s="5" cm="1">
         <f t="array" aca="1" ref="G48" ca="1">_FV(B48,"Change")</f>
-        <v>2.7</v>
+        <v>1.7749999999999999</v>
       </c>
       <c r="H48" s="6" cm="1">
         <f t="array" aca="1" ref="H48" ca="1">_FV(B48,"P/E",TRUE)</f>
@@ -18282,7 +18286,7 @@
       </c>
       <c r="P48" s="7" cm="1">
         <f t="array" aca="1" ref="P48" ca="1">_FV(B48,"Volume")</f>
-        <v>1184915</v>
+        <v>1361915</v>
       </c>
       <c r="Q48" s="7" cm="1">
         <f t="array" aca="1" ref="Q48" ca="1">_FV(B48,"Volume average",TRUE)</f>
@@ -18302,7 +18306,7 @@
       </c>
       <c r="U48" s="7" cm="1">
         <f t="array" aca="1" ref="U48" ca="1">_FV(B48,"Market cap",TRUE)</f>
-        <v>28427861339</v>
+        <v>28353461803</v>
       </c>
       <c r="V48" s="7" cm="1">
         <f t="array" aca="1" ref="V48" ca="1">_FV(B48,"Shares outstanding",TRUE)</f>
@@ -18318,7 +18322,7 @@
       </c>
       <c r="C49" s="2">
         <f t="array" aca="1" ref="C49" ca="1">_FV(B49,"Last trade time",TRUE)</f>
-        <v>46181.758963703127</v>
+        <v>46181.826033089841</v>
       </c>
       <c r="D49" t="str">
         <f t="array" aca="1" ref="D49" ca="1">_FV(B49,"Currency")</f>
@@ -18326,19 +18330,19 @@
       </c>
       <c r="E49" s="3">
         <f t="array" aca="1" ref="E49" ca="1">_FV(B49,"Price")</f>
-        <v>587.42999999999995</v>
+        <v>589.57000000000005</v>
       </c>
       <c r="F49" s="4">
         <f t="array" aca="1" ref="F49" ca="1">_FV(B49,"Change (%)",TRUE)</f>
-        <v>-9.3930000000000003E-3</v>
+        <v>-5.7840000000000001E-3</v>
       </c>
       <c r="G49" s="5">
         <f t="array" aca="1" ref="G49" ca="1">_FV(B49,"Change")</f>
-        <v>-5.57</v>
+        <v>-3.43</v>
       </c>
       <c r="H49" s="6">
         <f t="array" aca="1" ref="H49" ca="1">_FV(B49,"P/E",TRUE)</f>
-        <v>17.817599999999999</v>
+        <v>17.8826</v>
       </c>
       <c r="I49" s="6">
         <f t="array" aca="1" ref="I49" ca="1">_FV(B49,"Beta")</f>
@@ -18370,7 +18374,7 @@
       </c>
       <c r="P49" s="7">
         <f t="array" aca="1" ref="P49" ca="1">_FV(B49,"Volume")</f>
-        <v>8993627</v>
+        <v>10708591</v>
       </c>
       <c r="Q49" s="7">
         <f t="array" aca="1" ref="Q49" ca="1">_FV(B49,"Volume average",TRUE)</f>
@@ -18390,7 +18394,7 @@
       </c>
       <c r="U49" s="7">
         <f t="array" aca="1" ref="U49" ca="1">_FV(B49,"Market cap",TRUE)</f>
-        <v>1491145822889</v>
+        <v>1496578048110</v>
       </c>
       <c r="V49" s="7">
         <f t="array" aca="1" ref="V49" ca="1">_FV(B49,"Shares outstanding",TRUE)</f>
@@ -18406,7 +18410,7 @@
       </c>
       <c r="C50" s="2">
         <f t="array" aca="1" ref="C50" ca="1">_FV(B50,"Last trade time",TRUE)</f>
-        <v>46181.75899583281</v>
+        <v>46181.826047303126</v>
       </c>
       <c r="D50" t="str">
         <f t="array" aca="1" ref="D50" ca="1">_FV(B50,"Currency")</f>
@@ -18414,19 +18418,19 @@
       </c>
       <c r="E50" s="3">
         <f t="array" aca="1" ref="E50" ca="1">_FV(B50,"Price")</f>
-        <v>300.58</v>
+        <v>291.36</v>
       </c>
       <c r="F50" s="4">
         <f t="array" aca="1" ref="F50" ca="1">_FV(B50,"Change (%)",TRUE)</f>
-        <v>0.140851</v>
+        <v>0.10585599999999999</v>
       </c>
       <c r="G50" s="5">
         <f t="array" aca="1" ref="G50" ca="1">_FV(B50,"Change")</f>
-        <v>37.11</v>
+        <v>27.89</v>
       </c>
       <c r="H50" s="6">
         <f t="array" aca="1" ref="H50" ca="1">_FV(B50,"P/E",TRUE)</f>
-        <v>102.956</v>
+        <v>99.797899999999998</v>
       </c>
       <c r="I50" s="6">
         <f t="array" aca="1" ref="I50" ca="1">_FV(B50,"Beta")</f>
@@ -18458,7 +18462,7 @@
       </c>
       <c r="P50" s="7">
         <f t="array" aca="1" ref="P50" ca="1">_FV(B50,"Volume")</f>
-        <v>61583056</v>
+        <v>73446248</v>
       </c>
       <c r="Q50" s="7">
         <f t="array" aca="1" ref="Q50" ca="1">_FV(B50,"Volume average",TRUE)</f>
@@ -18478,7 +18482,7 @@
       </c>
       <c r="U50" s="7">
         <f t="array" aca="1" ref="U50" ca="1">_FV(B50,"Market cap",TRUE)</f>
-        <v>262947384000</v>
+        <v>254881728000</v>
       </c>
       <c r="V50" s="7">
         <f t="array" aca="1" ref="V50" ca="1">_FV(B50,"Shares outstanding",TRUE)</f>
@@ -18494,7 +18498,7 @@
       </c>
       <c r="C51" s="2">
         <f t="array" aca="1" ref="C51" ca="1">_FV(B51,"Last trade time",TRUE)</f>
-        <v>46181.758975080469</v>
+        <v>46181.826041828128</v>
       </c>
       <c r="D51" t="str">
         <f t="array" aca="1" ref="D51" ca="1">_FV(B51,"Currency")</f>
@@ -18502,19 +18506,19 @@
       </c>
       <c r="E51" s="3">
         <f t="array" aca="1" ref="E51" ca="1">_FV(B51,"Price")</f>
-        <v>412.32</v>
+        <v>412.84</v>
       </c>
       <c r="F51" s="4">
         <f t="array" aca="1" ref="F51" ca="1">_FV(B51,"Change (%)",TRUE)</f>
-        <v>-1.044E-2</v>
+        <v>-9.1920000000000005E-3</v>
       </c>
       <c r="G51" s="5">
         <f t="array" aca="1" ref="G51" ca="1">_FV(B51,"Change")</f>
-        <v>-4.3499999999999996</v>
+        <v>-3.83</v>
       </c>
       <c r="H51" s="6">
         <f t="array" aca="1" ref="H51" ca="1">_FV(B51,"P/E",TRUE)</f>
-        <v>24.5581</v>
+        <v>24.588999999999999</v>
       </c>
       <c r="I51" s="6">
         <f t="array" aca="1" ref="I51" ca="1">_FV(B51,"Beta")</f>
@@ -18546,7 +18550,7 @@
       </c>
       <c r="P51" s="7">
         <f t="array" aca="1" ref="P51" ca="1">_FV(B51,"Volume")</f>
-        <v>17476438</v>
+        <v>21060799</v>
       </c>
       <c r="Q51" s="7">
         <f t="array" aca="1" ref="Q51" ca="1">_FV(B51,"Volume average",TRUE)</f>
@@ -18566,7 +18570,7 @@
       </c>
       <c r="U51" s="7">
         <f t="array" aca="1" ref="U51" ca="1">_FV(B51,"Market cap",TRUE)</f>
-        <v>3062892319200</v>
+        <v>3066755105400</v>
       </c>
       <c r="V51" s="7">
         <f t="array" aca="1" ref="V51" ca="1">_FV(B51,"Shares outstanding",TRUE)</f>
@@ -18582,7 +18586,7 @@
       </c>
       <c r="C52" s="2">
         <f t="array" aca="1" ref="C52" ca="1">_FV(B52,"Last trade time",TRUE)</f>
-        <v>46181.758922522655</v>
+        <v>46181.825977128909</v>
       </c>
       <c r="D52" t="str">
         <f t="array" aca="1" ref="D52" ca="1">_FV(B52,"Currency")</f>
@@ -18590,15 +18594,15 @@
       </c>
       <c r="E52" s="3">
         <f t="array" aca="1" ref="E52" ca="1">_FV(B52,"Price")</f>
-        <v>127.92</v>
+        <v>127.36499999999999</v>
       </c>
       <c r="F52" s="4">
         <f t="array" aca="1" ref="F52" ca="1">_FV(B52,"Change (%)",TRUE)</f>
-        <v>6.2106000000000001E-2</v>
+        <v>5.7497999999999994E-2</v>
       </c>
       <c r="G52" s="5">
         <f t="array" aca="1" ref="G52" ca="1">_FV(B52,"Change")</f>
-        <v>7.48</v>
+        <v>6.9249999999999998</v>
       </c>
       <c r="H52" s="6">
         <f t="array" aca="1" ref="H52" ca="1">_FV(B52,"P/E",TRUE)</f>
@@ -18634,7 +18638,7 @@
       </c>
       <c r="P52" s="7">
         <f t="array" aca="1" ref="P52" ca="1">_FV(B52,"Volume")</f>
-        <v>13978206</v>
+        <v>16458677</v>
       </c>
       <c r="Q52" s="7">
         <f t="array" aca="1" ref="Q52" ca="1">_FV(B52,"Volume average",TRUE)</f>
@@ -18654,7 +18658,7 @@
       </c>
       <c r="U52" s="7">
         <f t="array" aca="1" ref="U52" ca="1">_FV(B52,"Market cap",TRUE)</f>
-        <v>45820675368</v>
+        <v>45621875533</v>
       </c>
       <c r="V52" s="7">
         <f t="array" aca="1" ref="V52" ca="1">_FV(B52,"Shares outstanding",TRUE)</f>
@@ -18670,7 +18674,7 @@
       </c>
       <c r="C53" s="2">
         <f t="array" aca="1" ref="C53" ca="1">_FV(B53,"Last trade time",TRUE)</f>
-        <v>46181.758937175779</v>
+        <v>46181.825993876562</v>
       </c>
       <c r="D53" t="str">
         <f t="array" aca="1" ref="D53" ca="1">_FV(B53,"Currency")</f>
@@ -18678,19 +18682,19 @@
       </c>
       <c r="E53" s="3">
         <f t="array" aca="1" ref="E53" ca="1">_FV(B53,"Price")</f>
-        <v>953.45</v>
+        <v>936.81</v>
       </c>
       <c r="F53" s="4">
         <f t="array" aca="1" ref="F53" ca="1">_FV(B53,"Change (%)",TRUE)</f>
-        <v>0.103517</v>
+        <v>8.4258E-2</v>
       </c>
       <c r="G53" s="5">
         <f t="array" aca="1" ref="G53" ca="1">_FV(B53,"Change")</f>
-        <v>89.44</v>
+        <v>72.8</v>
       </c>
       <c r="H53" s="6">
         <f t="array" aca="1" ref="H53" ca="1">_FV(B53,"P/E",TRUE)</f>
-        <v>45.013800000000003</v>
+        <v>44.228200000000001</v>
       </c>
       <c r="I53" s="6">
         <f t="array" aca="1" ref="I53" ca="1">_FV(B53,"Beta")</f>
@@ -18722,7 +18726,7 @@
       </c>
       <c r="P53" s="7">
         <f t="array" aca="1" ref="P53" ca="1">_FV(B53,"Volume")</f>
-        <v>39949230</v>
+        <v>47167463</v>
       </c>
       <c r="Q53" s="7">
         <f t="array" aca="1" ref="Q53" ca="1">_FV(B53,"Volume average",TRUE)</f>
@@ -18742,7 +18746,7 @@
       </c>
       <c r="U53" s="7">
         <f t="array" aca="1" ref="U53" ca="1">_FV(B53,"Market cap",TRUE)</f>
-        <v>1075237982300</v>
+        <v>1056472488539</v>
       </c>
       <c r="V53" s="7">
         <f t="array" aca="1" ref="V53" ca="1">_FV(B53,"Shares outstanding",TRUE)</f>
@@ -18758,7 +18762,7 @@
       </c>
       <c r="C54" s="2" cm="1">
         <f t="array" aca="1" ref="C54" ca="1">_FV(B54,"Last trade time",TRUE)</f>
-        <v>46181.758879108595</v>
+        <v>46181.825942742966</v>
       </c>
       <c r="D54" t="str" cm="1">
         <f t="array" aca="1" ref="D54" ca="1">_FV(B54,"Currency")</f>
@@ -18766,15 +18770,15 @@
       </c>
       <c r="E54" s="3" cm="1">
         <f t="array" aca="1" ref="E54" ca="1">_FV(B54,"Price")</f>
-        <v>248.14</v>
+        <v>247.5804</v>
       </c>
       <c r="F54" s="4" cm="1">
         <f t="array" aca="1" ref="F54" ca="1">_FV(B54,"Change (%)",TRUE)</f>
-        <v>-7.8770000000000003E-3</v>
+        <v>-1.0114000000000001E-2</v>
       </c>
       <c r="G54" s="5" cm="1">
         <f t="array" aca="1" ref="G54" ca="1">_FV(B54,"Change")</f>
-        <v>-1.97</v>
+        <v>-2.5295999999999998</v>
       </c>
       <c r="H54" s="6" t="e" cm="1" vm="13">
         <f t="array" ref="H54">_FV(B54,"P/E",TRUE)</f>
@@ -18810,7 +18814,7 @@
       </c>
       <c r="P54" s="7" cm="1">
         <f t="array" aca="1" ref="P54" ca="1">_FV(B54,"Volume")</f>
-        <v>1692810</v>
+        <v>2501060</v>
       </c>
       <c r="Q54" s="7" cm="1">
         <f t="array" aca="1" ref="Q54" ca="1">_FV(B54,"Volume average",TRUE)</f>
@@ -18830,7 +18834,7 @@
       </c>
       <c r="U54" s="7" cm="1">
         <f t="array" aca="1" ref="U54" ca="1">_FV(B54,"Market cap",TRUE)</f>
-        <v>87709102868</v>
+        <v>87511303182</v>
       </c>
       <c r="V54" s="7" cm="1">
         <f t="array" aca="1" ref="V54" ca="1">_FV(B54,"Shares outstanding",TRUE)</f>
@@ -18846,7 +18850,7 @@
       </c>
       <c r="C55" s="2" cm="1">
         <f t="array" aca="1" ref="C55" ca="1">_FV(B55,"Last trade time",TRUE)</f>
-        <v>46181.747916666667</v>
+        <v>46181.81527777778</v>
       </c>
       <c r="D55" t="str" cm="1">
         <f t="array" aca="1" ref="D55" ca="1">_FV(B55,"Currency")</f>
@@ -18934,7 +18938,7 @@
       </c>
       <c r="C56" s="2">
         <f t="array" aca="1" ref="C56" ca="1">_FV(B56,"Last trade time",TRUE)</f>
-        <v>46181.758973483593</v>
+        <v>46181.826048171097</v>
       </c>
       <c r="D56" t="str">
         <f t="array" aca="1" ref="D56" ca="1">_FV(B56,"Currency")</f>
@@ -18942,19 +18946,19 @@
       </c>
       <c r="E56" s="3">
         <f t="array" aca="1" ref="E56" ca="1">_FV(B56,"Price")</f>
-        <v>14.654999999999999</v>
+        <v>14.535</v>
       </c>
       <c r="F56" s="4">
         <f t="array" aca="1" ref="F56" ca="1">_FV(B56,"Change (%)",TRUE)</f>
-        <v>1.9124000000000002E-2</v>
+        <v>1.0779E-2</v>
       </c>
       <c r="G56" s="5">
         <f t="array" aca="1" ref="G56" ca="1">_FV(B56,"Change")</f>
-        <v>0.27500000000000002</v>
+        <v>0.155</v>
       </c>
       <c r="H56" s="6">
         <f t="array" aca="1" ref="H56" ca="1">_FV(B56,"P/E",TRUE)</f>
-        <v>91.081400000000002</v>
+        <v>90.335599999999999</v>
       </c>
       <c r="I56" s="6">
         <f t="array" aca="1" ref="I56" ca="1">_FV(B56,"Beta")</f>
@@ -18986,7 +18990,7 @@
       </c>
       <c r="P56" s="7">
         <f t="array" aca="1" ref="P56" ca="1">_FV(B56,"Volume")</f>
-        <v>84324029</v>
+        <v>97159904</v>
       </c>
       <c r="Q56" s="7">
         <f t="array" aca="1" ref="Q56" ca="1">_FV(B56,"Volume average",TRUE)</f>
@@ -19006,7 +19010,7 @@
       </c>
       <c r="U56" s="7">
         <f t="array" aca="1" ref="U56" ca="1">_FV(B56,"Market cap",TRUE)</f>
-        <v>84152527200</v>
+        <v>83463458400</v>
       </c>
       <c r="V56" s="7">
         <f t="array" aca="1" ref="V56" ca="1">_FV(B56,"Shares outstanding",TRUE)</f>
@@ -19022,7 +19026,7 @@
       </c>
       <c r="C57" s="2">
         <f t="array" aca="1" ref="C57" ca="1">_FV(B57,"Last trade time",TRUE)</f>
-        <v>46181.758879594534</v>
+        <v>46181.825956562498</v>
       </c>
       <c r="D57" t="str">
         <f t="array" aca="1" ref="D57" ca="1">_FV(B57,"Currency")</f>
@@ -19030,19 +19034,19 @@
       </c>
       <c r="E57" s="3">
         <f t="array" aca="1" ref="E57" ca="1">_FV(B57,"Price")</f>
-        <v>114.82</v>
+        <v>114.9499</v>
       </c>
       <c r="F57" s="4">
         <f t="array" aca="1" ref="F57" ca="1">_FV(B57,"Change (%)",TRUE)</f>
-        <v>2.1076000000000001E-2</v>
+        <v>2.2231000000000001E-2</v>
       </c>
       <c r="G57" s="5">
         <f t="array" aca="1" ref="G57" ca="1">_FV(B57,"Change")</f>
-        <v>2.37</v>
+        <v>2.4998999999999998</v>
       </c>
       <c r="H57" s="6">
         <f t="array" aca="1" ref="H57" ca="1">_FV(B57,"P/E",TRUE)</f>
-        <v>68.288300000000007</v>
+        <v>68.365600000000001</v>
       </c>
       <c r="I57" s="6">
         <f t="array" aca="1" ref="I57" ca="1">_FV(B57,"Beta")</f>
@@ -19074,7 +19078,7 @@
       </c>
       <c r="P57" s="7">
         <f t="array" aca="1" ref="P57" ca="1">_FV(B57,"Volume")</f>
-        <v>13131042</v>
+        <v>15931641</v>
       </c>
       <c r="Q57" s="7">
         <f t="array" aca="1" ref="Q57" ca="1">_FV(B57,"Volume average",TRUE)</f>
@@ -19094,7 +19098,7 @@
       </c>
       <c r="U57" s="7">
         <f t="array" aca="1" ref="U57" ca="1">_FV(B57,"Market cap",TRUE)</f>
-        <v>118414784560</v>
+        <v>118548751469</v>
       </c>
       <c r="V57" s="7">
         <f t="array" aca="1" ref="V57" ca="1">_FV(B57,"Shares outstanding",TRUE)</f>
@@ -19110,7 +19114,7 @@
       </c>
       <c r="C58" s="2">
         <f t="array" aca="1" ref="C58" ca="1">_FV(B58,"Last trade time",TRUE)</f>
-        <v>46181.758916353909</v>
+        <v>46181.825983159375</v>
       </c>
       <c r="D58" t="str">
         <f t="array" aca="1" ref="D58" ca="1">_FV(B58,"Currency")</f>
@@ -19118,19 +19122,19 @@
       </c>
       <c r="E58" s="3">
         <f t="array" aca="1" ref="E58" ca="1">_FV(B58,"Price")</f>
-        <v>208.97</v>
+        <v>207.83500000000001</v>
       </c>
       <c r="F58" s="4">
         <f t="array" aca="1" ref="F58" ca="1">_FV(B58,"Change (%)",TRUE)</f>
-        <v>1.8869E-2</v>
+        <v>1.3335E-2</v>
       </c>
       <c r="G58" s="5">
         <f t="array" aca="1" ref="G58" ca="1">_FV(B58,"Change")</f>
-        <v>3.87</v>
+        <v>2.7349999999999999</v>
       </c>
       <c r="H58" s="6">
         <f t="array" aca="1" ref="H58" ca="1">_FV(B58,"P/E",TRUE)</f>
-        <v>32.0015</v>
+        <v>31.8277</v>
       </c>
       <c r="I58" s="6">
         <f t="array" aca="1" ref="I58" ca="1">_FV(B58,"Beta")</f>
@@ -19162,7 +19166,7 @@
       </c>
       <c r="P58" s="7">
         <f t="array" aca="1" ref="P58" ca="1">_FV(B58,"Volume")</f>
-        <v>92076976</v>
+        <v>107341423</v>
       </c>
       <c r="Q58" s="7">
         <f t="array" aca="1" ref="Q58" ca="1">_FV(B58,"Volume average",TRUE)</f>
@@ -19182,7 +19186,7 @@
       </c>
       <c r="U58" s="7">
         <f t="array" aca="1" ref="U58" ca="1">_FV(B58,"Market cap",TRUE)</f>
-        <v>5057074000000</v>
+        <v>5029607000000</v>
       </c>
       <c r="V58" s="7">
         <f t="array" aca="1" ref="V58" ca="1">_FV(B58,"Shares outstanding",TRUE)</f>
@@ -19198,7 +19202,7 @@
       </c>
       <c r="C59" s="2" cm="1">
         <f t="array" aca="1" ref="C59" ca="1">_FV(B59,"Last trade time",TRUE)</f>
-        <v>46181.758901503905</v>
+        <v>46181.82596407344</v>
       </c>
       <c r="D59" t="str" cm="1">
         <f t="array" aca="1" ref="D59" ca="1">_FV(B59,"Currency")</f>
@@ -19206,19 +19210,19 @@
       </c>
       <c r="E59" s="3" cm="1">
         <f t="array" aca="1" ref="E59" ca="1">_FV(B59,"Price")</f>
-        <v>122.48</v>
+        <v>121.35</v>
       </c>
       <c r="F59" s="4" cm="1">
         <f t="array" aca="1" ref="F59" ca="1">_FV(B59,"Change (%)",TRUE)</f>
-        <v>4.4516E-2</v>
+        <v>3.4880000000000001E-2</v>
       </c>
       <c r="G59" s="5" cm="1">
         <f t="array" aca="1" ref="G59" ca="1">_FV(B59,"Change")</f>
-        <v>5.22</v>
+        <v>4.09</v>
       </c>
       <c r="H59" s="6" cm="1">
         <f t="array" aca="1" ref="H59" ca="1">_FV(B59,"P/E",TRUE)</f>
-        <v>87.460700000000003</v>
+        <v>86.653800000000004</v>
       </c>
       <c r="I59" s="6" cm="1">
         <f t="array" aca="1" ref="I59" ca="1">_FV(B59,"Beta")</f>
@@ -19250,7 +19254,7 @@
       </c>
       <c r="P59" s="7" cm="1">
         <f t="array" aca="1" ref="P59" ca="1">_FV(B59,"Volume")</f>
-        <v>5973169</v>
+        <v>8388512</v>
       </c>
       <c r="Q59" s="7" cm="1">
         <f t="array" aca="1" ref="Q59" ca="1">_FV(B59,"Volume average",TRUE)</f>
@@ -19270,7 +19274,7 @@
       </c>
       <c r="U59" s="7" cm="1">
         <f t="array" aca="1" ref="U59" ca="1">_FV(B59,"Market cap",TRUE)</f>
-        <v>48000303936</v>
+        <v>47557453320</v>
       </c>
       <c r="V59" s="7" cm="1">
         <f t="array" aca="1" ref="V59" ca="1">_FV(B59,"Shares outstanding",TRUE)</f>
@@ -19286,7 +19290,7 @@
       </c>
       <c r="C60" s="2">
         <f t="array" aca="1" ref="C60" ca="1">_FV(B60,"Last trade time",TRUE)</f>
-        <v>46181.758914628903</v>
+        <v>46181.825999756249</v>
       </c>
       <c r="D60" t="str">
         <f t="array" aca="1" ref="D60" ca="1">_FV(B60,"Currency")</f>
@@ -19294,19 +19298,19 @@
       </c>
       <c r="E60" s="3">
         <f t="array" aca="1" ref="E60" ca="1">_FV(B60,"Price")</f>
-        <v>10.5</v>
+        <v>10.305</v>
       </c>
       <c r="F60" s="4">
         <f t="array" aca="1" ref="F60" ca="1">_FV(B60,"Change (%)",TRUE)</f>
-        <v>6.711E-3</v>
+        <v>-1.1984999999999999E-2</v>
       </c>
       <c r="G60" s="5">
         <f t="array" aca="1" ref="G60" ca="1">_FV(B60,"Change")</f>
-        <v>7.0000000000000007E-2</v>
+        <v>-0.125</v>
       </c>
       <c r="H60" s="6">
         <f t="array" aca="1" ref="H60" ca="1">_FV(B60,"P/E",TRUE)</f>
-        <v>26.475000000000001</v>
+        <v>25.9834</v>
       </c>
       <c r="I60" s="6">
         <f t="array" aca="1" ref="I60" ca="1">_FV(B60,"Beta")</f>
@@ -19326,7 +19330,7 @@
       </c>
       <c r="M60" s="3">
         <f t="array" aca="1" ref="M60" ca="1">_FV(B60,"Low")</f>
-        <v>10.365</v>
+        <v>10.25</v>
       </c>
       <c r="N60" s="3">
         <f t="array" aca="1" ref="N60" ca="1">_FV(B60,"Open")</f>
@@ -19338,7 +19342,7 @@
       </c>
       <c r="P60" s="7">
         <f t="array" aca="1" ref="P60" ca="1">_FV(B60,"Volume")</f>
-        <v>28451220</v>
+        <v>35683679</v>
       </c>
       <c r="Q60" s="7">
         <f t="array" aca="1" ref="Q60" ca="1">_FV(B60,"Volume average",TRUE)</f>
@@ -19358,7 +19362,7 @@
       </c>
       <c r="U60" s="7">
         <f t="array" aca="1" ref="U60" ca="1">_FV(B60,"Market cap",TRUE)</f>
-        <v>5329851450</v>
+        <v>5230868494</v>
       </c>
       <c r="V60" s="7">
         <f t="array" aca="1" ref="V60" ca="1">_FV(B60,"Shares outstanding",TRUE)</f>
@@ -19374,7 +19378,7 @@
       </c>
       <c r="C61" s="2">
         <f t="array" aca="1" ref="C61" ca="1">_FV(B61,"Last trade time",TRUE)</f>
-        <v>46181.75898615703</v>
+        <v>46181.826033448437</v>
       </c>
       <c r="D61" t="str">
         <f t="array" aca="1" ref="D61" ca="1">_FV(B61,"Currency")</f>
@@ -19382,19 +19386,19 @@
       </c>
       <c r="E61" s="3">
         <f t="array" aca="1" ref="E61" ca="1">_FV(B61,"Price")</f>
-        <v>213.08</v>
+        <v>212.27</v>
       </c>
       <c r="F61" s="4">
         <f t="array" aca="1" ref="F61" ca="1">_FV(B61,"Change (%)",TRUE)</f>
-        <v>-2.8079999999999997E-3</v>
+        <v>-6.5990000000000007E-3</v>
       </c>
       <c r="G61" s="5">
         <f t="array" aca="1" ref="G61" ca="1">_FV(B61,"Change")</f>
-        <v>-0.6</v>
+        <v>-1.41</v>
       </c>
       <c r="H61" s="6">
         <f t="array" aca="1" ref="H61" ca="1">_FV(B61,"P/E",TRUE)</f>
-        <v>36.115900000000003</v>
+        <v>35.9786</v>
       </c>
       <c r="I61" s="6">
         <f t="array" aca="1" ref="I61" ca="1">_FV(B61,"Beta")</f>
@@ -19426,7 +19430,7 @@
       </c>
       <c r="P61" s="7">
         <f t="array" aca="1" ref="P61" ca="1">_FV(B61,"Volume")</f>
-        <v>12506811</v>
+        <v>14747163</v>
       </c>
       <c r="Q61" s="7">
         <f t="array" aca="1" ref="Q61" ca="1">_FV(B61,"Volume average",TRUE)</f>
@@ -19446,7 +19450,7 @@
       </c>
       <c r="U61" s="7">
         <f t="array" aca="1" ref="U61" ca="1">_FV(B61,"Market cap",TRUE)</f>
-        <v>612827881680</v>
+        <v>610498284420</v>
       </c>
       <c r="V61" s="7">
         <f t="array" aca="1" ref="V61" ca="1">_FV(B61,"Shares outstanding",TRUE)</f>
@@ -19462,7 +19466,7 @@
       </c>
       <c r="C62" s="2" cm="1">
         <f t="array" aca="1" ref="C62" ca="1">_FV(B62,"Last trade time",TRUE)</f>
-        <v>46181.758976620309</v>
+        <v>46181.826059964842</v>
       </c>
       <c r="D62" t="str" cm="1">
         <f t="array" aca="1" ref="D62" ca="1">_FV(B62,"Currency")</f>
@@ -19470,19 +19474,19 @@
       </c>
       <c r="E62" s="3" cm="1">
         <f t="array" aca="1" ref="E62" ca="1">_FV(B62,"Price")</f>
-        <v>267.41000000000003</v>
+        <v>266.22000000000003</v>
       </c>
       <c r="F62" s="4" cm="1">
         <f t="array" aca="1" ref="F62" ca="1">_FV(B62,"Change (%)",TRUE)</f>
-        <v>-1.7056000000000002E-2</v>
+        <v>-2.1429999999999998E-2</v>
       </c>
       <c r="G62" s="5" cm="1">
         <f t="array" aca="1" ref="G62" ca="1">_FV(B62,"Change")</f>
-        <v>-4.6399999999999997</v>
+        <v>-5.83</v>
       </c>
       <c r="H62" s="6" cm="1">
         <f t="array" aca="1" ref="H62" ca="1">_FV(B62,"P/E",TRUE)</f>
-        <v>220.18109999999999</v>
+        <v>219.2013</v>
       </c>
       <c r="I62" s="6" cm="1">
         <f t="array" aca="1" ref="I62" ca="1">_FV(B62,"Beta")</f>
@@ -19514,7 +19518,7 @@
       </c>
       <c r="P62" s="7" cm="1">
         <f t="array" aca="1" ref="P62" ca="1">_FV(B62,"Volume")</f>
-        <v>3770185</v>
+        <v>4709365</v>
       </c>
       <c r="Q62" s="7" cm="1">
         <f t="array" aca="1" ref="Q62" ca="1">_FV(B62,"Volume average",TRUE)</f>
@@ -19534,7 +19538,7 @@
       </c>
       <c r="U62" s="7" cm="1">
         <f t="array" aca="1" ref="U62" ca="1">_FV(B62,"Market cap",TRUE)</f>
-        <v>217939150000</v>
+        <v>216969300000</v>
       </c>
       <c r="V62" s="7" cm="1">
         <f t="array" aca="1" ref="V62" ca="1">_FV(B62,"Shares outstanding",TRUE)</f>
@@ -19550,7 +19554,7 @@
       </c>
       <c r="C63" s="2">
         <f t="array" aca="1" ref="C63" ca="1">_FV(B63,"Last trade time",TRUE)</f>
-        <v>46181.758948448434</v>
+        <v>46181.826027892967</v>
       </c>
       <c r="D63" t="str">
         <f t="array" aca="1" ref="D63" ca="1">_FV(B63,"Currency")</f>
@@ -19602,7 +19606,7 @@
       </c>
       <c r="P63" s="7">
         <f t="array" aca="1" ref="P63" ca="1">_FV(B63,"Volume")</f>
-        <v>21825731</v>
+        <v>34354214</v>
       </c>
       <c r="Q63" s="7">
         <f t="array" aca="1" ref="Q63" ca="1">_FV(B63,"Volume average",TRUE)</f>
@@ -19638,7 +19642,7 @@
       </c>
       <c r="C64" s="2" cm="1">
         <f t="array" aca="1" ref="C64" ca="1">_FV(B64,"Last trade time",TRUE)</f>
-        <v>46181.758914964841</v>
+        <v>46181.825993749997</v>
       </c>
       <c r="D64" t="str" cm="1">
         <f t="array" aca="1" ref="D64" ca="1">_FV(B64,"Currency")</f>
@@ -19646,19 +19650,19 @@
       </c>
       <c r="E64" s="3" cm="1">
         <f t="array" aca="1" ref="E64" ca="1">_FV(B64,"Price")</f>
-        <v>145.4401</v>
+        <v>145.24</v>
       </c>
       <c r="F64" s="4" cm="1">
         <f t="array" aca="1" ref="F64" ca="1">_FV(B64,"Change (%)",TRUE)</f>
-        <v>-7.5060000000000005E-3</v>
+        <v>-8.8710000000000004E-3</v>
       </c>
       <c r="G64" s="5" cm="1">
         <f t="array" aca="1" ref="G64" ca="1">_FV(B64,"Change")</f>
-        <v>-1.0999000000000001</v>
+        <v>-1.3</v>
       </c>
       <c r="H64" s="6" cm="1">
         <f t="array" aca="1" ref="H64" ca="1">_FV(B64,"P/E",TRUE)</f>
-        <v>21.270600000000002</v>
+        <v>21.241399999999999</v>
       </c>
       <c r="I64" s="6" cm="1">
         <f t="array" aca="1" ref="I64" ca="1">_FV(B64,"Beta")</f>
@@ -19690,7 +19694,7 @@
       </c>
       <c r="P64" s="7" cm="1">
         <f t="array" aca="1" ref="P64" ca="1">_FV(B64,"Volume")</f>
-        <v>2976290</v>
+        <v>3914585</v>
       </c>
       <c r="Q64" s="7" cm="1">
         <f t="array" aca="1" ref="Q64" ca="1">_FV(B64,"Volume average",TRUE)</f>
@@ -19710,7 +19714,7 @@
       </c>
       <c r="U64" s="7" cm="1">
         <f t="array" aca="1" ref="U64" ca="1">_FV(B64,"Market cap",TRUE)</f>
-        <v>338671671419</v>
+        <v>338205718760</v>
       </c>
       <c r="V64" s="7" cm="1">
         <f t="array" aca="1" ref="V64" ca="1">_FV(B64,"Shares outstanding",TRUE)</f>
@@ -19726,7 +19730,7 @@
       </c>
       <c r="C65" s="2">
         <f t="array" aca="1" ref="C65" ca="1">_FV(B65,"Last trade time",TRUE)</f>
-        <v>46181.758994930467</v>
+        <v>46181.826017800784</v>
       </c>
       <c r="D65" t="str">
         <f t="array" aca="1" ref="D65" ca="1">_FV(B65,"Currency")</f>
@@ -19734,19 +19738,19 @@
       </c>
       <c r="E65" s="3">
         <f t="array" aca="1" ref="E65" ca="1">_FV(B65,"Price")</f>
-        <v>30.355</v>
+        <v>29.84</v>
       </c>
       <c r="F65" s="4">
         <f t="array" aca="1" ref="F65" ca="1">_FV(B65,"Change (%)",TRUE)</f>
-        <v>4.1338E-2</v>
+        <v>2.3671000000000001E-2</v>
       </c>
       <c r="G65" s="5">
         <f t="array" aca="1" ref="G65" ca="1">_FV(B65,"Change")</f>
-        <v>1.2050000000000001</v>
+        <v>0.69</v>
       </c>
       <c r="H65" s="6">
         <f t="array" aca="1" ref="H65" ca="1">_FV(B65,"P/E",TRUE)</f>
-        <v>11.117000000000001</v>
+        <v>10.9284</v>
       </c>
       <c r="I65" s="6">
         <f t="array" aca="1" ref="I65" ca="1">_FV(B65,"Beta")</f>
@@ -19778,7 +19782,7 @@
       </c>
       <c r="P65" s="7">
         <f t="array" aca="1" ref="P65" ca="1">_FV(B65,"Volume")</f>
-        <v>1206206</v>
+        <v>1548575</v>
       </c>
       <c r="Q65" s="7">
         <f t="array" aca="1" ref="Q65" ca="1">_FV(B65,"Volume average",TRUE)</f>
@@ -19798,7 +19802,7 @@
       </c>
       <c r="U65" s="7">
         <f t="array" aca="1" ref="U65" ca="1">_FV(B65,"Market cap",TRUE)</f>
-        <v>1789924768</v>
+        <v>1759557077</v>
       </c>
       <c r="V65" s="7">
         <f t="array" aca="1" ref="V65" ca="1">_FV(B65,"Shares outstanding",TRUE)</f>
@@ -19814,7 +19818,7 @@
       </c>
       <c r="C66" s="2">
         <f t="array" aca="1" ref="C66" ca="1">_FV(B66,"Last trade time",TRUE)</f>
-        <v>46181.758940798434</v>
+        <v>46181.825984397656</v>
       </c>
       <c r="D66" t="str">
         <f t="array" aca="1" ref="D66" ca="1">_FV(B66,"Currency")</f>
@@ -19822,15 +19826,15 @@
       </c>
       <c r="E66" s="3">
         <f t="array" aca="1" ref="E66" ca="1">_FV(B66,"Price")</f>
-        <v>12.494999999999999</v>
+        <v>12.185</v>
       </c>
       <c r="F66" s="4">
         <f t="array" aca="1" ref="F66" ca="1">_FV(B66,"Change (%)",TRUE)</f>
-        <v>5.3540999999999998E-2</v>
+        <v>2.7403E-2</v>
       </c>
       <c r="G66" s="5">
         <f t="array" aca="1" ref="G66" ca="1">_FV(B66,"Change")</f>
-        <v>0.63500000000000001</v>
+        <v>0.32500000000000001</v>
       </c>
       <c r="H66" s="6">
         <f t="array" aca="1" ref="H66" ca="1">_FV(B66,"P/E",TRUE)</f>
@@ -19866,7 +19870,7 @@
       </c>
       <c r="P66" s="7">
         <f t="array" aca="1" ref="P66" ca="1">_FV(B66,"Volume")</f>
-        <v>21413310</v>
+        <v>24883865</v>
       </c>
       <c r="Q66" s="7">
         <f t="array" aca="1" ref="Q66" ca="1">_FV(B66,"Volume average",TRUE)</f>
@@ -19886,7 +19890,7 @@
       </c>
       <c r="U66" s="7">
         <f t="array" aca="1" ref="U66" ca="1">_FV(B66,"Market cap",TRUE)</f>
-        <v>2156579523</v>
+        <v>2103074949</v>
       </c>
       <c r="V66" s="7">
         <f t="array" aca="1" ref="V66" ca="1">_FV(B66,"Shares outstanding",TRUE)</f>
@@ -19902,7 +19906,7 @@
       </c>
       <c r="C67" s="2" cm="1">
         <f t="array" aca="1" ref="C67" ca="1">_FV(B67,"Last trade time",TRUE)</f>
-        <v>46181.758989918751</v>
+        <v>46181.826027858595</v>
       </c>
       <c r="D67" t="str" cm="1">
         <f t="array" aca="1" ref="D67" ca="1">_FV(B67,"Currency")</f>
@@ -19910,19 +19914,19 @@
       </c>
       <c r="E67" s="3" cm="1">
         <f t="array" aca="1" ref="E67" ca="1">_FV(B67,"Price")</f>
-        <v>220.17439999999999</v>
+        <v>216.56</v>
       </c>
       <c r="F67" s="4" cm="1">
         <f t="array" aca="1" ref="F67" ca="1">_FV(B67,"Change (%)",TRUE)</f>
-        <v>1.9609000000000001E-2</v>
+        <v>2.8710000000000003E-3</v>
       </c>
       <c r="G67" s="5" cm="1">
         <f t="array" aca="1" ref="G67" ca="1">_FV(B67,"Change")</f>
-        <v>4.2343999999999999</v>
+        <v>0.62</v>
       </c>
       <c r="H67" s="6" cm="1">
         <f t="array" aca="1" ref="H67" ca="1">_FV(B67,"P/E",TRUE)</f>
-        <v>23.949200000000001</v>
+        <v>23.556000000000001</v>
       </c>
       <c r="I67" s="6" cm="1">
         <f t="array" aca="1" ref="I67" ca="1">_FV(B67,"Beta")</f>
@@ -19954,7 +19958,7 @@
       </c>
       <c r="P67" s="7" cm="1">
         <f t="array" aca="1" ref="P67" ca="1">_FV(B67,"Volume")</f>
-        <v>9964355</v>
+        <v>11641443</v>
       </c>
       <c r="Q67" s="7" cm="1">
         <f t="array" aca="1" ref="Q67" ca="1">_FV(B67,"Volume average",TRUE)</f>
@@ -19974,7 +19978,7 @@
       </c>
       <c r="U67" s="7" cm="1">
         <f t="array" aca="1" ref="U67" ca="1">_FV(B67,"Market cap",TRUE)</f>
-        <v>232063817600</v>
+        <v>228254240000</v>
       </c>
       <c r="V67" s="7" cm="1">
         <f t="array" aca="1" ref="V67" ca="1">_FV(B67,"Shares outstanding",TRUE)</f>
@@ -19990,7 +19994,7 @@
       </c>
       <c r="C68" s="2">
         <f t="array" aca="1" ref="C68" ca="1">_FV(B68,"Last trade time",TRUE)</f>
-        <v>46181.758913657031</v>
+        <v>46181.825977673434</v>
       </c>
       <c r="D68" t="str">
         <f t="array" aca="1" ref="D68" ca="1">_FV(B68,"Currency")</f>
@@ -19998,19 +20002,19 @@
       </c>
       <c r="E68" s="3">
         <f t="array" aca="1" ref="E68" ca="1">_FV(B68,"Price")</f>
-        <v>109.67</v>
+        <v>109.765</v>
       </c>
       <c r="F68" s="4">
         <f t="array" aca="1" ref="F68" ca="1">_FV(B68,"Change (%)",TRUE)</f>
-        <v>-2.0930000000000002E-3</v>
+        <v>-1.2280000000000001E-3</v>
       </c>
       <c r="G68" s="5">
         <f t="array" aca="1" ref="G68" ca="1">_FV(B68,"Change")</f>
-        <v>-0.23</v>
+        <v>-0.13500000000000001</v>
       </c>
       <c r="H68" s="6">
         <f t="array" aca="1" ref="H68" ca="1">_FV(B68,"P/E",TRUE)</f>
-        <v>19.693300000000001</v>
+        <v>19.7104</v>
       </c>
       <c r="I68" s="6">
         <f t="array" aca="1" ref="I68" ca="1">_FV(B68,"Beta")</f>
@@ -20042,7 +20046,7 @@
       </c>
       <c r="P68" s="7">
         <f t="array" aca="1" ref="P68" ca="1">_FV(B68,"Volume")</f>
-        <v>218782</v>
+        <v>315101</v>
       </c>
       <c r="Q68" s="7">
         <f t="array" aca="1" ref="Q68" ca="1">_FV(B68,"Volume average",TRUE)</f>
@@ -20062,7 +20066,7 @@
       </c>
       <c r="U68" s="7">
         <f t="array" aca="1" ref="U68" ca="1">_FV(B68,"Market cap",TRUE)</f>
-        <v>3862249486</v>
+        <v>3865595102</v>
       </c>
       <c r="V68" s="7">
         <f t="array" aca="1" ref="V68" ca="1">_FV(B68,"Shares outstanding",TRUE)</f>
@@ -20078,7 +20082,7 @@
       </c>
       <c r="C69" s="2" cm="1">
         <f t="array" aca="1" ref="C69" ca="1">_FV(B69,"Last trade time",TRUE)</f>
-        <v>46181.758978657032</v>
+        <v>46181.826052950782</v>
       </c>
       <c r="D69" t="str" cm="1">
         <f t="array" aca="1" ref="D69" ca="1">_FV(B69,"Currency")</f>
@@ -20086,15 +20090,15 @@
       </c>
       <c r="E69" s="3" cm="1">
         <f t="array" aca="1" ref="E69" ca="1">_FV(B69,"Price")</f>
-        <v>718.56500000000005</v>
+        <v>715.57</v>
       </c>
       <c r="F69" s="4" cm="1">
         <f t="array" aca="1" ref="F69" ca="1">_FV(B69,"Change (%)",TRUE)</f>
-        <v>1.9154000000000001E-2</v>
+        <v>1.4906999999999998E-2</v>
       </c>
       <c r="G69" s="5" cm="1">
         <f t="array" aca="1" ref="G69" ca="1">_FV(B69,"Change")</f>
-        <v>13.505000000000001</v>
+        <v>10.51</v>
       </c>
       <c r="H69" s="6" t="e" cm="1" vm="13">
         <f t="array" ref="H69">_FV(B69,"P/E",TRUE)</f>
@@ -20130,7 +20134,7 @@
       </c>
       <c r="P69" s="7" cm="1">
         <f t="array" aca="1" ref="P69" ca="1">_FV(B69,"Volume")</f>
-        <v>32577622</v>
+        <v>41500485</v>
       </c>
       <c r="Q69" s="7" cm="1">
         <f t="array" aca="1" ref="Q69" ca="1">_FV(B69,"Volume average",TRUE)</f>
@@ -20166,7 +20170,7 @@
       </c>
       <c r="C70" s="2" cm="1">
         <f t="array" aca="1" ref="C70" ca="1">_FV(B70,"Last trade time",TRUE)</f>
-        <v>46181.758874779691</v>
+        <v>46181.825838193748</v>
       </c>
       <c r="D70" t="str" cm="1">
         <f t="array" aca="1" ref="D70" ca="1">_FV(B70,"Currency")</f>
@@ -20174,19 +20178,19 @@
       </c>
       <c r="E70" s="3" cm="1">
         <f t="array" aca="1" ref="E70" ca="1">_FV(B70,"Price")</f>
-        <v>450.44</v>
+        <v>451.78609999999998</v>
       </c>
       <c r="F70" s="4" cm="1">
         <f t="array" aca="1" ref="F70" ca="1">_FV(B70,"Change (%)",TRUE)</f>
-        <v>8.3499999999999998E-3</v>
+        <v>1.1363000000000002E-2</v>
       </c>
       <c r="G70" s="5" cm="1">
         <f t="array" aca="1" ref="G70" ca="1">_FV(B70,"Change")</f>
-        <v>3.73</v>
+        <v>5.0761000000000003</v>
       </c>
       <c r="H70" s="6" cm="1">
         <f t="array" aca="1" ref="H70" ca="1">_FV(B70,"P/E",TRUE)</f>
-        <v>46.793100000000003</v>
+        <v>46.933</v>
       </c>
       <c r="I70" s="6" cm="1">
         <f t="array" aca="1" ref="I70" ca="1">_FV(B70,"Beta")</f>
@@ -20218,7 +20222,7 @@
       </c>
       <c r="P70" s="7" cm="1">
         <f t="array" aca="1" ref="P70" ca="1">_FV(B70,"Volume")</f>
-        <v>334996</v>
+        <v>504313</v>
       </c>
       <c r="Q70" s="7" cm="1">
         <f t="array" aca="1" ref="Q70" ca="1">_FV(B70,"Volume average",TRUE)</f>
@@ -20238,7 +20242,7 @@
       </c>
       <c r="U70" s="7" cm="1">
         <f t="array" aca="1" ref="U70" ca="1">_FV(B70,"Market cap",TRUE)</f>
-        <v>50122215516</v>
+        <v>50272001312</v>
       </c>
       <c r="V70" s="7" cm="1">
         <f t="array" aca="1" ref="V70" ca="1">_FV(B70,"Shares outstanding",TRUE)</f>
@@ -20254,7 +20258,7 @@
       </c>
       <c r="C71" s="2" cm="1">
         <f t="array" aca="1" ref="C71" ca="1">_FV(B71,"Last trade time",TRUE)</f>
-        <v>46181.758983321095</v>
+        <v>46181.826022106252</v>
       </c>
       <c r="D71" t="str" cm="1">
         <f t="array" aca="1" ref="D71" ca="1">_FV(B71,"Currency")</f>
@@ -20262,15 +20266,15 @@
       </c>
       <c r="E71" s="3" cm="1">
         <f t="array" aca="1" ref="E71" ca="1">_FV(B71,"Price")</f>
-        <v>3.3149999999999999</v>
+        <v>3.3125</v>
       </c>
       <c r="F71" s="4" cm="1">
         <f t="array" aca="1" ref="F71" ca="1">_FV(B71,"Change (%)",TRUE)</f>
-        <v>0</v>
+        <v>-7.5410000000000006E-4</v>
       </c>
       <c r="G71" s="5" cm="1">
         <f t="array" aca="1" ref="G71" ca="1">_FV(B71,"Change")</f>
-        <v>0</v>
+        <v>-2.5000000000000001E-3</v>
       </c>
       <c r="H71" s="6" cm="1">
         <f t="array" aca="1" ref="H71" ca="1">_FV(B71,"P/E",TRUE)</f>
@@ -20306,7 +20310,7 @@
       </c>
       <c r="P71" s="7" cm="1">
         <f t="array" aca="1" ref="P71" ca="1">_FV(B71,"Volume")</f>
-        <v>10546617</v>
+        <v>14070341</v>
       </c>
       <c r="Q71" s="7" cm="1">
         <f t="array" aca="1" ref="Q71" ca="1">_FV(B71,"Volume average",TRUE)</f>
@@ -20326,7 +20330,7 @@
       </c>
       <c r="U71" s="7" cm="1">
         <f t="array" aca="1" ref="U71" ca="1">_FV(B71,"Market cap",TRUE)</f>
-        <v>1756635738</v>
+        <v>1755310975</v>
       </c>
       <c r="V71" s="7" cm="1">
         <f t="array" aca="1" ref="V71" ca="1">_FV(B71,"Shares outstanding",TRUE)</f>
@@ -20342,7 +20346,7 @@
       </c>
       <c r="C72" s="2" cm="1">
         <f t="array" aca="1" ref="C72" ca="1">_FV(B72,"Last trade time",TRUE)</f>
-        <v>46181.758981885934</v>
+        <v>46181.826070740623</v>
       </c>
       <c r="D72" t="str" cm="1">
         <f t="array" aca="1" ref="D72" ca="1">_FV(B72,"Currency")</f>
@@ -20350,15 +20354,15 @@
       </c>
       <c r="E72" s="3" cm="1">
         <f t="array" aca="1" ref="E72" ca="1">_FV(B72,"Price")</f>
-        <v>15.695</v>
+        <v>15.744999999999999</v>
       </c>
       <c r="F72" s="4" cm="1">
         <f t="array" aca="1" ref="F72" ca="1">_FV(B72,"Change (%)",TRUE)</f>
-        <v>-1.5987000000000001E-2</v>
+        <v>-1.2853000000000002E-2</v>
       </c>
       <c r="G72" s="5" cm="1">
         <f t="array" aca="1" ref="G72" ca="1">_FV(B72,"Change")</f>
-        <v>-0.255</v>
+        <v>-0.20499999999999999</v>
       </c>
       <c r="H72" s="6" t="e" cm="1" vm="13">
         <f t="array" ref="H72">_FV(B72,"P/E",TRUE)</f>
@@ -20394,7 +20398,7 @@
       </c>
       <c r="P72" s="7" cm="1">
         <f t="array" aca="1" ref="P72" ca="1">_FV(B72,"Volume")</f>
-        <v>3556133</v>
+        <v>4558351</v>
       </c>
       <c r="Q72" s="7" cm="1">
         <f t="array" aca="1" ref="Q72" ca="1">_FV(B72,"Volume average",TRUE)</f>
@@ -20414,7 +20418,7 @@
       </c>
       <c r="U72" s="7" cm="1">
         <f t="array" aca="1" ref="U72" ca="1">_FV(B72,"Market cap",TRUE)</f>
-        <v>5380304071</v>
+        <v>5397444256</v>
       </c>
       <c r="V72" s="7" cm="1">
         <f t="array" aca="1" ref="V72" ca="1">_FV(B72,"Shares outstanding",TRUE)</f>
@@ -20430,7 +20434,7 @@
       </c>
       <c r="C73" s="2" cm="1">
         <f t="array" aca="1" ref="C73" ca="1">_FV(B73,"Last trade time",TRUE)</f>
-        <v>46181.746990740743</v>
+        <v>46181.815532407411</v>
       </c>
       <c r="D73" t="str" cm="1">
         <f t="array" aca="1" ref="D73" ca="1">_FV(B73,"Currency")</f>
@@ -20482,7 +20486,7 @@
       </c>
       <c r="P73" s="7" cm="1">
         <f t="array" aca="1" ref="P73" ca="1">_FV(B73,"Volume")</f>
-        <v>2043878</v>
+        <v>2043989</v>
       </c>
       <c r="Q73" s="7" cm="1">
         <f t="array" aca="1" ref="Q73" ca="1">_FV(B73,"Volume average",TRUE)</f>
@@ -20518,7 +20522,7 @@
       </c>
       <c r="C74" s="2">
         <f t="array" aca="1" ref="C74" ca="1">_FV(B74,"Last trade time",TRUE)</f>
-        <v>46181.758986700785</v>
+        <v>46181.826051515622</v>
       </c>
       <c r="D74" t="str">
         <f t="array" aca="1" ref="D74" ca="1">_FV(B74,"Currency")</f>
@@ -20526,19 +20530,19 @@
       </c>
       <c r="E74" s="3">
         <f t="array" aca="1" ref="E74" ca="1">_FV(B74,"Price")</f>
-        <v>88.72</v>
+        <v>88.36</v>
       </c>
       <c r="F74" s="4">
         <f t="array" aca="1" ref="F74" ca="1">_FV(B74,"Change (%)",TRUE)</f>
-        <v>-1.351E-3</v>
+        <v>-5.4029999999999998E-3</v>
       </c>
       <c r="G74" s="5">
         <f t="array" aca="1" ref="G74" ca="1">_FV(B74,"Change")</f>
-        <v>-0.12</v>
+        <v>-0.48</v>
       </c>
       <c r="H74" s="6">
         <f t="array" aca="1" ref="H74" ca="1">_FV(B74,"P/E",TRUE)</f>
-        <v>17.593399999999999</v>
+        <v>17.521999999999998</v>
       </c>
       <c r="I74" s="6">
         <f t="array" aca="1" ref="I74" ca="1">_FV(B74,"Beta")</f>
@@ -20570,7 +20574,7 @@
       </c>
       <c r="P74" s="7">
         <f t="array" aca="1" ref="P74" ca="1">_FV(B74,"Volume")</f>
-        <v>3699177</v>
+        <v>5358193</v>
       </c>
       <c r="Q74" s="7">
         <f t="array" aca="1" ref="Q74" ca="1">_FV(B74,"Volume average",TRUE)</f>
@@ -20590,7 +20594,7 @@
       </c>
       <c r="U74" s="7">
         <f t="array" aca="1" ref="U74" ca="1">_FV(B74,"Market cap",TRUE)</f>
-        <v>154296057200</v>
+        <v>153669968600</v>
       </c>
       <c r="V74" s="7">
         <f t="array" aca="1" ref="V74" ca="1">_FV(B74,"Shares outstanding",TRUE)</f>
@@ -20694,7 +20698,7 @@
       </c>
       <c r="C76" s="2">
         <f t="array" aca="1" ref="C76" ca="1">_FV(B76,"Last trade time",TRUE)</f>
-        <v>46181.758976296092</v>
+        <v>46181.825991238278</v>
       </c>
       <c r="D76" t="str">
         <f t="array" aca="1" ref="D76" ca="1">_FV(B76,"Currency")</f>
@@ -20702,19 +20706,19 @@
       </c>
       <c r="E76" s="3">
         <f t="array" aca="1" ref="E76" ca="1">_FV(B76,"Price")</f>
-        <v>36.869999999999997</v>
+        <v>36.590000000000003</v>
       </c>
       <c r="F76" s="4">
         <f t="array" aca="1" ref="F76" ca="1">_FV(B76,"Change (%)",TRUE)</f>
-        <v>5.4332000000000005E-2</v>
+        <v>4.6325000000000005E-2</v>
       </c>
       <c r="G76" s="5">
         <f t="array" aca="1" ref="G76" ca="1">_FV(B76,"Change")</f>
-        <v>1.9</v>
+        <v>1.62</v>
       </c>
       <c r="H76" s="6">
         <f t="array" aca="1" ref="H76" ca="1">_FV(B76,"P/E",TRUE)</f>
-        <v>15.804399999999999</v>
+        <v>15.6843</v>
       </c>
       <c r="I76" s="6">
         <f t="array" aca="1" ref="I76" ca="1">_FV(B76,"Beta")</f>
@@ -20746,7 +20750,7 @@
       </c>
       <c r="P76" s="7">
         <f t="array" aca="1" ref="P76" ca="1">_FV(B76,"Volume")</f>
-        <v>392180</v>
+        <v>509281</v>
       </c>
       <c r="Q76" s="7">
         <f t="array" aca="1" ref="Q76" ca="1">_FV(B76,"Volume average",TRUE)</f>
@@ -20766,7 +20770,7 @@
       </c>
       <c r="U76" s="7">
         <f t="array" aca="1" ref="U76" ca="1">_FV(B76,"Market cap",TRUE)</f>
-        <v>1814173601</v>
+        <v>1800396314</v>
       </c>
       <c r="V76" s="7">
         <f t="array" aca="1" ref="V76" ca="1">_FV(B76,"Shares outstanding",TRUE)</f>
@@ -20782,7 +20786,7 @@
       </c>
       <c r="C77" s="2">
         <f t="array" aca="1" ref="C77" ca="1">_FV(B77,"Last trade time",TRUE)</f>
-        <v>46181.758996457815</v>
+        <v>46181.826085578126</v>
       </c>
       <c r="D77" t="str">
         <f t="array" aca="1" ref="D77" ca="1">_FV(B77,"Currency")</f>
@@ -20790,19 +20794,19 @@
       </c>
       <c r="E77" s="3">
         <f t="array" aca="1" ref="E77" ca="1">_FV(B77,"Price")</f>
-        <v>44.53</v>
+        <v>43.734999999999999</v>
       </c>
       <c r="F77" s="4">
         <f t="array" aca="1" ref="F77" ca="1">_FV(B77,"Change (%)",TRUE)</f>
-        <v>6.9404000000000007E-2</v>
+        <v>5.0312000000000003E-2</v>
       </c>
       <c r="G77" s="5">
         <f t="array" aca="1" ref="G77" ca="1">_FV(B77,"Change")</f>
-        <v>2.89</v>
+        <v>2.0950000000000002</v>
       </c>
       <c r="H77" s="6">
         <f t="array" aca="1" ref="H77" ca="1">_FV(B77,"P/E",TRUE)</f>
-        <v>24.263100000000001</v>
+        <v>23.829899999999999</v>
       </c>
       <c r="I77" s="6">
         <f t="array" aca="1" ref="I77" ca="1">_FV(B77,"Beta")</f>
@@ -20834,7 +20838,7 @@
       </c>
       <c r="P77" s="7">
         <f t="array" aca="1" ref="P77" ca="1">_FV(B77,"Volume")</f>
-        <v>21802515</v>
+        <v>26927326</v>
       </c>
       <c r="Q77" s="7">
         <f t="array" aca="1" ref="Q77" ca="1">_FV(B77,"Volume average",TRUE)</f>
@@ -20854,7 +20858,7 @@
       </c>
       <c r="U77" s="7">
         <f t="array" aca="1" ref="U77" ca="1">_FV(B77,"Market cap",TRUE)</f>
-        <v>26781165805</v>
+        <v>26303038097</v>
       </c>
       <c r="V77" s="7">
         <f t="array" aca="1" ref="V77" ca="1">_FV(B77,"Shares outstanding",TRUE)</f>
@@ -20870,7 +20874,7 @@
       </c>
       <c r="C78" s="2" cm="1">
         <f t="array" aca="1" ref="C78" ca="1">_FV(B78,"Last trade time",TRUE)</f>
-        <v>46181.759005983593</v>
+        <v>46181.826084120315</v>
       </c>
       <c r="D78" t="str" cm="1">
         <f t="array" aca="1" ref="D78" ca="1">_FV(B78,"Currency")</f>
@@ -20878,15 +20882,15 @@
       </c>
       <c r="E78" s="3" cm="1">
         <f t="array" aca="1" ref="E78" ca="1">_FV(B78,"Price")</f>
-        <v>602.21</v>
+        <v>596</v>
       </c>
       <c r="F78" s="4" cm="1">
         <f t="array" aca="1" ref="F78" ca="1">_FV(B78,"Change (%)",TRUE)</f>
-        <v>5.7084000000000003E-2</v>
+        <v>4.6182999999999995E-2</v>
       </c>
       <c r="G78" s="5" cm="1">
         <f t="array" aca="1" ref="G78" ca="1">_FV(B78,"Change")</f>
-        <v>32.520000000000003</v>
+        <v>26.31</v>
       </c>
       <c r="H78" s="6" t="e" cm="1" vm="13">
         <f t="array" ref="H78">_FV(B78,"P/E",TRUE)</f>
@@ -20922,7 +20926,7 @@
       </c>
       <c r="P78" s="7" cm="1">
         <f t="array" aca="1" ref="P78" ca="1">_FV(B78,"Volume")</f>
-        <v>10543031</v>
+        <v>12377521</v>
       </c>
       <c r="Q78" s="7" cm="1">
         <f t="array" aca="1" ref="Q78" ca="1">_FV(B78,"Volume average",TRUE)</f>
@@ -20958,7 +20962,7 @@
       </c>
       <c r="C79" s="2" cm="1">
         <f t="array" aca="1" ref="C79" ca="1">_FV(B79,"Last trade time",TRUE)</f>
-        <v>46181.759013171097</v>
+        <v>46181.826056874997</v>
       </c>
       <c r="D79" t="str" cm="1">
         <f t="array" aca="1" ref="D79" ca="1">_FV(B79,"Currency")</f>
@@ -20966,15 +20970,15 @@
       </c>
       <c r="E79" s="3" cm="1">
         <f t="array" aca="1" ref="E79" ca="1">_FV(B79,"Price")</f>
-        <v>10.785</v>
+        <v>10.664999999999999</v>
       </c>
       <c r="F79" s="4" cm="1">
         <f t="array" aca="1" ref="F79" ca="1">_FV(B79,"Change (%)",TRUE)</f>
-        <v>2.7143E-2</v>
+        <v>1.5713999999999999E-2</v>
       </c>
       <c r="G79" s="5" cm="1">
         <f t="array" aca="1" ref="G79" ca="1">_FV(B79,"Change")</f>
-        <v>0.28499999999999998</v>
+        <v>0.16500000000000001</v>
       </c>
       <c r="H79" s="6" cm="1">
         <f t="array" aca="1" ref="H79" ca="1">_FV(B79,"P/E",TRUE)</f>
@@ -21010,7 +21014,7 @@
       </c>
       <c r="P79" s="7" cm="1">
         <f t="array" aca="1" ref="P79" ca="1">_FV(B79,"Volume")</f>
-        <v>17149803</v>
+        <v>19821544</v>
       </c>
       <c r="Q79" s="7" cm="1">
         <f t="array" aca="1" ref="Q79" ca="1">_FV(B79,"Volume average",TRUE)</f>
@@ -21030,7 +21034,7 @@
       </c>
       <c r="U79" s="7" cm="1">
         <f t="array" aca="1" ref="U79" ca="1">_FV(B79,"Market cap",TRUE)</f>
-        <v>3941714742</v>
+        <v>3897856997</v>
       </c>
       <c r="V79" s="7" cm="1">
         <f t="array" aca="1" ref="V79" ca="1">_FV(B79,"Shares outstanding",TRUE)</f>
@@ -21046,7 +21050,7 @@
       </c>
       <c r="C80" s="2">
         <f t="array" aca="1" ref="C80" ca="1">_FV(B80,"Last trade time",TRUE)</f>
-        <v>46181.759005844535</v>
+        <v>46181.826078448437</v>
       </c>
       <c r="D80" t="str">
         <f t="array" aca="1" ref="D80" ca="1">_FV(B80,"Currency")</f>
@@ -21054,19 +21058,19 @@
       </c>
       <c r="E80" s="3">
         <f t="array" aca="1" ref="E80" ca="1">_FV(B80,"Price")</f>
-        <v>1632.42</v>
+        <v>1627.3898999999999</v>
       </c>
       <c r="F80" s="4">
         <f t="array" aca="1" ref="F80" ca="1">_FV(B80,"Change (%)",TRUE)</f>
-        <v>4.6878999999999997E-2</v>
+        <v>4.3653999999999998E-2</v>
       </c>
       <c r="G80" s="5">
         <f t="array" aca="1" ref="G80" ca="1">_FV(B80,"Change")</f>
-        <v>73.099999999999994</v>
+        <v>68.069900000000004</v>
       </c>
       <c r="H80" s="6">
         <f t="array" aca="1" ref="H80" ca="1">_FV(B80,"P/E",TRUE)</f>
-        <v>57.7121</v>
+        <v>57.534199999999998</v>
       </c>
       <c r="I80" s="6">
         <f t="array" aca="1" ref="I80" ca="1">_FV(B80,"Beta")</f>
@@ -21098,7 +21102,7 @@
       </c>
       <c r="P80" s="7">
         <f t="array" aca="1" ref="P80" ca="1">_FV(B80,"Volume")</f>
-        <v>6258773</v>
+        <v>7219610</v>
       </c>
       <c r="Q80" s="7">
         <f t="array" aca="1" ref="Q80" ca="1">_FV(B80,"Volume average",TRUE)</f>
@@ -21118,7 +21122,7 @@
       </c>
       <c r="U80" s="7">
         <f t="array" aca="1" ref="U80" ca="1">_FV(B80,"Market cap",TRUE)</f>
-        <v>241744751316</v>
+        <v>240999844813</v>
       </c>
       <c r="V80" s="7">
         <f t="array" aca="1" ref="V80" ca="1">_FV(B80,"Shares outstanding",TRUE)</f>
@@ -21134,7 +21138,7 @@
       </c>
       <c r="C81" s="2" cm="1">
         <f t="array" aca="1" ref="C81" ca="1">_FV(B81,"Last trade time",TRUE)</f>
-        <v>46181.759018378907</v>
+        <v>46181.826090253904</v>
       </c>
       <c r="D81" t="str" cm="1">
         <f t="array" aca="1" ref="D81" ca="1">_FV(B81,"Currency")</f>
@@ -21142,15 +21146,15 @@
       </c>
       <c r="E81" s="3" cm="1">
         <f t="array" aca="1" ref="E81" ca="1">_FV(B81,"Price")</f>
-        <v>241.97499999999999</v>
+        <v>240.19499999999999</v>
       </c>
       <c r="F81" s="4" cm="1">
         <f t="array" aca="1" ref="F81" ca="1">_FV(B81,"Change (%)",TRUE)</f>
-        <v>1.5592E-2</v>
+        <v>8.1209999999999997E-3</v>
       </c>
       <c r="G81" s="5" cm="1">
         <f t="array" aca="1" ref="G81" ca="1">_FV(B81,"Change")</f>
-        <v>3.7149999999999999</v>
+        <v>1.9350000000000001</v>
       </c>
       <c r="H81" s="6" cm="1">
         <f t="array" aca="1" ref="H81" ca="1">_FV(B81,"P/E",TRUE)</f>
@@ -21186,7 +21190,7 @@
       </c>
       <c r="P81" s="7" cm="1">
         <f t="array" aca="1" ref="P81" ca="1">_FV(B81,"Volume")</f>
-        <v>3298589</v>
+        <v>3965337</v>
       </c>
       <c r="Q81" s="7" cm="1">
         <f t="array" aca="1" ref="Q81" ca="1">_FV(B81,"Volume average",TRUE)</f>
@@ -21222,7 +21226,7 @@
       </c>
       <c r="C82" s="2" cm="1">
         <f t="array" aca="1" ref="C82" ca="1">_FV(B82,"Last trade time",TRUE)</f>
-        <v>46181.758963888278</v>
+        <v>46181.82608239531</v>
       </c>
       <c r="D82" t="str" cm="1">
         <f t="array" aca="1" ref="D82" ca="1">_FV(B82,"Currency")</f>
@@ -21230,19 +21234,19 @@
       </c>
       <c r="E82" s="3" cm="1">
         <f t="array" aca="1" ref="E82" ca="1">_FV(B82,"Price")</f>
-        <v>473.36</v>
+        <v>472.12</v>
       </c>
       <c r="F82" s="4" cm="1">
         <f t="array" aca="1" ref="F82" ca="1">_FV(B82,"Change (%)",TRUE)</f>
-        <v>1.8307E-2</v>
+        <v>1.5639E-2</v>
       </c>
       <c r="G82" s="5" cm="1">
         <f t="array" aca="1" ref="G82" ca="1">_FV(B82,"Change")</f>
-        <v>8.51</v>
+        <v>7.27</v>
       </c>
       <c r="H82" s="6" cm="1">
         <f t="array" aca="1" ref="H82" ca="1">_FV(B82,"P/E",TRUE)</f>
-        <v>109.70359999999999</v>
+        <v>109.4162</v>
       </c>
       <c r="I82" s="6" cm="1">
         <f t="array" aca="1" ref="I82" ca="1">_FV(B82,"Beta")</f>
@@ -21274,7 +21278,7 @@
       </c>
       <c r="P82" s="7" cm="1">
         <f t="array" aca="1" ref="P82" ca="1">_FV(B82,"Volume")</f>
-        <v>633893</v>
+        <v>837948</v>
       </c>
       <c r="Q82" s="7" cm="1">
         <f t="array" aca="1" ref="Q82" ca="1">_FV(B82,"Volume average",TRUE)</f>
@@ -21294,7 +21298,7 @@
       </c>
       <c r="U82" s="7" cm="1">
         <f t="array" aca="1" ref="U82" ca="1">_FV(B82,"Market cap",TRUE)</f>
-        <v>90638641448</v>
+        <v>90401207116</v>
       </c>
       <c r="V82" s="7" cm="1">
         <f t="array" aca="1" ref="V82" ca="1">_FV(B82,"Shares outstanding",TRUE)</f>
@@ -21310,7 +21314,7 @@
       </c>
       <c r="C83" s="2">
         <f t="array" aca="1" ref="C83" ca="1">_FV(B83,"Last trade time",TRUE)</f>
-        <v>46181.759004640626</v>
+        <v>46181.826075103905</v>
       </c>
       <c r="D83" t="str">
         <f t="array" aca="1" ref="D83" ca="1">_FV(B83,"Currency")</f>
@@ -21318,15 +21322,15 @@
       </c>
       <c r="E83" s="3">
         <f t="array" aca="1" ref="E83" ca="1">_FV(B83,"Price")</f>
-        <v>7.5899000000000001</v>
+        <v>7.5149999999999997</v>
       </c>
       <c r="F83" s="4">
         <f t="array" aca="1" ref="F83" ca="1">_FV(B83,"Change (%)",TRUE)</f>
-        <v>2.7050000000000001E-2</v>
+        <v>1.6914999999999999E-2</v>
       </c>
       <c r="G83" s="5">
         <f t="array" aca="1" ref="G83" ca="1">_FV(B83,"Change")</f>
-        <v>0.19989999999999999</v>
+        <v>0.125</v>
       </c>
       <c r="H83" s="6">
         <f t="array" aca="1" ref="H83" ca="1">_FV(B83,"P/E",TRUE)</f>
@@ -21346,7 +21350,7 @@
       </c>
       <c r="L83" s="3">
         <f t="array" aca="1" ref="L83" ca="1">_FV(B83,"High")</f>
-        <v>7.6</v>
+        <v>7.6459999999999999</v>
       </c>
       <c r="M83" s="3">
         <f t="array" aca="1" ref="M83" ca="1">_FV(B83,"Low")</f>
@@ -21362,7 +21366,7 @@
       </c>
       <c r="P83" s="7">
         <f t="array" aca="1" ref="P83" ca="1">_FV(B83,"Volume")</f>
-        <v>16074578</v>
+        <v>19247625</v>
       </c>
       <c r="Q83" s="7">
         <f t="array" aca="1" ref="Q83" ca="1">_FV(B83,"Volume average",TRUE)</f>
@@ -21382,7 +21386,7 @@
       </c>
       <c r="U83" s="7">
         <f t="array" aca="1" ref="U83" ca="1">_FV(B83,"Market cap",TRUE)</f>
-        <v>3284677987</v>
+        <v>3252263544</v>
       </c>
       <c r="V83" s="7">
         <f t="array" aca="1" ref="V83" ca="1">_FV(B83,"Shares outstanding",TRUE)</f>
@@ -21398,7 +21402,7 @@
       </c>
       <c r="C84" s="2" cm="1">
         <f t="array" aca="1" ref="C84" ca="1">_FV(B84,"Last trade time",TRUE)</f>
-        <v>46181.75902225625</v>
+        <v>46181.826077835154</v>
       </c>
       <c r="D84" t="str" cm="1">
         <f t="array" aca="1" ref="D84" ca="1">_FV(B84,"Currency")</f>
@@ -21406,15 +21410,15 @@
       </c>
       <c r="E84" s="3" cm="1">
         <f t="array" aca="1" ref="E84" ca="1">_FV(B84,"Price")</f>
-        <v>576.93499999999995</v>
+        <v>569.24</v>
       </c>
       <c r="F84" s="4" cm="1">
         <f t="array" aca="1" ref="F84" ca="1">_FV(B84,"Change (%)",TRUE)</f>
-        <v>6.8852999999999998E-2</v>
+        <v>5.4597E-2</v>
       </c>
       <c r="G84" s="5" cm="1">
         <f t="array" aca="1" ref="G84" ca="1">_FV(B84,"Change")</f>
-        <v>37.164999999999999</v>
+        <v>29.47</v>
       </c>
       <c r="H84" s="6" t="e" cm="1" vm="13">
         <f t="array" ref="H84">_FV(B84,"P/E",TRUE)</f>
@@ -21450,7 +21454,7 @@
       </c>
       <c r="P84" s="7" cm="1">
         <f t="array" aca="1" ref="P84" ca="1">_FV(B84,"Volume")</f>
-        <v>8126630</v>
+        <v>10994344</v>
       </c>
       <c r="Q84" s="7" cm="1">
         <f t="array" aca="1" ref="Q84" ca="1">_FV(B84,"Volume average",TRUE)</f>
@@ -21486,7 +21490,7 @@
       </c>
       <c r="C85" s="2" cm="1">
         <f t="array" aca="1" ref="C85" ca="1">_FV(B85,"Last trade time",TRUE)</f>
-        <v>46181.759019883597</v>
+        <v>46181.826099964841</v>
       </c>
       <c r="D85" t="str" cm="1">
         <f t="array" aca="1" ref="D85" ca="1">_FV(B85,"Currency")</f>
@@ -21494,15 +21498,15 @@
       </c>
       <c r="E85" s="3" cm="1">
         <f t="array" aca="1" ref="E85" ca="1">_FV(B85,"Price")</f>
-        <v>741.13</v>
+        <v>739.21</v>
       </c>
       <c r="F85" s="4" cm="1">
         <f t="array" aca="1" ref="F85" ca="1">_FV(B85,"Change (%)",TRUE)</f>
-        <v>4.8539999999999998E-3</v>
+        <v>2.251E-3</v>
       </c>
       <c r="G85" s="5" cm="1">
         <f t="array" aca="1" ref="G85" ca="1">_FV(B85,"Change")</f>
-        <v>3.58</v>
+        <v>1.66</v>
       </c>
       <c r="H85" s="6" t="e" vm="13">
         <f t="array" ref="H85">_FV(B85,"P/E",TRUE)</f>
@@ -21526,7 +21530,7 @@
       </c>
       <c r="M85" s="3" cm="1">
         <f t="array" aca="1" ref="M85" ca="1">_FV(B85,"Low")</f>
-        <v>740.08</v>
+        <v>738.19</v>
       </c>
       <c r="N85" s="3" cm="1">
         <f t="array" aca="1" ref="N85" ca="1">_FV(B85,"Open")</f>
@@ -21538,7 +21542,7 @@
       </c>
       <c r="P85" s="7" cm="1">
         <f t="array" aca="1" ref="P85" ca="1">_FV(B85,"Volume")</f>
-        <v>29181595</v>
+        <v>38023073</v>
       </c>
       <c r="Q85" s="7" cm="1">
         <f t="array" aca="1" ref="Q85" ca="1">_FV(B85,"Volume average",TRUE)</f>
@@ -21574,7 +21578,7 @@
       </c>
       <c r="C86" s="2">
         <f t="array" aca="1" ref="C86" ca="1">_FV(B86,"Last trade time",TRUE)</f>
-        <v>46181.758993796095</v>
+        <v>46181.826069721872</v>
       </c>
       <c r="D86" t="str">
         <f t="array" aca="1" ref="D86" ca="1">_FV(B86,"Currency")</f>
@@ -21582,19 +21586,19 @@
       </c>
       <c r="E86" s="3">
         <f t="array" aca="1" ref="E86" ca="1">_FV(B86,"Price")</f>
-        <v>76.959999999999994</v>
+        <v>75.650000000000006</v>
       </c>
       <c r="F86" s="4">
         <f t="array" aca="1" ref="F86" ca="1">_FV(B86,"Change (%)",TRUE)</f>
-        <v>4.6079000000000002E-2</v>
+        <v>2.8271999999999999E-2</v>
       </c>
       <c r="G86" s="5">
         <f t="array" aca="1" ref="G86" ca="1">_FV(B86,"Change")</f>
-        <v>3.39</v>
+        <v>2.08</v>
       </c>
       <c r="H86" s="6">
         <f t="array" aca="1" ref="H86" ca="1">_FV(B86,"P/E",TRUE)</f>
-        <v>30.404599999999999</v>
+        <v>29.887</v>
       </c>
       <c r="I86" s="6">
         <f t="array" aca="1" ref="I86" ca="1">_FV(B86,"Beta")</f>
@@ -21626,7 +21630,7 @@
       </c>
       <c r="P86" s="7">
         <f t="array" aca="1" ref="P86" ca="1">_FV(B86,"Volume")</f>
-        <v>2629542</v>
+        <v>3795020</v>
       </c>
       <c r="Q86" s="7">
         <f t="array" aca="1" ref="Q86" ca="1">_FV(B86,"Volume average",TRUE)</f>
@@ -21646,7 +21650,7 @@
       </c>
       <c r="U86" s="7">
         <f t="array" aca="1" ref="U86" ca="1">_FV(B86,"Market cap",TRUE)</f>
-        <v>11575238064</v>
+        <v>11378206335</v>
       </c>
       <c r="V86" s="7">
         <f t="array" aca="1" ref="V86" ca="1">_FV(B86,"Shares outstanding",TRUE)</f>
@@ -21662,7 +21666,7 @@
       </c>
       <c r="C87" s="2" cm="1">
         <f t="array" aca="1" ref="C87" ca="1">_FV(B87,"Last trade time",TRUE)</f>
-        <v>46181.758995253906</v>
+        <v>46181.826050659372</v>
       </c>
       <c r="D87" t="str" cm="1">
         <f t="array" aca="1" ref="D87" ca="1">_FV(B87,"Currency")</f>
@@ -21670,15 +21674,15 @@
       </c>
       <c r="E87" s="3" cm="1">
         <f t="array" aca="1" ref="E87" ca="1">_FV(B87,"Price")</f>
-        <v>44.75</v>
+        <v>44.67</v>
       </c>
       <c r="F87" s="4" cm="1">
         <f t="array" aca="1" ref="F87" ca="1">_FV(B87,"Change (%)",TRUE)</f>
-        <v>1.6583000000000001E-2</v>
+        <v>1.4766E-2</v>
       </c>
       <c r="G87" s="5" cm="1">
         <f t="array" aca="1" ref="G87" ca="1">_FV(B87,"Change")</f>
-        <v>0.73</v>
+        <v>0.65</v>
       </c>
       <c r="H87" s="6" cm="1">
         <f t="array" aca="1" ref="H87" ca="1">_FV(B87,"P/E",TRUE)</f>
@@ -21714,7 +21718,7 @@
       </c>
       <c r="P87" s="7" cm="1">
         <f t="array" aca="1" ref="P87" ca="1">_FV(B87,"Volume")</f>
-        <v>702676</v>
+        <v>983168</v>
       </c>
       <c r="Q87" s="7" cm="1">
         <f t="array" aca="1" ref="Q87" ca="1">_FV(B87,"Volume average",TRUE)</f>
@@ -21734,7 +21738,7 @@
       </c>
       <c r="U87" s="7" cm="1">
         <f t="array" aca="1" ref="U87" ca="1">_FV(B87,"Market cap",TRUE)</f>
-        <v>26971129300</v>
+        <v>26922912756</v>
       </c>
       <c r="V87" s="7" cm="1">
         <f t="array" aca="1" ref="V87" ca="1">_FV(B87,"Shares outstanding",TRUE)</f>
@@ -21750,7 +21754,7 @@
       </c>
       <c r="C88" s="2">
         <f t="array" aca="1" ref="C88" ca="1">_FV(B88,"Last trade time",TRUE)</f>
-        <v>46181.758948645314</v>
+        <v>46181.826012279686</v>
       </c>
       <c r="D88" t="str">
         <f t="array" aca="1" ref="D88" ca="1">_FV(B88,"Currency")</f>
@@ -21758,15 +21762,15 @@
       </c>
       <c r="E88" s="3">
         <f t="array" aca="1" ref="E88" ca="1">_FV(B88,"Price")</f>
-        <v>48.03</v>
+        <v>48.38</v>
       </c>
       <c r="F88" s="4">
         <f t="array" aca="1" ref="F88" ca="1">_FV(B88,"Change (%)",TRUE)</f>
-        <v>3.4460000000000005E-2</v>
+        <v>4.1999000000000002E-2</v>
       </c>
       <c r="G88" s="5">
         <f t="array" aca="1" ref="G88" ca="1">_FV(B88,"Change")</f>
-        <v>1.6</v>
+        <v>1.95</v>
       </c>
       <c r="H88" s="6">
         <f t="array" aca="1" ref="H88" ca="1">_FV(B88,"P/E",TRUE)</f>
@@ -21786,7 +21790,7 @@
       </c>
       <c r="L88" s="3">
         <f t="array" aca="1" ref="L88" ca="1">_FV(B88,"High")</f>
-        <v>48.4221</v>
+        <v>48.44</v>
       </c>
       <c r="M88" s="3">
         <f t="array" aca="1" ref="M88" ca="1">_FV(B88,"Low")</f>
@@ -21802,7 +21806,7 @@
       </c>
       <c r="P88" s="7">
         <f t="array" aca="1" ref="P88" ca="1">_FV(B88,"Volume")</f>
-        <v>3094866</v>
+        <v>3854567</v>
       </c>
       <c r="Q88" s="7">
         <f t="array" aca="1" ref="Q88" ca="1">_FV(B88,"Volume average",TRUE)</f>
@@ -21822,7 +21826,7 @@
       </c>
       <c r="U88" s="7">
         <f t="array" aca="1" ref="U88" ca="1">_FV(B88,"Market cap",TRUE)</f>
-        <v>8624497344</v>
+        <v>8687345024</v>
       </c>
       <c r="V88" s="7">
         <f t="array" aca="1" ref="V88" ca="1">_FV(B88,"Shares outstanding",TRUE)</f>
@@ -21838,7 +21842,7 @@
       </c>
       <c r="C89" s="2" cm="1">
         <f t="array" aca="1" ref="C89" ca="1">_FV(B89,"Last trade time",TRUE)</f>
-        <v>46181.758974988283</v>
+        <v>46181.826097661717</v>
       </c>
       <c r="D89" t="str" cm="1">
         <f t="array" aca="1" ref="D89" ca="1">_FV(B89,"Currency")</f>
@@ -21846,19 +21850,19 @@
       </c>
       <c r="E89" s="3" cm="1">
         <f t="array" aca="1" ref="E89" ca="1">_FV(B89,"Price")</f>
-        <v>377.11</v>
+        <v>371.28500000000003</v>
       </c>
       <c r="F89" s="4" cm="1">
         <f t="array" aca="1" ref="F89" ca="1">_FV(B89,"Change (%)",TRUE)</f>
-        <v>5.3586000000000002E-2</v>
+        <v>3.7311999999999998E-2</v>
       </c>
       <c r="G89" s="5" cm="1">
         <f t="array" aca="1" ref="G89" ca="1">_FV(B89,"Change")</f>
-        <v>19.18</v>
+        <v>13.355</v>
       </c>
       <c r="H89" s="6" cm="1">
         <f t="array" aca="1" ref="H89" ca="1">_FV(B89,"P/E",TRUE)</f>
-        <v>69.795100000000005</v>
+        <v>68.716999999999999</v>
       </c>
       <c r="I89" s="6" cm="1">
         <f t="array" aca="1" ref="I89" ca="1">_FV(B89,"Beta")</f>
@@ -21890,7 +21894,7 @@
       </c>
       <c r="P89" s="7" cm="1">
         <f t="array" aca="1" ref="P89" ca="1">_FV(B89,"Volume")</f>
-        <v>1344398</v>
+        <v>1768341</v>
       </c>
       <c r="Q89" s="7" cm="1">
         <f t="array" aca="1" ref="Q89" ca="1">_FV(B89,"Volume average",TRUE)</f>
@@ -21910,7 +21914,7 @@
       </c>
       <c r="U89" s="7" cm="1">
         <f t="array" aca="1" ref="U89" ca="1">_FV(B89,"Market cap",TRUE)</f>
-        <v>59033629042</v>
+        <v>58121770727</v>
       </c>
       <c r="V89" s="7" cm="1">
         <f t="array" aca="1" ref="V89" ca="1">_FV(B89,"Shares outstanding",TRUE)</f>
@@ -21926,7 +21930,7 @@
       </c>
       <c r="C90" s="2">
         <f t="array" aca="1" ref="C90" ca="1">_FV(B90,"Last trade time",TRUE)</f>
-        <v>46181.759033738279</v>
+        <v>46181.826093726566</v>
       </c>
       <c r="D90" t="str">
         <f t="array" aca="1" ref="D90" ca="1">_FV(B90,"Currency")</f>
@@ -21934,19 +21938,19 @@
       </c>
       <c r="E90" s="3">
         <f t="array" aca="1" ref="E90" ca="1">_FV(B90,"Price")</f>
-        <v>410.7</v>
+        <v>408.88499999999999</v>
       </c>
       <c r="F90" s="4">
         <f t="array" aca="1" ref="F90" ca="1">_FV(B90,"Change (%)",TRUE)</f>
-        <v>5.0384000000000005E-2</v>
+        <v>4.5742000000000005E-2</v>
       </c>
       <c r="G90" s="5">
         <f t="array" aca="1" ref="G90" ca="1">_FV(B90,"Change")</f>
-        <v>19.7</v>
+        <v>17.885000000000002</v>
       </c>
       <c r="H90" s="6">
         <f t="array" aca="1" ref="H90" ca="1">_FV(B90,"P/E",TRUE)</f>
-        <v>375.37700000000001</v>
+        <v>373.71809999999999</v>
       </c>
       <c r="I90" s="6">
         <f t="array" aca="1" ref="I90" ca="1">_FV(B90,"Beta")</f>
@@ -21962,7 +21966,7 @@
       </c>
       <c r="L90" s="3">
         <f t="array" aca="1" ref="L90" ca="1">_FV(B90,"High")</f>
-        <v>411.83</v>
+        <v>412.94</v>
       </c>
       <c r="M90" s="3">
         <f t="array" aca="1" ref="M90" ca="1">_FV(B90,"Low")</f>
@@ -21978,7 +21982,7 @@
       </c>
       <c r="P90" s="7">
         <f t="array" aca="1" ref="P90" ca="1">_FV(B90,"Volume")</f>
-        <v>33961318</v>
+        <v>42341061</v>
       </c>
       <c r="Q90" s="7">
         <f t="array" aca="1" ref="Q90" ca="1">_FV(B90,"Volume average",TRUE)</f>
@@ -21998,7 +22002,7 @@
       </c>
       <c r="U90" s="7">
         <f t="array" aca="1" ref="U90" ca="1">_FV(B90,"Market cap",TRUE)</f>
-        <v>1542475846800</v>
+        <v>1535659207740</v>
       </c>
       <c r="V90" s="7">
         <f t="array" aca="1" ref="V90" ca="1">_FV(B90,"Shares outstanding",TRUE)</f>
@@ -22014,7 +22018,7 @@
       </c>
       <c r="C91" s="2">
         <f t="array" aca="1" ref="C91" ca="1">_FV(B91,"Last trade time",TRUE)</f>
-        <v>46181.759024513281</v>
+        <v>46181.826098750003</v>
       </c>
       <c r="D91" t="str">
         <f t="array" aca="1" ref="D91" ca="1">_FV(B91,"Currency")</f>
@@ -22022,19 +22026,19 @@
       </c>
       <c r="E91" s="3">
         <f t="array" aca="1" ref="E91" ca="1">_FV(B91,"Price")</f>
-        <v>428.77</v>
+        <v>426.36500000000001</v>
       </c>
       <c r="F91" s="4">
         <f t="array" aca="1" ref="F91" ca="1">_FV(B91,"Change (%)",TRUE)</f>
-        <v>3.2757999999999995E-2</v>
+        <v>2.6964999999999999E-2</v>
       </c>
       <c r="G91" s="5">
         <f t="array" aca="1" ref="G91" ca="1">_FV(B91,"Change")</f>
-        <v>13.6</v>
+        <v>11.195</v>
       </c>
       <c r="H91" s="6">
         <f t="array" aca="1" ref="H91" ca="1">_FV(B91,"P/E",TRUE)</f>
-        <v>36.277700000000003</v>
+        <v>36.074199999999998</v>
       </c>
       <c r="I91" s="6">
         <f t="array" aca="1" ref="I91" ca="1">_FV(B91,"Beta")</f>
@@ -22066,7 +22070,7 @@
       </c>
       <c r="P91" s="7">
         <f t="array" aca="1" ref="P91" ca="1">_FV(B91,"Volume")</f>
-        <v>8269153</v>
+        <v>9466198</v>
       </c>
       <c r="Q91" s="7">
         <f t="array" aca="1" ref="Q91" ca="1">_FV(B91,"Volume average",TRUE)</f>
@@ -22086,7 +22090,7 @@
       </c>
       <c r="U91" s="7">
         <f t="array" aca="1" ref="U91" ca="1">_FV(B91,"Market cap",TRUE)</f>
-        <v>2223804456980</v>
+        <v>2211330987010</v>
       </c>
       <c r="V91" s="7">
         <f t="array" aca="1" ref="V91" ca="1">_FV(B91,"Shares outstanding",TRUE)</f>
@@ -22102,7 +22106,7 @@
       </c>
       <c r="C92" s="2" cm="1">
         <f t="array" aca="1" ref="C92" ca="1">_FV(B92,"Last trade time",TRUE)</f>
-        <v>46181.759025844534</v>
+        <v>46181.826084883593</v>
       </c>
       <c r="D92" t="str" cm="1">
         <f t="array" aca="1" ref="D92" ca="1">_FV(B92,"Currency")</f>
@@ -22110,19 +22114,19 @@
       </c>
       <c r="E92" s="3" cm="1">
         <f t="array" aca="1" ref="E92" ca="1">_FV(B92,"Price")</f>
-        <v>213.63</v>
+        <v>213.56</v>
       </c>
       <c r="F92" s="4" cm="1">
         <f t="array" aca="1" ref="F92" ca="1">_FV(B92,"Change (%)",TRUE)</f>
-        <v>-5.4692999999999999E-2</v>
+        <v>-5.5002000000000002E-2</v>
       </c>
       <c r="G92" s="5" cm="1">
         <f t="array" aca="1" ref="G92" ca="1">_FV(B92,"Change")</f>
-        <v>-12.36</v>
+        <v>-12.43</v>
       </c>
       <c r="H92" s="6" cm="1">
         <f t="array" aca="1" ref="H92" ca="1">_FV(B92,"P/E",TRUE)</f>
-        <v>332.08460000000002</v>
+        <v>331.97579999999999</v>
       </c>
       <c r="I92" s="6" cm="1">
         <f t="array" aca="1" ref="I92" ca="1">_FV(B92,"Beta")</f>
@@ -22142,7 +22146,7 @@
       </c>
       <c r="M92" s="3" cm="1">
         <f t="array" aca="1" ref="M92" ca="1">_FV(B92,"Low")</f>
-        <v>212.53</v>
+        <v>212.01009999999999</v>
       </c>
       <c r="N92" s="3" cm="1">
         <f t="array" aca="1" ref="N92" ca="1">_FV(B92,"Open")</f>
@@ -22154,7 +22158,7 @@
       </c>
       <c r="P92" s="7" cm="1">
         <f t="array" aca="1" ref="P92" ca="1">_FV(B92,"Volume")</f>
-        <v>1671334</v>
+        <v>2155716</v>
       </c>
       <c r="Q92" s="7" cm="1">
         <f t="array" aca="1" ref="Q92" ca="1">_FV(B92,"Volume average",TRUE)</f>
@@ -22174,7 +22178,7 @@
       </c>
       <c r="U92" s="7" cm="1">
         <f t="array" aca="1" ref="U92" ca="1">_FV(B92,"Market cap",TRUE)</f>
-        <v>32423458257</v>
+        <v>32412834084</v>
       </c>
       <c r="V92" s="7" cm="1">
         <f t="array" aca="1" ref="V92" ca="1">_FV(B92,"Shares outstanding",TRUE)</f>
@@ -22190,7 +22194,7 @@
       </c>
       <c r="C93" s="2" cm="1">
         <f t="array" aca="1" ref="C93" ca="1">_FV(B93,"Last trade time",TRUE)</f>
-        <v>46181.759030196095</v>
+        <v>46181.826102488281</v>
       </c>
       <c r="D93" t="str" cm="1">
         <f t="array" aca="1" ref="D93" ca="1">_FV(B93,"Currency")</f>
@@ -22198,19 +22202,19 @@
       </c>
       <c r="E93" s="3" cm="1">
         <f t="array" aca="1" ref="E93" ca="1">_FV(B93,"Price")</f>
-        <v>302</v>
+        <v>301.45</v>
       </c>
       <c r="F93" s="4" cm="1">
         <f t="array" aca="1" ref="F93" ca="1">_FV(B93,"Change (%)",TRUE)</f>
-        <v>4.9580000000000006E-3</v>
+        <v>3.1280000000000001E-3</v>
       </c>
       <c r="G93" s="5" cm="1">
         <f t="array" aca="1" ref="G93" ca="1">_FV(B93,"Change")</f>
-        <v>1.49</v>
+        <v>0.94</v>
       </c>
       <c r="H93" s="6" cm="1">
         <f t="array" aca="1" ref="H93" ca="1">_FV(B93,"P/E",TRUE)</f>
-        <v>75.822199999999995</v>
+        <v>75.684200000000004</v>
       </c>
       <c r="I93" s="6" cm="1">
         <f t="array" aca="1" ref="I93" ca="1">_FV(B93,"Beta")</f>
@@ -22242,7 +22246,7 @@
       </c>
       <c r="P93" s="7" cm="1">
         <f t="array" aca="1" ref="P93" ca="1">_FV(B93,"Volume")</f>
-        <v>3093135</v>
+        <v>3936692</v>
       </c>
       <c r="Q93" s="7" cm="1">
         <f t="array" aca="1" ref="Q93" ca="1">_FV(B93,"Volume average",TRUE)</f>
@@ -22262,7 +22266,7 @@
       </c>
       <c r="U93" s="7" cm="1">
         <f t="array" aca="1" ref="U93" ca="1">_FV(B93,"Market cap",TRUE)</f>
-        <v>116000857600</v>
+        <v>115789597760</v>
       </c>
       <c r="V93" s="7" cm="1">
         <f t="array" aca="1" ref="V93" ca="1">_FV(B93,"Shares outstanding",TRUE)</f>
@@ -22278,7 +22282,7 @@
       </c>
       <c r="C94" s="2" cm="1">
         <f t="array" aca="1" ref="C94" ca="1">_FV(B94,"Last trade time",TRUE)</f>
-        <v>46181.759015601565</v>
+        <v>46181.826111620314</v>
       </c>
       <c r="D94" t="str" cm="1">
         <f t="array" aca="1" ref="D94" ca="1">_FV(B94,"Currency")</f>
@@ -22286,19 +22290,19 @@
       </c>
       <c r="E94" s="3" cm="1">
         <f t="array" aca="1" ref="E94" ca="1">_FV(B94,"Price")</f>
-        <v>143.625</v>
+        <v>143.94999999999999</v>
       </c>
       <c r="F94" s="4" cm="1">
         <f t="array" aca="1" ref="F94" ca="1">_FV(B94,"Change (%)",TRUE)</f>
-        <v>-4.5399999999999998E-3</v>
+        <v>-2.287E-3</v>
       </c>
       <c r="G94" s="5" cm="1">
         <f t="array" aca="1" ref="G94" ca="1">_FV(B94,"Change")</f>
-        <v>-0.65500000000000003</v>
+        <v>-0.33</v>
       </c>
       <c r="H94" s="6" cm="1">
         <f t="array" aca="1" ref="H94" ca="1">_FV(B94,"P/E",TRUE)</f>
-        <v>44.833799999999997</v>
+        <v>44.935200000000002</v>
       </c>
       <c r="I94" s="6" cm="1">
         <f t="array" aca="1" ref="I94" ca="1">_FV(B94,"Beta")</f>
@@ -22330,7 +22334,7 @@
       </c>
       <c r="P94" s="7" cm="1">
         <f t="array" aca="1" ref="P94" ca="1">_FV(B94,"Volume")</f>
-        <v>1615228</v>
+        <v>2200528</v>
       </c>
       <c r="Q94" s="7" cm="1">
         <f t="array" aca="1" ref="Q94" ca="1">_FV(B94,"Volume average",TRUE)</f>
@@ -22350,7 +22354,7 @@
       </c>
       <c r="U94" s="7" cm="1">
         <f t="array" aca="1" ref="U94" ca="1">_FV(B94,"Market cap",TRUE)</f>
-        <v>35475375000</v>
+        <v>35555650000</v>
       </c>
       <c r="V94" s="7" cm="1">
         <f t="array" aca="1" ref="V94" ca="1">_FV(B94,"Shares outstanding",TRUE)</f>
@@ -22366,7 +22370,7 @@
       </c>
       <c r="C95" s="2" cm="1">
         <f t="array" aca="1" ref="C95" ca="1">_FV(B95,"Last trade time",TRUE)</f>
-        <v>46181.759036978903</v>
+        <v>46181.826076943747</v>
       </c>
       <c r="D95" t="str" cm="1">
         <f t="array" aca="1" ref="D95" ca="1">_FV(B95,"Currency")</f>
@@ -22374,15 +22378,15 @@
       </c>
       <c r="E95" s="3" cm="1">
         <f t="array" aca="1" ref="E95" ca="1">_FV(B95,"Price")</f>
-        <v>129.99</v>
+        <v>129.30500000000001</v>
       </c>
       <c r="F95" s="4" cm="1">
         <f t="array" aca="1" ref="F95" ca="1">_FV(B95,"Change (%)",TRUE)</f>
-        <v>-6.0409999999999995E-3</v>
+        <v>-1.1278E-2</v>
       </c>
       <c r="G95" s="5" cm="1">
         <f t="array" aca="1" ref="G95" ca="1">_FV(B95,"Change")</f>
-        <v>-0.79</v>
+        <v>-1.4750000000000001</v>
       </c>
       <c r="H95" s="6" cm="1">
         <f t="array" aca="1" ref="H95" ca="1">_FV(B95,"P/E",TRUE)</f>
@@ -22418,7 +22422,7 @@
       </c>
       <c r="P95" s="7" cm="1">
         <f t="array" aca="1" ref="P95" ca="1">_FV(B95,"Volume")</f>
-        <v>2039066</v>
+        <v>2590553</v>
       </c>
       <c r="Q95" s="7" cm="1">
         <f t="array" aca="1" ref="Q95" ca="1">_FV(B95,"Volume average",TRUE)</f>
@@ -22438,7 +22442,7 @@
       </c>
       <c r="U95" s="7" cm="1">
         <f t="array" aca="1" ref="U95" ca="1">_FV(B95,"Market cap",TRUE)</f>
-        <v>21020617905</v>
+        <v>20909846897</v>
       </c>
       <c r="V95" s="7" cm="1">
         <f t="array" aca="1" ref="V95" ca="1">_FV(B95,"Shares outstanding",TRUE)</f>
@@ -22549,27 +22553,27 @@
       </c>
       <c r="I2" s="46">
         <f t="shared" ref="I2:I10" ca="1" si="1">_FV(B2,"Price")</f>
-        <v>587.42999999999995</v>
+        <v>589.57000000000005</v>
       </c>
       <c r="J2" s="47">
         <f ca="1">Config!$C$1</f>
-        <v>0.74919999999999998</v>
+        <v>0.74950000000000006</v>
       </c>
       <c r="K2" s="48" cm="1">
         <f t="array" aca="1" ref="K2" ca="1">_FV(B2,"Change (%)",TRUE)</f>
-        <v>-9.3930000000000003E-3</v>
+        <v>-5.7840000000000001E-3</v>
       </c>
       <c r="L2" s="45">
         <f t="shared" ref="L2:L10" ca="1" si="2">F2*I2*J2</f>
-        <v>2640.6153359999998</v>
+        <v>2651.2962900000002</v>
       </c>
       <c r="M2" s="45">
         <f t="shared" ref="M2:M10" ca="1" si="3">L2-H2</f>
-        <v>-527.24466600000051</v>
+        <v>-516.56371200000012</v>
       </c>
       <c r="N2" s="48">
         <f t="shared" ref="N2:N10" ca="1" si="4">IF(H2=0,"",M2/H2)</f>
-        <v>-0.16643559553361867</v>
+        <v>-0.16306393327794544</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="24">
@@ -22601,27 +22605,27 @@
       </c>
       <c r="I3" s="46">
         <f t="shared" ca="1" si="1"/>
-        <v>85</v>
+        <v>84.974999999999994</v>
       </c>
       <c r="J3" s="47">
         <f ca="1">Config!$C$1</f>
-        <v>0.74919999999999998</v>
+        <v>0.74950000000000006</v>
       </c>
       <c r="K3" s="48" cm="1">
         <f t="array" aca="1" ref="K3" ca="1">_FV(B3,"Change (%)",TRUE)</f>
-        <v>3.0678E-2</v>
+        <v>3.0374999999999999E-2</v>
       </c>
       <c r="L3" s="45">
         <f t="shared" ca="1" si="2"/>
-        <v>4776.1499999999996</v>
+        <v>4776.6571875</v>
       </c>
       <c r="M3" s="45">
         <f t="shared" ca="1" si="3"/>
-        <v>1128.3507000000004</v>
+        <v>1128.8578875000007</v>
       </c>
       <c r="N3" s="48">
         <f t="shared" ca="1" si="4"/>
-        <v>0.30932367907412028</v>
+        <v>0.30946271838475353</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="24">
@@ -22653,27 +22657,27 @@
       </c>
       <c r="I4" s="46">
         <f t="shared" ca="1" si="1"/>
-        <v>208.97</v>
+        <v>207.83500000000001</v>
       </c>
       <c r="J4" s="47">
         <f ca="1">Config!$C$1</f>
-        <v>0.74919999999999998</v>
+        <v>0.74950000000000006</v>
       </c>
       <c r="K4" s="48" cm="1">
         <f t="array" aca="1" ref="K4" ca="1">_FV(B4,"Change (%)",TRUE)</f>
-        <v>1.8869E-2</v>
+        <v>1.3335E-2</v>
       </c>
       <c r="L4" s="45">
         <f t="shared" ca="1" si="2"/>
-        <v>2818.0858319999998</v>
+        <v>2803.9019850000004</v>
       </c>
       <c r="M4" s="45">
         <f t="shared" ca="1" si="3"/>
-        <v>485.6458319999997</v>
+        <v>471.46198500000037</v>
       </c>
       <c r="N4" s="48">
         <f t="shared" ca="1" si="4"/>
-        <v>0.20821364408087656</v>
+        <v>0.20213252430930714</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="24">
@@ -22705,27 +22709,27 @@
       </c>
       <c r="I5" s="46">
         <f t="shared" ca="1" si="1"/>
-        <v>491.387</v>
+        <v>487.97</v>
       </c>
       <c r="J5" s="47">
         <f ca="1">Config!$C$1</f>
-        <v>0.74919999999999998</v>
+        <v>0.74950000000000006</v>
       </c>
       <c r="K5" s="48" cm="1">
         <f t="array" aca="1" ref="K5" ca="1">_FV(B5,"Change (%)",TRUE)</f>
-        <v>5.3619E-2</v>
+        <v>4.6293000000000001E-2</v>
       </c>
       <c r="L5" s="45">
         <f t="shared" ca="1" si="2"/>
-        <v>4417.7656847999997</v>
+        <v>4388.8021800000006</v>
       </c>
       <c r="M5" s="45">
         <f t="shared" ca="1" si="3"/>
-        <v>2558.2456847999997</v>
+        <v>2529.2821800000006</v>
       </c>
       <c r="N5" s="48">
         <f t="shared" ca="1" si="4"/>
-        <v>1.3757559395973153</v>
+        <v>1.3601801432627778</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="24">
@@ -22757,27 +22761,27 @@
       </c>
       <c r="I6" s="46">
         <f t="shared" ca="1" si="1"/>
-        <v>103.1</v>
+        <v>102.13</v>
       </c>
       <c r="J6" s="47">
         <f ca="1">Config!$C$1</f>
-        <v>0.74919999999999998</v>
+        <v>0.74950000000000006</v>
       </c>
       <c r="K6" s="48" cm="1">
         <f t="array" aca="1" ref="K6" ca="1">_FV(B6,"Change (%)",TRUE)</f>
-        <v>2.6995000000000002E-2</v>
+        <v>1.7332E-2</v>
       </c>
       <c r="L6" s="45">
         <f t="shared" ca="1" si="2"/>
-        <v>2394.5181199999997</v>
+        <v>2372.9394849999999</v>
       </c>
       <c r="M6" s="45">
         <f t="shared" ca="1" si="3"/>
-        <v>320.42812099999946</v>
+        <v>298.84948599999962</v>
       </c>
       <c r="N6" s="48">
         <f t="shared" ca="1" si="4"/>
-        <v>0.15449094357259829</v>
+        <v>0.14408703872256587</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="24">
@@ -22809,27 +22813,27 @@
       </c>
       <c r="I7" s="46">
         <f t="shared" ca="1" si="1"/>
-        <v>410.7</v>
+        <v>408.88499999999999</v>
       </c>
       <c r="J7" s="47">
         <f ca="1">Config!$C$1</f>
-        <v>0.74919999999999998</v>
+        <v>0.74950000000000006</v>
       </c>
       <c r="K7" s="48" cm="1">
         <f t="array" aca="1" ref="K7" ca="1">_FV(B7,"Change (%)",TRUE)</f>
-        <v>5.0384000000000005E-2</v>
+        <v>4.5742000000000005E-2</v>
       </c>
       <c r="L7" s="45">
         <f t="shared" ca="1" si="2"/>
-        <v>5538.5359199999994</v>
+        <v>5516.2675350000009</v>
       </c>
       <c r="M7" s="45">
         <f t="shared" ca="1" si="3"/>
-        <v>684.26602000000003</v>
+        <v>661.99763500000154</v>
       </c>
       <c r="N7" s="48">
         <f t="shared" ca="1" si="4"/>
-        <v>0.14096167582276381</v>
+        <v>0.13637429492744144</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="24">
@@ -22861,27 +22865,27 @@
       </c>
       <c r="I8" s="46">
         <f t="shared" ca="1" si="1"/>
-        <v>10.164999999999999</v>
+        <v>10.020099999999999</v>
       </c>
       <c r="J8" s="47">
         <f ca="1">Config!$C$1</f>
-        <v>0.74919999999999998</v>
+        <v>0.74950000000000006</v>
       </c>
       <c r="K8" s="48" cm="1">
         <f t="array" aca="1" ref="K8" ca="1">_FV(B8,"Change (%)",TRUE)</f>
-        <v>2.4650000000000002E-3</v>
+        <v>-1.1823999999999999E-2</v>
       </c>
       <c r="L8" s="45">
         <f t="shared" ca="1" si="2"/>
-        <v>944.33663199999978</v>
+        <v>931.24805379999998</v>
       </c>
       <c r="M8" s="45">
         <f t="shared" ca="1" si="3"/>
-        <v>-148.89337200000023</v>
+        <v>-161.98195020000003</v>
       </c>
       <c r="N8" s="48">
         <f t="shared" ca="1" si="4"/>
-        <v>-0.13619583386406967</v>
+        <v>-0.14816822590610129</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="24">
@@ -22913,27 +22917,27 @@
       </c>
       <c r="I9" s="46">
         <f t="shared" ca="1" si="1"/>
-        <v>12.494999999999999</v>
+        <v>12.185</v>
       </c>
       <c r="J9" s="47">
         <f ca="1">Config!$C$1</f>
-        <v>0.74919999999999998</v>
+        <v>0.74950000000000006</v>
       </c>
       <c r="K9" s="48" cm="1">
         <f t="array" aca="1" ref="K9" ca="1">_FV(B9,"Change (%)",TRUE)</f>
-        <v>5.3540999999999998E-2</v>
+        <v>2.7403E-2</v>
       </c>
       <c r="L9" s="45">
         <f t="shared" ca="1" si="2"/>
-        <v>4175.1192839999994</v>
+        <v>4073.1652450000006</v>
       </c>
       <c r="M9" s="45">
         <f t="shared" ca="1" si="3"/>
-        <v>1665.249147999999</v>
+        <v>1563.2951090000001</v>
       </c>
       <c r="N9" s="48">
         <f t="shared" ca="1" si="4"/>
-        <v>0.66348020326418944</v>
+        <v>0.62285896253239448</v>
       </c>
     </row>
     <row r="10" spans="1:14" hidden="1">
@@ -22969,7 +22973,7 @@
       </c>
       <c r="J10" s="20">
         <f ca="1">Config!$C$1</f>
-        <v>0.74919999999999998</v>
+        <v>0.74950000000000006</v>
       </c>
       <c r="K10" s="36" cm="1">
         <f t="array" aca="1" ref="K10" ca="1">_FV(B10,"Change (%)",TRUE)</f>
@@ -22977,15 +22981,15 @@
       </c>
       <c r="L10" s="18">
         <f t="shared" ca="1" si="2"/>
-        <v>32298.011999999999</v>
+        <v>32310.945000000003</v>
       </c>
       <c r="M10" s="18">
         <f t="shared" ca="1" si="3"/>
-        <v>27298.011999999999</v>
+        <v>27310.945000000003</v>
       </c>
       <c r="N10" s="21">
         <f t="shared" ca="1" si="4"/>
-        <v>5.4596023999999996</v>
+        <v>5.4621890000000004</v>
       </c>
     </row>
   </sheetData>
@@ -23043,7 +23047,7 @@
       </c>
       <c r="C1" s="3" cm="1">
         <f t="array" aca="1" ref="C1" ca="1">_FV(B1,"Price")</f>
-        <v>0.74919999999999998</v>
+        <v>0.74950000000000006</v>
       </c>
     </row>
   </sheetData>

--- a/dashboard/trading_system.xlsx
+++ b/dashboard/trading_system.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\husainnatha\tradingsystem\dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDE5B21B-8BF3-4C9F-B0D4-CBB27257EE87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5555341B-1627-4F40-B850-AB10154C9532}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="2" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3690" yWindow="2258" windowWidth="16200" windowHeight="9307" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CONTRIBUTIONS" sheetId="11" r:id="rId1"/>
@@ -3355,63 +3355,6 @@
       </font>
     </dxf>
     <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_([$$-409]* #,##0.00_);_([$$-409]* \(#,##0.00\);_([$$-409]* &quot;-&quot;??_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_([$$-409]* #,##0.00_);_([$$-409]* \(#,##0.00\);_([$$-409]* &quot;-&quot;??_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_([$$-409]* #,##0.00_);_([$$-409]* \(#,##0.00\);_([$$-409]* &quot;-&quot;??_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_([$$-409]* #,##0.00_);_([$$-409]* \(#,##0.00\);_([$$-409]* &quot;-&quot;??_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_([$$-409]* #,##0.00_);_([$$-409]* \(#,##0.00\);_([$$-409]* &quot;-&quot;??_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_([$$-409]* #,##0.00_);_([$$-409]* \(#,##0.00\);_([$$-409]* &quot;-&quot;??_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="4" formatCode="#,##0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="4" formatCode="#,##0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_([$$-409]* #,##0.00_);_([$$-409]* \(#,##0.00\);_([$$-409]* &quot;-&quot;??_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="27" formatCode="dd/mm/yyyy\ hh:mm"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-    </dxf>
-    <dxf>
       <font>
         <b/>
         <i val="0"/>
@@ -3799,6 +3742,63 @@
       </fill>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_([$$-409]* #,##0.00_);_([$$-409]* \(#,##0.00\);_([$$-409]* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_([$$-409]* #,##0.00_);_([$$-409]* \(#,##0.00\);_([$$-409]* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_([$$-409]* #,##0.00_);_([$$-409]* \(#,##0.00\);_([$$-409]* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_([$$-409]* #,##0.00_);_([$$-409]* \(#,##0.00\);_([$$-409]* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_([$$-409]* #,##0.00_);_([$$-409]* \(#,##0.00\);_([$$-409]* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_([$$-409]* #,##0.00_);_([$$-409]* \(#,##0.00\);_([$$-409]* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="4" formatCode="#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="4" formatCode="#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_([$$-409]* #,##0.00_);_([$$-409]* \(#,##0.00\);_([$$-409]* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="27" formatCode="dd/mm/yyyy\ hh:mm"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -3942,11 +3942,11 @@
     <v>4</v>
     <v>233.67</v>
     <v>15.29</v>
-    <v>3.6392000000000002</v>
+    <v>3.6533000000000002</v>
     <v>-3.73</v>
-    <v>8.6960000000000006E-3</v>
+    <v>7.986E-3</v>
     <v>-2.1588E-2</v>
-    <v>1.47</v>
+    <v>1.35</v>
     <v>USD</v>
     <v>Applied Optoelectronics, Inc. is a developer and manufacturer of advanced optical and hybrid fiber coaxial (HFC) networking products that are the building blocks for artificial intelligence (AI) datacenters, Cable TV Broadband (CATV) and broadband fiber access networks around the world. The Company supplies this critical infrastructure to tier-one customers across cloud computing, CATV broadband, telecom, and fiber-to-the-home (FTTH) markets. It designs and manufactures a range of optical communications products at varying levels of integration, from components, subassemblies and modules to complete turn-key equipment. In the CATV market, it supplies a broad array of products, including lasers, transmitters and transceivers, and turn-key equipment. It supplies optical transceivers that plug into switches and servers within the data center and allow these network devices to send and receive data over fiber optic cables. In the telecom market, it supplies lasers and laser subassemblies.</v>
     <v>4691</v>
@@ -3957,7 +3957,7 @@
     <v>179.9</v>
     <v>Electronic Equipment &amp; Parts</v>
     <v>Stock</v>
-    <v>46185.991709640628</v>
+    <v>46185.999966839845</v>
     <v>0</v>
     <v>163.66</v>
     <v>13565040268</v>
@@ -3967,11 +3967,11 @@
     <v>0</v>
     <v>172.78</v>
     <v>169.05</v>
-    <v>170.52</v>
+    <v>170.4</v>
     <v>80242770</v>
     <v>AAOI</v>
     <v>APPLIED OPTOELECTRONICS, INC. (XNAS:AAOI)</v>
-    <v>12722744</v>
+    <v>12730850</v>
     <v>13978366</v>
     <v>2013</v>
   </rv>
@@ -3996,11 +3996,11 @@
     <v>4</v>
     <v>317.39999999999998</v>
     <v>195.07</v>
-    <v>1.0943000000000001</v>
+    <v>1.0979000000000001</v>
     <v>-4.5</v>
-    <v>9.2399999999999991E-4</v>
+    <v>1.542E-3</v>
     <v>-1.5221999999999999E-2</v>
-    <v>0.26900000000000002</v>
+    <v>0.44890000000000002</v>
     <v>USD</v>
     <v>Apple Inc. designs, manufactures and markets smartphones, personal computers, tablets, wearables and accessories, and sells a variety of related services. Its product categories include iPhone, Mac, iPad, Wearables, Home and Accessories. Its services include advertising, AppleCare, cloud services, digital content, and payment services. The Company operates various platforms, including the App Store, that allow customers to discover and download applications and digital content, such as books, music, video, games and podcasts. It also offers digital content through subscription-based services, including Apple Arcade, Apple Fitness+, Apple Music, Apple News+, and Apple TV+. Its wearables include smartwatches, wireless headphones, and spatial computers. Its products include iPhone 16 Pro, iPhone 16, iPhone 15, iPhone 14, iPhone SE, MacBook Air, MacBook Pro, iMac, Mac mini, Mac Studio, Mac Pro, iPad Pro, iPad Air, AirPods, AirPods Pro, AirPods Max, Apple TV, Apple Vision Pro and others.</v>
     <v>166000</v>
@@ -4011,21 +4011,21 @@
     <v>297.14</v>
     <v>Computers, Phones &amp; Household Electronics</v>
     <v>Stock</v>
-    <v>46185.991743772654</v>
+    <v>46185.999966029689</v>
     <v>3</v>
     <v>289.62</v>
     <v>4275931116800</v>
     <v>APPLE INC.</v>
     <v>APPLE INC.</v>
     <v>296.02999999999997</v>
-    <v>35.357900000000001</v>
+    <v>35.904400000000003</v>
     <v>295.63</v>
     <v>291.13</v>
-    <v>291.399</v>
+    <v>291.57889999999998</v>
     <v>14687360000</v>
     <v>AAPL</v>
     <v>APPLE INC. (XNAS:AAPL)</v>
-    <v>38772578</v>
+    <v>38784789</v>
     <v>49795178</v>
     <v>1977</v>
   </rv>
@@ -4070,11 +4070,11 @@
     <v>4</v>
     <v>416.39</v>
     <v>196.9</v>
-    <v>1.4311</v>
+    <v>1.4427000000000001</v>
     <v>-14.78</v>
-    <v>1.029E-3</v>
+    <v>1.127E-3</v>
     <v>-6.7549999999999999E-2</v>
-    <v>0.2099</v>
+    <v>0.23</v>
     <v>USD</v>
     <v>Adobe Inc. is a global technology company. The Company's products, services and solutions are used around the world to imagine, create, manage, deliver, measure, optimize and engage with content across surfaces and fuel digital experiences. Its segments include Digital Media, Digital Experience, and Publishing and Advertising. The Digital Media segment is centered around Adobe Creative Cloud and Adobe Document Cloud, which include Adobe Express, Adobe Firefly, Photoshop and other products, offering a variety of tools for creative professionals, communicators and other consumers. The Digital Experience segment provides an integrated platform and set of products, services and solutions through Adobe Experience Cloud. The Publishing and Advertising segment contains legacy products and services. In addition, its Adobe GenStudio solution allows businesses to simplify their content supply chain process with generative artificial intelligence (AI) capabilities and intelligent automation.</v>
     <v>31360</v>
@@ -4086,21 +4086,21 @@
     <v>9</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46185.991780798438</v>
+    <v>46185.999881260941</v>
     <v>10</v>
     <v>196.9</v>
     <v>82464884000</v>
     <v>ADOBE INC.</v>
     <v>ADOBE INC.</v>
     <v>202.4</v>
-    <v>11.6812</v>
+    <v>12.5275</v>
     <v>218.8</v>
     <v>204.02</v>
-    <v>204.22989999999999</v>
+    <v>204.25</v>
     <v>404200000</v>
     <v>ADBE</v>
     <v>ADOBE INC. (XNAS:ADBE)</v>
-    <v>25053187</v>
+    <v>25063668</v>
     <v>5544420</v>
     <v>1997</v>
   </rv>
@@ -4125,11 +4125,11 @@
     <v>4</v>
     <v>121.8</v>
     <v>10.887499999999999</v>
-    <v>3.1503000000000001</v>
+    <v>3.1440999999999999</v>
     <v>5.44</v>
-    <v>6.7300000000000007E-3</v>
+    <v>9.4959999999999992E-3</v>
     <v>5.28E-2</v>
-    <v>0.73</v>
+    <v>1.03</v>
     <v>USD</v>
     <v>Aehr Test Systems, Inc. offers test solutions for testing, burning-in, and stabilizing semiconductor devices in wafer level, singulated die, and package part form. The Company's products include the FOX-P family of test and burn-in systems and FOX WaferPak Aligner, FOX WaferPak Contactor, FOX DiePak Carrier and FOX DiePak Loader. The FOX-XP and FOX-NP systems are full wafer contact and singulated die/module test and burn-in systems that can test, burn-in and stabilize a range of devices such as silicon carbide-based and other power semiconductors, 2D and 3D sensors used in phones, tablets, and other computing devices, memory semiconductors, processors, microcontrollers, systems-on-a-chip, and photonics and integrated optical devices used in AI. FOX-CP system is a single-wafer compact test solution for logic, memory and photonic devices. FOX WaferPak Contactor contains a full wafer contactor capable of testing wafers up to 300 millimeters that enables integrated circuit manufacturers.</v>
     <v>136</v>
@@ -4140,7 +4140,7 @@
     <v>112.5</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46185.991013032028</v>
+    <v>46185.999518668752</v>
     <v>13</v>
     <v>101.2</v>
     <v>3411734027</v>
@@ -4150,11 +4150,11 @@
     <v>0</v>
     <v>103.03</v>
     <v>108.47</v>
-    <v>109.2</v>
+    <v>109.5</v>
     <v>31453250</v>
     <v>AEHR</v>
     <v>AEHR TEST SYSTEMS (XNAS:AEHR)</v>
-    <v>1408317</v>
+    <v>1408832</v>
     <v>2402485</v>
     <v>1977</v>
   </rv>
@@ -4175,7 +4175,7 @@
     <v>13</v>
     <v>12.24</v>
     <v>10.99</v>
-    <v>0.83430000000000004</v>
+    <v>0.83750000000000002</v>
     <v>7.0000000000000007E-2</v>
     <v>5.9630000000000004E-3</v>
     <v>CAD</v>
@@ -4223,9 +4223,9 @@
     <v>84.78</v>
     <v>2.64</v>
     <v>-0.32</v>
-    <v>1.321E-2</v>
+    <v>1.0459000000000001E-2</v>
     <v>-8.7080000000000002E-4</v>
-    <v>4.8498999999999999</v>
+    <v>3.84</v>
     <v>USD</v>
     <v>Astera Labs, Inc. is a global semiconductor company. The Company provides semiconductor-based connectivity solutions for cloud and artificial intelligence (AI) infrastructure. It has developed and deployed its Intelligent Connectivity Platform built from the ground up for cloud and AI infrastructure. Its Intelligent Connectivity Platform provides its customers with the ability to deploy and operate high-performance cloud and AI infrastructure on a scale, addressing an increasingly diverse set of requirements. It provides its connectivity products in various form factors, including Integrated Circuits (ICs), boards, and modules. Its PCIe, CXL and Ethernet semiconductor-based connectivity solutions are purpose-built to unleash the potential of accelerated computing at cloud-scale. The Company's products include Aries products, Taurus products, Leo products and Scorpio products.</v>
     <v>756</v>
@@ -4236,20 +4236,20 @@
     <v>390.98989999999998</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46185.991627303127</v>
+    <v>46185.999754640623</v>
     <v>360.06009999999998</v>
     <v>62932410484</v>
     <v>ASTERA LABS, INC.</v>
     <v>ASTERA LABS, INC.</v>
     <v>379.74</v>
-    <v>247.50569999999999</v>
+    <v>247.71979999999999</v>
     <v>367.47</v>
     <v>367.15</v>
-    <v>371.99990000000003</v>
+    <v>370.99</v>
     <v>171407900</v>
     <v>ALAB</v>
     <v>ASTERA LABS, INC. (XNAS:ALAB)</v>
-    <v>5379109</v>
+    <v>5380744</v>
     <v>6185873</v>
     <v>2017</v>
   </rv>
@@ -4274,11 +4274,11 @@
     <v>4</v>
     <v>96.69</v>
     <v>48.3</v>
-    <v>2.1518999999999999</v>
+    <v>2.1469999999999998</v>
     <v>1.98</v>
-    <v>1.8549999999999999E-3</v>
+    <v>1.4749999999999998E-4</v>
     <v>3.0091E-2</v>
-    <v>0.12570000000000001</v>
+    <v>0.01</v>
     <v>USD</v>
     <v>Ambarella, Inc. is a developer of low-power system-on-a-chip (SoC) semiconductors and software for edge artificial intelligence (AI) applications. The Company's technologies make electronic systems smarter, enabling them to become partially or fully autonomous with features, such as person detection, object classification, and analytics, in addition to performing complex data analysis in real time, delivering imagery, and preserving vital system resources, such as power and network bandwidth. It specializes in the development of deployable, scalable designs for intelligent electronic systems that utilize high-bandwidth sensors. Its products are used in a variety of human viewing, computer vision and edge AI applications, including a variety of automotive camera systems, video security cameras, mobile and fixed robots, industrial applications, and consumer devices, such as action, drone, and 360-degree cameras.</v>
     <v>959</v>
@@ -4289,7 +4289,7 @@
     <v>68.319900000000004</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46185.983880566404</v>
+    <v>46185.999812892966</v>
     <v>20</v>
     <v>64.330100000000002</v>
     <v>2973385240</v>
@@ -4299,11 +4299,11 @@
     <v>0</v>
     <v>65.8</v>
     <v>67.78</v>
-    <v>67.905699999999996</v>
+    <v>67.790000000000006</v>
     <v>43868180</v>
     <v>AMBA</v>
     <v>AMBARELLA, INC. (XNAS:AMBA)</v>
-    <v>879719</v>
+    <v>880488</v>
     <v>1695356</v>
     <v>2004</v>
   </rv>
@@ -4328,11 +4328,11 @@
     <v>4</v>
     <v>546.44000000000005</v>
     <v>115.06</v>
-    <v>2.4946000000000002</v>
+    <v>2.4863</v>
     <v>23.12</v>
-    <v>6.9979999999999999E-3</v>
+    <v>6.4440000000000001E-3</v>
     <v>4.7333E-2</v>
-    <v>3.58</v>
+    <v>3.2965</v>
     <v>USD</v>
     <v>Advanced Micro Devices, Inc. is a global semiconductor company. The Company is focused on high-performance computing and artificial intelligence (AI). Its segments include Data Center, Client and Gaming, and Embedded. Data Center segment includes AI accelerators, microprocessors (CPUs) for servers, graphics processing units (GPUs), accelerated processing units (APUs), data processing units (DPUs), Field Programmable Gate Arrays (FPGAs), and Adaptive system-on-Chip (SoC) products for data centers. Client and Gaming segment includes CPUs, APUs, chipsets for desktops and notebooks, discrete GPUs, and semi-custom SoC products and development services. Embedded segment includes embedded CPUs, APUs, FPGAs, system on modules (SOMs), and Adaptive SoC products. It markets and sells its products under the AMD trademark. Its products include AMD EPYC, AMD Ryzen, AMD Ryzen PRO, Virtex UltraScale+, among others.</v>
     <v>31000</v>
@@ -4343,7 +4343,7 @@
     <v>521.71</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46185.991781585159</v>
+    <v>46185.999992603909</v>
     <v>23</v>
     <v>494</v>
     <v>834166553570</v>
@@ -4353,11 +4353,11 @@
     <v>162.82210000000001</v>
     <v>488.45</v>
     <v>511.57</v>
-    <v>515.15</v>
+    <v>514.86649999999997</v>
     <v>1630601000</v>
     <v>AMD</v>
     <v>ADVANCED MICRO DEVICES, INC. (XNAS:AMD)</v>
-    <v>31602538</v>
+    <v>31618462</v>
     <v>34071185</v>
     <v>1969</v>
   </rv>
@@ -4382,11 +4382,11 @@
     <v>4</v>
     <v>278.56</v>
     <v>196</v>
-    <v>1.4634</v>
+    <v>1.4651000000000001</v>
     <v>-2.96</v>
-    <v>5.8690000000000001E-4</v>
+    <v>4.6109999999999999E-4</v>
     <v>-1.2256E-2</v>
-    <v>0.14000000000000001</v>
+    <v>0.11</v>
     <v>USD</v>
     <v>Amazon.com, Inc. provides a range of products and services to customers. The products offered through its stores include merchandise and content it has purchased for resale and products offered by third-party sellers. The Company’s segments include North America, International and Amazon Web Services (AWS). It serves consumers through its online and physical stores and focuses on selection, price, and convenience. Customers access its offerings through its websites, mobile apps, Alexa, devices, streaming, and physically visiting its stores. It also manufactures and sells electronic devices, including Kindle, Fire tablet, Fire TV, Echo, Ring, Blink, and eero, and develops and produces media content. It serves developers and enterprises of all sizes, including start-ups, government agencies, and academic institutions, through AWS, which offers a set of on-demand technology services, including compute, storage, database, analytics, and machine learning, and other services.</v>
     <v>1575000</v>
@@ -4397,21 +4397,21 @@
     <v>243.36</v>
     <v>Diversified Retail</v>
     <v>Stock</v>
-    <v>46185.991794513284</v>
+    <v>46185.999971075784</v>
     <v>26</v>
     <v>233.59</v>
     <v>2566108590500</v>
     <v>AMAZON.COM, INC.</v>
     <v>AMAZON.COM, INC.</v>
     <v>243.21</v>
-    <v>28.508400000000002</v>
+    <v>28.862200000000001</v>
     <v>241.51</v>
     <v>238.55</v>
-    <v>238.69</v>
+    <v>238.66</v>
     <v>10757110000</v>
     <v>AMZN</v>
     <v>AMAZON.COM, INC. (XNAS:AMZN)</v>
-    <v>51235722</v>
+    <v>51251141</v>
     <v>40007908</v>
     <v>1996</v>
   </rv>
@@ -4436,11 +4436,11 @@
     <v>4</v>
     <v>179.8</v>
     <v>85.58</v>
-    <v>1.6121000000000001</v>
-    <v>6.83</v>
-    <v>2.8179999999999998E-3</v>
-    <v>4.367E-2</v>
-    <v>0.46</v>
+    <v>1.6035999999999999</v>
+    <v>6.84</v>
+    <v>3.1849999999999999E-3</v>
+    <v>4.3734000000000002E-2</v>
+    <v>0.52</v>
     <v>USD</v>
     <v>Arista Networks, Inc. is a provider of data-driven, client-to-cloud networking for large artificial intelligence (AI), data center, campus and routing environments. The Company's cloud networking solutions consist of its Extensible Operating System (EOS), a set of network applications and its Ethernet switching and routing platforms. Its platforms deliver availability, agility, automation, analytics, and security through an advanced network operating stack. It offers a robust set of solutions, ranging from modular and fixed-form-factor campus spine switches to Power-over-Ethernet (PoE) leaf switches and Wi-Fi access points, all managed through CloudVision. The Company's network-as-a-service approach empowers customers of all sizes to leverage their data through offerings spanning three categories: Core (AI, Cloud, and Data Center Networking), Cognitive Adjacencies (Campus and Routing), and Cognitive Networks (Software and Services).</v>
     <v>5115</v>
@@ -4451,21 +4451,21 @@
     <v>165.25</v>
     <v>Communications &amp; Networking</v>
     <v>Stock</v>
-    <v>46185.98980977969</v>
+    <v>46185.999926353907</v>
     <v>29</v>
     <v>159.13499999999999</v>
-    <v>205539705690</v>
+    <v>205552297720</v>
     <v>ARISTA NETWORKS, INC.</v>
     <v>ARISTA NETWORKS, INC.</v>
     <v>160.11000000000001</v>
-    <v>55.908299999999997</v>
+    <v>53.568399999999997</v>
     <v>156.4</v>
-    <v>163.22999999999999</v>
-    <v>163.69999999999999</v>
+    <v>163.24</v>
+    <v>163.76</v>
     <v>1259203000</v>
     <v>ANET</v>
     <v>ARISTA NETWORKS, INC. (XNYS:ANET)</v>
-    <v>6050609</v>
+    <v>6052481</v>
     <v>10936189</v>
     <v>2011</v>
   </rv>
@@ -4490,11 +4490,11 @@
     <v>4</v>
     <v>745.61</v>
     <v>320</v>
-    <v>2.5085999999999999</v>
+    <v>2.4969000000000001</v>
     <v>18.2</v>
-    <v>-1.5499999999999999E-3</v>
+    <v>-5.4350000000000004E-4</v>
     <v>3.8030000000000001E-2</v>
-    <v>-0.77</v>
+    <v>-0.27</v>
     <v>USD</v>
     <v>AppLovin Corporation operates a marketing platform. It provides software and artificial intelligence solutions for businesses to reach, monetize and grow their audiences. Its advertising solutions include Axon Ads Manager, MAX, Adjust, and Wurl. Its clients use Axon Ads Manager to automate, optimize, and manage customer acquisition. They set marketing and transaction goals, and Axon Ads Manager maximizes advertising spend at their return on advertising spend targets and other marketing objectives. Publishers use MAX to optimize the sale of their app advertising inventory to demand-side platforms and ad networks. The MAX tool provides insights to manage against key performance indicators, understand the long-term value of users, and helps manage profitability. Axon Ads Manager comprises the amount charged to advertisers based on their campaign goals, less consideration paid or payable to publishers. Advertising clients use Wurl's connected TV platform to distribute streaming videos.</v>
     <v>898</v>
@@ -4505,7 +4505,7 @@
     <v>499.8</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46185.991691573436</v>
+    <v>46185.99989806641</v>
     <v>32</v>
     <v>472.05</v>
     <v>166884913800</v>
@@ -4515,11 +4515,11 @@
     <v>41.587600000000002</v>
     <v>478.57</v>
     <v>496.77</v>
-    <v>496</v>
+    <v>496.5</v>
     <v>335940000</v>
     <v>APP</v>
     <v>APPLOVIN CORPORATION (XNAS:APP)</v>
-    <v>4337779</v>
+    <v>4338272</v>
     <v>5262058</v>
     <v>2011</v>
   </rv>
@@ -4546,16 +4546,16 @@
     <v>60.54</v>
     <v>2.04</v>
     <v>0.17</v>
-    <v>1.983E-3</v>
+    <v>2.1150000000000001E-3</v>
     <v>2.2529999999999998E-3</v>
-    <v>0.15</v>
+    <v>0.16</v>
     <v>USD</v>
     <v>CBOE BZX Exchange</v>
     <v>BATS</v>
     <v>7.4999999999999997E-3</v>
     <v>76.180000000000007</v>
     <v>ETF</v>
-    <v>46185.983828553122</v>
+    <v>46185.993873344531</v>
     <v>35</v>
     <v>74.41</v>
     <v>7262198811.6000004</v>
@@ -4563,10 +4563,10 @@
     <v>75.459999999999994</v>
     <v>75.459999999999994</v>
     <v>75.63</v>
-    <v>75.8</v>
+    <v>75.81</v>
     <v>ARKK</v>
     <v>ARK Innovation (BATS:ARKK)</v>
-    <v>11557890</v>
+    <v>11557976</v>
     <v>7908022</v>
   </rv>
   <rv s="2">
@@ -4613,9 +4613,9 @@
     <v>100.02</v>
     <v>1.429</v>
     <v>38.58</v>
-    <v>9.0969999999999992E-3</v>
+    <v>9.9590000000000008E-3</v>
     <v>0.112731</v>
-    <v>3.4641999999999999</v>
+    <v>3.7926000000000002</v>
     <v>USD</v>
     <v>Arm Holdings plc is a United Kingdom-based company. The Company is engaged in the design of central processing units (CPUs) and compute platforms for semiconductor chips. It develops and licenses CPU products and related technology. Its cloud and data center solutions include Arm AGI CPU and Arm Neoverse Compute Subsystems. The Arm Agentic Generalized Infrastructure (AGI) CPU is a production-ready system on a chip (SoC) for artificial intelligence (AI) data centers, delivering compute at scale. The Arm Neoverse Compute Subsystems (CSS) are pre-validated, performance-optimized compute platforms designed to accelerate infrastructure silicon development. The Company's primary markets include smartphone applications, processors and other chips used in mobile phones, consumer electronics, networking equipment, cloud and data center servers, automotive applications, Internet of Things (loT) and other embedded computing devices.</v>
     <v>9584</v>
@@ -4626,20 +4626,20 @@
     <v>385.8</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46185.991800671094</v>
+    <v>46185.999993899997</v>
     <v>350.04</v>
     <v>406735163990</v>
     <v>ARM HOLDINGS PLC</v>
     <v>ARM HOLDINGS PLC</v>
     <v>353.12</v>
-    <v>449.91730000000001</v>
+    <v>404.3408</v>
     <v>342.23</v>
     <v>380.81</v>
-    <v>384.27420000000001</v>
+    <v>384.6026</v>
     <v>1068079000</v>
     <v>ARM</v>
     <v>ARM HOLDINGS PLC (XNAS:ARM)</v>
-    <v>16524017</v>
+    <v>16531864</v>
     <v>12479805</v>
     <v>2018</v>
   </rv>
@@ -4664,11 +4664,11 @@
     <v>4</v>
     <v>1903.5</v>
     <v>683.48</v>
-    <v>1.7627999999999999</v>
+    <v>1.7787999999999999</v>
     <v>-35.93</v>
-    <v>-2.6829999999999999E-5</v>
+    <v>0</v>
     <v>-1.8915999999999999E-2</v>
-    <v>-0.05</v>
+    <v>0</v>
     <v>USD</v>
     <v>ASML Holding N.V. is a holding company based in the Netherlands. The Company operates through its subsidiaries in the Netherlands, the United States, Italy, France, Germany, the United Kingdom, Ireland, Belgium, South Korea, Taiwan, Singapore, China, Hong Kong, Japan, Malaysia and Israel. The Company operates through one business segment which is engage in development, production, marketing, sales, upgrading and servicing of advanced semiconductor equipment systems, consisting of lithography, metrology and inspection systems. The Company offers TWINSCAN systems, equipped with lithography system with a mercury lamp as light source (i-line), Krypton Fluoride (KrF) and Argon Fluoride (ArF) light sources for processing wafers for manufacturing environments for which imaging at a small resolution is required. TWINSCAN systems also include immersion lithography systems (TWINSCAN immersion systems).</v>
     <v>43882</v>
@@ -4679,21 +4679,21 @@
     <v>1892.8</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46185.990558171092</v>
+    <v>46185.999688517972</v>
     <v>45</v>
     <v>1839</v>
     <v>723332646335</v>
     <v>ASML Holding NV</v>
     <v>ASML Holding NV</v>
     <v>1847.615</v>
-    <v>64.068600000000004</v>
+    <v>65.303799999999995</v>
     <v>1899.48</v>
     <v>1863.55</v>
-    <v>1863.5</v>
+    <v>1863.55</v>
     <v>388147700</v>
     <v>ASML</v>
     <v>ASML Holding NV (XNAS:ASML)</v>
-    <v>2530787</v>
+    <v>2531327</v>
     <v>1839374</v>
     <v>1994</v>
   </rv>
@@ -4718,11 +4718,11 @@
     <v>4</v>
     <v>495</v>
     <v>244.17</v>
-    <v>1.4699</v>
+    <v>1.4683999999999999</v>
     <v>-3.5</v>
-    <v>6.02E-4</v>
+    <v>1.2600000000000001E-3</v>
     <v>-9.077E-3</v>
-    <v>0.23</v>
+    <v>0.48139999999999999</v>
     <v>USD</v>
     <v>Broadcom Inc. is a global technology firm that designs, develops, and supplies a range of semiconductors, enterprise software and security solutions. The Company operates through two segments: semiconductor solutions and infrastructure software. Its semiconductor solutions segment includes all of its product lines and intellectual property (IP) licensing. It provides a variety of radio frequency semiconductor devices, wireless connectivity solutions, custom touch controllers, and inductive charging solutions for mobile applications. Its infrastructure software segment includes its private and hybrid cloud, application development and delivery, software-defined edge, application networking and security, mainframe, distributed and cybersecurity solutions, and its FC SAN business. It provides a portfolio of software solutions that enable customers to plan, develop, automate, manage and secure applications across mainframe, distributed, mobile and cloud platforms.</v>
     <v>33000</v>
@@ -4733,21 +4733,21 @@
     <v>384.97989999999999</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46185.99149697891</v>
+    <v>46185.999958796092</v>
     <v>48</v>
     <v>377</v>
     <v>1817728590600</v>
     <v>BROADCOM INC.</v>
     <v>BROADCOM INC.</v>
     <v>383.72</v>
-    <v>63.641199999999998</v>
+    <v>64.224400000000003</v>
     <v>385.57</v>
     <v>382.07</v>
-    <v>382.3</v>
+    <v>382.5514</v>
     <v>4757580000</v>
     <v>AVGO</v>
     <v>BROADCOM INC. (XNAS:AVGO)</v>
-    <v>27624297</v>
+    <v>27630074</v>
     <v>28844161</v>
     <v>2018</v>
   </rv>
@@ -4758,24 +4758,24 @@
     <v>https://www.bing.com/financeapi/forcetrigger?t=c4efww&amp;q=XNYS%3aBBAI&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
   </rv>
-  <rv s="1">
+  <rv s="10">
     <v>en-GB</v>
     <v>c4efww</v>
     <v>268435456</v>
     <v>1</v>
     <v>Powered by Refinitiv</v>
-    <v>0</v>
+    <v>19</v>
     <v>BIGBEAR.AI HOLDINGS, INC. (XNYS:BBAI)</v>
     <v>2</v>
-    <v>3</v>
+    <v>20</v>
     <v>Finance</v>
     <v>4</v>
     <v>9.39</v>
     <v>3.01</v>
-    <v>3.1198999999999999</v>
-    <v>-0.125</v>
+    <v>3.1240000000000001</v>
+    <v>-0.12</v>
     <v>0</v>
-    <v>-3.0192999999999998E-2</v>
+    <v>-2.8986000000000001E-2</v>
     <v>0</v>
     <v>USD</v>
     <v>BigBear.ai Holdings, Inc. operates as a specialized provider of artificial intelligence (AI) technology. The Company provides decision intelligence solutions for supply chains and logistics, enterprise operations, manned-unmanned teaming in autonomous systems, and cybersecurity. Its solutions include AI orchestration and sensor function, digital identity management, computer vision, cybersecurity, predictive intelligence, modeling &amp; simulation, enterprise automation and professional services. It offers Trueface, which performs one-to-many (1:N) facial matches with real-time photos, delivering identity verification. It also offers veriScan, which captures and transmits real-time photos into a biometric matching service supporting access control and biometric boarding/bag tags. The Company serves homeland &amp; border security, defense, intelligence, manufacturing &amp; suppy chain, travel and trade industries.</v>
@@ -4787,21 +4787,20 @@
     <v>4.22</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46185.991667175782</v>
+    <v>46185.999992094534</v>
     <v>51</v>
     <v>4</v>
-    <v>1922982242</v>
+    <v>1925376989</v>
     <v>BIGBEAR.AI HOLDINGS, INC.</v>
     <v>BIGBEAR.AI HOLDINGS, INC.</v>
     <v>4.1399999999999997</v>
-    <v>0</v>
     <v>4.1399999999999997</v>
-    <v>4.0149999999999997</v>
+    <v>4.0199999999999996</v>
     <v>4.0199999999999996</v>
     <v>478949500</v>
     <v>BBAI</v>
     <v>BIGBEAR.AI HOLDINGS, INC. (XNYS:BBAI)</v>
-    <v>26179858</v>
+    <v>26213060</v>
     <v>46938229</v>
     <v>2020</v>
   </rv>
@@ -4812,21 +4811,21 @@
     <v>https://www.bing.com/financeapi/forcetrigger?t=af5lim&amp;q=XFRA%3aBMW&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
   </rv>
-  <rv s="10">
+  <rv s="11">
     <v>en-GB</v>
     <v>af5lim</v>
     <v>268435456</v>
     <v>1</v>
     <v>Powered by Refinitiv</v>
-    <v>19</v>
+    <v>21</v>
     <v>Bayerische Motoren Werke AG (XFRA:BMW)</v>
     <v>2</v>
-    <v>20</v>
+    <v>22</v>
     <v>Finance</v>
-    <v>21</v>
+    <v>23</v>
     <v>115.25</v>
     <v>36.884999999999998</v>
-    <v>0.98099999999999998</v>
+    <v>0.9738</v>
     <v>-0.24</v>
     <v>-3.5490000000000001E-3</v>
     <v>EUR</v>
@@ -4877,7 +4876,7 @@
     <v>4</v>
     <v>416.69</v>
     <v>262.74900000000002</v>
-    <v>1.1368</v>
+    <v>1.139</v>
     <v>1.22</v>
     <v>2.702E-3</v>
     <v>3.179E-3</v>
@@ -4892,7 +4891,7 @@
     <v>389.8</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46185.991520289062</v>
+    <v>46185.997142800785</v>
     <v>57</v>
     <v>375.94</v>
     <v>106178127360</v>
@@ -4906,7 +4905,7 @@
     <v>275816000</v>
     <v>CDNS</v>
     <v>CADENCE DESIGN SYSTEMS, INC. (XNAS:CDNS)</v>
-    <v>1366230</v>
+    <v>1366238</v>
     <v>2383116</v>
     <v>1987</v>
   </rv>
@@ -4931,11 +4930,11 @@
     <v>4</v>
     <v>412.7</v>
     <v>240.51</v>
-    <v>1.1372</v>
+    <v>1.1256999999999999</v>
     <v>7.05</v>
-    <v>5.8720000000000005E-3</v>
+    <v>6.463E-3</v>
     <v>2.8576000000000001E-2</v>
-    <v>1.49</v>
+    <v>1.64</v>
     <v>USD</v>
     <v>Constellation Energy Corporation is a producer of emissions-free energy and an energy supplier to businesses, homes and public sector customers nationwide. The Company’s nuclear, hydro, wind, and solar generation facilities have the generating capacity to power the equivalent of 27 million homes, providing about 10% of the nation’s clean energy. Its segments include Mid-Atlantic, Midwest, New York, ERCOT, and Other Power Regions. Through its integrated business operations, it sells electricity, natural gas, and other energy-related products and sustainable solutions to various types of customers, including distribution utilities, municipalities, cooperatives, commercial, industrial, public sector, and residential customers in markets across multiple geographic regions. It operates approximately 55 gigawatts of capacity from nuclear, natural gas, geothermal, hydro, wind and solar facilities.</v>
     <v>15291</v>
@@ -4946,21 +4945,21 @@
     <v>255.12</v>
     <v>Electrical Utilities &amp; IPPs</v>
     <v>Stock</v>
-    <v>46185.991722383595</v>
+    <v>46185.999756330471</v>
     <v>60</v>
     <v>247.65</v>
     <v>91125723520</v>
     <v>CONSTELLATION ENERGY CORPORATION.</v>
     <v>CONSTELLATION ENERGY CORPORATION.</v>
     <v>249.83</v>
-    <v>22.0458</v>
+    <v>21.433399999999999</v>
     <v>246.71</v>
     <v>253.76</v>
-    <v>255.25</v>
+    <v>255.4</v>
     <v>359102000</v>
     <v>CEG</v>
     <v>CONSTELLATION ENERGY CORPORATION. (XNAS:CEG)</v>
-    <v>3418915</v>
+    <v>3419966</v>
     <v>4235482</v>
     <v>2021</v>
   </rv>
@@ -4971,25 +4970,25 @@
     <v>https://www.bing.com/financeapi/forcetrigger?t=c4s6z2&amp;q=XNAS%3aCRDO&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
   </rv>
-  <rv s="11">
+  <rv s="12">
     <v>en-GB</v>
     <v>c4s6z2</v>
     <v>268435456</v>
     <v>1</v>
     <v>Powered by Refinitiv</v>
-    <v>22</v>
+    <v>24</v>
     <v>Credo Technology Group Holding Ltd (XNAS:CRDO)</v>
     <v>2</v>
-    <v>23</v>
+    <v>25</v>
     <v>Finance</v>
     <v>4</v>
     <v>270.21170000000001</v>
     <v>70.78</v>
-    <v>3.1806999999999999</v>
+    <v>3.2073999999999998</v>
     <v>-13.95</v>
-    <v>4.3860000000000001E-3</v>
+    <v>3.947E-3</v>
     <v>-5.2689000000000007E-2</v>
-    <v>1.1000000000000001</v>
+    <v>0.99</v>
     <v>USD</v>
     <v>Credo Technology Group Holding Ltd is a Cayman Islands-based holding company. The Company delivers high-speed solutions to break bandwidth barriers on every wired connection in the data infrastructure market. It provides high-speed connectivity solutions that deliver improved power efficiency as data rates and corresponding bandwidth requirements increase exponentially throughout the data infrastructure market. Its connectivity solutions are optimized for optical and electrical Ethernet applications, including the emerging 100 gigabits per second (G), 200G, 400G, 800G and the emerging 1.6 terabits per second (T) port markets. Its products are based on its Serializer/Deserializer (SerDes) and Digital Signal Processor (DSP) technologies. Its product families include integrated circuits (ICs) for the optical and line card markets, active electrical cables (AECs) and SerDes Chiplets. The Company’s intellectual property (IP) solutions consist primarily of SerDes IP licensing.</v>
     <v>622</v>
@@ -5000,21 +4999,21 @@
     <v>270.21170000000001</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46185.991738957811</v>
+    <v>46185.999943402341</v>
     <v>63</v>
     <v>241.12</v>
     <v>46261879419</v>
     <v>Credo Technology Group Holding Ltd</v>
     <v>Credo Technology Group Holding Ltd</v>
     <v>270.02</v>
-    <v>101.1412</v>
+    <v>106.7662</v>
     <v>264.76</v>
     <v>250.81</v>
-    <v>251.91</v>
+    <v>251.8</v>
     <v>184449900</v>
     <v>CRDO</v>
     <v>Credo Technology Group Holding Ltd (XNAS:CRDO)</v>
-    <v>9023804</v>
+    <v>9028913</v>
     <v>8866411</v>
   </rv>
   <rv s="2">
@@ -5038,11 +5037,11 @@
     <v>4</v>
     <v>276.8</v>
     <v>161.4</v>
-    <v>1.1762999999999999</v>
-    <v>-0.36</v>
-    <v>6.6309999999999991E-4</v>
-    <v>-2.163E-3</v>
-    <v>0.11</v>
+    <v>1.175</v>
+    <v>-0.56000000000000005</v>
+    <v>-1.1200000000000001E-3</v>
+    <v>-3.3639999999999998E-3</v>
+    <v>-0.18579999999999999</v>
     <v>USD</v>
     <v>Salesforce, Inc. is a customer relationship management (CRM) technology company. Its artificial intelligence (AI) powered Agentforce 360 Platform offers sales, service, marketing, commerce, collaboration, data management, integration, analytics, and information technology (IT) service solutions. It enables customers to build and deploy digital labor for employees and customers, leveraging autonomous AI agents across business functions. Its service offerings include Agentforce Sales, Agentforce Service, Agentforce 360 Platform, Slack and Others. The Agentforce Sales provides sales capabilities and tools built for organizations across prospecting, sales engagement, team collaboration, sales analytics and AI, sales programs, sales performance, partner management, and revenue and orders. The Agentforce Service provides field service solutions that enable companies to connect service agents, dispatchers and mobile employees through platform to schedule, dispatch and manage jobs.</v>
     <v>83334</v>
@@ -5053,21 +5052,21 @@
     <v>166.54</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46185.991507164064</v>
+    <v>46185.999767546091</v>
     <v>66</v>
     <v>161.4</v>
-    <v>136027710000</v>
+    <v>135863909999</v>
     <v>SALESFORCE, INC.</v>
     <v>SALESFORCE, INC.</v>
     <v>164.74</v>
-    <v>19.2163</v>
+    <v>19.193100000000001</v>
     <v>166.45</v>
-    <v>166.09</v>
-    <v>166</v>
+    <v>165.89</v>
+    <v>165.70419999999999</v>
     <v>819000000</v>
     <v>CRM</v>
     <v>SALESFORCE, INC. (XNYS:CRM)</v>
-    <v>13587918</v>
+    <v>13589398</v>
     <v>15310391</v>
     <v>1999</v>
   </rv>
@@ -5092,11 +5091,11 @@
     <v>4</v>
     <v>785.66</v>
     <v>342.72</v>
-    <v>1.2551000000000001</v>
+    <v>1.2579</v>
     <v>-8.73</v>
-    <v>2.856E-4</v>
+    <v>-1.1720000000000001E-3</v>
     <v>-1.2624E-2</v>
-    <v>0.19500000000000001</v>
+    <v>-0.8</v>
     <v>USD</v>
     <v>CrowdStrike Holdings, Inc. is a global cybersecurity company. The Company provides a cloud-native platform for protecting critical areas of enterprise risk - endpoints and cloud workloads, identity, and data. The Company's artificial intelligence (AI)-native CrowdStrike Falcon platform is a cloud-native unified platform built with AI at the core, capable of harnessing security and enterprise data to deliver highly modular solutions through a single lightweight sensor. Using cloud-scale AI, its Security Cloud enriches and correlates cybersecurity events with indicators of attack, threat intelligence, and enterprise data (including data from across endpoints, workloads, identities, DevOps, IT assets, and configurations) to create actionable data, identify shifts in adversary tactics, and automatically prevent threats in real-time across its customer base. It sells its Falcon platform via a partner-first subscription model to organizations of all sizes across multiple industries globally.</v>
     <v>11157</v>
@@ -5107,7 +5106,7 @@
     <v>702.17</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46185.991226770311</v>
+    <v>46185.999911400002</v>
     <v>69</v>
     <v>678</v>
     <v>173816845440</v>
@@ -5117,11 +5116,11 @@
     <v>0</v>
     <v>691.53</v>
     <v>682.8</v>
-    <v>682.995</v>
+    <v>682</v>
     <v>254564800</v>
     <v>CRWD</v>
     <v>CROWDSTRIKE HOLDINGS, INC. (XNAS:CRWD)</v>
-    <v>2311690</v>
+    <v>2311891</v>
     <v>3854270</v>
     <v>2011</v>
   </rv>
@@ -5144,9 +5143,9 @@
     <v>63.8</v>
     <v>2.4790000000000001</v>
     <v>4.8099999999999996</v>
-    <v>1.5515000000000001E-2</v>
+    <v>1.6907000000000002E-2</v>
     <v>5.024E-2</v>
-    <v>1.56</v>
+    <v>1.7</v>
     <v>USD</v>
     <v>CoreWeave, Inc. is a cloud infrastructure technology company. The Company offers the CoreWeave Cloud Platform, which consists of software and cloud services that deliver the automation and efficiency needed to manage complex artificial intelligence (AI) infrastructure. Its CoreWeave Cloud Platform is an integrated solution that is purpose-built for running AI workloads such as model training and inference. Its solutions include infrastructure services, managed software services, and application software services. Its Infrastructure Services provide its customers with access to advanced graphics processing unit (GPU) and central processing unit (CPU) compute, highly performant networking, and storage. Its Managed Software Services include CKS, a flexible virtual private cloud and a bare metal service that runs kubernetes directly on high-performance servers. Its Application Software Services build on top of its infrastructure and managed software services, integrating additional tools.</v>
     <v>2189</v>
@@ -5157,7 +5156,7 @@
     <v>105.55</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46185.99180111094</v>
+    <v>46185.999990439064</v>
     <v>97.22</v>
     <v>54857103720</v>
     <v>COREWEAVE, INC.</v>
@@ -5166,11 +5165,11 @@
     <v>0</v>
     <v>95.74</v>
     <v>100.55</v>
-    <v>102.11</v>
+    <v>102.25</v>
     <v>545570400</v>
     <v>CRWV</v>
     <v>COREWEAVE, INC. (XNAS:CRWV)</v>
-    <v>36322874</v>
+    <v>36338090</v>
     <v>29302974</v>
     <v>2017</v>
   </rv>
@@ -5195,11 +5194,11 @@
     <v>4</v>
     <v>130.3656</v>
     <v>63.93</v>
-    <v>0.99550000000000005</v>
+    <v>0.99929999999999997</v>
     <v>-0.73</v>
-    <v>-9.7849999999999999E-4</v>
+    <v>-1.0730000000000002E-3</v>
     <v>-5.9919999999999999E-3</v>
-    <v>-0.11849999999999999</v>
+    <v>-0.13</v>
     <v>USD</v>
     <v>Cisco Systems, Inc. designs and sells a range of technologies that power the Internet. The Company is integrating its product portfolios across networking, security, collaboration, applications and cloud. The Company's segments include the Americas; Europe, Middle East, and Africa (EMEA), and Asia Pacific, Japan, and China (APJC). Its Networking product category represents its core networking technologies of switching, routing, wireless, fifth generation (5G), silicon, optics solutions and compute products. Its Security product category consists of its cloud and application security, industrial security, network security, and user and device security offerings. Its Collaboration product category consists of its meetings, collaboration devices, calling, contact center and platform as a service (CPaaS) offering. Its Observability product category consists of its full stack observability offerings.</v>
     <v>86200</v>
@@ -5210,21 +5209,21 @@
     <v>122.79</v>
     <v>Communications &amp; Networking</v>
     <v>Stock</v>
-    <v>46185.988973471874</v>
+    <v>46185.999661828122</v>
     <v>74</v>
     <v>120.73</v>
     <v>477307778500</v>
     <v>CISCO SYSTEMS, INC.</v>
     <v>CISCO SYSTEMS, INC.</v>
     <v>122.35</v>
-    <v>40.353200000000001</v>
+    <v>40.597099999999998</v>
     <v>121.83</v>
     <v>121.1</v>
-    <v>120.9815</v>
+    <v>120.97</v>
     <v>3941435000</v>
     <v>CSCO</v>
     <v>CISCO SYSTEMS, INC. (XNAS:CSCO)</v>
-    <v>18223291</v>
+    <v>18223791</v>
     <v>28995254</v>
     <v>2021</v>
   </rv>
@@ -5249,11 +5248,11 @@
     <v>4</v>
     <v>278.70499999999998</v>
     <v>98.010099999999994</v>
-    <v>1.5599000000000001</v>
+    <v>1.5649999999999999</v>
     <v>-4.34</v>
-    <v>-7.0520000000000001E-3</v>
+    <v>-3.6459999999999999E-3</v>
     <v>-1.8527999999999999E-2</v>
-    <v>-1.6213</v>
+    <v>-0.83819999999999995</v>
     <v>USD</v>
     <v>Datadog Inc provides an AI-powered observability and security platform for cloud applications. Its Software as a Service (SaaS) platform integrates and automates infrastructure monitoring, application performance monitoring, log management, user experience monitoring, cloud security and service management. Its proprietary platform combines the power of metrics, traces, logs, user sessions, security signals, and other data from a single agent and over 1,000 integrations to provide a unified view of infrastructure, application performance and real-time events impacting performance. Its solutions include built for dynamic cloud and hybrid infrastructures, simple but not simplistic, integrated data platform, built for collaboration, cloud-agnostic, ubiquitous, and integrates with its customers complex environments. Its platform is used by industries to enable digital transformation and cloud migration, and drive collaboration among development, operations, security and business teams.</v>
     <v>8100</v>
@@ -5264,21 +5263,21 @@
     <v>236.81</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46185.988537510937</v>
+    <v>46185.999707892966</v>
     <v>77</v>
     <v>227.2346</v>
     <v>81835249980</v>
     <v>DATADOG, INC.</v>
     <v>DATADOG, INC.</v>
     <v>235.43</v>
-    <v>582.46770000000004</v>
+    <v>593.49350000000004</v>
     <v>234.24</v>
     <v>229.9</v>
-    <v>228.27869999999999</v>
+    <v>229.06180000000001</v>
     <v>355960200</v>
     <v>DDOG</v>
     <v>DATADOG, INC. (XNAS:DDOG)</v>
-    <v>5756469</v>
+    <v>5756728</v>
     <v>7110386</v>
     <v>2026</v>
   </rv>
@@ -5303,11 +5302,11 @@
     <v>4</v>
     <v>469.47</v>
     <v>109.17</v>
-    <v>1.3208</v>
-    <v>4.2750000000000004</v>
-    <v>4.8859999999999997E-3</v>
-    <v>1.0921E-2</v>
-    <v>1.9326000000000001</v>
+    <v>1.3171999999999999</v>
+    <v>4.12</v>
+    <v>8.6199999999999992E-3</v>
+    <v>1.0525E-2</v>
+    <v>3.41</v>
     <v>USD</v>
     <v>Dell Technologies Inc. is engaged in designing, developing, manufacturing, marketing, selling, and supporting a wide range of comprehensive and integrated solutions, products, and services. The Company operates through two segments: Infrastructure Solutions Group (ISG) and Client Solutions Group (CSG). Its ISG segment enables the Company’s customer’s digital transformation with solutions that address artificial intelligence (AI), machine learning, data analytics, and multi cloud environments. Its comprehensive storage portfolio includes modern and traditional storage solutions, including all-flash arrays, scale-out file, object platforms, hyper-converged infrastructure, and software-defined storage. Its CSG segment offers branded personal computers (PCs) including notebooks, desktops, and workstations and branded peripherals that include displays, docking stations, keyboards, mice, and webcam and audio devices, as well as third-party software and peripherals.</v>
     <v>97000</v>
@@ -5318,21 +5317,21 @@
     <v>408.375</v>
     <v>Computers, Phones &amp; Household Electronics</v>
     <v>Stock</v>
-    <v>46185.990697499998</v>
+    <v>46185.999974698439</v>
     <v>80</v>
     <v>381.11</v>
-    <v>256472538300</v>
+    <v>256372081560</v>
     <v>DELL TECHNOLOGIES INC.</v>
     <v>DELL TECHNOLOGIES INC.</v>
     <v>385</v>
-    <v>31.4255</v>
+    <v>31.4131</v>
     <v>391.45</v>
-    <v>395.72500000000002</v>
-    <v>397.50259999999997</v>
+    <v>395.57</v>
+    <v>398.98</v>
     <v>648108000</v>
     <v>DELL</v>
     <v>DELL TECHNOLOGIES INC. (XNYS:DELL)</v>
-    <v>6056441</v>
+    <v>6059055</v>
     <v>11330953</v>
     <v>2013</v>
   </rv>
@@ -5373,11 +5372,11 @@
     <v>4</v>
     <v>124.69</v>
     <v>92.185000000000002</v>
-    <v>1.3828</v>
+    <v>1.3867</v>
     <v>-0.3</v>
-    <v>-4.4479999999999997E-4</v>
+    <v>-3.9980000000000001E-4</v>
     <v>-2.99E-3</v>
-    <v>-4.4499999999999998E-2</v>
+    <v>-0.04</v>
     <v>USD</v>
     <v>The Walt Disney Company is a diversified worldwide entertainment company. The Company's segments include Entertainment, Sports and Experiences. The Entertainment segment generally encompasses its non-sports focused global film and episodic content production and distribution activities. The lines of business within the Entertainment segment along with their business activities include Linear Networks, Direct-to-Consumer, and Content Sales/Licensing. The Sports segment encompasses its sports-focused global television and direct-to-consumer (DTC) video streaming content production and distribution activities. The lines of business within the Sports segment include ESPN and Star. The Experiences segment includes Parks and Experiences and Consumer Products. Parks and Experiences consists of Walt Disney World Resort in Florida, Disneyland Resort in California, Disney Cruise Line, and others. Consumer Products includes licensing of its trade names, characters, visual, literary and other IP.</v>
     <v>231000</v>
@@ -5389,7 +5388,7 @@
     <v>85</v>
     <v>Media &amp; Publishing</v>
     <v>Stock</v>
-    <v>46185.991267557809</v>
+    <v>46185.999869443753</v>
     <v>86</v>
     <v>99.534999999999997</v>
     <v>173720560440</v>
@@ -5399,11 +5398,11 @@
     <v>16.008400000000002</v>
     <v>100.34</v>
     <v>100.04</v>
-    <v>99.995500000000007</v>
+    <v>100</v>
     <v>1736511000</v>
     <v>DIS</v>
     <v>THE WALT DISNEY COMPANY (XNYS:DIS)</v>
-    <v>8256685</v>
+    <v>8257240</v>
     <v>8493019</v>
     <v>2018</v>
   </rv>
@@ -5425,10 +5424,10 @@
     <v>2</v>
     <v>3</v>
     <v>Finance</v>
-    <v>24</v>
+    <v>4</v>
     <v>57.55</v>
     <v>31.635000000000002</v>
-    <v>0.74719999999999998</v>
+    <v>0.745</v>
     <v>0.38</v>
     <v>2.0613000000000003E-2</v>
     <v>9.4129999999999995E-3</v>
@@ -5482,11 +5481,11 @@
     <v>4</v>
     <v>16.489999999999998</v>
     <v>4.6150000000000002</v>
-    <v>2.2429999999999999</v>
+    <v>2.2429000000000001</v>
     <v>-0.04</v>
-    <v>7.5079999999999999E-3</v>
+    <v>6.0060000000000001E-3</v>
     <v>-5.9699999999999996E-3</v>
-    <v>0.05</v>
+    <v>0.04</v>
     <v>USD</v>
     <v>Enovix Corporation is a high-performance battery company. The Company is focused on designing, developing, manufacturing, and commercializing Lithium-ion, or Li-ion, batteries, including silicon-anode architectures, for smartphones, smart eyewear, defense, industrial and emerging edge artificial intelligence (AI) applications. Its silicon-anode battery architecture enables energy density and performance relative to conventional battery cells, particularly in space-constrained devices. It focuses on developing a battery architecture that allows the use of active silicon and no graphite in the battery's anode, which is the negative electrode that stores lithium ions when a battery is charged. Its AI-1 battery platform is architected as a unified silicon-anode platform designed to address the high-performance consumer electronics and defense applications. The AI-1 platform is designed to support AI-enabled smartphones and smart eyewear, as well as other edge-AI devices.</v>
     <v>664</v>
@@ -5497,7 +5496,7 @@
     <v>6.85</v>
     <v>Machinery, Equipment &amp; Components</v>
     <v>Stock</v>
-    <v>46185.991443633597</v>
+    <v>46185.992927048435</v>
     <v>92</v>
     <v>6.53</v>
     <v>1452901644</v>
@@ -5507,11 +5506,11 @@
     <v>0</v>
     <v>6.7</v>
     <v>6.66</v>
-    <v>6.71</v>
+    <v>6.7</v>
     <v>218153400</v>
     <v>ENVX</v>
     <v>Enovix Corporation (XNAS:ENVX)</v>
-    <v>4057745</v>
+    <v>4058325</v>
     <v>8456203</v>
     <v>2020</v>
   </rv>
@@ -5536,11 +5535,11 @@
     <v>4</v>
     <v>435.43</v>
     <v>311.91500000000002</v>
-    <v>1.1911</v>
-    <v>-2.1269999999999998</v>
-    <v>9.0449999999999992E-3</v>
-    <v>-5.4029999999999998E-3</v>
-    <v>3.54</v>
+    <v>1.194</v>
+    <v>-2.25</v>
+    <v>9.2239999999999996E-3</v>
+    <v>-5.7159999999999997E-3</v>
+    <v>3.61</v>
     <v>USD</v>
     <v>Eaton Corporation plc is an intelligent power management company. Its Electrical Americas segment consists of electrical components, industrial components, power distribution and assemblies, residential products, circuit protection, utility power distribution, wiring devices and others. The Electrical Global segment consists of electrical components, industrial components, power distribution and assemblies, single phase and three phase power quality, and services. The Aerospace segment is a global supplier of aerospace fuel, hydraulics, and pneumatic systems for commercial and military use and filtration systems for industrial applications. The Vehicle segment designs, manufactures, markets, and supplies drivetrain, powertrain systems and critical components. The eMobility segment designs, manufactures, markets, and supplies mechanical, electrical, and electronic components and systems. The Company is also engaged in providing thermal monitoring for critical electrical equipment.</v>
     <v>97000</v>
@@ -5551,21 +5550,21 @@
     <v>399.13</v>
     <v>Machinery, Equipment &amp; Components</v>
     <v>Stock</v>
-    <v>46185.988845196094</v>
+    <v>46185.999693344529</v>
     <v>95</v>
     <v>388.33600000000001</v>
-    <v>152024497900</v>
+    <v>151976737000</v>
     <v>EATON CORPORATION PUBLIC LIMITED COMPANY</v>
     <v>EATON CORPORATION PUBLIC LIMITED COMPANY</v>
     <v>396.55</v>
-    <v>38.275599999999997</v>
+    <v>38.263500000000001</v>
     <v>393.64</v>
-    <v>391.51299999999998</v>
-    <v>394.93</v>
+    <v>391.39</v>
+    <v>395</v>
     <v>388300000</v>
     <v>ETN</v>
     <v>EATON CORPORATION PUBLIC LIMITED COMPANY (XNYS:ETN)</v>
-    <v>2175298</v>
+    <v>2175309</v>
     <v>2639834</v>
     <v>2012</v>
   </rv>
@@ -5587,14 +5586,14 @@
     <v>2</v>
     <v>3</v>
     <v>Finance</v>
-    <v>24</v>
+    <v>4</v>
     <v>29.71</v>
     <v>13.29</v>
-    <v>1.4681999999999999</v>
+    <v>1.4633</v>
     <v>0.4</v>
-    <v>1.1305000000000001E-2</v>
+    <v>-3.0380000000000003E-3</v>
     <v>1.9202999999999998E-2</v>
-    <v>0.24</v>
+    <v>-6.4500000000000002E-2</v>
     <v>USD</v>
     <v>Five9, Inc. helps organizations to create hyper-personalized artificial intelligence (AI)-driven customer experiences. The Company's Intelligent CX Platform, powered by its Five9 Genius AI suite, delivers a comprehensive suite of applications that enable customer service, sales, and marketing functions. It delivers a comprehensive, end-to-end cloud software solution for contact centers. Comprised of its Intelligent CX Platform and AI capabilities, including agentic AI agents, Agent Assist, Workflow Automation (WFA), AI Insights, AI Summaries, Workforce Engagement Management (WEM), and Revenue Execution, its solution allows simultaneous management and optimization of customer interactions across voice, chat, email, web, social media and mobile channels, either directly or through its application programming interfaces (APIs). The Company's agent interface is a browser-based design that provides visualization of customer profiles, context and cross-channel history.</v>
     <v>2910</v>
@@ -5605,7 +5604,7 @@
     <v>21.24</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46185.977991828127</v>
+    <v>46185.994621365622</v>
     <v>98</v>
     <v>20.085599999999999</v>
     <v>1625453507</v>
@@ -5615,11 +5614,11 @@
     <v>31.585999999999999</v>
     <v>20.83</v>
     <v>21.23</v>
-    <v>21.47</v>
+    <v>21.165500000000002</v>
     <v>76563990</v>
     <v>FIVN</v>
     <v>FIVE9, INC. (XNAS:FIVN)</v>
-    <v>1760038</v>
+    <v>1760040</v>
     <v>3368297</v>
     <v>2001</v>
   </rv>
@@ -5644,11 +5643,11 @@
     <v>4</v>
     <v>150.07</v>
     <v>70.12</v>
-    <v>1.0904</v>
+    <v>1.0920000000000001</v>
     <v>1.24</v>
-    <v>6.8349999999999994E-5</v>
+    <v>1.3669999999999999E-3</v>
     <v>8.548E-3</v>
-    <v>0.01</v>
+    <v>0.2</v>
     <v>USD</v>
     <v>Fortinet, Inc. is engaged in cybersecurity, driving the convergence of networking and security. The Company's integrated platform, Fortinet Security Fabric, spans secure networking, unified secure access service edge (SASE), and artificial intelligence (AI)-driven security operations (SecOps). Its products and services include FortiOS, FortiASIC, FortiCloud, FortiAI, FortiEndpoint, and OT Security. The FortiGuard Labs is a cybersecurity threat intelligence and research organization comprised of experienced threat hunters, researchers, analysts, engineers, and data scientists who develop and utilize machine learning and AI technologies. FortiGuard and Other Security Services is an AI-powered security that is integrated as part of the Fortinet Security Fabric to deliver detection and enforcement across the entire attack surface. FortiCare Technical Support Service is a technical support service which provides customers with access to operations and maintenance of Fortinet solutions.</v>
     <v>15311</v>
@@ -5659,21 +5658,21 @@
     <v>146.38</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46185.986923066404</v>
+    <v>46185.99929895781</v>
     <v>101</v>
     <v>142.14779999999999</v>
     <v>107186460920</v>
     <v>FORTINET, INC.</v>
     <v>FORTINET, INC.</v>
     <v>143.642</v>
-    <v>56.5214</v>
+    <v>56.043399999999998</v>
     <v>145.06</v>
     <v>146.30000000000001</v>
-    <v>146.31</v>
+    <v>146.5</v>
     <v>732648400</v>
     <v>FTNT</v>
     <v>FORTINET, INC. (XNAS:FTNT)</v>
-    <v>5083987</v>
+    <v>5084049</v>
     <v>6966766</v>
     <v>2000</v>
   </rv>
@@ -5698,11 +5697,11 @@
     <v>4</v>
     <v>404.47</v>
     <v>163.33000000000001</v>
-    <v>1.248</v>
+    <v>1.2466999999999999</v>
     <v>1.6</v>
-    <v>2.617E-3</v>
+    <v>2.9039999999999999E-3</v>
     <v>4.4869999999999997E-3</v>
-    <v>0.93720000000000003</v>
+    <v>1.04</v>
     <v>USD</v>
     <v>Alphabet Inc. is a holding company. The Company's segments include Google Services, Google Cloud, and Other Bets. The Google Services segment includes products and services such as ads, Android, Chrome, devices, Google Maps, Google Play, Search, and YouTube. The Google Cloud segment includes infrastructure and platform services, collaboration tools, and other services for enterprise customers. Its Other Bets segment is engaged in the sale of healthcare-related services and Internet services. Its Google Cloud provides enterprise-ready cloud services, including Google Cloud Platform and Google Workspace. Google Cloud Platform provides access to solutions such as artificial intelligence (AI) offerings, including its AI infrastructure, Vertex AI platform, and Gemini for Google Cloud; cybersecurity, and data and analytics. Google Workspace includes cloud-based communication and collaboration tools for enterprises, such as Calendar, Gmail, Docs, Drive, and Meet.</v>
     <v>194668</v>
@@ -5713,21 +5712,21 @@
     <v>364.77249999999998</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46185.991515775</v>
+    <v>46185.999964154689</v>
     <v>104</v>
     <v>353.34</v>
     <v>4360440409600</v>
     <v>ALPHABET INC.</v>
     <v>ALPHABET INC.</v>
     <v>361.1</v>
-    <v>27.353200000000001</v>
+    <v>27.230899999999998</v>
     <v>356.56</v>
     <v>358.16</v>
-    <v>359.09719999999999</v>
+    <v>359.2</v>
     <v>12174560000</v>
     <v>GOOG</v>
     <v>ALPHABET INC. (XNAS:GOOG)</v>
-    <v>17652461</v>
+    <v>17657657</v>
     <v>21920534</v>
     <v>2015</v>
   </rv>
@@ -5752,11 +5751,11 @@
     <v>4</v>
     <v>153.85990000000001</v>
     <v>63.515000000000001</v>
-    <v>2.3420000000000001</v>
+    <v>2.3431999999999999</v>
     <v>0.96</v>
-    <v>-2.039E-3</v>
+    <v>-1.0730000000000002E-3</v>
     <v>1.0409E-2</v>
-    <v>-0.19</v>
+    <v>-0.1</v>
     <v>USD</v>
     <v>Robinhood Markets, Inc. is focused on providing financial services offering retail brokerage, crypto, advisory, digital banking services, and private markets access to investors. Its offerings include Brokerage, Robinhood Crypto, Custody, Robinhood Wallet, Robinhood Gold, and Robinhood Gold Card. Brokerage services include investing, options trading, fractional trading, recurring investment, access to investing on margin, fully paid securities lending, cash sweep, instant withdrawals, Robinhood retirement, 24-hour market, joint investing accounts, and event contracts. It also offers a variety of ways for its customers to grow their financial knowledge, including Robinhood Learn, In-App Education, Newsfeeds, Sherwood Snacks, and Crypto Learn and Earn. It also operates regulated crypto platforms including Bitbuy and Coinsquare. Its self-clearing system, order routing system, data platform, and other back-end infrastructure allow its customers to focus on investing, saving and spending.</v>
     <v>2900</v>
@@ -5767,7 +5766,7 @@
     <v>96.1</v>
     <v>Financial Technology (Fintech) &amp; Infrastructure</v>
     <v>Stock</v>
-    <v>46185.991242858596</v>
+    <v>46185.999962395312</v>
     <v>107</v>
     <v>90.220100000000002</v>
     <v>83918070269</v>
@@ -5777,11 +5776,11 @@
     <v>51.307299999999998</v>
     <v>92.23</v>
     <v>93.19</v>
-    <v>93</v>
+    <v>93.09</v>
     <v>900505100</v>
     <v>HOOD</v>
     <v>ROBINHOOD MARKETS, INC. (XNAS:HOOD)</v>
-    <v>33071824</v>
+    <v>33082303</v>
     <v>27421079</v>
     <v>2013</v>
   </rv>
@@ -5822,11 +5821,11 @@
     <v>4</v>
     <v>332.46</v>
     <v>212.34</v>
-    <v>0.67789999999999995</v>
-    <v>-2.665</v>
-    <v>4.0410000000000001E-4</v>
-    <v>-9.6959999999999998E-3</v>
-    <v>0.11</v>
+    <v>0.67810000000000004</v>
+    <v>-2.61</v>
+    <v>2.0569999999999998E-3</v>
+    <v>-9.4959999999999992E-3</v>
+    <v>0.56000000000000005</v>
     <v>USD</v>
     <v>International Business Machines Corporation is a provider of global hybrid cloud and artificial intelligence (AI) and consulting expertise. The Company’s segments include Software, Consulting, Infrastructure and Financing. The Software segment includes hybrid cloud and AI platforms, which allow clients to realize their digital and AI transformations across the applications, data, and environments in which they operate. The Consulting segment focuses on integrating skills on strategy, experience, technology and operations by domain and industry. The Infrastructure segment is focused on the hybrid cloud infrastructure market, providing on-premises and cloud-based server and storage solutions. In addition, it offers a portfolio of life-cycle services for hybrid cloud infrastructure deployment. The Financing segment provides client and commercial financing, facilitating its clients’ acquisition of hardware, software and services. It helps clients in more than 175 countries.</v>
     <v>286800</v>
@@ -5838,21 +5837,21 @@
     <v>112</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46185.991204825783</v>
+    <v>46185.999914895314</v>
     <v>113</v>
     <v>267.68</v>
-    <v>255822680380</v>
+    <v>255874374072</v>
     <v>INTERNATIONAL BUSINESS MACHINES CORPORATION</v>
     <v>INTERNATIONAL BUSINESS MACHINES CORPORATION</v>
     <v>278.94</v>
-    <v>21.7818</v>
+    <v>21.786200000000001</v>
     <v>274.85000000000002</v>
-    <v>272.185</v>
-    <v>272.35000000000002</v>
+    <v>272.24</v>
+    <v>272.8</v>
     <v>939885300</v>
     <v>IBM</v>
     <v>INTERNATIONAL BUSINESS MACHINES CORPORATION (XNYS:IBM)</v>
-    <v>5747598</v>
+    <v>5748915</v>
     <v>11197414</v>
     <v>1911</v>
   </rv>
@@ -5877,11 +5876,11 @@
     <v>4</v>
     <v>125.14</v>
     <v>34.2301</v>
-    <v>2.8325</v>
+    <v>2.8462999999999998</v>
     <v>-4.46</v>
-    <v>3.4689999999999999E-3</v>
+    <v>1.487E-3</v>
     <v>-4.2331000000000001E-2</v>
-    <v>0.35</v>
+    <v>0.15</v>
     <v>USD</v>
     <v>Innodata Inc. is a global data engineering company. It provides a range of transferable solutions, platforms, and services for generative artificial intelligence (AI)/AI builders and adopters. Its Digital Data Solutions segment provides AI data preparation services, collecting or creating training data, annotating training data, and training AI algorithms for its customers, and AI model deployment and integration. It also provides a range of data engineering support services. Its Synodex segment provides an industry platform that transforms medical records into useable digital data organized in accordance with its proprietary data models or customer data models. Its Agility segment provides an industry platform that provides marketing communications and public relations professionals with the ability to target and distribute content to journalists and social media influencers worldwide and to monitor and analyze global news channels (print, Web, radio and TV) and social media channels.</v>
     <v>10020</v>
@@ -5892,21 +5891,21 @@
     <v>106.05</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46185.991058066407</v>
+    <v>46185.997785</v>
     <v>116</v>
     <v>99</v>
     <v>1490374656</v>
     <v>INNODATA INC.</v>
     <v>INNODATA INC.</v>
     <v>106.05</v>
-    <v>90.7864</v>
+    <v>94.796800000000005</v>
     <v>105.36</v>
     <v>100.9</v>
-    <v>101.25</v>
+    <v>101.05</v>
     <v>32655360</v>
     <v>INOD</v>
     <v>INNODATA INC. (XNAS:INOD)</v>
-    <v>784316</v>
+    <v>784371</v>
     <v>3097084</v>
     <v>1988</v>
   </rv>
@@ -5931,11 +5930,11 @@
     <v>4</v>
     <v>132.75</v>
     <v>18.965</v>
-    <v>2.2080000000000002</v>
+    <v>2.1974</v>
     <v>7.61</v>
-    <v>5.8599999999999998E-3</v>
+    <v>6.502E-3</v>
     <v>6.5064999999999998E-2</v>
-    <v>0.73</v>
+    <v>0.81</v>
     <v>USD</v>
     <v>Intel Corporation is a global designer and manufacturer of semiconductor products. The Company's segments include Intel Products, Intel Foundry, and All Other. Its Intel Products comprise Client Computing Group (CCG) and Data Center and AI (DCAI). CCG delivers platforms and processors that power PCs and edge devices, enabling enhanced performance, connectivity and user experience for consumer and commercial markets with capabilities that also support retail, industrial robotics and AI ecosystems at the edge. DCAI delivers workload-optimized solutions based upon its x86 architecture for data centers, including CPUs, AI accelerators, NICs, IPUs and custom ASICs, enabling performance and scalability for cloud, enterprise, telecommunication and HPC environments. The Intel Foundry segment comprises technology development, manufacturing and foundry services, developing new semiconductor process technologies and advanced packaging technologies. All Other segments include Mobileye and Other.</v>
     <v>83200</v>
@@ -5946,7 +5945,7 @@
     <v>127.6</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46185.991851874998</v>
+    <v>46185.999993796097</v>
     <v>119</v>
     <v>115.33</v>
     <v>626088820000</v>
@@ -5956,11 +5955,11 @@
     <v>0</v>
     <v>116.96</v>
     <v>124.57</v>
-    <v>125.3</v>
+    <v>125.38</v>
     <v>5026000000</v>
     <v>INTC</v>
     <v>INTEL CORPORATION (XNAS:INTC)</v>
-    <v>151429125</v>
+    <v>151526758</v>
     <v>135532200</v>
     <v>1989</v>
   </rv>
@@ -5985,11 +5984,11 @@
     <v>4</v>
     <v>84.64</v>
     <v>25.89</v>
-    <v>3.2286000000000001</v>
+    <v>3.2265999999999999</v>
     <v>-0.14000000000000001</v>
-    <v>6.2229999999999994E-3</v>
+    <v>7.0869999999999995E-3</v>
     <v>-2.4139999999999999E-3</v>
-    <v>0.36</v>
+    <v>0.41</v>
     <v>USD</v>
     <v>IonQ, Inc. is engaged in the quantum computing and networking industry, delivering high-performance systems capable of solving complex commercial and research use cases. Its generation quantum computers, IonQ Forte and IonQ Forte Enterprise, are cutting-edge systems, boasting 36 algorithmic qubits. It sells specialized quantum computing and networking hardware together with related maintenance and support. It also sells access to several quantum computers of various qubit capacities and is in the process of researching and developing technologies for quantum computers with increasing computational capabilities. It makes access to its quantum computers available via three cloud platforms, Amazon Web Services' (AWS) Amazon Braket, Microsoft's Azure Quantum and Google's Cloud Marketplace, and also to select customers via its own cloud service. Its product portfolio also includes quantum key distribution (QKD) systems, quantum random number generators (QRNGs), and single-photon detectors.</v>
     <v>1132</v>
@@ -6000,7 +5999,7 @@
     <v>60.23</v>
     <v>Computers, Phones &amp; Household Electronics</v>
     <v>Stock</v>
-    <v>46185.991752985938</v>
+    <v>46185.999992441408</v>
     <v>122</v>
     <v>56.16</v>
     <v>21593669500</v>
@@ -6010,11 +6009,11 @@
     <v>987.20140000000004</v>
     <v>57.99</v>
     <v>57.85</v>
-    <v>58.21</v>
+    <v>58.26</v>
     <v>373270000</v>
     <v>IONQ</v>
     <v>IONQ, INC. (XNYS:IONQ)</v>
-    <v>24715254</v>
+    <v>24732306</v>
     <v>33758420</v>
     <v>2020</v>
   </rv>
@@ -6039,11 +6038,11 @@
     <v>4</v>
     <v>76.87</v>
     <v>9.52</v>
-    <v>4.242</v>
+    <v>4.2333999999999996</v>
     <v>3.06</v>
-    <v>7.1940000000000007E-3</v>
+    <v>1.0388E-2</v>
     <v>5.3959E-2</v>
-    <v>0.43</v>
+    <v>0.62090000000000001</v>
     <v>USD</v>
     <v>IREN Limited is an Australia-based company, which owns and operates data centers powered by 100% renewable energy. Its facilities are optimized for Bitcoin mining, artificial intelligence (AI) cloud services, and other power-dense compute. Its data center mining facilities are in Canal Flats, Mackenzie, Prince George and Childress. Bitcoin Mining provides security to the Bitcoin network. Al Cloud Services provides cloud compute to Al customers, approximately 1,896 NVIDIA H100 and H200 GPUs. Its Canal Flats facility is in the Canadian Rockies, 100 kilometers (km) from Cranbrook regional airport and 500km east of Vancouver. Its facility is in Prince George, the city in northern British Columbia, located 500 km north of Vancouver. Its facility is located in Childress County, Texas, over 250 miles northwest of Dallas and in close proximity to multiple wind and solar generating facilities in the region. Its Childress operations comprise 200 Mega Watt of operating data centers.</v>
     <v>257</v>
@@ -6054,21 +6053,21 @@
     <v>61.4</v>
     <v>Financial Technology (Fintech) &amp; Infrastructure</v>
     <v>Stock</v>
-    <v>46185.991797106253</v>
+    <v>46185.999925207812</v>
     <v>125</v>
     <v>55.94</v>
     <v>21360524899</v>
     <v>IREN LIMITED</v>
     <v>IREN LIMITED</v>
     <v>56.505000000000003</v>
-    <v>130.303</v>
+    <v>123.62390000000001</v>
     <v>56.71</v>
     <v>59.77</v>
-    <v>60.2</v>
+    <v>60.390900000000002</v>
     <v>357378700</v>
     <v>IREN</v>
     <v>IREN LIMITED (XNAS:IREN)</v>
-    <v>45464015</v>
+    <v>45488280</v>
     <v>57625774</v>
     <v>2018</v>
   </rv>
@@ -6090,32 +6089,32 @@
     <v>16</v>
     <v>17</v>
     <v>Finance</v>
-    <v>18</v>
+    <v>26</v>
     <v>295.72000000000003</v>
     <v>206.81</v>
     <v>0.99929999999999997</v>
-    <v>2.5499999999999998</v>
-    <v>1.8759999999999998E-3</v>
-    <v>8.7810000000000006E-3</v>
-    <v>0.54949999999999999</v>
+    <v>2.54</v>
+    <v>2.7750000000000001E-3</v>
+    <v>8.7460000000000003E-3</v>
+    <v>0.81299999999999994</v>
     <v>USD</v>
     <v>NYSE Arca</v>
     <v>ARCX</v>
     <v>1.9E-3</v>
     <v>295.72000000000003</v>
     <v>ETF</v>
-    <v>46185.99182283516</v>
+    <v>46185.999670508594</v>
     <v>128</v>
     <v>290.31</v>
     <v>80933362748.720001</v>
     <v>iShares:Russ 2000 ETF</v>
     <v>291.63</v>
     <v>290.41000000000003</v>
-    <v>292.95999999999998</v>
-    <v>293.49950000000001</v>
+    <v>292.95</v>
+    <v>293.76299999999998</v>
     <v>IWM</v>
     <v>iShares:Russ 2000 ETF (ARCX:IWM)</v>
-    <v>34402871</v>
+    <v>34415247</v>
     <v>27902152</v>
   </rv>
   <rv s="2">
@@ -6139,11 +6138,11 @@
     <v>4</v>
     <v>254.93</v>
     <v>83.224000000000004</v>
-    <v>1.4276</v>
+    <v>1.423</v>
     <v>13.375999999999999</v>
-    <v>4.2040000000000003E-3</v>
+    <v>9.6640000000000007E-3</v>
     <v>5.5463999999999999E-2</v>
-    <v>1.07</v>
+    <v>2.46</v>
     <v>USD</v>
     <v>KLA Corporation (KLA) develops industry equipment and services. The Company provides advanced process control and process-enabling solutions for manufacturing wafers and reticles, integrated circuits, packaging, and printed circuit boards. It operates through three segments, which include Semiconductor Process Control, Specialty Semiconductor Process, and PCB and Component Inspection. The Semiconductor Process Control segment offers a portfolio of inspection, metrology and data analytics products, and related services. The Specialty Semiconductor Process segment develops and sells advanced vacuum deposition and etching process tools. The PCB and Component Inspection segment enables electronic device manufacturers to inspect, test and measure PCBs, flat panel displays, and integrated circuits (ICs) to verify their quality, pattern the desired electronic circuitry on the relevant substrate and perform three-dimensional shaping of metalized circuits on multiple surfaces.</v>
     <v>15000</v>
@@ -6154,21 +6153,21 @@
     <v>254.93</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46185.990906145315</v>
+    <v>46185.99989644609</v>
     <v>131</v>
     <v>236</v>
     <v>278973314100</v>
     <v>KLA CORPORATION</v>
     <v>KLA CORPORATION</v>
     <v>237.6</v>
-    <v>72.066299999999998</v>
+    <v>68.279300000000006</v>
     <v>241.16399999999999</v>
     <v>254.54</v>
-    <v>255.61</v>
-    <v>130627500</v>
+    <v>257</v>
+    <v>1306275000</v>
     <v>KLAC</v>
     <v>KLA CORPORATION (XNAS:KLAC)</v>
-    <v>10067212</v>
+    <v>10069200</v>
     <v>11128734</v>
     <v>1975</v>
   </rv>
@@ -6193,11 +6192,11 @@
     <v>4</v>
     <v>84.04</v>
     <v>65.353800000000007</v>
-    <v>0.34039999999999998</v>
+    <v>0.34239999999999998</v>
     <v>0.09</v>
-    <v>6.0519999999999997E-4</v>
+    <v>9.6829999999999996E-4</v>
     <v>1.091E-3</v>
-    <v>0.05</v>
+    <v>0.08</v>
     <v>USD</v>
     <v>The Coca-Cola Company is a beverage company. The Company's segments include Europe, Middle East and Africa (EMEA); Latin America; North America; Asia Pacific, and Bottling Investments. It sells multiple brands across several beverage categories worldwide. Its portfolio of sparkling soft drink brands includes Coca-Cola, Sprite and Fanta. Its water, sports, coffee and tea brands include Dasani, smartwater, vitaminwater, Topo Chico, BODYARMOR, Powerade, Costa, Georgia, Fuze Tea, Gold Peak and Ayataka. Its juice, value-added dairy and plant-based beverage brands include Minute Maid, Simply, innocent, Del Valle, fairlife and Santa Clara. It operates in two lines of business: concentrate operations and finished product operations. Its concentrate operations sell beverage concentrates, syrups, including fountain syrups, and certain finished beverages to authorized bottling operations. Its finished product operations sell sparkling soft drinks and a variety of other finished beverages.</v>
     <v>65900</v>
@@ -6208,7 +6207,7 @@
     <v>82.89</v>
     <v>Beverages</v>
     <v>Stock</v>
-    <v>46185.99108288125</v>
+    <v>46185.999995995313</v>
     <v>134</v>
     <v>81.87</v>
     <v>355471062840</v>
@@ -6218,11 +6217,11 @@
     <v>26.009799999999998</v>
     <v>82.53</v>
     <v>82.62</v>
-    <v>82.67</v>
+    <v>82.7</v>
     <v>4302482000</v>
     <v>KO</v>
     <v>THE COCA-COLA COMPANY (XNYS:KO)</v>
-    <v>11753507</v>
+    <v>11757678</v>
     <v>15903259</v>
     <v>1919</v>
   </rv>
@@ -6247,11 +6246,11 @@
     <v>4</v>
     <v>18.940000000000001</v>
     <v>2.75</v>
-    <v>1.3573999999999999</v>
+    <v>1.3752</v>
     <v>-1.38</v>
-    <v>2.1240999999999999E-2</v>
+    <v>2.1739000000000001E-2</v>
     <v>-8.8234999999999994E-2</v>
-    <v>0.3029</v>
+    <v>0.31</v>
     <v>USD</v>
     <v>LightPath Technologies, Inc. is a global, vertically integrated provider of optics, photonics and infrared solutions for the industrial, commercial, defense, telecommunications, and medical industries. The Company designs and manufactures optical and infrared components including molded glass aspheric lenses and assemblies, custom molded glass freeform lenses, infrared lenses and thermal imaging assemblies, fused fiber collimators, and BlackDiamond (BD6) chalcogenide-based glass lenses. It also offers custom optical assemblies, including full engineering design support. Its business is organized into four product groups: infrared components, visible components, assemblies and modules, and engineering services. Its infrared product group comprises both molded and turned infrared lenses and assemblies using a variety of infrared glass materials. Its assemblies and modules product group is comprised of other value-added products, including both infrared and visible components.</v>
     <v>345</v>
@@ -6262,7 +6261,7 @@
     <v>15.83</v>
     <v>Office Equipment</v>
     <v>Stock</v>
-    <v>46185.989785821097</v>
+    <v>46185.999923286719</v>
     <v>137</v>
     <v>13.930099999999999</v>
     <v>946305150</v>
@@ -6272,11 +6271,11 @@
     <v>0</v>
     <v>15.64</v>
     <v>14.26</v>
-    <v>14.562900000000001</v>
+    <v>14.57</v>
     <v>66360810</v>
     <v>LPTH</v>
     <v>LIGHTPATH TECHNOLOGIES, INC. (XNAS:LPTH)</v>
-    <v>4464432</v>
+    <v>4469506</v>
     <v>4434473</v>
     <v>1992</v>
   </rv>
@@ -6301,11 +6300,11 @@
     <v>4</v>
     <v>18.709</v>
     <v>1.19</v>
-    <v>2.4036</v>
+    <v>2.4154</v>
     <v>-0.45</v>
-    <v>-6.5900000000000004E-3</v>
+    <v>5.2139999999999999E-3</v>
     <v>-4.4821E-2</v>
-    <v>-6.3200000000000006E-2</v>
+    <v>0.05</v>
     <v>USD</v>
     <v>Lightwave Logic, Inc. is a technology platform company leveraging its proprietary engineered electro-optic (EO) polymers known as Perkinamine, to transmit data at higher speeds with less power in a small form factor. The Company’s organic polymers allow it to create next-generation photonic EO devices that convert data from electrical signals into light/optical signals for applications in telecommunications, and for data transmission potentially used to support generative Artificial Intelligence. It designs its own proprietary materials for electro-optical modulation devices. Electro-optical modulators convert data from electric signals into optical signals that can then be transmitted over high-speed fiber-optic cables. It is focused on testing and demonstrating the manufacturability and reliability of its devices. In polymer photonics, polymer devices such as modulators, waveguides, and multiplexers can be fabricated on to a silicon platform.</v>
     <v>34</v>
@@ -6316,7 +6315,7 @@
     <v>10.15</v>
     <v>Electronic Equipment &amp; Parts</v>
     <v>Stock</v>
-    <v>46185.983440392971</v>
+    <v>46185.998326318753</v>
     <v>140</v>
     <v>9.44</v>
     <v>1477623364</v>
@@ -6326,11 +6325,11 @@
     <v>0</v>
     <v>10.039999999999999</v>
     <v>9.59</v>
-    <v>9.5267999999999997</v>
+    <v>9.64</v>
     <v>154079600</v>
     <v>LWLG</v>
     <v>LIGHTWAVE LOGIC, INC. (XNAS:LWLG)</v>
-    <v>3692605</v>
+    <v>3694090</v>
     <v>7453675</v>
     <v>1997</v>
   </rv>
@@ -6371,11 +6370,11 @@
     <v>4</v>
     <v>341.75</v>
     <v>271.85000000000002</v>
-    <v>0.40529999999999999</v>
-    <v>-0.01</v>
-    <v>-7.0220000000000002E-5</v>
-    <v>-3.5120000000000003E-5</v>
-    <v>-0.02</v>
+    <v>0.40689999999999998</v>
+    <v>0.04</v>
+    <v>1.404E-4</v>
+    <v>1.405E-4</v>
+    <v>0.04</v>
     <v>USD</v>
     <v>McDonald's Corporation is a global foodservice retailer. Its segment includes U.S., International Operated Markets, and International Developmental Licensed Markets &amp; Corporate. The U.S. segment is its largest market and is 95% franchised. The International Operated Markets segment comprises markets or countries in which it operates and franchises restaurants, including Australia, Canada, France, Germany, Italy, Poland, Spain, and the United Kingdom. This segment is 89% franchised. The International Developmental Licensed Markets &amp; Corporate segment comprises development licensee and affiliate markets, including equity method investments in China and Japan. This segment is 99% franchised. Its menu features hamburgers and cheeseburgers, the Big Mac, the Quarter Pounder with Cheese, the Filet-O-Fish, and several chicken sandwiches, such as the McChicken and McCrispy as well as Chicken McNuggets, Fries, shakes, sundaes, cookies, soft drinks, coffee, and other beverages.</v>
     <v>150000</v>
@@ -6387,21 +6386,21 @@
     <v>145</v>
     <v>Hotels &amp; Entertainment Services</v>
     <v>Stock</v>
-    <v>46185.991143796091</v>
+    <v>46185.999877106253</v>
     <v>146</v>
     <v>284.02699999999999</v>
-    <v>202323660084</v>
+    <v>202359185379</v>
     <v>MCDONALD'S CORPORATION</v>
     <v>MCDONALD'S CORPORATION</v>
     <v>286</v>
-    <v>23.4724</v>
+    <v>23.476500000000001</v>
     <v>284.77</v>
-    <v>284.76</v>
-    <v>284.79000000000002</v>
+    <v>284.81</v>
+    <v>284.85000000000002</v>
     <v>710505900</v>
     <v>MCD</v>
     <v>MCDONALD'S CORPORATION (XNYS:MCD)</v>
-    <v>4028585</v>
+    <v>4028820</v>
     <v>4470236</v>
     <v>1964</v>
   </rv>
@@ -6446,11 +6445,11 @@
     <v>4</v>
     <v>444.72</v>
     <v>196</v>
-    <v>1.5255000000000001</v>
+    <v>1.5392999999999999</v>
     <v>-11.61</v>
-    <v>3.5010000000000002E-3</v>
+    <v>1.4000000000000002E-3</v>
     <v>-3.2759000000000003E-2</v>
-    <v>1.2</v>
+    <v>0.48</v>
     <v>USD</v>
     <v>MongoDB, Inc. is a developer data platform company. Its developer data platform is a globally distributed operational database integrated with a set of data services that allow development teams to address the growing variety of application requirements. Its customers can implement its developer data platform as a managed service offering, or they can choose a self-managed option. Its MongoDB Atlas is its managed multi-cloud database-as-a-service (DBaaS) offering that includes an integrated set of databases and related services. Atlas Vector Search allows the integration of an operational database and vector search in a unified, fully managed platform. MongoDB Enterprise Advanced is its proprietary self-managed commercial offering for enterprise customers that can run in the cloud, on-premises or in a hybrid environment. It also provides professional services for its customers.</v>
     <v>5636</v>
@@ -6462,7 +6461,7 @@
     <v>152</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46185.990484212503</v>
+    <v>46185.998144767967</v>
     <v>153</v>
     <v>340.5</v>
     <v>27572065604</v>
@@ -6472,11 +6471,11 @@
     <v>0</v>
     <v>354.41</v>
     <v>342.8</v>
-    <v>344</v>
+    <v>343.28</v>
     <v>80431930</v>
     <v>MDB</v>
     <v>MONGODB, INC. (XNAS:MDB)</v>
-    <v>939643</v>
+    <v>939690</v>
     <v>2823304</v>
     <v>2007</v>
   </rv>
@@ -6501,11 +6500,11 @@
     <v>4</v>
     <v>796.25</v>
     <v>520.26</v>
-    <v>1.2496</v>
+    <v>1.2486999999999999</v>
     <v>-1.45</v>
-    <v>2.8479999999999998E-3</v>
+    <v>4.0920000000000002E-3</v>
     <v>-2.5509999999999999E-3</v>
-    <v>1.615</v>
+    <v>2.3199999999999998</v>
     <v>USD</v>
     <v>Meta Platforms, Inc. is building human connections, powered by artificial intelligence and immersive technologies. The Company's products enable people to connect and share with friends and family through mobile devices, personal computers, virtual reality (VR) and mixed reality (MR) headsets, augmented reality (AR), and wearables. It also helps people discover and learn about what is going on in the world around them, enabling people to share their experiences, ideas, photos, videos, and other content with audiences ranging from their closest family members and friends to the public at large. The Company's segments include Family of Apps (FoA) and Reality Labs (RL). FoA segment includes Facebook, Instagram, Messenger, WhatsApp and Threads. RL segment includes its virtual, augmented, and mixed reality related consumer hardware, software and content. Its product offerings in VR include its Meta Quest devices, as well as software and content available through the Meta Horizon Store.</v>
     <v>77986</v>
@@ -6516,7 +6515,7 @@
     <v>576.07000000000005</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46185.991854235937</v>
+    <v>46185.999984247654</v>
     <v>156</v>
     <v>560.9</v>
     <v>1439235072540</v>
@@ -6526,11 +6525,11 @@
     <v>17.241299999999999</v>
     <v>568.42999999999995</v>
     <v>566.98</v>
-    <v>568.59500000000003</v>
+    <v>569.29999999999995</v>
     <v>2538423000</v>
     <v>META</v>
     <v>META PLATFORMS, INC. (XNAS:META)</v>
-    <v>14344391</v>
+    <v>14347769</v>
     <v>16753666</v>
     <v>2004</v>
   </rv>
@@ -6555,11 +6554,11 @@
     <v>4</v>
     <v>324.2</v>
     <v>61.44</v>
-    <v>2.1606000000000001</v>
+    <v>2.1802999999999999</v>
     <v>-1.01</v>
-    <v>4.6550000000000003E-3</v>
+    <v>5.2559999999999994E-3</v>
     <v>-3.5980000000000001E-3</v>
-    <v>1.302</v>
+    <v>1.47</v>
     <v>USD</v>
     <v>Marvell Technology, Inc. together with its consolidated subsidiaries, is a supplier of data infrastructure semiconductor solutions, spanning the data center core to network edge. It is engaged in the design, development and sale of integrated circuits. Its product offerings include custom application-specific integrated circuits (ASICs), interconnects, ethernet solutions, fiber channel adapters, processors and storage controllers. In addition, it is also developing Ultra Accelerator LinkTM (UALinkTM) switches and ethernet for scale-up networking (ESUN) switches for the emerging scale-out artificial intelligence market. Its solutions integrate multiple analogs, mixed-signal and digital intellectual property components incorporating hardware, firmware and software technologies and its system knowledge to provide its customers with integrated solutions for their end products. It designs and manufactures photonic integrated circuits for ultra-high-bandwidth and low-power applications.</v>
     <v>7480</v>
@@ -6570,21 +6569,21 @@
     <v>287.98</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46185.991857453126</v>
+    <v>46185.999876654685</v>
     <v>159</v>
     <v>267.31</v>
     <v>244681560000</v>
     <v>MARVELL TECHNOLOGY, INC.</v>
     <v>MARVELL TECHNOLOGY, INC.</v>
     <v>270.07</v>
-    <v>95.804100000000005</v>
+    <v>96.149000000000001</v>
     <v>280.70999999999998</v>
     <v>279.7</v>
-    <v>281.00200000000001</v>
+    <v>281.17</v>
     <v>874800000</v>
     <v>MRVL</v>
     <v>MARVELL TECHNOLOGY, INC. (XNAS:MRVL)</v>
-    <v>42143005</v>
+    <v>42162220</v>
     <v>48584406</v>
     <v>2020</v>
   </rv>
@@ -6625,11 +6624,11 @@
     <v>4</v>
     <v>555.45000000000005</v>
     <v>356.28</v>
-    <v>1.1322000000000001</v>
+    <v>1.1292</v>
     <v>0.4</v>
-    <v>-5.1180000000000008E-4</v>
+    <v>-1.551E-4</v>
     <v>1.0249999999999999E-3</v>
-    <v>-0.2</v>
+    <v>-6.0600000000000001E-2</v>
     <v>USD</v>
     <v>Microsoft Corporation is a technology company. The Company develops and supports software, services, devices, and solutions. The Company’s segments include Productivity and Business Processes, Intelligent Cloud, and More Personal Computing. The Productivity and Business Processes segment consists of products and services in its portfolio of productivity, communication, and information services. This segment primarily comprises: Office Commercial, Office Consumer, LinkedIn, and Dynamics business solutions. The Intelligent Cloud segment consists of server products and cloud services, including Azure and other cloud services, SQL Server, Windows Server, Visual Studio, System Center, and related Client Access Licenses (CALs), and Nuance and GitHub; and Enterprise Services, including enterprise support services, industry solutions and Nuance professional services. The More Personal Computing segment primarily comprises Windows, Devices, Gaming, and search and news advertising.</v>
     <v>228000</v>
@@ -6641,21 +6640,21 @@
     <v>164</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46185.991877036722</v>
+    <v>46185.99999211797</v>
     <v>165</v>
     <v>382.27</v>
     <v>2902586691900</v>
     <v>MICROSOFT CORPORATION</v>
     <v>MICROSOFT CORPORATION</v>
     <v>391.43</v>
-    <v>23.2727</v>
+    <v>23.248899999999999</v>
     <v>390.34</v>
     <v>390.74</v>
-    <v>390.54</v>
+    <v>390.67939999999999</v>
     <v>7428435000</v>
     <v>MSFT</v>
     <v>MICROSOFT CORPORATION (XNAS:MSFT)</v>
-    <v>34914267</v>
+    <v>34922036</v>
     <v>36884714</v>
     <v>1993</v>
   </rv>
@@ -6680,11 +6679,11 @@
     <v>4</v>
     <v>457.22</v>
     <v>104.16500000000001</v>
-    <v>3.5194000000000001</v>
+    <v>3.5110000000000001</v>
     <v>3.82</v>
-    <v>9.68E-4</v>
+    <v>3.3479999999999998E-3</v>
     <v>3.1793999999999996E-2</v>
-    <v>0.12</v>
+    <v>0.41499999999999998</v>
     <v>USD</v>
     <v>Strategy Inc. is a bitcoin treasury and business intelligence company. The Company provides cloud-native, artificial intelligence (AI)-powered enterprise analytics software to thousands of global customers. Its Software Business segment is engaged in the design, development, marketing, and sales of enterprise analytics software platform through cloud subscriptions and licensing arrangements and related services. Its Strategy ONE platform provides access to AI-powered workflows, unlimited data sources, cloud-native technologies, and performance to speed up time from data to action. Strategy One delivers visualization, reporting, and embedded analytics capabilities across retail, banking, technology, manufacturing, insurance, consulting, healthcare, public sector, and others. Its Strategy Mosaic is a universal intelligence layer that provides enterprises with consistent definitions and governance across data sources, regardless of where that data resides or which tools access it.</v>
     <v>1511</v>
@@ -6695,7 +6694,7 @@
     <v>128.6</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46185.991724293752</v>
+    <v>46185.999969003904</v>
     <v>168</v>
     <v>117.27</v>
     <v>44405793663</v>
@@ -6705,11 +6704,11 @@
     <v>0</v>
     <v>120.15</v>
     <v>123.97</v>
-    <v>124.09</v>
+    <v>124.38500000000001</v>
     <v>358197900</v>
     <v>MSTR</v>
     <v>STRATEGY INC (XNAS:MSTR)</v>
-    <v>16830307</v>
+    <v>16836331</v>
     <v>17848186</v>
     <v>1989</v>
   </rv>
@@ -6734,11 +6733,11 @@
     <v>4</v>
     <v>1089.29</v>
     <v>103.38</v>
-    <v>2.1598999999999999</v>
+    <v>2.1677</v>
     <v>-14.26</v>
-    <v>6.5000000000000006E-3</v>
+    <v>8.1399999999999997E-3</v>
     <v>-1.4319E-2</v>
-    <v>6.38</v>
+    <v>7.99</v>
     <v>USD</v>
     <v>Micron Technology, Inc. provides memory and storage solutions. The Company delivers a portfolio of high-performance dynamic random-access memory (DRAM), NAND, and NOR memory and storage products through its Micron and Crucial brands. The Company's products enable advancing in artificial intelligence (AI) and compute-intensive applications. Its segments include Cloud Memory Business Unit (CMBU), Core Data Center Business Unit (CDBU), Mobile and Client Business Unit (MCBU) and Automotive and Embedded Business Unit (AEBU). CMBU is focused on memory solutions for large hyperscale cloud customers, and high bandwidth memory (HBM) for all data center customers. CDBU is focused on memory solutions for mid-tier cloud, enterprise, and OEM data center customers and storage solutions for all data center customers. MCBU is focused on memory and storage solutions for mobile and client segments. AEBU is focused on memory and storage solutions for the automotive, industrial, and consumer segments.</v>
     <v>53000</v>
@@ -6749,21 +6748,21 @@
     <v>1012.6198000000001</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46185.991811550783</v>
+    <v>46185.999998182815</v>
     <v>171</v>
     <v>960.19</v>
     <v>1106994971740</v>
     <v>MICRON TECHNOLOGY, INC.</v>
     <v>MICRON TECHNOLOGY, INC.</v>
     <v>971.81</v>
-    <v>46.343200000000003</v>
+    <v>47.016500000000001</v>
     <v>995.87</v>
     <v>981.61</v>
-    <v>987.99</v>
+    <v>989.6</v>
     <v>1127734000</v>
     <v>MU</v>
     <v>MICRON TECHNOLOGY, INC. (XNAS:MU)</v>
-    <v>40946517</v>
+    <v>40995386</v>
     <v>56814566</v>
     <v>1984</v>
   </rv>
@@ -6774,25 +6773,25 @@
     <v>https://www.bing.com/financeapi/forcetrigger?t=brh6oc&amp;q=XNYS%3aNET&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
   </rv>
-  <rv s="12">
+  <rv s="10">
     <v>en-GB</v>
     <v>brh6oc</v>
     <v>268435456</v>
     <v>1</v>
     <v>Powered by Refinitiv</v>
-    <v>25</v>
+    <v>19</v>
     <v>CLOUDFLARE, INC. (XNYS:NET)</v>
     <v>2</v>
-    <v>26</v>
+    <v>20</v>
     <v>Finance</v>
     <v>4</v>
     <v>276.815</v>
     <v>158.83000000000001</v>
-    <v>1.6829000000000001</v>
-    <v>1.07</v>
-    <v>2.2759999999999998E-3</v>
-    <v>4.705E-3</v>
-    <v>0.52</v>
+    <v>1.6826000000000001</v>
+    <v>1.04</v>
+    <v>1.1819999999999999E-3</v>
+    <v>4.5729999999999998E-3</v>
+    <v>0.27</v>
     <v>USD</v>
     <v>Cloudflare, Inc. is a connectivity cloud company. The Company delivers a range of services to businesses of all sizes and in all geographies, enhancing the performance of business-critical applications. Its full suite of products consists of application services that help deliver security, performance, and reliability for any organization's applications connected to the Internet, including Websites and application programming interfaces (APIs) and its secure access service edge (SASE) platform, which contains its suite of and workplace security services and network services solutions to help ensure traffic in and out of an organization’s network and devices is verified and authorized and data is protected and secured, as well as to securely connect data centers, cloud services, and branch offices to an organization with its connectivity cloud. The Company also offers developer-based solutions which build and deploys serverless and artificial intelligence applications.</v>
     <v>5483</v>
@@ -6803,20 +6802,20 @@
     <v>231.9</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46185.985635126563</v>
+    <v>46185.999147325783</v>
     <v>174</v>
     <v>222.02</v>
-    <v>81107247996</v>
+    <v>81096599808</v>
     <v>CLOUDFLARE, INC.</v>
     <v>CLOUDFLARE, INC.</v>
     <v>229.95</v>
     <v>227.44</v>
-    <v>228.51</v>
-    <v>229</v>
+    <v>228.48</v>
+    <v>228.75</v>
     <v>354939600</v>
     <v>NET</v>
     <v>CLOUDFLARE, INC. (XNYS:NET)</v>
-    <v>2261887</v>
+    <v>2262011</v>
     <v>5068237</v>
     <v>2009</v>
   </rv>
@@ -6838,8 +6837,8 @@
     <v>2</v>
     <v>28</v>
     <v>Finance</v>
-    <v>21</v>
-    <v>1.1021000000000001</v>
+    <v>23</v>
+    <v>1.1107</v>
     <v>-0.33</v>
     <v>-8.3599999999999994E-3</v>
     <v>EUR</v>
@@ -6866,7 +6865,7 @@
     <v>NKE</v>
     <v>NIKE, INC. (XFRA:NKE)</v>
     <v>3662</v>
-    <v>22055800</v>
+    <v>19813320</v>
     <v>1969</v>
   </rv>
   <rv s="2">
@@ -6900,11 +6899,11 @@
     <v>4</v>
     <v>17.45</v>
     <v>4</v>
-    <v>1.1597</v>
+    <v>1.1482000000000001</v>
     <v>0.71</v>
-    <v>7.4319999999999994E-3</v>
+    <v>5.8779999999999995E-3</v>
     <v>5.0389999999999997E-2</v>
-    <v>0.11</v>
+    <v>8.6999999999999994E-2</v>
     <v>USD</v>
     <v>Nokia Oyj is a Finland-based company engaged in the network and Internet protocol (IP) infrastructure, software, and related services market. The Company's businesses include Nokia Networks and Nokia Technologies. The Company's segments include Ultra Broadband Networks, IP Networks and Applications, and Nokia Technologies. The Ultra Broadband Networks segment comprises Mobile Networks and Fixed Networks operating segments. The IP Networks and Applications segment comprises IP/Optical Networks and Applications &amp; Analytics operating segments. The Applications &amp; Analytics operating segment offers software solutions spanning customer experience management, network operations and management, communications and collaboration, policy and charging, as well as Cloud, Internet of things (IoT), security, and analytics platforms that enable digital services providers and enterprises to accelerate and optimize their customer experience. The Company has Comptel Oyj among its subsidiaries.</v>
     <v>77586</v>
@@ -6915,21 +6914,21 @@
     <v>15.07</v>
     <v>Communications &amp; Networking</v>
     <v>Stock</v>
-    <v>46185.99172277734</v>
+    <v>46185.999987441406</v>
     <v>182</v>
     <v>14.234999999999999</v>
     <v>84985152000</v>
     <v>Nokia Oyj</v>
     <v>Nokia Oyj</v>
     <v>14.34</v>
-    <v>91.982600000000005</v>
+    <v>87.584500000000006</v>
     <v>14.09</v>
     <v>14.8</v>
-    <v>14.91</v>
+    <v>14.887</v>
     <v>5742240000</v>
     <v>NOK</v>
     <v>Nokia Oyj (XNYS:NOK)</v>
-    <v>117839241</v>
+    <v>117902581</v>
     <v>124645398</v>
     <v>1997</v>
   </rv>
@@ -6954,11 +6953,11 @@
     <v>4</v>
     <v>211.47800000000001</v>
     <v>81.239999999999995</v>
-    <v>0.96730000000000005</v>
-    <v>-0.9</v>
-    <v>3.9160000000000002E-3</v>
-    <v>-8.7309999999999992E-3</v>
-    <v>0.4</v>
+    <v>0.96460000000000001</v>
+    <v>-0.93</v>
+    <v>7.1460000000000004E-3</v>
+    <v>-9.0220000000000005E-3</v>
+    <v>0.73</v>
     <v>USD</v>
     <v>ServiceNow, Inc. provides an artificial intelligence (AI) platform for business transformation. The Company’s AI platform connects people, processes, data, and devices to increase productivity and maximize business outcomes. Its intelligent platform, the Now Platform, is a cloud-based solution that helps enterprises and organizations across public and private sectors digitize workflows. The workflow applications built on the Now Platform are organized into four primary areas: Technology, CRM and Industry, Core Business and Creator. Its products include IT Service Management, IT Operations Management, HR Service Delivery, ServiceNow AI Agents, AI Experience, Build Agent, ServiceNow AI Control Tower, AI Agent Fabric, RaptorDB, Workflow Data Fabric, Workplace Service Delivery, ServiceNow Platform Encryption, Telecommunications Service Operations Management, and others. The Company also offers identity security, helping organizations secure access across the enterprise.</v>
     <v>29187</v>
@@ -6969,21 +6968,21 @@
     <v>103.45</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46185.991609560158</v>
+    <v>46185.999951457816</v>
     <v>185</v>
     <v>98.42</v>
-    <v>105379051440</v>
+    <v>105348112200</v>
     <v>SERVICENOW, INC.</v>
     <v>SERVICENOW, INC.</v>
     <v>103.38</v>
-    <v>60.770800000000001</v>
+    <v>60.752899999999997</v>
     <v>103.08</v>
-    <v>102.18</v>
-    <v>102.55</v>
+    <v>102.15</v>
+    <v>102.88</v>
     <v>1031308000</v>
     <v>NOW</v>
     <v>SERVICENOW, INC. (XNYS:NOW)</v>
-    <v>26043001</v>
+    <v>26049350</v>
     <v>33330509</v>
     <v>2012</v>
   </rv>
@@ -7008,11 +7007,11 @@
     <v>4</v>
     <v>236.54</v>
     <v>140.85499999999999</v>
-    <v>2.2021999999999999</v>
+    <v>2.2042999999999999</v>
     <v>0.32</v>
-    <v>1.5079999999999998E-3</v>
+    <v>1.139E-3</v>
     <v>1.562E-3</v>
-    <v>0.3095</v>
+    <v>0.23380000000000001</v>
     <v>USD</v>
     <v>NVIDIA Corporation is an artificial intelligence (AI) infrastructure company. The Company is engaged in accelerated computing to help solve the challenging computational problems. Its segments include Compute &amp; Networking and Graphics. The Compute &amp; Networking segment includes its Data Center accelerated computing and networking platforms and AI solutions and software, and automotive platforms and autonomous and electric vehicle solutions, including software. The Graphics segment includes GeForce GPUs for gaming and personal computers (PCs), and Quadro/NVIDIA RTX GPUs for enterprise workstation graphics. Its technology stack includes the foundational NVIDIA CUDA development platform that runs on all NVIDIA GPUs, as well as hundreds of domain-specific software libraries, frameworks, algorithms, software development kits (SDKs), and application programming interfaces (APIs). Its platforms address four markets, which include Data Center, Gaming, Professional Visualization, and Automotive.</v>
     <v>42000</v>
@@ -7023,21 +7022,21 @@
     <v>207.07</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46185.991765126564</v>
+    <v>46185.999999328124</v>
     <v>188</v>
     <v>203.4385</v>
     <v>4965598000000</v>
     <v>NVIDIA CORPORATION</v>
     <v>NVIDIA CORPORATION</v>
     <v>204.86</v>
-    <v>31.422699999999999</v>
+    <v>31.373799999999999</v>
     <v>204.87</v>
     <v>205.19</v>
-    <v>205.49950000000001</v>
+    <v>205.4238</v>
     <v>24200000000</v>
     <v>NVDA</v>
     <v>NVIDIA CORPORATION (XNAS:NVDA)</v>
-    <v>112225632</v>
+    <v>112345314</v>
     <v>174583178</v>
     <v>1998</v>
   </rv>
@@ -7062,11 +7061,11 @@
     <v>4</v>
     <v>134.91999999999999</v>
     <v>44.56</v>
-    <v>1.9766999999999999</v>
+    <v>1.9774</v>
     <v>0.83</v>
-    <v>-2.2260000000000001E-3</v>
+    <v>5.1369999999999996E-4</v>
     <v>7.1580000000000003E-3</v>
-    <v>-0.26</v>
+    <v>0.06</v>
     <v>USD</v>
     <v>ON Semiconductor Corporation is engaged in providing intelligent power and intelligent sensing solutions. The Company’s intelligent power technologies enable the electrification of drivetrain in the automotive industry to allow for lighter and longer-range electric vehicles. Its segments include Power Solutions Group (PSG), the Analog and Mixed-Signal Group (AMG) and the Intelligent Sensing Group (ISG). PSG segment provides a portfolio of discrete, module, and integrated semiconductor devices designed to enable conversion across artificial intelligence (AI) data centers, energy infrastructure, automotive and industrial. AMG segment designs and develops a range of analog and mixed-signal solutions including power‑management, sensor‑interface, connectivity, and products that serve automotive, industrial automation, AI data center, computing, and mobile end markets.</v>
     <v>22600</v>
@@ -7077,21 +7076,21 @@
     <v>118.58499999999999</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46185.991209606247</v>
+    <v>46185.997945323441</v>
     <v>191</v>
     <v>113.99</v>
     <v>45770374728</v>
     <v>ON SEMICONDUCTOR CORPORATION</v>
     <v>ON SEMICONDUCTOR CORPORATION</v>
     <v>115.96</v>
-    <v>83.397599999999997</v>
+    <v>82.806100000000001</v>
     <v>115.96</v>
     <v>116.79</v>
-    <v>116.53</v>
+    <v>116.85</v>
     <v>391903200</v>
     <v>ON</v>
     <v>ON SEMICONDUCTOR CORPORATION (XNAS:ON)</v>
-    <v>7351548</v>
+    <v>7351855</v>
     <v>12396254</v>
     <v>2000</v>
   </rv>
@@ -7116,11 +7115,11 @@
     <v>4</v>
     <v>15.28</v>
     <v>1.36</v>
-    <v>2.6909000000000001</v>
+    <v>2.6936</v>
     <v>-0.5</v>
-    <v>1.179E-2</v>
+    <v>1.1757999999999999E-2</v>
     <v>-5.0865E-2</v>
-    <v>0.11</v>
+    <v>0.10970000000000001</v>
     <v>USD</v>
     <v>Ondas Inc. is a provider of autonomous systems, robotics, and mission-critical connectivity solutions for defense, security, and industrial markets. Through its business units, Ondas Autonomous Systems (OAS), Ondas Capital and Ondas Networks, it develops and deploys integrated technologies that deliver advanced sensing, mobility, and communications capabilities. OAS delivers a portfolio of artificial-intelligence (AI)-powered defense and security platforms to protect sensitive sites, populations, and critical infrastructure. OAS also provides an integrated suite of autonomous aerial, ground, and counter-UAS solutions through its operating companies. It also provides Airborne Missile Protection Systems (AMPS) and airborne intelligence, surveillance and reconnaissance (ISR) solutions for the military, government and others. It also specializes in the procurement, integration, and lifecycle support of heavy engineering equipment for military and national infrastructure programs.</v>
     <v>459</v>
@@ -7131,21 +7130,21 @@
     <v>9.8780000000000001</v>
     <v>Communications &amp; Networking</v>
     <v>Stock</v>
-    <v>46185.991769490625</v>
+    <v>46185.999961758593</v>
     <v>194</v>
     <v>9.18</v>
     <v>4800248613</v>
     <v>ONDAS INC.</v>
     <v>ONDAS INC.</v>
     <v>9.7949999999999999</v>
-    <v>23.524999999999999</v>
+    <v>24.788799999999998</v>
     <v>9.83</v>
     <v>9.33</v>
-    <v>9.44</v>
+    <v>9.4397000000000002</v>
     <v>514496100</v>
     <v>ONDS</v>
     <v>ONDAS INC. (XNAS:ONDS)</v>
-    <v>55341963</v>
+    <v>55365320</v>
     <v>82222177</v>
     <v>2014</v>
   </rv>
@@ -7186,11 +7185,11 @@
     <v>4</v>
     <v>345.72</v>
     <v>134.57</v>
-    <v>1.6963999999999999</v>
-    <v>-0.01</v>
-    <v>-9.8680000000000013E-4</v>
-    <v>-5.4320000000000002E-5</v>
-    <v>-0.1817</v>
+    <v>1.6926000000000001</v>
+    <v>0.03</v>
+    <v>-1.0319999999999999E-3</v>
+    <v>1.6299999999999998E-4</v>
+    <v>-0.19</v>
     <v>USD</v>
     <v>Oracle Corporation offers integrated suites of applications plus secure, autonomous infrastructure in the Oracle Cloud. The Company operates through three businesses: cloud and license, hardware and service. Its cloud and license business is engaged in the sale, marketing and delivery of its enterprise applications and infrastructure technologies through cloud and on-premise deployment models including its cloud services and license support offerings, and its cloud license and on-premise license offerings. Its hardware business provides infrastructure technologies including Oracle Engineered Systems, servers, storage, industry-specific hardware, operating systems, virtualization, management and other hardware-related software to support diverse IT environments. Its services business provides services to customers and partners to help maximize the performance of their investments in Oracle applications and infrastructure technologies.</v>
     <v>162000</v>
@@ -7202,21 +7201,21 @@
     <v>199</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46185.991856122659</v>
+    <v>46185.999982418747</v>
     <v>200</v>
     <v>179</v>
-    <v>529451308140</v>
+    <v>529566349980</v>
     <v>ORACLE CORPORATION</v>
     <v>ORACLE CORPORATION</v>
     <v>185.01</v>
-    <v>29.7789</v>
+    <v>29.785299999999999</v>
     <v>184.1</v>
-    <v>184.09</v>
-    <v>183.94829999999999</v>
+    <v>184.13</v>
+    <v>183.94</v>
     <v>2876046000</v>
     <v>ORCL</v>
     <v>ORACLE CORPORATION (XNYS:ORCL)</v>
-    <v>29549532</v>
+    <v>29562284</v>
     <v>24688150</v>
     <v>2005</v>
   </rv>
@@ -7241,11 +7240,11 @@
     <v>4</v>
     <v>302.95</v>
     <v>139.57060000000001</v>
-    <v>0.94410000000000005</v>
+    <v>0.94489999999999996</v>
     <v>0.09</v>
-    <v>-1.0870000000000001E-3</v>
+    <v>-5.7940000000000005E-3</v>
     <v>3.2200000000000002E-4</v>
-    <v>-0.3039</v>
+    <v>-1.62</v>
     <v>USD</v>
     <v>Palo Alto Networks, Inc. is a global artificial intelligence (AI) cybersecurity company, with a comprehensive portfolio of cybersecurity solutions and platforms across network, cloud, security operations, AI and Identity. Its network security platform includes Secure Access Service Edge (SASE), Next-Generation Firewalls, Cloud Delivered Security Services (CDSS), Prisma AIRS, and Strata Cloud Manager (SCM). It delivers security operations capabilities that unifies standalone Security Information and Event Management (SIEM) tools, endpoint security, security automation, cloud detection and response (CDR), as well as attack surface management (ASM) capabilities on its Cortex platform. It delivers comprehensive security across the cloud application development lifecycle through Cortex Cloud. Its Unit 42 brings together expertise across threat research, incident response, and security consulting to deliver intelligence-driven, response-ready outcomes that help customers reduce cyber risk.</v>
     <v>21491</v>
@@ -7256,21 +7255,21 @@
     <v>281.98</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46185.990997753906</v>
+    <v>46185.999874409375</v>
     <v>203</v>
     <v>271.49</v>
     <v>227890300000</v>
     <v>PALO ALTO NETWORKS, INC.</v>
     <v>PALO ALTO NETWORKS, INC.</v>
     <v>276.935</v>
-    <v>230.2347</v>
+    <v>230.1662</v>
     <v>279.52999999999997</v>
     <v>279.62</v>
-    <v>279.31610000000001</v>
+    <v>278</v>
     <v>815000000</v>
     <v>PANW</v>
     <v>PALO ALTO NETWORKS, INC. (XNAS:PANW)</v>
-    <v>6774009</v>
+    <v>6774241</v>
     <v>9855800</v>
     <v>2005</v>
   </rv>
@@ -7295,11 +7294,11 @@
     <v>4</v>
     <v>19.84</v>
     <v>9.2002000000000006</v>
-    <v>0.97919999999999996</v>
-    <v>-0.105</v>
-    <v>-2.3699999999999997E-3</v>
-    <v>-9.8589999999999997E-3</v>
-    <v>-2.5000000000000001E-2</v>
+    <v>0.98089999999999999</v>
+    <v>-0.1</v>
+    <v>-9.479E-4</v>
+    <v>-9.389999999999999E-3</v>
+    <v>-0.01</v>
     <v>USD</v>
     <v>UiPath, Inc. is focused on agentic automation and orchestration, empowering enterprises to harness the full potential of AI agents to autonomously execute and optimize complex business processes. It is focused on building and managing automations, starting with computer vision technology and user interface automation in its initial robotic process automation offering. Its AI-powered UiPath Platform offers a robust set of capabilities that allows its customers to discover opportunities for automation, automate using a digital workforce that seamlessly collaborates with humans, and operate a mission-critical automation program at scale. It enables employees to quickly build automations for both existing and new processes and to automate a range of actions including logging into applications, moving folders, filling in forms, reading emails and others. Its platform allows users to design and combine UI automations, API integrations and AI-based document understanding in a single workflow.</v>
     <v>3981</v>
@@ -7310,21 +7309,21 @@
     <v>10.7</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46185.990983529686</v>
+    <v>46185.999587789061</v>
     <v>206</v>
     <v>10.07</v>
-    <v>5463578563</v>
+    <v>5466169165</v>
     <v>UIPATH, INC.</v>
     <v>UIPATH, INC.</v>
     <v>10.62</v>
-    <v>17.528300000000002</v>
+    <v>17.5366</v>
     <v>10.65</v>
-    <v>10.545</v>
-    <v>10.525</v>
+    <v>10.55</v>
+    <v>10.54</v>
     <v>518120300</v>
     <v>PATH</v>
     <v>UIPATH, INC. (XNYS:PATH)</v>
-    <v>40791231</v>
+    <v>40796703</v>
     <v>43720947</v>
     <v>2015</v>
   </rv>
@@ -7350,10 +7349,10 @@
     <v>167.25</v>
     <v>137.62</v>
     <v>0.37230000000000002</v>
-    <v>1.24</v>
-    <v>-9.3579999999999998E-4</v>
-    <v>8.3590000000000001E-3</v>
-    <v>-0.14000000000000001</v>
+    <v>1.27</v>
+    <v>6.0159999999999999E-4</v>
+    <v>8.5609999999999992E-3</v>
+    <v>0.09</v>
     <v>USD</v>
     <v>The Procter &amp; Gamble Company is focused on providing branded consumer packaged goods to consumers across the world. The Company’s segments include Beauty, Grooming, Health Care, Fabric &amp; Home Care and Baby, Feminine &amp; Family Care. The Company’s products are sold in approximately 180 countries and territories primarily through mass merchandisers, e-commerce, including social commerce channels, grocery stores, membership club stores, drug stores, department stores, distributors, wholesalers, specialty beauty stores, including airport duty-free stores), high-frequency stores, pharmacies, electronics stores and professional channels. It also sells direct to individual consumers. It has operations in approximately 70 countries. It offers products under brands, such as Head &amp; Shoulders, Herbal Essences, Pantene, Rejoice, Olay, Old Spice, Safeguard, Secret, SK-II, Braun, Gillette, Venus, Crest, Oral-B, Ariel, Downy, Gain, Tide, Always, Always Discreet, Tampax, Bounty and others.</v>
     <v>109000</v>
@@ -7364,21 +7363,21 @@
     <v>150.19999999999999</v>
     <v>Personal &amp; Household Products &amp; Services</v>
     <v>Stock</v>
-    <v>46185.990763633592</v>
+    <v>46185.999786885935</v>
     <v>209</v>
     <v>148.30000000000001</v>
-    <v>348311838420</v>
+    <v>348381696390</v>
     <v>THE PROCTER &amp; GAMBLE COMPANY</v>
     <v>THE PROCTER &amp; GAMBLE COMPANY</v>
     <v>149.38</v>
-    <v>21.876100000000001</v>
+    <v>21.880500000000001</v>
     <v>148.34</v>
-    <v>149.58000000000001</v>
-    <v>149.47</v>
+    <v>149.61000000000001</v>
+    <v>149.69999999999999</v>
     <v>2328599000</v>
     <v>PG</v>
     <v>THE PROCTER &amp; GAMBLE COMPANY (XNYS:PG)</v>
-    <v>6831292</v>
+    <v>6832001</v>
     <v>8399254</v>
     <v>1905</v>
   </rv>
@@ -7403,11 +7402,11 @@
     <v>4</v>
     <v>56</v>
     <v>18</v>
-    <v>1.3777999999999999</v>
+    <v>1.3705000000000001</v>
     <v>1.05</v>
-    <v>3.1470000000000001E-4</v>
+    <v>6.2929999999999995E-4</v>
     <v>3.4168999999999998E-2</v>
-    <v>0.01</v>
+    <v>0.02</v>
     <v>USD</v>
     <v>Photronics, Inc. is a manufacturer of photomasks, which are high-precision photographic quartz or glass plates containing microscopic images of electronic circuits. The Company manufactures photomasks, which are used as masters to transfer circuit patterns onto semiconductor wafers and FPD substrates. The photomasks the Company manufactures incorporate circuit designs provided on a confidential basis by its customers. The Company sells its photomasks to semiconductor designers and manufacturers, and manufacturers of FPDs. Photomask technology is also being applied to the fabrication of other higher-performance electronic products such as virtual reality/augmented reality advanced IC packages, photonics, micro-electronic mechanical systems, and certain nanotechnology applications. The Company operates approximately 11 manufacturing facilities, which are located in Taiwan, China, Korea, the United States, and Europe.</v>
     <v>1908</v>
@@ -7418,21 +7417,21 @@
     <v>31.98</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46185.990397198439</v>
+    <v>46185.997376943749</v>
     <v>212</v>
     <v>30.13</v>
-    <v>1873951874</v>
+    <v>1873866386</v>
     <v>PHOTRONICS, INC.</v>
     <v>PHOTRONICS, INC.</v>
     <v>30.79</v>
     <v>11.254300000000001</v>
     <v>30.73</v>
     <v>31.78</v>
-    <v>31.79</v>
-    <v>58966390</v>
+    <v>31.8</v>
+    <v>58963700</v>
     <v>PLAB</v>
     <v>PHOTRONICS, INC. (XNAS:PLAB)</v>
-    <v>1201949</v>
+    <v>1202084</v>
     <v>1967064</v>
     <v>1969</v>
   </rv>
@@ -7457,11 +7456,11 @@
     <v>4</v>
     <v>20.81</v>
     <v>3.87</v>
-    <v>0.7591</v>
+    <v>0.73129999999999995</v>
     <v>1.28</v>
-    <v>1.2768999999999999E-2</v>
+    <v>1.4366E-2</v>
     <v>0.113778</v>
-    <v>0.16</v>
+    <v>0.18</v>
     <v>USD</v>
     <v>POET Technologies Inc. is a design and development company. It offers high-speed optical engines, light source products and custom optical modules to the artificial intelligence (AI) systems market and to hyperscale data centers. Its photonic integration solutions are based on the POET Optical Interposer, a novel, patented platform that allows the integration of electronic and photonic devices into a single chip using wafer-level semiconductor manufacturing techniques. Its Optical Interposer-based products consume less power than comparable products, are smaller in size and are readily scalable to high production volumes. In addition, it has designed and produced novel light source products for chip-to-chip data communication within and between AI servers, the next frontier for solving bandwidth and latency problems in AI systems. Its Optical Interposer platform solves device integration challenges across a range of communication, computing and sensing applications.</v>
     <v>180</v>
@@ -7472,7 +7471,7 @@
     <v>12.93</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46185.990933275003</v>
+    <v>46185.999806539061</v>
     <v>215</v>
     <v>11.02</v>
     <v>2162620362</v>
@@ -7482,11 +7481,11 @@
     <v>0</v>
     <v>11.25</v>
     <v>12.53</v>
-    <v>12.69</v>
+    <v>12.71</v>
     <v>172595400</v>
     <v>POET</v>
     <v>POET Technologies Inc. (XNAS:POET)</v>
-    <v>34142496</v>
+    <v>34162850</v>
     <v>53198989</v>
     <v>2010</v>
   </rv>
@@ -7527,11 +7526,11 @@
     <v>4</v>
     <v>259.92</v>
     <v>121.99</v>
-    <v>1.6380999999999999</v>
+    <v>1.6257999999999999</v>
     <v>8.76</v>
-    <v>3.5899999999999999E-3</v>
+    <v>4.3930000000000002E-3</v>
     <v>4.3160999999999998E-2</v>
-    <v>0.76</v>
+    <v>0.93</v>
     <v>USD</v>
     <v>Qualcomm Incorporated is engaged in the development and commercialization of foundational technologies for the wireless industry, including third generation (3G), fourth generation (4G) and fifth generation (5G) wireless connectivity, and high-performance and low-power computing, including on-device artificial intelligence. Its segments include Qualcomm CDMA Technologies (QCT), Qualcomm Technology Licensing (QTL) and Qualcomm Strategic Initiatives. QCT develops and supplies integrated circuits and system software based on 3G/4G/5G and other technologies, including radio frequency front-end, digital cockpit and advanced driver assistance and automated driving, Internet of things including consumer electronic devices, industrial devices and edge networking products. QTL grants licenses or otherwise provides rights to use portions of its intellectual property portfolio that includes certain patent rights essential to and/or useful in the manufacture and sale of certain wireless products.</v>
     <v>52000</v>
@@ -7543,21 +7542,21 @@
     <v>220</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46185.99180695547</v>
+    <v>46185.999892094529</v>
     <v>221</v>
     <v>200.1</v>
     <v>223152880000</v>
     <v>QUALCOMM INCORPORATED</v>
     <v>QUALCOMM INCORPORATED</v>
     <v>201.85</v>
-    <v>23.029599999999999</v>
+    <v>22.076599999999999</v>
     <v>202.96</v>
     <v>211.72</v>
-    <v>212.48</v>
+    <v>212.65</v>
     <v>1054000000</v>
     <v>QCOM</v>
     <v>QUALCOMM INCORPORATED (XNAS:QCOM)</v>
-    <v>14132047</v>
+    <v>14134861</v>
     <v>26259248</v>
     <v>1991</v>
   </rv>
@@ -7579,10 +7578,10 @@
     <v>2</v>
     <v>3</v>
     <v>Finance</v>
-    <v>24</v>
+    <v>4</v>
     <v>155.47</v>
     <v>74.510000000000005</v>
-    <v>0.64229999999999998</v>
+    <v>0.64329999999999998</v>
     <v>0.41</v>
     <v>-3.5960000000000001E-4</v>
     <v>3.699E-3</v>
@@ -7604,7 +7603,7 @@
     <v>QUALYS, INC.</v>
     <v>QUALYS, INC.</v>
     <v>110.75</v>
-    <v>19.975200000000001</v>
+    <v>19.901599999999998</v>
     <v>110.83</v>
     <v>111.24</v>
     <v>111.2</v>
@@ -7633,21 +7632,21 @@
     <v>16</v>
     <v>17</v>
     <v>Finance</v>
-    <v>18</v>
+    <v>26</v>
     <v>748.65</v>
     <v>523.65</v>
     <v>1.0143</v>
     <v>4.22</v>
-    <v>2.4679999999999997E-3</v>
+    <v>2.274E-3</v>
     <v>5.8850000000000005E-3</v>
-    <v>1.78</v>
+    <v>1.64</v>
     <v>USD</v>
     <v>Nasdaq Stock Market</v>
     <v>XNAS</v>
     <v>1.8E-3</v>
     <v>724.01</v>
     <v>ETF</v>
-    <v>46185.99172371484</v>
+    <v>46185.999972175778</v>
     <v>227</v>
     <v>711.28</v>
     <v>493982650931.38</v>
@@ -7655,10 +7654,10 @@
     <v>717.61</v>
     <v>717.12</v>
     <v>721.34</v>
-    <v>723.12</v>
+    <v>722.98</v>
     <v>QQQ</v>
     <v>Invesco QQQ Trust 1 (XNAS:QQQ)</v>
-    <v>51224656</v>
+    <v>51236021</v>
     <v>46359461</v>
   </rv>
   <rv s="2">
@@ -7682,10 +7681,10 @@
     <v>4</v>
     <v>468.11</v>
     <v>305.44009999999997</v>
-    <v>1.5444</v>
-    <v>1.68</v>
+    <v>1.5475000000000001</v>
+    <v>1.75</v>
     <v>1.4369999999999999E-3</v>
-    <v>3.6709999999999998E-3</v>
+    <v>3.8240000000000001E-3</v>
     <v>0.66</v>
     <v>USD</v>
     <v>Rockwell Automation, Inc. is engaged in industrial automation and digital transformation. The Company operates in three segments: Intelligent Devices, Software &amp; Control, and Lifecycle Services. The Intelligent Devices segment portfolio includes power control, motion control, safety, sensing, and industrial components, and micro control and distributed input/output. The Software &amp; Control operating segment contains a comprehensive portfolio of production automation and production operations platforms, including hardware and software. This integrated portfolio is merging information technology (IT) and operational technology (OT), bringing the benefits of the Connected Enterprise to the production system. The Lifecycle Services segment includes consulting services, including cybersecurity and digital transformation strategy and design and professional services, including global automation and information program and project management and delivery capabilities, and connected services.</v>
@@ -7697,16 +7696,16 @@
     <v>463.88</v>
     <v>Machinery, Equipment &amp; Components</v>
     <v>Stock</v>
-    <v>46185.990280103906</v>
+    <v>46185.990280115628</v>
     <v>230</v>
     <v>455.99020000000002</v>
-    <v>51104764053</v>
+    <v>51112553226</v>
     <v>ROCKWELL AUTOMATION, INC.</v>
     <v>ROCKWELL AUTOMATION, INC.</v>
     <v>462.33</v>
-    <v>47.7104</v>
+    <v>47.717700000000001</v>
     <v>457.59</v>
-    <v>459.27</v>
+    <v>459.34</v>
     <v>460</v>
     <v>111273900</v>
     <v>ROK</v>
@@ -7736,11 +7735,11 @@
     <v>4</v>
     <v>7.18</v>
     <v>2.77</v>
-    <v>1.0251999999999999</v>
+    <v>1.0235000000000001</v>
     <v>0</v>
-    <v>6.3490000000000005E-3</v>
+    <v>9.111000000000001E-3</v>
     <v>0</v>
-    <v>0.02</v>
+    <v>2.87E-2</v>
     <v>USD</v>
     <v>Recursion Pharmaceuticals, Inc. is a clinical-stage TechBio company decoding biology and chemistry to industrialize drug discovery. Its Recursion Operating System (OS), a platform built across diverse technologies, enables the Company to map and navigate trillions of biological and chemical relationships within the Recursion Data Universe. The Company integrates physical and digital components as iterative loops of atoms and bits, scaling wet lab biology and chemistry data organized into virtuous cycles with computational tools to rapidly translate silico hypotheses into validated insights and novel chemistry. Its clinical programs in oncology and rare diseases include REC-617, REC-1245, REC-3565 and REC-4539. Its REC-617 is an orally bioavailable, cyclin-dependent kinase 7 (CDK7) inhibitor for the treatment of advanced solid tumors. Its REV102 program targets ectonucleotide pyrophosphatase/phosphodiesterase 1 (ENPP1), an enzyme implicated in the pathogenesis of HPP.</v>
     <v>600</v>
@@ -7751,7 +7750,7 @@
     <v>3.2949999999999999</v>
     <v>Biotechnology &amp; Medical Research</v>
     <v>Stock</v>
-    <v>46185.991276885936</v>
+    <v>46185.999885057812</v>
     <v>233</v>
     <v>3.12</v>
     <v>1669201380</v>
@@ -7761,11 +7760,11 @@
     <v>0</v>
     <v>3.15</v>
     <v>3.15</v>
-    <v>3.17</v>
+    <v>3.1787000000000001</v>
     <v>529905200</v>
     <v>RXRX</v>
     <v>RECURSION PHARMACEUTICALS, INC. (XNAS:RXRX)</v>
-    <v>14836675</v>
+    <v>14837646</v>
     <v>20061798</v>
     <v>2013</v>
   </rv>
@@ -7776,25 +7775,25 @@
     <v>https://www.bing.com/financeapi/forcetrigger?t=c2kadm&amp;q=XNYS%3aS&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
   </rv>
-  <rv s="1">
+  <rv s="10">
     <v>en-GB</v>
     <v>c2kadm</v>
     <v>268435456</v>
     <v>1</v>
     <v>Powered by Refinitiv</v>
-    <v>0</v>
+    <v>19</v>
     <v>SENTINELONE, INC. (XNYS:S)</v>
     <v>2</v>
-    <v>3</v>
+    <v>20</v>
     <v>Finance</v>
     <v>4</v>
     <v>21.4</v>
     <v>11.81</v>
-    <v>0.85340000000000005</v>
-    <v>0.1</v>
-    <v>2.6259999999999999E-4</v>
-    <v>6.7749999999999998E-3</v>
-    <v>3.8999999999999998E-3</v>
+    <v>0.85019999999999996</v>
+    <v>0.09</v>
+    <v>1.8590000000000002E-3</v>
+    <v>6.0980000000000001E-3</v>
+    <v>2.76E-2</v>
     <v>USD</v>
     <v>SentinelOne, Inc. is an artificial intelligence (AI)-powered cybersecurity provider. The Company’s Singularity Platform delivers AI-powered autonomous threat prevention, detection, response, and exposure management capabilities across an organization’s endpoints, cloud workloads, and identity credentials. The Company’s Singularity platform ingests, correlates, and queries petabytes of structured and unstructured data from a myriad of ever-expanding disparate external and internal sources in real time. Its distributed AI models run both locally on every endpoint and every cloud workload, as well as on its cloud platform. The Company through PingSafe Pte. Ltd. (PingSafe), which is a cloud native application protection platform (CNAPP) to bolster its cloud security product suite. By adding PingSafe’s CNAPP to its Cloud Workload Security (CWS), it provides enterprises with a comprehensive cloud security coverage that drives security, improved posture, and autonomous protection.</v>
     <v>2700</v>
@@ -7805,21 +7804,20 @@
     <v>14.975</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46185.991668900002</v>
+    <v>46185.994088738284</v>
     <v>236</v>
     <v>14.43</v>
-    <v>5094062982</v>
+    <v>5090634945</v>
     <v>SENTINELONE, INC.</v>
     <v>SENTINELONE, INC.</v>
     <v>14.74</v>
-    <v>0</v>
     <v>14.76</v>
-    <v>14.86</v>
-    <v>14.853899999999999</v>
+    <v>14.85</v>
+    <v>14.877599999999999</v>
     <v>342803700</v>
     <v>S</v>
     <v>SENTINELONE, INC. (XNYS:S)</v>
-    <v>5463207</v>
+    <v>5463213</v>
     <v>9711161</v>
     <v>2013</v>
   </rv>
@@ -7830,21 +7828,21 @@
     <v>https://www.bing.com/financeapi/forcetrigger?t=aftlr7&amp;q=XETR%3aSAP&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
   </rv>
-  <rv s="10">
+  <rv s="11">
     <v>en-GB</v>
     <v>aftlr7</v>
     <v>268435456</v>
     <v>1</v>
     <v>Powered by Refinitiv</v>
-    <v>19</v>
+    <v>21</v>
     <v>SAP SE (XETR:SAP)</v>
     <v>2</v>
-    <v>20</v>
+    <v>22</v>
     <v>Finance</v>
-    <v>21</v>
+    <v>23</v>
     <v>271.2</v>
     <v>135.44</v>
-    <v>1.1348</v>
+    <v>1.1307</v>
     <v>0.36</v>
     <v>2.5729999999999998E-3</v>
     <v>EUR</v>
@@ -7895,11 +7893,11 @@
     <v>4</v>
     <v>107.5</v>
     <v>83.96</v>
-    <v>0.76300000000000001</v>
-    <v>2.42</v>
-    <v>2.0479999999999999E-3</v>
-    <v>2.7282999999999998E-2</v>
-    <v>0.18659999999999999</v>
+    <v>0.75870000000000004</v>
+    <v>2.4</v>
+    <v>5.488E-4</v>
+    <v>2.7057000000000001E-2</v>
+    <v>0.05</v>
     <v>USD</v>
     <v>The Charles Schwab Corporation is a savings and loan holding company. The Company, through its subsidiaries, engages in wealth management, securities brokerage, banking, asset management, custody, and financial advisory services. The Company provides financial services to individuals and institutional clients through two segments: Investor Services, and Advisor Services. The Investor Services segment provides retail brokerage, investment advisory, and banking and trust services to individual investors, and retirement plan and business services, as well as other corporate brokerage services, to businesses and their employees. The Advisor Services segment provides custodial, trading, banking and trust, and support services to independent registered investment advisors (RIAs), independent retirement advisors, and recordkeepers. Its products and services include brokerage, mutual funds, exchange-traded funds (ETFs), managed investing solutions, alternative investments, banking, and trust.</v>
     <v>33500</v>
@@ -7910,21 +7908,21 @@
     <v>92.21</v>
     <v>Investment Banking &amp; Investment Services</v>
     <v>Stock</v>
-    <v>46185.991457013282</v>
+    <v>46185.999689212498</v>
     <v>242</v>
     <v>89.25</v>
-    <v>158469981200</v>
+    <v>158435198500</v>
     <v>THE CHARLES SCHWAB CORPORATION</v>
     <v>THE CHARLES SCHWAB CORPORATION</v>
     <v>89.53</v>
-    <v>18.069299999999998</v>
+    <v>18.0654</v>
     <v>88.7</v>
-    <v>91.12</v>
-    <v>91.286600000000007</v>
+    <v>91.1</v>
+    <v>91.15</v>
     <v>1739135000</v>
     <v>SCHW</v>
     <v>THE CHARLES SCHWAB CORPORATION (XNYS:SCHW)</v>
-    <v>11399425</v>
+    <v>11399437</v>
     <v>11706660</v>
     <v>1986</v>
   </rv>
@@ -7935,13 +7933,13 @@
     <v>https://www.bing.com/financeapi/forcetrigger?t=aodipr&amp;q=XLON%3aSGE&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
   </rv>
-  <rv s="10">
+  <rv s="11">
     <v>en-GB</v>
     <v>aodipr</v>
     <v>268435456</v>
     <v>1</v>
     <v>Powered by Refinitiv</v>
-    <v>19</v>
+    <v>21</v>
     <v>THE SAGE GROUP PLC. (XLON:SGE)</v>
     <v>2</v>
     <v>29</v>
@@ -7949,7 +7947,7 @@
     <v>30</v>
     <v>1335</v>
     <v>771.66</v>
-    <v>0.37009999999999998</v>
+    <v>0.35720000000000002</v>
     <v>12.8</v>
     <v>1.5889E-2</v>
     <v>GBp</v>
@@ -8000,11 +7998,11 @@
     <v>4</v>
     <v>39.93</v>
     <v>8.18</v>
-    <v>3.3271999999999999</v>
+    <v>3.3254999999999999</v>
     <v>0.81</v>
-    <v>1.934E-3</v>
+    <v>2.1849999999999999E-3</v>
     <v>2.2626E-2</v>
-    <v>7.0800000000000002E-2</v>
+    <v>0.08</v>
     <v>USD</v>
     <v>SkyWater Technology, Inc. is an independent, pure-play technology foundry that offers advanced semiconductor development and manufacturing services. The Company’s Technology-as-a-Service (TaaS) model leverages a foundation of proprietary technology, engineering know-how capabilities, and microelectronics manufacturing capacity to co-develop process technology intellectual property (IP) with its customers that enable disruptive concepts through its Advanced Technology Services (ATS) for diverse microelectronics (integrated circuits (ICs)) and related micro- and nanotechnology applications. In addition to differentiated technology development services, it supports customers with volume production of ICs for high-growth markets through its Wafer Services. Its Wafer Services include the manufacture of silicon-based analog and mixed-signal ICs for its end markets. Through its ATS model, it specializes in co-creating advanced solutions with its customers that directly serve its end markets.</v>
     <v>1551</v>
@@ -8015,7 +8013,7 @@
     <v>36.700000000000003</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46185.986547279688</v>
+    <v>46185.994230705466</v>
     <v>248</v>
     <v>34.92</v>
     <v>1801380406</v>
@@ -8025,11 +8023,11 @@
     <v>15.345599999999999</v>
     <v>35.799999999999997</v>
     <v>36.61</v>
-    <v>36.680799999999998</v>
+    <v>36.69</v>
     <v>49204600</v>
     <v>SKYT</v>
     <v>SKYWATER TECHNOLOGY, INC. (XNAS:SKYT)</v>
-    <v>702663</v>
+    <v>702723</v>
     <v>1119939</v>
     <v>2016</v>
   </rv>
@@ -8054,11 +8052,11 @@
     <v>4</v>
     <v>62.357999999999997</v>
     <v>19.48</v>
-    <v>1.9565999999999999</v>
+    <v>1.9545999999999999</v>
     <v>-1.51</v>
-    <v>1.3453999999999999E-2</v>
+    <v>1.2803999999999999E-2</v>
     <v>-4.7232000000000003E-2</v>
-    <v>0.4098</v>
+    <v>0.39</v>
     <v>USD</v>
     <v>Super Micro Computer, Inc. is an application-optimized Total IT solutions provider including server, artificial intelligence (AI) systems, storage, Internet of Things (IoT) devices, switches, software, and support services. Total IT Solutions include complete servers, storage systems, modular blade servers, workstations, full-rack scale solutions, networking devices, server sub-systems, and server management. Its products are designed and manufactured in-house (in the United States, Taiwan, and the Netherlands). The Company's portfolio of Server Building Block Solutions allows customers to optimize for their exact workload and application by selecting from a broad family of systems built from the Company's flexible and reusable building blocks that support a comprehensive set of form factors, processors, memory, GPUs, storage, networking, power, and cooling solutions (air-conditioned, free air cooling or liquid cooling).</v>
     <v>6238</v>
@@ -8069,7 +8067,7 @@
     <v>31.81</v>
     <v>Computers, Phones &amp; Household Electronics</v>
     <v>Stock</v>
-    <v>46185.991801260934</v>
+    <v>46185.999980115623</v>
     <v>251</v>
     <v>29.45</v>
     <v>18319207510</v>
@@ -8079,11 +8077,11 @@
     <v>17.420000000000002</v>
     <v>31.97</v>
     <v>30.46</v>
-    <v>30.869800000000001</v>
+    <v>30.85</v>
     <v>601418500</v>
     <v>SMCI</v>
     <v>SUPER MICRO COMPUTER, INC. (XNAS:SMCI)</v>
-    <v>84824220</v>
+    <v>84854716</v>
     <v>57555354</v>
     <v>2006</v>
   </rv>
@@ -8105,21 +8103,21 @@
     <v>16</v>
     <v>17</v>
     <v>Finance</v>
-    <v>18</v>
+    <v>26</v>
     <v>642.77</v>
     <v>256.05</v>
     <v>1.5568</v>
     <v>10.51</v>
-    <v>2.6290000000000003E-3</v>
+    <v>3.6129999999999999E-3</v>
     <v>1.7245E-2</v>
-    <v>1.63</v>
+    <v>2.2400000000000002</v>
     <v>USD</v>
     <v>Nasdaq Stock Market</v>
     <v>XNAS</v>
     <v>3.4999999999999996E-3</v>
     <v>624.62</v>
     <v>ETF</v>
-    <v>46185.991757557815</v>
+    <v>46185.999936411717</v>
     <v>254</v>
     <v>602.21</v>
     <v>67822489502.050003</v>
@@ -8127,10 +8125,10 @@
     <v>607.95000000000005</v>
     <v>609.45000000000005</v>
     <v>619.96</v>
-    <v>621.59</v>
+    <v>622.20000000000005</v>
     <v>SMH</v>
     <v>VanEck:Semiconductor (XNAS:SMH)</v>
-    <v>8985180</v>
+    <v>8986716</v>
     <v>11391225</v>
   </rv>
   <rv s="2">
@@ -8140,25 +8138,25 @@
     <v>https://www.bing.com/financeapi/forcetrigger?t=bx1rdm&amp;q=XNYS%3aSMR&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
   </rv>
-  <rv s="12">
+  <rv s="10">
     <v>en-GB</v>
     <v>bx1rdm</v>
     <v>268435456</v>
     <v>1</v>
     <v>Powered by Refinitiv</v>
-    <v>25</v>
+    <v>19</v>
     <v>NUSCALE POWER CORPORATION (XNYS:SMR)</v>
     <v>2</v>
-    <v>26</v>
+    <v>20</v>
     <v>Finance</v>
     <v>4</v>
     <v>57.42</v>
     <v>8.85</v>
-    <v>2.2753000000000001</v>
-    <v>0.34</v>
-    <v>1.2133E-2</v>
-    <v>3.5527999999999997E-2</v>
-    <v>0.12</v>
+    <v>2.2639999999999998</v>
+    <v>0.32</v>
+    <v>1.6177999999999998E-2</v>
+    <v>3.3437999999999996E-2</v>
+    <v>0.16</v>
     <v>USD</v>
     <v>NuScale Power Corporation is a provider of proprietary advanced small modular reactor (SMR) nuclear technology. The NuScale Power Module, the Company's SMR technology, is a small pressurized water reactor that can generate approximately 77 megawatts of electricity (MWe) or 250 megawatts thermal (gross) and can be scaled to meet customer needs through an array of flexible configurations of up to 924 MWe (12 modules) of output. In addition to the sale of NPMs, it offers a diversified suite of services throughout the development and operating life of the power plant. The Company's suite of services is planned to include licensing support, testing, training, fuel supply services and program management, among others. It serves a range of customers consisting of domestic and international governments, utilities, state-owned enterprises and technology and industrial companies in need of carbon-free, reliable energy.</v>
     <v>428</v>
@@ -8169,20 +8167,20 @@
     <v>10.295</v>
     <v>Electrical Utilities &amp; IPPs</v>
     <v>Stock</v>
-    <v>46185.991834131251</v>
+    <v>46185.999928610938</v>
     <v>257</v>
     <v>9.6600999999999999</v>
-    <v>3621918692</v>
+    <v>3614609068</v>
     <v>NUSCALE POWER CORPORATION</v>
     <v>NUSCALE POWER CORPORATION</v>
     <v>9.7949999999999999</v>
     <v>9.57</v>
-    <v>9.91</v>
-    <v>10.01</v>
+    <v>9.89</v>
+    <v>10.050000000000001</v>
     <v>365481200</v>
     <v>SMR</v>
     <v>NUSCALE POWER CORPORATION (XNYS:SMR)</v>
-    <v>31156457</v>
+    <v>31174378</v>
     <v>35875519</v>
     <v>2022</v>
   </rv>
@@ -8205,9 +8203,9 @@
     <v>39.44</v>
     <v>2.7989999999999999</v>
     <v>98.59</v>
-    <v>6.5049999999999995E-3</v>
+    <v>7.4999999999999997E-3</v>
     <v>5.2398999999999994E-2</v>
-    <v>12.88</v>
+    <v>14.85</v>
     <v>USD</v>
     <v>SanDisk Corporation is a developer, manufacturer and provider of data storage devices and solutions based on NAND flash technology and has consumer brands and franchises globally. The Company's solutions include a range of solid state drives (SSDs) embedded products, removable cards, universal serial bus (USB) drives, and wafers and components. Its broad portfolio of technology and products addresses multiple end markets of Datacenter, Edge and Consumer. Its Datacenter end market is composed primarily of products for public or private cloud environments and enterprise customers. The Company, through the Edge end market, provides original equipment manufacturer and channel customers a broad array of high-performance flash solutions across personal computer, mobile, gaming, automotive, virtual reality headsets, at-home entertainment, and industrial spaces. The Company serves the Consumer end market with a broad range of retail and other end-user products.</v>
     <v>11000</v>
@@ -8218,7 +8216,7 @@
     <v>2021.65</v>
     <v>Computers, Phones &amp; Household Electronics</v>
     <v>Stock</v>
-    <v>46185.991863008596</v>
+    <v>46185.999992870311</v>
     <v>1865.11</v>
     <v>293232612980</v>
     <v>SANDISK CORPORATION</v>
@@ -8227,11 +8225,11 @@
     <v>66.518299999999996</v>
     <v>1881.51</v>
     <v>1980.1</v>
-    <v>1992.98</v>
+    <v>1994.95</v>
     <v>148089800</v>
     <v>SNDK</v>
     <v>SANDISK CORPORATION (XNAS:SNDK)</v>
-    <v>11954335</v>
+    <v>11964511</v>
     <v>12405461</v>
     <v>2024</v>
   </rv>
@@ -8242,25 +8240,25 @@
     <v>https://www.bing.com/financeapi/forcetrigger?t=bvlqa2&amp;q=XNYS%3aSNOW&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
   </rv>
-  <rv s="12">
+  <rv s="10">
     <v>en-GB</v>
     <v>bvlqa2</v>
     <v>268435456</v>
     <v>1</v>
     <v>Powered by Refinitiv</v>
-    <v>25</v>
+    <v>19</v>
     <v>SNOWFLAKE INC. (XNYS:SNOW)</v>
     <v>2</v>
-    <v>26</v>
+    <v>20</v>
     <v>Finance</v>
     <v>4</v>
     <v>284.99</v>
     <v>118.3</v>
-    <v>1.3620000000000001</v>
-    <v>-7.7450000000000001</v>
-    <v>1.2889999999999998E-3</v>
-    <v>-3.2217999999999997E-2</v>
-    <v>0.3</v>
+    <v>1.3697999999999999</v>
+    <v>-7.61</v>
+    <v>2.2339999999999999E-3</v>
+    <v>-3.1657000000000005E-2</v>
+    <v>0.52</v>
     <v>USD</v>
     <v>Snowflake Inc. is an artificial intelligence (AI) data cloud company. The Company provides a platform which powers the AI data cloud, enabling customers to consolidate data into a single source of truth to drive insights, apply AI to solve business problems, build data applications, and share data and data products. Its cloud-native architecture includes three independently scalable but logically integrated layers across storage, compute, and cloud services. The storage layer ingests massive amounts and varieties of structured, semi-structured, and unstructured data. The compute layer provides dedicated resources to enable users to simultaneously access common data sets for many use cases with minimal latency. The cloud services layer enables users to securely use AI within applications, tools, and processes. Its platform supports a wide range of product categories for customers’ business objectives, including analytics, data engineering, AI, applications and collaboration.</v>
     <v>9060</v>
@@ -8271,7 +8269,7 @@
     <v>242.79990000000001</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46185.991349571093</v>
+    <v>46185.999389640623</v>
     <v>262</v>
     <v>230.44</v>
     <v>60745624254</v>
@@ -8279,12 +8277,12 @@
     <v>SNOWFLAKE INC.</v>
     <v>240.495</v>
     <v>240.39</v>
-    <v>232.64500000000001</v>
-    <v>233.08</v>
+    <v>232.78</v>
+    <v>233.3</v>
     <v>346600000</v>
     <v>SNOW</v>
     <v>SNOWFLAKE INC. (XNYS:SNOW)</v>
-    <v>7707159</v>
+    <v>7707338</v>
     <v>10670297</v>
     <v>2012</v>
   </rv>
@@ -8309,11 +8307,11 @@
     <v>4</v>
     <v>651.73</v>
     <v>376.18</v>
-    <v>1.2169000000000001</v>
+    <v>1.2191000000000001</v>
     <v>-2.4</v>
-    <v>2.4460000000000003E-3</v>
+    <v>2.8860000000000001E-3</v>
     <v>-5.2599999999999999E-3</v>
-    <v>1.1100000000000001</v>
+    <v>1.31</v>
     <v>USD</v>
     <v>Synopsys, Inc. is engaged in providing engineering solutions from silicon to systems, enabling customers to innovate artificial intelligence (AI)-powered products. It delivers silicon design, intellectual property (IP), simulation and analysis solutions, and design services. It supplies mission-critical electronic design automation (EDA) software that engineers use to design and test integrated circuits (ICs). Its Design Automation segment includes its silicon design, verification products and services, Ansys products, system integration products and services, digital, custom and field programmable gate array integrated circuit design software, verification software and hardware products, manufacturing software products and others. Its Design IP segment's portfolio includes logic libraries, embedded memories, interface IP, security IP, and subsystems that serve companies in the semiconductor and electronics industries.</v>
     <v>28000</v>
@@ -8324,21 +8322,21 @@
     <v>461.09</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46185.990671284373</v>
+    <v>46185.999985242968</v>
     <v>265</v>
     <v>445.01</v>
     <v>86910539477</v>
     <v>SYNOPSYS, INC.</v>
     <v>SYNOPSYS, INC.</v>
     <v>457.08499999999998</v>
-    <v>105.1913</v>
+    <v>105.7473</v>
     <v>456.29</v>
     <v>453.89</v>
-    <v>455</v>
+    <v>455.2</v>
     <v>191479300</v>
     <v>SNPS</v>
     <v>SYNOPSYS, INC. (XNAS:SNPS)</v>
-    <v>1289580</v>
+    <v>1289661</v>
     <v>1950214</v>
     <v>1987</v>
   </rv>
@@ -8363,11 +8361,11 @@
     <v>4</v>
     <v>22.17</v>
     <v>5.83</v>
-    <v>2.8155000000000001</v>
+    <v>2.8134000000000001</v>
     <v>-0.1</v>
-    <v>8.6960000000000006E-3</v>
+    <v>9.4199999999999996E-3</v>
     <v>-1.4286E-2</v>
-    <v>0.06</v>
+    <v>6.5000000000000002E-2</v>
     <v>USD</v>
     <v>SoundHound AI, Inc. is engaged in conversational intelligence, offering voice and conversational artificial intelligence (AI) solutions that let businesses offer experiences to their customers. Through its proprietary technology, its voice AI delivers speed and accuracy in numerous languages to product creators and service providers across retail, financial services, healthcare, automotive, smart devices, and restaurants via AI-driven products, such as Smart Answering, Smart Ordering, Dynamic Drive Thru, and Amelia AI Agents. Along with SoundHound Chat AI, a voice assistant with integrated Generative AI, it powers various products and services, and processes billions of interactions each year for businesses. Its developer platform, Houndify, is an open-access platform that allows developers to leverage its Voice AI technology and a library of over 100 content domains, including commonly used domains for points of interest, weather, flight status, sports and more.</v>
     <v>954</v>
@@ -8378,7 +8376,7 @@
     <v>7.1486000000000001</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46185.991871145314</v>
+    <v>46185.999918807815</v>
     <v>268</v>
     <v>6.8400999999999996</v>
     <v>2986110240</v>
@@ -8388,11 +8386,11 @@
     <v>0</v>
     <v>7</v>
     <v>6.9</v>
-    <v>6.96</v>
+    <v>6.9649999999999999</v>
     <v>432769600</v>
     <v>SOUN</v>
     <v>SOUNDHOUND AI, INC. (XNAS:SOUN)</v>
-    <v>26041115</v>
+    <v>26051484</v>
     <v>27892730</v>
     <v>2020</v>
   </rv>
@@ -8414,21 +8412,21 @@
     <v>16</v>
     <v>17</v>
     <v>Finance</v>
-    <v>18</v>
+    <v>26</v>
     <v>618.84</v>
     <v>220.3</v>
     <v>1.7036</v>
     <v>9.32</v>
-    <v>4.4609999999999997E-3</v>
+    <v>6.6749999999999995E-3</v>
     <v>1.5879000000000001E-2</v>
-    <v>2.66</v>
+    <v>3.98</v>
     <v>USD</v>
     <v>Nasdaq Stock Market</v>
     <v>XNAS</v>
     <v>3.4000000000000002E-3</v>
     <v>602.69000000000005</v>
     <v>ETF</v>
-    <v>46185.991859606249</v>
+    <v>46185.999884478908</v>
     <v>271</v>
     <v>578.53</v>
     <v>38373488686.160004</v>
@@ -8436,10 +8434,10 @@
     <v>584.11</v>
     <v>586.92999999999995</v>
     <v>596.25</v>
-    <v>598.91</v>
+    <v>600.23</v>
     <v>SOXX</v>
     <v>iShares:Semiconductor (XNAS:SOXX)</v>
-    <v>9943606</v>
+    <v>9947173</v>
     <v>10620406</v>
   </rv>
   <rv s="2">
@@ -8460,13 +8458,13 @@
     <v>16</v>
     <v>17</v>
     <v>Finance</v>
-    <v>18</v>
+    <v>26</v>
     <v>760.4</v>
     <v>591.89</v>
     <v>0.99870000000000003</v>
-    <v>4.01</v>
+    <v>3.99</v>
     <v>8.2239999999999993E-4</v>
-    <v>5.4349999999999997E-3</v>
+    <v>5.4079999999999996E-3</v>
     <v>0.61</v>
     <v>USD</v>
     <v>NYSE Arca</v>
@@ -8474,18 +8472,18 @@
     <v>9.4499999999999998E-4</v>
     <v>744.44</v>
     <v>ETF</v>
-    <v>46185.991846469529</v>
+    <v>46186.000000161715</v>
     <v>274</v>
     <v>735.03</v>
     <v>783796407176.76001</v>
     <v>State Street SPDR S&amp;P500</v>
     <v>740.71</v>
     <v>737.76</v>
-    <v>741.77</v>
+    <v>741.75</v>
     <v>742.36</v>
     <v>SPY</v>
     <v>State Street SPDR S&amp;P500 (ARCX:SPY)</v>
-    <v>57067321</v>
+    <v>57079533</v>
     <v>50495657</v>
   </rv>
   <rv s="2">
@@ -8506,14 +8504,14 @@
     <v>2</v>
     <v>3</v>
     <v>Finance</v>
-    <v>24</v>
+    <v>4</v>
     <v>90.9</v>
     <v>51.93</v>
-    <v>1.4834000000000001</v>
+    <v>1.4812000000000001</v>
     <v>1.24</v>
-    <v>-2.7040000000000001E-4</v>
+    <v>2.7040000000000001E-4</v>
     <v>1.7049000000000002E-2</v>
-    <v>-0.02</v>
+    <v>0.02</v>
     <v>USD</v>
     <v>Skyworks Solutions, Inc. provides wireless networking services. The Company’s analog and mixed-signal semiconductors are connecting people, places, and things, spanning a number of new applications within the aerospace, automotive, broadband, cellular infrastructure, connected home, defense, entertainment and gaming, industrial, medical, smartphone, tablet, and wearable markets. It operates engineering, manufacturing, sales, and service facilities throughout Asia, Europe, and North America. The Company offers a range of products, such as Amplifiers, Attenuators, Diodes, Audio And Radio, Clocks And Timing, Front-End Modules, Isolation, Modems And DAAs, Optocouplers, Power Management, Power Over Ethernet, RF Passives, Television (TV) And Video, Switches, and Voice. Its engineering, marketing, operations, sales, and support facilities are located throughout Asia, Europe, and North America.</v>
     <v>10000</v>
@@ -8524,21 +8522,21 @@
     <v>74.19</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46185.980195659373</v>
+    <v>46185.99791788125</v>
     <v>277</v>
     <v>71.27</v>
     <v>11125524423</v>
     <v>SKYWORKS SOLUTIONS, INC.</v>
     <v>SKYWORKS SOLUTIONS, INC.</v>
     <v>72.349999999999994</v>
-    <v>29.223299999999998</v>
+    <v>28.733000000000001</v>
     <v>72.73</v>
     <v>73.97</v>
-    <v>73.95</v>
+    <v>73.989999999999995</v>
     <v>150405900</v>
     <v>SWKS</v>
     <v>SKYWORKS SOLUTIONS, INC. (XNAS:SWKS)</v>
-    <v>2262221</v>
+    <v>2262474</v>
     <v>5327334</v>
     <v>2002</v>
   </rv>
@@ -8563,11 +8561,11 @@
     <v>4</v>
     <v>87.88</v>
     <v>27.26</v>
-    <v>1.9427000000000001</v>
+    <v>1.9490000000000001</v>
     <v>-1.2</v>
-    <v>1.1050000000000001E-3</v>
+    <v>8.8880000000000001E-3</v>
     <v>-2.8018000000000001E-2</v>
-    <v>4.5999999999999999E-2</v>
+    <v>0.37</v>
     <v>USD</v>
     <v>Symbotic Inc. is an automation technology company, which focuses on reimagining the supply chain with its end-to-end, artificial intelligence-powered robotic and software platform. It is engaged in developing, commercializing, and deploying innovative and comprehensive technology solutions that improve supply chain operations. The Company automates the processing of pallets, cases and individual items in warehouses. Its systems enhance operations at the front end of the supply chain and therefore benefit all supply partners further down the chain, irrespective of fulfillment strategy. Its robotic-based automation systems, which include hardware and essential software, move, store and sort cases and reach in warehouses. Its systems are operational in a number of retailers, including Walmart, wholesale distributors, including C&amp;S Wholesale Grocers, and are being deployed in GreenBox Systems LLC, which is doing business as Exol (Exol), its warehouse-as-a-service joint venture.</v>
     <v>2000</v>
@@ -8578,7 +8576,7 @@
     <v>43.265000000000001</v>
     <v>Machinery, Equipment &amp; Components</v>
     <v>Stock</v>
-    <v>46185.989600717185</v>
+    <v>46185.999824953127</v>
     <v>280</v>
     <v>41.56</v>
     <v>25090684084</v>
@@ -8588,11 +8586,11 @@
     <v>0</v>
     <v>42.83</v>
     <v>41.63</v>
-    <v>41.676000000000002</v>
+    <v>42</v>
     <v>602706800</v>
     <v>SYM</v>
     <v>SYMBOTIC INC. (XNAS:SYM)</v>
-    <v>1716476</v>
+    <v>1716539</v>
     <v>2643575</v>
     <v>2022</v>
   </rv>
@@ -8615,9 +8613,9 @@
     <v>41.73</v>
     <v>3.121</v>
     <v>-1.77</v>
-    <v>1.673E-3</v>
+    <v>4.1820000000000003E-4</v>
     <v>-3.5693000000000003E-2</v>
-    <v>0.08</v>
+    <v>0.02</v>
     <v>USD</v>
     <v>Tempus AI, Inc. is a technology company advancing precision medicine through the practical application of artificial intelligence in healthcare. It offers AI-enabled precision medicine solutions to physicians to deliver personalized patient care and, in parallel, facilitates discovery, development and delivery of optimal therapeutics. It provides three product lines: Genomics, Data and artificial intelligence applications (AI). The Genomics product line leverages its laboratories to provide next generation sequencing (NGS) diagnostics, polymerase chain reaction, profiling, molecular genotyping and other anatomic and molecular pathology testing. The data generated in its lab or ingested into its platform is structured and de-identified, prior to commercialization. Its AI Applications is focused on developing and providing diagnostics that are algorithmic in nature, implementing new software as a medical device, and building and deploying clinical decision support tools.</v>
     <v>3800</v>
@@ -8628,7 +8626,7 @@
     <v>49.98</v>
     <v>Biotechnology &amp; Medical Research</v>
     <v>Stock</v>
-    <v>46185.991180450779</v>
+    <v>46185.999885914061</v>
     <v>47.12</v>
     <v>8586788736</v>
     <v>TEMPUS AI, INC.</v>
@@ -8637,11 +8635,11 @@
     <v>0</v>
     <v>49.59</v>
     <v>47.82</v>
-    <v>47.9</v>
+    <v>47.84</v>
     <v>179564800</v>
     <v>TEM</v>
     <v>TEMPUS AI, INC. (XNAS:TEM)</v>
-    <v>6119728</v>
+    <v>6122843</v>
     <v>7248652</v>
     <v>2025</v>
   </rv>
@@ -8666,11 +8664,11 @@
     <v>4</v>
     <v>422.11</v>
     <v>83</v>
-    <v>1.7786999999999999</v>
+    <v>1.7688999999999999</v>
     <v>21.8</v>
-    <v>9.1269999999999997E-3</v>
+    <v>8.1599999999999989E-3</v>
     <v>5.7158E-2</v>
-    <v>3.68</v>
+    <v>3.29</v>
     <v>USD</v>
     <v>Teradyne, Inc. is a global supplier of automated test equipment and robotics solutions. It designs, develops, manufactures and sells automated test systems and robotics products. Its segment includes Semiconductor Test, Robotics, and Product Test. The Semiconductor Test segment includes operations related to the design, manufacturing and marketing of semiconductor test products and services, inclusive of storage and system level test products. The Robotics segment includes operations related to the design, manufacturing and marketing of collaborative robotic arms and autonomous mobile robots. The Product Test segment includes operations related to the design, manufacturing and marketing of products and services for defense/aerospace test, circuit-board test, wireless test systems, and silicon photonics testing. Its offerings also include defense/aerospace test instrumentation and systems, circuit-board test and inspection (production board test) systems, and wireless test systems.</v>
     <v>6600</v>
@@ -8681,21 +8679,21 @@
     <v>408</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46185.991301365626</v>
+    <v>46185.999523448438</v>
     <v>285</v>
     <v>380</v>
     <v>63117815040</v>
     <v>TERADYNE, INC.</v>
     <v>TERADYNE, INC.</v>
     <v>381.94</v>
-    <v>74.623800000000003</v>
+    <v>70.589799999999997</v>
     <v>381.4</v>
     <v>403.2</v>
-    <v>406.88</v>
+    <v>406.49</v>
     <v>156542200</v>
     <v>TER</v>
     <v>TERADYNE, INC. (XNAS:TER)</v>
-    <v>3326656</v>
+    <v>3326868</v>
     <v>3827115</v>
     <v>1960</v>
   </rv>
@@ -8720,11 +8718,11 @@
     <v>4</v>
     <v>498.83</v>
     <v>288.77010000000001</v>
-    <v>1.8110999999999999</v>
+    <v>1.8073999999999999</v>
     <v>7.28</v>
-    <v>-1.206E-3</v>
+    <v>-9.1040000000000001E-4</v>
     <v>1.8239000000000002E-2</v>
-    <v>-0.49</v>
+    <v>-0.37</v>
     <v>USD</v>
     <v>Tesla, Inc. designs, develops, manufactures, sells and leases high-performance fully electric vehicles and energy generation and storage systems, and offers services related to its products. Its segments include automotive, and energy generation and storage. The automotive segment includes the design, development, manufacturing, sales and leasing of high-performance fully electric vehicles, and sales of automotive regulatory credits. It also includes sales of used vehicles, non-warranty maintenance services and collisions, part sales, paid supercharging, insurance services revenue and retail merchandise sales. The energy generation and storage segment include the design, manufacture, installation, sales and leasing of solar energy generation and energy storage products and related services and sales of solar energy systems incentives. Its consumer vehicles include the Model 3, Y, S, X and Cybertruck. Its lithium-ion battery energy storage products include Powerwall and Megapack.</v>
     <v>134785</v>
@@ -8735,21 +8733,21 @@
     <v>406.68</v>
     <v>Automobiles &amp; Auto Parts</v>
     <v>Stock</v>
-    <v>46185.991885253905</v>
+    <v>46185.999977117972</v>
     <v>288</v>
     <v>386.76</v>
     <v>1526438905320</v>
     <v>TESLA, INC.</v>
     <v>TESLA, INC.</v>
     <v>399.49</v>
-    <v>371.47430000000003</v>
+    <v>364.83370000000002</v>
     <v>399.15</v>
     <v>406.43</v>
-    <v>405.94</v>
+    <v>406.06</v>
     <v>3755724000</v>
     <v>TSLA</v>
     <v>TESLA, INC. (XNAS:TSLA)</v>
-    <v>63629525</v>
+    <v>63652286</v>
     <v>50693491</v>
     <v>2024</v>
   </rv>
@@ -8774,11 +8772,11 @@
     <v>4</v>
     <v>450.16359999999997</v>
     <v>206.20150000000001</v>
-    <v>1.3855</v>
-    <v>2.75</v>
-    <v>2.996E-3</v>
-    <v>6.5310000000000003E-3</v>
-    <v>1.27</v>
+    <v>1.3866000000000001</v>
+    <v>2.86</v>
+    <v>4.411E-3</v>
+    <v>6.7920000000000003E-3</v>
+    <v>1.87</v>
     <v>USD</v>
     <v>Taiwan Semiconductor Manufacturing Co Ltd is a Taiwan-based integrated circuit foundry service provider. The Company is primarily engaged in integrated circuit manufacturing services. It offers advanced process technologies, specialised process solutions, advanced photomask and silicon stacking, and packaging-related technologies, while supporting a comprehensive design ecosystem. The Company's products serve diverse electronic sectors including artificial intelligence, high-performance computing, wired and wireless communications, automotive and industrial equipment, personal computing, information applications, consumer electronics, smart internet of things, and wearable devices.</v>
     <v>52045</v>
@@ -8789,21 +8787,21 @@
     <v>426.94</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46185.991411388284</v>
+    <v>46185.999904756252</v>
     <v>291</v>
     <v>417.21</v>
-    <v>2198131410680</v>
+    <v>2198701922820</v>
     <v>Taiwan Semiconductor Manufacturing Company Limited</v>
     <v>Taiwan Semiconductor Manufacturing Company Limited</v>
     <v>420.05</v>
-    <v>35.858899999999998</v>
+    <v>35.868200000000002</v>
     <v>421.07</v>
-    <v>423.82</v>
-    <v>425.2</v>
+    <v>423.93</v>
+    <v>425.8</v>
     <v>5186474000</v>
     <v>TSM</v>
     <v>Taiwan Semiconductor Manufacturing Company Limited (XNYS:TSM)</v>
-    <v>10359581</v>
+    <v>10362465</v>
     <v>13369706</v>
     <v>1987</v>
   </rv>
@@ -8825,14 +8823,14 @@
     <v>2</v>
     <v>3</v>
     <v>Finance</v>
-    <v>24</v>
+    <v>4</v>
     <v>238.47989999999999</v>
     <v>91.84</v>
-    <v>1.3432999999999999</v>
+    <v>1.3532</v>
     <v>-2.54</v>
-    <v>9.7509999999999993E-3</v>
+    <v>-1.47E-4</v>
     <v>-1.2293E-2</v>
-    <v>1.99</v>
+    <v>-0.03</v>
     <v>USD</v>
     <v>Twilio Inc. provides a customer engagement platform to build direct, personalized relationships with their customers everywhere in the world. Its platform provides developers with tools to build, scale, and deploy real-time communications within software applications. Its segments include Twilio Communications (Communications) and Twilio Segment (Segment). The Communications segment consists of a variety of application programming interfaces (APIs) and software solutions to optimize communications between its customers and their end users. Its key offerings in its Communications segment include Messaging, Voice, Email (includes Marketing Campaigns), Flex and User Authentication and Identity. Its Twilio Flex is a digital engagement center for the entire customer journey. Twilio Segment is a customer data platform that provides businesses with the tools to harness the power of contextual data by unifying real-time information collected throughout each customer’s journey into a profile.</v>
     <v>5558</v>
@@ -8843,21 +8841,21 @@
     <v>206.62</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46185.969372731248</v>
+    <v>46185.99614842578</v>
     <v>294</v>
     <v>198.22</v>
     <v>30974017512</v>
     <v>TWILIO INC.</v>
     <v>TWILIO INC.</v>
     <v>205.89</v>
-    <v>317.23919999999998</v>
+    <v>321.18259999999998</v>
     <v>206.62</v>
     <v>204.08</v>
-    <v>206.07</v>
+    <v>204.05</v>
     <v>151773900</v>
     <v>TWLO</v>
     <v>TWILIO INC. (XNYS:TWLO)</v>
-    <v>1567840</v>
+    <v>1567846</v>
     <v>2905645</v>
     <v>2008</v>
   </rv>
@@ -8882,11 +8880,11 @@
     <v>4</v>
     <v>379.935</v>
     <v>108.81</v>
-    <v>2.0487000000000002</v>
-    <v>4.83</v>
-    <v>6.0419999999999996E-3</v>
-    <v>1.6215E-2</v>
-    <v>1.83</v>
+    <v>2.0455999999999999</v>
+    <v>4.99</v>
+    <v>6.1580000000000003E-3</v>
+    <v>1.6752E-2</v>
+    <v>1.865</v>
     <v>USD</v>
     <v>Vertiv Holdings Co. provides mission-critical digital infrastructure technologies and lifecycle services primarily for data centers, communication networks, and commercial and industrial environments. The Company operates in three business segments: the Americas; Asia Pacific, and Europe, Middle East &amp; Africa. The Company's offerings include alternate current (AC) and direct current (DC) power management, thermal management, low/medium voltage switchgear, busbar, air cooled and liquid cooled thermal management products, integrated modular solutions, racks, single phase UPS, rack power distribution, rack thermal systems, configurable integrated solutions, energy storage solutions, hardware, software for managing IT equipment, management systems for monitoring and controlling digital infrastructure, and services. It also provides preventative maintenance, acceptance testing, engineering and consulting, remote monitoring, training, spare parts, specialized fluid management, and others.</v>
     <v>34000</v>
@@ -8897,21 +8895,21 @@
     <v>305.19</v>
     <v>Machinery, Equipment &amp; Components</v>
     <v>Stock</v>
-    <v>46185.991873714847</v>
+    <v>46185.999953517967</v>
     <v>297</v>
     <v>295.10000000000002</v>
-    <v>116273574847</v>
+    <v>116335032256</v>
     <v>VERTIV HOLDINGS CO</v>
     <v>VERTIV HOLDINGS CO</v>
     <v>303.48</v>
-    <v>76.000500000000002</v>
+    <v>74.787499999999994</v>
     <v>297.88</v>
-    <v>302.70999999999998</v>
-    <v>304.7</v>
+    <v>302.87</v>
+    <v>304.73500000000001</v>
     <v>384108800</v>
     <v>VRT</v>
     <v>VERTIV HOLDINGS CO (XNYS:VRT)</v>
-    <v>4956746</v>
+    <v>4958116</v>
     <v>6028136</v>
     <v>2016</v>
   </rv>
@@ -8936,11 +8934,11 @@
     <v>4</v>
     <v>253.5377</v>
     <v>110.36</v>
-    <v>1.0992</v>
+    <v>1.0974999999999999</v>
     <v>0.27</v>
-    <v>2.0639999999999999E-3</v>
+    <v>1.6819999999999998E-2</v>
     <v>2.068E-3</v>
-    <v>0.27</v>
+    <v>2.2000000000000002</v>
     <v>USD</v>
     <v>Workday, Inc. is an enterprise artificial intelligence (AI) platform for managing people, money, and agents. The Company provides organizations with cloud solutions powered by artificial intelligence (AI) to solve business challenges, including supporting and empowering the workforce, managing finances and spending. It offers a suite of cloud-based enterprise solutions that address the needs of the C-suite on a platform designed to be open, extensible, and configurable, allowing integration with other applications and the ability for customers and partners to build custom applications. It offers Workday Build, which is an open developer platform that provides customers and partners with the ability to create and share AI-powered solutions. It serves financial services, government, healthcare, higher education, hospitality, manufacturing, professional and business services, retail, technology and media, and transportation.</v>
     <v>20834</v>
@@ -8951,21 +8949,21 @@
     <v>131.03</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46185.990720265625</v>
+    <v>46185.999948529687</v>
     <v>300</v>
     <v>125.015</v>
     <v>32307600000</v>
     <v>WORKDAY, INC.</v>
     <v>WORKDAY, INC.</v>
     <v>129.63</v>
-    <v>40.830300000000001</v>
+    <v>40.746099999999998</v>
     <v>130.53</v>
     <v>130.80000000000001</v>
-    <v>131.07</v>
+    <v>133</v>
     <v>247000000</v>
     <v>WDAY</v>
     <v>WORKDAY, INC. (XNAS:WDAY)</v>
-    <v>6671416</v>
+    <v>6671469</v>
     <v>5445303</v>
     <v>2012</v>
   </rv>
@@ -8990,11 +8988,11 @@
     <v>4</v>
     <v>336.99</v>
     <v>114.625</v>
-    <v>0.98109999999999997</v>
+    <v>0.9738</v>
     <v>3.41</v>
-    <v>-1.699E-3</v>
+    <v>-2.934E-3</v>
     <v>2.7040000000000002E-2</v>
-    <v>-0.22</v>
+    <v>-0.38</v>
     <v>USD</v>
     <v>Zscaler, Inc. is a cloud security company. The Company has developed a platform incorporating core security functionalities needed to enable fast and secure access to cloud resources based on identity, context and an organization's policies. Its Zscaler Zero Trust Exchange is a cloud-native platform that securely connects users, devices, applications and workloads, including artificial intelligence (AI) agents, without relying on hub-and-spoke network architecture and firewall-centric security. It delivers its solutions using a software-as-a-service (SaaS) business model and sells subscriptions to customers to access its cloud platform, together with related support services. Its services include Zscaler Internet Access (ZIA), Zscaler Private Access (ZPA), and Zscaler Digital Experience (ZDX). ZIA provides secure access to externally managed applications, including SaaS applications and internet destinations, regardless of device, location or network.</v>
     <v>7923</v>
@@ -9005,7 +9003,7 @@
     <v>130</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46185.991325000003</v>
+    <v>46185.999896620313</v>
     <v>303</v>
     <v>119.5</v>
     <v>20944614440</v>
@@ -9015,11 +9013,11 @@
     <v>0</v>
     <v>126.11</v>
     <v>129.52000000000001</v>
-    <v>129.30000000000001</v>
+    <v>129.13999999999999</v>
     <v>161709500</v>
     <v>ZS</v>
     <v>ZSCALER, INC. (XNAS:ZS)</v>
-    <v>4759379</v>
+    <v>4760338</v>
     <v>6638580</v>
     <v>2007</v>
   </rv>
@@ -9323,6 +9321,52 @@
     <k n="52 week low"/>
     <k n="Beta"/>
     <k n="Change"/>
+    <k n="Change % (Extended hours)"/>
+    <k n="Change (%)"/>
+    <k n="Change (Extended hours)"/>
+    <k n="Currency" t="s"/>
+    <k n="Description" t="s"/>
+    <k n="Employees"/>
+    <k n="Exchange" t="s"/>
+    <k n="Exchange abbreviation" t="s"/>
+    <k n="ExchangeID" t="s"/>
+    <k n="Headquarters" t="s"/>
+    <k n="High"/>
+    <k n="Industry" t="s"/>
+    <k n="Instrument type" t="s"/>
+    <k n="Last trade time"/>
+    <k n="LearnMoreOnLink" t="r"/>
+    <k n="Low"/>
+    <k n="Market cap"/>
+    <k n="Name" t="s"/>
+    <k n="Official name" t="s"/>
+    <k n="Open"/>
+    <k n="Previous close"/>
+    <k n="Price"/>
+    <k n="Price (Extended hours)"/>
+    <k n="Shares outstanding"/>
+    <k n="Ticker symbol" t="s"/>
+    <k n="UniqueName" t="s"/>
+    <k n="Volume"/>
+    <k n="Volume average"/>
+    <k n="Year incorporated"/>
+  </s>
+  <s t="_linkedentitycore">
+    <k n="%EntityCulture" t="s"/>
+    <k n="%EntityId" t="s"/>
+    <k n="%EntityServiceId"/>
+    <k n="%IsRefreshable" t="b"/>
+    <k n="%ProviderInfo" t="s"/>
+    <k n="_Display" t="spb"/>
+    <k n="_DisplayString" t="s"/>
+    <k n="_Flags" t="spb"/>
+    <k n="_Format" t="spb"/>
+    <k n="_Icon" t="s"/>
+    <k n="_SubLabel" t="spb"/>
+    <k n="52 week high"/>
+    <k n="52 week low"/>
+    <k n="Beta"/>
+    <k n="Change"/>
     <k n="Change (%)"/>
     <k n="Currency" t="s"/>
     <k n="Description" t="s"/>
@@ -9396,52 +9440,6 @@
     <k n="UniqueName" t="s"/>
     <k n="Volume"/>
     <k n="Volume average"/>
-  </s>
-  <s t="_linkedentitycore">
-    <k n="%EntityCulture" t="s"/>
-    <k n="%EntityId" t="s"/>
-    <k n="%EntityServiceId"/>
-    <k n="%IsRefreshable" t="b"/>
-    <k n="%ProviderInfo" t="s"/>
-    <k n="_Display" t="spb"/>
-    <k n="_DisplayString" t="s"/>
-    <k n="_Flags" t="spb"/>
-    <k n="_Format" t="spb"/>
-    <k n="_Icon" t="s"/>
-    <k n="_SubLabel" t="spb"/>
-    <k n="52 week high"/>
-    <k n="52 week low"/>
-    <k n="Beta"/>
-    <k n="Change"/>
-    <k n="Change % (Extended hours)"/>
-    <k n="Change (%)"/>
-    <k n="Change (Extended hours)"/>
-    <k n="Currency" t="s"/>
-    <k n="Description" t="s"/>
-    <k n="Employees"/>
-    <k n="Exchange" t="s"/>
-    <k n="Exchange abbreviation" t="s"/>
-    <k n="ExchangeID" t="s"/>
-    <k n="Headquarters" t="s"/>
-    <k n="High"/>
-    <k n="Industry" t="s"/>
-    <k n="Instrument type" t="s"/>
-    <k n="Last trade time"/>
-    <k n="LearnMoreOnLink" t="r"/>
-    <k n="Low"/>
-    <k n="Market cap"/>
-    <k n="Name" t="s"/>
-    <k n="Official name" t="s"/>
-    <k n="Open"/>
-    <k n="Previous close"/>
-    <k n="Price"/>
-    <k n="Price (Extended hours)"/>
-    <k n="Shares outstanding"/>
-    <k n="Ticker symbol" t="s"/>
-    <k n="UniqueName" t="s"/>
-    <k n="Volume"/>
-    <k n="Volume average"/>
-    <k n="Year incorporated"/>
   </s>
   <s t="_linkedentitycore">
     <k n="%EntityCulture" t="s"/>
@@ -9740,6 +9738,52 @@
       <v t="s">LearnMoreOnLink</v>
       <v t="s">%ProviderInfo</v>
     </a>
+    <a count="44">
+      <v t="s">%EntityServiceId</v>
+      <v t="s">_Format</v>
+      <v t="s">%IsRefreshable</v>
+      <v t="s">%EntityCulture</v>
+      <v t="s">%EntityId</v>
+      <v t="s">_Icon</v>
+      <v t="s">_Display</v>
+      <v t="s">Name</v>
+      <v t="s">_SubLabel</v>
+      <v t="s">Price</v>
+      <v t="s">Price (Extended hours)</v>
+      <v t="s">Exchange</v>
+      <v t="s">Official name</v>
+      <v t="s">Last trade time</v>
+      <v t="s">Ticker symbol</v>
+      <v t="s">Exchange abbreviation</v>
+      <v t="s">Change</v>
+      <v t="s">Change (Extended hours)</v>
+      <v t="s">Change (%)</v>
+      <v t="s">Change % (Extended hours)</v>
+      <v t="s">Currency</v>
+      <v t="s">Previous close</v>
+      <v t="s">Open</v>
+      <v t="s">High</v>
+      <v t="s">Low</v>
+      <v t="s">52 week high</v>
+      <v t="s">52 week low</v>
+      <v t="s">Volume</v>
+      <v t="s">Volume average</v>
+      <v t="s">Market cap</v>
+      <v t="s">Beta</v>
+      <v t="s">Shares outstanding</v>
+      <v t="s">Description</v>
+      <v t="s">Employees</v>
+      <v t="s">Headquarters</v>
+      <v t="s">Industry</v>
+      <v t="s">Instrument type</v>
+      <v t="s">Year incorporated</v>
+      <v t="s">_Flags</v>
+      <v t="s">UniqueName</v>
+      <v t="s">_DisplayString</v>
+      <v t="s">LearnMoreOnLink</v>
+      <v t="s">ExchangeID</v>
+      <v t="s">%ProviderInfo</v>
+    </a>
     <a count="42">
       <v t="s">%EntityServiceId</v>
       <v t="s">_Format</v>
@@ -9823,52 +9867,6 @@
       <v t="s">Headquarters</v>
       <v t="s">Industry</v>
       <v t="s">Instrument type</v>
-      <v t="s">_Flags</v>
-      <v t="s">UniqueName</v>
-      <v t="s">_DisplayString</v>
-      <v t="s">LearnMoreOnLink</v>
-      <v t="s">ExchangeID</v>
-      <v t="s">%ProviderInfo</v>
-    </a>
-    <a count="44">
-      <v t="s">%EntityServiceId</v>
-      <v t="s">_Format</v>
-      <v t="s">%IsRefreshable</v>
-      <v t="s">%EntityCulture</v>
-      <v t="s">%EntityId</v>
-      <v t="s">_Icon</v>
-      <v t="s">_Display</v>
-      <v t="s">Name</v>
-      <v t="s">_SubLabel</v>
-      <v t="s">Price</v>
-      <v t="s">Price (Extended hours)</v>
-      <v t="s">Exchange</v>
-      <v t="s">Official name</v>
-      <v t="s">Last trade time</v>
-      <v t="s">Ticker symbol</v>
-      <v t="s">Exchange abbreviation</v>
-      <v t="s">Change</v>
-      <v t="s">Change (Extended hours)</v>
-      <v t="s">Change (%)</v>
-      <v t="s">Change % (Extended hours)</v>
-      <v t="s">Currency</v>
-      <v t="s">Previous close</v>
-      <v t="s">Open</v>
-      <v t="s">High</v>
-      <v t="s">Low</v>
-      <v t="s">52 week high</v>
-      <v t="s">52 week low</v>
-      <v t="s">Volume</v>
-      <v t="s">Volume average</v>
-      <v t="s">Market cap</v>
-      <v t="s">Beta</v>
-      <v t="s">Shares outstanding</v>
-      <v t="s">Description</v>
-      <v t="s">Employees</v>
-      <v t="s">Headquarters</v>
-      <v t="s">Industry</v>
-      <v t="s">Instrument type</v>
-      <v t="s">Year incorporated</v>
       <v t="s">_Flags</v>
       <v t="s">UniqueName</v>
       <v t="s">_DisplayString</v>
@@ -9991,9 +9989,9 @@
       <v>at close</v>
       <v>from previous close</v>
       <v>from previous close</v>
-      <v>Source: Nasdaq Last Sale</v>
+      <v>Source: Nasdaq</v>
       <v>GMT</v>
-      <v>Real-Time Nasdaq Last Sale</v>
+      <v>Delayed 15 minutes</v>
       <v>from close</v>
       <v>from close</v>
     </spb>
@@ -10129,6 +10127,35 @@
       <v>Name</v>
       <v>LearnMoreOnLink</v>
     </spb>
+    <spb s="16">
+      <v>1</v>
+      <v>2</v>
+      <v>1</v>
+      <v>3</v>
+      <v>1</v>
+      <v>1</v>
+      <v>1</v>
+      <v>4</v>
+      <v>4</v>
+      <v>5</v>
+      <v>6</v>
+      <v>1</v>
+      <v>1</v>
+      <v>1</v>
+      <v>4</v>
+      <v>7</v>
+      <v>8</v>
+      <v>9</v>
+      <v>4</v>
+      <v>1</v>
+      <v>1</v>
+      <v>5</v>
+    </spb>
+    <spb s="0">
+      <v>6</v>
+      <v>Name</v>
+      <v>LearnMoreOnLink</v>
+    </spb>
     <spb s="11">
       <v>13</v>
       <v>2</v>
@@ -10151,18 +10178,18 @@
       <v>9</v>
       <v>4</v>
     </spb>
-    <spb s="16">
+    <spb s="17">
       <v>Delayed 15 minutes</v>
       <v>from previous close</v>
       <v>from previous close</v>
       <v>GMT</v>
     </spb>
     <spb s="0">
-      <v>6</v>
+      <v>7</v>
       <v>Name</v>
       <v>LearnMoreOnLink</v>
     </spb>
-    <spb s="17">
+    <spb s="18">
       <v>1</v>
       <v>2</v>
       <v>2</v>
@@ -10186,44 +10213,15 @@
       <v>1</v>
       <v>5</v>
     </spb>
-    <spb s="4">
+    <spb s="15">
       <v>at close</v>
       <v>from previous close</v>
+      <v>Source: Nasdaq</v>
       <v>from previous close</v>
-      <v>Source: Nasdaq</v>
       <v>GMT</v>
       <v>Delayed 15 minutes</v>
       <v>from close</v>
       <v>from close</v>
-    </spb>
-    <spb s="0">
-      <v>7</v>
-      <v>Name</v>
-      <v>LearnMoreOnLink</v>
-    </spb>
-    <spb s="18">
-      <v>1</v>
-      <v>2</v>
-      <v>1</v>
-      <v>3</v>
-      <v>1</v>
-      <v>1</v>
-      <v>1</v>
-      <v>4</v>
-      <v>4</v>
-      <v>5</v>
-      <v>6</v>
-      <v>1</v>
-      <v>1</v>
-      <v>1</v>
-      <v>4</v>
-      <v>7</v>
-      <v>8</v>
-      <v>9</v>
-      <v>4</v>
-      <v>1</v>
-      <v>1</v>
-      <v>5</v>
     </spb>
     <spb s="0">
       <v>8</v>
@@ -10472,6 +10470,30 @@
     <k n="Change % (Extended hours)" t="s"/>
   </s>
   <s>
+    <k n="Low" t="i"/>
+    <k n="Beta" t="i"/>
+    <k n="High" t="i"/>
+    <k n="Name" t="i"/>
+    <k n="Open" t="i"/>
+    <k n="Price" t="i"/>
+    <k n="Change" t="i"/>
+    <k n="Volume" t="i"/>
+    <k n="Employees" t="i"/>
+    <k n="Change (%)" t="i"/>
+    <k n="Market cap" t="i"/>
+    <k n="52 week low" t="i"/>
+    <k n="52 week high" t="i"/>
+    <k n="Previous close" t="i"/>
+    <k n="Volume average" t="i"/>
+    <k n="Last trade time" t="i"/>
+    <k n="Year incorporated" t="i"/>
+    <k n="`%EntityServiceId" t="i"/>
+    <k n="Shares outstanding" t="i"/>
+    <k n="Price (Extended hours)" t="i"/>
+    <k n="Change (Extended hours)" t="i"/>
+    <k n="Change % (Extended hours)" t="i"/>
+  </s>
+  <s>
     <k n="Price" t="s"/>
     <k n="Change" t="s"/>
     <k n="Change (%)" t="s"/>
@@ -10495,30 +10517,6 @@
     <k n="Previous close" t="i"/>
     <k n="Volume average" t="i"/>
     <k n="Last trade time" t="i"/>
-    <k n="`%EntityServiceId" t="i"/>
-    <k n="Shares outstanding" t="i"/>
-    <k n="Price (Extended hours)" t="i"/>
-    <k n="Change (Extended hours)" t="i"/>
-    <k n="Change % (Extended hours)" t="i"/>
-  </s>
-  <s>
-    <k n="Low" t="i"/>
-    <k n="Beta" t="i"/>
-    <k n="High" t="i"/>
-    <k n="Name" t="i"/>
-    <k n="Open" t="i"/>
-    <k n="Price" t="i"/>
-    <k n="Change" t="i"/>
-    <k n="Volume" t="i"/>
-    <k n="Employees" t="i"/>
-    <k n="Change (%)" t="i"/>
-    <k n="Market cap" t="i"/>
-    <k n="52 week low" t="i"/>
-    <k n="52 week high" t="i"/>
-    <k n="Previous close" t="i"/>
-    <k n="Volume average" t="i"/>
-    <k n="Last trade time" t="i"/>
-    <k n="Year incorporated" t="i"/>
     <k n="`%EntityServiceId" t="i"/>
     <k n="Shares outstanding" t="i"/>
     <k n="Price (Extended hours)" t="i"/>
@@ -10662,7 +10660,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{F82495E7-9F34-4C1F-83EC-FA45D59FA2BD}" name="tblContributions" displayName="tblContributions" ref="A1:C2" totalsRowShown="0">
   <autoFilter ref="A1:C2" xr:uid="{F82495E7-9F34-4C1F-83EC-FA45D59FA2BD}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{EAE9033F-E950-4D8F-AC60-78CCDA7A0C9E}" name="DATE" dataDxfId="27"/>
+    <tableColumn id="1" xr3:uid="{EAE9033F-E950-4D8F-AC60-78CCDA7A0C9E}" name="DATE" dataDxfId="44"/>
     <tableColumn id="2" xr3:uid="{1D40F1FF-D66C-4703-9DEC-93C768793D8F}" name="AMMOUNT"/>
     <tableColumn id="3" xr3:uid="{49855D82-DE07-4257-837D-DD0BE41E988B}" name="Notes"/>
   </tableColumns>
@@ -10706,64 +10704,64 @@
   <tableColumns count="31">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="symbol"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="StockName"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="LastTradeTime" dataDxfId="26">
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="LastTradeTime" dataDxfId="43">
       <calculatedColumnFormula array="1">_FV(B2,"Last trade time",TRUE)</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="TradeCurrency">
       <calculatedColumnFormula array="1">_FV(B2,"Currency")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="StockPrice" dataDxfId="25">
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="StockPrice" dataDxfId="42">
       <calculatedColumnFormula array="1">_FV(B2,"Price")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="ChangePercent" dataDxfId="24">
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="ChangePercent" dataDxfId="41">
       <calculatedColumnFormula array="1">_FV(B2,"Change (%)",TRUE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Change" dataDxfId="23">
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Change" dataDxfId="40">
       <calculatedColumnFormula array="1">_FV(B2,"Change")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="P/E" dataDxfId="22">
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="P/E" dataDxfId="39">
       <calculatedColumnFormula array="1">_FV(B2,"P/E",TRUE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Beta" dataDxfId="21">
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Beta" dataDxfId="38">
       <calculatedColumnFormula array="1">_FV(B2,"Beta")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="52WkHigh" dataDxfId="20">
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="52WkHigh" dataDxfId="37">
       <calculatedColumnFormula array="1">_FV(B2,"52 week high",TRUE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="52WkLow" dataDxfId="19">
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="52WkLow" dataDxfId="36">
       <calculatedColumnFormula array="1">_FV(B2,"52 week low",TRUE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="DayHigh" dataDxfId="18">
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="DayHigh" dataDxfId="35">
       <calculatedColumnFormula array="1">_FV(B2,"High")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="DayLow" dataDxfId="17">
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="DayLow" dataDxfId="34">
       <calculatedColumnFormula array="1">_FV(B2,"Low")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="Open" dataDxfId="16">
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="Open" dataDxfId="33">
       <calculatedColumnFormula array="1">_FV(B2,"Open")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="PreviousClose" dataDxfId="15">
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="PreviousClose" dataDxfId="32">
       <calculatedColumnFormula array="1">_FV(B2,"Previous close",TRUE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Volume" dataDxfId="14">
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Volume" dataDxfId="31">
       <calculatedColumnFormula array="1">_FV(B2,"Volume")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="AverageVolume" dataDxfId="13">
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="AverageVolume" dataDxfId="30">
       <calculatedColumnFormula array="1">_FV(B2,"Volume average",TRUE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="YearIncorported" dataDxfId="12">
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="YearIncorported" dataDxfId="29">
       <calculatedColumnFormula array="1">_FV(B2,"Year incorporated",TRUE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="Employees" dataDxfId="11">
+    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="Employees" dataDxfId="28">
       <calculatedColumnFormula array="1">_FV(B2,"Employees")</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="Industry">
       <calculatedColumnFormula array="1">_FV(B2,"Industry")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0000-000015000000}" name="MarketCap" dataDxfId="10">
+    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0000-000015000000}" name="MarketCap" dataDxfId="27">
       <calculatedColumnFormula array="1">_FV(B2,"Market cap",TRUE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0000-000016000000}" name="SharesOutstanding" dataDxfId="9">
+    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0000-000016000000}" name="SharesOutstanding" dataDxfId="26">
       <calculatedColumnFormula array="1">_FV(B2,"Shares outstanding",TRUE)</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="23" xr3:uid="{00000000-0010-0000-0000-000017000000}" name="50SMA"/>
@@ -10781,37 +10779,37 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{D39CE96F-8D2C-4A60-A43A-B3602E27FDC2}" name="tblHoldings" displayName="tblHoldings" ref="A1:N10" totalsRowShown="0" headerRowDxfId="44" dataDxfId="43" tableBorderDxfId="42">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{D39CE96F-8D2C-4A60-A43A-B3602E27FDC2}" name="tblHoldings" displayName="tblHoldings" ref="A1:N10" totalsRowShown="0" headerRowDxfId="25" dataDxfId="24" tableBorderDxfId="23">
   <autoFilter ref="A1:N10" xr:uid="{D39CE96F-8D2C-4A60-A43A-B3602E27FDC2}"/>
   <tableColumns count="14">
-    <tableColumn id="1" xr3:uid="{AE3CE10F-629F-414E-93DE-8949C4E58E7D}" name="Symbol" dataDxfId="41"/>
-    <tableColumn id="2" xr3:uid="{40700DF4-EB97-4DB9-BA32-772C3F8E34CC}" name="StockName" dataDxfId="40"/>
-    <tableColumn id="3" xr3:uid="{BED1527E-0498-4FF1-8E69-ECDB2EB30C25}" name="TradeCurrency" dataDxfId="39">
+    <tableColumn id="1" xr3:uid="{AE3CE10F-629F-414E-93DE-8949C4E58E7D}" name="Symbol" dataDxfId="22"/>
+    <tableColumn id="2" xr3:uid="{40700DF4-EB97-4DB9-BA32-772C3F8E34CC}" name="StockName" dataDxfId="21"/>
+    <tableColumn id="3" xr3:uid="{BED1527E-0498-4FF1-8E69-ECDB2EB30C25}" name="TradeCurrency" dataDxfId="20">
       <calculatedColumnFormula>_FV(B2,"Currency")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{2218CAC2-8A57-48EA-B1D3-CD7E0BA08ECA}" name="TotalBought" dataDxfId="38"/>
-    <tableColumn id="5" xr3:uid="{77160EAF-769F-4559-B5AE-C08A0AC76566}" name="TotalSold" dataDxfId="37"/>
-    <tableColumn id="6" xr3:uid="{324BA50C-3A95-4946-A384-C4EF731BD7F3}" name="NetPosition" dataDxfId="36"/>
-    <tableColumn id="7" xr3:uid="{24A211AE-9FE1-4D72-98D4-96F240F7DCFD}" name="AvgCost" dataDxfId="35"/>
-    <tableColumn id="8" xr3:uid="{E1C8BF44-8957-447E-B3C1-A76A00A619B8}" name="AvgBuyCost" dataDxfId="34">
+    <tableColumn id="4" xr3:uid="{2218CAC2-8A57-48EA-B1D3-CD7E0BA08ECA}" name="TotalBought" dataDxfId="19"/>
+    <tableColumn id="5" xr3:uid="{77160EAF-769F-4559-B5AE-C08A0AC76566}" name="TotalSold" dataDxfId="18"/>
+    <tableColumn id="6" xr3:uid="{324BA50C-3A95-4946-A384-C4EF731BD7F3}" name="NetPosition" dataDxfId="17"/>
+    <tableColumn id="7" xr3:uid="{24A211AE-9FE1-4D72-98D4-96F240F7DCFD}" name="AvgCost" dataDxfId="16"/>
+    <tableColumn id="8" xr3:uid="{E1C8BF44-8957-447E-B3C1-A76A00A619B8}" name="AvgBuyCost" dataDxfId="15">
       <calculatedColumnFormula>F2*G2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{73ED87C5-FB66-49D5-B1EF-4BE32DC6D51F}" name="StockPrice" dataDxfId="33">
+    <tableColumn id="9" xr3:uid="{73ED87C5-FB66-49D5-B1EF-4BE32DC6D51F}" name="StockPrice" dataDxfId="14">
       <calculatedColumnFormula>_FV(B2,"Price")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{1E08B942-A194-43F5-A7DB-404EC54A5C02}" name="FXRate" dataDxfId="32">
+    <tableColumn id="10" xr3:uid="{1E08B942-A194-43F5-A7DB-404EC54A5C02}" name="FXRate" dataDxfId="13">
       <calculatedColumnFormula>Config!$C$1</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{42171935-FB72-4173-A1EB-132DDE8201DD}" name="ChangePercent" dataDxfId="31">
+    <tableColumn id="14" xr3:uid="{42171935-FB72-4173-A1EB-132DDE8201DD}" name="ChangePercent" dataDxfId="12">
       <calculatedColumnFormula array="1">_FV(B2,"Change (%)",TRUE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{96D6E4C8-F5BD-4A3E-88A2-BF403C882136}" name="MarketValue" dataDxfId="30">
+    <tableColumn id="11" xr3:uid="{96D6E4C8-F5BD-4A3E-88A2-BF403C882136}" name="MarketValue" dataDxfId="11">
       <calculatedColumnFormula>F2*I2*J2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{E928C781-D2C4-42A1-A053-38B541581BCB}" name="P&amp;L" dataDxfId="29">
+    <tableColumn id="12" xr3:uid="{E928C781-D2C4-42A1-A053-38B541581BCB}" name="P&amp;L" dataDxfId="10">
       <calculatedColumnFormula>L2-H2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{53BE744D-B35A-4E6B-8EA9-E422203F974E}" name="P&amp;LPercent" dataDxfId="28">
+    <tableColumn id="13" xr3:uid="{53BE744D-B35A-4E6B-8EA9-E422203F974E}" name="P&amp;LPercent" dataDxfId="9">
       <calculatedColumnFormula>IF(H2=0,"",M2/H2)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -13948,7 +13946,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J16"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="10.46484375" style="1" bestFit="1" customWidth="1"/>
@@ -14109,10 +14107,6 @@
         <f>1/1.3403</f>
         <v>0.74610161904051331</v>
       </c>
-      <c r="J5">
-        <f>+G5*E5*I5+H5</f>
-        <v>1887.3677169588898</v>
-      </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="11">
@@ -14352,12 +14346,6 @@
       <c r="I13">
         <f>1/1.353</f>
         <v>0.73909830007390986</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10">
-      <c r="E16">
-        <f>+E5*G5*I5</f>
-        <v>1859.4977169588899</v>
       </c>
     </row>
   </sheetData>
@@ -14544,7 +14532,7 @@
       </c>
       <c r="C2" s="2">
         <f t="array" aca="1" ref="C2" ca="1">_FV(B2,"Last trade time",TRUE)</f>
-        <v>46185.991709640628</v>
+        <v>46185.999966839845</v>
       </c>
       <c r="D2" t="str">
         <f t="array" aca="1" ref="D2" ca="1">_FV(B2,"Currency")</f>
@@ -14568,7 +14556,7 @@
       </c>
       <c r="I2" s="6">
         <f t="array" aca="1" ref="I2" ca="1">_FV(B2,"Beta")</f>
-        <v>3.6392000000000002</v>
+        <v>3.6533000000000002</v>
       </c>
       <c r="J2" s="3">
         <f t="array" aca="1" ref="J2" ca="1">_FV(B2,"52 week high",TRUE)</f>
@@ -14596,7 +14584,7 @@
       </c>
       <c r="P2" s="7">
         <f t="array" aca="1" ref="P2" ca="1">_FV(B2,"Volume")</f>
-        <v>12722744</v>
+        <v>12730850</v>
       </c>
       <c r="Q2" s="7">
         <f t="array" aca="1" ref="Q2" ca="1">_FV(B2,"Volume average",TRUE)</f>
@@ -14632,7 +14620,7 @@
       </c>
       <c r="C3" s="2">
         <f t="array" aca="1" ref="C3" ca="1">_FV(B3,"Last trade time",TRUE)</f>
-        <v>46185.991743772654</v>
+        <v>46185.999966029689</v>
       </c>
       <c r="D3" t="str">
         <f t="array" aca="1" ref="D3" ca="1">_FV(B3,"Currency")</f>
@@ -14652,11 +14640,11 @@
       </c>
       <c r="H3" s="6">
         <f t="array" aca="1" ref="H3" ca="1">_FV(B3,"P/E",TRUE)</f>
-        <v>35.357900000000001</v>
+        <v>35.904400000000003</v>
       </c>
       <c r="I3" s="6">
         <f t="array" aca="1" ref="I3" ca="1">_FV(B3,"Beta")</f>
-        <v>1.0943000000000001</v>
+        <v>1.0979000000000001</v>
       </c>
       <c r="J3" s="3">
         <f t="array" aca="1" ref="J3" ca="1">_FV(B3,"52 week high",TRUE)</f>
@@ -14684,7 +14672,7 @@
       </c>
       <c r="P3" s="7">
         <f t="array" aca="1" ref="P3" ca="1">_FV(B3,"Volume")</f>
-        <v>38772578</v>
+        <v>38784789</v>
       </c>
       <c r="Q3" s="7">
         <f t="array" aca="1" ref="Q3" ca="1">_FV(B3,"Volume average",TRUE)</f>
@@ -14720,7 +14708,7 @@
       </c>
       <c r="C4" s="2">
         <f t="array" aca="1" ref="C4" ca="1">_FV(B4,"Last trade time",TRUE)</f>
-        <v>46185.991780798438</v>
+        <v>46185.999881260941</v>
       </c>
       <c r="D4" t="str">
         <f t="array" aca="1" ref="D4" ca="1">_FV(B4,"Currency")</f>
@@ -14740,11 +14728,11 @@
       </c>
       <c r="H4" s="6">
         <f t="array" aca="1" ref="H4" ca="1">_FV(B4,"P/E",TRUE)</f>
-        <v>11.6812</v>
+        <v>12.5275</v>
       </c>
       <c r="I4" s="6">
         <f t="array" aca="1" ref="I4" ca="1">_FV(B4,"Beta")</f>
-        <v>1.4311</v>
+        <v>1.4427000000000001</v>
       </c>
       <c r="J4" s="3">
         <f t="array" aca="1" ref="J4" ca="1">_FV(B4,"52 week high",TRUE)</f>
@@ -14772,7 +14760,7 @@
       </c>
       <c r="P4" s="7">
         <f t="array" aca="1" ref="P4" ca="1">_FV(B4,"Volume")</f>
-        <v>25053187</v>
+        <v>25063668</v>
       </c>
       <c r="Q4" s="7">
         <f t="array" aca="1" ref="Q4" ca="1">_FV(B4,"Volume average",TRUE)</f>
@@ -14808,7 +14796,7 @@
       </c>
       <c r="C5" s="2">
         <f t="array" aca="1" ref="C5" ca="1">_FV(B5,"Last trade time",TRUE)</f>
-        <v>46185.991013032028</v>
+        <v>46185.999518668752</v>
       </c>
       <c r="D5" t="str">
         <f t="array" aca="1" ref="D5" ca="1">_FV(B5,"Currency")</f>
@@ -14832,7 +14820,7 @@
       </c>
       <c r="I5" s="6">
         <f t="array" aca="1" ref="I5" ca="1">_FV(B5,"Beta")</f>
-        <v>3.1503000000000001</v>
+        <v>3.1440999999999999</v>
       </c>
       <c r="J5" s="3">
         <f t="array" aca="1" ref="J5" ca="1">_FV(B5,"52 week high",TRUE)</f>
@@ -14860,7 +14848,7 @@
       </c>
       <c r="P5" s="7">
         <f t="array" aca="1" ref="P5" ca="1">_FV(B5,"Volume")</f>
-        <v>1408317</v>
+        <v>1408832</v>
       </c>
       <c r="Q5" s="7">
         <f t="array" aca="1" ref="Q5" ca="1">_FV(B5,"Volume average",TRUE)</f>
@@ -14920,7 +14908,7 @@
       </c>
       <c r="I6" s="6">
         <f t="array" aca="1" ref="I6" ca="1">_FV(B6,"Beta")</f>
-        <v>0.83430000000000004</v>
+        <v>0.83750000000000002</v>
       </c>
       <c r="J6" s="3">
         <f t="array" aca="1" ref="J6" ca="1">_FV(B6,"52 week high",TRUE)</f>
@@ -14984,7 +14972,7 @@
       </c>
       <c r="C7" s="2">
         <f t="array" aca="1" ref="C7" ca="1">_FV(B7,"Last trade time",TRUE)</f>
-        <v>46185.991627303127</v>
+        <v>46185.999754640623</v>
       </c>
       <c r="D7" t="str">
         <f t="array" aca="1" ref="D7" ca="1">_FV(B7,"Currency")</f>
@@ -15004,7 +14992,7 @@
       </c>
       <c r="H7" s="6">
         <f t="array" aca="1" ref="H7" ca="1">_FV(B7,"P/E",TRUE)</f>
-        <v>247.50569999999999</v>
+        <v>247.71979999999999</v>
       </c>
       <c r="I7" s="6">
         <f t="array" aca="1" ref="I7" ca="1">_FV(B7,"Beta")</f>
@@ -15036,7 +15024,7 @@
       </c>
       <c r="P7" s="7">
         <f t="array" aca="1" ref="P7" ca="1">_FV(B7,"Volume")</f>
-        <v>5379109</v>
+        <v>5380744</v>
       </c>
       <c r="Q7" s="7">
         <f t="array" aca="1" ref="Q7" ca="1">_FV(B7,"Volume average",TRUE)</f>
@@ -15072,7 +15060,7 @@
       </c>
       <c r="C8" s="2">
         <f t="array" aca="1" ref="C8" ca="1">_FV(B8,"Last trade time",TRUE)</f>
-        <v>46185.983880566404</v>
+        <v>46185.999812892966</v>
       </c>
       <c r="D8" t="str">
         <f t="array" aca="1" ref="D8" ca="1">_FV(B8,"Currency")</f>
@@ -15096,7 +15084,7 @@
       </c>
       <c r="I8" s="6">
         <f t="array" aca="1" ref="I8" ca="1">_FV(B8,"Beta")</f>
-        <v>2.1518999999999999</v>
+        <v>2.1469999999999998</v>
       </c>
       <c r="J8" s="3">
         <f t="array" aca="1" ref="J8" ca="1">_FV(B8,"52 week high",TRUE)</f>
@@ -15124,7 +15112,7 @@
       </c>
       <c r="P8" s="7">
         <f t="array" aca="1" ref="P8" ca="1">_FV(B8,"Volume")</f>
-        <v>879719</v>
+        <v>880488</v>
       </c>
       <c r="Q8" s="7">
         <f t="array" aca="1" ref="Q8" ca="1">_FV(B8,"Volume average",TRUE)</f>
@@ -15160,7 +15148,7 @@
       </c>
       <c r="C9" s="2">
         <f t="array" aca="1" ref="C9" ca="1">_FV(B9,"Last trade time",TRUE)</f>
-        <v>46185.991781585159</v>
+        <v>46185.999992603909</v>
       </c>
       <c r="D9" t="str">
         <f t="array" aca="1" ref="D9" ca="1">_FV(B9,"Currency")</f>
@@ -15184,7 +15172,7 @@
       </c>
       <c r="I9" s="6">
         <f t="array" aca="1" ref="I9" ca="1">_FV(B9,"Beta")</f>
-        <v>2.4946000000000002</v>
+        <v>2.4863</v>
       </c>
       <c r="J9" s="3">
         <f t="array" aca="1" ref="J9" ca="1">_FV(B9,"52 week high",TRUE)</f>
@@ -15212,7 +15200,7 @@
       </c>
       <c r="P9" s="7">
         <f t="array" aca="1" ref="P9" ca="1">_FV(B9,"Volume")</f>
-        <v>31602538</v>
+        <v>31618462</v>
       </c>
       <c r="Q9" s="7">
         <f t="array" aca="1" ref="Q9" ca="1">_FV(B9,"Volume average",TRUE)</f>
@@ -15248,7 +15236,7 @@
       </c>
       <c r="C10" s="2">
         <f t="array" aca="1" ref="C10" ca="1">_FV(B10,"Last trade time",TRUE)</f>
-        <v>46185.991794513284</v>
+        <v>46185.999971075784</v>
       </c>
       <c r="D10" t="str">
         <f t="array" aca="1" ref="D10" ca="1">_FV(B10,"Currency")</f>
@@ -15268,11 +15256,11 @@
       </c>
       <c r="H10" s="6">
         <f t="array" aca="1" ref="H10" ca="1">_FV(B10,"P/E",TRUE)</f>
-        <v>28.508400000000002</v>
+        <v>28.862200000000001</v>
       </c>
       <c r="I10" s="6">
         <f t="array" aca="1" ref="I10" ca="1">_FV(B10,"Beta")</f>
-        <v>1.4634</v>
+        <v>1.4651000000000001</v>
       </c>
       <c r="J10" s="3">
         <f t="array" aca="1" ref="J10" ca="1">_FV(B10,"52 week high",TRUE)</f>
@@ -15300,7 +15288,7 @@
       </c>
       <c r="P10" s="7">
         <f t="array" aca="1" ref="P10" ca="1">_FV(B10,"Volume")</f>
-        <v>51235722</v>
+        <v>51251141</v>
       </c>
       <c r="Q10" s="7">
         <f t="array" aca="1" ref="Q10" ca="1">_FV(B10,"Volume average",TRUE)</f>
@@ -15336,7 +15324,7 @@
       </c>
       <c r="C11" s="2">
         <f t="array" aca="1" ref="C11" ca="1">_FV(B11,"Last trade time",TRUE)</f>
-        <v>46185.98980977969</v>
+        <v>46185.999926353907</v>
       </c>
       <c r="D11" t="str">
         <f t="array" aca="1" ref="D11" ca="1">_FV(B11,"Currency")</f>
@@ -15344,23 +15332,23 @@
       </c>
       <c r="E11" s="3">
         <f t="array" aca="1" ref="E11" ca="1">_FV(B11,"Price")</f>
-        <v>163.22999999999999</v>
+        <v>163.24</v>
       </c>
       <c r="F11" s="4">
         <f t="array" aca="1" ref="F11" ca="1">_FV(B11,"Change (%)",TRUE)</f>
-        <v>4.367E-2</v>
+        <v>4.3734000000000002E-2</v>
       </c>
       <c r="G11" s="5">
         <f t="array" aca="1" ref="G11" ca="1">_FV(B11,"Change")</f>
-        <v>6.83</v>
+        <v>6.84</v>
       </c>
       <c r="H11" s="6">
         <f t="array" aca="1" ref="H11" ca="1">_FV(B11,"P/E",TRUE)</f>
-        <v>55.908299999999997</v>
+        <v>53.568399999999997</v>
       </c>
       <c r="I11" s="6">
         <f t="array" aca="1" ref="I11" ca="1">_FV(B11,"Beta")</f>
-        <v>1.6121000000000001</v>
+        <v>1.6035999999999999</v>
       </c>
       <c r="J11" s="3">
         <f t="array" aca="1" ref="J11" ca="1">_FV(B11,"52 week high",TRUE)</f>
@@ -15388,7 +15376,7 @@
       </c>
       <c r="P11" s="7">
         <f t="array" aca="1" ref="P11" ca="1">_FV(B11,"Volume")</f>
-        <v>6050609</v>
+        <v>6052481</v>
       </c>
       <c r="Q11" s="7">
         <f t="array" aca="1" ref="Q11" ca="1">_FV(B11,"Volume average",TRUE)</f>
@@ -15408,7 +15396,7 @@
       </c>
       <c r="U11" s="7">
         <f t="array" aca="1" ref="U11" ca="1">_FV(B11,"Market cap",TRUE)</f>
-        <v>205539705690</v>
+        <v>205552297720</v>
       </c>
       <c r="V11" s="7">
         <f t="array" aca="1" ref="V11" ca="1">_FV(B11,"Shares outstanding",TRUE)</f>
@@ -15424,7 +15412,7 @@
       </c>
       <c r="C12" s="2">
         <f t="array" aca="1" ref="C12" ca="1">_FV(B12,"Last trade time",TRUE)</f>
-        <v>46185.991691573436</v>
+        <v>46185.99989806641</v>
       </c>
       <c r="D12" t="str">
         <f t="array" aca="1" ref="D12" ca="1">_FV(B12,"Currency")</f>
@@ -15448,7 +15436,7 @@
       </c>
       <c r="I12" s="6">
         <f t="array" aca="1" ref="I12" ca="1">_FV(B12,"Beta")</f>
-        <v>2.5085999999999999</v>
+        <v>2.4969000000000001</v>
       </c>
       <c r="J12" s="3">
         <f t="array" aca="1" ref="J12" ca="1">_FV(B12,"52 week high",TRUE)</f>
@@ -15476,7 +15464,7 @@
       </c>
       <c r="P12" s="7">
         <f t="array" aca="1" ref="P12" ca="1">_FV(B12,"Volume")</f>
-        <v>4337779</v>
+        <v>4338272</v>
       </c>
       <c r="Q12" s="7">
         <f t="array" aca="1" ref="Q12" ca="1">_FV(B12,"Volume average",TRUE)</f>
@@ -15512,7 +15500,7 @@
       </c>
       <c r="C13" s="2" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(B13,"Last trade time",TRUE)</f>
-        <v>46185.983828553122</v>
+        <v>46185.993873344531</v>
       </c>
       <c r="D13" t="str" cm="1">
         <f t="array" aca="1" ref="D13" ca="1">_FV(B13,"Currency")</f>
@@ -15564,7 +15552,7 @@
       </c>
       <c r="P13" s="7" cm="1">
         <f t="array" aca="1" ref="P13" ca="1">_FV(B13,"Volume")</f>
-        <v>11557890</v>
+        <v>11557976</v>
       </c>
       <c r="Q13" s="7" cm="1">
         <f t="array" aca="1" ref="Q13" ca="1">_FV(B13,"Volume average",TRUE)</f>
@@ -15600,7 +15588,7 @@
       </c>
       <c r="C14" s="2">
         <f t="array" aca="1" ref="C14" ca="1">_FV(B14,"Last trade time",TRUE)</f>
-        <v>46185.991800671094</v>
+        <v>46185.999993899997</v>
       </c>
       <c r="D14" t="str">
         <f t="array" aca="1" ref="D14" ca="1">_FV(B14,"Currency")</f>
@@ -15620,7 +15608,7 @@
       </c>
       <c r="H14" s="6">
         <f t="array" aca="1" ref="H14" ca="1">_FV(B14,"P/E",TRUE)</f>
-        <v>449.91730000000001</v>
+        <v>404.3408</v>
       </c>
       <c r="I14" s="6">
         <f t="array" aca="1" ref="I14" ca="1">_FV(B14,"Beta")</f>
@@ -15652,7 +15640,7 @@
       </c>
       <c r="P14" s="7">
         <f t="array" aca="1" ref="P14" ca="1">_FV(B14,"Volume")</f>
-        <v>16524017</v>
+        <v>16531864</v>
       </c>
       <c r="Q14" s="7">
         <f t="array" aca="1" ref="Q14" ca="1">_FV(B14,"Volume average",TRUE)</f>
@@ -15688,7 +15676,7 @@
       </c>
       <c r="C15" s="2">
         <f t="array" aca="1" ref="C15" ca="1">_FV(B15,"Last trade time",TRUE)</f>
-        <v>46185.990558171092</v>
+        <v>46185.999688517972</v>
       </c>
       <c r="D15" t="str">
         <f t="array" aca="1" ref="D15" ca="1">_FV(B15,"Currency")</f>
@@ -15708,11 +15696,11 @@
       </c>
       <c r="H15" s="6">
         <f t="array" aca="1" ref="H15" ca="1">_FV(B15,"P/E",TRUE)</f>
-        <v>64.068600000000004</v>
+        <v>65.303799999999995</v>
       </c>
       <c r="I15" s="6">
         <f t="array" aca="1" ref="I15" ca="1">_FV(B15,"Beta")</f>
-        <v>1.7627999999999999</v>
+        <v>1.7787999999999999</v>
       </c>
       <c r="J15" s="3">
         <f t="array" aca="1" ref="J15" ca="1">_FV(B15,"52 week high",TRUE)</f>
@@ -15740,7 +15728,7 @@
       </c>
       <c r="P15" s="7">
         <f t="array" aca="1" ref="P15" ca="1">_FV(B15,"Volume")</f>
-        <v>2530787</v>
+        <v>2531327</v>
       </c>
       <c r="Q15" s="7">
         <f t="array" aca="1" ref="Q15" ca="1">_FV(B15,"Volume average",TRUE)</f>
@@ -15776,7 +15764,7 @@
       </c>
       <c r="C16" s="2">
         <f t="array" aca="1" ref="C16" ca="1">_FV(B16,"Last trade time",TRUE)</f>
-        <v>46185.99149697891</v>
+        <v>46185.999958796092</v>
       </c>
       <c r="D16" t="str">
         <f t="array" aca="1" ref="D16" ca="1">_FV(B16,"Currency")</f>
@@ -15796,11 +15784,11 @@
       </c>
       <c r="H16" s="6">
         <f t="array" aca="1" ref="H16" ca="1">_FV(B16,"P/E",TRUE)</f>
-        <v>63.641199999999998</v>
+        <v>64.224400000000003</v>
       </c>
       <c r="I16" s="6">
         <f t="array" aca="1" ref="I16" ca="1">_FV(B16,"Beta")</f>
-        <v>1.4699</v>
+        <v>1.4683999999999999</v>
       </c>
       <c r="J16" s="3">
         <f t="array" aca="1" ref="J16" ca="1">_FV(B16,"52 week high",TRUE)</f>
@@ -15828,7 +15816,7 @@
       </c>
       <c r="P16" s="7">
         <f t="array" aca="1" ref="P16" ca="1">_FV(B16,"Volume")</f>
-        <v>27624297</v>
+        <v>27630074</v>
       </c>
       <c r="Q16" s="7">
         <f t="array" aca="1" ref="Q16" ca="1">_FV(B16,"Volume average",TRUE)</f>
@@ -15864,7 +15852,7 @@
       </c>
       <c r="C17" s="2">
         <f t="array" aca="1" ref="C17" ca="1">_FV(B17,"Last trade time",TRUE)</f>
-        <v>46185.991667175782</v>
+        <v>46185.999992094534</v>
       </c>
       <c r="D17" t="str">
         <f t="array" aca="1" ref="D17" ca="1">_FV(B17,"Currency")</f>
@@ -15872,23 +15860,23 @@
       </c>
       <c r="E17" s="3">
         <f t="array" aca="1" ref="E17" ca="1">_FV(B17,"Price")</f>
-        <v>4.0149999999999997</v>
+        <v>4.0199999999999996</v>
       </c>
       <c r="F17" s="4">
         <f t="array" aca="1" ref="F17" ca="1">_FV(B17,"Change (%)",TRUE)</f>
-        <v>-3.0192999999999998E-2</v>
+        <v>-2.8986000000000001E-2</v>
       </c>
       <c r="G17" s="5">
         <f t="array" aca="1" ref="G17" ca="1">_FV(B17,"Change")</f>
-        <v>-0.125</v>
-      </c>
-      <c r="H17" s="6">
-        <f t="array" aca="1" ref="H17" ca="1">_FV(B17,"P/E",TRUE)</f>
-        <v>0</v>
+        <v>-0.12</v>
+      </c>
+      <c r="H17" s="6" t="e" vm="13">
+        <f t="array" ref="H17">_FV(B17,"P/E",TRUE)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="I17" s="6">
         <f t="array" aca="1" ref="I17" ca="1">_FV(B17,"Beta")</f>
-        <v>3.1198999999999999</v>
+        <v>3.1240000000000001</v>
       </c>
       <c r="J17" s="3">
         <f t="array" aca="1" ref="J17" ca="1">_FV(B17,"52 week high",TRUE)</f>
@@ -15916,7 +15904,7 @@
       </c>
       <c r="P17" s="7">
         <f t="array" aca="1" ref="P17" ca="1">_FV(B17,"Volume")</f>
-        <v>26179858</v>
+        <v>26213060</v>
       </c>
       <c r="Q17" s="7">
         <f t="array" aca="1" ref="Q17" ca="1">_FV(B17,"Volume average",TRUE)</f>
@@ -15936,7 +15924,7 @@
       </c>
       <c r="U17" s="7">
         <f t="array" aca="1" ref="U17" ca="1">_FV(B17,"Market cap",TRUE)</f>
-        <v>1922982242</v>
+        <v>1925376989</v>
       </c>
       <c r="V17" s="7">
         <f t="array" aca="1" ref="V17" ca="1">_FV(B17,"Shares outstanding",TRUE)</f>
@@ -15976,7 +15964,7 @@
       </c>
       <c r="I18" s="6" cm="1">
         <f t="array" aca="1" ref="I18" ca="1">_FV(B18,"Beta")</f>
-        <v>0.98099999999999998</v>
+        <v>0.9738</v>
       </c>
       <c r="J18" s="3" cm="1">
         <f t="array" aca="1" ref="J18" ca="1">_FV(B18,"52 week high",TRUE)</f>
@@ -16040,7 +16028,7 @@
       </c>
       <c r="C19" s="2" cm="1">
         <f t="array" aca="1" ref="C19" ca="1">_FV(B19,"Last trade time",TRUE)</f>
-        <v>46185.991520289062</v>
+        <v>46185.997142800785</v>
       </c>
       <c r="D19" t="str" cm="1">
         <f t="array" aca="1" ref="D19" ca="1">_FV(B19,"Currency")</f>
@@ -16064,7 +16052,7 @@
       </c>
       <c r="I19" s="6" cm="1">
         <f t="array" aca="1" ref="I19" ca="1">_FV(B19,"Beta")</f>
-        <v>1.1368</v>
+        <v>1.139</v>
       </c>
       <c r="J19" s="3" cm="1">
         <f t="array" aca="1" ref="J19" ca="1">_FV(B19,"52 week high",TRUE)</f>
@@ -16092,7 +16080,7 @@
       </c>
       <c r="P19" s="7" cm="1">
         <f t="array" aca="1" ref="P19" ca="1">_FV(B19,"Volume")</f>
-        <v>1366230</v>
+        <v>1366238</v>
       </c>
       <c r="Q19" s="7" cm="1">
         <f t="array" aca="1" ref="Q19" ca="1">_FV(B19,"Volume average",TRUE)</f>
@@ -16128,7 +16116,7 @@
       </c>
       <c r="C20" s="2" cm="1">
         <f t="array" aca="1" ref="C20" ca="1">_FV(B20,"Last trade time",TRUE)</f>
-        <v>46185.991722383595</v>
+        <v>46185.999756330471</v>
       </c>
       <c r="D20" t="str" cm="1">
         <f t="array" aca="1" ref="D20" ca="1">_FV(B20,"Currency")</f>
@@ -16148,11 +16136,11 @@
       </c>
       <c r="H20" s="6" cm="1">
         <f t="array" aca="1" ref="H20" ca="1">_FV(B20,"P/E",TRUE)</f>
-        <v>22.0458</v>
+        <v>21.433399999999999</v>
       </c>
       <c r="I20" s="6" cm="1">
         <f t="array" aca="1" ref="I20" ca="1">_FV(B20,"Beta")</f>
-        <v>1.1372</v>
+        <v>1.1256999999999999</v>
       </c>
       <c r="J20" s="3" cm="1">
         <f t="array" aca="1" ref="J20" ca="1">_FV(B20,"52 week high",TRUE)</f>
@@ -16180,7 +16168,7 @@
       </c>
       <c r="P20" s="7" cm="1">
         <f t="array" aca="1" ref="P20" ca="1">_FV(B20,"Volume")</f>
-        <v>3418915</v>
+        <v>3419966</v>
       </c>
       <c r="Q20" s="7" cm="1">
         <f t="array" aca="1" ref="Q20" ca="1">_FV(B20,"Volume average",TRUE)</f>
@@ -16216,7 +16204,7 @@
       </c>
       <c r="C21" s="2">
         <f t="array" aca="1" ref="C21" ca="1">_FV(B21,"Last trade time",TRUE)</f>
-        <v>46185.991738957811</v>
+        <v>46185.999943402341</v>
       </c>
       <c r="D21" t="str">
         <f t="array" aca="1" ref="D21" ca="1">_FV(B21,"Currency")</f>
@@ -16236,11 +16224,11 @@
       </c>
       <c r="H21" s="6">
         <f t="array" aca="1" ref="H21" ca="1">_FV(B21,"P/E",TRUE)</f>
-        <v>101.1412</v>
+        <v>106.7662</v>
       </c>
       <c r="I21" s="6">
         <f t="array" aca="1" ref="I21" ca="1">_FV(B21,"Beta")</f>
-        <v>3.1806999999999999</v>
+        <v>3.2073999999999998</v>
       </c>
       <c r="J21" s="3">
         <f t="array" aca="1" ref="J21" ca="1">_FV(B21,"52 week high",TRUE)</f>
@@ -16268,7 +16256,7 @@
       </c>
       <c r="P21" s="7">
         <f t="array" aca="1" ref="P21" ca="1">_FV(B21,"Volume")</f>
-        <v>9023804</v>
+        <v>9028913</v>
       </c>
       <c r="Q21" s="7">
         <f t="array" aca="1" ref="Q21" ca="1">_FV(B21,"Volume average",TRUE)</f>
@@ -16304,7 +16292,7 @@
       </c>
       <c r="C22" s="2">
         <f t="array" aca="1" ref="C22" ca="1">_FV(B22,"Last trade time",TRUE)</f>
-        <v>46185.991507164064</v>
+        <v>46185.999767546091</v>
       </c>
       <c r="D22" t="str">
         <f t="array" aca="1" ref="D22" ca="1">_FV(B22,"Currency")</f>
@@ -16312,23 +16300,23 @@
       </c>
       <c r="E22" s="3">
         <f t="array" aca="1" ref="E22" ca="1">_FV(B22,"Price")</f>
-        <v>166.09</v>
+        <v>165.89</v>
       </c>
       <c r="F22" s="4">
         <f t="array" aca="1" ref="F22" ca="1">_FV(B22,"Change (%)",TRUE)</f>
-        <v>-2.163E-3</v>
+        <v>-3.3639999999999998E-3</v>
       </c>
       <c r="G22" s="5">
         <f t="array" aca="1" ref="G22" ca="1">_FV(B22,"Change")</f>
-        <v>-0.36</v>
+        <v>-0.56000000000000005</v>
       </c>
       <c r="H22" s="6">
         <f t="array" aca="1" ref="H22" ca="1">_FV(B22,"P/E",TRUE)</f>
-        <v>19.2163</v>
+        <v>19.193100000000001</v>
       </c>
       <c r="I22" s="6">
         <f t="array" aca="1" ref="I22" ca="1">_FV(B22,"Beta")</f>
-        <v>1.1762999999999999</v>
+        <v>1.175</v>
       </c>
       <c r="J22" s="3">
         <f t="array" aca="1" ref="J22" ca="1">_FV(B22,"52 week high",TRUE)</f>
@@ -16356,7 +16344,7 @@
       </c>
       <c r="P22" s="7">
         <f t="array" aca="1" ref="P22" ca="1">_FV(B22,"Volume")</f>
-        <v>13587918</v>
+        <v>13589398</v>
       </c>
       <c r="Q22" s="7">
         <f t="array" aca="1" ref="Q22" ca="1">_FV(B22,"Volume average",TRUE)</f>
@@ -16376,7 +16364,7 @@
       </c>
       <c r="U22" s="7">
         <f t="array" aca="1" ref="U22" ca="1">_FV(B22,"Market cap",TRUE)</f>
-        <v>136027710000</v>
+        <v>135863909999</v>
       </c>
       <c r="V22" s="7">
         <f t="array" aca="1" ref="V22" ca="1">_FV(B22,"Shares outstanding",TRUE)</f>
@@ -16392,7 +16380,7 @@
       </c>
       <c r="C23" s="2" cm="1">
         <f t="array" aca="1" ref="C23" ca="1">_FV(B23,"Last trade time",TRUE)</f>
-        <v>46185.991226770311</v>
+        <v>46185.999911400002</v>
       </c>
       <c r="D23" t="str" cm="1">
         <f t="array" aca="1" ref="D23" ca="1">_FV(B23,"Currency")</f>
@@ -16416,7 +16404,7 @@
       </c>
       <c r="I23" s="6" cm="1">
         <f t="array" aca="1" ref="I23" ca="1">_FV(B23,"Beta")</f>
-        <v>1.2551000000000001</v>
+        <v>1.2579</v>
       </c>
       <c r="J23" s="3" cm="1">
         <f t="array" aca="1" ref="J23" ca="1">_FV(B23,"52 week high",TRUE)</f>
@@ -16444,7 +16432,7 @@
       </c>
       <c r="P23" s="7" cm="1">
         <f t="array" aca="1" ref="P23" ca="1">_FV(B23,"Volume")</f>
-        <v>2311690</v>
+        <v>2311891</v>
       </c>
       <c r="Q23" s="7" cm="1">
         <f t="array" aca="1" ref="Q23" ca="1">_FV(B23,"Volume average",TRUE)</f>
@@ -16480,7 +16468,7 @@
       </c>
       <c r="C24" s="2">
         <f t="array" aca="1" ref="C24" ca="1">_FV(B24,"Last trade time",TRUE)</f>
-        <v>46185.99180111094</v>
+        <v>46185.999990439064</v>
       </c>
       <c r="D24" t="str">
         <f t="array" aca="1" ref="D24" ca="1">_FV(B24,"Currency")</f>
@@ -16532,7 +16520,7 @@
       </c>
       <c r="P24" s="7">
         <f t="array" aca="1" ref="P24" ca="1">_FV(B24,"Volume")</f>
-        <v>36322874</v>
+        <v>36338090</v>
       </c>
       <c r="Q24" s="7">
         <f t="array" aca="1" ref="Q24" ca="1">_FV(B24,"Volume average",TRUE)</f>
@@ -16568,7 +16556,7 @@
       </c>
       <c r="C25" s="2" cm="1">
         <f t="array" aca="1" ref="C25" ca="1">_FV(B25,"Last trade time",TRUE)</f>
-        <v>46185.988973471874</v>
+        <v>46185.999661828122</v>
       </c>
       <c r="D25" t="str" cm="1">
         <f t="array" aca="1" ref="D25" ca="1">_FV(B25,"Currency")</f>
@@ -16588,11 +16576,11 @@
       </c>
       <c r="H25" s="6" cm="1">
         <f t="array" aca="1" ref="H25" ca="1">_FV(B25,"P/E",TRUE)</f>
-        <v>40.353200000000001</v>
+        <v>40.597099999999998</v>
       </c>
       <c r="I25" s="6" cm="1">
         <f t="array" aca="1" ref="I25" ca="1">_FV(B25,"Beta")</f>
-        <v>0.99550000000000005</v>
+        <v>0.99929999999999997</v>
       </c>
       <c r="J25" s="3" cm="1">
         <f t="array" aca="1" ref="J25" ca="1">_FV(B25,"52 week high",TRUE)</f>
@@ -16620,7 +16608,7 @@
       </c>
       <c r="P25" s="7" cm="1">
         <f t="array" aca="1" ref="P25" ca="1">_FV(B25,"Volume")</f>
-        <v>18223291</v>
+        <v>18223791</v>
       </c>
       <c r="Q25" s="7" cm="1">
         <f t="array" aca="1" ref="Q25" ca="1">_FV(B25,"Volume average",TRUE)</f>
@@ -16656,7 +16644,7 @@
       </c>
       <c r="C26" s="2">
         <f t="array" aca="1" ref="C26" ca="1">_FV(B26,"Last trade time",TRUE)</f>
-        <v>46185.988973471874</v>
+        <v>46185.999661828122</v>
       </c>
       <c r="D26" t="str">
         <f t="array" aca="1" ref="D26" ca="1">_FV(B26,"Currency")</f>
@@ -16676,11 +16664,11 @@
       </c>
       <c r="H26" s="6">
         <f t="array" aca="1" ref="H26" ca="1">_FV(B26,"P/E",TRUE)</f>
-        <v>40.353200000000001</v>
+        <v>40.597099999999998</v>
       </c>
       <c r="I26" s="6">
         <f t="array" aca="1" ref="I26" ca="1">_FV(B26,"Beta")</f>
-        <v>0.99550000000000005</v>
+        <v>0.99929999999999997</v>
       </c>
       <c r="J26" s="3">
         <f t="array" aca="1" ref="J26" ca="1">_FV(B26,"52 week high",TRUE)</f>
@@ -16708,7 +16696,7 @@
       </c>
       <c r="P26" s="7">
         <f t="array" aca="1" ref="P26" ca="1">_FV(B26,"Volume")</f>
-        <v>18223291</v>
+        <v>18223791</v>
       </c>
       <c r="Q26" s="7">
         <f t="array" aca="1" ref="Q26" ca="1">_FV(B26,"Volume average",TRUE)</f>
@@ -16744,7 +16732,7 @@
       </c>
       <c r="C27" s="2">
         <f t="array" aca="1" ref="C27" ca="1">_FV(B27,"Last trade time",TRUE)</f>
-        <v>46185.988537510937</v>
+        <v>46185.999707892966</v>
       </c>
       <c r="D27" t="str">
         <f t="array" aca="1" ref="D27" ca="1">_FV(B27,"Currency")</f>
@@ -16764,11 +16752,11 @@
       </c>
       <c r="H27" s="6">
         <f t="array" aca="1" ref="H27" ca="1">_FV(B27,"P/E",TRUE)</f>
-        <v>582.46770000000004</v>
+        <v>593.49350000000004</v>
       </c>
       <c r="I27" s="6">
         <f t="array" aca="1" ref="I27" ca="1">_FV(B27,"Beta")</f>
-        <v>1.5599000000000001</v>
+        <v>1.5649999999999999</v>
       </c>
       <c r="J27" s="3">
         <f t="array" aca="1" ref="J27" ca="1">_FV(B27,"52 week high",TRUE)</f>
@@ -16796,7 +16784,7 @@
       </c>
       <c r="P27" s="7">
         <f t="array" aca="1" ref="P27" ca="1">_FV(B27,"Volume")</f>
-        <v>5756469</v>
+        <v>5756728</v>
       </c>
       <c r="Q27" s="7">
         <f t="array" aca="1" ref="Q27" ca="1">_FV(B27,"Volume average",TRUE)</f>
@@ -16832,7 +16820,7 @@
       </c>
       <c r="C28" s="2" cm="1">
         <f t="array" aca="1" ref="C28" ca="1">_FV(B28,"Last trade time",TRUE)</f>
-        <v>46185.990697499998</v>
+        <v>46185.999974698439</v>
       </c>
       <c r="D28" t="str" cm="1">
         <f t="array" aca="1" ref="D28" ca="1">_FV(B28,"Currency")</f>
@@ -16840,23 +16828,23 @@
       </c>
       <c r="E28" s="3" cm="1">
         <f t="array" aca="1" ref="E28" ca="1">_FV(B28,"Price")</f>
-        <v>395.72500000000002</v>
+        <v>395.57</v>
       </c>
       <c r="F28" s="4" cm="1">
         <f t="array" aca="1" ref="F28" ca="1">_FV(B28,"Change (%)",TRUE)</f>
-        <v>1.0921E-2</v>
+        <v>1.0525E-2</v>
       </c>
       <c r="G28" s="5" cm="1">
         <f t="array" aca="1" ref="G28" ca="1">_FV(B28,"Change")</f>
-        <v>4.2750000000000004</v>
+        <v>4.12</v>
       </c>
       <c r="H28" s="6" cm="1">
         <f t="array" aca="1" ref="H28" ca="1">_FV(B28,"P/E",TRUE)</f>
-        <v>31.4255</v>
+        <v>31.4131</v>
       </c>
       <c r="I28" s="6" cm="1">
         <f t="array" aca="1" ref="I28" ca="1">_FV(B28,"Beta")</f>
-        <v>1.3208</v>
+        <v>1.3171999999999999</v>
       </c>
       <c r="J28" s="3" cm="1">
         <f t="array" aca="1" ref="J28" ca="1">_FV(B28,"52 week high",TRUE)</f>
@@ -16884,7 +16872,7 @@
       </c>
       <c r="P28" s="7" cm="1">
         <f t="array" aca="1" ref="P28" ca="1">_FV(B28,"Volume")</f>
-        <v>6056441</v>
+        <v>6059055</v>
       </c>
       <c r="Q28" s="7" cm="1">
         <f t="array" aca="1" ref="Q28" ca="1">_FV(B28,"Volume average",TRUE)</f>
@@ -16904,7 +16892,7 @@
       </c>
       <c r="U28" s="7" cm="1">
         <f t="array" aca="1" ref="U28" ca="1">_FV(B28,"Market cap",TRUE)</f>
-        <v>256472538300</v>
+        <v>256372081560</v>
       </c>
       <c r="V28" s="7" cm="1">
         <f t="array" aca="1" ref="V28" ca="1">_FV(B28,"Shares outstanding",TRUE)</f>
@@ -16920,7 +16908,7 @@
       </c>
       <c r="C29" s="2" cm="1">
         <f t="array" aca="1" ref="C29" ca="1">_FV(B29,"Last trade time",TRUE)</f>
-        <v>46185.991267557809</v>
+        <v>46185.999869443753</v>
       </c>
       <c r="D29" t="str" cm="1">
         <f t="array" aca="1" ref="D29" ca="1">_FV(B29,"Currency")</f>
@@ -16944,7 +16932,7 @@
       </c>
       <c r="I29" s="6" cm="1">
         <f t="array" aca="1" ref="I29" ca="1">_FV(B29,"Beta")</f>
-        <v>1.3828</v>
+        <v>1.3867</v>
       </c>
       <c r="J29" s="3" cm="1">
         <f t="array" aca="1" ref="J29" ca="1">_FV(B29,"52 week high",TRUE)</f>
@@ -16972,7 +16960,7 @@
       </c>
       <c r="P29" s="7" cm="1">
         <f t="array" aca="1" ref="P29" ca="1">_FV(B29,"Volume")</f>
-        <v>8256685</v>
+        <v>8257240</v>
       </c>
       <c r="Q29" s="7" cm="1">
         <f t="array" aca="1" ref="Q29" ca="1">_FV(B29,"Volume average",TRUE)</f>
@@ -17032,7 +17020,7 @@
       </c>
       <c r="I30" s="6" cm="1">
         <f t="array" aca="1" ref="I30" ca="1">_FV(B30,"Beta")</f>
-        <v>0.74719999999999998</v>
+        <v>0.745</v>
       </c>
       <c r="J30" s="3" cm="1">
         <f t="array" aca="1" ref="J30" ca="1">_FV(B30,"52 week high",TRUE)</f>
@@ -17096,7 +17084,7 @@
       </c>
       <c r="C31" s="2">
         <f t="array" aca="1" ref="C31" ca="1">_FV(B31,"Last trade time",TRUE)</f>
-        <v>46185.991443633597</v>
+        <v>46185.992927048435</v>
       </c>
       <c r="D31" t="str">
         <f t="array" aca="1" ref="D31" ca="1">_FV(B31,"Currency")</f>
@@ -17120,7 +17108,7 @@
       </c>
       <c r="I31" s="6">
         <f t="array" aca="1" ref="I31" ca="1">_FV(B31,"Beta")</f>
-        <v>2.2429999999999999</v>
+        <v>2.2429000000000001</v>
       </c>
       <c r="J31" s="3">
         <f t="array" aca="1" ref="J31" ca="1">_FV(B31,"52 week high",TRUE)</f>
@@ -17148,7 +17136,7 @@
       </c>
       <c r="P31" s="7">
         <f t="array" aca="1" ref="P31" ca="1">_FV(B31,"Volume")</f>
-        <v>4057745</v>
+        <v>4058325</v>
       </c>
       <c r="Q31" s="7">
         <f t="array" aca="1" ref="Q31" ca="1">_FV(B31,"Volume average",TRUE)</f>
@@ -17184,7 +17172,7 @@
       </c>
       <c r="C32" s="2" cm="1">
         <f t="array" aca="1" ref="C32" ca="1">_FV(B32,"Last trade time",TRUE)</f>
-        <v>46185.988845196094</v>
+        <v>46185.999693344529</v>
       </c>
       <c r="D32" t="str" cm="1">
         <f t="array" aca="1" ref="D32" ca="1">_FV(B32,"Currency")</f>
@@ -17192,23 +17180,23 @@
       </c>
       <c r="E32" s="3" cm="1">
         <f t="array" aca="1" ref="E32" ca="1">_FV(B32,"Price")</f>
-        <v>391.51299999999998</v>
+        <v>391.39</v>
       </c>
       <c r="F32" s="4" cm="1">
         <f t="array" aca="1" ref="F32" ca="1">_FV(B32,"Change (%)",TRUE)</f>
-        <v>-5.4029999999999998E-3</v>
+        <v>-5.7159999999999997E-3</v>
       </c>
       <c r="G32" s="5" cm="1">
         <f t="array" aca="1" ref="G32" ca="1">_FV(B32,"Change")</f>
-        <v>-2.1269999999999998</v>
+        <v>-2.25</v>
       </c>
       <c r="H32" s="6" cm="1">
         <f t="array" aca="1" ref="H32" ca="1">_FV(B32,"P/E",TRUE)</f>
-        <v>38.275599999999997</v>
+        <v>38.263500000000001</v>
       </c>
       <c r="I32" s="6" cm="1">
         <f t="array" aca="1" ref="I32" ca="1">_FV(B32,"Beta")</f>
-        <v>1.1911</v>
+        <v>1.194</v>
       </c>
       <c r="J32" s="3" cm="1">
         <f t="array" aca="1" ref="J32" ca="1">_FV(B32,"52 week high",TRUE)</f>
@@ -17236,7 +17224,7 @@
       </c>
       <c r="P32" s="7" cm="1">
         <f t="array" aca="1" ref="P32" ca="1">_FV(B32,"Volume")</f>
-        <v>2175298</v>
+        <v>2175309</v>
       </c>
       <c r="Q32" s="7" cm="1">
         <f t="array" aca="1" ref="Q32" ca="1">_FV(B32,"Volume average",TRUE)</f>
@@ -17256,7 +17244,7 @@
       </c>
       <c r="U32" s="7" cm="1">
         <f t="array" aca="1" ref="U32" ca="1">_FV(B32,"Market cap",TRUE)</f>
-        <v>152024497900</v>
+        <v>151976737000</v>
       </c>
       <c r="V32" s="7" cm="1">
         <f t="array" aca="1" ref="V32" ca="1">_FV(B32,"Shares outstanding",TRUE)</f>
@@ -17272,7 +17260,7 @@
       </c>
       <c r="C33" s="2">
         <f t="array" aca="1" ref="C33" ca="1">_FV(B33,"Last trade time",TRUE)</f>
-        <v>46185.977991828127</v>
+        <v>46185.994621365622</v>
       </c>
       <c r="D33" t="str">
         <f t="array" aca="1" ref="D33" ca="1">_FV(B33,"Currency")</f>
@@ -17296,7 +17284,7 @@
       </c>
       <c r="I33" s="6">
         <f t="array" aca="1" ref="I33" ca="1">_FV(B33,"Beta")</f>
-        <v>1.4681999999999999</v>
+        <v>1.4633</v>
       </c>
       <c r="J33" s="3">
         <f t="array" aca="1" ref="J33" ca="1">_FV(B33,"52 week high",TRUE)</f>
@@ -17324,7 +17312,7 @@
       </c>
       <c r="P33" s="7">
         <f t="array" aca="1" ref="P33" ca="1">_FV(B33,"Volume")</f>
-        <v>1760038</v>
+        <v>1760040</v>
       </c>
       <c r="Q33" s="7">
         <f t="array" aca="1" ref="Q33" ca="1">_FV(B33,"Volume average",TRUE)</f>
@@ -17360,7 +17348,7 @@
       </c>
       <c r="C34" s="2" cm="1">
         <f t="array" aca="1" ref="C34" ca="1">_FV(B34,"Last trade time",TRUE)</f>
-        <v>46185.986923066404</v>
+        <v>46185.99929895781</v>
       </c>
       <c r="D34" t="str" cm="1">
         <f t="array" aca="1" ref="D34" ca="1">_FV(B34,"Currency")</f>
@@ -17380,11 +17368,11 @@
       </c>
       <c r="H34" s="6" cm="1">
         <f t="array" aca="1" ref="H34" ca="1">_FV(B34,"P/E",TRUE)</f>
-        <v>56.5214</v>
+        <v>56.043399999999998</v>
       </c>
       <c r="I34" s="6" cm="1">
         <f t="array" aca="1" ref="I34" ca="1">_FV(B34,"Beta")</f>
-        <v>1.0904</v>
+        <v>1.0920000000000001</v>
       </c>
       <c r="J34" s="3" cm="1">
         <f t="array" aca="1" ref="J34" ca="1">_FV(B34,"52 week high",TRUE)</f>
@@ -17412,7 +17400,7 @@
       </c>
       <c r="P34" s="7" cm="1">
         <f t="array" aca="1" ref="P34" ca="1">_FV(B34,"Volume")</f>
-        <v>5083987</v>
+        <v>5084049</v>
       </c>
       <c r="Q34" s="7" cm="1">
         <f t="array" aca="1" ref="Q34" ca="1">_FV(B34,"Volume average",TRUE)</f>
@@ -17448,7 +17436,7 @@
       </c>
       <c r="C35" s="2">
         <f t="array" aca="1" ref="C35" ca="1">_FV(B35,"Last trade time",TRUE)</f>
-        <v>46185.991515775</v>
+        <v>46185.999964154689</v>
       </c>
       <c r="D35" t="str">
         <f t="array" aca="1" ref="D35" ca="1">_FV(B35,"Currency")</f>
@@ -17468,11 +17456,11 @@
       </c>
       <c r="H35" s="6">
         <f t="array" aca="1" ref="H35" ca="1">_FV(B35,"P/E",TRUE)</f>
-        <v>27.353200000000001</v>
+        <v>27.230899999999998</v>
       </c>
       <c r="I35" s="6">
         <f t="array" aca="1" ref="I35" ca="1">_FV(B35,"Beta")</f>
-        <v>1.248</v>
+        <v>1.2466999999999999</v>
       </c>
       <c r="J35" s="3">
         <f t="array" aca="1" ref="J35" ca="1">_FV(B35,"52 week high",TRUE)</f>
@@ -17500,7 +17488,7 @@
       </c>
       <c r="P35" s="7">
         <f t="array" aca="1" ref="P35" ca="1">_FV(B35,"Volume")</f>
-        <v>17652461</v>
+        <v>17657657</v>
       </c>
       <c r="Q35" s="7">
         <f t="array" aca="1" ref="Q35" ca="1">_FV(B35,"Volume average",TRUE)</f>
@@ -17536,7 +17524,7 @@
       </c>
       <c r="C36" s="2">
         <f t="array" aca="1" ref="C36" ca="1">_FV(B36,"Last trade time",TRUE)</f>
-        <v>46185.991242858596</v>
+        <v>46185.999962395312</v>
       </c>
       <c r="D36" t="str">
         <f t="array" aca="1" ref="D36" ca="1">_FV(B36,"Currency")</f>
@@ -17560,7 +17548,7 @@
       </c>
       <c r="I36" s="6">
         <f t="array" aca="1" ref="I36" ca="1">_FV(B36,"Beta")</f>
-        <v>2.3420000000000001</v>
+        <v>2.3431999999999999</v>
       </c>
       <c r="J36" s="3">
         <f t="array" aca="1" ref="J36" ca="1">_FV(B36,"52 week high",TRUE)</f>
@@ -17588,7 +17576,7 @@
       </c>
       <c r="P36" s="7">
         <f t="array" aca="1" ref="P36" ca="1">_FV(B36,"Volume")</f>
-        <v>33071824</v>
+        <v>33082303</v>
       </c>
       <c r="Q36" s="7">
         <f t="array" aca="1" ref="Q36" ca="1">_FV(B36,"Volume average",TRUE)</f>
@@ -17624,7 +17612,7 @@
       </c>
       <c r="C37" s="2">
         <f t="array" aca="1" ref="C37" ca="1">_FV(B37,"Last trade time",TRUE)</f>
-        <v>46185.991204825783</v>
+        <v>46185.999914895314</v>
       </c>
       <c r="D37" t="str">
         <f t="array" aca="1" ref="D37" ca="1">_FV(B37,"Currency")</f>
@@ -17632,23 +17620,23 @@
       </c>
       <c r="E37" s="3">
         <f t="array" aca="1" ref="E37" ca="1">_FV(B37,"Price")</f>
-        <v>272.185</v>
+        <v>272.24</v>
       </c>
       <c r="F37" s="4">
         <f t="array" aca="1" ref="F37" ca="1">_FV(B37,"Change (%)",TRUE)</f>
-        <v>-9.6959999999999998E-3</v>
+        <v>-9.4959999999999992E-3</v>
       </c>
       <c r="G37" s="5">
         <f t="array" aca="1" ref="G37" ca="1">_FV(B37,"Change")</f>
-        <v>-2.665</v>
+        <v>-2.61</v>
       </c>
       <c r="H37" s="6">
         <f t="array" aca="1" ref="H37" ca="1">_FV(B37,"P/E",TRUE)</f>
-        <v>21.7818</v>
+        <v>21.786200000000001</v>
       </c>
       <c r="I37" s="6">
         <f t="array" aca="1" ref="I37" ca="1">_FV(B37,"Beta")</f>
-        <v>0.67789999999999995</v>
+        <v>0.67810000000000004</v>
       </c>
       <c r="J37" s="3">
         <f t="array" aca="1" ref="J37" ca="1">_FV(B37,"52 week high",TRUE)</f>
@@ -17676,7 +17664,7 @@
       </c>
       <c r="P37" s="7">
         <f t="array" aca="1" ref="P37" ca="1">_FV(B37,"Volume")</f>
-        <v>5747598</v>
+        <v>5748915</v>
       </c>
       <c r="Q37" s="7">
         <f t="array" aca="1" ref="Q37" ca="1">_FV(B37,"Volume average",TRUE)</f>
@@ -17696,7 +17684,7 @@
       </c>
       <c r="U37" s="7">
         <f t="array" aca="1" ref="U37" ca="1">_FV(B37,"Market cap",TRUE)</f>
-        <v>255822680380</v>
+        <v>255874374072</v>
       </c>
       <c r="V37" s="7">
         <f t="array" aca="1" ref="V37" ca="1">_FV(B37,"Shares outstanding",TRUE)</f>
@@ -17712,7 +17700,7 @@
       </c>
       <c r="C38" s="2">
         <f t="array" aca="1" ref="C38" ca="1">_FV(B38,"Last trade time",TRUE)</f>
-        <v>46185.991058066407</v>
+        <v>46185.997785</v>
       </c>
       <c r="D38" t="str">
         <f t="array" aca="1" ref="D38" ca="1">_FV(B38,"Currency")</f>
@@ -17732,11 +17720,11 @@
       </c>
       <c r="H38" s="6">
         <f t="array" aca="1" ref="H38" ca="1">_FV(B38,"P/E",TRUE)</f>
-        <v>90.7864</v>
+        <v>94.796800000000005</v>
       </c>
       <c r="I38" s="6">
         <f t="array" aca="1" ref="I38" ca="1">_FV(B38,"Beta")</f>
-        <v>2.8325</v>
+        <v>2.8462999999999998</v>
       </c>
       <c r="J38" s="3">
         <f t="array" aca="1" ref="J38" ca="1">_FV(B38,"52 week high",TRUE)</f>
@@ -17764,7 +17752,7 @@
       </c>
       <c r="P38" s="7">
         <f t="array" aca="1" ref="P38" ca="1">_FV(B38,"Volume")</f>
-        <v>784316</v>
+        <v>784371</v>
       </c>
       <c r="Q38" s="7">
         <f t="array" aca="1" ref="Q38" ca="1">_FV(B38,"Volume average",TRUE)</f>
@@ -17800,7 +17788,7 @@
       </c>
       <c r="C39" s="2">
         <f t="array" aca="1" ref="C39" ca="1">_FV(B39,"Last trade time",TRUE)</f>
-        <v>46185.991851874998</v>
+        <v>46185.999993796097</v>
       </c>
       <c r="D39" t="str">
         <f t="array" aca="1" ref="D39" ca="1">_FV(B39,"Currency")</f>
@@ -17824,7 +17812,7 @@
       </c>
       <c r="I39" s="6">
         <f t="array" aca="1" ref="I39" ca="1">_FV(B39,"Beta")</f>
-        <v>2.2080000000000002</v>
+        <v>2.1974</v>
       </c>
       <c r="J39" s="3">
         <f t="array" aca="1" ref="J39" ca="1">_FV(B39,"52 week high",TRUE)</f>
@@ -17852,7 +17840,7 @@
       </c>
       <c r="P39" s="7">
         <f t="array" aca="1" ref="P39" ca="1">_FV(B39,"Volume")</f>
-        <v>151429125</v>
+        <v>151526758</v>
       </c>
       <c r="Q39" s="7">
         <f t="array" aca="1" ref="Q39" ca="1">_FV(B39,"Volume average",TRUE)</f>
@@ -17888,7 +17876,7 @@
       </c>
       <c r="C40" s="2">
         <f t="array" aca="1" ref="C40" ca="1">_FV(B40,"Last trade time",TRUE)</f>
-        <v>46185.991752985938</v>
+        <v>46185.999992441408</v>
       </c>
       <c r="D40" t="str">
         <f t="array" aca="1" ref="D40" ca="1">_FV(B40,"Currency")</f>
@@ -17912,7 +17900,7 @@
       </c>
       <c r="I40" s="6">
         <f t="array" aca="1" ref="I40" ca="1">_FV(B40,"Beta")</f>
-        <v>3.2286000000000001</v>
+        <v>3.2265999999999999</v>
       </c>
       <c r="J40" s="3">
         <f t="array" aca="1" ref="J40" ca="1">_FV(B40,"52 week high",TRUE)</f>
@@ -17940,7 +17928,7 @@
       </c>
       <c r="P40" s="7">
         <f t="array" aca="1" ref="P40" ca="1">_FV(B40,"Volume")</f>
-        <v>24715254</v>
+        <v>24732306</v>
       </c>
       <c r="Q40" s="7">
         <f t="array" aca="1" ref="Q40" ca="1">_FV(B40,"Volume average",TRUE)</f>
@@ -17976,7 +17964,7 @@
       </c>
       <c r="C41" s="2">
         <f t="array" aca="1" ref="C41" ca="1">_FV(B41,"Last trade time",TRUE)</f>
-        <v>46185.991797106253</v>
+        <v>46185.999925207812</v>
       </c>
       <c r="D41" t="str">
         <f t="array" aca="1" ref="D41" ca="1">_FV(B41,"Currency")</f>
@@ -17996,11 +17984,11 @@
       </c>
       <c r="H41" s="6">
         <f t="array" aca="1" ref="H41" ca="1">_FV(B41,"P/E",TRUE)</f>
-        <v>130.303</v>
+        <v>123.62390000000001</v>
       </c>
       <c r="I41" s="6">
         <f t="array" aca="1" ref="I41" ca="1">_FV(B41,"Beta")</f>
-        <v>4.242</v>
+        <v>4.2333999999999996</v>
       </c>
       <c r="J41" s="3">
         <f t="array" aca="1" ref="J41" ca="1">_FV(B41,"52 week high",TRUE)</f>
@@ -18028,7 +18016,7 @@
       </c>
       <c r="P41" s="7">
         <f t="array" aca="1" ref="P41" ca="1">_FV(B41,"Volume")</f>
-        <v>45464015</v>
+        <v>45488280</v>
       </c>
       <c r="Q41" s="7">
         <f t="array" aca="1" ref="Q41" ca="1">_FV(B41,"Volume average",TRUE)</f>
@@ -18064,7 +18052,7 @@
       </c>
       <c r="C42" s="2" cm="1">
         <f t="array" aca="1" ref="C42" ca="1">_FV(B42,"Last trade time",TRUE)</f>
-        <v>46185.99182283516</v>
+        <v>46185.999670508594</v>
       </c>
       <c r="D42" t="str" cm="1">
         <f t="array" aca="1" ref="D42" ca="1">_FV(B42,"Currency")</f>
@@ -18072,15 +18060,15 @@
       </c>
       <c r="E42" s="3" cm="1">
         <f t="array" aca="1" ref="E42" ca="1">_FV(B42,"Price")</f>
-        <v>292.95999999999998</v>
+        <v>292.95</v>
       </c>
       <c r="F42" s="4" cm="1">
         <f t="array" aca="1" ref="F42" ca="1">_FV(B42,"Change (%)",TRUE)</f>
-        <v>8.7810000000000006E-3</v>
+        <v>8.7460000000000003E-3</v>
       </c>
       <c r="G42" s="5" cm="1">
         <f t="array" aca="1" ref="G42" ca="1">_FV(B42,"Change")</f>
-        <v>2.5499999999999998</v>
+        <v>2.54</v>
       </c>
       <c r="H42" s="6" t="e" vm="13">
         <f t="array" ref="H42">_FV(B42,"P/E",TRUE)</f>
@@ -18116,7 +18104,7 @@
       </c>
       <c r="P42" s="7" cm="1">
         <f t="array" aca="1" ref="P42" ca="1">_FV(B42,"Volume")</f>
-        <v>34402871</v>
+        <v>34415247</v>
       </c>
       <c r="Q42" s="7" cm="1">
         <f t="array" aca="1" ref="Q42" ca="1">_FV(B42,"Volume average",TRUE)</f>
@@ -18152,7 +18140,7 @@
       </c>
       <c r="C43" s="2" cm="1">
         <f t="array" aca="1" ref="C43" ca="1">_FV(B43,"Last trade time",TRUE)</f>
-        <v>46185.990906145315</v>
+        <v>46185.99989644609</v>
       </c>
       <c r="D43" t="str" cm="1">
         <f t="array" aca="1" ref="D43" ca="1">_FV(B43,"Currency")</f>
@@ -18172,11 +18160,11 @@
       </c>
       <c r="H43" s="6" cm="1">
         <f t="array" aca="1" ref="H43" ca="1">_FV(B43,"P/E",TRUE)</f>
-        <v>72.066299999999998</v>
+        <v>68.279300000000006</v>
       </c>
       <c r="I43" s="6" cm="1">
         <f t="array" aca="1" ref="I43" ca="1">_FV(B43,"Beta")</f>
-        <v>1.4276</v>
+        <v>1.423</v>
       </c>
       <c r="J43" s="3" cm="1">
         <f t="array" aca="1" ref="J43" ca="1">_FV(B43,"52 week high",TRUE)</f>
@@ -18204,7 +18192,7 @@
       </c>
       <c r="P43" s="7" cm="1">
         <f t="array" aca="1" ref="P43" ca="1">_FV(B43,"Volume")</f>
-        <v>10067212</v>
+        <v>10069200</v>
       </c>
       <c r="Q43" s="7" cm="1">
         <f t="array" aca="1" ref="Q43" ca="1">_FV(B43,"Volume average",TRUE)</f>
@@ -18228,7 +18216,7 @@
       </c>
       <c r="V43" s="7" cm="1">
         <f t="array" aca="1" ref="V43" ca="1">_FV(B43,"Shares outstanding",TRUE)</f>
-        <v>130627500</v>
+        <v>1306275000</v>
       </c>
     </row>
     <row r="44" spans="1:22">
@@ -18240,7 +18228,7 @@
       </c>
       <c r="C44" s="2">
         <f t="array" aca="1" ref="C44" ca="1">_FV(B44,"Last trade time",TRUE)</f>
-        <v>46185.99108288125</v>
+        <v>46185.999995995313</v>
       </c>
       <c r="D44" t="str">
         <f t="array" aca="1" ref="D44" ca="1">_FV(B44,"Currency")</f>
@@ -18264,7 +18252,7 @@
       </c>
       <c r="I44" s="6">
         <f t="array" aca="1" ref="I44" ca="1">_FV(B44,"Beta")</f>
-        <v>0.34039999999999998</v>
+        <v>0.34239999999999998</v>
       </c>
       <c r="J44" s="3">
         <f t="array" aca="1" ref="J44" ca="1">_FV(B44,"52 week high",TRUE)</f>
@@ -18292,7 +18280,7 @@
       </c>
       <c r="P44" s="7">
         <f t="array" aca="1" ref="P44" ca="1">_FV(B44,"Volume")</f>
-        <v>11753507</v>
+        <v>11757678</v>
       </c>
       <c r="Q44" s="7">
         <f t="array" aca="1" ref="Q44" ca="1">_FV(B44,"Volume average",TRUE)</f>
@@ -18328,7 +18316,7 @@
       </c>
       <c r="C45" s="2">
         <f t="array" aca="1" ref="C45" ca="1">_FV(B45,"Last trade time",TRUE)</f>
-        <v>46185.989785821097</v>
+        <v>46185.999923286719</v>
       </c>
       <c r="D45" t="str">
         <f t="array" aca="1" ref="D45" ca="1">_FV(B45,"Currency")</f>
@@ -18352,7 +18340,7 @@
       </c>
       <c r="I45" s="6">
         <f t="array" aca="1" ref="I45" ca="1">_FV(B45,"Beta")</f>
-        <v>1.3573999999999999</v>
+        <v>1.3752</v>
       </c>
       <c r="J45" s="3">
         <f t="array" aca="1" ref="J45" ca="1">_FV(B45,"52 week high",TRUE)</f>
@@ -18380,7 +18368,7 @@
       </c>
       <c r="P45" s="7">
         <f t="array" aca="1" ref="P45" ca="1">_FV(B45,"Volume")</f>
-        <v>4464432</v>
+        <v>4469506</v>
       </c>
       <c r="Q45" s="7">
         <f t="array" aca="1" ref="Q45" ca="1">_FV(B45,"Volume average",TRUE)</f>
@@ -18416,7 +18404,7 @@
       </c>
       <c r="C46" s="2">
         <f t="array" aca="1" ref="C46" ca="1">_FV(B46,"Last trade time",TRUE)</f>
-        <v>46185.983440392971</v>
+        <v>46185.998326318753</v>
       </c>
       <c r="D46" t="str">
         <f t="array" aca="1" ref="D46" ca="1">_FV(B46,"Currency")</f>
@@ -18440,7 +18428,7 @@
       </c>
       <c r="I46" s="6">
         <f t="array" aca="1" ref="I46" ca="1">_FV(B46,"Beta")</f>
-        <v>2.4036</v>
+        <v>2.4154</v>
       </c>
       <c r="J46" s="3">
         <f t="array" aca="1" ref="J46" ca="1">_FV(B46,"52 week high",TRUE)</f>
@@ -18468,7 +18456,7 @@
       </c>
       <c r="P46" s="7">
         <f t="array" aca="1" ref="P46" ca="1">_FV(B46,"Volume")</f>
-        <v>3692605</v>
+        <v>3694090</v>
       </c>
       <c r="Q46" s="7">
         <f t="array" aca="1" ref="Q46" ca="1">_FV(B46,"Volume average",TRUE)</f>
@@ -18504,7 +18492,7 @@
       </c>
       <c r="C47" s="2" cm="1">
         <f t="array" aca="1" ref="C47" ca="1">_FV(B47,"Last trade time",TRUE)</f>
-        <v>46185.991143796091</v>
+        <v>46185.999877106253</v>
       </c>
       <c r="D47" t="str" cm="1">
         <f t="array" aca="1" ref="D47" ca="1">_FV(B47,"Currency")</f>
@@ -18512,23 +18500,23 @@
       </c>
       <c r="E47" s="3" cm="1">
         <f t="array" aca="1" ref="E47" ca="1">_FV(B47,"Price")</f>
-        <v>284.76</v>
+        <v>284.81</v>
       </c>
       <c r="F47" s="4" cm="1">
         <f t="array" aca="1" ref="F47" ca="1">_FV(B47,"Change (%)",TRUE)</f>
-        <v>-3.5120000000000003E-5</v>
+        <v>1.405E-4</v>
       </c>
       <c r="G47" s="5" cm="1">
         <f t="array" aca="1" ref="G47" ca="1">_FV(B47,"Change")</f>
-        <v>-0.01</v>
+        <v>0.04</v>
       </c>
       <c r="H47" s="6" cm="1">
         <f t="array" aca="1" ref="H47" ca="1">_FV(B47,"P/E",TRUE)</f>
-        <v>23.4724</v>
+        <v>23.476500000000001</v>
       </c>
       <c r="I47" s="6" cm="1">
         <f t="array" aca="1" ref="I47" ca="1">_FV(B47,"Beta")</f>
-        <v>0.40529999999999999</v>
+        <v>0.40689999999999998</v>
       </c>
       <c r="J47" s="3" cm="1">
         <f t="array" aca="1" ref="J47" ca="1">_FV(B47,"52 week high",TRUE)</f>
@@ -18556,7 +18544,7 @@
       </c>
       <c r="P47" s="7" cm="1">
         <f t="array" aca="1" ref="P47" ca="1">_FV(B47,"Volume")</f>
-        <v>4028585</v>
+        <v>4028820</v>
       </c>
       <c r="Q47" s="7" cm="1">
         <f t="array" aca="1" ref="Q47" ca="1">_FV(B47,"Volume average",TRUE)</f>
@@ -18576,7 +18564,7 @@
       </c>
       <c r="U47" s="7" cm="1">
         <f t="array" aca="1" ref="U47" ca="1">_FV(B47,"Market cap",TRUE)</f>
-        <v>202323660084</v>
+        <v>202359185379</v>
       </c>
       <c r="V47" s="7" cm="1">
         <f t="array" aca="1" ref="V47" ca="1">_FV(B47,"Shares outstanding",TRUE)</f>
@@ -18592,7 +18580,7 @@
       </c>
       <c r="C48" s="2" cm="1">
         <f t="array" aca="1" ref="C48" ca="1">_FV(B48,"Last trade time",TRUE)</f>
-        <v>46185.990484212503</v>
+        <v>46185.998144767967</v>
       </c>
       <c r="D48" t="str" cm="1">
         <f t="array" aca="1" ref="D48" ca="1">_FV(B48,"Currency")</f>
@@ -18616,7 +18604,7 @@
       </c>
       <c r="I48" s="6" cm="1">
         <f t="array" aca="1" ref="I48" ca="1">_FV(B48,"Beta")</f>
-        <v>1.5255000000000001</v>
+        <v>1.5392999999999999</v>
       </c>
       <c r="J48" s="3" cm="1">
         <f t="array" aca="1" ref="J48" ca="1">_FV(B48,"52 week high",TRUE)</f>
@@ -18644,7 +18632,7 @@
       </c>
       <c r="P48" s="7" cm="1">
         <f t="array" aca="1" ref="P48" ca="1">_FV(B48,"Volume")</f>
-        <v>939643</v>
+        <v>939690</v>
       </c>
       <c r="Q48" s="7" cm="1">
         <f t="array" aca="1" ref="Q48" ca="1">_FV(B48,"Volume average",TRUE)</f>
@@ -18680,7 +18668,7 @@
       </c>
       <c r="C49" s="2">
         <f t="array" aca="1" ref="C49" ca="1">_FV(B49,"Last trade time",TRUE)</f>
-        <v>46185.991854235937</v>
+        <v>46185.999984247654</v>
       </c>
       <c r="D49" t="str">
         <f t="array" aca="1" ref="D49" ca="1">_FV(B49,"Currency")</f>
@@ -18704,7 +18692,7 @@
       </c>
       <c r="I49" s="6">
         <f t="array" aca="1" ref="I49" ca="1">_FV(B49,"Beta")</f>
-        <v>1.2496</v>
+        <v>1.2486999999999999</v>
       </c>
       <c r="J49" s="3">
         <f t="array" aca="1" ref="J49" ca="1">_FV(B49,"52 week high",TRUE)</f>
@@ -18732,7 +18720,7 @@
       </c>
       <c r="P49" s="7">
         <f t="array" aca="1" ref="P49" ca="1">_FV(B49,"Volume")</f>
-        <v>14344391</v>
+        <v>14347769</v>
       </c>
       <c r="Q49" s="7">
         <f t="array" aca="1" ref="Q49" ca="1">_FV(B49,"Volume average",TRUE)</f>
@@ -18768,7 +18756,7 @@
       </c>
       <c r="C50" s="2">
         <f t="array" aca="1" ref="C50" ca="1">_FV(B50,"Last trade time",TRUE)</f>
-        <v>46185.991857453126</v>
+        <v>46185.999876654685</v>
       </c>
       <c r="D50" t="str">
         <f t="array" aca="1" ref="D50" ca="1">_FV(B50,"Currency")</f>
@@ -18788,11 +18776,11 @@
       </c>
       <c r="H50" s="6">
         <f t="array" aca="1" ref="H50" ca="1">_FV(B50,"P/E",TRUE)</f>
-        <v>95.804100000000005</v>
+        <v>96.149000000000001</v>
       </c>
       <c r="I50" s="6">
         <f t="array" aca="1" ref="I50" ca="1">_FV(B50,"Beta")</f>
-        <v>2.1606000000000001</v>
+        <v>2.1802999999999999</v>
       </c>
       <c r="J50" s="3">
         <f t="array" aca="1" ref="J50" ca="1">_FV(B50,"52 week high",TRUE)</f>
@@ -18820,7 +18808,7 @@
       </c>
       <c r="P50" s="7">
         <f t="array" aca="1" ref="P50" ca="1">_FV(B50,"Volume")</f>
-        <v>42143005</v>
+        <v>42162220</v>
       </c>
       <c r="Q50" s="7">
         <f t="array" aca="1" ref="Q50" ca="1">_FV(B50,"Volume average",TRUE)</f>
@@ -18856,7 +18844,7 @@
       </c>
       <c r="C51" s="2">
         <f t="array" aca="1" ref="C51" ca="1">_FV(B51,"Last trade time",TRUE)</f>
-        <v>46185.991877036722</v>
+        <v>46185.99999211797</v>
       </c>
       <c r="D51" t="str">
         <f t="array" aca="1" ref="D51" ca="1">_FV(B51,"Currency")</f>
@@ -18876,11 +18864,11 @@
       </c>
       <c r="H51" s="6">
         <f t="array" aca="1" ref="H51" ca="1">_FV(B51,"P/E",TRUE)</f>
-        <v>23.2727</v>
+        <v>23.248899999999999</v>
       </c>
       <c r="I51" s="6">
         <f t="array" aca="1" ref="I51" ca="1">_FV(B51,"Beta")</f>
-        <v>1.1322000000000001</v>
+        <v>1.1292</v>
       </c>
       <c r="J51" s="3">
         <f t="array" aca="1" ref="J51" ca="1">_FV(B51,"52 week high",TRUE)</f>
@@ -18908,7 +18896,7 @@
       </c>
       <c r="P51" s="7">
         <f t="array" aca="1" ref="P51" ca="1">_FV(B51,"Volume")</f>
-        <v>34914267</v>
+        <v>34922036</v>
       </c>
       <c r="Q51" s="7">
         <f t="array" aca="1" ref="Q51" ca="1">_FV(B51,"Volume average",TRUE)</f>
@@ -18944,7 +18932,7 @@
       </c>
       <c r="C52" s="2">
         <f t="array" aca="1" ref="C52" ca="1">_FV(B52,"Last trade time",TRUE)</f>
-        <v>46185.991724293752</v>
+        <v>46185.999969003904</v>
       </c>
       <c r="D52" t="str">
         <f t="array" aca="1" ref="D52" ca="1">_FV(B52,"Currency")</f>
@@ -18968,7 +18956,7 @@
       </c>
       <c r="I52" s="6">
         <f t="array" aca="1" ref="I52" ca="1">_FV(B52,"Beta")</f>
-        <v>3.5194000000000001</v>
+        <v>3.5110000000000001</v>
       </c>
       <c r="J52" s="3">
         <f t="array" aca="1" ref="J52" ca="1">_FV(B52,"52 week high",TRUE)</f>
@@ -18996,7 +18984,7 @@
       </c>
       <c r="P52" s="7">
         <f t="array" aca="1" ref="P52" ca="1">_FV(B52,"Volume")</f>
-        <v>16830307</v>
+        <v>16836331</v>
       </c>
       <c r="Q52" s="7">
         <f t="array" aca="1" ref="Q52" ca="1">_FV(B52,"Volume average",TRUE)</f>
@@ -19032,7 +19020,7 @@
       </c>
       <c r="C53" s="2">
         <f t="array" aca="1" ref="C53" ca="1">_FV(B53,"Last trade time",TRUE)</f>
-        <v>46185.991811550783</v>
+        <v>46185.999998182815</v>
       </c>
       <c r="D53" t="str">
         <f t="array" aca="1" ref="D53" ca="1">_FV(B53,"Currency")</f>
@@ -19052,11 +19040,11 @@
       </c>
       <c r="H53" s="6">
         <f t="array" aca="1" ref="H53" ca="1">_FV(B53,"P/E",TRUE)</f>
-        <v>46.343200000000003</v>
+        <v>47.016500000000001</v>
       </c>
       <c r="I53" s="6">
         <f t="array" aca="1" ref="I53" ca="1">_FV(B53,"Beta")</f>
-        <v>2.1598999999999999</v>
+        <v>2.1677</v>
       </c>
       <c r="J53" s="3">
         <f t="array" aca="1" ref="J53" ca="1">_FV(B53,"52 week high",TRUE)</f>
@@ -19084,7 +19072,7 @@
       </c>
       <c r="P53" s="7">
         <f t="array" aca="1" ref="P53" ca="1">_FV(B53,"Volume")</f>
-        <v>40946517</v>
+        <v>40995386</v>
       </c>
       <c r="Q53" s="7">
         <f t="array" aca="1" ref="Q53" ca="1">_FV(B53,"Volume average",TRUE)</f>
@@ -19120,7 +19108,7 @@
       </c>
       <c r="C54" s="2" cm="1">
         <f t="array" aca="1" ref="C54" ca="1">_FV(B54,"Last trade time",TRUE)</f>
-        <v>46185.985635126563</v>
+        <v>46185.999147325783</v>
       </c>
       <c r="D54" t="str" cm="1">
         <f t="array" aca="1" ref="D54" ca="1">_FV(B54,"Currency")</f>
@@ -19128,15 +19116,15 @@
       </c>
       <c r="E54" s="3" cm="1">
         <f t="array" aca="1" ref="E54" ca="1">_FV(B54,"Price")</f>
-        <v>228.51</v>
+        <v>228.48</v>
       </c>
       <c r="F54" s="4" cm="1">
         <f t="array" aca="1" ref="F54" ca="1">_FV(B54,"Change (%)",TRUE)</f>
-        <v>4.705E-3</v>
+        <v>4.5729999999999998E-3</v>
       </c>
       <c r="G54" s="5" cm="1">
         <f t="array" aca="1" ref="G54" ca="1">_FV(B54,"Change")</f>
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="H54" s="6" t="e" cm="1" vm="13">
         <f t="array" ref="H54">_FV(B54,"P/E",TRUE)</f>
@@ -19144,7 +19132,7 @@
       </c>
       <c r="I54" s="6" cm="1">
         <f t="array" aca="1" ref="I54" ca="1">_FV(B54,"Beta")</f>
-        <v>1.6829000000000001</v>
+        <v>1.6826000000000001</v>
       </c>
       <c r="J54" s="3" cm="1">
         <f t="array" aca="1" ref="J54" ca="1">_FV(B54,"52 week high",TRUE)</f>
@@ -19172,7 +19160,7 @@
       </c>
       <c r="P54" s="7" cm="1">
         <f t="array" aca="1" ref="P54" ca="1">_FV(B54,"Volume")</f>
-        <v>2261887</v>
+        <v>2262011</v>
       </c>
       <c r="Q54" s="7" cm="1">
         <f t="array" aca="1" ref="Q54" ca="1">_FV(B54,"Volume average",TRUE)</f>
@@ -19192,7 +19180,7 @@
       </c>
       <c r="U54" s="7" cm="1">
         <f t="array" aca="1" ref="U54" ca="1">_FV(B54,"Market cap",TRUE)</f>
-        <v>81107247996</v>
+        <v>81096599808</v>
       </c>
       <c r="V54" s="7" cm="1">
         <f t="array" aca="1" ref="V54" ca="1">_FV(B54,"Shares outstanding",TRUE)</f>
@@ -19232,7 +19220,7 @@
       </c>
       <c r="I55" s="6" cm="1">
         <f t="array" aca="1" ref="I55" ca="1">_FV(B55,"Beta")</f>
-        <v>1.1021000000000001</v>
+        <v>1.1107</v>
       </c>
       <c r="J55" s="3" t="e" cm="1" vm="59">
         <f t="array" ref="J55">_FV(B55,"52 week high",TRUE)</f>
@@ -19264,7 +19252,7 @@
       </c>
       <c r="Q55" s="7" cm="1">
         <f t="array" aca="1" ref="Q55" ca="1">_FV(B55,"Volume average",TRUE)</f>
-        <v>22055800</v>
+        <v>19813320</v>
       </c>
       <c r="R55" s="8" cm="1">
         <f t="array" aca="1" ref="R55" ca="1">_FV(B55,"Year incorporated",TRUE)</f>
@@ -19296,7 +19284,7 @@
       </c>
       <c r="C56" s="2">
         <f t="array" aca="1" ref="C56" ca="1">_FV(B56,"Last trade time",TRUE)</f>
-        <v>46185.99172277734</v>
+        <v>46185.999987441406</v>
       </c>
       <c r="D56" t="str">
         <f t="array" aca="1" ref="D56" ca="1">_FV(B56,"Currency")</f>
@@ -19316,11 +19304,11 @@
       </c>
       <c r="H56" s="6">
         <f t="array" aca="1" ref="H56" ca="1">_FV(B56,"P/E",TRUE)</f>
-        <v>91.982600000000005</v>
+        <v>87.584500000000006</v>
       </c>
       <c r="I56" s="6">
         <f t="array" aca="1" ref="I56" ca="1">_FV(B56,"Beta")</f>
-        <v>1.1597</v>
+        <v>1.1482000000000001</v>
       </c>
       <c r="J56" s="3">
         <f t="array" aca="1" ref="J56" ca="1">_FV(B56,"52 week high",TRUE)</f>
@@ -19348,7 +19336,7 @@
       </c>
       <c r="P56" s="7">
         <f t="array" aca="1" ref="P56" ca="1">_FV(B56,"Volume")</f>
-        <v>117839241</v>
+        <v>117902581</v>
       </c>
       <c r="Q56" s="7">
         <f t="array" aca="1" ref="Q56" ca="1">_FV(B56,"Volume average",TRUE)</f>
@@ -19384,7 +19372,7 @@
       </c>
       <c r="C57" s="2">
         <f t="array" aca="1" ref="C57" ca="1">_FV(B57,"Last trade time",TRUE)</f>
-        <v>46185.991609560158</v>
+        <v>46185.999951457816</v>
       </c>
       <c r="D57" t="str">
         <f t="array" aca="1" ref="D57" ca="1">_FV(B57,"Currency")</f>
@@ -19392,23 +19380,23 @@
       </c>
       <c r="E57" s="3">
         <f t="array" aca="1" ref="E57" ca="1">_FV(B57,"Price")</f>
-        <v>102.18</v>
+        <v>102.15</v>
       </c>
       <c r="F57" s="4">
         <f t="array" aca="1" ref="F57" ca="1">_FV(B57,"Change (%)",TRUE)</f>
-        <v>-8.7309999999999992E-3</v>
+        <v>-9.0220000000000005E-3</v>
       </c>
       <c r="G57" s="5">
         <f t="array" aca="1" ref="G57" ca="1">_FV(B57,"Change")</f>
-        <v>-0.9</v>
+        <v>-0.93</v>
       </c>
       <c r="H57" s="6">
         <f t="array" aca="1" ref="H57" ca="1">_FV(B57,"P/E",TRUE)</f>
-        <v>60.770800000000001</v>
+        <v>60.752899999999997</v>
       </c>
       <c r="I57" s="6">
         <f t="array" aca="1" ref="I57" ca="1">_FV(B57,"Beta")</f>
-        <v>0.96730000000000005</v>
+        <v>0.96460000000000001</v>
       </c>
       <c r="J57" s="3">
         <f t="array" aca="1" ref="J57" ca="1">_FV(B57,"52 week high",TRUE)</f>
@@ -19436,7 +19424,7 @@
       </c>
       <c r="P57" s="7">
         <f t="array" aca="1" ref="P57" ca="1">_FV(B57,"Volume")</f>
-        <v>26043001</v>
+        <v>26049350</v>
       </c>
       <c r="Q57" s="7">
         <f t="array" aca="1" ref="Q57" ca="1">_FV(B57,"Volume average",TRUE)</f>
@@ -19456,7 +19444,7 @@
       </c>
       <c r="U57" s="7">
         <f t="array" aca="1" ref="U57" ca="1">_FV(B57,"Market cap",TRUE)</f>
-        <v>105379051440</v>
+        <v>105348112200</v>
       </c>
       <c r="V57" s="7">
         <f t="array" aca="1" ref="V57" ca="1">_FV(B57,"Shares outstanding",TRUE)</f>
@@ -19472,7 +19460,7 @@
       </c>
       <c r="C58" s="2">
         <f t="array" aca="1" ref="C58" ca="1">_FV(B58,"Last trade time",TRUE)</f>
-        <v>46185.991765126564</v>
+        <v>46185.999999328124</v>
       </c>
       <c r="D58" t="str">
         <f t="array" aca="1" ref="D58" ca="1">_FV(B58,"Currency")</f>
@@ -19492,11 +19480,11 @@
       </c>
       <c r="H58" s="6">
         <f t="array" aca="1" ref="H58" ca="1">_FV(B58,"P/E",TRUE)</f>
-        <v>31.422699999999999</v>
+        <v>31.373799999999999</v>
       </c>
       <c r="I58" s="6">
         <f t="array" aca="1" ref="I58" ca="1">_FV(B58,"Beta")</f>
-        <v>2.2021999999999999</v>
+        <v>2.2042999999999999</v>
       </c>
       <c r="J58" s="3">
         <f t="array" aca="1" ref="J58" ca="1">_FV(B58,"52 week high",TRUE)</f>
@@ -19524,7 +19512,7 @@
       </c>
       <c r="P58" s="7">
         <f t="array" aca="1" ref="P58" ca="1">_FV(B58,"Volume")</f>
-        <v>112225632</v>
+        <v>112345314</v>
       </c>
       <c r="Q58" s="7">
         <f t="array" aca="1" ref="Q58" ca="1">_FV(B58,"Volume average",TRUE)</f>
@@ -19560,7 +19548,7 @@
       </c>
       <c r="C59" s="2" cm="1">
         <f t="array" aca="1" ref="C59" ca="1">_FV(B59,"Last trade time",TRUE)</f>
-        <v>46185.991209606247</v>
+        <v>46185.997945323441</v>
       </c>
       <c r="D59" t="str" cm="1">
         <f t="array" aca="1" ref="D59" ca="1">_FV(B59,"Currency")</f>
@@ -19580,11 +19568,11 @@
       </c>
       <c r="H59" s="6" cm="1">
         <f t="array" aca="1" ref="H59" ca="1">_FV(B59,"P/E",TRUE)</f>
-        <v>83.397599999999997</v>
+        <v>82.806100000000001</v>
       </c>
       <c r="I59" s="6" cm="1">
         <f t="array" aca="1" ref="I59" ca="1">_FV(B59,"Beta")</f>
-        <v>1.9766999999999999</v>
+        <v>1.9774</v>
       </c>
       <c r="J59" s="3" cm="1">
         <f t="array" aca="1" ref="J59" ca="1">_FV(B59,"52 week high",TRUE)</f>
@@ -19612,7 +19600,7 @@
       </c>
       <c r="P59" s="7" cm="1">
         <f t="array" aca="1" ref="P59" ca="1">_FV(B59,"Volume")</f>
-        <v>7351548</v>
+        <v>7351855</v>
       </c>
       <c r="Q59" s="7" cm="1">
         <f t="array" aca="1" ref="Q59" ca="1">_FV(B59,"Volume average",TRUE)</f>
@@ -19648,7 +19636,7 @@
       </c>
       <c r="C60" s="2">
         <f t="array" aca="1" ref="C60" ca="1">_FV(B60,"Last trade time",TRUE)</f>
-        <v>46185.991769490625</v>
+        <v>46185.999961758593</v>
       </c>
       <c r="D60" t="str">
         <f t="array" aca="1" ref="D60" ca="1">_FV(B60,"Currency")</f>
@@ -19668,11 +19656,11 @@
       </c>
       <c r="H60" s="6">
         <f t="array" aca="1" ref="H60" ca="1">_FV(B60,"P/E",TRUE)</f>
-        <v>23.524999999999999</v>
+        <v>24.788799999999998</v>
       </c>
       <c r="I60" s="6">
         <f t="array" aca="1" ref="I60" ca="1">_FV(B60,"Beta")</f>
-        <v>2.6909000000000001</v>
+        <v>2.6936</v>
       </c>
       <c r="J60" s="3">
         <f t="array" aca="1" ref="J60" ca="1">_FV(B60,"52 week high",TRUE)</f>
@@ -19700,7 +19688,7 @@
       </c>
       <c r="P60" s="7">
         <f t="array" aca="1" ref="P60" ca="1">_FV(B60,"Volume")</f>
-        <v>55341963</v>
+        <v>55365320</v>
       </c>
       <c r="Q60" s="7">
         <f t="array" aca="1" ref="Q60" ca="1">_FV(B60,"Volume average",TRUE)</f>
@@ -19736,7 +19724,7 @@
       </c>
       <c r="C61" s="2">
         <f t="array" aca="1" ref="C61" ca="1">_FV(B61,"Last trade time",TRUE)</f>
-        <v>46185.991856122659</v>
+        <v>46185.999982418747</v>
       </c>
       <c r="D61" t="str">
         <f t="array" aca="1" ref="D61" ca="1">_FV(B61,"Currency")</f>
@@ -19744,23 +19732,23 @@
       </c>
       <c r="E61" s="3">
         <f t="array" aca="1" ref="E61" ca="1">_FV(B61,"Price")</f>
-        <v>184.09</v>
+        <v>184.13</v>
       </c>
       <c r="F61" s="4">
         <f t="array" aca="1" ref="F61" ca="1">_FV(B61,"Change (%)",TRUE)</f>
-        <v>-5.4320000000000002E-5</v>
+        <v>1.6299999999999998E-4</v>
       </c>
       <c r="G61" s="5">
         <f t="array" aca="1" ref="G61" ca="1">_FV(B61,"Change")</f>
-        <v>-0.01</v>
+        <v>0.03</v>
       </c>
       <c r="H61" s="6">
         <f t="array" aca="1" ref="H61" ca="1">_FV(B61,"P/E",TRUE)</f>
-        <v>29.7789</v>
+        <v>29.785299999999999</v>
       </c>
       <c r="I61" s="6">
         <f t="array" aca="1" ref="I61" ca="1">_FV(B61,"Beta")</f>
-        <v>1.6963999999999999</v>
+        <v>1.6926000000000001</v>
       </c>
       <c r="J61" s="3">
         <f t="array" aca="1" ref="J61" ca="1">_FV(B61,"52 week high",TRUE)</f>
@@ -19788,7 +19776,7 @@
       </c>
       <c r="P61" s="7">
         <f t="array" aca="1" ref="P61" ca="1">_FV(B61,"Volume")</f>
-        <v>29549532</v>
+        <v>29562284</v>
       </c>
       <c r="Q61" s="7">
         <f t="array" aca="1" ref="Q61" ca="1">_FV(B61,"Volume average",TRUE)</f>
@@ -19808,7 +19796,7 @@
       </c>
       <c r="U61" s="7">
         <f t="array" aca="1" ref="U61" ca="1">_FV(B61,"Market cap",TRUE)</f>
-        <v>529451308140</v>
+        <v>529566349980</v>
       </c>
       <c r="V61" s="7">
         <f t="array" aca="1" ref="V61" ca="1">_FV(B61,"Shares outstanding",TRUE)</f>
@@ -19824,7 +19812,7 @@
       </c>
       <c r="C62" s="2" cm="1">
         <f t="array" aca="1" ref="C62" ca="1">_FV(B62,"Last trade time",TRUE)</f>
-        <v>46185.990997753906</v>
+        <v>46185.999874409375</v>
       </c>
       <c r="D62" t="str" cm="1">
         <f t="array" aca="1" ref="D62" ca="1">_FV(B62,"Currency")</f>
@@ -19844,11 +19832,11 @@
       </c>
       <c r="H62" s="6" cm="1">
         <f t="array" aca="1" ref="H62" ca="1">_FV(B62,"P/E",TRUE)</f>
-        <v>230.2347</v>
+        <v>230.1662</v>
       </c>
       <c r="I62" s="6" cm="1">
         <f t="array" aca="1" ref="I62" ca="1">_FV(B62,"Beta")</f>
-        <v>0.94410000000000005</v>
+        <v>0.94489999999999996</v>
       </c>
       <c r="J62" s="3" cm="1">
         <f t="array" aca="1" ref="J62" ca="1">_FV(B62,"52 week high",TRUE)</f>
@@ -19876,7 +19864,7 @@
       </c>
       <c r="P62" s="7" cm="1">
         <f t="array" aca="1" ref="P62" ca="1">_FV(B62,"Volume")</f>
-        <v>6774009</v>
+        <v>6774241</v>
       </c>
       <c r="Q62" s="7" cm="1">
         <f t="array" aca="1" ref="Q62" ca="1">_FV(B62,"Volume average",TRUE)</f>
@@ -19912,7 +19900,7 @@
       </c>
       <c r="C63" s="2">
         <f t="array" aca="1" ref="C63" ca="1">_FV(B63,"Last trade time",TRUE)</f>
-        <v>46185.990983529686</v>
+        <v>46185.999587789061</v>
       </c>
       <c r="D63" t="str">
         <f t="array" aca="1" ref="D63" ca="1">_FV(B63,"Currency")</f>
@@ -19920,23 +19908,23 @@
       </c>
       <c r="E63" s="3">
         <f t="array" aca="1" ref="E63" ca="1">_FV(B63,"Price")</f>
-        <v>10.545</v>
+        <v>10.55</v>
       </c>
       <c r="F63" s="4">
         <f t="array" aca="1" ref="F63" ca="1">_FV(B63,"Change (%)",TRUE)</f>
-        <v>-9.8589999999999997E-3</v>
+        <v>-9.389999999999999E-3</v>
       </c>
       <c r="G63" s="5">
         <f t="array" aca="1" ref="G63" ca="1">_FV(B63,"Change")</f>
-        <v>-0.105</v>
+        <v>-0.1</v>
       </c>
       <c r="H63" s="6">
         <f t="array" aca="1" ref="H63" ca="1">_FV(B63,"P/E",TRUE)</f>
-        <v>17.528300000000002</v>
+        <v>17.5366</v>
       </c>
       <c r="I63" s="6">
         <f t="array" aca="1" ref="I63" ca="1">_FV(B63,"Beta")</f>
-        <v>0.97919999999999996</v>
+        <v>0.98089999999999999</v>
       </c>
       <c r="J63" s="3">
         <f t="array" aca="1" ref="J63" ca="1">_FV(B63,"52 week high",TRUE)</f>
@@ -19964,7 +19952,7 @@
       </c>
       <c r="P63" s="7">
         <f t="array" aca="1" ref="P63" ca="1">_FV(B63,"Volume")</f>
-        <v>40791231</v>
+        <v>40796703</v>
       </c>
       <c r="Q63" s="7">
         <f t="array" aca="1" ref="Q63" ca="1">_FV(B63,"Volume average",TRUE)</f>
@@ -19984,7 +19972,7 @@
       </c>
       <c r="U63" s="7">
         <f t="array" aca="1" ref="U63" ca="1">_FV(B63,"Market cap",TRUE)</f>
-        <v>5463578563</v>
+        <v>5466169165</v>
       </c>
       <c r="V63" s="7">
         <f t="array" aca="1" ref="V63" ca="1">_FV(B63,"Shares outstanding",TRUE)</f>
@@ -20000,7 +19988,7 @@
       </c>
       <c r="C64" s="2" cm="1">
         <f t="array" aca="1" ref="C64" ca="1">_FV(B64,"Last trade time",TRUE)</f>
-        <v>46185.990763633592</v>
+        <v>46185.999786885935</v>
       </c>
       <c r="D64" t="str" cm="1">
         <f t="array" aca="1" ref="D64" ca="1">_FV(B64,"Currency")</f>
@@ -20008,19 +19996,19 @@
       </c>
       <c r="E64" s="3" cm="1">
         <f t="array" aca="1" ref="E64" ca="1">_FV(B64,"Price")</f>
-        <v>149.58000000000001</v>
+        <v>149.61000000000001</v>
       </c>
       <c r="F64" s="4" cm="1">
         <f t="array" aca="1" ref="F64" ca="1">_FV(B64,"Change (%)",TRUE)</f>
-        <v>8.3590000000000001E-3</v>
+        <v>8.5609999999999992E-3</v>
       </c>
       <c r="G64" s="5" cm="1">
         <f t="array" aca="1" ref="G64" ca="1">_FV(B64,"Change")</f>
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="H64" s="6" cm="1">
         <f t="array" aca="1" ref="H64" ca="1">_FV(B64,"P/E",TRUE)</f>
-        <v>21.876100000000001</v>
+        <v>21.880500000000001</v>
       </c>
       <c r="I64" s="6" cm="1">
         <f t="array" aca="1" ref="I64" ca="1">_FV(B64,"Beta")</f>
@@ -20052,7 +20040,7 @@
       </c>
       <c r="P64" s="7" cm="1">
         <f t="array" aca="1" ref="P64" ca="1">_FV(B64,"Volume")</f>
-        <v>6831292</v>
+        <v>6832001</v>
       </c>
       <c r="Q64" s="7" cm="1">
         <f t="array" aca="1" ref="Q64" ca="1">_FV(B64,"Volume average",TRUE)</f>
@@ -20072,7 +20060,7 @@
       </c>
       <c r="U64" s="7" cm="1">
         <f t="array" aca="1" ref="U64" ca="1">_FV(B64,"Market cap",TRUE)</f>
-        <v>348311838420</v>
+        <v>348381696390</v>
       </c>
       <c r="V64" s="7" cm="1">
         <f t="array" aca="1" ref="V64" ca="1">_FV(B64,"Shares outstanding",TRUE)</f>
@@ -20088,7 +20076,7 @@
       </c>
       <c r="C65" s="2">
         <f t="array" aca="1" ref="C65" ca="1">_FV(B65,"Last trade time",TRUE)</f>
-        <v>46185.990397198439</v>
+        <v>46185.997376943749</v>
       </c>
       <c r="D65" t="str">
         <f t="array" aca="1" ref="D65" ca="1">_FV(B65,"Currency")</f>
@@ -20112,7 +20100,7 @@
       </c>
       <c r="I65" s="6">
         <f t="array" aca="1" ref="I65" ca="1">_FV(B65,"Beta")</f>
-        <v>1.3777999999999999</v>
+        <v>1.3705000000000001</v>
       </c>
       <c r="J65" s="3">
         <f t="array" aca="1" ref="J65" ca="1">_FV(B65,"52 week high",TRUE)</f>
@@ -20140,7 +20128,7 @@
       </c>
       <c r="P65" s="7">
         <f t="array" aca="1" ref="P65" ca="1">_FV(B65,"Volume")</f>
-        <v>1201949</v>
+        <v>1202084</v>
       </c>
       <c r="Q65" s="7">
         <f t="array" aca="1" ref="Q65" ca="1">_FV(B65,"Volume average",TRUE)</f>
@@ -20160,11 +20148,11 @@
       </c>
       <c r="U65" s="7">
         <f t="array" aca="1" ref="U65" ca="1">_FV(B65,"Market cap",TRUE)</f>
-        <v>1873951874</v>
+        <v>1873866386</v>
       </c>
       <c r="V65" s="7">
         <f t="array" aca="1" ref="V65" ca="1">_FV(B65,"Shares outstanding",TRUE)</f>
-        <v>58966390</v>
+        <v>58963700</v>
       </c>
     </row>
     <row r="66" spans="1:22">
@@ -20176,7 +20164,7 @@
       </c>
       <c r="C66" s="2">
         <f t="array" aca="1" ref="C66" ca="1">_FV(B66,"Last trade time",TRUE)</f>
-        <v>46185.990933275003</v>
+        <v>46185.999806539061</v>
       </c>
       <c r="D66" t="str">
         <f t="array" aca="1" ref="D66" ca="1">_FV(B66,"Currency")</f>
@@ -20200,7 +20188,7 @@
       </c>
       <c r="I66" s="6">
         <f t="array" aca="1" ref="I66" ca="1">_FV(B66,"Beta")</f>
-        <v>0.7591</v>
+        <v>0.73129999999999995</v>
       </c>
       <c r="J66" s="3">
         <f t="array" aca="1" ref="J66" ca="1">_FV(B66,"52 week high",TRUE)</f>
@@ -20228,7 +20216,7 @@
       </c>
       <c r="P66" s="7">
         <f t="array" aca="1" ref="P66" ca="1">_FV(B66,"Volume")</f>
-        <v>34142496</v>
+        <v>34162850</v>
       </c>
       <c r="Q66" s="7">
         <f t="array" aca="1" ref="Q66" ca="1">_FV(B66,"Volume average",TRUE)</f>
@@ -20264,7 +20252,7 @@
       </c>
       <c r="C67" s="2" cm="1">
         <f t="array" aca="1" ref="C67" ca="1">_FV(B67,"Last trade time",TRUE)</f>
-        <v>46185.99180695547</v>
+        <v>46185.999892094529</v>
       </c>
       <c r="D67" t="str" cm="1">
         <f t="array" aca="1" ref="D67" ca="1">_FV(B67,"Currency")</f>
@@ -20284,11 +20272,11 @@
       </c>
       <c r="H67" s="6" cm="1">
         <f t="array" aca="1" ref="H67" ca="1">_FV(B67,"P/E",TRUE)</f>
-        <v>23.029599999999999</v>
+        <v>22.076599999999999</v>
       </c>
       <c r="I67" s="6" cm="1">
         <f t="array" aca="1" ref="I67" ca="1">_FV(B67,"Beta")</f>
-        <v>1.6380999999999999</v>
+        <v>1.6257999999999999</v>
       </c>
       <c r="J67" s="3" cm="1">
         <f t="array" aca="1" ref="J67" ca="1">_FV(B67,"52 week high",TRUE)</f>
@@ -20316,7 +20304,7 @@
       </c>
       <c r="P67" s="7" cm="1">
         <f t="array" aca="1" ref="P67" ca="1">_FV(B67,"Volume")</f>
-        <v>14132047</v>
+        <v>14134861</v>
       </c>
       <c r="Q67" s="7" cm="1">
         <f t="array" aca="1" ref="Q67" ca="1">_FV(B67,"Volume average",TRUE)</f>
@@ -20372,11 +20360,11 @@
       </c>
       <c r="H68" s="6">
         <f t="array" aca="1" ref="H68" ca="1">_FV(B68,"P/E",TRUE)</f>
-        <v>19.975200000000001</v>
+        <v>19.901599999999998</v>
       </c>
       <c r="I68" s="6">
         <f t="array" aca="1" ref="I68" ca="1">_FV(B68,"Beta")</f>
-        <v>0.64229999999999998</v>
+        <v>0.64329999999999998</v>
       </c>
       <c r="J68" s="3">
         <f t="array" aca="1" ref="J68" ca="1">_FV(B68,"52 week high",TRUE)</f>
@@ -20440,7 +20428,7 @@
       </c>
       <c r="C69" s="2" cm="1">
         <f t="array" aca="1" ref="C69" ca="1">_FV(B69,"Last trade time",TRUE)</f>
-        <v>46185.99172371484</v>
+        <v>46185.999972175778</v>
       </c>
       <c r="D69" t="str" cm="1">
         <f t="array" aca="1" ref="D69" ca="1">_FV(B69,"Currency")</f>
@@ -20492,7 +20480,7 @@
       </c>
       <c r="P69" s="7" cm="1">
         <f t="array" aca="1" ref="P69" ca="1">_FV(B69,"Volume")</f>
-        <v>51224656</v>
+        <v>51236021</v>
       </c>
       <c r="Q69" s="7" cm="1">
         <f t="array" aca="1" ref="Q69" ca="1">_FV(B69,"Volume average",TRUE)</f>
@@ -20528,7 +20516,7 @@
       </c>
       <c r="C70" s="2" cm="1">
         <f t="array" aca="1" ref="C70" ca="1">_FV(B70,"Last trade time",TRUE)</f>
-        <v>46185.990280103906</v>
+        <v>46185.990280115628</v>
       </c>
       <c r="D70" t="str" cm="1">
         <f t="array" aca="1" ref="D70" ca="1">_FV(B70,"Currency")</f>
@@ -20536,23 +20524,23 @@
       </c>
       <c r="E70" s="3" cm="1">
         <f t="array" aca="1" ref="E70" ca="1">_FV(B70,"Price")</f>
-        <v>459.27</v>
+        <v>459.34</v>
       </c>
       <c r="F70" s="4" cm="1">
         <f t="array" aca="1" ref="F70" ca="1">_FV(B70,"Change (%)",TRUE)</f>
-        <v>3.6709999999999998E-3</v>
+        <v>3.8240000000000001E-3</v>
       </c>
       <c r="G70" s="5" cm="1">
         <f t="array" aca="1" ref="G70" ca="1">_FV(B70,"Change")</f>
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="H70" s="6" cm="1">
         <f t="array" aca="1" ref="H70" ca="1">_FV(B70,"P/E",TRUE)</f>
-        <v>47.7104</v>
+        <v>47.717700000000001</v>
       </c>
       <c r="I70" s="6" cm="1">
         <f t="array" aca="1" ref="I70" ca="1">_FV(B70,"Beta")</f>
-        <v>1.5444</v>
+        <v>1.5475000000000001</v>
       </c>
       <c r="J70" s="3" cm="1">
         <f t="array" aca="1" ref="J70" ca="1">_FV(B70,"52 week high",TRUE)</f>
@@ -20600,7 +20588,7 @@
       </c>
       <c r="U70" s="7" cm="1">
         <f t="array" aca="1" ref="U70" ca="1">_FV(B70,"Market cap",TRUE)</f>
-        <v>51104764053</v>
+        <v>51112553226</v>
       </c>
       <c r="V70" s="7" cm="1">
         <f t="array" aca="1" ref="V70" ca="1">_FV(B70,"Shares outstanding",TRUE)</f>
@@ -20616,7 +20604,7 @@
       </c>
       <c r="C71" s="2" cm="1">
         <f t="array" aca="1" ref="C71" ca="1">_FV(B71,"Last trade time",TRUE)</f>
-        <v>46185.991276885936</v>
+        <v>46185.999885057812</v>
       </c>
       <c r="D71" t="str" cm="1">
         <f t="array" aca="1" ref="D71" ca="1">_FV(B71,"Currency")</f>
@@ -20640,7 +20628,7 @@
       </c>
       <c r="I71" s="6" cm="1">
         <f t="array" aca="1" ref="I71" ca="1">_FV(B71,"Beta")</f>
-        <v>1.0251999999999999</v>
+        <v>1.0235000000000001</v>
       </c>
       <c r="J71" s="3" cm="1">
         <f t="array" aca="1" ref="J71" ca="1">_FV(B71,"52 week high",TRUE)</f>
@@ -20668,7 +20656,7 @@
       </c>
       <c r="P71" s="7" cm="1">
         <f t="array" aca="1" ref="P71" ca="1">_FV(B71,"Volume")</f>
-        <v>14836675</v>
+        <v>14837646</v>
       </c>
       <c r="Q71" s="7" cm="1">
         <f t="array" aca="1" ref="Q71" ca="1">_FV(B71,"Volume average",TRUE)</f>
@@ -20704,7 +20692,7 @@
       </c>
       <c r="C72" s="2" cm="1">
         <f t="array" aca="1" ref="C72" ca="1">_FV(B72,"Last trade time",TRUE)</f>
-        <v>46185.991668900002</v>
+        <v>46185.994088738284</v>
       </c>
       <c r="D72" t="str" cm="1">
         <f t="array" aca="1" ref="D72" ca="1">_FV(B72,"Currency")</f>
@@ -20712,23 +20700,23 @@
       </c>
       <c r="E72" s="3" cm="1">
         <f t="array" aca="1" ref="E72" ca="1">_FV(B72,"Price")</f>
-        <v>14.86</v>
+        <v>14.85</v>
       </c>
       <c r="F72" s="4" cm="1">
         <f t="array" aca="1" ref="F72" ca="1">_FV(B72,"Change (%)",TRUE)</f>
-        <v>6.7749999999999998E-3</v>
+        <v>6.0980000000000001E-3</v>
       </c>
       <c r="G72" s="5" cm="1">
         <f t="array" aca="1" ref="G72" ca="1">_FV(B72,"Change")</f>
-        <v>0.1</v>
-      </c>
-      <c r="H72" s="6" cm="1">
-        <f t="array" aca="1" ref="H72" ca="1">_FV(B72,"P/E",TRUE)</f>
-        <v>0</v>
+        <v>0.09</v>
+      </c>
+      <c r="H72" s="6" t="e" cm="1" vm="13">
+        <f t="array" ref="H72">_FV(B72,"P/E",TRUE)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="I72" s="6" cm="1">
         <f t="array" aca="1" ref="I72" ca="1">_FV(B72,"Beta")</f>
-        <v>0.85340000000000005</v>
+        <v>0.85019999999999996</v>
       </c>
       <c r="J72" s="3" cm="1">
         <f t="array" aca="1" ref="J72" ca="1">_FV(B72,"52 week high",TRUE)</f>
@@ -20756,7 +20744,7 @@
       </c>
       <c r="P72" s="7" cm="1">
         <f t="array" aca="1" ref="P72" ca="1">_FV(B72,"Volume")</f>
-        <v>5463207</v>
+        <v>5463213</v>
       </c>
       <c r="Q72" s="7" cm="1">
         <f t="array" aca="1" ref="Q72" ca="1">_FV(B72,"Volume average",TRUE)</f>
@@ -20776,7 +20764,7 @@
       </c>
       <c r="U72" s="7" cm="1">
         <f t="array" aca="1" ref="U72" ca="1">_FV(B72,"Market cap",TRUE)</f>
-        <v>5094062982</v>
+        <v>5090634945</v>
       </c>
       <c r="V72" s="7" cm="1">
         <f t="array" aca="1" ref="V72" ca="1">_FV(B72,"Shares outstanding",TRUE)</f>
@@ -20816,7 +20804,7 @@
       </c>
       <c r="I73" s="6" cm="1">
         <f t="array" aca="1" ref="I73" ca="1">_FV(B73,"Beta")</f>
-        <v>1.1348</v>
+        <v>1.1307</v>
       </c>
       <c r="J73" s="3" cm="1">
         <f t="array" aca="1" ref="J73" ca="1">_FV(B73,"52 week high",TRUE)</f>
@@ -20880,7 +20868,7 @@
       </c>
       <c r="C74" s="2">
         <f t="array" aca="1" ref="C74" ca="1">_FV(B74,"Last trade time",TRUE)</f>
-        <v>46185.991457013282</v>
+        <v>46185.999689212498</v>
       </c>
       <c r="D74" t="str">
         <f t="array" aca="1" ref="D74" ca="1">_FV(B74,"Currency")</f>
@@ -20888,23 +20876,23 @@
       </c>
       <c r="E74" s="3">
         <f t="array" aca="1" ref="E74" ca="1">_FV(B74,"Price")</f>
-        <v>91.12</v>
+        <v>91.1</v>
       </c>
       <c r="F74" s="4">
         <f t="array" aca="1" ref="F74" ca="1">_FV(B74,"Change (%)",TRUE)</f>
-        <v>2.7282999999999998E-2</v>
+        <v>2.7057000000000001E-2</v>
       </c>
       <c r="G74" s="5">
         <f t="array" aca="1" ref="G74" ca="1">_FV(B74,"Change")</f>
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="H74" s="6">
         <f t="array" aca="1" ref="H74" ca="1">_FV(B74,"P/E",TRUE)</f>
-        <v>18.069299999999998</v>
+        <v>18.0654</v>
       </c>
       <c r="I74" s="6">
         <f t="array" aca="1" ref="I74" ca="1">_FV(B74,"Beta")</f>
-        <v>0.76300000000000001</v>
+        <v>0.75870000000000004</v>
       </c>
       <c r="J74" s="3">
         <f t="array" aca="1" ref="J74" ca="1">_FV(B74,"52 week high",TRUE)</f>
@@ -20932,7 +20920,7 @@
       </c>
       <c r="P74" s="7">
         <f t="array" aca="1" ref="P74" ca="1">_FV(B74,"Volume")</f>
-        <v>11399425</v>
+        <v>11399437</v>
       </c>
       <c r="Q74" s="7">
         <f t="array" aca="1" ref="Q74" ca="1">_FV(B74,"Volume average",TRUE)</f>
@@ -20952,7 +20940,7 @@
       </c>
       <c r="U74" s="7">
         <f t="array" aca="1" ref="U74" ca="1">_FV(B74,"Market cap",TRUE)</f>
-        <v>158469981200</v>
+        <v>158435198500</v>
       </c>
       <c r="V74" s="7">
         <f t="array" aca="1" ref="V74" ca="1">_FV(B74,"Shares outstanding",TRUE)</f>
@@ -20992,7 +20980,7 @@
       </c>
       <c r="I75" s="6">
         <f t="array" aca="1" ref="I75" ca="1">_FV(B75,"Beta")</f>
-        <v>0.37009999999999998</v>
+        <v>0.35720000000000002</v>
       </c>
       <c r="J75" s="9">
         <f t="array" aca="1" ref="J75" ca="1">_FV(B75,"52 week high",TRUE)</f>
@@ -21056,7 +21044,7 @@
       </c>
       <c r="C76" s="2">
         <f t="array" aca="1" ref="C76" ca="1">_FV(B76,"Last trade time",TRUE)</f>
-        <v>46185.986547279688</v>
+        <v>46185.994230705466</v>
       </c>
       <c r="D76" t="str">
         <f t="array" aca="1" ref="D76" ca="1">_FV(B76,"Currency")</f>
@@ -21080,7 +21068,7 @@
       </c>
       <c r="I76" s="6">
         <f t="array" aca="1" ref="I76" ca="1">_FV(B76,"Beta")</f>
-        <v>3.3271999999999999</v>
+        <v>3.3254999999999999</v>
       </c>
       <c r="J76" s="3">
         <f t="array" aca="1" ref="J76" ca="1">_FV(B76,"52 week high",TRUE)</f>
@@ -21108,7 +21096,7 @@
       </c>
       <c r="P76" s="7">
         <f t="array" aca="1" ref="P76" ca="1">_FV(B76,"Volume")</f>
-        <v>702663</v>
+        <v>702723</v>
       </c>
       <c r="Q76" s="7">
         <f t="array" aca="1" ref="Q76" ca="1">_FV(B76,"Volume average",TRUE)</f>
@@ -21144,7 +21132,7 @@
       </c>
       <c r="C77" s="2">
         <f t="array" aca="1" ref="C77" ca="1">_FV(B77,"Last trade time",TRUE)</f>
-        <v>46185.991801260934</v>
+        <v>46185.999980115623</v>
       </c>
       <c r="D77" t="str">
         <f t="array" aca="1" ref="D77" ca="1">_FV(B77,"Currency")</f>
@@ -21168,7 +21156,7 @@
       </c>
       <c r="I77" s="6">
         <f t="array" aca="1" ref="I77" ca="1">_FV(B77,"Beta")</f>
-        <v>1.9565999999999999</v>
+        <v>1.9545999999999999</v>
       </c>
       <c r="J77" s="3">
         <f t="array" aca="1" ref="J77" ca="1">_FV(B77,"52 week high",TRUE)</f>
@@ -21196,7 +21184,7 @@
       </c>
       <c r="P77" s="7">
         <f t="array" aca="1" ref="P77" ca="1">_FV(B77,"Volume")</f>
-        <v>84824220</v>
+        <v>84854716</v>
       </c>
       <c r="Q77" s="7">
         <f t="array" aca="1" ref="Q77" ca="1">_FV(B77,"Volume average",TRUE)</f>
@@ -21232,7 +21220,7 @@
       </c>
       <c r="C78" s="2" cm="1">
         <f t="array" aca="1" ref="C78" ca="1">_FV(B78,"Last trade time",TRUE)</f>
-        <v>46185.991757557815</v>
+        <v>46185.999936411717</v>
       </c>
       <c r="D78" t="str" cm="1">
         <f t="array" aca="1" ref="D78" ca="1">_FV(B78,"Currency")</f>
@@ -21284,7 +21272,7 @@
       </c>
       <c r="P78" s="7" cm="1">
         <f t="array" aca="1" ref="P78" ca="1">_FV(B78,"Volume")</f>
-        <v>8985180</v>
+        <v>8986716</v>
       </c>
       <c r="Q78" s="7" cm="1">
         <f t="array" aca="1" ref="Q78" ca="1">_FV(B78,"Volume average",TRUE)</f>
@@ -21320,7 +21308,7 @@
       </c>
       <c r="C79" s="2" cm="1">
         <f t="array" aca="1" ref="C79" ca="1">_FV(B79,"Last trade time",TRUE)</f>
-        <v>46185.991834131251</v>
+        <v>46185.999928610938</v>
       </c>
       <c r="D79" t="str" cm="1">
         <f t="array" aca="1" ref="D79" ca="1">_FV(B79,"Currency")</f>
@@ -21328,15 +21316,15 @@
       </c>
       <c r="E79" s="3" cm="1">
         <f t="array" aca="1" ref="E79" ca="1">_FV(B79,"Price")</f>
-        <v>9.91</v>
+        <v>9.89</v>
       </c>
       <c r="F79" s="4" cm="1">
         <f t="array" aca="1" ref="F79" ca="1">_FV(B79,"Change (%)",TRUE)</f>
-        <v>3.5527999999999997E-2</v>
+        <v>3.3437999999999996E-2</v>
       </c>
       <c r="G79" s="5" cm="1">
         <f t="array" aca="1" ref="G79" ca="1">_FV(B79,"Change")</f>
-        <v>0.34</v>
+        <v>0.32</v>
       </c>
       <c r="H79" s="6" t="e" cm="1" vm="13">
         <f t="array" ref="H79">_FV(B79,"P/E",TRUE)</f>
@@ -21344,7 +21332,7 @@
       </c>
       <c r="I79" s="6" cm="1">
         <f t="array" aca="1" ref="I79" ca="1">_FV(B79,"Beta")</f>
-        <v>2.2753000000000001</v>
+        <v>2.2639999999999998</v>
       </c>
       <c r="J79" s="3" cm="1">
         <f t="array" aca="1" ref="J79" ca="1">_FV(B79,"52 week high",TRUE)</f>
@@ -21372,7 +21360,7 @@
       </c>
       <c r="P79" s="7" cm="1">
         <f t="array" aca="1" ref="P79" ca="1">_FV(B79,"Volume")</f>
-        <v>31156457</v>
+        <v>31174378</v>
       </c>
       <c r="Q79" s="7" cm="1">
         <f t="array" aca="1" ref="Q79" ca="1">_FV(B79,"Volume average",TRUE)</f>
@@ -21392,7 +21380,7 @@
       </c>
       <c r="U79" s="7" cm="1">
         <f t="array" aca="1" ref="U79" ca="1">_FV(B79,"Market cap",TRUE)</f>
-        <v>3621918692</v>
+        <v>3614609068</v>
       </c>
       <c r="V79" s="7" cm="1">
         <f t="array" aca="1" ref="V79" ca="1">_FV(B79,"Shares outstanding",TRUE)</f>
@@ -21408,7 +21396,7 @@
       </c>
       <c r="C80" s="2">
         <f t="array" aca="1" ref="C80" ca="1">_FV(B80,"Last trade time",TRUE)</f>
-        <v>46185.991863008596</v>
+        <v>46185.999992870311</v>
       </c>
       <c r="D80" t="str">
         <f t="array" aca="1" ref="D80" ca="1">_FV(B80,"Currency")</f>
@@ -21460,7 +21448,7 @@
       </c>
       <c r="P80" s="7">
         <f t="array" aca="1" ref="P80" ca="1">_FV(B80,"Volume")</f>
-        <v>11954335</v>
+        <v>11964511</v>
       </c>
       <c r="Q80" s="7">
         <f t="array" aca="1" ref="Q80" ca="1">_FV(B80,"Volume average",TRUE)</f>
@@ -21496,7 +21484,7 @@
       </c>
       <c r="C81" s="2" cm="1">
         <f t="array" aca="1" ref="C81" ca="1">_FV(B81,"Last trade time",TRUE)</f>
-        <v>46185.991349571093</v>
+        <v>46185.999389640623</v>
       </c>
       <c r="D81" t="str" cm="1">
         <f t="array" aca="1" ref="D81" ca="1">_FV(B81,"Currency")</f>
@@ -21504,15 +21492,15 @@
       </c>
       <c r="E81" s="3" cm="1">
         <f t="array" aca="1" ref="E81" ca="1">_FV(B81,"Price")</f>
-        <v>232.64500000000001</v>
+        <v>232.78</v>
       </c>
       <c r="F81" s="4" cm="1">
         <f t="array" aca="1" ref="F81" ca="1">_FV(B81,"Change (%)",TRUE)</f>
-        <v>-3.2217999999999997E-2</v>
+        <v>-3.1657000000000005E-2</v>
       </c>
       <c r="G81" s="5" cm="1">
         <f t="array" aca="1" ref="G81" ca="1">_FV(B81,"Change")</f>
-        <v>-7.7450000000000001</v>
+        <v>-7.61</v>
       </c>
       <c r="H81" s="6" t="e" cm="1" vm="13">
         <f t="array" ref="H81">_FV(B81,"P/E",TRUE)</f>
@@ -21520,7 +21508,7 @@
       </c>
       <c r="I81" s="6" cm="1">
         <f t="array" aca="1" ref="I81" ca="1">_FV(B81,"Beta")</f>
-        <v>1.3620000000000001</v>
+        <v>1.3697999999999999</v>
       </c>
       <c r="J81" s="3" cm="1">
         <f t="array" aca="1" ref="J81" ca="1">_FV(B81,"52 week high",TRUE)</f>
@@ -21548,7 +21536,7 @@
       </c>
       <c r="P81" s="7" cm="1">
         <f t="array" aca="1" ref="P81" ca="1">_FV(B81,"Volume")</f>
-        <v>7707159</v>
+        <v>7707338</v>
       </c>
       <c r="Q81" s="7" cm="1">
         <f t="array" aca="1" ref="Q81" ca="1">_FV(B81,"Volume average",TRUE)</f>
@@ -21584,7 +21572,7 @@
       </c>
       <c r="C82" s="2" cm="1">
         <f t="array" aca="1" ref="C82" ca="1">_FV(B82,"Last trade time",TRUE)</f>
-        <v>46185.990671284373</v>
+        <v>46185.999985242968</v>
       </c>
       <c r="D82" t="str" cm="1">
         <f t="array" aca="1" ref="D82" ca="1">_FV(B82,"Currency")</f>
@@ -21604,11 +21592,11 @@
       </c>
       <c r="H82" s="6" cm="1">
         <f t="array" aca="1" ref="H82" ca="1">_FV(B82,"P/E",TRUE)</f>
-        <v>105.1913</v>
+        <v>105.7473</v>
       </c>
       <c r="I82" s="6" cm="1">
         <f t="array" aca="1" ref="I82" ca="1">_FV(B82,"Beta")</f>
-        <v>1.2169000000000001</v>
+        <v>1.2191000000000001</v>
       </c>
       <c r="J82" s="3" cm="1">
         <f t="array" aca="1" ref="J82" ca="1">_FV(B82,"52 week high",TRUE)</f>
@@ -21636,7 +21624,7 @@
       </c>
       <c r="P82" s="7" cm="1">
         <f t="array" aca="1" ref="P82" ca="1">_FV(B82,"Volume")</f>
-        <v>1289580</v>
+        <v>1289661</v>
       </c>
       <c r="Q82" s="7" cm="1">
         <f t="array" aca="1" ref="Q82" ca="1">_FV(B82,"Volume average",TRUE)</f>
@@ -21672,7 +21660,7 @@
       </c>
       <c r="C83" s="2">
         <f t="array" aca="1" ref="C83" ca="1">_FV(B83,"Last trade time",TRUE)</f>
-        <v>46185.991871145314</v>
+        <v>46185.999918807815</v>
       </c>
       <c r="D83" t="str">
         <f t="array" aca="1" ref="D83" ca="1">_FV(B83,"Currency")</f>
@@ -21696,7 +21684,7 @@
       </c>
       <c r="I83" s="6">
         <f t="array" aca="1" ref="I83" ca="1">_FV(B83,"Beta")</f>
-        <v>2.8155000000000001</v>
+        <v>2.8134000000000001</v>
       </c>
       <c r="J83" s="3">
         <f t="array" aca="1" ref="J83" ca="1">_FV(B83,"52 week high",TRUE)</f>
@@ -21724,7 +21712,7 @@
       </c>
       <c r="P83" s="7">
         <f t="array" aca="1" ref="P83" ca="1">_FV(B83,"Volume")</f>
-        <v>26041115</v>
+        <v>26051484</v>
       </c>
       <c r="Q83" s="7">
         <f t="array" aca="1" ref="Q83" ca="1">_FV(B83,"Volume average",TRUE)</f>
@@ -21760,7 +21748,7 @@
       </c>
       <c r="C84" s="2" cm="1">
         <f t="array" aca="1" ref="C84" ca="1">_FV(B84,"Last trade time",TRUE)</f>
-        <v>46185.991859606249</v>
+        <v>46185.999884478908</v>
       </c>
       <c r="D84" t="str" cm="1">
         <f t="array" aca="1" ref="D84" ca="1">_FV(B84,"Currency")</f>
@@ -21812,7 +21800,7 @@
       </c>
       <c r="P84" s="7" cm="1">
         <f t="array" aca="1" ref="P84" ca="1">_FV(B84,"Volume")</f>
-        <v>9943606</v>
+        <v>9947173</v>
       </c>
       <c r="Q84" s="7" cm="1">
         <f t="array" aca="1" ref="Q84" ca="1">_FV(B84,"Volume average",TRUE)</f>
@@ -21848,7 +21836,7 @@
       </c>
       <c r="C85" s="2" cm="1">
         <f t="array" aca="1" ref="C85" ca="1">_FV(B85,"Last trade time",TRUE)</f>
-        <v>46185.991846469529</v>
+        <v>46186.000000161715</v>
       </c>
       <c r="D85" t="str" cm="1">
         <f t="array" aca="1" ref="D85" ca="1">_FV(B85,"Currency")</f>
@@ -21856,15 +21844,15 @@
       </c>
       <c r="E85" s="3" cm="1">
         <f t="array" aca="1" ref="E85" ca="1">_FV(B85,"Price")</f>
-        <v>741.77</v>
+        <v>741.75</v>
       </c>
       <c r="F85" s="4" cm="1">
         <f t="array" aca="1" ref="F85" ca="1">_FV(B85,"Change (%)",TRUE)</f>
-        <v>5.4349999999999997E-3</v>
+        <v>5.4079999999999996E-3</v>
       </c>
       <c r="G85" s="5" cm="1">
         <f t="array" aca="1" ref="G85" ca="1">_FV(B85,"Change")</f>
-        <v>4.01</v>
+        <v>3.99</v>
       </c>
       <c r="H85" s="6" t="e" vm="13">
         <f t="array" ref="H85">_FV(B85,"P/E",TRUE)</f>
@@ -21900,7 +21888,7 @@
       </c>
       <c r="P85" s="7" cm="1">
         <f t="array" aca="1" ref="P85" ca="1">_FV(B85,"Volume")</f>
-        <v>57067321</v>
+        <v>57079533</v>
       </c>
       <c r="Q85" s="7" cm="1">
         <f t="array" aca="1" ref="Q85" ca="1">_FV(B85,"Volume average",TRUE)</f>
@@ -21936,7 +21924,7 @@
       </c>
       <c r="C86" s="2">
         <f t="array" aca="1" ref="C86" ca="1">_FV(B86,"Last trade time",TRUE)</f>
-        <v>46185.980195659373</v>
+        <v>46185.99791788125</v>
       </c>
       <c r="D86" t="str">
         <f t="array" aca="1" ref="D86" ca="1">_FV(B86,"Currency")</f>
@@ -21956,11 +21944,11 @@
       </c>
       <c r="H86" s="6">
         <f t="array" aca="1" ref="H86" ca="1">_FV(B86,"P/E",TRUE)</f>
-        <v>29.223299999999998</v>
+        <v>28.733000000000001</v>
       </c>
       <c r="I86" s="6">
         <f t="array" aca="1" ref="I86" ca="1">_FV(B86,"Beta")</f>
-        <v>1.4834000000000001</v>
+        <v>1.4812000000000001</v>
       </c>
       <c r="J86" s="3">
         <f t="array" aca="1" ref="J86" ca="1">_FV(B86,"52 week high",TRUE)</f>
@@ -21988,7 +21976,7 @@
       </c>
       <c r="P86" s="7">
         <f t="array" aca="1" ref="P86" ca="1">_FV(B86,"Volume")</f>
-        <v>2262221</v>
+        <v>2262474</v>
       </c>
       <c r="Q86" s="7">
         <f t="array" aca="1" ref="Q86" ca="1">_FV(B86,"Volume average",TRUE)</f>
@@ -22024,7 +22012,7 @@
       </c>
       <c r="C87" s="2" cm="1">
         <f t="array" aca="1" ref="C87" ca="1">_FV(B87,"Last trade time",TRUE)</f>
-        <v>46185.989600717185</v>
+        <v>46185.999824953127</v>
       </c>
       <c r="D87" t="str" cm="1">
         <f t="array" aca="1" ref="D87" ca="1">_FV(B87,"Currency")</f>
@@ -22048,7 +22036,7 @@
       </c>
       <c r="I87" s="6" cm="1">
         <f t="array" aca="1" ref="I87" ca="1">_FV(B87,"Beta")</f>
-        <v>1.9427000000000001</v>
+        <v>1.9490000000000001</v>
       </c>
       <c r="J87" s="3" cm="1">
         <f t="array" aca="1" ref="J87" ca="1">_FV(B87,"52 week high",TRUE)</f>
@@ -22076,7 +22064,7 @@
       </c>
       <c r="P87" s="7" cm="1">
         <f t="array" aca="1" ref="P87" ca="1">_FV(B87,"Volume")</f>
-        <v>1716476</v>
+        <v>1716539</v>
       </c>
       <c r="Q87" s="7" cm="1">
         <f t="array" aca="1" ref="Q87" ca="1">_FV(B87,"Volume average",TRUE)</f>
@@ -22112,7 +22100,7 @@
       </c>
       <c r="C88" s="2">
         <f t="array" aca="1" ref="C88" ca="1">_FV(B88,"Last trade time",TRUE)</f>
-        <v>46185.991180450779</v>
+        <v>46185.999885914061</v>
       </c>
       <c r="D88" t="str">
         <f t="array" aca="1" ref="D88" ca="1">_FV(B88,"Currency")</f>
@@ -22164,7 +22152,7 @@
       </c>
       <c r="P88" s="7">
         <f t="array" aca="1" ref="P88" ca="1">_FV(B88,"Volume")</f>
-        <v>6119728</v>
+        <v>6122843</v>
       </c>
       <c r="Q88" s="7">
         <f t="array" aca="1" ref="Q88" ca="1">_FV(B88,"Volume average",TRUE)</f>
@@ -22200,7 +22188,7 @@
       </c>
       <c r="C89" s="2" cm="1">
         <f t="array" aca="1" ref="C89" ca="1">_FV(B89,"Last trade time",TRUE)</f>
-        <v>46185.991301365626</v>
+        <v>46185.999523448438</v>
       </c>
       <c r="D89" t="str" cm="1">
         <f t="array" aca="1" ref="D89" ca="1">_FV(B89,"Currency")</f>
@@ -22220,11 +22208,11 @@
       </c>
       <c r="H89" s="6" cm="1">
         <f t="array" aca="1" ref="H89" ca="1">_FV(B89,"P/E",TRUE)</f>
-        <v>74.623800000000003</v>
+        <v>70.589799999999997</v>
       </c>
       <c r="I89" s="6" cm="1">
         <f t="array" aca="1" ref="I89" ca="1">_FV(B89,"Beta")</f>
-        <v>1.7786999999999999</v>
+        <v>1.7688999999999999</v>
       </c>
       <c r="J89" s="3" cm="1">
         <f t="array" aca="1" ref="J89" ca="1">_FV(B89,"52 week high",TRUE)</f>
@@ -22252,7 +22240,7 @@
       </c>
       <c r="P89" s="7" cm="1">
         <f t="array" aca="1" ref="P89" ca="1">_FV(B89,"Volume")</f>
-        <v>3326656</v>
+        <v>3326868</v>
       </c>
       <c r="Q89" s="7" cm="1">
         <f t="array" aca="1" ref="Q89" ca="1">_FV(B89,"Volume average",TRUE)</f>
@@ -22288,7 +22276,7 @@
       </c>
       <c r="C90" s="2">
         <f t="array" aca="1" ref="C90" ca="1">_FV(B90,"Last trade time",TRUE)</f>
-        <v>46185.991885253905</v>
+        <v>46185.999977117972</v>
       </c>
       <c r="D90" t="str">
         <f t="array" aca="1" ref="D90" ca="1">_FV(B90,"Currency")</f>
@@ -22308,11 +22296,11 @@
       </c>
       <c r="H90" s="6">
         <f t="array" aca="1" ref="H90" ca="1">_FV(B90,"P/E",TRUE)</f>
-        <v>371.47430000000003</v>
+        <v>364.83370000000002</v>
       </c>
       <c r="I90" s="6">
         <f t="array" aca="1" ref="I90" ca="1">_FV(B90,"Beta")</f>
-        <v>1.8110999999999999</v>
+        <v>1.8073999999999999</v>
       </c>
       <c r="J90" s="3">
         <f t="array" aca="1" ref="J90" ca="1">_FV(B90,"52 week high",TRUE)</f>
@@ -22340,7 +22328,7 @@
       </c>
       <c r="P90" s="7">
         <f t="array" aca="1" ref="P90" ca="1">_FV(B90,"Volume")</f>
-        <v>63629525</v>
+        <v>63652286</v>
       </c>
       <c r="Q90" s="7">
         <f t="array" aca="1" ref="Q90" ca="1">_FV(B90,"Volume average",TRUE)</f>
@@ -22376,7 +22364,7 @@
       </c>
       <c r="C91" s="2">
         <f t="array" aca="1" ref="C91" ca="1">_FV(B91,"Last trade time",TRUE)</f>
-        <v>46185.991411388284</v>
+        <v>46185.999904756252</v>
       </c>
       <c r="D91" t="str">
         <f t="array" aca="1" ref="D91" ca="1">_FV(B91,"Currency")</f>
@@ -22384,23 +22372,23 @@
       </c>
       <c r="E91" s="3">
         <f t="array" aca="1" ref="E91" ca="1">_FV(B91,"Price")</f>
-        <v>423.82</v>
+        <v>423.93</v>
       </c>
       <c r="F91" s="4">
         <f t="array" aca="1" ref="F91" ca="1">_FV(B91,"Change (%)",TRUE)</f>
-        <v>6.5310000000000003E-3</v>
+        <v>6.7920000000000003E-3</v>
       </c>
       <c r="G91" s="5">
         <f t="array" aca="1" ref="G91" ca="1">_FV(B91,"Change")</f>
-        <v>2.75</v>
+        <v>2.86</v>
       </c>
       <c r="H91" s="6">
         <f t="array" aca="1" ref="H91" ca="1">_FV(B91,"P/E",TRUE)</f>
-        <v>35.858899999999998</v>
+        <v>35.868200000000002</v>
       </c>
       <c r="I91" s="6">
         <f t="array" aca="1" ref="I91" ca="1">_FV(B91,"Beta")</f>
-        <v>1.3855</v>
+        <v>1.3866000000000001</v>
       </c>
       <c r="J91" s="3">
         <f t="array" aca="1" ref="J91" ca="1">_FV(B91,"52 week high",TRUE)</f>
@@ -22428,7 +22416,7 @@
       </c>
       <c r="P91" s="7">
         <f t="array" aca="1" ref="P91" ca="1">_FV(B91,"Volume")</f>
-        <v>10359581</v>
+        <v>10362465</v>
       </c>
       <c r="Q91" s="7">
         <f t="array" aca="1" ref="Q91" ca="1">_FV(B91,"Volume average",TRUE)</f>
@@ -22448,7 +22436,7 @@
       </c>
       <c r="U91" s="7">
         <f t="array" aca="1" ref="U91" ca="1">_FV(B91,"Market cap",TRUE)</f>
-        <v>2198131410680</v>
+        <v>2198701922820</v>
       </c>
       <c r="V91" s="7">
         <f t="array" aca="1" ref="V91" ca="1">_FV(B91,"Shares outstanding",TRUE)</f>
@@ -22464,7 +22452,7 @@
       </c>
       <c r="C92" s="2" cm="1">
         <f t="array" aca="1" ref="C92" ca="1">_FV(B92,"Last trade time",TRUE)</f>
-        <v>46185.969372731248</v>
+        <v>46185.99614842578</v>
       </c>
       <c r="D92" t="str" cm="1">
         <f t="array" aca="1" ref="D92" ca="1">_FV(B92,"Currency")</f>
@@ -22484,11 +22472,11 @@
       </c>
       <c r="H92" s="6" cm="1">
         <f t="array" aca="1" ref="H92" ca="1">_FV(B92,"P/E",TRUE)</f>
-        <v>317.23919999999998</v>
+        <v>321.18259999999998</v>
       </c>
       <c r="I92" s="6" cm="1">
         <f t="array" aca="1" ref="I92" ca="1">_FV(B92,"Beta")</f>
-        <v>1.3432999999999999</v>
+        <v>1.3532</v>
       </c>
       <c r="J92" s="3" cm="1">
         <f t="array" aca="1" ref="J92" ca="1">_FV(B92,"52 week high",TRUE)</f>
@@ -22516,7 +22504,7 @@
       </c>
       <c r="P92" s="7" cm="1">
         <f t="array" aca="1" ref="P92" ca="1">_FV(B92,"Volume")</f>
-        <v>1567840</v>
+        <v>1567846</v>
       </c>
       <c r="Q92" s="7" cm="1">
         <f t="array" aca="1" ref="Q92" ca="1">_FV(B92,"Volume average",TRUE)</f>
@@ -22552,7 +22540,7 @@
       </c>
       <c r="C93" s="2" cm="1">
         <f t="array" aca="1" ref="C93" ca="1">_FV(B93,"Last trade time",TRUE)</f>
-        <v>46185.991873714847</v>
+        <v>46185.999953517967</v>
       </c>
       <c r="D93" t="str" cm="1">
         <f t="array" aca="1" ref="D93" ca="1">_FV(B93,"Currency")</f>
@@ -22560,23 +22548,23 @@
       </c>
       <c r="E93" s="3" cm="1">
         <f t="array" aca="1" ref="E93" ca="1">_FV(B93,"Price")</f>
-        <v>302.70999999999998</v>
+        <v>302.87</v>
       </c>
       <c r="F93" s="4" cm="1">
         <f t="array" aca="1" ref="F93" ca="1">_FV(B93,"Change (%)",TRUE)</f>
-        <v>1.6215E-2</v>
+        <v>1.6752E-2</v>
       </c>
       <c r="G93" s="5" cm="1">
         <f t="array" aca="1" ref="G93" ca="1">_FV(B93,"Change")</f>
-        <v>4.83</v>
+        <v>4.99</v>
       </c>
       <c r="H93" s="6" cm="1">
         <f t="array" aca="1" ref="H93" ca="1">_FV(B93,"P/E",TRUE)</f>
-        <v>76.000500000000002</v>
+        <v>74.787499999999994</v>
       </c>
       <c r="I93" s="6" cm="1">
         <f t="array" aca="1" ref="I93" ca="1">_FV(B93,"Beta")</f>
-        <v>2.0487000000000002</v>
+        <v>2.0455999999999999</v>
       </c>
       <c r="J93" s="3" cm="1">
         <f t="array" aca="1" ref="J93" ca="1">_FV(B93,"52 week high",TRUE)</f>
@@ -22604,7 +22592,7 @@
       </c>
       <c r="P93" s="7" cm="1">
         <f t="array" aca="1" ref="P93" ca="1">_FV(B93,"Volume")</f>
-        <v>4956746</v>
+        <v>4958116</v>
       </c>
       <c r="Q93" s="7" cm="1">
         <f t="array" aca="1" ref="Q93" ca="1">_FV(B93,"Volume average",TRUE)</f>
@@ -22624,7 +22612,7 @@
       </c>
       <c r="U93" s="7" cm="1">
         <f t="array" aca="1" ref="U93" ca="1">_FV(B93,"Market cap",TRUE)</f>
-        <v>116273574847</v>
+        <v>116335032256</v>
       </c>
       <c r="V93" s="7" cm="1">
         <f t="array" aca="1" ref="V93" ca="1">_FV(B93,"Shares outstanding",TRUE)</f>
@@ -22640,7 +22628,7 @@
       </c>
       <c r="C94" s="2" cm="1">
         <f t="array" aca="1" ref="C94" ca="1">_FV(B94,"Last trade time",TRUE)</f>
-        <v>46185.990720265625</v>
+        <v>46185.999948529687</v>
       </c>
       <c r="D94" t="str" cm="1">
         <f t="array" aca="1" ref="D94" ca="1">_FV(B94,"Currency")</f>
@@ -22660,11 +22648,11 @@
       </c>
       <c r="H94" s="6" cm="1">
         <f t="array" aca="1" ref="H94" ca="1">_FV(B94,"P/E",TRUE)</f>
-        <v>40.830300000000001</v>
+        <v>40.746099999999998</v>
       </c>
       <c r="I94" s="6" cm="1">
         <f t="array" aca="1" ref="I94" ca="1">_FV(B94,"Beta")</f>
-        <v>1.0992</v>
+        <v>1.0974999999999999</v>
       </c>
       <c r="J94" s="3" cm="1">
         <f t="array" aca="1" ref="J94" ca="1">_FV(B94,"52 week high",TRUE)</f>
@@ -22692,7 +22680,7 @@
       </c>
       <c r="P94" s="7" cm="1">
         <f t="array" aca="1" ref="P94" ca="1">_FV(B94,"Volume")</f>
-        <v>6671416</v>
+        <v>6671469</v>
       </c>
       <c r="Q94" s="7" cm="1">
         <f t="array" aca="1" ref="Q94" ca="1">_FV(B94,"Volume average",TRUE)</f>
@@ -22728,7 +22716,7 @@
       </c>
       <c r="C95" s="2" cm="1">
         <f t="array" aca="1" ref="C95" ca="1">_FV(B95,"Last trade time",TRUE)</f>
-        <v>46185.991325000003</v>
+        <v>46185.999896620313</v>
       </c>
       <c r="D95" t="str" cm="1">
         <f t="array" aca="1" ref="D95" ca="1">_FV(B95,"Currency")</f>
@@ -22752,7 +22740,7 @@
       </c>
       <c r="I95" s="6" cm="1">
         <f t="array" aca="1" ref="I95" ca="1">_FV(B95,"Beta")</f>
-        <v>0.98109999999999997</v>
+        <v>0.9738</v>
       </c>
       <c r="J95" s="3" cm="1">
         <f t="array" aca="1" ref="J95" ca="1">_FV(B95,"52 week high",TRUE)</f>
@@ -22780,7 +22768,7 @@
       </c>
       <c r="P95" s="7" cm="1">
         <f t="array" aca="1" ref="P95" ca="1">_FV(B95,"Volume")</f>
-        <v>4759379</v>
+        <v>4760338</v>
       </c>
       <c r="Q95" s="7" cm="1">
         <f t="array" aca="1" ref="Q95" ca="1">_FV(B95,"Volume average",TRUE)</f>

--- a/dashboard/trading_system.xlsx
+++ b/dashboard/trading_system.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\husainnatha\tradingsystem\dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5555341B-1627-4F40-B850-AB10154C9532}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7E6BAE3-93A2-479D-872B-B28774A4B832}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3690" yWindow="2258" windowWidth="16200" windowHeight="9307" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="3" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CONTRIBUTIONS" sheetId="11" r:id="rId1"/>
@@ -4545,25 +4545,25 @@
     <v>92.65</v>
     <v>60.54</v>
     <v>2.04</v>
-    <v>0.17</v>
-    <v>2.1150000000000001E-3</v>
-    <v>2.2529999999999998E-3</v>
-    <v>0.16</v>
+    <v>0.19</v>
+    <v>1.8509999999999998E-3</v>
+    <v>2.5180000000000003E-3</v>
+    <v>0.14000000000000001</v>
     <v>USD</v>
     <v>CBOE BZX Exchange</v>
     <v>BATS</v>
     <v>7.4999999999999997E-3</v>
     <v>76.180000000000007</v>
     <v>ETF</v>
-    <v>46185.993873344531</v>
+    <v>46185.995102892972</v>
     <v>35</v>
     <v>74.41</v>
     <v>7262198811.6000004</v>
     <v>ARK Innovation</v>
     <v>75.459999999999994</v>
     <v>75.459999999999994</v>
-    <v>75.63</v>
-    <v>75.81</v>
+    <v>75.650000000000006</v>
+    <v>75.790000000000006</v>
     <v>ARKK</v>
     <v>ARK Innovation (BATS:ARKK)</v>
     <v>11557976</v>
@@ -5449,7 +5449,7 @@
     <v>DYNATRACE, INC.</v>
     <v>DYNATRACE, INC.</v>
     <v>41.08</v>
-    <v>76.054500000000004</v>
+    <v>75.346699999999998</v>
     <v>40.369999999999997</v>
     <v>40.75</v>
     <v>41.59</v>
@@ -5557,7 +5557,7 @@
     <v>EATON CORPORATION PUBLIC LIMITED COMPANY</v>
     <v>EATON CORPORATION PUBLIC LIMITED COMPANY</v>
     <v>396.55</v>
-    <v>38.263500000000001</v>
+    <v>38.483400000000003</v>
     <v>393.64</v>
     <v>391.39</v>
     <v>395</v>
@@ -6156,11 +6156,11 @@
     <v>46185.99989644609</v>
     <v>131</v>
     <v>236</v>
-    <v>278973314100</v>
+    <v>332499238500</v>
     <v>KLA CORPORATION</v>
     <v>KLA CORPORATION</v>
     <v>237.6</v>
-    <v>68.279300000000006</v>
+    <v>72.066800000000001</v>
     <v>241.16399999999999</v>
     <v>254.54</v>
     <v>257</v>
@@ -6194,9 +6194,9 @@
     <v>65.353800000000007</v>
     <v>0.34239999999999998</v>
     <v>0.09</v>
-    <v>9.6829999999999996E-4</v>
+    <v>0</v>
     <v>1.091E-3</v>
-    <v>0.08</v>
+    <v>0</v>
     <v>USD</v>
     <v>The Coca-Cola Company is a beverage company. The Company's segments include Europe, Middle East and Africa (EMEA); Latin America; North America; Asia Pacific, and Bottling Investments. It sells multiple brands across several beverage categories worldwide. Its portfolio of sparkling soft drink brands includes Coca-Cola, Sprite and Fanta. Its water, sports, coffee and tea brands include Dasani, smartwater, vitaminwater, Topo Chico, BODYARMOR, Powerade, Costa, Georgia, Fuze Tea, Gold Peak and Ayataka. Its juice, value-added dairy and plant-based beverage brands include Minute Maid, Simply, innocent, Del Valle, fairlife and Santa Clara. It operates in two lines of business: concentrate operations and finished product operations. Its concentrate operations sell beverage concentrates, syrups, including fountain syrups, and certain finished beverages to authorized bottling operations. Its finished product operations sell sparkling soft drinks and a variety of other finished beverages.</v>
     <v>65900</v>
@@ -6214,10 +6214,10 @@
     <v>THE COCA-COLA COMPANY</v>
     <v>THE COCA-COLA COMPANY</v>
     <v>82.71</v>
-    <v>26.009799999999998</v>
+    <v>25.9817</v>
     <v>82.53</v>
     <v>82.62</v>
-    <v>82.7</v>
+    <v>82.62</v>
     <v>4302482000</v>
     <v>KO</v>
     <v>THE COCA-COLA COMPANY (XNYS:KO)</v>
@@ -7208,7 +7208,7 @@
     <v>ORACLE CORPORATION</v>
     <v>ORACLE CORPORATION</v>
     <v>185.01</v>
-    <v>29.785299999999999</v>
+    <v>29.7807</v>
     <v>184.1</v>
     <v>184.13</v>
     <v>183.94</v>
@@ -7370,7 +7370,7 @@
     <v>THE PROCTER &amp; GAMBLE COMPANY</v>
     <v>THE PROCTER &amp; GAMBLE COMPANY</v>
     <v>149.38</v>
-    <v>21.880500000000001</v>
+    <v>21.694800000000001</v>
     <v>148.34</v>
     <v>149.61000000000001</v>
     <v>149.69999999999999</v>
@@ -7703,7 +7703,7 @@
     <v>ROCKWELL AUTOMATION, INC.</v>
     <v>ROCKWELL AUTOMATION, INC.</v>
     <v>462.33</v>
-    <v>47.717700000000001</v>
+    <v>47.536099999999998</v>
     <v>457.59</v>
     <v>459.34</v>
     <v>460</v>
@@ -8794,7 +8794,7 @@
     <v>Taiwan Semiconductor Manufacturing Company Limited</v>
     <v>Taiwan Semiconductor Manufacturing Company Limited</v>
     <v>420.05</v>
-    <v>35.868200000000002</v>
+    <v>35.626399999999997</v>
     <v>421.07</v>
     <v>423.93</v>
     <v>425.8</v>
@@ -10115,10 +10115,9 @@
     <spb s="15">
       <v>at close</v>
       <v>from previous close</v>
-      <v>Source: Nasdaq Last Sale</v>
       <v>from previous close</v>
       <v>GMT</v>
-      <v>Real-Time Nasdaq Last Sale</v>
+      <v>BATS BZX Real-Time Last Price</v>
       <v>from close</v>
       <v>from close</v>
     </spb>
@@ -10213,7 +10212,7 @@
       <v>1</v>
       <v>5</v>
     </spb>
-    <spb s="15">
+    <spb s="19">
       <v>at close</v>
       <v>from previous close</v>
       <v>Source: Nasdaq</v>
@@ -10228,7 +10227,7 @@
       <v>Name</v>
       <v>LearnMoreOnLink</v>
     </spb>
-    <spb s="19">
+    <spb s="20">
       <v>13</v>
       <v>2</v>
       <v>2</v>
@@ -10270,7 +10269,7 @@
       <v>9</v>
       <v>4</v>
     </spb>
-    <spb s="20">
+    <spb s="21">
       <v>Delayed 15 minutes</v>
       <v>from previous close</v>
       <v>from previous close</v>
@@ -10281,11 +10280,11 @@
       <v>9</v>
       <v>Name</v>
     </spb>
-    <spb s="21">
+    <spb s="22">
       <v>1</v>
       <v>1</v>
     </spb>
-    <spb s="22">
+    <spb s="23">
       <v>3</v>
       <v>17</v>
       <v>17</v>
@@ -10296,7 +10295,7 @@
       <v>7</v>
       <v>9</v>
     </spb>
-    <spb s="23">
+    <spb s="24">
       <v>GMT</v>
     </spb>
   </spbData>
@@ -10304,7 +10303,7 @@
 </file>
 
 <file path=xl/richData/rdsupportingpropertybagstructure.xml><?xml version="1.0" encoding="utf-8"?>
-<spbStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" count="24">
+<spbStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" count="25">
   <s>
     <k n="^Order" t="spba"/>
     <k n="TitleProperty" t="s"/>
@@ -10462,7 +10461,6 @@
   <s>
     <k n="Price" t="s"/>
     <k n="Change" t="s"/>
-    <k n="Exchange" t="s"/>
     <k n="Change (%)" t="s"/>
     <k n="Last trade time" t="s"/>
     <k n="Price (Extended hours)" t="s"/>
@@ -10522,6 +10520,16 @@
     <k n="Price (Extended hours)" t="i"/>
     <k n="Change (Extended hours)" t="i"/>
     <k n="Change % (Extended hours)" t="i"/>
+  </s>
+  <s>
+    <k n="Price" t="s"/>
+    <k n="Change" t="s"/>
+    <k n="Exchange" t="s"/>
+    <k n="Change (%)" t="s"/>
+    <k n="Last trade time" t="s"/>
+    <k n="Price (Extended hours)" t="s"/>
+    <k n="Change (Extended hours)" t="s"/>
+    <k n="Change % (Extended hours)" t="s"/>
   </s>
   <s>
     <k n="Low" t="i"/>
@@ -15500,7 +15508,7 @@
       </c>
       <c r="C13" s="2" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(B13,"Last trade time",TRUE)</f>
-        <v>46185.993873344531</v>
+        <v>46185.995102892972</v>
       </c>
       <c r="D13" t="str" cm="1">
         <f t="array" aca="1" ref="D13" ca="1">_FV(B13,"Currency")</f>
@@ -15508,15 +15516,15 @@
       </c>
       <c r="E13" s="3" cm="1">
         <f t="array" aca="1" ref="E13" ca="1">_FV(B13,"Price")</f>
-        <v>75.63</v>
+        <v>75.650000000000006</v>
       </c>
       <c r="F13" s="4" cm="1">
         <f t="array" aca="1" ref="F13" ca="1">_FV(B13,"Change (%)",TRUE)</f>
-        <v>2.2529999999999998E-3</v>
+        <v>2.5180000000000003E-3</v>
       </c>
       <c r="G13" s="5" cm="1">
         <f t="array" aca="1" ref="G13" ca="1">_FV(B13,"Change")</f>
-        <v>0.17</v>
+        <v>0.19</v>
       </c>
       <c r="H13" s="6" t="e" vm="13">
         <f t="array" ref="H13">_FV(B13,"P/E",TRUE)</f>
@@ -17016,7 +17024,7 @@
       </c>
       <c r="H30" s="6" cm="1">
         <f t="array" aca="1" ref="H30" ca="1">_FV(B30,"P/E",TRUE)</f>
-        <v>76.054500000000004</v>
+        <v>75.346699999999998</v>
       </c>
       <c r="I30" s="6" cm="1">
         <f t="array" aca="1" ref="I30" ca="1">_FV(B30,"Beta")</f>
@@ -17192,7 +17200,7 @@
       </c>
       <c r="H32" s="6" cm="1">
         <f t="array" aca="1" ref="H32" ca="1">_FV(B32,"P/E",TRUE)</f>
-        <v>38.263500000000001</v>
+        <v>38.483400000000003</v>
       </c>
       <c r="I32" s="6" cm="1">
         <f t="array" aca="1" ref="I32" ca="1">_FV(B32,"Beta")</f>
@@ -18160,7 +18168,7 @@
       </c>
       <c r="H43" s="6" cm="1">
         <f t="array" aca="1" ref="H43" ca="1">_FV(B43,"P/E",TRUE)</f>
-        <v>68.279300000000006</v>
+        <v>72.066800000000001</v>
       </c>
       <c r="I43" s="6" cm="1">
         <f t="array" aca="1" ref="I43" ca="1">_FV(B43,"Beta")</f>
@@ -18212,7 +18220,7 @@
       </c>
       <c r="U43" s="7" cm="1">
         <f t="array" aca="1" ref="U43" ca="1">_FV(B43,"Market cap",TRUE)</f>
-        <v>278973314100</v>
+        <v>332499238500</v>
       </c>
       <c r="V43" s="7" cm="1">
         <f t="array" aca="1" ref="V43" ca="1">_FV(B43,"Shares outstanding",TRUE)</f>
@@ -18248,7 +18256,7 @@
       </c>
       <c r="H44" s="6">
         <f t="array" aca="1" ref="H44" ca="1">_FV(B44,"P/E",TRUE)</f>
-        <v>26.009799999999998</v>
+        <v>25.9817</v>
       </c>
       <c r="I44" s="6">
         <f t="array" aca="1" ref="I44" ca="1">_FV(B44,"Beta")</f>
@@ -19744,7 +19752,7 @@
       </c>
       <c r="H61" s="6">
         <f t="array" aca="1" ref="H61" ca="1">_FV(B61,"P/E",TRUE)</f>
-        <v>29.785299999999999</v>
+        <v>29.7807</v>
       </c>
       <c r="I61" s="6">
         <f t="array" aca="1" ref="I61" ca="1">_FV(B61,"Beta")</f>
@@ -20008,7 +20016,7 @@
       </c>
       <c r="H64" s="6" cm="1">
         <f t="array" aca="1" ref="H64" ca="1">_FV(B64,"P/E",TRUE)</f>
-        <v>21.880500000000001</v>
+        <v>21.694800000000001</v>
       </c>
       <c r="I64" s="6" cm="1">
         <f t="array" aca="1" ref="I64" ca="1">_FV(B64,"Beta")</f>
@@ -20536,7 +20544,7 @@
       </c>
       <c r="H70" s="6" cm="1">
         <f t="array" aca="1" ref="H70" ca="1">_FV(B70,"P/E",TRUE)</f>
-        <v>47.717700000000001</v>
+        <v>47.536099999999998</v>
       </c>
       <c r="I70" s="6" cm="1">
         <f t="array" aca="1" ref="I70" ca="1">_FV(B70,"Beta")</f>
@@ -22384,7 +22392,7 @@
       </c>
       <c r="H91" s="6">
         <f t="array" aca="1" ref="H91" ca="1">_FV(B91,"P/E",TRUE)</f>
-        <v>35.868200000000002</v>
+        <v>35.626399999999997</v>
       </c>
       <c r="I91" s="6">
         <f t="array" aca="1" ref="I91" ca="1">_FV(B91,"Beta")</f>

--- a/dashboard/trading_system.xlsx
+++ b/dashboard/trading_system.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\husainnatha\tradingsystem\dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7E6BAE3-93A2-479D-872B-B28774A4B832}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F217D80-1AF7-44C0-A5C5-8ADB27BC18E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="3" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="3" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CONTRIBUTIONS" sheetId="11" r:id="rId1"/>
@@ -3355,6 +3355,63 @@
       </font>
     </dxf>
     <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_([$$-409]* #,##0.00_);_([$$-409]* \(#,##0.00\);_([$$-409]* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_([$$-409]* #,##0.00_);_([$$-409]* \(#,##0.00\);_([$$-409]* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_([$$-409]* #,##0.00_);_([$$-409]* \(#,##0.00\);_([$$-409]* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_([$$-409]* #,##0.00_);_([$$-409]* \(#,##0.00\);_([$$-409]* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_([$$-409]* #,##0.00_);_([$$-409]* \(#,##0.00\);_([$$-409]* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_([$$-409]* #,##0.00_);_([$$-409]* \(#,##0.00\);_([$$-409]* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="4" formatCode="#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="4" formatCode="#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_([$$-409]* #,##0.00_);_([$$-409]* \(#,##0.00\);_([$$-409]* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="27" formatCode="dd/mm/yyyy\ hh:mm"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+    </dxf>
+    <dxf>
       <font>
         <b/>
         <i val="0"/>
@@ -3741,63 +3798,6 @@
         </patternFill>
       </fill>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_([$$-409]* #,##0.00_);_([$$-409]* \(#,##0.00\);_([$$-409]* &quot;-&quot;??_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_([$$-409]* #,##0.00_);_([$$-409]* \(#,##0.00\);_([$$-409]* &quot;-&quot;??_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_([$$-409]* #,##0.00_);_([$$-409]* \(#,##0.00\);_([$$-409]* &quot;-&quot;??_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_([$$-409]* #,##0.00_);_([$$-409]* \(#,##0.00\);_([$$-409]* &quot;-&quot;??_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_([$$-409]* #,##0.00_);_([$$-409]* \(#,##0.00\);_([$$-409]* &quot;-&quot;??_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_([$$-409]* #,##0.00_);_([$$-409]* \(#,##0.00\);_([$$-409]* &quot;-&quot;??_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="4" formatCode="#,##0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="4" formatCode="#,##0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_([$$-409]* #,##0.00_);_([$$-409]* \(#,##0.00\);_([$$-409]* &quot;-&quot;??_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="27" formatCode="dd/mm/yyyy\ hh:mm"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -10668,7 +10668,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{F82495E7-9F34-4C1F-83EC-FA45D59FA2BD}" name="tblContributions" displayName="tblContributions" ref="A1:C2" totalsRowShown="0">
   <autoFilter ref="A1:C2" xr:uid="{F82495E7-9F34-4C1F-83EC-FA45D59FA2BD}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{EAE9033F-E950-4D8F-AC60-78CCDA7A0C9E}" name="DATE" dataDxfId="44"/>
+    <tableColumn id="1" xr3:uid="{EAE9033F-E950-4D8F-AC60-78CCDA7A0C9E}" name="DATE" dataDxfId="27"/>
     <tableColumn id="2" xr3:uid="{1D40F1FF-D66C-4703-9DEC-93C768793D8F}" name="AMMOUNT"/>
     <tableColumn id="3" xr3:uid="{49855D82-DE07-4257-837D-DD0BE41E988B}" name="Notes"/>
   </tableColumns>
@@ -10712,64 +10712,64 @@
   <tableColumns count="31">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="symbol"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="StockName"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="LastTradeTime" dataDxfId="43">
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="LastTradeTime" dataDxfId="26">
       <calculatedColumnFormula array="1">_FV(B2,"Last trade time",TRUE)</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="TradeCurrency">
       <calculatedColumnFormula array="1">_FV(B2,"Currency")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="StockPrice" dataDxfId="42">
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="StockPrice" dataDxfId="25">
       <calculatedColumnFormula array="1">_FV(B2,"Price")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="ChangePercent" dataDxfId="41">
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="ChangePercent" dataDxfId="24">
       <calculatedColumnFormula array="1">_FV(B2,"Change (%)",TRUE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Change" dataDxfId="40">
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Change" dataDxfId="23">
       <calculatedColumnFormula array="1">_FV(B2,"Change")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="P/E" dataDxfId="39">
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="P/E" dataDxfId="22">
       <calculatedColumnFormula array="1">_FV(B2,"P/E",TRUE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Beta" dataDxfId="38">
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Beta" dataDxfId="21">
       <calculatedColumnFormula array="1">_FV(B2,"Beta")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="52WkHigh" dataDxfId="37">
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="52WkHigh" dataDxfId="20">
       <calculatedColumnFormula array="1">_FV(B2,"52 week high",TRUE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="52WkLow" dataDxfId="36">
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="52WkLow" dataDxfId="19">
       <calculatedColumnFormula array="1">_FV(B2,"52 week low",TRUE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="DayHigh" dataDxfId="35">
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="DayHigh" dataDxfId="18">
       <calculatedColumnFormula array="1">_FV(B2,"High")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="DayLow" dataDxfId="34">
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="DayLow" dataDxfId="17">
       <calculatedColumnFormula array="1">_FV(B2,"Low")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="Open" dataDxfId="33">
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="Open" dataDxfId="16">
       <calculatedColumnFormula array="1">_FV(B2,"Open")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="PreviousClose" dataDxfId="32">
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="PreviousClose" dataDxfId="15">
       <calculatedColumnFormula array="1">_FV(B2,"Previous close",TRUE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Volume" dataDxfId="31">
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Volume" dataDxfId="14">
       <calculatedColumnFormula array="1">_FV(B2,"Volume")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="AverageVolume" dataDxfId="30">
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="AverageVolume" dataDxfId="13">
       <calculatedColumnFormula array="1">_FV(B2,"Volume average",TRUE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="YearIncorported" dataDxfId="29">
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="YearIncorported" dataDxfId="12">
       <calculatedColumnFormula array="1">_FV(B2,"Year incorporated",TRUE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="Employees" dataDxfId="28">
+    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="Employees" dataDxfId="11">
       <calculatedColumnFormula array="1">_FV(B2,"Employees")</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="Industry">
       <calculatedColumnFormula array="1">_FV(B2,"Industry")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0000-000015000000}" name="MarketCap" dataDxfId="27">
+    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0000-000015000000}" name="MarketCap" dataDxfId="10">
       <calculatedColumnFormula array="1">_FV(B2,"Market cap",TRUE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0000-000016000000}" name="SharesOutstanding" dataDxfId="26">
+    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0000-000016000000}" name="SharesOutstanding" dataDxfId="9">
       <calculatedColumnFormula array="1">_FV(B2,"Shares outstanding",TRUE)</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="23" xr3:uid="{00000000-0010-0000-0000-000017000000}" name="50SMA"/>
@@ -10787,37 +10787,37 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{D39CE96F-8D2C-4A60-A43A-B3602E27FDC2}" name="tblHoldings" displayName="tblHoldings" ref="A1:N10" totalsRowShown="0" headerRowDxfId="25" dataDxfId="24" tableBorderDxfId="23">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{D39CE96F-8D2C-4A60-A43A-B3602E27FDC2}" name="tblHoldings" displayName="tblHoldings" ref="A1:N10" totalsRowShown="0" headerRowDxfId="44" dataDxfId="43" tableBorderDxfId="42">
   <autoFilter ref="A1:N10" xr:uid="{D39CE96F-8D2C-4A60-A43A-B3602E27FDC2}"/>
   <tableColumns count="14">
-    <tableColumn id="1" xr3:uid="{AE3CE10F-629F-414E-93DE-8949C4E58E7D}" name="Symbol" dataDxfId="22"/>
-    <tableColumn id="2" xr3:uid="{40700DF4-EB97-4DB9-BA32-772C3F8E34CC}" name="StockName" dataDxfId="21"/>
-    <tableColumn id="3" xr3:uid="{BED1527E-0498-4FF1-8E69-ECDB2EB30C25}" name="TradeCurrency" dataDxfId="20">
+    <tableColumn id="1" xr3:uid="{AE3CE10F-629F-414E-93DE-8949C4E58E7D}" name="Symbol" dataDxfId="41"/>
+    <tableColumn id="2" xr3:uid="{40700DF4-EB97-4DB9-BA32-772C3F8E34CC}" name="StockName" dataDxfId="40"/>
+    <tableColumn id="3" xr3:uid="{BED1527E-0498-4FF1-8E69-ECDB2EB30C25}" name="TradeCurrency" dataDxfId="39">
       <calculatedColumnFormula>_FV(B2,"Currency")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{2218CAC2-8A57-48EA-B1D3-CD7E0BA08ECA}" name="TotalBought" dataDxfId="19"/>
-    <tableColumn id="5" xr3:uid="{77160EAF-769F-4559-B5AE-C08A0AC76566}" name="TotalSold" dataDxfId="18"/>
-    <tableColumn id="6" xr3:uid="{324BA50C-3A95-4946-A384-C4EF731BD7F3}" name="NetPosition" dataDxfId="17"/>
-    <tableColumn id="7" xr3:uid="{24A211AE-9FE1-4D72-98D4-96F240F7DCFD}" name="AvgCost" dataDxfId="16"/>
-    <tableColumn id="8" xr3:uid="{E1C8BF44-8957-447E-B3C1-A76A00A619B8}" name="AvgBuyCost" dataDxfId="15">
+    <tableColumn id="4" xr3:uid="{2218CAC2-8A57-48EA-B1D3-CD7E0BA08ECA}" name="TotalBought" dataDxfId="38"/>
+    <tableColumn id="5" xr3:uid="{77160EAF-769F-4559-B5AE-C08A0AC76566}" name="TotalSold" dataDxfId="37"/>
+    <tableColumn id="6" xr3:uid="{324BA50C-3A95-4946-A384-C4EF731BD7F3}" name="NetPosition" dataDxfId="36"/>
+    <tableColumn id="7" xr3:uid="{24A211AE-9FE1-4D72-98D4-96F240F7DCFD}" name="AvgCost" dataDxfId="35"/>
+    <tableColumn id="8" xr3:uid="{E1C8BF44-8957-447E-B3C1-A76A00A619B8}" name="AvgBuyCost" dataDxfId="34">
       <calculatedColumnFormula>F2*G2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{73ED87C5-FB66-49D5-B1EF-4BE32DC6D51F}" name="StockPrice" dataDxfId="14">
+    <tableColumn id="9" xr3:uid="{73ED87C5-FB66-49D5-B1EF-4BE32DC6D51F}" name="StockPrice" dataDxfId="33">
       <calculatedColumnFormula>_FV(B2,"Price")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{1E08B942-A194-43F5-A7DB-404EC54A5C02}" name="FXRate" dataDxfId="13">
+    <tableColumn id="10" xr3:uid="{1E08B942-A194-43F5-A7DB-404EC54A5C02}" name="FXRate" dataDxfId="32">
       <calculatedColumnFormula>Config!$C$1</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{42171935-FB72-4173-A1EB-132DDE8201DD}" name="ChangePercent" dataDxfId="12">
+    <tableColumn id="14" xr3:uid="{42171935-FB72-4173-A1EB-132DDE8201DD}" name="ChangePercent" dataDxfId="31">
       <calculatedColumnFormula array="1">_FV(B2,"Change (%)",TRUE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{96D6E4C8-F5BD-4A3E-88A2-BF403C882136}" name="MarketValue" dataDxfId="11">
+    <tableColumn id="11" xr3:uid="{96D6E4C8-F5BD-4A3E-88A2-BF403C882136}" name="MarketValue" dataDxfId="30">
       <calculatedColumnFormula>F2*I2*J2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{E928C781-D2C4-42A1-A053-38B541581BCB}" name="P&amp;L" dataDxfId="10">
+    <tableColumn id="12" xr3:uid="{E928C781-D2C4-42A1-A053-38B541581BCB}" name="P&amp;L" dataDxfId="29">
       <calculatedColumnFormula>L2-H2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{53BE744D-B35A-4E6B-8EA9-E422203F974E}" name="P&amp;LPercent" dataDxfId="9">
+    <tableColumn id="13" xr3:uid="{53BE744D-B35A-4E6B-8EA9-E422203F974E}" name="P&amp;LPercent" dataDxfId="28">
       <calculatedColumnFormula>IF(H2=0,"",M2/H2)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>

--- a/dashboard/trading_system.xlsx
+++ b/dashboard/trading_system.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\husainnatha\projects\tradingsystem\dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{510817E3-E99D-4238-88D4-F747B0482B1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9C12DA8-C7B7-4CDA-84A3-D07925B552C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CONTRIBUTIONS" sheetId="11" r:id="rId1"/>
@@ -3343,6 +3343,63 @@
       </font>
     </dxf>
     <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_([$$-409]* #,##0.00_);_([$$-409]* \(#,##0.00\);_([$$-409]* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_([$$-409]* #,##0.00_);_([$$-409]* \(#,##0.00\);_([$$-409]* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_([$$-409]* #,##0.00_);_([$$-409]* \(#,##0.00\);_([$$-409]* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_([$$-409]* #,##0.00_);_([$$-409]* \(#,##0.00\);_([$$-409]* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_([$$-409]* #,##0.00_);_([$$-409]* \(#,##0.00\);_([$$-409]* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_([$$-409]* #,##0.00_);_([$$-409]* \(#,##0.00\);_([$$-409]* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="4" formatCode="#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="4" formatCode="#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_([$$-409]* #,##0.00_);_([$$-409]* \(#,##0.00\);_([$$-409]* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="27" formatCode="dd/mm/yyyy\ hh:mm"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+    </dxf>
+    <dxf>
       <font>
         <b/>
         <i val="0"/>
@@ -3730,63 +3787,6 @@
       </fill>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
-    <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_([$$-409]* #,##0.00_);_([$$-409]* \(#,##0.00\);_([$$-409]* &quot;-&quot;??_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_([$$-409]* #,##0.00_);_([$$-409]* \(#,##0.00\);_([$$-409]* &quot;-&quot;??_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_([$$-409]* #,##0.00_);_([$$-409]* \(#,##0.00\);_([$$-409]* &quot;-&quot;??_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_([$$-409]* #,##0.00_);_([$$-409]* \(#,##0.00\);_([$$-409]* &quot;-&quot;??_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_([$$-409]* #,##0.00_);_([$$-409]* \(#,##0.00\);_([$$-409]* &quot;-&quot;??_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_([$$-409]* #,##0.00_);_([$$-409]* \(#,##0.00\);_([$$-409]* &quot;-&quot;??_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="4" formatCode="#,##0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="4" formatCode="#,##0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_([$$-409]* #,##0.00_);_([$$-409]* \(#,##0.00\);_([$$-409]* &quot;-&quot;??_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="27" formatCode="dd/mm/yyyy\ hh:mm"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -3931,8 +3931,8 @@
     <v>233.67</v>
     <v>16.899999999999999</v>
     <v>3.6537999999999999</v>
-    <v>4.3849999999999998</v>
-    <v>2.6204000000000002E-2</v>
+    <v>-2.16</v>
+    <v>-1.2907999999999999E-2</v>
     <v>USD</v>
     <v>Applied Optoelectronics, Inc. is a developer and manufacturer of advanced optical and hybrid fiber coaxial (HFC) networking products that are the building blocks for artificial intelligence (AI) datacenters, Cable TV Broadband (CATV) and broadband fiber access networks around the world. The Company supplies this critical infrastructure to tier-one customers across cloud computing, CATV broadband, telecom, and fiber-to-the-home (FTTH) markets. It designs and manufactures a range of optical communications products at varying levels of integration, from components, subassemblies and modules to complete turn-key equipment. In the CATV market, it supplies a broad array of products, including lasers, transmitters and transceivers, and turn-key equipment. It supplies optical transceivers that plug into switches and servers within the data center and allow these network devices to send and receive data over fiber optic cables. In the telecom market, it supplies lasers and laser subassemblies.</v>
     <v>4691</v>
@@ -3943,20 +3943,20 @@
     <v>174.75</v>
     <v>Electronic Equipment &amp; Parts</v>
     <v>Stock</v>
-    <v>46191.626761168751</v>
+    <v>46191.666718981251</v>
     <v>0</v>
     <v>158.69999999999999</v>
-    <v>13779689678</v>
+    <v>13254500748</v>
     <v>APPLIED OPTOELECTRONICS, INC.</v>
     <v>APPLIED OPTOELECTRONICS, INC.</v>
     <v>174.73</v>
     <v>0</v>
     <v>167.34</v>
-    <v>171.72499999999999</v>
+    <v>165.18</v>
     <v>80242770</v>
     <v>AAOI</v>
     <v>APPLIED OPTOELECTRONICS, INC. (XNAS:AAOI)</v>
-    <v>6505373</v>
+    <v>8405885</v>
     <v>13263710</v>
     <v>2013</v>
   </rv>
@@ -3982,8 +3982,8 @@
     <v>317.39999999999998</v>
     <v>195.07</v>
     <v>1.0942000000000001</v>
-    <v>2.91</v>
-    <v>9.8329999999999997E-3</v>
+    <v>1.5676000000000001</v>
+    <v>5.2969999999999996E-3</v>
     <v>USD</v>
     <v>Apple Inc. designs, manufactures and markets smartphones, personal computers, tablets, wearables and accessories, and sells a variety of related services. Its product categories include iPhone, Mac, iPad, Wearables, Home and Accessories. Its services include advertising, AppleCare, cloud services, digital content, and payment services. The Company operates various platforms, including the App Store, that allow customers to discover and download applications and digital content, such as books, music, video, games and podcasts. It also offers digital content through subscription-based services, including Apple Arcade, Apple Fitness+, Apple Music, Apple News+, and Apple TV+. Its wearables include smartwatches, wireless headphones, and spatial computers. Its products include iPhone 16 Pro, iPhone 16, iPhone 15, iPhone 14, iPhone SE, MacBook Air, MacBook Pro, iMac, Mac mini, Mac Studio, Mac Pro, iPad Pro, iPad Air, AirPods, AirPods Pro, AirPods Max, Apple TV, Apple Vision Pro and others.</v>
     <v>166000</v>
@@ -3994,20 +3994,20 @@
     <v>300.57</v>
     <v>Computers, Phones &amp; Household Electronics</v>
     <v>Stock</v>
-    <v>46191.626774941404</v>
+    <v>46191.666717916407</v>
     <v>3</v>
     <v>295.62</v>
-    <v>4389464409600</v>
+    <v>4369748097536</v>
     <v>APPLE INC.</v>
     <v>APPLE INC.</v>
     <v>298.43</v>
-    <v>36.296700000000001</v>
+    <v>36.133699999999997</v>
     <v>295.95</v>
-    <v>298.86</v>
+    <v>297.51760000000002</v>
     <v>14687360000</v>
     <v>AAPL</v>
     <v>APPLE INC. (XNAS:AAPL)</v>
-    <v>30257970</v>
+    <v>36514211</v>
     <v>49044152</v>
     <v>1977</v>
   </rv>
@@ -4053,8 +4053,8 @@
     <v>392.58</v>
     <v>190.12</v>
     <v>1.4516</v>
-    <v>-0.4</v>
-    <v>-2.0379999999999999E-3</v>
+    <v>-2.2850000000000001</v>
+    <v>-1.1642E-2</v>
     <v>USD</v>
     <v>Adobe Inc. is a global technology company. The Company's products, services and solutions are used around the world to imagine, create, manage, deliver, measure, optimize and engage with content across surfaces and fuel digital experiences. Its segments include Digital Media, Digital Experience, and Publishing and Advertising. The Digital Media segment is centered around Adobe Creative Cloud and Adobe Document Cloud, which include Adobe Express, Adobe Firefly, Photoshop and other products, offering a variety of tools for creative professionals, communicators and other consumers. The Digital Experience segment provides an integrated platform and set of products, services and solutions through Adobe Experience Cloud. The Publishing and Advertising segment contains legacy products and services. In addition, its Adobe GenStudio solution allows businesses to simplify their content supply chain process with generative artificial intelligence (AI) capabilities and intelligent automation.</v>
     <v>31360</v>
@@ -4066,20 +4066,20 @@
     <v>9</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46191.626769003909</v>
+    <v>46191.666697568748</v>
     <v>10</v>
     <v>190.12</v>
-    <v>77862300000</v>
+    <v>77113012500</v>
     <v>ADOBE INC.</v>
     <v>ADOBE INC.</v>
     <v>193.61</v>
-    <v>11.2096</v>
+    <v>11.101699999999999</v>
     <v>196.28</v>
-    <v>195.88</v>
+    <v>193.995</v>
     <v>397500000</v>
     <v>ADBE</v>
     <v>ADOBE INC. (XNAS:ADBE)</v>
-    <v>4545532</v>
+    <v>5360319</v>
     <v>7067597</v>
     <v>1997</v>
   </rv>
@@ -4105,8 +4105,8 @@
     <v>126.62</v>
     <v>10.887499999999999</v>
     <v>3.1297999999999999</v>
-    <v>4.8499999999999996</v>
-    <v>4.3064999999999999E-2</v>
+    <v>3.48</v>
+    <v>3.0899999999999997E-2</v>
     <v>USD</v>
     <v>Aehr Test Systems, Inc. offers test solutions for testing, burning-in, and stabilizing semiconductor devices in wafer level, singulated die, and package part form. The Company's products include the FOX-P family of test and burn-in systems and FOX WaferPak Aligner, FOX WaferPak Contactor, FOX DiePak Carrier and FOX DiePak Loader. The FOX-XP and FOX-NP systems are full wafer contact and singulated die/module test and burn-in systems that can test, burn-in and stabilize a range of devices such as silicon carbide-based and other power semiconductors, 2D and 3D sensors used in phones, tablets, and other computing devices, memory semiconductors, processors, microcontrollers, systems-on-a-chip, and photonics and integrated optical devices used in AI. FOX-CP system is a single-wafer compact test solution for logic, memory and photonic devices. FOX WaferPak Contactor contains a full wafer contactor capable of testing wafers up to 300 millimeters that enables integrated circuit manufacturers.</v>
     <v>136</v>
@@ -4117,20 +4117,20 @@
     <v>121.05</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46191.626766678128</v>
+    <v>46191.666672812498</v>
     <v>13</v>
     <v>114.15</v>
-    <v>3694813277</v>
+    <v>3651722325</v>
     <v>AEHR TEST SYSTEMS</v>
     <v>AEHR TEST SYSTEMS</v>
     <v>119.45</v>
     <v>0</v>
     <v>112.62</v>
-    <v>117.47</v>
+    <v>116.1</v>
     <v>31453250</v>
     <v>AEHR</v>
     <v>AEHR TEST SYSTEMS (XNAS:AEHR)</v>
-    <v>481686</v>
+    <v>578626</v>
     <v>2156360</v>
     <v>1977</v>
   </rv>
@@ -4152,8 +4152,8 @@
     <v>12.24</v>
     <v>10.99</v>
     <v>0.8397</v>
-    <v>0.03</v>
-    <v>2.519E-3</v>
+    <v>0.05</v>
+    <v>4.1980000000000003E-3</v>
     <v>CAD</v>
     <v>Atrium Mortgage Investment Corporation is a Canada-based company. The Company is a non-bank provider of residential and commercial mortgages that lends in urban centers in Canada. Its objectives are to provide its shareholders with dividends and preserve shareholders equity by lending within conservative risk parameters. Its investment strategy is to invest in commercial and residential mortgages from borrowers whose financing needs are not being met by the larger financial institutions. It finances various types of properties, which include residential houses, small multi-family residential properties comprising six units or fewer, residential apartment buildings, commercial and storefront retail properties, as well as residential and commercial land development sites. It also provides construction financing and short-term bridge loans to real estate developers. The Company is managed by Canadian Mortgage Capital Corporation (CMCC).</v>
     <v>0</v>
@@ -4161,22 +4161,22 @@
     <v>NEOE</v>
     <v>NEOE</v>
     <v>20 Adelaide Street East, Suite 900, TORONTO, ON, M5C 2T6 CA</v>
-    <v>11.95</v>
+    <v>11.96</v>
     <v>Banking Services</v>
     <v>Stock</v>
-    <v>46191.621620416408</v>
+    <v>46191.662628251564</v>
     <v>11.94</v>
-    <v>575981898</v>
+    <v>576946692</v>
     <v>ATRIUM MORTGAGE INVESTMENT CORPORATION</v>
     <v>ATRIUM MORTGAGE INVESTMENT CORPORATION</v>
     <v>11.95</v>
-    <v>11.3466</v>
+    <v>11.365600000000001</v>
     <v>11.91</v>
-    <v>11.94</v>
+    <v>11.96</v>
     <v>48239690</v>
     <v>AI</v>
     <v>ATRIUM MORTGAGE INVESTMENT CORPORATION (NEOE:AI)</v>
-    <v>900</v>
+    <v>1420</v>
     <v>96860</v>
     <v>2001</v>
   </rv>
@@ -4195,11 +4195,11 @@
     <v>3</v>
     <v>Finance</v>
     <v>4</v>
-    <v>414.74990000000003</v>
+    <v>417.745</v>
     <v>84.78</v>
     <v>2.65</v>
-    <v>37.1</v>
-    <v>9.9017999999999995E-2</v>
+    <v>43.064999999999998</v>
+    <v>0.114938</v>
     <v>USD</v>
     <v>Astera Labs, Inc. is a global semiconductor company. The Company provides semiconductor-based connectivity solutions for cloud and artificial intelligence (AI) infrastructure. It has developed and deployed its Intelligent Connectivity Platform built from the ground up for cloud and AI infrastructure. Its Intelligent Connectivity Platform provides its customers with the ability to deploy and operate high-performance cloud and AI infrastructure on a scale, addressing an increasingly diverse set of requirements. It provides its connectivity products in various form factors, including Integrated Circuits (ICs), boards, and modules. Its PCIe, CXL and Ethernet semiconductor-based connectivity solutions are purpose-built to unleash the potential of accelerated computing at cloud-scale. The Company's products include Aries products, Taurus products, Leo products and Scorpio products.</v>
     <v>756</v>
@@ -4207,22 +4207,22 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>2345 North First Street, SAN JOSE, CA, 95131 US</v>
-    <v>414.74990000000003</v>
+    <v>417.745</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46191.626750462499</v>
+    <v>46191.666720150002</v>
     <v>384.73</v>
-    <v>70582345062</v>
+    <v>71604793185</v>
     <v>ASTERA LABS, INC.</v>
     <v>ASTERA LABS, INC.</v>
     <v>384.73</v>
-    <v>277.59199999999998</v>
+    <v>281.61320000000001</v>
     <v>374.68</v>
-    <v>411.78</v>
+    <v>417.745</v>
     <v>171407900</v>
     <v>ALAB</v>
     <v>ASTERA LABS, INC. (XNAS:ALAB)</v>
-    <v>1619725</v>
+    <v>2707866</v>
     <v>6183611</v>
     <v>2017</v>
   </rv>
@@ -4248,8 +4248,8 @@
     <v>96.69</v>
     <v>48.3</v>
     <v>2.1528999999999998</v>
-    <v>2.9950000000000001</v>
-    <v>4.5461000000000001E-2</v>
+    <v>2.6</v>
+    <v>3.9466000000000001E-2</v>
     <v>USD</v>
     <v>Ambarella, Inc. is a developer of low-power system-on-a-chip (SoC) semiconductors and software for edge artificial intelligence (AI) applications. The Company's technologies make electronic systems smarter, enabling them to become partially or fully autonomous with features, such as person detection, object classification, and analytics, in addition to performing complex data analysis in real time, delivering imagery, and preserving vital system resources, such as power and network bandwidth. It specializes in the development of deployable, scalable designs for intelligent electronic systems that utilize high-bandwidth sensors. Its products are used in a variety of human viewing, computer vision and edge AI applications, including a variety of automotive camera systems, video security cameras, mobile and fixed robots, industrial applications, and consumer devices, such as action, drone, and 360-degree cameras.</v>
     <v>959</v>
@@ -4257,23 +4257,23 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>3101 Jay Street, CA, 95054 US</v>
-    <v>68.959999999999994</v>
+    <v>69.724999999999994</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46191.626740092186</v>
+    <v>46191.66671635391</v>
     <v>20</v>
     <v>66.22</v>
-    <v>3021420897</v>
+    <v>3004092966</v>
     <v>AMBARELLA, INC.</v>
     <v>AMBARELLA, INC.</v>
     <v>68.03</v>
     <v>0</v>
     <v>65.88</v>
-    <v>68.875</v>
+    <v>68.48</v>
     <v>43868180</v>
     <v>AMBA</v>
     <v>AMBARELLA, INC. (XNAS:AMBA)</v>
-    <v>461518</v>
+    <v>599671</v>
     <v>1652445</v>
     <v>2004</v>
   </rv>
@@ -4299,8 +4299,8 @@
     <v>558.37</v>
     <v>125.77</v>
     <v>2.4847000000000001</v>
-    <v>20.38</v>
-    <v>3.9767000000000004E-2</v>
+    <v>22.639700000000001</v>
+    <v>4.4177000000000001E-2</v>
     <v>USD</v>
     <v>Advanced Micro Devices, Inc. is a global semiconductor company. The Company is focused on high-performance computing and artificial intelligence (AI). Its segments include Data Center, Client and Gaming, and Embedded. Data Center segment includes AI accelerators, microprocessors (CPUs) for servers, graphics processing units (GPUs), accelerated processing units (APUs), data processing units (DPUs), Field Programmable Gate Arrays (FPGAs), and Adaptive system-on-Chip (SoC) products for data centers. Client and Gaming segment includes CPUs, APUs, chipsets for desktops and notebooks, discrete GPUs, and semi-custom SoC products and development services. Embedded segment includes embedded CPUs, APUs, FPGAs, system on modules (SOMs), and Adaptive SoC products. It markets and sells its products under the AMD trademark. Its products include AMD EPYC, AMD Ryzen, AMD Ryzen PRO, Virtex UltraScale+, among others.</v>
     <v>31000</v>
@@ -4308,23 +4308,23 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>2485 Augustine Drive, SANTA CLARA, CA, 95054 US</v>
-    <v>536.83000000000004</v>
+    <v>539.61990000000003</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46191.626757870312</v>
+    <v>46191.666724178125</v>
     <v>23</v>
-    <v>527</v>
-    <v>868882048860</v>
+    <v>526.31500000000005</v>
+    <v>872566717939</v>
     <v>ADVANCED MICRO DEVICES, INC.</v>
     <v>ADVANCED MICRO DEVICES, INC.</v>
     <v>532.73</v>
-    <v>177.6259</v>
+    <v>178.3792</v>
     <v>512.48</v>
-    <v>532.86</v>
+    <v>535.11969999999997</v>
     <v>1630601000</v>
     <v>AMD</v>
     <v>ADVANCED MICRO DEVICES, INC. (XNAS:AMD)</v>
-    <v>11481762</v>
+    <v>15734882</v>
     <v>31365270</v>
     <v>1969</v>
   </rv>
@@ -4350,8 +4350,8 @@
     <v>278.56</v>
     <v>196</v>
     <v>1.4664999999999999</v>
-    <v>3.9068999999999998</v>
-    <v>1.6449999999999999E-2</v>
+    <v>6.3601999999999999</v>
+    <v>2.6779999999999998E-2</v>
     <v>USD</v>
     <v>Amazon.com, Inc. provides a range of products and services to customers. The products offered through its stores include merchandise and content it has purchased for resale and products offered by third-party sellers. The Company’s segments include North America, International and Amazon Web Services (AWS). It serves consumers through its online and physical stores and focuses on selection, price, and convenience. Customers access its offerings through its websites, mobile apps, Alexa, devices, streaming, and physically visiting its stores. It also manufactures and sells electronic devices, including Kindle, Fire tablet, Fire TV, Echo, Ring, Blink, and eero, and develops and produces media content. It serves developers and enterprises of all sizes, including start-ups, government agencies, and academic institutions, through AWS, which offers a set of on-demand technology services, including compute, storage, database, analytics, and machine learning, and other services.</v>
     <v>1575000</v>
@@ -4359,23 +4359,23 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>410 Terry Avenue North, SEATTLE, WA, 98109 US</v>
-    <v>241.82</v>
+    <v>244.32</v>
     <v>Diversified Retail</v>
     <v>Stock</v>
-    <v>46191.626768738279</v>
+    <v>46191.666713240622</v>
     <v>26</v>
     <v>236.02</v>
-    <v>2596840578059</v>
+    <v>2623230996022</v>
     <v>AMAZON.COM, INC.</v>
     <v>AMAZON.COM, INC.</v>
     <v>240.31</v>
-    <v>28.849900000000002</v>
+    <v>29.143000000000001</v>
     <v>237.5</v>
-    <v>241.40690000000001</v>
+    <v>243.86019999999999</v>
     <v>10757110000</v>
     <v>AMZN</v>
     <v>AMAZON.COM, INC. (XNAS:AMZN)</v>
-    <v>21217746</v>
+    <v>29735475</v>
     <v>41102004</v>
     <v>1996</v>
   </rv>
@@ -4401,8 +4401,8 @@
     <v>179.8</v>
     <v>85.58</v>
     <v>1.5999000000000001</v>
-    <v>4.2050000000000001</v>
-    <v>2.5495999999999998E-2</v>
+    <v>4.07</v>
+    <v>2.4676999999999998E-2</v>
     <v>USD</v>
     <v>Arista Networks, Inc. is a provider of data-driven, client-to-cloud networking for large artificial intelligence (AI), data center, campus and routing environments. The Company's cloud networking solutions consist of its Extensible Operating System (EOS), a set of network applications and its Ethernet switching and routing platforms. Its platforms deliver availability, agility, automation, analytics, and security through an advanced network operating stack. It offers a robust set of solutions, ranging from modular and fixed-form-factor campus spine switches to Power-over-Ethernet (PoE) leaf switches and Wi-Fi access points, all managed through CloudVision. The Company's network-as-a-service approach empowers customers of all sizes to leverage their data through offerings spanning three categories: Core (AI, Cloud, and Data Center Networking), Cognitive Adjacencies (Campus and Routing), and Cognitive Networks (Software and Services).</v>
     <v>5115</v>
@@ -4413,20 +4413,20 @@
     <v>171.83500000000001</v>
     <v>Communications &amp; Networking</v>
     <v>Stock</v>
-    <v>46191.626728240626</v>
+    <v>46191.666690428123</v>
     <v>29</v>
     <v>167.65</v>
-    <v>212975299405</v>
+    <v>212805307000</v>
     <v>ARISTA NETWORKS, INC.</v>
     <v>ARISTA NETWORKS, INC.</v>
     <v>171.2</v>
-    <v>57.930900000000001</v>
+    <v>57.884599999999999</v>
     <v>164.93</v>
-    <v>169.13499999999999</v>
+    <v>169</v>
     <v>1259203000</v>
     <v>ANET</v>
     <v>ARISTA NETWORKS, INC. (XNYS:ANET)</v>
-    <v>2728161</v>
+    <v>3215628</v>
     <v>9242963</v>
     <v>2011</v>
   </rv>
@@ -4452,8 +4452,8 @@
     <v>745.61</v>
     <v>320</v>
     <v>2.5051999999999999</v>
-    <v>-8.3049999999999997</v>
-    <v>-1.7319999999999999E-2</v>
+    <v>-8.1</v>
+    <v>-1.6893000000000002E-2</v>
     <v>USD</v>
     <v>AppLovin Corporation operates a marketing platform. It provides software and artificial intelligence solutions for businesses to reach, monetize and grow their audiences. Its advertising solutions include Axon Ads Manager, MAX, Adjust, and Wurl. Its clients use Axon Ads Manager to automate, optimize, and manage customer acquisition. They set marketing and transaction goals, and Axon Ads Manager maximizes advertising spend at their return on advertising spend targets and other marketing objectives. Publishers use MAX to optimize the sale of their app advertising inventory to demand-side platforms and ad networks. The MAX tool provides insights to manage against key performance indicators, understand the long-term value of users, and helps manage profitability. Axon Ads Manager comprises the amount charged to advertisers based on their campaign goals, less consideration paid or payable to publishers. Advertising clients use Wurl's connected TV platform to distribute streaming videos.</v>
     <v>898</v>
@@ -4464,20 +4464,20 @@
     <v>483.9</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46191.626761562497</v>
+    <v>46191.666724409377</v>
     <v>32</v>
     <v>460.28</v>
-    <v>158289888900</v>
+    <v>158358756600</v>
     <v>APPLOVIN CORPORATION</v>
     <v>APPLOVIN CORPORATION</v>
     <v>479.49</v>
-    <v>40.945900000000002</v>
+    <v>40.963700000000003</v>
     <v>479.49</v>
-    <v>471.185</v>
+    <v>471.39</v>
     <v>335940000</v>
     <v>APP</v>
     <v>APPLOVIN CORPORATION (XNAS:APP)</v>
-    <v>1903939</v>
+    <v>2961607</v>
     <v>5039684</v>
     <v>2011</v>
   </rv>
@@ -4503,25 +4503,25 @@
     <v>92.65</v>
     <v>62.945</v>
     <v>2.04</v>
-    <v>1.177</v>
-    <v>1.4996000000000001E-2</v>
+    <v>0.61</v>
+    <v>7.7720000000000003E-3</v>
     <v>USD</v>
     <v>CBOE BZX Exchange</v>
     <v>BATS</v>
     <v>7.4999999999999997E-3</v>
     <v>80.08</v>
     <v>ETF</v>
-    <v>46191.626704478906</v>
+    <v>46191.666690068749</v>
     <v>35</v>
     <v>78.694999999999993</v>
     <v>7262198811.6000004</v>
     <v>ARK Innovation</v>
     <v>79.67</v>
     <v>78.489999999999995</v>
-    <v>79.667000000000002</v>
+    <v>79.099999999999994</v>
     <v>ARKK</v>
     <v>ARK Innovation (BATS:ARKK)</v>
-    <v>1675867</v>
+    <v>4059167</v>
     <v>8263496</v>
   </rv>
   <rv s="2">
@@ -4567,8 +4567,8 @@
     <v>452.608</v>
     <v>100.02</v>
     <v>1.448</v>
-    <v>28.83</v>
-    <v>6.8825999999999998E-2</v>
+    <v>25.024999999999999</v>
+    <v>5.9743000000000004E-2</v>
     <v>USD</v>
     <v>Arm Holdings plc is a United Kingdom-based company. The Company is engaged in the design of central processing units (CPUs) and compute platforms for semiconductor chips. It develops and licenses CPU products and related technology. Its cloud and data center solutions include Arm AGI CPU and Arm Neoverse Compute Subsystems. The Arm Agentic Generalized Infrastructure (AGI) CPU is a production-ready system on a chip (SoC) for artificial intelligence (AI) data centers, delivering compute at scale. The Arm Neoverse Compute Subsystems (CSS) are pre-validated, performance-optimized compute platforms designed to accelerate infrastructure silicon development. The Company's primary markets include smartphone applications, processors and other chips used in mobile phones, consumer electronics, networking equipment, cloud and data center servers, automotive applications, Internet of Things (loT) and other embedded computing devices.</v>
     <v>9584</v>
@@ -4579,19 +4579,19 @@
     <v>452.608</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46191.626752198441</v>
+    <v>46191.666708703124</v>
     <v>434.19</v>
-    <v>478189649090</v>
+    <v>474125608495</v>
     <v>ARM HOLDINGS PLC</v>
     <v>ARM HOLDINGS PLC</v>
     <v>441.75</v>
-    <v>528.9579</v>
+    <v>524.4624</v>
     <v>418.88</v>
-    <v>447.71</v>
+    <v>443.90499999999997</v>
     <v>1068079000</v>
     <v>ARM</v>
     <v>ARM HOLDINGS PLC (XNAS:ARM)</v>
-    <v>4189288</v>
+    <v>5062561</v>
     <v>12570991</v>
     <v>2018</v>
   </rv>
@@ -4617,8 +4617,8 @@
     <v>1941.52</v>
     <v>683.48</v>
     <v>1.7751999999999999</v>
-    <v>67.790000000000006</v>
-    <v>3.6292999999999999E-2</v>
+    <v>54.18</v>
+    <v>2.9007000000000002E-2</v>
     <v>USD</v>
     <v>ASML Holding N.V. is a holding company based in the Netherlands. The Company operates through its subsidiaries in the Netherlands, the United States, Italy, France, Germany, the United Kingdom, Ireland, Belgium, South Korea, Taiwan, Singapore, China, Hong Kong, Japan, Malaysia and Israel. The Company operates through one business segment which is engage in development, production, marketing, sales, upgrading and servicing of advanced semiconductor equipment systems, consisting of lithography, metrology and inspection systems. The Company offers TWINSCAN systems, equipped with lithography system with a mercury lamp as light source (i-line), Krypton Fluoride (KrF) and Argon Fluoride (ArF) light sources for processing wafers for manufacturing environments for which imaging at a small resolution is required. TWINSCAN systems also include immersion lithography systems (TWINSCAN immersion systems).</v>
     <v>43882</v>
@@ -4629,20 +4629,20 @@
     <v>1941.52</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46191.62674649297</v>
+    <v>46191.666716770313</v>
     <v>45</v>
     <v>1909.76</v>
-    <v>751306451074</v>
+    <v>746023760877</v>
     <v>ASML Holding NV</v>
     <v>ASML Holding NV</v>
     <v>1925.56</v>
-    <v>66.546300000000002</v>
+    <v>66.078400000000002</v>
     <v>1867.83</v>
-    <v>1935.62</v>
+    <v>1922.01</v>
     <v>388147700</v>
     <v>ASML</v>
     <v>ASML Holding NV (XNAS:ASML)</v>
-    <v>697110</v>
+    <v>874339</v>
     <v>1876885</v>
     <v>1994</v>
   </rv>
@@ -4668,8 +4668,8 @@
     <v>495</v>
     <v>244.17</v>
     <v>1.4635</v>
-    <v>16.29</v>
-    <v>4.1460999999999998E-2</v>
+    <v>15.24</v>
+    <v>3.8788000000000003E-2</v>
     <v>USD</v>
     <v>Broadcom Inc. is a global technology firm that designs, develops, and supplies a range of semiconductors, enterprise software and security solutions. The Company operates through two segments: semiconductor solutions and infrastructure software. Its semiconductor solutions segment includes all of its product lines and intellectual property (IP) licensing. It provides a variety of radio frequency semiconductor devices, wireless connectivity solutions, custom touch controllers, and inductive charging solutions for mobile applications. Its infrastructure software segment includes its private and hybrid cloud, application development and delivery, software-defined edge, application networking and security, mainframe, distributed and cybersecurity solutions, and its FC SAN business. It provides a portfolio of software solutions that enable customers to plan, develop, automate, manage and secure applications across mainframe, distributed, mobile and cloud platforms.</v>
     <v>33000</v>
@@ -4680,20 +4680,20 @@
     <v>412.48</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46191.626762094529</v>
+    <v>46191.666716758591</v>
     <v>48</v>
     <v>405.38</v>
-    <v>1946754160200</v>
+    <v>1941758701200</v>
     <v>BROADCOM INC.</v>
     <v>BROADCOM INC.</v>
     <v>409.8</v>
-    <v>68.158600000000007</v>
+    <v>67.983699999999999</v>
     <v>392.9</v>
-    <v>409.19</v>
+    <v>408.14</v>
     <v>4757580000</v>
     <v>AVGO</v>
     <v>BROADCOM INC. (XNAS:AVGO)</v>
-    <v>11189831</v>
+    <v>14286632</v>
     <v>30860978</v>
     <v>2018</v>
   </rv>
@@ -4719,8 +4719,8 @@
     <v>9.39</v>
     <v>3.01</v>
     <v>3.1318999999999999</v>
-    <v>0.03</v>
-    <v>7.7320000000000002E-3</v>
+    <v>-0.02</v>
+    <v>-5.1549999999999999E-3</v>
     <v>USD</v>
     <v>BigBear.ai Holdings, Inc. operates as a specialized provider of artificial intelligence (AI) technology. The Company provides decision intelligence solutions for supply chains and logistics, enterprise operations, manned-unmanned teaming in autonomous systems, and cybersecurity. Its solutions include AI orchestration and sensor function, digital identity management, computer vision, cybersecurity, predictive intelligence, modeling &amp; simulation, enterprise automation and professional services. It offers Trueface, which performs one-to-many (1:N) facial matches with real-time photos, delivering identity verification. It also offers veriScan, which captures and transmits real-time photos into a biometric matching service supporting access control and biometric boarding/bag tags. The Company serves homeland &amp; border security, defense, intelligence, manufacturing &amp; suppy chain, travel and trade industries.</v>
     <v>579</v>
@@ -4731,20 +4731,20 @@
     <v>3.94</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46191.626757383594</v>
+    <v>46191.666727546093</v>
     <v>51</v>
     <v>3.76</v>
-    <v>1872692545</v>
+    <v>1848745070</v>
     <v>BIGBEAR.AI HOLDINGS, INC.</v>
     <v>BIGBEAR.AI HOLDINGS, INC.</v>
     <v>3.9</v>
     <v>0</v>
     <v>3.88</v>
-    <v>3.91</v>
+    <v>3.86</v>
     <v>478949500</v>
     <v>BBAI</v>
     <v>BIGBEAR.AI HOLDINGS, INC. (XNYS:BBAI)</v>
-    <v>11417129</v>
+    <v>15249778</v>
     <v>45097609</v>
     <v>2020</v>
   </rv>
@@ -4770,8 +4770,8 @@
     <v>115.25</v>
     <v>36.884999999999998</v>
     <v>0.97750000000000004</v>
-    <v>-2.74</v>
-    <v>-4.4194000000000004E-2</v>
+    <v>-2.1</v>
+    <v>-3.3871000000000005E-2</v>
     <v>EUR</v>
     <v>Bayerische Motoren Werke AG (BMW) is a Germany-based company. The Company is engaged in the development and manufacturing of automobiles and motorcycles. Its business is divided into three segments: Automotive segment, Motorcycles segment, and Financial Services segment. The Automotive segment has three brands BMW, MINI and Rolls-Royce. The product range includes automobiles ranging from the compact class to the luxury class. The Motorcycles segment develops manufactures and sells motorcycles and scooters in the Sport, Tour, Roadster, Heritage, Adventure and Urban Mobility categories, as well as motorcycles for private use and special-purpose vehicles for operational use. The Financial Services segment offers credit financing and the leasing of BMW Group brand automobiles and motorcycles to retail customers. It also handles financing for dealerships and customer deposits.</v>
     <v>154540</v>
@@ -4782,20 +4782,20 @@
     <v>62.82</v>
     <v>Automobiles &amp; Auto Parts</v>
     <v>Stock</v>
-    <v>46191.615972222222</v>
+    <v>46191.654861111114</v>
     <v>54</v>
     <v>58.88</v>
     <v>54471310000</v>
     <v>Bayerische Motoren Werke AG</v>
     <v>Bayerische Motoren Werke AG</v>
     <v>62.38</v>
-    <v>5.3387000000000002</v>
+    <v>5.3963999999999999</v>
     <v>62</v>
-    <v>59.26</v>
+    <v>59.9</v>
     <v>615810400</v>
     <v>BMW</v>
     <v>Bayerische Motoren Werke AG (XFRA:BMW)</v>
-    <v>12312</v>
+    <v>12896</v>
     <v>1869040</v>
     <v>1995</v>
   </rv>
@@ -4821,8 +4821,8 @@
     <v>416.69</v>
     <v>262.74900000000002</v>
     <v>1.135</v>
-    <v>2.3650000000000002</v>
-    <v>6.0699999999999999E-3</v>
+    <v>2.0350000000000001</v>
+    <v>5.2230000000000002E-3</v>
     <v>USD</v>
     <v>Cadence Design Systems, Inc. is an electronic systems designing company. The Company applies its Intelligent System Design strategy to deliver software, hardware and intellectual property (IP) that turn design concepts into reality. Its product categories include Core Electronic Design Automation (EDA), Semiconductor IP, and System Design and Analysis (SD&amp;A). Core EDA includes software, hardware, and services used to design and verify a wide variety of semiconductors. The semiconductor IP portfolio includes silicon subsystems, software, and services that are used in semiconductor design. The SD&amp;A category provides solutions and services that enable the design and verification of complete electronic systems, from PCBs to complex system assemblies. Its semiconductors are used in various industries, including automotive, aerospace, biotech, hyperscale and cloud computing, data centers, telecommunications, medical technology, industrial Internet of things, and artificial intelligence (AI).</v>
     <v>13800</v>
@@ -4833,20 +4833,20 @@
     <v>401.18</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46191.626731712502</v>
+    <v>46191.666675185159</v>
     <v>57</v>
     <v>387.37</v>
-    <v>108110218440</v>
+    <v>108019199160</v>
     <v>CADENCE DESIGN SYSTEMS, INC.</v>
     <v>CADENCE DESIGN SYSTEMS, INC.</v>
     <v>392.85</v>
-    <v>91.505799999999994</v>
+    <v>91.428700000000006</v>
     <v>389.6</v>
-    <v>391.96499999999997</v>
+    <v>391.63499999999999</v>
     <v>275816000</v>
     <v>CDNS</v>
     <v>CADENCE DESIGN SYSTEMS, INC. (XNAS:CDNS)</v>
-    <v>1001367</v>
+    <v>1464930</v>
     <v>2319895</v>
     <v>1987</v>
   </rv>
@@ -4872,8 +4872,8 @@
     <v>412.7</v>
     <v>240.51</v>
     <v>1.1136999999999999</v>
-    <v>11.715</v>
-    <v>4.3848000000000005E-2</v>
+    <v>13.13</v>
+    <v>4.9145000000000001E-2</v>
     <v>USD</v>
     <v>Constellation Energy Corporation is a producer of emissions-free energy and an energy supplier to businesses, homes and public sector customers nationwide. The Company’s nuclear, hydro, wind, and solar generation facilities have the generating capacity to power the equivalent of 27 million homes, providing about 10% of the nation’s clean energy. Its segments include Mid-Atlantic, Midwest, New York, ERCOT, and Other Power Regions. Through its integrated business operations, it sells electricity, natural gas, and other energy-related products and sustainable solutions to various types of customers, including distribution utilities, municipalities, cooperatives, commercial, industrial, public sector, and residential customers in markets across multiple geographic regions. It operates approximately 55 gigawatts of capacity from nuclear, natural gas, geothermal, hydro, wind and solar facilities.</v>
     <v>15291</v>
@@ -4881,23 +4881,23 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>1310 Point Street, BALTIMORE, MD, 21231 US</v>
-    <v>279.92</v>
+    <v>281.2</v>
     <v>Electrical Utilities &amp; IPPs</v>
     <v>Stock</v>
-    <v>46191.626764015622</v>
+    <v>46191.666736724219</v>
     <v>60</v>
     <v>268</v>
-    <v>100148161270</v>
+    <v>100656290600</v>
     <v>CONSTELLATION ENERGY CORPORATION.</v>
     <v>CONSTELLATION ENERGY CORPORATION.</v>
     <v>269.14</v>
-    <v>24.2285</v>
+    <v>24.351500000000001</v>
     <v>267.17</v>
-    <v>278.88499999999999</v>
+    <v>280.3</v>
     <v>359102000</v>
     <v>CEG</v>
     <v>CONSTELLATION ENERGY CORPORATION. (XNAS:CEG)</v>
-    <v>2055660</v>
+    <v>2634506</v>
     <v>4187200</v>
     <v>2021</v>
   </rv>
@@ -4923,8 +4923,8 @@
     <v>270.21170000000001</v>
     <v>80.599999999999994</v>
     <v>3.2067999999999999</v>
-    <v>15.137499999999999</v>
-    <v>6.0712999999999996E-2</v>
+    <v>16.47</v>
+    <v>6.6056999999999991E-2</v>
     <v>USD</v>
     <v>Credo Technology Group Holding Ltd is a Cayman Islands-based holding company. The Company delivers high-speed solutions to break bandwidth barriers on every wired connection in the data infrastructure market. It provides high-speed connectivity solutions that deliver improved power efficiency as data rates and corresponding bandwidth requirements increase exponentially throughout the data infrastructure market. Its connectivity solutions are optimized for optical and electrical Ethernet applications, including the emerging 100 gigabits per second (G), 200G, 400G, 800G and the emerging 1.6 terabits per second (T) port markets. Its products are based on its Serializer/Deserializer (SerDes) and Digital Signal Processor (DSP) technologies. Its product families include integrated circuits (ICs) for the optical and line card markets, active electrical cables (AECs) and SerDes Chiplets. The Company’s intellectual property (IP) solutions consist primarily of SerDes IP licensing.</v>
     <v>807</v>
@@ -4932,23 +4932,23 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>C/O Maples Corporate Services, Limited, Po Box 309, Ugland House, GRAND CAYMAN, KY1-1104 KY</v>
-    <v>268.07</v>
+    <v>268.14999999999998</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46191.626767048438</v>
+    <v>46191.666702001559</v>
     <v>63</v>
     <v>252.73</v>
-    <v>49317344018</v>
+    <v>49565825820</v>
     <v>Credo Technology Group Holding Ltd</v>
     <v>Credo Technology Group Holding Ltd</v>
     <v>257.82</v>
-    <v>106.73480000000001</v>
+    <v>107.2726</v>
     <v>249.33</v>
-    <v>264.46749999999997</v>
+    <v>265.8</v>
     <v>186477900</v>
     <v>CRDO</v>
     <v>Credo Technology Group Holding Ltd (XNAS:CRDO)</v>
-    <v>2815787</v>
+    <v>3600297</v>
     <v>9162127</v>
   </rv>
   <rv s="2">
@@ -4973,8 +4973,8 @@
     <v>276.8</v>
     <v>149.80000000000001</v>
     <v>1.19</v>
-    <v>-2.4700000000000002</v>
-    <v>-1.5932999999999999E-2</v>
+    <v>-2.5449999999999999</v>
+    <v>-1.6417000000000001E-2</v>
     <v>USD</v>
     <v>Salesforce, Inc. is a customer relationship management (CRM) technology company. Its artificial intelligence (AI) powered Agentforce 360 Platform offers sales, service, marketing, commerce, collaboration, data management, integration, analytics, and information technology (IT) service solutions. It enables customers to build and deploy digital labor for employees and customers, leveraging autonomous AI agents across business functions. Its service offerings include Agentforce Sales, Agentforce Service, Agentforce 360 Platform, Slack and Others. The Agentforce Sales provides sales capabilities and tools built for organizations across prospecting, sales engagement, team collaboration, sales analytics and AI, sales programs, sales performance, partner management, and revenue and orders. The Agentforce Service provides field service solutions that enable companies to connect service agents, dispatchers and mobile employees through platform to schedule, dispatch and manage jobs.</v>
     <v>83334</v>
@@ -4985,20 +4985,20 @@
     <v>153.63999999999999</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46191.626772395313</v>
+    <v>46191.666697464847</v>
     <v>66</v>
     <v>149.80000000000001</v>
-    <v>124938450000</v>
+    <v>124877025000</v>
     <v>SALESFORCE, INC.</v>
     <v>SALESFORCE, INC.</v>
     <v>152.255</v>
-    <v>17.649699999999999</v>
+    <v>17.640999999999998</v>
     <v>155.02000000000001</v>
-    <v>152.55000000000001</v>
+    <v>152.47499999999999</v>
     <v>819000000</v>
     <v>CRM</v>
     <v>SALESFORCE, INC. (XNYS:CRM)</v>
-    <v>7824378</v>
+    <v>9266838</v>
     <v>15832976</v>
     <v>1999</v>
   </rv>
@@ -5024,8 +5024,8 @@
     <v>785.66</v>
     <v>342.72</v>
     <v>1.258</v>
-    <v>-2.81</v>
-    <v>-4.1139999999999996E-3</v>
+    <v>-9.4498999999999995</v>
+    <v>-1.3836999999999999E-2</v>
     <v>USD</v>
     <v>CrowdStrike Holdings, Inc. is a global cybersecurity company. The Company provides a cloud-native platform for protecting critical areas of enterprise risk - endpoints and cloud workloads, identity, and data. The Company's artificial intelligence (AI)-native CrowdStrike Falcon platform is a cloud-native unified platform built with AI at the core, capable of harnessing security and enterprise data to deliver highly modular solutions through a single lightweight sensor. Using cloud-scale AI, its Security Cloud enriches and correlates cybersecurity events with indicators of attack, threat intelligence, and enterprise data (including data from across endpoints, workloads, identities, DevOps, IT assets, and configurations) to create actionable data, identify shifts in adversary tactics, and automatically prevent threats in real-time across its customer base. It sells its Falcon platform via a partner-first subscription model to organizations of all sizes across multiple industries globally.</v>
     <v>11157</v>
@@ -5036,20 +5036,20 @@
     <v>695.91</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46191.62676030078</v>
+    <v>46191.666717140622</v>
     <v>69</v>
     <v>660.92</v>
-    <v>173142248720</v>
+    <v>171451963904</v>
     <v>CROWDSTRIKE HOLDINGS, INC.</v>
     <v>CROWDSTRIKE HOLDINGS, INC.</v>
     <v>685.48</v>
     <v>0</v>
     <v>682.96</v>
-    <v>680.15</v>
+    <v>673.51009999999997</v>
     <v>254564800</v>
     <v>CRWD</v>
     <v>CROWDSTRIKE HOLDINGS, INC. (XNAS:CRWD)</v>
-    <v>1104747</v>
+    <v>1310651</v>
     <v>3598503</v>
     <v>2011</v>
   </rv>
@@ -5071,8 +5071,8 @@
     <v>187</v>
     <v>63.8</v>
     <v>2.4809999999999999</v>
-    <v>3.98</v>
-    <v>3.4546E-2</v>
+    <v>2.6217999999999999</v>
+    <v>2.2756999999999999E-2</v>
     <v>USD</v>
     <v>CoreWeave, Inc. is a cloud infrastructure technology company. The Company offers the CoreWeave Cloud Platform, which consists of software and cloud services that deliver the automation and efficiency needed to manage complex artificial intelligence (AI) infrastructure. Its CoreWeave Cloud Platform is an integrated solution that is purpose-built for running AI workloads such as model training and inference. Its solutions include infrastructure services, managed software services, and application software services. Its Infrastructure Services provide its customers with access to advanced graphics processing unit (GPU) and central processing unit (CPU) compute, highly performant networking, and storage. Its Managed Software Services include CKS, a flexible virtual private cloud and a bare metal service that runs kubernetes directly on high-performance servers. Its Application Software Services build on top of its infrastructure and managed software services, integrating additional tools.</v>
     <v>2189</v>
@@ -5080,22 +5080,22 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>290 W. Mt. Pleasant Avenue, Suite 4100, LIVINGSTON, NJ, 07039 US</v>
-    <v>119.8</v>
+    <v>119.89</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46191.626762430467</v>
+    <v>46191.666716388281</v>
     <v>115.51009999999999</v>
-    <v>65026535976</v>
+    <v>64285542258</v>
     <v>COREWEAVE, INC.</v>
     <v>COREWEAVE, INC.</v>
     <v>118.76</v>
     <v>0</v>
     <v>115.21</v>
-    <v>119.19</v>
+    <v>117.8318</v>
     <v>545570400</v>
     <v>CRWV</v>
     <v>COREWEAVE, INC. (XNAS:CRWV)</v>
-    <v>9025426</v>
+    <v>11925907</v>
     <v>28399551</v>
     <v>2017</v>
   </rv>
@@ -5121,8 +5121,8 @@
     <v>130.3656</v>
     <v>65.38</v>
     <v>1.0065999999999999</v>
-    <v>0.78</v>
-    <v>6.6479999999999994E-3</v>
+    <v>1.0900000000000001</v>
+    <v>9.2899999999999996E-3</v>
     <v>USD</v>
     <v>Cisco Systems, Inc. designs and sells a range of technologies that power the Internet. The Company is integrating its product portfolios across networking, security, collaboration, applications and cloud. The Company's segments include the Americas; Europe, Middle East, and Africa (EMEA), and Asia Pacific, Japan, and China (APJC). Its Networking product category represents its core networking technologies of switching, routing, wireless, fifth generation (5G), silicon, optics solutions and compute products. Its Security product category consists of its cloud and application security, industrial security, network security, and user and device security offerings. Its Collaboration product category consists of its meetings, collaboration devices, calling, contact center and platform as a service (CPaaS) offering. Its Observability product category consists of its full stack observability offerings.</v>
     <v>86200</v>
@@ -5133,20 +5133,20 @@
     <v>119.56</v>
     <v>Communications &amp; Networking</v>
     <v>Stock</v>
-    <v>46191.626772488278</v>
+    <v>46191.666709999998</v>
     <v>74</v>
     <v>117.3</v>
-    <v>465522887850</v>
+    <v>466744732700</v>
     <v>CISCO SYSTEMS, INC.</v>
     <v>CISCO SYSTEMS, INC.</v>
     <v>118.6</v>
-    <v>39.356900000000003</v>
+    <v>39.4602</v>
     <v>117.33</v>
-    <v>118.11</v>
+    <v>118.42</v>
     <v>3941435000</v>
     <v>CSCO</v>
     <v>CISCO SYSTEMS, INC. (XNAS:CSCO)</v>
-    <v>8740645</v>
+    <v>11689693</v>
     <v>27959657</v>
     <v>2021</v>
   </rv>
@@ -5172,8 +5172,8 @@
     <v>278.70499999999998</v>
     <v>98.010099999999994</v>
     <v>1.5683</v>
-    <v>-5.18</v>
-    <v>-2.2856999999999999E-2</v>
+    <v>-7.06</v>
+    <v>-3.1152000000000003E-2</v>
     <v>USD</v>
     <v>Datadog Inc provides an AI-powered observability and security platform for cloud applications. Its Software as a Service (SaaS) platform integrates and automates infrastructure monitoring, application performance monitoring, log management, user experience monitoring, cloud security and service management. Its proprietary platform combines the power of metrics, traces, logs, user sessions, security signals, and other data from a single agent and over 1,000 integrations to provide a unified view of infrastructure, application performance and real-time events impacting performance. Its solutions include built for dynamic cloud and hybrid infrastructures, simple but not simplistic, integrated data platform, built for collaboration, cloud-agnostic, ubiquitous, and integrates with its customers complex environments. Its platform is used by industries to enable digital transformation and cloud migration, and drive collaboration among development, operations, security and business teams.</v>
     <v>8100</v>
@@ -5184,20 +5184,20 @@
     <v>225.58500000000001</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46191.626733760939</v>
+    <v>46191.666688935155</v>
     <v>77</v>
     <v>215.30009999999999</v>
-    <v>78827386290</v>
+    <v>78158181114</v>
     <v>DATADOG, INC.</v>
     <v>DATADOG, INC.</v>
     <v>224.69</v>
-    <v>561.05899999999997</v>
+    <v>556.29589999999996</v>
     <v>226.63</v>
-    <v>221.45</v>
+    <v>219.57</v>
     <v>355960200</v>
     <v>DDOG</v>
     <v>DATADOG, INC. (XNAS:DDOG)</v>
-    <v>1865886</v>
+    <v>2247622</v>
     <v>5860110</v>
     <v>2026</v>
   </rv>
@@ -5223,8 +5223,8 @@
     <v>469.47</v>
     <v>110.22</v>
     <v>1.3032999999999999</v>
-    <v>13.82</v>
-    <v>3.2958000000000001E-2</v>
+    <v>4.1399999999999997</v>
+    <v>9.8729999999999998E-3</v>
     <v>USD</v>
     <v>Dell Technologies Inc. is engaged in designing, developing, manufacturing, marketing, selling, and supporting a wide range of comprehensive and integrated solutions, products, and services. The Company operates through two segments: Infrastructure Solutions Group (ISG) and Client Solutions Group (CSG). Its ISG segment enables the Company’s customer’s digital transformation with solutions that address artificial intelligence (AI), machine learning, data analytics, and multi cloud environments. Its comprehensive storage portfolio includes modern and traditional storage solutions, including all-flash arrays, scale-out file, object platforms, hyper-converged infrastructure, and software-defined storage. Its CSG segment offers branded personal computers (PCs) including notebooks, desktops, and workstations and branded peripherals that include displays, docking stations, keyboards, mice, and webcam and audio devices, as well as third-party software and peripherals.</v>
     <v>97000</v>
@@ -5232,23 +5232,23 @@
     <v>XNYS</v>
     <v>XNYS</v>
     <v>ONE DELL WAY, ROUND ROCK, TX, 78682 US</v>
-    <v>434.99970000000002</v>
+    <v>436</v>
     <v>Computers, Phones &amp; Household Electronics</v>
     <v>Stock</v>
-    <v>46191.626767036716</v>
+    <v>46191.666698008594</v>
     <v>80</v>
     <v>421.71</v>
-    <v>280721499120</v>
+    <v>274447813680</v>
     <v>DELL TECHNOLOGIES INC.</v>
     <v>DELL TECHNOLOGIES INC.</v>
     <v>431.01</v>
-    <v>34.396700000000003</v>
+    <v>33.628</v>
     <v>419.32</v>
-    <v>433.14</v>
+    <v>423.46</v>
     <v>648108000</v>
     <v>DELL</v>
     <v>DELL TECHNOLOGIES INC. (XNYS:DELL)</v>
-    <v>2579019</v>
+    <v>3920614</v>
     <v>11030627</v>
     <v>2013</v>
   </rv>
@@ -5290,8 +5290,8 @@
     <v>124.69</v>
     <v>92.185000000000002</v>
     <v>1.3837999999999999</v>
-    <v>1.75</v>
-    <v>1.7351000000000002E-2</v>
+    <v>2.04</v>
+    <v>2.0226000000000001E-2</v>
     <v>USD</v>
     <v>The Walt Disney Company is a diversified worldwide entertainment company. The Company's segments include Entertainment, Sports and Experiences. The Entertainment segment generally encompasses its non-sports focused global film and episodic content production and distribution activities. The lines of business within the Entertainment segment along with their business activities include Linear Networks, Direct-to-Consumer, and Content Sales/Licensing. The Sports segment encompasses its sports-focused global television and direct-to-consumer (DTC) video streaming content production and distribution activities. The lines of business within the Sports segment include ESPN and Star. The Experiences segment includes Parks and Experiences and Consumer Products. Parks and Experiences consists of Walt Disney World Resort in Florida, Disneyland Resort in California, Disney Cruise Line, and others. Consumer Products includes licensing of its trade names, characters, visual, literary and other IP.</v>
     <v>231000</v>
@@ -5299,24 +5299,24 @@
     <v>XNYS</v>
     <v>XNYS</v>
     <v>500 South Buena Vista Street, BURBANK, CA, 91521-0001 US</v>
-    <v>102.61499999999999</v>
+    <v>102.95</v>
     <v>85</v>
     <v>Media &amp; Publishing</v>
     <v>Stock</v>
-    <v>46191.626755740625</v>
+    <v>46191.666689258593</v>
     <v>86</v>
     <v>100.83</v>
-    <v>178183393710</v>
+    <v>178686981900</v>
     <v>THE WALT DISNEY COMPANY</v>
     <v>THE WALT DISNEY COMPANY</v>
     <v>101.8</v>
-    <v>16.419699999999999</v>
+    <v>16.466100000000001</v>
     <v>100.86</v>
-    <v>102.61</v>
+    <v>102.9</v>
     <v>1736511000</v>
     <v>DIS</v>
     <v>THE WALT DISNEY COMPANY (XNYS:DIS)</v>
-    <v>3869894</v>
+    <v>4995502</v>
     <v>8451643</v>
     <v>2018</v>
   </rv>
@@ -5342,8 +5342,8 @@
     <v>57.55</v>
     <v>31.635000000000002</v>
     <v>0.7419</v>
-    <v>7.4999999999999997E-2</v>
-    <v>1.818E-3</v>
+    <v>0.04</v>
+    <v>9.6969999999999999E-4</v>
     <v>USD</v>
     <v>Dynatrace, Inc. is an artificial intelligence (AI)-powered observability platform. It is advancing observability for digital businesses and transforming the complexity of modern digital ecosystems into business assets. It enables organizations to analyze and automate. Its platform combines broad and deep observability, continuous runtime application security, and advanced AI to support information technology (IT) operations, development, security, and business teams, enabling organizations to optimize cloud and IT operations, accelerate secure software delivery, and improve digital performance. Its platform's solutions include infrastructure observability, application observability, AI observability, digital experience, business analytics, software delivery, threat observability, application security, and log management. Its application security detects, analyses, and remediates runtime application vulnerabilities and attacks in real time.</v>
     <v>5600</v>
@@ -5354,20 +5354,20 @@
     <v>41.715000000000003</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46191.626741260938</v>
+    <v>46191.666724073439</v>
     <v>89</v>
     <v>40.76</v>
-    <v>12045233302</v>
+    <v>12035031653</v>
     <v>DYNATRACE, INC.</v>
     <v>DYNATRACE, INC.</v>
     <v>41.52</v>
-    <v>77.127700000000004</v>
+    <v>77.062299999999993</v>
     <v>41.25</v>
-    <v>41.325000000000003</v>
+    <v>41.29</v>
     <v>291475700</v>
     <v>DT</v>
     <v>DYNATRACE, INC. (XNYS:DT)</v>
-    <v>1373527</v>
+    <v>2007780</v>
     <v>6162103</v>
     <v>2014</v>
   </rv>
@@ -5393,8 +5393,8 @@
     <v>16.489999999999998</v>
     <v>4.6150000000000002</v>
     <v>2.2425000000000002</v>
-    <v>0.38</v>
-    <v>5.6801000000000004E-2</v>
+    <v>0.23499999999999999</v>
+    <v>3.5126999999999999E-2</v>
     <v>USD</v>
     <v>Enovix Corporation is a high-performance battery company. The Company is focused on designing, developing, manufacturing, and commercializing Lithium-ion, or Li-ion, batteries, including silicon-anode architectures, for smartphones, smart eyewear, defense, industrial and emerging edge artificial intelligence (AI) applications. Its silicon-anode battery architecture enables energy density and performance relative to conventional battery cells, particularly in space-constrained devices. It focuses on developing a battery architecture that allows the use of active silicon and no graphite in the battery's anode, which is the negative electrode that stores lithium ions when a battery is charged. Its AI-1 battery platform is architected as a unified silicon-anode platform designed to address the high-performance consumer electronics and defense applications. The AI-1 platform is designed to support AI-enabled smartphones and smart eyewear, as well as other edge-AI devices.</v>
     <v>664</v>
@@ -5405,20 +5405,20 @@
     <v>7.085</v>
     <v>Machinery, Equipment &amp; Components</v>
     <v>Stock</v>
-    <v>46191.626755416408</v>
+    <v>46191.66669060156</v>
     <v>92</v>
     <v>6.73</v>
-    <v>1542344538</v>
+    <v>1510712295</v>
     <v>Enovix Corporation</v>
     <v>Enovix Corporation</v>
     <v>6.94</v>
     <v>0</v>
     <v>6.69</v>
-    <v>7.07</v>
+    <v>6.9249999999999998</v>
     <v>218153400</v>
     <v>ENVX</v>
     <v>Enovix Corporation (XNAS:ENVX)</v>
-    <v>1431300</v>
+    <v>1840432</v>
     <v>7996825</v>
     <v>2020</v>
   </rv>
@@ -5444,8 +5444,8 @@
     <v>435.43</v>
     <v>311.91500000000002</v>
     <v>1.1821999999999999</v>
-    <v>13.28</v>
-    <v>3.2418999999999996E-2</v>
+    <v>11.94</v>
+    <v>2.9148E-2</v>
     <v>USD</v>
     <v>Eaton Corporation plc is an intelligent power management company. Its Electrical Americas segment consists of electrical components, industrial components, power distribution and assemblies, residential products, circuit protection, utility power distribution, wiring devices and others. The Electrical Global segment consists of electrical components, industrial components, power distribution and assemblies, single phase and three phase power quality, and services. The Aerospace segment is a global supplier of aerospace fuel, hydraulics, and pneumatic systems for commercial and military use and filtration systems for industrial applications. The Vehicle segment designs, manufactures, markets, and supplies drivetrain, powertrain systems and critical components. The eMobility segment designs, manufactures, markets, and supplies mechanical, electrical, and electronic components and systems. The Company is also engaged in providing thermal monitoring for critical electrical equipment.</v>
     <v>97000</v>
@@ -5456,20 +5456,20 @@
     <v>424.81400000000002</v>
     <v>Machinery, Equipment &amp; Components</v>
     <v>Stock</v>
-    <v>46191.62672765</v>
+    <v>46191.666728113283</v>
     <v>95</v>
     <v>414.73</v>
-    <v>164219836000</v>
+    <v>163699514000</v>
     <v>EATON CORPORATION PUBLIC LIMITED COMPANY</v>
     <v>EATON CORPORATION PUBLIC LIMITED COMPANY</v>
     <v>419</v>
-    <v>41.345999999999997</v>
+    <v>41.215000000000003</v>
     <v>409.64</v>
-    <v>422.92</v>
+    <v>421.58</v>
     <v>388300000</v>
     <v>ETN</v>
     <v>EATON CORPORATION PUBLIC LIMITED COMPANY (XNYS:ETN)</v>
-    <v>953724</v>
+    <v>1128736</v>
     <v>2475385</v>
     <v>2012</v>
   </rv>
@@ -5507,7 +5507,7 @@
     <v>19.3</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46191.626701446097</v>
+    <v>46191.666690219528</v>
     <v>98</v>
     <v>18.559999999999999</v>
     <v>1462755028</v>
@@ -5520,7 +5520,7 @@
     <v>76563990</v>
     <v>FIVN</v>
     <v>FIVE9, INC. (XNAS:FIVN)</v>
-    <v>1235510</v>
+    <v>1501428</v>
     <v>3285121</v>
     <v>2001</v>
   </rv>
@@ -5546,8 +5546,8 @@
     <v>150.07</v>
     <v>70.12</v>
     <v>1.0947</v>
-    <v>1.095</v>
-    <v>7.5970000000000005E-3</v>
+    <v>0.21</v>
+    <v>1.457E-3</v>
     <v>USD</v>
     <v>Fortinet, Inc. is engaged in cybersecurity, driving the convergence of networking and security. The Company's integrated platform, Fortinet Security Fabric, spans secure networking, unified secure access service edge (SASE), and artificial intelligence (AI)-driven security operations (SecOps). Its products and services include FortiOS, FortiASIC, FortiCloud, FortiAI, FortiEndpoint, and OT Security. The FortiGuard Labs is a cybersecurity threat intelligence and research organization comprised of experienced threat hunters, researchers, analysts, engineers, and data scientists who develop and utilize machine learning and AI technologies. FortiGuard and Other Security Services is an AI-powered security that is integrated as part of the Fortinet Security Fabric to deliver detection and enforcement across the entire attack surface. FortiCare Technical Support Service is a technical support service which provides customers with access to operations and maintenance of Fortinet solutions.</v>
     <v>15311</v>
@@ -5558,20 +5558,20 @@
     <v>146.15199999999999</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46191.626754953126</v>
+    <v>46191.666679745314</v>
     <v>101</v>
     <v>139.79</v>
-    <v>106406190374</v>
+    <v>105757796540</v>
     <v>FORTINET, INC.</v>
     <v>FORTINET, INC.</v>
     <v>143.38999999999999</v>
-    <v>56.11</v>
+    <v>55.768000000000001</v>
     <v>144.13999999999999</v>
-    <v>145.23500000000001</v>
+    <v>144.35</v>
     <v>732648400</v>
     <v>FTNT</v>
     <v>FORTINET, INC. (XNAS:FTNT)</v>
-    <v>1686613</v>
+    <v>1974055</v>
     <v>6306446</v>
     <v>2000</v>
   </rv>
@@ -5597,8 +5597,8 @@
     <v>404.47</v>
     <v>163.33000000000001</v>
     <v>1.244</v>
-    <v>-0.62</v>
-    <v>-1.712E-3</v>
+    <v>2.2000000000000002</v>
+    <v>6.0760000000000007E-3</v>
     <v>USD</v>
     <v>Alphabet Inc. is a holding company. The Company's segments include Google Services, Google Cloud, and Other Bets. The Google Services segment includes products and services such as ads, Android, Chrome, devices, Google Maps, Google Play, Search, and YouTube. The Google Cloud segment includes infrastructure and platform services, collaboration tools, and other services for enterprise customers. Its Other Bets segment is engaged in the sale of healthcare-related services and Internet services. Its Google Cloud provides enterprise-ready cloud services, including Google Cloud Platform and Google Workspace. Google Cloud Platform provides access to solutions such as artificial intelligence (AI) offerings, including its AI infrastructure, Vertex AI platform, and Gemini for Google Cloud; cybersecurity, and data and analytics. Google Workspace includes cloud-based communication and collaboration tools for enterprises, such as Calendar, Gmail, Docs, Drive, and Meet.</v>
     <v>194668</v>
@@ -5609,20 +5609,20 @@
     <v>365.95</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46191.626777603909</v>
+    <v>46191.666716735941</v>
     <v>104</v>
     <v>356.60820000000001</v>
-    <v>4400859948800</v>
+    <v>4435192208000</v>
     <v>ALPHABET INC.</v>
     <v>ALPHABET INC.</v>
     <v>364.56</v>
-    <v>27.6067</v>
+    <v>27.822099999999999</v>
     <v>362.1</v>
-    <v>361.48</v>
+    <v>364.3</v>
     <v>12174560000</v>
     <v>GOOG</v>
     <v>ALPHABET INC. (XNAS:GOOG)</v>
-    <v>7795863</v>
+    <v>9162857</v>
     <v>22124039</v>
     <v>2015</v>
   </rv>
@@ -5648,8 +5648,8 @@
     <v>153.85990000000001</v>
     <v>63.515000000000001</v>
     <v>2.3100999999999998</v>
-    <v>3.5</v>
-    <v>3.3270000000000001E-2</v>
+    <v>0.61499999999999999</v>
+    <v>5.8460000000000005E-3</v>
     <v>USD</v>
     <v>Robinhood Markets, Inc. is focused on providing financial services offering retail brokerage, crypto, advisory, digital banking services, and private markets access to investors. Its offerings include Brokerage, Robinhood Crypto, Custody, Robinhood Wallet, Robinhood Gold, and Robinhood Gold Card. Brokerage services include investing, options trading, fractional trading, recurring investment, access to investing on margin, fully paid securities lending, cash sweep, instant withdrawals, Robinhood retirement, 24-hour market, joint investing accounts, and event contracts. It also offers a variety of ways for its customers to grow their financial knowledge, including Robinhood Learn, In-App Education, Newsfeeds, Sherwood Snacks, and Crypto Learn and Earn. It also operates regulated crypto platforms including Bitbuy and Coinsquare. Its self-clearing system, order routing system, data platform, and other back-end infrastructure allow its customers to focus on investing, saving and spending.</v>
     <v>2900</v>
@@ -5657,23 +5657,23 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>85 Willow Road, MENLO PARK, CA, 94025 US</v>
-    <v>108.93</v>
+    <v>109.08</v>
     <v>Financial Technology (Fintech) &amp; Infrastructure</v>
     <v>Stock</v>
-    <v>46191.626773865624</v>
+    <v>46191.666712904691</v>
     <v>107</v>
     <v>103.46</v>
-    <v>97884904370</v>
+    <v>95286947156</v>
     <v>ROBINHOOD MARKETS, INC.</v>
     <v>ROBINHOOD MARKETS, INC.</v>
     <v>107.75</v>
-    <v>60.469499999999996</v>
+    <v>58.864600000000003</v>
     <v>105.2</v>
-    <v>108.7</v>
+    <v>105.815</v>
     <v>900505100</v>
     <v>HOOD</v>
     <v>ROBINHOOD MARKETS, INC. (XNAS:HOOD)</v>
-    <v>14669737</v>
+    <v>19287151</v>
     <v>30962459</v>
     <v>2013</v>
   </rv>
@@ -5715,8 +5715,8 @@
     <v>332.46</v>
     <v>212.34</v>
     <v>0.68720000000000003</v>
-    <v>-14.58</v>
-    <v>-5.5574999999999999E-2</v>
+    <v>-14.904999999999999</v>
+    <v>-5.6813000000000002E-2</v>
     <v>USD</v>
     <v>International Business Machines Corporation is a provider of global hybrid cloud and artificial intelligence (AI) and consulting expertise. The Company’s segments include Software, Consulting, Infrastructure and Financing. The Software segment includes hybrid cloud and AI platforms, which allow clients to realize their digital and AI transformations across the applications, data, and environments in which they operate. The Consulting segment focuses on integrating skills on strategy, experience, technology and operations by domain and industry. The Infrastructure segment is focused on the hybrid cloud infrastructure market, providing on-premises and cloud-based server and storage solutions. In addition, it offers a portfolio of life-cycle services for hybrid cloud infrastructure deployment. The Financing segment provides client and commercial financing, facilitating its clients’ acquisition of hardware, software and services. It helps clients in more than 175 countries.</v>
     <v>286800</v>
@@ -5728,20 +5728,20 @@
     <v>112</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46191.626774652344</v>
+    <v>46191.666704941403</v>
     <v>113</v>
     <v>243.68</v>
-    <v>232875380781</v>
+    <v>232569918058</v>
     <v>INTERNATIONAL BUSINESS MACHINES CORPORATION</v>
     <v>INTERNATIONAL BUSINESS MACHINES CORPORATION</v>
     <v>250.55</v>
-    <v>19.8279</v>
+    <v>19.8019</v>
     <v>262.35000000000002</v>
-    <v>247.77</v>
+    <v>247.44499999999999</v>
     <v>939885300</v>
     <v>IBM</v>
     <v>INTERNATIONAL BUSINESS MACHINES CORPORATION (XNYS:IBM)</v>
-    <v>6155127</v>
+    <v>7171116</v>
     <v>11191078</v>
     <v>1911</v>
   </rv>
@@ -5767,8 +5767,8 @@
     <v>125.14</v>
     <v>34.2301</v>
     <v>2.8418999999999999</v>
-    <v>-7.29</v>
-    <v>-7.1108000000000005E-2</v>
+    <v>-7.8700999999999999</v>
+    <v>-7.6766000000000001E-2</v>
     <v>USD</v>
     <v>Innodata Inc. is a global data engineering company. It provides a range of transferable solutions, platforms, and services for generative artificial intelligence (AI)/AI builders and adopters. Its Digital Data Solutions segment provides AI data preparation services, collecting or creating training data, annotating training data, and training AI algorithms for its customers, and AI model deployment and integration. It also provides a range of data engineering support services. Its Synodex segment provides an industry platform that transforms medical records into useable digital data organized in accordance with its proprietary data models or customer data models. Its Agility segment provides an industry platform that provides marketing communications and public relations professionals with the ability to target and distribute content to journalists and social media influencers worldwide and to monitor and analyze global news channels (print, Web, radio and TV) and social media channels.</v>
     <v>10020</v>
@@ -5779,20 +5779,20 @@
     <v>104.84</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46191.626714617967</v>
+    <v>46191.666686469529</v>
     <v>116</v>
     <v>91.27</v>
     <v>1490374656</v>
     <v>INNODATA INC.</v>
     <v>INNODATA INC.</v>
     <v>104.22</v>
-    <v>85.684700000000007</v>
+    <v>85.162800000000004</v>
     <v>102.52</v>
-    <v>95.23</v>
+    <v>94.649900000000002</v>
     <v>32655360</v>
     <v>INOD</v>
     <v>INNODATA INC. (XNAS:INOD)</v>
-    <v>664431</v>
+    <v>827859</v>
     <v>1852434</v>
     <v>1988</v>
   </rv>
@@ -5818,8 +5818,8 @@
     <v>135.47999999999999</v>
     <v>18.965</v>
     <v>2.2027000000000001</v>
-    <v>9.4849999999999994</v>
-    <v>7.8324000000000005E-2</v>
+    <v>11.994999999999999</v>
+    <v>9.9049999999999999E-2</v>
     <v>USD</v>
     <v>Intel Corporation is a global designer and manufacturer of semiconductor products. The Company's segments include Intel Products, Intel Foundry, and All Other. Its Intel Products comprise Client Computing Group (CCG) and Data Center and AI (DCAI). CCG delivers platforms and processors that power PCs and edge devices, enabling enhanced performance, connectivity and user experience for consumer and commercial markets with capabilities that also support retail, industrial robotics and AI ecosystems at the edge. DCAI delivers workload-optimized solutions based upon its x86 architecture for data centers, including CPUs, AI accelerators, NICs, IPUs and custom ASICs, enabling performance and scalability for cloud, enterprise, telecommunication and HPC environments. The Intel Foundry segment comprises technology development, manufacturing and foundry services, developing new semiconductor process technologies and advanced packaging technologies. All Other segments include Mobileye and Other.</v>
     <v>83200</v>
@@ -5830,20 +5830,20 @@
     <v>135.47999999999999</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46191.626789628906</v>
+    <v>46191.666731272657</v>
     <v>119</v>
     <v>127.9</v>
-    <v>656320210000</v>
+    <v>668935470000</v>
     <v>INTEL CORPORATION</v>
     <v>INTEL CORPORATION</v>
     <v>132</v>
     <v>0</v>
     <v>121.1</v>
-    <v>130.58500000000001</v>
+    <v>133.095</v>
     <v>5026000000</v>
     <v>INTC</v>
     <v>INTEL CORPORATION (XNAS:INTC)</v>
-    <v>84543699</v>
+    <v>105262624</v>
     <v>128809703</v>
     <v>1989</v>
   </rv>
@@ -5869,8 +5869,8 @@
     <v>84.64</v>
     <v>25.89</v>
     <v>3.2385999999999999</v>
-    <v>0.69</v>
-    <v>1.2617E-2</v>
+    <v>4.4999999999999998E-2</v>
+    <v>8.2280000000000005E-4</v>
     <v>USD</v>
     <v>IonQ, Inc. is engaged in the quantum computing and networking industry, delivering high-performance systems capable of solving complex commercial and research use cases. Its generation quantum computers, IonQ Forte and IonQ Forte Enterprise, are cutting-edge systems, boasting 36 algorithmic qubits. It sells specialized quantum computing and networking hardware together with related maintenance and support. It also sells access to several quantum computers of various qubit capacities and is in the process of researching and developing technologies for quantum computers with increasing computational capabilities. It makes access to its quantum computers available via three cloud platforms, Amazon Web Services' (AWS) Amazon Braket, Microsoft's Azure Quantum and Google's Cloud Marketplace, and also to select customers via its own cloud service. Its product portfolio also includes quantum key distribution (QKD) systems, quantum random number generators (QRNGs), and single-photon detectors.</v>
     <v>1132</v>
@@ -5881,20 +5881,20 @@
     <v>56.54</v>
     <v>Computers, Phones &amp; Household Electronics</v>
     <v>Stock</v>
-    <v>46191.626764282031</v>
+    <v>46191.666716758591</v>
     <v>122</v>
     <v>52.9206</v>
-    <v>20671692600</v>
+    <v>20430933450</v>
     <v>IONQ, INC.</v>
     <v>IONQ, INC.</v>
     <v>55.8</v>
-    <v>945.05119999999999</v>
+    <v>934.0444</v>
     <v>54.69</v>
-    <v>55.38</v>
+    <v>54.734999999999999</v>
     <v>373270000</v>
     <v>IONQ</v>
     <v>IONQ, INC. (XNYS:IONQ)</v>
-    <v>7627739</v>
+    <v>9476644</v>
     <v>30137394</v>
     <v>2020</v>
   </rv>
@@ -5920,8 +5920,8 @@
     <v>76.87</v>
     <v>9.6334</v>
     <v>4.2389000000000001</v>
-    <v>2.38</v>
-    <v>4.0957E-2</v>
+    <v>2.395</v>
+    <v>4.1215000000000002E-2</v>
     <v>USD</v>
     <v>IREN Limited is an Australia-based company, which owns and operates data centers powered by 100% renewable energy. Its facilities are optimized for Bitcoin mining, artificial intelligence (AI) cloud services, and other power-dense compute. Its data center mining facilities are in Canal Flats, Mackenzie, Prince George and Childress. Bitcoin Mining provides security to the Bitcoin network. Al Cloud Services provides cloud compute to Al customers, approximately 1,896 NVIDIA H100 and H200 GPUs. Its Canal Flats facility is in the Canadian Rockies, 100 kilometers (km) from Cranbrook regional airport and 500km east of Vancouver. Its facility is in Prince George, the city in northern British Columbia, located 500 km north of Vancouver. Its facility is located in Childress County, Texas, over 250 miles northwest of Dallas and in close proximity to multiple wind and solar generating facilities in the region. Its Childress operations comprise 200 Mega Watt of operating data centers.</v>
     <v>257</v>
@@ -5932,20 +5932,20 @@
     <v>61.51</v>
     <v>Financial Technology (Fintech) &amp; Infrastructure</v>
     <v>Stock</v>
-    <v>46191.626770358591</v>
+    <v>46191.66673004609</v>
     <v>125</v>
     <v>58.2</v>
-    <v>21617837563</v>
+    <v>21623198243</v>
     <v>IREN LIMITED</v>
     <v>IREN LIMITED</v>
     <v>61.32</v>
-    <v>131.87270000000001</v>
+    <v>131.90539999999999</v>
     <v>58.11</v>
-    <v>60.49</v>
+    <v>60.505000000000003</v>
     <v>357378700</v>
     <v>IREN</v>
     <v>IREN LIMITED (XNAS:IREN)</v>
-    <v>12626595</v>
+    <v>17465044</v>
     <v>48257123</v>
     <v>2018</v>
   </rv>
@@ -5971,25 +5971,25 @@
     <v>297.91000000000003</v>
     <v>206.81</v>
     <v>0.99929999999999997</v>
-    <v>4.1749999999999998</v>
-    <v>1.4402999999999999E-2</v>
+    <v>3.98</v>
+    <v>1.3729999999999999E-2</v>
     <v>USD</v>
     <v>NYSE Arca</v>
     <v>ARCX</v>
     <v>1.9E-3</v>
     <v>295.11</v>
     <v>ETF</v>
-    <v>46191.626776064062</v>
+    <v>46191.666715601561</v>
     <v>128</v>
     <v>291.42950000000002</v>
     <v>80933362748.720001</v>
     <v>iShares:Russ 2000 ETF</v>
     <v>294.73</v>
     <v>289.88</v>
-    <v>294.05500000000001</v>
+    <v>293.86</v>
     <v>IWM</v>
     <v>iShares:Russ 2000 ETF (ARCX:IWM)</v>
-    <v>8975964</v>
+    <v>18315578</v>
     <v>28848249</v>
   </rv>
   <rv s="2">
@@ -6014,8 +6014,8 @@
     <v>267.16989999999998</v>
     <v>83.224000000000004</v>
     <v>1.4393</v>
-    <v>15.48</v>
-    <v>6.4842999999999998E-2</v>
+    <v>20.34</v>
+    <v>8.5200999999999999E-2</v>
     <v>USD</v>
     <v>KLA Corporation (KLA) develops industry equipment and services. The Company provides advanced process control and process-enabling solutions for manufacturing wafers and reticles, integrated circuits, packaging, and printed circuit boards. It operates through three segments, which include Semiconductor Process Control, Specialty Semiconductor Process, and PCB and Component Inspection. The Semiconductor Process Control segment offers a portfolio of inspection, metrology and data analytics products, and related services. The Specialty Semiconductor Process segment develops and sells advanced vacuum deposition and etching process tools. The PCB and Component Inspection segment enables electronic device manufacturers to inspect, test and measure PCBs, flat panel displays, and integrated circuits (ICs) to verify their quality, pattern the desired electronic circuitry on the relevant substrate and perform three-dimensional shaping of metalized circuits on multiple surfaces.</v>
     <v>15000</v>
@@ -6023,23 +6023,23 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>One Technology Drive, MILPITAS, CA, 95035 US</v>
-    <v>258.59100000000001</v>
+    <v>259.36</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46191.626778541409</v>
+    <v>46191.666717291409</v>
     <v>131</v>
     <v>250.5</v>
-    <v>332068167750</v>
+    <v>338416664250</v>
     <v>KLA CORPORATION</v>
     <v>KLA CORPORATION</v>
     <v>252</v>
-    <v>71.973399999999998</v>
+    <v>73.349400000000003</v>
     <v>238.73</v>
-    <v>254.21</v>
+    <v>259.07</v>
     <v>1306275000</v>
     <v>KLAC</v>
     <v>KLA CORPORATION (XNAS:KLAC)</v>
-    <v>3589591</v>
+    <v>5477367</v>
     <v>11447258</v>
     <v>1975</v>
   </rv>
@@ -6065,8 +6065,8 @@
     <v>84.04</v>
     <v>65.353800000000007</v>
     <v>0.3503</v>
-    <v>-1.1599999999999999</v>
-    <v>-1.4513E-2</v>
+    <v>-1.0149999999999999</v>
+    <v>-1.2699E-2</v>
     <v>USD</v>
     <v>The Coca-Cola Company is a beverage company. The Company's segments include Europe, Middle East and Africa (EMEA); Latin America; North America; Asia Pacific, and Bottling Investments. It sells multiple brands across several beverage categories worldwide. Its portfolio of sparkling soft drink brands includes Coca-Cola, Sprite and Fanta. Its water, sports, coffee and tea brands include Dasani, smartwater, vitaminwater, Topo Chico, BODYARMOR, Powerade, Costa, Georgia, Fuze Tea, Gold Peak and Ayataka. Its juice, value-added dairy and plant-based beverage brands include Minute Maid, Simply, innocent, Del Valle, fairlife and Santa Clara. It operates in two lines of business: concentrate operations and finished product operations. Its concentrate operations sell beverage concentrates, syrups, including fountain syrups, and certain finished beverages to authorized bottling operations. Its finished product operations sell sparkling soft drinks and a variety of other finished beverages.</v>
     <v>65900</v>
@@ -6077,20 +6077,20 @@
     <v>80.06</v>
     <v>Beverages</v>
     <v>Stock</v>
-    <v>46191.626780450781</v>
+    <v>46191.66671586797</v>
     <v>134</v>
     <v>78.760000000000005</v>
-    <v>338906507140</v>
+    <v>339530367030</v>
     <v>THE COCA-COLA COMPANY</v>
     <v>THE COCA-COLA COMPANY</v>
     <v>80.06</v>
-    <v>24.797699999999999</v>
+    <v>24.843399999999999</v>
     <v>79.930000000000007</v>
-    <v>78.77</v>
+    <v>78.915000000000006</v>
     <v>4302482000</v>
     <v>KO</v>
     <v>THE COCA-COLA COMPANY (XNYS:KO)</v>
-    <v>7469498</v>
+    <v>9006346</v>
     <v>16167413</v>
     <v>1919</v>
   </rv>
@@ -6116,8 +6116,8 @@
     <v>18.940000000000001</v>
     <v>2.75</v>
     <v>1.3716999999999999</v>
-    <v>0.31</v>
-    <v>2.1232999999999998E-2</v>
+    <v>0.23</v>
+    <v>1.5753E-2</v>
     <v>USD</v>
     <v>LightPath Technologies, Inc. is a global, vertically integrated provider of optics, photonics and infrared solutions for the industrial, commercial, defense, telecommunications, and medical industries. The Company designs and manufactures optical and infrared components including molded glass aspheric lenses and assemblies, custom molded glass freeform lenses, infrared lenses and thermal imaging assemblies, fused fiber collimators, and BlackDiamond (BD6) chalcogenide-based glass lenses. It also offers custom optical assemblies, including full engineering design support. Its business is organized into four product groups: infrared components, visible components, assemblies and modules, and engineering services. Its infrared product group comprises both molded and turned infrared lenses and assemblies using a variety of infrared glass materials. Its assemblies and modules product group is comprised of other value-added products, including both infrared and visible components.</v>
     <v>345</v>
@@ -6125,23 +6125,23 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>2603 CHALLENGER TECH CT, STE 100, ORLANDO, FL, 32826-2716 US</v>
-    <v>15.18</v>
+    <v>15.19</v>
     <v>Office Equipment</v>
     <v>Stock</v>
-    <v>46191.62678247656</v>
+    <v>46191.66671064766</v>
     <v>137</v>
     <v>14.15</v>
-    <v>989439677</v>
+    <v>984130812</v>
     <v>LIGHTPATH TECHNOLOGIES, INC.</v>
     <v>LIGHTPATH TECHNOLOGIES, INC.</v>
     <v>14.72</v>
     <v>0</v>
     <v>14.6</v>
-    <v>14.91</v>
+    <v>14.83</v>
     <v>66360810</v>
     <v>LPTH</v>
     <v>LIGHTPATH TECHNOLOGIES, INC. (XNAS:LPTH)</v>
-    <v>901406</v>
+    <v>1510876</v>
     <v>4295141</v>
     <v>1992</v>
   </rv>
@@ -6167,8 +6167,8 @@
     <v>18.709</v>
     <v>1.19</v>
     <v>2.4226000000000001</v>
-    <v>0.25</v>
-    <v>2.6939999999999999E-2</v>
+    <v>4.4999999999999998E-2</v>
+    <v>4.849E-3</v>
     <v>USD</v>
     <v>Lightwave Logic, Inc. is a technology platform company leveraging its proprietary engineered electro-optic (EO) polymers known as Perkinamine, to transmit data at higher speeds with less power in a small form factor. The Company’s organic polymers allow it to create next-generation photonic EO devices that convert data from electrical signals into light/optical signals for applications in telecommunications, and for data transmission potentially used to support generative Artificial Intelligence. It designs its own proprietary materials for electro-optical modulation devices. Electro-optical modulators convert data from electric signals into optical signals that can then be transmitted over high-speed fiber-optic cables. It is focused on testing and demonstrating the manufacturability and reliability of its devices. In polymer photonics, polymer devices such as modulators, waveguides, and multiplexers can be fabricated on to a silicon platform.</v>
     <v>34</v>
@@ -6179,20 +6179,20 @@
     <v>9.99</v>
     <v>Electronic Equipment &amp; Parts</v>
     <v>Stock</v>
-    <v>46191.62675320547</v>
+    <v>46191.666734247658</v>
     <v>140</v>
-    <v>9.3401999999999994</v>
-    <v>1468378588</v>
+    <v>9.2799999999999994</v>
+    <v>1436792270</v>
     <v>LIGHTWAVE LOGIC, INC.</v>
     <v>LIGHTWAVE LOGIC, INC.</v>
     <v>9.6999999999999993</v>
     <v>0</v>
     <v>9.2799999999999994</v>
-    <v>9.5299999999999994</v>
+    <v>9.3249999999999993</v>
     <v>154079600</v>
     <v>LWLG</v>
     <v>LIGHTWAVE LOGIC, INC. (XNAS:LWLG)</v>
-    <v>1030799</v>
+    <v>1451407</v>
     <v>6694352</v>
     <v>1997</v>
   </rv>
@@ -6234,8 +6234,8 @@
     <v>341.75</v>
     <v>271.85000000000002</v>
     <v>0.4073</v>
-    <v>-2.8683000000000001</v>
-    <v>-1.0105999999999999E-2</v>
+    <v>-2.79</v>
+    <v>-9.8300000000000002E-3</v>
     <v>USD</v>
     <v>McDonald's Corporation is a global foodservice retailer. Its segment includes U.S., International Operated Markets, and International Developmental Licensed Markets &amp; Corporate. The U.S. segment is its largest market and is 95% franchised. The International Operated Markets segment comprises markets or countries in which it operates and franchises restaurants, including Australia, Canada, France, Germany, Italy, Poland, Spain, and the United Kingdom. This segment is 89% franchised. The International Developmental Licensed Markets &amp; Corporate segment comprises development licensee and affiliate markets, including equity method investments in China and Japan. This segment is 99% franchised. Its menu features hamburgers and cheeseburgers, the Big Mac, the Quarter Pounder with Cheese, the Filet-O-Fish, and several chicken sandwiches, such as the McChicken and McCrispy as well as Chicken McNuggets, Fries, shakes, sundaes, cookies, soft drinks, coffee, and other beverages.</v>
     <v>150000</v>
@@ -6247,20 +6247,20 @@
     <v>145</v>
     <v>Hotels &amp; Entertainment Services</v>
     <v>Stock</v>
-    <v>46191.626764964843</v>
+    <v>46191.666710995312</v>
     <v>146</v>
     <v>279.65010000000001</v>
-    <v>199617840465</v>
+    <v>199673473076</v>
     <v>MCDONALD'S CORPORATION</v>
     <v>MCDONALD'S CORPORATION</v>
     <v>284.49</v>
-    <v>23.1585</v>
+    <v>23.164899999999999</v>
     <v>283.82</v>
-    <v>280.95170000000002</v>
+    <v>281.02999999999997</v>
     <v>710505900</v>
     <v>MCD</v>
     <v>MCDONALD'S CORPORATION (XNYS:MCD)</v>
-    <v>1814082</v>
+    <v>2093257</v>
     <v>4190604</v>
     <v>1964</v>
   </rv>
@@ -6306,8 +6306,8 @@
     <v>444.72</v>
     <v>196</v>
     <v>1.5442</v>
-    <v>-14.5</v>
-    <v>-4.3324000000000001E-2</v>
+    <v>-12.17</v>
+    <v>-3.6361999999999998E-2</v>
     <v>USD</v>
     <v>MongoDB, Inc. is a developer data platform company. Its developer data platform is a globally distributed operational database integrated with a set of data services that allow development teams to address the growing variety of application requirements. Its customers can implement its developer data platform as a managed service offering, or they can choose a self-managed option. Its MongoDB Atlas is its managed multi-cloud database-as-a-service (DBaaS) offering that includes an integrated set of databases and related services. Atlas Vector Search allows the integration of an operational database and vector search in a unified, fully managed platform. MongoDB Enterprise Advanced is its proprietary self-managed commercial offering for enterprise customers that can run in the cloud, on-premises or in a hybrid environment. It also provides professional services for its customers.</v>
     <v>5636</v>
@@ -6319,20 +6319,20 @@
     <v>152</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46191.626707522657</v>
+    <v>46191.666695207816</v>
     <v>153</v>
     <v>314.55799999999999</v>
-    <v>25753499666</v>
+    <v>25940906063</v>
     <v>MONGODB, INC.</v>
     <v>MONGODB, INC.</v>
     <v>331.71</v>
     <v>0</v>
     <v>334.69</v>
-    <v>320.19</v>
+    <v>322.52</v>
     <v>80431930</v>
     <v>MDB</v>
     <v>MONGODB, INC. (XNAS:MDB)</v>
-    <v>551369</v>
+    <v>815449</v>
     <v>2633834</v>
     <v>2007</v>
   </rv>
@@ -6358,8 +6358,8 @@
     <v>796.25</v>
     <v>520.26</v>
     <v>1.2490000000000001</v>
-    <v>4.99</v>
-    <v>8.7919999999999995E-3</v>
+    <v>9.6750000000000007</v>
+    <v>1.7045999999999999E-2</v>
     <v>USD</v>
     <v>Meta Platforms, Inc. is building human connections, powered by artificial intelligence and immersive technologies. The Company's products enable people to connect and share with friends and family through mobile devices, personal computers, virtual reality (VR) and mixed reality (MR) headsets, augmented reality (AR), and wearables. It also helps people discover and learn about what is going on in the world around them, enabling people to share their experiences, ideas, photos, videos, and other content with audiences ranging from their closest family members and friends to the public at large. The Company's segments include Family of Apps (FoA) and Reality Labs (RL). FoA segment includes Facebook, Instagram, Messenger, WhatsApp and Threads. RL segment includes its virtual, augmented, and mixed reality related consumer hardware, software and content. Its product offerings in VR include its Meta Quest devices, as well as software and content available through the Meta Horizon Store.</v>
     <v>77986</v>
@@ -6367,23 +6367,23 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>1 Meta Way, MENLO PARK, CA, 94025 US</v>
-    <v>576.6</v>
+    <v>578.69000000000005</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46191.626765323439</v>
+    <v>46191.666741435154</v>
     <v>156</v>
     <v>563.1</v>
-    <v>1453424857110</v>
+    <v>1465317368865</v>
     <v>META PLATFORMS, INC.</v>
     <v>META PLATFORMS, INC.</v>
     <v>572.86</v>
-    <v>17.366900000000001</v>
+    <v>17.509</v>
     <v>567.58000000000004</v>
-    <v>572.57000000000005</v>
+    <v>577.255</v>
     <v>2538423000</v>
     <v>META</v>
     <v>META PLATFORMS, INC. (XNAS:META)</v>
-    <v>7649280</v>
+    <v>9513579</v>
     <v>17180355</v>
     <v>2004</v>
   </rv>
@@ -6406,11 +6406,11 @@
     <v>3</v>
     <v>Finance</v>
     <v>4</v>
-    <v>325.92</v>
+    <v>326.20999999999998</v>
     <v>61.44</v>
     <v>2.1627000000000001</v>
-    <v>35.14</v>
-    <v>0.121365</v>
+    <v>34.75</v>
+    <v>0.120018</v>
     <v>USD</v>
     <v>Marvell Technology, Inc. together with its consolidated subsidiaries, is a supplier of data infrastructure semiconductor solutions, spanning the data center core to network edge. It is engaged in the design, development and sale of integrated circuits. Its product offerings include custom application-specific integrated circuits (ASICs), interconnects, ethernet solutions, fiber channel adapters, processors and storage controllers. In addition, it is also developing Ultra Accelerator LinkTM (UALinkTM) switches and ethernet for scale-up networking (ESUN) switches for the emerging scale-out artificial intelligence market. Its solutions integrate multiple analogs, mixed-signal and digital intellectual property components incorporating hardware, firmware and software technologies and its system knowledge to provide its customers with integrated solutions for their end products. It designs and manufactures photonic integrated circuits for ultra-high-bandwidth and low-power applications.</v>
     <v>7480</v>
@@ -6418,23 +6418,23 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>1000 N. West Street, Suite 1200, WILMINGTON, DE, 19801 US</v>
-    <v>325.92</v>
+    <v>326.20999999999998</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46191.626778298436</v>
+    <v>46191.666721503905</v>
     <v>159</v>
     <v>302.36</v>
-    <v>284030064000</v>
+    <v>283688892000</v>
     <v>MARVELL TECHNOLOGY, INC.</v>
     <v>MARVELL TECHNOLOGY, INC.</v>
     <v>305.63</v>
-    <v>111.21080000000001</v>
+    <v>111.0772</v>
     <v>289.54000000000002</v>
-    <v>324.68</v>
+    <v>324.29000000000002</v>
     <v>874800000</v>
     <v>MRVL</v>
     <v>MARVELL TECHNOLOGY, INC. (XNAS:MRVL)</v>
-    <v>27655856</v>
+    <v>35795838</v>
     <v>53318264</v>
     <v>2020</v>
   </rv>
@@ -6476,8 +6476,8 @@
     <v>555.45000000000005</v>
     <v>356.28</v>
     <v>1.1368</v>
-    <v>-2.2999999999999998</v>
-    <v>-6.0699999999999999E-3</v>
+    <v>-0.9</v>
+    <v>-2.3749999999999999E-3</v>
     <v>USD</v>
     <v>Microsoft Corporation is a technology company. The Company develops and supports software, services, devices, and solutions. The Company’s segments include Productivity and Business Processes, Intelligent Cloud, and More Personal Computing. The Productivity and Business Processes segment consists of products and services in its portfolio of productivity, communication, and information services. This segment primarily comprises: Office Commercial, Office Consumer, LinkedIn, and Dynamics business solutions. The Intelligent Cloud segment consists of server products and cloud services, including Azure and other cloud services, SQL Server, Windows Server, Visual Studio, System Center, and related Client Access Licenses (CALs), and Nuance and GitHub; and Enterprise Services, including enterprise support services, industry solutions and Nuance professional services. The More Personal Computing segment primarily comprises Windows, Devices, Gaming, and search and news advertising.</v>
     <v>228000</v>
@@ -6489,20 +6489,20 @@
     <v>164</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46191.626791376562</v>
+    <v>46191.666740439061</v>
     <v>165</v>
     <v>373.28</v>
-    <v>2797622905350</v>
+    <v>2808022714350</v>
     <v>MICROSOFT CORPORATION</v>
     <v>MICROSOFT CORPORATION</v>
     <v>378.1</v>
-    <v>22.431100000000001</v>
+    <v>22.514500000000002</v>
     <v>378.91</v>
-    <v>376.61</v>
+    <v>378.01</v>
     <v>7428435000</v>
     <v>MSFT</v>
     <v>MICROSOFT CORPORATION (XNAS:MSFT)</v>
-    <v>20441657</v>
+    <v>24695489</v>
     <v>36808904</v>
     <v>1993</v>
   </rv>
@@ -6528,8 +6528,8 @@
     <v>457.22</v>
     <v>104.16500000000001</v>
     <v>3.5234000000000001</v>
-    <v>-2.2599999999999998</v>
-    <v>-1.9389E-2</v>
+    <v>-6.05</v>
+    <v>-5.1905E-2</v>
     <v>USD</v>
     <v>Strategy Inc. is a bitcoin treasury and business intelligence company. The Company provides cloud-native, artificial intelligence (AI)-powered enterprise analytics software to thousands of global customers. Its Software Business segment is engaged in the design, development, marketing, and sales of enterprise analytics software platform through cloud subscriptions and licensing arrangements and related services. Its Strategy ONE platform provides access to AI-powered workflows, unlimited data sources, cloud-native technologies, and performance to speed up time from data to action. Strategy One delivers visualization, reporting, and embedded analytics capabilities across retail, banking, technology, manufacturing, insurance, consulting, healthcare, public sector, and others. Its Strategy Mosaic is a universal intelligence layer that provides enterprises with consistent definitions and governance across data sources, regardless of where that data resides or which tools access it.</v>
     <v>1511</v>
@@ -6540,20 +6540,20 @@
     <v>117.75</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46191.626765647656</v>
+    <v>46191.666729652345</v>
     <v>168</v>
-    <v>111.7</v>
-    <v>40942019970</v>
+    <v>110.05</v>
+    <v>39584449929</v>
     <v>STRATEGY INC</v>
     <v>STRATEGY INC</v>
     <v>117.5</v>
     <v>0</v>
     <v>116.56</v>
-    <v>114.3</v>
+    <v>110.51</v>
     <v>358197900</v>
     <v>MSTR</v>
     <v>STRATEGY INC (XNAS:MSTR)</v>
-    <v>9354058</v>
+    <v>13564399</v>
     <v>18246691</v>
     <v>1989</v>
   </rv>
@@ -6576,11 +6576,11 @@
     <v>3</v>
     <v>Finance</v>
     <v>4</v>
-    <v>1130.71</v>
+    <v>1133.2399</v>
     <v>103.38</v>
     <v>2.1505999999999998</v>
-    <v>86.745000000000005</v>
-    <v>8.3154000000000006E-2</v>
+    <v>82.555000000000007</v>
+    <v>7.9136999999999999E-2</v>
     <v>USD</v>
     <v>Micron Technology, Inc. provides memory and storage solutions. The Company delivers a portfolio of high-performance dynamic random-access memory (DRAM), NAND, and NOR memory and storage products through its Micron and Crucial brands. The Company's products enable advancing in artificial intelligence (AI) and compute-intensive applications. Its segments include Cloud Memory Business Unit (CMBU), Core Data Center Business Unit (CDBU), Mobile and Client Business Unit (MCBU) and Automotive and Embedded Business Unit (AEBU). CMBU is focused on memory solutions for large hyperscale cloud customers, and high bandwidth memory (HBM) for all data center customers. CDBU is focused on memory solutions for mid-tier cloud, enterprise, and OEM data center customers and storage solutions for all data center customers. MCBU is focused on memory and storage solutions for mobile and client segments. AEBU is focused on memory and storage solutions for the automotive, industrial, and consumer segments.</v>
     <v>53000</v>
@@ -6588,23 +6588,23 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>8000 S Federal Way, Po Box 6, BOISE, ID, 83716-9632 US</v>
-    <v>1130.71</v>
+    <v>1133.2399</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46191.626774652344</v>
+    <v>46191.666728448436</v>
     <v>171</v>
     <v>1092.7935</v>
-    <v>1274266117290</v>
+    <v>1269540911829</v>
     <v>MICRON TECHNOLOGY, INC.</v>
     <v>MICRON TECHNOLOGY, INC.</v>
     <v>1110</v>
-    <v>53.3459</v>
+    <v>53.148099999999999</v>
     <v>1043.19</v>
-    <v>1129.9349999999999</v>
+    <v>1125.7449999999999</v>
     <v>1127734000</v>
     <v>MU</v>
     <v>MICRON TECHNOLOGY, INC. (XNAS:MU)</v>
-    <v>20228699</v>
+    <v>25288839</v>
     <v>53625150</v>
     <v>1984</v>
   </rv>
@@ -6630,8 +6630,8 @@
     <v>276.815</v>
     <v>158.83000000000001</v>
     <v>1.6840999999999999</v>
-    <v>-3.3574000000000002</v>
-    <v>-1.4799E-2</v>
+    <v>-5.335</v>
+    <v>-2.3515999999999999E-2</v>
     <v>USD</v>
     <v>Cloudflare, Inc. is a connectivity cloud company. The Company delivers a range of services to businesses of all sizes and in all geographies, enhancing the performance of business-critical applications. Its full suite of products consists of application services that help deliver security, performance, and reliability for any organization's applications connected to the Internet, including Websites and application programming interfaces (APIs) and its secure access service edge (SASE) platform, which contains its suite of and workplace security services and network services solutions to help ensure traffic in and out of an organization’s network and devices is verified and authorized and data is protected and secured, as well as to securely connect data centers, cloud services, and branch offices to an organization with its connectivity cloud. The Company also offers developer-based solutions which build and deploys serverless and artificial intelligence applications.</v>
     <v>5483</v>
@@ -6642,20 +6642,20 @@
     <v>225.54</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46191.626750010939</v>
+    <v>46191.666702106253</v>
     <v>174</v>
     <v>216.03</v>
-    <v>79333472838</v>
+    <v>78631544286</v>
     <v>CLOUDFLARE, INC.</v>
     <v>CLOUDFLARE, INC.</v>
     <v>225</v>
     <v>0</v>
     <v>226.87</v>
-    <v>223.51259999999999</v>
+    <v>221.535</v>
     <v>354939600</v>
     <v>NET</v>
     <v>CLOUDFLARE, INC. (XNYS:NET)</v>
-    <v>998903</v>
+    <v>1277658</v>
     <v>3907677</v>
     <v>2009</v>
   </rv>
@@ -6679,8 +6679,8 @@
     <v>Finance</v>
     <v>20</v>
     <v>1.1141000000000001</v>
-    <v>-0.04</v>
-    <v>-1.0150000000000001E-3</v>
+    <v>0.315</v>
+    <v>7.9909999999999998E-3</v>
     <v>EUR</v>
     <v>NIKE, Inc. is engaged in the designing, marketing and distributing of athletic footwear, apparel, equipment and accessories and services for sports and fitness activities. The Company's operating segments include North America; Europe, Middle East &amp; Africa (EMEA); Greater China; and Asia Pacific &amp; Latin America (APLA). It sells a line of equipment and accessories under the NIKE Brand name, including bags, socks, sport balls, eyewear, timepieces, digital devices, bats, gloves, protective equipment and other equipment designed for sports activities. It also designs products specifically for the Jordan Brand and Converse. The Jordan Brand designs, distributes and licenses athletic and casual footwear, apparel and accessories predominantly focused on basketball performance and culture using the Jumpman trademark. The Company also designs, distributes and licenses casual sneakers, apparel and accessories under the Chuck Taylor, All Star, One Star, Star Chevron and Jack Purcell trademarks.</v>
     <v>77800</v>
@@ -6688,23 +6688,23 @@
     <v>XFRA</v>
     <v>XFRA</v>
     <v>One Bowerman Dr, BEAVERTON, OR, 97005-6453 US</v>
-    <v>39.450000000000003</v>
+    <v>39.734999999999999</v>
     <v>Textiles &amp; Apparel</v>
     <v>Stock</v>
-    <v>46191.615972222222</v>
+    <v>46191.655555555553</v>
     <v>177</v>
     <v>38.380000000000003</v>
     <v>98149420000</v>
     <v>NIKE, INC.</v>
     <v>NIKE, INC.</v>
     <v>39.06</v>
-    <v>30.527100000000001</v>
+    <v>30.802299999999999</v>
     <v>39.42</v>
-    <v>39.380000000000003</v>
+    <v>39.734999999999999</v>
     <v>1480887000</v>
     <v>NKE</v>
     <v>NIKE, INC. (XFRA:NKE)</v>
-    <v>6325</v>
+    <v>6345</v>
     <v>17875870</v>
     <v>1969</v>
   </rv>
@@ -6740,8 +6740,8 @@
     <v>17.45</v>
     <v>4</v>
     <v>1.1641999999999999</v>
-    <v>-9.1499999999999998E-2</v>
-    <v>-6.6159999999999995E-3</v>
+    <v>-0.23499999999999999</v>
+    <v>-1.6992E-2</v>
     <v>USD</v>
     <v>Nokia Oyj is a Finland-based company engaged in the network and Internet protocol (IP) infrastructure, software, and related services market. The Company's businesses include Nokia Networks and Nokia Technologies. The Company's segments include Ultra Broadband Networks, IP Networks and Applications, and Nokia Technologies. The Ultra Broadband Networks segment comprises Mobile Networks and Fixed Networks operating segments. The IP Networks and Applications segment comprises IP/Optical Networks and Applications &amp; Analytics operating segments. The Applications &amp; Analytics operating segment offers software solutions spanning customer experience management, network operations and management, communications and collaboration, policy and charging, as well as Cloud, Internet of things (IoT), security, and analytics platforms that enable digital services providers and enterprises to accelerate and optimize their customer experience. The Company has Comptel Oyj among its subsidiaries.</v>
     <v>77586</v>
@@ -6752,20 +6752,20 @@
     <v>14.04</v>
     <v>Communications &amp; Networking</v>
     <v>Stock</v>
-    <v>46191.626762510939</v>
+    <v>46191.666703240626</v>
     <v>182</v>
     <v>13.41</v>
-    <v>78889764240</v>
+    <v>78065752800</v>
     <v>Nokia Oyj</v>
     <v>Nokia Oyj</v>
     <v>14.01</v>
-    <v>85.385300000000001</v>
+    <v>84.493499999999997</v>
     <v>13.83</v>
-    <v>13.7385</v>
+    <v>13.595000000000001</v>
     <v>5742240000</v>
     <v>NOK</v>
     <v>Nokia Oyj (XNYS:NOK)</v>
-    <v>40182502</v>
+    <v>56034393</v>
     <v>124767956</v>
     <v>1997</v>
   </rv>
@@ -6791,8 +6791,8 @@
     <v>211.47800000000001</v>
     <v>81.239999999999995</v>
     <v>0.97970000000000002</v>
-    <v>0.38</v>
-    <v>3.98E-3</v>
+    <v>-0.40500000000000003</v>
+    <v>-4.2420000000000001E-3</v>
     <v>USD</v>
     <v>ServiceNow, Inc. provides an artificial intelligence (AI) platform for business transformation. The Company’s AI platform connects people, processes, data, and devices to increase productivity and maximize business outcomes. Its intelligent platform, the Now Platform, is a cloud-based solution that helps enterprises and organizations across public and private sectors digitize workflows. The workflow applications built on the Now Platform are organized into four primary areas: Technology, CRM and Industry, Core Business and Creator. Its products include IT Service Management, IT Operations Management, HR Service Delivery, ServiceNow AI Agents, AI Experience, Build Agent, ServiceNow AI Control Tower, AI Agent Fabric, RaptorDB, Workflow Data Fabric, Workplace Service Delivery, ServiceNow Platform Encryption, Telecommunications Service Operations Management, and others. The Company also offers identity security, helping organizations secure access across the enterprise.</v>
     <v>29187</v>
@@ -6803,20 +6803,20 @@
     <v>96.241299999999995</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46191.62675308984</v>
+    <v>46191.666707777345</v>
     <v>185</v>
     <v>92.45</v>
-    <v>98861184880</v>
+    <v>98051608100</v>
     <v>SERVICENOW, INC.</v>
     <v>SERVICENOW, INC.</v>
     <v>95.05</v>
-    <v>57.012</v>
+    <v>56.545099999999998</v>
     <v>95.48</v>
-    <v>95.86</v>
+    <v>95.075000000000003</v>
     <v>1031308000</v>
     <v>NOW</v>
     <v>SERVICENOW, INC. (XNYS:NOW)</v>
-    <v>12014595</v>
+    <v>14567961</v>
     <v>33411074</v>
     <v>2012</v>
   </rv>
@@ -6842,8 +6842,8 @@
     <v>236.54</v>
     <v>142.03</v>
     <v>2.2042999999999999</v>
-    <v>4.3555999999999999</v>
-    <v>2.1283E-2</v>
+    <v>4.4099000000000004</v>
+    <v>2.1547999999999998E-2</v>
     <v>USD</v>
     <v>NVIDIA Corporation is an artificial intelligence (AI) infrastructure company. The Company is engaged in accelerated computing to help solve the challenging computational problems. Its segments include Compute &amp; Networking and Graphics. The Compute &amp; Networking segment includes its Data Center accelerated computing and networking platforms and AI solutions and software, and automotive platforms and autonomous and electric vehicle solutions, including software. The Graphics segment includes GeForce GPUs for gaming and personal computers (PCs), and Quadro/NVIDIA RTX GPUs for enterprise workstation graphics. Its technology stack includes the foundational NVIDIA CUDA development platform that runs on all NVIDIA GPUs, as well as hundreds of domain-specific software libraries, frameworks, algorithms, software development kits (SDKs), and application programming interfaces (APIs). Its platforms address four markets, which include Data Center, Gaming, Professional Visualization, and Automotive.</v>
     <v>42000</v>
@@ -6854,20 +6854,20 @@
     <v>209.87</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46191.626757534374</v>
+    <v>46191.666705034375</v>
     <v>188</v>
     <v>206.5</v>
-    <v>5057935520000</v>
+    <v>5059249580000</v>
     <v>NVIDIA CORPORATION</v>
     <v>NVIDIA CORPORATION</v>
     <v>207.5</v>
-    <v>32.006999999999998</v>
+    <v>32.015300000000003</v>
     <v>204.65</v>
-    <v>209.00559999999999</v>
+    <v>209.0599</v>
     <v>24200000000</v>
     <v>NVDA</v>
     <v>NVIDIA CORPORATION (XNAS:NVDA)</v>
-    <v>61026518</v>
+    <v>73506622</v>
     <v>170253095</v>
     <v>1998</v>
   </rv>
@@ -6893,8 +6893,8 @@
     <v>134.91999999999999</v>
     <v>44.56</v>
     <v>1.9847999999999999</v>
-    <v>6.77</v>
-    <v>5.9954E-2</v>
+    <v>7.19</v>
+    <v>6.3673000000000007E-2</v>
     <v>USD</v>
     <v>ON Semiconductor Corporation is engaged in providing intelligent power and intelligent sensing solutions. The Company’s intelligent power technologies enable the electrification of drivetrain in the automotive industry to allow for lighter and longer-range electric vehicles. Its segments include Power Solutions Group (PSG), the Analog and Mixed-Signal Group (AMG) and the Intelligent Sensing Group (ISG). PSG segment provides a portfolio of discrete, module, and integrated semiconductor devices designed to enable conversion across artificial intelligence (AI) data centers, energy infrastructure, automotive and industrial. AMG segment designs and develops a range of analog and mixed-signal solutions including power‑management, sensor‑interface, connectivity, and products that serve automotive, industrial automation, AI data center, computing, and mobile end markets.</v>
     <v>22600</v>
@@ -6905,20 +6905,20 @@
     <v>121.39</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46191.626747626564</v>
+    <v>46191.666725219533</v>
     <v>191</v>
     <v>117.575</v>
-    <v>46906894008</v>
+    <v>47071493352</v>
     <v>ON SEMICONDUCTOR CORPORATION</v>
     <v>ON SEMICONDUCTOR CORPORATION</v>
     <v>118</v>
-    <v>85.468400000000003</v>
+    <v>85.7684</v>
     <v>112.92</v>
-    <v>119.69</v>
+    <v>120.11</v>
     <v>391903200</v>
     <v>ON</v>
     <v>ON SEMICONDUCTOR CORPORATION (XNAS:ON)</v>
-    <v>3310901</v>
+    <v>4019342</v>
     <v>12016690</v>
     <v>2000</v>
   </rv>
@@ -6944,8 +6944,8 @@
     <v>15.28</v>
     <v>1.36</v>
     <v>2.7000999999999999</v>
-    <v>0.1181</v>
-    <v>1.295E-2</v>
+    <v>-5.0000000000000001E-3</v>
+    <v>-5.4819999999999999E-4</v>
     <v>USD</v>
     <v>Ondas Inc. is a provider of autonomous systems, robotics, and mission-critical connectivity solutions for defense, security, and industrial markets. Through its business units, Ondas Autonomous Systems (OAS), Ondas Capital and Ondas Networks, it develops and deploys integrated technologies that deliver advanced sensing, mobility, and communications capabilities. OAS delivers a portfolio of artificial-intelligence (AI)-powered defense and security platforms to protect sensitive sites, populations, and critical infrastructure. OAS also provides an integrated suite of autonomous aerial, ground, and counter-UAS solutions through its operating companies. It also provides Airborne Missile Protection Systems (AMPS) and airborne intelligence, surveillance and reconnaissance (ISR) solutions for the military, government and others. It also specializes in the procurement, integration, and lifecycle support of heavy engineering equipment for military and national infrastructure programs.</v>
     <v>459</v>
@@ -6956,20 +6956,20 @@
     <v>9.4600000000000009</v>
     <v>Communications &amp; Networking</v>
     <v>Stock</v>
-    <v>46191.626774652344</v>
+    <v>46191.666731492965</v>
     <v>194</v>
     <v>8.92</v>
-    <v>4777929615</v>
+    <v>4714262504</v>
     <v>ONDAS INC.</v>
     <v>ONDAS INC.</v>
     <v>9.4</v>
-    <v>23.293199999999999</v>
+    <v>22.982900000000001</v>
     <v>9.1199999999999992</v>
-    <v>9.2380999999999993</v>
+    <v>9.1150000000000002</v>
     <v>517198300</v>
     <v>ONDS</v>
     <v>ONDAS INC. (XNAS:ONDS)</v>
-    <v>22132853</v>
+    <v>27813314</v>
     <v>84345570</v>
     <v>2014</v>
   </rv>
@@ -7011,8 +7011,8 @@
     <v>345.72</v>
     <v>134.57</v>
     <v>1.6944999999999999</v>
-    <v>1.0349999999999999</v>
-    <v>5.6389999999999999E-3</v>
+    <v>1.8199000000000001</v>
+    <v>9.9160000000000012E-3</v>
     <v>USD</v>
     <v>Oracle Corporation offers integrated suites of applications plus secure, autonomous infrastructure in the Oracle Cloud. The Company operates through three businesses: cloud and license, hardware and service. Its cloud and license business is engaged in the sale, marketing and delivery of its enterprise applications and infrastructure technologies through cloud and on-premise deployment models including its cloud services and license support offerings, and its cloud license and on-premise license offerings. Its hardware business provides infrastructure technologies including Oracle Engineered Systems, servers, storage, industry-specific hardware, operating systems, virtualization, management and other hardware-related software to support diverse IT environments. Its services business provides services to customers and partners to help maximize the performance of their investments in Oracle applications and infrastructure technologies.</v>
     <v>162000</v>
@@ -7020,24 +7020,24 @@
     <v>XNYS</v>
     <v>XNYS</v>
     <v>2300 Oracle Way, AUSTIN, TX, 78741 US</v>
-    <v>185.18119999999999</v>
+    <v>185.35</v>
     <v>199</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46191.626773900003</v>
+    <v>46191.666741596877</v>
     <v>200</v>
     <v>177.7</v>
-    <v>530817429990</v>
+    <v>533074838495</v>
     <v>ORACLE CORPORATION</v>
     <v>ORACLE CORPORATION</v>
     <v>183.08</v>
-    <v>29.855699999999999</v>
+    <v>29.982700000000001</v>
     <v>183.53</v>
-    <v>184.565</v>
+    <v>185.34989999999999</v>
     <v>2876046000</v>
     <v>ORCL</v>
     <v>ORACLE CORPORATION (XNYS:ORCL)</v>
-    <v>8554815</v>
+    <v>10032305</v>
     <v>24346902</v>
     <v>2005</v>
   </rv>
@@ -7063,8 +7063,8 @@
     <v>302.95</v>
     <v>139.57060000000001</v>
     <v>0.94240000000000002</v>
-    <v>1.6</v>
-    <v>5.6710000000000007E-3</v>
+    <v>1.62</v>
+    <v>5.7420000000000006E-3</v>
     <v>USD</v>
     <v>Palo Alto Networks, Inc. is a global artificial intelligence (AI) cybersecurity company, with a comprehensive portfolio of cybersecurity solutions and platforms across network, cloud, security operations, AI and Identity. Its network security platform includes Secure Access Service Edge (SASE), Next-Generation Firewalls, Cloud Delivered Security Services (CDSS), Prisma AIRS, and Strata Cloud Manager (SCM). It delivers security operations capabilities that unifies standalone Security Information and Event Management (SIEM) tools, endpoint security, security automation, cloud detection and response (CDR), as well as attack surface management (ASM) capabilities on its Cortex platform. It delivers comprehensive security across the cloud application development lifecycle through Cortex Cloud. Its Unit 42 brings together expertise across threat research, incident response, and security consulting to deliver intelligence-driven, response-ready outcomes that help customers reduce cyber risk.</v>
     <v>21491</v>
@@ -7075,20 +7075,20 @@
     <v>288.81</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46191.626794803124</v>
+    <v>46191.666702568749</v>
     <v>203</v>
     <v>276.46499999999997</v>
-    <v>231239950000</v>
+    <v>231256250000</v>
     <v>PALO ALTO NETWORKS, INC.</v>
     <v>PALO ALTO NETWORKS, INC.</v>
     <v>285.76</v>
-    <v>233.61879999999999</v>
+    <v>233.6352</v>
     <v>282.13</v>
-    <v>283.73</v>
+    <v>283.75</v>
     <v>815000000</v>
     <v>PANW</v>
     <v>PALO ALTO NETWORKS, INC. (XNAS:PANW)</v>
-    <v>2365524</v>
+    <v>2846807</v>
     <v>9255849</v>
     <v>2005</v>
   </rv>
@@ -7114,8 +7114,8 @@
     <v>19.84</v>
     <v>9.2002000000000006</v>
     <v>0.98799999999999999</v>
-    <v>0.04</v>
-    <v>3.9100000000000003E-3</v>
+    <v>-4.4999999999999998E-2</v>
+    <v>-4.3990000000000001E-3</v>
     <v>USD</v>
     <v>UiPath, Inc. is focused on agentic automation and orchestration, empowering enterprises to harness the full potential of AI agents to autonomously execute and optimize complex business processes. It is focused on building and managing automations, starting with computer vision technology and user interface automation in its initial robotic process automation offering. Its AI-powered UiPath Platform offers a robust set of capabilities that allows its customers to discover opportunities for automation, automate using a digital workforce that seamlessly collaborates with humans, and operate a mission-critical automation program at scale. It enables employees to quickly build automations for both existing and new processes and to automate a range of actions including logging into applications, moving folders, filling in forms, reading emails and others. Its platform allows users to design and combine UI automations, API integrations and AI-based document understanding in a single workflow.</v>
     <v>3981</v>
@@ -7126,20 +7126,20 @@
     <v>10.315</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46191.626774687502</v>
+    <v>46191.666717488282</v>
     <v>206</v>
     <v>9.8800000000000008</v>
-    <v>5321095481</v>
+    <v>5277055255</v>
     <v>UIPATH, INC.</v>
     <v>UIPATH, INC.</v>
     <v>10.199999999999999</v>
-    <v>17.071100000000001</v>
+    <v>16.9299</v>
     <v>10.23</v>
-    <v>10.27</v>
+    <v>10.185</v>
     <v>518120300</v>
     <v>PATH</v>
     <v>UIPATH, INC. (XNYS:PATH)</v>
-    <v>8547255</v>
+    <v>15272754</v>
     <v>46059779</v>
     <v>2015</v>
   </rv>
@@ -7165,8 +7165,8 @@
     <v>167.25</v>
     <v>137.62</v>
     <v>0.36990000000000001</v>
-    <v>0.67500000000000004</v>
-    <v>4.483E-3</v>
+    <v>0.56999999999999995</v>
+    <v>3.7859999999999999E-3</v>
     <v>USD</v>
     <v>The Procter &amp; Gamble Company is focused on providing branded consumer packaged goods to consumers across the world. The Company’s segments include Beauty, Grooming, Health Care, Fabric &amp; Home Care and Baby, Feminine &amp; Family Care. The Company’s products are sold in approximately 180 countries and territories primarily through mass merchandisers, e-commerce, including social commerce channels, grocery stores, membership club stores, drug stores, department stores, distributors, wholesalers, specialty beauty stores, including airport duty-free stores), high-frequency stores, pharmacies, electronics stores and professional channels. It also sells direct to individual consumers. It has operations in approximately 70 countries. It offers products under brands, such as Head &amp; Shoulders, Herbal Essences, Pantene, Rejoice, Olay, Old Spice, Safeguard, Secret, SK-II, Braun, Gillette, Venus, Crest, Oral-B, Ariel, Downy, Gain, Tide, Always, Always Discreet, Tampax, Bounty and others.</v>
     <v>109000</v>
@@ -7177,20 +7177,20 @@
     <v>152.29</v>
     <v>Personal &amp; Household Products &amp; Services</v>
     <v>Stock</v>
-    <v>46191.626786620312</v>
+    <v>46191.666723159375</v>
     <v>209</v>
     <v>150.5</v>
-    <v>352165669765</v>
+    <v>351921166870</v>
     <v>THE PROCTER &amp; GAMBLE COMPANY</v>
     <v>THE PROCTER &amp; GAMBLE COMPANY</v>
     <v>150.5</v>
-    <v>22.118099999999998</v>
+    <v>22.102799999999998</v>
     <v>150.56</v>
-    <v>151.23500000000001</v>
+    <v>151.13</v>
     <v>2328599000</v>
     <v>PG</v>
     <v>THE PROCTER &amp; GAMBLE COMPANY (XNYS:PG)</v>
-    <v>3801132</v>
+    <v>4553436</v>
     <v>8388782</v>
     <v>1905</v>
   </rv>
@@ -7216,8 +7216,8 @@
     <v>56</v>
     <v>18</v>
     <v>1.3759999999999999</v>
-    <v>2.41</v>
-    <v>7.7716999999999994E-2</v>
+    <v>2.2749999999999999</v>
+    <v>7.3362999999999998E-2</v>
     <v>USD</v>
     <v>Photronics, Inc. is a manufacturer of photomasks, which are high-precision photographic quartz or glass plates containing microscopic images of electronic circuits. The Company manufactures photomasks, which are used as masters to transfer circuit patterns onto semiconductor wafers and FPD substrates. The photomasks the Company manufactures incorporate circuit designs provided on a confidential basis by its customers. The Company sells its photomasks to semiconductor designers and manufacturers, and manufacturers of FPDs. Photomask technology is also being applied to the fabrication of other higher-performance electronic products such as virtual reality/augmented reality advanced IC packages, photonics, micro-electronic mechanical systems, and certain nanotechnology applications. The Company operates approximately 11 manufacturing facilities, which are located in Taiwan, China, Korea, the United States, and Europe.</v>
     <v>1908</v>
@@ -7225,23 +7225,23 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>15 Secor Rd, BROOKFIELD, CT, 06804-5226 US</v>
-    <v>33.546199999999999</v>
+    <v>33.590000000000003</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46191.62676982578</v>
+    <v>46191.666677522655</v>
     <v>212</v>
     <v>32.395000000000003</v>
-    <v>1970566854</v>
+    <v>1962606754</v>
     <v>PHOTRONICS, INC.</v>
     <v>PHOTRONICS, INC.</v>
     <v>32.83</v>
-    <v>12.2395</v>
+    <v>12.190099999999999</v>
     <v>31.01</v>
-    <v>33.42</v>
+    <v>33.284999999999997</v>
     <v>58963700</v>
     <v>PLAB</v>
     <v>PHOTRONICS, INC. (XNAS:PLAB)</v>
-    <v>547713</v>
+    <v>852995</v>
     <v>2073122</v>
     <v>1969</v>
   </rv>
@@ -7267,8 +7267,8 @@
     <v>20.81</v>
     <v>3.87</v>
     <v>0.7429</v>
-    <v>0.1</v>
-    <v>8.3680000000000004E-3</v>
+    <v>-6.5000000000000002E-2</v>
+    <v>-5.4390000000000003E-3</v>
     <v>USD</v>
     <v>POET Technologies Inc. is a design and development company. It offers high-speed optical engines, light source products and custom optical modules to the artificial intelligence (AI) systems market and to hyperscale data centers. Its photonic integration solutions are based on the POET Optical Interposer, a novel, patented platform that allows the integration of electronic and photonic devices into a single chip using wafer-level semiconductor manufacturing techniques. Its Optical Interposer-based products consume less power than comparable products, are smaller in size and are readily scalable to high production volumes. In addition, it has designed and produced novel light source products for chip-to-chip data communication within and between AI servers, the next frontier for solving bandwidth and latency problems in AI systems. Its Optical Interposer platform solves device integration challenges across a range of communication, computing and sensing applications.</v>
     <v>180</v>
@@ -7279,20 +7279,20 @@
     <v>12.36</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46191.626767233596</v>
+    <v>46191.666697395311</v>
     <v>215</v>
     <v>11.59</v>
-    <v>2079774570</v>
+    <v>2051296329</v>
     <v>POET Technologies Inc.</v>
     <v>POET Technologies Inc.</v>
     <v>12.19</v>
     <v>0</v>
     <v>11.95</v>
-    <v>12.05</v>
+    <v>11.885</v>
     <v>172595400</v>
     <v>POET</v>
     <v>POET Technologies Inc. (XNAS:POET)</v>
-    <v>7736379</v>
+    <v>9127576</v>
     <v>46719233</v>
     <v>2010</v>
   </rv>
@@ -7334,8 +7334,8 @@
     <v>259.92</v>
     <v>121.99</v>
     <v>1.6254</v>
-    <v>9.4295000000000009</v>
-    <v>4.4276000000000003E-2</v>
+    <v>7.4</v>
+    <v>3.4747E-2</v>
     <v>USD</v>
     <v>Qualcomm Incorporated is engaged in the development and commercialization of foundational technologies for the wireless industry, including third generation (3G), fourth generation (4G) and fifth generation (5G) wireless connectivity, and high-performance and low-power computing, including on-device artificial intelligence. Its segments include Qualcomm CDMA Technologies (QCT), Qualcomm Technology Licensing (QTL) and Qualcomm Strategic Initiatives. QCT develops and supplies integrated circuits and system software based on 3G/4G/5G and other technologies, including radio frequency front-end, digital cockpit and advanced driver assistance and automated driving, Internet of things including consumer electronic devices, industrial devices and edge networking products. QTL grants licenses or otherwise provides rights to use portions of its intellectual property portfolio that includes certain patent rights essential to and/or useful in the manufacture and sale of certain wireless products.</v>
     <v>52000</v>
@@ -7347,20 +7347,20 @@
     <v>220</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46191.626786666406</v>
+    <v>46191.666737314059</v>
     <v>221</v>
     <v>214.73</v>
-    <v>234409073000</v>
+    <v>232269980000</v>
     <v>QUALCOMM INCORPORATED</v>
     <v>QUALCOMM INCORPORATED</v>
     <v>220.72</v>
-    <v>24.191199999999998</v>
+    <v>23.970500000000001</v>
     <v>212.97</v>
-    <v>222.39949999999999</v>
+    <v>220.37</v>
     <v>1054000000</v>
     <v>QCOM</v>
     <v>QUALCOMM INCORPORATED (XNAS:QCOM)</v>
-    <v>7530750</v>
+    <v>9153347</v>
     <v>21727556</v>
     <v>1991</v>
   </rv>
@@ -7386,8 +7386,8 @@
     <v>155.47</v>
     <v>74.510000000000005</v>
     <v>0.64049999999999996</v>
-    <v>-1.4750000000000001</v>
-    <v>-1.3148999999999999E-2</v>
+    <v>-0.73</v>
+    <v>-6.5069999999999998E-3</v>
     <v>USD</v>
     <v>Qualys, Inc. is a provider of a cloud-based platform delivering information technology (IT), security and compliance solutions. The Company’s integrated suite of IT, security and compliance solutions delivered on Qualys' Enterprise TruRisk Platform enables its customers to identify and manage their IT and operational technology (OT) assets, collect, and analyze large amounts of IT security data, recommend, and implement remediation actions and verify the implementation of such actions. The Company provides its solutions through a software-as-a-service model, primarily with renewable annual subscriptions. Its cloud platform offers an integrated suite of solutions that automates the lifecycle of asset discovery and management, security and compliance assessments, and remediation for an organization’s IT infrastructure and assets, whether such infrastructure and assets reside inside the organization, on their network perimeter, on endpoints or in the cloud.</v>
     <v>2683</v>
@@ -7398,20 +7398,20 @@
     <v>112.41</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46191.626755786718</v>
+    <v>46191.666685404685</v>
     <v>224</v>
     <v>107.96</v>
-    <v>3898699092</v>
+    <v>3924935764</v>
     <v>QUALYS, INC.</v>
     <v>QUALYS, INC.</v>
     <v>111.75</v>
-    <v>19.879200000000001</v>
+    <v>20.012899999999998</v>
     <v>112.18</v>
-    <v>110.705</v>
+    <v>111.45</v>
     <v>35217010</v>
     <v>QLYS</v>
     <v>QUALYS, INC. (XNAS:QLYS)</v>
-    <v>152382</v>
+    <v>219894</v>
     <v>702390</v>
     <v>1999</v>
   </rv>
@@ -7437,25 +7437,25 @@
     <v>748.65</v>
     <v>523.65</v>
     <v>1.0143</v>
-    <v>15.185</v>
-    <v>2.1017000000000001E-2</v>
+    <v>15.960100000000001</v>
+    <v>2.2090000000000002E-2</v>
     <v>USD</v>
     <v>Nasdaq Stock Market</v>
     <v>XNAS</v>
     <v>1.8E-3</v>
-    <v>738.8</v>
+    <v>739.14</v>
     <v>ETF</v>
-    <v>46191.626790092188</v>
+    <v>46191.666711006248</v>
     <v>227</v>
     <v>732.53</v>
     <v>493982650931.38</v>
     <v>Invesco QQQ Trust 1</v>
     <v>736.67</v>
     <v>722.51</v>
-    <v>737.69500000000005</v>
+    <v>738.4701</v>
     <v>QQQ</v>
     <v>Invesco QQQ Trust 1 (XNAS:QQQ)</v>
-    <v>15370320</v>
+    <v>23168724</v>
     <v>47358364</v>
   </rv>
   <rv s="2">
@@ -7480,8 +7480,8 @@
     <v>474.99</v>
     <v>305.44009999999997</v>
     <v>1.5466</v>
-    <v>15.08</v>
-    <v>3.2875999999999996E-2</v>
+    <v>12.32</v>
+    <v>2.6859000000000001E-2</v>
     <v>USD</v>
     <v>Rockwell Automation, Inc. is engaged in industrial automation and digital transformation. The Company operates in three segments: Intelligent Devices, Software &amp; Control, and Lifecycle Services. The Intelligent Devices segment portfolio includes power control, motion control, safety, sensing, and industrial components, and micro control and distributed input/output. The Software &amp; Control operating segment contains a comprehensive portfolio of production automation and production operations platforms, including hardware and software. This integrated portfolio is merging information technology (IT) and operational technology (OT), bringing the benefits of the Connected Enterprise to the production system. The Lifecycle Services segment includes consulting services, including cybersecurity and digital transformation strategy and design and professional services, including global automation and information program and project management and delivery capabilities, and connected services.</v>
     <v>26000</v>
@@ -7489,23 +7489,23 @@
     <v>XNYS</v>
     <v>XNYS</v>
     <v>1201 South 2Nd Street, MILWAUKEE, WI, 53204 US</v>
-    <v>474.6345</v>
+    <v>474.7</v>
     <v>Machinery, Equipment &amp; Components</v>
     <v>Stock</v>
-    <v>46191.626705625</v>
+    <v>46191.666654606248</v>
     <v>230</v>
     <v>466.61</v>
-    <v>52718235603</v>
+    <v>52411119639</v>
     <v>ROCKWELL AUTOMATION, INC.</v>
     <v>ROCKWELL AUTOMATION, INC.</v>
     <v>472</v>
-    <v>49.216700000000003</v>
+    <v>48.93</v>
     <v>458.69</v>
-    <v>473.77</v>
+    <v>471.01</v>
     <v>111273900</v>
     <v>ROK</v>
     <v>ROCKWELL AUTOMATION, INC. (XNYS:ROK)</v>
-    <v>172872</v>
+    <v>203873</v>
     <v>666835</v>
     <v>1996</v>
   </rv>
@@ -7531,8 +7531,8 @@
     <v>7.18</v>
     <v>2.77</v>
     <v>1.0268999999999999</v>
-    <v>4.2599999999999999E-2</v>
-    <v>1.3697999999999998E-2</v>
+    <v>4.0099999999999997E-2</v>
+    <v>1.2894000000000001E-2</v>
     <v>USD</v>
     <v>Recursion Pharmaceuticals, Inc. is a clinical-stage TechBio company decoding biology and chemistry to industrialize drug discovery. Its Recursion Operating System (OS), a platform built across diverse technologies, enables the Company to map and navigate trillions of biological and chemical relationships within the Recursion Data Universe. The Company integrates physical and digital components as iterative loops of atoms and bits, scaling wet lab biology and chemistry data organized into virtuous cycles with computational tools to rapidly translate silico hypotheses into validated insights and novel chemistry. Its clinical programs in oncology and rare diseases include REC-617, REC-1245, REC-3565 and REC-4539. Its REC-617 is an orally bioavailable, cyclin-dependent kinase 7 (CDK7) inhibitor for the treatment of advanced solid tumors. Its REV102 program targets ectonucleotide pyrophosphatase/phosphodiesterase 1 (ENPP1), an enzyme implicated in the pathogenesis of HPP.</v>
     <v>600</v>
@@ -7543,20 +7543,20 @@
     <v>3.28</v>
     <v>Biotechnology &amp; Medical Research</v>
     <v>Stock</v>
-    <v>46191.626772673437</v>
+    <v>46191.666706145312</v>
     <v>233</v>
     <v>3.11</v>
-    <v>1670579133</v>
+    <v>1669254370</v>
     <v>RECURSION PHARMACEUTICALS, INC.</v>
     <v>RECURSION PHARMACEUTICALS, INC.</v>
     <v>3.18</v>
     <v>0</v>
     <v>3.11</v>
-    <v>3.1526000000000001</v>
+    <v>3.1501000000000001</v>
     <v>529905200</v>
     <v>RXRX</v>
     <v>RECURSION PHARMACEUTICALS, INC. (XNAS:RXRX)</v>
-    <v>6711728</v>
+    <v>8686737</v>
     <v>20604995</v>
     <v>2013</v>
   </rv>
@@ -7582,8 +7582,8 @@
     <v>21.4</v>
     <v>11.81</v>
     <v>0.85150000000000003</v>
-    <v>9.5000000000000001E-2</v>
-    <v>6.4190000000000002E-3</v>
+    <v>0</v>
+    <v>0</v>
     <v>USD</v>
     <v>SentinelOne, Inc. is an artificial intelligence (AI)-powered cybersecurity provider. The Company’s Singularity Platform delivers AI-powered autonomous threat prevention, detection, response, and exposure management capabilities across an organization’s endpoints, cloud workloads, and identity credentials. The Company’s Singularity platform ingests, correlates, and queries petabytes of structured and unstructured data from a myriad of ever-expanding disparate external and internal sources in real time. Its distributed AI models run both locally on every endpoint and every cloud workload, as well as on its cloud platform. The Company through PingSafe Pte. Ltd. (PingSafe), which is a cloud native application protection platform (CNAPP) to bolster its cloud security product suite. By adding PingSafe’s CNAPP to its Cloud Workload Security (CWS), it provides enterprises with a comprehensive cloud security coverage that drives security, improved posture, and autonomous protection.</v>
     <v>2700</v>
@@ -7594,19 +7594,19 @@
     <v>14.93</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46191.626686006253</v>
+    <v>46191.666690659375</v>
     <v>236</v>
     <v>14.382</v>
-    <v>5106061111</v>
+    <v>5073494760</v>
     <v>SENTINELONE, INC.</v>
     <v>SENTINELONE, INC.</v>
     <v>14.74</v>
     <v>14.8</v>
-    <v>14.895</v>
+    <v>14.8</v>
     <v>342803700</v>
     <v>S</v>
     <v>SENTINELONE, INC. (XNYS:S)</v>
-    <v>1122362</v>
+    <v>1504892</v>
     <v>9329331</v>
     <v>2013</v>
   </rv>
@@ -7630,10 +7630,10 @@
     <v>Finance</v>
     <v>20</v>
     <v>269.35000000000002</v>
-    <v>134.97999999999999</v>
+    <v>134.30000000000001</v>
     <v>1.1247</v>
-    <v>-5.08</v>
-    <v>-3.5982E-2</v>
+    <v>-6.32</v>
+    <v>-4.4766E-2</v>
     <v>EUR</v>
     <v>SAP SE (SAP) is a Germany-based application software company. The Company operates through two segments Applications, Technology &amp; Support (ATS) segment and its Core Services segment. The ATS segment covers the Company’s integrated product portfolio and includes cloud subscription offerings, support services, and training solutions. It also encompasses activities related to operating cloud technologies and delivering customer support associated with its software products. The Core Services segment complements the Company’s product portfolio by delivering consulting and premium support services to assist customers in adopting its innovations. Revenue in this segment is primarily derived from professional services and enhanced support offerings, while costs arise from the execution of these service activities.</v>
     <v>111038</v>
@@ -7644,20 +7644,20 @@
     <v>140.5</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46191.616354166668</v>
+    <v>46191.656111111108</v>
     <v>239</v>
-    <v>134.97999999999999</v>
+    <v>134.30000000000001</v>
     <v>262224200000</v>
     <v>SAP SE</v>
     <v>SAP SE</v>
     <v>139.78</v>
-    <v>21.6892</v>
+    <v>21.491599999999998</v>
     <v>141.18</v>
-    <v>136.1</v>
+    <v>134.86000000000001</v>
     <v>1228504000</v>
     <v>SAP</v>
     <v>SAP SE (XETR:SAP)</v>
-    <v>2432433</v>
+    <v>4837230</v>
     <v>2881320</v>
     <v>2014</v>
   </rv>
@@ -7683,8 +7683,8 @@
     <v>107.5</v>
     <v>83.96</v>
     <v>0.74790000000000001</v>
-    <v>-0.72</v>
-    <v>-7.6180000000000006E-3</v>
+    <v>-1.35</v>
+    <v>-1.4283999999999998E-2</v>
     <v>USD</v>
     <v>The Charles Schwab Corporation is a savings and loan holding company. The Company, through its subsidiaries, engages in wealth management, securities brokerage, banking, asset management, custody, and financial advisory services. The Company provides financial services to individuals and institutional clients through two segments: Investor Services, and Advisor Services. The Investor Services segment provides retail brokerage, investment advisory, and banking and trust services to individual investors, and retirement plan and business services, as well as other corporate brokerage services, to businesses and their employees. The Advisor Services segment provides custodial, trading, banking and trust, and support services to independent registered investment advisors (RIAs), independent retirement advisors, and recordkeepers. Its products and services include brokerage, mutual funds, exchange-traded funds (ETFs), managed investing solutions, alternative investments, banking, and trust.</v>
     <v>33500</v>
@@ -7695,20 +7695,20 @@
     <v>94.79</v>
     <v>Investment Banking &amp; Investment Services</v>
     <v>Stock</v>
-    <v>46191.626767962502</v>
+    <v>46191.666724571092</v>
     <v>242</v>
-    <v>93.53</v>
-    <v>163113471650</v>
+    <v>93.14</v>
+    <v>162017816600</v>
     <v>THE CHARLES SCHWAB CORPORATION</v>
     <v>THE CHARLES SCHWAB CORPORATION</v>
     <v>94.6</v>
-    <v>18.598800000000001</v>
+    <v>18.4739</v>
     <v>94.51</v>
-    <v>93.79</v>
+    <v>93.16</v>
     <v>1739135000</v>
     <v>SCHW</v>
     <v>THE CHARLES SCHWAB CORPORATION (XNYS:SCHW)</v>
-    <v>3797322</v>
+    <v>4579242</v>
     <v>11848844</v>
     <v>1986</v>
   </rv>
@@ -7734,8 +7734,8 @@
     <v>1335</v>
     <v>771.66</v>
     <v>0.35620000000000002</v>
-    <v>-34.799999999999997</v>
-    <v>-4.1797000000000001E-2</v>
+    <v>-29.8</v>
+    <v>-3.5790999999999996E-2</v>
     <v>GBp</v>
     <v>The Sage Group plc is a United Kingdom-based company. It provides accounting, financial, human resources (HR) and payroll technology for small and mid-sized businesses. Its segments include North America, United Kingdom, Ireland, Africa and APAC (UKIA) and Europe. Its products include Sage Accounting, Payroll software, Sage Intacct, Sage X3, Sage HR, Sage People, Sage Earth, Sage Ai and Payments and Banking. Sage Accounting is designed to enable small businesses operating in any industry, and accountants and bookkeepers, to manage customer data, accounts, and people in a single solution. Sage Intacct helps growing mid-sized organizations thrive in with digital world with solutions across accounting, planning, and analytics. Sage People is an HR and people management solution for mid-sized businesses. Sage Payroll is an intuitive solution that helps small businesses to run their payroll reliably and flexibly. Sage People is an HR and people management solution for mid-sized businesses.</v>
     <v>11074</v>
@@ -7746,7 +7746,7 @@
     <v>830.2</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46191.61575680547</v>
+    <v>46191.650347222225</v>
     <v>245</v>
     <v>792.4</v>
     <v>10571700000</v>
@@ -7755,11 +7755,11 @@
     <v>827</v>
     <v>0</v>
     <v>832.6</v>
-    <v>797.8</v>
+    <v>802.8</v>
     <v>907731600</v>
     <v>SGE</v>
     <v>THE SAGE GROUP PLC. (XLON:SGE)</v>
-    <v>2458301</v>
+    <v>4109328</v>
     <v>3509250</v>
     <v>1988</v>
   </rv>
@@ -7785,8 +7785,8 @@
     <v>39.93</v>
     <v>8.3512000000000004</v>
     <v>3.3285999999999998</v>
-    <v>0.5</v>
-    <v>1.3899999999999999E-2</v>
+    <v>-0.27</v>
+    <v>-7.5060000000000005E-3</v>
     <v>USD</v>
     <v>SkyWater Technology, Inc. is an independent, pure-play technology foundry that offers advanced semiconductor development and manufacturing services. The Company’s Technology-as-a-Service (TaaS) model leverages a foundation of proprietary technology, engineering know-how capabilities, and microelectronics manufacturing capacity to co-develop process technology intellectual property (IP) with its customers that enable disruptive concepts through its Advanced Technology Services (ATS) for diverse microelectronics (integrated circuits (ICs)) and related micro- and nanotechnology applications. In addition to differentiated technology development services, it supports customers with volume production of ICs for high-growth markets through its Wafer Services. Its Wafer Services include the manufacture of silicon-based analog and mixed-signal ICs for its end markets. Through its ATS model, it specializes in co-creating advanced solutions with its customers that directly serve its end markets.</v>
     <v>1551</v>
@@ -7797,20 +7797,20 @@
     <v>36.950000000000003</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46191.626741296095</v>
+    <v>46191.666681990624</v>
     <v>248</v>
-    <v>35.4</v>
-    <v>1794491762</v>
+    <v>35.39</v>
+    <v>1756604220</v>
     <v>SKYWATER TECHNOLOGY, INC.</v>
     <v>SKYWATER TECHNOLOGY, INC.</v>
     <v>36.85</v>
-    <v>15.632899999999999</v>
+    <v>15.3028</v>
     <v>35.97</v>
-    <v>36.47</v>
+    <v>35.700000000000003</v>
     <v>49204600</v>
     <v>SKYT</v>
     <v>SKYWATER TECHNOLOGY, INC. (XNAS:SKYT)</v>
-    <v>192747</v>
+    <v>262504</v>
     <v>936048</v>
     <v>2016</v>
   </rv>
@@ -7836,8 +7836,8 @@
     <v>62.357999999999997</v>
     <v>19.48</v>
     <v>1.9728000000000001</v>
-    <v>2.4750000000000001</v>
-    <v>8.9093000000000006E-2</v>
+    <v>2.4249999999999998</v>
+    <v>8.7293000000000009E-2</v>
     <v>USD</v>
     <v>Super Micro Computer, Inc. is an application-optimized Total IT solutions provider including server, artificial intelligence (AI) systems, storage, Internet of Things (IoT) devices, switches, software, and support services. Total IT Solutions include complete servers, storage systems, modular blade servers, workstations, full-rack scale solutions, networking devices, server sub-systems, and server management. Its products are designed and manufactured in-house (in the United States, Taiwan, and the Netherlands). The Company's portfolio of Server Building Block Solutions allows customers to optimize for their exact workload and application by selecting from a broad family of systems built from the Company's flexible and reusable building blocks that support a comprehensive set of form factors, processors, memory, GPUs, storage, networking, power, and cooling solutions (air-conditioned, free air cooling or liquid cooling).</v>
     <v>6238</v>
@@ -7845,23 +7845,23 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>980 Rock Avenue, CA, 95131 US</v>
-    <v>30.355</v>
+    <v>30.45</v>
     <v>Computers, Phones &amp; Household Electronics</v>
     <v>Stock</v>
-    <v>46191.626779883591</v>
+    <v>46191.666727198441</v>
     <v>251</v>
     <v>28.28</v>
-    <v>19569914262</v>
+    <v>19537572642</v>
     <v>SUPER MICRO COMPUTER, INC.</v>
     <v>SUPER MICRO COMPUTER, INC.</v>
     <v>28.45</v>
-    <v>16.484999999999999</v>
+    <v>16.457799999999999</v>
     <v>27.78</v>
-    <v>30.254999999999999</v>
+    <v>30.204999999999998</v>
     <v>646832400</v>
     <v>SMCI</v>
     <v>SUPER MICRO COMPUTER, INC. (XNAS:SMCI)</v>
-    <v>24995053</v>
+    <v>31173785</v>
     <v>60254668</v>
     <v>2006</v>
   </rv>
@@ -7884,28 +7884,28 @@
     <v>17</v>
     <v>Finance</v>
     <v>18</v>
-    <v>658.1</v>
+    <v>659.16</v>
     <v>257.12</v>
     <v>1.5568</v>
-    <v>32.67</v>
-    <v>5.2358000000000002E-2</v>
+    <v>33.549999999999997</v>
+    <v>5.3768999999999997E-2</v>
     <v>USD</v>
     <v>Nasdaq Stock Market</v>
     <v>XNAS</v>
     <v>3.4999999999999996E-3</v>
-    <v>658.1</v>
+    <v>659.16</v>
     <v>ETF</v>
-    <v>46191.626762071093</v>
+    <v>46191.666710635938</v>
     <v>254</v>
     <v>648.15</v>
     <v>67822489502.050003</v>
     <v>VanEck:Semiconductor</v>
     <v>649.11</v>
     <v>623.97</v>
-    <v>656.64</v>
+    <v>657.52</v>
     <v>SMH</v>
     <v>VanEck:Semiconductor (XNAS:SMH)</v>
-    <v>2863491</v>
+    <v>3798335</v>
     <v>11005165</v>
   </rv>
   <rv s="2">
@@ -7930,8 +7930,8 @@
     <v>57.42</v>
     <v>8.85</v>
     <v>2.2564000000000002</v>
-    <v>1.23</v>
-    <v>0.11895600000000001</v>
+    <v>1.2099</v>
+    <v>0.117012</v>
     <v>USD</v>
     <v>NuScale Power Corporation is a provider of proprietary advanced small modular reactor (SMR) nuclear technology. The NuScale Power Module, the Company's SMR technology, is a small pressurized water reactor that can generate approximately 77 megawatts of electricity (MWe) or 250 megawatts thermal (gross) and can be scaled to meet customer needs through an array of flexible configurations of up to 924 MWe (12 modules) of output. In addition to the sale of NPMs, it offers a diversified suite of services throughout the development and operating life of the power plant. The Company's suite of services is planned to include licensing support, testing, training, fuel supply services and program management, among others. It serves a range of customers consisting of domestic and international governments, utilities, state-owned enterprises and technology and industrial companies in need of carbon-free, reliable energy.</v>
     <v>428</v>
@@ -7939,22 +7939,22 @@
     <v>XNYS</v>
     <v>XNYS</v>
     <v>1100 Ne Circle Blvd., Suite 350, CORVALLIS, OR, 97330 US</v>
-    <v>11.64</v>
+    <v>11.8</v>
     <v>Electrical Utilities &amp; IPPs</v>
     <v>Stock</v>
-    <v>46191.626766724221</v>
+    <v>46191.666722082809</v>
     <v>257</v>
     <v>10.455</v>
-    <v>4228617484</v>
+    <v>4221271311</v>
     <v>NUSCALE POWER CORPORATION</v>
     <v>NUSCALE POWER CORPORATION</v>
     <v>10.58</v>
     <v>10.34</v>
-    <v>11.57</v>
+    <v>11.549899999999999</v>
     <v>365481200</v>
     <v>SMR</v>
     <v>NUSCALE POWER CORPORATION (XNYS:SMR)</v>
-    <v>18048981</v>
+    <v>29185836</v>
     <v>35110520</v>
     <v>2022</v>
   </rv>
@@ -7976,8 +7976,8 @@
     <v>2189.6799999999998</v>
     <v>40.1</v>
     <v>2.7989999999999999</v>
-    <v>212.27</v>
-    <v>0.108367</v>
+    <v>215.2</v>
+    <v>0.109863</v>
     <v>USD</v>
     <v>SanDisk Corporation is a developer, manufacturer and provider of data storage devices and solutions based on NAND flash technology and has consumer brands and franchises globally. The Company's solutions include a range of solid state drives (SSDs) embedded products, removable cards, universal serial bus (USB) drives, and wafers and components. Its broad portfolio of technology and products addresses multiple end markets of Datacenter, Edge and Consumer. Its Datacenter end market is composed primarily of products for public or private cloud environments and enterprise customers. The Company, through the Edge end market, provides original equipment manufacturer and channel customers a broad array of high-performance flash solutions across personal computer, mobile, gaming, automotive, virtual reality headsets, at-home entertainment, and industrial spaces. The Company serves the Consumer end market with a broad range of retail and other end-user products.</v>
     <v>11000</v>
@@ -7988,19 +7988,19 @@
     <v>2189.6799999999998</v>
     <v>Computers, Phones &amp; Household Electronics</v>
     <v>Stock</v>
-    <v>46191.626764664063</v>
+    <v>46191.666748008596</v>
     <v>2029</v>
-    <v>321513322086</v>
+    <v>321947225200</v>
     <v>SANDISK CORPORATION</v>
     <v>SANDISK CORPORATION</v>
     <v>2041.76</v>
-    <v>76.755300000000005</v>
+    <v>76.858900000000006</v>
     <v>1958.8</v>
-    <v>2171.0700000000002</v>
+    <v>2174</v>
     <v>148089800</v>
     <v>SNDK</v>
     <v>SANDISK CORPORATION (XNAS:SNDK)</v>
-    <v>4640297</v>
+    <v>5638564</v>
     <v>11182489</v>
     <v>2024</v>
   </rv>
@@ -8026,8 +8026,8 @@
     <v>284.99</v>
     <v>118.3</v>
     <v>1.3683000000000001</v>
-    <v>-4.0650000000000004</v>
-    <v>-1.7333000000000001E-2</v>
+    <v>-4.9200999999999997</v>
+    <v>-2.0979000000000001E-2</v>
     <v>USD</v>
     <v>Snowflake Inc. is an artificial intelligence (AI) data cloud company. The Company provides a platform which powers the AI data cloud, enabling customers to consolidate data into a single source of truth to drive insights, apply AI to solve business problems, build data applications, and share data and data products. Its cloud-native architecture includes three independently scalable but logically integrated layers across storage, compute, and cloud services. The storage layer ingests massive amounts and varieties of structured, semi-structured, and unstructured data. The compute layer provides dedicated resources to enable users to simultaneously access common data sets for many use cases with minimal latency. The cloud services layer enables users to securely use AI within applications, tools, and processes. Its platform supports a wide range of product categories for customers’ business objectives, including analytics, data engineering, AI, applications and collaboration.</v>
     <v>9060</v>
@@ -8038,19 +8038,19 @@
     <v>232.92</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46191.626781029685</v>
+    <v>46191.666722245311</v>
     <v>262</v>
     <v>219.69</v>
-    <v>79875703000</v>
+    <v>79579325340</v>
     <v>SNOWFLAKE INC.</v>
     <v>SNOWFLAKE INC.</v>
     <v>232.41</v>
     <v>234.52</v>
-    <v>230.45500000000001</v>
+    <v>229.59989999999999</v>
     <v>346600000</v>
     <v>SNOW</v>
     <v>SNOWFLAKE INC. (XNYS:SNOW)</v>
-    <v>2884610</v>
+    <v>3432265</v>
     <v>10461462</v>
     <v>2012</v>
   </rv>
@@ -8076,8 +8076,8 @@
     <v>651.73</v>
     <v>376.18</v>
     <v>1.2148000000000001</v>
-    <v>-1.37</v>
-    <v>-2.967E-3</v>
+    <v>-2.97</v>
+    <v>-6.4320000000000002E-3</v>
     <v>USD</v>
     <v>Synopsys, Inc. is engaged in providing engineering solutions from silicon to systems, enabling customers to innovate artificial intelligence (AI)-powered products. It delivers silicon design, intellectual property (IP), simulation and analysis solutions, and design services. It supplies mission-critical electronic design automation (EDA) software that engineers use to design and test integrated circuits (ICs). Its Design Automation segment includes its silicon design, verification products and services, Ansys products, system integration products and services, digital, custom and field programmable gate array integrated circuit design software, verification software and hardware products, manufacturing software products and others. Its Design IP segment's portfolio includes logic libraries, embedded memories, interface IP, security IP, and subsystems that serve companies in the semiconductor and electronics industries.</v>
     <v>28000</v>
@@ -8088,20 +8088,20 @@
     <v>466.05900000000003</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46191.626777279685</v>
+    <v>46191.666738089843</v>
     <v>265</v>
     <v>454</v>
-    <v>88151325341</v>
+    <v>87844958461</v>
     <v>SYNOPSYS, INC.</v>
     <v>SYNOPSYS, INC.</v>
     <v>461.99</v>
-    <v>106.6931</v>
+    <v>106.3223</v>
     <v>461.74</v>
-    <v>460.37</v>
+    <v>458.77</v>
     <v>191479300</v>
     <v>SNPS</v>
     <v>SYNOPSYS, INC. (XNAS:SNPS)</v>
-    <v>533604</v>
+    <v>666045</v>
     <v>2008238</v>
     <v>1987</v>
   </rv>
@@ -8127,8 +8127,8 @@
     <v>22.17</v>
     <v>5.83</v>
     <v>2.8132000000000001</v>
-    <v>3.5000000000000003E-2</v>
-    <v>5.0290000000000005E-3</v>
+    <v>-0.02</v>
+    <v>-2.8739999999999998E-3</v>
     <v>USD</v>
     <v>SoundHound AI, Inc. is engaged in conversational intelligence, offering voice and conversational artificial intelligence (AI) solutions that let businesses offer experiences to their customers. Through its proprietary technology, its voice AI delivers speed and accuracy in numerous languages to product creators and service providers across retail, financial services, healthcare, automotive, smart devices, and restaurants via AI-driven products, such as Smart Answering, Smart Ordering, Dynamic Drive Thru, and Amelia AI Agents. Along with SoundHound Chat AI, a voice assistant with integrated Generative AI, it powers various products and services, and processes billions of interactions each year for businesses. Its developer platform, Houndify, is an open-access platform that allows developers to leverage its Voice AI technology and a library of over 100 content domains, including commonly used domains for points of interest, weather, flight status, sports and more.</v>
     <v>954</v>
@@ -8139,20 +8139,20 @@
     <v>7.0650000000000004</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46191.626772395313</v>
+    <v>46191.666715740626</v>
     <v>268</v>
     <v>6.8550000000000004</v>
-    <v>3027223352</v>
+    <v>3003421024</v>
     <v>SOUNDHOUND AI, INC.</v>
     <v>SOUNDHOUND AI, INC.</v>
     <v>7.03</v>
     <v>0</v>
     <v>6.96</v>
-    <v>6.9950000000000001</v>
+    <v>6.94</v>
     <v>432769600</v>
     <v>SOUN</v>
     <v>SOUNDHOUND AI, INC. (XNAS:SOUN)</v>
-    <v>6064623</v>
+    <v>9052190</v>
     <v>25736921</v>
     <v>2020</v>
   </rv>
@@ -8175,28 +8175,28 @@
     <v>17</v>
     <v>Finance</v>
     <v>18</v>
-    <v>638</v>
+    <v>639.59</v>
     <v>221.86</v>
     <v>1.7036</v>
-    <v>37.130000000000003</v>
-    <v>6.1910999999999994E-2</v>
+    <v>38.159999999999997</v>
+    <v>6.3628999999999991E-2</v>
     <v>USD</v>
     <v>Nasdaq Stock Market</v>
     <v>XNAS</v>
     <v>3.4000000000000002E-3</v>
-    <v>638</v>
+    <v>639.59</v>
     <v>ETF</v>
-    <v>46191.626784698441</v>
+    <v>46191.666730323435</v>
     <v>271</v>
     <v>626.16</v>
     <v>38373488686.160004</v>
     <v>iShares:Semiconductor</v>
     <v>627.42999999999995</v>
     <v>599.73</v>
-    <v>636.86</v>
+    <v>637.89</v>
     <v>SOXX</v>
     <v>iShares:Semiconductor (XNAS:SOXX)</v>
-    <v>3552366</v>
+    <v>4733482</v>
     <v>10558398</v>
   </rv>
   <rv s="2">
@@ -8221,25 +8221,25 @@
     <v>760.4</v>
     <v>591.89</v>
     <v>0.99870000000000003</v>
-    <v>7.3884999999999996</v>
-    <v>9.9970000000000007E-3</v>
+    <v>7.3135000000000003</v>
+    <v>9.8960000000000003E-3</v>
     <v>USD</v>
     <v>NYSE Arca</v>
     <v>ARCX</v>
     <v>9.4499999999999998E-4</v>
     <v>748.18</v>
     <v>ETF</v>
-    <v>46191.626796562501</v>
+    <v>46191.666716770313</v>
     <v>274</v>
     <v>743.86</v>
     <v>783796407176.76001</v>
     <v>State Street SPDR S&amp;P500</v>
     <v>747.6</v>
     <v>739.05650000000003</v>
-    <v>746.44500000000005</v>
+    <v>746.37</v>
     <v>SPY</v>
     <v>State Street SPDR S&amp;P500 (ARCX:SPY)</v>
-    <v>17628866</v>
+    <v>31426376</v>
     <v>53721970</v>
   </rv>
   <rv s="2">
@@ -8264,8 +8264,8 @@
     <v>90.9</v>
     <v>51.93</v>
     <v>1.4954000000000001</v>
-    <v>1.4</v>
-    <v>2.0178999999999999E-2</v>
+    <v>1.33</v>
+    <v>1.917E-2</v>
     <v>USD</v>
     <v>Skyworks Solutions, Inc. provides wireless networking services. The Company’s analog and mixed-signal semiconductors are connecting people, places, and things, spanning a number of new applications within the aerospace, automotive, broadband, cellular infrastructure, connected home, defense, entertainment and gaming, industrial, medical, smartphone, tablet, and wearable markets. It operates engineering, manufacturing, sales, and service facilities throughout Asia, Europe, and North America. The Company offers a range of products, such as Amplifiers, Attenuators, Diodes, Audio And Radio, Clocks And Timing, Front-End Modules, Isolation, Modems And DAAs, Optocouplers, Power Management, Power Over Ethernet, RF Passives, Television (TV) And Video, Switches, and Voice. Its engineering, marketing, operations, sales, and support facilities are located throughout Asia, Europe, and North America.</v>
     <v>10000</v>
@@ -8276,20 +8276,20 @@
     <v>71.650000000000006</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46191.62673560156</v>
+    <v>46191.666697476561</v>
     <v>277</v>
     <v>68.487099999999998</v>
-    <v>10645729602</v>
+    <v>10635201189</v>
     <v>SKYWORKS SOLUTIONS, INC.</v>
     <v>SKYWORKS SOLUTIONS, INC.</v>
     <v>71.41</v>
-    <v>27.963000000000001</v>
+    <v>27.935400000000001</v>
     <v>69.38</v>
-    <v>70.78</v>
+    <v>70.709999999999994</v>
     <v>150405900</v>
     <v>SWKS</v>
     <v>SKYWORKS SOLUTIONS, INC. (XNAS:SWKS)</v>
-    <v>1522803</v>
+    <v>2112415</v>
     <v>4976951</v>
     <v>2002</v>
   </rv>
@@ -8315,8 +8315,8 @@
     <v>87.88</v>
     <v>30.7</v>
     <v>1.9573</v>
-    <v>1.1100000000000001</v>
-    <v>2.7633000000000001E-2</v>
+    <v>0.81</v>
+    <v>2.0164000000000001E-2</v>
     <v>USD</v>
     <v>Symbotic Inc. is an automation technology company, which focuses on reimagining the supply chain with its end-to-end, artificial intelligence-powered robotic and software platform. It is engaged in developing, commercializing, and deploying innovative and comprehensive technology solutions that improve supply chain operations. The Company automates the processing of pallets, cases and individual items in warehouses. Its systems enhance operations at the front end of the supply chain and therefore benefit all supply partners further down the chain, irrespective of fulfillment strategy. Its robotic-based automation systems, which include hardware and essential software, move, store and sort cases and reach in warehouses. Its systems are operational in a number of retailers, including Walmart, wholesale distributors, including C&amp;S Wholesale Grocers, and are being deployed in GreenBox Systems LLC, which is doing business as Exol (Exol), its warehouse-as-a-service joint venture.</v>
     <v>2000</v>
@@ -8324,23 +8324,23 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>200 Research Drive, WILMINGTON, MA, 01887 US</v>
-    <v>41.39</v>
+    <v>41.61</v>
     <v>Machinery, Equipment &amp; Components</v>
     <v>Stock</v>
-    <v>46191.626782048435</v>
+    <v>46191.666707245313</v>
     <v>280</v>
     <v>39.94</v>
-    <v>24879736704</v>
+    <v>24698924664</v>
     <v>SYMBOTIC INC.</v>
     <v>SYMBOTIC INC.</v>
     <v>40.770000000000003</v>
     <v>0</v>
     <v>40.17</v>
-    <v>41.28</v>
+    <v>40.98</v>
     <v>602706800</v>
     <v>SYM</v>
     <v>SYMBOTIC INC. (XNAS:SYM)</v>
-    <v>531617</v>
+    <v>713741</v>
     <v>2577977</v>
     <v>2022</v>
   </rv>
@@ -8362,8 +8362,8 @@
     <v>104.32</v>
     <v>41.73</v>
     <v>3.121</v>
-    <v>1.7314000000000001</v>
-    <v>3.5487000000000005E-2</v>
+    <v>0.54</v>
+    <v>1.1068E-2</v>
     <v>USD</v>
     <v>Tempus AI, Inc. is a technology company advancing precision medicine through the practical application of artificial intelligence in healthcare. It offers AI-enabled precision medicine solutions to physicians to deliver personalized patient care and, in parallel, facilitates discovery, development and delivery of optimal therapeutics. It provides three product lines: Genomics, Data and artificial intelligence applications (AI). The Genomics product line leverages its laboratories to provide next generation sequencing (NGS) diagnostics, polymerase chain reaction, profiling, molecular genotyping and other anatomic and molecular pathology testing. The data generated in its lab or ingested into its platform is structured and de-identified, prior to commercialization. Its AI Applications is focused on developing and providing diagnostics that are algorithmic in nature, implementing new software as a medical device, and building and deploying clinical decision support tools.</v>
     <v>3800</v>
@@ -8374,19 +8374,19 @@
     <v>50.854999999999997</v>
     <v>Biotechnology &amp; Medical Research</v>
     <v>Stock</v>
-    <v>46191.626772557815</v>
+    <v>46191.666737846877</v>
     <v>49.06</v>
-    <v>9071865086</v>
+    <v>8857931584</v>
     <v>TEMPUS AI, INC.</v>
     <v>TEMPUS AI, INC.</v>
     <v>49.85</v>
     <v>0</v>
     <v>48.79</v>
-    <v>50.5214</v>
+    <v>49.33</v>
     <v>179564800</v>
     <v>TEM</v>
     <v>TEMPUS AI, INC. (XNAS:TEM)</v>
-    <v>1398970</v>
+    <v>1927068</v>
     <v>6936860</v>
     <v>2025</v>
   </rv>
@@ -8412,8 +8412,8 @@
     <v>440.74990000000003</v>
     <v>84.240099999999998</v>
     <v>1.7634000000000001</v>
-    <v>23.08</v>
-    <v>5.6491E-2</v>
+    <v>22.16</v>
+    <v>5.4238999999999996E-2</v>
     <v>USD</v>
     <v>Teradyne, Inc. is a global supplier of automated test equipment and robotics solutions. It designs, develops, manufactures and sells automated test systems and robotics products. Its segment includes Semiconductor Test, Robotics, and Product Test. The Semiconductor Test segment includes operations related to the design, manufacturing and marketing of semiconductor test products and services, inclusive of storage and system level test products. The Robotics segment includes operations related to the design, manufacturing and marketing of collaborative robotic arms and autonomous mobile robots. The Product Test segment includes operations related to the design, manufacturing and marketing of products and services for defense/aerospace test, circuit-board test, wireless test systems, and silicon photonics testing. Its offerings also include defense/aerospace test instrumentation and systems, circuit-board test and inspection (production board test) systems, and wireless test systems.</v>
     <v>6600</v>
@@ -8421,23 +8421,23 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>600 Riverpark Dr, NORTH READING, MA, 01864-2634 US</v>
-    <v>434.8999</v>
+    <v>435</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46191.626776527344</v>
+    <v>46191.666725682815</v>
     <v>285</v>
     <v>423.58</v>
-    <v>67569875208</v>
+    <v>67425856384</v>
     <v>TERADYNE, INC.</v>
     <v>TERADYNE, INC.</v>
     <v>423.58</v>
-    <v>79.887500000000003</v>
+    <v>79.717200000000005</v>
     <v>408.56</v>
-    <v>431.64</v>
+    <v>430.72</v>
     <v>156542200</v>
     <v>TER</v>
     <v>TERADYNE, INC. (XNAS:TER)</v>
-    <v>895514</v>
+    <v>1221009</v>
     <v>3700271</v>
     <v>1960</v>
   </rv>
@@ -8463,8 +8463,8 @@
     <v>498.83</v>
     <v>288.77010000000001</v>
     <v>1.8129999999999999</v>
-    <v>-7.73</v>
-    <v>-1.9501000000000001E-2</v>
+    <v>-5.5698999999999996</v>
+    <v>-1.4052E-2</v>
     <v>USD</v>
     <v>Tesla, Inc. designs, develops, manufactures, sells and leases high-performance fully electric vehicles and energy generation and storage systems, and offers services related to its products. Its segments include automotive, and energy generation and storage. The automotive segment includes the design, development, manufacturing, sales and leasing of high-performance fully electric vehicles, and sales of automotive regulatory credits. It also includes sales of used vehicles, non-warranty maintenance services and collisions, part sales, paid supercharging, insurance services revenue and retail merchandise sales. The energy generation and storage segment include the design, manufacture, installation, sales and leasing of solar energy generation and energy storage products and related services and sales of solar energy systems incentives. Its consumer vehicles include the Model 3, Y, S, X and Cybertruck. Its lithium-ion battery energy storage products include Powerwall and Megapack.</v>
     <v>134785</v>
@@ -8475,20 +8475,20 @@
     <v>399</v>
     <v>Automobiles &amp; Auto Parts</v>
     <v>Stock</v>
-    <v>46191.626782661719</v>
+    <v>46191.666741770314</v>
     <v>288</v>
     <v>384.7</v>
-    <v>1459662132600</v>
+    <v>1467774872012</v>
     <v>TESLA, INC.</v>
     <v>TESLA, INC.</v>
     <v>398.56</v>
-    <v>355.2235</v>
+    <v>357.19779999999997</v>
     <v>396.38</v>
-    <v>388.65</v>
+    <v>390.81009999999998</v>
     <v>3755724000</v>
     <v>TSLA</v>
     <v>TESLA, INC. (XNAS:TSLA)</v>
-    <v>19208972</v>
+    <v>25011060</v>
     <v>47684409</v>
     <v>2024</v>
   </rv>
@@ -8514,8 +8514,8 @@
     <v>454.21339999999998</v>
     <v>206.20150000000001</v>
     <v>1.3808</v>
-    <v>20.059999999999999</v>
-    <v>4.6418999999999995E-2</v>
+    <v>21.614999999999998</v>
+    <v>5.0016999999999999E-2</v>
     <v>USD</v>
     <v>Taiwan Semiconductor Manufacturing Co Ltd is a Taiwan-based integrated circuit foundry service provider. The Company is primarily engaged in integrated circuit manufacturing services. It offers advanced process technologies, specialised process solutions, advanced photomask and silicon stacking, and packaging-related technologies, while supporting a comprehensive design ecosystem. The Company's products serve diverse electronic sectors including artificial intelligence, high-performance computing, wired and wireless communications, automotive and industrial equipment, personal computing, information applications, consumer electronics, smart internet of things, and wearable devices.</v>
     <v>52045</v>
@@ -8526,20 +8526,20 @@
     <v>454.21339999999998</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46191.626763610941</v>
+    <v>46191.666734050785</v>
     <v>291</v>
     <v>438.5</v>
-    <v>2345375407540</v>
+    <v>2353440374610</v>
     <v>Taiwan Semiconductor Manufacturing Company Limited</v>
     <v>Taiwan Semiconductor Manufacturing Company Limited</v>
     <v>439.02</v>
-    <v>38.261000000000003</v>
+    <v>38.392499999999998</v>
     <v>432.15</v>
-    <v>452.21</v>
+    <v>453.76499999999999</v>
     <v>5186474000</v>
     <v>TSM</v>
     <v>Taiwan Semiconductor Manufacturing Company Limited (XNYS:TSM)</v>
-    <v>4907771</v>
+    <v>6474052</v>
     <v>12517258</v>
     <v>1987</v>
   </rv>
@@ -8565,8 +8565,8 @@
     <v>238.47989999999999</v>
     <v>91.84</v>
     <v>1.3725000000000001</v>
-    <v>-2.74</v>
-    <v>-1.4565999999999999E-2</v>
+    <v>-3.14</v>
+    <v>-1.6691999999999999E-2</v>
     <v>USD</v>
     <v>Twilio Inc. provides a customer engagement platform to build direct, personalized relationships with their customers everywhere in the world. Its platform provides developers with tools to build, scale, and deploy real-time communications within software applications. Its segments include Twilio Communications (Communications) and Twilio Segment (Segment). The Communications segment consists of a variety of application programming interfaces (APIs) and software solutions to optimize communications between its customers and their end users. Its key offerings in its Communications segment include Messaging, Voice, Email (includes Marketing Campaigns), Flex and User Authentication and Identity. Its Twilio Flex is a digital engagement center for the entire customer journey. Twilio Segment is a customer data platform that provides businesses with the tools to harness the power of contextual data by unifying real-time information collected throughout each customer’s journey into a profile.</v>
     <v>5558</v>
@@ -8577,20 +8577,20 @@
     <v>188.8373</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46191.626763714841</v>
+    <v>46191.66669255781</v>
     <v>294</v>
     <v>179.35</v>
-    <v>28134327843</v>
+    <v>28073618283</v>
     <v>TWILIO INC.</v>
     <v>TWILIO INC.</v>
     <v>186.42</v>
-    <v>288.15480000000002</v>
+    <v>287.53300000000002</v>
     <v>188.11</v>
-    <v>185.37</v>
+    <v>184.97</v>
     <v>151773900</v>
     <v>TWLO</v>
     <v>TWILIO INC. (XNYS:TWLO)</v>
-    <v>749741</v>
+    <v>963481</v>
     <v>2795770</v>
     <v>2008</v>
   </rv>
@@ -8616,8 +8616,8 @@
     <v>379.935</v>
     <v>110.06</v>
     <v>2.0335000000000001</v>
-    <v>17.25</v>
-    <v>5.4317000000000004E-2</v>
+    <v>15.89</v>
+    <v>5.0034999999999996E-2</v>
     <v>USD</v>
     <v>Vertiv Holdings Co. provides mission-critical digital infrastructure technologies and lifecycle services primarily for data centers, communication networks, and commercial and industrial environments. The Company operates in three business segments: the Americas; Asia Pacific, and Europe, Middle East &amp; Africa. The Company's offerings include alternate current (AC) and direct current (DC) power management, thermal management, low/medium voltage switchgear, busbar, air cooled and liquid cooled thermal management products, integrated modular solutions, racks, single phase UPS, rack power distribution, rack thermal systems, configurable integrated solutions, energy storage solutions, hardware, software for managing IT equipment, management systems for monitoring and controlling digital infrastructure, and services. It also provides preventative maintenance, acceptance testing, engineering and consulting, remote monitoring, training, spare parts, specialized fluid management, and others.</v>
     <v>34000</v>
@@ -8628,20 +8628,20 @@
     <v>337.76</v>
     <v>Machinery, Equipment &amp; Components</v>
     <v>Stock</v>
-    <v>46191.626791423434</v>
+    <v>46191.666718599219</v>
     <v>297</v>
     <v>326.5</v>
-    <v>128611149504</v>
+    <v>128088761536</v>
     <v>VERTIV HOLDINGS CO</v>
     <v>VERTIV HOLDINGS CO</v>
     <v>331.23</v>
-    <v>84.064800000000005</v>
+    <v>83.723299999999995</v>
     <v>317.58</v>
-    <v>334.83</v>
+    <v>333.47</v>
     <v>384108800</v>
     <v>VRT</v>
     <v>VERTIV HOLDINGS CO (XNYS:VRT)</v>
-    <v>2581030</v>
+    <v>3193002</v>
     <v>5935867</v>
     <v>2016</v>
   </rv>
@@ -8667,8 +8667,8 @@
     <v>249.85</v>
     <v>110.36</v>
     <v>1.1133999999999999</v>
-    <v>-2.0699999999999998</v>
-    <v>-1.6990999999999999E-2</v>
+    <v>-3.18</v>
+    <v>-2.6102E-2</v>
     <v>USD</v>
     <v>Workday, Inc. is an enterprise artificial intelligence (AI) platform for managing people, money, and agents. The Company provides organizations with cloud solutions powered by artificial intelligence (AI) to solve business challenges, including supporting and empowering the workforce, managing finances and spending. It offers a suite of cloud-based enterprise solutions that address the needs of the C-suite on a platform designed to be open, extensible, and configurable, allowing integration with other applications and the ability for customers and partners to build custom applications. It offers Workday Build, which is an open developer platform that provides customers and partners with the ability to create and share AI-powered solutions. It serves financial services, government, healthcare, higher education, hospitality, manufacturing, professional and business services, retail, technology and media, and transportation.</v>
     <v>20834</v>
@@ -8679,20 +8679,20 @@
     <v>121.795</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46191.626787117966</v>
+    <v>46191.666725682815</v>
     <v>300</v>
     <v>117.5</v>
-    <v>29580720000</v>
+    <v>29306550000</v>
     <v>WORKDAY, INC.</v>
     <v>WORKDAY, INC.</v>
     <v>119.74</v>
-    <v>37.384099999999997</v>
+    <v>37.037599999999998</v>
     <v>121.83</v>
-    <v>119.76</v>
+    <v>118.65</v>
     <v>247000000</v>
     <v>WDAY</v>
     <v>WORKDAY, INC. (XNAS:WDAY)</v>
-    <v>1568263</v>
+    <v>2029123</v>
     <v>5594295</v>
     <v>2012</v>
   </rv>
@@ -8718,8 +8718,8 @@
     <v>336.99</v>
     <v>114.625</v>
     <v>0.98329999999999995</v>
-    <v>-0.86499999999999999</v>
-    <v>-6.9540000000000001E-3</v>
+    <v>-1.65</v>
+    <v>-1.3266E-2</v>
     <v>USD</v>
     <v>Zscaler, Inc. is a cloud security company. The Company has developed a platform incorporating core security functionalities needed to enable fast and secure access to cloud resources based on identity, context and an organization's policies. Its Zscaler Zero Trust Exchange is a cloud-native platform that securely connects users, devices, applications and workloads, including artificial intelligence (AI) agents, without relying on hub-and-spoke network architecture and firewall-centric security. It delivers its solutions using a software-as-a-service (SaaS) business model and sells subscriptions to customers to access its cloud platform, together with related support services. Its services include Zscaler Internet Access (ZIA), Zscaler Private Access (ZPA), and Zscaler Digital Experience (ZDX). ZIA provides secure access to externally managed applications, including SaaS applications and internet destinations, regardless of device, location or network.</v>
     <v>7923</v>
@@ -8730,20 +8730,20 @@
     <v>124.45</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46191.626774698438</v>
+    <v>46191.666726689065</v>
     <v>303</v>
     <v>119.9</v>
-    <v>19973548892</v>
+    <v>19846606935</v>
     <v>ZSCALER, INC.</v>
     <v>ZSCALER, INC.</v>
     <v>123.34</v>
     <v>0</v>
     <v>124.38</v>
-    <v>123.515</v>
+    <v>122.73</v>
     <v>161709500</v>
     <v>ZS</v>
     <v>ZSCALER, INC. (XNAS:ZS)</v>
-    <v>1312358</v>
+    <v>1614742</v>
     <v>6775940</v>
     <v>2007</v>
   </rv>
@@ -8764,18 +8764,18 @@
     <v>32</v>
     <v>0.76859999999999995</v>
     <v>0.72099999999999997</v>
-    <v>2.5539999999999998E-3</v>
-    <v>3.3960000000000001E-3</v>
+    <v>3.8089999999999999E-3</v>
+    <v>5.0639999999999999E-3</v>
     <v>GBP</v>
     <v>USD</v>
     <v>0.75719999999999998</v>
     <v>Currency Pair</v>
-    <v>46191.626770833333</v>
+    <v>46191.66673611111</v>
     <v>0.75049999999999994</v>
     <v>US Dollar/UK Pound Sterling FX Cross Rate</v>
     <v>0.75270000000000004</v>
     <v>0.75209999999999999</v>
-    <v>0.75470000000000004</v>
+    <v>0.75590000000000002</v>
     <v>USDGBP</v>
     <v>USD/GBP</v>
   </rv>
@@ -10148,7 +10148,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{F82495E7-9F34-4C1F-83EC-FA45D59FA2BD}" name="tblContributions" displayName="tblContributions" ref="A1:C2" totalsRowShown="0">
   <autoFilter ref="A1:C2" xr:uid="{F82495E7-9F34-4C1F-83EC-FA45D59FA2BD}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{EAE9033F-E950-4D8F-AC60-78CCDA7A0C9E}" name="DATE" dataDxfId="41"/>
+    <tableColumn id="1" xr3:uid="{EAE9033F-E950-4D8F-AC60-78CCDA7A0C9E}" name="DATE" dataDxfId="24"/>
     <tableColumn id="2" xr3:uid="{1D40F1FF-D66C-4703-9DEC-93C768793D8F}" name="AMMOUNT"/>
     <tableColumn id="3" xr3:uid="{49855D82-DE07-4257-837D-DD0BE41E988B}" name="Notes"/>
   </tableColumns>
@@ -10192,64 +10192,64 @@
   <tableColumns count="31">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="symbol"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="StockName"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="LastTradeTime" dataDxfId="40">
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="LastTradeTime" dataDxfId="23">
       <calculatedColumnFormula array="1">_FV(B2,"Last trade time",TRUE)</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="TradeCurrency">
       <calculatedColumnFormula array="1">_FV(B2,"Currency")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="StockPrice" dataDxfId="39">
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="StockPrice" dataDxfId="22">
       <calculatedColumnFormula array="1">_FV(B2,"Price")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="ChangePercent" dataDxfId="38">
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="ChangePercent" dataDxfId="21">
       <calculatedColumnFormula array="1">_FV(B2,"Change (%)",TRUE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Change" dataDxfId="37">
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Change" dataDxfId="20">
       <calculatedColumnFormula array="1">_FV(B2,"Change")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="P/E" dataDxfId="36">
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="P/E" dataDxfId="19">
       <calculatedColumnFormula array="1">_FV(B2,"P/E",TRUE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Beta" dataDxfId="35">
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Beta" dataDxfId="18">
       <calculatedColumnFormula array="1">_FV(B2,"Beta")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="52WkHigh" dataDxfId="34">
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="52WkHigh" dataDxfId="17">
       <calculatedColumnFormula array="1">_FV(B2,"52 week high",TRUE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="52WkLow" dataDxfId="33">
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="52WkLow" dataDxfId="16">
       <calculatedColumnFormula array="1">_FV(B2,"52 week low",TRUE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="DayHigh" dataDxfId="32">
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="DayHigh" dataDxfId="15">
       <calculatedColumnFormula array="1">_FV(B2,"High")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="DayLow" dataDxfId="31">
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="DayLow" dataDxfId="14">
       <calculatedColumnFormula array="1">_FV(B2,"Low")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="Open" dataDxfId="30">
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="Open" dataDxfId="13">
       <calculatedColumnFormula array="1">_FV(B2,"Open")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="PreviousClose" dataDxfId="29">
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="PreviousClose" dataDxfId="12">
       <calculatedColumnFormula array="1">_FV(B2,"Previous close",TRUE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Volume" dataDxfId="28">
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Volume" dataDxfId="11">
       <calculatedColumnFormula array="1">_FV(B2,"Volume")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="AverageVolume" dataDxfId="27">
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="AverageVolume" dataDxfId="10">
       <calculatedColumnFormula array="1">_FV(B2,"Volume average",TRUE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="YearIncorported" dataDxfId="26">
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="YearIncorported" dataDxfId="9">
       <calculatedColumnFormula array="1">_FV(B2,"Year incorporated",TRUE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="Employees" dataDxfId="25">
+    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="Employees" dataDxfId="8">
       <calculatedColumnFormula array="1">_FV(B2,"Employees")</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="Industry">
       <calculatedColumnFormula array="1">_FV(B2,"Industry")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0000-000015000000}" name="MarketCap" dataDxfId="24">
+    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0000-000015000000}" name="MarketCap" dataDxfId="7">
       <calculatedColumnFormula array="1">_FV(B2,"Market cap",TRUE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0000-000016000000}" name="SharesOutstanding" dataDxfId="23">
+    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0000-000016000000}" name="SharesOutstanding" dataDxfId="6">
       <calculatedColumnFormula array="1">_FV(B2,"Shares outstanding",TRUE)</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="23" xr3:uid="{00000000-0010-0000-0000-000017000000}" name="50SMA"/>
@@ -10267,37 +10267,37 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{D39CE96F-8D2C-4A60-A43A-B3602E27FDC2}" name="tblHoldings" displayName="tblHoldings" ref="A1:N9" totalsRowShown="0" headerRowDxfId="22" dataDxfId="21" tableBorderDxfId="20">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{D39CE96F-8D2C-4A60-A43A-B3602E27FDC2}" name="tblHoldings" displayName="tblHoldings" ref="A1:N9" totalsRowShown="0" headerRowDxfId="41" dataDxfId="40" tableBorderDxfId="39">
   <autoFilter ref="A1:N9" xr:uid="{D39CE96F-8D2C-4A60-A43A-B3602E27FDC2}"/>
   <tableColumns count="14">
-    <tableColumn id="1" xr3:uid="{AE3CE10F-629F-414E-93DE-8949C4E58E7D}" name="Symbol" dataDxfId="19"/>
-    <tableColumn id="2" xr3:uid="{40700DF4-EB97-4DB9-BA32-772C3F8E34CC}" name="StockName" dataDxfId="18"/>
-    <tableColumn id="3" xr3:uid="{BED1527E-0498-4FF1-8E69-ECDB2EB30C25}" name="TradeCurrency" dataDxfId="17">
+    <tableColumn id="1" xr3:uid="{AE3CE10F-629F-414E-93DE-8949C4E58E7D}" name="Symbol" dataDxfId="38"/>
+    <tableColumn id="2" xr3:uid="{40700DF4-EB97-4DB9-BA32-772C3F8E34CC}" name="StockName" dataDxfId="37"/>
+    <tableColumn id="3" xr3:uid="{BED1527E-0498-4FF1-8E69-ECDB2EB30C25}" name="TradeCurrency" dataDxfId="36">
       <calculatedColumnFormula>_FV(B2,"Currency")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{2218CAC2-8A57-48EA-B1D3-CD7E0BA08ECA}" name="TotalBought" dataDxfId="16"/>
-    <tableColumn id="5" xr3:uid="{77160EAF-769F-4559-B5AE-C08A0AC76566}" name="TotalSold" dataDxfId="15"/>
-    <tableColumn id="6" xr3:uid="{324BA50C-3A95-4946-A384-C4EF731BD7F3}" name="NetPosition" dataDxfId="14"/>
-    <tableColumn id="7" xr3:uid="{24A211AE-9FE1-4D72-98D4-96F240F7DCFD}" name="AvgCost" dataDxfId="13"/>
-    <tableColumn id="8" xr3:uid="{E1C8BF44-8957-447E-B3C1-A76A00A619B8}" name="AvgBuyCost" dataDxfId="12">
+    <tableColumn id="4" xr3:uid="{2218CAC2-8A57-48EA-B1D3-CD7E0BA08ECA}" name="TotalBought" dataDxfId="35"/>
+    <tableColumn id="5" xr3:uid="{77160EAF-769F-4559-B5AE-C08A0AC76566}" name="TotalSold" dataDxfId="34"/>
+    <tableColumn id="6" xr3:uid="{324BA50C-3A95-4946-A384-C4EF731BD7F3}" name="NetPosition" dataDxfId="33"/>
+    <tableColumn id="7" xr3:uid="{24A211AE-9FE1-4D72-98D4-96F240F7DCFD}" name="AvgCost" dataDxfId="32"/>
+    <tableColumn id="8" xr3:uid="{E1C8BF44-8957-447E-B3C1-A76A00A619B8}" name="AvgBuyCost" dataDxfId="31">
       <calculatedColumnFormula>F2*G2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{73ED87C5-FB66-49D5-B1EF-4BE32DC6D51F}" name="StockPrice" dataDxfId="11">
+    <tableColumn id="9" xr3:uid="{73ED87C5-FB66-49D5-B1EF-4BE32DC6D51F}" name="StockPrice" dataDxfId="30">
       <calculatedColumnFormula>_FV(B2,"Price")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{1E08B942-A194-43F5-A7DB-404EC54A5C02}" name="FXRate" dataDxfId="10">
+    <tableColumn id="10" xr3:uid="{1E08B942-A194-43F5-A7DB-404EC54A5C02}" name="FXRate" dataDxfId="29">
       <calculatedColumnFormula>Config!$C$1</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{42171935-FB72-4173-A1EB-132DDE8201DD}" name="ChangePercent" dataDxfId="9">
+    <tableColumn id="14" xr3:uid="{42171935-FB72-4173-A1EB-132DDE8201DD}" name="ChangePercent" dataDxfId="28">
       <calculatedColumnFormula array="1">_FV(B2,"Change (%)",TRUE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{96D6E4C8-F5BD-4A3E-88A2-BF403C882136}" name="MarketValue" dataDxfId="8">
+    <tableColumn id="11" xr3:uid="{96D6E4C8-F5BD-4A3E-88A2-BF403C882136}" name="MarketValue" dataDxfId="27">
       <calculatedColumnFormula>F2*I2*J2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{E928C781-D2C4-42A1-A053-38B541581BCB}" name="P&amp;L" dataDxfId="7">
+    <tableColumn id="12" xr3:uid="{E928C781-D2C4-42A1-A053-38B541581BCB}" name="P&amp;L" dataDxfId="26">
       <calculatedColumnFormula>L2-H2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{53BE744D-B35A-4E6B-8EA9-E422203F974E}" name="P&amp;LPercent" dataDxfId="6">
+    <tableColumn id="13" xr3:uid="{53BE744D-B35A-4E6B-8EA9-E422203F974E}" name="P&amp;LPercent" dataDxfId="25">
       <calculatedColumnFormula>IF(H2=0,"",M2/H2)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -14049,7 +14049,7 @@
       </c>
       <c r="C2" s="2">
         <f t="array" aca="1" ref="C2" ca="1">_FV(B2,"Last trade time",TRUE)</f>
-        <v>46191.626761168751</v>
+        <v>46191.666718981251</v>
       </c>
       <c r="D2" t="str">
         <f t="array" aca="1" ref="D2" ca="1">_FV(B2,"Currency")</f>
@@ -14057,15 +14057,15 @@
       </c>
       <c r="E2" s="3">
         <f t="array" aca="1" ref="E2" ca="1">_FV(B2,"Price")</f>
-        <v>171.72499999999999</v>
+        <v>165.18</v>
       </c>
       <c r="F2" s="4">
         <f t="array" aca="1" ref="F2" ca="1">_FV(B2,"Change (%)",TRUE)</f>
-        <v>2.6204000000000002E-2</v>
+        <v>-1.2907999999999999E-2</v>
       </c>
       <c r="G2" s="5">
         <f t="array" aca="1" ref="G2" ca="1">_FV(B2,"Change")</f>
-        <v>4.3849999999999998</v>
+        <v>-2.16</v>
       </c>
       <c r="H2" s="6">
         <f t="array" aca="1" ref="H2" ca="1">_FV(B2,"P/E",TRUE)</f>
@@ -14101,7 +14101,7 @@
       </c>
       <c r="P2" s="7">
         <f t="array" aca="1" ref="P2" ca="1">_FV(B2,"Volume")</f>
-        <v>6505373</v>
+        <v>8405885</v>
       </c>
       <c r="Q2" s="7">
         <f t="array" aca="1" ref="Q2" ca="1">_FV(B2,"Volume average",TRUE)</f>
@@ -14121,7 +14121,7 @@
       </c>
       <c r="U2" s="7">
         <f t="array" aca="1" ref="U2" ca="1">_FV(B2,"Market cap",TRUE)</f>
-        <v>13779689678</v>
+        <v>13254500748</v>
       </c>
       <c r="V2" s="7">
         <f t="array" aca="1" ref="V2" ca="1">_FV(B2,"Shares outstanding",TRUE)</f>
@@ -14137,7 +14137,7 @@
       </c>
       <c r="C3" s="2">
         <f t="array" aca="1" ref="C3" ca="1">_FV(B3,"Last trade time",TRUE)</f>
-        <v>46191.626774941404</v>
+        <v>46191.666717916407</v>
       </c>
       <c r="D3" t="str">
         <f t="array" aca="1" ref="D3" ca="1">_FV(B3,"Currency")</f>
@@ -14145,19 +14145,19 @@
       </c>
       <c r="E3" s="3">
         <f t="array" aca="1" ref="E3" ca="1">_FV(B3,"Price")</f>
-        <v>298.86</v>
+        <v>297.51760000000002</v>
       </c>
       <c r="F3" s="4">
         <f t="array" aca="1" ref="F3" ca="1">_FV(B3,"Change (%)",TRUE)</f>
-        <v>9.8329999999999997E-3</v>
+        <v>5.2969999999999996E-3</v>
       </c>
       <c r="G3" s="5">
         <f t="array" aca="1" ref="G3" ca="1">_FV(B3,"Change")</f>
-        <v>2.91</v>
+        <v>1.5676000000000001</v>
       </c>
       <c r="H3" s="6">
         <f t="array" aca="1" ref="H3" ca="1">_FV(B3,"P/E",TRUE)</f>
-        <v>36.296700000000001</v>
+        <v>36.133699999999997</v>
       </c>
       <c r="I3" s="6">
         <f t="array" aca="1" ref="I3" ca="1">_FV(B3,"Beta")</f>
@@ -14189,7 +14189,7 @@
       </c>
       <c r="P3" s="7">
         <f t="array" aca="1" ref="P3" ca="1">_FV(B3,"Volume")</f>
-        <v>30257970</v>
+        <v>36514211</v>
       </c>
       <c r="Q3" s="7">
         <f t="array" aca="1" ref="Q3" ca="1">_FV(B3,"Volume average",TRUE)</f>
@@ -14209,7 +14209,7 @@
       </c>
       <c r="U3" s="7">
         <f t="array" aca="1" ref="U3" ca="1">_FV(B3,"Market cap",TRUE)</f>
-        <v>4389464409600</v>
+        <v>4369748097536</v>
       </c>
       <c r="V3" s="7">
         <f t="array" aca="1" ref="V3" ca="1">_FV(B3,"Shares outstanding",TRUE)</f>
@@ -14225,7 +14225,7 @@
       </c>
       <c r="C4" s="2">
         <f t="array" aca="1" ref="C4" ca="1">_FV(B4,"Last trade time",TRUE)</f>
-        <v>46191.626769003909</v>
+        <v>46191.666697568748</v>
       </c>
       <c r="D4" t="str">
         <f t="array" aca="1" ref="D4" ca="1">_FV(B4,"Currency")</f>
@@ -14233,19 +14233,19 @@
       </c>
       <c r="E4" s="3">
         <f t="array" aca="1" ref="E4" ca="1">_FV(B4,"Price")</f>
-        <v>195.88</v>
+        <v>193.995</v>
       </c>
       <c r="F4" s="4">
         <f t="array" aca="1" ref="F4" ca="1">_FV(B4,"Change (%)",TRUE)</f>
-        <v>-2.0379999999999999E-3</v>
+        <v>-1.1642E-2</v>
       </c>
       <c r="G4" s="5">
         <f t="array" aca="1" ref="G4" ca="1">_FV(B4,"Change")</f>
-        <v>-0.4</v>
+        <v>-2.2850000000000001</v>
       </c>
       <c r="H4" s="6">
         <f t="array" aca="1" ref="H4" ca="1">_FV(B4,"P/E",TRUE)</f>
-        <v>11.2096</v>
+        <v>11.101699999999999</v>
       </c>
       <c r="I4" s="6">
         <f t="array" aca="1" ref="I4" ca="1">_FV(B4,"Beta")</f>
@@ -14277,7 +14277,7 @@
       </c>
       <c r="P4" s="7">
         <f t="array" aca="1" ref="P4" ca="1">_FV(B4,"Volume")</f>
-        <v>4545532</v>
+        <v>5360319</v>
       </c>
       <c r="Q4" s="7">
         <f t="array" aca="1" ref="Q4" ca="1">_FV(B4,"Volume average",TRUE)</f>
@@ -14297,7 +14297,7 @@
       </c>
       <c r="U4" s="7">
         <f t="array" aca="1" ref="U4" ca="1">_FV(B4,"Market cap",TRUE)</f>
-        <v>77862300000</v>
+        <v>77113012500</v>
       </c>
       <c r="V4" s="7">
         <f t="array" aca="1" ref="V4" ca="1">_FV(B4,"Shares outstanding",TRUE)</f>
@@ -14313,7 +14313,7 @@
       </c>
       <c r="C5" s="2">
         <f t="array" aca="1" ref="C5" ca="1">_FV(B5,"Last trade time",TRUE)</f>
-        <v>46191.626766678128</v>
+        <v>46191.666672812498</v>
       </c>
       <c r="D5" t="str">
         <f t="array" aca="1" ref="D5" ca="1">_FV(B5,"Currency")</f>
@@ -14321,15 +14321,15 @@
       </c>
       <c r="E5" s="3">
         <f t="array" aca="1" ref="E5" ca="1">_FV(B5,"Price")</f>
-        <v>117.47</v>
+        <v>116.1</v>
       </c>
       <c r="F5" s="4">
         <f t="array" aca="1" ref="F5" ca="1">_FV(B5,"Change (%)",TRUE)</f>
-        <v>4.3064999999999999E-2</v>
+        <v>3.0899999999999997E-2</v>
       </c>
       <c r="G5" s="5">
         <f t="array" aca="1" ref="G5" ca="1">_FV(B5,"Change")</f>
-        <v>4.8499999999999996</v>
+        <v>3.48</v>
       </c>
       <c r="H5" s="6">
         <f t="array" aca="1" ref="H5" ca="1">_FV(B5,"P/E",TRUE)</f>
@@ -14365,7 +14365,7 @@
       </c>
       <c r="P5" s="7">
         <f t="array" aca="1" ref="P5" ca="1">_FV(B5,"Volume")</f>
-        <v>481686</v>
+        <v>578626</v>
       </c>
       <c r="Q5" s="7">
         <f t="array" aca="1" ref="Q5" ca="1">_FV(B5,"Volume average",TRUE)</f>
@@ -14385,7 +14385,7 @@
       </c>
       <c r="U5" s="7">
         <f t="array" aca="1" ref="U5" ca="1">_FV(B5,"Market cap",TRUE)</f>
-        <v>3694813277</v>
+        <v>3651722325</v>
       </c>
       <c r="V5" s="7">
         <f t="array" aca="1" ref="V5" ca="1">_FV(B5,"Shares outstanding",TRUE)</f>
@@ -14401,7 +14401,7 @@
       </c>
       <c r="C6" s="2">
         <f t="array" aca="1" ref="C6" ca="1">_FV(B6,"Last trade time",TRUE)</f>
-        <v>46191.621620416408</v>
+        <v>46191.662628251564</v>
       </c>
       <c r="D6" t="str">
         <f t="array" aca="1" ref="D6" ca="1">_FV(B6,"Currency")</f>
@@ -14409,19 +14409,19 @@
       </c>
       <c r="E6" s="3">
         <f t="array" aca="1" ref="E6" ca="1">_FV(B6,"Price")</f>
-        <v>11.94</v>
+        <v>11.96</v>
       </c>
       <c r="F6" s="4">
         <f t="array" aca="1" ref="F6" ca="1">_FV(B6,"Change (%)",TRUE)</f>
-        <v>2.519E-3</v>
+        <v>4.1980000000000003E-3</v>
       </c>
       <c r="G6" s="5">
         <f t="array" aca="1" ref="G6" ca="1">_FV(B6,"Change")</f>
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
       <c r="H6" s="6">
         <f t="array" aca="1" ref="H6" ca="1">_FV(B6,"P/E",TRUE)</f>
-        <v>11.3466</v>
+        <v>11.365600000000001</v>
       </c>
       <c r="I6" s="6">
         <f t="array" aca="1" ref="I6" ca="1">_FV(B6,"Beta")</f>
@@ -14437,7 +14437,7 @@
       </c>
       <c r="L6" s="3">
         <f t="array" aca="1" ref="L6" ca="1">_FV(B6,"High")</f>
-        <v>11.95</v>
+        <v>11.96</v>
       </c>
       <c r="M6" s="3">
         <f t="array" aca="1" ref="M6" ca="1">_FV(B6,"Low")</f>
@@ -14453,7 +14453,7 @@
       </c>
       <c r="P6" s="7">
         <f t="array" aca="1" ref="P6" ca="1">_FV(B6,"Volume")</f>
-        <v>900</v>
+        <v>1420</v>
       </c>
       <c r="Q6" s="7">
         <f t="array" aca="1" ref="Q6" ca="1">_FV(B6,"Volume average",TRUE)</f>
@@ -14473,7 +14473,7 @@
       </c>
       <c r="U6" s="7">
         <f t="array" aca="1" ref="U6" ca="1">_FV(B6,"Market cap",TRUE)</f>
-        <v>575981898</v>
+        <v>576946692</v>
       </c>
       <c r="V6" s="7">
         <f t="array" aca="1" ref="V6" ca="1">_FV(B6,"Shares outstanding",TRUE)</f>
@@ -14489,7 +14489,7 @@
       </c>
       <c r="C7" s="2">
         <f t="array" aca="1" ref="C7" ca="1">_FV(B7,"Last trade time",TRUE)</f>
-        <v>46191.626750462499</v>
+        <v>46191.666720150002</v>
       </c>
       <c r="D7" t="str">
         <f t="array" aca="1" ref="D7" ca="1">_FV(B7,"Currency")</f>
@@ -14497,19 +14497,19 @@
       </c>
       <c r="E7" s="3">
         <f t="array" aca="1" ref="E7" ca="1">_FV(B7,"Price")</f>
-        <v>411.78</v>
+        <v>417.745</v>
       </c>
       <c r="F7" s="4">
         <f t="array" aca="1" ref="F7" ca="1">_FV(B7,"Change (%)",TRUE)</f>
-        <v>9.9017999999999995E-2</v>
+        <v>0.114938</v>
       </c>
       <c r="G7" s="5">
         <f t="array" aca="1" ref="G7" ca="1">_FV(B7,"Change")</f>
-        <v>37.1</v>
+        <v>43.064999999999998</v>
       </c>
       <c r="H7" s="6">
         <f t="array" aca="1" ref="H7" ca="1">_FV(B7,"P/E",TRUE)</f>
-        <v>277.59199999999998</v>
+        <v>281.61320000000001</v>
       </c>
       <c r="I7" s="6">
         <f t="array" aca="1" ref="I7" ca="1">_FV(B7,"Beta")</f>
@@ -14517,7 +14517,7 @@
       </c>
       <c r="J7" s="3">
         <f t="array" aca="1" ref="J7" ca="1">_FV(B7,"52 week high",TRUE)</f>
-        <v>414.74990000000003</v>
+        <v>417.745</v>
       </c>
       <c r="K7" s="3">
         <f t="array" aca="1" ref="K7" ca="1">_FV(B7,"52 week low",TRUE)</f>
@@ -14525,7 +14525,7 @@
       </c>
       <c r="L7" s="3">
         <f t="array" aca="1" ref="L7" ca="1">_FV(B7,"High")</f>
-        <v>414.74990000000003</v>
+        <v>417.745</v>
       </c>
       <c r="M7" s="3">
         <f t="array" aca="1" ref="M7" ca="1">_FV(B7,"Low")</f>
@@ -14541,7 +14541,7 @@
       </c>
       <c r="P7" s="7">
         <f t="array" aca="1" ref="P7" ca="1">_FV(B7,"Volume")</f>
-        <v>1619725</v>
+        <v>2707866</v>
       </c>
       <c r="Q7" s="7">
         <f t="array" aca="1" ref="Q7" ca="1">_FV(B7,"Volume average",TRUE)</f>
@@ -14561,7 +14561,7 @@
       </c>
       <c r="U7" s="7">
         <f t="array" aca="1" ref="U7" ca="1">_FV(B7,"Market cap",TRUE)</f>
-        <v>70582345062</v>
+        <v>71604793185</v>
       </c>
       <c r="V7" s="7">
         <f t="array" aca="1" ref="V7" ca="1">_FV(B7,"Shares outstanding",TRUE)</f>
@@ -14577,7 +14577,7 @@
       </c>
       <c r="C8" s="2">
         <f t="array" aca="1" ref="C8" ca="1">_FV(B8,"Last trade time",TRUE)</f>
-        <v>46191.626740092186</v>
+        <v>46191.66671635391</v>
       </c>
       <c r="D8" t="str">
         <f t="array" aca="1" ref="D8" ca="1">_FV(B8,"Currency")</f>
@@ -14585,15 +14585,15 @@
       </c>
       <c r="E8" s="3">
         <f t="array" aca="1" ref="E8" ca="1">_FV(B8,"Price")</f>
-        <v>68.875</v>
+        <v>68.48</v>
       </c>
       <c r="F8" s="4">
         <f t="array" aca="1" ref="F8" ca="1">_FV(B8,"Change (%)",TRUE)</f>
-        <v>4.5461000000000001E-2</v>
+        <v>3.9466000000000001E-2</v>
       </c>
       <c r="G8" s="5">
         <f t="array" aca="1" ref="G8" ca="1">_FV(B8,"Change")</f>
-        <v>2.9950000000000001</v>
+        <v>2.6</v>
       </c>
       <c r="H8" s="6">
         <f t="array" aca="1" ref="H8" ca="1">_FV(B8,"P/E",TRUE)</f>
@@ -14613,7 +14613,7 @@
       </c>
       <c r="L8" s="3">
         <f t="array" aca="1" ref="L8" ca="1">_FV(B8,"High")</f>
-        <v>68.959999999999994</v>
+        <v>69.724999999999994</v>
       </c>
       <c r="M8" s="3">
         <f t="array" aca="1" ref="M8" ca="1">_FV(B8,"Low")</f>
@@ -14629,7 +14629,7 @@
       </c>
       <c r="P8" s="7">
         <f t="array" aca="1" ref="P8" ca="1">_FV(B8,"Volume")</f>
-        <v>461518</v>
+        <v>599671</v>
       </c>
       <c r="Q8" s="7">
         <f t="array" aca="1" ref="Q8" ca="1">_FV(B8,"Volume average",TRUE)</f>
@@ -14649,7 +14649,7 @@
       </c>
       <c r="U8" s="7">
         <f t="array" aca="1" ref="U8" ca="1">_FV(B8,"Market cap",TRUE)</f>
-        <v>3021420897</v>
+        <v>3004092966</v>
       </c>
       <c r="V8" s="7">
         <f t="array" aca="1" ref="V8" ca="1">_FV(B8,"Shares outstanding",TRUE)</f>
@@ -14665,7 +14665,7 @@
       </c>
       <c r="C9" s="2">
         <f t="array" aca="1" ref="C9" ca="1">_FV(B9,"Last trade time",TRUE)</f>
-        <v>46191.626757870312</v>
+        <v>46191.666724178125</v>
       </c>
       <c r="D9" t="str">
         <f t="array" aca="1" ref="D9" ca="1">_FV(B9,"Currency")</f>
@@ -14673,19 +14673,19 @@
       </c>
       <c r="E9" s="3">
         <f t="array" aca="1" ref="E9" ca="1">_FV(B9,"Price")</f>
-        <v>532.86</v>
+        <v>535.11969999999997</v>
       </c>
       <c r="F9" s="4">
         <f t="array" aca="1" ref="F9" ca="1">_FV(B9,"Change (%)",TRUE)</f>
-        <v>3.9767000000000004E-2</v>
+        <v>4.4177000000000001E-2</v>
       </c>
       <c r="G9" s="5">
         <f t="array" aca="1" ref="G9" ca="1">_FV(B9,"Change")</f>
-        <v>20.38</v>
+        <v>22.639700000000001</v>
       </c>
       <c r="H9" s="6">
         <f t="array" aca="1" ref="H9" ca="1">_FV(B9,"P/E",TRUE)</f>
-        <v>177.6259</v>
+        <v>178.3792</v>
       </c>
       <c r="I9" s="6">
         <f t="array" aca="1" ref="I9" ca="1">_FV(B9,"Beta")</f>
@@ -14701,11 +14701,11 @@
       </c>
       <c r="L9" s="3">
         <f t="array" aca="1" ref="L9" ca="1">_FV(B9,"High")</f>
-        <v>536.83000000000004</v>
+        <v>539.61990000000003</v>
       </c>
       <c r="M9" s="3">
         <f t="array" aca="1" ref="M9" ca="1">_FV(B9,"Low")</f>
-        <v>527</v>
+        <v>526.31500000000005</v>
       </c>
       <c r="N9" s="3">
         <f t="array" aca="1" ref="N9" ca="1">_FV(B9,"Open")</f>
@@ -14717,7 +14717,7 @@
       </c>
       <c r="P9" s="7">
         <f t="array" aca="1" ref="P9" ca="1">_FV(B9,"Volume")</f>
-        <v>11481762</v>
+        <v>15734882</v>
       </c>
       <c r="Q9" s="7">
         <f t="array" aca="1" ref="Q9" ca="1">_FV(B9,"Volume average",TRUE)</f>
@@ -14737,7 +14737,7 @@
       </c>
       <c r="U9" s="7">
         <f t="array" aca="1" ref="U9" ca="1">_FV(B9,"Market cap",TRUE)</f>
-        <v>868882048860</v>
+        <v>872566717939</v>
       </c>
       <c r="V9" s="7">
         <f t="array" aca="1" ref="V9" ca="1">_FV(B9,"Shares outstanding",TRUE)</f>
@@ -14753,7 +14753,7 @@
       </c>
       <c r="C10" s="2">
         <f t="array" aca="1" ref="C10" ca="1">_FV(B10,"Last trade time",TRUE)</f>
-        <v>46191.626768738279</v>
+        <v>46191.666713240622</v>
       </c>
       <c r="D10" t="str">
         <f t="array" aca="1" ref="D10" ca="1">_FV(B10,"Currency")</f>
@@ -14761,19 +14761,19 @@
       </c>
       <c r="E10" s="3">
         <f t="array" aca="1" ref="E10" ca="1">_FV(B10,"Price")</f>
-        <v>241.40690000000001</v>
+        <v>243.86019999999999</v>
       </c>
       <c r="F10" s="4">
         <f t="array" aca="1" ref="F10" ca="1">_FV(B10,"Change (%)",TRUE)</f>
-        <v>1.6449999999999999E-2</v>
+        <v>2.6779999999999998E-2</v>
       </c>
       <c r="G10" s="5">
         <f t="array" aca="1" ref="G10" ca="1">_FV(B10,"Change")</f>
-        <v>3.9068999999999998</v>
+        <v>6.3601999999999999</v>
       </c>
       <c r="H10" s="6">
         <f t="array" aca="1" ref="H10" ca="1">_FV(B10,"P/E",TRUE)</f>
-        <v>28.849900000000002</v>
+        <v>29.143000000000001</v>
       </c>
       <c r="I10" s="6">
         <f t="array" aca="1" ref="I10" ca="1">_FV(B10,"Beta")</f>
@@ -14789,7 +14789,7 @@
       </c>
       <c r="L10" s="3">
         <f t="array" aca="1" ref="L10" ca="1">_FV(B10,"High")</f>
-        <v>241.82</v>
+        <v>244.32</v>
       </c>
       <c r="M10" s="3">
         <f t="array" aca="1" ref="M10" ca="1">_FV(B10,"Low")</f>
@@ -14805,7 +14805,7 @@
       </c>
       <c r="P10" s="7">
         <f t="array" aca="1" ref="P10" ca="1">_FV(B10,"Volume")</f>
-        <v>21217746</v>
+        <v>29735475</v>
       </c>
       <c r="Q10" s="7">
         <f t="array" aca="1" ref="Q10" ca="1">_FV(B10,"Volume average",TRUE)</f>
@@ -14825,7 +14825,7 @@
       </c>
       <c r="U10" s="7">
         <f t="array" aca="1" ref="U10" ca="1">_FV(B10,"Market cap",TRUE)</f>
-        <v>2596840578059</v>
+        <v>2623230996022</v>
       </c>
       <c r="V10" s="7">
         <f t="array" aca="1" ref="V10" ca="1">_FV(B10,"Shares outstanding",TRUE)</f>
@@ -14841,7 +14841,7 @@
       </c>
       <c r="C11" s="2">
         <f t="array" aca="1" ref="C11" ca="1">_FV(B11,"Last trade time",TRUE)</f>
-        <v>46191.626728240626</v>
+        <v>46191.666690428123</v>
       </c>
       <c r="D11" t="str">
         <f t="array" aca="1" ref="D11" ca="1">_FV(B11,"Currency")</f>
@@ -14849,19 +14849,19 @@
       </c>
       <c r="E11" s="3">
         <f t="array" aca="1" ref="E11" ca="1">_FV(B11,"Price")</f>
-        <v>169.13499999999999</v>
+        <v>169</v>
       </c>
       <c r="F11" s="4">
         <f t="array" aca="1" ref="F11" ca="1">_FV(B11,"Change (%)",TRUE)</f>
-        <v>2.5495999999999998E-2</v>
+        <v>2.4676999999999998E-2</v>
       </c>
       <c r="G11" s="5">
         <f t="array" aca="1" ref="G11" ca="1">_FV(B11,"Change")</f>
-        <v>4.2050000000000001</v>
+        <v>4.07</v>
       </c>
       <c r="H11" s="6">
         <f t="array" aca="1" ref="H11" ca="1">_FV(B11,"P/E",TRUE)</f>
-        <v>57.930900000000001</v>
+        <v>57.884599999999999</v>
       </c>
       <c r="I11" s="6">
         <f t="array" aca="1" ref="I11" ca="1">_FV(B11,"Beta")</f>
@@ -14893,7 +14893,7 @@
       </c>
       <c r="P11" s="7">
         <f t="array" aca="1" ref="P11" ca="1">_FV(B11,"Volume")</f>
-        <v>2728161</v>
+        <v>3215628</v>
       </c>
       <c r="Q11" s="7">
         <f t="array" aca="1" ref="Q11" ca="1">_FV(B11,"Volume average",TRUE)</f>
@@ -14913,7 +14913,7 @@
       </c>
       <c r="U11" s="7">
         <f t="array" aca="1" ref="U11" ca="1">_FV(B11,"Market cap",TRUE)</f>
-        <v>212975299405</v>
+        <v>212805307000</v>
       </c>
       <c r="V11" s="7">
         <f t="array" aca="1" ref="V11" ca="1">_FV(B11,"Shares outstanding",TRUE)</f>
@@ -14929,7 +14929,7 @@
       </c>
       <c r="C12" s="2">
         <f t="array" aca="1" ref="C12" ca="1">_FV(B12,"Last trade time",TRUE)</f>
-        <v>46191.626761562497</v>
+        <v>46191.666724409377</v>
       </c>
       <c r="D12" t="str">
         <f t="array" aca="1" ref="D12" ca="1">_FV(B12,"Currency")</f>
@@ -14937,19 +14937,19 @@
       </c>
       <c r="E12" s="3">
         <f t="array" aca="1" ref="E12" ca="1">_FV(B12,"Price")</f>
-        <v>471.185</v>
+        <v>471.39</v>
       </c>
       <c r="F12" s="4">
         <f t="array" aca="1" ref="F12" ca="1">_FV(B12,"Change (%)",TRUE)</f>
-        <v>-1.7319999999999999E-2</v>
+        <v>-1.6893000000000002E-2</v>
       </c>
       <c r="G12" s="5">
         <f t="array" aca="1" ref="G12" ca="1">_FV(B12,"Change")</f>
-        <v>-8.3049999999999997</v>
+        <v>-8.1</v>
       </c>
       <c r="H12" s="6">
         <f t="array" aca="1" ref="H12" ca="1">_FV(B12,"P/E",TRUE)</f>
-        <v>40.945900000000002</v>
+        <v>40.963700000000003</v>
       </c>
       <c r="I12" s="6">
         <f t="array" aca="1" ref="I12" ca="1">_FV(B12,"Beta")</f>
@@ -14981,7 +14981,7 @@
       </c>
       <c r="P12" s="7">
         <f t="array" aca="1" ref="P12" ca="1">_FV(B12,"Volume")</f>
-        <v>1903939</v>
+        <v>2961607</v>
       </c>
       <c r="Q12" s="7">
         <f t="array" aca="1" ref="Q12" ca="1">_FV(B12,"Volume average",TRUE)</f>
@@ -15001,7 +15001,7 @@
       </c>
       <c r="U12" s="7">
         <f t="array" aca="1" ref="U12" ca="1">_FV(B12,"Market cap",TRUE)</f>
-        <v>158289888900</v>
+        <v>158358756600</v>
       </c>
       <c r="V12" s="7">
         <f t="array" aca="1" ref="V12" ca="1">_FV(B12,"Shares outstanding",TRUE)</f>
@@ -15017,7 +15017,7 @@
       </c>
       <c r="C13" s="2" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(B13,"Last trade time",TRUE)</f>
-        <v>46191.626704478906</v>
+        <v>46191.666690068749</v>
       </c>
       <c r="D13" t="str" cm="1">
         <f t="array" aca="1" ref="D13" ca="1">_FV(B13,"Currency")</f>
@@ -15025,15 +15025,15 @@
       </c>
       <c r="E13" s="3" cm="1">
         <f t="array" aca="1" ref="E13" ca="1">_FV(B13,"Price")</f>
-        <v>79.667000000000002</v>
+        <v>79.099999999999994</v>
       </c>
       <c r="F13" s="4" cm="1">
         <f t="array" aca="1" ref="F13" ca="1">_FV(B13,"Change (%)",TRUE)</f>
-        <v>1.4996000000000001E-2</v>
+        <v>7.7720000000000003E-3</v>
       </c>
       <c r="G13" s="5" cm="1">
         <f t="array" aca="1" ref="G13" ca="1">_FV(B13,"Change")</f>
-        <v>1.177</v>
+        <v>0.61</v>
       </c>
       <c r="H13" s="6" t="e" vm="13">
         <f t="array" ref="H13">_FV(B13,"P/E",TRUE)</f>
@@ -15069,7 +15069,7 @@
       </c>
       <c r="P13" s="7" cm="1">
         <f t="array" aca="1" ref="P13" ca="1">_FV(B13,"Volume")</f>
-        <v>1675867</v>
+        <v>4059167</v>
       </c>
       <c r="Q13" s="7" cm="1">
         <f t="array" aca="1" ref="Q13" ca="1">_FV(B13,"Volume average",TRUE)</f>
@@ -15105,7 +15105,7 @@
       </c>
       <c r="C14" s="2">
         <f t="array" aca="1" ref="C14" ca="1">_FV(B14,"Last trade time",TRUE)</f>
-        <v>46191.626752198441</v>
+        <v>46191.666708703124</v>
       </c>
       <c r="D14" t="str">
         <f t="array" aca="1" ref="D14" ca="1">_FV(B14,"Currency")</f>
@@ -15113,19 +15113,19 @@
       </c>
       <c r="E14" s="3">
         <f t="array" aca="1" ref="E14" ca="1">_FV(B14,"Price")</f>
-        <v>447.71</v>
+        <v>443.90499999999997</v>
       </c>
       <c r="F14" s="4">
         <f t="array" aca="1" ref="F14" ca="1">_FV(B14,"Change (%)",TRUE)</f>
-        <v>6.8825999999999998E-2</v>
+        <v>5.9743000000000004E-2</v>
       </c>
       <c r="G14" s="5">
         <f t="array" aca="1" ref="G14" ca="1">_FV(B14,"Change")</f>
-        <v>28.83</v>
+        <v>25.024999999999999</v>
       </c>
       <c r="H14" s="6">
         <f t="array" aca="1" ref="H14" ca="1">_FV(B14,"P/E",TRUE)</f>
-        <v>528.9579</v>
+        <v>524.4624</v>
       </c>
       <c r="I14" s="6">
         <f t="array" aca="1" ref="I14" ca="1">_FV(B14,"Beta")</f>
@@ -15157,7 +15157,7 @@
       </c>
       <c r="P14" s="7">
         <f t="array" aca="1" ref="P14" ca="1">_FV(B14,"Volume")</f>
-        <v>4189288</v>
+        <v>5062561</v>
       </c>
       <c r="Q14" s="7">
         <f t="array" aca="1" ref="Q14" ca="1">_FV(B14,"Volume average",TRUE)</f>
@@ -15177,7 +15177,7 @@
       </c>
       <c r="U14" s="7">
         <f t="array" aca="1" ref="U14" ca="1">_FV(B14,"Market cap",TRUE)</f>
-        <v>478189649090</v>
+        <v>474125608495</v>
       </c>
       <c r="V14" s="7">
         <f t="array" aca="1" ref="V14" ca="1">_FV(B14,"Shares outstanding",TRUE)</f>
@@ -15193,7 +15193,7 @@
       </c>
       <c r="C15" s="2">
         <f t="array" aca="1" ref="C15" ca="1">_FV(B15,"Last trade time",TRUE)</f>
-        <v>46191.62674649297</v>
+        <v>46191.666716770313</v>
       </c>
       <c r="D15" t="str">
         <f t="array" aca="1" ref="D15" ca="1">_FV(B15,"Currency")</f>
@@ -15201,19 +15201,19 @@
       </c>
       <c r="E15" s="3">
         <f t="array" aca="1" ref="E15" ca="1">_FV(B15,"Price")</f>
-        <v>1935.62</v>
+        <v>1922.01</v>
       </c>
       <c r="F15" s="4">
         <f t="array" aca="1" ref="F15" ca="1">_FV(B15,"Change (%)",TRUE)</f>
-        <v>3.6292999999999999E-2</v>
+        <v>2.9007000000000002E-2</v>
       </c>
       <c r="G15" s="5">
         <f t="array" aca="1" ref="G15" ca="1">_FV(B15,"Change")</f>
-        <v>67.790000000000006</v>
+        <v>54.18</v>
       </c>
       <c r="H15" s="6">
         <f t="array" aca="1" ref="H15" ca="1">_FV(B15,"P/E",TRUE)</f>
-        <v>66.546300000000002</v>
+        <v>66.078400000000002</v>
       </c>
       <c r="I15" s="6">
         <f t="array" aca="1" ref="I15" ca="1">_FV(B15,"Beta")</f>
@@ -15245,7 +15245,7 @@
       </c>
       <c r="P15" s="7">
         <f t="array" aca="1" ref="P15" ca="1">_FV(B15,"Volume")</f>
-        <v>697110</v>
+        <v>874339</v>
       </c>
       <c r="Q15" s="7">
         <f t="array" aca="1" ref="Q15" ca="1">_FV(B15,"Volume average",TRUE)</f>
@@ -15265,7 +15265,7 @@
       </c>
       <c r="U15" s="7">
         <f t="array" aca="1" ref="U15" ca="1">_FV(B15,"Market cap",TRUE)</f>
-        <v>751306451074</v>
+        <v>746023760877</v>
       </c>
       <c r="V15" s="7">
         <f t="array" aca="1" ref="V15" ca="1">_FV(B15,"Shares outstanding",TRUE)</f>
@@ -15281,7 +15281,7 @@
       </c>
       <c r="C16" s="2">
         <f t="array" aca="1" ref="C16" ca="1">_FV(B16,"Last trade time",TRUE)</f>
-        <v>46191.626762094529</v>
+        <v>46191.666716758591</v>
       </c>
       <c r="D16" t="str">
         <f t="array" aca="1" ref="D16" ca="1">_FV(B16,"Currency")</f>
@@ -15289,19 +15289,19 @@
       </c>
       <c r="E16" s="3">
         <f t="array" aca="1" ref="E16" ca="1">_FV(B16,"Price")</f>
-        <v>409.19</v>
+        <v>408.14</v>
       </c>
       <c r="F16" s="4">
         <f t="array" aca="1" ref="F16" ca="1">_FV(B16,"Change (%)",TRUE)</f>
-        <v>4.1460999999999998E-2</v>
+        <v>3.8788000000000003E-2</v>
       </c>
       <c r="G16" s="5">
         <f t="array" aca="1" ref="G16" ca="1">_FV(B16,"Change")</f>
-        <v>16.29</v>
+        <v>15.24</v>
       </c>
       <c r="H16" s="6">
         <f t="array" aca="1" ref="H16" ca="1">_FV(B16,"P/E",TRUE)</f>
-        <v>68.158600000000007</v>
+        <v>67.983699999999999</v>
       </c>
       <c r="I16" s="6">
         <f t="array" aca="1" ref="I16" ca="1">_FV(B16,"Beta")</f>
@@ -15333,7 +15333,7 @@
       </c>
       <c r="P16" s="7">
         <f t="array" aca="1" ref="P16" ca="1">_FV(B16,"Volume")</f>
-        <v>11189831</v>
+        <v>14286632</v>
       </c>
       <c r="Q16" s="7">
         <f t="array" aca="1" ref="Q16" ca="1">_FV(B16,"Volume average",TRUE)</f>
@@ -15353,7 +15353,7 @@
       </c>
       <c r="U16" s="7">
         <f t="array" aca="1" ref="U16" ca="1">_FV(B16,"Market cap",TRUE)</f>
-        <v>1946754160200</v>
+        <v>1941758701200</v>
       </c>
       <c r="V16" s="7">
         <f t="array" aca="1" ref="V16" ca="1">_FV(B16,"Shares outstanding",TRUE)</f>
@@ -15369,7 +15369,7 @@
       </c>
       <c r="C17" s="2">
         <f t="array" aca="1" ref="C17" ca="1">_FV(B17,"Last trade time",TRUE)</f>
-        <v>46191.626757383594</v>
+        <v>46191.666727546093</v>
       </c>
       <c r="D17" t="str">
         <f t="array" aca="1" ref="D17" ca="1">_FV(B17,"Currency")</f>
@@ -15377,15 +15377,15 @@
       </c>
       <c r="E17" s="3">
         <f t="array" aca="1" ref="E17" ca="1">_FV(B17,"Price")</f>
-        <v>3.91</v>
+        <v>3.86</v>
       </c>
       <c r="F17" s="4">
         <f t="array" aca="1" ref="F17" ca="1">_FV(B17,"Change (%)",TRUE)</f>
-        <v>7.7320000000000002E-3</v>
+        <v>-5.1549999999999999E-3</v>
       </c>
       <c r="G17" s="5">
         <f t="array" aca="1" ref="G17" ca="1">_FV(B17,"Change")</f>
-        <v>0.03</v>
+        <v>-0.02</v>
       </c>
       <c r="H17" s="6">
         <f t="array" aca="1" ref="H17" ca="1">_FV(B17,"P/E",TRUE)</f>
@@ -15421,7 +15421,7 @@
       </c>
       <c r="P17" s="7">
         <f t="array" aca="1" ref="P17" ca="1">_FV(B17,"Volume")</f>
-        <v>11417129</v>
+        <v>15249778</v>
       </c>
       <c r="Q17" s="7">
         <f t="array" aca="1" ref="Q17" ca="1">_FV(B17,"Volume average",TRUE)</f>
@@ -15441,7 +15441,7 @@
       </c>
       <c r="U17" s="7">
         <f t="array" aca="1" ref="U17" ca="1">_FV(B17,"Market cap",TRUE)</f>
-        <v>1872692545</v>
+        <v>1848745070</v>
       </c>
       <c r="V17" s="7">
         <f t="array" aca="1" ref="V17" ca="1">_FV(B17,"Shares outstanding",TRUE)</f>
@@ -15457,7 +15457,7 @@
       </c>
       <c r="C18" s="2" cm="1">
         <f t="array" aca="1" ref="C18" ca="1">_FV(B18,"Last trade time",TRUE)</f>
-        <v>46191.615972222222</v>
+        <v>46191.654861111114</v>
       </c>
       <c r="D18" t="str" cm="1">
         <f t="array" aca="1" ref="D18" ca="1">_FV(B18,"Currency")</f>
@@ -15465,19 +15465,19 @@
       </c>
       <c r="E18" s="3" cm="1">
         <f t="array" aca="1" ref="E18" ca="1">_FV(B18,"Price")</f>
-        <v>59.26</v>
+        <v>59.9</v>
       </c>
       <c r="F18" s="4" cm="1">
         <f t="array" aca="1" ref="F18" ca="1">_FV(B18,"Change (%)",TRUE)</f>
-        <v>-4.4194000000000004E-2</v>
+        <v>-3.3871000000000005E-2</v>
       </c>
       <c r="G18" s="5" cm="1">
         <f t="array" aca="1" ref="G18" ca="1">_FV(B18,"Change")</f>
-        <v>-2.74</v>
+        <v>-2.1</v>
       </c>
       <c r="H18" s="6" cm="1">
         <f t="array" aca="1" ref="H18" ca="1">_FV(B18,"P/E",TRUE)</f>
-        <v>5.3387000000000002</v>
+        <v>5.3963999999999999</v>
       </c>
       <c r="I18" s="6" cm="1">
         <f t="array" aca="1" ref="I18" ca="1">_FV(B18,"Beta")</f>
@@ -15509,7 +15509,7 @@
       </c>
       <c r="P18" s="7" cm="1">
         <f t="array" aca="1" ref="P18" ca="1">_FV(B18,"Volume")</f>
-        <v>12312</v>
+        <v>12896</v>
       </c>
       <c r="Q18" s="7" cm="1">
         <f t="array" aca="1" ref="Q18" ca="1">_FV(B18,"Volume average",TRUE)</f>
@@ -15545,7 +15545,7 @@
       </c>
       <c r="C19" s="2" cm="1">
         <f t="array" aca="1" ref="C19" ca="1">_FV(B19,"Last trade time",TRUE)</f>
-        <v>46191.626731712502</v>
+        <v>46191.666675185159</v>
       </c>
       <c r="D19" t="str" cm="1">
         <f t="array" aca="1" ref="D19" ca="1">_FV(B19,"Currency")</f>
@@ -15553,19 +15553,19 @@
       </c>
       <c r="E19" s="3" cm="1">
         <f t="array" aca="1" ref="E19" ca="1">_FV(B19,"Price")</f>
-        <v>391.96499999999997</v>
+        <v>391.63499999999999</v>
       </c>
       <c r="F19" s="4" cm="1">
         <f t="array" aca="1" ref="F19" ca="1">_FV(B19,"Change (%)",TRUE)</f>
-        <v>6.0699999999999999E-3</v>
+        <v>5.2230000000000002E-3</v>
       </c>
       <c r="G19" s="5" cm="1">
         <f t="array" aca="1" ref="G19" ca="1">_FV(B19,"Change")</f>
-        <v>2.3650000000000002</v>
+        <v>2.0350000000000001</v>
       </c>
       <c r="H19" s="6" cm="1">
         <f t="array" aca="1" ref="H19" ca="1">_FV(B19,"P/E",TRUE)</f>
-        <v>91.505799999999994</v>
+        <v>91.428700000000006</v>
       </c>
       <c r="I19" s="6" cm="1">
         <f t="array" aca="1" ref="I19" ca="1">_FV(B19,"Beta")</f>
@@ -15597,7 +15597,7 @@
       </c>
       <c r="P19" s="7" cm="1">
         <f t="array" aca="1" ref="P19" ca="1">_FV(B19,"Volume")</f>
-        <v>1001367</v>
+        <v>1464930</v>
       </c>
       <c r="Q19" s="7" cm="1">
         <f t="array" aca="1" ref="Q19" ca="1">_FV(B19,"Volume average",TRUE)</f>
@@ -15617,7 +15617,7 @@
       </c>
       <c r="U19" s="7" cm="1">
         <f t="array" aca="1" ref="U19" ca="1">_FV(B19,"Market cap",TRUE)</f>
-        <v>108110218440</v>
+        <v>108019199160</v>
       </c>
       <c r="V19" s="7" cm="1">
         <f t="array" aca="1" ref="V19" ca="1">_FV(B19,"Shares outstanding",TRUE)</f>
@@ -15633,7 +15633,7 @@
       </c>
       <c r="C20" s="2" cm="1">
         <f t="array" aca="1" ref="C20" ca="1">_FV(B20,"Last trade time",TRUE)</f>
-        <v>46191.626764015622</v>
+        <v>46191.666736724219</v>
       </c>
       <c r="D20" t="str" cm="1">
         <f t="array" aca="1" ref="D20" ca="1">_FV(B20,"Currency")</f>
@@ -15641,19 +15641,19 @@
       </c>
       <c r="E20" s="3" cm="1">
         <f t="array" aca="1" ref="E20" ca="1">_FV(B20,"Price")</f>
-        <v>278.88499999999999</v>
+        <v>280.3</v>
       </c>
       <c r="F20" s="4" cm="1">
         <f t="array" aca="1" ref="F20" ca="1">_FV(B20,"Change (%)",TRUE)</f>
-        <v>4.3848000000000005E-2</v>
+        <v>4.9145000000000001E-2</v>
       </c>
       <c r="G20" s="5" cm="1">
         <f t="array" aca="1" ref="G20" ca="1">_FV(B20,"Change")</f>
-        <v>11.715</v>
+        <v>13.13</v>
       </c>
       <c r="H20" s="6" cm="1">
         <f t="array" aca="1" ref="H20" ca="1">_FV(B20,"P/E",TRUE)</f>
-        <v>24.2285</v>
+        <v>24.351500000000001</v>
       </c>
       <c r="I20" s="6" cm="1">
         <f t="array" aca="1" ref="I20" ca="1">_FV(B20,"Beta")</f>
@@ -15669,7 +15669,7 @@
       </c>
       <c r="L20" s="3" cm="1">
         <f t="array" aca="1" ref="L20" ca="1">_FV(B20,"High")</f>
-        <v>279.92</v>
+        <v>281.2</v>
       </c>
       <c r="M20" s="3" cm="1">
         <f t="array" aca="1" ref="M20" ca="1">_FV(B20,"Low")</f>
@@ -15685,7 +15685,7 @@
       </c>
       <c r="P20" s="7" cm="1">
         <f t="array" aca="1" ref="P20" ca="1">_FV(B20,"Volume")</f>
-        <v>2055660</v>
+        <v>2634506</v>
       </c>
       <c r="Q20" s="7" cm="1">
         <f t="array" aca="1" ref="Q20" ca="1">_FV(B20,"Volume average",TRUE)</f>
@@ -15705,7 +15705,7 @@
       </c>
       <c r="U20" s="7" cm="1">
         <f t="array" aca="1" ref="U20" ca="1">_FV(B20,"Market cap",TRUE)</f>
-        <v>100148161270</v>
+        <v>100656290600</v>
       </c>
       <c r="V20" s="7" cm="1">
         <f t="array" aca="1" ref="V20" ca="1">_FV(B20,"Shares outstanding",TRUE)</f>
@@ -15721,7 +15721,7 @@
       </c>
       <c r="C21" s="2">
         <f t="array" aca="1" ref="C21" ca="1">_FV(B21,"Last trade time",TRUE)</f>
-        <v>46191.626767048438</v>
+        <v>46191.666702001559</v>
       </c>
       <c r="D21" t="str">
         <f t="array" aca="1" ref="D21" ca="1">_FV(B21,"Currency")</f>
@@ -15729,19 +15729,19 @@
       </c>
       <c r="E21" s="3">
         <f t="array" aca="1" ref="E21" ca="1">_FV(B21,"Price")</f>
-        <v>264.46749999999997</v>
+        <v>265.8</v>
       </c>
       <c r="F21" s="4">
         <f t="array" aca="1" ref="F21" ca="1">_FV(B21,"Change (%)",TRUE)</f>
-        <v>6.0712999999999996E-2</v>
+        <v>6.6056999999999991E-2</v>
       </c>
       <c r="G21" s="5">
         <f t="array" aca="1" ref="G21" ca="1">_FV(B21,"Change")</f>
-        <v>15.137499999999999</v>
+        <v>16.47</v>
       </c>
       <c r="H21" s="6">
         <f t="array" aca="1" ref="H21" ca="1">_FV(B21,"P/E",TRUE)</f>
-        <v>106.73480000000001</v>
+        <v>107.2726</v>
       </c>
       <c r="I21" s="6">
         <f t="array" aca="1" ref="I21" ca="1">_FV(B21,"Beta")</f>
@@ -15757,7 +15757,7 @@
       </c>
       <c r="L21" s="3">
         <f t="array" aca="1" ref="L21" ca="1">_FV(B21,"High")</f>
-        <v>268.07</v>
+        <v>268.14999999999998</v>
       </c>
       <c r="M21" s="3">
         <f t="array" aca="1" ref="M21" ca="1">_FV(B21,"Low")</f>
@@ -15773,7 +15773,7 @@
       </c>
       <c r="P21" s="7">
         <f t="array" aca="1" ref="P21" ca="1">_FV(B21,"Volume")</f>
-        <v>2815787</v>
+        <v>3600297</v>
       </c>
       <c r="Q21" s="7">
         <f t="array" aca="1" ref="Q21" ca="1">_FV(B21,"Volume average",TRUE)</f>
@@ -15793,7 +15793,7 @@
       </c>
       <c r="U21" s="7">
         <f t="array" aca="1" ref="U21" ca="1">_FV(B21,"Market cap",TRUE)</f>
-        <v>49317344018</v>
+        <v>49565825820</v>
       </c>
       <c r="V21" s="7">
         <f t="array" aca="1" ref="V21" ca="1">_FV(B21,"Shares outstanding",TRUE)</f>
@@ -15809,7 +15809,7 @@
       </c>
       <c r="C22" s="2">
         <f t="array" aca="1" ref="C22" ca="1">_FV(B22,"Last trade time",TRUE)</f>
-        <v>46191.626772395313</v>
+        <v>46191.666697464847</v>
       </c>
       <c r="D22" t="str">
         <f t="array" aca="1" ref="D22" ca="1">_FV(B22,"Currency")</f>
@@ -15817,19 +15817,19 @@
       </c>
       <c r="E22" s="3">
         <f t="array" aca="1" ref="E22" ca="1">_FV(B22,"Price")</f>
-        <v>152.55000000000001</v>
+        <v>152.47499999999999</v>
       </c>
       <c r="F22" s="4">
         <f t="array" aca="1" ref="F22" ca="1">_FV(B22,"Change (%)",TRUE)</f>
-        <v>-1.5932999999999999E-2</v>
+        <v>-1.6417000000000001E-2</v>
       </c>
       <c r="G22" s="5">
         <f t="array" aca="1" ref="G22" ca="1">_FV(B22,"Change")</f>
-        <v>-2.4700000000000002</v>
+        <v>-2.5449999999999999</v>
       </c>
       <c r="H22" s="6">
         <f t="array" aca="1" ref="H22" ca="1">_FV(B22,"P/E",TRUE)</f>
-        <v>17.649699999999999</v>
+        <v>17.640999999999998</v>
       </c>
       <c r="I22" s="6">
         <f t="array" aca="1" ref="I22" ca="1">_FV(B22,"Beta")</f>
@@ -15861,7 +15861,7 @@
       </c>
       <c r="P22" s="7">
         <f t="array" aca="1" ref="P22" ca="1">_FV(B22,"Volume")</f>
-        <v>7824378</v>
+        <v>9266838</v>
       </c>
       <c r="Q22" s="7">
         <f t="array" aca="1" ref="Q22" ca="1">_FV(B22,"Volume average",TRUE)</f>
@@ -15881,7 +15881,7 @@
       </c>
       <c r="U22" s="7">
         <f t="array" aca="1" ref="U22" ca="1">_FV(B22,"Market cap",TRUE)</f>
-        <v>124938450000</v>
+        <v>124877025000</v>
       </c>
       <c r="V22" s="7">
         <f t="array" aca="1" ref="V22" ca="1">_FV(B22,"Shares outstanding",TRUE)</f>
@@ -15897,7 +15897,7 @@
       </c>
       <c r="C23" s="2" cm="1">
         <f t="array" aca="1" ref="C23" ca="1">_FV(B23,"Last trade time",TRUE)</f>
-        <v>46191.62676030078</v>
+        <v>46191.666717140622</v>
       </c>
       <c r="D23" t="str" cm="1">
         <f t="array" aca="1" ref="D23" ca="1">_FV(B23,"Currency")</f>
@@ -15905,15 +15905,15 @@
       </c>
       <c r="E23" s="3" cm="1">
         <f t="array" aca="1" ref="E23" ca="1">_FV(B23,"Price")</f>
-        <v>680.15</v>
+        <v>673.51009999999997</v>
       </c>
       <c r="F23" s="4" cm="1">
         <f t="array" aca="1" ref="F23" ca="1">_FV(B23,"Change (%)",TRUE)</f>
-        <v>-4.1139999999999996E-3</v>
+        <v>-1.3836999999999999E-2</v>
       </c>
       <c r="G23" s="5" cm="1">
         <f t="array" aca="1" ref="G23" ca="1">_FV(B23,"Change")</f>
-        <v>-2.81</v>
+        <v>-9.4498999999999995</v>
       </c>
       <c r="H23" s="6" cm="1">
         <f t="array" aca="1" ref="H23" ca="1">_FV(B23,"P/E",TRUE)</f>
@@ -15949,7 +15949,7 @@
       </c>
       <c r="P23" s="7" cm="1">
         <f t="array" aca="1" ref="P23" ca="1">_FV(B23,"Volume")</f>
-        <v>1104747</v>
+        <v>1310651</v>
       </c>
       <c r="Q23" s="7" cm="1">
         <f t="array" aca="1" ref="Q23" ca="1">_FV(B23,"Volume average",TRUE)</f>
@@ -15969,7 +15969,7 @@
       </c>
       <c r="U23" s="7" cm="1">
         <f t="array" aca="1" ref="U23" ca="1">_FV(B23,"Market cap",TRUE)</f>
-        <v>173142248720</v>
+        <v>171451963904</v>
       </c>
       <c r="V23" s="7" cm="1">
         <f t="array" aca="1" ref="V23" ca="1">_FV(B23,"Shares outstanding",TRUE)</f>
@@ -15985,7 +15985,7 @@
       </c>
       <c r="C24" s="2">
         <f t="array" aca="1" ref="C24" ca="1">_FV(B24,"Last trade time",TRUE)</f>
-        <v>46191.626762430467</v>
+        <v>46191.666716388281</v>
       </c>
       <c r="D24" t="str">
         <f t="array" aca="1" ref="D24" ca="1">_FV(B24,"Currency")</f>
@@ -15993,15 +15993,15 @@
       </c>
       <c r="E24" s="3">
         <f t="array" aca="1" ref="E24" ca="1">_FV(B24,"Price")</f>
-        <v>119.19</v>
+        <v>117.8318</v>
       </c>
       <c r="F24" s="4">
         <f t="array" aca="1" ref="F24" ca="1">_FV(B24,"Change (%)",TRUE)</f>
-        <v>3.4546E-2</v>
+        <v>2.2756999999999999E-2</v>
       </c>
       <c r="G24" s="5">
         <f t="array" aca="1" ref="G24" ca="1">_FV(B24,"Change")</f>
-        <v>3.98</v>
+        <v>2.6217999999999999</v>
       </c>
       <c r="H24" s="6">
         <f t="array" aca="1" ref="H24" ca="1">_FV(B24,"P/E",TRUE)</f>
@@ -16021,7 +16021,7 @@
       </c>
       <c r="L24" s="3">
         <f t="array" aca="1" ref="L24" ca="1">_FV(B24,"High")</f>
-        <v>119.8</v>
+        <v>119.89</v>
       </c>
       <c r="M24" s="3">
         <f t="array" aca="1" ref="M24" ca="1">_FV(B24,"Low")</f>
@@ -16037,7 +16037,7 @@
       </c>
       <c r="P24" s="7">
         <f t="array" aca="1" ref="P24" ca="1">_FV(B24,"Volume")</f>
-        <v>9025426</v>
+        <v>11925907</v>
       </c>
       <c r="Q24" s="7">
         <f t="array" aca="1" ref="Q24" ca="1">_FV(B24,"Volume average",TRUE)</f>
@@ -16057,7 +16057,7 @@
       </c>
       <c r="U24" s="7">
         <f t="array" aca="1" ref="U24" ca="1">_FV(B24,"Market cap",TRUE)</f>
-        <v>65026535976</v>
+        <v>64285542258</v>
       </c>
       <c r="V24" s="7">
         <f t="array" aca="1" ref="V24" ca="1">_FV(B24,"Shares outstanding",TRUE)</f>
@@ -16073,7 +16073,7 @@
       </c>
       <c r="C25" s="2" cm="1">
         <f t="array" aca="1" ref="C25" ca="1">_FV(B25,"Last trade time",TRUE)</f>
-        <v>46191.626772488278</v>
+        <v>46191.666709999998</v>
       </c>
       <c r="D25" t="str" cm="1">
         <f t="array" aca="1" ref="D25" ca="1">_FV(B25,"Currency")</f>
@@ -16081,19 +16081,19 @@
       </c>
       <c r="E25" s="3" cm="1">
         <f t="array" aca="1" ref="E25" ca="1">_FV(B25,"Price")</f>
-        <v>118.11</v>
+        <v>118.42</v>
       </c>
       <c r="F25" s="4" cm="1">
         <f t="array" aca="1" ref="F25" ca="1">_FV(B25,"Change (%)",TRUE)</f>
-        <v>6.6479999999999994E-3</v>
+        <v>9.2899999999999996E-3</v>
       </c>
       <c r="G25" s="5" cm="1">
         <f t="array" aca="1" ref="G25" ca="1">_FV(B25,"Change")</f>
-        <v>0.78</v>
+        <v>1.0900000000000001</v>
       </c>
       <c r="H25" s="6" cm="1">
         <f t="array" aca="1" ref="H25" ca="1">_FV(B25,"P/E",TRUE)</f>
-        <v>39.356900000000003</v>
+        <v>39.4602</v>
       </c>
       <c r="I25" s="6" cm="1">
         <f t="array" aca="1" ref="I25" ca="1">_FV(B25,"Beta")</f>
@@ -16125,7 +16125,7 @@
       </c>
       <c r="P25" s="7" cm="1">
         <f t="array" aca="1" ref="P25" ca="1">_FV(B25,"Volume")</f>
-        <v>8740645</v>
+        <v>11689693</v>
       </c>
       <c r="Q25" s="7" cm="1">
         <f t="array" aca="1" ref="Q25" ca="1">_FV(B25,"Volume average",TRUE)</f>
@@ -16145,7 +16145,7 @@
       </c>
       <c r="U25" s="7" cm="1">
         <f t="array" aca="1" ref="U25" ca="1">_FV(B25,"Market cap",TRUE)</f>
-        <v>465522887850</v>
+        <v>466744732700</v>
       </c>
       <c r="V25" s="7" cm="1">
         <f t="array" aca="1" ref="V25" ca="1">_FV(B25,"Shares outstanding",TRUE)</f>
@@ -16161,7 +16161,7 @@
       </c>
       <c r="C26" s="2">
         <f t="array" aca="1" ref="C26" ca="1">_FV(B26,"Last trade time",TRUE)</f>
-        <v>46191.626772488278</v>
+        <v>46191.666709999998</v>
       </c>
       <c r="D26" t="str">
         <f t="array" aca="1" ref="D26" ca="1">_FV(B26,"Currency")</f>
@@ -16169,19 +16169,19 @@
       </c>
       <c r="E26" s="3">
         <f t="array" aca="1" ref="E26" ca="1">_FV(B26,"Price")</f>
-        <v>118.11</v>
+        <v>118.42</v>
       </c>
       <c r="F26" s="4">
         <f t="array" aca="1" ref="F26" ca="1">_FV(B26,"Change (%)",TRUE)</f>
-        <v>6.6479999999999994E-3</v>
+        <v>9.2899999999999996E-3</v>
       </c>
       <c r="G26" s="5">
         <f t="array" aca="1" ref="G26" ca="1">_FV(B26,"Change")</f>
-        <v>0.78</v>
+        <v>1.0900000000000001</v>
       </c>
       <c r="H26" s="6">
         <f t="array" aca="1" ref="H26" ca="1">_FV(B26,"P/E",TRUE)</f>
-        <v>39.356900000000003</v>
+        <v>39.4602</v>
       </c>
       <c r="I26" s="6">
         <f t="array" aca="1" ref="I26" ca="1">_FV(B26,"Beta")</f>
@@ -16213,7 +16213,7 @@
       </c>
       <c r="P26" s="7">
         <f t="array" aca="1" ref="P26" ca="1">_FV(B26,"Volume")</f>
-        <v>8740645</v>
+        <v>11689693</v>
       </c>
       <c r="Q26" s="7">
         <f t="array" aca="1" ref="Q26" ca="1">_FV(B26,"Volume average",TRUE)</f>
@@ -16233,7 +16233,7 @@
       </c>
       <c r="U26" s="7">
         <f t="array" aca="1" ref="U26" ca="1">_FV(B26,"Market cap",TRUE)</f>
-        <v>465522887850</v>
+        <v>466744732700</v>
       </c>
       <c r="V26" s="7">
         <f t="array" aca="1" ref="V26" ca="1">_FV(B26,"Shares outstanding",TRUE)</f>
@@ -16249,7 +16249,7 @@
       </c>
       <c r="C27" s="2">
         <f t="array" aca="1" ref="C27" ca="1">_FV(B27,"Last trade time",TRUE)</f>
-        <v>46191.626733760939</v>
+        <v>46191.666688935155</v>
       </c>
       <c r="D27" t="str">
         <f t="array" aca="1" ref="D27" ca="1">_FV(B27,"Currency")</f>
@@ -16257,19 +16257,19 @@
       </c>
       <c r="E27" s="3">
         <f t="array" aca="1" ref="E27" ca="1">_FV(B27,"Price")</f>
-        <v>221.45</v>
+        <v>219.57</v>
       </c>
       <c r="F27" s="4">
         <f t="array" aca="1" ref="F27" ca="1">_FV(B27,"Change (%)",TRUE)</f>
-        <v>-2.2856999999999999E-2</v>
+        <v>-3.1152000000000003E-2</v>
       </c>
       <c r="G27" s="5">
         <f t="array" aca="1" ref="G27" ca="1">_FV(B27,"Change")</f>
-        <v>-5.18</v>
+        <v>-7.06</v>
       </c>
       <c r="H27" s="6">
         <f t="array" aca="1" ref="H27" ca="1">_FV(B27,"P/E",TRUE)</f>
-        <v>561.05899999999997</v>
+        <v>556.29589999999996</v>
       </c>
       <c r="I27" s="6">
         <f t="array" aca="1" ref="I27" ca="1">_FV(B27,"Beta")</f>
@@ -16301,7 +16301,7 @@
       </c>
       <c r="P27" s="7">
         <f t="array" aca="1" ref="P27" ca="1">_FV(B27,"Volume")</f>
-        <v>1865886</v>
+        <v>2247622</v>
       </c>
       <c r="Q27" s="7">
         <f t="array" aca="1" ref="Q27" ca="1">_FV(B27,"Volume average",TRUE)</f>
@@ -16321,7 +16321,7 @@
       </c>
       <c r="U27" s="7">
         <f t="array" aca="1" ref="U27" ca="1">_FV(B27,"Market cap",TRUE)</f>
-        <v>78827386290</v>
+        <v>78158181114</v>
       </c>
       <c r="V27" s="7">
         <f t="array" aca="1" ref="V27" ca="1">_FV(B27,"Shares outstanding",TRUE)</f>
@@ -16337,7 +16337,7 @@
       </c>
       <c r="C28" s="2" cm="1">
         <f t="array" aca="1" ref="C28" ca="1">_FV(B28,"Last trade time",TRUE)</f>
-        <v>46191.626767036716</v>
+        <v>46191.666698008594</v>
       </c>
       <c r="D28" t="str" cm="1">
         <f t="array" aca="1" ref="D28" ca="1">_FV(B28,"Currency")</f>
@@ -16345,19 +16345,19 @@
       </c>
       <c r="E28" s="3" cm="1">
         <f t="array" aca="1" ref="E28" ca="1">_FV(B28,"Price")</f>
-        <v>433.14</v>
+        <v>423.46</v>
       </c>
       <c r="F28" s="4" cm="1">
         <f t="array" aca="1" ref="F28" ca="1">_FV(B28,"Change (%)",TRUE)</f>
-        <v>3.2958000000000001E-2</v>
+        <v>9.8729999999999998E-3</v>
       </c>
       <c r="G28" s="5" cm="1">
         <f t="array" aca="1" ref="G28" ca="1">_FV(B28,"Change")</f>
-        <v>13.82</v>
+        <v>4.1399999999999997</v>
       </c>
       <c r="H28" s="6" cm="1">
         <f t="array" aca="1" ref="H28" ca="1">_FV(B28,"P/E",TRUE)</f>
-        <v>34.396700000000003</v>
+        <v>33.628</v>
       </c>
       <c r="I28" s="6" cm="1">
         <f t="array" aca="1" ref="I28" ca="1">_FV(B28,"Beta")</f>
@@ -16373,7 +16373,7 @@
       </c>
       <c r="L28" s="3" cm="1">
         <f t="array" aca="1" ref="L28" ca="1">_FV(B28,"High")</f>
-        <v>434.99970000000002</v>
+        <v>436</v>
       </c>
       <c r="M28" s="3" cm="1">
         <f t="array" aca="1" ref="M28" ca="1">_FV(B28,"Low")</f>
@@ -16389,7 +16389,7 @@
       </c>
       <c r="P28" s="7" cm="1">
         <f t="array" aca="1" ref="P28" ca="1">_FV(B28,"Volume")</f>
-        <v>2579019</v>
+        <v>3920614</v>
       </c>
       <c r="Q28" s="7" cm="1">
         <f t="array" aca="1" ref="Q28" ca="1">_FV(B28,"Volume average",TRUE)</f>
@@ -16409,7 +16409,7 @@
       </c>
       <c r="U28" s="7" cm="1">
         <f t="array" aca="1" ref="U28" ca="1">_FV(B28,"Market cap",TRUE)</f>
-        <v>280721499120</v>
+        <v>274447813680</v>
       </c>
       <c r="V28" s="7" cm="1">
         <f t="array" aca="1" ref="V28" ca="1">_FV(B28,"Shares outstanding",TRUE)</f>
@@ -16425,7 +16425,7 @@
       </c>
       <c r="C29" s="2" cm="1">
         <f t="array" aca="1" ref="C29" ca="1">_FV(B29,"Last trade time",TRUE)</f>
-        <v>46191.626755740625</v>
+        <v>46191.666689258593</v>
       </c>
       <c r="D29" t="str" cm="1">
         <f t="array" aca="1" ref="D29" ca="1">_FV(B29,"Currency")</f>
@@ -16433,19 +16433,19 @@
       </c>
       <c r="E29" s="3" cm="1">
         <f t="array" aca="1" ref="E29" ca="1">_FV(B29,"Price")</f>
-        <v>102.61</v>
+        <v>102.9</v>
       </c>
       <c r="F29" s="4" cm="1">
         <f t="array" aca="1" ref="F29" ca="1">_FV(B29,"Change (%)",TRUE)</f>
-        <v>1.7351000000000002E-2</v>
+        <v>2.0226000000000001E-2</v>
       </c>
       <c r="G29" s="5" cm="1">
         <f t="array" aca="1" ref="G29" ca="1">_FV(B29,"Change")</f>
-        <v>1.75</v>
+        <v>2.04</v>
       </c>
       <c r="H29" s="6" cm="1">
         <f t="array" aca="1" ref="H29" ca="1">_FV(B29,"P/E",TRUE)</f>
-        <v>16.419699999999999</v>
+        <v>16.466100000000001</v>
       </c>
       <c r="I29" s="6" cm="1">
         <f t="array" aca="1" ref="I29" ca="1">_FV(B29,"Beta")</f>
@@ -16461,7 +16461,7 @@
       </c>
       <c r="L29" s="3" cm="1">
         <f t="array" aca="1" ref="L29" ca="1">_FV(B29,"High")</f>
-        <v>102.61499999999999</v>
+        <v>102.95</v>
       </c>
       <c r="M29" s="3" cm="1">
         <f t="array" aca="1" ref="M29" ca="1">_FV(B29,"Low")</f>
@@ -16477,7 +16477,7 @@
       </c>
       <c r="P29" s="7" cm="1">
         <f t="array" aca="1" ref="P29" ca="1">_FV(B29,"Volume")</f>
-        <v>3869894</v>
+        <v>4995502</v>
       </c>
       <c r="Q29" s="7" cm="1">
         <f t="array" aca="1" ref="Q29" ca="1">_FV(B29,"Volume average",TRUE)</f>
@@ -16497,7 +16497,7 @@
       </c>
       <c r="U29" s="7" cm="1">
         <f t="array" aca="1" ref="U29" ca="1">_FV(B29,"Market cap",TRUE)</f>
-        <v>178183393710</v>
+        <v>178686981900</v>
       </c>
       <c r="V29" s="7" cm="1">
         <f t="array" aca="1" ref="V29" ca="1">_FV(B29,"Shares outstanding",TRUE)</f>
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C30" s="2" cm="1">
         <f t="array" aca="1" ref="C30" ca="1">_FV(B30,"Last trade time",TRUE)</f>
-        <v>46191.626741260938</v>
+        <v>46191.666724073439</v>
       </c>
       <c r="D30" t="str" cm="1">
         <f t="array" aca="1" ref="D30" ca="1">_FV(B30,"Currency")</f>
@@ -16521,19 +16521,19 @@
       </c>
       <c r="E30" s="3" cm="1">
         <f t="array" aca="1" ref="E30" ca="1">_FV(B30,"Price")</f>
-        <v>41.325000000000003</v>
+        <v>41.29</v>
       </c>
       <c r="F30" s="4" cm="1">
         <f t="array" aca="1" ref="F30" ca="1">_FV(B30,"Change (%)",TRUE)</f>
-        <v>1.818E-3</v>
+        <v>9.6969999999999999E-4</v>
       </c>
       <c r="G30" s="5" cm="1">
         <f t="array" aca="1" ref="G30" ca="1">_FV(B30,"Change")</f>
-        <v>7.4999999999999997E-2</v>
+        <v>0.04</v>
       </c>
       <c r="H30" s="6" cm="1">
         <f t="array" aca="1" ref="H30" ca="1">_FV(B30,"P/E",TRUE)</f>
-        <v>77.127700000000004</v>
+        <v>77.062299999999993</v>
       </c>
       <c r="I30" s="6" cm="1">
         <f t="array" aca="1" ref="I30" ca="1">_FV(B30,"Beta")</f>
@@ -16565,7 +16565,7 @@
       </c>
       <c r="P30" s="7" cm="1">
         <f t="array" aca="1" ref="P30" ca="1">_FV(B30,"Volume")</f>
-        <v>1373527</v>
+        <v>2007780</v>
       </c>
       <c r="Q30" s="7" cm="1">
         <f t="array" aca="1" ref="Q30" ca="1">_FV(B30,"Volume average",TRUE)</f>
@@ -16585,7 +16585,7 @@
       </c>
       <c r="U30" s="7" cm="1">
         <f t="array" aca="1" ref="U30" ca="1">_FV(B30,"Market cap",TRUE)</f>
-        <v>12045233302</v>
+        <v>12035031653</v>
       </c>
       <c r="V30" s="7" cm="1">
         <f t="array" aca="1" ref="V30" ca="1">_FV(B30,"Shares outstanding",TRUE)</f>
@@ -16601,7 +16601,7 @@
       </c>
       <c r="C31" s="2">
         <f t="array" aca="1" ref="C31" ca="1">_FV(B31,"Last trade time",TRUE)</f>
-        <v>46191.626755416408</v>
+        <v>46191.66669060156</v>
       </c>
       <c r="D31" t="str">
         <f t="array" aca="1" ref="D31" ca="1">_FV(B31,"Currency")</f>
@@ -16609,15 +16609,15 @@
       </c>
       <c r="E31" s="3">
         <f t="array" aca="1" ref="E31" ca="1">_FV(B31,"Price")</f>
-        <v>7.07</v>
+        <v>6.9249999999999998</v>
       </c>
       <c r="F31" s="4">
         <f t="array" aca="1" ref="F31" ca="1">_FV(B31,"Change (%)",TRUE)</f>
-        <v>5.6801000000000004E-2</v>
+        <v>3.5126999999999999E-2</v>
       </c>
       <c r="G31" s="5">
         <f t="array" aca="1" ref="G31" ca="1">_FV(B31,"Change")</f>
-        <v>0.38</v>
+        <v>0.23499999999999999</v>
       </c>
       <c r="H31" s="6">
         <f t="array" aca="1" ref="H31" ca="1">_FV(B31,"P/E",TRUE)</f>
@@ -16653,7 +16653,7 @@
       </c>
       <c r="P31" s="7">
         <f t="array" aca="1" ref="P31" ca="1">_FV(B31,"Volume")</f>
-        <v>1431300</v>
+        <v>1840432</v>
       </c>
       <c r="Q31" s="7">
         <f t="array" aca="1" ref="Q31" ca="1">_FV(B31,"Volume average",TRUE)</f>
@@ -16673,7 +16673,7 @@
       </c>
       <c r="U31" s="7">
         <f t="array" aca="1" ref="U31" ca="1">_FV(B31,"Market cap",TRUE)</f>
-        <v>1542344538</v>
+        <v>1510712295</v>
       </c>
       <c r="V31" s="7">
         <f t="array" aca="1" ref="V31" ca="1">_FV(B31,"Shares outstanding",TRUE)</f>
@@ -16689,7 +16689,7 @@
       </c>
       <c r="C32" s="2" cm="1">
         <f t="array" aca="1" ref="C32" ca="1">_FV(B32,"Last trade time",TRUE)</f>
-        <v>46191.62672765</v>
+        <v>46191.666728113283</v>
       </c>
       <c r="D32" t="str" cm="1">
         <f t="array" aca="1" ref="D32" ca="1">_FV(B32,"Currency")</f>
@@ -16697,19 +16697,19 @@
       </c>
       <c r="E32" s="3" cm="1">
         <f t="array" aca="1" ref="E32" ca="1">_FV(B32,"Price")</f>
-        <v>422.92</v>
+        <v>421.58</v>
       </c>
       <c r="F32" s="4" cm="1">
         <f t="array" aca="1" ref="F32" ca="1">_FV(B32,"Change (%)",TRUE)</f>
-        <v>3.2418999999999996E-2</v>
+        <v>2.9148E-2</v>
       </c>
       <c r="G32" s="5" cm="1">
         <f t="array" aca="1" ref="G32" ca="1">_FV(B32,"Change")</f>
-        <v>13.28</v>
+        <v>11.94</v>
       </c>
       <c r="H32" s="6" cm="1">
         <f t="array" aca="1" ref="H32" ca="1">_FV(B32,"P/E",TRUE)</f>
-        <v>41.345999999999997</v>
+        <v>41.215000000000003</v>
       </c>
       <c r="I32" s="6" cm="1">
         <f t="array" aca="1" ref="I32" ca="1">_FV(B32,"Beta")</f>
@@ -16741,7 +16741,7 @@
       </c>
       <c r="P32" s="7" cm="1">
         <f t="array" aca="1" ref="P32" ca="1">_FV(B32,"Volume")</f>
-        <v>953724</v>
+        <v>1128736</v>
       </c>
       <c r="Q32" s="7" cm="1">
         <f t="array" aca="1" ref="Q32" ca="1">_FV(B32,"Volume average",TRUE)</f>
@@ -16761,7 +16761,7 @@
       </c>
       <c r="U32" s="7" cm="1">
         <f t="array" aca="1" ref="U32" ca="1">_FV(B32,"Market cap",TRUE)</f>
-        <v>164219836000</v>
+        <v>163699514000</v>
       </c>
       <c r="V32" s="7" cm="1">
         <f t="array" aca="1" ref="V32" ca="1">_FV(B32,"Shares outstanding",TRUE)</f>
@@ -16777,7 +16777,7 @@
       </c>
       <c r="C33" s="2">
         <f t="array" aca="1" ref="C33" ca="1">_FV(B33,"Last trade time",TRUE)</f>
-        <v>46191.626701446097</v>
+        <v>46191.666690219528</v>
       </c>
       <c r="D33" t="str">
         <f t="array" aca="1" ref="D33" ca="1">_FV(B33,"Currency")</f>
@@ -16829,7 +16829,7 @@
       </c>
       <c r="P33" s="7">
         <f t="array" aca="1" ref="P33" ca="1">_FV(B33,"Volume")</f>
-        <v>1235510</v>
+        <v>1501428</v>
       </c>
       <c r="Q33" s="7">
         <f t="array" aca="1" ref="Q33" ca="1">_FV(B33,"Volume average",TRUE)</f>
@@ -16865,7 +16865,7 @@
       </c>
       <c r="C34" s="2" cm="1">
         <f t="array" aca="1" ref="C34" ca="1">_FV(B34,"Last trade time",TRUE)</f>
-        <v>46191.626754953126</v>
+        <v>46191.666679745314</v>
       </c>
       <c r="D34" t="str" cm="1">
         <f t="array" aca="1" ref="D34" ca="1">_FV(B34,"Currency")</f>
@@ -16873,19 +16873,19 @@
       </c>
       <c r="E34" s="3" cm="1">
         <f t="array" aca="1" ref="E34" ca="1">_FV(B34,"Price")</f>
-        <v>145.23500000000001</v>
+        <v>144.35</v>
       </c>
       <c r="F34" s="4" cm="1">
         <f t="array" aca="1" ref="F34" ca="1">_FV(B34,"Change (%)",TRUE)</f>
-        <v>7.5970000000000005E-3</v>
+        <v>1.457E-3</v>
       </c>
       <c r="G34" s="5" cm="1">
         <f t="array" aca="1" ref="G34" ca="1">_FV(B34,"Change")</f>
-        <v>1.095</v>
+        <v>0.21</v>
       </c>
       <c r="H34" s="6" cm="1">
         <f t="array" aca="1" ref="H34" ca="1">_FV(B34,"P/E",TRUE)</f>
-        <v>56.11</v>
+        <v>55.768000000000001</v>
       </c>
       <c r="I34" s="6" cm="1">
         <f t="array" aca="1" ref="I34" ca="1">_FV(B34,"Beta")</f>
@@ -16917,7 +16917,7 @@
       </c>
       <c r="P34" s="7" cm="1">
         <f t="array" aca="1" ref="P34" ca="1">_FV(B34,"Volume")</f>
-        <v>1686613</v>
+        <v>1974055</v>
       </c>
       <c r="Q34" s="7" cm="1">
         <f t="array" aca="1" ref="Q34" ca="1">_FV(B34,"Volume average",TRUE)</f>
@@ -16937,7 +16937,7 @@
       </c>
       <c r="U34" s="7" cm="1">
         <f t="array" aca="1" ref="U34" ca="1">_FV(B34,"Market cap",TRUE)</f>
-        <v>106406190374</v>
+        <v>105757796540</v>
       </c>
       <c r="V34" s="7" cm="1">
         <f t="array" aca="1" ref="V34" ca="1">_FV(B34,"Shares outstanding",TRUE)</f>
@@ -16953,7 +16953,7 @@
       </c>
       <c r="C35" s="2">
         <f t="array" aca="1" ref="C35" ca="1">_FV(B35,"Last trade time",TRUE)</f>
-        <v>46191.626777603909</v>
+        <v>46191.666716735941</v>
       </c>
       <c r="D35" t="str">
         <f t="array" aca="1" ref="D35" ca="1">_FV(B35,"Currency")</f>
@@ -16961,19 +16961,19 @@
       </c>
       <c r="E35" s="3">
         <f t="array" aca="1" ref="E35" ca="1">_FV(B35,"Price")</f>
-        <v>361.48</v>
+        <v>364.3</v>
       </c>
       <c r="F35" s="4">
         <f t="array" aca="1" ref="F35" ca="1">_FV(B35,"Change (%)",TRUE)</f>
-        <v>-1.712E-3</v>
+        <v>6.0760000000000007E-3</v>
       </c>
       <c r="G35" s="5">
         <f t="array" aca="1" ref="G35" ca="1">_FV(B35,"Change")</f>
-        <v>-0.62</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="H35" s="6">
         <f t="array" aca="1" ref="H35" ca="1">_FV(B35,"P/E",TRUE)</f>
-        <v>27.6067</v>
+        <v>27.822099999999999</v>
       </c>
       <c r="I35" s="6">
         <f t="array" aca="1" ref="I35" ca="1">_FV(B35,"Beta")</f>
@@ -17005,7 +17005,7 @@
       </c>
       <c r="P35" s="7">
         <f t="array" aca="1" ref="P35" ca="1">_FV(B35,"Volume")</f>
-        <v>7795863</v>
+        <v>9162857</v>
       </c>
       <c r="Q35" s="7">
         <f t="array" aca="1" ref="Q35" ca="1">_FV(B35,"Volume average",TRUE)</f>
@@ -17025,7 +17025,7 @@
       </c>
       <c r="U35" s="7">
         <f t="array" aca="1" ref="U35" ca="1">_FV(B35,"Market cap",TRUE)</f>
-        <v>4400859948800</v>
+        <v>4435192208000</v>
       </c>
       <c r="V35" s="7">
         <f t="array" aca="1" ref="V35" ca="1">_FV(B35,"Shares outstanding",TRUE)</f>
@@ -17041,7 +17041,7 @@
       </c>
       <c r="C36" s="2">
         <f t="array" aca="1" ref="C36" ca="1">_FV(B36,"Last trade time",TRUE)</f>
-        <v>46191.626773865624</v>
+        <v>46191.666712904691</v>
       </c>
       <c r="D36" t="str">
         <f t="array" aca="1" ref="D36" ca="1">_FV(B36,"Currency")</f>
@@ -17049,19 +17049,19 @@
       </c>
       <c r="E36" s="3">
         <f t="array" aca="1" ref="E36" ca="1">_FV(B36,"Price")</f>
-        <v>108.7</v>
+        <v>105.815</v>
       </c>
       <c r="F36" s="4">
         <f t="array" aca="1" ref="F36" ca="1">_FV(B36,"Change (%)",TRUE)</f>
-        <v>3.3270000000000001E-2</v>
+        <v>5.8460000000000005E-3</v>
       </c>
       <c r="G36" s="5">
         <f t="array" aca="1" ref="G36" ca="1">_FV(B36,"Change")</f>
-        <v>3.5</v>
+        <v>0.61499999999999999</v>
       </c>
       <c r="H36" s="6">
         <f t="array" aca="1" ref="H36" ca="1">_FV(B36,"P/E",TRUE)</f>
-        <v>60.469499999999996</v>
+        <v>58.864600000000003</v>
       </c>
       <c r="I36" s="6">
         <f t="array" aca="1" ref="I36" ca="1">_FV(B36,"Beta")</f>
@@ -17077,7 +17077,7 @@
       </c>
       <c r="L36" s="3">
         <f t="array" aca="1" ref="L36" ca="1">_FV(B36,"High")</f>
-        <v>108.93</v>
+        <v>109.08</v>
       </c>
       <c r="M36" s="3">
         <f t="array" aca="1" ref="M36" ca="1">_FV(B36,"Low")</f>
@@ -17093,7 +17093,7 @@
       </c>
       <c r="P36" s="7">
         <f t="array" aca="1" ref="P36" ca="1">_FV(B36,"Volume")</f>
-        <v>14669737</v>
+        <v>19287151</v>
       </c>
       <c r="Q36" s="7">
         <f t="array" aca="1" ref="Q36" ca="1">_FV(B36,"Volume average",TRUE)</f>
@@ -17113,7 +17113,7 @@
       </c>
       <c r="U36" s="7">
         <f t="array" aca="1" ref="U36" ca="1">_FV(B36,"Market cap",TRUE)</f>
-        <v>97884904370</v>
+        <v>95286947156</v>
       </c>
       <c r="V36" s="7">
         <f t="array" aca="1" ref="V36" ca="1">_FV(B36,"Shares outstanding",TRUE)</f>
@@ -17129,7 +17129,7 @@
       </c>
       <c r="C37" s="2">
         <f t="array" aca="1" ref="C37" ca="1">_FV(B37,"Last trade time",TRUE)</f>
-        <v>46191.626774652344</v>
+        <v>46191.666704941403</v>
       </c>
       <c r="D37" t="str">
         <f t="array" aca="1" ref="D37" ca="1">_FV(B37,"Currency")</f>
@@ -17137,19 +17137,19 @@
       </c>
       <c r="E37" s="3">
         <f t="array" aca="1" ref="E37" ca="1">_FV(B37,"Price")</f>
-        <v>247.77</v>
+        <v>247.44499999999999</v>
       </c>
       <c r="F37" s="4">
         <f t="array" aca="1" ref="F37" ca="1">_FV(B37,"Change (%)",TRUE)</f>
-        <v>-5.5574999999999999E-2</v>
+        <v>-5.6813000000000002E-2</v>
       </c>
       <c r="G37" s="5">
         <f t="array" aca="1" ref="G37" ca="1">_FV(B37,"Change")</f>
-        <v>-14.58</v>
+        <v>-14.904999999999999</v>
       </c>
       <c r="H37" s="6">
         <f t="array" aca="1" ref="H37" ca="1">_FV(B37,"P/E",TRUE)</f>
-        <v>19.8279</v>
+        <v>19.8019</v>
       </c>
       <c r="I37" s="6">
         <f t="array" aca="1" ref="I37" ca="1">_FV(B37,"Beta")</f>
@@ -17181,7 +17181,7 @@
       </c>
       <c r="P37" s="7">
         <f t="array" aca="1" ref="P37" ca="1">_FV(B37,"Volume")</f>
-        <v>6155127</v>
+        <v>7171116</v>
       </c>
       <c r="Q37" s="7">
         <f t="array" aca="1" ref="Q37" ca="1">_FV(B37,"Volume average",TRUE)</f>
@@ -17201,7 +17201,7 @@
       </c>
       <c r="U37" s="7">
         <f t="array" aca="1" ref="U37" ca="1">_FV(B37,"Market cap",TRUE)</f>
-        <v>232875380781</v>
+        <v>232569918058</v>
       </c>
       <c r="V37" s="7">
         <f t="array" aca="1" ref="V37" ca="1">_FV(B37,"Shares outstanding",TRUE)</f>
@@ -17217,7 +17217,7 @@
       </c>
       <c r="C38" s="2">
         <f t="array" aca="1" ref="C38" ca="1">_FV(B38,"Last trade time",TRUE)</f>
-        <v>46191.626714617967</v>
+        <v>46191.666686469529</v>
       </c>
       <c r="D38" t="str">
         <f t="array" aca="1" ref="D38" ca="1">_FV(B38,"Currency")</f>
@@ -17225,19 +17225,19 @@
       </c>
       <c r="E38" s="3">
         <f t="array" aca="1" ref="E38" ca="1">_FV(B38,"Price")</f>
-        <v>95.23</v>
+        <v>94.649900000000002</v>
       </c>
       <c r="F38" s="4">
         <f t="array" aca="1" ref="F38" ca="1">_FV(B38,"Change (%)",TRUE)</f>
-        <v>-7.1108000000000005E-2</v>
+        <v>-7.6766000000000001E-2</v>
       </c>
       <c r="G38" s="5">
         <f t="array" aca="1" ref="G38" ca="1">_FV(B38,"Change")</f>
-        <v>-7.29</v>
+        <v>-7.8700999999999999</v>
       </c>
       <c r="H38" s="6">
         <f t="array" aca="1" ref="H38" ca="1">_FV(B38,"P/E",TRUE)</f>
-        <v>85.684700000000007</v>
+        <v>85.162800000000004</v>
       </c>
       <c r="I38" s="6">
         <f t="array" aca="1" ref="I38" ca="1">_FV(B38,"Beta")</f>
@@ -17269,7 +17269,7 @@
       </c>
       <c r="P38" s="7">
         <f t="array" aca="1" ref="P38" ca="1">_FV(B38,"Volume")</f>
-        <v>664431</v>
+        <v>827859</v>
       </c>
       <c r="Q38" s="7">
         <f t="array" aca="1" ref="Q38" ca="1">_FV(B38,"Volume average",TRUE)</f>
@@ -17305,7 +17305,7 @@
       </c>
       <c r="C39" s="2">
         <f t="array" aca="1" ref="C39" ca="1">_FV(B39,"Last trade time",TRUE)</f>
-        <v>46191.626789628906</v>
+        <v>46191.666731272657</v>
       </c>
       <c r="D39" t="str">
         <f t="array" aca="1" ref="D39" ca="1">_FV(B39,"Currency")</f>
@@ -17313,15 +17313,15 @@
       </c>
       <c r="E39" s="3">
         <f t="array" aca="1" ref="E39" ca="1">_FV(B39,"Price")</f>
-        <v>130.58500000000001</v>
+        <v>133.095</v>
       </c>
       <c r="F39" s="4">
         <f t="array" aca="1" ref="F39" ca="1">_FV(B39,"Change (%)",TRUE)</f>
-        <v>7.8324000000000005E-2</v>
+        <v>9.9049999999999999E-2</v>
       </c>
       <c r="G39" s="5">
         <f t="array" aca="1" ref="G39" ca="1">_FV(B39,"Change")</f>
-        <v>9.4849999999999994</v>
+        <v>11.994999999999999</v>
       </c>
       <c r="H39" s="6">
         <f t="array" aca="1" ref="H39" ca="1">_FV(B39,"P/E",TRUE)</f>
@@ -17357,7 +17357,7 @@
       </c>
       <c r="P39" s="7">
         <f t="array" aca="1" ref="P39" ca="1">_FV(B39,"Volume")</f>
-        <v>84543699</v>
+        <v>105262624</v>
       </c>
       <c r="Q39" s="7">
         <f t="array" aca="1" ref="Q39" ca="1">_FV(B39,"Volume average",TRUE)</f>
@@ -17377,7 +17377,7 @@
       </c>
       <c r="U39" s="7">
         <f t="array" aca="1" ref="U39" ca="1">_FV(B39,"Market cap",TRUE)</f>
-        <v>656320210000</v>
+        <v>668935470000</v>
       </c>
       <c r="V39" s="7">
         <f t="array" aca="1" ref="V39" ca="1">_FV(B39,"Shares outstanding",TRUE)</f>
@@ -17393,7 +17393,7 @@
       </c>
       <c r="C40" s="2">
         <f t="array" aca="1" ref="C40" ca="1">_FV(B40,"Last trade time",TRUE)</f>
-        <v>46191.626764282031</v>
+        <v>46191.666716758591</v>
       </c>
       <c r="D40" t="str">
         <f t="array" aca="1" ref="D40" ca="1">_FV(B40,"Currency")</f>
@@ -17401,19 +17401,19 @@
       </c>
       <c r="E40" s="3">
         <f t="array" aca="1" ref="E40" ca="1">_FV(B40,"Price")</f>
-        <v>55.38</v>
+        <v>54.734999999999999</v>
       </c>
       <c r="F40" s="4">
         <f t="array" aca="1" ref="F40" ca="1">_FV(B40,"Change (%)",TRUE)</f>
-        <v>1.2617E-2</v>
+        <v>8.2280000000000005E-4</v>
       </c>
       <c r="G40" s="5">
         <f t="array" aca="1" ref="G40" ca="1">_FV(B40,"Change")</f>
-        <v>0.69</v>
+        <v>4.4999999999999998E-2</v>
       </c>
       <c r="H40" s="6">
         <f t="array" aca="1" ref="H40" ca="1">_FV(B40,"P/E",TRUE)</f>
-        <v>945.05119999999999</v>
+        <v>934.0444</v>
       </c>
       <c r="I40" s="6">
         <f t="array" aca="1" ref="I40" ca="1">_FV(B40,"Beta")</f>
@@ -17445,7 +17445,7 @@
       </c>
       <c r="P40" s="7">
         <f t="array" aca="1" ref="P40" ca="1">_FV(B40,"Volume")</f>
-        <v>7627739</v>
+        <v>9476644</v>
       </c>
       <c r="Q40" s="7">
         <f t="array" aca="1" ref="Q40" ca="1">_FV(B40,"Volume average",TRUE)</f>
@@ -17465,7 +17465,7 @@
       </c>
       <c r="U40" s="7">
         <f t="array" aca="1" ref="U40" ca="1">_FV(B40,"Market cap",TRUE)</f>
-        <v>20671692600</v>
+        <v>20430933450</v>
       </c>
       <c r="V40" s="7">
         <f t="array" aca="1" ref="V40" ca="1">_FV(B40,"Shares outstanding",TRUE)</f>
@@ -17481,7 +17481,7 @@
       </c>
       <c r="C41" s="2">
         <f t="array" aca="1" ref="C41" ca="1">_FV(B41,"Last trade time",TRUE)</f>
-        <v>46191.626770358591</v>
+        <v>46191.66673004609</v>
       </c>
       <c r="D41" t="str">
         <f t="array" aca="1" ref="D41" ca="1">_FV(B41,"Currency")</f>
@@ -17489,19 +17489,19 @@
       </c>
       <c r="E41" s="3">
         <f t="array" aca="1" ref="E41" ca="1">_FV(B41,"Price")</f>
-        <v>60.49</v>
+        <v>60.505000000000003</v>
       </c>
       <c r="F41" s="4">
         <f t="array" aca="1" ref="F41" ca="1">_FV(B41,"Change (%)",TRUE)</f>
-        <v>4.0957E-2</v>
+        <v>4.1215000000000002E-2</v>
       </c>
       <c r="G41" s="5">
         <f t="array" aca="1" ref="G41" ca="1">_FV(B41,"Change")</f>
-        <v>2.38</v>
+        <v>2.395</v>
       </c>
       <c r="H41" s="6">
         <f t="array" aca="1" ref="H41" ca="1">_FV(B41,"P/E",TRUE)</f>
-        <v>131.87270000000001</v>
+        <v>131.90539999999999</v>
       </c>
       <c r="I41" s="6">
         <f t="array" aca="1" ref="I41" ca="1">_FV(B41,"Beta")</f>
@@ -17533,7 +17533,7 @@
       </c>
       <c r="P41" s="7">
         <f t="array" aca="1" ref="P41" ca="1">_FV(B41,"Volume")</f>
-        <v>12626595</v>
+        <v>17465044</v>
       </c>
       <c r="Q41" s="7">
         <f t="array" aca="1" ref="Q41" ca="1">_FV(B41,"Volume average",TRUE)</f>
@@ -17553,7 +17553,7 @@
       </c>
       <c r="U41" s="7">
         <f t="array" aca="1" ref="U41" ca="1">_FV(B41,"Market cap",TRUE)</f>
-        <v>21617837563</v>
+        <v>21623198243</v>
       </c>
       <c r="V41" s="7">
         <f t="array" aca="1" ref="V41" ca="1">_FV(B41,"Shares outstanding",TRUE)</f>
@@ -17569,7 +17569,7 @@
       </c>
       <c r="C42" s="2" cm="1">
         <f t="array" aca="1" ref="C42" ca="1">_FV(B42,"Last trade time",TRUE)</f>
-        <v>46191.626776064062</v>
+        <v>46191.666715601561</v>
       </c>
       <c r="D42" t="str" cm="1">
         <f t="array" aca="1" ref="D42" ca="1">_FV(B42,"Currency")</f>
@@ -17577,15 +17577,15 @@
       </c>
       <c r="E42" s="3" cm="1">
         <f t="array" aca="1" ref="E42" ca="1">_FV(B42,"Price")</f>
-        <v>294.05500000000001</v>
+        <v>293.86</v>
       </c>
       <c r="F42" s="4" cm="1">
         <f t="array" aca="1" ref="F42" ca="1">_FV(B42,"Change (%)",TRUE)</f>
-        <v>1.4402999999999999E-2</v>
+        <v>1.3729999999999999E-2</v>
       </c>
       <c r="G42" s="5" cm="1">
         <f t="array" aca="1" ref="G42" ca="1">_FV(B42,"Change")</f>
-        <v>4.1749999999999998</v>
+        <v>3.98</v>
       </c>
       <c r="H42" s="6" t="e" vm="13">
         <f t="array" ref="H42">_FV(B42,"P/E",TRUE)</f>
@@ -17621,7 +17621,7 @@
       </c>
       <c r="P42" s="7" cm="1">
         <f t="array" aca="1" ref="P42" ca="1">_FV(B42,"Volume")</f>
-        <v>8975964</v>
+        <v>18315578</v>
       </c>
       <c r="Q42" s="7" cm="1">
         <f t="array" aca="1" ref="Q42" ca="1">_FV(B42,"Volume average",TRUE)</f>
@@ -17657,7 +17657,7 @@
       </c>
       <c r="C43" s="2" cm="1">
         <f t="array" aca="1" ref="C43" ca="1">_FV(B43,"Last trade time",TRUE)</f>
-        <v>46191.626778541409</v>
+        <v>46191.666717291409</v>
       </c>
       <c r="D43" t="str" cm="1">
         <f t="array" aca="1" ref="D43" ca="1">_FV(B43,"Currency")</f>
@@ -17665,19 +17665,19 @@
       </c>
       <c r="E43" s="3" cm="1">
         <f t="array" aca="1" ref="E43" ca="1">_FV(B43,"Price")</f>
-        <v>254.21</v>
+        <v>259.07</v>
       </c>
       <c r="F43" s="4" cm="1">
         <f t="array" aca="1" ref="F43" ca="1">_FV(B43,"Change (%)",TRUE)</f>
-        <v>6.4842999999999998E-2</v>
+        <v>8.5200999999999999E-2</v>
       </c>
       <c r="G43" s="5" cm="1">
         <f t="array" aca="1" ref="G43" ca="1">_FV(B43,"Change")</f>
-        <v>15.48</v>
+        <v>20.34</v>
       </c>
       <c r="H43" s="6" cm="1">
         <f t="array" aca="1" ref="H43" ca="1">_FV(B43,"P/E",TRUE)</f>
-        <v>71.973399999999998</v>
+        <v>73.349400000000003</v>
       </c>
       <c r="I43" s="6" cm="1">
         <f t="array" aca="1" ref="I43" ca="1">_FV(B43,"Beta")</f>
@@ -17693,7 +17693,7 @@
       </c>
       <c r="L43" s="3" cm="1">
         <f t="array" aca="1" ref="L43" ca="1">_FV(B43,"High")</f>
-        <v>258.59100000000001</v>
+        <v>259.36</v>
       </c>
       <c r="M43" s="3" cm="1">
         <f t="array" aca="1" ref="M43" ca="1">_FV(B43,"Low")</f>
@@ -17709,7 +17709,7 @@
       </c>
       <c r="P43" s="7" cm="1">
         <f t="array" aca="1" ref="P43" ca="1">_FV(B43,"Volume")</f>
-        <v>3589591</v>
+        <v>5477367</v>
       </c>
       <c r="Q43" s="7" cm="1">
         <f t="array" aca="1" ref="Q43" ca="1">_FV(B43,"Volume average",TRUE)</f>
@@ -17729,7 +17729,7 @@
       </c>
       <c r="U43" s="7" cm="1">
         <f t="array" aca="1" ref="U43" ca="1">_FV(B43,"Market cap",TRUE)</f>
-        <v>332068167750</v>
+        <v>338416664250</v>
       </c>
       <c r="V43" s="7" cm="1">
         <f t="array" aca="1" ref="V43" ca="1">_FV(B43,"Shares outstanding",TRUE)</f>
@@ -17745,7 +17745,7 @@
       </c>
       <c r="C44" s="2">
         <f t="array" aca="1" ref="C44" ca="1">_FV(B44,"Last trade time",TRUE)</f>
-        <v>46191.626780450781</v>
+        <v>46191.66671586797</v>
       </c>
       <c r="D44" t="str">
         <f t="array" aca="1" ref="D44" ca="1">_FV(B44,"Currency")</f>
@@ -17753,19 +17753,19 @@
       </c>
       <c r="E44" s="3">
         <f t="array" aca="1" ref="E44" ca="1">_FV(B44,"Price")</f>
-        <v>78.77</v>
+        <v>78.915000000000006</v>
       </c>
       <c r="F44" s="4">
         <f t="array" aca="1" ref="F44" ca="1">_FV(B44,"Change (%)",TRUE)</f>
-        <v>-1.4513E-2</v>
+        <v>-1.2699E-2</v>
       </c>
       <c r="G44" s="5">
         <f t="array" aca="1" ref="G44" ca="1">_FV(B44,"Change")</f>
-        <v>-1.1599999999999999</v>
+        <v>-1.0149999999999999</v>
       </c>
       <c r="H44" s="6">
         <f t="array" aca="1" ref="H44" ca="1">_FV(B44,"P/E",TRUE)</f>
-        <v>24.797699999999999</v>
+        <v>24.843399999999999</v>
       </c>
       <c r="I44" s="6">
         <f t="array" aca="1" ref="I44" ca="1">_FV(B44,"Beta")</f>
@@ -17797,7 +17797,7 @@
       </c>
       <c r="P44" s="7">
         <f t="array" aca="1" ref="P44" ca="1">_FV(B44,"Volume")</f>
-        <v>7469498</v>
+        <v>9006346</v>
       </c>
       <c r="Q44" s="7">
         <f t="array" aca="1" ref="Q44" ca="1">_FV(B44,"Volume average",TRUE)</f>
@@ -17817,7 +17817,7 @@
       </c>
       <c r="U44" s="7">
         <f t="array" aca="1" ref="U44" ca="1">_FV(B44,"Market cap",TRUE)</f>
-        <v>338906507140</v>
+        <v>339530367030</v>
       </c>
       <c r="V44" s="7">
         <f t="array" aca="1" ref="V44" ca="1">_FV(B44,"Shares outstanding",TRUE)</f>
@@ -17833,7 +17833,7 @@
       </c>
       <c r="C45" s="2">
         <f t="array" aca="1" ref="C45" ca="1">_FV(B45,"Last trade time",TRUE)</f>
-        <v>46191.62678247656</v>
+        <v>46191.66671064766</v>
       </c>
       <c r="D45" t="str">
         <f t="array" aca="1" ref="D45" ca="1">_FV(B45,"Currency")</f>
@@ -17841,15 +17841,15 @@
       </c>
       <c r="E45" s="3">
         <f t="array" aca="1" ref="E45" ca="1">_FV(B45,"Price")</f>
-        <v>14.91</v>
+        <v>14.83</v>
       </c>
       <c r="F45" s="4">
         <f t="array" aca="1" ref="F45" ca="1">_FV(B45,"Change (%)",TRUE)</f>
-        <v>2.1232999999999998E-2</v>
+        <v>1.5753E-2</v>
       </c>
       <c r="G45" s="5">
         <f t="array" aca="1" ref="G45" ca="1">_FV(B45,"Change")</f>
-        <v>0.31</v>
+        <v>0.23</v>
       </c>
       <c r="H45" s="6">
         <f t="array" aca="1" ref="H45" ca="1">_FV(B45,"P/E",TRUE)</f>
@@ -17869,7 +17869,7 @@
       </c>
       <c r="L45" s="3">
         <f t="array" aca="1" ref="L45" ca="1">_FV(B45,"High")</f>
-        <v>15.18</v>
+        <v>15.19</v>
       </c>
       <c r="M45" s="3">
         <f t="array" aca="1" ref="M45" ca="1">_FV(B45,"Low")</f>
@@ -17885,7 +17885,7 @@
       </c>
       <c r="P45" s="7">
         <f t="array" aca="1" ref="P45" ca="1">_FV(B45,"Volume")</f>
-        <v>901406</v>
+        <v>1510876</v>
       </c>
       <c r="Q45" s="7">
         <f t="array" aca="1" ref="Q45" ca="1">_FV(B45,"Volume average",TRUE)</f>
@@ -17905,7 +17905,7 @@
       </c>
       <c r="U45" s="7">
         <f t="array" aca="1" ref="U45" ca="1">_FV(B45,"Market cap",TRUE)</f>
-        <v>989439677</v>
+        <v>984130812</v>
       </c>
       <c r="V45" s="7">
         <f t="array" aca="1" ref="V45" ca="1">_FV(B45,"Shares outstanding",TRUE)</f>
@@ -17921,7 +17921,7 @@
       </c>
       <c r="C46" s="2">
         <f t="array" aca="1" ref="C46" ca="1">_FV(B46,"Last trade time",TRUE)</f>
-        <v>46191.62675320547</v>
+        <v>46191.666734247658</v>
       </c>
       <c r="D46" t="str">
         <f t="array" aca="1" ref="D46" ca="1">_FV(B46,"Currency")</f>
@@ -17929,15 +17929,15 @@
       </c>
       <c r="E46" s="3">
         <f t="array" aca="1" ref="E46" ca="1">_FV(B46,"Price")</f>
-        <v>9.5299999999999994</v>
+        <v>9.3249999999999993</v>
       </c>
       <c r="F46" s="4">
         <f t="array" aca="1" ref="F46" ca="1">_FV(B46,"Change (%)",TRUE)</f>
-        <v>2.6939999999999999E-2</v>
+        <v>4.849E-3</v>
       </c>
       <c r="G46" s="5">
         <f t="array" aca="1" ref="G46" ca="1">_FV(B46,"Change")</f>
-        <v>0.25</v>
+        <v>4.4999999999999998E-2</v>
       </c>
       <c r="H46" s="6">
         <f t="array" aca="1" ref="H46" ca="1">_FV(B46,"P/E",TRUE)</f>
@@ -17961,7 +17961,7 @@
       </c>
       <c r="M46" s="3">
         <f t="array" aca="1" ref="M46" ca="1">_FV(B46,"Low")</f>
-        <v>9.3401999999999994</v>
+        <v>9.2799999999999994</v>
       </c>
       <c r="N46" s="3">
         <f t="array" aca="1" ref="N46" ca="1">_FV(B46,"Open")</f>
@@ -17973,7 +17973,7 @@
       </c>
       <c r="P46" s="7">
         <f t="array" aca="1" ref="P46" ca="1">_FV(B46,"Volume")</f>
-        <v>1030799</v>
+        <v>1451407</v>
       </c>
       <c r="Q46" s="7">
         <f t="array" aca="1" ref="Q46" ca="1">_FV(B46,"Volume average",TRUE)</f>
@@ -17993,7 +17993,7 @@
       </c>
       <c r="U46" s="7">
         <f t="array" aca="1" ref="U46" ca="1">_FV(B46,"Market cap",TRUE)</f>
-        <v>1468378588</v>
+        <v>1436792270</v>
       </c>
       <c r="V46" s="7">
         <f t="array" aca="1" ref="V46" ca="1">_FV(B46,"Shares outstanding",TRUE)</f>
@@ -18009,7 +18009,7 @@
       </c>
       <c r="C47" s="2" cm="1">
         <f t="array" aca="1" ref="C47" ca="1">_FV(B47,"Last trade time",TRUE)</f>
-        <v>46191.626764964843</v>
+        <v>46191.666710995312</v>
       </c>
       <c r="D47" t="str" cm="1">
         <f t="array" aca="1" ref="D47" ca="1">_FV(B47,"Currency")</f>
@@ -18017,19 +18017,19 @@
       </c>
       <c r="E47" s="3" cm="1">
         <f t="array" aca="1" ref="E47" ca="1">_FV(B47,"Price")</f>
-        <v>280.95170000000002</v>
+        <v>281.02999999999997</v>
       </c>
       <c r="F47" s="4" cm="1">
         <f t="array" aca="1" ref="F47" ca="1">_FV(B47,"Change (%)",TRUE)</f>
-        <v>-1.0105999999999999E-2</v>
+        <v>-9.8300000000000002E-3</v>
       </c>
       <c r="G47" s="5" cm="1">
         <f t="array" aca="1" ref="G47" ca="1">_FV(B47,"Change")</f>
-        <v>-2.8683000000000001</v>
+        <v>-2.79</v>
       </c>
       <c r="H47" s="6" cm="1">
         <f t="array" aca="1" ref="H47" ca="1">_FV(B47,"P/E",TRUE)</f>
-        <v>23.1585</v>
+        <v>23.164899999999999</v>
       </c>
       <c r="I47" s="6" cm="1">
         <f t="array" aca="1" ref="I47" ca="1">_FV(B47,"Beta")</f>
@@ -18061,7 +18061,7 @@
       </c>
       <c r="P47" s="7" cm="1">
         <f t="array" aca="1" ref="P47" ca="1">_FV(B47,"Volume")</f>
-        <v>1814082</v>
+        <v>2093257</v>
       </c>
       <c r="Q47" s="7" cm="1">
         <f t="array" aca="1" ref="Q47" ca="1">_FV(B47,"Volume average",TRUE)</f>
@@ -18081,7 +18081,7 @@
       </c>
       <c r="U47" s="7" cm="1">
         <f t="array" aca="1" ref="U47" ca="1">_FV(B47,"Market cap",TRUE)</f>
-        <v>199617840465</v>
+        <v>199673473076</v>
       </c>
       <c r="V47" s="7" cm="1">
         <f t="array" aca="1" ref="V47" ca="1">_FV(B47,"Shares outstanding",TRUE)</f>
@@ -18097,7 +18097,7 @@
       </c>
       <c r="C48" s="2" cm="1">
         <f t="array" aca="1" ref="C48" ca="1">_FV(B48,"Last trade time",TRUE)</f>
-        <v>46191.626707522657</v>
+        <v>46191.666695207816</v>
       </c>
       <c r="D48" t="str" cm="1">
         <f t="array" aca="1" ref="D48" ca="1">_FV(B48,"Currency")</f>
@@ -18105,15 +18105,15 @@
       </c>
       <c r="E48" s="3" cm="1">
         <f t="array" aca="1" ref="E48" ca="1">_FV(B48,"Price")</f>
-        <v>320.19</v>
+        <v>322.52</v>
       </c>
       <c r="F48" s="4" cm="1">
         <f t="array" aca="1" ref="F48" ca="1">_FV(B48,"Change (%)",TRUE)</f>
-        <v>-4.3324000000000001E-2</v>
+        <v>-3.6361999999999998E-2</v>
       </c>
       <c r="G48" s="5" cm="1">
         <f t="array" aca="1" ref="G48" ca="1">_FV(B48,"Change")</f>
-        <v>-14.5</v>
+        <v>-12.17</v>
       </c>
       <c r="H48" s="6" cm="1">
         <f t="array" aca="1" ref="H48" ca="1">_FV(B48,"P/E",TRUE)</f>
@@ -18149,7 +18149,7 @@
       </c>
       <c r="P48" s="7" cm="1">
         <f t="array" aca="1" ref="P48" ca="1">_FV(B48,"Volume")</f>
-        <v>551369</v>
+        <v>815449</v>
       </c>
       <c r="Q48" s="7" cm="1">
         <f t="array" aca="1" ref="Q48" ca="1">_FV(B48,"Volume average",TRUE)</f>
@@ -18169,7 +18169,7 @@
       </c>
       <c r="U48" s="7" cm="1">
         <f t="array" aca="1" ref="U48" ca="1">_FV(B48,"Market cap",TRUE)</f>
-        <v>25753499666</v>
+        <v>25940906063</v>
       </c>
       <c r="V48" s="7" cm="1">
         <f t="array" aca="1" ref="V48" ca="1">_FV(B48,"Shares outstanding",TRUE)</f>
@@ -18185,7 +18185,7 @@
       </c>
       <c r="C49" s="2">
         <f t="array" aca="1" ref="C49" ca="1">_FV(B49,"Last trade time",TRUE)</f>
-        <v>46191.626765323439</v>
+        <v>46191.666741435154</v>
       </c>
       <c r="D49" t="str">
         <f t="array" aca="1" ref="D49" ca="1">_FV(B49,"Currency")</f>
@@ -18193,19 +18193,19 @@
       </c>
       <c r="E49" s="3">
         <f t="array" aca="1" ref="E49" ca="1">_FV(B49,"Price")</f>
-        <v>572.57000000000005</v>
+        <v>577.255</v>
       </c>
       <c r="F49" s="4">
         <f t="array" aca="1" ref="F49" ca="1">_FV(B49,"Change (%)",TRUE)</f>
-        <v>8.7919999999999995E-3</v>
+        <v>1.7045999999999999E-2</v>
       </c>
       <c r="G49" s="5">
         <f t="array" aca="1" ref="G49" ca="1">_FV(B49,"Change")</f>
-        <v>4.99</v>
+        <v>9.6750000000000007</v>
       </c>
       <c r="H49" s="6">
         <f t="array" aca="1" ref="H49" ca="1">_FV(B49,"P/E",TRUE)</f>
-        <v>17.366900000000001</v>
+        <v>17.509</v>
       </c>
       <c r="I49" s="6">
         <f t="array" aca="1" ref="I49" ca="1">_FV(B49,"Beta")</f>
@@ -18221,7 +18221,7 @@
       </c>
       <c r="L49" s="3">
         <f t="array" aca="1" ref="L49" ca="1">_FV(B49,"High")</f>
-        <v>576.6</v>
+        <v>578.69000000000005</v>
       </c>
       <c r="M49" s="3">
         <f t="array" aca="1" ref="M49" ca="1">_FV(B49,"Low")</f>
@@ -18237,7 +18237,7 @@
       </c>
       <c r="P49" s="7">
         <f t="array" aca="1" ref="P49" ca="1">_FV(B49,"Volume")</f>
-        <v>7649280</v>
+        <v>9513579</v>
       </c>
       <c r="Q49" s="7">
         <f t="array" aca="1" ref="Q49" ca="1">_FV(B49,"Volume average",TRUE)</f>
@@ -18257,7 +18257,7 @@
       </c>
       <c r="U49" s="7">
         <f t="array" aca="1" ref="U49" ca="1">_FV(B49,"Market cap",TRUE)</f>
-        <v>1453424857110</v>
+        <v>1465317368865</v>
       </c>
       <c r="V49" s="7">
         <f t="array" aca="1" ref="V49" ca="1">_FV(B49,"Shares outstanding",TRUE)</f>
@@ -18273,7 +18273,7 @@
       </c>
       <c r="C50" s="2">
         <f t="array" aca="1" ref="C50" ca="1">_FV(B50,"Last trade time",TRUE)</f>
-        <v>46191.626778298436</v>
+        <v>46191.666721503905</v>
       </c>
       <c r="D50" t="str">
         <f t="array" aca="1" ref="D50" ca="1">_FV(B50,"Currency")</f>
@@ -18281,19 +18281,19 @@
       </c>
       <c r="E50" s="3">
         <f t="array" aca="1" ref="E50" ca="1">_FV(B50,"Price")</f>
-        <v>324.68</v>
+        <v>324.29000000000002</v>
       </c>
       <c r="F50" s="4">
         <f t="array" aca="1" ref="F50" ca="1">_FV(B50,"Change (%)",TRUE)</f>
-        <v>0.121365</v>
+        <v>0.120018</v>
       </c>
       <c r="G50" s="5">
         <f t="array" aca="1" ref="G50" ca="1">_FV(B50,"Change")</f>
-        <v>35.14</v>
+        <v>34.75</v>
       </c>
       <c r="H50" s="6">
         <f t="array" aca="1" ref="H50" ca="1">_FV(B50,"P/E",TRUE)</f>
-        <v>111.21080000000001</v>
+        <v>111.0772</v>
       </c>
       <c r="I50" s="6">
         <f t="array" aca="1" ref="I50" ca="1">_FV(B50,"Beta")</f>
@@ -18301,7 +18301,7 @@
       </c>
       <c r="J50" s="3">
         <f t="array" aca="1" ref="J50" ca="1">_FV(B50,"52 week high",TRUE)</f>
-        <v>325.92</v>
+        <v>326.20999999999998</v>
       </c>
       <c r="K50" s="3">
         <f t="array" aca="1" ref="K50" ca="1">_FV(B50,"52 week low",TRUE)</f>
@@ -18309,7 +18309,7 @@
       </c>
       <c r="L50" s="3">
         <f t="array" aca="1" ref="L50" ca="1">_FV(B50,"High")</f>
-        <v>325.92</v>
+        <v>326.20999999999998</v>
       </c>
       <c r="M50" s="3">
         <f t="array" aca="1" ref="M50" ca="1">_FV(B50,"Low")</f>
@@ -18325,7 +18325,7 @@
       </c>
       <c r="P50" s="7">
         <f t="array" aca="1" ref="P50" ca="1">_FV(B50,"Volume")</f>
-        <v>27655856</v>
+        <v>35795838</v>
       </c>
       <c r="Q50" s="7">
         <f t="array" aca="1" ref="Q50" ca="1">_FV(B50,"Volume average",TRUE)</f>
@@ -18345,7 +18345,7 @@
       </c>
       <c r="U50" s="7">
         <f t="array" aca="1" ref="U50" ca="1">_FV(B50,"Market cap",TRUE)</f>
-        <v>284030064000</v>
+        <v>283688892000</v>
       </c>
       <c r="V50" s="7">
         <f t="array" aca="1" ref="V50" ca="1">_FV(B50,"Shares outstanding",TRUE)</f>
@@ -18361,7 +18361,7 @@
       </c>
       <c r="C51" s="2">
         <f t="array" aca="1" ref="C51" ca="1">_FV(B51,"Last trade time",TRUE)</f>
-        <v>46191.626791376562</v>
+        <v>46191.666740439061</v>
       </c>
       <c r="D51" t="str">
         <f t="array" aca="1" ref="D51" ca="1">_FV(B51,"Currency")</f>
@@ -18369,19 +18369,19 @@
       </c>
       <c r="E51" s="3">
         <f t="array" aca="1" ref="E51" ca="1">_FV(B51,"Price")</f>
-        <v>376.61</v>
+        <v>378.01</v>
       </c>
       <c r="F51" s="4">
         <f t="array" aca="1" ref="F51" ca="1">_FV(B51,"Change (%)",TRUE)</f>
-        <v>-6.0699999999999999E-3</v>
+        <v>-2.3749999999999999E-3</v>
       </c>
       <c r="G51" s="5">
         <f t="array" aca="1" ref="G51" ca="1">_FV(B51,"Change")</f>
-        <v>-2.2999999999999998</v>
+        <v>-0.9</v>
       </c>
       <c r="H51" s="6">
         <f t="array" aca="1" ref="H51" ca="1">_FV(B51,"P/E",TRUE)</f>
-        <v>22.431100000000001</v>
+        <v>22.514500000000002</v>
       </c>
       <c r="I51" s="6">
         <f t="array" aca="1" ref="I51" ca="1">_FV(B51,"Beta")</f>
@@ -18413,7 +18413,7 @@
       </c>
       <c r="P51" s="7">
         <f t="array" aca="1" ref="P51" ca="1">_FV(B51,"Volume")</f>
-        <v>20441657</v>
+        <v>24695489</v>
       </c>
       <c r="Q51" s="7">
         <f t="array" aca="1" ref="Q51" ca="1">_FV(B51,"Volume average",TRUE)</f>
@@ -18433,7 +18433,7 @@
       </c>
       <c r="U51" s="7">
         <f t="array" aca="1" ref="U51" ca="1">_FV(B51,"Market cap",TRUE)</f>
-        <v>2797622905350</v>
+        <v>2808022714350</v>
       </c>
       <c r="V51" s="7">
         <f t="array" aca="1" ref="V51" ca="1">_FV(B51,"Shares outstanding",TRUE)</f>
@@ -18449,7 +18449,7 @@
       </c>
       <c r="C52" s="2">
         <f t="array" aca="1" ref="C52" ca="1">_FV(B52,"Last trade time",TRUE)</f>
-        <v>46191.626765647656</v>
+        <v>46191.666729652345</v>
       </c>
       <c r="D52" t="str">
         <f t="array" aca="1" ref="D52" ca="1">_FV(B52,"Currency")</f>
@@ -18457,15 +18457,15 @@
       </c>
       <c r="E52" s="3">
         <f t="array" aca="1" ref="E52" ca="1">_FV(B52,"Price")</f>
-        <v>114.3</v>
+        <v>110.51</v>
       </c>
       <c r="F52" s="4">
         <f t="array" aca="1" ref="F52" ca="1">_FV(B52,"Change (%)",TRUE)</f>
-        <v>-1.9389E-2</v>
+        <v>-5.1905E-2</v>
       </c>
       <c r="G52" s="5">
         <f t="array" aca="1" ref="G52" ca="1">_FV(B52,"Change")</f>
-        <v>-2.2599999999999998</v>
+        <v>-6.05</v>
       </c>
       <c r="H52" s="6">
         <f t="array" aca="1" ref="H52" ca="1">_FV(B52,"P/E",TRUE)</f>
@@ -18489,7 +18489,7 @@
       </c>
       <c r="M52" s="3">
         <f t="array" aca="1" ref="M52" ca="1">_FV(B52,"Low")</f>
-        <v>111.7</v>
+        <v>110.05</v>
       </c>
       <c r="N52" s="3">
         <f t="array" aca="1" ref="N52" ca="1">_FV(B52,"Open")</f>
@@ -18501,7 +18501,7 @@
       </c>
       <c r="P52" s="7">
         <f t="array" aca="1" ref="P52" ca="1">_FV(B52,"Volume")</f>
-        <v>9354058</v>
+        <v>13564399</v>
       </c>
       <c r="Q52" s="7">
         <f t="array" aca="1" ref="Q52" ca="1">_FV(B52,"Volume average",TRUE)</f>
@@ -18521,7 +18521,7 @@
       </c>
       <c r="U52" s="7">
         <f t="array" aca="1" ref="U52" ca="1">_FV(B52,"Market cap",TRUE)</f>
-        <v>40942019970</v>
+        <v>39584449929</v>
       </c>
       <c r="V52" s="7">
         <f t="array" aca="1" ref="V52" ca="1">_FV(B52,"Shares outstanding",TRUE)</f>
@@ -18537,7 +18537,7 @@
       </c>
       <c r="C53" s="2">
         <f t="array" aca="1" ref="C53" ca="1">_FV(B53,"Last trade time",TRUE)</f>
-        <v>46191.626774652344</v>
+        <v>46191.666728448436</v>
       </c>
       <c r="D53" t="str">
         <f t="array" aca="1" ref="D53" ca="1">_FV(B53,"Currency")</f>
@@ -18545,19 +18545,19 @@
       </c>
       <c r="E53" s="3">
         <f t="array" aca="1" ref="E53" ca="1">_FV(B53,"Price")</f>
-        <v>1129.9349999999999</v>
+        <v>1125.7449999999999</v>
       </c>
       <c r="F53" s="4">
         <f t="array" aca="1" ref="F53" ca="1">_FV(B53,"Change (%)",TRUE)</f>
-        <v>8.3154000000000006E-2</v>
+        <v>7.9136999999999999E-2</v>
       </c>
       <c r="G53" s="5">
         <f t="array" aca="1" ref="G53" ca="1">_FV(B53,"Change")</f>
-        <v>86.745000000000005</v>
+        <v>82.555000000000007</v>
       </c>
       <c r="H53" s="6">
         <f t="array" aca="1" ref="H53" ca="1">_FV(B53,"P/E",TRUE)</f>
-        <v>53.3459</v>
+        <v>53.148099999999999</v>
       </c>
       <c r="I53" s="6">
         <f t="array" aca="1" ref="I53" ca="1">_FV(B53,"Beta")</f>
@@ -18565,7 +18565,7 @@
       </c>
       <c r="J53" s="3">
         <f t="array" aca="1" ref="J53" ca="1">_FV(B53,"52 week high",TRUE)</f>
-        <v>1130.71</v>
+        <v>1133.2399</v>
       </c>
       <c r="K53" s="3">
         <f t="array" aca="1" ref="K53" ca="1">_FV(B53,"52 week low",TRUE)</f>
@@ -18573,7 +18573,7 @@
       </c>
       <c r="L53" s="3">
         <f t="array" aca="1" ref="L53" ca="1">_FV(B53,"High")</f>
-        <v>1130.71</v>
+        <v>1133.2399</v>
       </c>
       <c r="M53" s="3">
         <f t="array" aca="1" ref="M53" ca="1">_FV(B53,"Low")</f>
@@ -18589,7 +18589,7 @@
       </c>
       <c r="P53" s="7">
         <f t="array" aca="1" ref="P53" ca="1">_FV(B53,"Volume")</f>
-        <v>20228699</v>
+        <v>25288839</v>
       </c>
       <c r="Q53" s="7">
         <f t="array" aca="1" ref="Q53" ca="1">_FV(B53,"Volume average",TRUE)</f>
@@ -18609,7 +18609,7 @@
       </c>
       <c r="U53" s="7">
         <f t="array" aca="1" ref="U53" ca="1">_FV(B53,"Market cap",TRUE)</f>
-        <v>1274266117290</v>
+        <v>1269540911829</v>
       </c>
       <c r="V53" s="7">
         <f t="array" aca="1" ref="V53" ca="1">_FV(B53,"Shares outstanding",TRUE)</f>
@@ -18625,7 +18625,7 @@
       </c>
       <c r="C54" s="2" cm="1">
         <f t="array" aca="1" ref="C54" ca="1">_FV(B54,"Last trade time",TRUE)</f>
-        <v>46191.626750010939</v>
+        <v>46191.666702106253</v>
       </c>
       <c r="D54" t="str" cm="1">
         <f t="array" aca="1" ref="D54" ca="1">_FV(B54,"Currency")</f>
@@ -18633,15 +18633,15 @@
       </c>
       <c r="E54" s="3" cm="1">
         <f t="array" aca="1" ref="E54" ca="1">_FV(B54,"Price")</f>
-        <v>223.51259999999999</v>
+        <v>221.535</v>
       </c>
       <c r="F54" s="4" cm="1">
         <f t="array" aca="1" ref="F54" ca="1">_FV(B54,"Change (%)",TRUE)</f>
-        <v>-1.4799E-2</v>
+        <v>-2.3515999999999999E-2</v>
       </c>
       <c r="G54" s="5" cm="1">
         <f t="array" aca="1" ref="G54" ca="1">_FV(B54,"Change")</f>
-        <v>-3.3574000000000002</v>
+        <v>-5.335</v>
       </c>
       <c r="H54" s="6" cm="1">
         <f t="array" aca="1" ref="H54" ca="1">_FV(B54,"P/E",TRUE)</f>
@@ -18677,7 +18677,7 @@
       </c>
       <c r="P54" s="7" cm="1">
         <f t="array" aca="1" ref="P54" ca="1">_FV(B54,"Volume")</f>
-        <v>998903</v>
+        <v>1277658</v>
       </c>
       <c r="Q54" s="7" cm="1">
         <f t="array" aca="1" ref="Q54" ca="1">_FV(B54,"Volume average",TRUE)</f>
@@ -18697,7 +18697,7 @@
       </c>
       <c r="U54" s="7" cm="1">
         <f t="array" aca="1" ref="U54" ca="1">_FV(B54,"Market cap",TRUE)</f>
-        <v>79333472838</v>
+        <v>78631544286</v>
       </c>
       <c r="V54" s="7" cm="1">
         <f t="array" aca="1" ref="V54" ca="1">_FV(B54,"Shares outstanding",TRUE)</f>
@@ -18713,7 +18713,7 @@
       </c>
       <c r="C55" s="2" cm="1">
         <f t="array" aca="1" ref="C55" ca="1">_FV(B55,"Last trade time",TRUE)</f>
-        <v>46191.615972222222</v>
+        <v>46191.655555555553</v>
       </c>
       <c r="D55" t="str" cm="1">
         <f t="array" aca="1" ref="D55" ca="1">_FV(B55,"Currency")</f>
@@ -18721,19 +18721,19 @@
       </c>
       <c r="E55" s="3" cm="1">
         <f t="array" aca="1" ref="E55" ca="1">_FV(B55,"Price")</f>
-        <v>39.380000000000003</v>
+        <v>39.734999999999999</v>
       </c>
       <c r="F55" s="4" cm="1">
         <f t="array" aca="1" ref="F55" ca="1">_FV(B55,"Change (%)",TRUE)</f>
-        <v>-1.0150000000000001E-3</v>
+        <v>7.9909999999999998E-3</v>
       </c>
       <c r="G55" s="5" cm="1">
         <f t="array" aca="1" ref="G55" ca="1">_FV(B55,"Change")</f>
-        <v>-0.04</v>
+        <v>0.315</v>
       </c>
       <c r="H55" s="6" cm="1">
         <f t="array" aca="1" ref="H55" ca="1">_FV(B55,"P/E",TRUE)</f>
-        <v>30.527100000000001</v>
+        <v>30.802299999999999</v>
       </c>
       <c r="I55" s="6" cm="1">
         <f t="array" aca="1" ref="I55" ca="1">_FV(B55,"Beta")</f>
@@ -18749,7 +18749,7 @@
       </c>
       <c r="L55" s="3" cm="1">
         <f t="array" aca="1" ref="L55" ca="1">_FV(B55,"High")</f>
-        <v>39.450000000000003</v>
+        <v>39.734999999999999</v>
       </c>
       <c r="M55" s="3" cm="1">
         <f t="array" aca="1" ref="M55" ca="1">_FV(B55,"Low")</f>
@@ -18765,7 +18765,7 @@
       </c>
       <c r="P55" s="7" cm="1">
         <f t="array" aca="1" ref="P55" ca="1">_FV(B55,"Volume")</f>
-        <v>6325</v>
+        <v>6345</v>
       </c>
       <c r="Q55" s="7" cm="1">
         <f t="array" aca="1" ref="Q55" ca="1">_FV(B55,"Volume average",TRUE)</f>
@@ -18801,7 +18801,7 @@
       </c>
       <c r="C56" s="2">
         <f t="array" aca="1" ref="C56" ca="1">_FV(B56,"Last trade time",TRUE)</f>
-        <v>46191.626762510939</v>
+        <v>46191.666703240626</v>
       </c>
       <c r="D56" t="str">
         <f t="array" aca="1" ref="D56" ca="1">_FV(B56,"Currency")</f>
@@ -18809,19 +18809,19 @@
       </c>
       <c r="E56" s="3">
         <f t="array" aca="1" ref="E56" ca="1">_FV(B56,"Price")</f>
-        <v>13.7385</v>
+        <v>13.595000000000001</v>
       </c>
       <c r="F56" s="4">
         <f t="array" aca="1" ref="F56" ca="1">_FV(B56,"Change (%)",TRUE)</f>
-        <v>-6.6159999999999995E-3</v>
+        <v>-1.6992E-2</v>
       </c>
       <c r="G56" s="5">
         <f t="array" aca="1" ref="G56" ca="1">_FV(B56,"Change")</f>
-        <v>-9.1499999999999998E-2</v>
+        <v>-0.23499999999999999</v>
       </c>
       <c r="H56" s="6">
         <f t="array" aca="1" ref="H56" ca="1">_FV(B56,"P/E",TRUE)</f>
-        <v>85.385300000000001</v>
+        <v>84.493499999999997</v>
       </c>
       <c r="I56" s="6">
         <f t="array" aca="1" ref="I56" ca="1">_FV(B56,"Beta")</f>
@@ -18853,7 +18853,7 @@
       </c>
       <c r="P56" s="7">
         <f t="array" aca="1" ref="P56" ca="1">_FV(B56,"Volume")</f>
-        <v>40182502</v>
+        <v>56034393</v>
       </c>
       <c r="Q56" s="7">
         <f t="array" aca="1" ref="Q56" ca="1">_FV(B56,"Volume average",TRUE)</f>
@@ -18873,7 +18873,7 @@
       </c>
       <c r="U56" s="7">
         <f t="array" aca="1" ref="U56" ca="1">_FV(B56,"Market cap",TRUE)</f>
-        <v>78889764240</v>
+        <v>78065752800</v>
       </c>
       <c r="V56" s="7">
         <f t="array" aca="1" ref="V56" ca="1">_FV(B56,"Shares outstanding",TRUE)</f>
@@ -18889,7 +18889,7 @@
       </c>
       <c r="C57" s="2">
         <f t="array" aca="1" ref="C57" ca="1">_FV(B57,"Last trade time",TRUE)</f>
-        <v>46191.62675308984</v>
+        <v>46191.666707777345</v>
       </c>
       <c r="D57" t="str">
         <f t="array" aca="1" ref="D57" ca="1">_FV(B57,"Currency")</f>
@@ -18897,19 +18897,19 @@
       </c>
       <c r="E57" s="3">
         <f t="array" aca="1" ref="E57" ca="1">_FV(B57,"Price")</f>
-        <v>95.86</v>
+        <v>95.075000000000003</v>
       </c>
       <c r="F57" s="4">
         <f t="array" aca="1" ref="F57" ca="1">_FV(B57,"Change (%)",TRUE)</f>
-        <v>3.98E-3</v>
+        <v>-4.2420000000000001E-3</v>
       </c>
       <c r="G57" s="5">
         <f t="array" aca="1" ref="G57" ca="1">_FV(B57,"Change")</f>
-        <v>0.38</v>
+        <v>-0.40500000000000003</v>
       </c>
       <c r="H57" s="6">
         <f t="array" aca="1" ref="H57" ca="1">_FV(B57,"P/E",TRUE)</f>
-        <v>57.012</v>
+        <v>56.545099999999998</v>
       </c>
       <c r="I57" s="6">
         <f t="array" aca="1" ref="I57" ca="1">_FV(B57,"Beta")</f>
@@ -18941,7 +18941,7 @@
       </c>
       <c r="P57" s="7">
         <f t="array" aca="1" ref="P57" ca="1">_FV(B57,"Volume")</f>
-        <v>12014595</v>
+        <v>14567961</v>
       </c>
       <c r="Q57" s="7">
         <f t="array" aca="1" ref="Q57" ca="1">_FV(B57,"Volume average",TRUE)</f>
@@ -18961,7 +18961,7 @@
       </c>
       <c r="U57" s="7">
         <f t="array" aca="1" ref="U57" ca="1">_FV(B57,"Market cap",TRUE)</f>
-        <v>98861184880</v>
+        <v>98051608100</v>
       </c>
       <c r="V57" s="7">
         <f t="array" aca="1" ref="V57" ca="1">_FV(B57,"Shares outstanding",TRUE)</f>
@@ -18977,7 +18977,7 @@
       </c>
       <c r="C58" s="2">
         <f t="array" aca="1" ref="C58" ca="1">_FV(B58,"Last trade time",TRUE)</f>
-        <v>46191.626757534374</v>
+        <v>46191.666705034375</v>
       </c>
       <c r="D58" t="str">
         <f t="array" aca="1" ref="D58" ca="1">_FV(B58,"Currency")</f>
@@ -18985,19 +18985,19 @@
       </c>
       <c r="E58" s="3">
         <f t="array" aca="1" ref="E58" ca="1">_FV(B58,"Price")</f>
-        <v>209.00559999999999</v>
+        <v>209.0599</v>
       </c>
       <c r="F58" s="4">
         <f t="array" aca="1" ref="F58" ca="1">_FV(B58,"Change (%)",TRUE)</f>
-        <v>2.1283E-2</v>
+        <v>2.1547999999999998E-2</v>
       </c>
       <c r="G58" s="5">
         <f t="array" aca="1" ref="G58" ca="1">_FV(B58,"Change")</f>
-        <v>4.3555999999999999</v>
+        <v>4.4099000000000004</v>
       </c>
       <c r="H58" s="6">
         <f t="array" aca="1" ref="H58" ca="1">_FV(B58,"P/E",TRUE)</f>
-        <v>32.006999999999998</v>
+        <v>32.015300000000003</v>
       </c>
       <c r="I58" s="6">
         <f t="array" aca="1" ref="I58" ca="1">_FV(B58,"Beta")</f>
@@ -19029,7 +19029,7 @@
       </c>
       <c r="P58" s="7">
         <f t="array" aca="1" ref="P58" ca="1">_FV(B58,"Volume")</f>
-        <v>61026518</v>
+        <v>73506622</v>
       </c>
       <c r="Q58" s="7">
         <f t="array" aca="1" ref="Q58" ca="1">_FV(B58,"Volume average",TRUE)</f>
@@ -19049,7 +19049,7 @@
       </c>
       <c r="U58" s="7">
         <f t="array" aca="1" ref="U58" ca="1">_FV(B58,"Market cap",TRUE)</f>
-        <v>5057935520000</v>
+        <v>5059249580000</v>
       </c>
       <c r="V58" s="7">
         <f t="array" aca="1" ref="V58" ca="1">_FV(B58,"Shares outstanding",TRUE)</f>
@@ -19065,7 +19065,7 @@
       </c>
       <c r="C59" s="2" cm="1">
         <f t="array" aca="1" ref="C59" ca="1">_FV(B59,"Last trade time",TRUE)</f>
-        <v>46191.626747626564</v>
+        <v>46191.666725219533</v>
       </c>
       <c r="D59" t="str" cm="1">
         <f t="array" aca="1" ref="D59" ca="1">_FV(B59,"Currency")</f>
@@ -19073,19 +19073,19 @@
       </c>
       <c r="E59" s="3" cm="1">
         <f t="array" aca="1" ref="E59" ca="1">_FV(B59,"Price")</f>
-        <v>119.69</v>
+        <v>120.11</v>
       </c>
       <c r="F59" s="4" cm="1">
         <f t="array" aca="1" ref="F59" ca="1">_FV(B59,"Change (%)",TRUE)</f>
-        <v>5.9954E-2</v>
+        <v>6.3673000000000007E-2</v>
       </c>
       <c r="G59" s="5" cm="1">
         <f t="array" aca="1" ref="G59" ca="1">_FV(B59,"Change")</f>
-        <v>6.77</v>
+        <v>7.19</v>
       </c>
       <c r="H59" s="6" cm="1">
         <f t="array" aca="1" ref="H59" ca="1">_FV(B59,"P/E",TRUE)</f>
-        <v>85.468400000000003</v>
+        <v>85.7684</v>
       </c>
       <c r="I59" s="6" cm="1">
         <f t="array" aca="1" ref="I59" ca="1">_FV(B59,"Beta")</f>
@@ -19117,7 +19117,7 @@
       </c>
       <c r="P59" s="7" cm="1">
         <f t="array" aca="1" ref="P59" ca="1">_FV(B59,"Volume")</f>
-        <v>3310901</v>
+        <v>4019342</v>
       </c>
       <c r="Q59" s="7" cm="1">
         <f t="array" aca="1" ref="Q59" ca="1">_FV(B59,"Volume average",TRUE)</f>
@@ -19137,7 +19137,7 @@
       </c>
       <c r="U59" s="7" cm="1">
         <f t="array" aca="1" ref="U59" ca="1">_FV(B59,"Market cap",TRUE)</f>
-        <v>46906894008</v>
+        <v>47071493352</v>
       </c>
       <c r="V59" s="7" cm="1">
         <f t="array" aca="1" ref="V59" ca="1">_FV(B59,"Shares outstanding",TRUE)</f>
@@ -19153,7 +19153,7 @@
       </c>
       <c r="C60" s="2">
         <f t="array" aca="1" ref="C60" ca="1">_FV(B60,"Last trade time",TRUE)</f>
-        <v>46191.626774652344</v>
+        <v>46191.666731492965</v>
       </c>
       <c r="D60" t="str">
         <f t="array" aca="1" ref="D60" ca="1">_FV(B60,"Currency")</f>
@@ -19161,19 +19161,19 @@
       </c>
       <c r="E60" s="3">
         <f t="array" aca="1" ref="E60" ca="1">_FV(B60,"Price")</f>
-        <v>9.2380999999999993</v>
+        <v>9.1150000000000002</v>
       </c>
       <c r="F60" s="4">
         <f t="array" aca="1" ref="F60" ca="1">_FV(B60,"Change (%)",TRUE)</f>
-        <v>1.295E-2</v>
+        <v>-5.4819999999999999E-4</v>
       </c>
       <c r="G60" s="5">
         <f t="array" aca="1" ref="G60" ca="1">_FV(B60,"Change")</f>
-        <v>0.1181</v>
+        <v>-5.0000000000000001E-3</v>
       </c>
       <c r="H60" s="6">
         <f t="array" aca="1" ref="H60" ca="1">_FV(B60,"P/E",TRUE)</f>
-        <v>23.293199999999999</v>
+        <v>22.982900000000001</v>
       </c>
       <c r="I60" s="6">
         <f t="array" aca="1" ref="I60" ca="1">_FV(B60,"Beta")</f>
@@ -19205,7 +19205,7 @@
       </c>
       <c r="P60" s="7">
         <f t="array" aca="1" ref="P60" ca="1">_FV(B60,"Volume")</f>
-        <v>22132853</v>
+        <v>27813314</v>
       </c>
       <c r="Q60" s="7">
         <f t="array" aca="1" ref="Q60" ca="1">_FV(B60,"Volume average",TRUE)</f>
@@ -19225,7 +19225,7 @@
       </c>
       <c r="U60" s="7">
         <f t="array" aca="1" ref="U60" ca="1">_FV(B60,"Market cap",TRUE)</f>
-        <v>4777929615</v>
+        <v>4714262504</v>
       </c>
       <c r="V60" s="7">
         <f t="array" aca="1" ref="V60" ca="1">_FV(B60,"Shares outstanding",TRUE)</f>
@@ -19241,7 +19241,7 @@
       </c>
       <c r="C61" s="2">
         <f t="array" aca="1" ref="C61" ca="1">_FV(B61,"Last trade time",TRUE)</f>
-        <v>46191.626773900003</v>
+        <v>46191.666741596877</v>
       </c>
       <c r="D61" t="str">
         <f t="array" aca="1" ref="D61" ca="1">_FV(B61,"Currency")</f>
@@ -19249,19 +19249,19 @@
       </c>
       <c r="E61" s="3">
         <f t="array" aca="1" ref="E61" ca="1">_FV(B61,"Price")</f>
-        <v>184.565</v>
+        <v>185.34989999999999</v>
       </c>
       <c r="F61" s="4">
         <f t="array" aca="1" ref="F61" ca="1">_FV(B61,"Change (%)",TRUE)</f>
-        <v>5.6389999999999999E-3</v>
+        <v>9.9160000000000012E-3</v>
       </c>
       <c r="G61" s="5">
         <f t="array" aca="1" ref="G61" ca="1">_FV(B61,"Change")</f>
-        <v>1.0349999999999999</v>
+        <v>1.8199000000000001</v>
       </c>
       <c r="H61" s="6">
         <f t="array" aca="1" ref="H61" ca="1">_FV(B61,"P/E",TRUE)</f>
-        <v>29.855699999999999</v>
+        <v>29.982700000000001</v>
       </c>
       <c r="I61" s="6">
         <f t="array" aca="1" ref="I61" ca="1">_FV(B61,"Beta")</f>
@@ -19277,7 +19277,7 @@
       </c>
       <c r="L61" s="3">
         <f t="array" aca="1" ref="L61" ca="1">_FV(B61,"High")</f>
-        <v>185.18119999999999</v>
+        <v>185.35</v>
       </c>
       <c r="M61" s="3">
         <f t="array" aca="1" ref="M61" ca="1">_FV(B61,"Low")</f>
@@ -19293,7 +19293,7 @@
       </c>
       <c r="P61" s="7">
         <f t="array" aca="1" ref="P61" ca="1">_FV(B61,"Volume")</f>
-        <v>8554815</v>
+        <v>10032305</v>
       </c>
       <c r="Q61" s="7">
         <f t="array" aca="1" ref="Q61" ca="1">_FV(B61,"Volume average",TRUE)</f>
@@ -19313,7 +19313,7 @@
       </c>
       <c r="U61" s="7">
         <f t="array" aca="1" ref="U61" ca="1">_FV(B61,"Market cap",TRUE)</f>
-        <v>530817429990</v>
+        <v>533074838495</v>
       </c>
       <c r="V61" s="7">
         <f t="array" aca="1" ref="V61" ca="1">_FV(B61,"Shares outstanding",TRUE)</f>
@@ -19329,7 +19329,7 @@
       </c>
       <c r="C62" s="2" cm="1">
         <f t="array" aca="1" ref="C62" ca="1">_FV(B62,"Last trade time",TRUE)</f>
-        <v>46191.626794803124</v>
+        <v>46191.666702568749</v>
       </c>
       <c r="D62" t="str" cm="1">
         <f t="array" aca="1" ref="D62" ca="1">_FV(B62,"Currency")</f>
@@ -19337,19 +19337,19 @@
       </c>
       <c r="E62" s="3" cm="1">
         <f t="array" aca="1" ref="E62" ca="1">_FV(B62,"Price")</f>
-        <v>283.73</v>
+        <v>283.75</v>
       </c>
       <c r="F62" s="4" cm="1">
         <f t="array" aca="1" ref="F62" ca="1">_FV(B62,"Change (%)",TRUE)</f>
-        <v>5.6710000000000007E-3</v>
+        <v>5.7420000000000006E-3</v>
       </c>
       <c r="G62" s="5" cm="1">
         <f t="array" aca="1" ref="G62" ca="1">_FV(B62,"Change")</f>
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="H62" s="6" cm="1">
         <f t="array" aca="1" ref="H62" ca="1">_FV(B62,"P/E",TRUE)</f>
-        <v>233.61879999999999</v>
+        <v>233.6352</v>
       </c>
       <c r="I62" s="6" cm="1">
         <f t="array" aca="1" ref="I62" ca="1">_FV(B62,"Beta")</f>
@@ -19381,7 +19381,7 @@
       </c>
       <c r="P62" s="7" cm="1">
         <f t="array" aca="1" ref="P62" ca="1">_FV(B62,"Volume")</f>
-        <v>2365524</v>
+        <v>2846807</v>
       </c>
       <c r="Q62" s="7" cm="1">
         <f t="array" aca="1" ref="Q62" ca="1">_FV(B62,"Volume average",TRUE)</f>
@@ -19401,7 +19401,7 @@
       </c>
       <c r="U62" s="7" cm="1">
         <f t="array" aca="1" ref="U62" ca="1">_FV(B62,"Market cap",TRUE)</f>
-        <v>231239950000</v>
+        <v>231256250000</v>
       </c>
       <c r="V62" s="7" cm="1">
         <f t="array" aca="1" ref="V62" ca="1">_FV(B62,"Shares outstanding",TRUE)</f>
@@ -19417,7 +19417,7 @@
       </c>
       <c r="C63" s="2">
         <f t="array" aca="1" ref="C63" ca="1">_FV(B63,"Last trade time",TRUE)</f>
-        <v>46191.626774687502</v>
+        <v>46191.666717488282</v>
       </c>
       <c r="D63" t="str">
         <f t="array" aca="1" ref="D63" ca="1">_FV(B63,"Currency")</f>
@@ -19425,19 +19425,19 @@
       </c>
       <c r="E63" s="3">
         <f t="array" aca="1" ref="E63" ca="1">_FV(B63,"Price")</f>
-        <v>10.27</v>
+        <v>10.185</v>
       </c>
       <c r="F63" s="4">
         <f t="array" aca="1" ref="F63" ca="1">_FV(B63,"Change (%)",TRUE)</f>
-        <v>3.9100000000000003E-3</v>
+        <v>-4.3990000000000001E-3</v>
       </c>
       <c r="G63" s="5">
         <f t="array" aca="1" ref="G63" ca="1">_FV(B63,"Change")</f>
-        <v>0.04</v>
+        <v>-4.4999999999999998E-2</v>
       </c>
       <c r="H63" s="6">
         <f t="array" aca="1" ref="H63" ca="1">_FV(B63,"P/E",TRUE)</f>
-        <v>17.071100000000001</v>
+        <v>16.9299</v>
       </c>
       <c r="I63" s="6">
         <f t="array" aca="1" ref="I63" ca="1">_FV(B63,"Beta")</f>
@@ -19469,7 +19469,7 @@
       </c>
       <c r="P63" s="7">
         <f t="array" aca="1" ref="P63" ca="1">_FV(B63,"Volume")</f>
-        <v>8547255</v>
+        <v>15272754</v>
       </c>
       <c r="Q63" s="7">
         <f t="array" aca="1" ref="Q63" ca="1">_FV(B63,"Volume average",TRUE)</f>
@@ -19489,7 +19489,7 @@
       </c>
       <c r="U63" s="7">
         <f t="array" aca="1" ref="U63" ca="1">_FV(B63,"Market cap",TRUE)</f>
-        <v>5321095481</v>
+        <v>5277055255</v>
       </c>
       <c r="V63" s="7">
         <f t="array" aca="1" ref="V63" ca="1">_FV(B63,"Shares outstanding",TRUE)</f>
@@ -19505,7 +19505,7 @@
       </c>
       <c r="C64" s="2" cm="1">
         <f t="array" aca="1" ref="C64" ca="1">_FV(B64,"Last trade time",TRUE)</f>
-        <v>46191.626786620312</v>
+        <v>46191.666723159375</v>
       </c>
       <c r="D64" t="str" cm="1">
         <f t="array" aca="1" ref="D64" ca="1">_FV(B64,"Currency")</f>
@@ -19513,19 +19513,19 @@
       </c>
       <c r="E64" s="3" cm="1">
         <f t="array" aca="1" ref="E64" ca="1">_FV(B64,"Price")</f>
-        <v>151.23500000000001</v>
+        <v>151.13</v>
       </c>
       <c r="F64" s="4" cm="1">
         <f t="array" aca="1" ref="F64" ca="1">_FV(B64,"Change (%)",TRUE)</f>
-        <v>4.483E-3</v>
+        <v>3.7859999999999999E-3</v>
       </c>
       <c r="G64" s="5" cm="1">
         <f t="array" aca="1" ref="G64" ca="1">_FV(B64,"Change")</f>
-        <v>0.67500000000000004</v>
+        <v>0.56999999999999995</v>
       </c>
       <c r="H64" s="6" cm="1">
         <f t="array" aca="1" ref="H64" ca="1">_FV(B64,"P/E",TRUE)</f>
-        <v>22.118099999999998</v>
+        <v>22.102799999999998</v>
       </c>
       <c r="I64" s="6" cm="1">
         <f t="array" aca="1" ref="I64" ca="1">_FV(B64,"Beta")</f>
@@ -19557,7 +19557,7 @@
       </c>
       <c r="P64" s="7" cm="1">
         <f t="array" aca="1" ref="P64" ca="1">_FV(B64,"Volume")</f>
-        <v>3801132</v>
+        <v>4553436</v>
       </c>
       <c r="Q64" s="7" cm="1">
         <f t="array" aca="1" ref="Q64" ca="1">_FV(B64,"Volume average",TRUE)</f>
@@ -19577,7 +19577,7 @@
       </c>
       <c r="U64" s="7" cm="1">
         <f t="array" aca="1" ref="U64" ca="1">_FV(B64,"Market cap",TRUE)</f>
-        <v>352165669765</v>
+        <v>351921166870</v>
       </c>
       <c r="V64" s="7" cm="1">
         <f t="array" aca="1" ref="V64" ca="1">_FV(B64,"Shares outstanding",TRUE)</f>
@@ -19593,7 +19593,7 @@
       </c>
       <c r="C65" s="2">
         <f t="array" aca="1" ref="C65" ca="1">_FV(B65,"Last trade time",TRUE)</f>
-        <v>46191.62676982578</v>
+        <v>46191.666677522655</v>
       </c>
       <c r="D65" t="str">
         <f t="array" aca="1" ref="D65" ca="1">_FV(B65,"Currency")</f>
@@ -19601,19 +19601,19 @@
       </c>
       <c r="E65" s="3">
         <f t="array" aca="1" ref="E65" ca="1">_FV(B65,"Price")</f>
-        <v>33.42</v>
+        <v>33.284999999999997</v>
       </c>
       <c r="F65" s="4">
         <f t="array" aca="1" ref="F65" ca="1">_FV(B65,"Change (%)",TRUE)</f>
-        <v>7.7716999999999994E-2</v>
+        <v>7.3362999999999998E-2</v>
       </c>
       <c r="G65" s="5">
         <f t="array" aca="1" ref="G65" ca="1">_FV(B65,"Change")</f>
-        <v>2.41</v>
+        <v>2.2749999999999999</v>
       </c>
       <c r="H65" s="6">
         <f t="array" aca="1" ref="H65" ca="1">_FV(B65,"P/E",TRUE)</f>
-        <v>12.2395</v>
+        <v>12.190099999999999</v>
       </c>
       <c r="I65" s="6">
         <f t="array" aca="1" ref="I65" ca="1">_FV(B65,"Beta")</f>
@@ -19629,7 +19629,7 @@
       </c>
       <c r="L65" s="3">
         <f t="array" aca="1" ref="L65" ca="1">_FV(B65,"High")</f>
-        <v>33.546199999999999</v>
+        <v>33.590000000000003</v>
       </c>
       <c r="M65" s="3">
         <f t="array" aca="1" ref="M65" ca="1">_FV(B65,"Low")</f>
@@ -19645,7 +19645,7 @@
       </c>
       <c r="P65" s="7">
         <f t="array" aca="1" ref="P65" ca="1">_FV(B65,"Volume")</f>
-        <v>547713</v>
+        <v>852995</v>
       </c>
       <c r="Q65" s="7">
         <f t="array" aca="1" ref="Q65" ca="1">_FV(B65,"Volume average",TRUE)</f>
@@ -19665,7 +19665,7 @@
       </c>
       <c r="U65" s="7">
         <f t="array" aca="1" ref="U65" ca="1">_FV(B65,"Market cap",TRUE)</f>
-        <v>1970566854</v>
+        <v>1962606754</v>
       </c>
       <c r="V65" s="7">
         <f t="array" aca="1" ref="V65" ca="1">_FV(B65,"Shares outstanding",TRUE)</f>
@@ -19681,7 +19681,7 @@
       </c>
       <c r="C66" s="2">
         <f t="array" aca="1" ref="C66" ca="1">_FV(B66,"Last trade time",TRUE)</f>
-        <v>46191.626767233596</v>
+        <v>46191.666697395311</v>
       </c>
       <c r="D66" t="str">
         <f t="array" aca="1" ref="D66" ca="1">_FV(B66,"Currency")</f>
@@ -19689,15 +19689,15 @@
       </c>
       <c r="E66" s="3">
         <f t="array" aca="1" ref="E66" ca="1">_FV(B66,"Price")</f>
-        <v>12.05</v>
+        <v>11.885</v>
       </c>
       <c r="F66" s="4">
         <f t="array" aca="1" ref="F66" ca="1">_FV(B66,"Change (%)",TRUE)</f>
-        <v>8.3680000000000004E-3</v>
+        <v>-5.4390000000000003E-3</v>
       </c>
       <c r="G66" s="5">
         <f t="array" aca="1" ref="G66" ca="1">_FV(B66,"Change")</f>
-        <v>0.1</v>
+        <v>-6.5000000000000002E-2</v>
       </c>
       <c r="H66" s="6">
         <f t="array" aca="1" ref="H66" ca="1">_FV(B66,"P/E",TRUE)</f>
@@ -19733,7 +19733,7 @@
       </c>
       <c r="P66" s="7">
         <f t="array" aca="1" ref="P66" ca="1">_FV(B66,"Volume")</f>
-        <v>7736379</v>
+        <v>9127576</v>
       </c>
       <c r="Q66" s="7">
         <f t="array" aca="1" ref="Q66" ca="1">_FV(B66,"Volume average",TRUE)</f>
@@ -19753,7 +19753,7 @@
       </c>
       <c r="U66" s="7">
         <f t="array" aca="1" ref="U66" ca="1">_FV(B66,"Market cap",TRUE)</f>
-        <v>2079774570</v>
+        <v>2051296329</v>
       </c>
       <c r="V66" s="7">
         <f t="array" aca="1" ref="V66" ca="1">_FV(B66,"Shares outstanding",TRUE)</f>
@@ -19769,7 +19769,7 @@
       </c>
       <c r="C67" s="2" cm="1">
         <f t="array" aca="1" ref="C67" ca="1">_FV(B67,"Last trade time",TRUE)</f>
-        <v>46191.626786666406</v>
+        <v>46191.666737314059</v>
       </c>
       <c r="D67" t="str" cm="1">
         <f t="array" aca="1" ref="D67" ca="1">_FV(B67,"Currency")</f>
@@ -19777,19 +19777,19 @@
       </c>
       <c r="E67" s="3" cm="1">
         <f t="array" aca="1" ref="E67" ca="1">_FV(B67,"Price")</f>
-        <v>222.39949999999999</v>
+        <v>220.37</v>
       </c>
       <c r="F67" s="4" cm="1">
         <f t="array" aca="1" ref="F67" ca="1">_FV(B67,"Change (%)",TRUE)</f>
-        <v>4.4276000000000003E-2</v>
+        <v>3.4747E-2</v>
       </c>
       <c r="G67" s="5" cm="1">
         <f t="array" aca="1" ref="G67" ca="1">_FV(B67,"Change")</f>
-        <v>9.4295000000000009</v>
+        <v>7.4</v>
       </c>
       <c r="H67" s="6" cm="1">
         <f t="array" aca="1" ref="H67" ca="1">_FV(B67,"P/E",TRUE)</f>
-        <v>24.191199999999998</v>
+        <v>23.970500000000001</v>
       </c>
       <c r="I67" s="6" cm="1">
         <f t="array" aca="1" ref="I67" ca="1">_FV(B67,"Beta")</f>
@@ -19821,7 +19821,7 @@
       </c>
       <c r="P67" s="7" cm="1">
         <f t="array" aca="1" ref="P67" ca="1">_FV(B67,"Volume")</f>
-        <v>7530750</v>
+        <v>9153347</v>
       </c>
       <c r="Q67" s="7" cm="1">
         <f t="array" aca="1" ref="Q67" ca="1">_FV(B67,"Volume average",TRUE)</f>
@@ -19841,7 +19841,7 @@
       </c>
       <c r="U67" s="7" cm="1">
         <f t="array" aca="1" ref="U67" ca="1">_FV(B67,"Market cap",TRUE)</f>
-        <v>234409073000</v>
+        <v>232269980000</v>
       </c>
       <c r="V67" s="7" cm="1">
         <f t="array" aca="1" ref="V67" ca="1">_FV(B67,"Shares outstanding",TRUE)</f>
@@ -19857,7 +19857,7 @@
       </c>
       <c r="C68" s="2">
         <f t="array" aca="1" ref="C68" ca="1">_FV(B68,"Last trade time",TRUE)</f>
-        <v>46191.626755786718</v>
+        <v>46191.666685404685</v>
       </c>
       <c r="D68" t="str">
         <f t="array" aca="1" ref="D68" ca="1">_FV(B68,"Currency")</f>
@@ -19865,19 +19865,19 @@
       </c>
       <c r="E68" s="3">
         <f t="array" aca="1" ref="E68" ca="1">_FV(B68,"Price")</f>
-        <v>110.705</v>
+        <v>111.45</v>
       </c>
       <c r="F68" s="4">
         <f t="array" aca="1" ref="F68" ca="1">_FV(B68,"Change (%)",TRUE)</f>
-        <v>-1.3148999999999999E-2</v>
+        <v>-6.5069999999999998E-3</v>
       </c>
       <c r="G68" s="5">
         <f t="array" aca="1" ref="G68" ca="1">_FV(B68,"Change")</f>
-        <v>-1.4750000000000001</v>
+        <v>-0.73</v>
       </c>
       <c r="H68" s="6">
         <f t="array" aca="1" ref="H68" ca="1">_FV(B68,"P/E",TRUE)</f>
-        <v>19.879200000000001</v>
+        <v>20.012899999999998</v>
       </c>
       <c r="I68" s="6">
         <f t="array" aca="1" ref="I68" ca="1">_FV(B68,"Beta")</f>
@@ -19909,7 +19909,7 @@
       </c>
       <c r="P68" s="7">
         <f t="array" aca="1" ref="P68" ca="1">_FV(B68,"Volume")</f>
-        <v>152382</v>
+        <v>219894</v>
       </c>
       <c r="Q68" s="7">
         <f t="array" aca="1" ref="Q68" ca="1">_FV(B68,"Volume average",TRUE)</f>
@@ -19929,7 +19929,7 @@
       </c>
       <c r="U68" s="7">
         <f t="array" aca="1" ref="U68" ca="1">_FV(B68,"Market cap",TRUE)</f>
-        <v>3898699092</v>
+        <v>3924935764</v>
       </c>
       <c r="V68" s="7">
         <f t="array" aca="1" ref="V68" ca="1">_FV(B68,"Shares outstanding",TRUE)</f>
@@ -19945,7 +19945,7 @@
       </c>
       <c r="C69" s="2" cm="1">
         <f t="array" aca="1" ref="C69" ca="1">_FV(B69,"Last trade time",TRUE)</f>
-        <v>46191.626790092188</v>
+        <v>46191.666711006248</v>
       </c>
       <c r="D69" t="str" cm="1">
         <f t="array" aca="1" ref="D69" ca="1">_FV(B69,"Currency")</f>
@@ -19953,15 +19953,15 @@
       </c>
       <c r="E69" s="3" cm="1">
         <f t="array" aca="1" ref="E69" ca="1">_FV(B69,"Price")</f>
-        <v>737.69500000000005</v>
+        <v>738.4701</v>
       </c>
       <c r="F69" s="4" cm="1">
         <f t="array" aca="1" ref="F69" ca="1">_FV(B69,"Change (%)",TRUE)</f>
-        <v>2.1017000000000001E-2</v>
+        <v>2.2090000000000002E-2</v>
       </c>
       <c r="G69" s="5" cm="1">
         <f t="array" aca="1" ref="G69" ca="1">_FV(B69,"Change")</f>
-        <v>15.185</v>
+        <v>15.960100000000001</v>
       </c>
       <c r="H69" s="6" t="e" cm="1" vm="13">
         <f t="array" ref="H69">_FV(B69,"P/E",TRUE)</f>
@@ -19981,7 +19981,7 @@
       </c>
       <c r="L69" s="3" cm="1">
         <f t="array" aca="1" ref="L69" ca="1">_FV(B69,"High")</f>
-        <v>738.8</v>
+        <v>739.14</v>
       </c>
       <c r="M69" s="3" cm="1">
         <f t="array" aca="1" ref="M69" ca="1">_FV(B69,"Low")</f>
@@ -19997,7 +19997,7 @@
       </c>
       <c r="P69" s="7" cm="1">
         <f t="array" aca="1" ref="P69" ca="1">_FV(B69,"Volume")</f>
-        <v>15370320</v>
+        <v>23168724</v>
       </c>
       <c r="Q69" s="7" cm="1">
         <f t="array" aca="1" ref="Q69" ca="1">_FV(B69,"Volume average",TRUE)</f>
@@ -20033,7 +20033,7 @@
       </c>
       <c r="C70" s="2" cm="1">
         <f t="array" aca="1" ref="C70" ca="1">_FV(B70,"Last trade time",TRUE)</f>
-        <v>46191.626705625</v>
+        <v>46191.666654606248</v>
       </c>
       <c r="D70" t="str" cm="1">
         <f t="array" aca="1" ref="D70" ca="1">_FV(B70,"Currency")</f>
@@ -20041,19 +20041,19 @@
       </c>
       <c r="E70" s="3" cm="1">
         <f t="array" aca="1" ref="E70" ca="1">_FV(B70,"Price")</f>
-        <v>473.77</v>
+        <v>471.01</v>
       </c>
       <c r="F70" s="4" cm="1">
         <f t="array" aca="1" ref="F70" ca="1">_FV(B70,"Change (%)",TRUE)</f>
-        <v>3.2875999999999996E-2</v>
+        <v>2.6859000000000001E-2</v>
       </c>
       <c r="G70" s="5" cm="1">
         <f t="array" aca="1" ref="G70" ca="1">_FV(B70,"Change")</f>
-        <v>15.08</v>
+        <v>12.32</v>
       </c>
       <c r="H70" s="6" cm="1">
         <f t="array" aca="1" ref="H70" ca="1">_FV(B70,"P/E",TRUE)</f>
-        <v>49.216700000000003</v>
+        <v>48.93</v>
       </c>
       <c r="I70" s="6" cm="1">
         <f t="array" aca="1" ref="I70" ca="1">_FV(B70,"Beta")</f>
@@ -20069,7 +20069,7 @@
       </c>
       <c r="L70" s="3" cm="1">
         <f t="array" aca="1" ref="L70" ca="1">_FV(B70,"High")</f>
-        <v>474.6345</v>
+        <v>474.7</v>
       </c>
       <c r="M70" s="3" cm="1">
         <f t="array" aca="1" ref="M70" ca="1">_FV(B70,"Low")</f>
@@ -20085,7 +20085,7 @@
       </c>
       <c r="P70" s="7" cm="1">
         <f t="array" aca="1" ref="P70" ca="1">_FV(B70,"Volume")</f>
-        <v>172872</v>
+        <v>203873</v>
       </c>
       <c r="Q70" s="7" cm="1">
         <f t="array" aca="1" ref="Q70" ca="1">_FV(B70,"Volume average",TRUE)</f>
@@ -20105,7 +20105,7 @@
       </c>
       <c r="U70" s="7" cm="1">
         <f t="array" aca="1" ref="U70" ca="1">_FV(B70,"Market cap",TRUE)</f>
-        <v>52718235603</v>
+        <v>52411119639</v>
       </c>
       <c r="V70" s="7" cm="1">
         <f t="array" aca="1" ref="V70" ca="1">_FV(B70,"Shares outstanding",TRUE)</f>
@@ -20121,7 +20121,7 @@
       </c>
       <c r="C71" s="2" cm="1">
         <f t="array" aca="1" ref="C71" ca="1">_FV(B71,"Last trade time",TRUE)</f>
-        <v>46191.626772673437</v>
+        <v>46191.666706145312</v>
       </c>
       <c r="D71" t="str" cm="1">
         <f t="array" aca="1" ref="D71" ca="1">_FV(B71,"Currency")</f>
@@ -20129,15 +20129,15 @@
       </c>
       <c r="E71" s="3" cm="1">
         <f t="array" aca="1" ref="E71" ca="1">_FV(B71,"Price")</f>
-        <v>3.1526000000000001</v>
+        <v>3.1501000000000001</v>
       </c>
       <c r="F71" s="4" cm="1">
         <f t="array" aca="1" ref="F71" ca="1">_FV(B71,"Change (%)",TRUE)</f>
-        <v>1.3697999999999998E-2</v>
+        <v>1.2894000000000001E-2</v>
       </c>
       <c r="G71" s="5" cm="1">
         <f t="array" aca="1" ref="G71" ca="1">_FV(B71,"Change")</f>
-        <v>4.2599999999999999E-2</v>
+        <v>4.0099999999999997E-2</v>
       </c>
       <c r="H71" s="6" cm="1">
         <f t="array" aca="1" ref="H71" ca="1">_FV(B71,"P/E",TRUE)</f>
@@ -20173,7 +20173,7 @@
       </c>
       <c r="P71" s="7" cm="1">
         <f t="array" aca="1" ref="P71" ca="1">_FV(B71,"Volume")</f>
-        <v>6711728</v>
+        <v>8686737</v>
       </c>
       <c r="Q71" s="7" cm="1">
         <f t="array" aca="1" ref="Q71" ca="1">_FV(B71,"Volume average",TRUE)</f>
@@ -20193,7 +20193,7 @@
       </c>
       <c r="U71" s="7" cm="1">
         <f t="array" aca="1" ref="U71" ca="1">_FV(B71,"Market cap",TRUE)</f>
-        <v>1670579133</v>
+        <v>1669254370</v>
       </c>
       <c r="V71" s="7" cm="1">
         <f t="array" aca="1" ref="V71" ca="1">_FV(B71,"Shares outstanding",TRUE)</f>
@@ -20209,7 +20209,7 @@
       </c>
       <c r="C72" s="2" cm="1">
         <f t="array" aca="1" ref="C72" ca="1">_FV(B72,"Last trade time",TRUE)</f>
-        <v>46191.626686006253</v>
+        <v>46191.666690659375</v>
       </c>
       <c r="D72" t="str" cm="1">
         <f t="array" aca="1" ref="D72" ca="1">_FV(B72,"Currency")</f>
@@ -20217,15 +20217,15 @@
       </c>
       <c r="E72" s="3" cm="1">
         <f t="array" aca="1" ref="E72" ca="1">_FV(B72,"Price")</f>
-        <v>14.895</v>
+        <v>14.8</v>
       </c>
       <c r="F72" s="4" cm="1">
         <f t="array" aca="1" ref="F72" ca="1">_FV(B72,"Change (%)",TRUE)</f>
-        <v>6.4190000000000002E-3</v>
+        <v>0</v>
       </c>
       <c r="G72" s="5" cm="1">
         <f t="array" aca="1" ref="G72" ca="1">_FV(B72,"Change")</f>
-        <v>9.5000000000000001E-2</v>
+        <v>0</v>
       </c>
       <c r="H72" s="6" t="e" cm="1" vm="13">
         <f t="array" ref="H72">_FV(B72,"P/E",TRUE)</f>
@@ -20261,7 +20261,7 @@
       </c>
       <c r="P72" s="7" cm="1">
         <f t="array" aca="1" ref="P72" ca="1">_FV(B72,"Volume")</f>
-        <v>1122362</v>
+        <v>1504892</v>
       </c>
       <c r="Q72" s="7" cm="1">
         <f t="array" aca="1" ref="Q72" ca="1">_FV(B72,"Volume average",TRUE)</f>
@@ -20281,7 +20281,7 @@
       </c>
       <c r="U72" s="7" cm="1">
         <f t="array" aca="1" ref="U72" ca="1">_FV(B72,"Market cap",TRUE)</f>
-        <v>5106061111</v>
+        <v>5073494760</v>
       </c>
       <c r="V72" s="7" cm="1">
         <f t="array" aca="1" ref="V72" ca="1">_FV(B72,"Shares outstanding",TRUE)</f>
@@ -20297,7 +20297,7 @@
       </c>
       <c r="C73" s="2" cm="1">
         <f t="array" aca="1" ref="C73" ca="1">_FV(B73,"Last trade time",TRUE)</f>
-        <v>46191.616354166668</v>
+        <v>46191.656111111108</v>
       </c>
       <c r="D73" t="str" cm="1">
         <f t="array" aca="1" ref="D73" ca="1">_FV(B73,"Currency")</f>
@@ -20305,19 +20305,19 @@
       </c>
       <c r="E73" s="3" cm="1">
         <f t="array" aca="1" ref="E73" ca="1">_FV(B73,"Price")</f>
-        <v>136.1</v>
+        <v>134.86000000000001</v>
       </c>
       <c r="F73" s="4" cm="1">
         <f t="array" aca="1" ref="F73" ca="1">_FV(B73,"Change (%)",TRUE)</f>
-        <v>-3.5982E-2</v>
+        <v>-4.4766E-2</v>
       </c>
       <c r="G73" s="5" cm="1">
         <f t="array" aca="1" ref="G73" ca="1">_FV(B73,"Change")</f>
-        <v>-5.08</v>
+        <v>-6.32</v>
       </c>
       <c r="H73" s="6" cm="1">
         <f t="array" aca="1" ref="H73" ca="1">_FV(B73,"P/E",TRUE)</f>
-        <v>21.6892</v>
+        <v>21.491599999999998</v>
       </c>
       <c r="I73" s="6" cm="1">
         <f t="array" aca="1" ref="I73" ca="1">_FV(B73,"Beta")</f>
@@ -20329,7 +20329,7 @@
       </c>
       <c r="K73" s="3" cm="1">
         <f t="array" aca="1" ref="K73" ca="1">_FV(B73,"52 week low",TRUE)</f>
-        <v>134.97999999999999</v>
+        <v>134.30000000000001</v>
       </c>
       <c r="L73" s="3" cm="1">
         <f t="array" aca="1" ref="L73" ca="1">_FV(B73,"High")</f>
@@ -20337,7 +20337,7 @@
       </c>
       <c r="M73" s="3" cm="1">
         <f t="array" aca="1" ref="M73" ca="1">_FV(B73,"Low")</f>
-        <v>134.97999999999999</v>
+        <v>134.30000000000001</v>
       </c>
       <c r="N73" s="3" cm="1">
         <f t="array" aca="1" ref="N73" ca="1">_FV(B73,"Open")</f>
@@ -20349,7 +20349,7 @@
       </c>
       <c r="P73" s="7" cm="1">
         <f t="array" aca="1" ref="P73" ca="1">_FV(B73,"Volume")</f>
-        <v>2432433</v>
+        <v>4837230</v>
       </c>
       <c r="Q73" s="7" cm="1">
         <f t="array" aca="1" ref="Q73" ca="1">_FV(B73,"Volume average",TRUE)</f>
@@ -20385,7 +20385,7 @@
       </c>
       <c r="C74" s="2">
         <f t="array" aca="1" ref="C74" ca="1">_FV(B74,"Last trade time",TRUE)</f>
-        <v>46191.626767962502</v>
+        <v>46191.666724571092</v>
       </c>
       <c r="D74" t="str">
         <f t="array" aca="1" ref="D74" ca="1">_FV(B74,"Currency")</f>
@@ -20393,19 +20393,19 @@
       </c>
       <c r="E74" s="3">
         <f t="array" aca="1" ref="E74" ca="1">_FV(B74,"Price")</f>
-        <v>93.79</v>
+        <v>93.16</v>
       </c>
       <c r="F74" s="4">
         <f t="array" aca="1" ref="F74" ca="1">_FV(B74,"Change (%)",TRUE)</f>
-        <v>-7.6180000000000006E-3</v>
+        <v>-1.4283999999999998E-2</v>
       </c>
       <c r="G74" s="5">
         <f t="array" aca="1" ref="G74" ca="1">_FV(B74,"Change")</f>
-        <v>-0.72</v>
+        <v>-1.35</v>
       </c>
       <c r="H74" s="6">
         <f t="array" aca="1" ref="H74" ca="1">_FV(B74,"P/E",TRUE)</f>
-        <v>18.598800000000001</v>
+        <v>18.4739</v>
       </c>
       <c r="I74" s="6">
         <f t="array" aca="1" ref="I74" ca="1">_FV(B74,"Beta")</f>
@@ -20425,7 +20425,7 @@
       </c>
       <c r="M74" s="3">
         <f t="array" aca="1" ref="M74" ca="1">_FV(B74,"Low")</f>
-        <v>93.53</v>
+        <v>93.14</v>
       </c>
       <c r="N74" s="3">
         <f t="array" aca="1" ref="N74" ca="1">_FV(B74,"Open")</f>
@@ -20437,7 +20437,7 @@
       </c>
       <c r="P74" s="7">
         <f t="array" aca="1" ref="P74" ca="1">_FV(B74,"Volume")</f>
-        <v>3797322</v>
+        <v>4579242</v>
       </c>
       <c r="Q74" s="7">
         <f t="array" aca="1" ref="Q74" ca="1">_FV(B74,"Volume average",TRUE)</f>
@@ -20457,7 +20457,7 @@
       </c>
       <c r="U74" s="7">
         <f t="array" aca="1" ref="U74" ca="1">_FV(B74,"Market cap",TRUE)</f>
-        <v>163113471650</v>
+        <v>162017816600</v>
       </c>
       <c r="V74" s="7">
         <f t="array" aca="1" ref="V74" ca="1">_FV(B74,"Shares outstanding",TRUE)</f>
@@ -20473,7 +20473,7 @@
       </c>
       <c r="C75" s="2">
         <f t="array" aca="1" ref="C75" ca="1">_FV(B75,"Last trade time",TRUE)</f>
-        <v>46191.61575680547</v>
+        <v>46191.650347222225</v>
       </c>
       <c r="D75" t="str">
         <f t="array" aca="1" ref="D75" ca="1">_FV(B75,"Currency")</f>
@@ -20481,15 +20481,15 @@
       </c>
       <c r="E75" s="9">
         <f t="array" aca="1" ref="E75" ca="1">_FV(B75,"Price")</f>
-        <v>797.8</v>
+        <v>802.8</v>
       </c>
       <c r="F75" s="4">
         <f t="array" aca="1" ref="F75" ca="1">_FV(B75,"Change (%)",TRUE)</f>
-        <v>-4.1797000000000001E-2</v>
+        <v>-3.5790999999999996E-2</v>
       </c>
       <c r="G75" s="5">
         <f t="array" aca="1" ref="G75" ca="1">_FV(B75,"Change")</f>
-        <v>-34.799999999999997</v>
+        <v>-29.8</v>
       </c>
       <c r="H75" s="6">
         <f t="array" aca="1" ref="H75" ca="1">_FV(B75,"P/E",TRUE)</f>
@@ -20525,7 +20525,7 @@
       </c>
       <c r="P75" s="7">
         <f t="array" aca="1" ref="P75" ca="1">_FV(B75,"Volume")</f>
-        <v>2458301</v>
+        <v>4109328</v>
       </c>
       <c r="Q75" s="7">
         <f t="array" aca="1" ref="Q75" ca="1">_FV(B75,"Volume average",TRUE)</f>
@@ -20561,7 +20561,7 @@
       </c>
       <c r="C76" s="2">
         <f t="array" aca="1" ref="C76" ca="1">_FV(B76,"Last trade time",TRUE)</f>
-        <v>46191.626741296095</v>
+        <v>46191.666681990624</v>
       </c>
       <c r="D76" t="str">
         <f t="array" aca="1" ref="D76" ca="1">_FV(B76,"Currency")</f>
@@ -20569,19 +20569,19 @@
       </c>
       <c r="E76" s="3">
         <f t="array" aca="1" ref="E76" ca="1">_FV(B76,"Price")</f>
-        <v>36.47</v>
+        <v>35.700000000000003</v>
       </c>
       <c r="F76" s="4">
         <f t="array" aca="1" ref="F76" ca="1">_FV(B76,"Change (%)",TRUE)</f>
-        <v>1.3899999999999999E-2</v>
+        <v>-7.5060000000000005E-3</v>
       </c>
       <c r="G76" s="5">
         <f t="array" aca="1" ref="G76" ca="1">_FV(B76,"Change")</f>
-        <v>0.5</v>
+        <v>-0.27</v>
       </c>
       <c r="H76" s="6">
         <f t="array" aca="1" ref="H76" ca="1">_FV(B76,"P/E",TRUE)</f>
-        <v>15.632899999999999</v>
+        <v>15.3028</v>
       </c>
       <c r="I76" s="6">
         <f t="array" aca="1" ref="I76" ca="1">_FV(B76,"Beta")</f>
@@ -20601,7 +20601,7 @@
       </c>
       <c r="M76" s="3">
         <f t="array" aca="1" ref="M76" ca="1">_FV(B76,"Low")</f>
-        <v>35.4</v>
+        <v>35.39</v>
       </c>
       <c r="N76" s="3">
         <f t="array" aca="1" ref="N76" ca="1">_FV(B76,"Open")</f>
@@ -20613,7 +20613,7 @@
       </c>
       <c r="P76" s="7">
         <f t="array" aca="1" ref="P76" ca="1">_FV(B76,"Volume")</f>
-        <v>192747</v>
+        <v>262504</v>
       </c>
       <c r="Q76" s="7">
         <f t="array" aca="1" ref="Q76" ca="1">_FV(B76,"Volume average",TRUE)</f>
@@ -20633,7 +20633,7 @@
       </c>
       <c r="U76" s="7">
         <f t="array" aca="1" ref="U76" ca="1">_FV(B76,"Market cap",TRUE)</f>
-        <v>1794491762</v>
+        <v>1756604220</v>
       </c>
       <c r="V76" s="7">
         <f t="array" aca="1" ref="V76" ca="1">_FV(B76,"Shares outstanding",TRUE)</f>
@@ -20649,7 +20649,7 @@
       </c>
       <c r="C77" s="2">
         <f t="array" aca="1" ref="C77" ca="1">_FV(B77,"Last trade time",TRUE)</f>
-        <v>46191.626779883591</v>
+        <v>46191.666727198441</v>
       </c>
       <c r="D77" t="str">
         <f t="array" aca="1" ref="D77" ca="1">_FV(B77,"Currency")</f>
@@ -20657,19 +20657,19 @@
       </c>
       <c r="E77" s="3">
         <f t="array" aca="1" ref="E77" ca="1">_FV(B77,"Price")</f>
-        <v>30.254999999999999</v>
+        <v>30.204999999999998</v>
       </c>
       <c r="F77" s="4">
         <f t="array" aca="1" ref="F77" ca="1">_FV(B77,"Change (%)",TRUE)</f>
-        <v>8.9093000000000006E-2</v>
+        <v>8.7293000000000009E-2</v>
       </c>
       <c r="G77" s="5">
         <f t="array" aca="1" ref="G77" ca="1">_FV(B77,"Change")</f>
-        <v>2.4750000000000001</v>
+        <v>2.4249999999999998</v>
       </c>
       <c r="H77" s="6">
         <f t="array" aca="1" ref="H77" ca="1">_FV(B77,"P/E",TRUE)</f>
-        <v>16.484999999999999</v>
+        <v>16.457799999999999</v>
       </c>
       <c r="I77" s="6">
         <f t="array" aca="1" ref="I77" ca="1">_FV(B77,"Beta")</f>
@@ -20685,7 +20685,7 @@
       </c>
       <c r="L77" s="3">
         <f t="array" aca="1" ref="L77" ca="1">_FV(B77,"High")</f>
-        <v>30.355</v>
+        <v>30.45</v>
       </c>
       <c r="M77" s="3">
         <f t="array" aca="1" ref="M77" ca="1">_FV(B77,"Low")</f>
@@